--- a/PATH.xlsx
+++ b/PATH.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29DE463E-EC64-6845-B9F1-B7FE14884A7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A13A6C25-1A2C-1A48-86F3-535B1F0BFD4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="2" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -135,7 +135,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="5">
+  <futureMetadata name="XLRICHVALUE" count="2">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -146,28 +146,7 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="3"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="4"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="5"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="8"/>
         </ext>
       </extLst>
     </bk>
@@ -177,21 +156,12 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="5">
+  <valueMetadata count="2">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
-    </bk>
-    <bk>
-      <rc t="2" v="2"/>
-    </bk>
-    <bk>
-      <rc t="2" v="3"/>
-    </bk>
-    <bk>
-      <rc t="2" v="4"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -2053,7 +2023,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="265">
+  <cellXfs count="266">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -2385,12 +2355,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2400,10 +2364,10 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2413,6 +2377,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2425,6 +2395,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -11793,7 +11766,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=c1dbvh&amp;q=XNYS%3aPATH&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
@@ -11813,8 +11786,10 @@
     <v>19.84</v>
     <v>9.2002000000000006</v>
     <v>0.96489999999999998</v>
-    <v>-0.57499999999999996</v>
-    <v>-4.7209000000000001E-2</v>
+    <v>-0.51</v>
+    <v>-4.1871999999999999E-2</v>
+    <v>-0.2326</v>
+    <v>-1.9931000000000001E-2</v>
     <v>USD</v>
     <v>UiPath, Inc. is focused on agentic automation and orchestration, empowering enterprises to harness the full potential of AI agents to autonomously execute and optimize complex business processes. It is focused on building and managing automations, starting with computer vision technology and user interface automation in its initial robotic process automation offering. Its AI-powered UiPath Platform offers a robust set of capabilities that allows its customers to discover opportunities for automation, automate using a digital workforce that seamlessly collaborates with humans, and operate a mission-critical automation program at scale. It enables employees to quickly build automations for both existing and new processes and to automate a range of actions including logging into applications, moving folders, filling in forms, reading emails and others. Its platform allows users to design and combine UI automations, API integrations and AI-based document understanding in a single workflow.</v>
     <v>3981</v>
@@ -11825,46 +11800,32 @@
     <v>12.24</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46176.724120323437</v>
+    <v>46176.925320381248</v>
     <v>0</v>
-    <v>11.511100000000001</v>
-    <v>6039745657</v>
+    <v>11.51</v>
+    <v>6073574478</v>
     <v>UIPATH, INC.</v>
     <v>UIPATH, INC.</v>
-    <v>12.16</v>
-    <v>19.290199999999999</v>
     <v>12.18</v>
-    <v>11.605</v>
+    <v>19.398299999999999</v>
+    <v>12.18</v>
+    <v>11.67</v>
+    <v>11.4374</v>
     <v>520443400</v>
     <v>PATH</v>
     <v>UIPATH, INC. (XNYS:PATH)</v>
-    <v>17779230</v>
+    <v>33612307</v>
     <v>39411001</v>
     <v>2015</v>
   </rv>
   <rv s="2">
     <v>1</v>
   </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Price (Extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Change (extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Change % (extended hours)</v>
-    <v>0</v>
-  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="4">
+  <rv s="3">
     <v>5</v>
     <v>10 Y TSY YLD NDX</v>
     <v>6</v>
@@ -11883,7 +11844,7 @@
     <v>US</v>
     <v>44.63</v>
     <v>Index</v>
-    <v>6</v>
+    <v>3</v>
     <v>44.28</v>
     <v>10 Y TSY YLD NDX</v>
     <v>44.3</v>
@@ -11893,13 +11854,13 @@
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="2">
-    <v>7</v>
+    <v>4</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -11921,6 +11882,8 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
+    <k n="Change (Extended hours)"/>
+    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -11941,6 +11904,7 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
+    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -11950,11 +11914,6 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
-  </s>
-  <s t="_error">
-    <k n="errorType" t="i"/>
-    <k n="field" t="s"/>
-    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -11990,7 +11949,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="42">
+    <a count="45">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -12001,13 +11960,16 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
+      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
+      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
+      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -12101,13 +12063,19 @@
       <v>8</v>
       <v>9</v>
       <v>4</v>
+      <v>1</v>
+      <v>1</v>
+      <v>5</v>
     </spb>
     <spb s="4">
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
       <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
+      <v>Real-Time Nasdaq Last Sale</v>
+      <v>from close</v>
+      <v>from close</v>
     </spb>
     <spb s="0">
       <v>1</v>
@@ -12179,6 +12147,9 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
+    <k n="Price (Extended hours)" t="i"/>
+    <k n="Change (Extended hours)" t="i"/>
+    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -12186,6 +12157,9 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
+    <k n="Price (Extended hours)" t="s"/>
+    <k n="Change (Extended hours)" t="s"/>
+    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="UniqueName" t="spb"/>
@@ -12702,7 +12676,7 @@
       </c>
       <c r="F3" s="211">
         <f ca="1">Statement!AC170</f>
-        <v>6129250.3799999999</v>
+        <v>6163580.5199999996</v>
       </c>
       <c r="H3" s="209" t="str">
         <f>'AVG target price'!B5</f>
@@ -12726,7 +12700,7 @@
       </c>
       <c r="F4" s="212">
         <f ca="1">Statement!AC171</f>
-        <v>4822006.38</v>
+        <v>4856336.5199999996</v>
       </c>
       <c r="H4" s="209" t="str">
         <f>'AVG target price'!B6</f>
@@ -12743,7 +12717,7 @@
       </c>
       <c r="C5" s="232" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>11.605</v>
+        <v>11.67</v>
       </c>
       <c r="E5" s="209" t="s">
         <v>295</v>
@@ -12765,16 +12739,16 @@
       <c r="B6" s="209" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="232" t="e" cm="1" vm="2">
-        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C6" s="232" cm="1">
+        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>11.4374</v>
       </c>
       <c r="E6" s="209" t="s">
         <v>289</v>
       </c>
       <c r="F6" s="214">
         <f ca="1">Statement!AC167</f>
-        <v>19.341666666666665</v>
+        <v>19.449999999999996</v>
       </c>
       <c r="H6" s="209" t="str">
         <f>'AVG target price'!B8</f>
@@ -12791,14 +12765,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-0.57499999999999996</v>
+        <v>-0.51</v>
       </c>
       <c r="E7" s="210" t="s">
         <v>243</v>
       </c>
       <c r="F7" s="215">
         <f ca="1">Statement!AC168</f>
-        <v>3.7385864220877458</v>
+        <v>3.7595263718883234</v>
       </c>
       <c r="H7" s="208" t="str">
         <f>'AVG target price'!B9</f>
@@ -12813,16 +12787,16 @@
       <c r="B8" s="209" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" t="e" cm="1" vm="3">
-        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C8" s="6" cm="1">
+        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>-0.2326</v>
       </c>
       <c r="E8" s="209" t="s">
         <v>317</v>
       </c>
       <c r="F8" s="216">
         <f ca="1">Statement!AC178</f>
-        <v>1.7556633083734459E-2</v>
+        <v>1.7458845495864472E-2</v>
       </c>
       <c r="H8" s="208" t="str">
         <f>'AVG target price'!B11</f>
@@ -12830,7 +12804,7 @@
       </c>
       <c r="I8" s="237">
         <f ca="1">'AVG target price'!C11</f>
-        <v>5.5376840322171786E-2</v>
+        <v>4.9498563148140884E-2</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -12839,30 +12813,30 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-4.7209000000000001E-2</v>
+        <v>-4.1871999999999999E-2</v>
       </c>
       <c r="E9" s="209" t="s">
         <v>341</v>
       </c>
       <c r="F9" s="216">
         <f ca="1">Statement!AC179</f>
-        <v>5.1701852649719951E-2</v>
+        <v>5.1413881748071988E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B10" s="209" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" t="e" cm="1" vm="4">
-        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C10" s="73" cm="1">
+        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>-1.9931000000000001E-2</v>
       </c>
       <c r="E10" s="209" t="s">
         <v>346</v>
       </c>
       <c r="F10" s="216">
         <f ca="1">Statement!AC181</f>
-        <v>5.6348163084830614E-2</v>
+        <v>5.6034312990527788E-2</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -12935,7 +12909,7 @@
       </c>
       <c r="F15" s="216">
         <f ca="1">Statement!AC192</f>
-        <v>0.21327958868601482</v>
+        <v>0.21209165610121697</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -13040,7 +13014,7 @@
       <c r="C26" s="193">
         <v>0.21</v>
       </c>
-      <c r="E26" s="209" t="e" vm="5">
+      <c r="E26" s="209" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="245" cm="1">
@@ -13052,7 +13026,7 @@
       <c r="B27" s="208" t="s">
         <v>214</v>
       </c>
-      <c r="C27" s="193">
+      <c r="C27" s="265">
         <v>0</v>
       </c>
       <c r="E27" s="210" t="s">
@@ -13218,8 +13192,8 @@
       <c r="D2" s="247"/>
       <c r="E2" s="247"/>
       <c r="F2" s="247"/>
-      <c r="G2" s="256"/>
-      <c r="H2" s="257" t="s">
+      <c r="G2" s="259"/>
+      <c r="H2" s="260" t="s">
         <v>138</v>
       </c>
       <c r="I2" s="247"/>
@@ -13252,32 +13226,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="258" t="s">
+      <c r="C4" s="256" t="s">
         <v>140</v>
       </c>
-      <c r="D4" s="258"/>
-      <c r="E4" s="258"/>
-      <c r="F4" s="258"/>
-      <c r="G4" s="258"/>
-      <c r="H4" s="258"/>
-      <c r="I4" s="258"/>
-      <c r="J4" s="258"/>
-      <c r="K4" s="258"/>
-      <c r="L4" s="258"/>
+      <c r="D4" s="256"/>
+      <c r="E4" s="256"/>
+      <c r="F4" s="256"/>
+      <c r="G4" s="256"/>
+      <c r="H4" s="256"/>
+      <c r="I4" s="256"/>
+      <c r="J4" s="256"/>
+      <c r="K4" s="256"/>
+      <c r="L4" s="256"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="259" t="s">
+      <c r="S4" s="257" t="s">
         <v>140</v>
       </c>
-      <c r="T4" s="260"/>
-      <c r="U4" s="260"/>
-      <c r="V4" s="260"/>
-      <c r="W4" s="260"/>
-      <c r="X4" s="260"/>
-      <c r="Y4" s="260"/>
-      <c r="Z4" s="260"/>
-      <c r="AA4" s="260"/>
-      <c r="AB4" s="260"/>
-      <c r="AC4" s="260"/>
+      <c r="T4" s="258"/>
+      <c r="U4" s="258"/>
+      <c r="V4" s="258"/>
+      <c r="W4" s="258"/>
+      <c r="X4" s="258"/>
+      <c r="Y4" s="258"/>
+      <c r="Z4" s="258"/>
+      <c r="AA4" s="258"/>
+      <c r="AB4" s="258"/>
+      <c r="AC4" s="258"/>
       <c r="AE4" s="89"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -13773,33 +13747,33 @@
       <c r="Q10" s="93"/>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C11" s="258" t="s">
+      <c r="C11" s="256" t="s">
         <v>146</v>
       </c>
-      <c r="D11" s="258"/>
-      <c r="E11" s="258"/>
-      <c r="F11" s="258"/>
-      <c r="G11" s="258"/>
-      <c r="H11" s="258"/>
-      <c r="I11" s="258"/>
-      <c r="J11" s="258"/>
-      <c r="K11" s="258"/>
-      <c r="L11" s="258"/>
+      <c r="D11" s="256"/>
+      <c r="E11" s="256"/>
+      <c r="F11" s="256"/>
+      <c r="G11" s="256"/>
+      <c r="H11" s="256"/>
+      <c r="I11" s="256"/>
+      <c r="J11" s="256"/>
+      <c r="K11" s="256"/>
+      <c r="L11" s="256"/>
       <c r="O11" s="5"/>
       <c r="Q11" s="93"/>
-      <c r="S11" s="259" t="s">
+      <c r="S11" s="257" t="s">
         <v>146</v>
       </c>
-      <c r="T11" s="260"/>
-      <c r="U11" s="260"/>
-      <c r="V11" s="260"/>
-      <c r="W11" s="260"/>
-      <c r="X11" s="260"/>
-      <c r="Y11" s="260"/>
-      <c r="Z11" s="260"/>
-      <c r="AA11" s="260"/>
-      <c r="AB11" s="260"/>
-      <c r="AC11" s="260"/>
+      <c r="T11" s="258"/>
+      <c r="U11" s="258"/>
+      <c r="V11" s="258"/>
+      <c r="W11" s="258"/>
+      <c r="X11" s="258"/>
+      <c r="Y11" s="258"/>
+      <c r="Z11" s="258"/>
+      <c r="AA11" s="258"/>
+      <c r="AB11" s="258"/>
+      <c r="AC11" s="258"/>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B12" s="16" t="s">
@@ -14240,33 +14214,33 @@
       <c r="Q18" s="93"/>
     </row>
     <row r="19" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C19" s="258" t="s">
+      <c r="C19" s="256" t="s">
         <v>148</v>
       </c>
-      <c r="D19" s="258"/>
-      <c r="E19" s="258"/>
-      <c r="F19" s="258"/>
-      <c r="G19" s="258"/>
-      <c r="H19" s="258"/>
-      <c r="I19" s="258"/>
-      <c r="J19" s="258"/>
-      <c r="K19" s="258"/>
-      <c r="L19" s="258"/>
+      <c r="D19" s="256"/>
+      <c r="E19" s="256"/>
+      <c r="F19" s="256"/>
+      <c r="G19" s="256"/>
+      <c r="H19" s="256"/>
+      <c r="I19" s="256"/>
+      <c r="J19" s="256"/>
+      <c r="K19" s="256"/>
+      <c r="L19" s="256"/>
       <c r="O19" s="5"/>
       <c r="Q19" s="93"/>
-      <c r="S19" s="259" t="s">
+      <c r="S19" s="257" t="s">
         <v>148</v>
       </c>
-      <c r="T19" s="260"/>
-      <c r="U19" s="260"/>
-      <c r="V19" s="260"/>
-      <c r="W19" s="260"/>
-      <c r="X19" s="260"/>
-      <c r="Y19" s="260"/>
-      <c r="Z19" s="260"/>
-      <c r="AA19" s="260"/>
-      <c r="AB19" s="260"/>
-      <c r="AC19" s="260"/>
+      <c r="T19" s="258"/>
+      <c r="U19" s="258"/>
+      <c r="V19" s="258"/>
+      <c r="W19" s="258"/>
+      <c r="X19" s="258"/>
+      <c r="Y19" s="258"/>
+      <c r="Z19" s="258"/>
+      <c r="AA19" s="258"/>
+      <c r="AB19" s="258"/>
+      <c r="AC19" s="258"/>
       <c r="AE19" s="89">
         <f>AE4</f>
         <v>0</v>
@@ -15084,32 +15058,32 @@
       <c r="O31" s="5"/>
     </row>
     <row r="32" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C32" s="258" t="s">
+      <c r="C32" s="256" t="s">
         <v>150</v>
       </c>
-      <c r="D32" s="258"/>
-      <c r="E32" s="258"/>
-      <c r="F32" s="258"/>
-      <c r="G32" s="258"/>
-      <c r="H32" s="258"/>
-      <c r="I32" s="258"/>
-      <c r="J32" s="258"/>
-      <c r="K32" s="258"/>
-      <c r="L32" s="258"/>
+      <c r="D32" s="256"/>
+      <c r="E32" s="256"/>
+      <c r="F32" s="256"/>
+      <c r="G32" s="256"/>
+      <c r="H32" s="256"/>
+      <c r="I32" s="256"/>
+      <c r="J32" s="256"/>
+      <c r="K32" s="256"/>
+      <c r="L32" s="256"/>
       <c r="O32" s="5"/>
-      <c r="S32" s="259" t="s">
+      <c r="S32" s="257" t="s">
         <v>150</v>
       </c>
-      <c r="T32" s="260"/>
-      <c r="U32" s="260"/>
-      <c r="V32" s="260"/>
-      <c r="W32" s="260"/>
-      <c r="X32" s="260"/>
-      <c r="Y32" s="260"/>
-      <c r="Z32" s="260"/>
-      <c r="AA32" s="260"/>
-      <c r="AB32" s="260"/>
-      <c r="AC32" s="260"/>
+      <c r="T32" s="258"/>
+      <c r="U32" s="258"/>
+      <c r="V32" s="258"/>
+      <c r="W32" s="258"/>
+      <c r="X32" s="258"/>
+      <c r="Y32" s="258"/>
+      <c r="Z32" s="258"/>
+      <c r="AA32" s="258"/>
+      <c r="AB32" s="258"/>
+      <c r="AC32" s="258"/>
     </row>
     <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B33" s="16" t="s">
@@ -15366,18 +15340,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="S11:AC11"/>
     <mergeCell ref="C19:L19"/>
     <mergeCell ref="S19:AC19"/>
     <mergeCell ref="C32:L32"/>
     <mergeCell ref="S32:AC32"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -15420,8 +15394,8 @@
       <c r="D2" s="247"/>
       <c r="E2" s="247"/>
       <c r="F2" s="247"/>
-      <c r="G2" s="256"/>
-      <c r="H2" s="257" t="s">
+      <c r="G2" s="259"/>
+      <c r="H2" s="260" t="s">
         <v>138</v>
       </c>
       <c r="I2" s="247"/>
@@ -15451,31 +15425,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="258" t="s">
+      <c r="C4" s="256" t="s">
         <v>140</v>
       </c>
-      <c r="D4" s="258"/>
-      <c r="E4" s="258"/>
-      <c r="F4" s="258"/>
-      <c r="G4" s="258"/>
-      <c r="H4" s="258"/>
-      <c r="I4" s="258"/>
-      <c r="J4" s="258"/>
-      <c r="K4" s="258"/>
-      <c r="L4" s="258"/>
-      <c r="P4" s="260" t="s">
+      <c r="D4" s="256"/>
+      <c r="E4" s="256"/>
+      <c r="F4" s="256"/>
+      <c r="G4" s="256"/>
+      <c r="H4" s="256"/>
+      <c r="I4" s="256"/>
+      <c r="J4" s="256"/>
+      <c r="K4" s="256"/>
+      <c r="L4" s="256"/>
+      <c r="P4" s="258" t="s">
         <v>140</v>
       </c>
-      <c r="Q4" s="260"/>
-      <c r="R4" s="260"/>
-      <c r="S4" s="260"/>
-      <c r="T4" s="260"/>
-      <c r="U4" s="260"/>
-      <c r="V4" s="260"/>
-      <c r="W4" s="260"/>
-      <c r="X4" s="260"/>
-      <c r="Y4" s="260"/>
-      <c r="Z4" s="260"/>
+      <c r="Q4" s="258"/>
+      <c r="R4" s="258"/>
+      <c r="S4" s="258"/>
+      <c r="T4" s="258"/>
+      <c r="U4" s="258"/>
+      <c r="V4" s="258"/>
+      <c r="W4" s="258"/>
+      <c r="X4" s="258"/>
+      <c r="Y4" s="258"/>
+      <c r="Z4" s="258"/>
       <c r="AB4" s="89"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -15670,32 +15644,32 @@
       <c r="N8" s="93"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="258" t="s">
+      <c r="C9" s="256" t="s">
         <v>166</v>
       </c>
-      <c r="D9" s="258"/>
-      <c r="E9" s="258"/>
-      <c r="F9" s="258"/>
-      <c r="G9" s="258"/>
-      <c r="H9" s="258"/>
-      <c r="I9" s="258"/>
-      <c r="J9" s="258"/>
-      <c r="K9" s="258"/>
-      <c r="L9" s="258"/>
+      <c r="D9" s="256"/>
+      <c r="E9" s="256"/>
+      <c r="F9" s="256"/>
+      <c r="G9" s="256"/>
+      <c r="H9" s="256"/>
+      <c r="I9" s="256"/>
+      <c r="J9" s="256"/>
+      <c r="K9" s="256"/>
+      <c r="L9" s="256"/>
       <c r="N9" s="93"/>
-      <c r="P9" s="260" t="s">
+      <c r="P9" s="258" t="s">
         <v>167</v>
       </c>
-      <c r="Q9" s="260"/>
-      <c r="R9" s="260"/>
-      <c r="S9" s="260"/>
-      <c r="T9" s="260"/>
-      <c r="U9" s="260"/>
-      <c r="V9" s="260"/>
-      <c r="W9" s="260"/>
-      <c r="X9" s="260"/>
-      <c r="Y9" s="260"/>
-      <c r="Z9" s="260"/>
+      <c r="Q9" s="258"/>
+      <c r="R9" s="258"/>
+      <c r="S9" s="258"/>
+      <c r="T9" s="258"/>
+      <c r="U9" s="258"/>
+      <c r="V9" s="258"/>
+      <c r="W9" s="258"/>
+      <c r="X9" s="258"/>
+      <c r="Y9" s="258"/>
+      <c r="Z9" s="258"/>
       <c r="AB9" s="89">
         <f>AB4</f>
         <v>0</v>
@@ -16544,31 +16518,31 @@
       </c>
     </row>
     <row r="21" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="C21" s="258" t="s">
+      <c r="C21" s="256" t="s">
         <v>169</v>
       </c>
-      <c r="D21" s="258"/>
-      <c r="E21" s="258"/>
-      <c r="F21" s="258"/>
-      <c r="G21" s="258"/>
-      <c r="H21" s="258"/>
-      <c r="I21" s="258"/>
-      <c r="J21" s="258"/>
-      <c r="K21" s="258"/>
-      <c r="L21" s="258"/>
-      <c r="P21" s="260" t="s">
+      <c r="D21" s="256"/>
+      <c r="E21" s="256"/>
+      <c r="F21" s="256"/>
+      <c r="G21" s="256"/>
+      <c r="H21" s="256"/>
+      <c r="I21" s="256"/>
+      <c r="J21" s="256"/>
+      <c r="K21" s="256"/>
+      <c r="L21" s="256"/>
+      <c r="P21" s="258" t="s">
         <v>169</v>
       </c>
-      <c r="Q21" s="260"/>
-      <c r="R21" s="260"/>
-      <c r="S21" s="260"/>
-      <c r="T21" s="260"/>
-      <c r="U21" s="260"/>
-      <c r="V21" s="260"/>
-      <c r="W21" s="260"/>
-      <c r="X21" s="260"/>
-      <c r="Y21" s="260"/>
-      <c r="Z21" s="260"/>
+      <c r="Q21" s="258"/>
+      <c r="R21" s="258"/>
+      <c r="S21" s="258"/>
+      <c r="T21" s="258"/>
+      <c r="U21" s="258"/>
+      <c r="V21" s="258"/>
+      <c r="W21" s="258"/>
+      <c r="X21" s="258"/>
+      <c r="Y21" s="258"/>
+      <c r="Z21" s="258"/>
     </row>
     <row r="22" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B22" s="16" t="s">
@@ -17389,8 +17363,8 @@
       <c r="D3" s="247"/>
       <c r="E3" s="247"/>
       <c r="F3" s="247"/>
-      <c r="G3" s="256"/>
-      <c r="H3" s="257" t="s">
+      <c r="G3" s="259"/>
+      <c r="H3" s="260" t="s">
         <v>138</v>
       </c>
       <c r="I3" s="247"/>
@@ -17414,18 +17388,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="88"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="258" t="s">
+      <c r="C5" s="256" t="s">
         <v>140</v>
       </c>
-      <c r="D5" s="258"/>
-      <c r="E5" s="258"/>
-      <c r="F5" s="258"/>
-      <c r="G5" s="258"/>
-      <c r="H5" s="258"/>
-      <c r="I5" s="258"/>
-      <c r="J5" s="258"/>
-      <c r="K5" s="258"/>
-      <c r="L5" s="258"/>
+      <c r="D5" s="256"/>
+      <c r="E5" s="256"/>
+      <c r="F5" s="256"/>
+      <c r="G5" s="256"/>
+      <c r="H5" s="256"/>
+      <c r="I5" s="256"/>
+      <c r="J5" s="256"/>
+      <c r="K5" s="256"/>
+      <c r="L5" s="256"/>
       <c r="P5" s="261"/>
       <c r="Q5" s="261"/>
       <c r="R5" s="261"/>
@@ -17622,18 +17596,18 @@
       <c r="N10" s="93"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="258" t="s">
+      <c r="C11" s="256" t="s">
         <v>173</v>
       </c>
-      <c r="D11" s="258"/>
-      <c r="E11" s="258"/>
-      <c r="F11" s="258"/>
-      <c r="G11" s="258"/>
-      <c r="H11" s="258"/>
-      <c r="I11" s="258"/>
-      <c r="J11" s="258"/>
-      <c r="K11" s="258"/>
-      <c r="L11" s="258"/>
+      <c r="D11" s="256"/>
+      <c r="E11" s="256"/>
+      <c r="F11" s="256"/>
+      <c r="G11" s="256"/>
+      <c r="H11" s="256"/>
+      <c r="I11" s="256"/>
+      <c r="J11" s="256"/>
+      <c r="K11" s="256"/>
+      <c r="L11" s="256"/>
       <c r="N11" s="93"/>
       <c r="P11" s="261"/>
       <c r="Q11" s="261"/>
@@ -17887,18 +17861,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="258" t="s">
+      <c r="C18" s="256" t="s">
         <v>178</v>
       </c>
-      <c r="D18" s="258"/>
-      <c r="E18" s="258"/>
-      <c r="F18" s="258"/>
-      <c r="G18" s="258"/>
-      <c r="H18" s="258"/>
-      <c r="I18" s="258"/>
-      <c r="J18" s="258"/>
-      <c r="K18" s="258"/>
-      <c r="L18" s="258"/>
+      <c r="D18" s="256"/>
+      <c r="E18" s="256"/>
+      <c r="F18" s="256"/>
+      <c r="G18" s="256"/>
+      <c r="H18" s="256"/>
+      <c r="I18" s="256"/>
+      <c r="J18" s="256"/>
+      <c r="K18" s="256"/>
+      <c r="L18" s="256"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -18116,18 +18090,18 @@
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="130"/>
-      <c r="C26" s="258" t="s">
+      <c r="C26" s="256" t="s">
         <v>184</v>
       </c>
-      <c r="D26" s="258"/>
-      <c r="E26" s="258"/>
-      <c r="F26" s="258"/>
-      <c r="G26" s="258"/>
-      <c r="H26" s="258"/>
-      <c r="I26" s="258"/>
-      <c r="J26" s="258"/>
-      <c r="K26" s="258"/>
-      <c r="L26" s="258"/>
+      <c r="D26" s="256"/>
+      <c r="E26" s="256"/>
+      <c r="F26" s="256"/>
+      <c r="G26" s="256"/>
+      <c r="H26" s="256"/>
+      <c r="I26" s="256"/>
+      <c r="J26" s="256"/>
+      <c r="K26" s="256"/>
+      <c r="L26" s="256"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -18319,18 +18293,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="130"/>
-      <c r="C33" s="258" t="s">
+      <c r="C33" s="256" t="s">
         <v>188</v>
       </c>
-      <c r="D33" s="258"/>
-      <c r="E33" s="258"/>
-      <c r="F33" s="258"/>
-      <c r="G33" s="258"/>
-      <c r="H33" s="258"/>
-      <c r="I33" s="258"/>
-      <c r="J33" s="258"/>
-      <c r="K33" s="258"/>
-      <c r="L33" s="258"/>
+      <c r="D33" s="256"/>
+      <c r="E33" s="256"/>
+      <c r="F33" s="256"/>
+      <c r="G33" s="256"/>
+      <c r="H33" s="256"/>
+      <c r="I33" s="256"/>
+      <c r="J33" s="256"/>
+      <c r="K33" s="256"/>
+      <c r="L33" s="256"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -18514,18 +18488,18 @@
       <c r="C39" s="146"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="258" t="s">
+      <c r="C40" s="256" t="s">
         <v>191</v>
       </c>
-      <c r="D40" s="258"/>
-      <c r="E40" s="258"/>
-      <c r="F40" s="258"/>
-      <c r="G40" s="258"/>
-      <c r="H40" s="258"/>
-      <c r="I40" s="258"/>
-      <c r="J40" s="258"/>
-      <c r="K40" s="258"/>
-      <c r="L40" s="258"/>
+      <c r="D40" s="256"/>
+      <c r="E40" s="256"/>
+      <c r="F40" s="256"/>
+      <c r="G40" s="256"/>
+      <c r="H40" s="256"/>
+      <c r="I40" s="256"/>
+      <c r="J40" s="256"/>
+      <c r="K40" s="256"/>
+      <c r="L40" s="256"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -18789,12 +18763,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18802,6 +18770,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -18845,8 +18819,8 @@
       <c r="D2" s="247"/>
       <c r="E2" s="247"/>
       <c r="F2" s="247"/>
-      <c r="G2" s="256"/>
-      <c r="H2" s="257" t="s">
+      <c r="G2" s="259"/>
+      <c r="H2" s="260" t="s">
         <v>138</v>
       </c>
       <c r="I2" s="247"/>
@@ -18870,18 +18844,18 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="258" t="s">
+      <c r="C4" s="256" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="258"/>
-      <c r="E4" s="258"/>
-      <c r="F4" s="258"/>
-      <c r="G4" s="258"/>
-      <c r="H4" s="258"/>
-      <c r="I4" s="258"/>
-      <c r="J4" s="258"/>
-      <c r="K4" s="258"/>
-      <c r="L4" s="258"/>
+      <c r="D4" s="256"/>
+      <c r="E4" s="256"/>
+      <c r="F4" s="256"/>
+      <c r="G4" s="256"/>
+      <c r="H4" s="256"/>
+      <c r="I4" s="256"/>
+      <c r="J4" s="256"/>
+      <c r="K4" s="256"/>
+      <c r="L4" s="256"/>
       <c r="S4" s="261"/>
       <c r="T4" s="261"/>
       <c r="U4" s="261"/>
@@ -19255,18 +19229,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="258" t="s">
+      <c r="C13" s="256" t="s">
         <v>199</v>
       </c>
-      <c r="D13" s="258"/>
-      <c r="E13" s="258"/>
-      <c r="F13" s="258"/>
-      <c r="G13" s="258"/>
-      <c r="H13" s="258"/>
-      <c r="I13" s="258"/>
-      <c r="J13" s="258"/>
-      <c r="K13" s="258"/>
-      <c r="L13" s="258"/>
+      <c r="D13" s="256"/>
+      <c r="E13" s="256"/>
+      <c r="F13" s="256"/>
+      <c r="G13" s="256"/>
+      <c r="H13" s="256"/>
+      <c r="I13" s="256"/>
+      <c r="J13" s="256"/>
+      <c r="K13" s="256"/>
+      <c r="L13" s="256"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -19359,18 +19333,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="258" t="s">
+      <c r="C18" s="256" t="s">
         <v>200</v>
       </c>
-      <c r="D18" s="258"/>
-      <c r="E18" s="258"/>
-      <c r="F18" s="258"/>
-      <c r="G18" s="258"/>
-      <c r="H18" s="258"/>
-      <c r="I18" s="258"/>
-      <c r="J18" s="258"/>
-      <c r="K18" s="258"/>
-      <c r="L18" s="258"/>
+      <c r="D18" s="256"/>
+      <c r="E18" s="256"/>
+      <c r="F18" s="256"/>
+      <c r="G18" s="256"/>
+      <c r="H18" s="256"/>
+      <c r="I18" s="256"/>
+      <c r="J18" s="256"/>
+      <c r="K18" s="256"/>
+      <c r="L18" s="256"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19562,18 +19536,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="258" t="s">
+      <c r="C25" s="256" t="s">
         <v>203</v>
       </c>
-      <c r="D25" s="258"/>
-      <c r="E25" s="258"/>
-      <c r="F25" s="258"/>
-      <c r="G25" s="258"/>
-      <c r="H25" s="258"/>
-      <c r="I25" s="258"/>
-      <c r="J25" s="258"/>
-      <c r="K25" s="258"/>
-      <c r="L25" s="258"/>
+      <c r="D25" s="256"/>
+      <c r="E25" s="256"/>
+      <c r="F25" s="256"/>
+      <c r="G25" s="256"/>
+      <c r="H25" s="256"/>
+      <c r="I25" s="256"/>
+      <c r="J25" s="256"/>
+      <c r="K25" s="256"/>
+      <c r="L25" s="256"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -19711,18 +19685,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="258" t="s">
+      <c r="C31" s="256" t="s">
         <v>78</v>
       </c>
-      <c r="D31" s="258"/>
-      <c r="E31" s="258"/>
-      <c r="F31" s="258"/>
-      <c r="G31" s="258"/>
-      <c r="H31" s="258"/>
-      <c r="I31" s="258"/>
-      <c r="J31" s="258"/>
-      <c r="K31" s="258"/>
-      <c r="L31" s="258"/>
+      <c r="D31" s="256"/>
+      <c r="E31" s="256"/>
+      <c r="F31" s="256"/>
+      <c r="G31" s="256"/>
+      <c r="H31" s="256"/>
+      <c r="I31" s="256"/>
+      <c r="J31" s="256"/>
+      <c r="K31" s="256"/>
+      <c r="L31" s="256"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -19861,16 +19835,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19953,7 +19927,7 @@
       </c>
       <c r="C6" s="154">
         <f ca="1">Overview!C5</f>
-        <v>11.605</v>
+        <v>11.67</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19962,7 +19936,7 @@
       </c>
       <c r="C7" s="155">
         <f ca="1">C5*C6</f>
-        <v>6129250.3799999999</v>
+        <v>6163580.5199999996</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20127,8 +20101,8 @@
       <c r="D3" s="247"/>
       <c r="E3" s="247"/>
       <c r="F3" s="247"/>
-      <c r="G3" s="256"/>
-      <c r="H3" s="257" t="s">
+      <c r="G3" s="259"/>
+      <c r="H3" s="260" t="s">
         <v>138</v>
       </c>
       <c r="I3" s="247"/>
@@ -20152,18 +20126,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="88"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="258" t="s">
+      <c r="C5" s="256" t="s">
         <v>222</v>
       </c>
-      <c r="D5" s="258"/>
-      <c r="E5" s="258"/>
-      <c r="F5" s="258"/>
-      <c r="G5" s="258"/>
-      <c r="H5" s="258"/>
-      <c r="I5" s="258"/>
-      <c r="J5" s="258"/>
-      <c r="K5" s="258"/>
-      <c r="L5" s="258"/>
+      <c r="D5" s="256"/>
+      <c r="E5" s="256"/>
+      <c r="F5" s="256"/>
+      <c r="G5" s="256"/>
+      <c r="H5" s="256"/>
+      <c r="I5" s="256"/>
+      <c r="J5" s="256"/>
+      <c r="K5" s="256"/>
+      <c r="L5" s="256"/>
       <c r="P5" s="261"/>
       <c r="Q5" s="261"/>
       <c r="R5" s="261"/>
@@ -20566,8 +20540,8 @@
       <c r="D2" s="247"/>
       <c r="E2" s="247"/>
       <c r="F2" s="247"/>
-      <c r="G2" s="256"/>
-      <c r="H2" s="257" t="s">
+      <c r="G2" s="259"/>
+      <c r="H2" s="260" t="s">
         <v>138</v>
       </c>
       <c r="I2" s="247"/>
@@ -20579,18 +20553,18 @@
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="258" t="s">
+      <c r="C4" s="256" t="s">
         <v>236</v>
       </c>
-      <c r="D4" s="258"/>
-      <c r="E4" s="258"/>
-      <c r="F4" s="258"/>
-      <c r="G4" s="258"/>
-      <c r="H4" s="258"/>
-      <c r="I4" s="258"/>
-      <c r="J4" s="258"/>
-      <c r="K4" s="258"/>
-      <c r="L4" s="258"/>
+      <c r="D4" s="256"/>
+      <c r="E4" s="256"/>
+      <c r="F4" s="256"/>
+      <c r="G4" s="256"/>
+      <c r="H4" s="256"/>
+      <c r="I4" s="256"/>
+      <c r="J4" s="256"/>
+      <c r="K4" s="256"/>
+      <c r="L4" s="256"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -20779,18 +20753,18 @@
       <c r="N9" s="93"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C10" s="258" t="s">
+      <c r="C10" s="256" t="s">
         <v>146</v>
       </c>
-      <c r="D10" s="258"/>
-      <c r="E10" s="258"/>
-      <c r="F10" s="258"/>
-      <c r="G10" s="258"/>
-      <c r="H10" s="258"/>
-      <c r="I10" s="258"/>
-      <c r="J10" s="258"/>
-      <c r="K10" s="258"/>
-      <c r="L10" s="258"/>
+      <c r="D10" s="256"/>
+      <c r="E10" s="256"/>
+      <c r="F10" s="256"/>
+      <c r="G10" s="256"/>
+      <c r="H10" s="256"/>
+      <c r="I10" s="256"/>
+      <c r="J10" s="256"/>
+      <c r="K10" s="256"/>
+      <c r="L10" s="256"/>
       <c r="N10" s="93"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -20984,18 +20958,18 @@
       <c r="N15" s="93"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C16" s="258" t="s">
+      <c r="C16" s="256" t="s">
         <v>238</v>
       </c>
-      <c r="D16" s="258"/>
-      <c r="E16" s="258"/>
-      <c r="F16" s="258"/>
-      <c r="G16" s="258"/>
-      <c r="H16" s="258"/>
-      <c r="I16" s="258"/>
-      <c r="J16" s="258"/>
-      <c r="K16" s="258"/>
-      <c r="L16" s="258"/>
+      <c r="D16" s="256"/>
+      <c r="E16" s="256"/>
+      <c r="F16" s="256"/>
+      <c r="G16" s="256"/>
+      <c r="H16" s="256"/>
+      <c r="I16" s="256"/>
+      <c r="J16" s="256"/>
+      <c r="K16" s="256"/>
+      <c r="L16" s="256"/>
       <c r="N16" s="93"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
@@ -21129,18 +21103,18 @@
       <c r="N20" s="93"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C21" s="258" t="s">
+      <c r="C21" s="256" t="s">
         <v>241</v>
       </c>
-      <c r="D21" s="258"/>
-      <c r="E21" s="258"/>
-      <c r="F21" s="258"/>
-      <c r="G21" s="258"/>
-      <c r="H21" s="258"/>
-      <c r="I21" s="258"/>
-      <c r="J21" s="258"/>
-      <c r="K21" s="258"/>
-      <c r="L21" s="258"/>
+      <c r="D21" s="256"/>
+      <c r="E21" s="256"/>
+      <c r="F21" s="256"/>
+      <c r="G21" s="256"/>
+      <c r="H21" s="256"/>
+      <c r="I21" s="256"/>
+      <c r="J21" s="256"/>
+      <c r="K21" s="256"/>
+      <c r="L21" s="256"/>
       <c r="N21" s="93"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
@@ -21224,18 +21198,18 @@
       <c r="N25" s="93"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C26" s="258" t="s">
+      <c r="C26" s="256" t="s">
         <v>242</v>
       </c>
-      <c r="D26" s="258"/>
-      <c r="E26" s="258"/>
-      <c r="F26" s="258"/>
-      <c r="G26" s="258"/>
-      <c r="H26" s="258"/>
-      <c r="I26" s="258"/>
-      <c r="J26" s="258"/>
-      <c r="K26" s="258"/>
-      <c r="L26" s="258"/>
+      <c r="D26" s="256"/>
+      <c r="E26" s="256"/>
+      <c r="F26" s="256"/>
+      <c r="G26" s="256"/>
+      <c r="H26" s="256"/>
+      <c r="I26" s="256"/>
+      <c r="J26" s="256"/>
+      <c r="K26" s="256"/>
+      <c r="L26" s="256"/>
       <c r="N26" s="93"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
@@ -21806,7 +21780,7 @@
       </c>
       <c r="C10" s="154">
         <f ca="1">Overview!C5</f>
-        <v>11.605</v>
+        <v>11.67</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21815,7 +21789,7 @@
       </c>
       <c r="C11" s="176">
         <f ca="1">(C9-C10)/C10</f>
-        <v>5.5376840322171786E-2</v>
+        <v>4.9498563148140884E-2</v>
       </c>
     </row>
   </sheetData>
@@ -21886,8 +21860,8 @@
       <c r="D3" s="247"/>
       <c r="E3" s="247"/>
       <c r="F3" s="247"/>
-      <c r="G3" s="256"/>
-      <c r="H3" s="257" t="s">
+      <c r="G3" s="259"/>
+      <c r="H3" s="260" t="s">
         <v>138</v>
       </c>
       <c r="I3" s="247"/>
@@ -21911,18 +21885,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="88"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="258" t="s">
+      <c r="C5" s="256" t="s">
         <v>222</v>
       </c>
-      <c r="D5" s="258"/>
-      <c r="E5" s="258"/>
-      <c r="F5" s="258"/>
-      <c r="G5" s="258"/>
-      <c r="H5" s="258"/>
-      <c r="I5" s="258"/>
-      <c r="J5" s="258"/>
-      <c r="K5" s="258"/>
-      <c r="L5" s="258"/>
+      <c r="D5" s="256"/>
+      <c r="E5" s="256"/>
+      <c r="F5" s="256"/>
+      <c r="G5" s="256"/>
+      <c r="H5" s="256"/>
+      <c r="I5" s="256"/>
+      <c r="J5" s="256"/>
+      <c r="K5" s="256"/>
+      <c r="L5" s="256"/>
       <c r="P5" s="261"/>
       <c r="Q5" s="261"/>
       <c r="R5" s="261"/>
@@ -22172,7 +22146,7 @@
       </c>
       <c r="C15" s="178">
         <f ca="1">Overview!C5</f>
-        <v>11.605</v>
+        <v>11.67</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22238,7 +22212,7 @@
       </c>
       <c r="C23" s="184">
         <f ca="1">C15*C22</f>
-        <v>6080114.8100000005</v>
+        <v>6114169.7400000002</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22265,7 +22239,7 @@
       </c>
       <c r="C26" s="185">
         <f ca="1">C23+C25-C24</f>
-        <v>4772870.8100000005</v>
+        <v>4806925.74</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -22348,18 +22322,18 @@
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C39" s="258" t="s">
+      <c r="C39" s="256" t="s">
         <v>272</v>
       </c>
-      <c r="D39" s="258"/>
-      <c r="E39" s="258"/>
-      <c r="F39" s="258"/>
-      <c r="G39" s="258"/>
-      <c r="H39" s="258"/>
-      <c r="I39" s="258"/>
-      <c r="J39" s="258"/>
-      <c r="K39" s="258"/>
-      <c r="L39" s="258"/>
+      <c r="D39" s="256"/>
+      <c r="E39" s="256"/>
+      <c r="F39" s="256"/>
+      <c r="G39" s="256"/>
+      <c r="H39" s="256"/>
+      <c r="I39" s="256"/>
+      <c r="J39" s="256"/>
+      <c r="K39" s="256"/>
+      <c r="L39" s="256"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="12">
@@ -22791,17 +22765,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -29743,7 +29717,7 @@
       <c r="AA125" s="68"/>
       <c r="AC125" s="63">
         <f ca="1">Overview!C5</f>
-        <v>11.605</v>
+        <v>11.67</v>
       </c>
     </row>
     <row r="126" spans="1:31" x14ac:dyDescent="0.2">
@@ -29790,7 +29764,7 @@
       <c r="AA126" s="68"/>
       <c r="AC126" s="65">
         <f t="shared" ref="AC126" ca="1" si="76">AC125/AC84</f>
-        <v>11.605</v>
+        <v>11.67</v>
       </c>
     </row>
     <row r="128" spans="1:31" x14ac:dyDescent="0.2">
@@ -30802,55 +30776,55 @@
         <v>180</v>
       </c>
       <c r="M158" s="139">
-        <f>M30/M5*365</f>
+        <f t="shared" ref="M158:Q159" si="97">M30/M5*365</f>
         <v>133.69421979440784</v>
       </c>
       <c r="N158" s="139">
-        <f>N30/N5*365</f>
+        <f t="shared" si="97"/>
         <v>152.91140215061483</v>
       </c>
       <c r="O158" s="139">
-        <f>O30/O5*365</f>
+        <f t="shared" si="97"/>
         <v>145.23661159324561</v>
       </c>
       <c r="P158" s="139">
-        <f>P30/P5*365</f>
+        <f t="shared" si="97"/>
         <v>137.8303503480538</v>
       </c>
       <c r="Q158" s="139">
-        <f>Q30/Q5*365</f>
+        <f t="shared" si="97"/>
         <v>131.6037563052133</v>
       </c>
       <c r="T158" s="139">
-        <f t="shared" ref="T158:AA158" si="97">T30/T5*90</f>
+        <f t="shared" ref="T158:AA158" si="98">T30/T5*90</f>
         <v>104.95764467056439</v>
       </c>
       <c r="U158" s="139">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>113.19501033404484</v>
       </c>
       <c r="V158" s="139">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>114.68995340449337</v>
       </c>
       <c r="W158" s="139">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>93.317359459823237</v>
       </c>
       <c r="X158" s="139">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>96.344546178343947</v>
       </c>
       <c r="Y158" s="139">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>108.60342533561332</v>
       </c>
       <c r="Z158" s="139">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>108.63165574394054</v>
       </c>
       <c r="AA158" s="139">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>64.534109976050601</v>
       </c>
       <c r="AC158" s="139">
@@ -30863,55 +30837,55 @@
         <v>181</v>
       </c>
       <c r="M159" s="139">
-        <f>M31/M6*365</f>
+        <f t="shared" si="97"/>
         <v>0</v>
       </c>
       <c r="N159" s="139">
-        <f>N31/N6*365</f>
+        <f t="shared" si="97"/>
         <v>0</v>
       </c>
       <c r="O159" s="139">
-        <f>O31/O6*365</f>
+        <f t="shared" si="97"/>
         <v>0</v>
       </c>
       <c r="P159" s="139">
-        <f>P31/P6*365</f>
+        <f t="shared" si="97"/>
         <v>0</v>
       </c>
       <c r="Q159" s="139">
-        <f>Q31/Q6*365</f>
+        <f t="shared" si="97"/>
         <v>0</v>
       </c>
       <c r="T159" s="139">
-        <f t="shared" ref="T159:AA159" si="98">T31/T6*365</f>
+        <f t="shared" ref="T159:AA159" si="99">T31/T6*365</f>
         <v>0</v>
       </c>
       <c r="U159" s="139">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>0</v>
       </c>
       <c r="V159" s="139">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>0</v>
       </c>
       <c r="W159" s="139">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>0</v>
       </c>
       <c r="X159" s="139">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>0</v>
       </c>
       <c r="Y159" s="139">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>0</v>
       </c>
       <c r="Z159" s="139">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>0</v>
       </c>
       <c r="AA159" s="139">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>0</v>
       </c>
       <c r="AC159" s="139">
@@ -30944,35 +30918,35 @@
         <v>13.686287751306349</v>
       </c>
       <c r="T160" s="139">
-        <f t="shared" ref="T160:AA160" si="99">T37/T6*90</f>
+        <f t="shared" ref="T160:AA160" si="100">T37/T6*90</f>
         <v>14.085596967782692</v>
       </c>
       <c r="U160" s="139">
-        <f t="shared" si="99"/>
+        <f t="shared" si="100"/>
         <v>26.007872904348915</v>
       </c>
       <c r="V160" s="139">
-        <f t="shared" si="99"/>
+        <f t="shared" si="100"/>
         <v>46.270493073418663</v>
       </c>
       <c r="W160" s="139">
-        <f t="shared" si="99"/>
+        <f t="shared" si="100"/>
         <v>23.797704245423365</v>
       </c>
       <c r="X160" s="139">
-        <f t="shared" si="99"/>
+        <f t="shared" si="100"/>
         <v>27.599720410065238</v>
       </c>
       <c r="Y160" s="139">
-        <f t="shared" si="99"/>
+        <f t="shared" si="100"/>
         <v>18.67697494623031</v>
       </c>
       <c r="Z160" s="139">
-        <f t="shared" si="99"/>
+        <f t="shared" si="100"/>
         <v>12.368837492391966</v>
       </c>
       <c r="AA160" s="139">
-        <f t="shared" si="99"/>
+        <f t="shared" si="100"/>
         <v>23.046355033277873</v>
       </c>
       <c r="AC160" s="139">
@@ -30989,55 +30963,55 @@
         <v>108.80510521971044</v>
       </c>
       <c r="N161" s="139">
-        <f t="shared" ref="N161:Q161" si="100">N158+N159-N160</f>
+        <f t="shared" ref="N161:Q161" si="101">N158+N159-N160</f>
         <v>134.88753669027304</v>
       </c>
       <c r="O161" s="139">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>138.81496340313109</v>
       </c>
       <c r="P161" s="139">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>88.790616321440268</v>
       </c>
       <c r="Q161" s="139">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>117.91746855390694</v>
       </c>
       <c r="T161" s="139">
-        <f t="shared" ref="T161" si="101">T158+T159-T160</f>
+        <f t="shared" ref="T161" si="102">T158+T159-T160</f>
         <v>90.8720477027817</v>
       </c>
       <c r="U161" s="139">
-        <f t="shared" ref="U161" si="102">U158+U159-U160</f>
+        <f t="shared" ref="U161" si="103">U158+U159-U160</f>
         <v>87.187137429695923</v>
       </c>
       <c r="V161" s="139">
-        <f t="shared" ref="V161" si="103">V158+V159-V160</f>
+        <f t="shared" ref="V161" si="104">V158+V159-V160</f>
         <v>68.419460331074703</v>
       </c>
       <c r="W161" s="139">
-        <f t="shared" ref="W161" si="104">W158+W159-W160</f>
+        <f t="shared" ref="W161" si="105">W158+W159-W160</f>
         <v>69.519655214399876</v>
       </c>
       <c r="X161" s="139">
-        <f t="shared" ref="X161" si="105">X158+X159-X160</f>
+        <f t="shared" ref="X161" si="106">X158+X159-X160</f>
         <v>68.744825768278702</v>
       </c>
       <c r="Y161" s="139">
-        <f t="shared" ref="Y161" si="106">Y158+Y159-Y160</f>
+        <f t="shared" ref="Y161" si="107">Y158+Y159-Y160</f>
         <v>89.926450389383007</v>
       </c>
       <c r="Z161" s="139">
-        <f t="shared" ref="Z161:AA161" si="107">Z158+Z159-Z160</f>
+        <f t="shared" ref="Z161:AA161" si="108">Z158+Z159-Z160</f>
         <v>96.26281825154858</v>
       </c>
       <c r="AA161" s="139">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>41.487754942772725</v>
       </c>
       <c r="AC161" s="139">
-        <f t="shared" ref="AC161" si="108">AC158+AC159-AC160</f>
+        <f t="shared" ref="AC161" si="109">AC158+AC159-AC160</f>
         <v>40.164814474593925</v>
       </c>
     </row>
@@ -31066,35 +31040,35 @@
         <v>0</v>
       </c>
       <c r="T162" s="139">
-        <f t="shared" ref="T162:AA162" si="109">T117/T48</f>
+        <f t="shared" ref="T162:AA162" si="110">T117/T48</f>
         <v>0</v>
       </c>
       <c r="U162" s="139">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>0</v>
       </c>
       <c r="V162" s="139">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>0</v>
       </c>
       <c r="W162" s="139">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>0</v>
       </c>
       <c r="X162" s="139">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>0</v>
       </c>
       <c r="Y162" s="139">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>0</v>
       </c>
       <c r="Z162" s="139">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>0</v>
       </c>
       <c r="AA162" s="139">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>0</v>
       </c>
       <c r="AC162" s="139">
@@ -31127,35 +31101,35 @@
         <v>-0.70704657236408375</v>
       </c>
       <c r="T163" s="203">
-        <f t="shared" ref="T163:AA163" si="110">(T117-T116)/T48</f>
+        <f t="shared" ref="T163:AA163" si="111">(T117-T116)/T48</f>
         <v>-0.95080282790888426</v>
       </c>
       <c r="U163" s="203">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>-0.90599389668243979</v>
       </c>
       <c r="V163" s="203">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>-0.88284296675302665</v>
       </c>
       <c r="W163" s="203">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>-0.91555413989488132</v>
       </c>
       <c r="X163" s="203">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>-0.86899465270819587</v>
       </c>
       <c r="Y163" s="203">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>-0.72647492981720518</v>
       </c>
       <c r="Z163" s="203">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>-0.70704657236408375</v>
       </c>
       <c r="AA163" s="203">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>-0.68695115254353079</v>
       </c>
       <c r="AC163" s="203">
@@ -31188,35 +31162,35 @@
         <v>2.2676594254840001</v>
       </c>
       <c r="T164" s="139">
-        <f t="shared" ref="T164:AA164" si="111">(T116+T30)/T39</f>
+        <f t="shared" ref="T164:AA164" si="112">(T116+T30)/T39</f>
         <v>3.3394102478565317</v>
       </c>
       <c r="U164" s="139">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>2.8974467736346341</v>
       </c>
       <c r="V164" s="139">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>2.715395784308817</v>
       </c>
       <c r="W164" s="139">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>2.6887704000882846</v>
       </c>
       <c r="X164" s="139">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>2.4846597518746183</v>
       </c>
       <c r="Y164" s="139">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>2.4017725370863445</v>
       </c>
       <c r="Z164" s="139">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>2.2676594254840001</v>
       </c>
       <c r="AA164" s="139">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>1.9325582625717537</v>
       </c>
       <c r="AC164" s="139">
@@ -31249,35 +31223,35 @@
         <v>2.4783388537733191</v>
       </c>
       <c r="T165" s="139">
-        <f t="shared" ref="T165:AA165" si="112">T32/T39</f>
+        <f t="shared" ref="T165:AA165" si="113">T32/T39</f>
         <v>3.5957679252114221</v>
       </c>
       <c r="U165" s="139">
-        <f t="shared" si="112"/>
+        <f t="shared" si="113"/>
         <v>3.129493165083332</v>
       </c>
       <c r="V165" s="139">
-        <f t="shared" si="112"/>
+        <f t="shared" si="113"/>
         <v>2.9271504030441093</v>
       </c>
       <c r="W165" s="139">
-        <f t="shared" si="112"/>
+        <f t="shared" si="113"/>
         <v>2.9470125037192663</v>
       </c>
       <c r="X165" s="139">
-        <f t="shared" si="112"/>
+        <f t="shared" si="113"/>
         <v>2.7501208666647705</v>
       </c>
       <c r="Y165" s="139">
-        <f t="shared" si="112"/>
+        <f t="shared" si="113"/>
         <v>2.6541688855077976</v>
       </c>
       <c r="Z165" s="139">
-        <f t="shared" si="112"/>
+        <f t="shared" si="113"/>
         <v>2.4783388537733191</v>
       </c>
       <c r="AA165" s="139">
-        <f t="shared" si="112"/>
+        <f t="shared" si="113"/>
         <v>2.3066495444084523</v>
       </c>
       <c r="AC165" s="139">
@@ -31310,35 +31284,35 @@
         <v>N/A</v>
       </c>
       <c r="T166" s="205" t="str">
-        <f t="shared" ref="T166:AA166" si="113">IF(T13&gt;=0,"N/A",IF(T12&lt;=0,"N/A",T12/-T13))</f>
+        <f t="shared" ref="T166:AA166" si="114">IF(T13&gt;=0,"N/A",IF(T12&lt;=0,"N/A",T12/-T13))</f>
         <v>N/A</v>
       </c>
       <c r="U166" s="205" t="str">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>N/A</v>
       </c>
       <c r="V166" s="205" t="str">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>N/A</v>
       </c>
       <c r="W166" s="205" t="str">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>N/A</v>
       </c>
       <c r="X166" s="205" t="str">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>N/A</v>
       </c>
       <c r="Y166" s="205" t="str">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>N/A</v>
       </c>
       <c r="Z166" s="205" t="str">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>N/A</v>
       </c>
       <c r="AA166" s="205" t="str">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>N/A</v>
       </c>
       <c r="AC166" s="205" t="str">
@@ -31380,7 +31354,7 @@
       <c r="AA167" s="49"/>
       <c r="AC167" s="72">
         <f ca="1">AC126/Statement!AC26</f>
-        <v>19.341666666666665</v>
+        <v>19.449999999999996</v>
       </c>
     </row>
     <row r="168" spans="2:29" x14ac:dyDescent="0.2">
@@ -31417,7 +31391,7 @@
       <c r="AA168" s="49"/>
       <c r="AC168" s="72">
         <f ca="1">AC126/(Statement!AC5/Statement!AC22)</f>
-        <v>3.7385864220877458</v>
+        <v>3.7595263718883234</v>
       </c>
     </row>
     <row r="169" spans="2:29" x14ac:dyDescent="0.2">
@@ -31454,7 +31428,7 @@
       <c r="AA169" s="49"/>
       <c r="AC169" s="72">
         <f ca="1">AC126/(Statement!AC48/Statement!AC74)</f>
-        <v>3.1950744285890704</v>
+        <v>3.2129701492145153</v>
       </c>
     </row>
     <row r="170" spans="2:29" x14ac:dyDescent="0.2">
@@ -31491,7 +31465,7 @@
       <c r="AA170" s="49"/>
       <c r="AC170" s="165">
         <f ca="1">Statement!AC126*Statement!AC77</f>
-        <v>6129250.3799999999</v>
+        <v>6163580.5199999996</v>
       </c>
     </row>
     <row r="171" spans="2:29" x14ac:dyDescent="0.2">
@@ -31528,7 +31502,7 @@
       <c r="AA171" s="49"/>
       <c r="AC171" s="165">
         <f ca="1">AC170+AC117-AC116+AC47+AC44</f>
-        <v>4822006.38</v>
+        <v>4856336.5199999996</v>
       </c>
     </row>
     <row r="172" spans="2:29" x14ac:dyDescent="0.2">
@@ -31565,7 +31539,7 @@
       <c r="AA172" s="49"/>
       <c r="AC172" s="207">
         <f ca="1">AC171/AC5</f>
-        <v>2.8834060143631937</v>
+        <v>2.9039343431021387</v>
       </c>
     </row>
     <row r="173" spans="2:29" x14ac:dyDescent="0.2">
@@ -31602,7 +31576,7 @@
       <c r="AA173" s="49"/>
       <c r="AC173" s="207">
         <f ca="1">AC171/AC12</f>
-        <v>47.667596358208364</v>
+        <v>48.006964481657583</v>
       </c>
     </row>
     <row r="174" spans="2:29" x14ac:dyDescent="0.2">
@@ -31634,31 +31608,31 @@
         <v>-49347</v>
       </c>
       <c r="U174" s="64">
-        <f t="shared" ref="U174:AA174" si="114">U58-U53+U119+U64</f>
+        <f t="shared" ref="U174:AA174" si="115">U58-U53+U119+U64</f>
         <v>-64293</v>
       </c>
       <c r="V174" s="64">
-        <f t="shared" si="114"/>
+        <f t="shared" si="115"/>
         <v>0</v>
       </c>
       <c r="W174" s="64">
-        <f t="shared" si="114"/>
+        <f t="shared" si="115"/>
         <v>29809</v>
       </c>
       <c r="X174" s="64">
-        <f t="shared" si="114"/>
+        <f t="shared" si="115"/>
         <v>-36419</v>
       </c>
       <c r="Y174" s="64">
-        <f t="shared" si="114"/>
+        <f t="shared" si="115"/>
         <v>-46368</v>
       </c>
       <c r="Z174" s="64">
-        <f t="shared" si="114"/>
+        <f t="shared" si="115"/>
         <v>114462</v>
       </c>
       <c r="AA174" s="64">
-        <f t="shared" si="114"/>
+        <f t="shared" si="115"/>
         <v>75934</v>
       </c>
       <c r="AC174" s="64">
@@ -31671,19 +31645,19 @@
         <v>314</v>
       </c>
       <c r="M175" s="64">
-        <f t="shared" ref="M175:P175" si="115">M118+M52+M119+M54+M56+M57+M55</f>
+        <f t="shared" ref="M175:P175" si="116">M118+M52+M119+M54+M56+M57+M55</f>
         <v>-603972</v>
       </c>
       <c r="N175" s="64">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>-500062</v>
       </c>
       <c r="O175" s="64">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>-216393</v>
       </c>
       <c r="P175" s="64">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>-202032</v>
       </c>
       <c r="Q175" s="64">
@@ -31712,19 +31686,19 @@
         <v>-31.117410328396652</v>
       </c>
       <c r="N176" s="72">
-        <f t="shared" ref="N176:Q176" si="116">N170/N174</f>
+        <f t="shared" ref="N176:Q176" si="117">N170/N174</f>
         <v>-20.121230787144853</v>
       </c>
       <c r="O176" s="72">
-        <f t="shared" si="116"/>
+        <f t="shared" si="117"/>
         <v>-169.18232313158387</v>
       </c>
       <c r="P176" s="72">
-        <f t="shared" si="116"/>
+        <f t="shared" si="117"/>
         <v>-153.13123350282808</v>
       </c>
       <c r="Q176" s="72">
-        <f t="shared" si="116"/>
+        <f t="shared" si="117"/>
         <v>108.6619548175135</v>
       </c>
       <c r="T176" s="49"/>
@@ -31736,8 +31710,8 @@
       <c r="Z176" s="49"/>
       <c r="AA176" s="49"/>
       <c r="AC176" s="72">
-        <f t="shared" ref="AC176:AC177" ca="1" si="117">AC170/AC174</f>
-        <v>56.958529305169641</v>
+        <f t="shared" ref="AC176:AC177" ca="1" si="118">AC170/AC174</f>
+        <v>57.277555966508373</v>
       </c>
     </row>
     <row r="177" spans="2:29" x14ac:dyDescent="0.2">
@@ -31749,19 +31723,19 @@
         <v>-26.916581960753149</v>
       </c>
       <c r="N177" s="72">
-        <f t="shared" ref="N177:Q177" si="118">N171/N175</f>
+        <f t="shared" ref="N177:Q177" si="119">N171/N175</f>
         <v>-12.727941955197556</v>
       </c>
       <c r="O177" s="72">
-        <f t="shared" si="118"/>
+        <f t="shared" si="119"/>
         <v>-54.027334756669582</v>
       </c>
       <c r="P177" s="72">
-        <f t="shared" si="118"/>
+        <f t="shared" si="119"/>
         <v>-31.733833947097491</v>
       </c>
       <c r="Q177" s="72">
-        <f t="shared" si="118"/>
+        <f t="shared" si="119"/>
         <v>-55.101089964665803</v>
       </c>
       <c r="T177" s="49"/>
@@ -31773,8 +31747,8 @@
       <c r="Z177" s="49"/>
       <c r="AA177" s="49"/>
       <c r="AC177" s="72">
-        <f t="shared" ca="1" si="117"/>
-        <v>-88.909493500507054</v>
+        <f t="shared" ca="1" si="118"/>
+        <v>-89.542482160966159</v>
       </c>
     </row>
     <row r="178" spans="2:29" x14ac:dyDescent="0.2">
@@ -31786,19 +31760,19 @@
         <v>-3.2136350340421331E-2</v>
       </c>
       <c r="N178" s="74">
-        <f t="shared" ref="N178:Q178" si="119">N174/N170</f>
+        <f t="shared" ref="N178:Q178" si="120">N174/N170</f>
         <v>-4.9698749076467263E-2</v>
       </c>
       <c r="O178" s="74">
-        <f t="shared" si="119"/>
+        <f t="shared" si="120"/>
         <v>-5.9107830031523813E-3</v>
       </c>
       <c r="P178" s="74">
-        <f t="shared" si="119"/>
+        <f t="shared" si="120"/>
         <v>-6.5303464037043202E-3</v>
       </c>
       <c r="Q178" s="74">
-        <f t="shared" si="119"/>
+        <f t="shared" si="120"/>
         <v>9.2028530287292954E-3</v>
       </c>
       <c r="T178" s="49"/>
@@ -31810,8 +31784,8 @@
       <c r="Z178" s="49"/>
       <c r="AA178" s="49"/>
       <c r="AC178" s="74">
-        <f t="shared" ref="AC178" ca="1" si="120">AC174/AC170</f>
-        <v>1.7556633083734459E-2</v>
+        <f t="shared" ref="AC178" ca="1" si="121">AC174/AC170</f>
+        <v>1.7458845495864472E-2</v>
       </c>
     </row>
     <row r="179" spans="2:29" x14ac:dyDescent="0.2">
@@ -31823,19 +31797,19 @@
         <v>-3.4699371821717021E-2</v>
       </c>
       <c r="N179" s="74">
-        <f t="shared" ref="N179:Q179" si="121">N26/N126</f>
+        <f t="shared" ref="N179:Q179" si="122">N26/N126</f>
         <v>-4.1180507892930679E-2</v>
       </c>
       <c r="O179" s="74">
-        <f t="shared" si="121"/>
+        <f t="shared" si="122"/>
         <v>-6.7085953878406705E-3</v>
       </c>
       <c r="P179" s="74">
-        <f t="shared" si="121"/>
+        <f t="shared" si="122"/>
         <v>-8.9163237311385458E-3</v>
       </c>
       <c r="Q179" s="74">
-        <f t="shared" si="121"/>
+        <f t="shared" si="122"/>
         <v>4.1302621127879274E-2</v>
       </c>
       <c r="T179" s="49"/>
@@ -31847,8 +31821,8 @@
       <c r="Z179" s="49"/>
       <c r="AA179" s="49"/>
       <c r="AC179" s="74">
-        <f t="shared" ref="AC179" ca="1" si="122">AC26/AC126</f>
-        <v>5.1701852649719951E-2</v>
+        <f t="shared" ref="AC179" ca="1" si="123">AC26/AC126</f>
+        <v>5.1413881748071988E-2</v>
       </c>
     </row>
     <row r="180" spans="2:29" x14ac:dyDescent="0.2">
@@ -31860,19 +31834,19 @@
         <v>0</v>
       </c>
       <c r="N180" s="176">
-        <f t="shared" ref="N180:Q180" si="123">N81/N126</f>
+        <f t="shared" ref="N180:Q180" si="124">N81/N126</f>
         <v>0</v>
       </c>
       <c r="O180" s="176">
-        <f t="shared" si="123"/>
+        <f t="shared" si="124"/>
         <v>0</v>
       </c>
       <c r="P180" s="176">
-        <f t="shared" si="123"/>
+        <f t="shared" si="124"/>
         <v>0</v>
       </c>
       <c r="Q180" s="176">
-        <f t="shared" si="123"/>
+        <f t="shared" si="124"/>
         <v>0</v>
       </c>
       <c r="T180" s="49"/>
@@ -31884,7 +31858,7 @@
       <c r="Z180" s="49"/>
       <c r="AA180" s="49"/>
       <c r="AC180" s="176">
-        <f t="shared" ref="AC180" ca="1" si="124">AC81/AC126</f>
+        <f t="shared" ref="AC180" ca="1" si="125">AC81/AC126</f>
         <v>0</v>
       </c>
     </row>
@@ -31922,7 +31896,7 @@
       <c r="AA181" s="49"/>
       <c r="AC181" s="176">
         <f ca="1">-AC62/AC170</f>
-        <v>5.6348163084830614E-2</v>
+        <v>5.6034312990527788E-2</v>
       </c>
     </row>
     <row r="182" spans="2:29" x14ac:dyDescent="0.2">
@@ -31959,7 +31933,7 @@
       <c r="AA182" s="49"/>
       <c r="AC182" s="176">
         <f ca="1">-(AC62+AC63)/AC170</f>
-        <v>5.6348163084830614E-2</v>
+        <v>5.6034312990527788E-2</v>
       </c>
     </row>
     <row r="183" spans="2:29" x14ac:dyDescent="0.2">
@@ -32172,35 +32146,35 @@
         <v>2.8105061440443424</v>
       </c>
       <c r="T188" s="72">
-        <f t="shared" ref="T188:AA188" si="125">T116/T74</f>
+        <f t="shared" ref="T188:AA188" si="126">T116/T74</f>
         <v>3.1700129828095962</v>
       </c>
       <c r="U188" s="72">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>2.8548832876333474</v>
       </c>
       <c r="V188" s="72">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>2.9547392260645196</v>
       </c>
       <c r="W188" s="72">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>2.90639187049916</v>
       </c>
       <c r="X188" s="72">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>2.7258512829976911</v>
       </c>
       <c r="Y188" s="72">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>2.6146535764375876</v>
       </c>
       <c r="Z188" s="72">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>2.8105061440443424</v>
       </c>
       <c r="AA188" s="72">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>2.4951118677971147</v>
       </c>
       <c r="AC188" s="72">
@@ -32233,35 +32207,35 @@
         <v>0.78305424452059225</v>
       </c>
       <c r="T189" s="176">
-        <f t="shared" ref="T189:AA189" si="126">T53/T58</f>
+        <f t="shared" ref="T189:AA189" si="127">T53/T58</f>
         <v>2.0334871485250994</v>
       </c>
       <c r="U189" s="176">
-        <f t="shared" si="126"/>
+        <f t="shared" si="127"/>
         <v>3.1167794798717492</v>
       </c>
       <c r="V189" s="176" t="e">
-        <f t="shared" si="126"/>
+        <f t="shared" si="127"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W189" s="176">
-        <f t="shared" si="126"/>
+        <f t="shared" si="127"/>
         <v>0.6416782911211576</v>
       </c>
       <c r="X189" s="176">
-        <f t="shared" si="126"/>
+        <f t="shared" si="127"/>
         <v>1.8757303965181427</v>
       </c>
       <c r="Y189" s="176">
-        <f t="shared" si="126"/>
+        <f t="shared" si="127"/>
         <v>2.5282091188850764</v>
       </c>
       <c r="Z189" s="176">
-        <f t="shared" si="126"/>
+        <f t="shared" si="127"/>
         <v>0.35555092460569898</v>
       </c>
       <c r="AA189" s="176">
-        <f t="shared" si="126"/>
+        <f t="shared" si="127"/>
         <v>0.40408404584318719</v>
       </c>
       <c r="AC189" s="176">
@@ -32294,35 +32268,35 @@
         <v>0.18047997854178516</v>
       </c>
       <c r="T190" s="176">
-        <f t="shared" ref="T190:AA190" si="127">T53/T5</f>
+        <f t="shared" ref="T190:AA190" si="128">T53/T5</f>
         <v>0.29819479973312507</v>
       </c>
       <c r="U190" s="176">
-        <f t="shared" si="127"/>
+        <f t="shared" si="128"/>
         <v>0.24668619749445234</v>
       </c>
       <c r="V190" s="176">
-        <f t="shared" si="127"/>
+        <f t="shared" si="128"/>
         <v>0</v>
       </c>
       <c r="W190" s="176">
-        <f t="shared" si="127"/>
+        <f t="shared" si="128"/>
         <v>0.21412187626183318</v>
       </c>
       <c r="X190" s="176">
-        <f t="shared" si="127"/>
+        <f t="shared" si="128"/>
         <v>0.21564822186836519</v>
       </c>
       <c r="Y190" s="176">
-        <f t="shared" si="127"/>
+        <f t="shared" si="128"/>
         <v>0.17385730930425455</v>
       </c>
       <c r="Z190" s="176">
-        <f t="shared" si="127"/>
+        <f t="shared" si="128"/>
         <v>0.13476004298420102</v>
       </c>
       <c r="AA190" s="176">
-        <f t="shared" si="127"/>
+        <f t="shared" si="128"/>
         <v>0.1274194396508454</v>
       </c>
       <c r="AC190" s="176">
@@ -32355,35 +32329,35 @@
         <v>2.8105061440443424</v>
       </c>
       <c r="T191" s="72">
-        <f t="shared" ref="T191:AA191" si="128">(T116-T117)/T74</f>
+        <f t="shared" ref="T191:AA191" si="129">(T116-T117)/T74</f>
         <v>3.1700129828095962</v>
       </c>
       <c r="U191" s="72">
-        <f t="shared" si="128"/>
+        <f t="shared" si="129"/>
         <v>2.8548832876333474</v>
       </c>
       <c r="V191" s="72">
-        <f t="shared" si="128"/>
+        <f t="shared" si="129"/>
         <v>2.9547392260645196</v>
       </c>
       <c r="W191" s="72">
-        <f t="shared" si="128"/>
+        <f t="shared" si="129"/>
         <v>2.90639187049916</v>
       </c>
       <c r="X191" s="72">
-        <f t="shared" si="128"/>
+        <f t="shared" si="129"/>
         <v>2.7258512829976911</v>
       </c>
       <c r="Y191" s="72">
-        <f t="shared" si="128"/>
+        <f t="shared" si="129"/>
         <v>2.6146535764375876</v>
       </c>
       <c r="Z191" s="72">
-        <f t="shared" si="128"/>
+        <f t="shared" si="129"/>
         <v>2.8105061440443424</v>
       </c>
       <c r="AA191" s="72">
-        <f t="shared" si="128"/>
+        <f t="shared" si="129"/>
         <v>2.4951118677971147</v>
       </c>
       <c r="AC191" s="72">
@@ -32425,7 +32399,7 @@
       <c r="AA192" s="49"/>
       <c r="AC192" s="176">
         <f ca="1">(AC116-AC117)/AC170</f>
-        <v>0.21327958868601482</v>
+        <v>0.21209165610121697</v>
       </c>
     </row>
     <row r="193" spans="2:29" x14ac:dyDescent="0.2">
@@ -32453,35 +32427,35 @@
         <v>1.1826854061786744E-2</v>
       </c>
       <c r="T193" s="176">
-        <f t="shared" ref="T193:AA193" si="129">-T119/T5</f>
+        <f t="shared" ref="T193:AA193" si="130">-T119/T5</f>
         <v>4.4837519327879894E-3</v>
       </c>
       <c r="U193" s="176">
-        <f t="shared" si="129"/>
+        <f t="shared" si="130"/>
         <v>1.3745830431435797E-2</v>
       </c>
       <c r="V193" s="176">
-        <f t="shared" si="129"/>
+        <f t="shared" si="130"/>
         <v>0</v>
       </c>
       <c r="W193" s="176">
-        <f t="shared" si="129"/>
+        <f t="shared" si="130"/>
         <v>3.5981874467225984E-2</v>
       </c>
       <c r="X193" s="176">
-        <f t="shared" si="129"/>
+        <f t="shared" si="130"/>
         <v>0</v>
       </c>
       <c r="Y193" s="176">
-        <f t="shared" si="129"/>
+        <f t="shared" si="130"/>
         <v>7.6961808553852587E-3</v>
       </c>
       <c r="Z193" s="176">
-        <f t="shared" si="129"/>
+        <f t="shared" si="130"/>
         <v>6.3437031679023587E-3</v>
       </c>
       <c r="AA193" s="176">
-        <f t="shared" si="129"/>
+        <f t="shared" si="130"/>
         <v>6.415189946030183E-3</v>
       </c>
       <c r="AC193" s="176">
@@ -32514,35 +32488,35 @@
         <v>5.1313549276955236E-2</v>
       </c>
       <c r="T194" s="176">
-        <f t="shared" ref="T194:AA194" si="130">-(T119/T58)</f>
+        <f t="shared" ref="T194:AA194" si="131">-(T119/T58)</f>
         <v>3.0576160082801448E-2</v>
       </c>
       <c r="U194" s="176">
-        <f t="shared" si="130"/>
+        <f t="shared" si="131"/>
         <v>0.17367296045600286</v>
       </c>
       <c r="V194" s="176" t="e">
-        <f t="shared" si="130"/>
+        <f t="shared" si="131"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W194" s="176">
-        <f t="shared" si="130"/>
+        <f t="shared" si="131"/>
         <v>0.10783012050217644</v>
       </c>
       <c r="X194" s="176">
-        <f t="shared" si="130"/>
+        <f t="shared" si="131"/>
         <v>0</v>
       </c>
       <c r="Y194" s="176">
-        <f t="shared" si="130"/>
+        <f t="shared" si="131"/>
         <v>0.11191680520674896</v>
       </c>
       <c r="Z194" s="176">
-        <f t="shared" si="130"/>
+        <f t="shared" si="131"/>
         <v>1.6737227718428501E-2</v>
       </c>
       <c r="AA194" s="176">
-        <f t="shared" si="130"/>
+        <f t="shared" si="131"/>
         <v>2.0344430295312594E-2</v>
       </c>
       <c r="AC194" s="176">
@@ -32575,35 +32549,35 @@
         <v>1.1225175319700631</v>
       </c>
       <c r="T195" s="176">
-        <f t="shared" ref="T195:AA195" si="131">-T119/T52</f>
+        <f t="shared" ref="T195:AA195" si="132">-T119/T52</f>
         <v>0.30953940187731938</v>
       </c>
       <c r="U195" s="176">
-        <f t="shared" si="131"/>
+        <f t="shared" si="132"/>
         <v>1.0752095280105867</v>
       </c>
       <c r="V195" s="176" t="e">
-        <f t="shared" si="131"/>
+        <f t="shared" si="132"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W195" s="176">
-        <f t="shared" si="131"/>
+        <f t="shared" si="132"/>
         <v>3.9446664617276359</v>
       </c>
       <c r="X195" s="176">
-        <f t="shared" si="131"/>
+        <f t="shared" si="132"/>
         <v>0</v>
       </c>
       <c r="Y195" s="176">
-        <f t="shared" si="131"/>
+        <f t="shared" si="132"/>
         <v>0.7010857522712165</v>
       </c>
       <c r="Z195" s="176">
-        <f t="shared" si="131"/>
+        <f t="shared" si="132"/>
         <v>0.61371405590187011</v>
       </c>
       <c r="AA195" s="176">
-        <f t="shared" si="131"/>
+        <f t="shared" si="132"/>
         <v>0.35743774137701423</v>
       </c>
       <c r="AC195" s="176">
@@ -32665,75 +32639,75 @@
         <v>1</v>
       </c>
       <c r="N199" s="81">
-        <f t="shared" ref="N199:Q199" si="132">IF(M105=0,
+        <f t="shared" ref="N199:Q199" si="133">IF(M105=0,
 IF(N105=0,0,IF(N105&gt;0,1,-1)),
 (N105-M105)/ABS(M105)
 )</f>
         <v>3.4084087514825716E-2</v>
       </c>
       <c r="O199" s="81">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>0.24818614965570993</v>
       </c>
       <c r="P199" s="81">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>-5.5102093364575021E-2</v>
       </c>
       <c r="Q199" s="81">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>3.2771752459329104E-2</v>
       </c>
       <c r="T199" s="81">
-        <f t="shared" ref="T199:T201" si="133">IF(S105=0,
+        <f t="shared" ref="T199:T201" si="134">IF(S105=0,
 IF(T105=0,0,IF(T105&gt;0,1,-1)),
 (T105-S105)/ABS(S105)
 )</f>
         <v>1</v>
       </c>
       <c r="U199" s="81">
-        <f t="shared" ref="U199:U201" si="134">IF(T105=0,
+        <f t="shared" ref="U199:U201" si="135">IF(T105=0,
 IF(U105=0,0,IF(U105&gt;0,1,-1)),
 (U105-T105)/ABS(T105)
 )</f>
         <v>0.22202920241245067</v>
       </c>
       <c r="V199" s="81">
-        <f t="shared" ref="V199:V201" si="135">IF(U105=0,
+        <f t="shared" ref="V199:V201" si="136">IF(U105=0,
 IF(V105=0,0,IF(V105&gt;0,1,-1)),
 (V105-U105)/ABS(U105)
 )</f>
         <v>0.44057182848061588</v>
       </c>
       <c r="W199" s="81">
-        <f t="shared" ref="W199:W201" si="136">IF(V105=0,
+        <f t="shared" ref="W199:W201" si="137">IF(V105=0,
 IF(W105=0,0,IF(W105&gt;0,1,-1)),
 (W105-V105)/ABS(V105)
 )</f>
         <v>-0.35080892064632685</v>
       </c>
       <c r="X199" s="81">
-        <f t="shared" ref="X199:X201" si="137">IF(W105=0,
+        <f t="shared" ref="X199:X201" si="138">IF(W105=0,
 IF(X105=0,0,IF(X105&gt;0,1,-1)),
 (X105-W105)/ABS(W105)
 )</f>
         <v>-0.12569571114540948</v>
       </c>
       <c r="Y199" s="81">
-        <f t="shared" ref="Y199:Y201" si="138">IF(X105=0,
+        <f t="shared" ref="Y199:Y201" si="139">IF(X105=0,
 IF(Y105=0,0,IF(Y105&gt;0,1,-1)),
 (Y105-X105)/ABS(X105)
 )</f>
         <v>0.33774663207353717</v>
       </c>
       <c r="Z199" s="81">
-        <f t="shared" ref="Z199:Z201" si="139">IF(Y105=0,
+        <f t="shared" ref="Z199:Z201" si="140">IF(Y105=0,
 IF(Z105=0,0,IF(Z105&gt;0,1,-1)),
 (Z105-Y105)/ABS(Y105)
 )</f>
         <v>0.43894750171617469</v>
       </c>
       <c r="AA199" s="81">
-        <f t="shared" ref="AA199:AA201" si="140">IF(Z105=0,
+        <f t="shared" ref="AA199:AA201" si="141">IF(Z105=0,
 IF(AA105=0,0,IF(AA105&gt;0,1,-1)),
 (AA105-Z105)/ABS(Z105)
 )</f>
@@ -32746,58 +32720,58 @@
         <v>114</v>
       </c>
       <c r="M200" s="81">
-        <f t="shared" ref="M200:Q200" si="141">IF(L106=0,
+        <f t="shared" ref="M200:Q200" si="142">IF(L106=0,
 IF(M106=0,0,IF(M106&gt;0,1,-1)),
 (M106-L106)/ABS(L106)
 )</f>
         <v>1</v>
       </c>
       <c r="N200" s="81">
+        <f t="shared" si="142"/>
+        <v>0.37569180272908909</v>
+      </c>
+      <c r="O200" s="81">
+        <f t="shared" si="142"/>
+        <v>0.27729682030883041</v>
+      </c>
+      <c r="P200" s="81">
+        <f t="shared" si="142"/>
+        <v>0.23392027917368038</v>
+      </c>
+      <c r="Q200" s="81">
+        <f t="shared" si="142"/>
+        <v>0.19019336689332336</v>
+      </c>
+      <c r="T200" s="81">
+        <f t="shared" si="134"/>
+        <v>1</v>
+      </c>
+      <c r="U200" s="81">
+        <f t="shared" si="135"/>
+        <v>6.292089812146523E-2</v>
+      </c>
+      <c r="V200" s="81">
+        <f t="shared" si="136"/>
+        <v>4.0106900184610626E-2</v>
+      </c>
+      <c r="W200" s="81">
+        <f t="shared" si="137"/>
+        <v>9.673777187170397E-3</v>
+      </c>
+      <c r="X200" s="81">
+        <f t="shared" si="138"/>
+        <v>9.6915367022084364E-2</v>
+      </c>
+      <c r="Y200" s="81">
+        <f t="shared" si="139"/>
+        <v>3.8638547089942653E-2</v>
+      </c>
+      <c r="Z200" s="81">
+        <f t="shared" si="140"/>
+        <v>1.4783518396594137E-2</v>
+      </c>
+      <c r="AA200" s="81">
         <f t="shared" si="141"/>
-        <v>0.37569180272908909</v>
-      </c>
-      <c r="O200" s="81">
-        <f t="shared" si="141"/>
-        <v>0.27729682030883041</v>
-      </c>
-      <c r="P200" s="81">
-        <f t="shared" si="141"/>
-        <v>0.23392027917368038</v>
-      </c>
-      <c r="Q200" s="81">
-        <f t="shared" si="141"/>
-        <v>0.19019336689332336</v>
-      </c>
-      <c r="T200" s="81">
-        <f t="shared" si="133"/>
-        <v>1</v>
-      </c>
-      <c r="U200" s="81">
-        <f t="shared" si="134"/>
-        <v>6.292089812146523E-2</v>
-      </c>
-      <c r="V200" s="81">
-        <f t="shared" si="135"/>
-        <v>4.0106900184610626E-2</v>
-      </c>
-      <c r="W200" s="81">
-        <f t="shared" si="136"/>
-        <v>9.673777187170397E-3</v>
-      </c>
-      <c r="X200" s="81">
-        <f t="shared" si="137"/>
-        <v>9.6915367022084364E-2</v>
-      </c>
-      <c r="Y200" s="81">
-        <f t="shared" si="138"/>
-        <v>3.8638547089942653E-2</v>
-      </c>
-      <c r="Z200" s="81">
-        <f t="shared" si="139"/>
-        <v>1.4783518396594137E-2</v>
-      </c>
-      <c r="AA200" s="81">
-        <f t="shared" si="140"/>
         <v>6.6472159310281692E-3</v>
       </c>
       <c r="AC200" s="49"/>
@@ -32807,58 +32781,58 @@
         <v>115</v>
       </c>
       <c r="M201" s="81">
-        <f t="shared" ref="M201:Q201" si="142">IF(L107=0,
+        <f t="shared" ref="M201:Q201" si="143">IF(L107=0,
 IF(M107=0,0,IF(M107&gt;0,1,-1)),
 (M107-L107)/ABS(L107)
 )</f>
         <v>1</v>
       </c>
       <c r="N201" s="81">
-        <f t="shared" si="142"/>
+        <f t="shared" si="143"/>
         <v>0.26768885199472631</v>
       </c>
       <c r="O201" s="81">
-        <f t="shared" si="142"/>
+        <f t="shared" si="143"/>
         <v>-0.29197642617772812</v>
       </c>
       <c r="P201" s="81">
-        <f t="shared" si="142"/>
+        <f t="shared" si="143"/>
         <v>0.10317719384146673</v>
       </c>
       <c r="Q201" s="81">
-        <f t="shared" si="142"/>
+        <f t="shared" si="143"/>
         <v>0.22564418690666996</v>
       </c>
       <c r="T201" s="81">
-        <f t="shared" si="133"/>
+        <f t="shared" si="134"/>
         <v>1</v>
       </c>
       <c r="U201" s="81">
-        <f t="shared" si="134"/>
+        <f t="shared" si="135"/>
         <v>0.13163254368099475</v>
       </c>
       <c r="V201" s="81">
-        <f t="shared" si="135"/>
+        <f t="shared" si="136"/>
         <v>2.4533484891541158E-2</v>
       </c>
       <c r="W201" s="81">
-        <f t="shared" si="136"/>
+        <f t="shared" si="137"/>
         <v>2.0247781065088757E-2</v>
       </c>
       <c r="X201" s="81">
-        <f t="shared" si="137"/>
+        <f t="shared" si="138"/>
         <v>1.5314907113729044E-2</v>
       </c>
       <c r="Y201" s="81">
-        <f t="shared" si="138"/>
+        <f t="shared" si="139"/>
         <v>0.20465905033916459</v>
       </c>
       <c r="Z201" s="81">
-        <f t="shared" si="139"/>
+        <f t="shared" si="140"/>
         <v>3.5044824775876122E-2</v>
       </c>
       <c r="AA201" s="81">
-        <f t="shared" si="140"/>
+        <f t="shared" si="141"/>
         <v>0.15748031496062992</v>
       </c>
       <c r="AC201" s="49"/>
@@ -32917,22 +32891,22 @@
         <v>0</v>
       </c>
       <c r="N205" s="81">
-        <f t="shared" ref="N205:Q205" si="143">IF(M63=0,
+        <f t="shared" ref="N205:Q205" si="144">IF(M63=0,
 IF(N63=0,0,IF(N63&gt;0,1,-1)),
 (N63-M63)/M63
 )</f>
         <v>0</v>
       </c>
       <c r="O205" s="81">
-        <f t="shared" si="143"/>
+        <f t="shared" si="144"/>
         <v>0</v>
       </c>
       <c r="P205" s="81">
-        <f t="shared" si="143"/>
+        <f t="shared" si="144"/>
         <v>0</v>
       </c>
       <c r="Q205" s="81">
-        <f t="shared" si="143"/>
+        <f t="shared" si="144"/>
         <v>0</v>
       </c>
       <c r="T205" s="49"/>
@@ -33012,7 +32986,7 @@
       </c>
       <c r="C5" s="196">
         <f ca="1">Overview!C5</f>
-        <v>11.605</v>
+        <v>11.67</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="153" t="s">
@@ -33028,7 +33002,7 @@
       </c>
       <c r="C6" s="197">
         <f ca="1">Statement!AC170</f>
-        <v>6129250.3799999999</v>
+        <v>6163580.5199999996</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>20</v>
@@ -33048,7 +33022,7 @@
       </c>
       <c r="C7" s="197">
         <f ca="1">Statement!AC171</f>
-        <v>4822006.38</v>
+        <v>4856336.5199999996</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>32</v>
@@ -33068,7 +33042,7 @@
       </c>
       <c r="C8" s="198">
         <f ca="1">Statement!AC167</f>
-        <v>19.341666666666665</v>
+        <v>19.449999999999996</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>295</v>
@@ -33088,7 +33062,7 @@
       </c>
       <c r="C9" s="198">
         <f ca="1">Statement!AC168</f>
-        <v>3.7385864220877458</v>
+        <v>3.7595263718883234</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>296</v>
@@ -33108,7 +33082,7 @@
       </c>
       <c r="C10" s="198">
         <f ca="1">Statement!AC169</f>
-        <v>3.1950744285890704</v>
+        <v>3.2129701492145153</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -33128,7 +33102,7 @@
       </c>
       <c r="C11" s="198">
         <f ca="1">Statement!AC172</f>
-        <v>2.8834060143631937</v>
+        <v>2.9039343431021387</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33137,7 +33111,7 @@
       </c>
       <c r="C12" s="198">
         <f ca="1">Statement!AC173</f>
-        <v>47.667596358208364</v>
+        <v>48.006964481657583</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -33373,7 +33347,7 @@
       </c>
       <c r="C38" s="199">
         <f ca="1">Statement!AC179</f>
-        <v>5.1701852649719951E-2</v>
+        <v>5.1413881748071988E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>323</v>
@@ -33389,7 +33363,7 @@
       </c>
       <c r="C39" s="240">
         <f ca="1">Statement!AC178</f>
-        <v>1.7556633083734459E-2</v>
+        <v>1.7458845495864472E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>325</v>
@@ -33421,7 +33395,7 @@
       </c>
       <c r="C41" s="199">
         <f ca="1">Statement!AC181</f>
-        <v>5.6348163084830614E-2</v>
+        <v>5.6034312990527788E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -33430,7 +33404,7 @@
       </c>
       <c r="C42" s="199">
         <f ca="1">Statement!AC182</f>
-        <v>5.6348163084830614E-2</v>
+        <v>5.6034312990527788E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -33474,7 +33448,7 @@
       </c>
       <c r="F48" s="199">
         <f ca="1">Statement!AC192</f>
-        <v>0.21327958868601482</v>
+        <v>0.21209165610121697</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -33653,7 +33627,7 @@
       </c>
       <c r="I6" s="196">
         <f ca="1">Statement!AC125</f>
-        <v>11.605</v>
+        <v>11.67</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -33682,7 +33656,7 @@
       </c>
       <c r="I7" s="197">
         <f ca="1">Statement!AC170</f>
-        <v>6129250.3799999999</v>
+        <v>6163580.5199999996</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -33711,7 +33685,7 @@
       </c>
       <c r="I8" s="197">
         <f ca="1">Statement!AC171</f>
-        <v>4822006.38</v>
+        <v>4856336.5199999996</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -33740,7 +33714,7 @@
       </c>
       <c r="I9" s="198">
         <f ca="1">Statement!AC167</f>
-        <v>19.341666666666665</v>
+        <v>19.449999999999996</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -33769,7 +33743,7 @@
       </c>
       <c r="I10" s="198">
         <f ca="1">Statement!AC168</f>
-        <v>3.7385864220877458</v>
+        <v>3.7595263718883234</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -33798,7 +33772,7 @@
       </c>
       <c r="I11" s="198">
         <f ca="1">Statement!AC169</f>
-        <v>3.1950744285890704</v>
+        <v>3.2129701492145153</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -33827,7 +33801,7 @@
       </c>
       <c r="I12" s="198">
         <f ca="1">Statement!AC172</f>
-        <v>2.8834060143631937</v>
+        <v>2.9039343431021387</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -33856,7 +33830,7 @@
       </c>
       <c r="I13" s="198">
         <f ca="1">Statement!AC173</f>
-        <v>47.667596358208364</v>
+        <v>48.006964481657583</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34629,7 +34603,7 @@
       </c>
       <c r="I51" s="199">
         <f ca="1">Statement!AC179</f>
-        <v>5.1701852649719951E-2</v>
+        <v>5.1413881748071988E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -34658,7 +34632,7 @@
       </c>
       <c r="I52" s="199">
         <f ca="1">Statement!AC178</f>
-        <v>1.7556633083734459E-2</v>
+        <v>1.7458845495864472E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -34716,7 +34690,7 @@
       </c>
       <c r="I54" s="199">
         <f ca="1">Statement!AC181</f>
-        <v>5.6348163084830614E-2</v>
+        <v>5.6034312990527788E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -34745,7 +34719,7 @@
       </c>
       <c r="I55" s="199">
         <f ca="1">Statement!AC182</f>
-        <v>5.6348163084830614E-2</v>
+        <v>5.6034312990527788E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34981,7 +34955,7 @@
       </c>
       <c r="I68" s="220">
         <f ca="1">Statement!AC192</f>
-        <v>0.21327958868601482</v>
+        <v>0.21209165610121697</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35467,14 +35441,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="253" t="s">
+      <c r="C3" s="251" t="s">
         <v>369</v>
       </c>
-      <c r="D3" s="254"/>
-      <c r="F3" s="255" t="s">
+      <c r="D3" s="252"/>
+      <c r="F3" s="253" t="s">
         <v>370</v>
       </c>
-      <c r="G3" s="254"/>
+      <c r="G3" s="252"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -35541,19 +35515,19 @@
       <c r="B7" s="230" t="s">
         <v>371</v>
       </c>
-      <c r="C7" s="251">
+      <c r="C7" s="254">
         <f>Statement!AA88</f>
         <v>-0.13037640275448081</v>
       </c>
-      <c r="D7" s="252"/>
-      <c r="F7" s="251">
+      <c r="D7" s="255"/>
+      <c r="F7" s="254">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.17317398716855847</v>
       </c>
-      <c r="G7" s="252"/>
+      <c r="G7" s="255"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="231" t="s">
@@ -35580,19 +35554,19 @@
       <c r="B9" s="230" t="s">
         <v>371</v>
       </c>
-      <c r="C9" s="251">
+      <c r="C9" s="254">
         <f>Statement!AA89</f>
         <v>4.0481504023804696E-2</v>
       </c>
-      <c r="D9" s="252"/>
-      <c r="F9" s="251">
+      <c r="D9" s="255"/>
+      <c r="F9" s="254">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.20469173309112548</v>
       </c>
-      <c r="G9" s="252"/>
+      <c r="G9" s="255"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="231" t="s">
@@ -35619,19 +35593,19 @@
       <c r="B11" s="230" t="s">
         <v>371</v>
       </c>
-      <c r="C11" s="251">
+      <c r="C11" s="254">
         <f>Statement!AA90</f>
         <v>-0.1614010786596328</v>
       </c>
-      <c r="D11" s="252"/>
-      <c r="F11" s="251">
+      <c r="D11" s="255"/>
+      <c r="F11" s="254">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.16629948047423376</v>
       </c>
-      <c r="G11" s="252"/>
+      <c r="G11" s="255"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="231" t="s">
@@ -35658,19 +35632,19 @@
       <c r="B13" s="230" t="s">
         <v>371</v>
       </c>
-      <c r="C13" s="251">
+      <c r="C13" s="254">
         <f>Statement!AA94</f>
         <v>-4.1051008608505718E-2</v>
       </c>
-      <c r="D13" s="252"/>
-      <c r="F13" s="251">
+      <c r="D13" s="255"/>
+      <c r="F13" s="254">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>1.3868988514743887E-2</v>
       </c>
-      <c r="G13" s="252"/>
+      <c r="G13" s="255"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="231" t="s">
@@ -35697,19 +35671,19 @@
       <c r="B15" s="230" t="s">
         <v>371</v>
       </c>
-      <c r="C15" s="251">
+      <c r="C15" s="254">
         <f>Statement!AA95</f>
         <v>-0.65140871384799337</v>
       </c>
-      <c r="D15" s="252"/>
-      <c r="F15" s="251">
+      <c r="D15" s="255"/>
+      <c r="F15" s="254">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>2.7052766268583963</v>
       </c>
-      <c r="G15" s="252"/>
+      <c r="G15" s="255"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="231" t="s">
@@ -35736,19 +35710,19 @@
       <c r="B17" s="230" t="s">
         <v>371</v>
       </c>
-      <c r="C17" s="251">
+      <c r="C17" s="254">
         <f>Statement!AA97</f>
         <v>-0.78437135034749483</v>
       </c>
-      <c r="D17" s="252"/>
-      <c r="F17" s="251">
+      <c r="D17" s="255"/>
+      <c r="F17" s="254">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>1.9986699179782754</v>
       </c>
-      <c r="G17" s="252"/>
+      <c r="G17" s="255"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="231" t="s">
@@ -35775,22 +35749,22 @@
       <c r="B19" s="230" t="s">
         <v>371</v>
       </c>
-      <c r="C19" s="251">
+      <c r="C19" s="254">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-3.2031015030699599E-2</v>
       </c>
-      <c r="D19" s="252"/>
-      <c r="F19" s="251">
+      <c r="D19" s="255"/>
+      <c r="F19" s="254">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-3.7620498458385526E-2</v>
       </c>
-      <c r="G19" s="252"/>
+      <c r="G19" s="255"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="231" t="s">
@@ -35817,22 +35791,22 @@
       <c r="B21" s="230" t="s">
         <v>371</v>
       </c>
-      <c r="C21" s="251">
+      <c r="C21" s="254">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>-0.78947368421052633</v>
       </c>
-      <c r="D21" s="252"/>
-      <c r="F21" s="251">
+      <c r="D21" s="255"/>
+      <c r="F21" s="254">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>2</v>
       </c>
-      <c r="G21" s="252"/>
+      <c r="G21" s="255"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -35880,22 +35854,22 @@
       <c r="B25" s="230" t="s">
         <v>371</v>
       </c>
-      <c r="C25" s="251">
+      <c r="C25" s="254">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>-0.30844727286201273</v>
       </c>
-      <c r="D25" s="252"/>
-      <c r="F25" s="251">
+      <c r="D25" s="255"/>
+      <c r="F25" s="254">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.16387602700216702</v>
       </c>
-      <c r="G25" s="252"/>
+      <c r="G25" s="255"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="s">
@@ -35922,22 +35896,22 @@
       <c r="B27" s="230" t="s">
         <v>371</v>
       </c>
-      <c r="C27" s="251">
+      <c r="C27" s="254">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>6.6472159310281692E-3</v>
       </c>
-      <c r="D27" s="252"/>
-      <c r="F27" s="251">
+      <c r="D27" s="255"/>
+      <c r="F27" s="254">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.16382654634312457</v>
       </c>
-      <c r="G27" s="252"/>
+      <c r="G27" s="255"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
@@ -35964,22 +35938,22 @@
       <c r="B29" s="230" t="s">
         <v>371</v>
       </c>
-      <c r="C29" s="251">
+      <c r="C29" s="254">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.15748031496062992</v>
       </c>
-      <c r="D29" s="252"/>
-      <c r="F29" s="251">
+      <c r="D29" s="255"/>
+      <c r="F29" s="254">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>0.46533756230176709</v>
       </c>
-      <c r="G29" s="252"/>
+      <c r="G29" s="255"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B31" s="8" t="s">
@@ -36027,22 +36001,22 @@
       <c r="B33" s="230" t="s">
         <v>371</v>
       </c>
-      <c r="C33" s="251">
+      <c r="C33" s="254">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>2.6257619832373135E-2</v>
       </c>
-      <c r="D33" s="252"/>
-      <c r="F33" s="251">
+      <c r="D33" s="255"/>
+      <c r="F33" s="254">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>0.12319376989075922</v>
       </c>
-      <c r="G33" s="252"/>
+      <c r="G33" s="255"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B34" s="20" t="s">
@@ -36069,43 +36043,25 @@
       <c r="B35" s="230" t="s">
         <v>371</v>
       </c>
-      <c r="C35" s="251">
+      <c r="C35" s="254">
         <f>IF(C34=0,
 IF(D34=0,0,IF(D34&gt;0,1,-1)),
 (D34-C34)/ABS(C34)
 )</f>
         <v>2.3001949317738791E-2</v>
       </c>
-      <c r="D35" s="252"/>
-      <c r="F35" s="251">
+      <c r="D35" s="255"/>
+      <c r="F35" s="254">
         <f>IF(F34=0,
 IF(G34=0,0,IF(G34&gt;0,1,-1)),
 (G34-F34)/ABS(F34)
 )</f>
         <v>0.10951374207188161</v>
       </c>
-      <c r="G35" s="252"/>
+      <c r="G35" s="255"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="F33:G33"/>
     <mergeCell ref="C35:D35"/>
@@ -36116,6 +36072,24 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/PATH.xlsx
+++ b/PATH.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A13A6C25-1A2C-1A48-86F3-535B1F0BFD4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5A82C00-2994-1C4D-82BE-4E1A9E2DE9E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="4" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -2343,6 +2343,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2355,6 +2358,12 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2364,10 +2373,10 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2377,12 +2386,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2395,9 +2398,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -11785,11 +11785,11 @@
     <v>Powered by Refinitiv</v>
     <v>19.84</v>
     <v>9.2002000000000006</v>
-    <v>0.96489999999999998</v>
-    <v>-0.51</v>
-    <v>-4.1871999999999999E-2</v>
-    <v>-0.2326</v>
-    <v>-1.9931000000000001E-2</v>
+    <v>0.96460000000000001</v>
+    <v>-0.43</v>
+    <v>-3.6846999999999998E-2</v>
+    <v>-0.11</v>
+    <v>-9.7859999999999996E-3</v>
     <v>USD</v>
     <v>UiPath, Inc. is focused on agentic automation and orchestration, empowering enterprises to harness the full potential of AI agents to autonomously execute and optimize complex business processes. It is focused on building and managing automations, starting with computer vision technology and user interface automation in its initial robotic process automation offering. Its AI-powered UiPath Platform offers a robust set of capabilities that allows its customers to discover opportunities for automation, automate using a digital workforce that seamlessly collaborates with humans, and operate a mission-critical automation program at scale. It enables employees to quickly build automations for both existing and new processes and to automate a range of actions including logging into applications, moving folders, filling in forms, reading emails and others. Its platform allows users to design and combine UI automations, API integrations and AI-based document understanding in a single workflow.</v>
     <v>3981</v>
@@ -11797,25 +11797,25 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>One Vanderbilt Avenue, 60th Floor, NEW YORK, NY, 10017 US</v>
-    <v>12.24</v>
+    <v>11.94</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46176.925320381248</v>
+    <v>46178.999919571092</v>
     <v>0</v>
-    <v>11.51</v>
-    <v>6073574478</v>
+    <v>11.045</v>
+    <v>5823672172</v>
     <v>UIPATH, INC.</v>
     <v>UIPATH, INC.</v>
-    <v>12.18</v>
-    <v>19.398299999999999</v>
-    <v>12.18</v>
+    <v>11.64</v>
+    <v>19.3992</v>
     <v>11.67</v>
-    <v>11.4374</v>
-    <v>520443400</v>
+    <v>11.24</v>
+    <v>11.13</v>
+    <v>518120300</v>
     <v>PATH</v>
     <v>UIPATH, INC. (XNYS:PATH)</v>
-    <v>33612307</v>
-    <v>39411001</v>
+    <v>35568433</v>
+    <v>40933553</v>
     <v>2015</v>
   </rv>
   <rv s="2">
@@ -11839,17 +11839,17 @@
     <v>Powered by Refinitiv</v>
     <v>46.87</v>
     <v>39.47</v>
-    <v>-0.2</v>
-    <v>-4.4689999999999999E-3</v>
+    <v>0.59</v>
+    <v>1.3178E-2</v>
     <v>US</v>
-    <v>44.63</v>
+    <v>45.54</v>
     <v>Index</v>
     <v>3</v>
-    <v>44.28</v>
+    <v>44.65</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>44.3</v>
-    <v>44.75</v>
-    <v>44.55</v>
+    <v>44.67</v>
+    <v>44.77</v>
+    <v>45.36</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -12071,9 +12071,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq Last Sale</v>
+      <v>Source: Nasdaq</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>Delayed 15 minutes</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -12650,18 +12650,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="248" t="s">
+      <c r="B2" s="249" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="249"/>
-      <c r="E2" s="248" t="s">
+      <c r="C2" s="250"/>
+      <c r="E2" s="249" t="s">
         <v>340</v>
       </c>
-      <c r="F2" s="249"/>
-      <c r="H2" s="248" t="s">
+      <c r="F2" s="250"/>
+      <c r="H2" s="249" t="s">
         <v>385</v>
       </c>
-      <c r="I2" s="249"/>
+      <c r="I2" s="250"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="209" t="s">
@@ -12676,7 +12676,7 @@
       </c>
       <c r="F3" s="211">
         <f ca="1">Statement!AC170</f>
-        <v>6163580.5199999996</v>
+        <v>5936473.4400000004</v>
       </c>
       <c r="H3" s="209" t="str">
         <f>'AVG target price'!B5</f>
@@ -12684,7 +12684,7 @@
       </c>
       <c r="I3" s="235">
         <f ca="1">'AVG target price'!C5</f>
-        <v>6.6936952540628525</v>
+        <v>6.6357378047186275</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -12700,7 +12700,7 @@
       </c>
       <c r="F4" s="212">
         <f ca="1">Statement!AC171</f>
-        <v>4856336.5199999996</v>
+        <v>4629229.4400000004</v>
       </c>
       <c r="H4" s="209" t="str">
         <f>'AVG target price'!B6</f>
@@ -12708,7 +12708,7 @@
       </c>
       <c r="I4" s="235">
         <f ca="1">'AVG target price'!C6</f>
-        <v>15.996134440941134</v>
+        <v>15.937709207716596</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -12717,7 +12717,7 @@
       </c>
       <c r="C5" s="232" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>11.67</v>
+        <v>11.24</v>
       </c>
       <c r="E5" s="209" t="s">
         <v>295</v>
@@ -12732,7 +12732,7 @@
       </c>
       <c r="I5" s="235">
         <f ca="1">'AVG target price'!C7</f>
-        <v>16.178217386651543</v>
+        <v>16.119127102841901</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.2">
@@ -12741,14 +12741,14 @@
       </c>
       <c r="C6" s="232" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>11.4374</v>
+        <v>11.13</v>
       </c>
       <c r="E6" s="209" t="s">
         <v>289</v>
       </c>
       <c r="F6" s="214">
         <f ca="1">Statement!AC167</f>
-        <v>19.449999999999996</v>
+        <v>18.733333333333331</v>
       </c>
       <c r="H6" s="209" t="str">
         <f>'AVG target price'!B8</f>
@@ -12756,7 +12756,7 @@
       </c>
       <c r="I6" s="235">
         <f ca="1">'AVG target price'!C8</f>
-        <v>10.12254584609968</v>
+        <v>10.085573657345705</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -12765,14 +12765,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-0.51</v>
+        <v>-0.43</v>
       </c>
       <c r="E7" s="210" t="s">
         <v>243</v>
       </c>
       <c r="F7" s="215">
         <f ca="1">Statement!AC168</f>
-        <v>3.7595263718883234</v>
+        <v>3.6210005501306561</v>
       </c>
       <c r="H7" s="208" t="str">
         <f>'AVG target price'!B9</f>
@@ -12780,7 +12780,7 @@
       </c>
       <c r="I7" s="236">
         <f ca="1">'AVG target price'!C9</f>
-        <v>12.247648231938804</v>
+        <v>12.194536943155708</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -12789,14 +12789,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-0.2326</v>
+        <v>-0.11</v>
       </c>
       <c r="E8" s="209" t="s">
         <v>317</v>
       </c>
       <c r="F8" s="216">
         <f ca="1">Statement!AC178</f>
-        <v>1.7458845495864472E-2</v>
+        <v>1.8126755065546118E-2</v>
       </c>
       <c r="H8" s="208" t="str">
         <f>'AVG target price'!B11</f>
@@ -12804,7 +12804,7 @@
       </c>
       <c r="I8" s="237">
         <f ca="1">'AVG target price'!C11</f>
-        <v>4.9498563148140884E-2</v>
+        <v>8.4923215583247988E-2</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -12813,14 +12813,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-4.1871999999999999E-2</v>
+        <v>-3.6846999999999998E-2</v>
       </c>
       <c r="E9" s="209" t="s">
         <v>341</v>
       </c>
       <c r="F9" s="216">
         <f ca="1">Statement!AC179</f>
-        <v>5.1413881748071988E-2</v>
+        <v>5.3380782918149475E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -12829,14 +12829,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-1.9931000000000001E-2</v>
+        <v>-9.7859999999999996E-3</v>
       </c>
       <c r="E10" s="209" t="s">
         <v>346</v>
       </c>
       <c r="F10" s="216">
         <f ca="1">Statement!AC181</f>
-        <v>5.6034312990527788E-2</v>
+        <v>5.8177974430556868E-2</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -12877,7 +12877,7 @@
       </c>
       <c r="C13" s="233" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>0.96489999999999998</v>
+        <v>0.96460000000000001</v>
       </c>
       <c r="E13" s="209" t="s">
         <v>123</v>
@@ -12893,7 +12893,7 @@
       </c>
       <c r="C14" s="234" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>39411001</v>
+        <v>40933553</v>
       </c>
       <c r="E14" s="210" t="s">
         <v>124</v>
@@ -12909,7 +12909,7 @@
       </c>
       <c r="F15" s="216">
         <f ca="1">Statement!AC192</f>
-        <v>0.21209165610121697</v>
+        <v>0.22020548280259802</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -12922,10 +12922,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="250" t="s">
+      <c r="B17" s="251" t="s">
         <v>103</v>
       </c>
-      <c r="C17" s="250"/>
+      <c r="C17" s="251"/>
       <c r="E17" s="208" t="s">
         <v>349</v>
       </c>
@@ -12998,14 +12998,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="250" t="s">
+      <c r="B25" s="251" t="s">
         <v>126</v>
       </c>
-      <c r="C25" s="250"/>
-      <c r="E25" s="248" t="s">
+      <c r="C25" s="251"/>
+      <c r="E25" s="249" t="s">
         <v>405</v>
       </c>
-      <c r="F25" s="249"/>
+      <c r="F25" s="250"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="208" t="s">
@@ -13019,14 +13019,14 @@
       </c>
       <c r="F26" s="245" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>44.55</v>
+        <v>45.36</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B27" s="208" t="s">
         <v>214</v>
       </c>
-      <c r="C27" s="265">
+      <c r="C27" s="247">
         <v>0</v>
       </c>
       <c r="E27" s="210" t="s">
@@ -13034,19 +13034,19 @@
       </c>
       <c r="F27" s="246">
         <f ca="1">F26/1000</f>
-        <v>4.4549999999999999E-2</v>
+        <v>4.5359999999999998E-2</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B31" s="247" t="s">
+      <c r="B31" s="248" t="s">
         <v>395</v>
       </c>
-      <c r="C31" s="247"/>
-      <c r="D31" s="247"/>
-      <c r="E31" s="247"/>
-      <c r="F31" s="247"/>
-      <c r="G31" s="247"/>
-      <c r="H31" s="247"/>
+      <c r="C31" s="248"/>
+      <c r="D31" s="248"/>
+      <c r="E31" s="248"/>
+      <c r="F31" s="248"/>
+      <c r="G31" s="248"/>
+      <c r="H31" s="248"/>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B33" s="16" t="s">
@@ -13065,24 +13065,24 @@
       </c>
     </row>
     <row r="37" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B37" s="247"/>
-      <c r="C37" s="247"/>
-      <c r="D37" s="247"/>
-      <c r="E37" s="247"/>
-      <c r="F37" s="247"/>
-      <c r="G37" s="247"/>
-      <c r="H37" s="247"/>
+      <c r="B37" s="248"/>
+      <c r="C37" s="248"/>
+      <c r="D37" s="248"/>
+      <c r="E37" s="248"/>
+      <c r="F37" s="248"/>
+      <c r="G37" s="248"/>
+      <c r="H37" s="248"/>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B40" s="247" t="s">
+      <c r="B40" s="248" t="s">
         <v>398</v>
       </c>
-      <c r="C40" s="247"/>
-      <c r="D40" s="247"/>
-      <c r="E40" s="247"/>
-      <c r="F40" s="247"/>
-      <c r="G40" s="247"/>
-      <c r="H40" s="247"/>
+      <c r="C40" s="248"/>
+      <c r="D40" s="248"/>
+      <c r="E40" s="248"/>
+      <c r="F40" s="248"/>
+      <c r="G40" s="248"/>
+      <c r="H40" s="248"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B42" s="41" t="s">
@@ -13097,13 +13097,13 @@
       <c r="E42" s="243"/>
     </row>
     <row r="47" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B47" s="247"/>
-      <c r="C47" s="247"/>
-      <c r="D47" s="247"/>
-      <c r="E47" s="247"/>
-      <c r="F47" s="247"/>
-      <c r="G47" s="247"/>
-      <c r="H47" s="247"/>
+      <c r="B47" s="248"/>
+      <c r="C47" s="248"/>
+      <c r="D47" s="248"/>
+      <c r="E47" s="248"/>
+      <c r="F47" s="248"/>
+      <c r="G47" s="248"/>
+      <c r="H47" s="248"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -13186,36 +13186,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="247" t="s">
+      <c r="C2" s="248" t="s">
         <v>137</v>
       </c>
-      <c r="D2" s="247"/>
-      <c r="E2" s="247"/>
-      <c r="F2" s="247"/>
-      <c r="G2" s="259"/>
-      <c r="H2" s="260" t="s">
+      <c r="D2" s="248"/>
+      <c r="E2" s="248"/>
+      <c r="F2" s="248"/>
+      <c r="G2" s="257"/>
+      <c r="H2" s="258" t="s">
         <v>138</v>
       </c>
-      <c r="I2" s="247"/>
-      <c r="J2" s="247"/>
-      <c r="K2" s="247"/>
-      <c r="L2" s="247"/>
+      <c r="I2" s="248"/>
+      <c r="J2" s="248"/>
+      <c r="K2" s="248"/>
+      <c r="L2" s="248"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="247" t="s">
+      <c r="S2" s="248" t="s">
         <v>137</v>
       </c>
-      <c r="T2" s="247"/>
-      <c r="U2" s="247"/>
-      <c r="V2" s="247"/>
-      <c r="W2" s="247"/>
-      <c r="X2" s="247"/>
-      <c r="Y2" s="247"/>
-      <c r="Z2" s="247"/>
-      <c r="AA2" s="247" t="s">
+      <c r="T2" s="248"/>
+      <c r="U2" s="248"/>
+      <c r="V2" s="248"/>
+      <c r="W2" s="248"/>
+      <c r="X2" s="248"/>
+      <c r="Y2" s="248"/>
+      <c r="Z2" s="248"/>
+      <c r="AA2" s="248" t="s">
         <v>138</v>
       </c>
-      <c r="AB2" s="247"/>
-      <c r="AC2" s="247"/>
+      <c r="AB2" s="248"/>
+      <c r="AC2" s="248"/>
       <c r="AE2" s="87" t="s">
         <v>139</v>
       </c>
@@ -13226,32 +13226,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="256" t="s">
+      <c r="C4" s="259" t="s">
         <v>140</v>
       </c>
-      <c r="D4" s="256"/>
-      <c r="E4" s="256"/>
-      <c r="F4" s="256"/>
-      <c r="G4" s="256"/>
-      <c r="H4" s="256"/>
-      <c r="I4" s="256"/>
-      <c r="J4" s="256"/>
-      <c r="K4" s="256"/>
-      <c r="L4" s="256"/>
+      <c r="D4" s="259"/>
+      <c r="E4" s="259"/>
+      <c r="F4" s="259"/>
+      <c r="G4" s="259"/>
+      <c r="H4" s="259"/>
+      <c r="I4" s="259"/>
+      <c r="J4" s="259"/>
+      <c r="K4" s="259"/>
+      <c r="L4" s="259"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="257" t="s">
+      <c r="S4" s="260" t="s">
         <v>140</v>
       </c>
-      <c r="T4" s="258"/>
-      <c r="U4" s="258"/>
-      <c r="V4" s="258"/>
-      <c r="W4" s="258"/>
-      <c r="X4" s="258"/>
-      <c r="Y4" s="258"/>
-      <c r="Z4" s="258"/>
-      <c r="AA4" s="258"/>
-      <c r="AB4" s="258"/>
-      <c r="AC4" s="258"/>
+      <c r="T4" s="261"/>
+      <c r="U4" s="261"/>
+      <c r="V4" s="261"/>
+      <c r="W4" s="261"/>
+      <c r="X4" s="261"/>
+      <c r="Y4" s="261"/>
+      <c r="Z4" s="261"/>
+      <c r="AA4" s="261"/>
+      <c r="AB4" s="261"/>
+      <c r="AC4" s="261"/>
       <c r="AE4" s="89"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -13747,33 +13747,33 @@
       <c r="Q10" s="93"/>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C11" s="256" t="s">
+      <c r="C11" s="259" t="s">
         <v>146</v>
       </c>
-      <c r="D11" s="256"/>
-      <c r="E11" s="256"/>
-      <c r="F11" s="256"/>
-      <c r="G11" s="256"/>
-      <c r="H11" s="256"/>
-      <c r="I11" s="256"/>
-      <c r="J11" s="256"/>
-      <c r="K11" s="256"/>
-      <c r="L11" s="256"/>
+      <c r="D11" s="259"/>
+      <c r="E11" s="259"/>
+      <c r="F11" s="259"/>
+      <c r="G11" s="259"/>
+      <c r="H11" s="259"/>
+      <c r="I11" s="259"/>
+      <c r="J11" s="259"/>
+      <c r="K11" s="259"/>
+      <c r="L11" s="259"/>
       <c r="O11" s="5"/>
       <c r="Q11" s="93"/>
-      <c r="S11" s="257" t="s">
+      <c r="S11" s="260" t="s">
         <v>146</v>
       </c>
-      <c r="T11" s="258"/>
-      <c r="U11" s="258"/>
-      <c r="V11" s="258"/>
-      <c r="W11" s="258"/>
-      <c r="X11" s="258"/>
-      <c r="Y11" s="258"/>
-      <c r="Z11" s="258"/>
-      <c r="AA11" s="258"/>
-      <c r="AB11" s="258"/>
-      <c r="AC11" s="258"/>
+      <c r="T11" s="261"/>
+      <c r="U11" s="261"/>
+      <c r="V11" s="261"/>
+      <c r="W11" s="261"/>
+      <c r="X11" s="261"/>
+      <c r="Y11" s="261"/>
+      <c r="Z11" s="261"/>
+      <c r="AA11" s="261"/>
+      <c r="AB11" s="261"/>
+      <c r="AC11" s="261"/>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B12" s="16" t="s">
@@ -14214,33 +14214,33 @@
       <c r="Q18" s="93"/>
     </row>
     <row r="19" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C19" s="256" t="s">
+      <c r="C19" s="259" t="s">
         <v>148</v>
       </c>
-      <c r="D19" s="256"/>
-      <c r="E19" s="256"/>
-      <c r="F19" s="256"/>
-      <c r="G19" s="256"/>
-      <c r="H19" s="256"/>
-      <c r="I19" s="256"/>
-      <c r="J19" s="256"/>
-      <c r="K19" s="256"/>
-      <c r="L19" s="256"/>
+      <c r="D19" s="259"/>
+      <c r="E19" s="259"/>
+      <c r="F19" s="259"/>
+      <c r="G19" s="259"/>
+      <c r="H19" s="259"/>
+      <c r="I19" s="259"/>
+      <c r="J19" s="259"/>
+      <c r="K19" s="259"/>
+      <c r="L19" s="259"/>
       <c r="O19" s="5"/>
       <c r="Q19" s="93"/>
-      <c r="S19" s="257" t="s">
+      <c r="S19" s="260" t="s">
         <v>148</v>
       </c>
-      <c r="T19" s="258"/>
-      <c r="U19" s="258"/>
-      <c r="V19" s="258"/>
-      <c r="W19" s="258"/>
-      <c r="X19" s="258"/>
-      <c r="Y19" s="258"/>
-      <c r="Z19" s="258"/>
-      <c r="AA19" s="258"/>
-      <c r="AB19" s="258"/>
-      <c r="AC19" s="258"/>
+      <c r="T19" s="261"/>
+      <c r="U19" s="261"/>
+      <c r="V19" s="261"/>
+      <c r="W19" s="261"/>
+      <c r="X19" s="261"/>
+      <c r="Y19" s="261"/>
+      <c r="Z19" s="261"/>
+      <c r="AA19" s="261"/>
+      <c r="AB19" s="261"/>
+      <c r="AC19" s="261"/>
       <c r="AE19" s="89">
         <f>AE4</f>
         <v>0</v>
@@ -15058,32 +15058,32 @@
       <c r="O31" s="5"/>
     </row>
     <row r="32" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C32" s="256" t="s">
+      <c r="C32" s="259" t="s">
         <v>150</v>
       </c>
-      <c r="D32" s="256"/>
-      <c r="E32" s="256"/>
-      <c r="F32" s="256"/>
-      <c r="G32" s="256"/>
-      <c r="H32" s="256"/>
-      <c r="I32" s="256"/>
-      <c r="J32" s="256"/>
-      <c r="K32" s="256"/>
-      <c r="L32" s="256"/>
+      <c r="D32" s="259"/>
+      <c r="E32" s="259"/>
+      <c r="F32" s="259"/>
+      <c r="G32" s="259"/>
+      <c r="H32" s="259"/>
+      <c r="I32" s="259"/>
+      <c r="J32" s="259"/>
+      <c r="K32" s="259"/>
+      <c r="L32" s="259"/>
       <c r="O32" s="5"/>
-      <c r="S32" s="257" t="s">
+      <c r="S32" s="260" t="s">
         <v>150</v>
       </c>
-      <c r="T32" s="258"/>
-      <c r="U32" s="258"/>
-      <c r="V32" s="258"/>
-      <c r="W32" s="258"/>
-      <c r="X32" s="258"/>
-      <c r="Y32" s="258"/>
-      <c r="Z32" s="258"/>
-      <c r="AA32" s="258"/>
-      <c r="AB32" s="258"/>
-      <c r="AC32" s="258"/>
+      <c r="T32" s="261"/>
+      <c r="U32" s="261"/>
+      <c r="V32" s="261"/>
+      <c r="W32" s="261"/>
+      <c r="X32" s="261"/>
+      <c r="Y32" s="261"/>
+      <c r="Z32" s="261"/>
+      <c r="AA32" s="261"/>
+      <c r="AB32" s="261"/>
+      <c r="AC32" s="261"/>
     </row>
     <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B33" s="16" t="s">
@@ -15340,18 +15340,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="C11:L11"/>
+    <mergeCell ref="S11:AC11"/>
+    <mergeCell ref="C19:L19"/>
+    <mergeCell ref="S19:AC19"/>
+    <mergeCell ref="C32:L32"/>
+    <mergeCell ref="S32:AC32"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C11:L11"/>
-    <mergeCell ref="S11:AC11"/>
-    <mergeCell ref="C19:L19"/>
-    <mergeCell ref="S19:AC19"/>
-    <mergeCell ref="C32:L32"/>
-    <mergeCell ref="S32:AC32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -15388,35 +15388,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="247" t="s">
+      <c r="C2" s="248" t="s">
         <v>137</v>
       </c>
-      <c r="D2" s="247"/>
-      <c r="E2" s="247"/>
-      <c r="F2" s="247"/>
-      <c r="G2" s="259"/>
-      <c r="H2" s="260" t="s">
+      <c r="D2" s="248"/>
+      <c r="E2" s="248"/>
+      <c r="F2" s="248"/>
+      <c r="G2" s="257"/>
+      <c r="H2" s="258" t="s">
         <v>138</v>
       </c>
-      <c r="I2" s="247"/>
-      <c r="J2" s="247"/>
-      <c r="K2" s="247"/>
-      <c r="L2" s="247"/>
-      <c r="P2" s="247" t="s">
+      <c r="I2" s="248"/>
+      <c r="J2" s="248"/>
+      <c r="K2" s="248"/>
+      <c r="L2" s="248"/>
+      <c r="P2" s="248" t="s">
         <v>137</v>
       </c>
-      <c r="Q2" s="247"/>
-      <c r="R2" s="247"/>
-      <c r="S2" s="247"/>
-      <c r="T2" s="247"/>
-      <c r="U2" s="247"/>
-      <c r="V2" s="247"/>
-      <c r="W2" s="247"/>
-      <c r="X2" s="247" t="s">
+      <c r="Q2" s="248"/>
+      <c r="R2" s="248"/>
+      <c r="S2" s="248"/>
+      <c r="T2" s="248"/>
+      <c r="U2" s="248"/>
+      <c r="V2" s="248"/>
+      <c r="W2" s="248"/>
+      <c r="X2" s="248" t="s">
         <v>138</v>
       </c>
-      <c r="Y2" s="247"/>
-      <c r="Z2" s="247"/>
+      <c r="Y2" s="248"/>
+      <c r="Z2" s="248"/>
       <c r="AB2" s="87" t="s">
         <v>139</v>
       </c>
@@ -15425,31 +15425,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="256" t="s">
+      <c r="C4" s="259" t="s">
         <v>140</v>
       </c>
-      <c r="D4" s="256"/>
-      <c r="E4" s="256"/>
-      <c r="F4" s="256"/>
-      <c r="G4" s="256"/>
-      <c r="H4" s="256"/>
-      <c r="I4" s="256"/>
-      <c r="J4" s="256"/>
-      <c r="K4" s="256"/>
-      <c r="L4" s="256"/>
-      <c r="P4" s="258" t="s">
+      <c r="D4" s="259"/>
+      <c r="E4" s="259"/>
+      <c r="F4" s="259"/>
+      <c r="G4" s="259"/>
+      <c r="H4" s="259"/>
+      <c r="I4" s="259"/>
+      <c r="J4" s="259"/>
+      <c r="K4" s="259"/>
+      <c r="L4" s="259"/>
+      <c r="P4" s="261" t="s">
         <v>140</v>
       </c>
-      <c r="Q4" s="258"/>
-      <c r="R4" s="258"/>
-      <c r="S4" s="258"/>
-      <c r="T4" s="258"/>
-      <c r="U4" s="258"/>
-      <c r="V4" s="258"/>
-      <c r="W4" s="258"/>
-      <c r="X4" s="258"/>
-      <c r="Y4" s="258"/>
-      <c r="Z4" s="258"/>
+      <c r="Q4" s="261"/>
+      <c r="R4" s="261"/>
+      <c r="S4" s="261"/>
+      <c r="T4" s="261"/>
+      <c r="U4" s="261"/>
+      <c r="V4" s="261"/>
+      <c r="W4" s="261"/>
+      <c r="X4" s="261"/>
+      <c r="Y4" s="261"/>
+      <c r="Z4" s="261"/>
       <c r="AB4" s="89"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -15644,32 +15644,32 @@
       <c r="N8" s="93"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="256" t="s">
+      <c r="C9" s="259" t="s">
         <v>166</v>
       </c>
-      <c r="D9" s="256"/>
-      <c r="E9" s="256"/>
-      <c r="F9" s="256"/>
-      <c r="G9" s="256"/>
-      <c r="H9" s="256"/>
-      <c r="I9" s="256"/>
-      <c r="J9" s="256"/>
-      <c r="K9" s="256"/>
-      <c r="L9" s="256"/>
+      <c r="D9" s="259"/>
+      <c r="E9" s="259"/>
+      <c r="F9" s="259"/>
+      <c r="G9" s="259"/>
+      <c r="H9" s="259"/>
+      <c r="I9" s="259"/>
+      <c r="J9" s="259"/>
+      <c r="K9" s="259"/>
+      <c r="L9" s="259"/>
       <c r="N9" s="93"/>
-      <c r="P9" s="258" t="s">
+      <c r="P9" s="261" t="s">
         <v>167</v>
       </c>
-      <c r="Q9" s="258"/>
-      <c r="R9" s="258"/>
-      <c r="S9" s="258"/>
-      <c r="T9" s="258"/>
-      <c r="U9" s="258"/>
-      <c r="V9" s="258"/>
-      <c r="W9" s="258"/>
-      <c r="X9" s="258"/>
-      <c r="Y9" s="258"/>
-      <c r="Z9" s="258"/>
+      <c r="Q9" s="261"/>
+      <c r="R9" s="261"/>
+      <c r="S9" s="261"/>
+      <c r="T9" s="261"/>
+      <c r="U9" s="261"/>
+      <c r="V9" s="261"/>
+      <c r="W9" s="261"/>
+      <c r="X9" s="261"/>
+      <c r="Y9" s="261"/>
+      <c r="Z9" s="261"/>
       <c r="AB9" s="89">
         <f>AB4</f>
         <v>0</v>
@@ -16518,31 +16518,31 @@
       </c>
     </row>
     <row r="21" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="C21" s="256" t="s">
+      <c r="C21" s="259" t="s">
         <v>169</v>
       </c>
-      <c r="D21" s="256"/>
-      <c r="E21" s="256"/>
-      <c r="F21" s="256"/>
-      <c r="G21" s="256"/>
-      <c r="H21" s="256"/>
-      <c r="I21" s="256"/>
-      <c r="J21" s="256"/>
-      <c r="K21" s="256"/>
-      <c r="L21" s="256"/>
-      <c r="P21" s="258" t="s">
+      <c r="D21" s="259"/>
+      <c r="E21" s="259"/>
+      <c r="F21" s="259"/>
+      <c r="G21" s="259"/>
+      <c r="H21" s="259"/>
+      <c r="I21" s="259"/>
+      <c r="J21" s="259"/>
+      <c r="K21" s="259"/>
+      <c r="L21" s="259"/>
+      <c r="P21" s="261" t="s">
         <v>169</v>
       </c>
-      <c r="Q21" s="258"/>
-      <c r="R21" s="258"/>
-      <c r="S21" s="258"/>
-      <c r="T21" s="258"/>
-      <c r="U21" s="258"/>
-      <c r="V21" s="258"/>
-      <c r="W21" s="258"/>
-      <c r="X21" s="258"/>
-      <c r="Y21" s="258"/>
-      <c r="Z21" s="258"/>
+      <c r="Q21" s="261"/>
+      <c r="R21" s="261"/>
+      <c r="S21" s="261"/>
+      <c r="T21" s="261"/>
+      <c r="U21" s="261"/>
+      <c r="V21" s="261"/>
+      <c r="W21" s="261"/>
+      <c r="X21" s="261"/>
+      <c r="Y21" s="261"/>
+      <c r="Z21" s="261"/>
     </row>
     <row r="22" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B22" s="16" t="s">
@@ -17357,60 +17357,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="247" t="s">
+      <c r="C3" s="248" t="s">
         <v>137</v>
       </c>
-      <c r="D3" s="247"/>
-      <c r="E3" s="247"/>
-      <c r="F3" s="247"/>
-      <c r="G3" s="259"/>
-      <c r="H3" s="260" t="s">
+      <c r="D3" s="248"/>
+      <c r="E3" s="248"/>
+      <c r="F3" s="248"/>
+      <c r="G3" s="257"/>
+      <c r="H3" s="258" t="s">
         <v>138</v>
       </c>
-      <c r="I3" s="247"/>
-      <c r="J3" s="247"/>
-      <c r="K3" s="247"/>
-      <c r="L3" s="247"/>
-      <c r="P3" s="261"/>
-      <c r="Q3" s="261"/>
-      <c r="R3" s="261"/>
-      <c r="S3" s="261"/>
-      <c r="T3" s="261"/>
-      <c r="U3" s="261"/>
-      <c r="V3" s="261"/>
-      <c r="W3" s="261"/>
-      <c r="X3" s="261"/>
-      <c r="Y3" s="261"/>
-      <c r="Z3" s="261"/>
+      <c r="I3" s="248"/>
+      <c r="J3" s="248"/>
+      <c r="K3" s="248"/>
+      <c r="L3" s="248"/>
+      <c r="P3" s="262"/>
+      <c r="Q3" s="262"/>
+      <c r="R3" s="262"/>
+      <c r="S3" s="262"/>
+      <c r="T3" s="262"/>
+      <c r="U3" s="262"/>
+      <c r="V3" s="262"/>
+      <c r="W3" s="262"/>
+      <c r="X3" s="262"/>
+      <c r="Y3" s="262"/>
+      <c r="Z3" s="262"/>
       <c r="AB3" s="130"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="88"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="256" t="s">
+      <c r="C5" s="259" t="s">
         <v>140</v>
       </c>
-      <c r="D5" s="256"/>
-      <c r="E5" s="256"/>
-      <c r="F5" s="256"/>
-      <c r="G5" s="256"/>
-      <c r="H5" s="256"/>
-      <c r="I5" s="256"/>
-      <c r="J5" s="256"/>
-      <c r="K5" s="256"/>
-      <c r="L5" s="256"/>
-      <c r="P5" s="261"/>
-      <c r="Q5" s="261"/>
-      <c r="R5" s="261"/>
-      <c r="S5" s="261"/>
-      <c r="T5" s="261"/>
-      <c r="U5" s="261"/>
-      <c r="V5" s="261"/>
-      <c r="W5" s="261"/>
-      <c r="X5" s="261"/>
-      <c r="Y5" s="261"/>
-      <c r="Z5" s="261"/>
+      <c r="D5" s="259"/>
+      <c r="E5" s="259"/>
+      <c r="F5" s="259"/>
+      <c r="G5" s="259"/>
+      <c r="H5" s="259"/>
+      <c r="I5" s="259"/>
+      <c r="J5" s="259"/>
+      <c r="K5" s="259"/>
+      <c r="L5" s="259"/>
+      <c r="P5" s="262"/>
+      <c r="Q5" s="262"/>
+      <c r="R5" s="262"/>
+      <c r="S5" s="262"/>
+      <c r="T5" s="262"/>
+      <c r="U5" s="262"/>
+      <c r="V5" s="262"/>
+      <c r="W5" s="262"/>
+      <c r="X5" s="262"/>
+      <c r="Y5" s="262"/>
+      <c r="Z5" s="262"/>
       <c r="AB5" s="131"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -17596,30 +17596,30 @@
       <c r="N10" s="93"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="256" t="s">
+      <c r="C11" s="259" t="s">
         <v>173</v>
       </c>
-      <c r="D11" s="256"/>
-      <c r="E11" s="256"/>
-      <c r="F11" s="256"/>
-      <c r="G11" s="256"/>
-      <c r="H11" s="256"/>
-      <c r="I11" s="256"/>
-      <c r="J11" s="256"/>
-      <c r="K11" s="256"/>
-      <c r="L11" s="256"/>
+      <c r="D11" s="259"/>
+      <c r="E11" s="259"/>
+      <c r="F11" s="259"/>
+      <c r="G11" s="259"/>
+      <c r="H11" s="259"/>
+      <c r="I11" s="259"/>
+      <c r="J11" s="259"/>
+      <c r="K11" s="259"/>
+      <c r="L11" s="259"/>
       <c r="N11" s="93"/>
-      <c r="P11" s="261"/>
-      <c r="Q11" s="261"/>
-      <c r="R11" s="261"/>
-      <c r="S11" s="261"/>
-      <c r="T11" s="261"/>
-      <c r="U11" s="261"/>
-      <c r="V11" s="261"/>
-      <c r="W11" s="261"/>
-      <c r="X11" s="261"/>
-      <c r="Y11" s="261"/>
-      <c r="Z11" s="261"/>
+      <c r="P11" s="262"/>
+      <c r="Q11" s="262"/>
+      <c r="R11" s="262"/>
+      <c r="S11" s="262"/>
+      <c r="T11" s="262"/>
+      <c r="U11" s="262"/>
+      <c r="V11" s="262"/>
+      <c r="W11" s="262"/>
+      <c r="X11" s="262"/>
+      <c r="Y11" s="262"/>
+      <c r="Z11" s="262"/>
       <c r="AB11" s="131"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -17861,18 +17861,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="256" t="s">
+      <c r="C18" s="259" t="s">
         <v>178</v>
       </c>
-      <c r="D18" s="256"/>
-      <c r="E18" s="256"/>
-      <c r="F18" s="256"/>
-      <c r="G18" s="256"/>
-      <c r="H18" s="256"/>
-      <c r="I18" s="256"/>
-      <c r="J18" s="256"/>
-      <c r="K18" s="256"/>
-      <c r="L18" s="256"/>
+      <c r="D18" s="259"/>
+      <c r="E18" s="259"/>
+      <c r="F18" s="259"/>
+      <c r="G18" s="259"/>
+      <c r="H18" s="259"/>
+      <c r="I18" s="259"/>
+      <c r="J18" s="259"/>
+      <c r="K18" s="259"/>
+      <c r="L18" s="259"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -18085,23 +18085,23 @@
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="261"/>
-      <c r="C25" s="261"/>
+      <c r="B25" s="262"/>
+      <c r="C25" s="262"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="130"/>
-      <c r="C26" s="256" t="s">
+      <c r="C26" s="259" t="s">
         <v>184</v>
       </c>
-      <c r="D26" s="256"/>
-      <c r="E26" s="256"/>
-      <c r="F26" s="256"/>
-      <c r="G26" s="256"/>
-      <c r="H26" s="256"/>
-      <c r="I26" s="256"/>
-      <c r="J26" s="256"/>
-      <c r="K26" s="256"/>
-      <c r="L26" s="256"/>
+      <c r="D26" s="259"/>
+      <c r="E26" s="259"/>
+      <c r="F26" s="259"/>
+      <c r="G26" s="259"/>
+      <c r="H26" s="259"/>
+      <c r="I26" s="259"/>
+      <c r="J26" s="259"/>
+      <c r="K26" s="259"/>
+      <c r="L26" s="259"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -18293,18 +18293,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="130"/>
-      <c r="C33" s="256" t="s">
+      <c r="C33" s="259" t="s">
         <v>188</v>
       </c>
-      <c r="D33" s="256"/>
-      <c r="E33" s="256"/>
-      <c r="F33" s="256"/>
-      <c r="G33" s="256"/>
-      <c r="H33" s="256"/>
-      <c r="I33" s="256"/>
-      <c r="J33" s="256"/>
-      <c r="K33" s="256"/>
-      <c r="L33" s="256"/>
+      <c r="D33" s="259"/>
+      <c r="E33" s="259"/>
+      <c r="F33" s="259"/>
+      <c r="G33" s="259"/>
+      <c r="H33" s="259"/>
+      <c r="I33" s="259"/>
+      <c r="J33" s="259"/>
+      <c r="K33" s="259"/>
+      <c r="L33" s="259"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -18488,18 +18488,18 @@
       <c r="C39" s="146"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="256" t="s">
+      <c r="C40" s="259" t="s">
         <v>191</v>
       </c>
-      <c r="D40" s="256"/>
-      <c r="E40" s="256"/>
-      <c r="F40" s="256"/>
-      <c r="G40" s="256"/>
-      <c r="H40" s="256"/>
-      <c r="I40" s="256"/>
-      <c r="J40" s="256"/>
-      <c r="K40" s="256"/>
-      <c r="L40" s="256"/>
+      <c r="D40" s="259"/>
+      <c r="E40" s="259"/>
+      <c r="F40" s="259"/>
+      <c r="G40" s="259"/>
+      <c r="H40" s="259"/>
+      <c r="I40" s="259"/>
+      <c r="J40" s="259"/>
+      <c r="K40" s="259"/>
+      <c r="L40" s="259"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -18763,6 +18763,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18770,12 +18776,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -18813,60 +18813,60 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="247" t="s">
+      <c r="C2" s="248" t="s">
         <v>137</v>
       </c>
-      <c r="D2" s="247"/>
-      <c r="E2" s="247"/>
-      <c r="F2" s="247"/>
-      <c r="G2" s="259"/>
-      <c r="H2" s="260" t="s">
+      <c r="D2" s="248"/>
+      <c r="E2" s="248"/>
+      <c r="F2" s="248"/>
+      <c r="G2" s="257"/>
+      <c r="H2" s="258" t="s">
         <v>138</v>
       </c>
-      <c r="I2" s="247"/>
-      <c r="J2" s="247"/>
-      <c r="K2" s="247"/>
-      <c r="L2" s="247"/>
-      <c r="S2" s="261"/>
-      <c r="T2" s="261"/>
-      <c r="U2" s="261"/>
-      <c r="V2" s="261"/>
-      <c r="W2" s="261"/>
-      <c r="X2" s="261"/>
-      <c r="Y2" s="261"/>
-      <c r="Z2" s="261"/>
-      <c r="AA2" s="261"/>
-      <c r="AB2" s="261"/>
-      <c r="AC2" s="261"/>
+      <c r="I2" s="248"/>
+      <c r="J2" s="248"/>
+      <c r="K2" s="248"/>
+      <c r="L2" s="248"/>
+      <c r="S2" s="262"/>
+      <c r="T2" s="262"/>
+      <c r="U2" s="262"/>
+      <c r="V2" s="262"/>
+      <c r="W2" s="262"/>
+      <c r="X2" s="262"/>
+      <c r="Y2" s="262"/>
+      <c r="Z2" s="262"/>
+      <c r="AA2" s="262"/>
+      <c r="AB2" s="262"/>
+      <c r="AC2" s="262"/>
       <c r="AE2" s="130"/>
     </row>
     <row r="3" spans="1:31" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="256" t="s">
+      <c r="C4" s="259" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="256"/>
-      <c r="E4" s="256"/>
-      <c r="F4" s="256"/>
-      <c r="G4" s="256"/>
-      <c r="H4" s="256"/>
-      <c r="I4" s="256"/>
-      <c r="J4" s="256"/>
-      <c r="K4" s="256"/>
-      <c r="L4" s="256"/>
-      <c r="S4" s="261"/>
-      <c r="T4" s="261"/>
-      <c r="U4" s="261"/>
-      <c r="V4" s="261"/>
-      <c r="W4" s="261"/>
-      <c r="X4" s="261"/>
-      <c r="Y4" s="261"/>
-      <c r="Z4" s="261"/>
-      <c r="AA4" s="261"/>
-      <c r="AB4" s="261"/>
-      <c r="AC4" s="261"/>
+      <c r="D4" s="259"/>
+      <c r="E4" s="259"/>
+      <c r="F4" s="259"/>
+      <c r="G4" s="259"/>
+      <c r="H4" s="259"/>
+      <c r="I4" s="259"/>
+      <c r="J4" s="259"/>
+      <c r="K4" s="259"/>
+      <c r="L4" s="259"/>
+      <c r="S4" s="262"/>
+      <c r="T4" s="262"/>
+      <c r="U4" s="262"/>
+      <c r="V4" s="262"/>
+      <c r="W4" s="262"/>
+      <c r="X4" s="262"/>
+      <c r="Y4" s="262"/>
+      <c r="Z4" s="262"/>
+      <c r="AA4" s="262"/>
+      <c r="AB4" s="262"/>
+      <c r="AC4" s="262"/>
       <c r="AE4" s="131"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -19229,18 +19229,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="256" t="s">
+      <c r="C13" s="259" t="s">
         <v>199</v>
       </c>
-      <c r="D13" s="256"/>
-      <c r="E13" s="256"/>
-      <c r="F13" s="256"/>
-      <c r="G13" s="256"/>
-      <c r="H13" s="256"/>
-      <c r="I13" s="256"/>
-      <c r="J13" s="256"/>
-      <c r="K13" s="256"/>
-      <c r="L13" s="256"/>
+      <c r="D13" s="259"/>
+      <c r="E13" s="259"/>
+      <c r="F13" s="259"/>
+      <c r="G13" s="259"/>
+      <c r="H13" s="259"/>
+      <c r="I13" s="259"/>
+      <c r="J13" s="259"/>
+      <c r="K13" s="259"/>
+      <c r="L13" s="259"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -19333,18 +19333,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="256" t="s">
+      <c r="C18" s="259" t="s">
         <v>200</v>
       </c>
-      <c r="D18" s="256"/>
-      <c r="E18" s="256"/>
-      <c r="F18" s="256"/>
-      <c r="G18" s="256"/>
-      <c r="H18" s="256"/>
-      <c r="I18" s="256"/>
-      <c r="J18" s="256"/>
-      <c r="K18" s="256"/>
-      <c r="L18" s="256"/>
+      <c r="D18" s="259"/>
+      <c r="E18" s="259"/>
+      <c r="F18" s="259"/>
+      <c r="G18" s="259"/>
+      <c r="H18" s="259"/>
+      <c r="I18" s="259"/>
+      <c r="J18" s="259"/>
+      <c r="K18" s="259"/>
+      <c r="L18" s="259"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19536,18 +19536,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="256" t="s">
+      <c r="C25" s="259" t="s">
         <v>203</v>
       </c>
-      <c r="D25" s="256"/>
-      <c r="E25" s="256"/>
-      <c r="F25" s="256"/>
-      <c r="G25" s="256"/>
-      <c r="H25" s="256"/>
-      <c r="I25" s="256"/>
-      <c r="J25" s="256"/>
-      <c r="K25" s="256"/>
-      <c r="L25" s="256"/>
+      <c r="D25" s="259"/>
+      <c r="E25" s="259"/>
+      <c r="F25" s="259"/>
+      <c r="G25" s="259"/>
+      <c r="H25" s="259"/>
+      <c r="I25" s="259"/>
+      <c r="J25" s="259"/>
+      <c r="K25" s="259"/>
+      <c r="L25" s="259"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -19685,18 +19685,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="256" t="s">
+      <c r="C31" s="259" t="s">
         <v>78</v>
       </c>
-      <c r="D31" s="256"/>
-      <c r="E31" s="256"/>
-      <c r="F31" s="256"/>
-      <c r="G31" s="256"/>
-      <c r="H31" s="256"/>
-      <c r="I31" s="256"/>
-      <c r="J31" s="256"/>
-      <c r="K31" s="256"/>
-      <c r="L31" s="256"/>
+      <c r="D31" s="259"/>
+      <c r="E31" s="259"/>
+      <c r="F31" s="259"/>
+      <c r="G31" s="259"/>
+      <c r="H31" s="259"/>
+      <c r="I31" s="259"/>
+      <c r="J31" s="259"/>
+      <c r="K31" s="259"/>
+      <c r="L31" s="259"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -19835,16 +19835,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19907,10 +19907,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="247" t="s">
+      <c r="B4" s="248" t="s">
         <v>208</v>
       </c>
-      <c r="C4" s="247"/>
+      <c r="C4" s="248"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -19927,7 +19927,7 @@
       </c>
       <c r="C6" s="154">
         <f ca="1">Overview!C5</f>
-        <v>11.67</v>
+        <v>11.24</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19936,7 +19936,7 @@
       </c>
       <c r="C7" s="155">
         <f ca="1">C5*C6</f>
-        <v>6163580.5199999996</v>
+        <v>5936473.4400000004</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19954,7 +19954,7 @@
       </c>
       <c r="C9" s="156">
         <f ca="1">Overview!F27</f>
-        <v>4.4549999999999999E-2</v>
+        <v>4.5359999999999998E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19963,7 +19963,7 @@
       </c>
       <c r="C10" s="154">
         <f ca="1">Overview!C13</f>
-        <v>0.96489999999999998</v>
+        <v>0.96460000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19995,10 +19995,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="247" t="s">
+      <c r="B15" s="248" t="s">
         <v>215</v>
       </c>
-      <c r="C15" s="247"/>
+      <c r="C15" s="248"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -20033,7 +20033,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>8.7970500000000007E-2</v>
+        <v>8.8766999999999999E-2</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20042,7 +20042,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>8.7970500000000007E-2</v>
+        <v>8.8766999999999999E-2</v>
       </c>
     </row>
     <row r="21" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20095,60 +20095,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="247" t="s">
+      <c r="C3" s="248" t="s">
         <v>137</v>
       </c>
-      <c r="D3" s="247"/>
-      <c r="E3" s="247"/>
-      <c r="F3" s="247"/>
-      <c r="G3" s="259"/>
-      <c r="H3" s="260" t="s">
+      <c r="D3" s="248"/>
+      <c r="E3" s="248"/>
+      <c r="F3" s="248"/>
+      <c r="G3" s="257"/>
+      <c r="H3" s="258" t="s">
         <v>138</v>
       </c>
-      <c r="I3" s="247"/>
-      <c r="J3" s="247"/>
-      <c r="K3" s="247"/>
-      <c r="L3" s="247"/>
-      <c r="P3" s="261"/>
-      <c r="Q3" s="261"/>
-      <c r="R3" s="261"/>
-      <c r="S3" s="261"/>
-      <c r="T3" s="261"/>
-      <c r="U3" s="261"/>
-      <c r="V3" s="261"/>
-      <c r="W3" s="261"/>
-      <c r="X3" s="261"/>
-      <c r="Y3" s="261"/>
-      <c r="Z3" s="261"/>
+      <c r="I3" s="248"/>
+      <c r="J3" s="248"/>
+      <c r="K3" s="248"/>
+      <c r="L3" s="248"/>
+      <c r="P3" s="262"/>
+      <c r="Q3" s="262"/>
+      <c r="R3" s="262"/>
+      <c r="S3" s="262"/>
+      <c r="T3" s="262"/>
+      <c r="U3" s="262"/>
+      <c r="V3" s="262"/>
+      <c r="W3" s="262"/>
+      <c r="X3" s="262"/>
+      <c r="Y3" s="262"/>
+      <c r="Z3" s="262"/>
       <c r="AB3" s="130"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="88"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="256" t="s">
+      <c r="C5" s="259" t="s">
         <v>222</v>
       </c>
-      <c r="D5" s="256"/>
-      <c r="E5" s="256"/>
-      <c r="F5" s="256"/>
-      <c r="G5" s="256"/>
-      <c r="H5" s="256"/>
-      <c r="I5" s="256"/>
-      <c r="J5" s="256"/>
-      <c r="K5" s="256"/>
-      <c r="L5" s="256"/>
-      <c r="P5" s="261"/>
-      <c r="Q5" s="261"/>
-      <c r="R5" s="261"/>
-      <c r="S5" s="261"/>
-      <c r="T5" s="261"/>
-      <c r="U5" s="261"/>
-      <c r="V5" s="261"/>
-      <c r="W5" s="261"/>
-      <c r="X5" s="261"/>
-      <c r="Y5" s="261"/>
-      <c r="Z5" s="261"/>
+      <c r="D5" s="259"/>
+      <c r="E5" s="259"/>
+      <c r="F5" s="259"/>
+      <c r="G5" s="259"/>
+      <c r="H5" s="259"/>
+      <c r="I5" s="259"/>
+      <c r="J5" s="259"/>
+      <c r="K5" s="259"/>
+      <c r="L5" s="259"/>
+      <c r="P5" s="262"/>
+      <c r="Q5" s="262"/>
+      <c r="R5" s="262"/>
+      <c r="S5" s="262"/>
+      <c r="T5" s="262"/>
+      <c r="U5" s="262"/>
+      <c r="V5" s="262"/>
+      <c r="W5" s="262"/>
+      <c r="X5" s="262"/>
+      <c r="Y5" s="262"/>
+      <c r="Z5" s="262"/>
       <c r="AB5" s="131"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -20301,7 +20301,7 @@
       </c>
       <c r="L8" s="147">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>2987701.1721932362</v>
+        <v>2953095.8530190405</v>
       </c>
       <c r="N8" s="93"/>
       <c r="O8" s="16"/>
@@ -20355,23 +20355,23 @@
       <c r="G10" s="160"/>
       <c r="H10" s="147">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>3310.2840941880327</v>
+        <v>3307.8624178504683</v>
       </c>
       <c r="I10" s="147">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>-3558.4507195714136</v>
+        <v>-3553.2461730273121</v>
       </c>
       <c r="J10" s="147">
         <f t="shared" ca="1" si="0"/>
-        <v>59934.297704966149</v>
+        <v>59802.857037865957</v>
       </c>
       <c r="K10" s="147">
         <f t="shared" ca="1" si="0"/>
-        <v>77796.922040773221</v>
+        <v>77569.518805815926</v>
       </c>
       <c r="L10" s="147">
         <f t="shared" ca="1" si="0"/>
-        <v>130608.62326262318</v>
+        <v>130131.58055562242</v>
       </c>
       <c r="N10" s="93"/>
     </row>
@@ -20390,14 +20390,14 @@
       <c r="K11" s="159"/>
       <c r="L11" s="147">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>1959979.6342218409</v>
+        <v>1930202.1633448438</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="247" t="s">
+      <c r="B13" s="248" t="s">
         <v>226</v>
       </c>
-      <c r="C13" s="247"/>
+      <c r="C13" s="248"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -20413,14 +20413,14 @@
       </c>
       <c r="C15" s="156">
         <f ca="1">IF(WACC!C21&gt;0,WACC!C21,WACC!C20)</f>
-        <v>8.7970500000000007E-2</v>
+        <v>8.8766999999999999E-2</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="247" t="s">
+      <c r="B18" s="248" t="s">
         <v>228</v>
       </c>
-      <c r="C18" s="247"/>
+      <c r="C18" s="248"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -20428,7 +20428,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>268091.67638297915</v>
+        <v>267258.57264412747</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -20437,7 +20437,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>1959979.6342218409</v>
+        <v>1930202.1633448438</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -20446,7 +20446,7 @@
       </c>
       <c r="C21" s="96">
         <f ca="1">C19+C20</f>
-        <v>2228071.31060482</v>
+        <v>2197460.7359889713</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -20473,7 +20473,7 @@
       </c>
       <c r="C24" s="96">
         <f ca="1">C21+C22-C23</f>
-        <v>3535315.31060482</v>
+        <v>3504704.7359889713</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -20491,7 +20491,7 @@
       </c>
       <c r="C26" s="164">
         <f ca="1">C24/C25</f>
-        <v>6.6936952540628525</v>
+        <v>6.6357378047186275</v>
       </c>
     </row>
   </sheetData>
@@ -20534,37 +20534,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="247" t="s">
+      <c r="C2" s="248" t="s">
         <v>137</v>
       </c>
-      <c r="D2" s="247"/>
-      <c r="E2" s="247"/>
-      <c r="F2" s="247"/>
-      <c r="G2" s="259"/>
-      <c r="H2" s="260" t="s">
+      <c r="D2" s="248"/>
+      <c r="E2" s="248"/>
+      <c r="F2" s="248"/>
+      <c r="G2" s="257"/>
+      <c r="H2" s="258" t="s">
         <v>138</v>
       </c>
-      <c r="I2" s="247"/>
-      <c r="J2" s="247"/>
-      <c r="K2" s="247"/>
-      <c r="L2" s="247"/>
+      <c r="I2" s="248"/>
+      <c r="J2" s="248"/>
+      <c r="K2" s="248"/>
+      <c r="L2" s="248"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="256" t="s">
+      <c r="C4" s="259" t="s">
         <v>236</v>
       </c>
-      <c r="D4" s="256"/>
-      <c r="E4" s="256"/>
-      <c r="F4" s="256"/>
-      <c r="G4" s="256"/>
-      <c r="H4" s="256"/>
-      <c r="I4" s="256"/>
-      <c r="J4" s="256"/>
-      <c r="K4" s="256"/>
-      <c r="L4" s="256"/>
+      <c r="D4" s="259"/>
+      <c r="E4" s="259"/>
+      <c r="F4" s="259"/>
+      <c r="G4" s="259"/>
+      <c r="H4" s="259"/>
+      <c r="I4" s="259"/>
+      <c r="J4" s="259"/>
+      <c r="K4" s="259"/>
+      <c r="L4" s="259"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -20753,18 +20753,18 @@
       <c r="N9" s="93"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C10" s="256" t="s">
+      <c r="C10" s="259" t="s">
         <v>146</v>
       </c>
-      <c r="D10" s="256"/>
-      <c r="E10" s="256"/>
-      <c r="F10" s="256"/>
-      <c r="G10" s="256"/>
-      <c r="H10" s="256"/>
-      <c r="I10" s="256"/>
-      <c r="J10" s="256"/>
-      <c r="K10" s="256"/>
-      <c r="L10" s="256"/>
+      <c r="D10" s="259"/>
+      <c r="E10" s="259"/>
+      <c r="F10" s="259"/>
+      <c r="G10" s="259"/>
+      <c r="H10" s="259"/>
+      <c r="I10" s="259"/>
+      <c r="J10" s="259"/>
+      <c r="K10" s="259"/>
+      <c r="L10" s="259"/>
       <c r="N10" s="93"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -20958,18 +20958,18 @@
       <c r="N15" s="93"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C16" s="256" t="s">
+      <c r="C16" s="259" t="s">
         <v>238</v>
       </c>
-      <c r="D16" s="256"/>
-      <c r="E16" s="256"/>
-      <c r="F16" s="256"/>
-      <c r="G16" s="256"/>
-      <c r="H16" s="256"/>
-      <c r="I16" s="256"/>
-      <c r="J16" s="256"/>
-      <c r="K16" s="256"/>
-      <c r="L16" s="256"/>
+      <c r="D16" s="259"/>
+      <c r="E16" s="259"/>
+      <c r="F16" s="259"/>
+      <c r="G16" s="259"/>
+      <c r="H16" s="259"/>
+      <c r="I16" s="259"/>
+      <c r="J16" s="259"/>
+      <c r="K16" s="259"/>
+      <c r="L16" s="259"/>
       <c r="N16" s="93"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
@@ -21103,18 +21103,18 @@
       <c r="N20" s="93"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C21" s="256" t="s">
+      <c r="C21" s="259" t="s">
         <v>241</v>
       </c>
-      <c r="D21" s="256"/>
-      <c r="E21" s="256"/>
-      <c r="F21" s="256"/>
-      <c r="G21" s="256"/>
-      <c r="H21" s="256"/>
-      <c r="I21" s="256"/>
-      <c r="J21" s="256"/>
-      <c r="K21" s="256"/>
-      <c r="L21" s="256"/>
+      <c r="D21" s="259"/>
+      <c r="E21" s="259"/>
+      <c r="F21" s="259"/>
+      <c r="G21" s="259"/>
+      <c r="H21" s="259"/>
+      <c r="I21" s="259"/>
+      <c r="J21" s="259"/>
+      <c r="K21" s="259"/>
+      <c r="L21" s="259"/>
       <c r="N21" s="93"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
@@ -21198,18 +21198,18 @@
       <c r="N25" s="93"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C26" s="256" t="s">
+      <c r="C26" s="259" t="s">
         <v>242</v>
       </c>
-      <c r="D26" s="256"/>
-      <c r="E26" s="256"/>
-      <c r="F26" s="256"/>
-      <c r="G26" s="256"/>
-      <c r="H26" s="256"/>
-      <c r="I26" s="256"/>
-      <c r="J26" s="256"/>
-      <c r="K26" s="256"/>
-      <c r="L26" s="256"/>
+      <c r="D26" s="259"/>
+      <c r="E26" s="259"/>
+      <c r="F26" s="259"/>
+      <c r="G26" s="259"/>
+      <c r="H26" s="259"/>
+      <c r="I26" s="259"/>
+      <c r="J26" s="259"/>
+      <c r="K26" s="259"/>
+      <c r="L26" s="259"/>
       <c r="N26" s="93"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
@@ -21479,10 +21479,10 @@
       <c r="N36" s="93"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="247" t="s">
+      <c r="B37" s="248" t="s">
         <v>247</v>
       </c>
-      <c r="C37" s="247"/>
+      <c r="C37" s="248"/>
       <c r="N37" s="93"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -21500,7 +21500,7 @@
       </c>
       <c r="C39" s="156">
         <f ca="1">IF(WACC!C21&gt;0,WACC!C21,WACC!C20)</f>
-        <v>8.7970500000000007E-2</v>
+        <v>8.8766999999999999E-2</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -21544,14 +21544,14 @@
       </c>
       <c r="C44" s="164">
         <f ca="1">C43/(1+C48)^5</f>
-        <v>15.996134440941134</v>
+        <v>15.937709207716596</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B46" s="247" t="s">
+      <c r="B46" s="248" t="s">
         <v>252</v>
       </c>
-      <c r="C46" s="247"/>
+      <c r="C46" s="248"/>
     </row>
     <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B47" s="1" t="s">
@@ -21568,7 +21568,7 @@
       </c>
       <c r="C48" s="156">
         <f ca="1">IF(WACC!C21&gt;0,WACC!C21,WACC!C20)</f>
-        <v>8.7970500000000007E-2</v>
+        <v>8.8766999999999999E-2</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -21603,14 +21603,14 @@
       </c>
       <c r="C52" s="164">
         <f ca="1">C51/(1+C48)^5</f>
-        <v>16.178217386651543</v>
+        <v>16.119127102841901</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B54" s="247" t="s">
+      <c r="B54" s="248" t="s">
         <v>379</v>
       </c>
-      <c r="C54" s="247"/>
+      <c r="C54" s="248"/>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B55" s="1" t="s">
@@ -21627,7 +21627,7 @@
       </c>
       <c r="C56" s="156">
         <f ca="1">IF(WACC!C21&gt;0,WACC!C21,WACC!C20)</f>
-        <v>8.7970500000000007E-2</v>
+        <v>8.8766999999999999E-2</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
@@ -21671,7 +21671,7 @@
       </c>
       <c r="C61" s="164">
         <f ca="1">C60/(1+C56)^5</f>
-        <v>10.12254584609968</v>
+        <v>10.085573657345705</v>
       </c>
     </row>
   </sheetData>
@@ -21723,10 +21723,10 @@
       <c r="N3" s="93"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="247" t="s">
+      <c r="B4" s="248" t="s">
         <v>258</v>
       </c>
-      <c r="C4" s="247"/>
+      <c r="C4" s="248"/>
       <c r="N4" s="93"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -21735,7 +21735,7 @@
       </c>
       <c r="C5" s="154">
         <f ca="1">DCF!C26</f>
-        <v>6.6936952540628525</v>
+        <v>6.6357378047186275</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -21744,7 +21744,7 @@
       </c>
       <c r="C6" s="154">
         <f ca="1">Multiples!C44</f>
-        <v>15.996134440941134</v>
+        <v>15.937709207716596</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -21753,7 +21753,7 @@
       </c>
       <c r="C7" s="154">
         <f ca="1">Multiples!C52</f>
-        <v>16.178217386651543</v>
+        <v>16.119127102841901</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -21762,7 +21762,7 @@
       </c>
       <c r="C8" s="154">
         <f ca="1">Multiples!C61</f>
-        <v>10.12254584609968</v>
+        <v>10.085573657345705</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -21771,7 +21771,7 @@
       </c>
       <c r="C9" s="164">
         <f ca="1">AVERAGE(C5:C8)</f>
-        <v>12.247648231938804</v>
+        <v>12.194536943155708</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21780,7 +21780,7 @@
       </c>
       <c r="C10" s="154">
         <f ca="1">Overview!C5</f>
-        <v>11.67</v>
+        <v>11.24</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21789,7 +21789,7 @@
       </c>
       <c r="C11" s="176">
         <f ca="1">(C9-C10)/C10</f>
-        <v>4.9498563148140884E-2</v>
+        <v>8.4923215583247988E-2</v>
       </c>
     </row>
   </sheetData>
@@ -21854,60 +21854,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="247" t="s">
+      <c r="C3" s="248" t="s">
         <v>137</v>
       </c>
-      <c r="D3" s="247"/>
-      <c r="E3" s="247"/>
-      <c r="F3" s="247"/>
-      <c r="G3" s="259"/>
-      <c r="H3" s="260" t="s">
+      <c r="D3" s="248"/>
+      <c r="E3" s="248"/>
+      <c r="F3" s="248"/>
+      <c r="G3" s="257"/>
+      <c r="H3" s="258" t="s">
         <v>138</v>
       </c>
-      <c r="I3" s="247"/>
-      <c r="J3" s="247"/>
-      <c r="K3" s="247"/>
-      <c r="L3" s="247"/>
-      <c r="P3" s="261"/>
-      <c r="Q3" s="261"/>
-      <c r="R3" s="261"/>
-      <c r="S3" s="261"/>
-      <c r="T3" s="261"/>
-      <c r="U3" s="261"/>
-      <c r="V3" s="261"/>
-      <c r="W3" s="261"/>
-      <c r="X3" s="261"/>
-      <c r="Y3" s="261"/>
-      <c r="Z3" s="261"/>
+      <c r="I3" s="248"/>
+      <c r="J3" s="248"/>
+      <c r="K3" s="248"/>
+      <c r="L3" s="248"/>
+      <c r="P3" s="262"/>
+      <c r="Q3" s="262"/>
+      <c r="R3" s="262"/>
+      <c r="S3" s="262"/>
+      <c r="T3" s="262"/>
+      <c r="U3" s="262"/>
+      <c r="V3" s="262"/>
+      <c r="W3" s="262"/>
+      <c r="X3" s="262"/>
+      <c r="Y3" s="262"/>
+      <c r="Z3" s="262"/>
       <c r="AB3" s="130"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="88"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="256" t="s">
+      <c r="C5" s="259" t="s">
         <v>222</v>
       </c>
-      <c r="D5" s="256"/>
-      <c r="E5" s="256"/>
-      <c r="F5" s="256"/>
-      <c r="G5" s="256"/>
-      <c r="H5" s="256"/>
-      <c r="I5" s="256"/>
-      <c r="J5" s="256"/>
-      <c r="K5" s="256"/>
-      <c r="L5" s="256"/>
-      <c r="P5" s="261"/>
-      <c r="Q5" s="261"/>
-      <c r="R5" s="261"/>
-      <c r="S5" s="261"/>
-      <c r="T5" s="261"/>
-      <c r="U5" s="261"/>
-      <c r="V5" s="261"/>
-      <c r="W5" s="261"/>
-      <c r="X5" s="261"/>
-      <c r="Y5" s="261"/>
-      <c r="Z5" s="261"/>
+      <c r="D5" s="259"/>
+      <c r="E5" s="259"/>
+      <c r="F5" s="259"/>
+      <c r="G5" s="259"/>
+      <c r="H5" s="259"/>
+      <c r="I5" s="259"/>
+      <c r="J5" s="259"/>
+      <c r="K5" s="259"/>
+      <c r="L5" s="259"/>
+      <c r="P5" s="262"/>
+      <c r="Q5" s="262"/>
+      <c r="R5" s="262"/>
+      <c r="S5" s="262"/>
+      <c r="T5" s="262"/>
+      <c r="U5" s="262"/>
+      <c r="V5" s="262"/>
+      <c r="W5" s="262"/>
+      <c r="X5" s="262"/>
+      <c r="Y5" s="262"/>
+      <c r="Z5" s="262"/>
       <c r="AB5" s="131"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -22041,7 +22041,7 @@
       <c r="K8" s="159"/>
       <c r="L8" s="147">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>6187042.4846072933</v>
+        <v>6115380.5051841736</v>
       </c>
       <c r="N8" s="93"/>
       <c r="O8" s="16"/>
@@ -22095,23 +22095,23 @@
       <c r="G10" s="160"/>
       <c r="H10" s="147">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>16176.909208475781</v>
+        <v>16165.074804802129</v>
       </c>
       <c r="I10" s="147">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>32711.548942408572</v>
+        <v>32663.705430606075</v>
       </c>
       <c r="J10" s="147">
         <f t="shared" ca="1" si="1"/>
-        <v>66146.469663744429</v>
+        <v>66001.40521097109</v>
       </c>
       <c r="K10" s="147">
         <f t="shared" ca="1" si="1"/>
-        <v>133755.67927644894</v>
+        <v>133364.70655717561</v>
       </c>
       <c r="L10" s="147">
         <f t="shared" ca="1" si="1"/>
-        <v>270469.18497164</v>
+        <v>269481.30722715356</v>
       </c>
       <c r="N10" s="93"/>
     </row>
@@ -22130,15 +22130,15 @@
       <c r="K11" s="159"/>
       <c r="L11" s="147">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>4058798.5768984016</v>
+        <v>3997134.2849287689</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="262" t="s">
+      <c r="B14" s="263" t="s">
         <v>266</v>
       </c>
-      <c r="C14" s="263"/>
+      <c r="C14" s="264"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="177" t="s">
@@ -22146,7 +22146,7 @@
       </c>
       <c r="C15" s="178">
         <f ca="1">Overview!C5</f>
-        <v>11.67</v>
+        <v>11.24</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22155,7 +22155,7 @@
       </c>
       <c r="C16" s="178">
         <f ca="1">C36</f>
-        <v>11.233165182911042</v>
+        <v>11.112445142901953</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -22165,20 +22165,20 @@
       <c r="C17" s="180">
         <v>1.2</v>
       </c>
-      <c r="E17" s="264" t="s">
+      <c r="E17" s="265" t="s">
         <v>269</v>
       </c>
-      <c r="F17" s="264"/>
-      <c r="G17" s="264"/>
-      <c r="H17" s="264"/>
-      <c r="I17" s="264"/>
+      <c r="F17" s="265"/>
+      <c r="G17" s="265"/>
+      <c r="H17" s="265"/>
+      <c r="I17" s="265"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="262" t="s">
+      <c r="B19" s="263" t="s">
         <v>226</v>
       </c>
-      <c r="C19" s="263"/>
+      <c r="C19" s="264"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="181" t="s">
@@ -22194,7 +22194,7 @@
       </c>
       <c r="C21" s="183">
         <f ca="1">IF(WACC!C21&gt;0,WACC!C21,WACC!C20)</f>
-        <v>8.7970500000000007E-2</v>
+        <v>8.8766999999999999E-2</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -22212,7 +22212,7 @@
       </c>
       <c r="C23" s="184">
         <f ca="1">C15*C22</f>
-        <v>6114169.7400000002</v>
+        <v>5888883.2800000003</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22239,15 +22239,15 @@
       </c>
       <c r="C26" s="185">
         <f ca="1">C23+C25-C24</f>
-        <v>4806925.74</v>
+        <v>4581639.28</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="262" t="s">
+      <c r="B28" s="263" t="s">
         <v>228</v>
       </c>
-      <c r="C28" s="263"/>
+      <c r="C28" s="264"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="181" t="s">
@@ -22255,7 +22255,7 @@
       </c>
       <c r="C29" s="184">
         <f ca="1">SUM(H10:L10)</f>
-        <v>519259.79206271772</v>
+        <v>517676.19923070847</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -22264,7 +22264,7 @@
       </c>
       <c r="C30" s="184">
         <f ca="1">L11</f>
-        <v>4058798.5768984016</v>
+        <v>3997134.2849287689</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -22273,7 +22273,7 @@
       </c>
       <c r="C31" s="187">
         <f ca="1">C29+C30</f>
-        <v>4578058.3689611191</v>
+        <v>4514810.4841594771</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -22300,7 +22300,7 @@
       </c>
       <c r="C34" s="187">
         <f ca="1">C31+C32-C33</f>
-        <v>5885302.3689611191</v>
+        <v>5822054.4841594771</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -22318,22 +22318,22 @@
       </c>
       <c r="C36" s="190">
         <f ca="1">C34/C35</f>
-        <v>11.233165182911042</v>
+        <v>11.112445142901953</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C39" s="256" t="s">
+      <c r="C39" s="259" t="s">
         <v>272</v>
       </c>
-      <c r="D39" s="256"/>
-      <c r="E39" s="256"/>
-      <c r="F39" s="256"/>
-      <c r="G39" s="256"/>
-      <c r="H39" s="256"/>
-      <c r="I39" s="256"/>
-      <c r="J39" s="256"/>
-      <c r="K39" s="256"/>
-      <c r="L39" s="256"/>
+      <c r="D39" s="259"/>
+      <c r="E39" s="259"/>
+      <c r="F39" s="259"/>
+      <c r="G39" s="259"/>
+      <c r="H39" s="259"/>
+      <c r="I39" s="259"/>
+      <c r="J39" s="259"/>
+      <c r="K39" s="259"/>
+      <c r="L39" s="259"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="12">
@@ -22765,17 +22765,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -29717,7 +29717,7 @@
       <c r="AA125" s="68"/>
       <c r="AC125" s="63">
         <f ca="1">Overview!C5</f>
-        <v>11.67</v>
+        <v>11.24</v>
       </c>
     </row>
     <row r="126" spans="1:31" x14ac:dyDescent="0.2">
@@ -29764,7 +29764,7 @@
       <c r="AA126" s="68"/>
       <c r="AC126" s="65">
         <f t="shared" ref="AC126" ca="1" si="76">AC125/AC84</f>
-        <v>11.67</v>
+        <v>11.24</v>
       </c>
     </row>
     <row r="128" spans="1:31" x14ac:dyDescent="0.2">
@@ -31354,7 +31354,7 @@
       <c r="AA167" s="49"/>
       <c r="AC167" s="72">
         <f ca="1">AC126/Statement!AC26</f>
-        <v>19.449999999999996</v>
+        <v>18.733333333333331</v>
       </c>
     </row>
     <row r="168" spans="2:29" x14ac:dyDescent="0.2">
@@ -31391,7 +31391,7 @@
       <c r="AA168" s="49"/>
       <c r="AC168" s="72">
         <f ca="1">AC126/(Statement!AC5/Statement!AC22)</f>
-        <v>3.7595263718883234</v>
+        <v>3.6210005501306561</v>
       </c>
     </row>
     <row r="169" spans="2:29" x14ac:dyDescent="0.2">
@@ -31428,7 +31428,7 @@
       <c r="AA169" s="49"/>
       <c r="AC169" s="72">
         <f ca="1">AC126/(Statement!AC48/Statement!AC74)</f>
-        <v>3.2129701492145153</v>
+        <v>3.0945830743077249</v>
       </c>
     </row>
     <row r="170" spans="2:29" x14ac:dyDescent="0.2">
@@ -31465,7 +31465,7 @@
       <c r="AA170" s="49"/>
       <c r="AC170" s="165">
         <f ca="1">Statement!AC126*Statement!AC77</f>
-        <v>6163580.5199999996</v>
+        <v>5936473.4400000004</v>
       </c>
     </row>
     <row r="171" spans="2:29" x14ac:dyDescent="0.2">
@@ -31502,7 +31502,7 @@
       <c r="AA171" s="49"/>
       <c r="AC171" s="165">
         <f ca="1">AC170+AC117-AC116+AC47+AC44</f>
-        <v>4856336.5199999996</v>
+        <v>4629229.4400000004</v>
       </c>
     </row>
     <row r="172" spans="2:29" x14ac:dyDescent="0.2">
@@ -31539,7 +31539,7 @@
       <c r="AA172" s="49"/>
       <c r="AC172" s="207">
         <f ca="1">AC171/AC5</f>
-        <v>2.9039343431021387</v>
+        <v>2.7681315529829642</v>
       </c>
     </row>
     <row r="173" spans="2:29" x14ac:dyDescent="0.2">
@@ -31576,7 +31576,7 @@
       <c r="AA173" s="49"/>
       <c r="AC173" s="207">
         <f ca="1">AC171/AC12</f>
-        <v>48.006964481657583</v>
+        <v>45.761913818839652</v>
       </c>
     </row>
     <row r="174" spans="2:29" x14ac:dyDescent="0.2">
@@ -31711,7 +31711,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="72">
         <f t="shared" ref="AC176:AC177" ca="1" si="118">AC170/AC174</f>
-        <v>57.277555966508373</v>
+        <v>55.167071899190589</v>
       </c>
     </row>
     <row r="177" spans="2:29" x14ac:dyDescent="0.2">
@@ -31748,7 +31748,7 @@
       <c r="AA177" s="49"/>
       <c r="AC177" s="72">
         <f t="shared" ca="1" si="118"/>
-        <v>-89.542482160966159</v>
+        <v>-85.355018714852037</v>
       </c>
     </row>
     <row r="178" spans="2:29" x14ac:dyDescent="0.2">
@@ -31785,7 +31785,7 @@
       <c r="AA178" s="49"/>
       <c r="AC178" s="74">
         <f t="shared" ref="AC178" ca="1" si="121">AC174/AC170</f>
-        <v>1.7458845495864472E-2</v>
+        <v>1.8126755065546118E-2</v>
       </c>
     </row>
     <row r="179" spans="2:29" x14ac:dyDescent="0.2">
@@ -31822,7 +31822,7 @@
       <c r="AA179" s="49"/>
       <c r="AC179" s="74">
         <f t="shared" ref="AC179" ca="1" si="123">AC26/AC126</f>
-        <v>5.1413881748071988E-2</v>
+        <v>5.3380782918149475E-2</v>
       </c>
     </row>
     <row r="180" spans="2:29" x14ac:dyDescent="0.2">
@@ -31896,7 +31896,7 @@
       <c r="AA181" s="49"/>
       <c r="AC181" s="176">
         <f ca="1">-AC62/AC170</f>
-        <v>5.6034312990527788E-2</v>
+        <v>5.8177974430556868E-2</v>
       </c>
     </row>
     <row r="182" spans="2:29" x14ac:dyDescent="0.2">
@@ -31933,7 +31933,7 @@
       <c r="AA182" s="49"/>
       <c r="AC182" s="176">
         <f ca="1">-(AC62+AC63)/AC170</f>
-        <v>5.6034312990527788E-2</v>
+        <v>5.8177974430556868E-2</v>
       </c>
     </row>
     <row r="183" spans="2:29" x14ac:dyDescent="0.2">
@@ -32399,7 +32399,7 @@
       <c r="AA192" s="49"/>
       <c r="AC192" s="176">
         <f ca="1">(AC116-AC117)/AC170</f>
-        <v>0.21209165610121697</v>
+        <v>0.22020548280259802</v>
       </c>
     </row>
     <row r="193" spans="2:29" x14ac:dyDescent="0.2">
@@ -32970,15 +32970,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="247" t="s">
+      <c r="B4" s="248" t="s">
         <v>285</v>
       </c>
-      <c r="C4" s="247"/>
-      <c r="E4" s="247" t="s">
+      <c r="C4" s="248"/>
+      <c r="E4" s="248" t="s">
         <v>292</v>
       </c>
-      <c r="F4" s="247"/>
-      <c r="G4" s="247"/>
+      <c r="F4" s="248"/>
+      <c r="G4" s="248"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -32986,7 +32986,7 @@
       </c>
       <c r="C5" s="196">
         <f ca="1">Overview!C5</f>
-        <v>11.67</v>
+        <v>11.24</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="153" t="s">
@@ -33002,7 +33002,7 @@
       </c>
       <c r="C6" s="197">
         <f ca="1">Statement!AC170</f>
-        <v>6163580.5199999996</v>
+        <v>5936473.4400000004</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>20</v>
@@ -33022,7 +33022,7 @@
       </c>
       <c r="C7" s="197">
         <f ca="1">Statement!AC171</f>
-        <v>4856336.5199999996</v>
+        <v>4629229.4400000004</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>32</v>
@@ -33042,7 +33042,7 @@
       </c>
       <c r="C8" s="198">
         <f ca="1">Statement!AC167</f>
-        <v>19.449999999999996</v>
+        <v>18.733333333333331</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>295</v>
@@ -33062,7 +33062,7 @@
       </c>
       <c r="C9" s="198">
         <f ca="1">Statement!AC168</f>
-        <v>3.7595263718883234</v>
+        <v>3.6210005501306561</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>296</v>
@@ -33082,17 +33082,17 @@
       </c>
       <c r="C10" s="198">
         <f ca="1">Statement!AC169</f>
-        <v>3.2129701492145153</v>
+        <v>3.0945830743077249</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
       </c>
       <c r="F10" s="202">
-        <f>IF(Statement!M125&lt;=0,"N/A",_xlfn.RRI(4,Statement!M125,Statement!Q125))</f>
+        <f>IF(Statement!M126&lt;=0,"N/A",_xlfn.RRI(4,Statement!M126,Statement!Q126))</f>
         <v>-0.21662025481427405</v>
       </c>
       <c r="G10" s="202" t="str">
-        <f>IF(Statement!H125&lt;=0,"N/A",_xlfn.RRI(9,Statement!H125,Statement!Q125))</f>
+        <f>IF(Statement!H126&lt;=0,"N/A",_xlfn.RRI(9,Statement!H126,Statement!Q126))</f>
         <v>N/A</v>
       </c>
     </row>
@@ -33102,7 +33102,7 @@
       </c>
       <c r="C11" s="198">
         <f ca="1">Statement!AC172</f>
-        <v>2.9039343431021387</v>
+        <v>2.7681315529829642</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33111,18 +33111,18 @@
       </c>
       <c r="C12" s="198">
         <f ca="1">Statement!AC173</f>
-        <v>48.006964481657583</v>
+        <v>45.761913818839652</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="247" t="s">
+      <c r="B15" s="248" t="s">
         <v>78</v>
       </c>
-      <c r="C15" s="247"/>
-      <c r="E15" s="247" t="s">
+      <c r="C15" s="248"/>
+      <c r="E15" s="248" t="s">
         <v>298</v>
       </c>
-      <c r="F15" s="247"/>
+      <c r="F15" s="248"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -33173,14 +33173,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="247" t="s">
+      <c r="B21" s="248" t="s">
         <v>297</v>
       </c>
-      <c r="C21" s="247"/>
-      <c r="E21" s="247" t="s">
+      <c r="C21" s="248"/>
+      <c r="E21" s="248" t="s">
         <v>301</v>
       </c>
-      <c r="F21" s="247"/>
+      <c r="F21" s="248"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -33249,14 +33249,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="247" t="s">
+      <c r="B29" s="248" t="s">
         <v>302</v>
       </c>
-      <c r="C29" s="247"/>
-      <c r="E29" s="247" t="s">
+      <c r="C29" s="248"/>
+      <c r="E29" s="248" t="s">
         <v>308</v>
       </c>
-      <c r="F29" s="247"/>
+      <c r="F29" s="248"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -33332,14 +33332,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="247" t="s">
+      <c r="B37" s="248" t="s">
         <v>321</v>
       </c>
-      <c r="C37" s="247"/>
-      <c r="E37" s="247" t="s">
+      <c r="C37" s="248"/>
+      <c r="E37" s="248" t="s">
         <v>324</v>
       </c>
-      <c r="F37" s="247"/>
+      <c r="F37" s="248"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -33347,7 +33347,7 @@
       </c>
       <c r="C38" s="199">
         <f ca="1">Statement!AC179</f>
-        <v>5.1413881748071988E-2</v>
+        <v>5.3380782918149475E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>323</v>
@@ -33363,7 +33363,7 @@
       </c>
       <c r="C39" s="240">
         <f ca="1">Statement!AC178</f>
-        <v>1.7458845495864472E-2</v>
+        <v>1.8126755065546118E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>325</v>
@@ -33395,7 +33395,7 @@
       </c>
       <c r="C41" s="199">
         <f ca="1">Statement!AC181</f>
-        <v>5.6034312990527788E-2</v>
+        <v>5.8177974430556868E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -33404,18 +33404,18 @@
       </c>
       <c r="C42" s="199">
         <f ca="1">Statement!AC182</f>
-        <v>5.6034312990527788E-2</v>
+        <v>5.8177974430556868E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="247" t="s">
+      <c r="B45" s="248" t="s">
         <v>332</v>
       </c>
-      <c r="C45" s="247"/>
-      <c r="E45" s="247" t="s">
+      <c r="C45" s="248"/>
+      <c r="E45" s="248" t="s">
         <v>338</v>
       </c>
-      <c r="F45" s="247"/>
+      <c r="F45" s="248"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -33448,18 +33448,18 @@
       </c>
       <c r="F48" s="199">
         <f ca="1">Statement!AC192</f>
-        <v>0.21209165610121697</v>
+        <v>0.22020548280259802</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="247" t="s">
+      <c r="B51" s="248" t="s">
         <v>335</v>
       </c>
-      <c r="C51" s="247"/>
-      <c r="E51" s="247" t="s">
+      <c r="C51" s="248"/>
+      <c r="E51" s="248" t="s">
         <v>356</v>
       </c>
-      <c r="F51" s="247"/>
+      <c r="F51" s="248"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -33627,7 +33627,7 @@
       </c>
       <c r="I6" s="196">
         <f ca="1">Statement!AC125</f>
-        <v>11.67</v>
+        <v>11.24</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -33656,7 +33656,7 @@
       </c>
       <c r="I7" s="197">
         <f ca="1">Statement!AC170</f>
-        <v>6163580.5199999996</v>
+        <v>5936473.4400000004</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -33685,7 +33685,7 @@
       </c>
       <c r="I8" s="197">
         <f ca="1">Statement!AC171</f>
-        <v>4856336.5199999996</v>
+        <v>4629229.4400000004</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -33714,7 +33714,7 @@
       </c>
       <c r="I9" s="198">
         <f ca="1">Statement!AC167</f>
-        <v>19.449999999999996</v>
+        <v>18.733333333333331</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -33743,7 +33743,7 @@
       </c>
       <c r="I10" s="198">
         <f ca="1">Statement!AC168</f>
-        <v>3.7595263718883234</v>
+        <v>3.6210005501306561</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -33772,7 +33772,7 @@
       </c>
       <c r="I11" s="198">
         <f ca="1">Statement!AC169</f>
-        <v>3.2129701492145153</v>
+        <v>3.0945830743077249</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -33801,7 +33801,7 @@
       </c>
       <c r="I12" s="198">
         <f ca="1">Statement!AC172</f>
-        <v>2.9039343431021387</v>
+        <v>2.7681315529829642</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -33830,7 +33830,7 @@
       </c>
       <c r="I13" s="198">
         <f ca="1">Statement!AC173</f>
-        <v>48.006964481657583</v>
+        <v>45.761913818839652</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34603,7 +34603,7 @@
       </c>
       <c r="I51" s="199">
         <f ca="1">Statement!AC179</f>
-        <v>5.1413881748071988E-2</v>
+        <v>5.3380782918149475E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -34632,7 +34632,7 @@
       </c>
       <c r="I52" s="199">
         <f ca="1">Statement!AC178</f>
-        <v>1.7458845495864472E-2</v>
+        <v>1.8126755065546118E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -34690,7 +34690,7 @@
       </c>
       <c r="I54" s="199">
         <f ca="1">Statement!AC181</f>
-        <v>5.6034312990527788E-2</v>
+        <v>5.8177974430556868E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -34719,7 +34719,7 @@
       </c>
       <c r="I55" s="199">
         <f ca="1">Statement!AC182</f>
-        <v>5.6034312990527788E-2</v>
+        <v>5.8177974430556868E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34955,7 +34955,7 @@
       </c>
       <c r="I68" s="220">
         <f ca="1">Statement!AC192</f>
-        <v>0.21209165610121697</v>
+        <v>0.22020548280259802</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35441,14 +35441,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="251" t="s">
+      <c r="C3" s="254" t="s">
         <v>369</v>
       </c>
-      <c r="D3" s="252"/>
-      <c r="F3" s="253" t="s">
+      <c r="D3" s="255"/>
+      <c r="F3" s="256" t="s">
         <v>370</v>
       </c>
-      <c r="G3" s="252"/>
+      <c r="G3" s="255"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -35515,19 +35515,19 @@
       <c r="B7" s="230" t="s">
         <v>371</v>
       </c>
-      <c r="C7" s="254">
+      <c r="C7" s="252">
         <f>Statement!AA88</f>
         <v>-0.13037640275448081</v>
       </c>
-      <c r="D7" s="255"/>
-      <c r="F7" s="254">
+      <c r="D7" s="253"/>
+      <c r="F7" s="252">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.17317398716855847</v>
       </c>
-      <c r="G7" s="255"/>
+      <c r="G7" s="253"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="231" t="s">
@@ -35554,19 +35554,19 @@
       <c r="B9" s="230" t="s">
         <v>371</v>
       </c>
-      <c r="C9" s="254">
+      <c r="C9" s="252">
         <f>Statement!AA89</f>
         <v>4.0481504023804696E-2</v>
       </c>
-      <c r="D9" s="255"/>
-      <c r="F9" s="254">
+      <c r="D9" s="253"/>
+      <c r="F9" s="252">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.20469173309112548</v>
       </c>
-      <c r="G9" s="255"/>
+      <c r="G9" s="253"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="231" t="s">
@@ -35593,19 +35593,19 @@
       <c r="B11" s="230" t="s">
         <v>371</v>
       </c>
-      <c r="C11" s="254">
+      <c r="C11" s="252">
         <f>Statement!AA90</f>
         <v>-0.1614010786596328</v>
       </c>
-      <c r="D11" s="255"/>
-      <c r="F11" s="254">
+      <c r="D11" s="253"/>
+      <c r="F11" s="252">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.16629948047423376</v>
       </c>
-      <c r="G11" s="255"/>
+      <c r="G11" s="253"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="231" t="s">
@@ -35632,19 +35632,19 @@
       <c r="B13" s="230" t="s">
         <v>371</v>
       </c>
-      <c r="C13" s="254">
+      <c r="C13" s="252">
         <f>Statement!AA94</f>
         <v>-4.1051008608505718E-2</v>
       </c>
-      <c r="D13" s="255"/>
-      <c r="F13" s="254">
+      <c r="D13" s="253"/>
+      <c r="F13" s="252">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>1.3868988514743887E-2</v>
       </c>
-      <c r="G13" s="255"/>
+      <c r="G13" s="253"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="231" t="s">
@@ -35671,19 +35671,19 @@
       <c r="B15" s="230" t="s">
         <v>371</v>
       </c>
-      <c r="C15" s="254">
+      <c r="C15" s="252">
         <f>Statement!AA95</f>
         <v>-0.65140871384799337</v>
       </c>
-      <c r="D15" s="255"/>
-      <c r="F15" s="254">
+      <c r="D15" s="253"/>
+      <c r="F15" s="252">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>2.7052766268583963</v>
       </c>
-      <c r="G15" s="255"/>
+      <c r="G15" s="253"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="231" t="s">
@@ -35710,19 +35710,19 @@
       <c r="B17" s="230" t="s">
         <v>371</v>
       </c>
-      <c r="C17" s="254">
+      <c r="C17" s="252">
         <f>Statement!AA97</f>
         <v>-0.78437135034749483</v>
       </c>
-      <c r="D17" s="255"/>
-      <c r="F17" s="254">
+      <c r="D17" s="253"/>
+      <c r="F17" s="252">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>1.9986699179782754</v>
       </c>
-      <c r="G17" s="255"/>
+      <c r="G17" s="253"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="231" t="s">
@@ -35749,22 +35749,22 @@
       <c r="B19" s="230" t="s">
         <v>371</v>
       </c>
-      <c r="C19" s="254">
+      <c r="C19" s="252">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-3.2031015030699599E-2</v>
       </c>
-      <c r="D19" s="255"/>
-      <c r="F19" s="254">
+      <c r="D19" s="253"/>
+      <c r="F19" s="252">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-3.7620498458385526E-2</v>
       </c>
-      <c r="G19" s="255"/>
+      <c r="G19" s="253"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="231" t="s">
@@ -35791,22 +35791,22 @@
       <c r="B21" s="230" t="s">
         <v>371</v>
       </c>
-      <c r="C21" s="254">
+      <c r="C21" s="252">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>-0.78947368421052633</v>
       </c>
-      <c r="D21" s="255"/>
-      <c r="F21" s="254">
+      <c r="D21" s="253"/>
+      <c r="F21" s="252">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>2</v>
       </c>
-      <c r="G21" s="255"/>
+      <c r="G21" s="253"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -35854,22 +35854,22 @@
       <c r="B25" s="230" t="s">
         <v>371</v>
       </c>
-      <c r="C25" s="254">
+      <c r="C25" s="252">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>-0.30844727286201273</v>
       </c>
-      <c r="D25" s="255"/>
-      <c r="F25" s="254">
+      <c r="D25" s="253"/>
+      <c r="F25" s="252">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.16387602700216702</v>
       </c>
-      <c r="G25" s="255"/>
+      <c r="G25" s="253"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="s">
@@ -35896,22 +35896,22 @@
       <c r="B27" s="230" t="s">
         <v>371</v>
       </c>
-      <c r="C27" s="254">
+      <c r="C27" s="252">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>6.6472159310281692E-3</v>
       </c>
-      <c r="D27" s="255"/>
-      <c r="F27" s="254">
+      <c r="D27" s="253"/>
+      <c r="F27" s="252">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.16382654634312457</v>
       </c>
-      <c r="G27" s="255"/>
+      <c r="G27" s="253"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
@@ -35938,22 +35938,22 @@
       <c r="B29" s="230" t="s">
         <v>371</v>
       </c>
-      <c r="C29" s="254">
+      <c r="C29" s="252">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.15748031496062992</v>
       </c>
-      <c r="D29" s="255"/>
-      <c r="F29" s="254">
+      <c r="D29" s="253"/>
+      <c r="F29" s="252">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>0.46533756230176709</v>
       </c>
-      <c r="G29" s="255"/>
+      <c r="G29" s="253"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B31" s="8" t="s">
@@ -36001,22 +36001,22 @@
       <c r="B33" s="230" t="s">
         <v>371</v>
       </c>
-      <c r="C33" s="254">
+      <c r="C33" s="252">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>2.6257619832373135E-2</v>
       </c>
-      <c r="D33" s="255"/>
-      <c r="F33" s="254">
+      <c r="D33" s="253"/>
+      <c r="F33" s="252">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>0.12319376989075922</v>
       </c>
-      <c r="G33" s="255"/>
+      <c r="G33" s="253"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B34" s="20" t="s">
@@ -36043,25 +36043,43 @@
       <c r="B35" s="230" t="s">
         <v>371</v>
       </c>
-      <c r="C35" s="254">
+      <c r="C35" s="252">
         <f>IF(C34=0,
 IF(D34=0,0,IF(D34&gt;0,1,-1)),
 (D34-C34)/ABS(C34)
 )</f>
         <v>2.3001949317738791E-2</v>
       </c>
-      <c r="D35" s="255"/>
-      <c r="F35" s="254">
+      <c r="D35" s="253"/>
+      <c r="F35" s="252">
         <f>IF(F34=0,
 IF(G34=0,0,IF(G34&gt;0,1,-1)),
 (G34-F34)/ABS(F34)
 )</f>
         <v>0.10951374207188161</v>
       </c>
-      <c r="G35" s="255"/>
+      <c r="G35" s="253"/>
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="F33:G33"/>
     <mergeCell ref="C35:D35"/>
@@ -36072,24 +36090,6 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/PATH.xlsx
+++ b/PATH.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5A82C00-2994-1C4D-82BE-4E1A9E2DE9E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B10EE8BC-8B65-EB4F-840C-BE78E0080105}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="4" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="2" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -168,7 +168,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="754" uniqueCount="409">
   <si>
     <t>Ticker</t>
   </si>
@@ -1130,9 +1130,6 @@
     <t>Dividend yield</t>
   </si>
   <si>
-    <t>FCF/Sales</t>
-  </si>
-  <si>
     <t>Earnings yields</t>
   </si>
   <si>
@@ -1392,6 +1389,12 @@
   </si>
   <si>
     <t>Last market price for period adjusted</t>
+  </si>
+  <si>
+    <t>FCFF/Sales (FCFF Margin)</t>
+  </si>
+  <si>
+    <t>FCFE/Sales (FCFE Margin)</t>
   </si>
 </sst>
 </file>
@@ -12655,11 +12658,11 @@
       </c>
       <c r="C2" s="250"/>
       <c r="E2" s="249" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F2" s="250"/>
       <c r="H2" s="249" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="I2" s="250"/>
     </row>
@@ -12816,7 +12819,7 @@
         <v>-3.6846999999999998E-2</v>
       </c>
       <c r="E9" s="209" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F9" s="216">
         <f ca="1">Statement!AC179</f>
@@ -12832,7 +12835,7 @@
         <v>-9.7859999999999996E-3</v>
       </c>
       <c r="E10" s="209" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F10" s="216">
         <f ca="1">Statement!AC181</f>
@@ -12848,7 +12851,7 @@
         <v>19.84</v>
       </c>
       <c r="E11" s="210" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F11" s="217">
         <f ca="1">Statement!AC180</f>
@@ -12905,19 +12908,19 @@
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.2">
       <c r="E15" s="209" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F15" s="216">
-        <f ca="1">Statement!AC192</f>
+        <f ca="1">Statement!AC193</f>
         <v>0.22020548280259802</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
       <c r="E16" s="210" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F16" s="215">
-        <f>Statement!AC191</f>
+        <f>Statement!AC192</f>
         <v>2.4951118677971147</v>
       </c>
     </row>
@@ -12927,10 +12930,10 @@
       </c>
       <c r="C17" s="251"/>
       <c r="E17" s="208" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F17" s="218">
-        <f>Statement!AC187</f>
+        <f>Statement!AC188</f>
         <v>0.22116382280992736</v>
       </c>
     </row>
@@ -12942,7 +12945,7 @@
         <v>14</v>
       </c>
       <c r="E18" s="209" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F18" s="214">
         <f>Statement!AC161</f>
@@ -12973,7 +12976,7 @@
         <v>105</v>
       </c>
       <c r="E20" s="210" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F20" s="215">
         <f>Statement!AC164</f>
@@ -13003,7 +13006,7 @@
       </c>
       <c r="C25" s="251"/>
       <c r="E25" s="249" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="F25" s="250"/>
     </row>
@@ -13030,7 +13033,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="210" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F27" s="246">
         <f ca="1">F26/1000</f>
@@ -13039,7 +13042,7 @@
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B31" s="248" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C31" s="248"/>
       <c r="D31" s="248"/>
@@ -13050,18 +13053,18 @@
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B33" s="16" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="37" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -13075,7 +13078,7 @@
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B40" s="248" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C40" s="248"/>
       <c r="D40" s="248"/>
@@ -13086,13 +13089,13 @@
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B42" s="41" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C42" s="41" t="s">
+        <v>385</v>
+      </c>
+      <c r="D42" s="41" t="s">
         <v>386</v>
-      </c>
-      <c r="D42" s="41" t="s">
-        <v>387</v>
       </c>
       <c r="E42" s="243"/>
     </row>
@@ -19700,7 +19703,7 @@
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C32" s="12">
         <f>C5</f>
@@ -20346,7 +20349,7 @@
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B10" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C10" s="159"/>
       <c r="D10" s="159"/>
@@ -21443,7 +21446,7 @@
     </row>
     <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C34" s="171">
         <f>C32/C8</f>
@@ -21608,7 +21611,7 @@
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B54" s="248" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C54" s="248"/>
     </row>
@@ -21758,7 +21761,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B8" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C8" s="154">
         <f ca="1">Multiples!C61</f>
@@ -22086,7 +22089,7 @@
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B10" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C10" s="159"/>
       <c r="D10" s="159"/>
@@ -22160,7 +22163,7 @@
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B17" s="179" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C17" s="180">
         <v>1.2</v>
@@ -22469,7 +22472,7 @@
     </row>
     <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B43" s="143" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C43" s="97">
         <f>C41/C42</f>
@@ -22554,7 +22557,7 @@
     </row>
     <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B45" s="143" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C45" s="97">
         <f>C41/C44</f>
@@ -22594,7 +22597,7 @@
     </row>
     <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B46" s="143" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C46" s="159"/>
       <c r="D46" s="97">
@@ -22785,7 +22788,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0548B83C-60BF-4548-84AB-1D4A73B251A4}">
-  <dimension ref="A1:AE205"/>
+  <dimension ref="A1:AE206"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.6640625" style="1" customWidth="1"/>
@@ -22859,7 +22862,7 @@
         <v>86</v>
       </c>
       <c r="AA2" s="10" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AB2" s="7"/>
       <c r="AD2" s="7"/>
@@ -22909,7 +22912,7 @@
         <v>91</v>
       </c>
       <c r="AA3" s="10" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AB3" s="11"/>
       <c r="AC3" s="59" t="s">
@@ -23737,7 +23740,7 @@
     </row>
     <row r="17" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B17" s="23" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C17" s="21"/>
       <c r="D17" s="21"/>
@@ -25425,7 +25428,7 @@
     </row>
     <row r="44" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B44" s="20" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C44" s="21"/>
       <c r="D44" s="21"/>
@@ -25541,7 +25544,7 @@
     </row>
     <row r="46" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C46" s="21"/>
       <c r="D46" s="21"/>
@@ -25599,7 +25602,7 @@
     </row>
     <row r="47" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B47" s="20" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C47" s="21"/>
       <c r="D47" s="21"/>
@@ -26437,7 +26440,7 @@
     </row>
     <row r="63" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B63" s="20" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C63" s="62"/>
       <c r="D63" s="62"/>
@@ -26495,7 +26498,7 @@
     </row>
     <row r="64" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B64" s="20" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C64" s="62"/>
       <c r="D64" s="62"/>
@@ -27307,7 +27310,7 @@
     </row>
     <row r="78" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B78" s="20" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C78" s="25"/>
       <c r="D78" s="25"/>
@@ -27354,7 +27357,7 @@
     </row>
     <row r="79" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B79" s="20" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C79" s="25"/>
       <c r="D79" s="25"/>
@@ -29442,7 +29445,7 @@
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B119" s="20" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C119" s="25"/>
       <c r="D119" s="25"/>
@@ -29513,7 +29516,7 @@
     </row>
     <row r="120" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B120" s="20" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C120" s="25"/>
       <c r="D120" s="25"/>
@@ -29584,7 +29587,7 @@
     </row>
     <row r="121" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B121" s="20" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C121" s="25"/>
       <c r="D121" s="25"/>
@@ -29722,7 +29725,7 @@
     </row>
     <row r="126" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B126" s="20" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C126" s="26"/>
       <c r="D126" s="26"/>
@@ -30463,7 +30466,7 @@
       <c r="P149" s="49"/>
       <c r="Q149" s="49"/>
       <c r="T149" s="195" t="str">
-        <f t="shared" ref="T149:AA149" si="80">IF(U5&gt;T147, "BEAT", IF(U5&lt;T146, "MISSED", "MET"))</f>
+        <f t="shared" ref="T149:Z149" si="80">IF(T148&gt;T147, "BEAT", IF(T148&lt;T146, "MISSED", "MET"))</f>
         <v>BEAT</v>
       </c>
       <c r="U149" s="195" t="str">
@@ -30491,7 +30494,7 @@
         <v>BEAT</v>
       </c>
       <c r="AA149" s="195" t="str">
-        <f t="shared" si="80"/>
+        <f>IF(AA148&gt;AA147, "BEAT", IF(AA148&lt;AA146, "MISSED", "MET"))</f>
         <v>MISSED</v>
       </c>
       <c r="AC149" s="49"/>
@@ -30659,35 +30662,35 @@
       <c r="P153" s="49"/>
       <c r="Q153" s="49"/>
       <c r="T153" s="195" t="str">
-        <f t="shared" ref="T153" si="89">IF(U138&gt;T151, "BEAT", IF(U138&lt;T150, "MISSED", "MET"))</f>
+        <f t="shared" ref="T153:Z153" si="89">IF(T152&gt;T151, "BEAT", IF(T152&lt;T150, "MISSED", "MET"))</f>
         <v>BEAT</v>
       </c>
       <c r="U153" s="195" t="str">
-        <f t="shared" ref="U153" si="90">IF(V138&gt;U151, "BEAT", IF(V138&lt;U150, "MISSED", "MET"))</f>
+        <f t="shared" si="89"/>
         <v>MISSED</v>
       </c>
       <c r="V153" s="195" t="str">
-        <f t="shared" ref="V153" si="91">IF(W138&gt;V151, "BEAT", IF(W138&lt;V150, "MISSED", "MET"))</f>
+        <f t="shared" si="89"/>
         <v>BEAT</v>
       </c>
       <c r="W153" s="195" t="str">
-        <f t="shared" ref="W153" si="92">IF(X138&gt;W151, "BEAT", IF(X138&lt;W150, "MISSED", "MET"))</f>
+        <f t="shared" si="89"/>
         <v>BEAT</v>
       </c>
       <c r="X153" s="195" t="str">
-        <f t="shared" ref="X153" si="93">IF(Y138&gt;X151, "BEAT", IF(Y138&lt;X150, "MISSED", "MET"))</f>
+        <f t="shared" si="89"/>
         <v>BEAT</v>
       </c>
       <c r="Y153" s="195" t="str">
-        <f t="shared" ref="Y153" si="94">IF(Z138&gt;Y151, "BEAT", IF(Z138&lt;Y150, "MISSED", "MET"))</f>
+        <f t="shared" si="89"/>
         <v>BEAT</v>
       </c>
       <c r="Z153" s="195" t="str">
-        <f t="shared" ref="Z153" si="95">IF(AA138&gt;Z151, "BEAT", IF(AA138&lt;Z150, "MISSED", "MET"))</f>
+        <f t="shared" si="89"/>
         <v>BEAT</v>
       </c>
       <c r="AA153" s="195" t="str">
-        <f t="shared" ref="AA153" si="96">IF(AB138&gt;AA151, "BEAT", IF(AB138&lt;AA150, "MISSED", "MET"))</f>
+        <f>IF(AA152&gt;AA151, "BEAT", IF(AA152&lt;AA150, "MISSED", "MET"))</f>
         <v>MISSED</v>
       </c>
       <c r="AC153" s="49"/>
@@ -30776,55 +30779,55 @@
         <v>180</v>
       </c>
       <c r="M158" s="139">
-        <f t="shared" ref="M158:Q159" si="97">M30/M5*365</f>
+        <f t="shared" ref="M158:Q159" si="90">M30/M5*365</f>
         <v>133.69421979440784</v>
       </c>
       <c r="N158" s="139">
-        <f t="shared" si="97"/>
+        <f t="shared" si="90"/>
         <v>152.91140215061483</v>
       </c>
       <c r="O158" s="139">
-        <f t="shared" si="97"/>
+        <f t="shared" si="90"/>
         <v>145.23661159324561</v>
       </c>
       <c r="P158" s="139">
-        <f t="shared" si="97"/>
+        <f t="shared" si="90"/>
         <v>137.8303503480538</v>
       </c>
       <c r="Q158" s="139">
-        <f t="shared" si="97"/>
+        <f t="shared" si="90"/>
         <v>131.6037563052133</v>
       </c>
       <c r="T158" s="139">
-        <f t="shared" ref="T158:AA158" si="98">T30/T5*90</f>
+        <f t="shared" ref="T158:AA158" si="91">T30/T5*90</f>
         <v>104.95764467056439</v>
       </c>
       <c r="U158" s="139">
-        <f t="shared" si="98"/>
+        <f t="shared" si="91"/>
         <v>113.19501033404484</v>
       </c>
       <c r="V158" s="139">
-        <f t="shared" si="98"/>
+        <f t="shared" si="91"/>
         <v>114.68995340449337</v>
       </c>
       <c r="W158" s="139">
-        <f t="shared" si="98"/>
+        <f t="shared" si="91"/>
         <v>93.317359459823237</v>
       </c>
       <c r="X158" s="139">
-        <f t="shared" si="98"/>
+        <f t="shared" si="91"/>
         <v>96.344546178343947</v>
       </c>
       <c r="Y158" s="139">
-        <f t="shared" si="98"/>
+        <f t="shared" si="91"/>
         <v>108.60342533561332</v>
       </c>
       <c r="Z158" s="139">
-        <f t="shared" si="98"/>
+        <f t="shared" si="91"/>
         <v>108.63165574394054</v>
       </c>
       <c r="AA158" s="139">
-        <f t="shared" si="98"/>
+        <f t="shared" si="91"/>
         <v>64.534109976050601</v>
       </c>
       <c r="AC158" s="139">
@@ -30837,55 +30840,55 @@
         <v>181</v>
       </c>
       <c r="M159" s="139">
-        <f t="shared" si="97"/>
+        <f t="shared" si="90"/>
         <v>0</v>
       </c>
       <c r="N159" s="139">
-        <f t="shared" si="97"/>
+        <f t="shared" si="90"/>
         <v>0</v>
       </c>
       <c r="O159" s="139">
-        <f t="shared" si="97"/>
+        <f t="shared" si="90"/>
         <v>0</v>
       </c>
       <c r="P159" s="139">
-        <f t="shared" si="97"/>
+        <f t="shared" si="90"/>
         <v>0</v>
       </c>
       <c r="Q159" s="139">
-        <f t="shared" si="97"/>
+        <f t="shared" si="90"/>
         <v>0</v>
       </c>
       <c r="T159" s="139">
-        <f t="shared" ref="T159:AA159" si="99">T31/T6*365</f>
+        <f t="shared" ref="T159:AA159" si="92">T31/T6*365</f>
         <v>0</v>
       </c>
       <c r="U159" s="139">
-        <f t="shared" si="99"/>
+        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="V159" s="139">
-        <f t="shared" si="99"/>
+        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="W159" s="139">
-        <f t="shared" si="99"/>
+        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="X159" s="139">
-        <f t="shared" si="99"/>
+        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="Y159" s="139">
-        <f t="shared" si="99"/>
+        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="Z159" s="139">
-        <f t="shared" si="99"/>
+        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="AA159" s="139">
-        <f t="shared" si="99"/>
+        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="AC159" s="139">
@@ -30918,35 +30921,35 @@
         <v>13.686287751306349</v>
       </c>
       <c r="T160" s="139">
-        <f t="shared" ref="T160:AA160" si="100">T37/T6*90</f>
+        <f t="shared" ref="T160:AA160" si="93">T37/T6*90</f>
         <v>14.085596967782692</v>
       </c>
       <c r="U160" s="139">
-        <f t="shared" si="100"/>
+        <f t="shared" si="93"/>
         <v>26.007872904348915</v>
       </c>
       <c r="V160" s="139">
-        <f t="shared" si="100"/>
+        <f t="shared" si="93"/>
         <v>46.270493073418663</v>
       </c>
       <c r="W160" s="139">
-        <f t="shared" si="100"/>
+        <f t="shared" si="93"/>
         <v>23.797704245423365</v>
       </c>
       <c r="X160" s="139">
-        <f t="shared" si="100"/>
+        <f t="shared" si="93"/>
         <v>27.599720410065238</v>
       </c>
       <c r="Y160" s="139">
-        <f t="shared" si="100"/>
+        <f t="shared" si="93"/>
         <v>18.67697494623031</v>
       </c>
       <c r="Z160" s="139">
-        <f t="shared" si="100"/>
+        <f t="shared" si="93"/>
         <v>12.368837492391966</v>
       </c>
       <c r="AA160" s="139">
-        <f t="shared" si="100"/>
+        <f t="shared" si="93"/>
         <v>23.046355033277873</v>
       </c>
       <c r="AC160" s="139">
@@ -30963,55 +30966,55 @@
         <v>108.80510521971044</v>
       </c>
       <c r="N161" s="139">
-        <f t="shared" ref="N161:Q161" si="101">N158+N159-N160</f>
+        <f t="shared" ref="N161:Q161" si="94">N158+N159-N160</f>
         <v>134.88753669027304</v>
       </c>
       <c r="O161" s="139">
+        <f t="shared" si="94"/>
+        <v>138.81496340313109</v>
+      </c>
+      <c r="P161" s="139">
+        <f t="shared" si="94"/>
+        <v>88.790616321440268</v>
+      </c>
+      <c r="Q161" s="139">
+        <f t="shared" si="94"/>
+        <v>117.91746855390694</v>
+      </c>
+      <c r="T161" s="139">
+        <f t="shared" ref="T161" si="95">T158+T159-T160</f>
+        <v>90.8720477027817</v>
+      </c>
+      <c r="U161" s="139">
+        <f t="shared" ref="U161" si="96">U158+U159-U160</f>
+        <v>87.187137429695923</v>
+      </c>
+      <c r="V161" s="139">
+        <f t="shared" ref="V161" si="97">V158+V159-V160</f>
+        <v>68.419460331074703</v>
+      </c>
+      <c r="W161" s="139">
+        <f t="shared" ref="W161" si="98">W158+W159-W160</f>
+        <v>69.519655214399876</v>
+      </c>
+      <c r="X161" s="139">
+        <f t="shared" ref="X161" si="99">X158+X159-X160</f>
+        <v>68.744825768278702</v>
+      </c>
+      <c r="Y161" s="139">
+        <f t="shared" ref="Y161" si="100">Y158+Y159-Y160</f>
+        <v>89.926450389383007</v>
+      </c>
+      <c r="Z161" s="139">
+        <f t="shared" ref="Z161:AA161" si="101">Z158+Z159-Z160</f>
+        <v>96.26281825154858</v>
+      </c>
+      <c r="AA161" s="139">
         <f t="shared" si="101"/>
-        <v>138.81496340313109</v>
-      </c>
-      <c r="P161" s="139">
-        <f t="shared" si="101"/>
-        <v>88.790616321440268</v>
-      </c>
-      <c r="Q161" s="139">
-        <f t="shared" si="101"/>
-        <v>117.91746855390694</v>
-      </c>
-      <c r="T161" s="139">
-        <f t="shared" ref="T161" si="102">T158+T159-T160</f>
-        <v>90.8720477027817</v>
-      </c>
-      <c r="U161" s="139">
-        <f t="shared" ref="U161" si="103">U158+U159-U160</f>
-        <v>87.187137429695923</v>
-      </c>
-      <c r="V161" s="139">
-        <f t="shared" ref="V161" si="104">V158+V159-V160</f>
-        <v>68.419460331074703</v>
-      </c>
-      <c r="W161" s="139">
-        <f t="shared" ref="W161" si="105">W158+W159-W160</f>
-        <v>69.519655214399876</v>
-      </c>
-      <c r="X161" s="139">
-        <f t="shared" ref="X161" si="106">X158+X159-X160</f>
-        <v>68.744825768278702</v>
-      </c>
-      <c r="Y161" s="139">
-        <f t="shared" ref="Y161" si="107">Y158+Y159-Y160</f>
-        <v>89.926450389383007</v>
-      </c>
-      <c r="Z161" s="139">
-        <f t="shared" ref="Z161:AA161" si="108">Z158+Z159-Z160</f>
-        <v>96.26281825154858</v>
-      </c>
-      <c r="AA161" s="139">
-        <f t="shared" si="108"/>
         <v>41.487754942772725</v>
       </c>
       <c r="AC161" s="139">
-        <f t="shared" ref="AC161" si="109">AC158+AC159-AC160</f>
+        <f t="shared" ref="AC161" si="102">AC158+AC159-AC160</f>
         <v>40.164814474593925</v>
       </c>
     </row>
@@ -31040,35 +31043,35 @@
         <v>0</v>
       </c>
       <c r="T162" s="139">
-        <f t="shared" ref="T162:AA162" si="110">T117/T48</f>
+        <f t="shared" ref="T162:AA162" si="103">T117/T48</f>
         <v>0</v>
       </c>
       <c r="U162" s="139">
-        <f t="shared" si="110"/>
+        <f t="shared" si="103"/>
         <v>0</v>
       </c>
       <c r="V162" s="139">
-        <f t="shared" si="110"/>
+        <f t="shared" si="103"/>
         <v>0</v>
       </c>
       <c r="W162" s="139">
-        <f t="shared" si="110"/>
+        <f t="shared" si="103"/>
         <v>0</v>
       </c>
       <c r="X162" s="139">
-        <f t="shared" si="110"/>
+        <f t="shared" si="103"/>
         <v>0</v>
       </c>
       <c r="Y162" s="139">
-        <f t="shared" si="110"/>
+        <f t="shared" si="103"/>
         <v>0</v>
       </c>
       <c r="Z162" s="139">
-        <f t="shared" si="110"/>
+        <f t="shared" si="103"/>
         <v>0</v>
       </c>
       <c r="AA162" s="139">
-        <f t="shared" si="110"/>
+        <f t="shared" si="103"/>
         <v>0</v>
       </c>
       <c r="AC162" s="139">
@@ -31101,35 +31104,35 @@
         <v>-0.70704657236408375</v>
       </c>
       <c r="T163" s="203">
-        <f t="shared" ref="T163:AA163" si="111">(T117-T116)/T48</f>
+        <f t="shared" ref="T163:AA163" si="104">(T117-T116)/T48</f>
         <v>-0.95080282790888426</v>
       </c>
       <c r="U163" s="203">
-        <f t="shared" si="111"/>
+        <f t="shared" si="104"/>
         <v>-0.90599389668243979</v>
       </c>
       <c r="V163" s="203">
-        <f t="shared" si="111"/>
+        <f t="shared" si="104"/>
         <v>-0.88284296675302665</v>
       </c>
       <c r="W163" s="203">
-        <f t="shared" si="111"/>
+        <f t="shared" si="104"/>
         <v>-0.91555413989488132</v>
       </c>
       <c r="X163" s="203">
-        <f t="shared" si="111"/>
+        <f t="shared" si="104"/>
         <v>-0.86899465270819587</v>
       </c>
       <c r="Y163" s="203">
-        <f t="shared" si="111"/>
+        <f t="shared" si="104"/>
         <v>-0.72647492981720518</v>
       </c>
       <c r="Z163" s="203">
-        <f t="shared" si="111"/>
+        <f t="shared" si="104"/>
         <v>-0.70704657236408375</v>
       </c>
       <c r="AA163" s="203">
-        <f t="shared" si="111"/>
+        <f t="shared" si="104"/>
         <v>-0.68695115254353079</v>
       </c>
       <c r="AC163" s="203">
@@ -31162,35 +31165,35 @@
         <v>2.2676594254840001</v>
       </c>
       <c r="T164" s="139">
-        <f t="shared" ref="T164:AA164" si="112">(T116+T30)/T39</f>
+        <f t="shared" ref="T164:AA164" si="105">(T116+T30)/T39</f>
         <v>3.3394102478565317</v>
       </c>
       <c r="U164" s="139">
-        <f t="shared" si="112"/>
+        <f t="shared" si="105"/>
         <v>2.8974467736346341</v>
       </c>
       <c r="V164" s="139">
-        <f t="shared" si="112"/>
+        <f t="shared" si="105"/>
         <v>2.715395784308817</v>
       </c>
       <c r="W164" s="139">
-        <f t="shared" si="112"/>
+        <f t="shared" si="105"/>
         <v>2.6887704000882846</v>
       </c>
       <c r="X164" s="139">
-        <f t="shared" si="112"/>
+        <f t="shared" si="105"/>
         <v>2.4846597518746183</v>
       </c>
       <c r="Y164" s="139">
-        <f t="shared" si="112"/>
+        <f t="shared" si="105"/>
         <v>2.4017725370863445</v>
       </c>
       <c r="Z164" s="139">
-        <f t="shared" si="112"/>
+        <f t="shared" si="105"/>
         <v>2.2676594254840001</v>
       </c>
       <c r="AA164" s="139">
-        <f t="shared" si="112"/>
+        <f t="shared" si="105"/>
         <v>1.9325582625717537</v>
       </c>
       <c r="AC164" s="139">
@@ -31223,35 +31226,35 @@
         <v>2.4783388537733191</v>
       </c>
       <c r="T165" s="139">
-        <f t="shared" ref="T165:AA165" si="113">T32/T39</f>
+        <f t="shared" ref="T165:AA165" si="106">T32/T39</f>
         <v>3.5957679252114221</v>
       </c>
       <c r="U165" s="139">
-        <f t="shared" si="113"/>
+        <f t="shared" si="106"/>
         <v>3.129493165083332</v>
       </c>
       <c r="V165" s="139">
-        <f t="shared" si="113"/>
+        <f t="shared" si="106"/>
         <v>2.9271504030441093</v>
       </c>
       <c r="W165" s="139">
-        <f t="shared" si="113"/>
+        <f t="shared" si="106"/>
         <v>2.9470125037192663</v>
       </c>
       <c r="X165" s="139">
-        <f t="shared" si="113"/>
+        <f t="shared" si="106"/>
         <v>2.7501208666647705</v>
       </c>
       <c r="Y165" s="139">
-        <f t="shared" si="113"/>
+        <f t="shared" si="106"/>
         <v>2.6541688855077976</v>
       </c>
       <c r="Z165" s="139">
-        <f t="shared" si="113"/>
+        <f t="shared" si="106"/>
         <v>2.4783388537733191</v>
       </c>
       <c r="AA165" s="139">
-        <f t="shared" si="113"/>
+        <f t="shared" si="106"/>
         <v>2.3066495444084523</v>
       </c>
       <c r="AC165" s="139">
@@ -31284,35 +31287,35 @@
         <v>N/A</v>
       </c>
       <c r="T166" s="205" t="str">
-        <f t="shared" ref="T166:AA166" si="114">IF(T13&gt;=0,"N/A",IF(T12&lt;=0,"N/A",T12/-T13))</f>
+        <f t="shared" ref="T166:AA166" si="107">IF(T13&gt;=0,"N/A",IF(T12&lt;=0,"N/A",T12/-T13))</f>
         <v>N/A</v>
       </c>
       <c r="U166" s="205" t="str">
-        <f t="shared" si="114"/>
+        <f t="shared" si="107"/>
         <v>N/A</v>
       </c>
       <c r="V166" s="205" t="str">
-        <f t="shared" si="114"/>
+        <f t="shared" si="107"/>
         <v>N/A</v>
       </c>
       <c r="W166" s="205" t="str">
-        <f t="shared" si="114"/>
+        <f t="shared" si="107"/>
         <v>N/A</v>
       </c>
       <c r="X166" s="205" t="str">
-        <f t="shared" si="114"/>
+        <f t="shared" si="107"/>
         <v>N/A</v>
       </c>
       <c r="Y166" s="205" t="str">
-        <f t="shared" si="114"/>
+        <f t="shared" si="107"/>
         <v>N/A</v>
       </c>
       <c r="Z166" s="205" t="str">
-        <f t="shared" si="114"/>
+        <f t="shared" si="107"/>
         <v>N/A</v>
       </c>
       <c r="AA166" s="205" t="str">
-        <f t="shared" si="114"/>
+        <f t="shared" si="107"/>
         <v>N/A</v>
       </c>
       <c r="AC166" s="205" t="str">
@@ -31608,31 +31611,31 @@
         <v>-49347</v>
       </c>
       <c r="U174" s="64">
-        <f t="shared" ref="U174:AA174" si="115">U58-U53+U119+U64</f>
+        <f t="shared" ref="U174:AA174" si="108">U58-U53+U119+U64</f>
         <v>-64293</v>
       </c>
       <c r="V174" s="64">
-        <f t="shared" si="115"/>
+        <f t="shared" si="108"/>
         <v>0</v>
       </c>
       <c r="W174" s="64">
-        <f t="shared" si="115"/>
+        <f t="shared" si="108"/>
         <v>29809</v>
       </c>
       <c r="X174" s="64">
-        <f t="shared" si="115"/>
+        <f t="shared" si="108"/>
         <v>-36419</v>
       </c>
       <c r="Y174" s="64">
-        <f t="shared" si="115"/>
+        <f t="shared" si="108"/>
         <v>-46368</v>
       </c>
       <c r="Z174" s="64">
-        <f t="shared" si="115"/>
+        <f t="shared" si="108"/>
         <v>114462</v>
       </c>
       <c r="AA174" s="64">
-        <f t="shared" si="115"/>
+        <f t="shared" si="108"/>
         <v>75934</v>
       </c>
       <c r="AC174" s="64">
@@ -31645,19 +31648,19 @@
         <v>314</v>
       </c>
       <c r="M175" s="64">
-        <f t="shared" ref="M175:P175" si="116">M118+M52+M119+M54+M56+M57+M55</f>
+        <f t="shared" ref="M175:P175" si="109">M118+M52+M119+M54+M56+M57+M55</f>
         <v>-603972</v>
       </c>
       <c r="N175" s="64">
-        <f t="shared" si="116"/>
+        <f t="shared" si="109"/>
         <v>-500062</v>
       </c>
       <c r="O175" s="64">
-        <f t="shared" si="116"/>
+        <f t="shared" si="109"/>
         <v>-216393</v>
       </c>
       <c r="P175" s="64">
-        <f t="shared" si="116"/>
+        <f t="shared" si="109"/>
         <v>-202032</v>
       </c>
       <c r="Q175" s="64">
@@ -31686,19 +31689,19 @@
         <v>-31.117410328396652</v>
       </c>
       <c r="N176" s="72">
-        <f t="shared" ref="N176:Q176" si="117">N170/N174</f>
+        <f t="shared" ref="N176:Q176" si="110">N170/N174</f>
         <v>-20.121230787144853</v>
       </c>
       <c r="O176" s="72">
-        <f t="shared" si="117"/>
+        <f t="shared" si="110"/>
         <v>-169.18232313158387</v>
       </c>
       <c r="P176" s="72">
-        <f t="shared" si="117"/>
+        <f t="shared" si="110"/>
         <v>-153.13123350282808</v>
       </c>
       <c r="Q176" s="72">
-        <f t="shared" si="117"/>
+        <f t="shared" si="110"/>
         <v>108.6619548175135</v>
       </c>
       <c r="T176" s="49"/>
@@ -31710,7 +31713,7 @@
       <c r="Z176" s="49"/>
       <c r="AA176" s="49"/>
       <c r="AC176" s="72">
-        <f t="shared" ref="AC176:AC177" ca="1" si="118">AC170/AC174</f>
+        <f t="shared" ref="AC176:AC177" ca="1" si="111">AC170/AC174</f>
         <v>55.167071899190589</v>
       </c>
     </row>
@@ -31723,19 +31726,19 @@
         <v>-26.916581960753149</v>
       </c>
       <c r="N177" s="72">
-        <f t="shared" ref="N177:Q177" si="119">N171/N175</f>
+        <f t="shared" ref="N177:Q177" si="112">N171/N175</f>
         <v>-12.727941955197556</v>
       </c>
       <c r="O177" s="72">
-        <f t="shared" si="119"/>
+        <f t="shared" si="112"/>
         <v>-54.027334756669582</v>
       </c>
       <c r="P177" s="72">
-        <f t="shared" si="119"/>
+        <f t="shared" si="112"/>
         <v>-31.733833947097491</v>
       </c>
       <c r="Q177" s="72">
-        <f t="shared" si="119"/>
+        <f t="shared" si="112"/>
         <v>-55.101089964665803</v>
       </c>
       <c r="T177" s="49"/>
@@ -31747,7 +31750,7 @@
       <c r="Z177" s="49"/>
       <c r="AA177" s="49"/>
       <c r="AC177" s="72">
-        <f t="shared" ca="1" si="118"/>
+        <f t="shared" ca="1" si="111"/>
         <v>-85.355018714852037</v>
       </c>
     </row>
@@ -31760,19 +31763,19 @@
         <v>-3.2136350340421331E-2</v>
       </c>
       <c r="N178" s="74">
-        <f t="shared" ref="N178:Q178" si="120">N174/N170</f>
+        <f t="shared" ref="N178:Q178" si="113">N174/N170</f>
         <v>-4.9698749076467263E-2</v>
       </c>
       <c r="O178" s="74">
-        <f t="shared" si="120"/>
+        <f t="shared" si="113"/>
         <v>-5.9107830031523813E-3</v>
       </c>
       <c r="P178" s="74">
-        <f t="shared" si="120"/>
+        <f t="shared" si="113"/>
         <v>-6.5303464037043202E-3</v>
       </c>
       <c r="Q178" s="74">
-        <f t="shared" si="120"/>
+        <f t="shared" si="113"/>
         <v>9.2028530287292954E-3</v>
       </c>
       <c r="T178" s="49"/>
@@ -31784,7 +31787,7 @@
       <c r="Z178" s="49"/>
       <c r="AA178" s="49"/>
       <c r="AC178" s="74">
-        <f t="shared" ref="AC178" ca="1" si="121">AC174/AC170</f>
+        <f t="shared" ref="AC178" ca="1" si="114">AC174/AC170</f>
         <v>1.8126755065546118E-2</v>
       </c>
     </row>
@@ -31797,19 +31800,19 @@
         <v>-3.4699371821717021E-2</v>
       </c>
       <c r="N179" s="74">
-        <f t="shared" ref="N179:Q179" si="122">N26/N126</f>
+        <f t="shared" ref="N179:Q179" si="115">N26/N126</f>
         <v>-4.1180507892930679E-2</v>
       </c>
       <c r="O179" s="74">
-        <f t="shared" si="122"/>
+        <f t="shared" si="115"/>
         <v>-6.7085953878406705E-3</v>
       </c>
       <c r="P179" s="74">
-        <f t="shared" si="122"/>
+        <f t="shared" si="115"/>
         <v>-8.9163237311385458E-3</v>
       </c>
       <c r="Q179" s="74">
-        <f t="shared" si="122"/>
+        <f t="shared" si="115"/>
         <v>4.1302621127879274E-2</v>
       </c>
       <c r="T179" s="49"/>
@@ -31821,7 +31824,7 @@
       <c r="Z179" s="49"/>
       <c r="AA179" s="49"/>
       <c r="AC179" s="74">
-        <f t="shared" ref="AC179" ca="1" si="123">AC26/AC126</f>
+        <f t="shared" ref="AC179" ca="1" si="116">AC26/AC126</f>
         <v>5.3380782918149475E-2</v>
       </c>
     </row>
@@ -31834,19 +31837,19 @@
         <v>0</v>
       </c>
       <c r="N180" s="176">
-        <f t="shared" ref="N180:Q180" si="124">N81/N126</f>
+        <f t="shared" ref="N180:Q180" si="117">N81/N126</f>
         <v>0</v>
       </c>
       <c r="O180" s="176">
-        <f t="shared" si="124"/>
+        <f t="shared" si="117"/>
         <v>0</v>
       </c>
       <c r="P180" s="176">
-        <f t="shared" si="124"/>
+        <f t="shared" si="117"/>
         <v>0</v>
       </c>
       <c r="Q180" s="176">
-        <f t="shared" si="124"/>
+        <f t="shared" si="117"/>
         <v>0</v>
       </c>
       <c r="T180" s="49"/>
@@ -31858,13 +31861,13 @@
       <c r="Z180" s="49"/>
       <c r="AA180" s="49"/>
       <c r="AC180" s="176">
-        <f t="shared" ref="AC180" ca="1" si="125">AC81/AC126</f>
+        <f t="shared" ref="AC180" ca="1" si="118">AC81/AC126</f>
         <v>0</v>
       </c>
     </row>
     <row r="181" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B181" s="20" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="M181" s="176">
         <f>-M62/M170</f>
@@ -31901,7 +31904,7 @@
     </row>
     <row r="182" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B182" s="20" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="M182" s="176">
         <f>-(M62+M63)/M170</f>
@@ -31938,25 +31941,25 @@
     </row>
     <row r="183" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B183" s="20" t="s">
-        <v>320</v>
-      </c>
-      <c r="M183" s="72">
+        <v>407</v>
+      </c>
+      <c r="M183" s="176">
         <f>M175/M5</f>
         <v>-0.67690742077350341</v>
       </c>
-      <c r="N183" s="72">
+      <c r="N183" s="176">
         <f>N175/N5</f>
         <v>-0.47238898109828159</v>
       </c>
-      <c r="O183" s="72">
+      <c r="O183" s="176">
         <f>O175/O5</f>
         <v>-0.16542896721281397</v>
       </c>
-      <c r="P183" s="72">
+      <c r="P183" s="176">
         <f>P175/P5</f>
         <v>-0.14131432280591805</v>
       </c>
-      <c r="Q183" s="72">
+      <c r="Q183" s="176">
         <f>Q175/Q5</f>
         <v>-5.8690949550842808E-2</v>
       </c>
@@ -31968,34 +31971,34 @@
       <c r="Y183" s="49"/>
       <c r="Z183" s="49"/>
       <c r="AA183" s="49"/>
-      <c r="AC183" s="72">
+      <c r="AC183" s="176">
         <f>AC175/AC5</f>
         <v>-3.2430800141120472E-2</v>
       </c>
     </row>
     <row r="184" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B184" s="20" t="s">
-        <v>323</v>
+        <v>408</v>
       </c>
       <c r="M184" s="176">
-        <f>-M63/M174</f>
-        <v>0</v>
+        <f>M174/M5</f>
+        <v>-0.6527023755620609</v>
       </c>
       <c r="N184" s="176">
-        <f>-N63/N174</f>
-        <v>0</v>
+        <f t="shared" ref="N184:Q184" si="119">N174/N5</f>
+        <v>-0.3812991164587311</v>
       </c>
       <c r="O184" s="176">
-        <f>-O63/O174</f>
-        <v>0</v>
+        <f t="shared" si="119"/>
+        <v>-6.132307701716725E-2</v>
       </c>
       <c r="P184" s="176">
-        <f>-P63/P174</f>
-        <v>0</v>
+        <f t="shared" si="119"/>
+        <v>-3.6728210264789486E-2</v>
       </c>
       <c r="Q184" s="176">
-        <f>-Q63/Q174</f>
-        <v>0</v>
+        <f t="shared" si="119"/>
+        <v>3.8175256989442262E-2</v>
       </c>
       <c r="T184" s="49"/>
       <c r="U184" s="49"/>
@@ -32006,33 +32009,33 @@
       <c r="Z184" s="49"/>
       <c r="AA184" s="49"/>
       <c r="AC184" s="176">
-        <f>-AC63/AC174</f>
-        <v>0</v>
+        <f t="shared" ref="AC184" si="120">AC174/AC5</f>
+        <v>6.4346749744368631E-2</v>
       </c>
     </row>
     <row r="185" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B185" s="20" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="M185" s="176">
-        <f>-M62/M174</f>
+        <f>-M63/M174</f>
         <v>0</v>
       </c>
       <c r="N185" s="176">
-        <f>-N62/N174</f>
+        <f>-N63/N174</f>
         <v>0</v>
       </c>
       <c r="O185" s="176">
-        <f>-O62/O174</f>
-        <v>-1.2792495169232687</v>
+        <f>-O63/O174</f>
+        <v>0</v>
       </c>
       <c r="P185" s="176">
-        <f>-P62/P174</f>
-        <v>-7.44160048753547</v>
+        <f>-P63/P174</f>
+        <v>0</v>
       </c>
       <c r="Q185" s="176">
-        <f>-Q62/Q174</f>
-        <v>5.3526283260685705</v>
+        <f>-Q63/Q174</f>
+        <v>0</v>
       </c>
       <c r="T185" s="49"/>
       <c r="U185" s="49"/>
@@ -32043,32 +32046,32 @@
       <c r="Z185" s="49"/>
       <c r="AA185" s="49"/>
       <c r="AC185" s="176">
-        <f>-AC62/AC174</f>
-        <v>3.2095084983598028</v>
+        <f>-AC63/AC174</f>
+        <v>0</v>
       </c>
     </row>
     <row r="186" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B186" s="20" t="s">
-        <v>336</v>
+        <v>324</v>
       </c>
       <c r="M186" s="176">
-        <f>(-M63-M62)/M174</f>
+        <f>-M62/M174</f>
         <v>0</v>
       </c>
       <c r="N186" s="176">
-        <f>(-N63-N62)/N174</f>
+        <f>-N62/N174</f>
         <v>0</v>
       </c>
       <c r="O186" s="176">
-        <f>(-O63-O62)/O174</f>
+        <f>-O62/O174</f>
         <v>-1.2792495169232687</v>
       </c>
       <c r="P186" s="176">
-        <f>(-P63-P62)/P174</f>
+        <f>-P62/P174</f>
         <v>-7.44160048753547</v>
       </c>
       <c r="Q186" s="176">
-        <f>(-Q63-Q62)/Q174</f>
+        <f>-Q62/Q174</f>
         <v>5.3526283260685705</v>
       </c>
       <c r="T186" s="49"/>
@@ -32080,33 +32083,33 @@
       <c r="Z186" s="49"/>
       <c r="AA186" s="49"/>
       <c r="AC186" s="176">
-        <f>(-AC63-AC62)/AC174</f>
+        <f>-AC62/AC174</f>
         <v>3.2095084983598028</v>
       </c>
     </row>
     <row r="187" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B187" s="20" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="M187" s="176">
-        <f>M79/M77</f>
-        <v>0.32041292188722126</v>
+        <f>(-M63-M62)/M174</f>
+        <v>0</v>
       </c>
       <c r="N187" s="176">
-        <f>N79/N77</f>
-        <v>0.31207180184527727</v>
+        <f>(-N63-N62)/N174</f>
+        <v>0</v>
       </c>
       <c r="O187" s="176">
-        <f>O79/O77</f>
-        <v>0.22510733498180183</v>
+        <f>(-O63-O62)/O174</f>
+        <v>-1.2792495169232687</v>
       </c>
       <c r="P187" s="176">
-        <f>P79/P77</f>
-        <v>0.22494029842627195</v>
+        <f>(-P63-P62)/P174</f>
+        <v>-7.44160048753547</v>
       </c>
       <c r="Q187" s="176">
-        <f>Q79/Q77</f>
-        <v>0.22012147206199109</v>
+        <f>(-Q63-Q62)/Q174</f>
+        <v>5.3526283260685705</v>
       </c>
       <c r="T187" s="49"/>
       <c r="U187" s="49"/>
@@ -32117,807 +32120,844 @@
       <c r="Z187" s="49"/>
       <c r="AA187" s="49"/>
       <c r="AC187" s="176">
+        <f>(-AC63-AC62)/AC174</f>
+        <v>3.2095084983598028</v>
+      </c>
+    </row>
+    <row r="188" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B188" s="20" t="s">
+        <v>329</v>
+      </c>
+      <c r="M188" s="176">
+        <f>M79/M77</f>
+        <v>0.32041292188722126</v>
+      </c>
+      <c r="N188" s="176">
+        <f>N79/N77</f>
+        <v>0.31207180184527727</v>
+      </c>
+      <c r="O188" s="176">
+        <f>O79/O77</f>
+        <v>0.22510733498180183</v>
+      </c>
+      <c r="P188" s="176">
+        <f>P79/P77</f>
+        <v>0.22494029842627195</v>
+      </c>
+      <c r="Q188" s="176">
+        <f>Q79/Q77</f>
+        <v>0.22012147206199109</v>
+      </c>
+      <c r="T188" s="49"/>
+      <c r="U188" s="49"/>
+      <c r="V188" s="49"/>
+      <c r="W188" s="49"/>
+      <c r="X188" s="49"/>
+      <c r="Y188" s="49"/>
+      <c r="Z188" s="49"/>
+      <c r="AA188" s="49"/>
+      <c r="AC188" s="176">
         <f>AC79/AC77</f>
         <v>0.22116382280992736</v>
       </c>
     </row>
-    <row r="188" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B188" s="20" t="s">
-        <v>331</v>
-      </c>
-      <c r="M188" s="72">
+    <row r="189" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B189" s="20" t="s">
+        <v>330</v>
+      </c>
+      <c r="M189" s="72">
         <f>M116/M74</f>
         <v>3.4406590811823912</v>
       </c>
-      <c r="N188" s="72">
+      <c r="N189" s="72">
         <f>N116/N74</f>
         <v>3.1518128961309455</v>
       </c>
-      <c r="O188" s="72">
+      <c r="O189" s="72">
         <f>O116/O74</f>
         <v>3.3036556282545391</v>
       </c>
-      <c r="P188" s="72">
+      <c r="P189" s="72">
         <f>P116/P74</f>
         <v>2.9547392260645196</v>
       </c>
-      <c r="Q188" s="72">
+      <c r="Q189" s="72">
         <f>Q116/Q74</f>
         <v>2.8105061440443424</v>
       </c>
-      <c r="T188" s="72">
-        <f t="shared" ref="T188:AA188" si="126">T116/T74</f>
+      <c r="T189" s="72">
+        <f t="shared" ref="T189:AA189" si="121">T116/T74</f>
         <v>3.1700129828095962</v>
       </c>
-      <c r="U188" s="72">
-        <f t="shared" si="126"/>
+      <c r="U189" s="72">
+        <f t="shared" si="121"/>
         <v>2.8548832876333474</v>
       </c>
-      <c r="V188" s="72">
-        <f t="shared" si="126"/>
+      <c r="V189" s="72">
+        <f t="shared" si="121"/>
         <v>2.9547392260645196</v>
       </c>
-      <c r="W188" s="72">
-        <f t="shared" si="126"/>
+      <c r="W189" s="72">
+        <f t="shared" si="121"/>
         <v>2.90639187049916</v>
       </c>
-      <c r="X188" s="72">
-        <f t="shared" si="126"/>
+      <c r="X189" s="72">
+        <f t="shared" si="121"/>
         <v>2.7258512829976911</v>
       </c>
-      <c r="Y188" s="72">
-        <f t="shared" si="126"/>
+      <c r="Y189" s="72">
+        <f t="shared" si="121"/>
         <v>2.6146535764375876</v>
       </c>
-      <c r="Z188" s="72">
-        <f t="shared" si="126"/>
+      <c r="Z189" s="72">
+        <f t="shared" si="121"/>
         <v>2.8105061440443424</v>
       </c>
-      <c r="AA188" s="72">
-        <f t="shared" si="126"/>
+      <c r="AA189" s="72">
+        <f t="shared" si="121"/>
         <v>2.4951118677971147</v>
       </c>
-      <c r="AC188" s="72">
+      <c r="AC189" s="72">
         <f>AC116/AC74</f>
         <v>2.4951118677971147</v>
       </c>
     </row>
-    <row r="189" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B189" s="20" t="s">
-        <v>333</v>
-      </c>
-      <c r="M189" s="176">
+    <row r="190" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B190" s="20" t="s">
+        <v>332</v>
+      </c>
+      <c r="M190" s="176">
         <f>M53/M58</f>
         <v>-9.3805469133780903</v>
       </c>
-      <c r="N189" s="176">
+      <c r="N190" s="176">
         <f>N53/N58</f>
         <v>-37.054403366396151</v>
       </c>
-      <c r="O189" s="176">
+      <c r="O190" s="176">
         <f>O53/O58</f>
         <v>1.243655586093446</v>
       </c>
-      <c r="P189" s="176">
+      <c r="P190" s="176">
         <f>P53/P58</f>
         <v>1.1172492318250589</v>
       </c>
-      <c r="Q189" s="176">
+      <c r="Q190" s="176">
         <f>Q53/Q58</f>
         <v>0.78305424452059225</v>
       </c>
-      <c r="T189" s="176">
-        <f t="shared" ref="T189:AA189" si="127">T53/T58</f>
+      <c r="T190" s="176">
+        <f t="shared" ref="T190:AA190" si="122">T53/T58</f>
         <v>2.0334871485250994</v>
       </c>
-      <c r="U189" s="176">
+      <c r="U190" s="176">
+        <f t="shared" si="122"/>
+        <v>3.1167794798717492</v>
+      </c>
+      <c r="V190" s="176" t="e">
+        <f t="shared" si="122"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W190" s="176">
+        <f t="shared" si="122"/>
+        <v>0.6416782911211576</v>
+      </c>
+      <c r="X190" s="176">
+        <f t="shared" si="122"/>
+        <v>1.8757303965181427</v>
+      </c>
+      <c r="Y190" s="176">
+        <f t="shared" si="122"/>
+        <v>2.5282091188850764</v>
+      </c>
+      <c r="Z190" s="176">
+        <f t="shared" si="122"/>
+        <v>0.35555092460569898</v>
+      </c>
+      <c r="AA190" s="176">
+        <f t="shared" si="122"/>
+        <v>0.40408404584318719</v>
+      </c>
+      <c r="AC190" s="176">
+        <f>AC53/AC58</f>
+        <v>0.69669698594761198</v>
+      </c>
+    </row>
+    <row r="191" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B191" s="20" t="s">
+        <v>333</v>
+      </c>
+      <c r="M191" s="176">
+        <f>M53/M5</f>
+        <v>0.57784459995606618</v>
+      </c>
+      <c r="N191" s="176">
+        <f>N53/N5</f>
+        <v>0.3493733592422309</v>
+      </c>
+      <c r="O191" s="176">
+        <f>O53/O5</f>
+        <v>0.28435361356255617</v>
+      </c>
+      <c r="P191" s="176">
+        <f>P53/P5</f>
+        <v>0.25051410681111086</v>
+      </c>
+      <c r="Q191" s="176">
+        <f>Q53/Q5</f>
+        <v>0.18047997854178516</v>
+      </c>
+      <c r="T191" s="176">
+        <f t="shared" ref="T191:AA191" si="123">T53/T5</f>
+        <v>0.29819479973312507</v>
+      </c>
+      <c r="U191" s="176">
+        <f t="shared" si="123"/>
+        <v>0.24668619749445234</v>
+      </c>
+      <c r="V191" s="176">
+        <f t="shared" si="123"/>
+        <v>0</v>
+      </c>
+      <c r="W191" s="176">
+        <f t="shared" si="123"/>
+        <v>0.21412187626183318</v>
+      </c>
+      <c r="X191" s="176">
+        <f t="shared" si="123"/>
+        <v>0.21564822186836519</v>
+      </c>
+      <c r="Y191" s="176">
+        <f t="shared" si="123"/>
+        <v>0.17385730930425455</v>
+      </c>
+      <c r="Z191" s="176">
+        <f t="shared" si="123"/>
+        <v>0.13476004298420102</v>
+      </c>
+      <c r="AA191" s="176">
+        <f t="shared" si="123"/>
+        <v>0.1274194396508454</v>
+      </c>
+      <c r="AC191" s="176">
+        <f>AC53/AC5</f>
+        <v>0.16003121393504871</v>
+      </c>
+    </row>
+    <row r="192" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B192" s="20" t="s">
+        <v>338</v>
+      </c>
+      <c r="M192" s="72">
+        <f>(M116-M117)/M74</f>
+        <v>3.4406590811823912</v>
+      </c>
+      <c r="N192" s="72">
+        <f>(N116-N117)/N74</f>
+        <v>3.1518128961309455</v>
+      </c>
+      <c r="O192" s="72">
+        <f>(O116-O117)/O74</f>
+        <v>3.3036556282545391</v>
+      </c>
+      <c r="P192" s="72">
+        <f>(P116-P117)/P74</f>
+        <v>2.9547392260645196</v>
+      </c>
+      <c r="Q192" s="72">
+        <f>(Q116-Q117)/Q74</f>
+        <v>2.8105061440443424</v>
+      </c>
+      <c r="T192" s="72">
+        <f t="shared" ref="T192:AA192" si="124">(T116-T117)/T74</f>
+        <v>3.1700129828095962</v>
+      </c>
+      <c r="U192" s="72">
+        <f t="shared" si="124"/>
+        <v>2.8548832876333474</v>
+      </c>
+      <c r="V192" s="72">
+        <f t="shared" si="124"/>
+        <v>2.9547392260645196</v>
+      </c>
+      <c r="W192" s="72">
+        <f t="shared" si="124"/>
+        <v>2.90639187049916</v>
+      </c>
+      <c r="X192" s="72">
+        <f t="shared" si="124"/>
+        <v>2.7258512829976911</v>
+      </c>
+      <c r="Y192" s="72">
+        <f t="shared" si="124"/>
+        <v>2.6146535764375876</v>
+      </c>
+      <c r="Z192" s="72">
+        <f t="shared" si="124"/>
+        <v>2.8105061440443424</v>
+      </c>
+      <c r="AA192" s="72">
+        <f t="shared" si="124"/>
+        <v>2.4951118677971147</v>
+      </c>
+      <c r="AC192" s="72">
+        <f>(AC116-AC117)/AC74</f>
+        <v>2.4951118677971147</v>
+      </c>
+    </row>
+    <row r="193" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B193" s="20" t="s">
+        <v>343</v>
+      </c>
+      <c r="M193" s="176">
+        <f>(M116-M117)/M170</f>
+        <v>0.10292130066354745</v>
+      </c>
+      <c r="N193" s="176">
+        <f>(N116-N117)/N170</f>
+        <v>0.21632209307693517</v>
+      </c>
+      <c r="O193" s="176">
+        <f>(O116-O117)/O170</f>
+        <v>0.1385180556920142</v>
+      </c>
+      <c r="P193" s="176">
+        <f>(P116-P117)/P170</f>
+        <v>0.20265701138988473</v>
+      </c>
+      <c r="Q193" s="176">
+        <f>(Q116-Q117)/Q170</f>
+        <v>0.22039997795949329</v>
+      </c>
+      <c r="T193" s="49"/>
+      <c r="U193" s="49"/>
+      <c r="V193" s="49"/>
+      <c r="W193" s="49"/>
+      <c r="X193" s="49"/>
+      <c r="Y193" s="49"/>
+      <c r="Z193" s="49"/>
+      <c r="AA193" s="49"/>
+      <c r="AC193" s="176">
+        <f ca="1">(AC116-AC117)/AC170</f>
+        <v>0.22020548280259802</v>
+      </c>
+    </row>
+    <row r="194" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B194" s="20" t="s">
+        <v>352</v>
+      </c>
+      <c r="M194" s="176">
+        <f>-M119/M5</f>
+        <v>1.325746537973577E-2</v>
+      </c>
+      <c r="N194" s="176">
+        <f>-N119/N5</f>
+        <v>2.2497097529617479E-2</v>
+      </c>
+      <c r="O194" s="176">
+        <f>-O119/O5</f>
+        <v>5.6128408833764501E-3</v>
+      </c>
+      <c r="P194" s="176">
+        <f>-P119/P5</f>
+        <v>1.0438116928173332E-2</v>
+      </c>
+      <c r="Q194" s="176">
+        <f>-Q119/Q5</f>
+        <v>1.1826854061786744E-2</v>
+      </c>
+      <c r="T194" s="176">
+        <f t="shared" ref="T194:AA194" si="125">-T119/T5</f>
+        <v>4.4837519327879894E-3</v>
+      </c>
+      <c r="U194" s="176">
+        <f t="shared" si="125"/>
+        <v>1.3745830431435797E-2</v>
+      </c>
+      <c r="V194" s="176">
+        <f t="shared" si="125"/>
+        <v>0</v>
+      </c>
+      <c r="W194" s="176">
+        <f t="shared" si="125"/>
+        <v>3.5981874467225984E-2</v>
+      </c>
+      <c r="X194" s="176">
+        <f t="shared" si="125"/>
+        <v>0</v>
+      </c>
+      <c r="Y194" s="176">
+        <f t="shared" si="125"/>
+        <v>7.6961808553852587E-3</v>
+      </c>
+      <c r="Z194" s="176">
+        <f t="shared" si="125"/>
+        <v>6.3437031679023587E-3</v>
+      </c>
+      <c r="AA194" s="176">
+        <f t="shared" si="125"/>
+        <v>6.415189946030183E-3</v>
+      </c>
+      <c r="AC194" s="176">
+        <f>-AC119/AC5</f>
+        <v>5.3219161289936798E-3</v>
+      </c>
+    </row>
+    <row r="195" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B195" s="20" t="s">
+        <v>353</v>
+      </c>
+      <c r="M195" s="176">
+        <f>-(M119/M58)</f>
+        <v>-0.21521750996124667</v>
+      </c>
+      <c r="N195" s="176">
+        <f>-(N119/N58)</f>
+        <v>-2.3860334635808034</v>
+      </c>
+      <c r="O195" s="176">
+        <f>-(O119/O58)</f>
+        <v>2.4548451595214689E-2</v>
+      </c>
+      <c r="P195" s="176">
+        <f>-(P119/P58)</f>
+        <v>4.6552181304883568E-2</v>
+      </c>
+      <c r="Q195" s="176">
+        <f>-(Q119/Q58)</f>
+        <v>5.1313549276955236E-2</v>
+      </c>
+      <c r="T195" s="176">
+        <f t="shared" ref="T195:AA195" si="126">-(T119/T58)</f>
+        <v>3.0576160082801448E-2</v>
+      </c>
+      <c r="U195" s="176">
+        <f t="shared" si="126"/>
+        <v>0.17367296045600286</v>
+      </c>
+      <c r="V195" s="176" t="e">
+        <f t="shared" si="126"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W195" s="176">
+        <f t="shared" si="126"/>
+        <v>0.10783012050217644</v>
+      </c>
+      <c r="X195" s="176">
+        <f t="shared" si="126"/>
+        <v>0</v>
+      </c>
+      <c r="Y195" s="176">
+        <f t="shared" si="126"/>
+        <v>0.11191680520674896</v>
+      </c>
+      <c r="Z195" s="176">
+        <f t="shared" si="126"/>
+        <v>1.6737227718428501E-2</v>
+      </c>
+      <c r="AA195" s="176">
+        <f t="shared" si="126"/>
+        <v>2.0344430295312594E-2</v>
+      </c>
+      <c r="AC195" s="176">
+        <f>-(AC119/AC58)</f>
+        <v>2.3168998318295178E-2</v>
+      </c>
+    </row>
+    <row r="196" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B196" s="20" t="s">
+        <v>354</v>
+      </c>
+      <c r="M196" s="176">
+        <f>-M119/M52</f>
+        <v>0.80442026521591292</v>
+      </c>
+      <c r="N196" s="176">
+        <f>-N119/N52</f>
+        <v>1.2719649628798804</v>
+      </c>
+      <c r="O196" s="176">
+        <f>-O119/O52</f>
+        <v>0.32491038633446917</v>
+      </c>
+      <c r="P196" s="176">
+        <f>-P119/P52</f>
+        <v>0.86600510677808729</v>
+      </c>
+      <c r="Q196" s="176">
+        <f>-Q119/Q52</f>
+        <v>1.1225175319700631</v>
+      </c>
+      <c r="T196" s="176">
+        <f t="shared" ref="T196:AA196" si="127">-T119/T52</f>
+        <v>0.30953940187731938</v>
+      </c>
+      <c r="U196" s="176">
         <f t="shared" si="127"/>
-        <v>3.1167794798717492</v>
-      </c>
-      <c r="V189" s="176" t="e">
+        <v>1.0752095280105867</v>
+      </c>
+      <c r="V196" s="176" t="e">
         <f t="shared" si="127"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W189" s="176">
+      <c r="W196" s="176">
         <f t="shared" si="127"/>
-        <v>0.6416782911211576</v>
-      </c>
-      <c r="X189" s="176">
+        <v>3.9446664617276359</v>
+      </c>
+      <c r="X196" s="176">
         <f t="shared" si="127"/>
-        <v>1.8757303965181427</v>
-      </c>
-      <c r="Y189" s="176">
+        <v>0</v>
+      </c>
+      <c r="Y196" s="176">
         <f t="shared" si="127"/>
-        <v>2.5282091188850764</v>
-      </c>
-      <c r="Z189" s="176">
+        <v>0.7010857522712165</v>
+      </c>
+      <c r="Z196" s="176">
         <f t="shared" si="127"/>
-        <v>0.35555092460569898</v>
-      </c>
-      <c r="AA189" s="176">
+        <v>0.61371405590187011</v>
+      </c>
+      <c r="AA196" s="176">
         <f t="shared" si="127"/>
-        <v>0.40408404584318719</v>
-      </c>
-      <c r="AC189" s="176">
-        <f>AC53/AC58</f>
-        <v>0.69669698594761198</v>
-      </c>
-    </row>
-    <row r="190" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B190" s="20" t="s">
-        <v>334</v>
-      </c>
-      <c r="M190" s="176">
-        <f>M53/M5</f>
-        <v>0.57784459995606618</v>
-      </c>
-      <c r="N190" s="176">
-        <f>N53/N5</f>
-        <v>0.3493733592422309</v>
-      </c>
-      <c r="O190" s="176">
-        <f>O53/O5</f>
-        <v>0.28435361356255617</v>
-      </c>
-      <c r="P190" s="176">
-        <f>P53/P5</f>
-        <v>0.25051410681111086</v>
-      </c>
-      <c r="Q190" s="176">
-        <f>Q53/Q5</f>
-        <v>0.18047997854178516</v>
-      </c>
-      <c r="T190" s="176">
-        <f t="shared" ref="T190:AA190" si="128">T53/T5</f>
-        <v>0.29819479973312507</v>
-      </c>
-      <c r="U190" s="176">
-        <f t="shared" si="128"/>
-        <v>0.24668619749445234</v>
-      </c>
-      <c r="V190" s="176">
-        <f t="shared" si="128"/>
-        <v>0</v>
-      </c>
-      <c r="W190" s="176">
-        <f t="shared" si="128"/>
-        <v>0.21412187626183318</v>
-      </c>
-      <c r="X190" s="176">
-        <f t="shared" si="128"/>
-        <v>0.21564822186836519</v>
-      </c>
-      <c r="Y190" s="176">
-        <f t="shared" si="128"/>
-        <v>0.17385730930425455</v>
-      </c>
-      <c r="Z190" s="176">
-        <f t="shared" si="128"/>
-        <v>0.13476004298420102</v>
-      </c>
-      <c r="AA190" s="176">
-        <f t="shared" si="128"/>
-        <v>0.1274194396508454</v>
-      </c>
-      <c r="AC190" s="176">
-        <f>AC53/AC5</f>
-        <v>0.16003121393504871</v>
-      </c>
-    </row>
-    <row r="191" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B191" s="20" t="s">
-        <v>339</v>
-      </c>
-      <c r="M191" s="72">
-        <f>(M116-M117)/M74</f>
-        <v>3.4406590811823912</v>
-      </c>
-      <c r="N191" s="72">
-        <f>(N116-N117)/N74</f>
-        <v>3.1518128961309455</v>
-      </c>
-      <c r="O191" s="72">
-        <f>(O116-O117)/O74</f>
-        <v>3.3036556282545391</v>
-      </c>
-      <c r="P191" s="72">
-        <f>(P116-P117)/P74</f>
-        <v>2.9547392260645196</v>
-      </c>
-      <c r="Q191" s="72">
-        <f>(Q116-Q117)/Q74</f>
-        <v>2.8105061440443424</v>
-      </c>
-      <c r="T191" s="72">
-        <f t="shared" ref="T191:AA191" si="129">(T116-T117)/T74</f>
-        <v>3.1700129828095962</v>
-      </c>
-      <c r="U191" s="72">
-        <f t="shared" si="129"/>
-        <v>2.8548832876333474</v>
-      </c>
-      <c r="V191" s="72">
-        <f t="shared" si="129"/>
-        <v>2.9547392260645196</v>
-      </c>
-      <c r="W191" s="72">
-        <f t="shared" si="129"/>
-        <v>2.90639187049916</v>
-      </c>
-      <c r="X191" s="72">
-        <f t="shared" si="129"/>
-        <v>2.7258512829976911</v>
-      </c>
-      <c r="Y191" s="72">
-        <f t="shared" si="129"/>
-        <v>2.6146535764375876</v>
-      </c>
-      <c r="Z191" s="72">
-        <f t="shared" si="129"/>
-        <v>2.8105061440443424</v>
-      </c>
-      <c r="AA191" s="72">
-        <f t="shared" si="129"/>
-        <v>2.4951118677971147</v>
-      </c>
-      <c r="AC191" s="72">
-        <f>(AC116-AC117)/AC74</f>
-        <v>2.4951118677971147</v>
-      </c>
-    </row>
-    <row r="192" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B192" s="20" t="s">
-        <v>344</v>
-      </c>
-      <c r="M192" s="176">
-        <f>(M116-M117)/M170</f>
-        <v>0.10292130066354745</v>
-      </c>
-      <c r="N192" s="176">
-        <f>(N116-N117)/N170</f>
-        <v>0.21632209307693517</v>
-      </c>
-      <c r="O192" s="176">
-        <f>(O116-O117)/O170</f>
-        <v>0.1385180556920142</v>
-      </c>
-      <c r="P192" s="176">
-        <f>(P116-P117)/P170</f>
-        <v>0.20265701138988473</v>
-      </c>
-      <c r="Q192" s="176">
-        <f>(Q116-Q117)/Q170</f>
-        <v>0.22039997795949329</v>
-      </c>
-      <c r="T192" s="49"/>
-      <c r="U192" s="49"/>
-      <c r="V192" s="49"/>
-      <c r="W192" s="49"/>
-      <c r="X192" s="49"/>
-      <c r="Y192" s="49"/>
-      <c r="Z192" s="49"/>
-      <c r="AA192" s="49"/>
-      <c r="AC192" s="176">
-        <f ca="1">(AC116-AC117)/AC170</f>
-        <v>0.22020548280259802</v>
-      </c>
-    </row>
-    <row r="193" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B193" s="20" t="s">
-        <v>353</v>
-      </c>
-      <c r="M193" s="176">
-        <f>-M119/M5</f>
-        <v>1.325746537973577E-2</v>
-      </c>
-      <c r="N193" s="176">
-        <f>-N119/N5</f>
-        <v>2.2497097529617479E-2</v>
-      </c>
-      <c r="O193" s="176">
-        <f>-O119/O5</f>
-        <v>5.6128408833764501E-3</v>
-      </c>
-      <c r="P193" s="176">
-        <f>-P119/P5</f>
-        <v>1.0438116928173332E-2</v>
-      </c>
-      <c r="Q193" s="176">
-        <f>-Q119/Q5</f>
-        <v>1.1826854061786744E-2</v>
-      </c>
-      <c r="T193" s="176">
-        <f t="shared" ref="T193:AA193" si="130">-T119/T5</f>
-        <v>4.4837519327879894E-3</v>
-      </c>
-      <c r="U193" s="176">
-        <f t="shared" si="130"/>
-        <v>1.3745830431435797E-2</v>
-      </c>
-      <c r="V193" s="176">
-        <f t="shared" si="130"/>
-        <v>0</v>
-      </c>
-      <c r="W193" s="176">
-        <f t="shared" si="130"/>
-        <v>3.5981874467225984E-2</v>
-      </c>
-      <c r="X193" s="176">
-        <f t="shared" si="130"/>
-        <v>0</v>
-      </c>
-      <c r="Y193" s="176">
-        <f t="shared" si="130"/>
-        <v>7.6961808553852587E-3</v>
-      </c>
-      <c r="Z193" s="176">
-        <f t="shared" si="130"/>
-        <v>6.3437031679023587E-3</v>
-      </c>
-      <c r="AA193" s="176">
-        <f t="shared" si="130"/>
-        <v>6.415189946030183E-3</v>
-      </c>
-      <c r="AC193" s="176">
-        <f>-AC119/AC5</f>
-        <v>5.3219161289936798E-3</v>
-      </c>
-    </row>
-    <row r="194" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B194" s="20" t="s">
-        <v>354</v>
-      </c>
-      <c r="M194" s="176">
-        <f>-(M119/M58)</f>
-        <v>-0.21521750996124667</v>
-      </c>
-      <c r="N194" s="176">
-        <f>-(N119/N58)</f>
-        <v>-2.3860334635808034</v>
-      </c>
-      <c r="O194" s="176">
-        <f>-(O119/O58)</f>
-        <v>2.4548451595214689E-2</v>
-      </c>
-      <c r="P194" s="176">
-        <f>-(P119/P58)</f>
-        <v>4.6552181304883568E-2</v>
-      </c>
-      <c r="Q194" s="176">
-        <f>-(Q119/Q58)</f>
-        <v>5.1313549276955236E-2</v>
-      </c>
-      <c r="T194" s="176">
-        <f t="shared" ref="T194:AA194" si="131">-(T119/T58)</f>
-        <v>3.0576160082801448E-2</v>
-      </c>
-      <c r="U194" s="176">
-        <f t="shared" si="131"/>
-        <v>0.17367296045600286</v>
-      </c>
-      <c r="V194" s="176" t="e">
-        <f t="shared" si="131"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W194" s="176">
-        <f t="shared" si="131"/>
-        <v>0.10783012050217644</v>
-      </c>
-      <c r="X194" s="176">
-        <f t="shared" si="131"/>
-        <v>0</v>
-      </c>
-      <c r="Y194" s="176">
-        <f t="shared" si="131"/>
-        <v>0.11191680520674896</v>
-      </c>
-      <c r="Z194" s="176">
-        <f t="shared" si="131"/>
-        <v>1.6737227718428501E-2</v>
-      </c>
-      <c r="AA194" s="176">
-        <f t="shared" si="131"/>
-        <v>2.0344430295312594E-2</v>
-      </c>
-      <c r="AC194" s="176">
-        <f>-(AC119/AC58)</f>
-        <v>2.3168998318295178E-2</v>
-      </c>
-    </row>
-    <row r="195" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B195" s="20" t="s">
-        <v>355</v>
-      </c>
-      <c r="M195" s="176">
-        <f>-M119/M52</f>
-        <v>0.80442026521591292</v>
-      </c>
-      <c r="N195" s="176">
-        <f>-N119/N52</f>
-        <v>1.2719649628798804</v>
-      </c>
-      <c r="O195" s="176">
-        <f>-O119/O52</f>
-        <v>0.32491038633446917</v>
-      </c>
-      <c r="P195" s="176">
-        <f>-P119/P52</f>
-        <v>0.86600510677808729</v>
-      </c>
-      <c r="Q195" s="176">
-        <f>-Q119/Q52</f>
-        <v>1.1225175319700631</v>
-      </c>
-      <c r="T195" s="176">
-        <f t="shared" ref="T195:AA195" si="132">-T119/T52</f>
-        <v>0.30953940187731938</v>
-      </c>
-      <c r="U195" s="176">
-        <f t="shared" si="132"/>
-        <v>1.0752095280105867</v>
-      </c>
-      <c r="V195" s="176" t="e">
-        <f t="shared" si="132"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W195" s="176">
-        <f t="shared" si="132"/>
-        <v>3.9446664617276359</v>
-      </c>
-      <c r="X195" s="176">
-        <f t="shared" si="132"/>
-        <v>0</v>
-      </c>
-      <c r="Y195" s="176">
-        <f t="shared" si="132"/>
-        <v>0.7010857522712165</v>
-      </c>
-      <c r="Z195" s="176">
-        <f t="shared" si="132"/>
-        <v>0.61371405590187011</v>
-      </c>
-      <c r="AA195" s="176">
-        <f t="shared" si="132"/>
         <v>0.35743774137701423</v>
       </c>
-      <c r="AC195" s="176">
+      <c r="AC196" s="176">
         <f>-AC119/AC52</f>
         <v>0.41931684334511188</v>
       </c>
     </row>
-    <row r="197" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B197" s="1"/>
-    </row>
-    <row r="198" spans="2:29" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B198" s="14" t="s">
-        <v>367</v>
-      </c>
-      <c r="C198" s="194"/>
-      <c r="D198" s="194"/>
-      <c r="E198" s="194"/>
-      <c r="F198" s="194"/>
-      <c r="G198" s="194"/>
-      <c r="H198" s="194"/>
-      <c r="I198" s="194"/>
-      <c r="J198" s="194"/>
-      <c r="K198" s="194"/>
-      <c r="L198" s="194"/>
-      <c r="M198" s="194"/>
-      <c r="N198" s="194"/>
-      <c r="O198" s="194"/>
-      <c r="P198" s="194"/>
-      <c r="Q198" s="194"/>
-      <c r="T198" s="194"/>
-      <c r="U198" s="194"/>
-      <c r="V198" s="194"/>
-      <c r="W198" s="194"/>
-      <c r="X198" s="194"/>
-      <c r="Y198" s="194"/>
-      <c r="Z198" s="194"/>
-      <c r="AA198" s="194"/>
-      <c r="AC198" s="194"/>
-    </row>
-    <row r="199" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B199" s="20" t="s">
+    <row r="198" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B198" s="1"/>
+    </row>
+    <row r="199" spans="2:29" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B199" s="14" t="s">
+        <v>366</v>
+      </c>
+      <c r="C199" s="194"/>
+      <c r="D199" s="194"/>
+      <c r="E199" s="194"/>
+      <c r="F199" s="194"/>
+      <c r="G199" s="194"/>
+      <c r="H199" s="194"/>
+      <c r="I199" s="194"/>
+      <c r="J199" s="194"/>
+      <c r="K199" s="194"/>
+      <c r="L199" s="194"/>
+      <c r="M199" s="194"/>
+      <c r="N199" s="194"/>
+      <c r="O199" s="194"/>
+      <c r="P199" s="194"/>
+      <c r="Q199" s="194"/>
+      <c r="T199" s="194"/>
+      <c r="U199" s="194"/>
+      <c r="V199" s="194"/>
+      <c r="W199" s="194"/>
+      <c r="X199" s="194"/>
+      <c r="Y199" s="194"/>
+      <c r="Z199" s="194"/>
+      <c r="AA199" s="194"/>
+      <c r="AC199" s="194"/>
+    </row>
+    <row r="200" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B200" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="C199" s="81"/>
-      <c r="D199" s="81"/>
-      <c r="E199" s="81"/>
-      <c r="F199" s="81"/>
-      <c r="G199" s="81"/>
-      <c r="H199" s="81"/>
-      <c r="I199" s="81"/>
-      <c r="J199" s="81"/>
-      <c r="K199" s="81"/>
-      <c r="L199" s="81"/>
-      <c r="M199" s="81">
+      <c r="C200" s="81"/>
+      <c r="D200" s="81"/>
+      <c r="E200" s="81"/>
+      <c r="F200" s="81"/>
+      <c r="G200" s="81"/>
+      <c r="H200" s="81"/>
+      <c r="I200" s="81"/>
+      <c r="J200" s="81"/>
+      <c r="K200" s="81"/>
+      <c r="L200" s="81"/>
+      <c r="M200" s="81">
         <f>IF(L105=0,
 IF(M105=0,0,IF(M105&gt;0,1,-1)),
 (M105-L105)/ABS(L105)
 )</f>
         <v>1</v>
       </c>
-      <c r="N199" s="81">
-        <f t="shared" ref="N199:Q199" si="133">IF(M105=0,
+      <c r="N200" s="81">
+        <f t="shared" ref="N200:Q200" si="128">IF(M105=0,
 IF(N105=0,0,IF(N105&gt;0,1,-1)),
 (N105-M105)/ABS(M105)
 )</f>
         <v>3.4084087514825716E-2</v>
       </c>
-      <c r="O199" s="81">
-        <f t="shared" si="133"/>
+      <c r="O200" s="81">
+        <f t="shared" si="128"/>
         <v>0.24818614965570993</v>
       </c>
-      <c r="P199" s="81">
-        <f t="shared" si="133"/>
+      <c r="P200" s="81">
+        <f t="shared" si="128"/>
         <v>-5.5102093364575021E-2</v>
       </c>
-      <c r="Q199" s="81">
-        <f t="shared" si="133"/>
+      <c r="Q200" s="81">
+        <f t="shared" si="128"/>
         <v>3.2771752459329104E-2</v>
       </c>
-      <c r="T199" s="81">
-        <f t="shared" ref="T199:T201" si="134">IF(S105=0,
+      <c r="T200" s="81">
+        <f t="shared" ref="T200:T202" si="129">IF(S105=0,
 IF(T105=0,0,IF(T105&gt;0,1,-1)),
 (T105-S105)/ABS(S105)
 )</f>
         <v>1</v>
       </c>
-      <c r="U199" s="81">
-        <f t="shared" ref="U199:U201" si="135">IF(T105=0,
+      <c r="U200" s="81">
+        <f t="shared" ref="U200:U202" si="130">IF(T105=0,
 IF(U105=0,0,IF(U105&gt;0,1,-1)),
 (U105-T105)/ABS(T105)
 )</f>
         <v>0.22202920241245067</v>
       </c>
-      <c r="V199" s="81">
-        <f t="shared" ref="V199:V201" si="136">IF(U105=0,
+      <c r="V200" s="81">
+        <f t="shared" ref="V200:V202" si="131">IF(U105=0,
 IF(V105=0,0,IF(V105&gt;0,1,-1)),
 (V105-U105)/ABS(U105)
 )</f>
         <v>0.44057182848061588</v>
       </c>
-      <c r="W199" s="81">
-        <f t="shared" ref="W199:W201" si="137">IF(V105=0,
+      <c r="W200" s="81">
+        <f t="shared" ref="W200:W202" si="132">IF(V105=0,
 IF(W105=0,0,IF(W105&gt;0,1,-1)),
 (W105-V105)/ABS(V105)
 )</f>
         <v>-0.35080892064632685</v>
       </c>
-      <c r="X199" s="81">
-        <f t="shared" ref="X199:X201" si="138">IF(W105=0,
+      <c r="X200" s="81">
+        <f t="shared" ref="X200:X202" si="133">IF(W105=0,
 IF(X105=0,0,IF(X105&gt;0,1,-1)),
 (X105-W105)/ABS(W105)
 )</f>
         <v>-0.12569571114540948</v>
       </c>
-      <c r="Y199" s="81">
-        <f t="shared" ref="Y199:Y201" si="139">IF(X105=0,
+      <c r="Y200" s="81">
+        <f t="shared" ref="Y200:Y202" si="134">IF(X105=0,
 IF(Y105=0,0,IF(Y105&gt;0,1,-1)),
 (Y105-X105)/ABS(X105)
 )</f>
         <v>0.33774663207353717</v>
       </c>
-      <c r="Z199" s="81">
-        <f t="shared" ref="Z199:Z201" si="140">IF(Y105=0,
+      <c r="Z200" s="81">
+        <f t="shared" ref="Z200:Z202" si="135">IF(Y105=0,
 IF(Z105=0,0,IF(Z105&gt;0,1,-1)),
 (Z105-Y105)/ABS(Y105)
 )</f>
         <v>0.43894750171617469</v>
       </c>
-      <c r="AA199" s="81">
-        <f t="shared" ref="AA199:AA201" si="141">IF(Z105=0,
+      <c r="AA200" s="81">
+        <f t="shared" ref="AA200:AA202" si="136">IF(Z105=0,
 IF(AA105=0,0,IF(AA105&gt;0,1,-1)),
 (AA105-Z105)/ABS(Z105)
 )</f>
         <v>-0.30844727286201273</v>
       </c>
-      <c r="AC199" s="49"/>
-    </row>
-    <row r="200" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B200" s="20" t="s">
+      <c r="AC200" s="49"/>
+    </row>
+    <row r="201" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B201" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="M200" s="81">
-        <f t="shared" ref="M200:Q200" si="142">IF(L106=0,
+      <c r="M201" s="81">
+        <f t="shared" ref="M201:Q201" si="137">IF(L106=0,
 IF(M106=0,0,IF(M106&gt;0,1,-1)),
 (M106-L106)/ABS(L106)
 )</f>
         <v>1</v>
       </c>
-      <c r="N200" s="81">
-        <f t="shared" si="142"/>
+      <c r="N201" s="81">
+        <f t="shared" si="137"/>
         <v>0.37569180272908909</v>
       </c>
-      <c r="O200" s="81">
-        <f t="shared" si="142"/>
+      <c r="O201" s="81">
+        <f t="shared" si="137"/>
         <v>0.27729682030883041</v>
       </c>
-      <c r="P200" s="81">
-        <f t="shared" si="142"/>
+      <c r="P201" s="81">
+        <f t="shared" si="137"/>
         <v>0.23392027917368038</v>
       </c>
-      <c r="Q200" s="81">
-        <f t="shared" si="142"/>
+      <c r="Q201" s="81">
+        <f t="shared" si="137"/>
         <v>0.19019336689332336</v>
       </c>
-      <c r="T200" s="81">
+      <c r="T201" s="81">
+        <f t="shared" si="129"/>
+        <v>1</v>
+      </c>
+      <c r="U201" s="81">
+        <f t="shared" si="130"/>
+        <v>6.292089812146523E-2</v>
+      </c>
+      <c r="V201" s="81">
+        <f t="shared" si="131"/>
+        <v>4.0106900184610626E-2</v>
+      </c>
+      <c r="W201" s="81">
+        <f t="shared" si="132"/>
+        <v>9.673777187170397E-3</v>
+      </c>
+      <c r="X201" s="81">
+        <f t="shared" si="133"/>
+        <v>9.6915367022084364E-2</v>
+      </c>
+      <c r="Y201" s="81">
         <f t="shared" si="134"/>
-        <v>1</v>
-      </c>
-      <c r="U200" s="81">
+        <v>3.8638547089942653E-2</v>
+      </c>
+      <c r="Z201" s="81">
         <f t="shared" si="135"/>
-        <v>6.292089812146523E-2</v>
-      </c>
-      <c r="V200" s="81">
+        <v>1.4783518396594137E-2</v>
+      </c>
+      <c r="AA201" s="81">
         <f t="shared" si="136"/>
-        <v>4.0106900184610626E-2</v>
-      </c>
-      <c r="W200" s="81">
-        <f t="shared" si="137"/>
-        <v>9.673777187170397E-3</v>
-      </c>
-      <c r="X200" s="81">
-        <f t="shared" si="138"/>
-        <v>9.6915367022084364E-2</v>
-      </c>
-      <c r="Y200" s="81">
-        <f t="shared" si="139"/>
-        <v>3.8638547089942653E-2</v>
-      </c>
-      <c r="Z200" s="81">
-        <f t="shared" si="140"/>
-        <v>1.4783518396594137E-2</v>
-      </c>
-      <c r="AA200" s="81">
-        <f t="shared" si="141"/>
         <v>6.6472159310281692E-3</v>
       </c>
-      <c r="AC200" s="49"/>
-    </row>
-    <row r="201" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B201" s="20" t="s">
+      <c r="AC201" s="49"/>
+    </row>
+    <row r="202" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B202" s="20" t="s">
         <v>115</v>
       </c>
-      <c r="M201" s="81">
-        <f t="shared" ref="M201:Q201" si="143">IF(L107=0,
+      <c r="M202" s="81">
+        <f t="shared" ref="M202:Q202" si="138">IF(L107=0,
 IF(M107=0,0,IF(M107&gt;0,1,-1)),
 (M107-L107)/ABS(L107)
 )</f>
         <v>1</v>
       </c>
-      <c r="N201" s="81">
-        <f t="shared" si="143"/>
+      <c r="N202" s="81">
+        <f t="shared" si="138"/>
         <v>0.26768885199472631</v>
       </c>
-      <c r="O201" s="81">
-        <f t="shared" si="143"/>
+      <c r="O202" s="81">
+        <f t="shared" si="138"/>
         <v>-0.29197642617772812</v>
       </c>
-      <c r="P201" s="81">
-        <f t="shared" si="143"/>
+      <c r="P202" s="81">
+        <f t="shared" si="138"/>
         <v>0.10317719384146673</v>
       </c>
-      <c r="Q201" s="81">
-        <f t="shared" si="143"/>
+      <c r="Q202" s="81">
+        <f t="shared" si="138"/>
         <v>0.22564418690666996</v>
       </c>
-      <c r="T201" s="81">
+      <c r="T202" s="81">
+        <f t="shared" si="129"/>
+        <v>1</v>
+      </c>
+      <c r="U202" s="81">
+        <f t="shared" si="130"/>
+        <v>0.13163254368099475</v>
+      </c>
+      <c r="V202" s="81">
+        <f t="shared" si="131"/>
+        <v>2.4533484891541158E-2</v>
+      </c>
+      <c r="W202" s="81">
+        <f t="shared" si="132"/>
+        <v>2.0247781065088757E-2</v>
+      </c>
+      <c r="X202" s="81">
+        <f t="shared" si="133"/>
+        <v>1.5314907113729044E-2</v>
+      </c>
+      <c r="Y202" s="81">
         <f t="shared" si="134"/>
-        <v>1</v>
-      </c>
-      <c r="U201" s="81">
+        <v>0.20465905033916459</v>
+      </c>
+      <c r="Z202" s="81">
         <f t="shared" si="135"/>
-        <v>0.13163254368099475</v>
-      </c>
-      <c r="V201" s="81">
+        <v>3.5044824775876122E-2</v>
+      </c>
+      <c r="AA202" s="81">
         <f t="shared" si="136"/>
-        <v>2.4533484891541158E-2</v>
-      </c>
-      <c r="W201" s="81">
-        <f t="shared" si="137"/>
-        <v>2.0247781065088757E-2</v>
-      </c>
-      <c r="X201" s="81">
-        <f t="shared" si="138"/>
-        <v>1.5314907113729044E-2</v>
-      </c>
-      <c r="Y201" s="81">
-        <f t="shared" si="139"/>
-        <v>0.20465905033916459</v>
-      </c>
-      <c r="Z201" s="81">
-        <f t="shared" si="140"/>
-        <v>3.5044824775876122E-2</v>
-      </c>
-      <c r="AA201" s="81">
-        <f t="shared" si="141"/>
         <v>0.15748031496062992</v>
       </c>
-      <c r="AC201" s="49"/>
-    </row>
-    <row r="203" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B203" s="1"/>
-    </row>
-    <row r="204" spans="2:29" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B204" s="14" t="s">
-        <v>368</v>
-      </c>
-      <c r="C204" s="194"/>
-      <c r="D204" s="194"/>
-      <c r="E204" s="194"/>
-      <c r="F204" s="194"/>
-      <c r="G204" s="194"/>
-      <c r="H204" s="194"/>
-      <c r="I204" s="194"/>
-      <c r="J204" s="194"/>
-      <c r="K204" s="194"/>
-      <c r="L204" s="194"/>
-      <c r="M204" s="194"/>
-      <c r="N204" s="194"/>
-      <c r="O204" s="194"/>
-      <c r="P204" s="194"/>
-      <c r="Q204" s="194"/>
-      <c r="T204" s="194"/>
-      <c r="U204" s="194"/>
-      <c r="V204" s="194"/>
-      <c r="W204" s="194"/>
-      <c r="X204" s="194"/>
-      <c r="Y204" s="194"/>
-      <c r="Z204" s="194"/>
-      <c r="AA204" s="194"/>
-      <c r="AC204" s="194"/>
-    </row>
-    <row r="205" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B205" s="20" t="s">
-        <v>337</v>
-      </c>
-      <c r="C205" s="81"/>
-      <c r="D205" s="81"/>
-      <c r="E205" s="81"/>
-      <c r="F205" s="81"/>
-      <c r="G205" s="81"/>
-      <c r="H205" s="81"/>
-      <c r="I205" s="81"/>
-      <c r="J205" s="81"/>
-      <c r="K205" s="81"/>
-      <c r="L205" s="81"/>
-      <c r="M205" s="81">
+      <c r="AC202" s="49"/>
+    </row>
+    <row r="204" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B204" s="1"/>
+    </row>
+    <row r="205" spans="2:29" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B205" s="14" t="s">
+        <v>367</v>
+      </c>
+      <c r="C205" s="194"/>
+      <c r="D205" s="194"/>
+      <c r="E205" s="194"/>
+      <c r="F205" s="194"/>
+      <c r="G205" s="194"/>
+      <c r="H205" s="194"/>
+      <c r="I205" s="194"/>
+      <c r="J205" s="194"/>
+      <c r="K205" s="194"/>
+      <c r="L205" s="194"/>
+      <c r="M205" s="194"/>
+      <c r="N205" s="194"/>
+      <c r="O205" s="194"/>
+      <c r="P205" s="194"/>
+      <c r="Q205" s="194"/>
+      <c r="T205" s="194"/>
+      <c r="U205" s="194"/>
+      <c r="V205" s="194"/>
+      <c r="W205" s="194"/>
+      <c r="X205" s="194"/>
+      <c r="Y205" s="194"/>
+      <c r="Z205" s="194"/>
+      <c r="AA205" s="194"/>
+      <c r="AC205" s="194"/>
+    </row>
+    <row r="206" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B206" s="20" t="s">
+        <v>336</v>
+      </c>
+      <c r="C206" s="81"/>
+      <c r="D206" s="81"/>
+      <c r="E206" s="81"/>
+      <c r="F206" s="81"/>
+      <c r="G206" s="81"/>
+      <c r="H206" s="81"/>
+      <c r="I206" s="81"/>
+      <c r="J206" s="81"/>
+      <c r="K206" s="81"/>
+      <c r="L206" s="81"/>
+      <c r="M206" s="81">
         <f>IF(L63=0,
 IF(M63=0,0,IF(M63&gt;0,1,-1)),
 (M63-L63)/L63
 )</f>
         <v>0</v>
       </c>
-      <c r="N205" s="81">
-        <f t="shared" ref="N205:Q205" si="144">IF(M63=0,
+      <c r="N206" s="81">
+        <f t="shared" ref="N206:Q206" si="139">IF(M63=0,
 IF(N63=0,0,IF(N63&gt;0,1,-1)),
 (N63-M63)/M63
 )</f>
         <v>0</v>
       </c>
-      <c r="O205" s="81">
-        <f t="shared" si="144"/>
-        <v>0</v>
-      </c>
-      <c r="P205" s="81">
-        <f t="shared" si="144"/>
-        <v>0</v>
-      </c>
-      <c r="Q205" s="81">
-        <f t="shared" si="144"/>
-        <v>0</v>
-      </c>
-      <c r="T205" s="49"/>
-      <c r="U205" s="49"/>
-      <c r="V205" s="49"/>
-      <c r="W205" s="49"/>
-      <c r="X205" s="49"/>
-      <c r="Y205" s="49"/>
-      <c r="Z205" s="49"/>
-      <c r="AA205" s="49"/>
-      <c r="AC205" s="49"/>
+      <c r="O206" s="81">
+        <f t="shared" si="139"/>
+        <v>0</v>
+      </c>
+      <c r="P206" s="81">
+        <f t="shared" si="139"/>
+        <v>0</v>
+      </c>
+      <c r="Q206" s="81">
+        <f t="shared" si="139"/>
+        <v>0</v>
+      </c>
+      <c r="T206" s="49"/>
+      <c r="U206" s="49"/>
+      <c r="V206" s="49"/>
+      <c r="W206" s="49"/>
+      <c r="X206" s="49"/>
+      <c r="Y206" s="49"/>
+      <c r="Z206" s="49"/>
+      <c r="AA206" s="49"/>
+      <c r="AC206" s="49"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -32966,7 +33006,7 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B1" s="84" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
@@ -33333,11 +33373,11 @@
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B37" s="248" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C37" s="248"/>
       <c r="E37" s="248" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F37" s="248"/>
     </row>
@@ -33350,26 +33390,26 @@
         <v>5.3380782918149475E-2</v>
       </c>
       <c r="E38" s="20" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F38" s="199">
-        <f>Statement!AC184</f>
+        <f>Statement!AC185</f>
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B39" s="54" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C39" s="240">
         <f ca="1">Statement!AC178</f>
         <v>1.8126755065546118E-2</v>
       </c>
       <c r="E39" s="20" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F39" s="199">
-        <f>Statement!AC185</f>
+        <f>Statement!AC186</f>
         <v>3.2095084983598028</v>
       </c>
     </row>
@@ -33382,16 +33422,16 @@
         <v>0</v>
       </c>
       <c r="E40" s="20" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F40" s="199">
-        <f>Statement!AC186</f>
+        <f>Statement!AC187</f>
         <v>3.2095084983598028</v>
       </c>
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B41" s="20" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C41" s="199">
         <f ca="1">Statement!AC181</f>
@@ -33400,7 +33440,7 @@
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B42" s="20" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C42" s="199">
         <f ca="1">Statement!AC182</f>
@@ -33409,96 +33449,96 @@
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B45" s="248" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C45" s="248"/>
       <c r="E45" s="248" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F45" s="248"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
+        <v>329</v>
+      </c>
+      <c r="C46" s="199">
+        <f>Statement!AC188</f>
+        <v>0.22116382280992736</v>
+      </c>
+      <c r="E46" s="20" t="s">
         <v>330</v>
       </c>
-      <c r="C46" s="199">
-        <f>Statement!AC187</f>
-        <v>0.22116382280992736</v>
-      </c>
-      <c r="E46" s="20" t="s">
-        <v>331</v>
-      </c>
       <c r="F46" s="198">
-        <f>Statement!AC188</f>
+        <f>Statement!AC189</f>
         <v>2.4951118677971147</v>
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.2">
       <c r="E47" s="20" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F47" s="198">
-        <f>Statement!AC191</f>
+        <f>Statement!AC192</f>
         <v>2.4951118677971147</v>
       </c>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.2">
       <c r="E48" s="20" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F48" s="199">
-        <f ca="1">Statement!AC192</f>
+        <f ca="1">Statement!AC193</f>
         <v>0.22020548280259802</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B51" s="248" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C51" s="248"/>
       <c r="E51" s="248" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F51" s="248"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C52" s="199">
-        <f>Statement!AC189</f>
+        <f>Statement!AC190</f>
         <v>0.69669698594761198</v>
       </c>
       <c r="E52" s="20" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F52" s="199">
-        <f>Statement!AC193</f>
+        <f>Statement!AC194</f>
         <v>5.3219161289936798E-3</v>
       </c>
     </row>
     <row r="53" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B53" s="20" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C53" s="199">
-        <f>Statement!AC190</f>
+        <f>Statement!AC191</f>
         <v>0.16003121393504871</v>
       </c>
       <c r="E53" s="20" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F53" s="199">
-        <f>Statement!AC194</f>
+        <f>Statement!AC195</f>
         <v>2.3168998318295178E-2</v>
       </c>
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.2">
       <c r="E54" s="20" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F54" s="199">
-        <f>Statement!AC195</f>
+        <f>Statement!AC196</f>
         <v>0.41931684334511188</v>
       </c>
     </row>
@@ -34187,7 +34227,7 @@
     </row>
     <row r="32" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B32" s="14" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C32" s="14"/>
       <c r="D32" s="14"/>
@@ -34568,7 +34608,7 @@
     </row>
     <row r="50" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B50" s="14" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C50" s="14"/>
       <c r="D50" s="14"/>
@@ -34608,7 +34648,7 @@
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C52" s="199">
         <f>Statement!M178</f>
@@ -34666,7 +34706,7 @@
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B54" s="20" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C54" s="199">
         <f>Statement!M181</f>
@@ -34695,7 +34735,7 @@
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B55" s="20" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C55" s="199">
         <f>Statement!M182</f>
@@ -34724,7 +34764,7 @@
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B57" s="14" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C57" s="14"/>
       <c r="D57" s="14"/>
@@ -34735,94 +34775,94 @@
     </row>
     <row r="58" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B58" s="20" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C58" s="199">
-        <f>Statement!M184</f>
+        <f>Statement!M185</f>
         <v>0</v>
       </c>
       <c r="D58" s="199">
-        <f>Statement!N184</f>
+        <f>Statement!N185</f>
         <v>0</v>
       </c>
       <c r="E58" s="199">
-        <f>Statement!O184</f>
+        <f>Statement!O185</f>
         <v>0</v>
       </c>
       <c r="F58" s="199">
-        <f>Statement!P184</f>
+        <f>Statement!P185</f>
         <v>0</v>
       </c>
       <c r="G58" s="199">
-        <f>Statement!Q184</f>
+        <f>Statement!Q185</f>
         <v>0</v>
       </c>
       <c r="I58" s="199">
-        <f>Statement!AC184</f>
+        <f>Statement!AC185</f>
         <v>0</v>
       </c>
     </row>
     <row r="59" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B59" s="20" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C59" s="199">
-        <f>Statement!M185</f>
+        <f>Statement!M186</f>
         <v>0</v>
       </c>
       <c r="D59" s="199">
-        <f>Statement!N185</f>
+        <f>Statement!N186</f>
         <v>0</v>
       </c>
       <c r="E59" s="199">
-        <f>Statement!O185</f>
+        <f>Statement!O186</f>
         <v>-1.2792495169232687</v>
       </c>
       <c r="F59" s="199">
-        <f>Statement!P185</f>
+        <f>Statement!P186</f>
         <v>-7.44160048753547</v>
       </c>
       <c r="G59" s="199">
-        <f>Statement!Q185</f>
+        <f>Statement!Q186</f>
         <v>5.3526283260685705</v>
       </c>
       <c r="I59" s="199">
-        <f>Statement!AC185</f>
+        <f>Statement!AC186</f>
         <v>3.2095084983598028</v>
       </c>
     </row>
     <row r="60" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B60" s="20" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C60" s="199">
-        <f>Statement!M186</f>
+        <f>Statement!M187</f>
         <v>0</v>
       </c>
       <c r="D60" s="199">
-        <f>Statement!N186</f>
+        <f>Statement!N187</f>
         <v>0</v>
       </c>
       <c r="E60" s="199">
-        <f>Statement!O186</f>
+        <f>Statement!O187</f>
         <v>-1.2792495169232687</v>
       </c>
       <c r="F60" s="199">
-        <f>Statement!P186</f>
+        <f>Statement!P187</f>
         <v>-7.44160048753547</v>
       </c>
       <c r="G60" s="199">
-        <f>Statement!Q186</f>
+        <f>Statement!Q187</f>
         <v>5.3526283260685705</v>
       </c>
       <c r="I60" s="199">
-        <f>Statement!AC186</f>
+        <f>Statement!AC187</f>
         <v>3.2095084983598028</v>
       </c>
     </row>
     <row r="62" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B62" s="14" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C62" s="14"/>
       <c r="D62" s="14"/>
@@ -34833,36 +34873,36 @@
     </row>
     <row r="63" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B63" s="20" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C63" s="199">
-        <f>Statement!M187</f>
+        <f>Statement!M188</f>
         <v>0.32041292188722126</v>
       </c>
       <c r="D63" s="199">
-        <f>Statement!N187</f>
+        <f>Statement!N188</f>
         <v>0.31207180184527727</v>
       </c>
       <c r="E63" s="199">
-        <f>Statement!O187</f>
+        <f>Statement!O188</f>
         <v>0.22510733498180183</v>
       </c>
       <c r="F63" s="199">
-        <f>Statement!P187</f>
+        <f>Statement!P188</f>
         <v>0.22494029842627195</v>
       </c>
       <c r="G63" s="199">
-        <f>Statement!Q187</f>
+        <f>Statement!Q188</f>
         <v>0.22012147206199109</v>
       </c>
       <c r="I63" s="199">
-        <f>Statement!AC187</f>
+        <f>Statement!AC188</f>
         <v>0.22116382280992736</v>
       </c>
     </row>
     <row r="65" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B65" s="14" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C65" s="14"/>
       <c r="D65" s="14"/>
@@ -34873,94 +34913,94 @@
     </row>
     <row r="66" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B66" s="20" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C66" s="198">
-        <f>Statement!M188</f>
+        <f>Statement!M189</f>
         <v>3.4406590811823912</v>
       </c>
       <c r="D66" s="198">
-        <f>Statement!N188</f>
+        <f>Statement!N189</f>
         <v>3.1518128961309455</v>
       </c>
       <c r="E66" s="198">
-        <f>Statement!O188</f>
+        <f>Statement!O189</f>
         <v>3.3036556282545391</v>
       </c>
       <c r="F66" s="198">
-        <f>Statement!P188</f>
+        <f>Statement!P189</f>
         <v>2.9547392260645196</v>
       </c>
       <c r="G66" s="198">
-        <f>Statement!Q188</f>
+        <f>Statement!Q189</f>
         <v>2.8105061440443424</v>
       </c>
       <c r="I66" s="198">
-        <f>Statement!AC188</f>
+        <f>Statement!AC189</f>
         <v>2.4951118677971147</v>
       </c>
     </row>
     <row r="67" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B67" s="20" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C67" s="198">
-        <f>Statement!M191</f>
+        <f>Statement!M192</f>
         <v>3.4406590811823912</v>
       </c>
       <c r="D67" s="198">
-        <f>Statement!N191</f>
+        <f>Statement!N192</f>
         <v>3.1518128961309455</v>
       </c>
       <c r="E67" s="198">
-        <f>Statement!O191</f>
+        <f>Statement!O192</f>
         <v>3.3036556282545391</v>
       </c>
       <c r="F67" s="198">
-        <f>Statement!P191</f>
+        <f>Statement!P192</f>
         <v>2.9547392260645196</v>
       </c>
       <c r="G67" s="198">
-        <f>Statement!Q191</f>
+        <f>Statement!Q192</f>
         <v>2.8105061440443424</v>
       </c>
       <c r="I67" s="198">
-        <f>Statement!AC191</f>
+        <f>Statement!AC192</f>
         <v>2.4951118677971147</v>
       </c>
     </row>
     <row r="68" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B68" s="20" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C68" s="220">
-        <f>Statement!M192</f>
+        <f>Statement!M193</f>
         <v>0.10292130066354745</v>
       </c>
       <c r="D68" s="220">
-        <f>Statement!N192</f>
+        <f>Statement!N193</f>
         <v>0.21632209307693517</v>
       </c>
       <c r="E68" s="220">
-        <f>Statement!O192</f>
+        <f>Statement!O193</f>
         <v>0.1385180556920142</v>
       </c>
       <c r="F68" s="220">
-        <f>Statement!P192</f>
+        <f>Statement!P193</f>
         <v>0.20265701138988473</v>
       </c>
       <c r="G68" s="220">
-        <f>Statement!Q192</f>
+        <f>Statement!Q193</f>
         <v>0.22039997795949329</v>
       </c>
       <c r="I68" s="220">
-        <f ca="1">Statement!AC192</f>
+        <f ca="1">Statement!AC193</f>
         <v>0.22020548280259802</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B70" s="14" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C70" s="14"/>
       <c r="D70" s="14"/>
@@ -34971,65 +35011,65 @@
     </row>
     <row r="71" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B71" s="20" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C71" s="199">
-        <f>Statement!M189</f>
+        <f>Statement!M190</f>
         <v>-9.3805469133780903</v>
       </c>
       <c r="D71" s="199">
-        <f>Statement!N189</f>
+        <f>Statement!N190</f>
         <v>-37.054403366396151</v>
       </c>
       <c r="E71" s="199">
-        <f>Statement!O189</f>
+        <f>Statement!O190</f>
         <v>1.243655586093446</v>
       </c>
       <c r="F71" s="199">
-        <f>Statement!P189</f>
+        <f>Statement!P190</f>
         <v>1.1172492318250589</v>
       </c>
       <c r="G71" s="199">
-        <f>Statement!Q189</f>
+        <f>Statement!Q190</f>
         <v>0.78305424452059225</v>
       </c>
       <c r="I71" s="199">
-        <f>Statement!AC189</f>
+        <f>Statement!AC190</f>
         <v>0.69669698594761198</v>
       </c>
     </row>
     <row r="72" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B72" s="20" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C72" s="199">
-        <f>Statement!M190</f>
+        <f>Statement!M191</f>
         <v>0.57784459995606618</v>
       </c>
       <c r="D72" s="199">
-        <f>Statement!N190</f>
+        <f>Statement!N191</f>
         <v>0.3493733592422309</v>
       </c>
       <c r="E72" s="199">
-        <f>Statement!O190</f>
+        <f>Statement!O191</f>
         <v>0.28435361356255617</v>
       </c>
       <c r="F72" s="199">
-        <f>Statement!P190</f>
+        <f>Statement!P191</f>
         <v>0.25051410681111086</v>
       </c>
       <c r="G72" s="199">
-        <f>Statement!Q190</f>
+        <f>Statement!Q191</f>
         <v>0.18047997854178516</v>
       </c>
       <c r="I72" s="199">
-        <f>Statement!AC190</f>
+        <f>Statement!AC191</f>
         <v>0.16003121393504871</v>
       </c>
     </row>
     <row r="74" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B74" s="14" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C74" s="14"/>
       <c r="D74" s="14"/>
@@ -35040,88 +35080,88 @@
     </row>
     <row r="75" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B75" s="20" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C75" s="199">
-        <f>Statement!M193</f>
+        <f>Statement!M194</f>
         <v>1.325746537973577E-2</v>
       </c>
       <c r="D75" s="199">
-        <f>Statement!N193</f>
+        <f>Statement!N194</f>
         <v>2.2497097529617479E-2</v>
       </c>
       <c r="E75" s="199">
-        <f>Statement!O193</f>
+        <f>Statement!O194</f>
         <v>5.6128408833764501E-3</v>
       </c>
       <c r="F75" s="199">
-        <f>Statement!P193</f>
+        <f>Statement!P194</f>
         <v>1.0438116928173332E-2</v>
       </c>
       <c r="G75" s="199">
-        <f>Statement!Q193</f>
+        <f>Statement!Q194</f>
         <v>1.1826854061786744E-2</v>
       </c>
       <c r="I75" s="199">
-        <f>Statement!AC193</f>
+        <f>Statement!AC194</f>
         <v>5.3219161289936798E-3</v>
       </c>
     </row>
     <row r="76" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B76" s="20" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C76" s="199">
-        <f>Statement!M194</f>
+        <f>Statement!M195</f>
         <v>-0.21521750996124667</v>
       </c>
       <c r="D76" s="199">
-        <f>Statement!N194</f>
+        <f>Statement!N195</f>
         <v>-2.3860334635808034</v>
       </c>
       <c r="E76" s="199">
-        <f>Statement!O194</f>
+        <f>Statement!O195</f>
         <v>2.4548451595214689E-2</v>
       </c>
       <c r="F76" s="199">
-        <f>Statement!P194</f>
+        <f>Statement!P195</f>
         <v>4.6552181304883568E-2</v>
       </c>
       <c r="G76" s="199">
-        <f>Statement!Q194</f>
+        <f>Statement!Q195</f>
         <v>5.1313549276955236E-2</v>
       </c>
       <c r="I76" s="199">
-        <f>Statement!AC194</f>
+        <f>Statement!AC195</f>
         <v>2.3168998318295178E-2</v>
       </c>
     </row>
     <row r="77" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B77" s="20" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C77" s="199">
-        <f>Statement!M195</f>
+        <f>Statement!M196</f>
         <v>0.80442026521591292</v>
       </c>
       <c r="D77" s="199">
-        <f>Statement!N195</f>
+        <f>Statement!N196</f>
         <v>1.2719649628798804</v>
       </c>
       <c r="E77" s="199">
-        <f>Statement!O195</f>
+        <f>Statement!O196</f>
         <v>0.32491038633446917</v>
       </c>
       <c r="F77" s="199">
-        <f>Statement!P195</f>
+        <f>Statement!P196</f>
         <v>0.86600510677808729</v>
       </c>
       <c r="G77" s="199">
-        <f>Statement!Q195</f>
+        <f>Statement!Q196</f>
         <v>1.1225175319700631</v>
       </c>
       <c r="I77" s="199">
-        <f>Statement!AC195</f>
+        <f>Statement!AC196</f>
         <v>0.41931684334511188</v>
       </c>
     </row>
@@ -35242,7 +35282,7 @@
     </row>
     <row r="84" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B84" s="20" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C84" s="199">
         <f>Statement!M95</f>
@@ -35268,7 +35308,7 @@
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B85" s="20" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C85" s="199">
         <f>Statement!M97</f>
@@ -35294,7 +35334,7 @@
     </row>
     <row r="88" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B88" s="14" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C88" s="14"/>
       <c r="D88" s="14"/>
@@ -35305,85 +35345,85 @@
     </row>
     <row r="89" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B89" s="20" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C89" s="199">
-        <f>Statement!M199</f>
+        <f>Statement!M200</f>
         <v>1</v>
       </c>
       <c r="D89" s="199">
-        <f>Statement!N199</f>
+        <f>Statement!N200</f>
         <v>3.4084087514825716E-2</v>
       </c>
       <c r="E89" s="199">
-        <f>Statement!O199</f>
+        <f>Statement!O200</f>
         <v>0.24818614965570993</v>
       </c>
       <c r="F89" s="199">
-        <f>Statement!P199</f>
+        <f>Statement!P200</f>
         <v>-5.5102093364575021E-2</v>
       </c>
       <c r="G89" s="199">
-        <f>Statement!Q199</f>
+        <f>Statement!Q200</f>
         <v>3.2771752459329104E-2</v>
       </c>
       <c r="I89" s="221"/>
     </row>
     <row r="90" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B90" s="20" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C90" s="199">
-        <f>Statement!M200</f>
+        <f>Statement!M201</f>
         <v>1</v>
       </c>
       <c r="D90" s="199">
-        <f>Statement!N200</f>
+        <f>Statement!N201</f>
         <v>0.37569180272908909</v>
       </c>
       <c r="E90" s="199">
-        <f>Statement!O200</f>
+        <f>Statement!O201</f>
         <v>0.27729682030883041</v>
       </c>
       <c r="F90" s="199">
-        <f>Statement!P200</f>
+        <f>Statement!P201</f>
         <v>0.23392027917368038</v>
       </c>
       <c r="G90" s="199">
-        <f>Statement!Q200</f>
+        <f>Statement!Q201</f>
         <v>0.19019336689332336</v>
       </c>
       <c r="I90" s="221"/>
     </row>
     <row r="91" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B91" s="20" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C91" s="199">
-        <f>Statement!M201</f>
+        <f>Statement!M202</f>
         <v>1</v>
       </c>
       <c r="D91" s="199">
-        <f>Statement!N201</f>
+        <f>Statement!N202</f>
         <v>0.26768885199472631</v>
       </c>
       <c r="E91" s="199">
-        <f>Statement!O201</f>
+        <f>Statement!O202</f>
         <v>-0.29197642617772812</v>
       </c>
       <c r="F91" s="199">
-        <f>Statement!P201</f>
+        <f>Statement!P202</f>
         <v>0.10317719384146673</v>
       </c>
       <c r="G91" s="199">
-        <f>Statement!Q201</f>
+        <f>Statement!Q202</f>
         <v>0.22564418690666996</v>
       </c>
       <c r="I91" s="221"/>
     </row>
     <row r="93" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B93" s="14" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C93" s="14"/>
       <c r="D93" s="14"/>
@@ -35394,26 +35434,26 @@
     </row>
     <row r="94" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B94" s="20" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C94" s="199">
-        <f>Statement!M205</f>
+        <f>Statement!M206</f>
         <v>0</v>
       </c>
       <c r="D94" s="199">
-        <f>Statement!N205</f>
+        <f>Statement!N206</f>
         <v>0</v>
       </c>
       <c r="E94" s="199">
-        <f>Statement!O205</f>
+        <f>Statement!O206</f>
         <v>0</v>
       </c>
       <c r="F94" s="199">
-        <f>Statement!P205</f>
+        <f>Statement!P206</f>
         <v>0</v>
       </c>
       <c r="G94" s="199">
-        <f>Statement!Q205</f>
+        <f>Statement!Q206</f>
         <v>0</v>
       </c>
       <c r="I94" s="221"/>
@@ -35442,11 +35482,11 @@
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
       <c r="C3" s="254" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D3" s="255"/>
       <c r="F3" s="256" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="G3" s="255"/>
     </row>
@@ -35471,7 +35511,7 @@
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="8" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C5" s="10" t="str">
         <f>Statement!Z3</f>
@@ -35513,7 +35553,7 @@
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B7" s="230" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C7" s="252">
         <f>Statement!AA88</f>
@@ -35552,7 +35592,7 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B9" s="230" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C9" s="252">
         <f>Statement!AA89</f>
@@ -35591,7 +35631,7 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B11" s="230" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C11" s="252">
         <f>Statement!AA90</f>
@@ -35630,7 +35670,7 @@
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B13" s="230" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C13" s="252">
         <f>Statement!AA94</f>
@@ -35648,7 +35688,7 @@
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="231" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C14" s="224">
         <f>Statement!Z12</f>
@@ -35669,7 +35709,7 @@
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B15" s="230" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C15" s="252">
         <f>Statement!AA95</f>
@@ -35708,7 +35748,7 @@
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B17" s="230" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C17" s="252">
         <f>Statement!AA97</f>
@@ -35726,7 +35766,7 @@
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="231" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C18" s="224">
         <f>Statement!Z22</f>
@@ -35747,7 +35787,7 @@
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B19" s="230" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C19" s="252">
         <f>IF(C18=0,
@@ -35789,7 +35829,7 @@
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B21" s="230" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C21" s="252">
         <f>IF(C20=0,
@@ -35810,7 +35850,7 @@
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C23" s="10" t="str">
         <f>C5</f>
@@ -35852,7 +35892,7 @@
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B25" s="230" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C25" s="252">
         <f>IF(C24=0,
@@ -35894,7 +35934,7 @@
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B27" s="230" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C27" s="252">
         <f>IF(C26=0,
@@ -35936,7 +35976,7 @@
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B29" s="230" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C29" s="252">
         <f>IF(C28=0,
@@ -35957,7 +35997,7 @@
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B31" s="8" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C31" s="10" t="str">
         <f>C5</f>
@@ -35999,7 +36039,7 @@
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B33" s="230" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C33" s="252">
         <f>IF(C32=0,
@@ -36041,7 +36081,7 @@
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B35" s="230" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C35" s="252">
         <f>IF(C34=0,
@@ -36556,7 +36596,7 @@
     </row>
     <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B65" s="20" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C65" s="64">
         <f>Statement!H105</f>
@@ -36601,7 +36641,7 @@
     </row>
     <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B66" s="20" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C66" s="64">
         <f>Statement!H106</f>
@@ -36646,7 +36686,7 @@
     </row>
     <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B67" s="20" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C67" s="64">
         <f>Statement!H107</f>
@@ -37134,7 +37174,7 @@
     </row>
     <row r="63" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B63" s="20" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C63" s="64">
         <f>Statement!T105</f>
@@ -37171,7 +37211,7 @@
     </row>
     <row r="64" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B64" s="20" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C64" s="64">
         <f>Statement!T106</f>
@@ -37208,7 +37248,7 @@
     </row>
     <row r="65" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B65" s="20" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C65" s="64">
         <f>Statement!T107</f>

--- a/PATH.xlsx
+++ b/PATH.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B10EE8BC-8B65-EB4F-840C-BE78E0080105}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35A98096-71EC-9646-A926-8B01B867406B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="2" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="9" activeTab="16" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -168,7 +168,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="754" uniqueCount="409">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="756" uniqueCount="411">
   <si>
     <t>Ticker</t>
   </si>
@@ -938,9 +938,6 @@
     <t>Year 5 UFCF</t>
   </si>
   <si>
-    <t>Applied EV/UFCF ratio</t>
-  </si>
-  <si>
     <t>AVG target price</t>
   </si>
   <si>
@@ -998,9 +995,6 @@
     <t>EBIT margin</t>
   </si>
   <si>
-    <t>WACC set manually</t>
-  </si>
-  <si>
     <t>Company guidance next Quarter</t>
   </si>
   <si>
@@ -1395,6 +1389,18 @@
   </si>
   <si>
     <t>FCFE/Sales (FCFE Margin)</t>
+  </si>
+  <si>
+    <t>Manual WACC</t>
+  </si>
+  <si>
+    <t>Discount rate</t>
+  </si>
+  <si>
+    <t>PV of EV</t>
+  </si>
+  <si>
+    <t>Applied EV/FCFF ratio</t>
   </si>
 </sst>
 </file>
@@ -2228,7 +2234,6 @@
     <xf numFmtId="4" fontId="12" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="12" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="10" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="12" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="24" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="37" fontId="10" fillId="11" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2254,7 +2259,6 @@
     <xf numFmtId="10" fontId="10" fillId="3" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="10" fillId="3" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="10" fillId="2" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="0" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="10" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2361,12 +2365,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2376,10 +2374,10 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2389,6 +2387,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2403,6 +2407,8 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="10" fontId="12" fillId="2" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="12" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -12636,7 +12642,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{825B172E-7ADE-4B4A-B533-F037BCFCDCB0}">
-  <dimension ref="B1:I47"/>
+  <dimension ref="B1:I49"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="1" customWidth="1"/>
@@ -12653,338 +12659,338 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="249" t="s">
+      <c r="B2" s="247" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="250"/>
-      <c r="E2" s="249" t="s">
-        <v>339</v>
-      </c>
-      <c r="F2" s="250"/>
-      <c r="H2" s="249" t="s">
-        <v>384</v>
-      </c>
-      <c r="I2" s="250"/>
+      <c r="C2" s="248"/>
+      <c r="E2" s="247" t="s">
+        <v>337</v>
+      </c>
+      <c r="F2" s="248"/>
+      <c r="H2" s="247" t="s">
+        <v>382</v>
+      </c>
+      <c r="I2" s="248"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B3" s="209" t="s">
+      <c r="B3" s="207" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="242" t="e" vm="1">
+      <c r="C3" s="240" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
       <c r="D3" s="2"/>
-      <c r="E3" s="209" t="s">
-        <v>291</v>
-      </c>
-      <c r="F3" s="211">
+      <c r="E3" s="207" t="s">
+        <v>289</v>
+      </c>
+      <c r="F3" s="209">
         <f ca="1">Statement!AC170</f>
         <v>5936473.4400000004</v>
       </c>
-      <c r="H3" s="209" t="str">
+      <c r="H3" s="207" t="str">
         <f>'AVG target price'!B5</f>
         <v>DCF price</v>
       </c>
-      <c r="I3" s="235">
+      <c r="I3" s="233">
         <f ca="1">'AVG target price'!C5</f>
         <v>6.6357378047186275</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B4" s="209" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="213" t="str" cm="1">
+      <c r="B4" s="207" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="211" t="str" cm="1">
         <f t="array" aca="1" ref="C4" ca="1">_FV(C3,"Ticker symbol",TRUE)</f>
         <v>PATH</v>
       </c>
-      <c r="E4" s="210" t="s">
+      <c r="E4" s="208" t="s">
         <v>230</v>
       </c>
-      <c r="F4" s="212">
+      <c r="F4" s="210">
         <f ca="1">Statement!AC171</f>
         <v>4629229.4400000004</v>
       </c>
-      <c r="H4" s="209" t="str">
+      <c r="H4" s="207" t="str">
         <f>'AVG target price'!B6</f>
         <v>EV/EBIT price</v>
       </c>
-      <c r="I4" s="235">
+      <c r="I4" s="233">
         <f ca="1">'AVG target price'!C6</f>
-        <v>15.937709207716596</v>
+        <v>15.525998591677991</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B5" s="209" t="s">
+      <c r="B5" s="207" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="232" cm="1">
+      <c r="C5" s="230" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
         <v>11.24</v>
       </c>
-      <c r="E5" s="209" t="s">
-        <v>295</v>
-      </c>
-      <c r="F5" s="213">
+      <c r="E5" s="207" t="s">
+        <v>293</v>
+      </c>
+      <c r="F5" s="211">
         <f>Statement!AC26</f>
         <v>0.60000000000000009</v>
       </c>
-      <c r="H5" s="209" t="str">
+      <c r="H5" s="207" t="str">
         <f>'AVG target price'!B7</f>
         <v>PS price</v>
       </c>
-      <c r="I5" s="235">
-        <f ca="1">'AVG target price'!C7</f>
-        <v>16.119127102841901</v>
+      <c r="I5" s="233">
+        <f>'AVG target price'!C7</f>
+        <v>13.993493556532998</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B6" s="209" t="s">
+      <c r="B6" s="207" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="232" cm="1">
+      <c r="C6" s="230" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
         <v>11.13</v>
       </c>
-      <c r="E6" s="209" t="s">
-        <v>289</v>
-      </c>
-      <c r="F6" s="214">
+      <c r="E6" s="207" t="s">
+        <v>287</v>
+      </c>
+      <c r="F6" s="212">
         <f ca="1">Statement!AC167</f>
         <v>18.733333333333331</v>
       </c>
-      <c r="H6" s="209" t="str">
+      <c r="H6" s="207" t="str">
         <f>'AVG target price'!B8</f>
         <v>EV/FCFF price</v>
       </c>
-      <c r="I6" s="235">
+      <c r="I6" s="233">
         <f ca="1">'AVG target price'!C8</f>
-        <v>10.085573657345705</v>
+        <v>10.179631428344415</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B7" s="209" t="s">
+      <c r="B7" s="207" t="s">
         <v>3</v>
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
         <v>-0.43</v>
       </c>
-      <c r="E7" s="210" t="s">
+      <c r="E7" s="208" t="s">
         <v>243</v>
       </c>
-      <c r="F7" s="215">
+      <c r="F7" s="213">
         <f ca="1">Statement!AC168</f>
         <v>3.6210005501306561</v>
       </c>
-      <c r="H7" s="208" t="str">
+      <c r="H7" s="206" t="str">
         <f>'AVG target price'!B9</f>
         <v>AVG price</v>
       </c>
-      <c r="I7" s="236">
+      <c r="I7" s="234">
         <f ca="1">'AVG target price'!C9</f>
-        <v>12.194536943155708</v>
+        <v>11.583715345318508</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B8" s="209" t="s">
+      <c r="B8" s="207" t="s">
         <v>4</v>
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
         <v>-0.11</v>
       </c>
-      <c r="E8" s="209" t="s">
-        <v>317</v>
-      </c>
-      <c r="F8" s="216">
+      <c r="E8" s="207" t="s">
+        <v>315</v>
+      </c>
+      <c r="F8" s="214">
         <f ca="1">Statement!AC178</f>
         <v>1.8126755065546118E-2</v>
       </c>
-      <c r="H8" s="208" t="str">
+      <c r="H8" s="206" t="str">
         <f>'AVG target price'!B11</f>
         <v>Upside/Downside</v>
       </c>
-      <c r="I8" s="237">
+      <c r="I8" s="235">
         <f ca="1">'AVG target price'!C11</f>
-        <v>8.4923215583247988E-2</v>
+        <v>3.0579657056806722E-2</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B9" s="209" t="s">
+      <c r="B9" s="207" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
         <v>-3.6846999999999998E-2</v>
       </c>
-      <c r="E9" s="209" t="s">
-        <v>340</v>
-      </c>
-      <c r="F9" s="216">
+      <c r="E9" s="207" t="s">
+        <v>338</v>
+      </c>
+      <c r="F9" s="214">
         <f ca="1">Statement!AC179</f>
         <v>5.3380782918149475E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B10" s="209" t="s">
+      <c r="B10" s="207" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
         <v>-9.7859999999999996E-3</v>
       </c>
-      <c r="E10" s="209" t="s">
-        <v>345</v>
-      </c>
-      <c r="F10" s="216">
+      <c r="E10" s="207" t="s">
+        <v>343</v>
+      </c>
+      <c r="F10" s="214">
         <f ca="1">Statement!AC181</f>
         <v>5.8177974430556868E-2</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B11" s="209" t="s">
+      <c r="B11" s="207" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="233" cm="1">
+      <c r="C11" s="231" cm="1">
         <f t="array" aca="1" ref="C11" ca="1">_FV(C3,"52 week high",TRUE)</f>
         <v>19.84</v>
       </c>
-      <c r="E11" s="210" t="s">
-        <v>341</v>
-      </c>
-      <c r="F11" s="217">
+      <c r="E11" s="208" t="s">
+        <v>339</v>
+      </c>
+      <c r="F11" s="215">
         <f ca="1">Statement!AC180</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B12" s="209" t="s">
+      <c r="B12" s="207" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="233" cm="1">
+      <c r="C12" s="231" cm="1">
         <f t="array" aca="1" ref="C12" ca="1">_FV(C3,"52 week low",TRUE)</f>
         <v>9.2002000000000006</v>
       </c>
-      <c r="E12" s="209" t="s">
+      <c r="E12" s="207" t="s">
         <v>121</v>
       </c>
-      <c r="F12" s="216">
+      <c r="F12" s="214">
         <f>Statement!AC132</f>
         <v>0.1127173202051847</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B13" s="209" t="s">
+      <c r="B13" s="207" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="233" cm="1">
+      <c r="C13" s="231" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
         <v>0.96460000000000001</v>
       </c>
-      <c r="E13" s="209" t="s">
+      <c r="E13" s="207" t="s">
         <v>123</v>
       </c>
-      <c r="F13" s="216">
+      <c r="F13" s="214">
         <f>Statement!AC134</f>
         <v>0.17205256008386913</v>
       </c>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B14" s="210" t="s">
+      <c r="B14" s="208" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="234" cm="1">
+      <c r="C14" s="232" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
         <v>40933553</v>
       </c>
-      <c r="E14" s="210" t="s">
+      <c r="E14" s="208" t="s">
         <v>124</v>
       </c>
-      <c r="F14" s="217">
+      <c r="F14" s="215">
         <f>Statement!AC157</f>
         <v>0.16980935706480046</v>
       </c>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="E15" s="209" t="s">
-        <v>342</v>
-      </c>
-      <c r="F15" s="216">
+      <c r="E15" s="207" t="s">
+        <v>340</v>
+      </c>
+      <c r="F15" s="214">
         <f ca="1">Statement!AC193</f>
         <v>0.22020548280259802</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="E16" s="210" t="s">
-        <v>347</v>
-      </c>
-      <c r="F16" s="215">
+      <c r="E16" s="208" t="s">
+        <v>345</v>
+      </c>
+      <c r="F16" s="213">
         <f>Statement!AC192</f>
         <v>2.4951118677971147</v>
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="251" t="s">
+      <c r="B17" s="249" t="s">
         <v>103</v>
       </c>
-      <c r="C17" s="251"/>
-      <c r="E17" s="208" t="s">
-        <v>348</v>
-      </c>
-      <c r="F17" s="218">
+      <c r="C17" s="249"/>
+      <c r="E17" s="206" t="s">
+        <v>346</v>
+      </c>
+      <c r="F17" s="216">
         <f>Statement!AC188</f>
         <v>0.22116382280992736</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B18" s="208" t="s">
+      <c r="B18" s="206" t="s">
         <v>12</v>
       </c>
       <c r="C18" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="E18" s="209" t="s">
-        <v>349</v>
-      </c>
-      <c r="F18" s="214">
+      <c r="E18" s="207" t="s">
+        <v>347</v>
+      </c>
+      <c r="F18" s="212">
         <f>Statement!AC161</f>
         <v>40.164814474593925</v>
       </c>
       <c r="I18" s="50"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="208" t="s">
+      <c r="B19" s="206" t="s">
         <v>13</v>
       </c>
       <c r="C19" s="70">
         <v>1000</v>
       </c>
-      <c r="E19" s="209" t="s">
-        <v>310</v>
-      </c>
-      <c r="F19" s="214">
+      <c r="E19" s="207" t="s">
+        <v>308</v>
+      </c>
+      <c r="F19" s="212">
         <f>Statement!AC163</f>
         <v>-0.68695115254353079</v>
       </c>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B20" s="208" t="s">
+      <c r="B20" s="206" t="s">
         <v>104</v>
       </c>
       <c r="C20" s="69" t="s">
         <v>105</v>
       </c>
-      <c r="E20" s="210" t="s">
-        <v>350</v>
-      </c>
-      <c r="F20" s="215">
+      <c r="E20" s="208" t="s">
+        <v>348</v>
+      </c>
+      <c r="F20" s="213">
         <f>Statement!AC164</f>
         <v>1.9325582625717537</v>
       </c>
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B21" s="208" t="s">
+      <c r="B21" s="206" t="s">
         <v>106</v>
       </c>
       <c r="C21" s="69" t="s">
@@ -12993,7 +12999,7 @@
       <c r="I21" s="50"/>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B22" s="208" t="s">
+      <c r="B22" s="206" t="s">
         <v>108</v>
       </c>
       <c r="C22" s="69" t="s">
@@ -13001,119 +13007,135 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="251" t="s">
+      <c r="B25" s="249" t="s">
         <v>126</v>
       </c>
-      <c r="C25" s="251"/>
-      <c r="E25" s="249" t="s">
-        <v>404</v>
-      </c>
-      <c r="F25" s="250"/>
+      <c r="C25" s="249"/>
+      <c r="E25" s="247" t="s">
+        <v>402</v>
+      </c>
+      <c r="F25" s="248"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B26" s="208" t="s">
+      <c r="B26" s="206" t="s">
         <v>127</v>
       </c>
-      <c r="C26" s="193">
+      <c r="C26" s="191">
         <v>0.21</v>
       </c>
-      <c r="E26" s="209" t="e" vm="2">
+      <c r="E26" s="207" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="F26" s="245" cm="1">
+      <c r="F26" s="243" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
         <v>45.36</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B27" s="208" t="s">
+      <c r="B27" s="206" t="s">
         <v>214</v>
       </c>
-      <c r="C27" s="247">
-        <v>0</v>
-      </c>
-      <c r="E27" s="210" t="s">
-        <v>405</v>
-      </c>
-      <c r="F27" s="246">
+      <c r="C27" s="245">
+        <v>0</v>
+      </c>
+      <c r="E27" s="208" t="s">
+        <v>403</v>
+      </c>
+      <c r="F27" s="244">
         <f ca="1">F26/1000</f>
         <v>4.5359999999999998E-2</v>
       </c>
     </row>
-    <row r="31" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B31" s="248" t="s">
+    <row r="28" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B28" s="206" t="s">
+        <v>407</v>
+      </c>
+      <c r="C28" s="245">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B29" s="206" t="s">
+        <v>408</v>
+      </c>
+      <c r="C29" s="245">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="33" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B33" s="246" t="s">
+        <v>392</v>
+      </c>
+      <c r="C33" s="246"/>
+      <c r="D33" s="246"/>
+      <c r="E33" s="246"/>
+      <c r="F33" s="246"/>
+      <c r="G33" s="246"/>
+      <c r="H33" s="246"/>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B35" s="16" t="s">
+        <v>393</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B36" s="16" t="s">
         <v>394</v>
       </c>
-      <c r="C31" s="248"/>
-      <c r="D31" s="248"/>
-      <c r="E31" s="248"/>
-      <c r="F31" s="248"/>
-      <c r="G31" s="248"/>
-      <c r="H31" s="248"/>
-    </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="16" t="s">
+      <c r="C36" s="1" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B39" s="246"/>
+      <c r="C39" s="246"/>
+      <c r="D39" s="246"/>
+      <c r="E39" s="246"/>
+      <c r="F39" s="246"/>
+      <c r="G39" s="246"/>
+      <c r="H39" s="246"/>
+    </row>
+    <row r="42" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B42" s="246" t="s">
         <v>395</v>
       </c>
-      <c r="C33" s="1" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B34" s="16" t="s">
+      <c r="C42" s="246"/>
+      <c r="D42" s="246"/>
+      <c r="E42" s="246"/>
+      <c r="F42" s="246"/>
+      <c r="G42" s="246"/>
+      <c r="H42" s="246"/>
+    </row>
+    <row r="44" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B44" s="41" t="s">
         <v>396</v>
       </c>
-      <c r="C34" s="1" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="37" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B37" s="248"/>
-      <c r="C37" s="248"/>
-      <c r="D37" s="248"/>
-      <c r="E37" s="248"/>
-      <c r="F37" s="248"/>
-      <c r="G37" s="248"/>
-      <c r="H37" s="248"/>
-    </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B40" s="248" t="s">
-        <v>397</v>
-      </c>
-      <c r="C40" s="248"/>
-      <c r="D40" s="248"/>
-      <c r="E40" s="248"/>
-      <c r="F40" s="248"/>
-      <c r="G40" s="248"/>
-      <c r="H40" s="248"/>
-    </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="41" t="s">
-        <v>398</v>
-      </c>
-      <c r="C42" s="41" t="s">
-        <v>385</v>
-      </c>
-      <c r="D42" s="41" t="s">
-        <v>386</v>
-      </c>
-      <c r="E42" s="243"/>
-    </row>
-    <row r="47" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B47" s="248"/>
-      <c r="C47" s="248"/>
-      <c r="D47" s="248"/>
-      <c r="E47" s="248"/>
-      <c r="F47" s="248"/>
-      <c r="G47" s="248"/>
-      <c r="H47" s="248"/>
+      <c r="C44" s="41" t="s">
+        <v>383</v>
+      </c>
+      <c r="D44" s="41" t="s">
+        <v>384</v>
+      </c>
+      <c r="E44" s="241"/>
+    </row>
+    <row r="49" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B49" s="246"/>
+      <c r="C49" s="246"/>
+      <c r="D49" s="246"/>
+      <c r="E49" s="246"/>
+      <c r="F49" s="246"/>
+      <c r="G49" s="246"/>
+      <c r="H49" s="246"/>
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="B31:H31"/>
-    <mergeCell ref="B37:H37"/>
-    <mergeCell ref="B40:H40"/>
-    <mergeCell ref="B47:H47"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="B49:H49"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B25:C25"/>
@@ -13189,36 +13211,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="248" t="s">
+      <c r="C2" s="246" t="s">
         <v>137</v>
       </c>
-      <c r="D2" s="248"/>
-      <c r="E2" s="248"/>
-      <c r="F2" s="248"/>
-      <c r="G2" s="257"/>
-      <c r="H2" s="258" t="s">
+      <c r="D2" s="246"/>
+      <c r="E2" s="246"/>
+      <c r="F2" s="246"/>
+      <c r="G2" s="258"/>
+      <c r="H2" s="259" t="s">
         <v>138</v>
       </c>
-      <c r="I2" s="248"/>
-      <c r="J2" s="248"/>
-      <c r="K2" s="248"/>
-      <c r="L2" s="248"/>
+      <c r="I2" s="246"/>
+      <c r="J2" s="246"/>
+      <c r="K2" s="246"/>
+      <c r="L2" s="246"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="248" t="s">
+      <c r="S2" s="246" t="s">
         <v>137</v>
       </c>
-      <c r="T2" s="248"/>
-      <c r="U2" s="248"/>
-      <c r="V2" s="248"/>
-      <c r="W2" s="248"/>
-      <c r="X2" s="248"/>
-      <c r="Y2" s="248"/>
-      <c r="Z2" s="248"/>
-      <c r="AA2" s="248" t="s">
+      <c r="T2" s="246"/>
+      <c r="U2" s="246"/>
+      <c r="V2" s="246"/>
+      <c r="W2" s="246"/>
+      <c r="X2" s="246"/>
+      <c r="Y2" s="246"/>
+      <c r="Z2" s="246"/>
+      <c r="AA2" s="246" t="s">
         <v>138</v>
       </c>
-      <c r="AB2" s="248"/>
-      <c r="AC2" s="248"/>
+      <c r="AB2" s="246"/>
+      <c r="AC2" s="246"/>
       <c r="AE2" s="87" t="s">
         <v>139</v>
       </c>
@@ -13229,32 +13251,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="259" t="s">
+      <c r="C4" s="255" t="s">
         <v>140</v>
       </c>
-      <c r="D4" s="259"/>
-      <c r="E4" s="259"/>
-      <c r="F4" s="259"/>
-      <c r="G4" s="259"/>
-      <c r="H4" s="259"/>
-      <c r="I4" s="259"/>
-      <c r="J4" s="259"/>
-      <c r="K4" s="259"/>
-      <c r="L4" s="259"/>
+      <c r="D4" s="255"/>
+      <c r="E4" s="255"/>
+      <c r="F4" s="255"/>
+      <c r="G4" s="255"/>
+      <c r="H4" s="255"/>
+      <c r="I4" s="255"/>
+      <c r="J4" s="255"/>
+      <c r="K4" s="255"/>
+      <c r="L4" s="255"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="260" t="s">
+      <c r="S4" s="256" t="s">
         <v>140</v>
       </c>
-      <c r="T4" s="261"/>
-      <c r="U4" s="261"/>
-      <c r="V4" s="261"/>
-      <c r="W4" s="261"/>
-      <c r="X4" s="261"/>
-      <c r="Y4" s="261"/>
-      <c r="Z4" s="261"/>
-      <c r="AA4" s="261"/>
-      <c r="AB4" s="261"/>
-      <c r="AC4" s="261"/>
+      <c r="T4" s="257"/>
+      <c r="U4" s="257"/>
+      <c r="V4" s="257"/>
+      <c r="W4" s="257"/>
+      <c r="X4" s="257"/>
+      <c r="Y4" s="257"/>
+      <c r="Z4" s="257"/>
+      <c r="AA4" s="257"/>
+      <c r="AB4" s="257"/>
+      <c r="AC4" s="257"/>
       <c r="AE4" s="89"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -13750,33 +13772,33 @@
       <c r="Q10" s="93"/>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C11" s="259" t="s">
+      <c r="C11" s="255" t="s">
         <v>146</v>
       </c>
-      <c r="D11" s="259"/>
-      <c r="E11" s="259"/>
-      <c r="F11" s="259"/>
-      <c r="G11" s="259"/>
-      <c r="H11" s="259"/>
-      <c r="I11" s="259"/>
-      <c r="J11" s="259"/>
-      <c r="K11" s="259"/>
-      <c r="L11" s="259"/>
+      <c r="D11" s="255"/>
+      <c r="E11" s="255"/>
+      <c r="F11" s="255"/>
+      <c r="G11" s="255"/>
+      <c r="H11" s="255"/>
+      <c r="I11" s="255"/>
+      <c r="J11" s="255"/>
+      <c r="K11" s="255"/>
+      <c r="L11" s="255"/>
       <c r="O11" s="5"/>
       <c r="Q11" s="93"/>
-      <c r="S11" s="260" t="s">
+      <c r="S11" s="256" t="s">
         <v>146</v>
       </c>
-      <c r="T11" s="261"/>
-      <c r="U11" s="261"/>
-      <c r="V11" s="261"/>
-      <c r="W11" s="261"/>
-      <c r="X11" s="261"/>
-      <c r="Y11" s="261"/>
-      <c r="Z11" s="261"/>
-      <c r="AA11" s="261"/>
-      <c r="AB11" s="261"/>
-      <c r="AC11" s="261"/>
+      <c r="T11" s="257"/>
+      <c r="U11" s="257"/>
+      <c r="V11" s="257"/>
+      <c r="W11" s="257"/>
+      <c r="X11" s="257"/>
+      <c r="Y11" s="257"/>
+      <c r="Z11" s="257"/>
+      <c r="AA11" s="257"/>
+      <c r="AB11" s="257"/>
+      <c r="AC11" s="257"/>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B12" s="16" t="s">
@@ -14217,33 +14239,33 @@
       <c r="Q18" s="93"/>
     </row>
     <row r="19" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C19" s="259" t="s">
+      <c r="C19" s="255" t="s">
         <v>148</v>
       </c>
-      <c r="D19" s="259"/>
-      <c r="E19" s="259"/>
-      <c r="F19" s="259"/>
-      <c r="G19" s="259"/>
-      <c r="H19" s="259"/>
-      <c r="I19" s="259"/>
-      <c r="J19" s="259"/>
-      <c r="K19" s="259"/>
-      <c r="L19" s="259"/>
+      <c r="D19" s="255"/>
+      <c r="E19" s="255"/>
+      <c r="F19" s="255"/>
+      <c r="G19" s="255"/>
+      <c r="H19" s="255"/>
+      <c r="I19" s="255"/>
+      <c r="J19" s="255"/>
+      <c r="K19" s="255"/>
+      <c r="L19" s="255"/>
       <c r="O19" s="5"/>
       <c r="Q19" s="93"/>
-      <c r="S19" s="260" t="s">
+      <c r="S19" s="256" t="s">
         <v>148</v>
       </c>
-      <c r="T19" s="261"/>
-      <c r="U19" s="261"/>
-      <c r="V19" s="261"/>
-      <c r="W19" s="261"/>
-      <c r="X19" s="261"/>
-      <c r="Y19" s="261"/>
-      <c r="Z19" s="261"/>
-      <c r="AA19" s="261"/>
-      <c r="AB19" s="261"/>
-      <c r="AC19" s="261"/>
+      <c r="T19" s="257"/>
+      <c r="U19" s="257"/>
+      <c r="V19" s="257"/>
+      <c r="W19" s="257"/>
+      <c r="X19" s="257"/>
+      <c r="Y19" s="257"/>
+      <c r="Z19" s="257"/>
+      <c r="AA19" s="257"/>
+      <c r="AB19" s="257"/>
+      <c r="AC19" s="257"/>
       <c r="AE19" s="89">
         <f>AE4</f>
         <v>0</v>
@@ -15061,32 +15083,32 @@
       <c r="O31" s="5"/>
     </row>
     <row r="32" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C32" s="259" t="s">
+      <c r="C32" s="255" t="s">
         <v>150</v>
       </c>
-      <c r="D32" s="259"/>
-      <c r="E32" s="259"/>
-      <c r="F32" s="259"/>
-      <c r="G32" s="259"/>
-      <c r="H32" s="259"/>
-      <c r="I32" s="259"/>
-      <c r="J32" s="259"/>
-      <c r="K32" s="259"/>
-      <c r="L32" s="259"/>
+      <c r="D32" s="255"/>
+      <c r="E32" s="255"/>
+      <c r="F32" s="255"/>
+      <c r="G32" s="255"/>
+      <c r="H32" s="255"/>
+      <c r="I32" s="255"/>
+      <c r="J32" s="255"/>
+      <c r="K32" s="255"/>
+      <c r="L32" s="255"/>
       <c r="O32" s="5"/>
-      <c r="S32" s="260" t="s">
+      <c r="S32" s="256" t="s">
         <v>150</v>
       </c>
-      <c r="T32" s="261"/>
-      <c r="U32" s="261"/>
-      <c r="V32" s="261"/>
-      <c r="W32" s="261"/>
-      <c r="X32" s="261"/>
-      <c r="Y32" s="261"/>
-      <c r="Z32" s="261"/>
-      <c r="AA32" s="261"/>
-      <c r="AB32" s="261"/>
-      <c r="AC32" s="261"/>
+      <c r="T32" s="257"/>
+      <c r="U32" s="257"/>
+      <c r="V32" s="257"/>
+      <c r="W32" s="257"/>
+      <c r="X32" s="257"/>
+      <c r="Y32" s="257"/>
+      <c r="Z32" s="257"/>
+      <c r="AA32" s="257"/>
+      <c r="AB32" s="257"/>
+      <c r="AC32" s="257"/>
     </row>
     <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B33" s="16" t="s">
@@ -15343,18 +15365,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="S11:AC11"/>
     <mergeCell ref="C19:L19"/>
     <mergeCell ref="S19:AC19"/>
     <mergeCell ref="C32:L32"/>
     <mergeCell ref="S32:AC32"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -15391,35 +15413,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="248" t="s">
+      <c r="C2" s="246" t="s">
         <v>137</v>
       </c>
-      <c r="D2" s="248"/>
-      <c r="E2" s="248"/>
-      <c r="F2" s="248"/>
-      <c r="G2" s="257"/>
-      <c r="H2" s="258" t="s">
+      <c r="D2" s="246"/>
+      <c r="E2" s="246"/>
+      <c r="F2" s="246"/>
+      <c r="G2" s="258"/>
+      <c r="H2" s="259" t="s">
         <v>138</v>
       </c>
-      <c r="I2" s="248"/>
-      <c r="J2" s="248"/>
-      <c r="K2" s="248"/>
-      <c r="L2" s="248"/>
-      <c r="P2" s="248" t="s">
+      <c r="I2" s="246"/>
+      <c r="J2" s="246"/>
+      <c r="K2" s="246"/>
+      <c r="L2" s="246"/>
+      <c r="P2" s="246" t="s">
         <v>137</v>
       </c>
-      <c r="Q2" s="248"/>
-      <c r="R2" s="248"/>
-      <c r="S2" s="248"/>
-      <c r="T2" s="248"/>
-      <c r="U2" s="248"/>
-      <c r="V2" s="248"/>
-      <c r="W2" s="248"/>
-      <c r="X2" s="248" t="s">
+      <c r="Q2" s="246"/>
+      <c r="R2" s="246"/>
+      <c r="S2" s="246"/>
+      <c r="T2" s="246"/>
+      <c r="U2" s="246"/>
+      <c r="V2" s="246"/>
+      <c r="W2" s="246"/>
+      <c r="X2" s="246" t="s">
         <v>138</v>
       </c>
-      <c r="Y2" s="248"/>
-      <c r="Z2" s="248"/>
+      <c r="Y2" s="246"/>
+      <c r="Z2" s="246"/>
       <c r="AB2" s="87" t="s">
         <v>139</v>
       </c>
@@ -15428,31 +15450,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="259" t="s">
+      <c r="C4" s="255" t="s">
         <v>140</v>
       </c>
-      <c r="D4" s="259"/>
-      <c r="E4" s="259"/>
-      <c r="F4" s="259"/>
-      <c r="G4" s="259"/>
-      <c r="H4" s="259"/>
-      <c r="I4" s="259"/>
-      <c r="J4" s="259"/>
-      <c r="K4" s="259"/>
-      <c r="L4" s="259"/>
-      <c r="P4" s="261" t="s">
+      <c r="D4" s="255"/>
+      <c r="E4" s="255"/>
+      <c r="F4" s="255"/>
+      <c r="G4" s="255"/>
+      <c r="H4" s="255"/>
+      <c r="I4" s="255"/>
+      <c r="J4" s="255"/>
+      <c r="K4" s="255"/>
+      <c r="L4" s="255"/>
+      <c r="P4" s="257" t="s">
         <v>140</v>
       </c>
-      <c r="Q4" s="261"/>
-      <c r="R4" s="261"/>
-      <c r="S4" s="261"/>
-      <c r="T4" s="261"/>
-      <c r="U4" s="261"/>
-      <c r="V4" s="261"/>
-      <c r="W4" s="261"/>
-      <c r="X4" s="261"/>
-      <c r="Y4" s="261"/>
-      <c r="Z4" s="261"/>
+      <c r="Q4" s="257"/>
+      <c r="R4" s="257"/>
+      <c r="S4" s="257"/>
+      <c r="T4" s="257"/>
+      <c r="U4" s="257"/>
+      <c r="V4" s="257"/>
+      <c r="W4" s="257"/>
+      <c r="X4" s="257"/>
+      <c r="Y4" s="257"/>
+      <c r="Z4" s="257"/>
       <c r="AB4" s="89"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -15647,32 +15669,32 @@
       <c r="N8" s="93"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="259" t="s">
+      <c r="C9" s="255" t="s">
         <v>166</v>
       </c>
-      <c r="D9" s="259"/>
-      <c r="E9" s="259"/>
-      <c r="F9" s="259"/>
-      <c r="G9" s="259"/>
-      <c r="H9" s="259"/>
-      <c r="I9" s="259"/>
-      <c r="J9" s="259"/>
-      <c r="K9" s="259"/>
-      <c r="L9" s="259"/>
+      <c r="D9" s="255"/>
+      <c r="E9" s="255"/>
+      <c r="F9" s="255"/>
+      <c r="G9" s="255"/>
+      <c r="H9" s="255"/>
+      <c r="I9" s="255"/>
+      <c r="J9" s="255"/>
+      <c r="K9" s="255"/>
+      <c r="L9" s="255"/>
       <c r="N9" s="93"/>
-      <c r="P9" s="261" t="s">
+      <c r="P9" s="257" t="s">
         <v>167</v>
       </c>
-      <c r="Q9" s="261"/>
-      <c r="R9" s="261"/>
-      <c r="S9" s="261"/>
-      <c r="T9" s="261"/>
-      <c r="U9" s="261"/>
-      <c r="V9" s="261"/>
-      <c r="W9" s="261"/>
-      <c r="X9" s="261"/>
-      <c r="Y9" s="261"/>
-      <c r="Z9" s="261"/>
+      <c r="Q9" s="257"/>
+      <c r="R9" s="257"/>
+      <c r="S9" s="257"/>
+      <c r="T9" s="257"/>
+      <c r="U9" s="257"/>
+      <c r="V9" s="257"/>
+      <c r="W9" s="257"/>
+      <c r="X9" s="257"/>
+      <c r="Y9" s="257"/>
+      <c r="Z9" s="257"/>
       <c r="AB9" s="89">
         <f>AB4</f>
         <v>0</v>
@@ -16521,31 +16543,31 @@
       </c>
     </row>
     <row r="21" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="C21" s="259" t="s">
+      <c r="C21" s="255" t="s">
         <v>169</v>
       </c>
-      <c r="D21" s="259"/>
-      <c r="E21" s="259"/>
-      <c r="F21" s="259"/>
-      <c r="G21" s="259"/>
-      <c r="H21" s="259"/>
-      <c r="I21" s="259"/>
-      <c r="J21" s="259"/>
-      <c r="K21" s="259"/>
-      <c r="L21" s="259"/>
-      <c r="P21" s="261" t="s">
+      <c r="D21" s="255"/>
+      <c r="E21" s="255"/>
+      <c r="F21" s="255"/>
+      <c r="G21" s="255"/>
+      <c r="H21" s="255"/>
+      <c r="I21" s="255"/>
+      <c r="J21" s="255"/>
+      <c r="K21" s="255"/>
+      <c r="L21" s="255"/>
+      <c r="P21" s="257" t="s">
         <v>169</v>
       </c>
-      <c r="Q21" s="261"/>
-      <c r="R21" s="261"/>
-      <c r="S21" s="261"/>
-      <c r="T21" s="261"/>
-      <c r="U21" s="261"/>
-      <c r="V21" s="261"/>
-      <c r="W21" s="261"/>
-      <c r="X21" s="261"/>
-      <c r="Y21" s="261"/>
-      <c r="Z21" s="261"/>
+      <c r="Q21" s="257"/>
+      <c r="R21" s="257"/>
+      <c r="S21" s="257"/>
+      <c r="T21" s="257"/>
+      <c r="U21" s="257"/>
+      <c r="V21" s="257"/>
+      <c r="W21" s="257"/>
+      <c r="X21" s="257"/>
+      <c r="Y21" s="257"/>
+      <c r="Z21" s="257"/>
     </row>
     <row r="22" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B22" s="16" t="s">
@@ -17360,60 +17382,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="248" t="s">
+      <c r="C3" s="246" t="s">
         <v>137</v>
       </c>
-      <c r="D3" s="248"/>
-      <c r="E3" s="248"/>
-      <c r="F3" s="248"/>
-      <c r="G3" s="257"/>
-      <c r="H3" s="258" t="s">
+      <c r="D3" s="246"/>
+      <c r="E3" s="246"/>
+      <c r="F3" s="246"/>
+      <c r="G3" s="258"/>
+      <c r="H3" s="259" t="s">
         <v>138</v>
       </c>
-      <c r="I3" s="248"/>
-      <c r="J3" s="248"/>
-      <c r="K3" s="248"/>
-      <c r="L3" s="248"/>
-      <c r="P3" s="262"/>
-      <c r="Q3" s="262"/>
-      <c r="R3" s="262"/>
-      <c r="S3" s="262"/>
-      <c r="T3" s="262"/>
-      <c r="U3" s="262"/>
-      <c r="V3" s="262"/>
-      <c r="W3" s="262"/>
-      <c r="X3" s="262"/>
-      <c r="Y3" s="262"/>
-      <c r="Z3" s="262"/>
+      <c r="I3" s="246"/>
+      <c r="J3" s="246"/>
+      <c r="K3" s="246"/>
+      <c r="L3" s="246"/>
+      <c r="P3" s="260"/>
+      <c r="Q3" s="260"/>
+      <c r="R3" s="260"/>
+      <c r="S3" s="260"/>
+      <c r="T3" s="260"/>
+      <c r="U3" s="260"/>
+      <c r="V3" s="260"/>
+      <c r="W3" s="260"/>
+      <c r="X3" s="260"/>
+      <c r="Y3" s="260"/>
+      <c r="Z3" s="260"/>
       <c r="AB3" s="130"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="88"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="259" t="s">
+      <c r="C5" s="255" t="s">
         <v>140</v>
       </c>
-      <c r="D5" s="259"/>
-      <c r="E5" s="259"/>
-      <c r="F5" s="259"/>
-      <c r="G5" s="259"/>
-      <c r="H5" s="259"/>
-      <c r="I5" s="259"/>
-      <c r="J5" s="259"/>
-      <c r="K5" s="259"/>
-      <c r="L5" s="259"/>
-      <c r="P5" s="262"/>
-      <c r="Q5" s="262"/>
-      <c r="R5" s="262"/>
-      <c r="S5" s="262"/>
-      <c r="T5" s="262"/>
-      <c r="U5" s="262"/>
-      <c r="V5" s="262"/>
-      <c r="W5" s="262"/>
-      <c r="X5" s="262"/>
-      <c r="Y5" s="262"/>
-      <c r="Z5" s="262"/>
+      <c r="D5" s="255"/>
+      <c r="E5" s="255"/>
+      <c r="F5" s="255"/>
+      <c r="G5" s="255"/>
+      <c r="H5" s="255"/>
+      <c r="I5" s="255"/>
+      <c r="J5" s="255"/>
+      <c r="K5" s="255"/>
+      <c r="L5" s="255"/>
+      <c r="P5" s="260"/>
+      <c r="Q5" s="260"/>
+      <c r="R5" s="260"/>
+      <c r="S5" s="260"/>
+      <c r="T5" s="260"/>
+      <c r="U5" s="260"/>
+      <c r="V5" s="260"/>
+      <c r="W5" s="260"/>
+      <c r="X5" s="260"/>
+      <c r="Y5" s="260"/>
+      <c r="Z5" s="260"/>
       <c r="AB5" s="131"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -17599,30 +17621,30 @@
       <c r="N10" s="93"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="259" t="s">
+      <c r="C11" s="255" t="s">
         <v>173</v>
       </c>
-      <c r="D11" s="259"/>
-      <c r="E11" s="259"/>
-      <c r="F11" s="259"/>
-      <c r="G11" s="259"/>
-      <c r="H11" s="259"/>
-      <c r="I11" s="259"/>
-      <c r="J11" s="259"/>
-      <c r="K11" s="259"/>
-      <c r="L11" s="259"/>
+      <c r="D11" s="255"/>
+      <c r="E11" s="255"/>
+      <c r="F11" s="255"/>
+      <c r="G11" s="255"/>
+      <c r="H11" s="255"/>
+      <c r="I11" s="255"/>
+      <c r="J11" s="255"/>
+      <c r="K11" s="255"/>
+      <c r="L11" s="255"/>
       <c r="N11" s="93"/>
-      <c r="P11" s="262"/>
-      <c r="Q11" s="262"/>
-      <c r="R11" s="262"/>
-      <c r="S11" s="262"/>
-      <c r="T11" s="262"/>
-      <c r="U11" s="262"/>
-      <c r="V11" s="262"/>
-      <c r="W11" s="262"/>
-      <c r="X11" s="262"/>
-      <c r="Y11" s="262"/>
-      <c r="Z11" s="262"/>
+      <c r="P11" s="260"/>
+      <c r="Q11" s="260"/>
+      <c r="R11" s="260"/>
+      <c r="S11" s="260"/>
+      <c r="T11" s="260"/>
+      <c r="U11" s="260"/>
+      <c r="V11" s="260"/>
+      <c r="W11" s="260"/>
+      <c r="X11" s="260"/>
+      <c r="Y11" s="260"/>
+      <c r="Z11" s="260"/>
       <c r="AB11" s="131"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -17864,18 +17886,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="259" t="s">
+      <c r="C18" s="255" t="s">
         <v>178</v>
       </c>
-      <c r="D18" s="259"/>
-      <c r="E18" s="259"/>
-      <c r="F18" s="259"/>
-      <c r="G18" s="259"/>
-      <c r="H18" s="259"/>
-      <c r="I18" s="259"/>
-      <c r="J18" s="259"/>
-      <c r="K18" s="259"/>
-      <c r="L18" s="259"/>
+      <c r="D18" s="255"/>
+      <c r="E18" s="255"/>
+      <c r="F18" s="255"/>
+      <c r="G18" s="255"/>
+      <c r="H18" s="255"/>
+      <c r="I18" s="255"/>
+      <c r="J18" s="255"/>
+      <c r="K18" s="255"/>
+      <c r="L18" s="255"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -18088,23 +18110,23 @@
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="262"/>
-      <c r="C25" s="262"/>
+      <c r="B25" s="260"/>
+      <c r="C25" s="260"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="130"/>
-      <c r="C26" s="259" t="s">
+      <c r="C26" s="255" t="s">
         <v>184</v>
       </c>
-      <c r="D26" s="259"/>
-      <c r="E26" s="259"/>
-      <c r="F26" s="259"/>
-      <c r="G26" s="259"/>
-      <c r="H26" s="259"/>
-      <c r="I26" s="259"/>
-      <c r="J26" s="259"/>
-      <c r="K26" s="259"/>
-      <c r="L26" s="259"/>
+      <c r="D26" s="255"/>
+      <c r="E26" s="255"/>
+      <c r="F26" s="255"/>
+      <c r="G26" s="255"/>
+      <c r="H26" s="255"/>
+      <c r="I26" s="255"/>
+      <c r="J26" s="255"/>
+      <c r="K26" s="255"/>
+      <c r="L26" s="255"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -18296,18 +18318,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="130"/>
-      <c r="C33" s="259" t="s">
+      <c r="C33" s="255" t="s">
         <v>188</v>
       </c>
-      <c r="D33" s="259"/>
-      <c r="E33" s="259"/>
-      <c r="F33" s="259"/>
-      <c r="G33" s="259"/>
-      <c r="H33" s="259"/>
-      <c r="I33" s="259"/>
-      <c r="J33" s="259"/>
-      <c r="K33" s="259"/>
-      <c r="L33" s="259"/>
+      <c r="D33" s="255"/>
+      <c r="E33" s="255"/>
+      <c r="F33" s="255"/>
+      <c r="G33" s="255"/>
+      <c r="H33" s="255"/>
+      <c r="I33" s="255"/>
+      <c r="J33" s="255"/>
+      <c r="K33" s="255"/>
+      <c r="L33" s="255"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -18491,18 +18513,18 @@
       <c r="C39" s="146"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="259" t="s">
+      <c r="C40" s="255" t="s">
         <v>191</v>
       </c>
-      <c r="D40" s="259"/>
-      <c r="E40" s="259"/>
-      <c r="F40" s="259"/>
-      <c r="G40" s="259"/>
-      <c r="H40" s="259"/>
-      <c r="I40" s="259"/>
-      <c r="J40" s="259"/>
-      <c r="K40" s="259"/>
-      <c r="L40" s="259"/>
+      <c r="D40" s="255"/>
+      <c r="E40" s="255"/>
+      <c r="F40" s="255"/>
+      <c r="G40" s="255"/>
+      <c r="H40" s="255"/>
+      <c r="I40" s="255"/>
+      <c r="J40" s="255"/>
+      <c r="K40" s="255"/>
+      <c r="L40" s="255"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -18766,12 +18788,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18779,6 +18795,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -18816,60 +18838,60 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="248" t="s">
+      <c r="C2" s="246" t="s">
         <v>137</v>
       </c>
-      <c r="D2" s="248"/>
-      <c r="E2" s="248"/>
-      <c r="F2" s="248"/>
-      <c r="G2" s="257"/>
-      <c r="H2" s="258" t="s">
+      <c r="D2" s="246"/>
+      <c r="E2" s="246"/>
+      <c r="F2" s="246"/>
+      <c r="G2" s="258"/>
+      <c r="H2" s="259" t="s">
         <v>138</v>
       </c>
-      <c r="I2" s="248"/>
-      <c r="J2" s="248"/>
-      <c r="K2" s="248"/>
-      <c r="L2" s="248"/>
-      <c r="S2" s="262"/>
-      <c r="T2" s="262"/>
-      <c r="U2" s="262"/>
-      <c r="V2" s="262"/>
-      <c r="W2" s="262"/>
-      <c r="X2" s="262"/>
-      <c r="Y2" s="262"/>
-      <c r="Z2" s="262"/>
-      <c r="AA2" s="262"/>
-      <c r="AB2" s="262"/>
-      <c r="AC2" s="262"/>
+      <c r="I2" s="246"/>
+      <c r="J2" s="246"/>
+      <c r="K2" s="246"/>
+      <c r="L2" s="246"/>
+      <c r="S2" s="260"/>
+      <c r="T2" s="260"/>
+      <c r="U2" s="260"/>
+      <c r="V2" s="260"/>
+      <c r="W2" s="260"/>
+      <c r="X2" s="260"/>
+      <c r="Y2" s="260"/>
+      <c r="Z2" s="260"/>
+      <c r="AA2" s="260"/>
+      <c r="AB2" s="260"/>
+      <c r="AC2" s="260"/>
       <c r="AE2" s="130"/>
     </row>
     <row r="3" spans="1:31" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="259" t="s">
+      <c r="C4" s="255" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="259"/>
-      <c r="E4" s="259"/>
-      <c r="F4" s="259"/>
-      <c r="G4" s="259"/>
-      <c r="H4" s="259"/>
-      <c r="I4" s="259"/>
-      <c r="J4" s="259"/>
-      <c r="K4" s="259"/>
-      <c r="L4" s="259"/>
-      <c r="S4" s="262"/>
-      <c r="T4" s="262"/>
-      <c r="U4" s="262"/>
-      <c r="V4" s="262"/>
-      <c r="W4" s="262"/>
-      <c r="X4" s="262"/>
-      <c r="Y4" s="262"/>
-      <c r="Z4" s="262"/>
-      <c r="AA4" s="262"/>
-      <c r="AB4" s="262"/>
-      <c r="AC4" s="262"/>
+      <c r="D4" s="255"/>
+      <c r="E4" s="255"/>
+      <c r="F4" s="255"/>
+      <c r="G4" s="255"/>
+      <c r="H4" s="255"/>
+      <c r="I4" s="255"/>
+      <c r="J4" s="255"/>
+      <c r="K4" s="255"/>
+      <c r="L4" s="255"/>
+      <c r="S4" s="260"/>
+      <c r="T4" s="260"/>
+      <c r="U4" s="260"/>
+      <c r="V4" s="260"/>
+      <c r="W4" s="260"/>
+      <c r="X4" s="260"/>
+      <c r="Y4" s="260"/>
+      <c r="Z4" s="260"/>
+      <c r="AA4" s="260"/>
+      <c r="AB4" s="260"/>
+      <c r="AC4" s="260"/>
       <c r="AE4" s="131"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -19232,18 +19254,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="259" t="s">
+      <c r="C13" s="255" t="s">
         <v>199</v>
       </c>
-      <c r="D13" s="259"/>
-      <c r="E13" s="259"/>
-      <c r="F13" s="259"/>
-      <c r="G13" s="259"/>
-      <c r="H13" s="259"/>
-      <c r="I13" s="259"/>
-      <c r="J13" s="259"/>
-      <c r="K13" s="259"/>
-      <c r="L13" s="259"/>
+      <c r="D13" s="255"/>
+      <c r="E13" s="255"/>
+      <c r="F13" s="255"/>
+      <c r="G13" s="255"/>
+      <c r="H13" s="255"/>
+      <c r="I13" s="255"/>
+      <c r="J13" s="255"/>
+      <c r="K13" s="255"/>
+      <c r="L13" s="255"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -19336,18 +19358,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="259" t="s">
+      <c r="C18" s="255" t="s">
         <v>200</v>
       </c>
-      <c r="D18" s="259"/>
-      <c r="E18" s="259"/>
-      <c r="F18" s="259"/>
-      <c r="G18" s="259"/>
-      <c r="H18" s="259"/>
-      <c r="I18" s="259"/>
-      <c r="J18" s="259"/>
-      <c r="K18" s="259"/>
-      <c r="L18" s="259"/>
+      <c r="D18" s="255"/>
+      <c r="E18" s="255"/>
+      <c r="F18" s="255"/>
+      <c r="G18" s="255"/>
+      <c r="H18" s="255"/>
+      <c r="I18" s="255"/>
+      <c r="J18" s="255"/>
+      <c r="K18" s="255"/>
+      <c r="L18" s="255"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19539,18 +19561,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="259" t="s">
+      <c r="C25" s="255" t="s">
         <v>203</v>
       </c>
-      <c r="D25" s="259"/>
-      <c r="E25" s="259"/>
-      <c r="F25" s="259"/>
-      <c r="G25" s="259"/>
-      <c r="H25" s="259"/>
-      <c r="I25" s="259"/>
-      <c r="J25" s="259"/>
-      <c r="K25" s="259"/>
-      <c r="L25" s="259"/>
+      <c r="D25" s="255"/>
+      <c r="E25" s="255"/>
+      <c r="F25" s="255"/>
+      <c r="G25" s="255"/>
+      <c r="H25" s="255"/>
+      <c r="I25" s="255"/>
+      <c r="J25" s="255"/>
+      <c r="K25" s="255"/>
+      <c r="L25" s="255"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -19644,7 +19666,7 @@
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B28" s="16" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C28" s="96">
         <f>C27+C20-C21+C22</f>
@@ -19688,22 +19710,22 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="259" t="s">
+      <c r="C31" s="255" t="s">
         <v>78</v>
       </c>
-      <c r="D31" s="259"/>
-      <c r="E31" s="259"/>
-      <c r="F31" s="259"/>
-      <c r="G31" s="259"/>
-      <c r="H31" s="259"/>
-      <c r="I31" s="259"/>
-      <c r="J31" s="259"/>
-      <c r="K31" s="259"/>
-      <c r="L31" s="259"/>
+      <c r="D31" s="255"/>
+      <c r="E31" s="255"/>
+      <c r="F31" s="255"/>
+      <c r="G31" s="255"/>
+      <c r="H31" s="255"/>
+      <c r="I31" s="255"/>
+      <c r="J31" s="255"/>
+      <c r="K31" s="255"/>
+      <c r="L31" s="255"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C32" s="12">
         <f>C5</f>
@@ -19770,23 +19792,23 @@
         <f>Statement!Q100</f>
         <v>0.83174673345867178</v>
       </c>
-      <c r="H33" s="241">
+      <c r="H33" s="239">
         <f>H8/H6</f>
         <v>0.84199999999999997</v>
       </c>
-      <c r="I33" s="241">
+      <c r="I33" s="239">
         <f t="shared" ref="I33:L33" si="9">I8/I6</f>
         <v>0.84199999999999997</v>
       </c>
-      <c r="J33" s="241">
+      <c r="J33" s="239">
         <f t="shared" si="9"/>
         <v>0.85799999999999998</v>
       </c>
-      <c r="K33" s="241">
+      <c r="K33" s="239">
         <f t="shared" si="9"/>
         <v>0.8580000000000001</v>
       </c>
-      <c r="L33" s="241">
+      <c r="L33" s="239">
         <f t="shared" si="9"/>
         <v>0.873</v>
       </c>
@@ -19815,39 +19837,39 @@
         <f>Statement!Q101</f>
         <v>3.5242137575966802E-2</v>
       </c>
-      <c r="H34" s="241">
+      <c r="H34" s="239">
         <f>H10/H6</f>
         <v>7.1999999999999925E-2</v>
       </c>
-      <c r="I34" s="241">
+      <c r="I34" s="239">
         <f t="shared" ref="I34:L34" si="10">I10/I6</f>
         <v>7.1999999999999911E-2</v>
       </c>
-      <c r="J34" s="241">
+      <c r="J34" s="239">
         <f t="shared" si="10"/>
         <v>0.123</v>
       </c>
-      <c r="K34" s="241">
+      <c r="K34" s="239">
         <f t="shared" si="10"/>
         <v>0.12800000000000003</v>
       </c>
-      <c r="L34" s="241">
+      <c r="L34" s="239">
         <f t="shared" si="10"/>
         <v>0.17300000000000001</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19879,7 +19901,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9236FE7C-2B1B-7C49-B055-001352253955}">
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="85" customWidth="1"/>
@@ -19910,16 +19932,16 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="248" t="s">
+      <c r="B4" s="246" t="s">
         <v>208</v>
       </c>
-      <c r="C4" s="248"/>
+      <c r="C4" s="246"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="C5" s="158">
+      <c r="C5" s="157">
         <f>Statement!AC77</f>
         <v>528156</v>
       </c>
@@ -19998,10 +20020,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="248" t="s">
+      <c r="B15" s="246" t="s">
         <v>215</v>
       </c>
-      <c r="C15" s="248"/>
+      <c r="C15" s="246"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -20046,14 +20068,6 @@
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
         <v>8.8766999999999999E-2</v>
-      </c>
-    </row>
-    <row r="21" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="C21" s="157">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -20098,60 +20112,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="248" t="s">
+      <c r="C3" s="246" t="s">
         <v>137</v>
       </c>
-      <c r="D3" s="248"/>
-      <c r="E3" s="248"/>
-      <c r="F3" s="248"/>
-      <c r="G3" s="257"/>
-      <c r="H3" s="258" t="s">
+      <c r="D3" s="246"/>
+      <c r="E3" s="246"/>
+      <c r="F3" s="246"/>
+      <c r="G3" s="258"/>
+      <c r="H3" s="259" t="s">
         <v>138</v>
       </c>
-      <c r="I3" s="248"/>
-      <c r="J3" s="248"/>
-      <c r="K3" s="248"/>
-      <c r="L3" s="248"/>
-      <c r="P3" s="262"/>
-      <c r="Q3" s="262"/>
-      <c r="R3" s="262"/>
-      <c r="S3" s="262"/>
-      <c r="T3" s="262"/>
-      <c r="U3" s="262"/>
-      <c r="V3" s="262"/>
-      <c r="W3" s="262"/>
-      <c r="X3" s="262"/>
-      <c r="Y3" s="262"/>
-      <c r="Z3" s="262"/>
+      <c r="I3" s="246"/>
+      <c r="J3" s="246"/>
+      <c r="K3" s="246"/>
+      <c r="L3" s="246"/>
+      <c r="P3" s="260"/>
+      <c r="Q3" s="260"/>
+      <c r="R3" s="260"/>
+      <c r="S3" s="260"/>
+      <c r="T3" s="260"/>
+      <c r="U3" s="260"/>
+      <c r="V3" s="260"/>
+      <c r="W3" s="260"/>
+      <c r="X3" s="260"/>
+      <c r="Y3" s="260"/>
+      <c r="Z3" s="260"/>
       <c r="AB3" s="130"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="88"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="259" t="s">
+      <c r="C5" s="255" t="s">
         <v>222</v>
       </c>
-      <c r="D5" s="259"/>
-      <c r="E5" s="259"/>
-      <c r="F5" s="259"/>
-      <c r="G5" s="259"/>
-      <c r="H5" s="259"/>
-      <c r="I5" s="259"/>
-      <c r="J5" s="259"/>
-      <c r="K5" s="259"/>
-      <c r="L5" s="259"/>
-      <c r="P5" s="262"/>
-      <c r="Q5" s="262"/>
-      <c r="R5" s="262"/>
-      <c r="S5" s="262"/>
-      <c r="T5" s="262"/>
-      <c r="U5" s="262"/>
-      <c r="V5" s="262"/>
-      <c r="W5" s="262"/>
-      <c r="X5" s="262"/>
-      <c r="Y5" s="262"/>
-      <c r="Z5" s="262"/>
+      <c r="D5" s="255"/>
+      <c r="E5" s="255"/>
+      <c r="F5" s="255"/>
+      <c r="G5" s="255"/>
+      <c r="H5" s="255"/>
+      <c r="I5" s="255"/>
+      <c r="J5" s="255"/>
+      <c r="K5" s="255"/>
+      <c r="L5" s="255"/>
+      <c r="P5" s="260"/>
+      <c r="Q5" s="260"/>
+      <c r="R5" s="260"/>
+      <c r="S5" s="260"/>
+      <c r="T5" s="260"/>
+      <c r="U5" s="260"/>
+      <c r="V5" s="260"/>
+      <c r="W5" s="260"/>
+      <c r="X5" s="260"/>
+      <c r="Y5" s="260"/>
+      <c r="Z5" s="260"/>
       <c r="AB5" s="131"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -20214,7 +20228,7 @@
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B7" s="39" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C7" s="133">
         <f>'FCF &amp; Other'!C28</f>
@@ -20325,37 +20339,37 @@
       <c r="B9" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="C9" s="159"/>
-      <c r="D9" s="159"/>
-      <c r="E9" s="159"/>
-      <c r="F9" s="159"/>
-      <c r="G9" s="160"/>
-      <c r="H9" s="161">
+      <c r="C9" s="158"/>
+      <c r="D9" s="158"/>
+      <c r="E9" s="158"/>
+      <c r="F9" s="158"/>
+      <c r="G9" s="159"/>
+      <c r="H9" s="160">
         <v>1</v>
       </c>
-      <c r="I9" s="161">
+      <c r="I9" s="160">
         <v>2</v>
       </c>
-      <c r="J9" s="161">
+      <c r="J9" s="160">
         <v>3</v>
       </c>
-      <c r="K9" s="161">
+      <c r="K9" s="160">
         <v>4</v>
       </c>
-      <c r="L9" s="161">
+      <c r="L9" s="160">
         <v>5</v>
       </c>
       <c r="N9" s="93"/>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B10" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="C10" s="159"/>
-      <c r="D10" s="159"/>
-      <c r="E10" s="159"/>
-      <c r="F10" s="159"/>
-      <c r="G10" s="160"/>
+        <v>374</v>
+      </c>
+      <c r="C10" s="158"/>
+      <c r="D10" s="158"/>
+      <c r="E10" s="158"/>
+      <c r="F10" s="158"/>
+      <c r="G10" s="159"/>
       <c r="H10" s="147">
         <f ca="1">H7/(1+$C$15)^H9</f>
         <v>3307.8624178504683</v>
@@ -20382,31 +20396,31 @@
       <c r="B11" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="C11" s="159"/>
-      <c r="D11" s="159"/>
-      <c r="E11" s="159"/>
-      <c r="F11" s="159"/>
-      <c r="G11" s="160"/>
-      <c r="H11" s="159"/>
-      <c r="I11" s="159"/>
-      <c r="J11" s="159"/>
-      <c r="K11" s="159"/>
+      <c r="C11" s="158"/>
+      <c r="D11" s="158"/>
+      <c r="E11" s="158"/>
+      <c r="F11" s="158"/>
+      <c r="G11" s="159"/>
+      <c r="H11" s="158"/>
+      <c r="I11" s="158"/>
+      <c r="J11" s="158"/>
+      <c r="K11" s="158"/>
       <c r="L11" s="147">
         <f ca="1">L8/(1+C15)^L9</f>
         <v>1930202.1633448438</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="248" t="s">
+      <c r="B13" s="246" t="s">
         <v>226</v>
       </c>
-      <c r="C13" s="248"/>
+      <c r="C13" s="246"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="C14" s="162">
+      <c r="C14" s="161">
         <v>0.02</v>
       </c>
     </row>
@@ -20415,15 +20429,15 @@
         <v>207</v>
       </c>
       <c r="C15" s="156">
-        <f ca="1">IF(WACC!C21&gt;0,WACC!C21,WACC!C20)</f>
+        <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
         <v>8.8766999999999999E-2</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="248" t="s">
+      <c r="B18" s="246" t="s">
         <v>228</v>
       </c>
-      <c r="C18" s="248"/>
+      <c r="C18" s="246"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -20456,7 +20470,7 @@
       <c r="B22" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="C22" s="24">
+      <c r="C22" s="90">
         <f>Statement!AC116</f>
         <v>1307244</v>
       </c>
@@ -20465,7 +20479,7 @@
       <c r="B23" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="C23" s="24">
+      <c r="C23" s="90">
         <f>Statement!AC117</f>
         <v>0</v>
       </c>
@@ -20483,16 +20497,16 @@
       <c r="B25" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C25" s="64">
+      <c r="C25" s="90">
         <f>Statement!AC77</f>
         <v>528156</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B26" s="163" t="s">
+      <c r="B26" s="162" t="s">
         <v>234</v>
       </c>
-      <c r="C26" s="164">
+      <c r="C26" s="163">
         <f ca="1">C24/C25</f>
         <v>6.6357378047186275</v>
       </c>
@@ -20515,7 +20529,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2D33819-10E3-B843-9B8A-30FFCAB234A7}">
-  <dimension ref="A1:N61"/>
+  <dimension ref="A1:N62"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="85" customWidth="1"/>
@@ -20537,37 +20551,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="248" t="s">
+      <c r="C2" s="246" t="s">
         <v>137</v>
       </c>
-      <c r="D2" s="248"/>
-      <c r="E2" s="248"/>
-      <c r="F2" s="248"/>
-      <c r="G2" s="257"/>
-      <c r="H2" s="258" t="s">
+      <c r="D2" s="246"/>
+      <c r="E2" s="246"/>
+      <c r="F2" s="246"/>
+      <c r="G2" s="258"/>
+      <c r="H2" s="259" t="s">
         <v>138</v>
       </c>
-      <c r="I2" s="248"/>
-      <c r="J2" s="248"/>
-      <c r="K2" s="248"/>
-      <c r="L2" s="248"/>
+      <c r="I2" s="246"/>
+      <c r="J2" s="246"/>
+      <c r="K2" s="246"/>
+      <c r="L2" s="246"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="259" t="s">
+      <c r="C4" s="255" t="s">
         <v>236</v>
       </c>
-      <c r="D4" s="259"/>
-      <c r="E4" s="259"/>
-      <c r="F4" s="259"/>
-      <c r="G4" s="259"/>
-      <c r="H4" s="259"/>
-      <c r="I4" s="259"/>
-      <c r="J4" s="259"/>
-      <c r="K4" s="259"/>
-      <c r="L4" s="259"/>
+      <c r="D4" s="255"/>
+      <c r="E4" s="255"/>
+      <c r="F4" s="255"/>
+      <c r="G4" s="255"/>
+      <c r="H4" s="255"/>
+      <c r="I4" s="255"/>
+      <c r="J4" s="255"/>
+      <c r="K4" s="255"/>
+      <c r="L4" s="255"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -20708,7 +20722,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B8" s="16" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C8" s="94">
         <f>'FCF &amp; Other'!C28</f>
@@ -20756,18 +20770,18 @@
       <c r="N9" s="93"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C10" s="259" t="s">
+      <c r="C10" s="255" t="s">
         <v>146</v>
       </c>
-      <c r="D10" s="259"/>
-      <c r="E10" s="259"/>
-      <c r="F10" s="259"/>
-      <c r="G10" s="259"/>
-      <c r="H10" s="259"/>
-      <c r="I10" s="259"/>
-      <c r="J10" s="259"/>
-      <c r="K10" s="259"/>
-      <c r="L10" s="259"/>
+      <c r="D10" s="255"/>
+      <c r="E10" s="255"/>
+      <c r="F10" s="255"/>
+      <c r="G10" s="255"/>
+      <c r="H10" s="255"/>
+      <c r="I10" s="255"/>
+      <c r="J10" s="255"/>
+      <c r="K10" s="255"/>
+      <c r="L10" s="255"/>
       <c r="N10" s="93"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -20820,7 +20834,7 @@
       <c r="B12" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="159"/>
+      <c r="C12" s="158"/>
       <c r="D12" s="97">
         <f>(D6-C6)/C6</f>
         <v>0.18641482451146088</v>
@@ -20863,7 +20877,7 @@
       <c r="B13" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="C13" s="159"/>
+      <c r="C13" s="158"/>
       <c r="D13" s="97">
         <f>IF(C7=0,
 IF(D7=0,0,IF(D7&gt;0,1,-1)),
@@ -20910,9 +20924,9 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="C14" s="159"/>
+        <v>312</v>
+      </c>
+      <c r="C14" s="158"/>
       <c r="D14" s="97">
         <f>IF(C8=0,
 IF(D8=0,0,IF(D8&gt;0,1,-1)),
@@ -20961,18 +20975,18 @@
       <c r="N15" s="93"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C16" s="259" t="s">
+      <c r="C16" s="255" t="s">
         <v>238</v>
       </c>
-      <c r="D16" s="259"/>
-      <c r="E16" s="259"/>
-      <c r="F16" s="259"/>
-      <c r="G16" s="259"/>
-      <c r="H16" s="259"/>
-      <c r="I16" s="259"/>
-      <c r="J16" s="259"/>
-      <c r="K16" s="259"/>
-      <c r="L16" s="259"/>
+      <c r="D16" s="255"/>
+      <c r="E16" s="255"/>
+      <c r="F16" s="255"/>
+      <c r="G16" s="255"/>
+      <c r="H16" s="255"/>
+      <c r="I16" s="255"/>
+      <c r="J16" s="255"/>
+      <c r="K16" s="255"/>
+      <c r="L16" s="255"/>
       <c r="N16" s="93"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
@@ -21042,23 +21056,23 @@
         <f>Statement!Q22</f>
         <v>544860</v>
       </c>
-      <c r="H18" s="165">
+      <c r="H18" s="164">
         <f>G18*(1+H19)</f>
         <v>528514.19999999995</v>
       </c>
-      <c r="I18" s="165">
+      <c r="I18" s="164">
         <f t="shared" ref="I18:L18" si="5">H18*(1+I19)</f>
         <v>512658.77399999992</v>
       </c>
-      <c r="J18" s="165">
+      <c r="J18" s="164">
         <f t="shared" si="5"/>
         <v>502405.59851999988</v>
       </c>
-      <c r="K18" s="165">
+      <c r="K18" s="164">
         <f t="shared" si="5"/>
         <v>492357.48654959985</v>
       </c>
-      <c r="L18" s="165">
+      <c r="L18" s="164">
         <f t="shared" si="5"/>
         <v>482510.33681860787</v>
       </c>
@@ -21068,24 +21082,24 @@
       <c r="B19" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="C19" s="159"/>
-      <c r="D19" s="166">
+      <c r="C19" s="158"/>
+      <c r="D19" s="165">
         <f>D18/C18-1</f>
         <v>0.20543744844652179</v>
       </c>
-      <c r="E19" s="166">
+      <c r="E19" s="165">
         <f t="shared" ref="E19:G19" si="6">E18/D18-1</f>
         <v>0.19311815948994759</v>
       </c>
-      <c r="F19" s="166">
+      <c r="F19" s="165">
         <f t="shared" si="6"/>
         <v>-0.14364346835307518</v>
       </c>
-      <c r="G19" s="167">
+      <c r="G19" s="166">
         <f t="shared" si="6"/>
         <v>-2.6919292129594097E-2</v>
       </c>
-      <c r="H19" s="168">
+      <c r="H19" s="167">
         <v>-0.03</v>
       </c>
       <c r="I19" s="99">
@@ -21106,18 +21120,18 @@
       <c r="N20" s="93"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C21" s="259" t="s">
+      <c r="C21" s="255" t="s">
         <v>241</v>
       </c>
-      <c r="D21" s="259"/>
-      <c r="E21" s="259"/>
-      <c r="F21" s="259"/>
-      <c r="G21" s="259"/>
-      <c r="H21" s="259"/>
-      <c r="I21" s="259"/>
-      <c r="J21" s="259"/>
-      <c r="K21" s="259"/>
-      <c r="L21" s="259"/>
+      <c r="D21" s="255"/>
+      <c r="E21" s="255"/>
+      <c r="F21" s="255"/>
+      <c r="G21" s="255"/>
+      <c r="H21" s="255"/>
+      <c r="I21" s="255"/>
+      <c r="J21" s="255"/>
+      <c r="K21" s="255"/>
+      <c r="L21" s="255"/>
       <c r="N21" s="93"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
@@ -21167,31 +21181,31 @@
       <c r="B23" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C23" s="169">
+      <c r="C23" s="168">
         <f>Statement!M125</f>
         <v>33.43</v>
       </c>
-      <c r="D23" s="169">
+      <c r="D23" s="168">
         <f>Statement!N125</f>
         <v>14.57</v>
       </c>
-      <c r="E23" s="169">
+      <c r="E23" s="168">
         <f>Statement!O125</f>
         <v>23.85</v>
       </c>
-      <c r="F23" s="169">
+      <c r="F23" s="168">
         <f>Statement!P125</f>
         <v>14.58</v>
       </c>
-      <c r="G23" s="170">
+      <c r="G23" s="169">
         <f>Statement!Q125</f>
         <v>12.59</v>
       </c>
-      <c r="H23" s="159"/>
-      <c r="I23" s="159"/>
-      <c r="J23" s="159"/>
-      <c r="K23" s="159"/>
-      <c r="L23" s="159"/>
+      <c r="H23" s="158"/>
+      <c r="I23" s="158"/>
+      <c r="J23" s="158"/>
+      <c r="K23" s="158"/>
+      <c r="L23" s="158"/>
       <c r="N23" s="93"/>
     </row>
     <row r="24" spans="2:14" x14ac:dyDescent="0.2">
@@ -21201,18 +21215,18 @@
       <c r="N25" s="93"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C26" s="259" t="s">
+      <c r="C26" s="255" t="s">
         <v>242</v>
       </c>
-      <c r="D26" s="259"/>
-      <c r="E26" s="259"/>
-      <c r="F26" s="259"/>
-      <c r="G26" s="259"/>
-      <c r="H26" s="259"/>
-      <c r="I26" s="259"/>
-      <c r="J26" s="259"/>
-      <c r="K26" s="259"/>
-      <c r="L26" s="259"/>
+      <c r="D26" s="255"/>
+      <c r="E26" s="255"/>
+      <c r="F26" s="255"/>
+      <c r="G26" s="255"/>
+      <c r="H26" s="255"/>
+      <c r="I26" s="255"/>
+      <c r="J26" s="255"/>
+      <c r="K26" s="255"/>
+      <c r="L26" s="255"/>
       <c r="N26" s="93"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
@@ -21262,62 +21276,62 @@
       <c r="B28" s="16" t="s">
         <v>243</v>
       </c>
-      <c r="C28" s="171">
+      <c r="C28" s="170">
         <f>C23/(C6/C18)</f>
         <v>17.03343197885799</v>
       </c>
-      <c r="D28" s="171">
+      <c r="D28" s="170">
         <f t="shared" ref="D28:G28" si="9">D23/(D6/D18)</f>
         <v>7.5428149003241138</v>
       </c>
-      <c r="E28" s="171">
+      <c r="E28" s="170">
         <f t="shared" si="9"/>
         <v>11.921699837623619</v>
       </c>
-      <c r="F28" s="171">
+      <c r="F28" s="170">
         <f t="shared" si="9"/>
         <v>5.7103089537122012</v>
       </c>
-      <c r="G28" s="172">
+      <c r="G28" s="171">
         <f t="shared" si="9"/>
         <v>4.2592243004348767</v>
       </c>
-      <c r="H28" s="159"/>
-      <c r="I28" s="159"/>
-      <c r="J28" s="159"/>
-      <c r="K28" s="159"/>
-      <c r="L28" s="159"/>
+      <c r="H28" s="158"/>
+      <c r="I28" s="158"/>
+      <c r="J28" s="158"/>
+      <c r="K28" s="158"/>
+      <c r="L28" s="158"/>
       <c r="N28" s="93"/>
     </row>
     <row r="29" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B29" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="C29" s="165">
+      <c r="C29" s="164">
         <f>C23*C18</f>
         <v>15198113.75</v>
       </c>
-      <c r="D29" s="165">
+      <c r="D29" s="164">
         <f t="shared" ref="D29:G29" si="10">D23*D18</f>
         <v>7984680.54</v>
       </c>
-      <c r="E29" s="165">
+      <c r="E29" s="164">
         <f t="shared" si="10"/>
         <v>15594441.75</v>
       </c>
-      <c r="F29" s="165">
+      <c r="F29" s="164">
         <f t="shared" si="10"/>
         <v>8163823.1399999997</v>
       </c>
-      <c r="G29" s="173">
+      <c r="G29" s="172">
         <f t="shared" si="10"/>
         <v>6859787.4000000004</v>
       </c>
-      <c r="H29" s="159"/>
-      <c r="I29" s="159"/>
-      <c r="J29" s="159"/>
-      <c r="K29" s="159"/>
-      <c r="L29" s="159"/>
+      <c r="H29" s="158"/>
+      <c r="I29" s="158"/>
+      <c r="J29" s="158"/>
+      <c r="K29" s="158"/>
+      <c r="L29" s="158"/>
       <c r="N29" s="93"/>
     </row>
     <row r="30" spans="2:14" x14ac:dyDescent="0.2">
@@ -21328,151 +21342,151 @@
         <f>Statement!M117</f>
         <v>0</v>
       </c>
-      <c r="D30" s="174">
+      <c r="D30" s="173">
         <f>Statement!N117</f>
         <v>0</v>
       </c>
-      <c r="E30" s="174">
+      <c r="E30" s="173">
         <f>Statement!O117</f>
         <v>0</v>
       </c>
-      <c r="F30" s="174">
+      <c r="F30" s="173">
         <f>Statement!P117</f>
         <v>0</v>
       </c>
-      <c r="G30" s="175">
+      <c r="G30" s="174">
         <f>Statement!Q117</f>
         <v>0</v>
       </c>
-      <c r="H30" s="159"/>
-      <c r="I30" s="159"/>
-      <c r="J30" s="159"/>
-      <c r="K30" s="159"/>
-      <c r="L30" s="159"/>
+      <c r="H30" s="158"/>
+      <c r="I30" s="158"/>
+      <c r="J30" s="158"/>
+      <c r="K30" s="158"/>
+      <c r="L30" s="158"/>
       <c r="N30" s="93"/>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B31" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="C31" s="174">
+      <c r="C31" s="173">
         <f>Statement!M116</f>
         <v>1865140</v>
       </c>
-      <c r="D31" s="174">
+      <c r="D31" s="173">
         <f>Statement!N116</f>
         <v>1756893</v>
       </c>
-      <c r="E31" s="174">
+      <c r="E31" s="173">
         <f>Statement!O116</f>
         <v>1879823</v>
       </c>
-      <c r="F31" s="174">
+      <c r="F31" s="173">
         <f>Statement!P116</f>
         <v>1629518</v>
       </c>
-      <c r="G31" s="175">
+      <c r="G31" s="174">
         <f>Statement!Q116</f>
         <v>1472486</v>
       </c>
-      <c r="H31" s="159"/>
-      <c r="I31" s="159"/>
-      <c r="J31" s="159"/>
-      <c r="K31" s="159"/>
-      <c r="L31" s="159"/>
+      <c r="H31" s="158"/>
+      <c r="I31" s="158"/>
+      <c r="J31" s="158"/>
+      <c r="K31" s="158"/>
+      <c r="L31" s="158"/>
       <c r="N31" s="93"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="C32" s="165">
+      <c r="C32" s="164">
         <f>C29+C30-C31</f>
         <v>13332973.75</v>
       </c>
-      <c r="D32" s="165">
+      <c r="D32" s="164">
         <f t="shared" ref="D32:G32" si="11">D29+D30-D31</f>
         <v>6227787.54</v>
       </c>
-      <c r="E32" s="165">
+      <c r="E32" s="164">
         <f t="shared" si="11"/>
         <v>13714618.75</v>
       </c>
-      <c r="F32" s="165">
+      <c r="F32" s="164">
         <f t="shared" si="11"/>
         <v>6534305.1399999997</v>
       </c>
-      <c r="G32" s="173">
+      <c r="G32" s="172">
         <f t="shared" si="11"/>
         <v>5387301.4000000004</v>
       </c>
-      <c r="H32" s="159"/>
-      <c r="I32" s="159"/>
-      <c r="J32" s="159"/>
-      <c r="K32" s="159"/>
-      <c r="L32" s="159"/>
+      <c r="H32" s="158"/>
+      <c r="I32" s="158"/>
+      <c r="J32" s="158"/>
+      <c r="K32" s="158"/>
+      <c r="L32" s="158"/>
       <c r="N32" s="93"/>
     </row>
     <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B33" s="16" t="s">
         <v>246</v>
       </c>
-      <c r="C33" s="171">
+      <c r="C33" s="170">
         <f>C32/C7</f>
         <v>-26.615590802202234</v>
       </c>
-      <c r="D33" s="171">
+      <c r="D33" s="170">
         <f t="shared" ref="D33:G33" si="12">D32/D7</f>
         <v>-17.88139972378784</v>
       </c>
-      <c r="E33" s="171">
+      <c r="E33" s="170">
         <f t="shared" si="12"/>
         <v>-83.260191537153958</v>
       </c>
-      <c r="F33" s="171">
+      <c r="F33" s="170">
         <f t="shared" si="12"/>
         <v>-40.194041545436093</v>
       </c>
-      <c r="G33" s="172">
+      <c r="G33" s="171">
         <f t="shared" si="12"/>
         <v>94.913696264975343</v>
       </c>
-      <c r="H33" s="159"/>
-      <c r="I33" s="159"/>
-      <c r="J33" s="159"/>
-      <c r="K33" s="159"/>
-      <c r="L33" s="159"/>
+      <c r="H33" s="158"/>
+      <c r="I33" s="158"/>
+      <c r="J33" s="158"/>
+      <c r="K33" s="158"/>
+      <c r="L33" s="158"/>
       <c r="N33" s="93"/>
     </row>
     <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
-        <v>377</v>
-      </c>
-      <c r="C34" s="171">
+        <v>375</v>
+      </c>
+      <c r="C34" s="170">
         <f>C32/C8</f>
         <v>-22.183836448582582</v>
       </c>
-      <c r="D34" s="171">
+      <c r="D34" s="170">
         <f t="shared" ref="D34:G34" si="13">D32/D8</f>
         <v>-12.454030780183258</v>
       </c>
-      <c r="E34" s="171">
+      <c r="E34" s="170">
         <f t="shared" si="13"/>
         <v>-63.37829204271857</v>
       </c>
-      <c r="F34" s="171">
+      <c r="F34" s="170">
         <f t="shared" si="13"/>
         <v>-32.342921616377602</v>
       </c>
-      <c r="G34" s="172">
+      <c r="G34" s="171">
         <f t="shared" si="13"/>
         <v>-56.992799864587525</v>
       </c>
-      <c r="H34" s="159"/>
-      <c r="I34" s="159"/>
-      <c r="J34" s="159"/>
-      <c r="K34" s="159"/>
-      <c r="L34" s="159"/>
+      <c r="H34" s="158"/>
+      <c r="I34" s="158"/>
+      <c r="J34" s="158"/>
+      <c r="K34" s="158"/>
+      <c r="L34" s="158"/>
       <c r="N34" s="93"/>
     </row>
     <row r="35" spans="2:14" x14ac:dyDescent="0.2">
@@ -21482,10 +21496,10 @@
       <c r="N36" s="93"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="248" t="s">
+      <c r="B37" s="246" t="s">
         <v>247</v>
       </c>
-      <c r="C37" s="248"/>
+      <c r="C37" s="246"/>
       <c r="N37" s="93"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -21502,7 +21516,7 @@
         <v>207</v>
       </c>
       <c r="C39" s="156">
-        <f ca="1">IF(WACC!C21&gt;0,WACC!C21,WACC!C20)</f>
+        <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
         <v>8.8766999999999999E-2</v>
       </c>
     </row>
@@ -21528,126 +21542,126 @@
         <v>245</v>
       </c>
       <c r="C42" s="24">
-        <f>(C38*C40)-G30+G31</f>
-        <v>11765415.416936001</v>
+        <f>(C38*C40)</f>
+        <v>10292929.416936001</v>
       </c>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B43" s="1" t="s">
-        <v>234</v>
+        <v>409</v>
       </c>
       <c r="C43" s="24">
-        <f>C42/C41</f>
-        <v>24.383758272434736</v>
+        <f ca="1">C42/(1+C39)^5-G30+G31</f>
+        <v>8200149.3121862812</v>
       </c>
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B44" s="163" t="s">
+      <c r="B44" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C44" s="90">
+        <f>Statement!AC77</f>
+        <v>528156</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B45" s="162" t="s">
         <v>251</v>
       </c>
-      <c r="C44" s="164">
-        <f ca="1">C43/(1+C48)^5</f>
-        <v>15.937709207716596</v>
-      </c>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B46" s="248" t="s">
+      <c r="C45" s="163">
+        <f ca="1">C43/C44</f>
+        <v>15.525998591677991</v>
+      </c>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B47" s="246" t="s">
         <v>252</v>
       </c>
-      <c r="C46" s="248"/>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B47" s="1" t="s">
+      <c r="C47" s="246"/>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B48" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="C47" s="64">
+      <c r="C48" s="64">
         <f>L6</f>
         <v>2379868.0732800001</v>
       </c>
     </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B48" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="C48" s="156">
-        <f ca="1">IF(WACC!C21&gt;0,WACC!C21,WACC!C20)</f>
-        <v>8.8766999999999999E-2</v>
-      </c>
-    </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="39" t="s">
+      <c r="B49" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="C49" s="156">
+        <f>Overview!C29</f>
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="50" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B50" s="39" t="s">
         <v>254</v>
       </c>
-      <c r="C49" s="114">
+      <c r="C50" s="114">
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B50" s="1" t="s">
+    <row r="51" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B51" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="C50" s="24">
+      <c r="C51" s="24">
         <f>L18</f>
         <v>482510.33681860787</v>
       </c>
     </row>
-    <row r="51" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B51" s="1" t="s">
+    <row r="52" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B52" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="C51" s="24">
-        <f>(C47*C49)/C50</f>
+      <c r="C52" s="24">
+        <f>(C48*C50)/C51</f>
         <v>24.661316988268727</v>
       </c>
     </row>
-    <row r="52" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B52" s="163" t="s">
+    <row r="53" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B53" s="162" t="s">
         <v>251</v>
       </c>
-      <c r="C52" s="164">
-        <f ca="1">C51/(1+C48)^5</f>
-        <v>16.119127102841901</v>
-      </c>
-    </row>
-    <row r="54" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B54" s="248" t="s">
-        <v>378</v>
-      </c>
-      <c r="C54" s="248"/>
+      <c r="C53" s="163">
+        <f>C52/(1+C49)^5</f>
+        <v>13.993493556532998</v>
+      </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B55" s="1" t="s">
+      <c r="B55" s="246" t="s">
+        <v>376</v>
+      </c>
+      <c r="C55" s="246"/>
+    </row>
+    <row r="56" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B56" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="C55" s="64">
+      <c r="C56" s="64">
         <f>L8</f>
         <v>199093.66914172584</v>
       </c>
     </row>
-    <row r="56" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B56" s="1" t="s">
+    <row r="57" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B57" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="C56" s="156">
-        <f ca="1">IF(WACC!C21&gt;0,WACC!C21,WACC!C20)</f>
+      <c r="C57" s="156">
+        <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
         <v>8.8766999999999999E-2</v>
       </c>
     </row>
-    <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="39" t="s">
-        <v>256</v>
-      </c>
-      <c r="C57" s="114">
+    <row r="58" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B58" s="39" t="s">
+        <v>410</v>
+      </c>
+      <c r="C58" s="114">
         <v>30</v>
-      </c>
-    </row>
-    <row r="58" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B58" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="C58" s="24">
-        <f>L18</f>
-        <v>482510.33681860787</v>
       </c>
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.2">
@@ -21655,34 +21669,43 @@
         <v>245</v>
       </c>
       <c r="C59" s="24">
-        <f>(C55*C57)-G30+G31</f>
-        <v>7445296.0742517756</v>
+        <f>(C56*C58)</f>
+        <v>5972810.0742517756</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B60" s="1" t="s">
-        <v>234</v>
+        <v>409</v>
       </c>
       <c r="C60" s="24">
-        <f>C59/C58</f>
-        <v>15.43033486772889</v>
+        <f ca="1">C59/(1+C57)^5-G30+G31</f>
+        <v>5376433.416668673</v>
       </c>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B61" s="163" t="s">
+      <c r="B61" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C61" s="90">
+        <f>Statement!AC77</f>
+        <v>528156</v>
+      </c>
+    </row>
+    <row r="62" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B62" s="162" t="s">
         <v>251</v>
       </c>
-      <c r="C61" s="164">
-        <f ca="1">C60/(1+C56)^5</f>
-        <v>10.085573657345705</v>
+      <c r="C62" s="163">
+        <f ca="1">C60/C61</f>
+        <v>10.179631428344415</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B55:C55"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
@@ -21716,7 +21739,7 @@
     <row r="1" spans="1:14" s="85" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4"/>
       <c r="B1" s="84" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
@@ -21726,15 +21749,15 @@
       <c r="N3" s="93"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="248" t="s">
-        <v>258</v>
-      </c>
-      <c r="C4" s="248"/>
+      <c r="B4" s="246" t="s">
+        <v>257</v>
+      </c>
+      <c r="C4" s="246"/>
       <c r="N4" s="93"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C5" s="154">
         <f ca="1">DCF!C26</f>
@@ -21743,43 +21766,43 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C6" s="154">
-        <f ca="1">Multiples!C44</f>
-        <v>15.937709207716596</v>
+        <f ca="1">Multiples!C45</f>
+        <v>15.525998591677991</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B7" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C7" s="154">
-        <f ca="1">Multiples!C52</f>
-        <v>16.119127102841901</v>
+        <f>Multiples!C53</f>
+        <v>13.993493556532998</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B8" s="1" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C8" s="154">
-        <f ca="1">Multiples!C61</f>
-        <v>10.085573657345705</v>
+        <f ca="1">Multiples!C62</f>
+        <v>10.179631428344415</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B9" s="163" t="s">
-        <v>262</v>
-      </c>
-      <c r="C9" s="164">
+      <c r="B9" s="162" t="s">
+        <v>261</v>
+      </c>
+      <c r="C9" s="163">
         <f ca="1">AVERAGE(C5:C8)</f>
-        <v>12.194536943155708</v>
+        <v>11.583715345318508</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B10" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C10" s="154">
         <f ca="1">Overview!C5</f>
@@ -21788,11 +21811,11 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B11" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="C11" s="176">
+        <v>263</v>
+      </c>
+      <c r="C11" s="175">
         <f ca="1">(C9-C10)/C10</f>
-        <v>8.4923215583247988E-2</v>
+        <v>3.0579657056806722E-2</v>
       </c>
     </row>
   </sheetData>
@@ -21848,7 +21871,7 @@
     <row r="1" spans="1:28" s="85" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4"/>
       <c r="B1" s="84" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" spans="1:28" s="85" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -21857,60 +21880,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="248" t="s">
+      <c r="C3" s="246" t="s">
         <v>137</v>
       </c>
-      <c r="D3" s="248"/>
-      <c r="E3" s="248"/>
-      <c r="F3" s="248"/>
-      <c r="G3" s="257"/>
-      <c r="H3" s="258" t="s">
+      <c r="D3" s="246"/>
+      <c r="E3" s="246"/>
+      <c r="F3" s="246"/>
+      <c r="G3" s="258"/>
+      <c r="H3" s="259" t="s">
         <v>138</v>
       </c>
-      <c r="I3" s="248"/>
-      <c r="J3" s="248"/>
-      <c r="K3" s="248"/>
-      <c r="L3" s="248"/>
-      <c r="P3" s="262"/>
-      <c r="Q3" s="262"/>
-      <c r="R3" s="262"/>
-      <c r="S3" s="262"/>
-      <c r="T3" s="262"/>
-      <c r="U3" s="262"/>
-      <c r="V3" s="262"/>
-      <c r="W3" s="262"/>
-      <c r="X3" s="262"/>
-      <c r="Y3" s="262"/>
-      <c r="Z3" s="262"/>
+      <c r="I3" s="246"/>
+      <c r="J3" s="246"/>
+      <c r="K3" s="246"/>
+      <c r="L3" s="246"/>
+      <c r="P3" s="260"/>
+      <c r="Q3" s="260"/>
+      <c r="R3" s="260"/>
+      <c r="S3" s="260"/>
+      <c r="T3" s="260"/>
+      <c r="U3" s="260"/>
+      <c r="V3" s="260"/>
+      <c r="W3" s="260"/>
+      <c r="X3" s="260"/>
+      <c r="Y3" s="260"/>
+      <c r="Z3" s="260"/>
       <c r="AB3" s="130"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="88"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="259" t="s">
+      <c r="C5" s="255" t="s">
         <v>222</v>
       </c>
-      <c r="D5" s="259"/>
-      <c r="E5" s="259"/>
-      <c r="F5" s="259"/>
-      <c r="G5" s="259"/>
-      <c r="H5" s="259"/>
-      <c r="I5" s="259"/>
-      <c r="J5" s="259"/>
-      <c r="K5" s="259"/>
-      <c r="L5" s="259"/>
-      <c r="P5" s="262"/>
-      <c r="Q5" s="262"/>
-      <c r="R5" s="262"/>
-      <c r="S5" s="262"/>
-      <c r="T5" s="262"/>
-      <c r="U5" s="262"/>
-      <c r="V5" s="262"/>
-      <c r="W5" s="262"/>
-      <c r="X5" s="262"/>
-      <c r="Y5" s="262"/>
-      <c r="Z5" s="262"/>
+      <c r="D5" s="255"/>
+      <c r="E5" s="255"/>
+      <c r="F5" s="255"/>
+      <c r="G5" s="255"/>
+      <c r="H5" s="255"/>
+      <c r="I5" s="255"/>
+      <c r="J5" s="255"/>
+      <c r="K5" s="255"/>
+      <c r="L5" s="255"/>
+      <c r="P5" s="260"/>
+      <c r="Q5" s="260"/>
+      <c r="R5" s="260"/>
+      <c r="S5" s="260"/>
+      <c r="T5" s="260"/>
+      <c r="U5" s="260"/>
+      <c r="V5" s="260"/>
+      <c r="W5" s="260"/>
+      <c r="X5" s="260"/>
+      <c r="Y5" s="260"/>
+      <c r="Z5" s="260"/>
       <c r="AB5" s="131"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -21973,7 +21996,7 @@
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B7" s="39" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C7" s="133">
         <f>'FCF &amp; Other'!C28</f>
@@ -22033,15 +22056,15 @@
       <c r="B8" s="39" t="s">
         <v>223</v>
       </c>
-      <c r="C8" s="159"/>
-      <c r="D8" s="159"/>
-      <c r="E8" s="159"/>
-      <c r="F8" s="159"/>
-      <c r="G8" s="160"/>
-      <c r="H8" s="159"/>
-      <c r="I8" s="159"/>
-      <c r="J8" s="159"/>
-      <c r="K8" s="159"/>
+      <c r="C8" s="158"/>
+      <c r="D8" s="158"/>
+      <c r="E8" s="158"/>
+      <c r="F8" s="158"/>
+      <c r="G8" s="159"/>
+      <c r="H8" s="158"/>
+      <c r="I8" s="158"/>
+      <c r="J8" s="158"/>
+      <c r="K8" s="158"/>
       <c r="L8" s="147">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
         <v>6115380.5051841736</v>
@@ -22065,37 +22088,37 @@
       <c r="B9" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="C9" s="159"/>
-      <c r="D9" s="159"/>
-      <c r="E9" s="159"/>
-      <c r="F9" s="159"/>
-      <c r="G9" s="160"/>
-      <c r="H9" s="161">
+      <c r="C9" s="158"/>
+      <c r="D9" s="158"/>
+      <c r="E9" s="158"/>
+      <c r="F9" s="158"/>
+      <c r="G9" s="159"/>
+      <c r="H9" s="160">
         <v>1</v>
       </c>
-      <c r="I9" s="161">
+      <c r="I9" s="160">
         <v>2</v>
       </c>
-      <c r="J9" s="161">
+      <c r="J9" s="160">
         <v>3</v>
       </c>
-      <c r="K9" s="161">
+      <c r="K9" s="160">
         <v>4</v>
       </c>
-      <c r="L9" s="161">
+      <c r="L9" s="160">
         <v>5</v>
       </c>
       <c r="N9" s="93"/>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B10" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="C10" s="159"/>
-      <c r="D10" s="159"/>
-      <c r="E10" s="159"/>
-      <c r="F10" s="159"/>
-      <c r="G10" s="160"/>
+        <v>374</v>
+      </c>
+      <c r="C10" s="158"/>
+      <c r="D10" s="158"/>
+      <c r="E10" s="158"/>
+      <c r="F10" s="158"/>
+      <c r="G10" s="159"/>
       <c r="H10" s="147">
         <f ca="1">H7/(1+$C$21)^H9</f>
         <v>16165.074804802129</v>
@@ -22122,15 +22145,15 @@
       <c r="B11" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="C11" s="159"/>
-      <c r="D11" s="159"/>
-      <c r="E11" s="159"/>
-      <c r="F11" s="159"/>
-      <c r="G11" s="160"/>
-      <c r="H11" s="159"/>
-      <c r="I11" s="159"/>
-      <c r="J11" s="159"/>
-      <c r="K11" s="159"/>
+      <c r="C11" s="158"/>
+      <c r="D11" s="158"/>
+      <c r="E11" s="158"/>
+      <c r="F11" s="158"/>
+      <c r="G11" s="159"/>
+      <c r="H11" s="158"/>
+      <c r="I11" s="158"/>
+      <c r="J11" s="158"/>
+      <c r="K11" s="158"/>
       <c r="L11" s="147">
         <f ca="1">L8/(1+C21)^L9</f>
         <v>3997134.2849287689</v>
@@ -22138,205 +22161,205 @@
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="263" t="s">
+      <c r="B14" s="261" t="s">
+        <v>265</v>
+      </c>
+      <c r="C14" s="262"/>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="B15" s="176" t="s">
         <v>266</v>
       </c>
-      <c r="C14" s="264"/>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B15" s="177" t="s">
-        <v>267</v>
-      </c>
-      <c r="C15" s="178">
+      <c r="C15" s="177">
         <f ca="1">Overview!C5</f>
         <v>11.24</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B16" s="177" t="s">
-        <v>268</v>
-      </c>
-      <c r="C16" s="178">
+      <c r="B16" s="176" t="s">
+        <v>267</v>
+      </c>
+      <c r="C16" s="177">
         <f ca="1">C36</f>
         <v>11.112445142901953</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="179" t="s">
-        <v>380</v>
-      </c>
-      <c r="C17" s="180">
+      <c r="B17" s="178" t="s">
+        <v>378</v>
+      </c>
+      <c r="C17" s="179">
         <v>1.2</v>
       </c>
-      <c r="E17" s="265" t="s">
-        <v>269</v>
-      </c>
-      <c r="F17" s="265"/>
-      <c r="G17" s="265"/>
-      <c r="H17" s="265"/>
-      <c r="I17" s="265"/>
+      <c r="E17" s="263" t="s">
+        <v>268</v>
+      </c>
+      <c r="F17" s="263"/>
+      <c r="G17" s="263"/>
+      <c r="H17" s="263"/>
+      <c r="I17" s="263"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="263" t="s">
+      <c r="B19" s="261" t="s">
         <v>226</v>
       </c>
-      <c r="C19" s="264"/>
+      <c r="C19" s="262"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B20" s="181" t="s">
+      <c r="B20" s="180" t="s">
         <v>227</v>
       </c>
-      <c r="C20" s="182">
+      <c r="C20" s="181">
         <v>0.02</v>
       </c>
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B21" s="181" t="s">
+      <c r="B21" s="180" t="s">
         <v>207</v>
       </c>
-      <c r="C21" s="183">
-        <f ca="1">IF(WACC!C21&gt;0,WACC!C21,WACC!C20)</f>
+      <c r="C21" s="264">
+        <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
         <v>8.8766999999999999E-2</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B22" s="181" t="s">
+      <c r="B22" s="180" t="s">
         <v>70</v>
       </c>
-      <c r="C22" s="184">
+      <c r="C22" s="265">
         <f>Statement!AC74</f>
         <v>523922</v>
       </c>
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B23" s="181" t="s">
-        <v>270</v>
-      </c>
-      <c r="C23" s="184">
+      <c r="B23" s="180" t="s">
+        <v>269</v>
+      </c>
+      <c r="C23" s="182">
         <f ca="1">C15*C22</f>
         <v>5888883.2800000003</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B24" s="181" t="s">
+      <c r="B24" s="180" t="s">
         <v>220</v>
       </c>
-      <c r="C24" s="184">
+      <c r="C24" s="265">
         <f>Statement!AC116</f>
         <v>1307244</v>
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="181" t="s">
+      <c r="B25" s="180" t="s">
         <v>211</v>
       </c>
-      <c r="C25" s="184">
+      <c r="C25" s="265">
         <f>Statement!AC117</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="179" t="s">
-        <v>271</v>
-      </c>
-      <c r="C26" s="185">
+      <c r="B26" s="178" t="s">
+        <v>270</v>
+      </c>
+      <c r="C26" s="183">
         <f ca="1">C23+C25-C24</f>
         <v>4581639.28</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="263" t="s">
+      <c r="B28" s="261" t="s">
         <v>228</v>
       </c>
-      <c r="C28" s="264"/>
+      <c r="C28" s="262"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B29" s="181" t="s">
+      <c r="B29" s="180" t="s">
         <v>229</v>
       </c>
-      <c r="C29" s="184">
+      <c r="C29" s="182">
         <f ca="1">SUM(H10:L10)</f>
         <v>517676.19923070847</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B30" s="181" t="s">
+      <c r="B30" s="180" t="s">
         <v>225</v>
       </c>
-      <c r="C30" s="184">
+      <c r="C30" s="182">
         <f ca="1">L11</f>
         <v>3997134.2849287689</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B31" s="186" t="s">
+      <c r="B31" s="184" t="s">
         <v>230</v>
       </c>
-      <c r="C31" s="187">
+      <c r="C31" s="185">
         <f ca="1">C29+C30</f>
         <v>4514810.4841594771</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B32" s="181" t="s">
+      <c r="B32" s="180" t="s">
         <v>231</v>
       </c>
-      <c r="C32" s="188">
+      <c r="C32" s="186">
         <f>C24</f>
         <v>1307244</v>
       </c>
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B33" s="181" t="s">
+      <c r="B33" s="180" t="s">
         <v>232</v>
       </c>
-      <c r="C33" s="188">
+      <c r="C33" s="186">
         <f>C25</f>
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B34" s="186" t="s">
+      <c r="B34" s="184" t="s">
         <v>233</v>
       </c>
-      <c r="C34" s="187">
+      <c r="C34" s="185">
         <f ca="1">C31+C32-C33</f>
         <v>5822054.4841594771</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B35" s="181" t="s">
+      <c r="B35" s="180" t="s">
         <v>70</v>
       </c>
-      <c r="C35" s="184">
+      <c r="C35" s="182">
         <f>C22</f>
         <v>523922</v>
       </c>
     </row>
     <row r="36" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="189" t="s">
+      <c r="B36" s="187" t="s">
         <v>234</v>
       </c>
-      <c r="C36" s="190">
+      <c r="C36" s="188">
         <f ca="1">C34/C35</f>
         <v>11.112445142901953</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C39" s="259" t="s">
-        <v>272</v>
-      </c>
-      <c r="D39" s="259"/>
-      <c r="E39" s="259"/>
-      <c r="F39" s="259"/>
-      <c r="G39" s="259"/>
-      <c r="H39" s="259"/>
-      <c r="I39" s="259"/>
-      <c r="J39" s="259"/>
-      <c r="K39" s="259"/>
-      <c r="L39" s="259"/>
+      <c r="C39" s="255" t="s">
+        <v>271</v>
+      </c>
+      <c r="D39" s="255"/>
+      <c r="E39" s="255"/>
+      <c r="F39" s="255"/>
+      <c r="G39" s="255"/>
+      <c r="H39" s="255"/>
+      <c r="I39" s="255"/>
+      <c r="J39" s="255"/>
+      <c r="K39" s="255"/>
+      <c r="L39" s="255"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="12">
@@ -22382,7 +22405,7 @@
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="39" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C41" s="133">
         <f>C7</f>
@@ -22404,23 +22427,23 @@
         <f t="shared" si="2"/>
         <v>8000</v>
       </c>
-      <c r="H41" s="165">
+      <c r="H41" s="164">
         <f t="shared" si="2"/>
         <v>17600</v>
       </c>
-      <c r="I41" s="165">
+      <c r="I41" s="164">
         <f t="shared" si="2"/>
         <v>38720</v>
       </c>
-      <c r="J41" s="165">
+      <c r="J41" s="164">
         <f t="shared" si="2"/>
         <v>85184</v>
       </c>
-      <c r="K41" s="165">
+      <c r="K41" s="164">
         <f t="shared" si="2"/>
         <v>187404.80000000002</v>
       </c>
-      <c r="L41" s="165">
+      <c r="L41" s="164">
         <f t="shared" si="2"/>
         <v>412290.56000000006</v>
       </c>
@@ -22449,30 +22472,30 @@
         <f>'FCF &amp; Other'!G10</f>
         <v>56760</v>
       </c>
-      <c r="H42" s="165">
+      <c r="H42" s="164">
         <f>H41/H43</f>
         <v>15999.999999999998</v>
       </c>
-      <c r="I42" s="165">
+      <c r="I42" s="164">
         <f t="shared" ref="I42:L42" si="3">I41/I43</f>
         <v>35200</v>
       </c>
-      <c r="J42" s="165">
+      <c r="J42" s="164">
         <f t="shared" si="3"/>
         <v>77440</v>
       </c>
-      <c r="K42" s="165">
+      <c r="K42" s="164">
         <f t="shared" si="3"/>
         <v>170368</v>
       </c>
-      <c r="L42" s="165">
+      <c r="L42" s="164">
         <f t="shared" si="3"/>
         <v>374809.60000000003</v>
       </c>
     </row>
     <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B43" s="143" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C43" s="97">
         <f>C41/C42</f>
@@ -22494,19 +22517,19 @@
         <f t="shared" si="4"/>
         <v>0.14094432699083861</v>
       </c>
-      <c r="H43" s="191">
+      <c r="H43" s="189">
         <v>1.1000000000000001</v>
       </c>
-      <c r="I43" s="191">
+      <c r="I43" s="189">
         <v>1.1000000000000001</v>
       </c>
-      <c r="J43" s="191">
+      <c r="J43" s="189">
         <v>1.1000000000000001</v>
       </c>
-      <c r="K43" s="191">
+      <c r="K43" s="189">
         <v>1.1000000000000001</v>
       </c>
-      <c r="L43" s="191">
+      <c r="L43" s="189">
         <v>1.1000000000000001</v>
       </c>
     </row>
@@ -22534,30 +22557,30 @@
         <f>Revenue!G9</f>
         <v>1610572</v>
       </c>
-      <c r="H44" s="165">
+      <c r="H44" s="164">
         <f>H41/H45</f>
         <v>1760000</v>
       </c>
-      <c r="I44" s="165">
+      <c r="I44" s="164">
         <f t="shared" ref="I44:L44" si="5">I41/I45</f>
         <v>1936000</v>
       </c>
-      <c r="J44" s="165">
+      <c r="J44" s="164">
         <f t="shared" si="5"/>
         <v>2028190.476190476</v>
       </c>
-      <c r="K44" s="165">
+      <c r="K44" s="164">
         <f t="shared" si="5"/>
         <v>2677211.4285714286</v>
       </c>
-      <c r="L44" s="165">
+      <c r="L44" s="164">
         <f t="shared" si="5"/>
         <v>2748603.7333333339</v>
       </c>
     </row>
     <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B45" s="143" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C45" s="97">
         <f>C41/C44</f>
@@ -22579,27 +22602,27 @@
         <f t="shared" si="6"/>
         <v>4.967179362363185E-3</v>
       </c>
-      <c r="H45" s="191">
+      <c r="H45" s="189">
         <v>0.01</v>
       </c>
-      <c r="I45" s="191">
+      <c r="I45" s="189">
         <v>0.02</v>
       </c>
-      <c r="J45" s="191">
+      <c r="J45" s="189">
         <v>4.2000000000000003E-2</v>
       </c>
-      <c r="K45" s="191">
+      <c r="K45" s="189">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="L45" s="191">
+      <c r="L45" s="189">
         <v>0.15</v>
       </c>
     </row>
     <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B46" s="143" t="s">
-        <v>383</v>
-      </c>
-      <c r="C46" s="159"/>
+        <v>381</v>
+      </c>
+      <c r="C46" s="158"/>
       <c r="D46" s="97">
         <f>D41/C41-1</f>
         <v>-0.16798053981385042</v>
@@ -22616,32 +22639,32 @@
         <f t="shared" si="7"/>
         <v>-1.0395976874950503</v>
       </c>
-      <c r="H46" s="192">
+      <c r="H46" s="190">
         <f t="shared" si="7"/>
         <v>1.2000000000000002</v>
       </c>
-      <c r="I46" s="192">
+      <c r="I46" s="190">
         <f t="shared" si="7"/>
         <v>1.2000000000000002</v>
       </c>
-      <c r="J46" s="192">
+      <c r="J46" s="190">
         <f t="shared" si="7"/>
         <v>1.2000000000000002</v>
       </c>
-      <c r="K46" s="192">
+      <c r="K46" s="190">
         <f t="shared" si="7"/>
         <v>1.2000000000000002</v>
       </c>
-      <c r="L46" s="192">
+      <c r="L46" s="190">
         <f t="shared" si="7"/>
         <v>1.2000000000000002</v>
       </c>
     </row>
     <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B47" s="143" t="s">
-        <v>273</v>
-      </c>
-      <c r="C47" s="159"/>
+        <v>272</v>
+      </c>
+      <c r="C47" s="158"/>
       <c r="D47" s="97">
         <f>D42/C42-1</f>
         <v>-0.30474941410850676</v>
@@ -22658,32 +22681,32 @@
         <f t="shared" si="7"/>
         <v>-1.3491440557547871</v>
       </c>
-      <c r="H47" s="192">
+      <c r="H47" s="190">
         <f t="shared" si="7"/>
         <v>-0.71811134601832283</v>
       </c>
-      <c r="I47" s="192">
+      <c r="I47" s="190">
         <f t="shared" si="7"/>
         <v>1.2000000000000002</v>
       </c>
-      <c r="J47" s="192">
+      <c r="J47" s="190">
         <f t="shared" si="7"/>
         <v>1.2000000000000002</v>
       </c>
-      <c r="K47" s="192">
+      <c r="K47" s="190">
         <f t="shared" si="7"/>
         <v>1.2000000000000002</v>
       </c>
-      <c r="L47" s="192">
+      <c r="L47" s="190">
         <f t="shared" si="7"/>
         <v>1.2000000000000002</v>
       </c>
     </row>
     <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B48" s="143" t="s">
-        <v>274</v>
-      </c>
-      <c r="C48" s="159"/>
+        <v>273</v>
+      </c>
+      <c r="C48" s="158"/>
       <c r="D48" s="97">
         <f>D44/C44-1</f>
         <v>0.18641482451146096</v>
@@ -22700,30 +22723,30 @@
         <f t="shared" si="8"/>
         <v>0.12653882310808684</v>
       </c>
-      <c r="H48" s="192">
+      <c r="H48" s="190">
         <f t="shared" si="8"/>
         <v>9.2779459719900759E-2</v>
       </c>
-      <c r="I48" s="192">
+      <c r="I48" s="190">
         <f t="shared" si="8"/>
         <v>0.10000000000000009</v>
       </c>
-      <c r="J48" s="192">
+      <c r="J48" s="190">
         <f t="shared" si="8"/>
         <v>4.761904761904745E-2</v>
       </c>
-      <c r="K48" s="192">
+      <c r="K48" s="190">
         <f t="shared" si="8"/>
         <v>0.32000000000000006</v>
       </c>
-      <c r="L48" s="192">
+      <c r="L48" s="190">
         <f t="shared" si="8"/>
         <v>2.6666666666666838E-2</v>
       </c>
     </row>
     <row r="49" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B49" s="143" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C49" s="97">
         <f>C42/C44</f>
@@ -22745,40 +22768,40 @@
         <f t="shared" si="9"/>
         <v>3.5242137575966802E-2</v>
       </c>
-      <c r="H49" s="192">
+      <c r="H49" s="190">
         <f t="shared" si="9"/>
         <v>9.0909090909090905E-3</v>
       </c>
-      <c r="I49" s="192">
+      <c r="I49" s="190">
         <f t="shared" si="9"/>
         <v>1.8181818181818181E-2</v>
       </c>
-      <c r="J49" s="192">
+      <c r="J49" s="190">
         <f t="shared" si="9"/>
         <v>3.8181818181818185E-2</v>
       </c>
-      <c r="K49" s="192">
+      <c r="K49" s="190">
         <f t="shared" si="9"/>
         <v>6.363636363636363E-2</v>
       </c>
-      <c r="L49" s="192">
+      <c r="L49" s="190">
         <f t="shared" si="9"/>
         <v>0.13636363636363635</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -22862,7 +22885,7 @@
         <v>86</v>
       </c>
       <c r="AA2" s="10" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="AB2" s="7"/>
       <c r="AD2" s="7"/>
@@ -22912,7 +22935,7 @@
         <v>91</v>
       </c>
       <c r="AA3" s="10" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="AB3" s="11"/>
       <c r="AC3" s="59" t="s">
@@ -23740,7 +23763,7 @@
     </row>
     <row r="17" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B17" s="23" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C17" s="21"/>
       <c r="D17" s="21"/>
@@ -25428,7 +25451,7 @@
     </row>
     <row r="44" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B44" s="20" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C44" s="21"/>
       <c r="D44" s="21"/>
@@ -25544,7 +25567,7 @@
     </row>
     <row r="46" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C46" s="21"/>
       <c r="D46" s="21"/>
@@ -25602,7 +25625,7 @@
     </row>
     <row r="47" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B47" s="20" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C47" s="21"/>
       <c r="D47" s="21"/>
@@ -26440,7 +26463,7 @@
     </row>
     <row r="63" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B63" s="20" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C63" s="62"/>
       <c r="D63" s="62"/>
@@ -26498,7 +26521,7 @@
     </row>
     <row r="64" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B64" s="20" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C64" s="62"/>
       <c r="D64" s="62"/>
@@ -27028,7 +27051,7 @@
         <f t="shared" ref="Z73:AA73" si="34">459231+64691</f>
         <v>523922</v>
       </c>
-      <c r="AA73" s="239">
+      <c r="AA73" s="237">
         <f t="shared" si="34"/>
         <v>523922</v>
       </c>
@@ -27110,7 +27133,7 @@
     </row>
     <row r="75" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B75" s="20" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C75" s="25"/>
       <c r="D75" s="25"/>
@@ -27168,7 +27191,7 @@
     </row>
     <row r="76" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B76" s="20" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C76" s="25"/>
       <c r="D76" s="25"/>
@@ -27239,7 +27262,7 @@
     </row>
     <row r="77" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B77" s="20" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C77" s="25"/>
       <c r="D77" s="25"/>
@@ -27310,7 +27333,7 @@
     </row>
     <row r="78" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B78" s="20" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C78" s="25"/>
       <c r="D78" s="25"/>
@@ -27357,7 +27380,7 @@
     </row>
     <row r="79" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B79" s="20" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C79" s="25"/>
       <c r="D79" s="25"/>
@@ -29445,7 +29468,7 @@
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B119" s="20" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C119" s="25"/>
       <c r="D119" s="25"/>
@@ -29516,7 +29539,7 @@
     </row>
     <row r="120" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B120" s="20" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C120" s="25"/>
       <c r="D120" s="25"/>
@@ -29587,7 +29610,7 @@
     </row>
     <row r="121" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B121" s="20" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C121" s="25"/>
       <c r="D121" s="25"/>
@@ -29725,7 +29748,7 @@
     </row>
     <row r="126" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B126" s="20" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C126" s="26"/>
       <c r="D126" s="26"/>
@@ -30276,36 +30299,36 @@
     </row>
     <row r="145" spans="2:29" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B145" s="14" t="s">
-        <v>277</v>
-      </c>
-      <c r="C145" s="194"/>
-      <c r="D145" s="194"/>
-      <c r="E145" s="194"/>
-      <c r="F145" s="194"/>
-      <c r="G145" s="194"/>
-      <c r="H145" s="194"/>
-      <c r="I145" s="194"/>
-      <c r="J145" s="194"/>
-      <c r="K145" s="194"/>
-      <c r="L145" s="194"/>
-      <c r="M145" s="194"/>
-      <c r="N145" s="194"/>
-      <c r="O145" s="194"/>
-      <c r="P145" s="194"/>
-      <c r="Q145" s="194"/>
-      <c r="T145" s="194"/>
-      <c r="U145" s="194"/>
-      <c r="V145" s="194"/>
-      <c r="W145" s="194"/>
-      <c r="X145" s="194"/>
-      <c r="Y145" s="194"/>
-      <c r="Z145" s="194"/>
-      <c r="AA145" s="194"/>
-      <c r="AC145" s="194"/>
+        <v>275</v>
+      </c>
+      <c r="C145" s="192"/>
+      <c r="D145" s="192"/>
+      <c r="E145" s="192"/>
+      <c r="F145" s="192"/>
+      <c r="G145" s="192"/>
+      <c r="H145" s="192"/>
+      <c r="I145" s="192"/>
+      <c r="J145" s="192"/>
+      <c r="K145" s="192"/>
+      <c r="L145" s="192"/>
+      <c r="M145" s="192"/>
+      <c r="N145" s="192"/>
+      <c r="O145" s="192"/>
+      <c r="P145" s="192"/>
+      <c r="Q145" s="192"/>
+      <c r="T145" s="192"/>
+      <c r="U145" s="192"/>
+      <c r="V145" s="192"/>
+      <c r="W145" s="192"/>
+      <c r="X145" s="192"/>
+      <c r="Y145" s="192"/>
+      <c r="Z145" s="192"/>
+      <c r="AA145" s="192"/>
+      <c r="AC145" s="192"/>
     </row>
     <row r="146" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B146" s="20" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C146" s="49"/>
       <c r="D146" s="49"/>
@@ -30350,7 +30373,7 @@
     </row>
     <row r="147" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B147" s="20" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C147" s="49"/>
       <c r="D147" s="49"/>
@@ -30395,7 +30418,7 @@
     </row>
     <row r="148" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B148" s="20" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C148" s="49"/>
       <c r="D148" s="49"/>
@@ -30465,35 +30488,35 @@
       <c r="O149" s="49"/>
       <c r="P149" s="49"/>
       <c r="Q149" s="49"/>
-      <c r="T149" s="195" t="str">
+      <c r="T149" s="193" t="str">
         <f t="shared" ref="T149:Z149" si="80">IF(T148&gt;T147, "BEAT", IF(T148&lt;T146, "MISSED", "MET"))</f>
         <v>BEAT</v>
       </c>
-      <c r="U149" s="195" t="str">
+      <c r="U149" s="193" t="str">
         <f t="shared" si="80"/>
         <v>MET</v>
       </c>
-      <c r="V149" s="195" t="str">
+      <c r="V149" s="193" t="str">
         <f t="shared" si="80"/>
         <v>BEAT</v>
       </c>
-      <c r="W149" s="195" t="str">
+      <c r="W149" s="193" t="str">
         <f t="shared" si="80"/>
         <v>BEAT</v>
       </c>
-      <c r="X149" s="195" t="str">
+      <c r="X149" s="193" t="str">
         <f t="shared" si="80"/>
         <v>BEAT</v>
       </c>
-      <c r="Y149" s="195" t="str">
+      <c r="Y149" s="193" t="str">
         <f t="shared" si="80"/>
         <v>BEAT</v>
       </c>
-      <c r="Z149" s="195" t="str">
+      <c r="Z149" s="193" t="str">
         <f t="shared" si="80"/>
         <v>BEAT</v>
       </c>
-      <c r="AA149" s="195" t="str">
+      <c r="AA149" s="193" t="str">
         <f>IF(AA148&gt;AA147, "BEAT", IF(AA148&lt;AA146, "MISSED", "MET"))</f>
         <v>MISSED</v>
       </c>
@@ -30501,7 +30524,7 @@
     </row>
     <row r="150" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B150" s="20" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C150" s="49"/>
       <c r="D150" s="49"/>
@@ -30546,7 +30569,7 @@
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B151" s="20" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C151" s="49"/>
       <c r="D151" s="49"/>
@@ -30591,7 +30614,7 @@
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B152" s="20" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C152" s="49"/>
       <c r="D152" s="49"/>
@@ -30661,35 +30684,35 @@
       <c r="O153" s="49"/>
       <c r="P153" s="49"/>
       <c r="Q153" s="49"/>
-      <c r="T153" s="195" t="str">
+      <c r="T153" s="193" t="str">
         <f t="shared" ref="T153:Z153" si="89">IF(T152&gt;T151, "BEAT", IF(T152&lt;T150, "MISSED", "MET"))</f>
         <v>BEAT</v>
       </c>
-      <c r="U153" s="195" t="str">
+      <c r="U153" s="193" t="str">
         <f t="shared" si="89"/>
         <v>MISSED</v>
       </c>
-      <c r="V153" s="195" t="str">
+      <c r="V153" s="193" t="str">
         <f t="shared" si="89"/>
         <v>BEAT</v>
       </c>
-      <c r="W153" s="195" t="str">
+      <c r="W153" s="193" t="str">
         <f t="shared" si="89"/>
         <v>BEAT</v>
       </c>
-      <c r="X153" s="195" t="str">
+      <c r="X153" s="193" t="str">
         <f t="shared" si="89"/>
         <v>BEAT</v>
       </c>
-      <c r="Y153" s="195" t="str">
+      <c r="Y153" s="193" t="str">
         <f t="shared" si="89"/>
         <v>BEAT</v>
       </c>
-      <c r="Z153" s="195" t="str">
+      <c r="Z153" s="193" t="str">
         <f t="shared" si="89"/>
         <v>BEAT</v>
       </c>
-      <c r="AA153" s="195" t="str">
+      <c r="AA153" s="193" t="str">
         <f>IF(AA152&gt;AA151, "BEAT", IF(AA152&lt;AA150, "MISSED", "MET"))</f>
         <v>MISSED</v>
       </c>
@@ -30700,32 +30723,32 @@
     </row>
     <row r="156" spans="2:29" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B156" s="14" t="s">
-        <v>300</v>
-      </c>
-      <c r="C156" s="194"/>
-      <c r="D156" s="194"/>
-      <c r="E156" s="194"/>
-      <c r="F156" s="194"/>
-      <c r="G156" s="194"/>
-      <c r="H156" s="194"/>
-      <c r="I156" s="194"/>
-      <c r="J156" s="194"/>
-      <c r="K156" s="194"/>
-      <c r="L156" s="194"/>
-      <c r="M156" s="194"/>
-      <c r="N156" s="194"/>
-      <c r="O156" s="194"/>
-      <c r="P156" s="194"/>
-      <c r="Q156" s="194"/>
-      <c r="T156" s="194"/>
-      <c r="U156" s="194"/>
-      <c r="V156" s="194"/>
-      <c r="W156" s="194"/>
-      <c r="X156" s="194"/>
-      <c r="Y156" s="194"/>
-      <c r="Z156" s="194"/>
-      <c r="AA156" s="194"/>
-      <c r="AC156" s="194"/>
+        <v>298</v>
+      </c>
+      <c r="C156" s="192"/>
+      <c r="D156" s="192"/>
+      <c r="E156" s="192"/>
+      <c r="F156" s="192"/>
+      <c r="G156" s="192"/>
+      <c r="H156" s="192"/>
+      <c r="I156" s="192"/>
+      <c r="J156" s="192"/>
+      <c r="K156" s="192"/>
+      <c r="L156" s="192"/>
+      <c r="M156" s="192"/>
+      <c r="N156" s="192"/>
+      <c r="O156" s="192"/>
+      <c r="P156" s="192"/>
+      <c r="Q156" s="192"/>
+      <c r="T156" s="192"/>
+      <c r="U156" s="192"/>
+      <c r="V156" s="192"/>
+      <c r="W156" s="192"/>
+      <c r="X156" s="192"/>
+      <c r="Y156" s="192"/>
+      <c r="Z156" s="192"/>
+      <c r="AA156" s="192"/>
+      <c r="AC156" s="192"/>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B157" s="20" t="s">
@@ -31020,7 +31043,7 @@
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B162" s="20" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="M162" s="139">
         <f>M117/M48</f>
@@ -31081,68 +31104,68 @@
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B163" s="20" t="s">
-        <v>307</v>
-      </c>
-      <c r="M163" s="203">
+        <v>305</v>
+      </c>
+      <c r="M163" s="201">
         <f>(M117-M116)/M48</f>
         <v>-0.97045814153264687</v>
       </c>
-      <c r="N163" s="203">
+      <c r="N163" s="201">
         <f>(N117-N116)/N48</f>
         <v>-0.91497314283512088</v>
       </c>
-      <c r="O163" s="203">
+      <c r="O163" s="201">
         <f>(O117-O116)/O48</f>
         <v>-0.93239915996813671</v>
       </c>
-      <c r="P163" s="203">
+      <c r="P163" s="201">
         <f>(P117-P116)/P48</f>
         <v>-0.88284296675302665</v>
       </c>
-      <c r="Q163" s="203">
+      <c r="Q163" s="201">
         <f>(Q117-Q116)/Q48</f>
         <v>-0.70704657236408375</v>
       </c>
-      <c r="T163" s="203">
+      <c r="T163" s="201">
         <f t="shared" ref="T163:AA163" si="104">(T117-T116)/T48</f>
         <v>-0.95080282790888426</v>
       </c>
-      <c r="U163" s="203">
+      <c r="U163" s="201">
         <f t="shared" si="104"/>
         <v>-0.90599389668243979</v>
       </c>
-      <c r="V163" s="203">
+      <c r="V163" s="201">
         <f t="shared" si="104"/>
         <v>-0.88284296675302665</v>
       </c>
-      <c r="W163" s="203">
+      <c r="W163" s="201">
         <f t="shared" si="104"/>
         <v>-0.91555413989488132</v>
       </c>
-      <c r="X163" s="203">
+      <c r="X163" s="201">
         <f t="shared" si="104"/>
         <v>-0.86899465270819587</v>
       </c>
-      <c r="Y163" s="203">
+      <c r="Y163" s="201">
         <f t="shared" si="104"/>
         <v>-0.72647492981720518</v>
       </c>
-      <c r="Z163" s="203">
+      <c r="Z163" s="201">
         <f t="shared" si="104"/>
         <v>-0.70704657236408375</v>
       </c>
-      <c r="AA163" s="203">
+      <c r="AA163" s="201">
         <f t="shared" si="104"/>
         <v>-0.68695115254353079</v>
       </c>
-      <c r="AC163" s="203">
+      <c r="AC163" s="201">
         <f>(AC117-AC116)/AC48</f>
         <v>-0.68695115254353079</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B164" s="20" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="M164" s="139">
         <f>(M116+M30)/M39</f>
@@ -31203,7 +31226,7 @@
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B165" s="20" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="M165" s="139">
         <f>M32/M39</f>
@@ -31264,68 +31287,68 @@
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B166" s="20" t="s">
-        <v>311</v>
-      </c>
-      <c r="M166" s="205" t="str">
+        <v>309</v>
+      </c>
+      <c r="M166" s="203" t="str">
         <f>IF(M13&gt;=0,"N/A",IF(M12&lt;=0,"N/A",M12/-M13))</f>
         <v>N/A</v>
       </c>
-      <c r="N166" s="205" t="str">
+      <c r="N166" s="203" t="str">
         <f>IF(N13&gt;=0,"N/A",IF(N12&lt;=0,"N/A",N12/-N13))</f>
         <v>N/A</v>
       </c>
-      <c r="O166" s="205" t="str">
+      <c r="O166" s="203" t="str">
         <f>IF(O13&gt;=0,"N/A",IF(O12&lt;=0,"N/A",O12/-O13))</f>
         <v>N/A</v>
       </c>
-      <c r="P166" s="205" t="str">
+      <c r="P166" s="203" t="str">
         <f>IF(P13&gt;=0,"N/A",IF(P12&lt;=0,"N/A",P12/-P13))</f>
         <v>N/A</v>
       </c>
-      <c r="Q166" s="205" t="str">
+      <c r="Q166" s="203" t="str">
         <f>IF(Q13&gt;=0,"N/A",IF(Q12&lt;=0,"N/A",Q12/-Q13))</f>
         <v>N/A</v>
       </c>
-      <c r="T166" s="205" t="str">
+      <c r="T166" s="203" t="str">
         <f t="shared" ref="T166:AA166" si="107">IF(T13&gt;=0,"N/A",IF(T12&lt;=0,"N/A",T12/-T13))</f>
         <v>N/A</v>
       </c>
-      <c r="U166" s="205" t="str">
+      <c r="U166" s="203" t="str">
         <f t="shared" si="107"/>
         <v>N/A</v>
       </c>
-      <c r="V166" s="205" t="str">
+      <c r="V166" s="203" t="str">
         <f t="shared" si="107"/>
         <v>N/A</v>
       </c>
-      <c r="W166" s="205" t="str">
+      <c r="W166" s="203" t="str">
         <f t="shared" si="107"/>
         <v>N/A</v>
       </c>
-      <c r="X166" s="205" t="str">
+      <c r="X166" s="203" t="str">
         <f t="shared" si="107"/>
         <v>N/A</v>
       </c>
-      <c r="Y166" s="205" t="str">
+      <c r="Y166" s="203" t="str">
         <f t="shared" si="107"/>
         <v>N/A</v>
       </c>
-      <c r="Z166" s="205" t="str">
+      <c r="Z166" s="203" t="str">
         <f t="shared" si="107"/>
         <v>N/A</v>
       </c>
-      <c r="AA166" s="205" t="str">
+      <c r="AA166" s="203" t="str">
         <f t="shared" si="107"/>
         <v>N/A</v>
       </c>
-      <c r="AC166" s="205" t="str">
+      <c r="AC166" s="203" t="str">
         <f>IF(AC13&gt;=0,"N/A",IF(AC12&lt;=0,"N/A",AC12/-AC13))</f>
         <v>N/A</v>
       </c>
     </row>
     <row r="167" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B167" s="20" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="M167" s="72">
         <f>M126/Statement!M26</f>
@@ -31399,7 +31422,7 @@
     </row>
     <row r="169" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B169" s="20" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="M169" s="72">
         <f>M126/(Statement!M48/Statement!M74)</f>
@@ -31436,25 +31459,25 @@
     </row>
     <row r="170" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B170" s="20" t="s">
-        <v>291</v>
-      </c>
-      <c r="M170" s="165">
+        <v>289</v>
+      </c>
+      <c r="M170" s="164">
         <f>Statement!M126*Statement!M77</f>
         <v>18122001.84</v>
       </c>
-      <c r="N170" s="165">
+      <c r="N170" s="164">
         <f>Statement!N126*Statement!N77</f>
         <v>8121653.1100000003</v>
       </c>
-      <c r="O170" s="165">
+      <c r="O170" s="164">
         <f>Statement!O126*Statement!O77</f>
         <v>13570960.050000001</v>
       </c>
-      <c r="P170" s="165">
+      <c r="P170" s="164">
         <f>Statement!P126*Statement!P77</f>
         <v>8040767.9400000004</v>
       </c>
-      <c r="Q170" s="165">
+      <c r="Q170" s="164">
         <f>Statement!Q126*Statement!Q77</f>
         <v>6680971.6299999999</v>
       </c>
@@ -31466,7 +31489,7 @@
       <c r="Y170" s="49"/>
       <c r="Z170" s="49"/>
       <c r="AA170" s="49"/>
-      <c r="AC170" s="165">
+      <c r="AC170" s="164">
         <f ca="1">Statement!AC126*Statement!AC77</f>
         <v>5936473.4400000004</v>
       </c>
@@ -31475,23 +31498,23 @@
       <c r="B171" s="20" t="s">
         <v>230</v>
       </c>
-      <c r="M171" s="165">
+      <c r="M171" s="164">
         <f>M170+M117-M116+M47+M44</f>
         <v>16256861.84</v>
       </c>
-      <c r="N171" s="165">
+      <c r="N171" s="164">
         <f>N170+N117-N116+N47+N44</f>
         <v>6364760.1100000003</v>
       </c>
-      <c r="O171" s="165">
+      <c r="O171" s="164">
         <f>O170+O117-O116+O47+O44</f>
         <v>11691137.050000001</v>
       </c>
-      <c r="P171" s="165">
+      <c r="P171" s="164">
         <f>P170+P117-P116+P47+P44</f>
         <v>6411249.9400000004</v>
       </c>
-      <c r="Q171" s="165">
+      <c r="Q171" s="164">
         <f>Q170+Q117-Q116+Q47+Q44</f>
         <v>5208485.63</v>
       </c>
@@ -31503,32 +31526,32 @@
       <c r="Y171" s="49"/>
       <c r="Z171" s="49"/>
       <c r="AA171" s="49"/>
-      <c r="AC171" s="165">
+      <c r="AC171" s="164">
         <f ca="1">AC170+AC117-AC116+AC47+AC44</f>
         <v>4629229.4400000004</v>
       </c>
     </row>
     <row r="172" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B172" s="20" t="s">
-        <v>312</v>
-      </c>
-      <c r="M172" s="207">
+        <v>310</v>
+      </c>
+      <c r="M172" s="205">
         <f>M171/M5</f>
         <v>18.220034071092023</v>
       </c>
-      <c r="N172" s="207">
+      <c r="N172" s="205">
         <f>N171/N5</f>
         <v>6.012539531693843</v>
       </c>
-      <c r="O172" s="207">
+      <c r="O172" s="205">
         <f>O171/O5</f>
         <v>8.9376861900568176</v>
       </c>
-      <c r="P172" s="207">
+      <c r="P172" s="205">
         <f>P171/P5</f>
         <v>4.4844452542695352</v>
       </c>
-      <c r="Q172" s="207">
+      <c r="Q172" s="205">
         <f>Q171/Q5</f>
         <v>3.2339352913126516</v>
       </c>
@@ -31540,7 +31563,7 @@
       <c r="Y172" s="49"/>
       <c r="Z172" s="49"/>
       <c r="AA172" s="49"/>
-      <c r="AC172" s="207">
+      <c r="AC172" s="205">
         <f ca="1">AC171/AC5</f>
         <v>2.7681315529829642</v>
       </c>
@@ -31549,23 +31572,23 @@
       <c r="B173" s="20" t="s">
         <v>246</v>
       </c>
-      <c r="M173" s="207">
+      <c r="M173" s="205">
         <f>M171/M12</f>
         <v>-32.452323883212962</v>
       </c>
-      <c r="N173" s="207">
+      <c r="N173" s="205">
         <f>N171/N12</f>
         <v>-18.274679240732393</v>
       </c>
-      <c r="O173" s="207">
+      <c r="O173" s="205">
         <f>O171/O12</f>
         <v>-70.97581987615348</v>
       </c>
-      <c r="P173" s="207">
+      <c r="P173" s="205">
         <f>P171/P12</f>
         <v>-39.437100185152154</v>
       </c>
-      <c r="Q173" s="207">
+      <c r="Q173" s="205">
         <f>Q171/Q12</f>
         <v>91.763312720225514</v>
       </c>
@@ -31577,14 +31600,14 @@
       <c r="Y173" s="49"/>
       <c r="Z173" s="49"/>
       <c r="AA173" s="49"/>
-      <c r="AC173" s="207">
+      <c r="AC173" s="205">
         <f ca="1">AC171/AC12</f>
         <v>45.761913818839652</v>
       </c>
     </row>
     <row r="174" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B174" s="20" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="M174" s="64">
         <f>M58-M53+M119+M64</f>
@@ -31645,7 +31668,7 @@
     </row>
     <row r="175" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B175" s="20" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="M175" s="64">
         <f t="shared" ref="M175:P175" si="109">M118+M52+M119+M54+M56+M57+M55</f>
@@ -31682,7 +31705,7 @@
     </row>
     <row r="176" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B176" s="20" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="M176" s="72">
         <f>M170/M174</f>
@@ -31719,7 +31742,7 @@
     </row>
     <row r="177" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B177" s="20" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="M177" s="72">
         <f>M171/M175</f>
@@ -31756,7 +31779,7 @@
     </row>
     <row r="178" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B178" s="20" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="M178" s="74">
         <f>M174/M170</f>
@@ -31793,7 +31816,7 @@
     </row>
     <row r="179" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B179" s="20" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="M179" s="74">
         <f>M26/M126</f>
@@ -31830,25 +31853,25 @@
     </row>
     <row r="180" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B180" s="20" t="s">
-        <v>319</v>
-      </c>
-      <c r="M180" s="176">
+        <v>317</v>
+      </c>
+      <c r="M180" s="175">
         <f>M81/M126</f>
         <v>0</v>
       </c>
-      <c r="N180" s="176">
+      <c r="N180" s="175">
         <f t="shared" ref="N180:Q180" si="117">N81/N126</f>
         <v>0</v>
       </c>
-      <c r="O180" s="176">
+      <c r="O180" s="175">
         <f t="shared" si="117"/>
         <v>0</v>
       </c>
-      <c r="P180" s="176">
+      <c r="P180" s="175">
         <f t="shared" si="117"/>
         <v>0</v>
       </c>
-      <c r="Q180" s="176">
+      <c r="Q180" s="175">
         <f t="shared" si="117"/>
         <v>0</v>
       </c>
@@ -31860,32 +31883,32 @@
       <c r="Y180" s="49"/>
       <c r="Z180" s="49"/>
       <c r="AA180" s="49"/>
-      <c r="AC180" s="176">
+      <c r="AC180" s="175">
         <f t="shared" ref="AC180" ca="1" si="118">AC81/AC126</f>
         <v>0</v>
       </c>
     </row>
     <row r="181" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B181" s="20" t="s">
-        <v>344</v>
-      </c>
-      <c r="M181" s="176">
+        <v>342</v>
+      </c>
+      <c r="M181" s="175">
         <f>-M62/M170</f>
         <v>0</v>
       </c>
-      <c r="N181" s="176">
+      <c r="N181" s="175">
         <f>-N62/N170</f>
         <v>0</v>
       </c>
-      <c r="O181" s="176">
+      <c r="O181" s="175">
         <f>-O62/O170</f>
         <v>7.5613663014209515E-3</v>
       </c>
-      <c r="P181" s="176">
+      <c r="P181" s="175">
         <f>-P62/P170</f>
         <v>4.8596228981581578E-2</v>
       </c>
-      <c r="Q181" s="176">
+      <c r="Q181" s="175">
         <f>-Q62/Q170</f>
         <v>4.9259451802222368E-2</v>
       </c>
@@ -31897,32 +31920,32 @@
       <c r="Y181" s="49"/>
       <c r="Z181" s="49"/>
       <c r="AA181" s="49"/>
-      <c r="AC181" s="176">
+      <c r="AC181" s="175">
         <f ca="1">-AC62/AC170</f>
         <v>5.8177974430556868E-2</v>
       </c>
     </row>
     <row r="182" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B182" s="20" t="s">
-        <v>346</v>
-      </c>
-      <c r="M182" s="176">
+        <v>344</v>
+      </c>
+      <c r="M182" s="175">
         <f>-(M62+M63)/M170</f>
         <v>0</v>
       </c>
-      <c r="N182" s="176">
+      <c r="N182" s="175">
         <f>-(N62+N63)/N170</f>
         <v>0</v>
       </c>
-      <c r="O182" s="176">
+      <c r="O182" s="175">
         <f>-(O62+O63)/O170</f>
         <v>7.5613663014209515E-3</v>
       </c>
-      <c r="P182" s="176">
+      <c r="P182" s="175">
         <f>-(P62+P63)/P170</f>
         <v>4.8596228981581578E-2</v>
       </c>
-      <c r="Q182" s="176">
+      <c r="Q182" s="175">
         <f>-(Q62+Q63)/Q170</f>
         <v>4.9259451802222368E-2</v>
       </c>
@@ -31934,32 +31957,32 @@
       <c r="Y182" s="49"/>
       <c r="Z182" s="49"/>
       <c r="AA182" s="49"/>
-      <c r="AC182" s="176">
+      <c r="AC182" s="175">
         <f ca="1">-(AC62+AC63)/AC170</f>
         <v>5.8177974430556868E-2</v>
       </c>
     </row>
     <row r="183" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B183" s="20" t="s">
-        <v>407</v>
-      </c>
-      <c r="M183" s="176">
+        <v>405</v>
+      </c>
+      <c r="M183" s="175">
         <f>M175/M5</f>
         <v>-0.67690742077350341</v>
       </c>
-      <c r="N183" s="176">
+      <c r="N183" s="175">
         <f>N175/N5</f>
         <v>-0.47238898109828159</v>
       </c>
-      <c r="O183" s="176">
+      <c r="O183" s="175">
         <f>O175/O5</f>
         <v>-0.16542896721281397</v>
       </c>
-      <c r="P183" s="176">
+      <c r="P183" s="175">
         <f>P175/P5</f>
         <v>-0.14131432280591805</v>
       </c>
-      <c r="Q183" s="176">
+      <c r="Q183" s="175">
         <f>Q175/Q5</f>
         <v>-5.8690949550842808E-2</v>
       </c>
@@ -31971,32 +31994,32 @@
       <c r="Y183" s="49"/>
       <c r="Z183" s="49"/>
       <c r="AA183" s="49"/>
-      <c r="AC183" s="176">
+      <c r="AC183" s="175">
         <f>AC175/AC5</f>
         <v>-3.2430800141120472E-2</v>
       </c>
     </row>
     <row r="184" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B184" s="20" t="s">
-        <v>408</v>
-      </c>
-      <c r="M184" s="176">
+        <v>406</v>
+      </c>
+      <c r="M184" s="175">
         <f>M174/M5</f>
         <v>-0.6527023755620609</v>
       </c>
-      <c r="N184" s="176">
+      <c r="N184" s="175">
         <f t="shared" ref="N184:Q184" si="119">N174/N5</f>
         <v>-0.3812991164587311</v>
       </c>
-      <c r="O184" s="176">
+      <c r="O184" s="175">
         <f t="shared" si="119"/>
         <v>-6.132307701716725E-2</v>
       </c>
-      <c r="P184" s="176">
+      <c r="P184" s="175">
         <f t="shared" si="119"/>
         <v>-3.6728210264789486E-2</v>
       </c>
-      <c r="Q184" s="176">
+      <c r="Q184" s="175">
         <f t="shared" si="119"/>
         <v>3.8175256989442262E-2</v>
       </c>
@@ -32008,32 +32031,32 @@
       <c r="Y184" s="49"/>
       <c r="Z184" s="49"/>
       <c r="AA184" s="49"/>
-      <c r="AC184" s="176">
+      <c r="AC184" s="175">
         <f t="shared" ref="AC184" si="120">AC174/AC5</f>
         <v>6.4346749744368631E-2</v>
       </c>
     </row>
     <row r="185" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B185" s="20" t="s">
-        <v>322</v>
-      </c>
-      <c r="M185" s="176">
+        <v>320</v>
+      </c>
+      <c r="M185" s="175">
         <f>-M63/M174</f>
         <v>0</v>
       </c>
-      <c r="N185" s="176">
+      <c r="N185" s="175">
         <f>-N63/N174</f>
         <v>0</v>
       </c>
-      <c r="O185" s="176">
+      <c r="O185" s="175">
         <f>-O63/O174</f>
         <v>0</v>
       </c>
-      <c r="P185" s="176">
+      <c r="P185" s="175">
         <f>-P63/P174</f>
         <v>0</v>
       </c>
-      <c r="Q185" s="176">
+      <c r="Q185" s="175">
         <f>-Q63/Q174</f>
         <v>0</v>
       </c>
@@ -32045,32 +32068,32 @@
       <c r="Y185" s="49"/>
       <c r="Z185" s="49"/>
       <c r="AA185" s="49"/>
-      <c r="AC185" s="176">
+      <c r="AC185" s="175">
         <f>-AC63/AC174</f>
         <v>0</v>
       </c>
     </row>
     <row r="186" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B186" s="20" t="s">
-        <v>324</v>
-      </c>
-      <c r="M186" s="176">
+        <v>322</v>
+      </c>
+      <c r="M186" s="175">
         <f>-M62/M174</f>
         <v>0</v>
       </c>
-      <c r="N186" s="176">
+      <c r="N186" s="175">
         <f>-N62/N174</f>
         <v>0</v>
       </c>
-      <c r="O186" s="176">
+      <c r="O186" s="175">
         <f>-O62/O174</f>
         <v>-1.2792495169232687</v>
       </c>
-      <c r="P186" s="176">
+      <c r="P186" s="175">
         <f>-P62/P174</f>
         <v>-7.44160048753547</v>
       </c>
-      <c r="Q186" s="176">
+      <c r="Q186" s="175">
         <f>-Q62/Q174</f>
         <v>5.3526283260685705</v>
       </c>
@@ -32082,32 +32105,32 @@
       <c r="Y186" s="49"/>
       <c r="Z186" s="49"/>
       <c r="AA186" s="49"/>
-      <c r="AC186" s="176">
+      <c r="AC186" s="175">
         <f>-AC62/AC174</f>
         <v>3.2095084983598028</v>
       </c>
     </row>
     <row r="187" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B187" s="20" t="s">
-        <v>335</v>
-      </c>
-      <c r="M187" s="176">
+        <v>333</v>
+      </c>
+      <c r="M187" s="175">
         <f>(-M63-M62)/M174</f>
         <v>0</v>
       </c>
-      <c r="N187" s="176">
+      <c r="N187" s="175">
         <f>(-N63-N62)/N174</f>
         <v>0</v>
       </c>
-      <c r="O187" s="176">
+      <c r="O187" s="175">
         <f>(-O63-O62)/O174</f>
         <v>-1.2792495169232687</v>
       </c>
-      <c r="P187" s="176">
+      <c r="P187" s="175">
         <f>(-P63-P62)/P174</f>
         <v>-7.44160048753547</v>
       </c>
-      <c r="Q187" s="176">
+      <c r="Q187" s="175">
         <f>(-Q63-Q62)/Q174</f>
         <v>5.3526283260685705</v>
       </c>
@@ -32119,32 +32142,32 @@
       <c r="Y187" s="49"/>
       <c r="Z187" s="49"/>
       <c r="AA187" s="49"/>
-      <c r="AC187" s="176">
+      <c r="AC187" s="175">
         <f>(-AC63-AC62)/AC174</f>
         <v>3.2095084983598028</v>
       </c>
     </row>
     <row r="188" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B188" s="20" t="s">
-        <v>329</v>
-      </c>
-      <c r="M188" s="176">
+        <v>327</v>
+      </c>
+      <c r="M188" s="175">
         <f>M79/M77</f>
         <v>0.32041292188722126</v>
       </c>
-      <c r="N188" s="176">
+      <c r="N188" s="175">
         <f>N79/N77</f>
         <v>0.31207180184527727</v>
       </c>
-      <c r="O188" s="176">
+      <c r="O188" s="175">
         <f>O79/O77</f>
         <v>0.22510733498180183</v>
       </c>
-      <c r="P188" s="176">
+      <c r="P188" s="175">
         <f>P79/P77</f>
         <v>0.22494029842627195</v>
       </c>
-      <c r="Q188" s="176">
+      <c r="Q188" s="175">
         <f>Q79/Q77</f>
         <v>0.22012147206199109</v>
       </c>
@@ -32156,14 +32179,14 @@
       <c r="Y188" s="49"/>
       <c r="Z188" s="49"/>
       <c r="AA188" s="49"/>
-      <c r="AC188" s="176">
+      <c r="AC188" s="175">
         <f>AC79/AC77</f>
         <v>0.22116382280992736</v>
       </c>
     </row>
     <row r="189" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B189" s="20" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="M189" s="72">
         <f>M116/M74</f>
@@ -32224,129 +32247,129 @@
     </row>
     <row r="190" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B190" s="20" t="s">
-        <v>332</v>
-      </c>
-      <c r="M190" s="176">
+        <v>330</v>
+      </c>
+      <c r="M190" s="175">
         <f>M53/M58</f>
         <v>-9.3805469133780903</v>
       </c>
-      <c r="N190" s="176">
+      <c r="N190" s="175">
         <f>N53/N58</f>
         <v>-37.054403366396151</v>
       </c>
-      <c r="O190" s="176">
+      <c r="O190" s="175">
         <f>O53/O58</f>
         <v>1.243655586093446</v>
       </c>
-      <c r="P190" s="176">
+      <c r="P190" s="175">
         <f>P53/P58</f>
         <v>1.1172492318250589</v>
       </c>
-      <c r="Q190" s="176">
+      <c r="Q190" s="175">
         <f>Q53/Q58</f>
         <v>0.78305424452059225</v>
       </c>
-      <c r="T190" s="176">
+      <c r="T190" s="175">
         <f t="shared" ref="T190:AA190" si="122">T53/T58</f>
         <v>2.0334871485250994</v>
       </c>
-      <c r="U190" s="176">
+      <c r="U190" s="175">
         <f t="shared" si="122"/>
         <v>3.1167794798717492</v>
       </c>
-      <c r="V190" s="176" t="e">
+      <c r="V190" s="175" t="e">
         <f t="shared" si="122"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W190" s="176">
+      <c r="W190" s="175">
         <f t="shared" si="122"/>
         <v>0.6416782911211576</v>
       </c>
-      <c r="X190" s="176">
+      <c r="X190" s="175">
         <f t="shared" si="122"/>
         <v>1.8757303965181427</v>
       </c>
-      <c r="Y190" s="176">
+      <c r="Y190" s="175">
         <f t="shared" si="122"/>
         <v>2.5282091188850764</v>
       </c>
-      <c r="Z190" s="176">
+      <c r="Z190" s="175">
         <f t="shared" si="122"/>
         <v>0.35555092460569898</v>
       </c>
-      <c r="AA190" s="176">
+      <c r="AA190" s="175">
         <f t="shared" si="122"/>
         <v>0.40408404584318719</v>
       </c>
-      <c r="AC190" s="176">
+      <c r="AC190" s="175">
         <f>AC53/AC58</f>
         <v>0.69669698594761198</v>
       </c>
     </row>
     <row r="191" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B191" s="20" t="s">
-        <v>333</v>
-      </c>
-      <c r="M191" s="176">
+        <v>331</v>
+      </c>
+      <c r="M191" s="175">
         <f>M53/M5</f>
         <v>0.57784459995606618</v>
       </c>
-      <c r="N191" s="176">
+      <c r="N191" s="175">
         <f>N53/N5</f>
         <v>0.3493733592422309</v>
       </c>
-      <c r="O191" s="176">
+      <c r="O191" s="175">
         <f>O53/O5</f>
         <v>0.28435361356255617</v>
       </c>
-      <c r="P191" s="176">
+      <c r="P191" s="175">
         <f>P53/P5</f>
         <v>0.25051410681111086</v>
       </c>
-      <c r="Q191" s="176">
+      <c r="Q191" s="175">
         <f>Q53/Q5</f>
         <v>0.18047997854178516</v>
       </c>
-      <c r="T191" s="176">
+      <c r="T191" s="175">
         <f t="shared" ref="T191:AA191" si="123">T53/T5</f>
         <v>0.29819479973312507</v>
       </c>
-      <c r="U191" s="176">
+      <c r="U191" s="175">
         <f t="shared" si="123"/>
         <v>0.24668619749445234</v>
       </c>
-      <c r="V191" s="176">
+      <c r="V191" s="175">
         <f t="shared" si="123"/>
         <v>0</v>
       </c>
-      <c r="W191" s="176">
+      <c r="W191" s="175">
         <f t="shared" si="123"/>
         <v>0.21412187626183318</v>
       </c>
-      <c r="X191" s="176">
+      <c r="X191" s="175">
         <f t="shared" si="123"/>
         <v>0.21564822186836519</v>
       </c>
-      <c r="Y191" s="176">
+      <c r="Y191" s="175">
         <f t="shared" si="123"/>
         <v>0.17385730930425455</v>
       </c>
-      <c r="Z191" s="176">
+      <c r="Z191" s="175">
         <f t="shared" si="123"/>
         <v>0.13476004298420102</v>
       </c>
-      <c r="AA191" s="176">
+      <c r="AA191" s="175">
         <f t="shared" si="123"/>
         <v>0.1274194396508454</v>
       </c>
-      <c r="AC191" s="176">
+      <c r="AC191" s="175">
         <f>AC53/AC5</f>
         <v>0.16003121393504871</v>
       </c>
     </row>
     <row r="192" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B192" s="20" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="M192" s="72">
         <f>(M116-M117)/M74</f>
@@ -32407,25 +32430,25 @@
     </row>
     <row r="193" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B193" s="20" t="s">
-        <v>343</v>
-      </c>
-      <c r="M193" s="176">
+        <v>341</v>
+      </c>
+      <c r="M193" s="175">
         <f>(M116-M117)/M170</f>
         <v>0.10292130066354745</v>
       </c>
-      <c r="N193" s="176">
+      <c r="N193" s="175">
         <f>(N116-N117)/N170</f>
         <v>0.21632209307693517</v>
       </c>
-      <c r="O193" s="176">
+      <c r="O193" s="175">
         <f>(O116-O117)/O170</f>
         <v>0.1385180556920142</v>
       </c>
-      <c r="P193" s="176">
+      <c r="P193" s="175">
         <f>(P116-P117)/P170</f>
         <v>0.20265701138988473</v>
       </c>
-      <c r="Q193" s="176">
+      <c r="Q193" s="175">
         <f>(Q116-Q117)/Q170</f>
         <v>0.22039997795949329</v>
       </c>
@@ -32437,190 +32460,190 @@
       <c r="Y193" s="49"/>
       <c r="Z193" s="49"/>
       <c r="AA193" s="49"/>
-      <c r="AC193" s="176">
+      <c r="AC193" s="175">
         <f ca="1">(AC116-AC117)/AC170</f>
         <v>0.22020548280259802</v>
       </c>
     </row>
     <row r="194" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B194" s="20" t="s">
-        <v>352</v>
-      </c>
-      <c r="M194" s="176">
+        <v>350</v>
+      </c>
+      <c r="M194" s="175">
         <f>-M119/M5</f>
         <v>1.325746537973577E-2</v>
       </c>
-      <c r="N194" s="176">
+      <c r="N194" s="175">
         <f>-N119/N5</f>
         <v>2.2497097529617479E-2</v>
       </c>
-      <c r="O194" s="176">
+      <c r="O194" s="175">
         <f>-O119/O5</f>
         <v>5.6128408833764501E-3</v>
       </c>
-      <c r="P194" s="176">
+      <c r="P194" s="175">
         <f>-P119/P5</f>
         <v>1.0438116928173332E-2</v>
       </c>
-      <c r="Q194" s="176">
+      <c r="Q194" s="175">
         <f>-Q119/Q5</f>
         <v>1.1826854061786744E-2</v>
       </c>
-      <c r="T194" s="176">
+      <c r="T194" s="175">
         <f t="shared" ref="T194:AA194" si="125">-T119/T5</f>
         <v>4.4837519327879894E-3</v>
       </c>
-      <c r="U194" s="176">
+      <c r="U194" s="175">
         <f t="shared" si="125"/>
         <v>1.3745830431435797E-2</v>
       </c>
-      <c r="V194" s="176">
+      <c r="V194" s="175">
         <f t="shared" si="125"/>
         <v>0</v>
       </c>
-      <c r="W194" s="176">
+      <c r="W194" s="175">
         <f t="shared" si="125"/>
         <v>3.5981874467225984E-2</v>
       </c>
-      <c r="X194" s="176">
+      <c r="X194" s="175">
         <f t="shared" si="125"/>
         <v>0</v>
       </c>
-      <c r="Y194" s="176">
+      <c r="Y194" s="175">
         <f t="shared" si="125"/>
         <v>7.6961808553852587E-3</v>
       </c>
-      <c r="Z194" s="176">
+      <c r="Z194" s="175">
         <f t="shared" si="125"/>
         <v>6.3437031679023587E-3</v>
       </c>
-      <c r="AA194" s="176">
+      <c r="AA194" s="175">
         <f t="shared" si="125"/>
         <v>6.415189946030183E-3</v>
       </c>
-      <c r="AC194" s="176">
+      <c r="AC194" s="175">
         <f>-AC119/AC5</f>
         <v>5.3219161289936798E-3</v>
       </c>
     </row>
     <row r="195" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B195" s="20" t="s">
-        <v>353</v>
-      </c>
-      <c r="M195" s="176">
+        <v>351</v>
+      </c>
+      <c r="M195" s="175">
         <f>-(M119/M58)</f>
         <v>-0.21521750996124667</v>
       </c>
-      <c r="N195" s="176">
+      <c r="N195" s="175">
         <f>-(N119/N58)</f>
         <v>-2.3860334635808034</v>
       </c>
-      <c r="O195" s="176">
+      <c r="O195" s="175">
         <f>-(O119/O58)</f>
         <v>2.4548451595214689E-2</v>
       </c>
-      <c r="P195" s="176">
+      <c r="P195" s="175">
         <f>-(P119/P58)</f>
         <v>4.6552181304883568E-2</v>
       </c>
-      <c r="Q195" s="176">
+      <c r="Q195" s="175">
         <f>-(Q119/Q58)</f>
         <v>5.1313549276955236E-2</v>
       </c>
-      <c r="T195" s="176">
+      <c r="T195" s="175">
         <f t="shared" ref="T195:AA195" si="126">-(T119/T58)</f>
         <v>3.0576160082801448E-2</v>
       </c>
-      <c r="U195" s="176">
+      <c r="U195" s="175">
         <f t="shared" si="126"/>
         <v>0.17367296045600286</v>
       </c>
-      <c r="V195" s="176" t="e">
+      <c r="V195" s="175" t="e">
         <f t="shared" si="126"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W195" s="176">
+      <c r="W195" s="175">
         <f t="shared" si="126"/>
         <v>0.10783012050217644</v>
       </c>
-      <c r="X195" s="176">
+      <c r="X195" s="175">
         <f t="shared" si="126"/>
         <v>0</v>
       </c>
-      <c r="Y195" s="176">
+      <c r="Y195" s="175">
         <f t="shared" si="126"/>
         <v>0.11191680520674896</v>
       </c>
-      <c r="Z195" s="176">
+      <c r="Z195" s="175">
         <f t="shared" si="126"/>
         <v>1.6737227718428501E-2</v>
       </c>
-      <c r="AA195" s="176">
+      <c r="AA195" s="175">
         <f t="shared" si="126"/>
         <v>2.0344430295312594E-2</v>
       </c>
-      <c r="AC195" s="176">
+      <c r="AC195" s="175">
         <f>-(AC119/AC58)</f>
         <v>2.3168998318295178E-2</v>
       </c>
     </row>
     <row r="196" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B196" s="20" t="s">
-        <v>354</v>
-      </c>
-      <c r="M196" s="176">
+        <v>352</v>
+      </c>
+      <c r="M196" s="175">
         <f>-M119/M52</f>
         <v>0.80442026521591292</v>
       </c>
-      <c r="N196" s="176">
+      <c r="N196" s="175">
         <f>-N119/N52</f>
         <v>1.2719649628798804</v>
       </c>
-      <c r="O196" s="176">
+      <c r="O196" s="175">
         <f>-O119/O52</f>
         <v>0.32491038633446917</v>
       </c>
-      <c r="P196" s="176">
+      <c r="P196" s="175">
         <f>-P119/P52</f>
         <v>0.86600510677808729</v>
       </c>
-      <c r="Q196" s="176">
+      <c r="Q196" s="175">
         <f>-Q119/Q52</f>
         <v>1.1225175319700631</v>
       </c>
-      <c r="T196" s="176">
+      <c r="T196" s="175">
         <f t="shared" ref="T196:AA196" si="127">-T119/T52</f>
         <v>0.30953940187731938</v>
       </c>
-      <c r="U196" s="176">
+      <c r="U196" s="175">
         <f t="shared" si="127"/>
         <v>1.0752095280105867</v>
       </c>
-      <c r="V196" s="176" t="e">
+      <c r="V196" s="175" t="e">
         <f t="shared" si="127"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W196" s="176">
+      <c r="W196" s="175">
         <f t="shared" si="127"/>
         <v>3.9446664617276359</v>
       </c>
-      <c r="X196" s="176">
+      <c r="X196" s="175">
         <f t="shared" si="127"/>
         <v>0</v>
       </c>
-      <c r="Y196" s="176">
+      <c r="Y196" s="175">
         <f t="shared" si="127"/>
         <v>0.7010857522712165</v>
       </c>
-      <c r="Z196" s="176">
+      <c r="Z196" s="175">
         <f t="shared" si="127"/>
         <v>0.61371405590187011</v>
       </c>
-      <c r="AA196" s="176">
+      <c r="AA196" s="175">
         <f t="shared" si="127"/>
         <v>0.35743774137701423</v>
       </c>
-      <c r="AC196" s="176">
+      <c r="AC196" s="175">
         <f>-AC119/AC52</f>
         <v>0.41931684334511188</v>
       </c>
@@ -32630,32 +32653,32 @@
     </row>
     <row r="199" spans="2:29" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B199" s="14" t="s">
-        <v>366</v>
-      </c>
-      <c r="C199" s="194"/>
-      <c r="D199" s="194"/>
-      <c r="E199" s="194"/>
-      <c r="F199" s="194"/>
-      <c r="G199" s="194"/>
-      <c r="H199" s="194"/>
-      <c r="I199" s="194"/>
-      <c r="J199" s="194"/>
-      <c r="K199" s="194"/>
-      <c r="L199" s="194"/>
-      <c r="M199" s="194"/>
-      <c r="N199" s="194"/>
-      <c r="O199" s="194"/>
-      <c r="P199" s="194"/>
-      <c r="Q199" s="194"/>
-      <c r="T199" s="194"/>
-      <c r="U199" s="194"/>
-      <c r="V199" s="194"/>
-      <c r="W199" s="194"/>
-      <c r="X199" s="194"/>
-      <c r="Y199" s="194"/>
-      <c r="Z199" s="194"/>
-      <c r="AA199" s="194"/>
-      <c r="AC199" s="194"/>
+        <v>364</v>
+      </c>
+      <c r="C199" s="192"/>
+      <c r="D199" s="192"/>
+      <c r="E199" s="192"/>
+      <c r="F199" s="192"/>
+      <c r="G199" s="192"/>
+      <c r="H199" s="192"/>
+      <c r="I199" s="192"/>
+      <c r="J199" s="192"/>
+      <c r="K199" s="192"/>
+      <c r="L199" s="192"/>
+      <c r="M199" s="192"/>
+      <c r="N199" s="192"/>
+      <c r="O199" s="192"/>
+      <c r="P199" s="192"/>
+      <c r="Q199" s="192"/>
+      <c r="T199" s="192"/>
+      <c r="U199" s="192"/>
+      <c r="V199" s="192"/>
+      <c r="W199" s="192"/>
+      <c r="X199" s="192"/>
+      <c r="Y199" s="192"/>
+      <c r="Z199" s="192"/>
+      <c r="AA199" s="192"/>
+      <c r="AC199" s="192"/>
     </row>
     <row r="200" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B200" s="20" t="s">
@@ -32882,36 +32905,36 @@
     </row>
     <row r="205" spans="2:29" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B205" s="14" t="s">
-        <v>367</v>
-      </c>
-      <c r="C205" s="194"/>
-      <c r="D205" s="194"/>
-      <c r="E205" s="194"/>
-      <c r="F205" s="194"/>
-      <c r="G205" s="194"/>
-      <c r="H205" s="194"/>
-      <c r="I205" s="194"/>
-      <c r="J205" s="194"/>
-      <c r="K205" s="194"/>
-      <c r="L205" s="194"/>
-      <c r="M205" s="194"/>
-      <c r="N205" s="194"/>
-      <c r="O205" s="194"/>
-      <c r="P205" s="194"/>
-      <c r="Q205" s="194"/>
-      <c r="T205" s="194"/>
-      <c r="U205" s="194"/>
-      <c r="V205" s="194"/>
-      <c r="W205" s="194"/>
-      <c r="X205" s="194"/>
-      <c r="Y205" s="194"/>
-      <c r="Z205" s="194"/>
-      <c r="AA205" s="194"/>
-      <c r="AC205" s="194"/>
+        <v>365</v>
+      </c>
+      <c r="C205" s="192"/>
+      <c r="D205" s="192"/>
+      <c r="E205" s="192"/>
+      <c r="F205" s="192"/>
+      <c r="G205" s="192"/>
+      <c r="H205" s="192"/>
+      <c r="I205" s="192"/>
+      <c r="J205" s="192"/>
+      <c r="K205" s="192"/>
+      <c r="L205" s="192"/>
+      <c r="M205" s="192"/>
+      <c r="N205" s="192"/>
+      <c r="O205" s="192"/>
+      <c r="P205" s="192"/>
+      <c r="Q205" s="192"/>
+      <c r="T205" s="192"/>
+      <c r="U205" s="192"/>
+      <c r="V205" s="192"/>
+      <c r="W205" s="192"/>
+      <c r="X205" s="192"/>
+      <c r="Y205" s="192"/>
+      <c r="Z205" s="192"/>
+      <c r="AA205" s="192"/>
+      <c r="AC205" s="192"/>
     </row>
     <row r="206" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B206" s="20" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C206" s="81"/>
       <c r="D206" s="81"/>
@@ -32983,7 +33006,7 @@
   <sheetData>
     <row r="13" spans="2:2" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
   </sheetData>
@@ -33006,52 +33029,52 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B1" s="84" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="248" t="s">
-        <v>285</v>
-      </c>
-      <c r="C4" s="248"/>
-      <c r="E4" s="248" t="s">
-        <v>292</v>
-      </c>
-      <c r="F4" s="248"/>
-      <c r="G4" s="248"/>
+      <c r="B4" s="246" t="s">
+        <v>283</v>
+      </c>
+      <c r="C4" s="246"/>
+      <c r="E4" s="246" t="s">
+        <v>290</v>
+      </c>
+      <c r="F4" s="246"/>
+      <c r="G4" s="246"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="196">
+      <c r="C5" s="194">
         <f ca="1">Overview!C5</f>
         <v>11.24</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="153" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="G5" s="153" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B6" s="20" t="s">
-        <v>291</v>
-      </c>
-      <c r="C6" s="197">
+        <v>289</v>
+      </c>
+      <c r="C6" s="195">
         <f ca="1">Statement!AC170</f>
         <v>5936473.4400000004</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="F6" s="202">
+      <c r="F6" s="200">
         <f>IF(Statement!M5&lt;=0,"N/A",_xlfn.RRI(4,Statement!M5,Statement!Q5))</f>
         <v>0.15910599918172563</v>
       </c>
-      <c r="G6" s="202" t="str">
+      <c r="G6" s="200" t="str">
         <f>IF(Statement!H5&lt;=0,"N/A",_xlfn.RRI(9,Statement!H5,Statement!Q5))</f>
         <v>N/A</v>
       </c>
@@ -33060,38 +33083,38 @@
       <c r="B7" s="20" t="s">
         <v>230</v>
       </c>
-      <c r="C7" s="197">
+      <c r="C7" s="195">
         <f ca="1">Statement!AC171</f>
         <v>4629229.4400000004</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="F7" s="202" t="str">
+      <c r="F7" s="200" t="str">
         <f>IF(OR(Statement!M18&lt;=0, Statement!Q18&lt;=0), "N/A", _xlfn.RRI(4, Statement!M18, Statement!Q18))</f>
         <v>N/A</v>
       </c>
-      <c r="G7" s="202" t="str">
+      <c r="G7" s="200" t="str">
         <f>IF(OR(Statement!H18&lt;=0, Statement!Q18&lt;=0), "N/A", _xlfn.RRI(9, Statement!H18, Statement!Q18))</f>
         <v>N/A</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="20" t="s">
-        <v>289</v>
-      </c>
-      <c r="C8" s="198">
+        <v>287</v>
+      </c>
+      <c r="C8" s="196">
         <f ca="1">Statement!AC167</f>
         <v>18.733333333333331</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>295</v>
-      </c>
-      <c r="F8" s="202" t="str">
+        <v>293</v>
+      </c>
+      <c r="F8" s="200" t="str">
         <f>IF(OR(Statement!M26&lt;=0, Statement!Q26&lt;=0), "N/A", _xlfn.RRI(4, Statement!M26, Statement!Q26))</f>
         <v>N/A</v>
       </c>
-      <c r="G8" s="202" t="str">
+      <c r="G8" s="200" t="str">
         <f>IF(OR(Statement!H26&lt;=0, Statement!Q26&lt;=0), "N/A", _xlfn.RRI(9, Statement!H26, Statement!Q26))</f>
         <v>N/A</v>
       </c>
@@ -33100,47 +33123,47 @@
       <c r="B9" s="20" t="s">
         <v>243</v>
       </c>
-      <c r="C9" s="198">
+      <c r="C9" s="196">
         <f ca="1">Statement!AC168</f>
         <v>3.6210005501306561</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>296</v>
-      </c>
-      <c r="F9" s="202" t="str">
+        <v>294</v>
+      </c>
+      <c r="F9" s="200" t="str">
         <f>IF(Statement!M81&lt;=0,"N/A",_xlfn.RRI(4,Statement!M81,Statement!Q81))</f>
         <v>N/A</v>
       </c>
-      <c r="G9" s="202" t="str">
+      <c r="G9" s="200" t="str">
         <f>IF(Statement!H81&lt;=0,"N/A",_xlfn.RRI(9,Statement!H81,Statement!Q81))</f>
         <v>N/A</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="20" t="s">
-        <v>290</v>
-      </c>
-      <c r="C10" s="198">
+        <v>288</v>
+      </c>
+      <c r="C10" s="196">
         <f ca="1">Statement!AC169</f>
         <v>3.0945830743077249</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="F10" s="202">
+      <c r="F10" s="200">
         <f>IF(Statement!M126&lt;=0,"N/A",_xlfn.RRI(4,Statement!M126,Statement!Q126))</f>
         <v>-0.21662025481427405</v>
       </c>
-      <c r="G10" s="202" t="str">
+      <c r="G10" s="200" t="str">
         <f>IF(Statement!H126&lt;=0,"N/A",_xlfn.RRI(9,Statement!H126,Statement!Q126))</f>
         <v>N/A</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B11" s="20" t="s">
-        <v>312</v>
-      </c>
-      <c r="C11" s="198">
+        <v>310</v>
+      </c>
+      <c r="C11" s="196">
         <f ca="1">Statement!AC172</f>
         <v>2.7681315529829642</v>
       </c>
@@ -33149,33 +33172,33 @@
       <c r="B12" s="20" t="s">
         <v>246</v>
       </c>
-      <c r="C12" s="198">
+      <c r="C12" s="196">
         <f ca="1">Statement!AC173</f>
         <v>45.761913818839652</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="248" t="s">
+      <c r="B15" s="246" t="s">
         <v>78</v>
       </c>
-      <c r="C15" s="248"/>
-      <c r="E15" s="248" t="s">
-        <v>298</v>
-      </c>
-      <c r="F15" s="248"/>
+      <c r="C15" s="246"/>
+      <c r="E15" s="246" t="s">
+        <v>296</v>
+      </c>
+      <c r="F15" s="246"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="C16" s="199">
+      <c r="C16" s="197">
         <f>Statement!AC100</f>
         <v>0.83014417010996633</v>
       </c>
       <c r="E16" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="F16" s="197">
+      <c r="F16" s="195">
         <f>Statement!AC18</f>
         <v>327410</v>
       </c>
@@ -33184,14 +33207,14 @@
       <c r="B17" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="C17" s="199">
+      <c r="C17" s="197">
         <f>Statement!AC101</f>
         <v>6.0489855471109168E-2</v>
       </c>
       <c r="E17" s="20" t="s">
-        <v>299</v>
-      </c>
-      <c r="F17" s="197">
+        <v>297</v>
+      </c>
+      <c r="F17" s="195">
         <f>Statement!AC58</f>
         <v>384134</v>
       </c>
@@ -33200,40 +33223,40 @@
       <c r="B18" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="C18" s="199">
+      <c r="C18" s="197">
         <f>Statement!AC102</f>
         <v>0.19578073705548546</v>
       </c>
       <c r="E18" s="20" t="s">
-        <v>306</v>
-      </c>
-      <c r="F18" s="201">
+        <v>304</v>
+      </c>
+      <c r="F18" s="199">
         <f>IF(OR(F16&lt;=0, F17&lt;=0),"N/A",F16-F17)</f>
         <v>-56724</v>
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="248" t="s">
-        <v>297</v>
-      </c>
-      <c r="C21" s="248"/>
-      <c r="E21" s="248" t="s">
-        <v>301</v>
-      </c>
-      <c r="F21" s="248"/>
+      <c r="B21" s="246" t="s">
+        <v>295</v>
+      </c>
+      <c r="C21" s="246"/>
+      <c r="E21" s="246" t="s">
+        <v>299</v>
+      </c>
+      <c r="F21" s="246"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
         <v>119</v>
       </c>
-      <c r="C22" s="199">
+      <c r="C22" s="197">
         <f>Statement!AC130</f>
         <v>0.19578073705548546</v>
       </c>
       <c r="E22" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="F22" s="199">
+      <c r="F22" s="197">
         <f>C24</f>
         <v>0.1127173202051847</v>
       </c>
@@ -33242,14 +33265,14 @@
       <c r="B23" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="C23" s="198">
+      <c r="C23" s="196">
         <f>Statement!AC131</f>
         <v>0.57573243364202842</v>
       </c>
       <c r="E23" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="F23" s="199">
+      <c r="F23" s="197">
         <f>C26</f>
         <v>0.17205256008386913</v>
       </c>
@@ -33258,14 +33281,14 @@
       <c r="B24" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="C24" s="200">
+      <c r="C24" s="198">
         <f>Statement!AC132</f>
         <v>0.1127173202051847</v>
       </c>
       <c r="E24" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="F24" s="199">
+      <c r="F24" s="197">
         <f>Statement!AC157</f>
         <v>0.16980935706480046</v>
       </c>
@@ -33274,7 +33297,7 @@
       <c r="B25" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="C25" s="198">
+      <c r="C25" s="196">
         <f>Statement!AC133</f>
         <v>1.5264074746513994</v>
       </c>
@@ -33283,33 +33306,33 @@
       <c r="B26" s="32" t="s">
         <v>123</v>
       </c>
-      <c r="C26" s="200">
+      <c r="C26" s="198">
         <f>Statement!AC134</f>
         <v>0.17205256008386913</v>
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="248" t="s">
-        <v>302</v>
-      </c>
-      <c r="C29" s="248"/>
-      <c r="E29" s="248" t="s">
-        <v>308</v>
-      </c>
-      <c r="F29" s="248"/>
+      <c r="B29" s="246" t="s">
+        <v>300</v>
+      </c>
+      <c r="C29" s="246"/>
+      <c r="E29" s="246" t="s">
+        <v>306</v>
+      </c>
+      <c r="F29" s="246"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
         <v>180</v>
       </c>
-      <c r="C30" s="198">
+      <c r="C30" s="196">
         <f>Statement!AC158</f>
         <v>65.477289171395597</v>
       </c>
       <c r="E30" s="20" t="s">
-        <v>309</v>
-      </c>
-      <c r="F30" s="204">
+        <v>307</v>
+      </c>
+      <c r="F30" s="202">
         <f>Statement!AC162</f>
         <v>0</v>
       </c>
@@ -33318,14 +33341,14 @@
       <c r="B31" s="20" t="s">
         <v>181</v>
       </c>
-      <c r="C31" s="198">
+      <c r="C31" s="196">
         <f>Statement!AC159</f>
         <v>0</v>
       </c>
       <c r="E31" s="20" t="s">
-        <v>310</v>
-      </c>
-      <c r="F31" s="204">
+        <v>308</v>
+      </c>
+      <c r="F31" s="202">
         <f>Statement!AC163</f>
         <v>-0.68695115254353079</v>
       </c>
@@ -33334,14 +33357,14 @@
       <c r="B32" s="20" t="s">
         <v>182</v>
       </c>
-      <c r="C32" s="198">
+      <c r="C32" s="196">
         <f>Statement!AC160</f>
         <v>25.312474696801676</v>
       </c>
       <c r="E32" s="20" t="s">
-        <v>305</v>
-      </c>
-      <c r="F32" s="204">
+        <v>303</v>
+      </c>
+      <c r="F32" s="202">
         <f>Statement!AC165</f>
         <v>2.3066495444084523</v>
       </c>
@@ -33350,194 +33373,194 @@
       <c r="B33" s="20" t="s">
         <v>183</v>
       </c>
-      <c r="C33" s="198">
+      <c r="C33" s="196">
         <f>Statement!AC161</f>
         <v>40.164814474593925</v>
       </c>
       <c r="E33" s="20" t="s">
-        <v>304</v>
-      </c>
-      <c r="F33" s="204">
+        <v>302</v>
+      </c>
+      <c r="F33" s="202">
         <f>Statement!AC164</f>
         <v>1.9325582625717537</v>
       </c>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.2">
       <c r="E34" s="20" t="s">
-        <v>311</v>
-      </c>
-      <c r="F34" s="206" t="str">
+        <v>309</v>
+      </c>
+      <c r="F34" s="204" t="str">
         <f>Statement!AC166</f>
         <v>N/A</v>
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="248" t="s">
-        <v>320</v>
-      </c>
-      <c r="C37" s="248"/>
-      <c r="E37" s="248" t="s">
-        <v>323</v>
-      </c>
-      <c r="F37" s="248"/>
+      <c r="B37" s="246" t="s">
+        <v>318</v>
+      </c>
+      <c r="C37" s="246"/>
+      <c r="E37" s="246" t="s">
+        <v>321</v>
+      </c>
+      <c r="F37" s="246"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
-        <v>318</v>
-      </c>
-      <c r="C38" s="199">
+        <v>316</v>
+      </c>
+      <c r="C38" s="197">
         <f ca="1">Statement!AC179</f>
         <v>5.3380782918149475E-2</v>
       </c>
       <c r="E38" s="20" t="s">
-        <v>322</v>
-      </c>
-      <c r="F38" s="199">
+        <v>320</v>
+      </c>
+      <c r="F38" s="197">
         <f>Statement!AC185</f>
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B39" s="54" t="s">
-        <v>321</v>
-      </c>
-      <c r="C39" s="240">
+        <v>319</v>
+      </c>
+      <c r="C39" s="238">
         <f ca="1">Statement!AC178</f>
         <v>1.8126755065546118E-2</v>
       </c>
       <c r="E39" s="20" t="s">
-        <v>324</v>
-      </c>
-      <c r="F39" s="199">
+        <v>322</v>
+      </c>
+      <c r="F39" s="197">
         <f>Statement!AC186</f>
         <v>3.2095084983598028</v>
       </c>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B40" s="20" t="s">
-        <v>319</v>
-      </c>
-      <c r="C40" s="199">
+        <v>317</v>
+      </c>
+      <c r="C40" s="197">
         <f ca="1">Statement!AC180</f>
         <v>0</v>
       </c>
       <c r="E40" s="20" t="s">
-        <v>325</v>
-      </c>
-      <c r="F40" s="199">
+        <v>323</v>
+      </c>
+      <c r="F40" s="197">
         <f>Statement!AC187</f>
         <v>3.2095084983598028</v>
       </c>
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B41" s="20" t="s">
-        <v>344</v>
-      </c>
-      <c r="C41" s="199">
+        <v>342</v>
+      </c>
+      <c r="C41" s="197">
         <f ca="1">Statement!AC181</f>
         <v>5.8177974430556868E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B42" s="20" t="s">
-        <v>346</v>
-      </c>
-      <c r="C42" s="199">
+        <v>344</v>
+      </c>
+      <c r="C42" s="197">
         <f ca="1">Statement!AC182</f>
         <v>5.8177974430556868E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="248" t="s">
-        <v>331</v>
-      </c>
-      <c r="C45" s="248"/>
-      <c r="E45" s="248" t="s">
-        <v>337</v>
-      </c>
-      <c r="F45" s="248"/>
+      <c r="B45" s="246" t="s">
+        <v>329</v>
+      </c>
+      <c r="C45" s="246"/>
+      <c r="E45" s="246" t="s">
+        <v>335</v>
+      </c>
+      <c r="F45" s="246"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
-        <v>329</v>
-      </c>
-      <c r="C46" s="199">
+        <v>327</v>
+      </c>
+      <c r="C46" s="197">
         <f>Statement!AC188</f>
         <v>0.22116382280992736</v>
       </c>
       <c r="E46" s="20" t="s">
-        <v>330</v>
-      </c>
-      <c r="F46" s="198">
+        <v>328</v>
+      </c>
+      <c r="F46" s="196">
         <f>Statement!AC189</f>
         <v>2.4951118677971147</v>
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.2">
       <c r="E47" s="20" t="s">
-        <v>338</v>
-      </c>
-      <c r="F47" s="198">
+        <v>336</v>
+      </c>
+      <c r="F47" s="196">
         <f>Statement!AC192</f>
         <v>2.4951118677971147</v>
       </c>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.2">
       <c r="E48" s="20" t="s">
-        <v>343</v>
-      </c>
-      <c r="F48" s="199">
+        <v>341</v>
+      </c>
+      <c r="F48" s="197">
         <f ca="1">Statement!AC193</f>
         <v>0.22020548280259802</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="248" t="s">
-        <v>334</v>
-      </c>
-      <c r="C51" s="248"/>
-      <c r="E51" s="248" t="s">
-        <v>355</v>
-      </c>
-      <c r="F51" s="248"/>
+      <c r="B51" s="246" t="s">
+        <v>332</v>
+      </c>
+      <c r="C51" s="246"/>
+      <c r="E51" s="246" t="s">
+        <v>353</v>
+      </c>
+      <c r="F51" s="246"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
-        <v>332</v>
-      </c>
-      <c r="C52" s="199">
+        <v>330</v>
+      </c>
+      <c r="C52" s="197">
         <f>Statement!AC190</f>
         <v>0.69669698594761198</v>
       </c>
       <c r="E52" s="20" t="s">
-        <v>356</v>
-      </c>
-      <c r="F52" s="199">
+        <v>354</v>
+      </c>
+      <c r="F52" s="197">
         <f>Statement!AC194</f>
         <v>5.3219161289936798E-3</v>
       </c>
     </row>
     <row r="53" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B53" s="20" t="s">
-        <v>333</v>
-      </c>
-      <c r="C53" s="199">
+        <v>331</v>
+      </c>
+      <c r="C53" s="197">
         <f>Statement!AC191</f>
         <v>0.16003121393504871</v>
       </c>
       <c r="E53" s="20" t="s">
-        <v>353</v>
-      </c>
-      <c r="F53" s="199">
+        <v>351</v>
+      </c>
+      <c r="F53" s="197">
         <f>Statement!AC195</f>
         <v>2.3168998318295178E-2</v>
       </c>
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.2">
       <c r="E54" s="20" t="s">
-        <v>354</v>
-      </c>
-      <c r="F54" s="199">
+        <v>352</v>
+      </c>
+      <c r="F54" s="197">
         <f>Statement!AC196</f>
         <v>0.41931684334511188</v>
       </c>
@@ -33632,7 +33655,7 @@
     </row>
     <row r="5" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B5" s="14" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C5" s="14"/>
       <c r="D5" s="14"/>
@@ -33645,56 +33668,56 @@
       <c r="B6" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="196">
+      <c r="C6" s="194">
         <f>Statement!M125</f>
         <v>33.43</v>
       </c>
-      <c r="D6" s="196">
+      <c r="D6" s="194">
         <f>Statement!N125</f>
         <v>14.57</v>
       </c>
-      <c r="E6" s="196">
+      <c r="E6" s="194">
         <f>Statement!O125</f>
         <v>23.85</v>
       </c>
-      <c r="F6" s="196">
+      <c r="F6" s="194">
         <f>Statement!P125</f>
         <v>14.58</v>
       </c>
-      <c r="G6" s="196">
+      <c r="G6" s="194">
         <f>Statement!Q125</f>
         <v>12.59</v>
       </c>
-      <c r="I6" s="196">
+      <c r="I6" s="194">
         <f ca="1">Statement!AC125</f>
         <v>11.24</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B7" s="20" t="s">
-        <v>291</v>
-      </c>
-      <c r="C7" s="197">
+        <v>289</v>
+      </c>
+      <c r="C7" s="195">
         <f>Statement!M170</f>
         <v>18122001.84</v>
       </c>
-      <c r="D7" s="197">
+      <c r="D7" s="195">
         <f>Statement!N170</f>
         <v>8121653.1100000003</v>
       </c>
-      <c r="E7" s="197">
+      <c r="E7" s="195">
         <f>Statement!O170</f>
         <v>13570960.050000001</v>
       </c>
-      <c r="F7" s="197">
+      <c r="F7" s="195">
         <f>Statement!P170</f>
         <v>8040767.9400000004</v>
       </c>
-      <c r="G7" s="197">
+      <c r="G7" s="195">
         <f>Statement!Q170</f>
         <v>6680971.6299999999</v>
       </c>
-      <c r="I7" s="197">
+      <c r="I7" s="195">
         <f ca="1">Statement!AC170</f>
         <v>5936473.4400000004</v>
       </c>
@@ -33703,56 +33726,56 @@
       <c r="B8" s="20" t="s">
         <v>230</v>
       </c>
-      <c r="C8" s="197">
+      <c r="C8" s="195">
         <f>Statement!M171</f>
         <v>16256861.84</v>
       </c>
-      <c r="D8" s="197">
+      <c r="D8" s="195">
         <f>Statement!N171</f>
         <v>6364760.1100000003</v>
       </c>
-      <c r="E8" s="197">
+      <c r="E8" s="195">
         <f>Statement!O171</f>
         <v>11691137.050000001</v>
       </c>
-      <c r="F8" s="197">
+      <c r="F8" s="195">
         <f>Statement!P171</f>
         <v>6411249.9400000004</v>
       </c>
-      <c r="G8" s="197">
+      <c r="G8" s="195">
         <f>Statement!Q171</f>
         <v>5208485.63</v>
       </c>
-      <c r="I8" s="197">
+      <c r="I8" s="195">
         <f ca="1">Statement!AC171</f>
         <v>4629229.4400000004</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B9" s="20" t="s">
-        <v>289</v>
-      </c>
-      <c r="C9" s="198">
+        <v>287</v>
+      </c>
+      <c r="C9" s="196">
         <f>Statement!M167</f>
         <v>-28.818965517241381</v>
       </c>
-      <c r="D9" s="198">
+      <c r="D9" s="196">
         <f>Statement!N167</f>
         <v>-24.283333333333335</v>
       </c>
-      <c r="E9" s="198">
+      <c r="E9" s="196">
         <f>Statement!O167</f>
         <v>-149.0625</v>
       </c>
-      <c r="F9" s="198">
+      <c r="F9" s="196">
         <f>Statement!P167</f>
         <v>-112.15384615384615</v>
       </c>
-      <c r="G9" s="198">
+      <c r="G9" s="196">
         <f>Statement!Q167</f>
         <v>24.21153846153846</v>
       </c>
-      <c r="I9" s="198">
+      <c r="I9" s="196">
         <f ca="1">Statement!AC167</f>
         <v>18.733333333333331</v>
       </c>
@@ -33761,85 +33784,85 @@
       <c r="B10" s="20" t="s">
         <v>243</v>
       </c>
-      <c r="C10" s="198">
+      <c r="C10" s="196">
         <f>Statement!M168</f>
         <v>17.03343197885799</v>
       </c>
-      <c r="D10" s="198">
+      <c r="D10" s="196">
         <f>Statement!N168</f>
         <v>7.5428149003241138</v>
       </c>
-      <c r="E10" s="198">
+      <c r="E10" s="196">
         <f>Statement!O168</f>
         <v>11.921699837623619</v>
       </c>
-      <c r="F10" s="198">
+      <c r="F10" s="196">
         <f>Statement!P168</f>
         <v>5.7103089537122012</v>
       </c>
-      <c r="G10" s="198">
+      <c r="G10" s="196">
         <f>Statement!Q168</f>
         <v>4.2592243004348767</v>
       </c>
-      <c r="I10" s="198">
+      <c r="I10" s="196">
         <f ca="1">Statement!AC168</f>
         <v>3.6210005501306561</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B11" s="20" t="s">
-        <v>290</v>
-      </c>
-      <c r="C11" s="198">
+        <v>288</v>
+      </c>
+      <c r="C11" s="196">
         <f>Statement!M169</f>
         <v>9.4291282297830765</v>
       </c>
-      <c r="D11" s="198">
+      <c r="D11" s="196">
         <f>Statement!N169</f>
         <v>4.2296795940750709</v>
       </c>
-      <c r="E11" s="198">
+      <c r="E11" s="196">
         <f>Statement!O169</f>
         <v>6.731246372972957</v>
       </c>
-      <c r="F11" s="198">
+      <c r="F11" s="196">
         <f>Statement!P169</f>
         <v>4.3563406007925183</v>
       </c>
-      <c r="G11" s="198">
+      <c r="G11" s="196">
         <f>Statement!Q169</f>
         <v>3.1673000839820857</v>
       </c>
-      <c r="I11" s="198">
+      <c r="I11" s="196">
         <f ca="1">Statement!AC169</f>
         <v>3.0945830743077249</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B12" s="20" t="s">
-        <v>312</v>
-      </c>
-      <c r="C12" s="198">
+        <v>310</v>
+      </c>
+      <c r="C12" s="196">
         <f>Statement!M172</f>
         <v>18.220034071092023</v>
       </c>
-      <c r="D12" s="198">
+      <c r="D12" s="196">
         <f>Statement!N172</f>
         <v>6.012539531693843</v>
       </c>
-      <c r="E12" s="198">
+      <c r="E12" s="196">
         <f>Statement!O172</f>
         <v>8.9376861900568176</v>
       </c>
-      <c r="F12" s="198">
+      <c r="F12" s="196">
         <f>Statement!P172</f>
         <v>4.4844452542695352</v>
       </c>
-      <c r="G12" s="198">
+      <c r="G12" s="196">
         <f>Statement!Q172</f>
         <v>3.2339352913126516</v>
       </c>
-      <c r="I12" s="198">
+      <c r="I12" s="196">
         <f ca="1">Statement!AC172</f>
         <v>2.7681315529829642</v>
       </c>
@@ -33848,27 +33871,27 @@
       <c r="B13" s="20" t="s">
         <v>246</v>
       </c>
-      <c r="C13" s="198">
+      <c r="C13" s="196">
         <f>Statement!M173</f>
         <v>-32.452323883212962</v>
       </c>
-      <c r="D13" s="198">
+      <c r="D13" s="196">
         <f>Statement!N173</f>
         <v>-18.274679240732393</v>
       </c>
-      <c r="E13" s="198">
+      <c r="E13" s="196">
         <f>Statement!O173</f>
         <v>-70.97581987615348</v>
       </c>
-      <c r="F13" s="198">
+      <c r="F13" s="196">
         <f>Statement!P173</f>
         <v>-39.437100185152154</v>
       </c>
-      <c r="G13" s="198">
+      <c r="G13" s="196">
         <f>Statement!Q173</f>
         <v>91.763312720225514</v>
       </c>
-      <c r="I13" s="198">
+      <c r="I13" s="196">
         <f ca="1">Statement!AC173</f>
         <v>45.761913818839652</v>
       </c>
@@ -33888,27 +33911,27 @@
       <c r="B16" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="C16" s="199">
+      <c r="C16" s="197">
         <f>Statement!M100</f>
         <v>0.81073956684882742</v>
       </c>
-      <c r="D16" s="199">
+      <c r="D16" s="197">
         <f>Statement!N100</f>
         <v>0.82991287393217905</v>
       </c>
-      <c r="E16" s="199">
+      <c r="E16" s="197">
         <f>Statement!O100</f>
         <v>0.85021925398601916</v>
       </c>
-      <c r="F16" s="199">
+      <c r="F16" s="197">
         <f>Statement!P100</f>
         <v>0.82727270183763457</v>
       </c>
-      <c r="G16" s="199">
+      <c r="G16" s="197">
         <f>Statement!Q100</f>
         <v>0.83174673345867178</v>
       </c>
-      <c r="I16" s="199">
+      <c r="I16" s="197">
         <f>Statement!AC100</f>
         <v>0.83014417010996633</v>
       </c>
@@ -33917,27 +33940,27 @@
       <c r="B17" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="C17" s="199">
+      <c r="C17" s="197">
         <f>Statement!M101</f>
         <v>-0.56144004160259653</v>
       </c>
-      <c r="D17" s="199">
+      <c r="D17" s="197">
         <f>Statement!N101</f>
         <v>-0.32900930585377974</v>
       </c>
-      <c r="E17" s="199">
+      <c r="E17" s="197">
         <f>Statement!O101</f>
         <v>-0.12592579001767487</v>
       </c>
-      <c r="F17" s="199">
+      <c r="F17" s="197">
         <f>Statement!P101</f>
         <v>-0.11371133357208407</v>
       </c>
-      <c r="G17" s="199">
+      <c r="G17" s="197">
         <f>Statement!Q101</f>
         <v>3.5242137575966802E-2</v>
       </c>
-      <c r="I17" s="199">
+      <c r="I17" s="197">
         <f>Statement!AC101</f>
         <v>6.0489855471109168E-2</v>
       </c>
@@ -33946,34 +33969,34 @@
       <c r="B18" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="C18" s="199">
+      <c r="C18" s="197">
         <f>Statement!M102</f>
         <v>-0.58905555829519018</v>
       </c>
-      <c r="D18" s="199">
+      <c r="D18" s="197">
         <f>Statement!N102</f>
         <v>-0.31018127096556619</v>
       </c>
-      <c r="E18" s="199">
+      <c r="E18" s="197">
         <f>Statement!O102</f>
         <v>-6.8714107480322181E-2</v>
       </c>
-      <c r="F18" s="199">
+      <c r="F18" s="197">
         <f>Statement!P102</f>
         <v>-5.1546377330617545E-2</v>
       </c>
-      <c r="G18" s="199">
+      <c r="G18" s="197">
         <f>Statement!Q102</f>
         <v>0.17529796867199976</v>
       </c>
-      <c r="I18" s="199">
+      <c r="I18" s="197">
         <f>Statement!AC102</f>
         <v>0.19578073705548546</v>
       </c>
     </row>
     <row r="20" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B20" s="14" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C20" s="14"/>
       <c r="D20" s="14"/>
@@ -33986,92 +34009,92 @@
       <c r="B21" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="C21" s="201">
+      <c r="C21" s="199">
         <f>Statement!M18</f>
         <v>-525586</v>
       </c>
-      <c r="D21" s="201">
+      <c r="D21" s="199">
         <f>Statement!N18</f>
         <v>-328352</v>
       </c>
-      <c r="E21" s="201">
+      <c r="E21" s="199">
         <f>Statement!O18</f>
         <v>-89883</v>
       </c>
-      <c r="F21" s="201">
+      <c r="F21" s="199">
         <f>Statement!P18</f>
         <v>-73694</v>
       </c>
-      <c r="G21" s="201">
+      <c r="G21" s="199">
         <f>Statement!Q18</f>
         <v>282330</v>
       </c>
-      <c r="I21" s="201">
+      <c r="I21" s="199">
         <f>Statement!AC18</f>
         <v>327410</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
-        <v>299</v>
-      </c>
-      <c r="C22" s="201">
+        <v>297</v>
+      </c>
+      <c r="C22" s="199">
         <f>Statement!M58</f>
         <v>-54963</v>
       </c>
-      <c r="D22" s="201">
+      <c r="D22" s="199">
         <f>Statement!N58</f>
         <v>-9981</v>
       </c>
-      <c r="E22" s="201">
+      <c r="E22" s="199">
         <f>Statement!O58</f>
         <v>299082</v>
       </c>
-      <c r="F22" s="201">
+      <c r="F22" s="199">
         <f>Statement!P58</f>
         <v>320565</v>
       </c>
-      <c r="G22" s="201">
+      <c r="G22" s="199">
         <f>Statement!Q58</f>
         <v>371208</v>
       </c>
-      <c r="I22" s="201">
+      <c r="I22" s="199">
         <f>Statement!AC58</f>
         <v>384134</v>
       </c>
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B23" s="20" t="s">
-        <v>306</v>
-      </c>
-      <c r="C23" s="219" t="str">
+        <v>304</v>
+      </c>
+      <c r="C23" s="217" t="str">
         <f>IF(OR(C21&lt;=0, C22&lt;=0),"N/A",C21-C22)</f>
         <v>N/A</v>
       </c>
-      <c r="D23" s="219" t="str">
+      <c r="D23" s="217" t="str">
         <f t="shared" ref="D23:I23" si="0">IF(OR(D21&lt;=0, D22&lt;=0),"N/A",D21-D22)</f>
         <v>N/A</v>
       </c>
-      <c r="E23" s="219" t="str">
+      <c r="E23" s="217" t="str">
         <f t="shared" si="0"/>
         <v>N/A</v>
       </c>
-      <c r="F23" s="219" t="str">
+      <c r="F23" s="217" t="str">
         <f t="shared" si="0"/>
         <v>N/A</v>
       </c>
-      <c r="G23" s="219">
+      <c r="G23" s="217">
         <f t="shared" si="0"/>
         <v>-88878</v>
       </c>
-      <c r="I23" s="219">
+      <c r="I23" s="217">
         <f t="shared" si="0"/>
         <v>-56724</v>
       </c>
     </row>
     <row r="25" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B25" s="14" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C25" s="14"/>
       <c r="D25" s="14"/>
@@ -34084,27 +34107,27 @@
       <c r="B26" s="20" t="s">
         <v>119</v>
       </c>
-      <c r="C26" s="199">
+      <c r="C26" s="197">
         <f>Statement!M130</f>
         <v>-0.58905555829519018</v>
       </c>
-      <c r="D26" s="199">
+      <c r="D26" s="197">
         <f>Statement!N130</f>
         <v>-0.31018127096556619</v>
       </c>
-      <c r="E26" s="199">
+      <c r="E26" s="197">
         <f>Statement!O130</f>
         <v>-6.8714107480322181E-2</v>
       </c>
-      <c r="F26" s="199">
+      <c r="F26" s="197">
         <f>Statement!P130</f>
         <v>-5.1546377330617545E-2</v>
       </c>
-      <c r="G26" s="199">
+      <c r="G26" s="197">
         <f>Statement!Q130</f>
         <v>0.17529796867199976</v>
       </c>
-      <c r="I26" s="199">
+      <c r="I26" s="197">
         <f>Statement!AC130</f>
         <v>0.19578073705548546</v>
       </c>
@@ -34113,27 +34136,27 @@
       <c r="B27" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="C27" s="238">
+      <c r="C27" s="236">
         <f>Statement!M131</f>
         <v>0.346849112713561</v>
       </c>
-      <c r="D27" s="238">
+      <c r="D27" s="236">
         <f>Statement!N131</f>
         <v>0.38702057541552631</v>
       </c>
-      <c r="E27" s="238">
+      <c r="E27" s="236">
         <f>Statement!O131</f>
         <v>0.44270021436611728</v>
       </c>
-      <c r="F27" s="238">
+      <c r="F27" s="236">
         <f>Statement!P131</f>
         <v>0.49896309946357587</v>
       </c>
-      <c r="G27" s="238">
+      <c r="G27" s="236">
         <f>Statement!Q131</f>
         <v>0.50659662808253647</v>
       </c>
-      <c r="I27" s="238">
+      <c r="I27" s="236">
         <f>Statement!AC131</f>
         <v>0.57573243364202842</v>
       </c>
@@ -34142,27 +34165,27 @@
       <c r="B28" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="C28" s="200">
+      <c r="C28" s="198">
         <f>Statement!M132</f>
         <v>-0.20431339773367801</v>
       </c>
-      <c r="D28" s="200">
+      <c r="D28" s="198">
         <f>Statement!N132</f>
         <v>-0.12004653397221271</v>
       </c>
-      <c r="E28" s="200">
+      <c r="E28" s="198">
         <f>Statement!O132</f>
         <v>-3.0419750111515053E-2</v>
       </c>
-      <c r="F28" s="200">
+      <c r="F28" s="198">
         <f>Statement!P132</f>
         <v>-2.5719740199003933E-2</v>
       </c>
-      <c r="G28" s="200">
+      <c r="G28" s="198">
         <f>Statement!Q132</f>
         <v>8.8805359838953199E-2</v>
       </c>
-      <c r="I28" s="200">
+      <c r="I28" s="198">
         <f>Statement!AC132</f>
         <v>0.1127173202051847</v>
       </c>
@@ -34171,27 +34194,27 @@
       <c r="B29" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="C29" s="238">
+      <c r="C29" s="236">
         <f>Statement!M133</f>
         <v>1.3384813183920012</v>
       </c>
-      <c r="D29" s="238">
+      <c r="D29" s="236">
         <f>Statement!N133</f>
         <v>1.4244692363857558</v>
       </c>
-      <c r="E29" s="238">
+      <c r="E29" s="236">
         <f>Statement!O133</f>
         <v>1.4655708952965953</v>
       </c>
-      <c r="F29" s="238">
+      <c r="F29" s="236">
         <f>Statement!P133</f>
         <v>1.5523507364438103</v>
       </c>
-      <c r="G29" s="238">
+      <c r="G29" s="236">
         <f>Statement!Q133</f>
         <v>1.526562875884657</v>
       </c>
-      <c r="I29" s="238">
+      <c r="I29" s="236">
         <f>Statement!AC133</f>
         <v>1.5264074746513994</v>
       </c>
@@ -34200,34 +34223,34 @@
       <c r="B30" s="32" t="s">
         <v>123</v>
       </c>
-      <c r="C30" s="200">
+      <c r="C30" s="198">
         <f>Statement!M134</f>
         <v>-0.27346966596372269</v>
       </c>
-      <c r="D30" s="200">
+      <c r="D30" s="198">
         <f>Statement!N134</f>
         <v>-0.17100259457815453</v>
       </c>
-      <c r="E30" s="200">
+      <c r="E30" s="198">
         <f>Statement!O134</f>
         <v>-4.4582300405631825E-2</v>
       </c>
-      <c r="F30" s="200">
+      <c r="F30" s="198">
         <f>Statement!P134</f>
         <v>-3.9926057639067224E-2</v>
       </c>
-      <c r="G30" s="200">
+      <c r="G30" s="198">
         <f>Statement!Q134</f>
         <v>0.13556696550972422</v>
       </c>
-      <c r="I30" s="200">
+      <c r="I30" s="198">
         <f>Statement!AC134</f>
         <v>0.17205256008386913</v>
       </c>
     </row>
     <row r="32" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B32" s="14" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C32" s="14"/>
       <c r="D32" s="14"/>
@@ -34240,27 +34263,27 @@
       <c r="B33" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="C33" s="199">
+      <c r="C33" s="197">
         <f>C28</f>
         <v>-0.20431339773367801</v>
       </c>
-      <c r="D33" s="199">
+      <c r="D33" s="197">
         <f t="shared" ref="D33:G33" si="1">D28</f>
         <v>-0.12004653397221271</v>
       </c>
-      <c r="E33" s="199">
+      <c r="E33" s="197">
         <f t="shared" si="1"/>
         <v>-3.0419750111515053E-2</v>
       </c>
-      <c r="F33" s="199">
+      <c r="F33" s="197">
         <f t="shared" si="1"/>
         <v>-2.5719740199003933E-2</v>
       </c>
-      <c r="G33" s="199">
+      <c r="G33" s="197">
         <f t="shared" si="1"/>
         <v>8.8805359838953199E-2</v>
       </c>
-      <c r="I33" s="199">
+      <c r="I33" s="197">
         <f>I28</f>
         <v>0.1127173202051847</v>
       </c>
@@ -34269,27 +34292,27 @@
       <c r="B34" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="C34" s="199">
+      <c r="C34" s="197">
         <f>C30</f>
         <v>-0.27346966596372269</v>
       </c>
-      <c r="D34" s="199">
+      <c r="D34" s="197">
         <f t="shared" ref="D34:G34" si="2">D30</f>
         <v>-0.17100259457815453</v>
       </c>
-      <c r="E34" s="199">
+      <c r="E34" s="197">
         <f t="shared" si="2"/>
         <v>-4.4582300405631825E-2</v>
       </c>
-      <c r="F34" s="199">
+      <c r="F34" s="197">
         <f t="shared" si="2"/>
         <v>-3.9926057639067224E-2</v>
       </c>
-      <c r="G34" s="199">
+      <c r="G34" s="197">
         <f t="shared" si="2"/>
         <v>0.13556696550972422</v>
       </c>
-      <c r="I34" s="199">
+      <c r="I34" s="197">
         <f>I30</f>
         <v>0.17205256008386913</v>
       </c>
@@ -34298,34 +34321,34 @@
       <c r="B35" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="C35" s="199">
+      <c r="C35" s="197">
         <f>Statement!M157</f>
         <v>-8.8230445426845385</v>
       </c>
-      <c r="D35" s="199">
+      <c r="D35" s="197">
         <f>Statement!N157</f>
         <v>-2.1332373748200779</v>
       </c>
-      <c r="E35" s="199">
+      <c r="E35" s="197">
         <f>Statement!O157</f>
         <v>-1.2085904425090432</v>
       </c>
-      <c r="F35" s="199">
+      <c r="F35" s="197">
         <f>Statement!P157</f>
         <v>-0.75178502062484975</v>
       </c>
-      <c r="G35" s="199">
+      <c r="G35" s="197">
         <f>Statement!Q157</f>
         <v>9.3033776374731397E-2</v>
       </c>
-      <c r="I35" s="199">
+      <c r="I35" s="197">
         <f>Statement!AC157</f>
         <v>0.16980935706480046</v>
       </c>
     </row>
     <row r="37" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B37" s="14" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C37" s="14"/>
       <c r="D37" s="14"/>
@@ -34338,27 +34361,27 @@
       <c r="B38" s="20" t="s">
         <v>180</v>
       </c>
-      <c r="C38" s="198">
+      <c r="C38" s="196">
         <f>Statement!M158</f>
         <v>133.69421979440784</v>
       </c>
-      <c r="D38" s="198">
+      <c r="D38" s="196">
         <f>Statement!N158</f>
         <v>152.91140215061483</v>
       </c>
-      <c r="E38" s="198">
+      <c r="E38" s="196">
         <f>Statement!O158</f>
         <v>145.23661159324561</v>
       </c>
-      <c r="F38" s="198">
+      <c r="F38" s="196">
         <f>Statement!P158</f>
         <v>137.8303503480538</v>
       </c>
-      <c r="G38" s="198">
+      <c r="G38" s="196">
         <f>Statement!Q158</f>
         <v>131.6037563052133</v>
       </c>
-      <c r="I38" s="198">
+      <c r="I38" s="196">
         <f>Statement!AC158</f>
         <v>65.477289171395597</v>
       </c>
@@ -34367,27 +34390,27 @@
       <c r="B39" s="20" t="s">
         <v>181</v>
       </c>
-      <c r="C39" s="198">
+      <c r="C39" s="196">
         <f>Statement!M159</f>
         <v>0</v>
       </c>
-      <c r="D39" s="198">
+      <c r="D39" s="196">
         <f>Statement!N159</f>
         <v>0</v>
       </c>
-      <c r="E39" s="198">
+      <c r="E39" s="196">
         <f>Statement!O159</f>
         <v>0</v>
       </c>
-      <c r="F39" s="198">
+      <c r="F39" s="196">
         <f>Statement!P159</f>
         <v>0</v>
       </c>
-      <c r="G39" s="198">
+      <c r="G39" s="196">
         <f>Statement!Q159</f>
         <v>0</v>
       </c>
-      <c r="I39" s="198">
+      <c r="I39" s="196">
         <f>Statement!AC159</f>
         <v>0</v>
       </c>
@@ -34396,27 +34419,27 @@
       <c r="B40" s="20" t="s">
         <v>182</v>
       </c>
-      <c r="C40" s="198">
+      <c r="C40" s="196">
         <f>Statement!M160</f>
         <v>24.889114574697395</v>
       </c>
-      <c r="D40" s="198">
+      <c r="D40" s="196">
         <f>Statement!N160</f>
         <v>18.023865460341792</v>
       </c>
-      <c r="E40" s="198">
+      <c r="E40" s="196">
         <f>Statement!O160</f>
         <v>6.4216481901145333</v>
       </c>
-      <c r="F40" s="198">
+      <c r="F40" s="196">
         <f>Statement!P160</f>
         <v>49.039734026613537</v>
       </c>
-      <c r="G40" s="198">
+      <c r="G40" s="196">
         <f>Statement!Q160</f>
         <v>13.686287751306349</v>
       </c>
-      <c r="I40" s="198">
+      <c r="I40" s="196">
         <f>Statement!AC160</f>
         <v>25.312474696801676</v>
       </c>
@@ -34425,34 +34448,34 @@
       <c r="B41" s="20" t="s">
         <v>183</v>
       </c>
-      <c r="C41" s="198">
+      <c r="C41" s="196">
         <f>Statement!M161</f>
         <v>108.80510521971044</v>
       </c>
-      <c r="D41" s="198">
+      <c r="D41" s="196">
         <f>Statement!N161</f>
         <v>134.88753669027304</v>
       </c>
-      <c r="E41" s="198">
+      <c r="E41" s="196">
         <f>Statement!O161</f>
         <v>138.81496340313109</v>
       </c>
-      <c r="F41" s="198">
+      <c r="F41" s="196">
         <f>Statement!P161</f>
         <v>88.790616321440268</v>
       </c>
-      <c r="G41" s="198">
+      <c r="G41" s="196">
         <f>Statement!Q161</f>
         <v>117.91746855390694</v>
       </c>
-      <c r="I41" s="198">
+      <c r="I41" s="196">
         <f>Statement!AC161</f>
         <v>40.164814474593925</v>
       </c>
     </row>
     <row r="43" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B43" s="14" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C43" s="14"/>
       <c r="D43" s="14"/>
@@ -34463,152 +34486,152 @@
     </row>
     <row r="44" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B44" s="20" t="s">
-        <v>309</v>
-      </c>
-      <c r="C44" s="204">
+        <v>307</v>
+      </c>
+      <c r="C44" s="202">
         <f>Statement!M162</f>
         <v>0</v>
       </c>
-      <c r="D44" s="204">
+      <c r="D44" s="202">
         <f>Statement!N162</f>
         <v>0</v>
       </c>
-      <c r="E44" s="204">
+      <c r="E44" s="202">
         <f>Statement!O162</f>
         <v>0</v>
       </c>
-      <c r="F44" s="204">
+      <c r="F44" s="202">
         <f>Statement!P162</f>
         <v>0</v>
       </c>
-      <c r="G44" s="204">
+      <c r="G44" s="202">
         <f>Statement!Q162</f>
         <v>0</v>
       </c>
-      <c r="I44" s="204">
+      <c r="I44" s="202">
         <f>Statement!AC162</f>
         <v>0</v>
       </c>
     </row>
     <row r="45" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B45" s="20" t="s">
-        <v>310</v>
-      </c>
-      <c r="C45" s="204">
+        <v>308</v>
+      </c>
+      <c r="C45" s="202">
         <f>Statement!M163</f>
         <v>-0.97045814153264687</v>
       </c>
-      <c r="D45" s="204">
+      <c r="D45" s="202">
         <f>Statement!N163</f>
         <v>-0.91497314283512088</v>
       </c>
-      <c r="E45" s="204">
+      <c r="E45" s="202">
         <f>Statement!O163</f>
         <v>-0.93239915996813671</v>
       </c>
-      <c r="F45" s="204">
+      <c r="F45" s="202">
         <f>Statement!P163</f>
         <v>-0.88284296675302665</v>
       </c>
-      <c r="G45" s="204">
+      <c r="G45" s="202">
         <f>Statement!Q163</f>
         <v>-0.70704657236408375</v>
       </c>
-      <c r="I45" s="204">
+      <c r="I45" s="202">
         <f>Statement!AC163</f>
         <v>-0.68695115254353079</v>
       </c>
     </row>
     <row r="46" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
-        <v>304</v>
-      </c>
-      <c r="C46" s="204">
+        <v>302</v>
+      </c>
+      <c r="C46" s="202">
         <f>Statement!M164</f>
         <v>4.1553646343798398</v>
       </c>
-      <c r="D46" s="204">
+      <c r="D46" s="202">
         <f>Statement!N164</f>
         <v>3.5124319181677128</v>
       </c>
-      <c r="E46" s="204">
+      <c r="E46" s="202">
         <f>Statement!O164</f>
         <v>3.3726940484002186</v>
       </c>
-      <c r="F46" s="204">
+      <c r="F46" s="202">
         <f>Statement!P164</f>
         <v>2.715395784308817</v>
       </c>
-      <c r="G46" s="204">
+      <c r="G46" s="202">
         <f>Statement!Q164</f>
         <v>2.2676594254840001</v>
       </c>
-      <c r="I46" s="204">
+      <c r="I46" s="202">
         <f>Statement!AC164</f>
         <v>1.9325582625717537</v>
       </c>
     </row>
     <row r="47" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B47" s="20" t="s">
-        <v>305</v>
-      </c>
-      <c r="C47" s="204">
+        <v>303</v>
+      </c>
+      <c r="C47" s="202">
         <f>Statement!M165</f>
         <v>4.3171501096680389</v>
       </c>
-      <c r="D47" s="204">
+      <c r="D47" s="202">
         <f>Statement!N165</f>
         <v>3.7423569563190795</v>
       </c>
-      <c r="E47" s="204">
+      <c r="E47" s="202">
         <f>Statement!O165</f>
         <v>3.6257476910625539</v>
       </c>
-      <c r="F47" s="204">
+      <c r="F47" s="202">
         <f>Statement!P165</f>
         <v>2.9271504030441093</v>
       </c>
-      <c r="G47" s="204">
+      <c r="G47" s="202">
         <f>Statement!Q165</f>
         <v>2.4783388537733191</v>
       </c>
-      <c r="I47" s="204">
+      <c r="I47" s="202">
         <f>Statement!AC165</f>
         <v>2.3066495444084523</v>
       </c>
     </row>
     <row r="48" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B48" s="20" t="s">
-        <v>311</v>
-      </c>
-      <c r="C48" s="206" t="str">
+        <v>309</v>
+      </c>
+      <c r="C48" s="204" t="str">
         <f>Statement!M166</f>
         <v>N/A</v>
       </c>
-      <c r="D48" s="206" t="str">
+      <c r="D48" s="204" t="str">
         <f>Statement!N166</f>
         <v>N/A</v>
       </c>
-      <c r="E48" s="206" t="str">
+      <c r="E48" s="204" t="str">
         <f>Statement!O166</f>
         <v>N/A</v>
       </c>
-      <c r="F48" s="206" t="str">
+      <c r="F48" s="204" t="str">
         <f>Statement!P166</f>
         <v>N/A</v>
       </c>
-      <c r="G48" s="206" t="str">
+      <c r="G48" s="204" t="str">
         <f>Statement!Q166</f>
         <v>N/A</v>
       </c>
-      <c r="I48" s="206" t="str">
+      <c r="I48" s="204" t="str">
         <f>Statement!AC166</f>
         <v>N/A</v>
       </c>
     </row>
     <row r="50" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B50" s="14" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C50" s="14"/>
       <c r="D50" s="14"/>
@@ -34619,152 +34642,152 @@
     </row>
     <row r="51" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B51" s="20" t="s">
-        <v>318</v>
-      </c>
-      <c r="C51" s="199">
+        <v>316</v>
+      </c>
+      <c r="C51" s="197">
         <f>Statement!M179</f>
         <v>-3.4699371821717021E-2</v>
       </c>
-      <c r="D51" s="199">
+      <c r="D51" s="197">
         <f>Statement!N179</f>
         <v>-4.1180507892930679E-2</v>
       </c>
-      <c r="E51" s="199">
+      <c r="E51" s="197">
         <f>Statement!O179</f>
         <v>-6.7085953878406705E-3</v>
       </c>
-      <c r="F51" s="199">
+      <c r="F51" s="197">
         <f>Statement!P179</f>
         <v>-8.9163237311385458E-3</v>
       </c>
-      <c r="G51" s="199">
+      <c r="G51" s="197">
         <f>Statement!Q179</f>
         <v>4.1302621127879274E-2</v>
       </c>
-      <c r="I51" s="199">
+      <c r="I51" s="197">
         <f ca="1">Statement!AC179</f>
         <v>5.3380782918149475E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
-        <v>321</v>
-      </c>
-      <c r="C52" s="199">
+        <v>319</v>
+      </c>
+      <c r="C52" s="197">
         <f>Statement!M178</f>
         <v>-3.2136350340421331E-2</v>
       </c>
-      <c r="D52" s="199">
+      <c r="D52" s="197">
         <f>Statement!N178</f>
         <v>-4.9698749076467263E-2</v>
       </c>
-      <c r="E52" s="199">
+      <c r="E52" s="197">
         <f>Statement!O178</f>
         <v>-5.9107830031523813E-3</v>
       </c>
-      <c r="F52" s="199">
+      <c r="F52" s="197">
         <f>Statement!P178</f>
         <v>-6.5303464037043202E-3</v>
       </c>
-      <c r="G52" s="199">
+      <c r="G52" s="197">
         <f>Statement!Q178</f>
         <v>9.2028530287292954E-3</v>
       </c>
-      <c r="I52" s="199">
+      <c r="I52" s="197">
         <f ca="1">Statement!AC178</f>
         <v>1.8126755065546118E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B53" s="20" t="s">
-        <v>319</v>
-      </c>
-      <c r="C53" s="199">
+        <v>317</v>
+      </c>
+      <c r="C53" s="197">
         <f>Statement!M180</f>
         <v>0</v>
       </c>
-      <c r="D53" s="199">
+      <c r="D53" s="197">
         <f>Statement!N180</f>
         <v>0</v>
       </c>
-      <c r="E53" s="199">
+      <c r="E53" s="197">
         <f>Statement!O180</f>
         <v>0</v>
       </c>
-      <c r="F53" s="199">
+      <c r="F53" s="197">
         <f>Statement!P180</f>
         <v>0</v>
       </c>
-      <c r="G53" s="199">
+      <c r="G53" s="197">
         <f>Statement!Q180</f>
         <v>0</v>
       </c>
-      <c r="I53" s="199">
+      <c r="I53" s="197">
         <f ca="1">Statement!AC180</f>
         <v>0</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B54" s="20" t="s">
-        <v>344</v>
-      </c>
-      <c r="C54" s="199">
+        <v>342</v>
+      </c>
+      <c r="C54" s="197">
         <f>Statement!M181</f>
         <v>0</v>
       </c>
-      <c r="D54" s="199">
+      <c r="D54" s="197">
         <f>Statement!N181</f>
         <v>0</v>
       </c>
-      <c r="E54" s="199">
+      <c r="E54" s="197">
         <f>Statement!O181</f>
         <v>7.5613663014209515E-3</v>
       </c>
-      <c r="F54" s="199">
+      <c r="F54" s="197">
         <f>Statement!P181</f>
         <v>4.8596228981581578E-2</v>
       </c>
-      <c r="G54" s="199">
+      <c r="G54" s="197">
         <f>Statement!Q181</f>
         <v>4.9259451802222368E-2</v>
       </c>
-      <c r="I54" s="199">
+      <c r="I54" s="197">
         <f ca="1">Statement!AC181</f>
         <v>5.8177974430556868E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B55" s="20" t="s">
-        <v>346</v>
-      </c>
-      <c r="C55" s="199">
+        <v>344</v>
+      </c>
+      <c r="C55" s="197">
         <f>Statement!M182</f>
         <v>0</v>
       </c>
-      <c r="D55" s="199">
+      <c r="D55" s="197">
         <f>Statement!N182</f>
         <v>0</v>
       </c>
-      <c r="E55" s="199">
+      <c r="E55" s="197">
         <f>Statement!O182</f>
         <v>7.5613663014209515E-3</v>
       </c>
-      <c r="F55" s="199">
+      <c r="F55" s="197">
         <f>Statement!P182</f>
         <v>4.8596228981581578E-2</v>
       </c>
-      <c r="G55" s="199">
+      <c r="G55" s="197">
         <f>Statement!Q182</f>
         <v>4.9259451802222368E-2</v>
       </c>
-      <c r="I55" s="199">
+      <c r="I55" s="197">
         <f ca="1">Statement!AC182</f>
         <v>5.8177974430556868E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B57" s="14" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C57" s="14"/>
       <c r="D57" s="14"/>
@@ -34775,94 +34798,94 @@
     </row>
     <row r="58" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B58" s="20" t="s">
-        <v>322</v>
-      </c>
-      <c r="C58" s="199">
+        <v>320</v>
+      </c>
+      <c r="C58" s="197">
         <f>Statement!M185</f>
         <v>0</v>
       </c>
-      <c r="D58" s="199">
+      <c r="D58" s="197">
         <f>Statement!N185</f>
         <v>0</v>
       </c>
-      <c r="E58" s="199">
+      <c r="E58" s="197">
         <f>Statement!O185</f>
         <v>0</v>
       </c>
-      <c r="F58" s="199">
+      <c r="F58" s="197">
         <f>Statement!P185</f>
         <v>0</v>
       </c>
-      <c r="G58" s="199">
+      <c r="G58" s="197">
         <f>Statement!Q185</f>
         <v>0</v>
       </c>
-      <c r="I58" s="199">
+      <c r="I58" s="197">
         <f>Statement!AC185</f>
         <v>0</v>
       </c>
     </row>
     <row r="59" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B59" s="20" t="s">
-        <v>324</v>
-      </c>
-      <c r="C59" s="199">
+        <v>322</v>
+      </c>
+      <c r="C59" s="197">
         <f>Statement!M186</f>
         <v>0</v>
       </c>
-      <c r="D59" s="199">
+      <c r="D59" s="197">
         <f>Statement!N186</f>
         <v>0</v>
       </c>
-      <c r="E59" s="199">
+      <c r="E59" s="197">
         <f>Statement!O186</f>
         <v>-1.2792495169232687</v>
       </c>
-      <c r="F59" s="199">
+      <c r="F59" s="197">
         <f>Statement!P186</f>
         <v>-7.44160048753547</v>
       </c>
-      <c r="G59" s="199">
+      <c r="G59" s="197">
         <f>Statement!Q186</f>
         <v>5.3526283260685705</v>
       </c>
-      <c r="I59" s="199">
+      <c r="I59" s="197">
         <f>Statement!AC186</f>
         <v>3.2095084983598028</v>
       </c>
     </row>
     <row r="60" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B60" s="20" t="s">
-        <v>325</v>
-      </c>
-      <c r="C60" s="199">
+        <v>323</v>
+      </c>
+      <c r="C60" s="197">
         <f>Statement!M187</f>
         <v>0</v>
       </c>
-      <c r="D60" s="199">
+      <c r="D60" s="197">
         <f>Statement!N187</f>
         <v>0</v>
       </c>
-      <c r="E60" s="199">
+      <c r="E60" s="197">
         <f>Statement!O187</f>
         <v>-1.2792495169232687</v>
       </c>
-      <c r="F60" s="199">
+      <c r="F60" s="197">
         <f>Statement!P187</f>
         <v>-7.44160048753547</v>
       </c>
-      <c r="G60" s="199">
+      <c r="G60" s="197">
         <f>Statement!Q187</f>
         <v>5.3526283260685705</v>
       </c>
-      <c r="I60" s="199">
+      <c r="I60" s="197">
         <f>Statement!AC187</f>
         <v>3.2095084983598028</v>
       </c>
     </row>
     <row r="62" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B62" s="14" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C62" s="14"/>
       <c r="D62" s="14"/>
@@ -34873,36 +34896,36 @@
     </row>
     <row r="63" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B63" s="20" t="s">
-        <v>329</v>
-      </c>
-      <c r="C63" s="199">
+        <v>327</v>
+      </c>
+      <c r="C63" s="197">
         <f>Statement!M188</f>
         <v>0.32041292188722126</v>
       </c>
-      <c r="D63" s="199">
+      <c r="D63" s="197">
         <f>Statement!N188</f>
         <v>0.31207180184527727</v>
       </c>
-      <c r="E63" s="199">
+      <c r="E63" s="197">
         <f>Statement!O188</f>
         <v>0.22510733498180183</v>
       </c>
-      <c r="F63" s="199">
+      <c r="F63" s="197">
         <f>Statement!P188</f>
         <v>0.22494029842627195</v>
       </c>
-      <c r="G63" s="199">
+      <c r="G63" s="197">
         <f>Statement!Q188</f>
         <v>0.22012147206199109</v>
       </c>
-      <c r="I63" s="199">
+      <c r="I63" s="197">
         <f>Statement!AC188</f>
         <v>0.22116382280992736</v>
       </c>
     </row>
     <row r="65" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B65" s="14" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C65" s="14"/>
       <c r="D65" s="14"/>
@@ -34913,94 +34936,94 @@
     </row>
     <row r="66" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B66" s="20" t="s">
-        <v>330</v>
-      </c>
-      <c r="C66" s="198">
+        <v>328</v>
+      </c>
+      <c r="C66" s="196">
         <f>Statement!M189</f>
         <v>3.4406590811823912</v>
       </c>
-      <c r="D66" s="198">
+      <c r="D66" s="196">
         <f>Statement!N189</f>
         <v>3.1518128961309455</v>
       </c>
-      <c r="E66" s="198">
+      <c r="E66" s="196">
         <f>Statement!O189</f>
         <v>3.3036556282545391</v>
       </c>
-      <c r="F66" s="198">
+      <c r="F66" s="196">
         <f>Statement!P189</f>
         <v>2.9547392260645196</v>
       </c>
-      <c r="G66" s="198">
+      <c r="G66" s="196">
         <f>Statement!Q189</f>
         <v>2.8105061440443424</v>
       </c>
-      <c r="I66" s="198">
+      <c r="I66" s="196">
         <f>Statement!AC189</f>
         <v>2.4951118677971147</v>
       </c>
     </row>
     <row r="67" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B67" s="20" t="s">
-        <v>338</v>
-      </c>
-      <c r="C67" s="198">
+        <v>336</v>
+      </c>
+      <c r="C67" s="196">
         <f>Statement!M192</f>
         <v>3.4406590811823912</v>
       </c>
-      <c r="D67" s="198">
+      <c r="D67" s="196">
         <f>Statement!N192</f>
         <v>3.1518128961309455</v>
       </c>
-      <c r="E67" s="198">
+      <c r="E67" s="196">
         <f>Statement!O192</f>
         <v>3.3036556282545391</v>
       </c>
-      <c r="F67" s="198">
+      <c r="F67" s="196">
         <f>Statement!P192</f>
         <v>2.9547392260645196</v>
       </c>
-      <c r="G67" s="198">
+      <c r="G67" s="196">
         <f>Statement!Q192</f>
         <v>2.8105061440443424</v>
       </c>
-      <c r="I67" s="198">
+      <c r="I67" s="196">
         <f>Statement!AC192</f>
         <v>2.4951118677971147</v>
       </c>
     </row>
     <row r="68" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B68" s="20" t="s">
-        <v>343</v>
-      </c>
-      <c r="C68" s="220">
+        <v>341</v>
+      </c>
+      <c r="C68" s="218">
         <f>Statement!M193</f>
         <v>0.10292130066354745</v>
       </c>
-      <c r="D68" s="220">
+      <c r="D68" s="218">
         <f>Statement!N193</f>
         <v>0.21632209307693517</v>
       </c>
-      <c r="E68" s="220">
+      <c r="E68" s="218">
         <f>Statement!O193</f>
         <v>0.1385180556920142</v>
       </c>
-      <c r="F68" s="220">
+      <c r="F68" s="218">
         <f>Statement!P193</f>
         <v>0.20265701138988473</v>
       </c>
-      <c r="G68" s="220">
+      <c r="G68" s="218">
         <f>Statement!Q193</f>
         <v>0.22039997795949329</v>
       </c>
-      <c r="I68" s="220">
+      <c r="I68" s="218">
         <f ca="1">Statement!AC193</f>
         <v>0.22020548280259802</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B70" s="14" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C70" s="14"/>
       <c r="D70" s="14"/>
@@ -35011,65 +35034,65 @@
     </row>
     <row r="71" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B71" s="20" t="s">
-        <v>332</v>
-      </c>
-      <c r="C71" s="199">
+        <v>330</v>
+      </c>
+      <c r="C71" s="197">
         <f>Statement!M190</f>
         <v>-9.3805469133780903</v>
       </c>
-      <c r="D71" s="199">
+      <c r="D71" s="197">
         <f>Statement!N190</f>
         <v>-37.054403366396151</v>
       </c>
-      <c r="E71" s="199">
+      <c r="E71" s="197">
         <f>Statement!O190</f>
         <v>1.243655586093446</v>
       </c>
-      <c r="F71" s="199">
+      <c r="F71" s="197">
         <f>Statement!P190</f>
         <v>1.1172492318250589</v>
       </c>
-      <c r="G71" s="199">
+      <c r="G71" s="197">
         <f>Statement!Q190</f>
         <v>0.78305424452059225</v>
       </c>
-      <c r="I71" s="199">
+      <c r="I71" s="197">
         <f>Statement!AC190</f>
         <v>0.69669698594761198</v>
       </c>
     </row>
     <row r="72" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B72" s="20" t="s">
-        <v>333</v>
-      </c>
-      <c r="C72" s="199">
+        <v>331</v>
+      </c>
+      <c r="C72" s="197">
         <f>Statement!M191</f>
         <v>0.57784459995606618</v>
       </c>
-      <c r="D72" s="199">
+      <c r="D72" s="197">
         <f>Statement!N191</f>
         <v>0.3493733592422309</v>
       </c>
-      <c r="E72" s="199">
+      <c r="E72" s="197">
         <f>Statement!O191</f>
         <v>0.28435361356255617</v>
       </c>
-      <c r="F72" s="199">
+      <c r="F72" s="197">
         <f>Statement!P191</f>
         <v>0.25051410681111086</v>
       </c>
-      <c r="G72" s="199">
+      <c r="G72" s="197">
         <f>Statement!Q191</f>
         <v>0.18047997854178516</v>
       </c>
-      <c r="I72" s="199">
+      <c r="I72" s="197">
         <f>Statement!AC191</f>
         <v>0.16003121393504871</v>
       </c>
     </row>
     <row r="74" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B74" s="14" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C74" s="14"/>
       <c r="D74" s="14"/>
@@ -35080,87 +35103,87 @@
     </row>
     <row r="75" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B75" s="20" t="s">
-        <v>356</v>
-      </c>
-      <c r="C75" s="199">
+        <v>354</v>
+      </c>
+      <c r="C75" s="197">
         <f>Statement!M194</f>
         <v>1.325746537973577E-2</v>
       </c>
-      <c r="D75" s="199">
+      <c r="D75" s="197">
         <f>Statement!N194</f>
         <v>2.2497097529617479E-2</v>
       </c>
-      <c r="E75" s="199">
+      <c r="E75" s="197">
         <f>Statement!O194</f>
         <v>5.6128408833764501E-3</v>
       </c>
-      <c r="F75" s="199">
+      <c r="F75" s="197">
         <f>Statement!P194</f>
         <v>1.0438116928173332E-2</v>
       </c>
-      <c r="G75" s="199">
+      <c r="G75" s="197">
         <f>Statement!Q194</f>
         <v>1.1826854061786744E-2</v>
       </c>
-      <c r="I75" s="199">
+      <c r="I75" s="197">
         <f>Statement!AC194</f>
         <v>5.3219161289936798E-3</v>
       </c>
     </row>
     <row r="76" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B76" s="20" t="s">
-        <v>353</v>
-      </c>
-      <c r="C76" s="199">
+        <v>351</v>
+      </c>
+      <c r="C76" s="197">
         <f>Statement!M195</f>
         <v>-0.21521750996124667</v>
       </c>
-      <c r="D76" s="199">
+      <c r="D76" s="197">
         <f>Statement!N195</f>
         <v>-2.3860334635808034</v>
       </c>
-      <c r="E76" s="199">
+      <c r="E76" s="197">
         <f>Statement!O195</f>
         <v>2.4548451595214689E-2</v>
       </c>
-      <c r="F76" s="199">
+      <c r="F76" s="197">
         <f>Statement!P195</f>
         <v>4.6552181304883568E-2</v>
       </c>
-      <c r="G76" s="199">
+      <c r="G76" s="197">
         <f>Statement!Q195</f>
         <v>5.1313549276955236E-2</v>
       </c>
-      <c r="I76" s="199">
+      <c r="I76" s="197">
         <f>Statement!AC195</f>
         <v>2.3168998318295178E-2</v>
       </c>
     </row>
     <row r="77" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B77" s="20" t="s">
-        <v>354</v>
-      </c>
-      <c r="C77" s="199">
+        <v>352</v>
+      </c>
+      <c r="C77" s="197">
         <f>Statement!M196</f>
         <v>0.80442026521591292</v>
       </c>
-      <c r="D77" s="199">
+      <c r="D77" s="197">
         <f>Statement!N196</f>
         <v>1.2719649628798804</v>
       </c>
-      <c r="E77" s="199">
+      <c r="E77" s="197">
         <f>Statement!O196</f>
         <v>0.32491038633446917</v>
       </c>
-      <c r="F77" s="199">
+      <c r="F77" s="197">
         <f>Statement!P196</f>
         <v>0.86600510677808729</v>
       </c>
-      <c r="G77" s="199">
+      <c r="G77" s="197">
         <f>Statement!Q196</f>
         <v>1.1225175319700631</v>
       </c>
-      <c r="I77" s="199">
+      <c r="I77" s="197">
         <f>Statement!AC196</f>
         <v>0.41931684334511188</v>
       </c>
@@ -35180,161 +35203,161 @@
       <c r="B80" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="C80" s="199">
+      <c r="C80" s="197">
         <f>Statement!M88</f>
         <v>1</v>
       </c>
-      <c r="D80" s="199">
+      <c r="D80" s="197">
         <f>Statement!N88</f>
         <v>0.18641482451146088</v>
       </c>
-      <c r="E80" s="199">
+      <c r="E80" s="197">
         <f>Statement!O88</f>
         <v>0.23568437370404344</v>
       </c>
-      <c r="F80" s="199">
+      <c r="F80" s="197">
         <f>Statement!P88</f>
         <v>9.2955127852289474E-2</v>
       </c>
-      <c r="G80" s="199">
+      <c r="G80" s="197">
         <f>Statement!Q88</f>
         <v>0.12653882310808692</v>
       </c>
-      <c r="I80" s="221"/>
+      <c r="I80" s="219"/>
     </row>
     <row r="81" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B81" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="C81" s="199">
+      <c r="C81" s="197">
         <f>Statement!M89</f>
         <v>1</v>
       </c>
-      <c r="D81" s="199">
+      <c r="D81" s="197">
         <f>Statement!N89</f>
         <v>6.6223322358291689E-2</v>
       </c>
-      <c r="E81" s="199">
+      <c r="E81" s="197">
         <f>Statement!O89</f>
         <v>8.8158355132712404E-2</v>
       </c>
-      <c r="F81" s="199">
+      <c r="F81" s="197">
         <f>Statement!P89</f>
         <v>0.26039688858945303</v>
       </c>
-      <c r="G81" s="199">
+      <c r="G81" s="197">
         <f>Statement!Q89</f>
         <v>9.7358893991301598E-2</v>
       </c>
-      <c r="I81" s="221"/>
+      <c r="I81" s="219"/>
     </row>
     <row r="82" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B82" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="C82" s="199">
+      <c r="C82" s="197">
         <f>Statement!M90</f>
         <v>1</v>
       </c>
-      <c r="D82" s="199">
+      <c r="D82" s="197">
         <f>Statement!N90</f>
         <v>0.21447253464273469</v>
       </c>
-      <c r="E82" s="199">
+      <c r="E82" s="197">
         <f>Statement!O90</f>
         <v>0.26591920594629664</v>
       </c>
-      <c r="F82" s="199">
+      <c r="F82" s="197">
         <f>Statement!P90</f>
         <v>6.3457381571517466E-2</v>
       </c>
-      <c r="G82" s="199">
+      <c r="G82" s="197">
         <f>Statement!Q90</f>
         <v>0.13263133686529885</v>
       </c>
-      <c r="I82" s="221"/>
+      <c r="I82" s="219"/>
     </row>
     <row r="83" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B83" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="C83" s="199">
+      <c r="C83" s="197">
         <f>Statement!M94</f>
         <v>1</v>
       </c>
-      <c r="D83" s="199">
+      <c r="D83" s="197">
         <f>Statement!N94</f>
         <v>2.0280479935964979E-3</v>
       </c>
-      <c r="E83" s="199">
+      <c r="E83" s="197">
         <f>Statement!O94</f>
         <v>4.080083924770931E-2</v>
       </c>
-      <c r="F83" s="199">
+      <c r="F83" s="197">
         <f>Statement!P94</f>
         <v>5.3586588433573397E-2</v>
       </c>
-      <c r="G83" s="199">
+      <c r="G83" s="197">
         <f>Statement!Q94</f>
         <v>-4.6430846560335276E-2</v>
       </c>
-      <c r="I83" s="221"/>
+      <c r="I83" s="219"/>
     </row>
     <row r="84" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B84" s="20" t="s">
-        <v>360</v>
-      </c>
-      <c r="C84" s="199">
+        <v>358</v>
+      </c>
+      <c r="C84" s="197">
         <f>Statement!M95</f>
         <v>-1</v>
       </c>
-      <c r="D84" s="199">
+      <c r="D84" s="197">
         <f>Statement!N95</f>
         <v>0.3047494141085067</v>
       </c>
-      <c r="E84" s="199">
+      <c r="E84" s="197">
         <f>Statement!O95</f>
         <v>0.52705127726590162</v>
       </c>
-      <c r="F84" s="199">
+      <c r="F84" s="197">
         <f>Statement!P95</f>
         <v>1.3058523555123847E-2</v>
       </c>
-      <c r="G84" s="199">
+      <c r="G84" s="197">
         <f>Statement!Q95</f>
         <v>1.3491440557547871</v>
       </c>
-      <c r="I84" s="221"/>
+      <c r="I84" s="219"/>
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B85" s="20" t="s">
-        <v>361</v>
-      </c>
-      <c r="C85" s="199">
+        <v>359</v>
+      </c>
+      <c r="C85" s="197">
         <f>Statement!M97</f>
         <v>-1</v>
       </c>
-      <c r="D85" s="199">
+      <c r="D85" s="197">
         <f>Statement!N97</f>
         <v>0.37526494236908897</v>
       </c>
-      <c r="E85" s="199">
+      <c r="E85" s="197">
         <f>Statement!O97</f>
         <v>0.72626023292076791</v>
       </c>
-      <c r="F85" s="199">
+      <c r="F85" s="197">
         <f>Statement!P97</f>
         <v>0.18011192327803924</v>
       </c>
-      <c r="G85" s="199">
+      <c r="G85" s="197">
         <f>Statement!Q97</f>
         <v>4.8311124379189625</v>
       </c>
-      <c r="I85" s="221"/>
+      <c r="I85" s="219"/>
     </row>
     <row r="88" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B88" s="14" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C88" s="14"/>
       <c r="D88" s="14"/>
@@ -35345,85 +35368,85 @@
     </row>
     <row r="89" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B89" s="20" t="s">
-        <v>363</v>
-      </c>
-      <c r="C89" s="199">
+        <v>361</v>
+      </c>
+      <c r="C89" s="197">
         <f>Statement!M200</f>
         <v>1</v>
       </c>
-      <c r="D89" s="199">
+      <c r="D89" s="197">
         <f>Statement!N200</f>
         <v>3.4084087514825716E-2</v>
       </c>
-      <c r="E89" s="199">
+      <c r="E89" s="197">
         <f>Statement!O200</f>
         <v>0.24818614965570993</v>
       </c>
-      <c r="F89" s="199">
+      <c r="F89" s="197">
         <f>Statement!P200</f>
         <v>-5.5102093364575021E-2</v>
       </c>
-      <c r="G89" s="199">
+      <c r="G89" s="197">
         <f>Statement!Q200</f>
         <v>3.2771752459329104E-2</v>
       </c>
-      <c r="I89" s="221"/>
+      <c r="I89" s="219"/>
     </row>
     <row r="90" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B90" s="20" t="s">
-        <v>364</v>
-      </c>
-      <c r="C90" s="199">
+        <v>362</v>
+      </c>
+      <c r="C90" s="197">
         <f>Statement!M201</f>
         <v>1</v>
       </c>
-      <c r="D90" s="199">
+      <c r="D90" s="197">
         <f>Statement!N201</f>
         <v>0.37569180272908909</v>
       </c>
-      <c r="E90" s="199">
+      <c r="E90" s="197">
         <f>Statement!O201</f>
         <v>0.27729682030883041</v>
       </c>
-      <c r="F90" s="199">
+      <c r="F90" s="197">
         <f>Statement!P201</f>
         <v>0.23392027917368038</v>
       </c>
-      <c r="G90" s="199">
+      <c r="G90" s="197">
         <f>Statement!Q201</f>
         <v>0.19019336689332336</v>
       </c>
-      <c r="I90" s="221"/>
+      <c r="I90" s="219"/>
     </row>
     <row r="91" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B91" s="20" t="s">
-        <v>365</v>
-      </c>
-      <c r="C91" s="199">
+        <v>363</v>
+      </c>
+      <c r="C91" s="197">
         <f>Statement!M202</f>
         <v>1</v>
       </c>
-      <c r="D91" s="199">
+      <c r="D91" s="197">
         <f>Statement!N202</f>
         <v>0.26768885199472631</v>
       </c>
-      <c r="E91" s="199">
+      <c r="E91" s="197">
         <f>Statement!O202</f>
         <v>-0.29197642617772812</v>
       </c>
-      <c r="F91" s="199">
+      <c r="F91" s="197">
         <f>Statement!P202</f>
         <v>0.10317719384146673</v>
       </c>
-      <c r="G91" s="199">
+      <c r="G91" s="197">
         <f>Statement!Q202</f>
         <v>0.22564418690666996</v>
       </c>
-      <c r="I91" s="221"/>
+      <c r="I91" s="219"/>
     </row>
     <row r="93" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B93" s="14" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C93" s="14"/>
       <c r="D93" s="14"/>
@@ -35434,29 +35457,29 @@
     </row>
     <row r="94" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B94" s="20" t="s">
-        <v>336</v>
-      </c>
-      <c r="C94" s="199">
+        <v>334</v>
+      </c>
+      <c r="C94" s="197">
         <f>Statement!M206</f>
         <v>0</v>
       </c>
-      <c r="D94" s="199">
+      <c r="D94" s="197">
         <f>Statement!N206</f>
         <v>0</v>
       </c>
-      <c r="E94" s="199">
+      <c r="E94" s="197">
         <f>Statement!O206</f>
         <v>0</v>
       </c>
-      <c r="F94" s="199">
+      <c r="F94" s="197">
         <f>Statement!P206</f>
         <v>0</v>
       </c>
-      <c r="G94" s="199">
+      <c r="G94" s="197">
         <f>Statement!Q206</f>
         <v>0</v>
       </c>
-      <c r="I94" s="221"/>
+      <c r="I94" s="219"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -35481,14 +35504,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="254" t="s">
-        <v>368</v>
-      </c>
-      <c r="D3" s="255"/>
-      <c r="F3" s="256" t="s">
-        <v>369</v>
-      </c>
-      <c r="G3" s="255"/>
+      <c r="C3" s="250" t="s">
+        <v>366</v>
+      </c>
+      <c r="D3" s="251"/>
+      <c r="F3" s="252" t="s">
+        <v>367</v>
+      </c>
+      <c r="G3" s="251"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -35496,375 +35519,375 @@
         <f>Statement!Z2</f>
         <v>31.01.2026</v>
       </c>
-      <c r="D4" s="227" t="str">
+      <c r="D4" s="225" t="str">
         <f>Statement!AA2</f>
         <v>30.04.2026</v>
       </c>
-      <c r="F4" s="228" t="str">
+      <c r="F4" s="226" t="str">
         <f>Statement!W2</f>
         <v>30.04.2025</v>
       </c>
-      <c r="G4" s="227" t="str">
+      <c r="G4" s="225" t="str">
         <f>Statement!AA2</f>
         <v>30.04.2026</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="8" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C5" s="10" t="str">
         <f>Statement!Z3</f>
         <v>Q4 2026</v>
       </c>
-      <c r="D5" s="227" t="str">
+      <c r="D5" s="225" t="str">
         <f>Statement!AA3</f>
         <v>Q1 2027</v>
       </c>
-      <c r="F5" s="228" t="str">
+      <c r="F5" s="226" t="str">
         <f>Statement!W3</f>
         <v>Q1 2026</v>
       </c>
-      <c r="G5" s="227" t="str">
+      <c r="G5" s="225" t="str">
         <f>Statement!AA3</f>
         <v>Q1 2027</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B6" s="229" t="s">
+      <c r="B6" s="227" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="223">
+      <c r="C6" s="221">
         <f>Statement!Z5</f>
         <v>481107</v>
       </c>
-      <c r="D6" s="222">
+      <c r="D6" s="220">
         <f>Statement!AA5</f>
         <v>418382</v>
       </c>
-      <c r="F6" s="223">
+      <c r="F6" s="221">
         <f>Statement!W5</f>
         <v>356624</v>
       </c>
-      <c r="G6" s="222">
+      <c r="G6" s="220">
         <f>Statement!AA5</f>
         <v>418382</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B7" s="230" t="s">
-        <v>370</v>
-      </c>
-      <c r="C7" s="252">
+      <c r="B7" s="228" t="s">
+        <v>368</v>
+      </c>
+      <c r="C7" s="253">
         <f>Statement!AA88</f>
         <v>-0.13037640275448081</v>
       </c>
-      <c r="D7" s="253"/>
-      <c r="F7" s="252">
+      <c r="D7" s="254"/>
+      <c r="F7" s="253">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.17317398716855847</v>
       </c>
-      <c r="G7" s="253"/>
+      <c r="G7" s="254"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B8" s="231" t="s">
+      <c r="B8" s="229" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="224">
+      <c r="C8" s="222">
         <f>Statement!Z6</f>
         <v>73935</v>
       </c>
-      <c r="D8" s="222">
+      <c r="D8" s="220">
         <f>Statement!AA6</f>
         <v>76928</v>
       </c>
-      <c r="F8" s="224">
+      <c r="F8" s="222">
         <f>Statement!W6</f>
         <v>63857</v>
       </c>
-      <c r="G8" s="222">
+      <c r="G8" s="220">
         <f>Statement!AA6</f>
         <v>76928</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B9" s="230" t="s">
-        <v>370</v>
-      </c>
-      <c r="C9" s="252">
+      <c r="B9" s="228" t="s">
+        <v>368</v>
+      </c>
+      <c r="C9" s="253">
         <f>Statement!AA89</f>
         <v>4.0481504023804696E-2</v>
       </c>
-      <c r="D9" s="253"/>
-      <c r="F9" s="252">
+      <c r="D9" s="254"/>
+      <c r="F9" s="253">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.20469173309112548</v>
       </c>
-      <c r="G9" s="253"/>
+      <c r="G9" s="254"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B10" s="231" t="s">
+      <c r="B10" s="229" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="224">
+      <c r="C10" s="222">
         <f>Statement!Z7</f>
         <v>407172</v>
       </c>
-      <c r="D10" s="222">
+      <c r="D10" s="220">
         <f>Statement!AA7</f>
         <v>341454</v>
       </c>
-      <c r="F10" s="224">
+      <c r="F10" s="222">
         <f>Statement!W7</f>
         <v>292767</v>
       </c>
-      <c r="G10" s="222">
+      <c r="G10" s="220">
         <f>Statement!AA7</f>
         <v>341454</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B11" s="230" t="s">
-        <v>370</v>
-      </c>
-      <c r="C11" s="252">
+      <c r="B11" s="228" t="s">
+        <v>368</v>
+      </c>
+      <c r="C11" s="253">
         <f>Statement!AA90</f>
         <v>-0.1614010786596328</v>
       </c>
-      <c r="D11" s="253"/>
-      <c r="F11" s="252">
+      <c r="D11" s="254"/>
+      <c r="F11" s="253">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.16629948047423376</v>
       </c>
-      <c r="G11" s="253"/>
+      <c r="G11" s="254"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B12" s="231" t="s">
+      <c r="B12" s="229" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="224">
+      <c r="C12" s="222">
         <f>Statement!Z11</f>
         <v>326886</v>
       </c>
-      <c r="D12" s="222">
+      <c r="D12" s="220">
         <f>Statement!AA11</f>
         <v>313467</v>
       </c>
-      <c r="F12" s="224">
+      <c r="F12" s="222">
         <f>Statement!W11</f>
         <v>309179</v>
       </c>
-      <c r="G12" s="222">
+      <c r="G12" s="220">
         <f>Statement!AA11</f>
         <v>313467</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B13" s="230" t="s">
-        <v>370</v>
-      </c>
-      <c r="C13" s="252">
+      <c r="B13" s="228" t="s">
+        <v>368</v>
+      </c>
+      <c r="C13" s="253">
         <f>Statement!AA94</f>
         <v>-4.1051008608505718E-2</v>
       </c>
-      <c r="D13" s="253"/>
-      <c r="F13" s="252">
+      <c r="D13" s="254"/>
+      <c r="F13" s="253">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>1.3868988514743887E-2</v>
       </c>
-      <c r="G13" s="253"/>
+      <c r="G13" s="254"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B14" s="231" t="s">
-        <v>371</v>
-      </c>
-      <c r="C14" s="224">
+      <c r="B14" s="229" t="s">
+        <v>369</v>
+      </c>
+      <c r="C14" s="222">
         <f>Statement!Z12</f>
         <v>80286</v>
       </c>
-      <c r="D14" s="222">
+      <c r="D14" s="220">
         <f>Statement!AA12</f>
         <v>27987</v>
       </c>
-      <c r="F14" s="224">
+      <c r="F14" s="222">
         <f>Statement!W12</f>
         <v>-16412</v>
       </c>
-      <c r="G14" s="222">
+      <c r="G14" s="220">
         <f>Statement!AA12</f>
         <v>27987</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="230" t="s">
-        <v>370</v>
-      </c>
-      <c r="C15" s="252">
+      <c r="B15" s="228" t="s">
+        <v>368</v>
+      </c>
+      <c r="C15" s="253">
         <f>Statement!AA95</f>
         <v>-0.65140871384799337</v>
       </c>
-      <c r="D15" s="253"/>
-      <c r="F15" s="252">
+      <c r="D15" s="254"/>
+      <c r="F15" s="253">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>2.7052766268583963</v>
       </c>
-      <c r="G15" s="253"/>
+      <c r="G15" s="254"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B16" s="231" t="s">
+      <c r="B16" s="229" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="224">
+      <c r="C16" s="222">
         <f>Statement!Z18</f>
         <v>104462</v>
       </c>
-      <c r="D16" s="222">
+      <c r="D16" s="220">
         <f>Statement!AA18</f>
         <v>22525</v>
       </c>
-      <c r="F16" s="224">
+      <c r="F16" s="222">
         <f>Statement!W18</f>
         <v>-22555</v>
       </c>
-      <c r="G16" s="222">
+      <c r="G16" s="220">
         <f>Statement!AA18</f>
         <v>22525</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B17" s="230" t="s">
-        <v>370</v>
-      </c>
-      <c r="C17" s="252">
+      <c r="B17" s="228" t="s">
+        <v>368</v>
+      </c>
+      <c r="C17" s="253">
         <f>Statement!AA97</f>
         <v>-0.78437135034749483</v>
       </c>
-      <c r="D17" s="253"/>
-      <c r="F17" s="252">
+      <c r="D17" s="254"/>
+      <c r="F17" s="253">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>1.9986699179782754</v>
       </c>
-      <c r="G17" s="253"/>
+      <c r="G17" s="254"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B18" s="231" t="s">
-        <v>372</v>
-      </c>
-      <c r="C18" s="224">
+      <c r="B18" s="229" t="s">
+        <v>370</v>
+      </c>
+      <c r="C18" s="222">
         <f>Statement!Z22</f>
         <v>545284</v>
       </c>
-      <c r="D18" s="222">
+      <c r="D18" s="220">
         <f>Statement!AA22</f>
         <v>527818</v>
       </c>
-      <c r="F18" s="224">
+      <c r="F18" s="222">
         <f>Statement!W22</f>
         <v>548451</v>
       </c>
-      <c r="G18" s="222">
+      <c r="G18" s="220">
         <f>Statement!AA22</f>
         <v>527818</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B19" s="230" t="s">
-        <v>370</v>
-      </c>
-      <c r="C19" s="252">
+      <c r="B19" s="228" t="s">
+        <v>368</v>
+      </c>
+      <c r="C19" s="253">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-3.2031015030699599E-2</v>
       </c>
-      <c r="D19" s="253"/>
-      <c r="F19" s="252">
+      <c r="D19" s="254"/>
+      <c r="F19" s="253">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-3.7620498458385526E-2</v>
       </c>
-      <c r="G19" s="253"/>
+      <c r="G19" s="254"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B20" s="231" t="s">
+      <c r="B20" s="229" t="s">
         <v>39</v>
       </c>
-      <c r="C20" s="225">
+      <c r="C20" s="223">
         <f>Statement!Z26</f>
         <v>0.19</v>
       </c>
-      <c r="D20" s="226">
+      <c r="D20" s="224">
         <f>Statement!AA26</f>
         <v>0.04</v>
       </c>
-      <c r="F20" s="225">
+      <c r="F20" s="223">
         <f>Statement!W26</f>
         <v>-0.04</v>
       </c>
-      <c r="G20" s="226">
+      <c r="G20" s="224">
         <f>Statement!AA26</f>
         <v>0.04</v>
       </c>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B21" s="230" t="s">
-        <v>370</v>
-      </c>
-      <c r="C21" s="252">
+      <c r="B21" s="228" t="s">
+        <v>368</v>
+      </c>
+      <c r="C21" s="253">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>-0.78947368421052633</v>
       </c>
-      <c r="D21" s="253"/>
-      <c r="F21" s="252">
+      <c r="D21" s="254"/>
+      <c r="F21" s="253">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>2</v>
       </c>
-      <c r="G21" s="253"/>
+      <c r="G21" s="254"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C23" s="10" t="str">
         <f>C5</f>
         <v>Q4 2026</v>
       </c>
-      <c r="D23" s="227" t="str">
+      <c r="D23" s="225" t="str">
         <f>D5</f>
         <v>Q1 2027</v>
       </c>
-      <c r="F23" s="228" t="str">
+      <c r="F23" s="226" t="str">
         <f>F5</f>
         <v>Q1 2026</v>
       </c>
-      <c r="G23" s="227" t="str">
+      <c r="G23" s="225" t="str">
         <f>G5</f>
         <v>Q1 2027</v>
       </c>
@@ -35873,131 +35896,131 @@
       <c r="B24" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="C24" s="224">
+      <c r="C24" s="222">
         <f>Statement!Z105</f>
         <v>215904</v>
       </c>
-      <c r="D24" s="222">
+      <c r="D24" s="220">
         <f>Statement!AA105</f>
         <v>149309</v>
       </c>
-      <c r="F24" s="224">
+      <c r="F24" s="222">
         <f>Statement!W105</f>
         <v>128286</v>
       </c>
-      <c r="G24" s="222">
+      <c r="G24" s="220">
         <f>Statement!AA105</f>
         <v>149309</v>
       </c>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B25" s="230" t="s">
-        <v>370</v>
-      </c>
-      <c r="C25" s="252">
+      <c r="B25" s="228" t="s">
+        <v>368</v>
+      </c>
+      <c r="C25" s="253">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>-0.30844727286201273</v>
       </c>
-      <c r="D25" s="253"/>
-      <c r="F25" s="252">
+      <c r="D25" s="254"/>
+      <c r="F25" s="253">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.16387602700216702</v>
       </c>
-      <c r="G25" s="253"/>
+      <c r="G25" s="254"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="C26" s="224">
+      <c r="C26" s="222">
         <f>Statement!Z106</f>
         <v>251233</v>
       </c>
-      <c r="D26" s="222">
+      <c r="D26" s="220">
         <f>Statement!AA106</f>
         <v>252903</v>
       </c>
-      <c r="F26" s="224">
+      <c r="F26" s="222">
         <f>Statement!W106</f>
         <v>217303</v>
       </c>
-      <c r="G26" s="222">
+      <c r="G26" s="220">
         <f>Statement!AA106</f>
         <v>252903</v>
       </c>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B27" s="230" t="s">
-        <v>370</v>
-      </c>
-      <c r="C27" s="252">
+      <c r="B27" s="228" t="s">
+        <v>368</v>
+      </c>
+      <c r="C27" s="253">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>6.6472159310281692E-3</v>
       </c>
-      <c r="D27" s="253"/>
-      <c r="F27" s="252">
+      <c r="D27" s="254"/>
+      <c r="F27" s="253">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.16382654634312457</v>
       </c>
-      <c r="G27" s="253"/>
+      <c r="G27" s="254"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
         <v>115</v>
       </c>
-      <c r="C28" s="224">
+      <c r="C28" s="222">
         <f>Statement!Z107</f>
         <v>13970</v>
       </c>
-      <c r="D28" s="222">
+      <c r="D28" s="220">
         <f>Statement!AA107</f>
         <v>16170</v>
       </c>
-      <c r="F28" s="224">
+      <c r="F28" s="222">
         <f>Statement!W107</f>
         <v>11035</v>
       </c>
-      <c r="G28" s="222">
+      <c r="G28" s="220">
         <f>Statement!AA107</f>
         <v>16170</v>
       </c>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B29" s="230" t="s">
-        <v>370</v>
-      </c>
-      <c r="C29" s="252">
+      <c r="B29" s="228" t="s">
+        <v>368</v>
+      </c>
+      <c r="C29" s="253">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.15748031496062992</v>
       </c>
-      <c r="D29" s="253"/>
-      <c r="F29" s="252">
+      <c r="D29" s="254"/>
+      <c r="F29" s="253">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>0.46533756230176709</v>
       </c>
-      <c r="G29" s="253"/>
+      <c r="G29" s="254"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B31" s="8" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C31" s="10" t="str">
         <f>C5</f>
@@ -36020,106 +36043,88 @@
       <c r="B32" s="20" t="s">
         <v>130</v>
       </c>
-      <c r="C32" s="224">
+      <c r="C32" s="222">
         <f>Statement!Z138</f>
         <v>1852567</v>
       </c>
-      <c r="D32" s="224">
+      <c r="D32" s="222">
         <f>Statement!AA138</f>
         <v>1901211</v>
       </c>
-      <c r="F32" s="224">
+      <c r="F32" s="222">
         <f>Statement!W138</f>
         <v>1692683</v>
       </c>
-      <c r="G32" s="222">
+      <c r="G32" s="220">
         <f>Statement!AA138</f>
         <v>1901211</v>
       </c>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B33" s="230" t="s">
-        <v>370</v>
-      </c>
-      <c r="C33" s="252">
+      <c r="B33" s="228" t="s">
+        <v>368</v>
+      </c>
+      <c r="C33" s="253">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>2.6257619832373135E-2</v>
       </c>
-      <c r="D33" s="253"/>
-      <c r="F33" s="252">
+      <c r="D33" s="254"/>
+      <c r="F33" s="253">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>0.12319376989075922</v>
       </c>
-      <c r="G33" s="253"/>
+      <c r="G33" s="254"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B34" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="C34" s="224">
+      <c r="C34" s="222">
         <f>Statement!Z142</f>
         <v>2565</v>
       </c>
-      <c r="D34" s="224">
+      <c r="D34" s="222">
         <f>Statement!AA142</f>
         <v>2624</v>
       </c>
-      <c r="F34" s="224">
+      <c r="F34" s="222">
         <f>Statement!W142</f>
         <v>2365</v>
       </c>
-      <c r="G34" s="222">
+      <c r="G34" s="220">
         <f>Statement!AA142</f>
         <v>2624</v>
       </c>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B35" s="230" t="s">
-        <v>370</v>
-      </c>
-      <c r="C35" s="252">
+      <c r="B35" s="228" t="s">
+        <v>368</v>
+      </c>
+      <c r="C35" s="253">
         <f>IF(C34=0,
 IF(D34=0,0,IF(D34&gt;0,1,-1)),
 (D34-C34)/ABS(C34)
 )</f>
         <v>2.3001949317738791E-2</v>
       </c>
-      <c r="D35" s="253"/>
-      <c r="F35" s="252">
+      <c r="D35" s="254"/>
+      <c r="F35" s="253">
         <f>IF(F34=0,
 IF(G34=0,0,IF(G34&gt;0,1,-1)),
 (G34-F34)/ABS(F34)
 )</f>
         <v>0.10951374207188161</v>
       </c>
-      <c r="G35" s="253"/>
+      <c r="G35" s="254"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="F33:G33"/>
     <mergeCell ref="C35:D35"/>
@@ -36130,6 +36135,24 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -36371,7 +36394,7 @@
     </row>
     <row r="60" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B60" s="20" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C60" s="64">
         <f>Statement!H174</f>
@@ -36416,7 +36439,7 @@
     </row>
     <row r="61" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B61" s="20" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C61" s="64">
         <f>Statement!H175</f>
@@ -36596,7 +36619,7 @@
     </row>
     <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B65" s="20" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C65" s="64">
         <f>Statement!H105</f>
@@ -36641,7 +36664,7 @@
     </row>
     <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B66" s="20" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C66" s="64">
         <f>Statement!H106</f>
@@ -36686,7 +36709,7 @@
     </row>
     <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B67" s="20" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C67" s="64">
         <f>Statement!H107</f>
@@ -36733,43 +36756,43 @@
       <c r="B68" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="C68" s="244">
+      <c r="C68" s="242">
         <f>Statement!H132</f>
         <v>0</v>
       </c>
-      <c r="D68" s="244">
+      <c r="D68" s="242">
         <f>Statement!I132</f>
         <v>0</v>
       </c>
-      <c r="E68" s="244">
+      <c r="E68" s="242">
         <f>Statement!J132</f>
         <v>0</v>
       </c>
-      <c r="F68" s="244">
+      <c r="F68" s="242">
         <f>Statement!K132</f>
         <v>0</v>
       </c>
-      <c r="G68" s="244">
+      <c r="G68" s="242">
         <f>Statement!L132</f>
         <v>0</v>
       </c>
-      <c r="H68" s="244">
+      <c r="H68" s="242">
         <f>Statement!M132</f>
         <v>-0.20431339773367801</v>
       </c>
-      <c r="I68" s="244">
+      <c r="I68" s="242">
         <f>Statement!N132</f>
         <v>-0.12004653397221271</v>
       </c>
-      <c r="J68" s="244">
+      <c r="J68" s="242">
         <f>Statement!O132</f>
         <v>-3.0419750111515053E-2</v>
       </c>
-      <c r="K68" s="244">
+      <c r="K68" s="242">
         <f>Statement!P132</f>
         <v>-2.5719740199003933E-2</v>
       </c>
-      <c r="L68" s="244">
+      <c r="L68" s="242">
         <f>Statement!Q132</f>
         <v>8.8805359838953199E-2</v>
       </c>
@@ -36778,43 +36801,43 @@
       <c r="B69" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="C69" s="244">
+      <c r="C69" s="242">
         <f>Statement!H134</f>
         <v>0</v>
       </c>
-      <c r="D69" s="244">
+      <c r="D69" s="242">
         <f>Statement!I134</f>
         <v>0</v>
       </c>
-      <c r="E69" s="244">
+      <c r="E69" s="242">
         <f>Statement!J134</f>
         <v>0</v>
       </c>
-      <c r="F69" s="244">
+      <c r="F69" s="242">
         <f>Statement!K134</f>
         <v>0</v>
       </c>
-      <c r="G69" s="244">
+      <c r="G69" s="242">
         <f>Statement!L134</f>
         <v>0</v>
       </c>
-      <c r="H69" s="244">
+      <c r="H69" s="242">
         <f>Statement!M134</f>
         <v>-0.27346966596372269</v>
       </c>
-      <c r="I69" s="244">
+      <c r="I69" s="242">
         <f>Statement!N134</f>
         <v>-0.17100259457815453</v>
       </c>
-      <c r="J69" s="244">
+      <c r="J69" s="242">
         <f>Statement!O134</f>
         <v>-4.4582300405631825E-2</v>
       </c>
-      <c r="K69" s="244">
+      <c r="K69" s="242">
         <f>Statement!P134</f>
         <v>-3.9926057639067224E-2</v>
       </c>
-      <c r="L69" s="244">
+      <c r="L69" s="242">
         <f>Statement!Q134</f>
         <v>0.13556696550972422</v>
       </c>
@@ -36823,43 +36846,43 @@
       <c r="B70" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="C70" s="244">
+      <c r="C70" s="242">
         <f>Statement!H157</f>
         <v>0</v>
       </c>
-      <c r="D70" s="244">
+      <c r="D70" s="242">
         <f>Statement!I157</f>
         <v>0</v>
       </c>
-      <c r="E70" s="244">
+      <c r="E70" s="242">
         <f>Statement!J157</f>
         <v>0</v>
       </c>
-      <c r="F70" s="244">
+      <c r="F70" s="242">
         <f>Statement!K157</f>
         <v>0</v>
       </c>
-      <c r="G70" s="244">
+      <c r="G70" s="242">
         <f>Statement!L157</f>
         <v>0</v>
       </c>
-      <c r="H70" s="244">
+      <c r="H70" s="242">
         <f>Statement!M157</f>
         <v>-8.8230445426845385</v>
       </c>
-      <c r="I70" s="244">
+      <c r="I70" s="242">
         <f>Statement!N157</f>
         <v>-2.1332373748200779</v>
       </c>
-      <c r="J70" s="244">
+      <c r="J70" s="242">
         <f>Statement!O157</f>
         <v>-1.2085904425090432</v>
       </c>
-      <c r="K70" s="244">
+      <c r="K70" s="242">
         <f>Statement!P157</f>
         <v>-0.75178502062484975</v>
       </c>
-      <c r="L70" s="244">
+      <c r="L70" s="242">
         <f>Statement!Q157</f>
         <v>9.3033776374731397E-2</v>
       </c>
@@ -37174,7 +37197,7 @@
     </row>
     <row r="63" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B63" s="20" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C63" s="64">
         <f>Statement!T105</f>
@@ -37211,7 +37234,7 @@
     </row>
     <row r="64" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B64" s="20" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C64" s="64">
         <f>Statement!T106</f>
@@ -37248,7 +37271,7 @@
     </row>
     <row r="65" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B65" s="20" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C65" s="64">
         <f>Statement!T107</f>
@@ -37285,7 +37308,7 @@
     </row>
     <row r="66" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B66" s="20" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C66" s="64">
         <f>Statement!T174</f>

--- a/PATH.xlsx
+++ b/PATH.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0610A70C-69FE-0345-A599-0BFE1FE2250F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9E8A4D7-5F40-8645-B15B-DE4B408564F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="9" activeTab="13" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -135,7 +135,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="2">
+  <futureMetadata name="XLRICHVALUE" count="5">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -146,7 +146,28 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="3"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="4"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="5"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="8"/>
         </ext>
       </extLst>
     </bk>
@@ -156,19 +177,28 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="2">
+  <valueMetadata count="5">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
     </bk>
+    <bk>
+      <rc t="2" v="2"/>
+    </bk>
+    <bk>
+      <rc t="2" v="3"/>
+    </bk>
+    <bk>
+      <rc t="2" v="4"/>
+    </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="416">
   <si>
     <t>Ticker</t>
   </si>
@@ -777,9 +807,6 @@
   </si>
   <si>
     <t>Change in NWC</t>
-  </si>
-  <si>
-    <t>UFCF</t>
   </si>
   <si>
     <t>NOPAT</t>
@@ -11787,7 +11814,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=c1dbvh&amp;q=XNYS%3aPATH&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
@@ -11806,11 +11833,9 @@
     <v>Powered by Refinitiv</v>
     <v>19.84</v>
     <v>9.2002000000000006</v>
-    <v>0.97670000000000001</v>
-    <v>0</v>
-    <v>0</v>
-    <v>-5.4800000000000001E-2</v>
-    <v>-5.0980000000000001E-3</v>
+    <v>0.97399999999999998</v>
+    <v>-0.17749999999999999</v>
+    <v>-1.6511999999999999E-2</v>
     <v>USD</v>
     <v>UiPath, Inc. is focused on agentic automation and orchestration, empowering enterprises to harness the full potential of AI agents to autonomously execute and optimize complex business processes. It is focused on building and managing automations, starting with computer vision technology and user interface automation in its initial robotic process automation offering. Its AI-powered UiPath Platform offers a robust set of capabilities that allows its customers to discover opportunities for automation, automate using a digital workforce that seamlessly collaborates with humans, and operate a mission-critical automation program at scale. It enables employees to quickly build automations for both existing and new processes and to automate a range of actions including logging into applications, moving folders, filling in forms, reading emails and others. Its platform allows users to design and combine UI automations, API integrations and AI-based document understanding in a single workflow.</v>
     <v>3981</v>
@@ -11818,35 +11843,49 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>One Vanderbilt Avenue, 60th Floor, NEW YORK, NY, 10017 US</v>
-    <v>10.975</v>
+    <v>10.72</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46183.909881053129</v>
+    <v>46184.657924988278</v>
     <v>0</v>
-    <v>10.33</v>
-    <v>5569793225</v>
+    <v>10.305</v>
+    <v>5477826871</v>
     <v>UIPATH, INC.</v>
     <v>UIPATH, INC.</v>
-    <v>10.59</v>
-    <v>17.869</v>
+    <v>10.46</v>
+    <v>17.574000000000002</v>
     <v>10.75</v>
-    <v>10.75</v>
-    <v>10.6952</v>
+    <v>10.5725</v>
     <v>518120300</v>
     <v>PATH</v>
     <v>UIPATH, INC. (XNYS:PATH)</v>
-    <v>47024332</v>
-    <v>42469915</v>
+    <v>19387541</v>
+    <v>43177471</v>
     <v>2015</v>
   </rv>
   <rv s="2">
     <v>1</v>
   </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Price (Extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Change (extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Change % (extended hours)</v>
+    <v>0</v>
+  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="3">
+  <rv s="4">
     <v>5</v>
     <v>10 Y TSY YLD NDX</v>
     <v>6</v>
@@ -11860,28 +11899,28 @@
     <v>Powered by Refinitiv</v>
     <v>46.87</v>
     <v>39.47</v>
-    <v>-0.24</v>
-    <v>-5.2719999999999998E-3</v>
+    <v>0.14000000000000001</v>
+    <v>3.0919999999999997E-3</v>
     <v>US</v>
-    <v>45.56</v>
+    <v>45.6</v>
     <v>Index</v>
-    <v>3</v>
-    <v>45.2</v>
+    <v>6</v>
+    <v>45.13</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>45.46</v>
-    <v>45.52</v>
+    <v>45.34</v>
     <v>45.28</v>
+    <v>45.42</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="2">
-    <v>4</v>
+    <v>7</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -11903,8 +11942,6 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
-    <k n="Change (Extended hours)"/>
-    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -11925,7 +11962,6 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
-    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -11935,6 +11971,11 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
+  </s>
+  <s t="_error">
+    <k n="errorType" t="i"/>
+    <k n="field" t="s"/>
+    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -11970,7 +12011,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="45">
+    <a count="42">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -11981,16 +12022,13 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
-      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
-      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
-      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -12084,19 +12122,13 @@
       <v>8</v>
       <v>9</v>
       <v>4</v>
-      <v>1</v>
-      <v>1</v>
-      <v>5</v>
     </spb>
     <spb s="4">
-      <v>at close</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from previous close</v>
       <v>from previous close</v>
       <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
-      <v>from close</v>
-      <v>from close</v>
     </spb>
     <spb s="0">
       <v>1</v>
@@ -12168,9 +12200,6 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
-    <k n="Price (Extended hours)" t="i"/>
-    <k n="Change (Extended hours)" t="i"/>
-    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -12178,9 +12207,6 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
-    <k n="Price (Extended hours)" t="s"/>
-    <k n="Change (Extended hours)" t="s"/>
-    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="UniqueName" t="spb"/>
@@ -12676,11 +12702,11 @@
       </c>
       <c r="C2" s="250"/>
       <c r="E2" s="249" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F2" s="250"/>
       <c r="H2" s="249" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="I2" s="250"/>
     </row>
@@ -12693,11 +12719,11 @@
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="207" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F3" s="209">
         <f ca="1">Statement!AC153</f>
-        <v>5615316.25</v>
+        <v>5522598.2374999998</v>
       </c>
       <c r="H3" s="207" t="str">
         <f>'AVG target price'!B5</f>
@@ -12705,7 +12731,7 @@
       </c>
       <c r="I3" s="233">
         <f ca="1">'AVG target price'!C5</f>
-        <v>6.883608684038804</v>
+        <v>6.8822824136162613</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -12717,11 +12743,11 @@
         <v>PATH</v>
       </c>
       <c r="E4" s="208" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F4" s="210">
         <f ca="1">Statement!AC154</f>
-        <v>4199570.25</v>
+        <v>4106852.2374999998</v>
       </c>
       <c r="H4" s="207" t="str">
         <f>'AVG target price'!B6</f>
@@ -12729,7 +12755,7 @@
       </c>
       <c r="I4" s="233">
         <f ca="1">'AVG target price'!C6</f>
-        <v>16.086390610353249</v>
+        <v>16.085299241165604</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -12738,10 +12764,10 @@
       </c>
       <c r="C5" s="230" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>10.75</v>
+        <v>10.5725</v>
       </c>
       <c r="E5" s="207" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F5" s="211">
         <f>Statement!AC26</f>
@@ -12760,16 +12786,16 @@
       <c r="B6" s="207" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="230" cm="1">
-        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>10.6952</v>
+      <c r="C6" s="230" t="e" cm="1" vm="2">
+        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E6" s="207" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F6" s="212">
         <f ca="1">Statement!AC150</f>
-        <v>17.916666666666664</v>
+        <v>17.62083333333333</v>
       </c>
       <c r="H6" s="207" t="str">
         <f>'AVG target price'!B8</f>
@@ -12777,7 +12803,7 @@
       </c>
       <c r="I6" s="233">
         <f ca="1">'AVG target price'!C8</f>
-        <v>10.692166000283517</v>
+        <v>10.691532697497239</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -12786,14 +12812,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>0</v>
+        <v>-0.17749999999999999</v>
       </c>
       <c r="E7" s="208" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F7" s="213">
         <f ca="1">Statement!AC151</f>
-        <v>3.4631455439416863</v>
+        <v>3.4059633733324164</v>
       </c>
       <c r="H7" s="206" t="str">
         <f>'AVG target price'!B9</f>
@@ -12801,23 +12827,23 @@
       </c>
       <c r="I7" s="234">
         <f ca="1">'AVG target price'!C9</f>
-        <v>11.913914712802143</v>
+        <v>11.913151977203025</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B8" s="207" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" cm="1">
-        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-5.4800000000000001E-2</v>
+      <c r="C8" s="6" t="e" cm="1" vm="3">
+        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E8" s="207" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F8" s="214">
         <f ca="1">Statement!AC161</f>
-        <v>1.9163479884147221E-2</v>
+        <v>1.9485212462008288E-2</v>
       </c>
       <c r="H8" s="206" t="str">
         <f>'AVG target price'!B11</f>
@@ -12825,7 +12851,7 @@
       </c>
       <c r="I8" s="235">
         <f ca="1">'AVG target price'!C11</f>
-        <v>0.10827113607461793</v>
+        <v>0.12680557835923628</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -12834,30 +12860,30 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>0</v>
+        <v>-1.6511999999999999E-2</v>
       </c>
       <c r="E9" s="207" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F9" s="214">
         <f ca="1">Statement!AC162</f>
-        <v>5.5813953488372099E-2</v>
+        <v>5.6751004965712941E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B10" s="207" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" cm="1">
-        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-5.0980000000000001E-3</v>
+      <c r="C10" s="73" t="e" cm="1" vm="4">
+        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E10" s="207" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F10" s="214">
         <f ca="1">Statement!AC164</f>
-        <v>6.150535154631763E-2</v>
+        <v>6.2537954989161926E-2</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -12869,7 +12895,7 @@
         <v>19.84</v>
       </c>
       <c r="E11" s="208" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F11" s="215">
         <f ca="1">Statement!AC163</f>
@@ -12898,7 +12924,7 @@
       </c>
       <c r="C13" s="231" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>0.97670000000000001</v>
+        <v>0.97399999999999998</v>
       </c>
       <c r="E13" s="207" t="s">
         <v>123</v>
@@ -12914,7 +12940,7 @@
       </c>
       <c r="C14" s="232" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>42469915</v>
+        <v>43177471</v>
       </c>
       <c r="E14" s="208" t="s">
         <v>124</v>
@@ -12926,16 +12952,16 @@
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.2">
       <c r="E15" s="207" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F15" s="214">
         <f ca="1">Statement!AC176</f>
-        <v>0.25212222018661906</v>
+        <v>0.2563550595418449</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
       <c r="E16" s="208" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F16" s="213">
         <f>Statement!AC175</f>
@@ -12948,7 +12974,7 @@
       </c>
       <c r="C17" s="251"/>
       <c r="E17" s="206" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F17" s="216">
         <f>Statement!AC171</f>
@@ -12963,7 +12989,7 @@
         <v>14</v>
       </c>
       <c r="E18" s="207" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F18" s="212">
         <f>Statement!AC144</f>
@@ -12979,7 +13005,7 @@
         <v>1000</v>
       </c>
       <c r="E19" s="207" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F19" s="212">
         <f>Statement!AC146</f>
@@ -12994,7 +13020,7 @@
         <v>105</v>
       </c>
       <c r="E20" s="208" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F20" s="213">
         <f>Statement!AC147</f>
@@ -13024,7 +13050,7 @@
       </c>
       <c r="C25" s="251"/>
       <c r="E25" s="249" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="F25" s="250"/>
     </row>
@@ -13035,32 +13061,32 @@
       <c r="C26" s="191">
         <v>0.21</v>
       </c>
-      <c r="E26" s="207" t="e" vm="2">
+      <c r="E26" s="207" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="242" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>45.28</v>
+        <v>45.42</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B27" s="206" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C27" s="244">
         <v>0</v>
       </c>
       <c r="E27" s="208" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="F27" s="243">
         <f ca="1">F26/1000</f>
-        <v>4.5280000000000001E-2</v>
+        <v>4.5420000000000002E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B28" s="206" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C28" s="244">
         <v>0</v>
@@ -13068,7 +13094,7 @@
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="206" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C29" s="244">
         <v>0.12</v>
@@ -13076,7 +13102,7 @@
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B33" s="248" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C33" s="248"/>
       <c r="D33" s="248"/>
@@ -13087,18 +13113,18 @@
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B36" s="16" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -13112,7 +13138,7 @@
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B42" s="248" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C42" s="248"/>
       <c r="D42" s="248"/>
@@ -13123,13 +13149,13 @@
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C44" s="41" t="s">
+        <v>382</v>
+      </c>
+      <c r="D44" s="41" t="s">
         <v>383</v>
-      </c>
-      <c r="D44" s="41" t="s">
-        <v>384</v>
       </c>
       <c r="E44" s="240"/>
     </row>
@@ -19366,7 +19392,7 @@
         <v>0.21</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
@@ -19574,7 +19600,7 @@
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C25" s="257" t="s">
-        <v>203</v>
+        <v>311</v>
       </c>
       <c r="D25" s="257"/>
       <c r="E25" s="257"/>
@@ -19633,7 +19659,7 @@
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B27" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C27" s="147">
         <f>C10*(1-C15)</f>
@@ -19678,7 +19704,7 @@
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B28" s="16" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C28" s="96">
         <f>C27+C20-C21+C22</f>
@@ -19737,7 +19763,7 @@
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C32" s="12">
         <f>C5</f>
@@ -19903,7 +19929,7 @@
   <sheetData>
     <row r="13" spans="2:2" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
   </sheetData>
@@ -19935,7 +19961,7 @@
     <row r="1" spans="1:3" s="85" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4"/>
       <c r="B1" s="84" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="2" spans="1:3" s="85" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -19945,13 +19971,13 @@
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="248" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C4" s="248"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C5" s="157">
         <f>Statement!AC78</f>
@@ -19964,21 +19990,21 @@
       </c>
       <c r="C6" s="154">
         <f ca="1">Overview!C5</f>
-        <v>10.75</v>
+        <v>10.5725</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C7" s="155">
         <f ca="1">C5*C6</f>
-        <v>5615316.25</v>
+        <v>5522598.2374999998</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C8" s="133">
         <f>Statement!AC108</f>
@@ -19987,11 +20013,11 @@
     </row>
     <row r="9" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C9" s="156">
         <f ca="1">Overview!F27</f>
-        <v>4.5280000000000001E-2</v>
+        <v>4.5420000000000002E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20000,12 +20026,12 @@
       </c>
       <c r="C10" s="154">
         <f ca="1">Overview!C13</f>
-        <v>0.97670000000000001</v>
+        <v>0.97399999999999998</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C11" s="156">
         <f>[1]Sheet1!$C$12</f>
@@ -20023,7 +20049,7 @@
     </row>
     <row r="13" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C13" s="156">
         <f>Overview!C27</f>
@@ -20033,13 +20059,13 @@
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="248" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C15" s="248"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
@@ -20048,7 +20074,7 @@
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B17" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
@@ -20057,7 +20083,7 @@
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B18" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C18" s="46">
         <f>C13*(1-C12)</f>
@@ -20066,20 +20092,20 @@
     </row>
     <row r="19" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>8.9231499999999991E-2</v>
+        <v>8.9249999999999996E-2</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B20" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>8.9231499999999991E-2</v>
+        <v>8.9249999999999996E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20115,7 +20141,7 @@
     <row r="1" spans="1:28" s="85" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4"/>
       <c r="B1" s="84" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="2" spans="1:28" s="85" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -20156,7 +20182,7 @@
       <c r="A5" s="88"/>
       <c r="B5" s="60"/>
       <c r="C5" s="257" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D5" s="257"/>
       <c r="E5" s="257"/>
@@ -20240,7 +20266,7 @@
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B7" s="39" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C7" s="133">
         <f>'FCF &amp; Other'!C28</f>
@@ -20299,7 +20325,7 @@
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B8" s="39" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C8" s="147">
         <v>0</v>
@@ -20330,7 +20356,7 @@
       </c>
       <c r="L8" s="147">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>2933282.429595782</v>
+        <v>2932498.8090189225</v>
       </c>
       <c r="N8" s="93"/>
       <c r="O8" s="16"/>
@@ -20349,7 +20375,7 @@
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B9" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C9" s="158"/>
       <c r="D9" s="158"/>
@@ -20375,7 +20401,7 @@
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B10" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C10" s="158"/>
       <c r="D10" s="158"/>
@@ -20384,29 +20410,29 @@
       <c r="G10" s="159"/>
       <c r="H10" s="147">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>3306.4517883441686</v>
+        <v>3306.3956310266703</v>
       </c>
       <c r="I10" s="147">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>-3550.2162736436335</v>
+        <v>-3550.0956797610329</v>
       </c>
       <c r="J10" s="147">
         <f t="shared" ca="1" si="0"/>
-        <v>59726.38133163139</v>
+        <v>59723.338175455217</v>
       </c>
       <c r="K10" s="147">
         <f t="shared" ca="1" si="0"/>
-        <v>77437.286126102757</v>
+        <v>77432.02543003943</v>
       </c>
       <c r="L10" s="147">
         <f t="shared" ca="1" si="0"/>
-        <v>129854.34570260318</v>
+        <v>129843.318740039</v>
       </c>
       <c r="N10" s="93"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B11" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C11" s="158"/>
       <c r="D11" s="158"/>
@@ -20419,18 +20445,18 @@
       <c r="K11" s="158"/>
       <c r="L11" s="147">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>1913167.1654760514</v>
+        <v>1912493.6478677229</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B13" s="248" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C13" s="248"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C14" s="161">
         <v>0.02</v>
@@ -20438,49 +20464,49 @@
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C15" s="156">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>8.9231499999999991E-2</v>
+        <v>8.9249999999999996E-2</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B18" s="248" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C18" s="248"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>266774.24867503787</v>
+        <v>266754.98229679931</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B20" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>1913167.1654760514</v>
+        <v>1912493.6478677229</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B21" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C21" s="96">
         <f ca="1">C19+C20</f>
-        <v>2179941.4141510893</v>
+        <v>2179248.6301645222</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B22" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C22" s="90">
         <f>Statement!AC107</f>
@@ -20489,7 +20515,7 @@
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B23" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C23" s="90">
         <f>Statement!AC108</f>
@@ -20498,11 +20524,11 @@
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B24" s="16" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C24" s="96">
         <f ca="1">C21+C22-C23</f>
-        <v>3595687.4141510893</v>
+        <v>3594994.6301645222</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -20516,11 +20542,11 @@
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B26" s="162" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C26" s="163">
         <f ca="1">C24/C25</f>
-        <v>6.883608684038804</v>
+        <v>6.8822824136162613</v>
       </c>
     </row>
   </sheetData>
@@ -20558,7 +20584,7 @@
     <row r="1" spans="1:14" s="85" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4"/>
       <c r="B1" s="84" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
@@ -20583,7 +20609,7 @@
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
       <c r="C4" s="257" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D4" s="257"/>
       <c r="E4" s="257"/>
@@ -20734,7 +20760,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B8" s="16" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C8" s="94">
         <f>'FCF &amp; Other'!C28</f>
@@ -20798,7 +20824,7 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B11" s="16" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C11" s="12">
         <f>C5</f>
@@ -20936,7 +20962,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C14" s="158"/>
       <c r="D14" s="97">
@@ -20988,7 +21014,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C16" s="257" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D16" s="257"/>
       <c r="E16" s="257"/>
@@ -21046,7 +21072,7 @@
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B18" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C18" s="103">
         <f>Statement!M22</f>
@@ -21092,7 +21118,7 @@
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C19" s="158"/>
       <c r="D19" s="165">
@@ -21133,7 +21159,7 @@
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C21" s="257" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D21" s="257"/>
       <c r="E21" s="257"/>
@@ -21228,7 +21254,7 @@
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C26" s="257" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D26" s="257"/>
       <c r="E26" s="257"/>
@@ -21286,7 +21312,7 @@
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B28" s="16" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C28" s="170">
         <f>C23/(C6/C18)</f>
@@ -21317,7 +21343,7 @@
     </row>
     <row r="29" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B29" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C29" s="164">
         <f>C23*C18</f>
@@ -21348,7 +21374,7 @@
     </row>
     <row r="30" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B30" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C30" s="90">
         <f>Statement!M108</f>
@@ -21379,7 +21405,7 @@
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B31" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C31" s="173">
         <f>Statement!M107</f>
@@ -21410,7 +21436,7 @@
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C32" s="164">
         <f>C29+C30-C31</f>
@@ -21441,7 +21467,7 @@
     </row>
     <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B33" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C33" s="170">
         <f>C32/C7</f>
@@ -21472,7 +21498,7 @@
     </row>
     <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C34" s="170">
         <f>C32/C8</f>
@@ -21509,14 +21535,14 @@
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="248" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C37" s="248"/>
       <c r="N37" s="93"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B38" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C38" s="64">
         <f>L7</f>
@@ -21525,16 +21551,16 @@
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B39" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C39" s="156">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>8.9231499999999991E-2</v>
+        <v>8.9249999999999996E-2</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B40" s="39" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C40" s="114">
         <v>25</v>
@@ -21542,7 +21568,7 @@
     </row>
     <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B41" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C41" s="24">
         <f>L18</f>
@@ -21551,7 +21577,7 @@
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B42" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C42" s="24">
         <f>(C38*C40)</f>
@@ -21560,11 +21586,11 @@
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B43" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C43" s="24">
         <f ca="1">C42/(1+C39)^5-G30+G31</f>
-        <v>8402806.5672710706</v>
+        <v>8402236.4851190597</v>
       </c>
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.2">
@@ -21578,22 +21604,22 @@
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B45" s="162" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C45" s="163">
         <f ca="1">C43/C44</f>
-        <v>16.086390610353249</v>
+        <v>16.085299241165604</v>
       </c>
     </row>
     <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B47" s="248" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C47" s="248"/>
     </row>
     <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B48" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C48" s="64">
         <f>L6</f>
@@ -21602,7 +21628,7 @@
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B49" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C49" s="156">
         <f>Overview!C29</f>
@@ -21611,7 +21637,7 @@
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B50" s="39" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C50" s="114">
         <v>5</v>
@@ -21619,7 +21645,7 @@
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B51" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C51" s="24">
         <f>L18</f>
@@ -21628,7 +21654,7 @@
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B52" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C52" s="24">
         <f>(C48*C50)/C51</f>
@@ -21637,7 +21663,7 @@
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B53" s="162" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C53" s="163">
         <f>C52/(1+C49)^5</f>
@@ -21646,13 +21672,13 @@
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B55" s="248" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C55" s="248"/>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B56" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C56" s="64">
         <f>L8</f>
@@ -21661,16 +21687,16 @@
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B57" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C57" s="156">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>8.9231499999999991E-2</v>
+        <v>8.9249999999999996E-2</v>
       </c>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B58" s="39" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C58" s="114">
         <v>30</v>
@@ -21678,7 +21704,7 @@
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B59" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C59" s="24">
         <f>(C56*C58)</f>
@@ -21687,11 +21713,11 @@
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B60" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C60" s="24">
         <f ca="1">C59/(1+C57)^5-G30+G31</f>
-        <v>5585106.3710780963</v>
+        <v>5584775.5622011703</v>
       </c>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.2">
@@ -21705,11 +21731,11 @@
     </row>
     <row r="62" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B62" s="162" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C62" s="163">
         <f ca="1">C60/C61</f>
-        <v>10.692166000283517</v>
+        <v>10.691532697497239</v>
       </c>
     </row>
   </sheetData>
@@ -21751,7 +21777,7 @@
     <row r="1" spans="1:14" s="85" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4"/>
       <c r="B1" s="84" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
@@ -21762,32 +21788,32 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B4" s="248" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C4" s="248"/>
       <c r="N4" s="93"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C5" s="154">
         <f ca="1">DCF!C26</f>
-        <v>6.883608684038804</v>
+        <v>6.8822824136162613</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C6" s="154">
         <f ca="1">Multiples!C45</f>
-        <v>16.086390610353249</v>
+        <v>16.085299241165604</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B7" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C7" s="154">
         <f>Multiples!C53</f>
@@ -21796,38 +21822,38 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B8" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C8" s="154">
         <f ca="1">Multiples!C62</f>
-        <v>10.692166000283517</v>
+        <v>10.691532697497239</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B9" s="162" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C9" s="163">
         <f ca="1">AVERAGE(C5:C8)</f>
-        <v>11.913914712802143</v>
+        <v>11.913151977203025</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B10" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C10" s="154">
         <f ca="1">Overview!C5</f>
-        <v>10.75</v>
+        <v>10.5725</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B11" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C11" s="175">
         <f ca="1">(C9-C10)/C10</f>
-        <v>0.10827113607461793</v>
+        <v>0.12680557835923628</v>
       </c>
     </row>
   </sheetData>
@@ -21883,7 +21909,7 @@
     <row r="1" spans="1:28" s="85" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4"/>
       <c r="B1" s="84" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="2" spans="1:28" s="85" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -21924,7 +21950,7 @@
       <c r="A5" s="88"/>
       <c r="B5" s="60"/>
       <c r="C5" s="257" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D5" s="257"/>
       <c r="E5" s="257"/>
@@ -22008,7 +22034,7 @@
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B7" s="39" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C7" s="133">
         <f>'FCF &amp; Other'!C28</f>
@@ -22066,7 +22092,7 @@
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B8" s="39" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C8" s="158"/>
       <c r="D8" s="158"/>
@@ -22079,7 +22105,7 @@
       <c r="K8" s="158"/>
       <c r="L8" s="147">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>6074350.1325263809</v>
+        <v>6072727.3819494601</v>
       </c>
       <c r="N8" s="93"/>
       <c r="O8" s="16"/>
@@ -22098,7 +22124,7 @@
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B9" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C9" s="158"/>
       <c r="D9" s="158"/>
@@ -22124,7 +22150,7 @@
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B10" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C10" s="158"/>
       <c r="D10" s="158"/>
@@ -22133,29 +22159,29 @@
       <c r="G10" s="159"/>
       <c r="H10" s="147">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>16158.181249807778</v>
+        <v>16157.906816616938</v>
       </c>
       <c r="I10" s="147">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>32635.852662704958</v>
+        <v>32634.744086809515</v>
       </c>
       <c r="J10" s="147">
         <f t="shared" ca="1" si="1"/>
-        <v>65917.002820751062</v>
+        <v>65913.644242351103</v>
       </c>
       <c r="K10" s="147">
         <f t="shared" ca="1" si="1"/>
-        <v>133137.3598777233</v>
+        <v>133128.31520144359</v>
       </c>
       <c r="L10" s="147">
         <f t="shared" ca="1" si="1"/>
-        <v>268907.19900314242</v>
+        <v>268884.36395976669</v>
       </c>
       <c r="N10" s="93"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B11" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C11" s="158"/>
       <c r="D11" s="158"/>
@@ -22168,43 +22194,43 @@
       <c r="K11" s="158"/>
       <c r="L11" s="147">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>3961857.5790385203</v>
+        <v>3960462.8337756256</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="263" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C14" s="264"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="176" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C15" s="177">
         <f ca="1">Overview!C5</f>
-        <v>10.75</v>
+        <v>10.5725</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B16" s="176" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C16" s="177">
         <f ca="1">C36</f>
-        <v>11.376414340767214</v>
+        <v>11.373651730160741</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B17" s="178" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C17" s="179">
         <v>1.2</v>
       </c>
       <c r="E17" s="265" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F17" s="265"/>
       <c r="G17" s="265"/>
@@ -22214,13 +22240,13 @@
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B19" s="263" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C19" s="264"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="180" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C20" s="181">
         <v>0.02</v>
@@ -22228,11 +22254,11 @@
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B21" s="180" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C21" s="245">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>8.9231499999999991E-2</v>
+        <v>8.9249999999999996E-2</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -22246,16 +22272,16 @@
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B23" s="180" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C23" s="182">
         <f ca="1">C15*C22</f>
-        <v>5569800.75</v>
+        <v>5477834.2725</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B24" s="180" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C24" s="246">
         <f>Statement!AC107</f>
@@ -22264,7 +22290,7 @@
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B25" s="180" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C25" s="246">
         <f>Statement!AC108</f>
@@ -22273,50 +22299,50 @@
     </row>
     <row r="26" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B26" s="178" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C26" s="183">
         <f ca="1">C23+C25-C24</f>
-        <v>4154054.75</v>
+        <v>4062088.2725</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B28" s="263" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C28" s="264"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="180" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C29" s="182">
         <f ca="1">SUM(H10:L10)</f>
-        <v>516755.5956141295</v>
+        <v>516718.97430698783</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B30" s="180" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C30" s="182">
         <f ca="1">L11</f>
-        <v>3961857.5790385203</v>
+        <v>3960462.8337756256</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B31" s="184" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C31" s="185">
         <f ca="1">C29+C30</f>
-        <v>4478613.17465265</v>
+        <v>4477181.8080826132</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B32" s="180" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C32" s="186">
         <f>C24</f>
@@ -22325,7 +22351,7 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="180" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C33" s="186">
         <f>C25</f>
@@ -22334,11 +22360,11 @@
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="184" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C34" s="185">
         <f ca="1">C31+C32-C33</f>
-        <v>5894359.17465265</v>
+        <v>5892927.8080826132</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -22352,16 +22378,16 @@
     </row>
     <row r="36" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B36" s="187" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C36" s="188">
         <f ca="1">C34/C35</f>
-        <v>11.376414340767214</v>
+        <v>11.373651730160741</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C39" s="257" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D39" s="257"/>
       <c r="E39" s="257"/>
@@ -22417,7 +22443,7 @@
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="39" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C41" s="133">
         <f>C7</f>
@@ -22507,7 +22533,7 @@
     </row>
     <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B43" s="143" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C43" s="97">
         <f>C41/C42</f>
@@ -22592,7 +22618,7 @@
     </row>
     <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B45" s="143" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C45" s="97">
         <f>C41/C44</f>
@@ -22632,7 +22658,7 @@
     </row>
     <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B46" s="143" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C46" s="158"/>
       <c r="D46" s="97">
@@ -22674,7 +22700,7 @@
     </row>
     <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B47" s="143" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C47" s="158"/>
       <c r="D47" s="97">
@@ -22716,7 +22742,7 @@
     </row>
     <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B48" s="143" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C48" s="158"/>
       <c r="D48" s="97">
@@ -22758,7 +22784,7 @@
     </row>
     <row r="49" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B49" s="143" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C49" s="97">
         <f>C42/C44</f>
@@ -22897,7 +22923,7 @@
         <v>86</v>
       </c>
       <c r="AA2" s="10" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AB2" s="7"/>
       <c r="AD2" s="7"/>
@@ -22947,7 +22973,7 @@
         <v>91</v>
       </c>
       <c r="AA3" s="10" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AB3" s="11"/>
       <c r="AC3" s="59" t="s">
@@ -23775,7 +23801,7 @@
     </row>
     <row r="17" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B17" s="23" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C17" s="21"/>
       <c r="D17" s="21"/>
@@ -24827,7 +24853,7 @@
     </row>
     <row r="34" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B34" s="20" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C34" s="21"/>
       <c r="D34" s="21"/>
@@ -25142,7 +25168,7 @@
     </row>
     <row r="39" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B39" s="20" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C39" s="21"/>
       <c r="D39" s="21"/>
@@ -25264,7 +25290,7 @@
     </row>
     <row r="41" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B41" s="20" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C41" s="21"/>
       <c r="D41" s="21"/>
@@ -25521,7 +25547,7 @@
     </row>
     <row r="45" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B45" s="20" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C45" s="21"/>
       <c r="D45" s="21"/>
@@ -25637,7 +25663,7 @@
     </row>
     <row r="47" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B47" s="20" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C47" s="21"/>
       <c r="D47" s="21"/>
@@ -25695,7 +25721,7 @@
     </row>
     <row r="48" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B48" s="20" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C48" s="21"/>
       <c r="D48" s="21"/>
@@ -26533,7 +26559,7 @@
     </row>
     <row r="64" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B64" s="20" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C64" s="62"/>
       <c r="D64" s="62"/>
@@ -26591,7 +26617,7 @@
     </row>
     <row r="65" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B65" s="20" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C65" s="62"/>
       <c r="D65" s="62"/>
@@ -27203,7 +27229,7 @@
     </row>
     <row r="76" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B76" s="20" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C76" s="25"/>
       <c r="D76" s="25"/>
@@ -27261,7 +27287,7 @@
     </row>
     <row r="77" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B77" s="20" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C77" s="25"/>
       <c r="D77" s="25"/>
@@ -27332,7 +27358,7 @@
     </row>
     <row r="78" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B78" s="20" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C78" s="25"/>
       <c r="D78" s="25"/>
@@ -27403,7 +27429,7 @@
     </row>
     <row r="79" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B79" s="20" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C79" s="25"/>
       <c r="D79" s="25"/>
@@ -27450,7 +27476,7 @@
     </row>
     <row r="80" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B80" s="20" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C80" s="25"/>
       <c r="D80" s="25"/>
@@ -27854,96 +27880,63 @@
       <c r="K89" s="48"/>
       <c r="L89" s="48"/>
       <c r="M89" s="48">
-        <f>IF(L5=0,
+        <f t="shared" ref="M89:Q96" si="60">IF(L5=0,
 IF(M5=0,0,IF(M5&gt;0,1,-1)),
 (M5-L5)/ABS(L5)
 )</f>
         <v>1</v>
       </c>
       <c r="N89" s="48">
-        <f>IF(M5=0,
-IF(N5=0,0,IF(N5&gt;0,1,-1)),
-(N5-M5)/ABS(M5)
-)</f>
+        <f t="shared" si="60"/>
         <v>0.18641482451146088</v>
       </c>
       <c r="O89" s="48">
-        <f>IF(N5=0,
-IF(O5=0,0,IF(O5&gt;0,1,-1)),
-(O5-N5)/ABS(N5)
-)</f>
+        <f t="shared" si="60"/>
         <v>0.23568437370404344</v>
       </c>
       <c r="P89" s="48">
-        <f>IF(O5=0,
-IF(P5=0,0,IF(P5&gt;0,1,-1)),
-(P5-O5)/ABS(O5)
-)</f>
+        <f t="shared" si="60"/>
         <v>9.2955127852289474E-2</v>
       </c>
       <c r="Q89" s="48">
-        <f>IF(P5=0,
-IF(Q5=0,0,IF(Q5&gt;0,1,-1)),
-(Q5-P5)/ABS(P5)
-)</f>
+        <f t="shared" si="60"/>
         <v>0.12653882310808692</v>
       </c>
       <c r="R89" s="1"/>
       <c r="S89" s="1"/>
       <c r="T89" s="48">
-        <f>IF(S5=0,
+        <f t="shared" ref="T89:AA96" si="61">IF(S5=0,
 IF(T5=0,0,IF(T5&gt;0,1,-1)),
 (T5-S5)/ABS(S5)
 )</f>
         <v>1</v>
       </c>
       <c r="U89" s="48">
-        <f>IF(T5=0,
-IF(U5=0,0,IF(U5&gt;0,1,-1)),
-(U5-T5)/ABS(T5)
-)</f>
+        <f t="shared" si="61"/>
         <v>0.12142177307408941</v>
       </c>
       <c r="V89" s="48">
-        <f>IF(U5=0,
-IF(V5=0,0,IF(V5&gt;0,1,-1)),
-(V5-U5)/ABS(U5)
-)</f>
+        <f t="shared" si="61"/>
         <v>0.1945366315807282</v>
       </c>
       <c r="W89" s="48">
-        <f>IF(V5=0,
-IF(W5=0,0,IF(W5&gt;0,1,-1)),
-(W5-V5)/ABS(V5)
-)</f>
+        <f t="shared" si="61"/>
         <v>-0.15820283916288599</v>
       </c>
       <c r="X89" s="48">
-        <f>IF(W5=0,
-IF(X5=0,0,IF(X5&gt;0,1,-1)),
-(X5-W5)/ABS(W5)
-)</f>
+        <f t="shared" si="61"/>
         <v>1.4311992462649737E-2</v>
       </c>
       <c r="Y89" s="48">
-        <f>IF(X5=0,
-IF(Y5=0,0,IF(Y5&gt;0,1,-1)),
-(Y5-X5)/ABS(X5)
-)</f>
+        <f t="shared" si="61"/>
         <v>0.13652523443029016</v>
       </c>
       <c r="Z89" s="48">
-        <f>IF(Y5=0,
-IF(Z5=0,0,IF(Z5&gt;0,1,-1)),
-(Z5-Y5)/ABS(Y5)
-)</f>
+        <f t="shared" si="61"/>
         <v>0.17025489342346264</v>
       </c>
       <c r="AA89" s="48">
-        <f>IF(Z5=0,
-IF(AA5=0,0,IF(AA5&gt;0,1,-1)),
-(AA5-Z5)/ABS(Z5)
-)</f>
+        <f t="shared" si="61"/>
         <v>-0.13037640275448081</v>
       </c>
       <c r="AB89" s="1"/>
@@ -27966,94 +27959,55 @@
       <c r="K90" s="50"/>
       <c r="L90" s="50"/>
       <c r="M90" s="50">
-        <f>IF(L6=0,
-IF(M6=0,0,IF(M6&gt;0,1,-1)),
-(M6-L6)/ABS(L6)
-)</f>
+        <f t="shared" si="60"/>
         <v>1</v>
       </c>
       <c r="N90" s="50">
-        <f>IF(M6=0,
-IF(N6=0,0,IF(N6&gt;0,1,-1)),
-(N6-M6)/ABS(M6)
-)</f>
+        <f t="shared" si="60"/>
         <v>6.6223322358291689E-2</v>
       </c>
       <c r="O90" s="50">
-        <f>IF(N6=0,
-IF(O6=0,0,IF(O6&gt;0,1,-1)),
-(O6-N6)/ABS(N6)
-)</f>
+        <f t="shared" si="60"/>
         <v>8.8158355132712404E-2</v>
       </c>
       <c r="P90" s="50">
-        <f>IF(O6=0,
-IF(P6=0,0,IF(P6&gt;0,1,-1)),
-(P6-O6)/ABS(O6)
-)</f>
+        <f t="shared" si="60"/>
         <v>0.26039688858945303</v>
       </c>
       <c r="Q90" s="50">
-        <f>IF(P6=0,
-IF(Q6=0,0,IF(Q6&gt;0,1,-1)),
-(Q6-P6)/ABS(P6)
-)</f>
+        <f t="shared" si="60"/>
         <v>9.7358893991301598E-2</v>
       </c>
       <c r="T90" s="50">
-        <f>IF(S6=0,
-IF(T6=0,0,IF(T6&gt;0,1,-1)),
-(T6-S6)/ABS(S6)
-)</f>
+        <f t="shared" si="61"/>
         <v>1</v>
       </c>
       <c r="U90" s="50">
-        <f>IF(T6=0,
-IF(U6=0,0,IF(U6&gt;0,1,-1)),
-(U6-T6)/ABS(T6)
-)</f>
+        <f t="shared" si="61"/>
         <v>6.9962097283638664E-3</v>
       </c>
       <c r="V90" s="50">
-        <f>IF(U6=0,
-IF(V6=0,0,IF(V6&gt;0,1,-1)),
-(V6-U6)/ABS(U6)
-)</f>
+        <f t="shared" si="61"/>
         <v>1.2091651898436397E-2</v>
       </c>
       <c r="W90" s="50">
-        <f>IF(V6=0,
-IF(W6=0,0,IF(W6&gt;0,1,-1)),
-(W6-V6)/ABS(V6)
-)</f>
+        <f t="shared" si="61"/>
         <v>-1.0490594105432795E-2</v>
       </c>
       <c r="X90" s="50">
-        <f>IF(W6=0,
-IF(X6=0,0,IF(X6&gt;0,1,-1)),
-(X6-W6)/ABS(W6)
-)</f>
+        <f t="shared" si="61"/>
         <v>8.1901749220915487E-3</v>
       </c>
       <c r="Y90" s="50">
-        <f>IF(X6=0,
-IF(Y6=0,0,IF(Y6&gt;0,1,-1)),
-(Y6-X6)/ABS(X6)
-)</f>
+        <f t="shared" si="61"/>
         <v>6.8841255048151598E-2</v>
       </c>
       <c r="Z90" s="50">
-        <f>IF(Y6=0,
-IF(Z6=0,0,IF(Z6&gt;0,1,-1)),
-(Z6-Y6)/ABS(Y6)
-)</f>
+        <f t="shared" si="61"/>
         <v>7.4449223972562928E-2</v>
       </c>
       <c r="AA90" s="50">
-        <f>IF(Z6=0,
-IF(AA6=0,0,IF(AA6&gt;0,1,-1)),
-(AA6-Z6)/ABS(Z6)
-)</f>
+        <f t="shared" si="61"/>
         <v>4.0481504023804696E-2</v>
       </c>
       <c r="AC90" s="68"/>
@@ -28074,96 +28028,57 @@
       <c r="K91" s="48"/>
       <c r="L91" s="48"/>
       <c r="M91" s="48">
-        <f>IF(L7=0,
-IF(M7=0,0,IF(M7&gt;0,1,-1)),
-(M7-L7)/ABS(L7)
-)</f>
+        <f t="shared" si="60"/>
         <v>1</v>
       </c>
       <c r="N91" s="48">
-        <f>IF(M7=0,
-IF(N7=0,0,IF(N7&gt;0,1,-1)),
-(N7-M7)/ABS(M7)
-)</f>
+        <f t="shared" si="60"/>
         <v>0.21447253464273469</v>
       </c>
       <c r="O91" s="48">
-        <f>IF(N7=0,
-IF(O7=0,0,IF(O7&gt;0,1,-1)),
-(O7-N7)/ABS(N7)
-)</f>
+        <f t="shared" si="60"/>
         <v>0.26591920594629664</v>
       </c>
       <c r="P91" s="48">
-        <f>IF(O7=0,
-IF(P7=0,0,IF(P7&gt;0,1,-1)),
-(P7-O7)/ABS(O7)
-)</f>
+        <f t="shared" si="60"/>
         <v>6.3457381571517466E-2</v>
       </c>
       <c r="Q91" s="48">
-        <f>IF(P7=0,
-IF(Q7=0,0,IF(Q7&gt;0,1,-1)),
-(Q7-P7)/ABS(P7)
-)</f>
+        <f t="shared" si="60"/>
         <v>0.13263133686529885</v>
       </c>
       <c r="R91" s="1"/>
       <c r="S91" s="1"/>
       <c r="T91" s="48">
-        <f>IF(S7=0,
-IF(T7=0,0,IF(T7&gt;0,1,-1)),
-(T7-S7)/ABS(S7)
-)</f>
+        <f t="shared" si="61"/>
         <v>1</v>
       </c>
       <c r="U91" s="48">
-        <f>IF(T7=0,
-IF(U7=0,0,IF(U7&gt;0,1,-1)),
-(U7-T7)/ABS(T7)
-)</f>
+        <f t="shared" si="61"/>
         <v>0.15006740915578434</v>
       </c>
       <c r="V91" s="48">
-        <f>IF(U7=0,
-IF(V7=0,0,IF(V7&gt;0,1,-1)),
-(V7-U7)/ABS(U7)
-)</f>
+        <f t="shared" si="61"/>
         <v>0.23452851593385815</v>
       </c>
       <c r="W91" s="48">
-        <f>IF(V7=0,
-IF(W7=0,0,IF(W7&gt;0,1,-1)),
-(W7-V7)/ABS(V7)
-)</f>
+        <f t="shared" si="61"/>
         <v>-0.18474737686292855</v>
       </c>
       <c r="X91" s="48">
-        <f>IF(W7=0,
-IF(X7=0,0,IF(X7&gt;0,1,-1)),
-(X7-W7)/ABS(W7)
-)</f>
+        <f t="shared" si="61"/>
         <v>1.5647255325907633E-2</v>
       </c>
       <c r="Y91" s="48">
-        <f>IF(X7=0,
-IF(Y7=0,0,IF(Y7&gt;0,1,-1)),
-(Y7-X7)/ABS(X7)
-)</f>
+        <f t="shared" si="61"/>
         <v>0.15117976243324321</v>
       </c>
       <c r="Z91" s="48">
-        <f>IF(Y7=0,
-IF(Z7=0,0,IF(Z7&gt;0,1,-1)),
-(Z7-Y7)/ABS(Y7)
-)</f>
+        <f t="shared" si="61"/>
         <v>0.18951449163163414</v>
       </c>
       <c r="AA91" s="48">
-        <f>IF(Z7=0,
-IF(AA7=0,0,IF(AA7&gt;0,1,-1)),
-(AA7-Z7)/ABS(Z7)
-)</f>
+        <f t="shared" si="61"/>
         <v>-0.1614010786596328</v>
       </c>
       <c r="AB91" s="1"/>
@@ -28186,94 +28101,55 @@
       <c r="K92" s="50"/>
       <c r="L92" s="50"/>
       <c r="M92" s="50">
-        <f>IF(L8=0,
-IF(M8=0,0,IF(M8&gt;0,1,-1)),
-(M8-L8)/ABS(L8)
-)</f>
+        <f t="shared" si="60"/>
         <v>1</v>
       </c>
       <c r="N92" s="50">
-        <f>IF(M8=0,
-IF(N8=0,0,IF(N8&gt;0,1,-1)),
-(N8-M8)/ABS(M8)
-)</f>
+        <f t="shared" si="60"/>
         <v>5.5555396298026891E-3</v>
       </c>
       <c r="O92" s="50">
-        <f>IF(N8=0,
-IF(O8=0,0,IF(O8&gt;0,1,-1)),
-(O8-N8)/ABS(N8)
-)</f>
+        <f t="shared" si="60"/>
         <v>1.6494716046285551E-2</v>
       </c>
       <c r="P92" s="50">
-        <f>IF(O8=0,
-IF(P8=0,0,IF(P8&gt;0,1,-1)),
-(P8-O8)/ABS(O8)
-)</f>
+        <f t="shared" si="60"/>
         <v>3.55657453760184E-2</v>
       </c>
       <c r="Q92" s="50">
-        <f>IF(P8=0,
-IF(Q8=0,0,IF(Q8&gt;0,1,-1)),
-(Q8-P8)/ABS(P8)
-)</f>
+        <f t="shared" si="60"/>
         <v>-7.4698067551080383E-2</v>
       </c>
       <c r="T92" s="50">
-        <f>IF(S8=0,
-IF(T8=0,0,IF(T8&gt;0,1,-1)),
-(T8-S8)/ABS(S8)
-)</f>
+        <f t="shared" si="61"/>
         <v>1</v>
       </c>
       <c r="U92" s="50">
-        <f>IF(T8=0,
-IF(U8=0,0,IF(U8&gt;0,1,-1)),
-(U8-T8)/ABS(T8)
-)</f>
+        <f t="shared" si="61"/>
         <v>-3.6751916842484432E-2</v>
       </c>
       <c r="V92" s="50">
-        <f>IF(U8=0,
-IF(V8=0,0,IF(V8&gt;0,1,-1)),
-(V8-U8)/ABS(U8)
-)</f>
+        <f t="shared" si="61"/>
         <v>-5.5302690343398082E-2</v>
       </c>
       <c r="W92" s="50">
-        <f>IF(V8=0,
-IF(W8=0,0,IF(W8&gt;0,1,-1)),
-(W8-V8)/ABS(V8)
-)</f>
+        <f t="shared" si="61"/>
         <v>-9.7123888800922889E-2</v>
       </c>
       <c r="X92" s="50">
-        <f>IF(W8=0,
-IF(X8=0,0,IF(X8&gt;0,1,-1)),
-(X8-W8)/ABS(W8)
-)</f>
+        <f t="shared" si="61"/>
         <v>4.1600641358879129E-2</v>
       </c>
       <c r="Y92" s="50">
-        <f>IF(X8=0,
-IF(Y8=0,0,IF(Y8&gt;0,1,-1)),
-(Y8-X8)/ABS(X8)
-)</f>
+        <f t="shared" si="61"/>
         <v>7.746703306615034E-2</v>
       </c>
       <c r="Z92" s="50">
-        <f>IF(Y8=0,
-IF(Z8=0,0,IF(Z8&gt;0,1,-1)),
-(Z8-Y8)/ABS(Y8)
-)</f>
+        <f t="shared" si="61"/>
         <v>-5.6198586943176365E-3</v>
       </c>
       <c r="AA92" s="50">
-        <f>IF(Z8=0,
-IF(AA8=0,0,IF(AA8&gt;0,1,-1)),
-(AA8-Z8)/ABS(Z8)
-)</f>
+        <f t="shared" si="61"/>
         <v>-5.7919283417237719E-2</v>
       </c>
       <c r="AC92" s="68"/>
@@ -28293,94 +28169,55 @@
       <c r="K93" s="50"/>
       <c r="L93" s="50"/>
       <c r="M93" s="50">
-        <f>IF(L9=0,
-IF(M9=0,0,IF(M9&gt;0,1,-1)),
-(M9-L9)/ABS(L9)
-)</f>
+        <f t="shared" si="60"/>
         <v>1</v>
       </c>
       <c r="N93" s="50">
-        <f>IF(M9=0,
-IF(N9=0,0,IF(N9&gt;0,1,-1)),
-(N9-M9)/ABS(M9)
-)</f>
+        <f t="shared" si="60"/>
         <v>3.2867413439746689E-2</v>
       </c>
       <c r="O93" s="50">
-        <f>IF(N9=0,
-IF(O9=0,0,IF(O9&gt;0,1,-1)),
-(O9-N9)/ABS(N9)
-)</f>
+        <f t="shared" si="60"/>
         <v>0.16220822397200349</v>
       </c>
       <c r="P93" s="50">
-        <f>IF(O9=0,
-IF(P9=0,0,IF(P9&gt;0,1,-1)),
-(P9-O9)/ABS(O9)
-)</f>
+        <f t="shared" si="60"/>
         <v>0.14628381125019196</v>
       </c>
       <c r="Q93" s="50">
-        <f>IF(P9=0,
-IF(Q9=0,0,IF(Q9&gt;0,1,-1)),
-(Q9-P9)/ABS(P9)
-)</f>
+        <f t="shared" si="60"/>
         <v>1.1889188351432428E-2</v>
       </c>
       <c r="T93" s="50">
-        <f>IF(S9=0,
-IF(T9=0,0,IF(T9&gt;0,1,-1)),
-(T9-S9)/ABS(S9)
-)</f>
+        <f t="shared" si="61"/>
         <v>1</v>
       </c>
       <c r="U93" s="50">
-        <f>IF(T9=0,
-IF(U9=0,0,IF(U9&gt;0,1,-1)),
-(U9-T9)/ABS(T9)
-)</f>
+        <f t="shared" si="61"/>
         <v>-1.4801946501681347E-2</v>
       </c>
       <c r="V93" s="50">
-        <f>IF(U9=0,
-IF(V9=0,0,IF(V9&gt;0,1,-1)),
-(V9-U9)/ABS(U9)
-)</f>
+        <f t="shared" si="61"/>
         <v>2.7780069295495792E-2</v>
       </c>
       <c r="W93" s="50">
-        <f>IF(V9=0,
-IF(W9=0,0,IF(W9&gt;0,1,-1)),
-(W9-V9)/ABS(V9)
-)</f>
+        <f t="shared" si="61"/>
         <v>-4.8469950837764626E-2</v>
       </c>
       <c r="X93" s="50">
-        <f>IF(W9=0,
-IF(X9=0,0,IF(X9&gt;0,1,-1)),
-(X9-W9)/ABS(W9)
-)</f>
+        <f t="shared" si="61"/>
         <v>3.6925737302164724E-2</v>
       </c>
       <c r="Y93" s="50">
-        <f>IF(X9=0,
-IF(Y9=0,0,IF(Y9&gt;0,1,-1)),
-(Y9-X9)/ABS(X9)
-)</f>
+        <f t="shared" si="61"/>
         <v>-1.4968324503513285E-2</v>
       </c>
       <c r="Z93" s="50">
-        <f>IF(Y9=0,
-IF(Z9=0,0,IF(Z9&gt;0,1,-1)),
-(Z9-Y9)/ABS(Y9)
-)</f>
+        <f t="shared" si="61"/>
         <v>-1.7652706232127925E-2</v>
       </c>
       <c r="AA93" s="50">
-        <f>IF(Z9=0,
-IF(AA9=0,0,IF(AA9&gt;0,1,-1)),
-(AA9-Z9)/ABS(Z9)
-)</f>
+        <f t="shared" si="61"/>
         <v>-2.371819796340861E-2</v>
       </c>
       <c r="AC93" s="68"/>
@@ -28400,94 +28237,55 @@
       <c r="K94" s="50"/>
       <c r="L94" s="50"/>
       <c r="M94" s="50">
-        <f>IF(L10=0,
-IF(M10=0,0,IF(M10&gt;0,1,-1)),
-(M10-L10)/ABS(L10)
-)</f>
+        <f t="shared" si="60"/>
         <v>1</v>
       </c>
       <c r="N94" s="50">
-        <f>IF(M10=0,
-IF(N10=0,0,IF(N10&gt;0,1,-1)),
-(N10-M10)/ABS(M10)
-)</f>
+        <f t="shared" si="60"/>
         <v>-4.1945510038361382E-2</v>
       </c>
       <c r="O94" s="50">
-        <f>IF(N10=0,
-IF(O10=0,0,IF(O10&gt;0,1,-1)),
-(O10-N10)/ABS(N10)
-)</f>
+        <f t="shared" si="60"/>
         <v>-3.2851088703784892E-2</v>
       </c>
       <c r="P94" s="50">
-        <f>IF(O10=0,
-IF(P10=0,0,IF(P10&gt;0,1,-1)),
-(P10-O10)/ABS(O10)
-)</f>
+        <f t="shared" si="60"/>
         <v>-2.383470689052267E-2</v>
       </c>
       <c r="Q94" s="50">
-        <f>IF(P10=0,
-IF(Q10=0,0,IF(Q10&gt;0,1,-1)),
-(Q10-P10)/ABS(P10)
-)</f>
+        <f t="shared" si="60"/>
         <v>-5.2296166569371472E-2</v>
       </c>
       <c r="T94" s="50">
-        <f>IF(S10=0,
-IF(T10=0,0,IF(T10&gt;0,1,-1)),
-(T10-S10)/ABS(S10)
-)</f>
+        <f t="shared" si="61"/>
         <v>1</v>
       </c>
       <c r="U94" s="50">
-        <f>IF(T10=0,
-IF(U10=0,0,IF(U10&gt;0,1,-1)),
-(U10-T10)/ABS(T10)
-)</f>
+        <f t="shared" si="61"/>
         <v>-0.21141705631385885</v>
       </c>
       <c r="V94" s="50">
-        <f>IF(U10=0,
-IF(V10=0,0,IF(V10&gt;0,1,-1)),
-(V10-U10)/ABS(U10)
-)</f>
+        <f t="shared" si="61"/>
         <v>-2.1820722699141544E-2</v>
       </c>
       <c r="W94" s="50">
-        <f>IF(V10=0,
-IF(W10=0,0,IF(W10&gt;0,1,-1)),
-(W10-V10)/ABS(V10)
-)</f>
+        <f t="shared" si="61"/>
         <v>0.11596628365001939</v>
       </c>
       <c r="X94" s="50">
-        <f>IF(W10=0,
-IF(X10=0,0,IF(X10&gt;0,1,-1)),
-(X10-W10)/ABS(W10)
-)</f>
+        <f t="shared" si="61"/>
         <v>-3.2736516761462352E-2</v>
       </c>
       <c r="Y94" s="50">
-        <f>IF(X10=0,
-IF(Y10=0,0,IF(Y10&gt;0,1,-1)),
-(Y10-X10)/ABS(X10)
-)</f>
+        <f t="shared" si="61"/>
         <v>5.407551664807427E-3</v>
       </c>
       <c r="Z94" s="50">
-        <f>IF(Y10=0,
-IF(Z10=0,0,IF(Z10&gt;0,1,-1)),
-(Z10-Y10)/ABS(Y10)
-)</f>
+        <f t="shared" si="61"/>
         <v>7.014574518100611E-3</v>
       </c>
       <c r="AA94" s="50">
-        <f>IF(Z10=0,
-IF(AA10=0,0,IF(AA10&gt;0,1,-1)),
-(AA10-Z10)/ABS(Z10)
-)</f>
+        <f t="shared" si="61"/>
         <v>-1.5724210054530514E-2</v>
       </c>
       <c r="AC94" s="68"/>
@@ -28507,94 +28305,55 @@
       <c r="K95" s="50"/>
       <c r="L95" s="50"/>
       <c r="M95" s="50">
-        <f>IF(L11=0,
-IF(M11=0,0,IF(M11&gt;0,1,-1)),
-(M11-L11)/ABS(L11)
-)</f>
+        <f t="shared" si="60"/>
         <v>1</v>
       </c>
       <c r="N95" s="50">
-        <f>IF(M11=0,
-IF(N11=0,0,IF(N11&gt;0,1,-1)),
-(N11-M11)/ABS(M11)
-)</f>
+        <f t="shared" si="60"/>
         <v>2.0280479935964979E-3</v>
       </c>
       <c r="O95" s="50">
-        <f>IF(N11=0,
-IF(O11=0,0,IF(O11&gt;0,1,-1)),
-(O11-N11)/ABS(N11)
-)</f>
+        <f t="shared" si="60"/>
         <v>4.080083924770931E-2</v>
       </c>
       <c r="P95" s="50">
-        <f>IF(O11=0,
-IF(P11=0,0,IF(P11&gt;0,1,-1)),
-(P11-O11)/ABS(O11)
-)</f>
+        <f t="shared" si="60"/>
         <v>5.3586588433573397E-2</v>
       </c>
       <c r="Q95" s="50">
-        <f>IF(P11=0,
-IF(Q11=0,0,IF(Q11&gt;0,1,-1)),
-(Q11-P11)/ABS(P11)
-)</f>
+        <f t="shared" si="60"/>
         <v>-4.6430846560335276E-2</v>
       </c>
       <c r="T95" s="50">
-        <f>IF(S11=0,
-IF(T11=0,0,IF(T11&gt;0,1,-1)),
-(T11-S11)/ABS(S11)
-)</f>
+        <f t="shared" si="61"/>
         <v>1</v>
       </c>
       <c r="U95" s="50">
-        <f>IF(T11=0,
-IF(U11=0,0,IF(U11&gt;0,1,-1)),
-(U11-T11)/ABS(T11)
-)</f>
+        <f t="shared" si="61"/>
         <v>-6.1827428834462586E-2</v>
       </c>
       <c r="V95" s="50">
-        <f>IF(U11=0,
-IF(V11=0,0,IF(V11&gt;0,1,-1)),
-(V11-U11)/ABS(U11)
-)</f>
+        <f t="shared" si="61"/>
         <v>-2.6180688937155576E-2</v>
       </c>
       <c r="W95" s="50">
-        <f>IF(V11=0,
-IF(W11=0,0,IF(W11&gt;0,1,-1)),
-(W11-V11)/ABS(V11)
-)</f>
+        <f t="shared" si="61"/>
         <v>-5.0150075421731902E-2</v>
       </c>
       <c r="X95" s="50">
-        <f>IF(W11=0,
-IF(X11=0,0,IF(X11&gt;0,1,-1)),
-(X11-W11)/ABS(W11)
-)</f>
+        <f t="shared" si="61"/>
         <v>2.7019946374106908E-2</v>
       </c>
       <c r="Y95" s="50">
-        <f>IF(X11=0,
-IF(Y11=0,0,IF(Y11&gt;0,1,-1)),
-(Y11-X11)/ABS(X11)
-)</f>
+        <f t="shared" si="61"/>
         <v>3.6837116142259228E-2</v>
       </c>
       <c r="Z95" s="50">
-        <f>IF(Y11=0,
-IF(Z11=0,0,IF(Z11&gt;0,1,-1)),
-(Z11-Y11)/ABS(Y11)
-)</f>
+        <f t="shared" si="61"/>
         <v>-7.119642802903745E-3</v>
       </c>
       <c r="AA95" s="50">
-        <f>IF(Z11=0,
-IF(AA11=0,0,IF(AA11&gt;0,1,-1)),
-(AA11-Z11)/ABS(Z11)
-)</f>
+        <f t="shared" si="61"/>
         <v>-4.1051008608505718E-2</v>
       </c>
       <c r="AC95" s="68"/>
@@ -28615,96 +28374,57 @@
       <c r="K96" s="48"/>
       <c r="L96" s="48"/>
       <c r="M96" s="48">
-        <f>IF(L12=0,
-IF(M12=0,0,IF(M12&gt;0,1,-1)),
-(M12-L12)/ABS(L12)
-)</f>
+        <f t="shared" si="60"/>
         <v>-1</v>
       </c>
       <c r="N96" s="48">
-        <f>IF(M12=0,
-IF(N12=0,0,IF(N12&gt;0,1,-1)),
-(N12-M12)/ABS(M12)
-)</f>
+        <f t="shared" si="60"/>
         <v>0.3047494141085067</v>
       </c>
       <c r="O96" s="48">
-        <f>IF(N12=0,
-IF(O12=0,0,IF(O12&gt;0,1,-1)),
-(O12-N12)/ABS(N12)
-)</f>
+        <f t="shared" si="60"/>
         <v>0.52705127726590162</v>
       </c>
       <c r="P96" s="48">
-        <f>IF(O12=0,
-IF(P12=0,0,IF(P12&gt;0,1,-1)),
-(P12-O12)/ABS(O12)
-)</f>
+        <f t="shared" si="60"/>
         <v>1.3058523555123847E-2</v>
       </c>
       <c r="Q96" s="48">
-        <f>IF(P12=0,
-IF(Q12=0,0,IF(Q12&gt;0,1,-1)),
-(Q12-P12)/ABS(P12)
-)</f>
+        <f t="shared" si="60"/>
         <v>1.3491440557547871</v>
       </c>
       <c r="R96" s="1"/>
       <c r="S96" s="1"/>
       <c r="T96" s="48">
-        <f>IF(S12=0,
-IF(T12=0,0,IF(T12&gt;0,1,-1)),
-(T12-S12)/ABS(S12)
-)</f>
+        <f t="shared" si="61"/>
         <v>-1</v>
       </c>
       <c r="U96" s="48">
-        <f>IF(T12=0,
-IF(U12=0,0,IF(U12&gt;0,1,-1)),
-(U12-T12)/ABS(T12)
-)</f>
+        <f t="shared" si="61"/>
         <v>0.58041200205130195</v>
       </c>
       <c r="V96" s="48">
-        <f>IF(U12=0,
-IF(V12=0,0,IF(V12&gt;0,1,-1)),
-(V12-U12)/ABS(U12)
-)</f>
+        <f t="shared" si="61"/>
         <v>1.7750438151462042</v>
       </c>
       <c r="W96" s="48">
-        <f>IF(V12=0,
-IF(W12=0,0,IF(W12&gt;0,1,-1)),
-(W12-V12)/ABS(V12)
-)</f>
+        <f t="shared" si="61"/>
         <v>-1.4883215805290249</v>
       </c>
       <c r="X96" s="48">
-        <f>IF(W12=0,
-IF(X12=0,0,IF(X12&gt;0,1,-1)),
-(X12-W12)/ABS(W12)
-)</f>
+        <f t="shared" si="61"/>
         <v>-0.22989276139410186</v>
       </c>
       <c r="Y96" s="48">
-        <f>IF(X12=0,
-IF(Y12=0,0,IF(Y12&gt;0,1,-1)),
-(Y12-X12)/ABS(X12)
-)</f>
+        <f t="shared" si="61"/>
         <v>1.6475600693584345</v>
       </c>
       <c r="Z96" s="48">
-        <f>IF(Y12=0,
-IF(Z12=0,0,IF(Z12&gt;0,1,-1)),
-(Z12-Y12)/ABS(Y12)
-)</f>
+        <f t="shared" si="61"/>
         <v>5.1422997475327064</v>
       </c>
       <c r="AA96" s="48">
-        <f>IF(Z12=0,
-IF(AA12=0,0,IF(AA12&gt;0,1,-1)),
-(AA12-Z12)/ABS(Z12)
-)</f>
+        <f t="shared" si="61"/>
         <v>-0.65140871384799337</v>
       </c>
       <c r="AB96" s="1"/>
@@ -28765,38 +28485,38 @@
       <c r="R97" s="1"/>
       <c r="S97" s="1"/>
       <c r="T97" s="52">
-        <f t="shared" ref="T97:AA97" si="60">IF(S15=0,
+        <f t="shared" ref="T97:AA97" si="62">IF(S15=0,
 IF(T15=0,0,IF(T15&gt;0,1,-1)),
 (T15-S15)/ABS(S15)
 )</f>
         <v>-1</v>
       </c>
       <c r="U97" s="52">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>0.69005336153350594</v>
       </c>
       <c r="V97" s="52">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>3.1422016549668617</v>
       </c>
       <c r="W97" s="52">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>-1.3611599297012302</v>
       </c>
       <c r="X97" s="52">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>1.1686435523114356</v>
       </c>
       <c r="Y97" s="52">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>6.3916441238352872</v>
       </c>
       <c r="Z97" s="52">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>2.7588240078074171</v>
       </c>
       <c r="AA97" s="52">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>-0.55680084814522324</v>
       </c>
       <c r="AB97" s="1"/>
@@ -28857,38 +28577,38 @@
       <c r="R98" s="1"/>
       <c r="S98" s="1"/>
       <c r="T98" s="52">
-        <f t="shared" ref="T98:AA98" si="61">IF(S18=0,
+        <f t="shared" ref="T98:AA98" si="63">IF(S18=0,
 IF(T18=0,0,IF(T18&gt;0,1,-1)),
 (T18-S18)/ABS(S18)
 )</f>
         <v>-1</v>
       </c>
       <c r="U98" s="52">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v>0.87624423615224689</v>
       </c>
       <c r="V98" s="52">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v>5.86100422336931</v>
       </c>
       <c r="W98" s="52">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v>-1.435475151561957</v>
       </c>
       <c r="X98" s="52">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v>1.0702283307470628</v>
       </c>
       <c r="Y98" s="52">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v>124.52967171717172</v>
       </c>
       <c r="Z98" s="52">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v>-0.47464028686525278</v>
       </c>
       <c r="AA98" s="52">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v>-0.78437135034749483</v>
       </c>
       <c r="AB98" s="1"/>
@@ -28945,35 +28665,35 @@
         <v>0.83174673345867178</v>
       </c>
       <c r="T101" s="50">
-        <f t="shared" ref="T101:AA101" si="62">T7/T5</f>
+        <f t="shared" ref="T101:AA101" si="64">T7/T5</f>
         <v>0.79978055544137128</v>
       </c>
       <c r="U101" s="50">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>0.82021017727186851</v>
       </c>
       <c r="V101" s="50">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>0.84766998862257636</v>
       </c>
       <c r="W101" s="50">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>0.82094026201265202</v>
       </c>
       <c r="X101" s="50">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>0.82202096602972397</v>
       </c>
       <c r="Y101" s="50">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>0.83262022850165285</v>
       </c>
       <c r="Z101" s="50">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>0.84632316719565504</v>
       </c>
       <c r="AA101" s="50">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>0.81612975701631518</v>
       </c>
       <c r="AC101" s="50">
@@ -29016,35 +28736,35 @@
         <v>3.5242137575966802E-2</v>
       </c>
       <c r="T102" s="50">
-        <f t="shared" ref="T102:AA102" si="63">T12/T5</f>
+        <f t="shared" ref="T102:AA102" si="65">T12/T5</f>
         <v>-0.32679215691234548</v>
       </c>
       <c r="U102" s="50">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v>-0.12227162888795527</v>
       </c>
       <c r="V102" s="50">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v>7.9332744791642082E-2</v>
       </c>
       <c r="W102" s="50">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v>-4.602045852214097E-2</v>
       </c>
       <c r="X102" s="50">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v>-5.5801596779900917E-2</v>
       </c>
       <c r="Y102" s="50">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v>3.1794178242964828E-2</v>
       </c>
       <c r="Z102" s="50">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v>0.16687763844633313</v>
       </c>
       <c r="AA102" s="50">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v>6.689341319655244E-2</v>
       </c>
       <c r="AC102" s="50">
@@ -29090,35 +28810,35 @@
       <c r="R103" s="1"/>
       <c r="S103" s="1"/>
       <c r="T103" s="55">
-        <f t="shared" ref="T103:AA103" si="64">T111/T5</f>
+        <f t="shared" ref="T103:AA103" si="66">T111/T5</f>
         <v>-0.27224089573853844</v>
       </c>
       <c r="U103" s="55">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v>-3.0043450922450959E-2</v>
       </c>
       <c r="V103" s="55">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v>0.12225773405154303</v>
       </c>
       <c r="W103" s="55">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v>-6.3245883619722734E-2</v>
       </c>
       <c r="X103" s="55">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v>4.3789808917197451E-3</v>
       </c>
       <c r="Y103" s="55">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v>0.48366021020984495</v>
       </c>
       <c r="Z103" s="55">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v>0.2171284142612766</v>
       </c>
       <c r="AA103" s="55">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v>5.3838358246769698E-2</v>
       </c>
       <c r="AB103" s="1"/>
@@ -29148,95 +28868,95 @@
         <v>74</v>
       </c>
       <c r="C106" s="81">
-        <f t="shared" ref="C106:Q106" si="65">IF(AND(C83&gt;=0,C12&gt;=0),C83,0)</f>
+        <f t="shared" ref="C106:Q106" si="67">IF(AND(C83&gt;=0,C12&gt;=0),C83,0)</f>
         <v>0</v>
       </c>
       <c r="D106" s="81">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="E106" s="81">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="F106" s="81">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="G106" s="81">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="H106" s="81">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="I106" s="81">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="J106" s="81">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="K106" s="81">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="L106" s="81">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="M106" s="81">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="N106" s="81">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="O106" s="81">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="P106" s="81">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="Q106" s="81">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="T106" s="81">
-        <f t="shared" ref="T106:AA106" si="66">IF(AND(T83&gt;=0,T12&gt;=0),T83,0)</f>
+        <f t="shared" ref="T106:AA106" si="68">IF(AND(T83&gt;=0,T12&gt;=0),T83,0)</f>
         <v>0</v>
       </c>
       <c r="U106" s="81">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="V106" s="81">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>5.1808728763913299E-2</v>
       </c>
       <c r="W106" s="81">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="X106" s="81">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="Y106" s="81">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="Z106" s="81">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="AA106" s="81">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>0.45018062878344073</v>
       </c>
       <c r="AC106" s="81">
@@ -29246,7 +28966,7 @@
     </row>
     <row r="107" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B107" s="20" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C107" s="25"/>
       <c r="D107" s="25"/>
@@ -29263,51 +28983,51 @@
         <v>1884663</v>
       </c>
       <c r="N107" s="25">
-        <f t="shared" ref="N107:Q107" si="67">N29+N34</f>
+        <f t="shared" ref="N107:Q107" si="69">N29+N34</f>
         <v>1759835</v>
       </c>
       <c r="O107" s="25">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v>1879823</v>
       </c>
       <c r="P107" s="25">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v>1723631</v>
       </c>
       <c r="Q107" s="25">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v>1689476</v>
       </c>
       <c r="T107" s="25">
-        <f t="shared" ref="T107:AA107" si="68">T29+T34</f>
+        <f t="shared" ref="T107:AA107" si="70">T29+T34</f>
         <v>1743374</v>
       </c>
       <c r="U107" s="25">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>1603438</v>
       </c>
       <c r="V107" s="25">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>1723631</v>
       </c>
       <c r="W107" s="25">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>1591500</v>
       </c>
       <c r="X107" s="25">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>1522638</v>
       </c>
       <c r="Y107" s="25">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>1519795</v>
       </c>
       <c r="Z107" s="25">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>1689476</v>
       </c>
       <c r="AA107" s="25">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>1415746</v>
       </c>
       <c r="AC107" s="25">
@@ -29317,7 +29037,7 @@
     </row>
     <row r="108" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B108" s="20" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C108" s="25">
         <v>0</v>
@@ -29370,35 +29090,35 @@
         <v>0</v>
       </c>
       <c r="T108" s="25">
-        <f t="shared" ref="T108:AA108" si="69">T39+T41</f>
+        <f t="shared" ref="T108:AA108" si="71">T39+T41</f>
         <v>0</v>
       </c>
       <c r="U108" s="25">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="V108" s="25">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="W108" s="25">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="X108" s="25">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="Y108" s="25">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="Z108" s="25">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="AA108" s="25">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="AC108" s="25">
@@ -29408,7 +29128,7 @@
     </row>
     <row r="109" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B109" s="20" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C109" s="25"/>
       <c r="D109" s="25"/>
@@ -29455,7 +29175,7 @@
     </row>
     <row r="110" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B110" s="20" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C110" s="25"/>
       <c r="D110" s="25"/>
@@ -29488,35 +29208,35 @@
         <v>-19048</v>
       </c>
       <c r="T110" s="147">
-        <f t="shared" ref="T110:AA110" si="70">T60+T61</f>
+        <f t="shared" ref="T110:AA110" si="72">T60+T61</f>
         <v>-1418</v>
       </c>
       <c r="U110" s="147">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v>-4875</v>
       </c>
       <c r="V110" s="147">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="W110" s="147">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v>-12832</v>
       </c>
       <c r="X110" s="147">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="Y110" s="147">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v>-3164</v>
       </c>
       <c r="Z110" s="147">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v>-3052</v>
       </c>
       <c r="AA110" s="147">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v>-2684</v>
       </c>
       <c r="AC110" s="147">
@@ -29526,7 +29246,7 @@
     </row>
     <row r="111" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B111" s="20" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C111" s="25"/>
       <c r="D111" s="25"/>
@@ -29559,35 +29279,35 @@
         <v>282330</v>
       </c>
       <c r="T111" s="147">
-        <f t="shared" ref="T111:AA111" si="71">T17+T18</f>
+        <f t="shared" ref="T111:AA111" si="73">T17+T18</f>
         <v>-86097</v>
       </c>
       <c r="U111" s="147">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>-10655</v>
       </c>
       <c r="V111" s="147">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>51794</v>
       </c>
       <c r="W111" s="147">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>-22555</v>
       </c>
       <c r="X111" s="147">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>1584</v>
       </c>
       <c r="Y111" s="147">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>198839</v>
       </c>
       <c r="Z111" s="147">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>104462</v>
       </c>
       <c r="AA111" s="147">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>22525</v>
       </c>
       <c r="AC111" s="147">
@@ -29597,7 +29317,7 @@
     </row>
     <row r="112" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B112" s="20" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C112" s="25"/>
       <c r="D112" s="25"/>
@@ -29630,35 +29350,35 @@
         <v>2082587</v>
       </c>
       <c r="T112" s="147">
-        <f t="shared" ref="T112:AA112" si="72">T49+T48</f>
+        <f t="shared" ref="T112:AA112" si="74">T49+T48</f>
         <v>1833581</v>
       </c>
       <c r="U112" s="147">
-        <f t="shared" si="72"/>
+        <f t="shared" si="74"/>
         <v>1731845</v>
       </c>
       <c r="V112" s="147">
-        <f t="shared" si="72"/>
+        <f t="shared" si="74"/>
         <v>1845762</v>
       </c>
       <c r="W112" s="147">
-        <f t="shared" si="72"/>
+        <f t="shared" si="74"/>
         <v>1698461</v>
       </c>
       <c r="X112" s="147">
-        <f t="shared" si="72"/>
+        <f t="shared" si="74"/>
         <v>1665703</v>
       </c>
       <c r="Y112" s="147">
-        <f t="shared" si="72"/>
+        <f t="shared" si="74"/>
         <v>1924617</v>
       </c>
       <c r="Z112" s="147">
-        <f t="shared" si="72"/>
+        <f t="shared" si="74"/>
         <v>2082587</v>
       </c>
       <c r="AA112" s="147">
-        <f t="shared" si="72"/>
+        <f t="shared" si="74"/>
         <v>1902965</v>
       </c>
       <c r="AC112" s="147">
@@ -29730,12 +29450,12 @@
       <c r="AA116" s="68"/>
       <c r="AC116" s="63">
         <f ca="1">Overview!C5</f>
-        <v>10.75</v>
+        <v>10.5725</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B117" s="20" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C117" s="26"/>
       <c r="D117" s="26"/>
@@ -29777,7 +29497,7 @@
       <c r="AA117" s="68"/>
       <c r="AC117" s="65">
         <f ca="1">AC116/AC85</f>
-        <v>10.75</v>
+        <v>10.5725</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -29891,19 +29611,19 @@
         <v>121</v>
       </c>
       <c r="M123" s="76">
-        <f t="shared" ref="M123:P123" si="73">M121*M122</f>
+        <f t="shared" ref="M123:P123" si="75">M121*M122</f>
         <v>-0.20431339773367801</v>
       </c>
       <c r="N123" s="76">
-        <f t="shared" si="73"/>
+        <f t="shared" si="75"/>
         <v>-0.12004653397221271</v>
       </c>
       <c r="O123" s="76">
-        <f t="shared" si="73"/>
+        <f t="shared" si="75"/>
         <v>-3.0419750111515053E-2</v>
       </c>
       <c r="P123" s="76">
-        <f t="shared" si="73"/>
+        <f t="shared" si="75"/>
         <v>-2.5719740199003933E-2</v>
       </c>
       <c r="Q123" s="76">
@@ -29965,19 +29685,19 @@
         <v>123</v>
       </c>
       <c r="M125" s="76">
-        <f t="shared" ref="M125:P125" si="74">M123*M124</f>
+        <f t="shared" ref="M125:P125" si="76">M123*M124</f>
         <v>-0.27346966596372269</v>
       </c>
       <c r="N125" s="76">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>-0.17100259457815453</v>
       </c>
       <c r="O125" s="76">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>-4.4582300405631825E-2</v>
       </c>
       <c r="P125" s="76">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>-3.9926057639067224E-2</v>
       </c>
       <c r="Q125" s="76">
@@ -30002,7 +29722,7 @@
     </row>
     <row r="128" spans="1:31" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B128" s="14" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C128" s="192"/>
       <c r="D128" s="192"/>
@@ -30031,7 +29751,7 @@
     </row>
     <row r="129" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B129" s="20" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C129" s="49"/>
       <c r="D129" s="49"/>
@@ -30076,7 +29796,7 @@
     </row>
     <row r="130" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B130" s="20" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C130" s="49"/>
       <c r="D130" s="49"/>
@@ -30121,7 +29841,7 @@
     </row>
     <row r="131" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B131" s="20" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C131" s="49"/>
       <c r="D131" s="49"/>
@@ -30139,42 +29859,42 @@
       <c r="P131" s="49"/>
       <c r="Q131" s="49"/>
       <c r="T131" s="25">
-        <f t="shared" ref="T131:AA131" si="75">U5</f>
+        <f t="shared" ref="T131:AA131" si="77">U5</f>
         <v>354653</v>
       </c>
       <c r="U131" s="25">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>423646</v>
       </c>
       <c r="V131" s="25">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>356624</v>
       </c>
       <c r="W131" s="25">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>361728</v>
       </c>
       <c r="X131" s="25">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>411113</v>
       </c>
       <c r="Y131" s="25">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>481107</v>
       </c>
       <c r="Z131" s="25">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>418382</v>
       </c>
       <c r="AA131" s="25">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="AC131" s="49"/>
     </row>
     <row r="132" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B132" s="20" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C132" s="49"/>
       <c r="D132" s="49"/>
@@ -30192,31 +29912,31 @@
       <c r="P132" s="49"/>
       <c r="Q132" s="49"/>
       <c r="T132" s="193" t="str">
-        <f t="shared" ref="T132:Z132" si="76">IF(T131&gt;T130, "BEAT", IF(T131&lt;T129, "MISSED", "MET"))</f>
+        <f t="shared" ref="T132:Z132" si="78">IF(T131&gt;T130, "BEAT", IF(T131&lt;T129, "MISSED", "MET"))</f>
         <v>BEAT</v>
       </c>
       <c r="U132" s="193" t="str">
-        <f t="shared" si="76"/>
+        <f t="shared" si="78"/>
         <v>MET</v>
       </c>
       <c r="V132" s="193" t="str">
-        <f t="shared" si="76"/>
+        <f t="shared" si="78"/>
         <v>BEAT</v>
       </c>
       <c r="W132" s="193" t="str">
-        <f t="shared" si="76"/>
+        <f t="shared" si="78"/>
         <v>BEAT</v>
       </c>
       <c r="X132" s="193" t="str">
-        <f t="shared" si="76"/>
+        <f t="shared" si="78"/>
         <v>BEAT</v>
       </c>
       <c r="Y132" s="193" t="str">
-        <f t="shared" si="76"/>
+        <f t="shared" si="78"/>
         <v>BEAT</v>
       </c>
       <c r="Z132" s="193" t="str">
-        <f t="shared" si="76"/>
+        <f t="shared" si="78"/>
         <v>BEAT</v>
       </c>
       <c r="AA132" s="193" t="str">
@@ -30227,7 +29947,7 @@
     </row>
     <row r="133" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B133" s="20" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C133" s="49"/>
       <c r="D133" s="49"/>
@@ -30272,7 +29992,7 @@
     </row>
     <row r="134" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B134" s="20" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C134" s="49"/>
       <c r="D134" s="49"/>
@@ -30317,7 +30037,7 @@
     </row>
     <row r="135" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B135" s="20" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C135" s="49"/>
       <c r="D135" s="49"/>
@@ -30335,42 +30055,42 @@
       <c r="P135" s="49"/>
       <c r="Q135" s="49"/>
       <c r="T135" s="25">
-        <f t="shared" ref="T135:AA135" si="77">U210</f>
+        <f t="shared" ref="T135:AA135" si="79">U210</f>
         <v>1606561</v>
       </c>
       <c r="U135" s="25">
-        <f t="shared" si="77"/>
+        <f t="shared" si="79"/>
         <v>1666136</v>
       </c>
       <c r="V135" s="25">
-        <f t="shared" si="77"/>
+        <f t="shared" si="79"/>
         <v>1692683</v>
       </c>
       <c r="W135" s="25">
-        <f t="shared" si="77"/>
+        <f t="shared" si="79"/>
         <v>1723401</v>
       </c>
       <c r="X135" s="25">
-        <f t="shared" si="77"/>
+        <f t="shared" si="79"/>
         <v>1782384</v>
       </c>
       <c r="Y135" s="25">
-        <f t="shared" si="77"/>
+        <f t="shared" si="79"/>
         <v>1852567</v>
       </c>
       <c r="Z135" s="25">
-        <f t="shared" si="77"/>
+        <f t="shared" si="79"/>
         <v>1901211</v>
       </c>
       <c r="AA135" s="25">
-        <f t="shared" si="77"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="AC135" s="49"/>
     </row>
     <row r="136" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B136" s="20" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C136" s="49"/>
       <c r="D136" s="49"/>
@@ -30388,31 +30108,31 @@
       <c r="P136" s="49"/>
       <c r="Q136" s="49"/>
       <c r="T136" s="193" t="str">
-        <f t="shared" ref="T136:Z136" si="78">IF(T135&gt;T134, "BEAT", IF(T135&lt;T133, "MISSED", "MET"))</f>
+        <f t="shared" ref="T136:Z136" si="80">IF(T135&gt;T134, "BEAT", IF(T135&lt;T133, "MISSED", "MET"))</f>
         <v>BEAT</v>
       </c>
       <c r="U136" s="193" t="str">
-        <f t="shared" si="78"/>
+        <f t="shared" si="80"/>
         <v>MISSED</v>
       </c>
       <c r="V136" s="193" t="str">
-        <f t="shared" si="78"/>
+        <f t="shared" si="80"/>
         <v>BEAT</v>
       </c>
       <c r="W136" s="193" t="str">
-        <f t="shared" si="78"/>
+        <f t="shared" si="80"/>
         <v>BEAT</v>
       </c>
       <c r="X136" s="193" t="str">
-        <f t="shared" si="78"/>
+        <f t="shared" si="80"/>
         <v>BEAT</v>
       </c>
       <c r="Y136" s="193" t="str">
-        <f t="shared" si="78"/>
+        <f t="shared" si="80"/>
         <v>BEAT</v>
       </c>
       <c r="Z136" s="193" t="str">
-        <f t="shared" si="78"/>
+        <f t="shared" si="80"/>
         <v>BEAT</v>
       </c>
       <c r="AA136" s="193" t="str">
@@ -30426,7 +30146,7 @@
     </row>
     <row r="139" spans="2:29" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B139" s="14" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C139" s="192"/>
       <c r="D139" s="192"/>
@@ -30505,55 +30225,55 @@
         <v>180</v>
       </c>
       <c r="M141" s="139">
-        <f>M30/M5*365</f>
+        <f t="shared" ref="M141:Q142" si="81">M30/M5*365</f>
         <v>133.69421979440784</v>
       </c>
       <c r="N141" s="139">
-        <f>N30/N5*365</f>
+        <f t="shared" si="81"/>
         <v>152.91140215061483</v>
       </c>
       <c r="O141" s="139">
-        <f>O30/O5*365</f>
+        <f t="shared" si="81"/>
         <v>145.23661159324561</v>
       </c>
       <c r="P141" s="139">
-        <f>P30/P5*365</f>
+        <f t="shared" si="81"/>
         <v>137.8303503480538</v>
       </c>
       <c r="Q141" s="139">
-        <f>Q30/Q5*365</f>
+        <f t="shared" si="81"/>
         <v>131.6037563052133</v>
       </c>
       <c r="T141" s="139">
-        <f t="shared" ref="T141:AA141" si="79">T30/T5*90</f>
+        <f t="shared" ref="T141:AA141" si="82">T30/T5*90</f>
         <v>104.95764467056439</v>
       </c>
       <c r="U141" s="139">
-        <f t="shared" si="79"/>
+        <f t="shared" si="82"/>
         <v>113.19501033404484</v>
       </c>
       <c r="V141" s="139">
-        <f t="shared" si="79"/>
+        <f t="shared" si="82"/>
         <v>114.68995340449337</v>
       </c>
       <c r="W141" s="139">
-        <f t="shared" si="79"/>
+        <f t="shared" si="82"/>
         <v>93.317359459823237</v>
       </c>
       <c r="X141" s="139">
-        <f t="shared" si="79"/>
+        <f t="shared" si="82"/>
         <v>96.344546178343947</v>
       </c>
       <c r="Y141" s="139">
-        <f t="shared" si="79"/>
+        <f t="shared" si="82"/>
         <v>108.60342533561332</v>
       </c>
       <c r="Z141" s="139">
-        <f t="shared" si="79"/>
+        <f t="shared" si="82"/>
         <v>108.63165574394054</v>
       </c>
       <c r="AA141" s="139">
-        <f t="shared" si="79"/>
+        <f t="shared" si="82"/>
         <v>64.534109976050601</v>
       </c>
       <c r="AC141" s="139">
@@ -30566,55 +30286,55 @@
         <v>181</v>
       </c>
       <c r="M142" s="139">
-        <f>M31/M6*365</f>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="N142" s="139">
-        <f>N31/N6*365</f>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="O142" s="139">
-        <f>O31/O6*365</f>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="P142" s="139">
-        <f>P31/P6*365</f>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="Q142" s="139">
-        <f>Q31/Q6*365</f>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="T142" s="139">
-        <f t="shared" ref="T142:AA142" si="80">T31/T6*365</f>
+        <f t="shared" ref="T142:AA142" si="83">T31/T6*365</f>
         <v>0</v>
       </c>
       <c r="U142" s="139">
-        <f t="shared" si="80"/>
+        <f t="shared" si="83"/>
         <v>0</v>
       </c>
       <c r="V142" s="139">
-        <f t="shared" si="80"/>
+        <f t="shared" si="83"/>
         <v>0</v>
       </c>
       <c r="W142" s="139">
-        <f t="shared" si="80"/>
+        <f t="shared" si="83"/>
         <v>0</v>
       </c>
       <c r="X142" s="139">
-        <f t="shared" si="80"/>
+        <f t="shared" si="83"/>
         <v>0</v>
       </c>
       <c r="Y142" s="139">
-        <f t="shared" si="80"/>
+        <f t="shared" si="83"/>
         <v>0</v>
       </c>
       <c r="Z142" s="139">
-        <f t="shared" si="80"/>
+        <f t="shared" si="83"/>
         <v>0</v>
       </c>
       <c r="AA142" s="139">
-        <f t="shared" si="80"/>
+        <f t="shared" si="83"/>
         <v>0</v>
       </c>
       <c r="AC142" s="139">
@@ -30647,35 +30367,35 @@
         <v>13.686287751306349</v>
       </c>
       <c r="T143" s="139">
-        <f t="shared" ref="T143:AA143" si="81">T38/T6*90</f>
+        <f t="shared" ref="T143:AA143" si="84">T38/T6*90</f>
         <v>14.085596967782692</v>
       </c>
       <c r="U143" s="139">
-        <f t="shared" si="81"/>
+        <f t="shared" si="84"/>
         <v>26.007872904348915</v>
       </c>
       <c r="V143" s="139">
-        <f t="shared" si="81"/>
+        <f t="shared" si="84"/>
         <v>46.270493073418663</v>
       </c>
       <c r="W143" s="139">
-        <f t="shared" si="81"/>
+        <f t="shared" si="84"/>
         <v>23.797704245423365</v>
       </c>
       <c r="X143" s="139">
-        <f t="shared" si="81"/>
+        <f t="shared" si="84"/>
         <v>27.599720410065238</v>
       </c>
       <c r="Y143" s="139">
-        <f t="shared" si="81"/>
+        <f t="shared" si="84"/>
         <v>18.67697494623031</v>
       </c>
       <c r="Z143" s="139">
-        <f t="shared" si="81"/>
+        <f t="shared" si="84"/>
         <v>12.368837492391966</v>
       </c>
       <c r="AA143" s="139">
-        <f t="shared" si="81"/>
+        <f t="shared" si="84"/>
         <v>23.046355033277873</v>
       </c>
       <c r="AC143" s="139">
@@ -30692,61 +30412,61 @@
         <v>108.80510521971044</v>
       </c>
       <c r="N144" s="139">
-        <f t="shared" ref="N144:Q144" si="82">N141+N142-N143</f>
+        <f t="shared" ref="N144:Q144" si="85">N141+N142-N143</f>
         <v>134.88753669027304</v>
       </c>
       <c r="O144" s="139">
-        <f t="shared" si="82"/>
+        <f t="shared" si="85"/>
         <v>138.81496340313109</v>
       </c>
       <c r="P144" s="139">
-        <f t="shared" si="82"/>
+        <f t="shared" si="85"/>
         <v>88.790616321440268</v>
       </c>
       <c r="Q144" s="139">
-        <f t="shared" si="82"/>
+        <f t="shared" si="85"/>
         <v>117.91746855390694</v>
       </c>
       <c r="T144" s="139">
-        <f t="shared" ref="T144" si="83">T141+T142-T143</f>
+        <f t="shared" ref="T144" si="86">T141+T142-T143</f>
         <v>90.8720477027817</v>
       </c>
       <c r="U144" s="139">
-        <f t="shared" ref="U144" si="84">U141+U142-U143</f>
+        <f t="shared" ref="U144" si="87">U141+U142-U143</f>
         <v>87.187137429695923</v>
       </c>
       <c r="V144" s="139">
-        <f t="shared" ref="V144" si="85">V141+V142-V143</f>
+        <f t="shared" ref="V144" si="88">V141+V142-V143</f>
         <v>68.419460331074703</v>
       </c>
       <c r="W144" s="139">
-        <f t="shared" ref="W144" si="86">W141+W142-W143</f>
+        <f t="shared" ref="W144" si="89">W141+W142-W143</f>
         <v>69.519655214399876</v>
       </c>
       <c r="X144" s="139">
-        <f t="shared" ref="X144" si="87">X141+X142-X143</f>
+        <f t="shared" ref="X144" si="90">X141+X142-X143</f>
         <v>68.744825768278702</v>
       </c>
       <c r="Y144" s="139">
-        <f t="shared" ref="Y144" si="88">Y141+Y142-Y143</f>
+        <f t="shared" ref="Y144" si="91">Y141+Y142-Y143</f>
         <v>89.926450389383007</v>
       </c>
       <c r="Z144" s="139">
-        <f t="shared" ref="Z144:AA144" si="89">Z141+Z142-Z143</f>
+        <f t="shared" ref="Z144:AA144" si="92">Z141+Z142-Z143</f>
         <v>96.26281825154858</v>
       </c>
       <c r="AA144" s="139">
-        <f t="shared" si="89"/>
+        <f t="shared" si="92"/>
         <v>41.487754942772725</v>
       </c>
       <c r="AC144" s="139">
-        <f t="shared" ref="AC144" si="90">AC141+AC142-AC143</f>
+        <f t="shared" ref="AC144" si="93">AC141+AC142-AC143</f>
         <v>40.164814474593925</v>
       </c>
     </row>
     <row r="145" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B145" s="20" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="M145" s="139">
         <f>M108/M49</f>
@@ -30769,35 +30489,35 @@
         <v>0</v>
       </c>
       <c r="T145" s="139">
-        <f t="shared" ref="T145:AA145" si="91">T108/T49</f>
+        <f t="shared" ref="T145:AA145" si="94">T108/T49</f>
         <v>0</v>
       </c>
       <c r="U145" s="139">
-        <f t="shared" si="91"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="V145" s="139">
-        <f t="shared" si="91"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="W145" s="139">
-        <f t="shared" si="91"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="X145" s="139">
-        <f t="shared" si="91"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="Y145" s="139">
-        <f t="shared" si="91"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="Z145" s="139">
-        <f t="shared" si="91"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="AA145" s="139">
-        <f t="shared" si="91"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="AC145" s="139">
@@ -30807,7 +30527,7 @@
     </row>
     <row r="146" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B146" s="20" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="M146" s="201">
         <f>(M108-M107)/M49</f>
@@ -30830,35 +30550,35 @@
         <v>-0.81123909829457308</v>
       </c>
       <c r="T146" s="201">
-        <f t="shared" ref="T146:AA146" si="92">(T108-T107)/T49</f>
+        <f t="shared" ref="T146:AA146" si="95">(T108-T107)/T49</f>
         <v>-0.95080282790888426</v>
       </c>
       <c r="U146" s="201">
-        <f t="shared" si="92"/>
+        <f t="shared" si="95"/>
         <v>-0.92585537389316019</v>
       </c>
       <c r="V146" s="201">
-        <f t="shared" si="92"/>
+        <f t="shared" si="95"/>
         <v>-0.93383166410403939</v>
       </c>
       <c r="W146" s="201">
-        <f t="shared" si="92"/>
+        <f t="shared" si="95"/>
         <v>-0.93702475358574611</v>
       </c>
       <c r="X146" s="201">
-        <f t="shared" si="92"/>
+        <f t="shared" si="95"/>
         <v>-0.91411133917631171</v>
       </c>
       <c r="Y146" s="201">
-        <f t="shared" si="92"/>
+        <f t="shared" si="95"/>
         <v>-0.78966100787845062</v>
       </c>
       <c r="Z146" s="201">
-        <f t="shared" si="92"/>
+        <f t="shared" si="95"/>
         <v>-0.81123909829457308</v>
       </c>
       <c r="AA146" s="201">
-        <f t="shared" si="92"/>
+        <f t="shared" si="95"/>
         <v>-0.74396849127545694</v>
       </c>
       <c r="AC146" s="201">
@@ -30868,7 +30588,7 @@
     </row>
     <row r="147" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B147" s="20" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="M147" s="139">
         <f>(M107+M30)/M40</f>
@@ -30891,35 +30611,35 @@
         <v>2.5073153653043936</v>
       </c>
       <c r="T147" s="139">
-        <f t="shared" ref="T147:AA147" si="93">(T107+T30)/T40</f>
+        <f t="shared" ref="T147:AA147" si="96">(T107+T30)/T40</f>
         <v>3.3394102478565317</v>
       </c>
       <c r="U147" s="139">
-        <f t="shared" si="93"/>
+        <f t="shared" si="96"/>
         <v>2.9469051997705158</v>
       </c>
       <c r="V147" s="139">
-        <f t="shared" si="93"/>
+        <f t="shared" si="96"/>
         <v>2.833196064687328</v>
       </c>
       <c r="W147" s="139">
-        <f t="shared" si="93"/>
+        <f t="shared" si="96"/>
         <v>2.7397114268432543</v>
       </c>
       <c r="X147" s="139">
-        <f t="shared" si="93"/>
+        <f t="shared" si="96"/>
         <v>2.5864328692324254</v>
       </c>
       <c r="Y147" s="139">
-        <f t="shared" si="93"/>
+        <f t="shared" si="96"/>
         <v>2.5559617091416253</v>
       </c>
       <c r="Z147" s="139">
-        <f t="shared" si="93"/>
+        <f t="shared" si="96"/>
         <v>2.5073153653043936</v>
       </c>
       <c r="AA147" s="139">
-        <f t="shared" si="93"/>
+        <f t="shared" si="96"/>
         <v>2.063021693804965</v>
       </c>
       <c r="AC147" s="139">
@@ -30929,7 +30649,7 @@
     </row>
     <row r="148" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B148" s="20" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="M148" s="139">
         <f>M32/M40</f>
@@ -30952,35 +30672,35 @@
         <v>2.4783388537733191</v>
       </c>
       <c r="T148" s="139">
-        <f t="shared" ref="T148:AA148" si="94">T32/T40</f>
+        <f t="shared" ref="T148:AA148" si="97">T32/T40</f>
         <v>3.5957679252114221</v>
       </c>
       <c r="U148" s="139">
-        <f t="shared" si="94"/>
+        <f t="shared" si="97"/>
         <v>3.129493165083332</v>
       </c>
       <c r="V148" s="139">
-        <f t="shared" si="94"/>
+        <f t="shared" si="97"/>
         <v>2.9271504030441093</v>
       </c>
       <c r="W148" s="139">
-        <f t="shared" si="94"/>
+        <f t="shared" si="97"/>
         <v>2.9470125037192663</v>
       </c>
       <c r="X148" s="139">
-        <f t="shared" si="94"/>
+        <f t="shared" si="97"/>
         <v>2.7501208666647705</v>
       </c>
       <c r="Y148" s="139">
-        <f t="shared" si="94"/>
+        <f t="shared" si="97"/>
         <v>2.6541688855077976</v>
       </c>
       <c r="Z148" s="139">
-        <f t="shared" si="94"/>
+        <f t="shared" si="97"/>
         <v>2.4783388537733191</v>
       </c>
       <c r="AA148" s="139">
-        <f t="shared" si="94"/>
+        <f t="shared" si="97"/>
         <v>2.3066495444084523</v>
       </c>
       <c r="AC148" s="139">
@@ -30990,7 +30710,7 @@
     </row>
     <row r="149" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B149" s="20" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="M149" s="203" t="str">
         <f>IF(M13&gt;=0,"N/A",IF(M12&lt;=0,"N/A",M12/-M13))</f>
@@ -31013,35 +30733,35 @@
         <v>N/A</v>
       </c>
       <c r="T149" s="203" t="str">
-        <f t="shared" ref="T149:AA149" si="95">IF(T13&gt;=0,"N/A",IF(T12&lt;=0,"N/A",T12/-T13))</f>
+        <f t="shared" ref="T149:AA149" si="98">IF(T13&gt;=0,"N/A",IF(T12&lt;=0,"N/A",T12/-T13))</f>
         <v>N/A</v>
       </c>
       <c r="U149" s="203" t="str">
-        <f t="shared" si="95"/>
+        <f t="shared" si="98"/>
         <v>N/A</v>
       </c>
       <c r="V149" s="203" t="str">
-        <f t="shared" si="95"/>
+        <f t="shared" si="98"/>
         <v>N/A</v>
       </c>
       <c r="W149" s="203" t="str">
-        <f t="shared" si="95"/>
+        <f t="shared" si="98"/>
         <v>N/A</v>
       </c>
       <c r="X149" s="203" t="str">
-        <f t="shared" si="95"/>
+        <f t="shared" si="98"/>
         <v>N/A</v>
       </c>
       <c r="Y149" s="203" t="str">
-        <f t="shared" si="95"/>
+        <f t="shared" si="98"/>
         <v>N/A</v>
       </c>
       <c r="Z149" s="203" t="str">
-        <f t="shared" si="95"/>
+        <f t="shared" si="98"/>
         <v>N/A</v>
       </c>
       <c r="AA149" s="203" t="str">
-        <f t="shared" si="95"/>
+        <f t="shared" si="98"/>
         <v>N/A</v>
       </c>
       <c r="AC149" s="203" t="str">
@@ -31051,7 +30771,7 @@
     </row>
     <row r="150" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B150" s="20" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="M150" s="72">
         <f>M117/Statement!M26</f>
@@ -31083,12 +30803,12 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>17.916666666666664</v>
+        <v>17.62083333333333</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B151" s="20" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="M151" s="72">
         <f>M117/(Statement!M5/Statement!M22)</f>
@@ -31120,12 +30840,12 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>3.4631455439416863</v>
+        <v>3.4059633733324164</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B152" s="20" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="M152" s="72">
         <f>M117/(Statement!M49/Statement!M75)</f>
@@ -31157,12 +30877,12 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="72">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>2.9269065642300305</v>
+        <v>2.8785785721229762</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B153" s="20" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="M153" s="164">
         <f>Statement!M117*Statement!M78</f>
@@ -31194,12 +30914,12 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="164">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>5615316.25</v>
+        <v>5522598.2374999998</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B154" s="20" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="M154" s="164">
         <f>M153+M108-M107+M48+M45</f>
@@ -31231,12 +30951,12 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="164">
         <f ca="1">AC153+AC108-AC107+AC48+AC45</f>
-        <v>4199570.25</v>
+        <v>4106852.2374999998</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B155" s="20" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="M155" s="205">
         <f>M154/M5</f>
@@ -31268,12 +30988,12 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="205">
         <f ca="1">AC154/AC5</f>
-        <v>2.5112090616086538</v>
+        <v>2.4557666474320259</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B156" s="20" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="M156" s="205">
         <f>M154/M12</f>
@@ -31305,12 +31025,12 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="205">
         <f ca="1">AC154/AC12</f>
-        <v>41.514548878498204</v>
+        <v>40.597991651756146</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B157" s="20" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M157" s="64">
         <f>M59-M54+M110+M65</f>
@@ -31333,35 +31053,35 @@
         <v>61484</v>
       </c>
       <c r="T157" s="64">
-        <f t="shared" ref="T157:AA157" si="96">T59-T54+T110+T65</f>
+        <f t="shared" ref="T157:AA157" si="99">T59-T54+T110+T65</f>
         <v>-49347</v>
       </c>
       <c r="U157" s="64">
-        <f t="shared" si="96"/>
+        <f t="shared" si="99"/>
         <v>-64293</v>
       </c>
       <c r="V157" s="64">
-        <f t="shared" si="96"/>
+        <f t="shared" si="99"/>
         <v>0</v>
       </c>
       <c r="W157" s="64">
-        <f t="shared" si="96"/>
+        <f t="shared" si="99"/>
         <v>29809</v>
       </c>
       <c r="X157" s="64">
-        <f t="shared" si="96"/>
+        <f t="shared" si="99"/>
         <v>-36419</v>
       </c>
       <c r="Y157" s="64">
-        <f t="shared" si="96"/>
+        <f t="shared" si="99"/>
         <v>-46368</v>
       </c>
       <c r="Z157" s="64">
-        <f t="shared" si="96"/>
+        <f t="shared" si="99"/>
         <v>114462</v>
       </c>
       <c r="AA157" s="64">
-        <f t="shared" si="96"/>
+        <f t="shared" si="99"/>
         <v>75934</v>
       </c>
       <c r="AC157" s="64">
@@ -31371,7 +31091,7 @@
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B158" s="20" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="M158" s="64">
         <f>M109+M53+M110+M55+M57+M58+M56</f>
@@ -31408,26 +31128,26 @@
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B159" s="20" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="M159" s="72">
         <f>M153/M157</f>
         <v>-31.117410328396652</v>
       </c>
       <c r="N159" s="72">
-        <f t="shared" ref="N159:Q159" si="97">N153/N157</f>
+        <f t="shared" ref="N159:Q159" si="100">N153/N157</f>
         <v>-20.121230787144853</v>
       </c>
       <c r="O159" s="72">
-        <f t="shared" si="97"/>
+        <f t="shared" si="100"/>
         <v>-169.18232313158387</v>
       </c>
       <c r="P159" s="72">
-        <f t="shared" si="97"/>
+        <f t="shared" si="100"/>
         <v>-153.13123350282808</v>
       </c>
       <c r="Q159" s="72">
-        <f t="shared" si="97"/>
+        <f t="shared" si="100"/>
         <v>108.6619548175135</v>
       </c>
       <c r="T159" s="49"/>
@@ -31439,32 +31159,32 @@
       <c r="Z159" s="49"/>
       <c r="AA159" s="49"/>
       <c r="AC159" s="72">
-        <f t="shared" ref="AC159:AC160" ca="1" si="98">AC153/AC157</f>
-        <v>52.182589281565669</v>
+        <f t="shared" ref="AC159:AC160" ca="1" si="101">AC153/AC157</f>
+        <v>51.320969784125865</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B160" s="20" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M160" s="72">
         <f>M154/M158</f>
         <v>-26.884257614591405</v>
       </c>
       <c r="N160" s="72">
-        <f t="shared" ref="N160:Q160" si="99">N154/N158</f>
+        <f t="shared" ref="N160:Q160" si="102">N154/N158</f>
         <v>-12.722058684723095</v>
       </c>
       <c r="O160" s="72">
-        <f t="shared" si="99"/>
+        <f t="shared" si="102"/>
         <v>-54.027334756669582</v>
       </c>
       <c r="P160" s="72">
-        <f t="shared" si="99"/>
+        <f t="shared" si="102"/>
         <v>-31.268001801694783</v>
       </c>
       <c r="Q160" s="72">
-        <f t="shared" si="99"/>
+        <f t="shared" si="102"/>
         <v>-52.805531070816492</v>
       </c>
       <c r="T160" s="49"/>
@@ -31476,32 +31196,32 @@
       <c r="Z160" s="49"/>
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
-        <f t="shared" ca="1" si="98"/>
-        <v>-77.43284318244676</v>
+        <f t="shared" ca="1" si="101"/>
+        <v>-75.723282704895354</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B161" s="20" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="M161" s="74">
         <f>M157/M153</f>
         <v>-3.2136350340421331E-2</v>
       </c>
       <c r="N161" s="74">
-        <f t="shared" ref="N161:Q161" si="100">N157/N153</f>
+        <f t="shared" ref="N161:Q161" si="103">N157/N153</f>
         <v>-4.9698749076467263E-2</v>
       </c>
       <c r="O161" s="74">
-        <f t="shared" si="100"/>
+        <f t="shared" si="103"/>
         <v>-5.9107830031523813E-3</v>
       </c>
       <c r="P161" s="74">
-        <f t="shared" si="100"/>
+        <f t="shared" si="103"/>
         <v>-6.5303464037043202E-3</v>
       </c>
       <c r="Q161" s="74">
-        <f t="shared" si="100"/>
+        <f t="shared" si="103"/>
         <v>9.2028530287292954E-3</v>
       </c>
       <c r="T161" s="49"/>
@@ -31513,13 +31233,13 @@
       <c r="Z161" s="49"/>
       <c r="AA161" s="49"/>
       <c r="AC161" s="74">
-        <f t="shared" ref="AC161" ca="1" si="101">AC157/AC153</f>
-        <v>1.9163479884147221E-2</v>
+        <f t="shared" ref="AC161" ca="1" si="104">AC157/AC153</f>
+        <v>1.9485212462008288E-2</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B162" s="20" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="M162" s="74">
         <f>M26/M117</f>
@@ -31551,12 +31271,12 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f ca="1">AC26/AC117</f>
-        <v>5.5813953488372099E-2</v>
+        <v>5.6751004965712941E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B163" s="20" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M163" s="175">
         <f>M82/M117</f>
@@ -31593,7 +31313,7 @@
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B164" s="20" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="M164" s="175">
         <f>-M63/M153</f>
@@ -31625,12 +31345,12 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="175">
         <f ca="1">-AC63/AC153</f>
-        <v>6.150535154631763E-2</v>
+        <v>6.2537954989161926E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B165" s="20" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="M165" s="175">
         <f>-(M63+M64)/M153</f>
@@ -31662,12 +31382,12 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="175">
         <f ca="1">-(AC63+AC64)/AC153</f>
-        <v>6.150535154631763E-2</v>
+        <v>6.2537954989161926E-2</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B166" s="20" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="M166" s="175">
         <f>M158/M5</f>
@@ -31704,7 +31424,7 @@
     </row>
     <row r="167" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B167" s="20" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="M167" s="175">
         <f>M157/M5</f>
@@ -31741,7 +31461,7 @@
     </row>
     <row r="168" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B168" s="20" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="M168" s="175">
         <f>-M64/M157</f>
@@ -31778,7 +31498,7 @@
     </row>
     <row r="169" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B169" s="20" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="M169" s="175">
         <f>-M63/M157</f>
@@ -31815,7 +31535,7 @@
     </row>
     <row r="170" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B170" s="20" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="M170" s="175">
         <f>(-M64-M63)/M157</f>
@@ -31852,7 +31572,7 @@
     </row>
     <row r="171" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B171" s="20" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="M171" s="175">
         <f>M80/M78</f>
@@ -31889,7 +31609,7 @@
     </row>
     <row r="172" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B172" s="20" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="M172" s="72">
         <f>M107/M75</f>
@@ -31912,35 +31632,35 @@
         <v>3.224670847950649</v>
       </c>
       <c r="T172" s="72">
-        <f t="shared" ref="T172:AA172" si="102">T107/T75</f>
+        <f t="shared" ref="T172:AA172" si="105">T107/T75</f>
         <v>3.1700129828095962</v>
       </c>
       <c r="U172" s="72">
-        <f t="shared" si="102"/>
+        <f t="shared" si="105"/>
         <v>2.9174689182476676</v>
       </c>
       <c r="V172" s="72">
-        <f t="shared" si="102"/>
+        <f t="shared" si="105"/>
         <v>3.125390530795495</v>
       </c>
       <c r="W172" s="72">
-        <f t="shared" si="102"/>
+        <f t="shared" si="105"/>
         <v>2.9745495188201234</v>
       </c>
       <c r="X172" s="72">
-        <f t="shared" si="102"/>
+        <f t="shared" si="105"/>
         <v>2.8673727265537021</v>
       </c>
       <c r="Y172" s="72">
-        <f t="shared" si="102"/>
+        <f t="shared" si="105"/>
         <v>2.8420663861617577</v>
       </c>
       <c r="Z172" s="72">
-        <f t="shared" si="102"/>
+        <f t="shared" si="105"/>
         <v>3.224670847950649</v>
       </c>
       <c r="AA172" s="72">
-        <f t="shared" si="102"/>
+        <f t="shared" si="105"/>
         <v>2.732462108272006</v>
       </c>
       <c r="AC172" s="72">
@@ -31950,7 +31670,7 @@
     </row>
     <row r="173" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B173" s="20" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="M173" s="175">
         <f>M54/M59</f>
@@ -31973,35 +31693,35 @@
         <v>0.78305424452059225</v>
       </c>
       <c r="T173" s="175">
-        <f t="shared" ref="T173:AA173" si="103">T54/T59</f>
+        <f t="shared" ref="T173:AA173" si="106">T54/T59</f>
         <v>2.0334871485250994</v>
       </c>
       <c r="U173" s="175">
-        <f t="shared" si="103"/>
+        <f t="shared" si="106"/>
         <v>3.1167794798717492</v>
       </c>
       <c r="V173" s="175" t="e">
-        <f t="shared" si="103"/>
+        <f t="shared" si="106"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W173" s="175">
-        <f t="shared" si="103"/>
+        <f t="shared" si="106"/>
         <v>0.6416782911211576</v>
       </c>
       <c r="X173" s="175">
-        <f t="shared" si="103"/>
+        <f t="shared" si="106"/>
         <v>1.8757303965181427</v>
       </c>
       <c r="Y173" s="175">
-        <f t="shared" si="103"/>
+        <f t="shared" si="106"/>
         <v>2.5282091188850764</v>
       </c>
       <c r="Z173" s="175">
-        <f t="shared" si="103"/>
+        <f t="shared" si="106"/>
         <v>0.35555092460569898</v>
       </c>
       <c r="AA173" s="175">
-        <f t="shared" si="103"/>
+        <f t="shared" si="106"/>
         <v>0.40408404584318719</v>
       </c>
       <c r="AC173" s="175">
@@ -32011,7 +31731,7 @@
     </row>
     <row r="174" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B174" s="20" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="M174" s="175">
         <f>M54/M5</f>
@@ -32034,35 +31754,35 @@
         <v>0.18047997854178516</v>
       </c>
       <c r="T174" s="175">
-        <f t="shared" ref="T174:AA174" si="104">T54/T5</f>
+        <f t="shared" ref="T174:AA174" si="107">T54/T5</f>
         <v>0.29819479973312507</v>
       </c>
       <c r="U174" s="175">
-        <f t="shared" si="104"/>
+        <f t="shared" si="107"/>
         <v>0.24668619749445234</v>
       </c>
       <c r="V174" s="175">
-        <f t="shared" si="104"/>
+        <f t="shared" si="107"/>
         <v>0</v>
       </c>
       <c r="W174" s="175">
-        <f t="shared" si="104"/>
+        <f t="shared" si="107"/>
         <v>0.21412187626183318</v>
       </c>
       <c r="X174" s="175">
-        <f t="shared" si="104"/>
+        <f t="shared" si="107"/>
         <v>0.21564822186836519</v>
       </c>
       <c r="Y174" s="175">
-        <f t="shared" si="104"/>
+        <f t="shared" si="107"/>
         <v>0.17385730930425455</v>
       </c>
       <c r="Z174" s="175">
-        <f t="shared" si="104"/>
+        <f t="shared" si="107"/>
         <v>0.13476004298420102</v>
       </c>
       <c r="AA174" s="175">
-        <f t="shared" si="104"/>
+        <f t="shared" si="107"/>
         <v>0.1274194396508454</v>
       </c>
       <c r="AC174" s="175">
@@ -32072,7 +31792,7 @@
     </row>
     <row r="175" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B175" s="20" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="M175" s="72">
         <f>(M107-M108)/M75</f>
@@ -32095,35 +31815,35 @@
         <v>3.224670847950649</v>
       </c>
       <c r="T175" s="72">
-        <f t="shared" ref="T175:AA175" si="105">(T107-T108)/T75</f>
+        <f t="shared" ref="T175:AA175" si="108">(T107-T108)/T75</f>
         <v>3.1700129828095962</v>
       </c>
       <c r="U175" s="72">
-        <f t="shared" si="105"/>
+        <f t="shared" si="108"/>
         <v>2.9174689182476676</v>
       </c>
       <c r="V175" s="72">
-        <f t="shared" si="105"/>
+        <f t="shared" si="108"/>
         <v>3.125390530795495</v>
       </c>
       <c r="W175" s="72">
-        <f t="shared" si="105"/>
+        <f t="shared" si="108"/>
         <v>2.9745495188201234</v>
       </c>
       <c r="X175" s="72">
-        <f t="shared" si="105"/>
+        <f t="shared" si="108"/>
         <v>2.8673727265537021</v>
       </c>
       <c r="Y175" s="72">
-        <f t="shared" si="105"/>
+        <f t="shared" si="108"/>
         <v>2.8420663861617577</v>
       </c>
       <c r="Z175" s="72">
-        <f t="shared" si="105"/>
+        <f t="shared" si="108"/>
         <v>3.224670847950649</v>
       </c>
       <c r="AA175" s="72">
-        <f t="shared" si="105"/>
+        <f t="shared" si="108"/>
         <v>2.732462108272006</v>
       </c>
       <c r="AC175" s="72">
@@ -32133,7 +31853,7 @@
     </row>
     <row r="176" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B176" s="20" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="M176" s="175">
         <f>(M107-M108)/M153</f>
@@ -32165,12 +31885,12 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="175">
         <f ca="1">(AC107-AC108)/AC153</f>
-        <v>0.25212222018661906</v>
+        <v>0.2563550595418449</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B177" s="20" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="M177" s="175">
         <f>-M110/M5</f>
@@ -32193,35 +31913,35 @@
         <v>1.1826854061786744E-2</v>
       </c>
       <c r="T177" s="175">
-        <f t="shared" ref="T177:AA177" si="106">-T110/T5</f>
+        <f t="shared" ref="T177:AA177" si="109">-T110/T5</f>
         <v>4.4837519327879894E-3</v>
       </c>
       <c r="U177" s="175">
-        <f t="shared" si="106"/>
+        <f t="shared" si="109"/>
         <v>1.3745830431435797E-2</v>
       </c>
       <c r="V177" s="175">
-        <f t="shared" si="106"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="W177" s="175">
-        <f t="shared" si="106"/>
+        <f t="shared" si="109"/>
         <v>3.5981874467225984E-2</v>
       </c>
       <c r="X177" s="175">
-        <f t="shared" si="106"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="Y177" s="175">
-        <f t="shared" si="106"/>
+        <f t="shared" si="109"/>
         <v>7.6961808553852587E-3</v>
       </c>
       <c r="Z177" s="175">
-        <f t="shared" si="106"/>
+        <f t="shared" si="109"/>
         <v>6.3437031679023587E-3</v>
       </c>
       <c r="AA177" s="175">
-        <f t="shared" si="106"/>
+        <f t="shared" si="109"/>
         <v>6.415189946030183E-3</v>
       </c>
       <c r="AC177" s="175">
@@ -32231,7 +31951,7 @@
     </row>
     <row r="178" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B178" s="20" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="M178" s="175">
         <f>-(M110/M59)</f>
@@ -32254,35 +31974,35 @@
         <v>5.1313549276955236E-2</v>
       </c>
       <c r="T178" s="175">
-        <f t="shared" ref="T178:AA178" si="107">-(T110/T59)</f>
+        <f t="shared" ref="T178:AA178" si="110">-(T110/T59)</f>
         <v>3.0576160082801448E-2</v>
       </c>
       <c r="U178" s="175">
-        <f t="shared" si="107"/>
+        <f t="shared" si="110"/>
         <v>0.17367296045600286</v>
       </c>
       <c r="V178" s="175" t="e">
-        <f t="shared" si="107"/>
+        <f t="shared" si="110"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W178" s="175">
-        <f t="shared" si="107"/>
+        <f t="shared" si="110"/>
         <v>0.10783012050217644</v>
       </c>
       <c r="X178" s="175">
-        <f t="shared" si="107"/>
+        <f t="shared" si="110"/>
         <v>0</v>
       </c>
       <c r="Y178" s="175">
-        <f t="shared" si="107"/>
+        <f t="shared" si="110"/>
         <v>0.11191680520674896</v>
       </c>
       <c r="Z178" s="175">
-        <f t="shared" si="107"/>
+        <f t="shared" si="110"/>
         <v>1.6737227718428501E-2</v>
       </c>
       <c r="AA178" s="175">
-        <f t="shared" si="107"/>
+        <f t="shared" si="110"/>
         <v>2.0344430295312594E-2</v>
       </c>
       <c r="AC178" s="175">
@@ -32292,7 +32012,7 @@
     </row>
     <row r="179" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B179" s="20" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="M179" s="175">
         <f>-M110/M53</f>
@@ -32315,35 +32035,35 @@
         <v>1.1225175319700631</v>
       </c>
       <c r="T179" s="175">
-        <f t="shared" ref="T179:AA179" si="108">-T110/T53</f>
+        <f t="shared" ref="T179:AA179" si="111">-T110/T53</f>
         <v>0.30953940187731938</v>
       </c>
       <c r="U179" s="175">
-        <f t="shared" si="108"/>
+        <f t="shared" si="111"/>
         <v>1.0752095280105867</v>
       </c>
       <c r="V179" s="175" t="e">
-        <f t="shared" si="108"/>
+        <f t="shared" si="111"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W179" s="175">
-        <f t="shared" si="108"/>
+        <f t="shared" si="111"/>
         <v>3.9446664617276359</v>
       </c>
       <c r="X179" s="175">
-        <f t="shared" si="108"/>
+        <f t="shared" si="111"/>
         <v>0</v>
       </c>
       <c r="Y179" s="175">
-        <f t="shared" si="108"/>
+        <f t="shared" si="111"/>
         <v>0.7010857522712165</v>
       </c>
       <c r="Z179" s="175">
-        <f t="shared" si="108"/>
+        <f t="shared" si="111"/>
         <v>0.61371405590187011</v>
       </c>
       <c r="AA179" s="175">
-        <f t="shared" si="108"/>
+        <f t="shared" si="111"/>
         <v>0.35743774137701423</v>
       </c>
       <c r="AC179" s="175">
@@ -32353,7 +32073,7 @@
     </row>
     <row r="180" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B180" s="20" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="M180" s="247">
         <f>M37/M5</f>
@@ -32514,7 +32234,7 @@
         <v>252903</v>
       </c>
       <c r="AC185" s="62">
-        <f t="shared" ref="AC185:AC190" si="109">SUM(X185:AA185)</f>
+        <f t="shared" ref="AC185:AC190" si="112">SUM(X185:AA185)</f>
         <v>990072</v>
       </c>
     </row>
@@ -32572,7 +32292,7 @@
         <v>16170</v>
       </c>
       <c r="AC186" s="62">
-        <f t="shared" si="109"/>
+        <f t="shared" si="112"/>
         <v>54841</v>
       </c>
     </row>
@@ -32644,7 +32364,7 @@
         <v>1664</v>
       </c>
       <c r="AC188" s="62">
-        <f t="shared" si="109"/>
+        <f t="shared" si="112"/>
         <v>5730</v>
       </c>
     </row>
@@ -32702,7 +32422,7 @@
         <v>43988</v>
       </c>
       <c r="AC189" s="62">
-        <f t="shared" si="109"/>
+        <f t="shared" si="112"/>
         <v>163108</v>
       </c>
     </row>
@@ -32760,7 +32480,7 @@
         <v>31276</v>
       </c>
       <c r="AC190" s="62">
-        <f t="shared" si="109"/>
+        <f t="shared" si="112"/>
         <v>115217</v>
       </c>
     </row>
@@ -32782,7 +32502,7 @@
     </row>
     <row r="193" spans="2:29" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B193" s="14" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C193" s="192"/>
       <c r="D193" s="192"/>
@@ -32824,61 +32544,61 @@
       <c r="K194" s="81"/>
       <c r="L194" s="81"/>
       <c r="M194" s="81">
-        <f t="shared" ref="M194:Q196" si="110">IF(L184=0,
+        <f t="shared" ref="M194:Q196" si="113">IF(L184=0,
 IF(M184=0,0,IF(M184&gt;0,1,-1)),
 (M184-L184)/ABS(L184)
 )</f>
         <v>1</v>
       </c>
       <c r="N194" s="81">
-        <f t="shared" si="110"/>
+        <f t="shared" si="113"/>
         <v>3.4084087514825716E-2</v>
       </c>
       <c r="O194" s="81">
-        <f t="shared" si="110"/>
+        <f t="shared" si="113"/>
         <v>0.24818614965570993</v>
       </c>
       <c r="P194" s="81">
-        <f t="shared" si="110"/>
+        <f t="shared" si="113"/>
         <v>-5.5102093364575021E-2</v>
       </c>
       <c r="Q194" s="81">
-        <f t="shared" si="110"/>
+        <f t="shared" si="113"/>
         <v>3.2771752459329104E-2</v>
       </c>
       <c r="T194" s="81">
-        <f t="shared" ref="T194:AA196" si="111">IF(S184=0,
+        <f t="shared" ref="T194:AA196" si="114">IF(S184=0,
 IF(T184=0,0,IF(T184&gt;0,1,-1)),
 (T184-S184)/ABS(S184)
 )</f>
         <v>1</v>
       </c>
       <c r="U194" s="81">
-        <f t="shared" si="111"/>
+        <f t="shared" si="114"/>
         <v>0.22202920241245067</v>
       </c>
       <c r="V194" s="81">
-        <f t="shared" si="111"/>
+        <f t="shared" si="114"/>
         <v>0.44057182848061588</v>
       </c>
       <c r="W194" s="81">
-        <f t="shared" si="111"/>
+        <f t="shared" si="114"/>
         <v>-0.35080892064632685</v>
       </c>
       <c r="X194" s="81">
-        <f t="shared" si="111"/>
+        <f t="shared" si="114"/>
         <v>-0.12569571114540948</v>
       </c>
       <c r="Y194" s="81">
-        <f t="shared" si="111"/>
+        <f t="shared" si="114"/>
         <v>0.33774663207353717</v>
       </c>
       <c r="Z194" s="81">
-        <f t="shared" si="111"/>
+        <f t="shared" si="114"/>
         <v>0.43894750171617469</v>
       </c>
       <c r="AA194" s="81">
-        <f t="shared" si="111"/>
+        <f t="shared" si="114"/>
         <v>-0.30844727286201273</v>
       </c>
       <c r="AC194" s="49"/>
@@ -32888,55 +32608,55 @@
         <v>114</v>
       </c>
       <c r="M195" s="81">
-        <f t="shared" si="110"/>
+        <f t="shared" si="113"/>
         <v>1</v>
       </c>
       <c r="N195" s="81">
-        <f t="shared" si="110"/>
+        <f t="shared" si="113"/>
         <v>0.37569180272908909</v>
       </c>
       <c r="O195" s="81">
-        <f t="shared" si="110"/>
+        <f t="shared" si="113"/>
         <v>0.27729682030883041</v>
       </c>
       <c r="P195" s="81">
-        <f t="shared" si="110"/>
+        <f t="shared" si="113"/>
         <v>0.23392027917368038</v>
       </c>
       <c r="Q195" s="81">
-        <f t="shared" si="110"/>
+        <f t="shared" si="113"/>
         <v>0.19019336689332336</v>
       </c>
       <c r="T195" s="81">
-        <f t="shared" si="111"/>
+        <f t="shared" si="114"/>
         <v>1</v>
       </c>
       <c r="U195" s="81">
-        <f t="shared" si="111"/>
+        <f t="shared" si="114"/>
         <v>6.292089812146523E-2</v>
       </c>
       <c r="V195" s="81">
-        <f t="shared" si="111"/>
+        <f t="shared" si="114"/>
         <v>4.0106900184610626E-2</v>
       </c>
       <c r="W195" s="81">
-        <f t="shared" si="111"/>
+        <f t="shared" si="114"/>
         <v>9.673777187170397E-3</v>
       </c>
       <c r="X195" s="81">
-        <f t="shared" si="111"/>
+        <f t="shared" si="114"/>
         <v>9.6915367022084364E-2</v>
       </c>
       <c r="Y195" s="81">
-        <f t="shared" si="111"/>
+        <f t="shared" si="114"/>
         <v>3.8638547089942653E-2</v>
       </c>
       <c r="Z195" s="81">
-        <f t="shared" si="111"/>
+        <f t="shared" si="114"/>
         <v>1.4783518396594137E-2</v>
       </c>
       <c r="AA195" s="81">
-        <f t="shared" si="111"/>
+        <f t="shared" si="114"/>
         <v>6.6472159310281692E-3</v>
       </c>
       <c r="AC195" s="49"/>
@@ -32946,55 +32666,55 @@
         <v>115</v>
       </c>
       <c r="M196" s="81">
-        <f t="shared" si="110"/>
+        <f t="shared" si="113"/>
         <v>1</v>
       </c>
       <c r="N196" s="81">
-        <f t="shared" si="110"/>
+        <f t="shared" si="113"/>
         <v>0.26768885199472631</v>
       </c>
       <c r="O196" s="81">
-        <f t="shared" si="110"/>
+        <f t="shared" si="113"/>
         <v>-0.29197642617772812</v>
       </c>
       <c r="P196" s="81">
-        <f t="shared" si="110"/>
+        <f t="shared" si="113"/>
         <v>0.10317719384146673</v>
       </c>
       <c r="Q196" s="81">
-        <f t="shared" si="110"/>
+        <f t="shared" si="113"/>
         <v>0.22564418690666996</v>
       </c>
       <c r="T196" s="81">
-        <f t="shared" si="111"/>
+        <f t="shared" si="114"/>
         <v>1</v>
       </c>
       <c r="U196" s="81">
-        <f t="shared" si="111"/>
+        <f t="shared" si="114"/>
         <v>0.13163254368099475</v>
       </c>
       <c r="V196" s="81">
-        <f t="shared" si="111"/>
+        <f t="shared" si="114"/>
         <v>2.4533484891541158E-2</v>
       </c>
       <c r="W196" s="81">
-        <f t="shared" si="111"/>
+        <f t="shared" si="114"/>
         <v>2.0247781065088757E-2</v>
       </c>
       <c r="X196" s="81">
-        <f t="shared" si="111"/>
+        <f t="shared" si="114"/>
         <v>1.5314907113729044E-2</v>
       </c>
       <c r="Y196" s="81">
-        <f t="shared" si="111"/>
+        <f t="shared" si="114"/>
         <v>0.20465905033916459</v>
       </c>
       <c r="Z196" s="81">
-        <f t="shared" si="111"/>
+        <f t="shared" si="114"/>
         <v>3.5044824775876122E-2</v>
       </c>
       <c r="AA196" s="81">
-        <f t="shared" si="111"/>
+        <f t="shared" si="114"/>
         <v>0.15748031496062992</v>
       </c>
       <c r="AC196" s="49"/>
@@ -33004,7 +32724,7 @@
     </row>
     <row r="199" spans="2:29" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B199" s="14" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C199" s="192"/>
       <c r="D199" s="192"/>
@@ -33033,7 +32753,7 @@
     </row>
     <row r="200" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B200" s="20" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C200" s="81"/>
       <c r="D200" s="81"/>
@@ -33095,7 +32815,7 @@
     </row>
     <row r="203" spans="2:29" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B203" s="14" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C203" s="192"/>
       <c r="D203" s="192"/>
@@ -33124,7 +32844,7 @@
     </row>
     <row r="204" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B204" s="20" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="M204" s="164">
         <v>100</v>
@@ -33134,15 +32854,15 @@
         <v>43.583607538139404</v>
       </c>
       <c r="O204" s="164">
-        <f t="shared" ref="O204:Q204" si="112">100*(1+((O117-$M117)/ABS($M117)))</f>
+        <f t="shared" ref="O204:Q204" si="115">100*(1+((O117-$M117)/ABS($M117)))</f>
         <v>71.343104995513016</v>
       </c>
       <c r="P204" s="164">
-        <f t="shared" si="112"/>
+        <f t="shared" si="115"/>
         <v>43.613520789709838</v>
       </c>
       <c r="Q204" s="164">
-        <f t="shared" si="112"/>
+        <f t="shared" si="115"/>
         <v>37.660783727191152</v>
       </c>
       <c r="T204" s="49"/>
@@ -33157,7 +32877,7 @@
     </row>
     <row r="205" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B205" s="20" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="M205" s="164">
         <v>100</v>
@@ -33167,15 +32887,15 @@
         <v>118.64148245114609</v>
       </c>
       <c r="O205" s="164">
-        <f t="shared" ref="O205:Q205" si="113">100*(1+((O5-$M5)/ABS($M5)))</f>
+        <f t="shared" ref="O205:Q205" si="116">100*(1+((O5-$M5)/ABS($M5)))</f>
         <v>146.60342593796372</v>
       </c>
       <c r="P205" s="164">
-        <f t="shared" si="113"/>
+        <f t="shared" si="116"/>
         <v>160.23096613961079</v>
       </c>
       <c r="Q205" s="164">
-        <f t="shared" si="113"/>
+        <f t="shared" si="116"/>
         <v>180.50640402038886</v>
       </c>
       <c r="T205" s="49"/>
@@ -33190,7 +32910,7 @@
     </row>
     <row r="206" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B206" s="20" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="M206" s="164">
         <v>100</v>
@@ -33200,15 +32920,15 @@
         <v>148.27586206896552</v>
       </c>
       <c r="O206" s="164">
-        <f t="shared" ref="O206:Q206" si="114">100*(1+((O26-$M26)/ABS($M26)))</f>
+        <f t="shared" ref="O206:Q206" si="117">100*(1+((O26-$M26)/ABS($M26)))</f>
         <v>186.20689655172413</v>
       </c>
       <c r="P206" s="164">
-        <f t="shared" si="114"/>
+        <f t="shared" si="117"/>
         <v>188.79310344827584</v>
       </c>
       <c r="Q206" s="164">
-        <f t="shared" si="114"/>
+        <f t="shared" si="117"/>
         <v>244.82758620689654</v>
       </c>
       <c r="T206" s="49"/>
@@ -33532,7 +33252,7 @@
   <sheetData>
     <row r="13" spans="2:2" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
   </sheetData>
@@ -33555,16 +33275,16 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B1" s="84" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="248" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C4" s="248"/>
       <c r="E4" s="248" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F4" s="248"/>
       <c r="G4" s="248"/>
@@ -33575,23 +33295,23 @@
       </c>
       <c r="C5" s="194">
         <f ca="1">Overview!C5</f>
-        <v>10.75</v>
+        <v>10.5725</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="153" t="s">
+        <v>290</v>
+      </c>
+      <c r="G5" s="153" t="s">
         <v>291</v>
-      </c>
-      <c r="G5" s="153" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B6" s="20" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C6" s="195">
         <f ca="1">Statement!AC153</f>
-        <v>5615316.25</v>
+        <v>5522598.2374999998</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>20</v>
@@ -33607,11 +33327,11 @@
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B7" s="20" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C7" s="195">
         <f ca="1">Statement!AC154</f>
-        <v>4199570.25</v>
+        <v>4106852.2374999998</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>32</v>
@@ -33627,14 +33347,14 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="20" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C8" s="196">
         <f ca="1">Statement!AC150</f>
-        <v>17.916666666666664</v>
+        <v>17.62083333333333</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F8" s="200" t="str">
         <f>IF(OR(Statement!M26&lt;=0, Statement!Q26&lt;=0), "N/A", _xlfn.RRI(4, Statement!M26, Statement!Q26))</f>
@@ -33647,14 +33367,14 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B9" s="20" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C9" s="196">
         <f ca="1">Statement!AC151</f>
-        <v>3.4631455439416863</v>
+        <v>3.4059633733324164</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F9" s="200" t="str">
         <f>IF(Statement!M82&lt;=0,"N/A",_xlfn.RRI(4,Statement!M82,Statement!Q82))</f>
@@ -33667,11 +33387,11 @@
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="20" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C10" s="196">
         <f ca="1">Statement!AC152</f>
-        <v>2.9269065642300305</v>
+        <v>2.8785785721229762</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -33687,20 +33407,20 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B11" s="20" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C11" s="196">
         <f ca="1">Statement!AC155</f>
-        <v>2.5112090616086538</v>
+        <v>2.4557666474320259</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="20" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C12" s="196">
         <f ca="1">Statement!AC156</f>
-        <v>41.514548878498204</v>
+        <v>40.597991651756146</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -33709,7 +33429,7 @@
       </c>
       <c r="C15" s="248"/>
       <c r="E15" s="248" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F15" s="248"/>
     </row>
@@ -33738,7 +33458,7 @@
         <v>6.0489855471109168E-2</v>
       </c>
       <c r="E17" s="20" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F17" s="195">
         <f>Statement!AC59</f>
@@ -33754,7 +33474,7 @@
         <v>0.19578073705548546</v>
       </c>
       <c r="E18" s="20" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F18" s="199">
         <f>IF(OR(F16&lt;=0, F17&lt;=0),"N/A",F16-F17)</f>
@@ -33763,11 +33483,11 @@
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B21" s="248" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C21" s="248"/>
       <c r="E21" s="248" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F21" s="248"/>
     </row>
@@ -33839,11 +33559,11 @@
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B29" s="248" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C29" s="248"/>
       <c r="E29" s="248" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F29" s="248"/>
     </row>
@@ -33856,7 +33576,7 @@
         <v>65.477289171395597</v>
       </c>
       <c r="E30" s="20" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F30" s="202">
         <f>Statement!AC145</f>
@@ -33872,7 +33592,7 @@
         <v>0</v>
       </c>
       <c r="E31" s="20" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F31" s="202">
         <f>Statement!AC146</f>
@@ -33888,7 +33608,7 @@
         <v>25.312474696801676</v>
       </c>
       <c r="E32" s="20" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F32" s="202">
         <f>Statement!AC148</f>
@@ -33904,7 +33624,7 @@
         <v>40.164814474593925</v>
       </c>
       <c r="E33" s="20" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F33" s="202">
         <f>Statement!AC147</f>
@@ -33913,7 +33633,7 @@
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.2">
       <c r="E34" s="20" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F34" s="204" t="str">
         <f>Statement!AC149</f>
@@ -33922,24 +33642,24 @@
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B37" s="248" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C37" s="248"/>
       <c r="E37" s="248" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F37" s="248"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C38" s="197">
         <f ca="1">Statement!AC162</f>
-        <v>5.5813953488372099E-2</v>
+        <v>5.6751004965712941E-2</v>
       </c>
       <c r="E38" s="20" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F38" s="197">
         <f>Statement!AC168</f>
@@ -33948,14 +33668,14 @@
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B39" s="54" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C39" s="237">
         <f ca="1">Statement!AC161</f>
-        <v>1.9163479884147221E-2</v>
+        <v>1.9485212462008288E-2</v>
       </c>
       <c r="E39" s="20" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F39" s="197">
         <f>Statement!AC169</f>
@@ -33964,14 +33684,14 @@
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B40" s="20" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C40" s="197">
         <f ca="1">Statement!AC163</f>
         <v>0</v>
       </c>
       <c r="E40" s="20" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F40" s="197">
         <f>Statement!AC170</f>
@@ -33980,42 +33700,42 @@
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B41" s="20" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C41" s="197">
         <f ca="1">Statement!AC164</f>
-        <v>6.150535154631763E-2</v>
+        <v>6.2537954989161926E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B42" s="20" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C42" s="197">
         <f ca="1">Statement!AC165</f>
-        <v>6.150535154631763E-2</v>
+        <v>6.2537954989161926E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B45" s="248" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C45" s="248"/>
       <c r="E45" s="248" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F45" s="248"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C46" s="197">
         <f>Statement!AC171</f>
         <v>0.2236199519483876</v>
       </c>
       <c r="E46" s="20" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F46" s="196">
         <f>Statement!AC172</f>
@@ -34024,7 +33744,7 @@
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.2">
       <c r="E47" s="20" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F47" s="196">
         <f>Statement!AC175</f>
@@ -34033,33 +33753,33 @@
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.2">
       <c r="E48" s="20" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F48" s="197">
         <f ca="1">Statement!AC176</f>
-        <v>0.25212222018661906</v>
+        <v>0.2563550595418449</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B51" s="248" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C51" s="248"/>
       <c r="E51" s="248" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F51" s="248"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C52" s="197">
         <f>Statement!AC173</f>
         <v>0.69669698594761198</v>
       </c>
       <c r="E52" s="20" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F52" s="197">
         <f>Statement!AC177</f>
@@ -34068,14 +33788,14 @@
     </row>
     <row r="53" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B53" s="20" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C53" s="197">
         <f>Statement!AC174</f>
         <v>0.16003121393504871</v>
       </c>
       <c r="E53" s="20" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F53" s="197">
         <f>Statement!AC178</f>
@@ -34084,7 +33804,7 @@
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.2">
       <c r="E54" s="20" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F54" s="197">
         <f>Statement!AC179</f>
@@ -34181,7 +33901,7 @@
     </row>
     <row r="5" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B5" s="14" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C5" s="14"/>
       <c r="D5" s="14"/>
@@ -34216,12 +33936,12 @@
       </c>
       <c r="I6" s="194">
         <f ca="1">Statement!AC116</f>
-        <v>10.75</v>
+        <v>10.5725</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B7" s="20" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C7" s="195">
         <f>Statement!M153</f>
@@ -34245,12 +33965,12 @@
       </c>
       <c r="I7" s="195">
         <f ca="1">Statement!AC153</f>
-        <v>5615316.25</v>
+        <v>5522598.2374999998</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B8" s="20" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C8" s="195">
         <f>Statement!M154</f>
@@ -34274,12 +33994,12 @@
       </c>
       <c r="I8" s="195">
         <f ca="1">Statement!AC154</f>
-        <v>4199570.25</v>
+        <v>4106852.2374999998</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B9" s="20" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C9" s="196">
         <f>Statement!M150</f>
@@ -34303,12 +34023,12 @@
       </c>
       <c r="I9" s="196">
         <f ca="1">Statement!AC150</f>
-        <v>17.916666666666664</v>
+        <v>17.62083333333333</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B10" s="20" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C10" s="196">
         <f>Statement!M151</f>
@@ -34332,12 +34052,12 @@
       </c>
       <c r="I10" s="196">
         <f ca="1">Statement!AC151</f>
-        <v>3.4631455439416863</v>
+        <v>3.4059633733324164</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B11" s="20" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C11" s="196">
         <f>Statement!M152</f>
@@ -34361,12 +34081,12 @@
       </c>
       <c r="I11" s="196">
         <f ca="1">Statement!AC152</f>
-        <v>2.9269065642300305</v>
+        <v>2.8785785721229762</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B12" s="20" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C12" s="196">
         <f>Statement!M155</f>
@@ -34390,12 +34110,12 @@
       </c>
       <c r="I12" s="196">
         <f ca="1">Statement!AC155</f>
-        <v>2.5112090616086538</v>
+        <v>2.4557666474320259</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B13" s="20" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C13" s="196">
         <f>Statement!M156</f>
@@ -34419,7 +34139,7 @@
       </c>
       <c r="I13" s="196">
         <f ca="1">Statement!AC156</f>
-        <v>41.514548878498204</v>
+        <v>40.597991651756146</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34522,7 +34242,7 @@
     </row>
     <row r="20" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B20" s="14" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C20" s="14"/>
       <c r="D20" s="14"/>
@@ -34562,7 +34282,7 @@
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C22" s="199">
         <f>Statement!M59</f>
@@ -34591,7 +34311,7 @@
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B23" s="20" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C23" s="217" t="str">
         <f>IF(OR(C21&lt;=0, C22&lt;=0),"N/A",C21-C22)</f>
@@ -34620,7 +34340,7 @@
     </row>
     <row r="25" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B25" s="14" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C25" s="14"/>
       <c r="D25" s="14"/>
@@ -34776,7 +34496,7 @@
     </row>
     <row r="32" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B32" s="14" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C32" s="14"/>
       <c r="D32" s="14"/>
@@ -34874,7 +34594,7 @@
     </row>
     <row r="37" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B37" s="14" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C37" s="14"/>
       <c r="D37" s="14"/>
@@ -35001,7 +34721,7 @@
     </row>
     <row r="43" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B43" s="14" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C43" s="14"/>
       <c r="D43" s="14"/>
@@ -35012,7 +34732,7 @@
     </row>
     <row r="44" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B44" s="20" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C44" s="202">
         <f>Statement!M145</f>
@@ -35041,7 +34761,7 @@
     </row>
     <row r="45" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B45" s="20" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C45" s="202">
         <f>Statement!M146</f>
@@ -35070,7 +34790,7 @@
     </row>
     <row r="46" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C46" s="202">
         <f>Statement!M147</f>
@@ -35099,7 +34819,7 @@
     </row>
     <row r="47" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B47" s="20" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C47" s="202">
         <f>Statement!M148</f>
@@ -35128,7 +34848,7 @@
     </row>
     <row r="48" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B48" s="20" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C48" s="204" t="str">
         <f>Statement!M149</f>
@@ -35157,7 +34877,7 @@
     </row>
     <row r="50" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B50" s="14" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C50" s="14"/>
       <c r="D50" s="14"/>
@@ -35168,7 +34888,7 @@
     </row>
     <row r="51" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B51" s="20" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C51" s="197">
         <f>Statement!M162</f>
@@ -35192,12 +34912,12 @@
       </c>
       <c r="I51" s="197">
         <f ca="1">Statement!AC162</f>
-        <v>5.5813953488372099E-2</v>
+        <v>5.6751004965712941E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C52" s="197">
         <f>Statement!M161</f>
@@ -35221,12 +34941,12 @@
       </c>
       <c r="I52" s="197">
         <f ca="1">Statement!AC161</f>
-        <v>1.9163479884147221E-2</v>
+        <v>1.9485212462008288E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B53" s="20" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C53" s="197">
         <f>Statement!M163</f>
@@ -35255,7 +34975,7 @@
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B54" s="20" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C54" s="197">
         <f>Statement!M164</f>
@@ -35279,12 +34999,12 @@
       </c>
       <c r="I54" s="197">
         <f ca="1">Statement!AC164</f>
-        <v>6.150535154631763E-2</v>
+        <v>6.2537954989161926E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B55" s="20" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C55" s="197">
         <f>Statement!M165</f>
@@ -35308,12 +35028,12 @@
       </c>
       <c r="I55" s="197">
         <f ca="1">Statement!AC165</f>
-        <v>6.150535154631763E-2</v>
+        <v>6.2537954989161926E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B57" s="14" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C57" s="14"/>
       <c r="D57" s="14"/>
@@ -35324,7 +35044,7 @@
     </row>
     <row r="58" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B58" s="20" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C58" s="197">
         <f>Statement!M168</f>
@@ -35353,7 +35073,7 @@
     </row>
     <row r="59" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B59" s="20" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C59" s="197">
         <f>Statement!M169</f>
@@ -35382,7 +35102,7 @@
     </row>
     <row r="60" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B60" s="20" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C60" s="197">
         <f>Statement!M170</f>
@@ -35411,7 +35131,7 @@
     </row>
     <row r="62" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B62" s="14" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C62" s="14"/>
       <c r="D62" s="14"/>
@@ -35422,7 +35142,7 @@
     </row>
     <row r="63" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B63" s="20" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C63" s="197">
         <f>Statement!M171</f>
@@ -35451,7 +35171,7 @@
     </row>
     <row r="65" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B65" s="14" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C65" s="14"/>
       <c r="D65" s="14"/>
@@ -35462,7 +35182,7 @@
     </row>
     <row r="66" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B66" s="20" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C66" s="196">
         <f>Statement!M172</f>
@@ -35491,7 +35211,7 @@
     </row>
     <row r="67" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B67" s="20" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C67" s="196">
         <f>Statement!M175</f>
@@ -35520,7 +35240,7 @@
     </row>
     <row r="68" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B68" s="20" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C68" s="218">
         <f>Statement!M176</f>
@@ -35544,12 +35264,12 @@
       </c>
       <c r="I68" s="218">
         <f ca="1">Statement!AC176</f>
-        <v>0.25212222018661906</v>
+        <v>0.2563550595418449</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B70" s="14" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C70" s="14"/>
       <c r="D70" s="14"/>
@@ -35560,7 +35280,7 @@
     </row>
     <row r="71" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B71" s="20" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C71" s="197">
         <f>Statement!M173</f>
@@ -35589,7 +35309,7 @@
     </row>
     <row r="72" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B72" s="20" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C72" s="197">
         <f>Statement!M174</f>
@@ -35618,7 +35338,7 @@
     </row>
     <row r="74" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B74" s="14" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C74" s="14"/>
       <c r="D74" s="14"/>
@@ -35629,7 +35349,7 @@
     </row>
     <row r="75" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B75" s="20" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C75" s="197">
         <f>Statement!M177</f>
@@ -35658,7 +35378,7 @@
     </row>
     <row r="76" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B76" s="20" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C76" s="197">
         <f>Statement!M178</f>
@@ -35687,7 +35407,7 @@
     </row>
     <row r="77" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B77" s="20" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C77" s="197">
         <f>Statement!M179</f>
@@ -35831,7 +35551,7 @@
     </row>
     <row r="84" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B84" s="20" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C84" s="197">
         <f>Statement!M96</f>
@@ -35857,7 +35577,7 @@
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B85" s="20" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C85" s="197">
         <f>Statement!M98</f>
@@ -35883,7 +35603,7 @@
     </row>
     <row r="88" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B88" s="14" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C88" s="14"/>
       <c r="D88" s="14"/>
@@ -35894,7 +35614,7 @@
     </row>
     <row r="89" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B89" s="20" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C89" s="197">
         <f>Statement!M194</f>
@@ -35920,7 +35640,7 @@
     </row>
     <row r="90" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B90" s="20" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C90" s="197">
         <f>Statement!M195</f>
@@ -35946,7 +35666,7 @@
     </row>
     <row r="91" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B91" s="20" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C91" s="197">
         <f>Statement!M196</f>
@@ -35972,7 +35692,7 @@
     </row>
     <row r="93" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B93" s="14" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C93" s="14"/>
       <c r="D93" s="14"/>
@@ -35983,7 +35703,7 @@
     </row>
     <row r="94" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B94" s="20" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C94" s="197">
         <f>Statement!M200</f>
@@ -36031,11 +35751,11 @@
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
       <c r="C3" s="252" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D3" s="253"/>
       <c r="F3" s="254" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="G3" s="253"/>
     </row>
@@ -36060,7 +35780,7 @@
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="8" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C5" s="10" t="str">
         <f>Statement!Z3</f>
@@ -36102,7 +35822,7 @@
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B7" s="228" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C7" s="255">
         <f>Statement!AA89</f>
@@ -36141,7 +35861,7 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B9" s="228" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C9" s="255">
         <f>Statement!AA90</f>
@@ -36180,7 +35900,7 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B11" s="228" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C11" s="255">
         <f>Statement!AA91</f>
@@ -36219,7 +35939,7 @@
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B13" s="228" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C13" s="255">
         <f>Statement!AA95</f>
@@ -36237,7 +35957,7 @@
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="229" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C14" s="222">
         <f>Statement!Z12</f>
@@ -36258,7 +35978,7 @@
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B15" s="228" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C15" s="255">
         <f>Statement!AA96</f>
@@ -36297,7 +36017,7 @@
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B17" s="228" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C17" s="255">
         <f>Statement!AA98</f>
@@ -36315,7 +36035,7 @@
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="229" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C18" s="222">
         <f>Statement!Z22</f>
@@ -36336,7 +36056,7 @@
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B19" s="228" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C19" s="255">
         <f>IF(C18=0,
@@ -36378,7 +36098,7 @@
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B21" s="228" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C21" s="255">
         <f>IF(C20=0,
@@ -36399,7 +36119,7 @@
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C23" s="10" t="str">
         <f>C5</f>
@@ -36441,7 +36161,7 @@
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B25" s="228" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C25" s="255">
         <f>IF(C24=0,
@@ -36483,7 +36203,7 @@
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B27" s="228" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C27" s="255">
         <f>IF(C26=0,
@@ -36525,7 +36245,7 @@
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B29" s="228" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C29" s="255">
         <f>IF(C28=0,
@@ -36546,7 +36266,7 @@
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B31" s="8" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C31" s="10" t="str">
         <f>C5</f>
@@ -36588,7 +36308,7 @@
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B33" s="228" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C33" s="255">
         <f>IF(C32=0,
@@ -36630,7 +36350,7 @@
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B35" s="228" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C35" s="255">
         <f>IF(C34=0,
@@ -36920,7 +36640,7 @@
     </row>
     <row r="60" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B60" s="20" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C60" s="64">
         <f>Statement!H157</f>
@@ -36965,7 +36685,7 @@
     </row>
     <row r="61" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B61" s="20" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C61" s="64">
         <f>Statement!H158</f>
@@ -37145,7 +36865,7 @@
     </row>
     <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B65" s="20" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C65" s="64">
         <f>Statement!H184</f>
@@ -37190,7 +36910,7 @@
     </row>
     <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B66" s="20" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C66" s="64">
         <f>Statement!H185</f>
@@ -37235,7 +36955,7 @@
     </row>
     <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B67" s="20" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C67" s="64">
         <f>Statement!H186</f>
@@ -37723,7 +37443,7 @@
     </row>
     <row r="63" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B63" s="20" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C63" s="64">
         <f>Statement!T184</f>
@@ -37760,7 +37480,7 @@
     </row>
     <row r="64" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B64" s="20" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C64" s="64">
         <f>Statement!T185</f>
@@ -37797,7 +37517,7 @@
     </row>
     <row r="65" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B65" s="20" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C65" s="64">
         <f>Statement!T186</f>
@@ -37834,7 +37554,7 @@
     </row>
     <row r="66" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B66" s="20" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C66" s="64">
         <f>Statement!T157</f>

--- a/PATH.xlsx
+++ b/PATH.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9E8A4D7-5F40-8645-B15B-DE4B408564F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{429B8039-99B6-8842-810E-0C385785D173}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="9" activeTab="13" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -82,7 +82,7 @@
     Take the closing price of the last day of the period. In case the price has seen heavy fluctuations make an average of the last days. Info found at Yahoo Finance in the Historical Data section</t>
       </text>
     </comment>
-    <comment ref="B213" authorId="2" shapeId="0" xr:uid="{BD518828-4CC2-0B4C-8B09-D92EFD9BB7AB}">
+    <comment ref="B216" authorId="2" shapeId="0" xr:uid="{BD518828-4CC2-0B4C-8B09-D92EFD9BB7AB}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -90,7 +90,7 @@
     Actual value</t>
       </text>
     </comment>
-    <comment ref="B214" authorId="3" shapeId="0" xr:uid="{9D8CB7E8-8C73-9749-8D8A-8250F244A2BB}">
+    <comment ref="B217" authorId="3" shapeId="0" xr:uid="{9D8CB7E8-8C73-9749-8D8A-8250F244A2BB}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -135,7 +135,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="5">
+  <futureMetadata name="XLRICHVALUE" count="2">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -146,28 +146,7 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="3"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="4"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="5"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="8"/>
         </ext>
       </extLst>
     </bk>
@@ -177,28 +156,19 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="5">
+  <valueMetadata count="2">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
     </bk>
-    <bk>
-      <rc t="2" v="2"/>
-    </bk>
-    <bk>
-      <rc t="2" v="3"/>
-    </bk>
-    <bk>
-      <rc t="2" v="4"/>
-    </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="769" uniqueCount="419">
   <si>
     <t>Ticker</t>
   </si>
@@ -1430,9 +1400,6 @@
     <t>Applied EV/FCFF ratio</t>
   </si>
   <si>
-    <t>Capital intensity</t>
-  </si>
-  <si>
     <t>Common size growth rates</t>
   </si>
   <si>
@@ -1446,6 +1413,18 @@
   </si>
   <si>
     <t>Marketable securities and investments</t>
+  </si>
+  <si>
+    <t>Debt/EBIT</t>
+  </si>
+  <si>
+    <t>Net Debt/EBIT</t>
+  </si>
+  <si>
+    <t>Sales/Invested Capital</t>
+  </si>
+  <si>
+    <t>Sales/Assets</t>
   </si>
 </sst>
 </file>
@@ -2311,9 +2290,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="2" fontId="10" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -2382,7 +2358,6 @@
     <xf numFmtId="0" fontId="0" fillId="17" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="39" fontId="0" fillId="17" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -2394,6 +2369,12 @@
     <xf numFmtId="10" fontId="12" fillId="2" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="12" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -11814,7 +11795,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=c1dbvh&amp;q=XNYS%3aPATH&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
@@ -11833,9 +11814,11 @@
     <v>Powered by Refinitiv</v>
     <v>19.84</v>
     <v>9.2002000000000006</v>
-    <v>0.97399999999999998</v>
-    <v>-0.17749999999999999</v>
-    <v>-1.6511999999999999E-2</v>
+    <v>0.97860000000000003</v>
+    <v>-0.26</v>
+    <v>-2.4714999999999997E-2</v>
+    <v>0.08</v>
+    <v>7.8200000000000006E-3</v>
     <v>USD</v>
     <v>UiPath, Inc. is focused on agentic automation and orchestration, empowering enterprises to harness the full potential of AI agents to autonomously execute and optimize complex business processes. It is focused on building and managing automations, starting with computer vision technology and user interface automation in its initial robotic process automation offering. Its AI-powered UiPath Platform offers a robust set of capabilities that allows its customers to discover opportunities for automation, automate using a digital workforce that seamlessly collaborates with humans, and operate a mission-critical automation program at scale. It enables employees to quickly build automations for both existing and new processes and to automate a range of actions including logging into applications, moving folders, filling in forms, reading emails and others. Its platform allows users to design and combine UI automations, API integrations and AI-based document understanding in a single workflow.</v>
     <v>3981</v>
@@ -11843,49 +11826,35 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>One Vanderbilt Avenue, 60th Floor, NEW YORK, NY, 10017 US</v>
-    <v>10.72</v>
+    <v>10.8</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46184.657924988278</v>
+    <v>46190.872235647657</v>
     <v>0</v>
-    <v>10.305</v>
-    <v>5477826871</v>
+    <v>10.23</v>
+    <v>5315914278</v>
     <v>UIPATH, INC.</v>
     <v>UIPATH, INC.</v>
-    <v>10.46</v>
-    <v>17.574000000000002</v>
-    <v>10.75</v>
-    <v>10.5725</v>
+    <v>10.44</v>
+    <v>17.054500000000001</v>
+    <v>10.52</v>
+    <v>10.26</v>
+    <v>10.31</v>
     <v>518120300</v>
     <v>PATH</v>
     <v>UIPATH, INC. (XNYS:PATH)</v>
-    <v>19387541</v>
-    <v>43177471</v>
+    <v>40413749</v>
+    <v>45663865</v>
     <v>2015</v>
   </rv>
   <rv s="2">
     <v>1</v>
   </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Price (Extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Change (extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Change % (extended hours)</v>
-    <v>0</v>
-  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="4">
+  <rv s="3">
     <v>5</v>
     <v>10 Y TSY YLD NDX</v>
     <v>6</v>
@@ -11899,28 +11868,28 @@
     <v>Powered by Refinitiv</v>
     <v>46.87</v>
     <v>39.47</v>
-    <v>0.14000000000000001</v>
-    <v>3.0919999999999997E-3</v>
+    <v>-0.41</v>
+    <v>-9.1739999999999999E-3</v>
     <v>US</v>
-    <v>45.6</v>
+    <v>44.59</v>
     <v>Index</v>
-    <v>6</v>
-    <v>45.13</v>
+    <v>3</v>
+    <v>44.2</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>45.34</v>
-    <v>45.28</v>
-    <v>45.42</v>
+    <v>44.43</v>
+    <v>44.69</v>
+    <v>44.28</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="2">
-    <v>7</v>
+    <v>4</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -11942,6 +11911,8 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
+    <k n="Change (Extended hours)"/>
+    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -11962,6 +11933,7 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
+    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -11971,11 +11943,6 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
-  </s>
-  <s t="_error">
-    <k n="errorType" t="i"/>
-    <k n="field" t="s"/>
-    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -12011,7 +11978,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="42">
+    <a count="45">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -12022,13 +11989,16 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
+      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
+      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
+      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -12122,13 +12092,19 @@
       <v>8</v>
       <v>9</v>
       <v>4</v>
+      <v>1</v>
+      <v>1</v>
+      <v>5</v>
     </spb>
     <spb s="4">
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
       <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
+      <v>Real-Time Nasdaq Last Sale</v>
+      <v>from close</v>
+      <v>from close</v>
     </spb>
     <spb s="0">
       <v>1</v>
@@ -12200,6 +12176,9 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
+    <k n="Price (Extended hours)" t="i"/>
+    <k n="Change (Extended hours)" t="i"/>
+    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -12207,6 +12186,9 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
+    <k n="Price (Extended hours)" t="s"/>
+    <k n="Change (Extended hours)" t="s"/>
+    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="UniqueName" t="spb"/>
@@ -12613,10 +12595,10 @@
   <threadedComment ref="B116" dT="2026-04-25T21:52:20.00" personId="{A0F62302-F8D3-B346-B5DF-839B413AE710}" id="{8A10573A-B1E5-5443-A272-E27CCC9C056F}">
     <text>Take the closing price of the last day of the period. In case the price has seen heavy fluctuations make an average of the last days. Info found at Yahoo Finance in the Historical Data section</text>
   </threadedComment>
-  <threadedComment ref="B213" dT="2026-05-20T20:26:42.93" personId="{A0F62302-F8D3-B346-B5DF-839B413AE710}" id="{BD518828-4CC2-0B4C-8B09-D92EFD9BB7AB}">
+  <threadedComment ref="B216" dT="2026-05-20T20:26:42.93" personId="{A0F62302-F8D3-B346-B5DF-839B413AE710}" id="{BD518828-4CC2-0B4C-8B09-D92EFD9BB7AB}">
     <text>Actual value</text>
   </threadedComment>
-  <threadedComment ref="B214" dT="2026-05-20T20:26:51.62" personId="{A0F62302-F8D3-B346-B5DF-839B413AE710}" id="{9D8CB7E8-8C73-9749-8D8A-8250F244A2BB}">
+  <threadedComment ref="B217" dT="2026-05-20T20:26:51.62" personId="{A0F62302-F8D3-B346-B5DF-839B413AE710}" id="{9D8CB7E8-8C73-9749-8D8A-8250F244A2BB}">
     <text>Actual value</text>
   </threadedComment>
 </ThreadedComments>
@@ -12680,7 +12662,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{825B172E-7ADE-4B4A-B533-F037BCFCDCB0}">
-  <dimension ref="B1:I49"/>
+  <dimension ref="B1:I59"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="1" customWidth="1"/>
@@ -12711,259 +12693,259 @@
       <c r="I2" s="250"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B3" s="207" t="s">
+      <c r="B3" s="206" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="239" t="e" vm="1">
+      <c r="C3" s="238" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
       <c r="D3" s="2"/>
-      <c r="E3" s="207" t="s">
+      <c r="E3" s="206" t="s">
         <v>288</v>
       </c>
-      <c r="F3" s="209">
+      <c r="F3" s="208">
         <f ca="1">Statement!AC153</f>
-        <v>5522598.2374999998</v>
-      </c>
-      <c r="H3" s="207" t="str">
+        <v>5359362.3</v>
+      </c>
+      <c r="H3" s="206" t="str">
         <f>'AVG target price'!B5</f>
         <v>DCF price</v>
       </c>
-      <c r="I3" s="233">
-        <f ca="1">'AVG target price'!C5</f>
-        <v>6.8822824136162613</v>
+      <c r="I3" s="232">
+        <f>'AVG target price'!C5</f>
+        <v>6.2175596245918179</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B4" s="207" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="211" t="str" cm="1">
+      <c r="B4" s="206" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="210" t="str" cm="1">
         <f t="array" aca="1" ref="C4" ca="1">_FV(C3,"Ticker symbol",TRUE)</f>
         <v>PATH</v>
       </c>
-      <c r="E4" s="208" t="s">
+      <c r="E4" s="207" t="s">
         <v>229</v>
       </c>
-      <c r="F4" s="210">
+      <c r="F4" s="209">
         <f ca="1">Statement!AC154</f>
-        <v>4106852.2374999998</v>
-      </c>
-      <c r="H4" s="207" t="str">
+        <v>3943616.3</v>
+      </c>
+      <c r="H4" s="206" t="str">
         <f>'AVG target price'!B6</f>
         <v>EV/EBIT price</v>
       </c>
-      <c r="I4" s="233">
-        <f ca="1">'AVG target price'!C6</f>
-        <v>16.085299241165604</v>
+      <c r="I4" s="232">
+        <f>'AVG target price'!C6</f>
+        <v>15.469508957927841</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B5" s="207" t="s">
+      <c r="B5" s="206" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="230" cm="1">
+      <c r="C5" s="229" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>10.5725</v>
-      </c>
-      <c r="E5" s="207" t="s">
+        <v>10.26</v>
+      </c>
+      <c r="E5" s="206" t="s">
         <v>292</v>
       </c>
-      <c r="F5" s="211">
+      <c r="F5" s="210">
         <f>Statement!AC26</f>
         <v>0.60000000000000009</v>
       </c>
-      <c r="H5" s="207" t="str">
+      <c r="H5" s="206" t="str">
         <f>'AVG target price'!B7</f>
         <v>PS price</v>
       </c>
-      <c r="I5" s="233">
+      <c r="I5" s="232">
         <f>'AVG target price'!C7</f>
         <v>13.993493556532998</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B6" s="207" t="s">
+      <c r="B6" s="206" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="230" t="e" cm="1" vm="2">
-        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E6" s="207" t="s">
+      <c r="C6" s="229" cm="1">
+        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>10.31</v>
+      </c>
+      <c r="E6" s="206" t="s">
         <v>286</v>
       </c>
-      <c r="F6" s="212">
+      <c r="F6" s="211">
         <f ca="1">Statement!AC150</f>
-        <v>17.62083333333333</v>
-      </c>
-      <c r="H6" s="207" t="str">
+        <v>17.099999999999998</v>
+      </c>
+      <c r="H6" s="206" t="str">
         <f>'AVG target price'!B8</f>
         <v>EV/FCFF price</v>
       </c>
-      <c r="I6" s="233">
-        <f ca="1">'AVG target price'!C8</f>
-        <v>10.691532697497239</v>
+      <c r="I6" s="232">
+        <f>'AVG target price'!C8</f>
+        <v>10.334200177437685</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B7" s="207" t="s">
+      <c r="B7" s="206" t="s">
         <v>3</v>
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-0.17749999999999999</v>
-      </c>
-      <c r="E7" s="208" t="s">
+        <v>-0.26</v>
+      </c>
+      <c r="E7" s="207" t="s">
         <v>242</v>
       </c>
-      <c r="F7" s="213">
+      <c r="F7" s="212">
         <f ca="1">Statement!AC151</f>
-        <v>3.4059633733324164</v>
-      </c>
-      <c r="H7" s="206" t="str">
+        <v>3.305290537752716</v>
+      </c>
+      <c r="H7" s="205" t="str">
         <f>'AVG target price'!B9</f>
         <v>AVG price</v>
       </c>
-      <c r="I7" s="234">
-        <f ca="1">'AVG target price'!C9</f>
-        <v>11.913151977203025</v>
+      <c r="I7" s="233">
+        <f>'AVG target price'!C9</f>
+        <v>11.503690579122585</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B8" s="207" t="s">
+      <c r="B8" s="206" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" t="e" cm="1" vm="3">
-        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E8" s="207" t="s">
+      <c r="C8" s="6" cm="1">
+        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>0.08</v>
+      </c>
+      <c r="E8" s="206" t="s">
         <v>314</v>
       </c>
-      <c r="F8" s="214">
+      <c r="F8" s="213">
         <f ca="1">Statement!AC161</f>
-        <v>1.9485212462008288E-2</v>
-      </c>
-      <c r="H8" s="206" t="str">
+        <v>2.0078694810388171E-2</v>
+      </c>
+      <c r="H8" s="205" t="str">
         <f>'AVG target price'!B11</f>
         <v>Upside/Downside</v>
       </c>
-      <c r="I8" s="235">
+      <c r="I8" s="234">
         <f ca="1">'AVG target price'!C11</f>
-        <v>0.12680557835923628</v>
+        <v>0.12121740537257168</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B9" s="207" t="s">
+      <c r="B9" s="206" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-1.6511999999999999E-2</v>
-      </c>
-      <c r="E9" s="207" t="s">
+        <v>-2.4714999999999997E-2</v>
+      </c>
+      <c r="E9" s="206" t="s">
         <v>337</v>
       </c>
-      <c r="F9" s="214">
+      <c r="F9" s="213">
         <f ca="1">Statement!AC162</f>
-        <v>5.6751004965712941E-2</v>
+        <v>5.8479532163742701E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B10" s="207" t="s">
+      <c r="B10" s="206" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" t="e" cm="1" vm="4">
-        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E10" s="207" t="s">
+      <c r="C10" s="73" cm="1">
+        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>7.8200000000000006E-3</v>
+      </c>
+      <c r="E10" s="206" t="s">
         <v>342</v>
       </c>
-      <c r="F10" s="214">
+      <c r="F10" s="213">
         <f ca="1">Statement!AC164</f>
-        <v>6.2537954989161926E-2</v>
+        <v>6.4442741629913702E-2</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B11" s="207" t="s">
+      <c r="B11" s="206" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="231" cm="1">
+      <c r="C11" s="230" cm="1">
         <f t="array" aca="1" ref="C11" ca="1">_FV(C3,"52 week high",TRUE)</f>
         <v>19.84</v>
       </c>
-      <c r="E11" s="208" t="s">
+      <c r="E11" s="207" t="s">
         <v>338</v>
       </c>
-      <c r="F11" s="215">
+      <c r="F11" s="214">
         <f ca="1">Statement!AC163</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B12" s="207" t="s">
+      <c r="B12" s="206" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="231" cm="1">
+      <c r="C12" s="230" cm="1">
         <f t="array" aca="1" ref="C12" ca="1">_FV(C3,"52 week low",TRUE)</f>
         <v>9.2002000000000006</v>
       </c>
-      <c r="E12" s="207" t="s">
+      <c r="E12" s="206" t="s">
         <v>121</v>
       </c>
-      <c r="F12" s="214">
+      <c r="F12" s="213">
         <f>Statement!AC123</f>
         <v>0.1127173202051847</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B13" s="207" t="s">
+      <c r="B13" s="206" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="231" cm="1">
+      <c r="C13" s="230" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>0.97399999999999998</v>
-      </c>
-      <c r="E13" s="207" t="s">
+        <v>0.97860000000000003</v>
+      </c>
+      <c r="E13" s="206" t="s">
         <v>123</v>
       </c>
-      <c r="F13" s="214">
+      <c r="F13" s="213">
         <f>Statement!AC125</f>
         <v>0.17205256008386913</v>
       </c>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B14" s="208" t="s">
+      <c r="B14" s="207" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="232" cm="1">
+      <c r="C14" s="231" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>43177471</v>
-      </c>
-      <c r="E14" s="208" t="s">
+        <v>45663865</v>
+      </c>
+      <c r="E14" s="207" t="s">
         <v>124</v>
       </c>
-      <c r="F14" s="215">
+      <c r="F14" s="214">
         <f>Statement!AC140</f>
         <v>0.2076253183886507</v>
       </c>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="E15" s="207" t="s">
+      <c r="E15" s="206" t="s">
         <v>339</v>
       </c>
-      <c r="F15" s="214">
+      <c r="F15" s="213">
         <f ca="1">Statement!AC176</f>
-        <v>0.2563550595418449</v>
+        <v>0.26416314493237375</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="E16" s="208" t="s">
+      <c r="E16" s="207" t="s">
         <v>344</v>
       </c>
-      <c r="F16" s="213">
+      <c r="F16" s="212">
         <f>Statement!AC175</f>
         <v>2.732462108272006</v>
       </c>
@@ -12973,62 +12955,62 @@
         <v>103</v>
       </c>
       <c r="C17" s="251"/>
-      <c r="E17" s="206" t="s">
+      <c r="E17" s="205" t="s">
         <v>345</v>
       </c>
-      <c r="F17" s="216">
+      <c r="F17" s="215">
         <f>Statement!AC171</f>
         <v>0.2236199519483876</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B18" s="206" t="s">
+      <c r="B18" s="205" t="s">
         <v>12</v>
       </c>
       <c r="C18" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="E18" s="207" t="s">
+      <c r="E18" s="206" t="s">
         <v>346</v>
       </c>
-      <c r="F18" s="212">
+      <c r="F18" s="211">
         <f>Statement!AC144</f>
         <v>40.164814474593925</v>
       </c>
       <c r="I18" s="50"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="206" t="s">
+      <c r="B19" s="205" t="s">
         <v>13</v>
       </c>
       <c r="C19" s="70">
         <v>1000</v>
       </c>
-      <c r="E19" s="207" t="s">
+      <c r="E19" s="206" t="s">
         <v>307</v>
       </c>
-      <c r="F19" s="212">
+      <c r="F19" s="211">
         <f>Statement!AC146</f>
         <v>-0.74396849127545694</v>
       </c>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B20" s="206" t="s">
+      <c r="B20" s="205" t="s">
         <v>104</v>
       </c>
       <c r="C20" s="69" t="s">
         <v>105</v>
       </c>
-      <c r="E20" s="208" t="s">
+      <c r="E20" s="207" t="s">
         <v>347</v>
       </c>
-      <c r="F20" s="213">
+      <c r="F20" s="212">
         <f>Statement!AC147</f>
         <v>2.063021693804965</v>
       </c>
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B21" s="206" t="s">
+      <c r="B21" s="205" t="s">
         <v>106</v>
       </c>
       <c r="C21" s="69" t="s">
@@ -13037,7 +13019,7 @@
       <c r="I21" s="50"/>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B22" s="206" t="s">
+      <c r="B22" s="205" t="s">
         <v>108</v>
       </c>
       <c r="C22" s="69" t="s">
@@ -13055,48 +13037,48 @@
       <c r="F25" s="250"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B26" s="206" t="s">
+      <c r="B26" s="205" t="s">
         <v>127</v>
       </c>
       <c r="C26" s="191">
         <v>0.21</v>
       </c>
-      <c r="E26" s="207" t="e" vm="5">
+      <c r="E26" s="206" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="F26" s="242" cm="1">
+      <c r="F26" s="240" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>45.42</v>
+        <v>44.28</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B27" s="206" t="s">
+      <c r="B27" s="205" t="s">
         <v>213</v>
       </c>
-      <c r="C27" s="244">
-        <v>0</v>
-      </c>
-      <c r="E27" s="208" t="s">
+      <c r="C27" s="242">
+        <v>0</v>
+      </c>
+      <c r="E27" s="207" t="s">
         <v>402</v>
       </c>
-      <c r="F27" s="243">
+      <c r="F27" s="241">
         <f ca="1">F26/1000</f>
-        <v>4.5420000000000002E-2</v>
+        <v>4.428E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="206" t="s">
+      <c r="B28" s="205" t="s">
         <v>406</v>
       </c>
-      <c r="C28" s="244">
-        <v>0</v>
+      <c r="C28" s="242">
+        <v>0.1</v>
       </c>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B29" s="206" t="s">
+      <c r="B29" s="205" t="s">
         <v>407</v>
       </c>
-      <c r="C29" s="244">
+      <c r="C29" s="242">
         <v>0.12</v>
       </c>
     </row>
@@ -13154,10 +13136,10 @@
       <c r="C44" s="41" t="s">
         <v>382</v>
       </c>
-      <c r="D44" s="41" t="s">
+      <c r="D44" s="41"/>
+      <c r="E44" s="41" t="s">
         <v>383</v>
       </c>
-      <c r="E44" s="240"/>
     </row>
     <row r="49" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B49" s="248"/>
@@ -13168,18 +13150,52 @@
       <c r="G49" s="248"/>
       <c r="H49" s="248"/>
     </row>
+    <row r="52" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B52" s="248" t="s">
+        <v>128</v>
+      </c>
+      <c r="C52" s="248"/>
+      <c r="D52" s="248"/>
+      <c r="E52" s="248"/>
+      <c r="F52" s="248"/>
+      <c r="G52" s="248"/>
+      <c r="H52" s="248"/>
+    </row>
+    <row r="54" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B54" s="41" t="s">
+        <v>395</v>
+      </c>
+      <c r="C54" s="41" t="s">
+        <v>382</v>
+      </c>
+      <c r="D54" s="41"/>
+      <c r="E54" s="41" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="59" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B59" s="248"/>
+      <c r="C59" s="248"/>
+      <c r="D59" s="248"/>
+      <c r="E59" s="248"/>
+      <c r="F59" s="248"/>
+      <c r="G59" s="248"/>
+      <c r="H59" s="248"/>
+    </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="B33:H33"/>
-    <mergeCell ref="B39:H39"/>
-    <mergeCell ref="B42:H42"/>
-    <mergeCell ref="B49:H49"/>
+  <mergeCells count="12">
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="E25:F25"/>
+    <mergeCell ref="B52:H52"/>
+    <mergeCell ref="B59:H59"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="B49:H49"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -13413,27 +13429,27 @@
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="str">
-        <f>Statement!B184</f>
+        <f>Statement!B187</f>
         <v>Licenses</v>
       </c>
       <c r="C6" s="90">
-        <f>Statement!M184</f>
+        <f>Statement!M187</f>
         <v>481427</v>
       </c>
       <c r="D6" s="90">
-        <f>Statement!N184</f>
+        <f>Statement!N187</f>
         <v>497836</v>
       </c>
       <c r="E6" s="90">
-        <f>Statement!O184</f>
+        <f>Statement!O187</f>
         <v>621392</v>
       </c>
       <c r="F6" s="90">
-        <f>Statement!P184</f>
+        <f>Statement!P187</f>
         <v>587152</v>
       </c>
       <c r="G6" s="91">
-        <f>Statement!Q184</f>
+        <f>Statement!Q187</f>
         <v>606394</v>
       </c>
       <c r="H6" s="64">
@@ -13468,35 +13484,35 @@
         <v>Licenses</v>
       </c>
       <c r="S6" s="90">
-        <f>Statement!T184</f>
+        <f>Statement!T187</f>
         <v>112251</v>
       </c>
       <c r="T6" s="90">
-        <f>Statement!U184</f>
+        <f>Statement!U187</f>
         <v>137174</v>
       </c>
       <c r="U6" s="90">
-        <f>Statement!V184</f>
+        <f>Statement!V187</f>
         <v>197609</v>
       </c>
       <c r="V6" s="90">
-        <f>Statement!W184</f>
+        <f>Statement!W187</f>
         <v>128286</v>
       </c>
       <c r="W6" s="90">
-        <f>Statement!X184</f>
+        <f>Statement!X187</f>
         <v>112161</v>
       </c>
       <c r="X6" s="90">
-        <f>Statement!Y184</f>
+        <f>Statement!Y187</f>
         <v>150043</v>
       </c>
       <c r="Y6" s="90">
-        <f>Statement!Z184</f>
+        <f>Statement!Z187</f>
         <v>215904</v>
       </c>
       <c r="Z6" s="91">
-        <f>Statement!AA184</f>
+        <f>Statement!AA187</f>
         <v>149309</v>
       </c>
       <c r="AA6" s="64">
@@ -13512,27 +13528,27 @@
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B7" s="1" t="str">
-        <f>Statement!B185</f>
+        <f>Statement!B188</f>
         <v>Subscription services</v>
       </c>
       <c r="C7" s="90">
-        <f>Statement!M185</f>
+        <f>Statement!M188</f>
         <v>369867</v>
       </c>
       <c r="D7" s="90">
-        <f>Statement!N185</f>
+        <f>Statement!N188</f>
         <v>508823</v>
       </c>
       <c r="E7" s="90">
-        <f>Statement!O185</f>
+        <f>Statement!O188</f>
         <v>649918</v>
       </c>
       <c r="F7" s="90">
-        <f>Statement!P185</f>
+        <f>Statement!P188</f>
         <v>801947</v>
       </c>
       <c r="G7" s="91">
-        <f>Statement!Q185</f>
+        <f>Statement!Q188</f>
         <v>954472</v>
       </c>
       <c r="H7" s="64">
@@ -13567,35 +13583,35 @@
         <v>Subscription services</v>
       </c>
       <c r="S7" s="90">
-        <f>Statement!T185</f>
+        <f>Statement!T188</f>
         <v>194673</v>
       </c>
       <c r="T7" s="90">
-        <f>Statement!U185</f>
+        <f>Statement!U188</f>
         <v>206922</v>
       </c>
       <c r="U7" s="90">
-        <f>Statement!V185</f>
+        <f>Statement!V188</f>
         <v>215221</v>
       </c>
       <c r="V7" s="90">
-        <f>Statement!W185</f>
+        <f>Statement!W188</f>
         <v>217303</v>
       </c>
       <c r="W7" s="90">
-        <f>Statement!X185</f>
+        <f>Statement!X188</f>
         <v>238363</v>
       </c>
       <c r="X7" s="90">
-        <f>Statement!Y185</f>
+        <f>Statement!Y188</f>
         <v>247573</v>
       </c>
       <c r="Y7" s="90">
-        <f>Statement!Z185</f>
+        <f>Statement!Z188</f>
         <v>251233</v>
       </c>
       <c r="Z7" s="91">
-        <f>Statement!AA185</f>
+        <f>Statement!AA188</f>
         <v>252903</v>
       </c>
       <c r="AA7" s="64">
@@ -13611,27 +13627,27 @@
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B8" s="1" t="str">
-        <f>Statement!B186</f>
+        <f>Statement!B189</f>
         <v>Professional services</v>
       </c>
       <c r="C8" s="90">
-        <f>Statement!M186</f>
+        <f>Statement!M189</f>
         <v>40958</v>
       </c>
       <c r="D8" s="90">
-        <f>Statement!N186</f>
+        <f>Statement!N189</f>
         <v>51922</v>
       </c>
       <c r="E8" s="90">
-        <f>Statement!O186</f>
+        <f>Statement!O189</f>
         <v>36762</v>
       </c>
       <c r="F8" s="90">
-        <f>Statement!P186</f>
+        <f>Statement!P189</f>
         <v>40555</v>
       </c>
       <c r="G8" s="91">
-        <f>Statement!Q186</f>
+        <f>Statement!Q189</f>
         <v>49706</v>
       </c>
       <c r="H8" s="64">
@@ -13666,35 +13682,35 @@
         <v>Professional services</v>
       </c>
       <c r="S8" s="90">
-        <f>Statement!T186</f>
+        <f>Statement!T189</f>
         <v>9329</v>
       </c>
       <c r="T8" s="90">
-        <f>Statement!U186</f>
+        <f>Statement!U189</f>
         <v>10557</v>
       </c>
       <c r="U8" s="90">
-        <f>Statement!V186</f>
+        <f>Statement!V189</f>
         <v>10816</v>
       </c>
       <c r="V8" s="90">
-        <f>Statement!W186</f>
+        <f>Statement!W189</f>
         <v>11035</v>
       </c>
       <c r="W8" s="90">
-        <f>Statement!X186</f>
+        <f>Statement!X189</f>
         <v>11204</v>
       </c>
       <c r="X8" s="90">
-        <f>Statement!Y186</f>
+        <f>Statement!Y189</f>
         <v>13497</v>
       </c>
       <c r="Y8" s="90">
-        <f>Statement!Z186</f>
+        <f>Statement!Z189</f>
         <v>13970</v>
       </c>
       <c r="Z8" s="91">
-        <f>Statement!AA186</f>
+        <f>Statement!AA189</f>
         <v>16170</v>
       </c>
       <c r="AA8" s="64">
@@ -14412,23 +14428,23 @@
         <v>130</v>
       </c>
       <c r="C21" s="115">
-        <f>Statement!M210</f>
+        <f>Statement!M213</f>
         <v>925276</v>
       </c>
       <c r="D21" s="100">
-        <f>Statement!N210</f>
+        <f>Statement!N213</f>
         <v>1203845</v>
       </c>
       <c r="E21" s="100">
-        <f>Statement!O210</f>
+        <f>Statement!O213</f>
         <v>1463698</v>
       </c>
       <c r="F21" s="100">
-        <f>Statement!P210</f>
+        <f>Statement!P213</f>
         <v>1666136</v>
       </c>
       <c r="G21" s="101">
-        <f>Statement!Q210</f>
+        <f>Statement!Q213</f>
         <v>1852567</v>
       </c>
       <c r="H21" s="109">
@@ -14461,35 +14477,35 @@
         <v>130</v>
       </c>
       <c r="S21" s="100">
-        <f>Statement!T210</f>
+        <f>Statement!T213</f>
         <v>1550605</v>
       </c>
       <c r="T21" s="100">
-        <f>Statement!U210</f>
+        <f>Statement!U213</f>
         <v>1606561</v>
       </c>
       <c r="U21" s="100">
-        <f>Statement!V210</f>
+        <f>Statement!V213</f>
         <v>1666136</v>
       </c>
       <c r="V21" s="100">
-        <f>Statement!W210</f>
+        <f>Statement!W213</f>
         <v>1692683</v>
       </c>
       <c r="W21" s="100">
-        <f>Statement!X210</f>
+        <f>Statement!X213</f>
         <v>1723401</v>
       </c>
       <c r="X21" s="100">
-        <f>Statement!Y210</f>
+        <f>Statement!Y213</f>
         <v>1782384</v>
       </c>
       <c r="Y21" s="100">
-        <f>Statement!Z210</f>
+        <f>Statement!Z213</f>
         <v>1852567</v>
       </c>
       <c r="Z21" s="102">
-        <f>Statement!AA210</f>
+        <f>Statement!AA213</f>
         <v>1901211</v>
       </c>
       <c r="AA21" s="111">
@@ -14507,23 +14523,23 @@
         <v>132</v>
       </c>
       <c r="C22" s="116">
-        <f>Statement!M212</f>
+        <f>Statement!M215</f>
         <v>1.45</v>
       </c>
       <c r="D22" s="116">
-        <f>Statement!N212</f>
+        <f>Statement!N215</f>
         <v>1.23</v>
       </c>
       <c r="E22" s="116">
-        <f>Statement!O212</f>
+        <f>Statement!O215</f>
         <v>1.19</v>
       </c>
       <c r="F22" s="116">
-        <f>Statement!P212</f>
+        <f>Statement!P215</f>
         <v>1.1000000000000001</v>
       </c>
       <c r="G22" s="117">
-        <f>Statement!Q212</f>
+        <f>Statement!Q215</f>
         <v>1.07</v>
       </c>
       <c r="H22" s="118">
@@ -14548,35 +14564,35 @@
         <v>132</v>
       </c>
       <c r="S22" s="116">
-        <f>Statement!T212</f>
+        <f>Statement!T215</f>
         <v>1.1499999999999999</v>
       </c>
       <c r="T22" s="116">
-        <f>Statement!U212</f>
+        <f>Statement!U215</f>
         <v>1.1299999999999999</v>
       </c>
       <c r="U22" s="116">
-        <f>Statement!V212</f>
+        <f>Statement!V215</f>
         <v>1.1000000000000001</v>
       </c>
       <c r="V22" s="116">
-        <f>Statement!W212</f>
+        <f>Statement!W215</f>
         <v>1.08</v>
       </c>
       <c r="W22" s="116">
-        <f>Statement!X212</f>
+        <f>Statement!X215</f>
         <v>1.08</v>
       </c>
       <c r="X22" s="116">
-        <f>Statement!Y212</f>
+        <f>Statement!Y215</f>
         <v>1.07</v>
       </c>
       <c r="Y22" s="116">
-        <f>Statement!Z212</f>
+        <f>Statement!Z215</f>
         <v>1.07</v>
       </c>
       <c r="Z22" s="119">
-        <f>Statement!AA212</f>
+        <f>Statement!AA215</f>
         <v>1.0900000000000001</v>
       </c>
       <c r="AA22" s="118">
@@ -14594,23 +14610,23 @@
         <v>131</v>
       </c>
       <c r="C23" s="103">
-        <f>Statement!M211</f>
+        <f>Statement!M214</f>
         <v>344793</v>
       </c>
       <c r="D23" s="103">
-        <f>Statement!N211</f>
+        <f>Statement!N214</f>
         <v>278569</v>
       </c>
       <c r="E23" s="103">
-        <f>Statement!O211</f>
+        <f>Statement!O214</f>
         <v>259853</v>
       </c>
       <c r="F23" s="103">
-        <f>Statement!P211</f>
+        <f>Statement!P214</f>
         <v>202438</v>
       </c>
       <c r="G23" s="104">
-        <f>Statement!Q211</f>
+        <f>Statement!Q214</f>
         <v>186431</v>
       </c>
       <c r="H23" s="24">
@@ -14644,35 +14660,35 @@
         <v>131</v>
       </c>
       <c r="S23" s="103">
-        <f>Statement!T211</f>
+        <f>Statement!T214</f>
         <v>43000</v>
       </c>
       <c r="T23" s="103">
-        <f>Statement!U211</f>
+        <f>Statement!U214</f>
         <v>56000</v>
       </c>
       <c r="U23" s="103">
-        <f>Statement!V211</f>
+        <f>Statement!V214</f>
         <v>60000</v>
       </c>
       <c r="V23" s="103">
-        <f>Statement!W211</f>
+        <f>Statement!W214</f>
         <v>27000</v>
       </c>
       <c r="W23" s="103">
-        <f>Statement!X211</f>
+        <f>Statement!X214</f>
         <v>31000</v>
       </c>
       <c r="X23" s="103">
-        <f>Statement!Y211</f>
+        <f>Statement!Y214</f>
         <v>59000</v>
       </c>
       <c r="Y23" s="103">
-        <f>Statement!Z211</f>
+        <f>Statement!Z214</f>
         <v>70000</v>
       </c>
       <c r="Z23" s="105">
-        <f>Statement!AA211</f>
+        <f>Statement!AA214</f>
         <v>49000</v>
       </c>
       <c r="AA23" s="24">
@@ -14747,19 +14763,19 @@
       </c>
       <c r="C25" s="47"/>
       <c r="D25" s="100">
-        <f>Statement!N214-Statement!M214</f>
+        <f>Statement!N217-Statement!M217</f>
         <v>292</v>
       </c>
       <c r="E25" s="100">
-        <f>Statement!O214-Statement!N214</f>
+        <f>Statement!O217-Statement!N217</f>
         <v>269</v>
       </c>
       <c r="F25" s="100">
-        <f>Statement!P214-Statement!O214</f>
+        <f>Statement!P217-Statement!O217</f>
         <v>238</v>
       </c>
       <c r="G25" s="101">
-        <f>Statement!Q214-Statement!P214</f>
+        <f>Statement!Q217-Statement!P217</f>
         <v>273</v>
       </c>
       <c r="H25" s="111">
@@ -14784,31 +14800,31 @@
       </c>
       <c r="S25" s="47"/>
       <c r="T25" s="120">
-        <f>Statement!U214-Statement!T214</f>
+        <f>Statement!U217-Statement!T217</f>
         <v>72</v>
       </c>
       <c r="U25" s="120">
-        <f>Statement!V214-Statement!U214</f>
+        <f>Statement!V217-Statement!U217</f>
         <v>57</v>
       </c>
       <c r="V25" s="120">
-        <f>Statement!W214-Statement!V214</f>
+        <f>Statement!W217-Statement!V217</f>
         <v>73</v>
       </c>
       <c r="W25" s="120">
-        <f>Statement!X214-Statement!W214</f>
+        <f>Statement!X217-Statement!W217</f>
         <v>67</v>
       </c>
       <c r="X25" s="120">
-        <f>Statement!Y214-Statement!X214</f>
+        <f>Statement!Y217-Statement!X217</f>
         <v>74</v>
       </c>
       <c r="Y25" s="120">
-        <f>Statement!Z214-Statement!Y214</f>
+        <f>Statement!Z217-Statement!Y217</f>
         <v>59</v>
       </c>
       <c r="Z25" s="121">
-        <f>Statement!AA214-Statement!Z214</f>
+        <f>Statement!AA217-Statement!Z217</f>
         <v>59</v>
       </c>
       <c r="AA25" s="106">
@@ -15837,27 +15853,27 @@
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B11" s="39" t="str">
-        <f>Statement!B188</f>
+        <f>Statement!B191</f>
         <v>Licenses COGS</v>
       </c>
       <c r="C11" s="128">
-        <f>Statement!M188</f>
+        <f>Statement!M191</f>
         <v>11888</v>
       </c>
       <c r="D11" s="128">
-        <f>Statement!N188</f>
+        <f>Statement!N191</f>
         <v>10421</v>
       </c>
       <c r="E11" s="128">
-        <f>Statement!O188</f>
+        <f>Statement!O191</f>
         <v>10469</v>
       </c>
       <c r="F11" s="128">
-        <f>Statement!P188</f>
+        <f>Statement!P191</f>
         <v>8565</v>
       </c>
       <c r="G11" s="129">
-        <f>Statement!Q188</f>
+        <f>Statement!Q191</f>
         <v>5334</v>
       </c>
       <c r="H11" s="25">
@@ -15886,35 +15902,35 @@
         <v>Licenses COGS</v>
       </c>
       <c r="P11" s="128">
-        <f>Statement!T188</f>
+        <f>Statement!T191</f>
         <v>2393</v>
       </c>
       <c r="Q11" s="128">
-        <f>Statement!U188</f>
+        <f>Statement!U191</f>
         <v>2340</v>
       </c>
       <c r="R11" s="128">
-        <f>Statement!V188</f>
+        <f>Statement!V191</f>
         <v>1231</v>
       </c>
       <c r="S11" s="128">
-        <f>Statement!W188</f>
+        <f>Statement!W191</f>
         <v>1268</v>
       </c>
       <c r="T11" s="128">
-        <f>Statement!X188</f>
+        <f>Statement!X191</f>
         <v>1200</v>
       </c>
       <c r="U11" s="128">
-        <f>Statement!Y188</f>
+        <f>Statement!Y191</f>
         <v>1311</v>
       </c>
       <c r="V11" s="128">
-        <f>Statement!Z188</f>
+        <f>Statement!Z191</f>
         <v>1555</v>
       </c>
       <c r="W11" s="129">
-        <f>Statement!AA188</f>
+        <f>Statement!AA191</f>
         <v>1664</v>
       </c>
       <c r="X11" s="25">
@@ -15930,27 +15946,27 @@
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B12" s="39" t="str">
-        <f>Statement!B189</f>
+        <f>Statement!B192</f>
         <v>Subscription services COGS</v>
       </c>
       <c r="C12" s="128">
-        <f>Statement!M189</f>
+        <f>Statement!M192</f>
         <v>60565</v>
       </c>
       <c r="D12" s="128">
-        <f>Statement!N189</f>
+        <f>Statement!N192</f>
         <v>87366</v>
       </c>
       <c r="E12" s="128">
-        <f>Statement!O189</f>
+        <f>Statement!O192</f>
         <v>111922</v>
       </c>
       <c r="F12" s="128">
-        <f>Statement!P189</f>
+        <f>Statement!P192</f>
         <v>167630</v>
       </c>
       <c r="G12" s="129">
-        <f>Statement!Q189</f>
+        <f>Statement!Q192</f>
         <v>157588</v>
       </c>
       <c r="H12" s="25">
@@ -15979,35 +15995,35 @@
         <v>Subscription services COGS</v>
       </c>
       <c r="P12" s="128">
-        <f>Statement!T189</f>
+        <f>Statement!T192</f>
         <v>43529</v>
       </c>
       <c r="Q12" s="128">
-        <f>Statement!U189</f>
+        <f>Statement!U192</f>
         <v>43487</v>
       </c>
       <c r="R12" s="128">
-        <f>Statement!V189</f>
+        <f>Statement!V192</f>
         <v>43860</v>
       </c>
       <c r="S12" s="128">
-        <f>Statement!W189</f>
+        <f>Statement!W192</f>
         <v>38468</v>
       </c>
       <c r="T12" s="128">
-        <f>Statement!X189</f>
+        <f>Statement!X192</f>
         <v>38229</v>
       </c>
       <c r="U12" s="128">
-        <f>Statement!Y189</f>
+        <f>Statement!Y192</f>
         <v>40121</v>
       </c>
       <c r="V12" s="128">
-        <f>Statement!Z189</f>
+        <f>Statement!Z192</f>
         <v>40770</v>
       </c>
       <c r="W12" s="129">
-        <f>Statement!AA189</f>
+        <f>Statement!AA192</f>
         <v>43988</v>
       </c>
       <c r="X12" s="25">
@@ -16023,27 +16039,27 @@
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B13" s="39" t="str">
-        <f>Statement!B190</f>
+        <f>Statement!B193</f>
         <v>Professional services COGS</v>
       </c>
       <c r="C13" s="128">
-        <f>Statement!M190</f>
+        <f>Statement!M193</f>
         <v>96415</v>
       </c>
       <c r="D13" s="128">
-        <f>Statement!N190</f>
+        <f>Statement!N193</f>
         <v>82264</v>
       </c>
       <c r="E13" s="128">
-        <f>Statement!O190</f>
+        <f>Statement!O193</f>
         <v>73533</v>
       </c>
       <c r="F13" s="128">
-        <f>Statement!P190</f>
+        <f>Statement!P193</f>
         <v>70747</v>
       </c>
       <c r="G13" s="129">
-        <f>Statement!Q190</f>
+        <f>Statement!Q193</f>
         <v>108062</v>
       </c>
       <c r="H13" s="25">
@@ -16072,35 +16088,35 @@
         <v>Professional services COGS</v>
       </c>
       <c r="P13" s="128">
-        <f>Statement!T190</f>
+        <f>Statement!T193</f>
         <v>17398</v>
       </c>
       <c r="Q13" s="128">
-        <f>Statement!U190</f>
+        <f>Statement!U193</f>
         <v>17936</v>
       </c>
       <c r="R13" s="128">
-        <f>Statement!V190</f>
+        <f>Statement!V193</f>
         <v>19443</v>
       </c>
       <c r="S13" s="128">
-        <f>Statement!W190</f>
+        <f>Statement!W193</f>
         <v>24121</v>
       </c>
       <c r="T13" s="128">
-        <f>Statement!X190</f>
+        <f>Statement!X193</f>
         <v>24951</v>
       </c>
       <c r="U13" s="128">
-        <f>Statement!Y190</f>
+        <f>Statement!Y193</f>
         <v>27380</v>
       </c>
       <c r="V13" s="128">
-        <f>Statement!Z190</f>
+        <f>Statement!Z193</f>
         <v>31610</v>
       </c>
       <c r="W13" s="129">
-        <f>Statement!AA190</f>
+        <f>Statement!AA193</f>
         <v>31276</v>
       </c>
       <c r="X13" s="25">
@@ -19830,23 +19846,23 @@
         <f>Statement!Q101</f>
         <v>0.83174673345867178</v>
       </c>
-      <c r="H33" s="238">
+      <c r="H33" s="237">
         <f>H8/H6</f>
         <v>0.84199999999999997</v>
       </c>
-      <c r="I33" s="238">
+      <c r="I33" s="237">
         <f t="shared" ref="I33:L33" si="9">I8/I6</f>
         <v>0.84199999999999997</v>
       </c>
-      <c r="J33" s="238">
+      <c r="J33" s="237">
         <f t="shared" si="9"/>
         <v>0.85799999999999998</v>
       </c>
-      <c r="K33" s="238">
+      <c r="K33" s="237">
         <f t="shared" si="9"/>
         <v>0.8580000000000001</v>
       </c>
-      <c r="L33" s="238">
+      <c r="L33" s="237">
         <f t="shared" si="9"/>
         <v>0.873</v>
       </c>
@@ -19875,23 +19891,23 @@
         <f>Statement!Q102</f>
         <v>3.5242137575966802E-2</v>
       </c>
-      <c r="H34" s="238">
+      <c r="H34" s="237">
         <f>H10/H6</f>
         <v>7.1999999999999925E-2</v>
       </c>
-      <c r="I34" s="238">
+      <c r="I34" s="237">
         <f t="shared" ref="I34:L34" si="10">I10/I6</f>
         <v>7.1999999999999911E-2</v>
       </c>
-      <c r="J34" s="238">
+      <c r="J34" s="237">
         <f t="shared" si="10"/>
         <v>0.123</v>
       </c>
-      <c r="K34" s="238">
+      <c r="K34" s="237">
         <f t="shared" si="10"/>
         <v>0.12800000000000003</v>
       </c>
-      <c r="L34" s="238">
+      <c r="L34" s="237">
         <f t="shared" si="10"/>
         <v>0.17300000000000001</v>
       </c>
@@ -19990,7 +20006,7 @@
       </c>
       <c r="C6" s="154">
         <f ca="1">Overview!C5</f>
-        <v>10.5725</v>
+        <v>10.26</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19999,7 +20015,7 @@
       </c>
       <c r="C7" s="155">
         <f ca="1">C5*C6</f>
-        <v>5522598.2374999998</v>
+        <v>5359362.3</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20017,7 +20033,7 @@
       </c>
       <c r="C9" s="156">
         <f ca="1">Overview!F27</f>
-        <v>4.5420000000000002E-2</v>
+        <v>4.428E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20026,7 +20042,7 @@
       </c>
       <c r="C10" s="154">
         <f ca="1">Overview!C13</f>
-        <v>0.97399999999999998</v>
+        <v>0.97860000000000003</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20096,7 +20112,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>8.9249999999999996E-2</v>
+        <v>8.8317000000000007E-2</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20105,7 +20121,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>8.9249999999999996E-2</v>
+        <v>8.8317000000000007E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20355,8 +20371,8 @@
         <v>0</v>
       </c>
       <c r="L8" s="147">
-        <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>2932498.8090189225</v>
+        <f>L7*(1+C14)/(C15-C14)</f>
+        <v>2538444.2815570044</v>
       </c>
       <c r="N8" s="93"/>
       <c r="O8" s="16"/>
@@ -20409,24 +20425,24 @@
       <c r="F10" s="158"/>
       <c r="G10" s="159"/>
       <c r="H10" s="147">
-        <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>3306.3956310266703</v>
+        <f>H7/(1+$C$15)^H9</f>
+        <v>3274.0831282689096</v>
       </c>
       <c r="I10" s="147">
-        <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>-3550.0956797610329</v>
+        <f t="shared" ref="I10:L10" si="0">I7/(1+$C$15)^I9</f>
+        <v>-3481.0465021623909</v>
       </c>
       <c r="J10" s="147">
-        <f t="shared" ca="1" si="0"/>
-        <v>59723.338175455217</v>
+        <f t="shared" si="0"/>
+        <v>57989.414591845882</v>
       </c>
       <c r="K10" s="147">
-        <f t="shared" ca="1" si="0"/>
-        <v>77432.02543003943</v>
+        <f t="shared" si="0"/>
+        <v>74449.220213203545</v>
       </c>
       <c r="L10" s="147">
-        <f t="shared" ca="1" si="0"/>
-        <v>129843.318740039</v>
+        <f t="shared" si="0"/>
+        <v>123621.50445618207</v>
       </c>
       <c r="N10" s="93"/>
     </row>
@@ -20444,8 +20460,8 @@
       <c r="J11" s="158"/>
       <c r="K11" s="158"/>
       <c r="L11" s="147">
-        <f ca="1">L8/(1+C15)^L9</f>
-        <v>1912493.6478677229</v>
+        <f>L8/(1+C15)^L9</f>
+        <v>1576174.1818163213</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -20467,8 +20483,8 @@
         <v>206</v>
       </c>
       <c r="C15" s="156">
-        <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>8.9249999999999996E-2</v>
+        <f>IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
+        <v>0.1</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
@@ -20482,8 +20498,8 @@
         <v>228</v>
       </c>
       <c r="C19" s="64">
-        <f ca="1">SUM(H10:L10)</f>
-        <v>266754.98229679931</v>
+        <f>SUM(H10:L10)</f>
+        <v>255853.175887338</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -20491,8 +20507,8 @@
         <v>224</v>
       </c>
       <c r="C20" s="64">
-        <f ca="1">L11</f>
-        <v>1912493.6478677229</v>
+        <f>L11</f>
+        <v>1576174.1818163213</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -20500,8 +20516,8 @@
         <v>229</v>
       </c>
       <c r="C21" s="96">
-        <f ca="1">C19+C20</f>
-        <v>2179248.6301645222</v>
+        <f>C19+C20</f>
+        <v>1832027.3577036592</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -20527,8 +20543,8 @@
         <v>232</v>
       </c>
       <c r="C24" s="96">
-        <f ca="1">C21+C22-C23</f>
-        <v>3594994.6301645222</v>
+        <f>C21+C22-C23</f>
+        <v>3247773.3577036592</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -20545,8 +20561,8 @@
         <v>233</v>
       </c>
       <c r="C26" s="163">
-        <f ca="1">C24/C25</f>
-        <v>6.8822824136162613</v>
+        <f>C24/C25</f>
+        <v>6.2175596245918179</v>
       </c>
     </row>
   </sheetData>
@@ -21554,8 +21570,8 @@
         <v>206</v>
       </c>
       <c r="C39" s="156">
-        <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>8.9249999999999996E-2</v>
+        <f>IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
+        <v>0.1</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -21589,8 +21605,8 @@
         <v>408</v>
       </c>
       <c r="C43" s="24">
-        <f ca="1">C42/(1+C39)^5-G30+G31</f>
-        <v>8402236.4851190597</v>
+        <f>C42/(1+C39)^5-G30+G31</f>
+        <v>8080575.3517183978</v>
       </c>
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.2">
@@ -21607,8 +21623,8 @@
         <v>250</v>
       </c>
       <c r="C45" s="163">
-        <f ca="1">C43/C44</f>
-        <v>16.085299241165604</v>
+        <f>C43/C44</f>
+        <v>15.469508957927841</v>
       </c>
     </row>
     <row r="47" spans="2:14" x14ac:dyDescent="0.2">
@@ -21690,8 +21706,8 @@
         <v>206</v>
       </c>
       <c r="C57" s="156">
-        <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>8.9249999999999996E-2</v>
+        <f>IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
+        <v>0.1</v>
       </c>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.2">
@@ -21716,8 +21732,8 @@
         <v>408</v>
       </c>
       <c r="C60" s="24">
-        <f ca="1">C59/(1+C57)^5-G30+G31</f>
-        <v>5584775.5622011703</v>
+        <f>C59/(1+C57)^5-G30+G31</f>
+        <v>5398121.1336854622</v>
       </c>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.2">
@@ -21734,8 +21750,8 @@
         <v>250</v>
       </c>
       <c r="C62" s="163">
-        <f ca="1">C60/C61</f>
-        <v>10.691532697497239</v>
+        <f>C60/C61</f>
+        <v>10.334200177437685</v>
       </c>
     </row>
   </sheetData>
@@ -21798,8 +21814,8 @@
         <v>257</v>
       </c>
       <c r="C5" s="154">
-        <f ca="1">DCF!C26</f>
-        <v>6.8822824136162613</v>
+        <f>DCF!C26</f>
+        <v>6.2175596245918179</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -21807,8 +21823,8 @@
         <v>258</v>
       </c>
       <c r="C6" s="154">
-        <f ca="1">Multiples!C45</f>
-        <v>16.085299241165604</v>
+        <f>Multiples!C45</f>
+        <v>15.469508957927841</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -21825,8 +21841,8 @@
         <v>376</v>
       </c>
       <c r="C8" s="154">
-        <f ca="1">Multiples!C62</f>
-        <v>10.691532697497239</v>
+        <f>Multiples!C62</f>
+        <v>10.334200177437685</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -21834,8 +21850,8 @@
         <v>260</v>
       </c>
       <c r="C9" s="163">
-        <f ca="1">AVERAGE(C5:C8)</f>
-        <v>11.913151977203025</v>
+        <f>AVERAGE(C5:C8)</f>
+        <v>11.503690579122585</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21844,7 +21860,7 @@
       </c>
       <c r="C10" s="154">
         <f ca="1">Overview!C5</f>
-        <v>10.5725</v>
+        <v>10.26</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21853,7 +21869,7 @@
       </c>
       <c r="C11" s="175">
         <f ca="1">(C9-C10)/C10</f>
-        <v>0.12680557835923628</v>
+        <v>0.12121740537257168</v>
       </c>
     </row>
   </sheetData>
@@ -22104,8 +22120,8 @@
       <c r="J8" s="158"/>
       <c r="K8" s="158"/>
       <c r="L8" s="147">
-        <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>6072727.3819494601</v>
+        <f>L7*(1+C20)/(C21-C20)</f>
+        <v>5256704.6400000006</v>
       </c>
       <c r="N8" s="93"/>
       <c r="O8" s="16"/>
@@ -22158,24 +22174,24 @@
       <c r="F10" s="158"/>
       <c r="G10" s="159"/>
       <c r="H10" s="147">
-        <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>16157.906816616938</v>
+        <f>H7/(1+$C$21)^H9</f>
+        <v>15999.999999999998</v>
       </c>
       <c r="I10" s="147">
-        <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>32634.744086809515</v>
+        <f t="shared" ref="I10:L10" si="1">I7/(1+$C$21)^I9</f>
+        <v>31999.999999999996</v>
       </c>
       <c r="J10" s="147">
-        <f t="shared" ca="1" si="1"/>
-        <v>65913.644242351103</v>
+        <f t="shared" si="1"/>
+        <v>63999.999999999978</v>
       </c>
       <c r="K10" s="147">
-        <f t="shared" ca="1" si="1"/>
-        <v>133128.31520144359</v>
+        <f t="shared" si="1"/>
+        <v>127999.99999999997</v>
       </c>
       <c r="L10" s="147">
-        <f t="shared" ca="1" si="1"/>
-        <v>268884.36395976669</v>
+        <f t="shared" si="1"/>
+        <v>255999.99999999994</v>
       </c>
       <c r="N10" s="93"/>
     </row>
@@ -22193,8 +22209,8 @@
       <c r="J11" s="158"/>
       <c r="K11" s="158"/>
       <c r="L11" s="147">
-        <f ca="1">L8/(1+C21)^L9</f>
-        <v>3960462.8337756256</v>
+        <f>L8/(1+C21)^L9</f>
+        <v>3263999.9999999991</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -22210,7 +22226,7 @@
       </c>
       <c r="C15" s="177">
         <f ca="1">Overview!C5</f>
-        <v>10.5725</v>
+        <v>10.26</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22218,8 +22234,8 @@
         <v>266</v>
       </c>
       <c r="C16" s="177">
-        <f ca="1">C36</f>
-        <v>11.373651730160741</v>
+        <f>C36</f>
+        <v>9.9894542008526948</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -22256,16 +22272,16 @@
       <c r="B21" s="180" t="s">
         <v>206</v>
       </c>
-      <c r="C21" s="245">
-        <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>8.9249999999999996E-2</v>
+      <c r="C21" s="243">
+        <f>IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
+        <v>0.1</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B22" s="180" t="s">
         <v>70</v>
       </c>
-      <c r="C22" s="246">
+      <c r="C22" s="244">
         <f>Statement!AC75</f>
         <v>518121</v>
       </c>
@@ -22276,14 +22292,14 @@
       </c>
       <c r="C23" s="182">
         <f ca="1">C15*C22</f>
-        <v>5477834.2725</v>
+        <v>5315921.46</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B24" s="180" t="s">
         <v>219</v>
       </c>
-      <c r="C24" s="246">
+      <c r="C24" s="244">
         <f>Statement!AC107</f>
         <v>1415746</v>
       </c>
@@ -22292,7 +22308,7 @@
       <c r="B25" s="180" t="s">
         <v>210</v>
       </c>
-      <c r="C25" s="246">
+      <c r="C25" s="244">
         <f>Statement!AC108</f>
         <v>0</v>
       </c>
@@ -22303,7 +22319,7 @@
       </c>
       <c r="C26" s="183">
         <f ca="1">C23+C25-C24</f>
-        <v>4062088.2725</v>
+        <v>3900175.46</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -22318,8 +22334,8 @@
         <v>228</v>
       </c>
       <c r="C29" s="182">
-        <f ca="1">SUM(H10:L10)</f>
-        <v>516718.97430698783</v>
+        <f>SUM(H10:L10)</f>
+        <v>495999.99999999988</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -22327,8 +22343,8 @@
         <v>224</v>
       </c>
       <c r="C30" s="182">
-        <f ca="1">L11</f>
-        <v>3960462.8337756256</v>
+        <f>L11</f>
+        <v>3263999.9999999991</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -22336,8 +22352,8 @@
         <v>229</v>
       </c>
       <c r="C31" s="185">
-        <f ca="1">C29+C30</f>
-        <v>4477181.8080826132</v>
+        <f>C29+C30</f>
+        <v>3759999.9999999991</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -22363,8 +22379,8 @@
         <v>232</v>
       </c>
       <c r="C34" s="185">
-        <f ca="1">C31+C32-C33</f>
-        <v>5892927.8080826132</v>
+        <f>C31+C32-C33</f>
+        <v>5175745.9999999991</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -22381,8 +22397,8 @@
         <v>233</v>
       </c>
       <c r="C36" s="188">
-        <f ca="1">C34/C35</f>
-        <v>11.373651730160741</v>
+        <f>C34/C35</f>
+        <v>9.9894542008526948</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
@@ -22849,7 +22865,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0548B83C-60BF-4548-84AB-1D4A73B251A4}">
-  <dimension ref="A1:AE215"/>
+  <dimension ref="A1:AE218"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.6640625" style="1" customWidth="1"/>
@@ -24853,7 +24869,7 @@
     </row>
     <row r="34" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B34" s="20" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C34" s="21"/>
       <c r="D34" s="21"/>
@@ -29450,7 +29466,7 @@
       <c r="AA116" s="68"/>
       <c r="AC116" s="63">
         <f ca="1">Overview!C5</f>
-        <v>10.5725</v>
+        <v>10.26</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -29497,7 +29513,7 @@
       <c r="AA117" s="68"/>
       <c r="AC117" s="65">
         <f ca="1">AC116/AC85</f>
-        <v>10.5725</v>
+        <v>10.26</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -29911,35 +29927,35 @@
       <c r="O132" s="49"/>
       <c r="P132" s="49"/>
       <c r="Q132" s="49"/>
-      <c r="T132" s="193" t="str">
+      <c r="T132" s="246" t="str">
         <f t="shared" ref="T132:Z132" si="78">IF(T131&gt;T130, "BEAT", IF(T131&lt;T129, "MISSED", "MET"))</f>
         <v>BEAT</v>
       </c>
-      <c r="U132" s="193" t="str">
+      <c r="U132" s="246" t="str">
         <f t="shared" si="78"/>
         <v>MET</v>
       </c>
-      <c r="V132" s="193" t="str">
+      <c r="V132" s="246" t="str">
         <f t="shared" si="78"/>
         <v>BEAT</v>
       </c>
-      <c r="W132" s="193" t="str">
+      <c r="W132" s="246" t="str">
         <f t="shared" si="78"/>
         <v>BEAT</v>
       </c>
-      <c r="X132" s="193" t="str">
+      <c r="X132" s="246" t="str">
         <f t="shared" si="78"/>
         <v>BEAT</v>
       </c>
-      <c r="Y132" s="193" t="str">
+      <c r="Y132" s="246" t="str">
         <f t="shared" si="78"/>
         <v>BEAT</v>
       </c>
-      <c r="Z132" s="193" t="str">
+      <c r="Z132" s="246" t="str">
         <f t="shared" si="78"/>
         <v>BEAT</v>
       </c>
-      <c r="AA132" s="193" t="str">
+      <c r="AA132" s="246" t="str">
         <f>IF(AA131&gt;AA130, "BEAT", IF(AA131&lt;AA129, "MISSED", "MET"))</f>
         <v>MISSED</v>
       </c>
@@ -30055,7 +30071,7 @@
       <c r="P135" s="49"/>
       <c r="Q135" s="49"/>
       <c r="T135" s="25">
-        <f t="shared" ref="T135:AA135" si="79">U210</f>
+        <f t="shared" ref="T135:AA135" si="79">U213</f>
         <v>1606561</v>
       </c>
       <c r="U135" s="25">
@@ -30107,35 +30123,35 @@
       <c r="O136" s="49"/>
       <c r="P136" s="49"/>
       <c r="Q136" s="49"/>
-      <c r="T136" s="193" t="str">
+      <c r="T136" s="246" t="str">
         <f t="shared" ref="T136:Z136" si="80">IF(T135&gt;T134, "BEAT", IF(T135&lt;T133, "MISSED", "MET"))</f>
         <v>BEAT</v>
       </c>
-      <c r="U136" s="193" t="str">
+      <c r="U136" s="246" t="str">
         <f t="shared" si="80"/>
         <v>MISSED</v>
       </c>
-      <c r="V136" s="193" t="str">
+      <c r="V136" s="246" t="str">
         <f t="shared" si="80"/>
         <v>BEAT</v>
       </c>
-      <c r="W136" s="193" t="str">
+      <c r="W136" s="246" t="str">
         <f t="shared" si="80"/>
         <v>BEAT</v>
       </c>
-      <c r="X136" s="193" t="str">
+      <c r="X136" s="246" t="str">
         <f t="shared" si="80"/>
         <v>BEAT</v>
       </c>
-      <c r="Y136" s="193" t="str">
+      <c r="Y136" s="246" t="str">
         <f t="shared" si="80"/>
         <v>BEAT</v>
       </c>
-      <c r="Z136" s="193" t="str">
+      <c r="Z136" s="246" t="str">
         <f t="shared" si="80"/>
         <v>BEAT</v>
       </c>
-      <c r="AA136" s="193" t="str">
+      <c r="AA136" s="246" t="str">
         <f>IF(AA135&gt;AA134, "BEAT", IF(AA135&lt;AA133, "MISSED", "MET"))</f>
         <v>MISSED</v>
       </c>
@@ -30529,59 +30545,59 @@
       <c r="B146" s="20" t="s">
         <v>304</v>
       </c>
-      <c r="M146" s="201">
+      <c r="M146" s="200">
         <f>(M108-M107)/M49</f>
         <v>-0.98061622848437269</v>
       </c>
-      <c r="N146" s="201">
+      <c r="N146" s="200">
         <f>(N108-N107)/N49</f>
         <v>-0.91650530841732814</v>
       </c>
-      <c r="O146" s="201">
+      <c r="O146" s="200">
         <f>(O108-O107)/O49</f>
         <v>-0.93239915996813671</v>
       </c>
-      <c r="P146" s="201">
+      <c r="P146" s="200">
         <f>(P108-P107)/P49</f>
         <v>-0.93383166410403939</v>
       </c>
-      <c r="Q146" s="201">
+      <c r="Q146" s="200">
         <f>(Q108-Q107)/Q49</f>
         <v>-0.81123909829457308</v>
       </c>
-      <c r="T146" s="201">
+      <c r="T146" s="200">
         <f t="shared" ref="T146:AA146" si="95">(T108-T107)/T49</f>
         <v>-0.95080282790888426</v>
       </c>
-      <c r="U146" s="201">
+      <c r="U146" s="200">
         <f t="shared" si="95"/>
         <v>-0.92585537389316019</v>
       </c>
-      <c r="V146" s="201">
+      <c r="V146" s="200">
         <f t="shared" si="95"/>
         <v>-0.93383166410403939</v>
       </c>
-      <c r="W146" s="201">
+      <c r="W146" s="200">
         <f t="shared" si="95"/>
         <v>-0.93702475358574611</v>
       </c>
-      <c r="X146" s="201">
+      <c r="X146" s="200">
         <f t="shared" si="95"/>
         <v>-0.91411133917631171</v>
       </c>
-      <c r="Y146" s="201">
+      <c r="Y146" s="200">
         <f t="shared" si="95"/>
         <v>-0.78966100787845062</v>
       </c>
-      <c r="Z146" s="201">
+      <c r="Z146" s="200">
         <f t="shared" si="95"/>
         <v>-0.81123909829457308</v>
       </c>
-      <c r="AA146" s="201">
+      <c r="AA146" s="200">
         <f t="shared" si="95"/>
         <v>-0.74396849127545694</v>
       </c>
-      <c r="AC146" s="201">
+      <c r="AC146" s="200">
         <f>(AC108-AC107)/AC49</f>
         <v>-0.74396849127545694</v>
       </c>
@@ -30712,59 +30728,59 @@
       <c r="B149" s="20" t="s">
         <v>308</v>
       </c>
-      <c r="M149" s="203" t="str">
+      <c r="M149" s="202" t="str">
         <f>IF(M13&gt;=0,"N/A",IF(M12&lt;=0,"N/A",M12/-M13))</f>
         <v>N/A</v>
       </c>
-      <c r="N149" s="203" t="str">
+      <c r="N149" s="202" t="str">
         <f>IF(N13&gt;=0,"N/A",IF(N12&lt;=0,"N/A",N12/-N13))</f>
         <v>N/A</v>
       </c>
-      <c r="O149" s="203" t="str">
+      <c r="O149" s="202" t="str">
         <f>IF(O13&gt;=0,"N/A",IF(O12&lt;=0,"N/A",O12/-O13))</f>
         <v>N/A</v>
       </c>
-      <c r="P149" s="203" t="str">
+      <c r="P149" s="202" t="str">
         <f>IF(P13&gt;=0,"N/A",IF(P12&lt;=0,"N/A",P12/-P13))</f>
         <v>N/A</v>
       </c>
-      <c r="Q149" s="203" t="str">
+      <c r="Q149" s="202" t="str">
         <f>IF(Q13&gt;=0,"N/A",IF(Q12&lt;=0,"N/A",Q12/-Q13))</f>
         <v>N/A</v>
       </c>
-      <c r="T149" s="203" t="str">
+      <c r="T149" s="202" t="str">
         <f t="shared" ref="T149:AA149" si="98">IF(T13&gt;=0,"N/A",IF(T12&lt;=0,"N/A",T12/-T13))</f>
         <v>N/A</v>
       </c>
-      <c r="U149" s="203" t="str">
+      <c r="U149" s="202" t="str">
         <f t="shared" si="98"/>
         <v>N/A</v>
       </c>
-      <c r="V149" s="203" t="str">
+      <c r="V149" s="202" t="str">
         <f t="shared" si="98"/>
         <v>N/A</v>
       </c>
-      <c r="W149" s="203" t="str">
+      <c r="W149" s="202" t="str">
         <f t="shared" si="98"/>
         <v>N/A</v>
       </c>
-      <c r="X149" s="203" t="str">
+      <c r="X149" s="202" t="str">
         <f t="shared" si="98"/>
         <v>N/A</v>
       </c>
-      <c r="Y149" s="203" t="str">
+      <c r="Y149" s="202" t="str">
         <f t="shared" si="98"/>
         <v>N/A</v>
       </c>
-      <c r="Z149" s="203" t="str">
+      <c r="Z149" s="202" t="str">
         <f t="shared" si="98"/>
         <v>N/A</v>
       </c>
-      <c r="AA149" s="203" t="str">
+      <c r="AA149" s="202" t="str">
         <f t="shared" si="98"/>
         <v>N/A</v>
       </c>
-      <c r="AC149" s="203" t="str">
+      <c r="AC149" s="202" t="str">
         <f>IF(AC13&gt;=0,"N/A",IF(AC12&lt;=0,"N/A",AC12/-AC13))</f>
         <v>N/A</v>
       </c>
@@ -30803,7 +30819,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>17.62083333333333</v>
+        <v>17.099999999999998</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -30840,7 +30856,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>3.4059633733324164</v>
+        <v>3.305290537752716</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -30877,7 +30893,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="72">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>2.8785785721229762</v>
+        <v>2.7934940789767544</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -30914,7 +30930,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="164">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>5522598.2374999998</v>
+        <v>5359362.3</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -30951,30 +30967,30 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="164">
         <f ca="1">AC153+AC108-AC107+AC48+AC45</f>
-        <v>4106852.2374999998</v>
+        <v>3943616.3</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B155" s="20" t="s">
         <v>309</v>
       </c>
-      <c r="M155" s="205">
+      <c r="M155" s="204">
         <f>M154/M5</f>
         <v>18.198153481303489</v>
       </c>
-      <c r="N155" s="205">
+      <c r="N155" s="204">
         <f>N154/N5</f>
         <v>6.0097603395488868</v>
       </c>
-      <c r="O155" s="205">
+      <c r="O155" s="204">
         <f>O154/O5</f>
         <v>8.9376861900568176</v>
       </c>
-      <c r="P155" s="205">
+      <c r="P155" s="204">
         <f>P154/P5</f>
         <v>4.4186165001007236</v>
       </c>
-      <c r="Q155" s="205">
+      <c r="Q155" s="204">
         <f>Q154/Q5</f>
         <v>3.0992067600827533</v>
       </c>
@@ -30986,32 +31002,32 @@
       <c r="Y155" s="49"/>
       <c r="Z155" s="49"/>
       <c r="AA155" s="49"/>
-      <c r="AC155" s="205">
+      <c r="AC155" s="204">
         <f ca="1">AC154/AC5</f>
-        <v>2.4557666474320259</v>
+        <v>2.3581567633182443</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B156" s="20" t="s">
         <v>245</v>
       </c>
-      <c r="M156" s="205">
+      <c r="M156" s="204">
         <f>M154/M12</f>
         <v>-32.413351618737352</v>
       </c>
-      <c r="N156" s="205">
+      <c r="N156" s="204">
         <f>N154/N12</f>
         <v>-18.266232087124553</v>
       </c>
-      <c r="O156" s="205">
+      <c r="O156" s="204">
         <f>O154/O12</f>
         <v>-70.97581987615348</v>
       </c>
-      <c r="P156" s="205">
+      <c r="P156" s="204">
         <f>P154/P12</f>
         <v>-38.858189076638233</v>
       </c>
-      <c r="Q156" s="205">
+      <c r="Q156" s="204">
         <f>Q154/Q12</f>
         <v>87.94037403100775</v>
       </c>
@@ -31023,9 +31039,9 @@
       <c r="Y156" s="49"/>
       <c r="Z156" s="49"/>
       <c r="AA156" s="49"/>
-      <c r="AC156" s="205">
+      <c r="AC156" s="204">
         <f ca="1">AC154/AC12</f>
-        <v>40.597991651756146</v>
+        <v>38.98433456242153</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -31160,7 +31176,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="72">
         <f t="shared" ref="AC159:AC160" ca="1" si="101">AC153/AC157</f>
-        <v>51.320969784125865</v>
+        <v>49.804034049196623</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -31197,7 +31213,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
         <f t="shared" ca="1" si="101"/>
-        <v>-75.723282704895354</v>
+        <v>-72.713493131741487</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -31234,7 +31250,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="74">
         <f t="shared" ref="AC161" ca="1" si="104">AC157/AC153</f>
-        <v>1.9485212462008288E-2</v>
+        <v>2.0078694810388171E-2</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -31271,7 +31287,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f ca="1">AC26/AC117</f>
-        <v>5.6751004965712941E-2</v>
+        <v>5.8479532163742701E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31345,7 +31361,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="175">
         <f ca="1">-AC63/AC153</f>
-        <v>6.2537954989161926E-2</v>
+        <v>6.4442741629913702E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -31382,7 +31398,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="175">
         <f ca="1">-(AC63+AC64)/AC153</f>
-        <v>6.2537954989161926E-2</v>
+        <v>6.4442741629913702E-2</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -31885,7 +31901,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="175">
         <f ca="1">(AC107-AC108)/AC153</f>
-        <v>0.2563550595418449</v>
+        <v>0.26416314493237375</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -32073,27 +32089,27 @@
     </row>
     <row r="180" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B180" s="20" t="s">
-        <v>410</v>
-      </c>
-      <c r="M180" s="247">
-        <f>M37/M5</f>
-        <v>2.8830980485333741</v>
-      </c>
-      <c r="N180" s="247">
-        <f>N37/N5</f>
-        <v>2.5838419544654592</v>
-      </c>
-      <c r="O180" s="247">
-        <f>O37/O5</f>
-        <v>2.2588649554458775</v>
-      </c>
-      <c r="P180" s="247">
-        <f>P37/P5</f>
-        <v>2.0041562213219328</v>
-      </c>
-      <c r="Q180" s="247">
-        <f>Q37/Q5</f>
-        <v>1.9739570786031297</v>
+        <v>418</v>
+      </c>
+      <c r="M180" s="245">
+        <f>M5/M37</f>
+        <v>0.346849112713561</v>
+      </c>
+      <c r="N180" s="245">
+        <f t="shared" ref="N180:Q180" si="112">N5/N37</f>
+        <v>0.38702057541552631</v>
+      </c>
+      <c r="O180" s="245">
+        <f t="shared" si="112"/>
+        <v>0.44270021436611728</v>
+      </c>
+      <c r="P180" s="245">
+        <f t="shared" si="112"/>
+        <v>0.49896309946357587</v>
+      </c>
+      <c r="Q180" s="245">
+        <f t="shared" si="112"/>
+        <v>0.50659662808253647</v>
       </c>
       <c r="T180" s="49"/>
       <c r="U180" s="49"/>
@@ -32103,216 +32119,197 @@
       <c r="Y180" s="49"/>
       <c r="Z180" s="49"/>
       <c r="AA180" s="49"/>
-      <c r="AC180" s="247">
-        <f>AC37/AC5</f>
-        <v>1.7369179527963978</v>
+      <c r="AC180" s="245">
+        <f t="shared" ref="AC180" si="113">AC5/AC37</f>
+        <v>0.57573243364202842</v>
+      </c>
+    </row>
+    <row r="181" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="B181" s="20" t="s">
+        <v>415</v>
+      </c>
+      <c r="M181" s="247" t="str">
+        <f>IF(AND(M12&gt;0,M108&gt;0),M108/M12,"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="N181" s="247" t="str">
+        <f t="shared" ref="N181:Q181" si="114">IF(AND(N12&gt;0,N108&gt;0),N108/N12,"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="O181" s="247" t="str">
+        <f t="shared" si="114"/>
+        <v>N/A</v>
+      </c>
+      <c r="P181" s="247" t="str">
+        <f t="shared" si="114"/>
+        <v>N/A</v>
+      </c>
+      <c r="Q181" s="247" t="str">
+        <f t="shared" si="114"/>
+        <v>N/A</v>
+      </c>
+      <c r="T181" s="49"/>
+      <c r="U181" s="49"/>
+      <c r="V181" s="49"/>
+      <c r="W181" s="49"/>
+      <c r="X181" s="49"/>
+      <c r="Y181" s="49"/>
+      <c r="Z181" s="49"/>
+      <c r="AA181" s="49"/>
+      <c r="AC181" s="247" t="str">
+        <f t="shared" ref="AC181" si="115">IF(AND(AC12&gt;0,AC108&gt;0),AC108/AC12,"N/A")</f>
+        <v>N/A</v>
       </c>
     </row>
     <row r="182" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="B182" s="1"/>
-    </row>
-    <row r="183" spans="1:31" s="15" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A183" s="11"/>
-      <c r="B183" s="14" t="s">
+      <c r="B182" s="20" t="s">
+        <v>416</v>
+      </c>
+      <c r="M182" s="247" t="str">
+        <f>IF(AND(M12&gt;0,M108&gt;0),(M108-M107)/M12,"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="N182" s="247" t="str">
+        <f t="shared" ref="N182:Q182" si="116">IF(AND(N12&gt;0,N108&gt;0),(N108-N107)/N12,"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="O182" s="247" t="str">
+        <f t="shared" si="116"/>
+        <v>N/A</v>
+      </c>
+      <c r="P182" s="247" t="str">
+        <f t="shared" si="116"/>
+        <v>N/A</v>
+      </c>
+      <c r="Q182" s="247" t="str">
+        <f t="shared" si="116"/>
+        <v>N/A</v>
+      </c>
+      <c r="T182" s="49"/>
+      <c r="U182" s="49"/>
+      <c r="V182" s="49"/>
+      <c r="W182" s="49"/>
+      <c r="X182" s="49"/>
+      <c r="Y182" s="49"/>
+      <c r="Z182" s="49"/>
+      <c r="AA182" s="49"/>
+      <c r="AC182" s="247" t="str">
+        <f t="shared" ref="AC182" si="117">IF(AND(AC12&gt;0,AC108&gt;0),(AC108-AC107)/AC12,"N/A")</f>
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="183" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="B183" s="20" t="s">
+        <v>417</v>
+      </c>
+      <c r="M183" s="247">
+        <f>M5/(M108+M112-M107)</f>
+        <v>23.950501959521127</v>
+      </c>
+      <c r="N183" s="247">
+        <f t="shared" ref="N183:Q183" si="118">N5/(N108+N112-N107)</f>
+        <v>6.6028018437778737</v>
+      </c>
+      <c r="O183" s="247">
+        <f t="shared" si="118"/>
+        <v>9.5976403430894184</v>
+      </c>
+      <c r="P183" s="247">
+        <f t="shared" si="118"/>
+        <v>11.705987832736978</v>
+      </c>
+      <c r="Q183" s="247">
+        <f t="shared" si="118"/>
+        <v>4.0969904174647871</v>
+      </c>
+      <c r="T183" s="49"/>
+      <c r="U183" s="49"/>
+      <c r="V183" s="49"/>
+      <c r="W183" s="49"/>
+      <c r="X183" s="49"/>
+      <c r="Y183" s="49"/>
+      <c r="Z183" s="49"/>
+      <c r="AA183" s="49"/>
+      <c r="AC183" s="247">
+        <f t="shared" ref="AC183" si="119">AC5/(AC108+AC112-AC107)</f>
+        <v>3.4323989827982899</v>
+      </c>
+    </row>
+    <row r="185" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="B185" s="1"/>
+    </row>
+    <row r="186" spans="1:31" s="15" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A186" s="11"/>
+      <c r="B186" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="R183" s="1"/>
-      <c r="S183" s="1"/>
-      <c r="AB183" s="1"/>
-      <c r="AD183" s="1"/>
-      <c r="AE183" s="1"/>
-    </row>
-    <row r="184" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="B184" s="20" t="s">
+      <c r="R186" s="1"/>
+      <c r="S186" s="1"/>
+      <c r="AB186" s="1"/>
+      <c r="AD186" s="1"/>
+      <c r="AE186" s="1"/>
+    </row>
+    <row r="187" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="B187" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="C184" s="62"/>
-      <c r="D184" s="62"/>
-      <c r="E184" s="62"/>
-      <c r="F184" s="62"/>
-      <c r="G184" s="62"/>
-      <c r="H184" s="62"/>
-      <c r="I184" s="62"/>
-      <c r="J184" s="62"/>
-      <c r="K184" s="62"/>
-      <c r="L184" s="62"/>
-      <c r="M184" s="62">
+      <c r="C187" s="62"/>
+      <c r="D187" s="62"/>
+      <c r="E187" s="62"/>
+      <c r="F187" s="62"/>
+      <c r="G187" s="62"/>
+      <c r="H187" s="62"/>
+      <c r="I187" s="62"/>
+      <c r="J187" s="62"/>
+      <c r="K187" s="62"/>
+      <c r="L187" s="62"/>
+      <c r="M187" s="62">
         <v>481427</v>
       </c>
-      <c r="N184" s="62">
+      <c r="N187" s="62">
         <v>497836</v>
       </c>
-      <c r="O184" s="62">
+      <c r="O187" s="62">
         <v>621392</v>
       </c>
-      <c r="P184" s="62">
+      <c r="P187" s="62">
         <v>587152</v>
       </c>
-      <c r="Q184" s="62">
+      <c r="Q187" s="62">
         <v>606394</v>
       </c>
-      <c r="T184" s="62">
+      <c r="T187" s="62">
         <v>112251</v>
       </c>
-      <c r="U184" s="62">
+      <c r="U187" s="62">
         <v>137174</v>
       </c>
-      <c r="V184" s="62">
+      <c r="V187" s="62">
         <v>197609</v>
       </c>
-      <c r="W184" s="62">
+      <c r="W187" s="62">
         <v>128286</v>
       </c>
-      <c r="X184" s="62">
+      <c r="X187" s="62">
         <v>112161</v>
       </c>
-      <c r="Y184" s="62">
+      <c r="Y187" s="62">
         <v>150043</v>
       </c>
-      <c r="Z184" s="62">
+      <c r="Z187" s="62">
         <v>215904</v>
       </c>
-      <c r="AA184" s="62">
+      <c r="AA187" s="62">
         <v>149309</v>
       </c>
-      <c r="AC184" s="62">
-        <f>SUM(X184:AA184)</f>
+      <c r="AC187" s="62">
+        <f>SUM(X187:AA187)</f>
         <v>627417</v>
       </c>
-    </row>
-    <row r="185" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="B185" s="20" t="s">
-        <v>114</v>
-      </c>
-      <c r="C185" s="62"/>
-      <c r="D185" s="62"/>
-      <c r="E185" s="62"/>
-      <c r="F185" s="62"/>
-      <c r="G185" s="62"/>
-      <c r="H185" s="62"/>
-      <c r="I185" s="62"/>
-      <c r="J185" s="62"/>
-      <c r="K185" s="62"/>
-      <c r="L185" s="62"/>
-      <c r="M185" s="62">
-        <v>369867</v>
-      </c>
-      <c r="N185" s="62">
-        <v>508823</v>
-      </c>
-      <c r="O185" s="62">
-        <v>649918</v>
-      </c>
-      <c r="P185" s="62">
-        <v>801947</v>
-      </c>
-      <c r="Q185" s="62">
-        <v>954472</v>
-      </c>
-      <c r="T185" s="62">
-        <v>194673</v>
-      </c>
-      <c r="U185" s="62">
-        <v>206922</v>
-      </c>
-      <c r="V185" s="62">
-        <v>215221</v>
-      </c>
-      <c r="W185" s="62">
-        <v>217303</v>
-      </c>
-      <c r="X185" s="62">
-        <v>238363</v>
-      </c>
-      <c r="Y185" s="62">
-        <v>247573</v>
-      </c>
-      <c r="Z185" s="62">
-        <v>251233</v>
-      </c>
-      <c r="AA185" s="62">
-        <v>252903</v>
-      </c>
-      <c r="AC185" s="62">
-        <f t="shared" ref="AC185:AC190" si="112">SUM(X185:AA185)</f>
-        <v>990072</v>
-      </c>
-    </row>
-    <row r="186" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="B186" s="20" t="s">
-        <v>115</v>
-      </c>
-      <c r="C186" s="62"/>
-      <c r="D186" s="62"/>
-      <c r="E186" s="62"/>
-      <c r="F186" s="62"/>
-      <c r="G186" s="62"/>
-      <c r="H186" s="62"/>
-      <c r="I186" s="62"/>
-      <c r="J186" s="62"/>
-      <c r="K186" s="62"/>
-      <c r="L186" s="62"/>
-      <c r="M186" s="62">
-        <v>40958</v>
-      </c>
-      <c r="N186" s="62">
-        <v>51922</v>
-      </c>
-      <c r="O186" s="62">
-        <v>36762</v>
-      </c>
-      <c r="P186" s="62">
-        <v>40555</v>
-      </c>
-      <c r="Q186" s="62">
-        <v>49706</v>
-      </c>
-      <c r="T186" s="62">
-        <v>9329</v>
-      </c>
-      <c r="U186" s="62">
-        <v>10557</v>
-      </c>
-      <c r="V186" s="62">
-        <v>10816</v>
-      </c>
-      <c r="W186" s="62">
-        <v>11035</v>
-      </c>
-      <c r="X186" s="62">
-        <v>11204</v>
-      </c>
-      <c r="Y186" s="62">
-        <v>13497</v>
-      </c>
-      <c r="Z186" s="62">
-        <v>13970</v>
-      </c>
-      <c r="AA186" s="62">
-        <v>16170</v>
-      </c>
-      <c r="AC186" s="62">
-        <f t="shared" si="112"/>
-        <v>54841</v>
-      </c>
-    </row>
-    <row r="187" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C187" s="21"/>
-      <c r="D187" s="21"/>
-      <c r="E187" s="21"/>
-      <c r="F187" s="21"/>
-      <c r="G187" s="21"/>
-      <c r="H187" s="21"/>
-      <c r="I187" s="21"/>
-      <c r="J187" s="21"/>
-      <c r="K187" s="21"/>
-      <c r="L187" s="21"/>
-      <c r="M187" s="21"/>
-      <c r="AC187" s="62"/>
     </row>
     <row r="188" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B188" s="20" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C188" s="62"/>
       <c r="D188" s="62"/>
@@ -32325,52 +32322,52 @@
       <c r="K188" s="62"/>
       <c r="L188" s="62"/>
       <c r="M188" s="62">
-        <v>11888</v>
+        <v>369867</v>
       </c>
       <c r="N188" s="62">
-        <v>10421</v>
+        <v>508823</v>
       </c>
       <c r="O188" s="62">
-        <v>10469</v>
+        <v>649918</v>
       </c>
       <c r="P188" s="62">
-        <v>8565</v>
+        <v>801947</v>
       </c>
       <c r="Q188" s="62">
-        <v>5334</v>
+        <v>954472</v>
       </c>
       <c r="T188" s="62">
-        <v>2393</v>
+        <v>194673</v>
       </c>
       <c r="U188" s="62">
-        <v>2340</v>
+        <v>206922</v>
       </c>
       <c r="V188" s="62">
-        <v>1231</v>
+        <v>215221</v>
       </c>
       <c r="W188" s="62">
-        <v>1268</v>
+        <v>217303</v>
       </c>
       <c r="X188" s="62">
-        <v>1200</v>
+        <v>238363</v>
       </c>
       <c r="Y188" s="62">
-        <v>1311</v>
+        <v>247573</v>
       </c>
       <c r="Z188" s="62">
-        <v>1555</v>
+        <v>251233</v>
       </c>
       <c r="AA188" s="62">
-        <v>1664</v>
+        <v>252903</v>
       </c>
       <c r="AC188" s="62">
-        <f t="shared" si="112"/>
-        <v>5730</v>
+        <f t="shared" ref="AC188:AC193" si="120">SUM(X188:AA188)</f>
+        <v>990072</v>
       </c>
     </row>
     <row r="189" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B189" s="20" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C189" s="62"/>
       <c r="D189" s="62"/>
@@ -32383,850 +32380,980 @@
       <c r="K189" s="62"/>
       <c r="L189" s="62"/>
       <c r="M189" s="62">
+        <v>40958</v>
+      </c>
+      <c r="N189" s="62">
+        <v>51922</v>
+      </c>
+      <c r="O189" s="62">
+        <v>36762</v>
+      </c>
+      <c r="P189" s="62">
+        <v>40555</v>
+      </c>
+      <c r="Q189" s="62">
+        <v>49706</v>
+      </c>
+      <c r="T189" s="62">
+        <v>9329</v>
+      </c>
+      <c r="U189" s="62">
+        <v>10557</v>
+      </c>
+      <c r="V189" s="62">
+        <v>10816</v>
+      </c>
+      <c r="W189" s="62">
+        <v>11035</v>
+      </c>
+      <c r="X189" s="62">
+        <v>11204</v>
+      </c>
+      <c r="Y189" s="62">
+        <v>13497</v>
+      </c>
+      <c r="Z189" s="62">
+        <v>13970</v>
+      </c>
+      <c r="AA189" s="62">
+        <v>16170</v>
+      </c>
+      <c r="AC189" s="62">
+        <f t="shared" si="120"/>
+        <v>54841</v>
+      </c>
+    </row>
+    <row r="190" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="C190" s="21"/>
+      <c r="D190" s="21"/>
+      <c r="E190" s="21"/>
+      <c r="F190" s="21"/>
+      <c r="G190" s="21"/>
+      <c r="H190" s="21"/>
+      <c r="I190" s="21"/>
+      <c r="J190" s="21"/>
+      <c r="K190" s="21"/>
+      <c r="L190" s="21"/>
+      <c r="M190" s="21"/>
+      <c r="AC190" s="62"/>
+    </row>
+    <row r="191" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="B191" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="C191" s="62"/>
+      <c r="D191" s="62"/>
+      <c r="E191" s="62"/>
+      <c r="F191" s="62"/>
+      <c r="G191" s="62"/>
+      <c r="H191" s="62"/>
+      <c r="I191" s="62"/>
+      <c r="J191" s="62"/>
+      <c r="K191" s="62"/>
+      <c r="L191" s="62"/>
+      <c r="M191" s="62">
+        <v>11888</v>
+      </c>
+      <c r="N191" s="62">
+        <v>10421</v>
+      </c>
+      <c r="O191" s="62">
+        <v>10469</v>
+      </c>
+      <c r="P191" s="62">
+        <v>8565</v>
+      </c>
+      <c r="Q191" s="62">
+        <v>5334</v>
+      </c>
+      <c r="T191" s="62">
+        <v>2393</v>
+      </c>
+      <c r="U191" s="62">
+        <v>2340</v>
+      </c>
+      <c r="V191" s="62">
+        <v>1231</v>
+      </c>
+      <c r="W191" s="62">
+        <v>1268</v>
+      </c>
+      <c r="X191" s="62">
+        <v>1200</v>
+      </c>
+      <c r="Y191" s="62">
+        <v>1311</v>
+      </c>
+      <c r="Z191" s="62">
+        <v>1555</v>
+      </c>
+      <c r="AA191" s="62">
+        <v>1664</v>
+      </c>
+      <c r="AC191" s="62">
+        <f t="shared" si="120"/>
+        <v>5730</v>
+      </c>
+    </row>
+    <row r="192" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="B192" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="C192" s="62"/>
+      <c r="D192" s="62"/>
+      <c r="E192" s="62"/>
+      <c r="F192" s="62"/>
+      <c r="G192" s="62"/>
+      <c r="H192" s="62"/>
+      <c r="I192" s="62"/>
+      <c r="J192" s="62"/>
+      <c r="K192" s="62"/>
+      <c r="L192" s="62"/>
+      <c r="M192" s="62">
         <v>60565</v>
       </c>
-      <c r="N189" s="62">
+      <c r="N192" s="62">
         <v>87366</v>
       </c>
-      <c r="O189" s="62">
+      <c r="O192" s="62">
         <v>111922</v>
       </c>
-      <c r="P189" s="62">
+      <c r="P192" s="62">
         <v>167630</v>
       </c>
-      <c r="Q189" s="62">
+      <c r="Q192" s="62">
         <v>157588</v>
       </c>
-      <c r="T189" s="62">
+      <c r="T192" s="62">
         <v>43529</v>
       </c>
-      <c r="U189" s="62">
+      <c r="U192" s="62">
         <v>43487</v>
       </c>
-      <c r="V189" s="62">
+      <c r="V192" s="62">
         <v>43860</v>
       </c>
-      <c r="W189" s="62">
+      <c r="W192" s="62">
         <v>38468</v>
       </c>
-      <c r="X189" s="62">
+      <c r="X192" s="62">
         <v>38229</v>
       </c>
-      <c r="Y189" s="62">
+      <c r="Y192" s="62">
         <v>40121</v>
       </c>
-      <c r="Z189" s="62">
+      <c r="Z192" s="62">
         <v>40770</v>
       </c>
-      <c r="AA189" s="62">
+      <c r="AA192" s="62">
         <v>43988</v>
       </c>
-      <c r="AC189" s="62">
-        <f t="shared" si="112"/>
+      <c r="AC192" s="62">
+        <f t="shared" si="120"/>
         <v>163108</v>
       </c>
     </row>
-    <row r="190" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="B190" s="20" t="s">
+    <row r="193" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B193" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="C190" s="62"/>
-      <c r="D190" s="62"/>
-      <c r="E190" s="62"/>
-      <c r="F190" s="62"/>
-      <c r="G190" s="62"/>
-      <c r="H190" s="62"/>
-      <c r="I190" s="62"/>
-      <c r="J190" s="62"/>
-      <c r="K190" s="62"/>
-      <c r="L190" s="62"/>
-      <c r="M190" s="62">
+      <c r="C193" s="62"/>
+      <c r="D193" s="62"/>
+      <c r="E193" s="62"/>
+      <c r="F193" s="62"/>
+      <c r="G193" s="62"/>
+      <c r="H193" s="62"/>
+      <c r="I193" s="62"/>
+      <c r="J193" s="62"/>
+      <c r="K193" s="62"/>
+      <c r="L193" s="62"/>
+      <c r="M193" s="62">
         <v>96415</v>
       </c>
-      <c r="N190" s="62">
+      <c r="N193" s="62">
         <v>82264</v>
       </c>
-      <c r="O190" s="62">
+      <c r="O193" s="62">
         <v>73533</v>
       </c>
-      <c r="P190" s="62">
+      <c r="P193" s="62">
         <v>70747</v>
       </c>
-      <c r="Q190" s="62">
+      <c r="Q193" s="62">
         <v>108062</v>
       </c>
-      <c r="T190" s="62">
+      <c r="T193" s="62">
         <v>17398</v>
       </c>
-      <c r="U190" s="62">
+      <c r="U193" s="62">
         <v>17936</v>
       </c>
-      <c r="V190" s="62">
+      <c r="V193" s="62">
         <v>19443</v>
       </c>
-      <c r="W190" s="62">
+      <c r="W193" s="62">
         <v>24121</v>
       </c>
-      <c r="X190" s="62">
+      <c r="X193" s="62">
         <v>24951</v>
       </c>
-      <c r="Y190" s="62">
+      <c r="Y193" s="62">
         <v>27380</v>
       </c>
-      <c r="Z190" s="62">
+      <c r="Z193" s="62">
         <v>31610</v>
       </c>
-      <c r="AA190" s="62">
+      <c r="AA193" s="62">
         <v>31276</v>
       </c>
-      <c r="AC190" s="62">
-        <f t="shared" si="112"/>
+      <c r="AC193" s="62">
+        <f t="shared" si="120"/>
         <v>115217</v>
       </c>
     </row>
-    <row r="191" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C191" s="21"/>
-      <c r="D191" s="21"/>
-      <c r="E191" s="21"/>
-      <c r="F191" s="21"/>
-      <c r="G191" s="21"/>
-      <c r="H191" s="21"/>
-      <c r="I191" s="21"/>
-      <c r="J191" s="21"/>
-      <c r="K191" s="21"/>
-      <c r="L191" s="21"/>
-      <c r="M191" s="21"/>
-    </row>
-    <row r="192" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="B192" s="1"/>
-    </row>
-    <row r="193" spans="2:29" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B193" s="14" t="s">
+    <row r="194" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="C194" s="21"/>
+      <c r="D194" s="21"/>
+      <c r="E194" s="21"/>
+      <c r="F194" s="21"/>
+      <c r="G194" s="21"/>
+      <c r="H194" s="21"/>
+      <c r="I194" s="21"/>
+      <c r="J194" s="21"/>
+      <c r="K194" s="21"/>
+      <c r="L194" s="21"/>
+      <c r="M194" s="21"/>
+    </row>
+    <row r="195" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B195" s="1"/>
+    </row>
+    <row r="196" spans="2:29" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B196" s="14" t="s">
         <v>363</v>
       </c>
-      <c r="C193" s="192"/>
-      <c r="D193" s="192"/>
-      <c r="E193" s="192"/>
-      <c r="F193" s="192"/>
-      <c r="G193" s="192"/>
-      <c r="H193" s="192"/>
-      <c r="I193" s="192"/>
-      <c r="J193" s="192"/>
-      <c r="K193" s="192"/>
-      <c r="L193" s="192"/>
-      <c r="M193" s="192"/>
-      <c r="N193" s="192"/>
-      <c r="O193" s="192"/>
-      <c r="P193" s="192"/>
-      <c r="Q193" s="192"/>
-      <c r="T193" s="192"/>
-      <c r="U193" s="192"/>
-      <c r="V193" s="192"/>
-      <c r="W193" s="192"/>
-      <c r="X193" s="192"/>
-      <c r="Y193" s="192"/>
-      <c r="Z193" s="192"/>
-      <c r="AA193" s="192"/>
-      <c r="AC193" s="192"/>
-    </row>
-    <row r="194" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B194" s="20" t="s">
+      <c r="C196" s="192"/>
+      <c r="D196" s="192"/>
+      <c r="E196" s="192"/>
+      <c r="F196" s="192"/>
+      <c r="G196" s="192"/>
+      <c r="H196" s="192"/>
+      <c r="I196" s="192"/>
+      <c r="J196" s="192"/>
+      <c r="K196" s="192"/>
+      <c r="L196" s="192"/>
+      <c r="M196" s="192"/>
+      <c r="N196" s="192"/>
+      <c r="O196" s="192"/>
+      <c r="P196" s="192"/>
+      <c r="Q196" s="192"/>
+      <c r="T196" s="192"/>
+      <c r="U196" s="192"/>
+      <c r="V196" s="192"/>
+      <c r="W196" s="192"/>
+      <c r="X196" s="192"/>
+      <c r="Y196" s="192"/>
+      <c r="Z196" s="192"/>
+      <c r="AA196" s="192"/>
+      <c r="AC196" s="192"/>
+    </row>
+    <row r="197" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B197" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="C194" s="81"/>
-      <c r="D194" s="81"/>
-      <c r="E194" s="81"/>
-      <c r="F194" s="81"/>
-      <c r="G194" s="81"/>
-      <c r="H194" s="81"/>
-      <c r="I194" s="81"/>
-      <c r="J194" s="81"/>
-      <c r="K194" s="81"/>
-      <c r="L194" s="81"/>
-      <c r="M194" s="81">
-        <f t="shared" ref="M194:Q196" si="113">IF(L184=0,
-IF(M184=0,0,IF(M184&gt;0,1,-1)),
-(M184-L184)/ABS(L184)
+      <c r="C197" s="81"/>
+      <c r="D197" s="81"/>
+      <c r="E197" s="81"/>
+      <c r="F197" s="81"/>
+      <c r="G197" s="81"/>
+      <c r="H197" s="81"/>
+      <c r="I197" s="81"/>
+      <c r="J197" s="81"/>
+      <c r="K197" s="81"/>
+      <c r="L197" s="81"/>
+      <c r="M197" s="81">
+        <f t="shared" ref="M197:Q199" si="121">IF(L187=0,
+IF(M187=0,0,IF(M187&gt;0,1,-1)),
+(M187-L187)/ABS(L187)
 )</f>
         <v>1</v>
       </c>
-      <c r="N194" s="81">
-        <f t="shared" si="113"/>
+      <c r="N197" s="81">
+        <f t="shared" si="121"/>
         <v>3.4084087514825716E-2</v>
       </c>
-      <c r="O194" s="81">
-        <f t="shared" si="113"/>
+      <c r="O197" s="81">
+        <f t="shared" si="121"/>
         <v>0.24818614965570993</v>
       </c>
-      <c r="P194" s="81">
-        <f t="shared" si="113"/>
+      <c r="P197" s="81">
+        <f t="shared" si="121"/>
         <v>-5.5102093364575021E-2</v>
       </c>
-      <c r="Q194" s="81">
-        <f t="shared" si="113"/>
+      <c r="Q197" s="81">
+        <f t="shared" si="121"/>
         <v>3.2771752459329104E-2</v>
       </c>
-      <c r="T194" s="81">
-        <f t="shared" ref="T194:AA196" si="114">IF(S184=0,
-IF(T184=0,0,IF(T184&gt;0,1,-1)),
-(T184-S184)/ABS(S184)
+      <c r="T197" s="81">
+        <f t="shared" ref="T197:AA199" si="122">IF(S187=0,
+IF(T187=0,0,IF(T187&gt;0,1,-1)),
+(T187-S187)/ABS(S187)
 )</f>
         <v>1</v>
       </c>
-      <c r="U194" s="81">
-        <f t="shared" si="114"/>
+      <c r="U197" s="81">
+        <f t="shared" si="122"/>
         <v>0.22202920241245067</v>
       </c>
-      <c r="V194" s="81">
-        <f t="shared" si="114"/>
+      <c r="V197" s="81">
+        <f t="shared" si="122"/>
         <v>0.44057182848061588</v>
       </c>
-      <c r="W194" s="81">
-        <f t="shared" si="114"/>
+      <c r="W197" s="81">
+        <f t="shared" si="122"/>
         <v>-0.35080892064632685</v>
       </c>
-      <c r="X194" s="81">
-        <f t="shared" si="114"/>
+      <c r="X197" s="81">
+        <f t="shared" si="122"/>
         <v>-0.12569571114540948</v>
       </c>
-      <c r="Y194" s="81">
-        <f t="shared" si="114"/>
+      <c r="Y197" s="81">
+        <f t="shared" si="122"/>
         <v>0.33774663207353717</v>
       </c>
-      <c r="Z194" s="81">
-        <f t="shared" si="114"/>
+      <c r="Z197" s="81">
+        <f t="shared" si="122"/>
         <v>0.43894750171617469</v>
       </c>
-      <c r="AA194" s="81">
-        <f t="shared" si="114"/>
+      <c r="AA197" s="81">
+        <f t="shared" si="122"/>
         <v>-0.30844727286201273</v>
       </c>
-      <c r="AC194" s="49"/>
-    </row>
-    <row r="195" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B195" s="20" t="s">
+      <c r="AC197" s="49"/>
+    </row>
+    <row r="198" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B198" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="M195" s="81">
-        <f t="shared" si="113"/>
+      <c r="M198" s="81">
+        <f t="shared" si="121"/>
         <v>1</v>
       </c>
-      <c r="N195" s="81">
-        <f t="shared" si="113"/>
+      <c r="N198" s="81">
+        <f t="shared" si="121"/>
         <v>0.37569180272908909</v>
       </c>
-      <c r="O195" s="81">
-        <f t="shared" si="113"/>
+      <c r="O198" s="81">
+        <f t="shared" si="121"/>
         <v>0.27729682030883041</v>
       </c>
-      <c r="P195" s="81">
-        <f t="shared" si="113"/>
+      <c r="P198" s="81">
+        <f t="shared" si="121"/>
         <v>0.23392027917368038</v>
       </c>
-      <c r="Q195" s="81">
-        <f t="shared" si="113"/>
+      <c r="Q198" s="81">
+        <f t="shared" si="121"/>
         <v>0.19019336689332336</v>
       </c>
-      <c r="T195" s="81">
-        <f t="shared" si="114"/>
+      <c r="T198" s="81">
+        <f t="shared" si="122"/>
         <v>1</v>
       </c>
-      <c r="U195" s="81">
-        <f t="shared" si="114"/>
+      <c r="U198" s="81">
+        <f t="shared" si="122"/>
         <v>6.292089812146523E-2</v>
       </c>
-      <c r="V195" s="81">
-        <f t="shared" si="114"/>
+      <c r="V198" s="81">
+        <f t="shared" si="122"/>
         <v>4.0106900184610626E-2</v>
       </c>
-      <c r="W195" s="81">
-        <f t="shared" si="114"/>
+      <c r="W198" s="81">
+        <f t="shared" si="122"/>
         <v>9.673777187170397E-3</v>
       </c>
-      <c r="X195" s="81">
-        <f t="shared" si="114"/>
+      <c r="X198" s="81">
+        <f t="shared" si="122"/>
         <v>9.6915367022084364E-2</v>
       </c>
-      <c r="Y195" s="81">
-        <f t="shared" si="114"/>
+      <c r="Y198" s="81">
+        <f t="shared" si="122"/>
         <v>3.8638547089942653E-2</v>
       </c>
-      <c r="Z195" s="81">
-        <f t="shared" si="114"/>
+      <c r="Z198" s="81">
+        <f t="shared" si="122"/>
         <v>1.4783518396594137E-2</v>
       </c>
-      <c r="AA195" s="81">
-        <f t="shared" si="114"/>
+      <c r="AA198" s="81">
+        <f t="shared" si="122"/>
         <v>6.6472159310281692E-3</v>
       </c>
-      <c r="AC195" s="49"/>
-    </row>
-    <row r="196" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B196" s="20" t="s">
+      <c r="AC198" s="49"/>
+    </row>
+    <row r="199" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B199" s="20" t="s">
         <v>115</v>
       </c>
-      <c r="M196" s="81">
-        <f t="shared" si="113"/>
+      <c r="M199" s="81">
+        <f t="shared" si="121"/>
         <v>1</v>
       </c>
-      <c r="N196" s="81">
-        <f t="shared" si="113"/>
+      <c r="N199" s="81">
+        <f t="shared" si="121"/>
         <v>0.26768885199472631</v>
       </c>
-      <c r="O196" s="81">
-        <f t="shared" si="113"/>
+      <c r="O199" s="81">
+        <f t="shared" si="121"/>
         <v>-0.29197642617772812</v>
       </c>
-      <c r="P196" s="81">
-        <f t="shared" si="113"/>
+      <c r="P199" s="81">
+        <f t="shared" si="121"/>
         <v>0.10317719384146673</v>
       </c>
-      <c r="Q196" s="81">
-        <f t="shared" si="113"/>
+      <c r="Q199" s="81">
+        <f t="shared" si="121"/>
         <v>0.22564418690666996</v>
       </c>
-      <c r="T196" s="81">
-        <f t="shared" si="114"/>
+      <c r="T199" s="81">
+        <f t="shared" si="122"/>
         <v>1</v>
       </c>
-      <c r="U196" s="81">
-        <f t="shared" si="114"/>
+      <c r="U199" s="81">
+        <f t="shared" si="122"/>
         <v>0.13163254368099475</v>
       </c>
-      <c r="V196" s="81">
-        <f t="shared" si="114"/>
+      <c r="V199" s="81">
+        <f t="shared" si="122"/>
         <v>2.4533484891541158E-2</v>
       </c>
-      <c r="W196" s="81">
-        <f t="shared" si="114"/>
+      <c r="W199" s="81">
+        <f t="shared" si="122"/>
         <v>2.0247781065088757E-2</v>
       </c>
-      <c r="X196" s="81">
-        <f t="shared" si="114"/>
+      <c r="X199" s="81">
+        <f t="shared" si="122"/>
         <v>1.5314907113729044E-2</v>
       </c>
-      <c r="Y196" s="81">
-        <f t="shared" si="114"/>
+      <c r="Y199" s="81">
+        <f t="shared" si="122"/>
         <v>0.20465905033916459</v>
       </c>
-      <c r="Z196" s="81">
-        <f t="shared" si="114"/>
+      <c r="Z199" s="81">
+        <f t="shared" si="122"/>
         <v>3.5044824775876122E-2</v>
       </c>
-      <c r="AA196" s="81">
-        <f t="shared" si="114"/>
+      <c r="AA199" s="81">
+        <f t="shared" si="122"/>
         <v>0.15748031496062992</v>
       </c>
-      <c r="AC196" s="49"/>
-    </row>
-    <row r="198" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B198" s="1"/>
-    </row>
-    <row r="199" spans="2:29" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B199" s="14" t="s">
+      <c r="AC199" s="49"/>
+    </row>
+    <row r="201" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B201" s="1"/>
+    </row>
+    <row r="202" spans="2:29" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B202" s="14" t="s">
         <v>364</v>
       </c>
-      <c r="C199" s="192"/>
-      <c r="D199" s="192"/>
-      <c r="E199" s="192"/>
-      <c r="F199" s="192"/>
-      <c r="G199" s="192"/>
-      <c r="H199" s="192"/>
-      <c r="I199" s="192"/>
-      <c r="J199" s="192"/>
-      <c r="K199" s="192"/>
-      <c r="L199" s="192"/>
-      <c r="M199" s="192"/>
-      <c r="N199" s="192"/>
-      <c r="O199" s="192"/>
-      <c r="P199" s="192"/>
-      <c r="Q199" s="192"/>
-      <c r="T199" s="192"/>
-      <c r="U199" s="192"/>
-      <c r="V199" s="192"/>
-      <c r="W199" s="192"/>
-      <c r="X199" s="192"/>
-      <c r="Y199" s="192"/>
-      <c r="Z199" s="192"/>
-      <c r="AA199" s="192"/>
-      <c r="AC199" s="192"/>
-    </row>
-    <row r="200" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B200" s="20" t="s">
+      <c r="C202" s="192"/>
+      <c r="D202" s="192"/>
+      <c r="E202" s="192"/>
+      <c r="F202" s="192"/>
+      <c r="G202" s="192"/>
+      <c r="H202" s="192"/>
+      <c r="I202" s="192"/>
+      <c r="J202" s="192"/>
+      <c r="K202" s="192"/>
+      <c r="L202" s="192"/>
+      <c r="M202" s="192"/>
+      <c r="N202" s="192"/>
+      <c r="O202" s="192"/>
+      <c r="P202" s="192"/>
+      <c r="Q202" s="192"/>
+      <c r="T202" s="192"/>
+      <c r="U202" s="192"/>
+      <c r="V202" s="192"/>
+      <c r="W202" s="192"/>
+      <c r="X202" s="192"/>
+      <c r="Y202" s="192"/>
+      <c r="Z202" s="192"/>
+      <c r="AA202" s="192"/>
+      <c r="AC202" s="192"/>
+    </row>
+    <row r="203" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B203" s="20" t="s">
         <v>333</v>
       </c>
-      <c r="C200" s="81"/>
-      <c r="D200" s="81"/>
-      <c r="E200" s="81"/>
-      <c r="F200" s="81"/>
-      <c r="G200" s="81"/>
-      <c r="H200" s="81"/>
-      <c r="I200" s="81"/>
-      <c r="J200" s="81"/>
-      <c r="K200" s="81"/>
-      <c r="L200" s="81"/>
-      <c r="M200" s="81">
+      <c r="C203" s="81"/>
+      <c r="D203" s="81"/>
+      <c r="E203" s="81"/>
+      <c r="F203" s="81"/>
+      <c r="G203" s="81"/>
+      <c r="H203" s="81"/>
+      <c r="I203" s="81"/>
+      <c r="J203" s="81"/>
+      <c r="K203" s="81"/>
+      <c r="L203" s="81"/>
+      <c r="M203" s="81">
         <f>IF(L64=0,
 IF(M64=0,0,IF(M64&gt;0,1,-1)),
 (M64-L64)/L64
 )</f>
         <v>0</v>
       </c>
-      <c r="N200" s="81">
+      <c r="N203" s="81">
         <f>IF(M64=0,
 IF(N64=0,0,IF(N64&gt;0,1,-1)),
 (N64-M64)/M64
 )</f>
         <v>0</v>
       </c>
-      <c r="O200" s="81">
+      <c r="O203" s="81">
         <f>IF(N64=0,
 IF(O64=0,0,IF(O64&gt;0,1,-1)),
 (O64-N64)/N64
 )</f>
         <v>0</v>
       </c>
-      <c r="P200" s="81">
+      <c r="P203" s="81">
         <f>IF(O64=0,
 IF(P64=0,0,IF(P64&gt;0,1,-1)),
 (P64-O64)/O64
 )</f>
         <v>0</v>
       </c>
-      <c r="Q200" s="81">
+      <c r="Q203" s="81">
         <f>IF(P64=0,
 IF(Q64=0,0,IF(Q64&gt;0,1,-1)),
 (Q64-P64)/P64
 )</f>
         <v>0</v>
       </c>
-      <c r="T200" s="49"/>
-      <c r="U200" s="49"/>
-      <c r="V200" s="49"/>
-      <c r="W200" s="49"/>
-      <c r="X200" s="49"/>
-      <c r="Y200" s="49"/>
-      <c r="Z200" s="49"/>
-      <c r="AA200" s="49"/>
-      <c r="AC200" s="49"/>
-    </row>
-    <row r="202" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B202" s="1"/>
-    </row>
-    <row r="203" spans="2:29" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B203" s="14" t="s">
+      <c r="T203" s="49"/>
+      <c r="U203" s="49"/>
+      <c r="V203" s="49"/>
+      <c r="W203" s="49"/>
+      <c r="X203" s="49"/>
+      <c r="Y203" s="49"/>
+      <c r="Z203" s="49"/>
+      <c r="AA203" s="49"/>
+      <c r="AC203" s="49"/>
+    </row>
+    <row r="205" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B205" s="1"/>
+    </row>
+    <row r="206" spans="2:29" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B206" s="14" t="s">
+        <v>410</v>
+      </c>
+      <c r="C206" s="192"/>
+      <c r="D206" s="192"/>
+      <c r="E206" s="192"/>
+      <c r="F206" s="192"/>
+      <c r="G206" s="192"/>
+      <c r="H206" s="192"/>
+      <c r="I206" s="192"/>
+      <c r="J206" s="192"/>
+      <c r="K206" s="192"/>
+      <c r="L206" s="192"/>
+      <c r="M206" s="192"/>
+      <c r="N206" s="192"/>
+      <c r="O206" s="192"/>
+      <c r="P206" s="192"/>
+      <c r="Q206" s="192"/>
+      <c r="T206" s="192"/>
+      <c r="U206" s="192"/>
+      <c r="V206" s="192"/>
+      <c r="W206" s="192"/>
+      <c r="X206" s="192"/>
+      <c r="Y206" s="192"/>
+      <c r="Z206" s="192"/>
+      <c r="AA206" s="192"/>
+      <c r="AC206" s="192"/>
+    </row>
+    <row r="207" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B207" s="20" t="s">
         <v>411</v>
       </c>
-      <c r="C203" s="192"/>
-      <c r="D203" s="192"/>
-      <c r="E203" s="192"/>
-      <c r="F203" s="192"/>
-      <c r="G203" s="192"/>
-      <c r="H203" s="192"/>
-      <c r="I203" s="192"/>
-      <c r="J203" s="192"/>
-      <c r="K203" s="192"/>
-      <c r="L203" s="192"/>
-      <c r="M203" s="192"/>
-      <c r="N203" s="192"/>
-      <c r="O203" s="192"/>
-      <c r="P203" s="192"/>
-      <c r="Q203" s="192"/>
-      <c r="T203" s="192"/>
-      <c r="U203" s="192"/>
-      <c r="V203" s="192"/>
-      <c r="W203" s="192"/>
-      <c r="X203" s="192"/>
-      <c r="Y203" s="192"/>
-      <c r="Z203" s="192"/>
-      <c r="AA203" s="192"/>
-      <c r="AC203" s="192"/>
-    </row>
-    <row r="204" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B204" s="20" t="s">
-        <v>412</v>
-      </c>
-      <c r="M204" s="164">
+      <c r="M207" s="164">
         <v>100</v>
       </c>
-      <c r="N204" s="164">
+      <c r="N207" s="164">
         <f>100*(1+((N117-$M117)/ABS($M117)))</f>
         <v>43.583607538139404</v>
       </c>
-      <c r="O204" s="164">
-        <f t="shared" ref="O204:Q204" si="115">100*(1+((O117-$M117)/ABS($M117)))</f>
+      <c r="O207" s="164">
+        <f t="shared" ref="O207:Q207" si="123">100*(1+((O117-$M117)/ABS($M117)))</f>
         <v>71.343104995513016</v>
       </c>
-      <c r="P204" s="164">
-        <f t="shared" si="115"/>
+      <c r="P207" s="164">
+        <f t="shared" si="123"/>
         <v>43.613520789709838</v>
       </c>
-      <c r="Q204" s="164">
-        <f t="shared" si="115"/>
+      <c r="Q207" s="164">
+        <f t="shared" si="123"/>
         <v>37.660783727191152</v>
       </c>
-      <c r="T204" s="49"/>
-      <c r="U204" s="49"/>
-      <c r="V204" s="49"/>
-      <c r="W204" s="49"/>
-      <c r="X204" s="49"/>
-      <c r="Y204" s="49"/>
-      <c r="Z204" s="49"/>
-      <c r="AA204" s="49"/>
-      <c r="AC204" s="49"/>
-    </row>
-    <row r="205" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B205" s="20" t="s">
-        <v>413</v>
-      </c>
-      <c r="M205" s="164">
+      <c r="T207" s="49"/>
+      <c r="U207" s="49"/>
+      <c r="V207" s="49"/>
+      <c r="W207" s="49"/>
+      <c r="X207" s="49"/>
+      <c r="Y207" s="49"/>
+      <c r="Z207" s="49"/>
+      <c r="AA207" s="49"/>
+      <c r="AC207" s="49"/>
+    </row>
+    <row r="208" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B208" s="20" t="s">
+        <v>412</v>
+      </c>
+      <c r="M208" s="164">
         <v>100</v>
       </c>
-      <c r="N205" s="164">
+      <c r="N208" s="164">
         <f>100*(1+((N5-$M5)/ABS($M5)))</f>
         <v>118.64148245114609</v>
       </c>
-      <c r="O205" s="164">
-        <f t="shared" ref="O205:Q205" si="116">100*(1+((O5-$M5)/ABS($M5)))</f>
+      <c r="O208" s="164">
+        <f t="shared" ref="O208:Q208" si="124">100*(1+((O5-$M5)/ABS($M5)))</f>
         <v>146.60342593796372</v>
       </c>
-      <c r="P205" s="164">
-        <f t="shared" si="116"/>
+      <c r="P208" s="164">
+        <f t="shared" si="124"/>
         <v>160.23096613961079</v>
       </c>
-      <c r="Q205" s="164">
-        <f t="shared" si="116"/>
+      <c r="Q208" s="164">
+        <f t="shared" si="124"/>
         <v>180.50640402038886</v>
       </c>
-      <c r="T205" s="49"/>
-      <c r="U205" s="49"/>
-      <c r="V205" s="49"/>
-      <c r="W205" s="49"/>
-      <c r="X205" s="49"/>
-      <c r="Y205" s="49"/>
-      <c r="Z205" s="49"/>
-      <c r="AA205" s="49"/>
-      <c r="AC205" s="49"/>
-    </row>
-    <row r="206" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B206" s="20" t="s">
-        <v>414</v>
-      </c>
-      <c r="M206" s="164">
+      <c r="T208" s="49"/>
+      <c r="U208" s="49"/>
+      <c r="V208" s="49"/>
+      <c r="W208" s="49"/>
+      <c r="X208" s="49"/>
+      <c r="Y208" s="49"/>
+      <c r="Z208" s="49"/>
+      <c r="AA208" s="49"/>
+      <c r="AC208" s="49"/>
+    </row>
+    <row r="209" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="B209" s="20" t="s">
+        <v>413</v>
+      </c>
+      <c r="M209" s="164">
         <v>100</v>
       </c>
-      <c r="N206" s="164">
+      <c r="N209" s="164">
         <f>100*(1+((N26-$M26)/ABS($M26)))</f>
         <v>148.27586206896552</v>
       </c>
-      <c r="O206" s="164">
-        <f t="shared" ref="O206:Q206" si="117">100*(1+((O26-$M26)/ABS($M26)))</f>
+      <c r="O209" s="164">
+        <f t="shared" ref="O209:Q209" si="125">100*(1+((O26-$M26)/ABS($M26)))</f>
         <v>186.20689655172413</v>
       </c>
-      <c r="P206" s="164">
-        <f t="shared" si="117"/>
+      <c r="P209" s="164">
+        <f t="shared" si="125"/>
         <v>188.79310344827584</v>
       </c>
-      <c r="Q206" s="164">
-        <f t="shared" si="117"/>
+      <c r="Q209" s="164">
+        <f t="shared" si="125"/>
         <v>244.82758620689654</v>
       </c>
-      <c r="T206" s="49"/>
-      <c r="U206" s="49"/>
-      <c r="V206" s="49"/>
-      <c r="W206" s="49"/>
-      <c r="X206" s="49"/>
-      <c r="Y206" s="49"/>
-      <c r="Z206" s="49"/>
-      <c r="AA206" s="49"/>
-      <c r="AC206" s="49"/>
-    </row>
-    <row r="208" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B208" s="1"/>
-    </row>
-    <row r="209" spans="1:31" s="15" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A209" s="11"/>
-      <c r="B209" s="14" t="s">
+      <c r="T209" s="49"/>
+      <c r="U209" s="49"/>
+      <c r="V209" s="49"/>
+      <c r="W209" s="49"/>
+      <c r="X209" s="49"/>
+      <c r="Y209" s="49"/>
+      <c r="Z209" s="49"/>
+      <c r="AA209" s="49"/>
+      <c r="AC209" s="49"/>
+    </row>
+    <row r="211" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="B211" s="1"/>
+    </row>
+    <row r="212" spans="1:31" s="15" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A212" s="11"/>
+      <c r="B212" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="R209" s="1"/>
-      <c r="S209" s="1"/>
-      <c r="AB209" s="1"/>
-      <c r="AD209" s="1"/>
-      <c r="AE209" s="1"/>
-    </row>
-    <row r="210" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="B210" s="20" t="s">
-        <v>130</v>
-      </c>
-      <c r="C210" s="62"/>
-      <c r="D210" s="62"/>
-      <c r="E210" s="62"/>
-      <c r="F210" s="62"/>
-      <c r="G210" s="62"/>
-      <c r="H210" s="62"/>
-      <c r="I210" s="62"/>
-      <c r="J210" s="62"/>
-      <c r="K210" s="62"/>
-      <c r="L210" s="62"/>
-      <c r="M210" s="62">
-        <v>925276</v>
-      </c>
-      <c r="N210" s="62">
-        <v>1203845</v>
-      </c>
-      <c r="O210" s="62">
-        <v>1463698</v>
-      </c>
-      <c r="P210" s="62">
-        <v>1666136</v>
-      </c>
-      <c r="Q210" s="62">
-        <v>1852567</v>
-      </c>
-      <c r="T210" s="62">
-        <v>1550605</v>
-      </c>
-      <c r="U210" s="62">
-        <v>1606561</v>
-      </c>
-      <c r="V210" s="62">
-        <v>1666136</v>
-      </c>
-      <c r="W210" s="62">
-        <v>1692683</v>
-      </c>
-      <c r="X210" s="62">
-        <v>1723401</v>
-      </c>
-      <c r="Y210" s="62">
-        <v>1782384</v>
-      </c>
-      <c r="Z210" s="62">
-        <v>1852567</v>
-      </c>
-      <c r="AA210" s="62">
-        <v>1901211</v>
-      </c>
-      <c r="AC210" s="62">
-        <f>AA210</f>
-        <v>1901211</v>
-      </c>
-    </row>
-    <row r="211" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="B211" s="20" t="s">
-        <v>131</v>
-      </c>
-      <c r="C211" s="62"/>
-      <c r="D211" s="62"/>
-      <c r="E211" s="62"/>
-      <c r="F211" s="62"/>
-      <c r="G211" s="62"/>
-      <c r="H211" s="62"/>
-      <c r="I211" s="62"/>
-      <c r="J211" s="62"/>
-      <c r="K211" s="62"/>
-      <c r="L211" s="62"/>
-      <c r="M211" s="62">
-        <v>344793</v>
-      </c>
-      <c r="N211" s="62">
-        <v>278569</v>
-      </c>
-      <c r="O211" s="62">
-        <v>259853</v>
-      </c>
-      <c r="P211" s="62">
-        <v>202438</v>
-      </c>
-      <c r="Q211" s="62">
-        <v>186431</v>
-      </c>
-      <c r="T211" s="62">
-        <v>43000</v>
-      </c>
-      <c r="U211" s="62">
-        <v>56000</v>
-      </c>
-      <c r="V211" s="62">
-        <v>60000</v>
-      </c>
-      <c r="W211" s="62">
-        <v>27000</v>
-      </c>
-      <c r="X211" s="62">
-        <v>31000</v>
-      </c>
-      <c r="Y211" s="62">
-        <v>59000</v>
-      </c>
-      <c r="Z211" s="62">
-        <v>70000</v>
-      </c>
-      <c r="AA211" s="62">
-        <v>49000</v>
-      </c>
-      <c r="AC211" s="83">
-        <f>SUM(X211:AA211)</f>
-        <v>209000</v>
-      </c>
-    </row>
-    <row r="212" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="B212" s="20" t="s">
-        <v>132</v>
-      </c>
-      <c r="C212" s="57"/>
-      <c r="D212" s="57"/>
-      <c r="E212" s="57"/>
-      <c r="F212" s="57"/>
-      <c r="G212" s="57"/>
-      <c r="H212" s="57"/>
-      <c r="I212" s="57"/>
-      <c r="J212" s="57"/>
-      <c r="K212" s="57"/>
-      <c r="L212" s="82"/>
-      <c r="M212" s="82">
-        <v>1.45</v>
-      </c>
-      <c r="N212" s="82">
-        <v>1.23</v>
-      </c>
-      <c r="O212" s="82">
-        <v>1.19</v>
-      </c>
-      <c r="P212" s="82">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="Q212" s="82">
-        <v>1.07</v>
-      </c>
-      <c r="T212" s="82">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="U212" s="82">
-        <v>1.1299999999999999</v>
-      </c>
-      <c r="V212" s="82">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="W212" s="82">
-        <v>1.08</v>
-      </c>
-      <c r="X212" s="82">
-        <v>1.08</v>
-      </c>
-      <c r="Y212" s="82">
-        <v>1.07</v>
-      </c>
-      <c r="Z212" s="82">
-        <v>1.07</v>
-      </c>
-      <c r="AA212" s="82">
-        <v>1.0900000000000001</v>
-      </c>
-      <c r="AC212" s="82">
-        <f>AA212</f>
-        <v>1.0900000000000001</v>
-      </c>
+      <c r="R212" s="1"/>
+      <c r="S212" s="1"/>
+      <c r="AB212" s="1"/>
+      <c r="AD212" s="1"/>
+      <c r="AE212" s="1"/>
     </row>
     <row r="213" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B213" s="20" t="s">
-        <v>133</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="C213" s="62"/>
+      <c r="D213" s="62"/>
+      <c r="E213" s="62"/>
+      <c r="F213" s="62"/>
+      <c r="G213" s="62"/>
+      <c r="H213" s="62"/>
+      <c r="I213" s="62"/>
+      <c r="J213" s="62"/>
+      <c r="K213" s="62"/>
+      <c r="L213" s="62"/>
       <c r="M213" s="62">
-        <v>158</v>
+        <v>925276</v>
       </c>
       <c r="N213" s="62">
-        <v>229</v>
+        <v>1203845</v>
       </c>
       <c r="O213" s="62">
-        <v>288</v>
+        <v>1463698</v>
       </c>
       <c r="P213" s="62">
-        <v>317</v>
+        <v>1666136</v>
       </c>
       <c r="Q213" s="62">
-        <v>357</v>
+        <v>1852567</v>
       </c>
       <c r="T213" s="62">
-        <v>293</v>
+        <v>1550605</v>
       </c>
       <c r="U213" s="62">
-        <v>302</v>
+        <v>1606561</v>
       </c>
       <c r="V213" s="62">
-        <v>317</v>
+        <v>1666136</v>
       </c>
       <c r="W213" s="62">
-        <v>316</v>
+        <v>1692683</v>
       </c>
       <c r="X213" s="62">
-        <v>320</v>
+        <v>1723401</v>
       </c>
       <c r="Y213" s="62">
-        <v>333</v>
+        <v>1782384</v>
       </c>
       <c r="Z213" s="62">
-        <v>357</v>
+        <v>1852567</v>
       </c>
       <c r="AA213" s="62">
-        <v>374</v>
+        <v>1901211</v>
       </c>
       <c r="AC213" s="62">
         <f>AA213</f>
-        <v>374</v>
+        <v>1901211</v>
       </c>
     </row>
     <row r="214" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B214" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="C214" s="62"/>
+      <c r="D214" s="62"/>
+      <c r="E214" s="62"/>
+      <c r="F214" s="62"/>
+      <c r="G214" s="62"/>
+      <c r="H214" s="62"/>
+      <c r="I214" s="62"/>
+      <c r="J214" s="62"/>
+      <c r="K214" s="62"/>
+      <c r="L214" s="62"/>
+      <c r="M214" s="62">
+        <v>344793</v>
+      </c>
+      <c r="N214" s="62">
+        <v>278569</v>
+      </c>
+      <c r="O214" s="62">
+        <v>259853</v>
+      </c>
+      <c r="P214" s="62">
+        <v>202438</v>
+      </c>
+      <c r="Q214" s="62">
+        <v>186431</v>
+      </c>
+      <c r="T214" s="62">
+        <v>43000</v>
+      </c>
+      <c r="U214" s="62">
+        <v>56000</v>
+      </c>
+      <c r="V214" s="62">
+        <v>60000</v>
+      </c>
+      <c r="W214" s="62">
+        <v>27000</v>
+      </c>
+      <c r="X214" s="62">
+        <v>31000</v>
+      </c>
+      <c r="Y214" s="62">
+        <v>59000</v>
+      </c>
+      <c r="Z214" s="62">
+        <v>70000</v>
+      </c>
+      <c r="AA214" s="62">
+        <v>49000</v>
+      </c>
+      <c r="AC214" s="83">
+        <f>SUM(X214:AA214)</f>
+        <v>209000</v>
+      </c>
+    </row>
+    <row r="215" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="B215" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="C215" s="57"/>
+      <c r="D215" s="57"/>
+      <c r="E215" s="57"/>
+      <c r="F215" s="57"/>
+      <c r="G215" s="57"/>
+      <c r="H215" s="57"/>
+      <c r="I215" s="57"/>
+      <c r="J215" s="57"/>
+      <c r="K215" s="57"/>
+      <c r="L215" s="82"/>
+      <c r="M215" s="82">
+        <v>1.45</v>
+      </c>
+      <c r="N215" s="82">
+        <v>1.23</v>
+      </c>
+      <c r="O215" s="82">
+        <v>1.19</v>
+      </c>
+      <c r="P215" s="82">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="Q215" s="82">
+        <v>1.07</v>
+      </c>
+      <c r="T215" s="82">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="U215" s="82">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="V215" s="82">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="W215" s="82">
+        <v>1.08</v>
+      </c>
+      <c r="X215" s="82">
+        <v>1.08</v>
+      </c>
+      <c r="Y215" s="82">
+        <v>1.07</v>
+      </c>
+      <c r="Z215" s="82">
+        <v>1.07</v>
+      </c>
+      <c r="AA215" s="82">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="AC215" s="82">
+        <f>AA215</f>
+        <v>1.0900000000000001</v>
+      </c>
+    </row>
+    <row r="216" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="B216" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="M216" s="62">
+        <v>158</v>
+      </c>
+      <c r="N216" s="62">
+        <v>229</v>
+      </c>
+      <c r="O216" s="62">
+        <v>288</v>
+      </c>
+      <c r="P216" s="62">
+        <v>317</v>
+      </c>
+      <c r="Q216" s="62">
+        <v>357</v>
+      </c>
+      <c r="T216" s="62">
+        <v>293</v>
+      </c>
+      <c r="U216" s="62">
+        <v>302</v>
+      </c>
+      <c r="V216" s="62">
+        <v>317</v>
+      </c>
+      <c r="W216" s="62">
+        <v>316</v>
+      </c>
+      <c r="X216" s="62">
+        <v>320</v>
+      </c>
+      <c r="Y216" s="62">
+        <v>333</v>
+      </c>
+      <c r="Z216" s="62">
+        <v>357</v>
+      </c>
+      <c r="AA216" s="62">
+        <v>374</v>
+      </c>
+      <c r="AC216" s="62">
+        <f>AA216</f>
+        <v>374</v>
+      </c>
+    </row>
+    <row r="217" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="B217" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="M214" s="62">
+      <c r="M217" s="62">
         <v>1493</v>
       </c>
-      <c r="N214" s="62">
+      <c r="N217" s="62">
         <v>1785</v>
       </c>
-      <c r="O214" s="62">
+      <c r="O217" s="62">
         <v>2054</v>
       </c>
-      <c r="P214" s="62">
+      <c r="P217" s="62">
         <v>2292</v>
       </c>
-      <c r="Q214" s="62">
+      <c r="Q217" s="62">
         <v>2565</v>
       </c>
-      <c r="T214" s="62">
+      <c r="T217" s="62">
         <v>2163</v>
       </c>
-      <c r="U214" s="62">
+      <c r="U217" s="62">
         <v>2235</v>
       </c>
-      <c r="V214" s="62">
+      <c r="V217" s="62">
         <v>2292</v>
       </c>
-      <c r="W214" s="62">
+      <c r="W217" s="62">
         <v>2365</v>
       </c>
-      <c r="X214" s="62">
+      <c r="X217" s="62">
         <v>2432</v>
       </c>
-      <c r="Y214" s="62">
+      <c r="Y217" s="62">
         <v>2506</v>
       </c>
-      <c r="Z214" s="62">
+      <c r="Z217" s="62">
         <v>2565</v>
       </c>
-      <c r="AA214" s="62">
+      <c r="AA217" s="62">
         <v>2624</v>
       </c>
-      <c r="AC214" s="62">
-        <f>AA214</f>
+      <c r="AC217" s="62">
+        <f>AA217</f>
         <v>2624</v>
       </c>
     </row>
-    <row r="215" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="B215" s="1"/>
+    <row r="218" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="B218" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -33293,9 +33420,9 @@
       <c r="B5" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="194">
+      <c r="C5" s="193">
         <f ca="1">Overview!C5</f>
-        <v>10.5725</v>
+        <v>10.26</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="153" t="s">
@@ -33309,18 +33436,18 @@
       <c r="B6" s="20" t="s">
         <v>288</v>
       </c>
-      <c r="C6" s="195">
+      <c r="C6" s="194">
         <f ca="1">Statement!AC153</f>
-        <v>5522598.2374999998</v>
+        <v>5359362.3</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="F6" s="200">
+      <c r="F6" s="199">
         <f>IF(Statement!M5&lt;=0,"N/A",_xlfn.RRI(4,Statement!M5,Statement!Q5))</f>
         <v>0.15910599918172563</v>
       </c>
-      <c r="G6" s="200" t="str">
+      <c r="G6" s="199" t="str">
         <f>IF(Statement!H5&lt;=0,"N/A",_xlfn.RRI(9,Statement!H5,Statement!Q5))</f>
         <v>N/A</v>
       </c>
@@ -33329,18 +33456,18 @@
       <c r="B7" s="20" t="s">
         <v>229</v>
       </c>
-      <c r="C7" s="195">
+      <c r="C7" s="194">
         <f ca="1">Statement!AC154</f>
-        <v>4106852.2374999998</v>
+        <v>3943616.3</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="F7" s="200" t="str">
+      <c r="F7" s="199" t="str">
         <f>IF(OR(Statement!M18&lt;=0, Statement!Q18&lt;=0), "N/A", _xlfn.RRI(4, Statement!M18, Statement!Q18))</f>
         <v>N/A</v>
       </c>
-      <c r="G7" s="200" t="str">
+      <c r="G7" s="199" t="str">
         <f>IF(OR(Statement!H18&lt;=0, Statement!Q18&lt;=0), "N/A", _xlfn.RRI(9, Statement!H18, Statement!Q18))</f>
         <v>N/A</v>
       </c>
@@ -33349,18 +33476,18 @@
       <c r="B8" s="20" t="s">
         <v>286</v>
       </c>
-      <c r="C8" s="196">
+      <c r="C8" s="195">
         <f ca="1">Statement!AC150</f>
-        <v>17.62083333333333</v>
+        <v>17.099999999999998</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>292</v>
       </c>
-      <c r="F8" s="200" t="str">
+      <c r="F8" s="199" t="str">
         <f>IF(OR(Statement!M26&lt;=0, Statement!Q26&lt;=0), "N/A", _xlfn.RRI(4, Statement!M26, Statement!Q26))</f>
         <v>N/A</v>
       </c>
-      <c r="G8" s="200" t="str">
+      <c r="G8" s="199" t="str">
         <f>IF(OR(Statement!H26&lt;=0, Statement!Q26&lt;=0), "N/A", _xlfn.RRI(9, Statement!H26, Statement!Q26))</f>
         <v>N/A</v>
       </c>
@@ -33369,18 +33496,18 @@
       <c r="B9" s="20" t="s">
         <v>242</v>
       </c>
-      <c r="C9" s="196">
+      <c r="C9" s="195">
         <f ca="1">Statement!AC151</f>
-        <v>3.4059633733324164</v>
+        <v>3.305290537752716</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>293</v>
       </c>
-      <c r="F9" s="200" t="str">
+      <c r="F9" s="199" t="str">
         <f>IF(Statement!M82&lt;=0,"N/A",_xlfn.RRI(4,Statement!M82,Statement!Q82))</f>
         <v>N/A</v>
       </c>
-      <c r="G9" s="200" t="str">
+      <c r="G9" s="199" t="str">
         <f>IF(Statement!H82&lt;=0,"N/A",_xlfn.RRI(9,Statement!H82,Statement!Q82))</f>
         <v>N/A</v>
       </c>
@@ -33389,18 +33516,18 @@
       <c r="B10" s="20" t="s">
         <v>287</v>
       </c>
-      <c r="C10" s="196">
+      <c r="C10" s="195">
         <f ca="1">Statement!AC152</f>
-        <v>2.8785785721229762</v>
+        <v>2.7934940789767544</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="F10" s="200">
+      <c r="F10" s="199">
         <f>IF(Statement!M117&lt;=0,"N/A",_xlfn.RRI(4,Statement!M117,Statement!Q117))</f>
         <v>-0.21662025481427405</v>
       </c>
-      <c r="G10" s="200" t="str">
+      <c r="G10" s="199" t="str">
         <f>IF(Statement!H117&lt;=0,"N/A",_xlfn.RRI(9,Statement!H117,Statement!Q117))</f>
         <v>N/A</v>
       </c>
@@ -33409,18 +33536,18 @@
       <c r="B11" s="20" t="s">
         <v>309</v>
       </c>
-      <c r="C11" s="196">
+      <c r="C11" s="195">
         <f ca="1">Statement!AC155</f>
-        <v>2.4557666474320259</v>
+        <v>2.3581567633182443</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="20" t="s">
         <v>245</v>
       </c>
-      <c r="C12" s="196">
+      <c r="C12" s="195">
         <f ca="1">Statement!AC156</f>
-        <v>40.597991651756146</v>
+        <v>38.98433456242153</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -33437,14 +33564,14 @@
       <c r="B16" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="C16" s="197">
+      <c r="C16" s="196">
         <f>Statement!AC101</f>
         <v>0.83014417010996633</v>
       </c>
       <c r="E16" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="F16" s="195">
+      <c r="F16" s="194">
         <f>Statement!AC18</f>
         <v>327410</v>
       </c>
@@ -33453,14 +33580,14 @@
       <c r="B17" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="C17" s="197">
+      <c r="C17" s="196">
         <f>Statement!AC102</f>
         <v>6.0489855471109168E-2</v>
       </c>
       <c r="E17" s="20" t="s">
         <v>296</v>
       </c>
-      <c r="F17" s="195">
+      <c r="F17" s="194">
         <f>Statement!AC59</f>
         <v>384134</v>
       </c>
@@ -33469,14 +33596,14 @@
       <c r="B18" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="C18" s="197">
+      <c r="C18" s="196">
         <f>Statement!AC103</f>
         <v>0.19578073705548546</v>
       </c>
       <c r="E18" s="20" t="s">
         <v>303</v>
       </c>
-      <c r="F18" s="199">
+      <c r="F18" s="198">
         <f>IF(OR(F16&lt;=0, F17&lt;=0),"N/A",F16-F17)</f>
         <v>-56724</v>
       </c>
@@ -33495,14 +33622,14 @@
       <c r="B22" s="20" t="s">
         <v>119</v>
       </c>
-      <c r="C22" s="197">
+      <c r="C22" s="196">
         <f>Statement!AC121</f>
         <v>0.19578073705548546</v>
       </c>
       <c r="E22" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="F22" s="197">
+      <c r="F22" s="196">
         <f>C24</f>
         <v>0.1127173202051847</v>
       </c>
@@ -33511,14 +33638,14 @@
       <c r="B23" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="C23" s="196">
+      <c r="C23" s="195">
         <f>Statement!AC122</f>
         <v>0.57573243364202842</v>
       </c>
       <c r="E23" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="F23" s="197">
+      <c r="F23" s="196">
         <f>C26</f>
         <v>0.17205256008386913</v>
       </c>
@@ -33527,14 +33654,14 @@
       <c r="B24" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="C24" s="198">
+      <c r="C24" s="197">
         <f>Statement!AC123</f>
         <v>0.1127173202051847</v>
       </c>
       <c r="E24" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="F24" s="197">
+      <c r="F24" s="196">
         <f>Statement!AC140</f>
         <v>0.2076253183886507</v>
       </c>
@@ -33543,7 +33670,7 @@
       <c r="B25" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="C25" s="196">
+      <c r="C25" s="195">
         <f>Statement!AC124</f>
         <v>1.5264074746513994</v>
       </c>
@@ -33552,7 +33679,7 @@
       <c r="B26" s="32" t="s">
         <v>123</v>
       </c>
-      <c r="C26" s="198">
+      <c r="C26" s="197">
         <f>Statement!AC125</f>
         <v>0.17205256008386913</v>
       </c>
@@ -33571,14 +33698,14 @@
       <c r="B30" s="20" t="s">
         <v>180</v>
       </c>
-      <c r="C30" s="196">
+      <c r="C30" s="195">
         <f>Statement!AC141</f>
         <v>65.477289171395597</v>
       </c>
       <c r="E30" s="20" t="s">
         <v>306</v>
       </c>
-      <c r="F30" s="202">
+      <c r="F30" s="201">
         <f>Statement!AC145</f>
         <v>0</v>
       </c>
@@ -33587,14 +33714,14 @@
       <c r="B31" s="20" t="s">
         <v>181</v>
       </c>
-      <c r="C31" s="196">
+      <c r="C31" s="195">
         <f>Statement!AC142</f>
         <v>0</v>
       </c>
       <c r="E31" s="20" t="s">
         <v>307</v>
       </c>
-      <c r="F31" s="202">
+      <c r="F31" s="201">
         <f>Statement!AC146</f>
         <v>-0.74396849127545694</v>
       </c>
@@ -33603,14 +33730,14 @@
       <c r="B32" s="20" t="s">
         <v>182</v>
       </c>
-      <c r="C32" s="196">
+      <c r="C32" s="195">
         <f>Statement!AC143</f>
         <v>25.312474696801676</v>
       </c>
       <c r="E32" s="20" t="s">
         <v>302</v>
       </c>
-      <c r="F32" s="202">
+      <c r="F32" s="201">
         <f>Statement!AC148</f>
         <v>2.3066495444084523</v>
       </c>
@@ -33619,14 +33746,14 @@
       <c r="B33" s="20" t="s">
         <v>183</v>
       </c>
-      <c r="C33" s="196">
+      <c r="C33" s="195">
         <f>Statement!AC144</f>
         <v>40.164814474593925</v>
       </c>
       <c r="E33" s="20" t="s">
         <v>301</v>
       </c>
-      <c r="F33" s="202">
+      <c r="F33" s="201">
         <f>Statement!AC147</f>
         <v>2.063021693804965</v>
       </c>
@@ -33635,7 +33762,7 @@
       <c r="E34" s="20" t="s">
         <v>308</v>
       </c>
-      <c r="F34" s="204" t="str">
+      <c r="F34" s="203" t="str">
         <f>Statement!AC149</f>
         <v>N/A</v>
       </c>
@@ -33654,14 +33781,14 @@
       <c r="B38" s="20" t="s">
         <v>315</v>
       </c>
-      <c r="C38" s="197">
+      <c r="C38" s="196">
         <f ca="1">Statement!AC162</f>
-        <v>5.6751004965712941E-2</v>
+        <v>5.8479532163742701E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>319</v>
       </c>
-      <c r="F38" s="197">
+      <c r="F38" s="196">
         <f>Statement!AC168</f>
         <v>0</v>
       </c>
@@ -33670,14 +33797,14 @@
       <c r="B39" s="54" t="s">
         <v>318</v>
       </c>
-      <c r="C39" s="237">
+      <c r="C39" s="236">
         <f ca="1">Statement!AC161</f>
-        <v>1.9485212462008288E-2</v>
+        <v>2.0078694810388171E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>321</v>
       </c>
-      <c r="F39" s="197">
+      <c r="F39" s="196">
         <f>Statement!AC169</f>
         <v>3.2095084983598028</v>
       </c>
@@ -33686,14 +33813,14 @@
       <c r="B40" s="20" t="s">
         <v>316</v>
       </c>
-      <c r="C40" s="197">
+      <c r="C40" s="196">
         <f ca="1">Statement!AC163</f>
         <v>0</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>322</v>
       </c>
-      <c r="F40" s="197">
+      <c r="F40" s="196">
         <f>Statement!AC170</f>
         <v>3.2095084983598028</v>
       </c>
@@ -33702,18 +33829,18 @@
       <c r="B41" s="20" t="s">
         <v>341</v>
       </c>
-      <c r="C41" s="197">
+      <c r="C41" s="196">
         <f ca="1">Statement!AC164</f>
-        <v>6.2537954989161926E-2</v>
+        <v>6.4442741629913702E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B42" s="20" t="s">
         <v>343</v>
       </c>
-      <c r="C42" s="197">
+      <c r="C42" s="196">
         <f ca="1">Statement!AC165</f>
-        <v>6.2537954989161926E-2</v>
+        <v>6.4442741629913702E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -33730,14 +33857,14 @@
       <c r="B46" s="20" t="s">
         <v>326</v>
       </c>
-      <c r="C46" s="197">
+      <c r="C46" s="196">
         <f>Statement!AC171</f>
         <v>0.2236199519483876</v>
       </c>
       <c r="E46" s="20" t="s">
         <v>327</v>
       </c>
-      <c r="F46" s="196">
+      <c r="F46" s="195">
         <f>Statement!AC172</f>
         <v>2.732462108272006</v>
       </c>
@@ -33746,7 +33873,7 @@
       <c r="E47" s="20" t="s">
         <v>335</v>
       </c>
-      <c r="F47" s="196">
+      <c r="F47" s="195">
         <f>Statement!AC175</f>
         <v>2.732462108272006</v>
       </c>
@@ -33755,9 +33882,9 @@
       <c r="E48" s="20" t="s">
         <v>340</v>
       </c>
-      <c r="F48" s="197">
+      <c r="F48" s="196">
         <f ca="1">Statement!AC176</f>
-        <v>0.2563550595418449</v>
+        <v>0.26416314493237375</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -33774,14 +33901,14 @@
       <c r="B52" s="20" t="s">
         <v>329</v>
       </c>
-      <c r="C52" s="197">
+      <c r="C52" s="196">
         <f>Statement!AC173</f>
         <v>0.69669698594761198</v>
       </c>
       <c r="E52" s="20" t="s">
         <v>353</v>
       </c>
-      <c r="F52" s="197">
+      <c r="F52" s="196">
         <f>Statement!AC177</f>
         <v>5.3219161289936798E-3</v>
       </c>
@@ -33790,14 +33917,14 @@
       <c r="B53" s="20" t="s">
         <v>330</v>
       </c>
-      <c r="C53" s="197">
+      <c r="C53" s="196">
         <f>Statement!AC174</f>
         <v>0.16003121393504871</v>
       </c>
       <c r="E53" s="20" t="s">
         <v>350</v>
       </c>
-      <c r="F53" s="197">
+      <c r="F53" s="196">
         <f>Statement!AC178</f>
         <v>2.3168998318295178E-2</v>
       </c>
@@ -33806,7 +33933,7 @@
       <c r="E54" s="20" t="s">
         <v>351</v>
       </c>
-      <c r="F54" s="197">
+      <c r="F54" s="196">
         <f>Statement!AC179</f>
         <v>0.41931684334511188</v>
       </c>
@@ -33914,232 +34041,232 @@
       <c r="B6" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="194">
+      <c r="C6" s="193">
         <f>Statement!M116</f>
         <v>33.43</v>
       </c>
-      <c r="D6" s="194">
+      <c r="D6" s="193">
         <f>Statement!N116</f>
         <v>14.57</v>
       </c>
-      <c r="E6" s="194">
+      <c r="E6" s="193">
         <f>Statement!O116</f>
         <v>23.85</v>
       </c>
-      <c r="F6" s="194">
+      <c r="F6" s="193">
         <f>Statement!P116</f>
         <v>14.58</v>
       </c>
-      <c r="G6" s="194">
+      <c r="G6" s="193">
         <f>Statement!Q116</f>
         <v>12.59</v>
       </c>
-      <c r="I6" s="194">
+      <c r="I6" s="193">
         <f ca="1">Statement!AC116</f>
-        <v>10.5725</v>
+        <v>10.26</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B7" s="20" t="s">
         <v>288</v>
       </c>
-      <c r="C7" s="195">
+      <c r="C7" s="194">
         <f>Statement!M153</f>
         <v>18122001.84</v>
       </c>
-      <c r="D7" s="195">
+      <c r="D7" s="194">
         <f>Statement!N153</f>
         <v>8121653.1100000003</v>
       </c>
-      <c r="E7" s="195">
+      <c r="E7" s="194">
         <f>Statement!O153</f>
         <v>13570960.050000001</v>
       </c>
-      <c r="F7" s="195">
+      <c r="F7" s="194">
         <f>Statement!P153</f>
         <v>8040767.9400000004</v>
       </c>
-      <c r="G7" s="195">
+      <c r="G7" s="194">
         <f>Statement!Q153</f>
         <v>6680971.6299999999</v>
       </c>
-      <c r="I7" s="195">
+      <c r="I7" s="194">
         <f ca="1">Statement!AC153</f>
-        <v>5522598.2374999998</v>
+        <v>5359362.3</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B8" s="20" t="s">
         <v>229</v>
       </c>
-      <c r="C8" s="195">
+      <c r="C8" s="194">
         <f>Statement!M154</f>
         <v>16237338.84</v>
       </c>
-      <c r="D8" s="195">
+      <c r="D8" s="194">
         <f>Statement!N154</f>
         <v>6361818.1100000003</v>
       </c>
-      <c r="E8" s="195">
+      <c r="E8" s="194">
         <f>Statement!O154</f>
         <v>11691137.050000001</v>
       </c>
-      <c r="F8" s="195">
+      <c r="F8" s="194">
         <f>Statement!P154</f>
         <v>6317136.9400000004</v>
       </c>
-      <c r="G8" s="195">
+      <c r="G8" s="194">
         <f>Statement!Q154</f>
         <v>4991495.63</v>
       </c>
-      <c r="I8" s="195">
+      <c r="I8" s="194">
         <f ca="1">Statement!AC154</f>
-        <v>4106852.2374999998</v>
+        <v>3943616.3</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B9" s="20" t="s">
         <v>286</v>
       </c>
-      <c r="C9" s="196">
+      <c r="C9" s="195">
         <f>Statement!M150</f>
         <v>-28.818965517241381</v>
       </c>
-      <c r="D9" s="196">
+      <c r="D9" s="195">
         <f>Statement!N150</f>
         <v>-24.283333333333335</v>
       </c>
-      <c r="E9" s="196">
+      <c r="E9" s="195">
         <f>Statement!O150</f>
         <v>-149.0625</v>
       </c>
-      <c r="F9" s="196">
+      <c r="F9" s="195">
         <f>Statement!P150</f>
         <v>-112.15384615384615</v>
       </c>
-      <c r="G9" s="196">
+      <c r="G9" s="195">
         <f>Statement!Q150</f>
         <v>24.21153846153846</v>
       </c>
-      <c r="I9" s="196">
+      <c r="I9" s="195">
         <f ca="1">Statement!AC150</f>
-        <v>17.62083333333333</v>
+        <v>17.099999999999998</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B10" s="20" t="s">
         <v>242</v>
       </c>
-      <c r="C10" s="196">
+      <c r="C10" s="195">
         <f>Statement!M151</f>
         <v>17.03343197885799</v>
       </c>
-      <c r="D10" s="196">
+      <c r="D10" s="195">
         <f>Statement!N151</f>
         <v>7.5428149003241138</v>
       </c>
-      <c r="E10" s="196">
+      <c r="E10" s="195">
         <f>Statement!O151</f>
         <v>11.921699837623619</v>
       </c>
-      <c r="F10" s="196">
+      <c r="F10" s="195">
         <f>Statement!P151</f>
         <v>5.7103089537122012</v>
       </c>
-      <c r="G10" s="196">
+      <c r="G10" s="195">
         <f>Statement!Q151</f>
         <v>4.2592243004348767</v>
       </c>
-      <c r="I10" s="196">
+      <c r="I10" s="195">
         <f ca="1">Statement!AC151</f>
-        <v>3.4059633733324164</v>
+        <v>3.305290537752716</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B11" s="20" t="s">
         <v>287</v>
       </c>
-      <c r="C11" s="196">
+      <c r="C11" s="195">
         <f>Statement!M152</f>
         <v>9.4291282297830765</v>
       </c>
-      <c r="D11" s="196">
+      <c r="D11" s="195">
         <f>Statement!N152</f>
         <v>4.2296795940750709</v>
       </c>
-      <c r="E11" s="196">
+      <c r="E11" s="195">
         <f>Statement!O152</f>
         <v>6.731246372972957</v>
       </c>
-      <c r="F11" s="196">
+      <c r="F11" s="195">
         <f>Statement!P152</f>
         <v>4.3563406007925183</v>
       </c>
-      <c r="G11" s="196">
+      <c r="G11" s="195">
         <f>Statement!Q152</f>
         <v>3.1673000839820857</v>
       </c>
-      <c r="I11" s="196">
+      <c r="I11" s="195">
         <f ca="1">Statement!AC152</f>
-        <v>2.8785785721229762</v>
+        <v>2.7934940789767544</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B12" s="20" t="s">
         <v>309</v>
       </c>
-      <c r="C12" s="196">
+      <c r="C12" s="195">
         <f>Statement!M155</f>
         <v>18.198153481303489</v>
       </c>
-      <c r="D12" s="196">
+      <c r="D12" s="195">
         <f>Statement!N155</f>
         <v>6.0097603395488868</v>
       </c>
-      <c r="E12" s="196">
+      <c r="E12" s="195">
         <f>Statement!O155</f>
         <v>8.9376861900568176</v>
       </c>
-      <c r="F12" s="196">
+      <c r="F12" s="195">
         <f>Statement!P155</f>
         <v>4.4186165001007236</v>
       </c>
-      <c r="G12" s="196">
+      <c r="G12" s="195">
         <f>Statement!Q155</f>
         <v>3.0992067600827533</v>
       </c>
-      <c r="I12" s="196">
+      <c r="I12" s="195">
         <f ca="1">Statement!AC155</f>
-        <v>2.4557666474320259</v>
+        <v>2.3581567633182443</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B13" s="20" t="s">
         <v>245</v>
       </c>
-      <c r="C13" s="196">
+      <c r="C13" s="195">
         <f>Statement!M156</f>
         <v>-32.413351618737352</v>
       </c>
-      <c r="D13" s="196">
+      <c r="D13" s="195">
         <f>Statement!N156</f>
         <v>-18.266232087124553</v>
       </c>
-      <c r="E13" s="196">
+      <c r="E13" s="195">
         <f>Statement!O156</f>
         <v>-70.97581987615348</v>
       </c>
-      <c r="F13" s="196">
+      <c r="F13" s="195">
         <f>Statement!P156</f>
         <v>-38.858189076638233</v>
       </c>
-      <c r="G13" s="196">
+      <c r="G13" s="195">
         <f>Statement!Q156</f>
         <v>87.94037403100775</v>
       </c>
-      <c r="I13" s="196">
+      <c r="I13" s="195">
         <f ca="1">Statement!AC156</f>
-        <v>40.597991651756146</v>
+        <v>38.98433456242153</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34157,27 +34284,27 @@
       <c r="B16" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="C16" s="197">
+      <c r="C16" s="196">
         <f>Statement!M101</f>
         <v>0.81073956684882742</v>
       </c>
-      <c r="D16" s="197">
+      <c r="D16" s="196">
         <f>Statement!N101</f>
         <v>0.82991287393217905</v>
       </c>
-      <c r="E16" s="197">
+      <c r="E16" s="196">
         <f>Statement!O101</f>
         <v>0.85021925398601916</v>
       </c>
-      <c r="F16" s="197">
+      <c r="F16" s="196">
         <f>Statement!P101</f>
         <v>0.82727270183763457</v>
       </c>
-      <c r="G16" s="197">
+      <c r="G16" s="196">
         <f>Statement!Q101</f>
         <v>0.83174673345867178</v>
       </c>
-      <c r="I16" s="197">
+      <c r="I16" s="196">
         <f>Statement!AC101</f>
         <v>0.83014417010996633</v>
       </c>
@@ -34186,27 +34313,27 @@
       <c r="B17" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="C17" s="197">
+      <c r="C17" s="196">
         <f>Statement!M102</f>
         <v>-0.56144004160259653</v>
       </c>
-      <c r="D17" s="197">
+      <c r="D17" s="196">
         <f>Statement!N102</f>
         <v>-0.32900930585377974</v>
       </c>
-      <c r="E17" s="197">
+      <c r="E17" s="196">
         <f>Statement!O102</f>
         <v>-0.12592579001767487</v>
       </c>
-      <c r="F17" s="197">
+      <c r="F17" s="196">
         <f>Statement!P102</f>
         <v>-0.11371133357208407</v>
       </c>
-      <c r="G17" s="197">
+      <c r="G17" s="196">
         <f>Statement!Q102</f>
         <v>3.5242137575966802E-2</v>
       </c>
-      <c r="I17" s="197">
+      <c r="I17" s="196">
         <f>Statement!AC102</f>
         <v>6.0489855471109168E-2</v>
       </c>
@@ -34215,27 +34342,27 @@
       <c r="B18" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="C18" s="197">
+      <c r="C18" s="196">
         <f>Statement!M103</f>
         <v>-0.58905555829519018</v>
       </c>
-      <c r="D18" s="197">
+      <c r="D18" s="196">
         <f>Statement!N103</f>
         <v>-0.31018127096556619</v>
       </c>
-      <c r="E18" s="197">
+      <c r="E18" s="196">
         <f>Statement!O103</f>
         <v>-6.8714107480322181E-2</v>
       </c>
-      <c r="F18" s="197">
+      <c r="F18" s="196">
         <f>Statement!P103</f>
         <v>-5.1546377330617545E-2</v>
       </c>
-      <c r="G18" s="197">
+      <c r="G18" s="196">
         <f>Statement!Q103</f>
         <v>0.17529796867199976</v>
       </c>
-      <c r="I18" s="197">
+      <c r="I18" s="196">
         <f>Statement!AC103</f>
         <v>0.19578073705548546</v>
       </c>
@@ -34255,27 +34382,27 @@
       <c r="B21" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="C21" s="199">
+      <c r="C21" s="198">
         <f>Statement!M18</f>
         <v>-525586</v>
       </c>
-      <c r="D21" s="199">
+      <c r="D21" s="198">
         <f>Statement!N18</f>
         <v>-328352</v>
       </c>
-      <c r="E21" s="199">
+      <c r="E21" s="198">
         <f>Statement!O18</f>
         <v>-89883</v>
       </c>
-      <c r="F21" s="199">
+      <c r="F21" s="198">
         <f>Statement!P18</f>
         <v>-73694</v>
       </c>
-      <c r="G21" s="199">
+      <c r="G21" s="198">
         <f>Statement!Q18</f>
         <v>282330</v>
       </c>
-      <c r="I21" s="199">
+      <c r="I21" s="198">
         <f>Statement!AC18</f>
         <v>327410</v>
       </c>
@@ -34284,27 +34411,27 @@
       <c r="B22" s="20" t="s">
         <v>296</v>
       </c>
-      <c r="C22" s="199">
+      <c r="C22" s="198">
         <f>Statement!M59</f>
         <v>-54963</v>
       </c>
-      <c r="D22" s="199">
+      <c r="D22" s="198">
         <f>Statement!N59</f>
         <v>-9981</v>
       </c>
-      <c r="E22" s="199">
+      <c r="E22" s="198">
         <f>Statement!O59</f>
         <v>299082</v>
       </c>
-      <c r="F22" s="199">
+      <c r="F22" s="198">
         <f>Statement!P59</f>
         <v>320565</v>
       </c>
-      <c r="G22" s="199">
+      <c r="G22" s="198">
         <f>Statement!Q59</f>
         <v>371208</v>
       </c>
-      <c r="I22" s="199">
+      <c r="I22" s="198">
         <f>Statement!AC59</f>
         <v>384134</v>
       </c>
@@ -34313,27 +34440,27 @@
       <c r="B23" s="20" t="s">
         <v>303</v>
       </c>
-      <c r="C23" s="217" t="str">
+      <c r="C23" s="216" t="str">
         <f>IF(OR(C21&lt;=0, C22&lt;=0),"N/A",C21-C22)</f>
         <v>N/A</v>
       </c>
-      <c r="D23" s="217" t="str">
+      <c r="D23" s="216" t="str">
         <f t="shared" ref="D23:I23" si="0">IF(OR(D21&lt;=0, D22&lt;=0),"N/A",D21-D22)</f>
         <v>N/A</v>
       </c>
-      <c r="E23" s="217" t="str">
+      <c r="E23" s="216" t="str">
         <f t="shared" si="0"/>
         <v>N/A</v>
       </c>
-      <c r="F23" s="217" t="str">
+      <c r="F23" s="216" t="str">
         <f t="shared" si="0"/>
         <v>N/A</v>
       </c>
-      <c r="G23" s="217">
+      <c r="G23" s="216">
         <f t="shared" si="0"/>
         <v>-88878</v>
       </c>
-      <c r="I23" s="217">
+      <c r="I23" s="216">
         <f t="shared" si="0"/>
         <v>-56724</v>
       </c>
@@ -34353,27 +34480,27 @@
       <c r="B26" s="20" t="s">
         <v>119</v>
       </c>
-      <c r="C26" s="197">
+      <c r="C26" s="196">
         <f>Statement!M121</f>
         <v>-0.58905555829519018</v>
       </c>
-      <c r="D26" s="197">
+      <c r="D26" s="196">
         <f>Statement!N121</f>
         <v>-0.31018127096556619</v>
       </c>
-      <c r="E26" s="197">
+      <c r="E26" s="196">
         <f>Statement!O121</f>
         <v>-6.8714107480322181E-2</v>
       </c>
-      <c r="F26" s="197">
+      <c r="F26" s="196">
         <f>Statement!P121</f>
         <v>-5.1546377330617545E-2</v>
       </c>
-      <c r="G26" s="197">
+      <c r="G26" s="196">
         <f>Statement!Q121</f>
         <v>0.17529796867199976</v>
       </c>
-      <c r="I26" s="197">
+      <c r="I26" s="196">
         <f>Statement!AC121</f>
         <v>0.19578073705548546</v>
       </c>
@@ -34382,27 +34509,27 @@
       <c r="B27" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="C27" s="236">
+      <c r="C27" s="235">
         <f>Statement!M122</f>
         <v>0.346849112713561</v>
       </c>
-      <c r="D27" s="236">
+      <c r="D27" s="235">
         <f>Statement!N122</f>
         <v>0.38702057541552631</v>
       </c>
-      <c r="E27" s="236">
+      <c r="E27" s="235">
         <f>Statement!O122</f>
         <v>0.44270021436611728</v>
       </c>
-      <c r="F27" s="236">
+      <c r="F27" s="235">
         <f>Statement!P122</f>
         <v>0.49896309946357587</v>
       </c>
-      <c r="G27" s="236">
+      <c r="G27" s="235">
         <f>Statement!Q122</f>
         <v>0.50659662808253647</v>
       </c>
-      <c r="I27" s="236">
+      <c r="I27" s="235">
         <f>Statement!AC122</f>
         <v>0.57573243364202842</v>
       </c>
@@ -34411,27 +34538,27 @@
       <c r="B28" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="C28" s="198">
+      <c r="C28" s="197">
         <f>Statement!M123</f>
         <v>-0.20431339773367801</v>
       </c>
-      <c r="D28" s="198">
+      <c r="D28" s="197">
         <f>Statement!N123</f>
         <v>-0.12004653397221271</v>
       </c>
-      <c r="E28" s="198">
+      <c r="E28" s="197">
         <f>Statement!O123</f>
         <v>-3.0419750111515053E-2</v>
       </c>
-      <c r="F28" s="198">
+      <c r="F28" s="197">
         <f>Statement!P123</f>
         <v>-2.5719740199003933E-2</v>
       </c>
-      <c r="G28" s="198">
+      <c r="G28" s="197">
         <f>Statement!Q123</f>
         <v>8.8805359838953199E-2</v>
       </c>
-      <c r="I28" s="198">
+      <c r="I28" s="197">
         <f>Statement!AC123</f>
         <v>0.1127173202051847</v>
       </c>
@@ -34440,27 +34567,27 @@
       <c r="B29" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="C29" s="236">
+      <c r="C29" s="235">
         <f>Statement!M124</f>
         <v>1.3384813183920012</v>
       </c>
-      <c r="D29" s="236">
+      <c r="D29" s="235">
         <f>Statement!N124</f>
         <v>1.4244692363857558</v>
       </c>
-      <c r="E29" s="236">
+      <c r="E29" s="235">
         <f>Statement!O124</f>
         <v>1.4655708952965953</v>
       </c>
-      <c r="F29" s="236">
+      <c r="F29" s="235">
         <f>Statement!P124</f>
         <v>1.5523507364438103</v>
       </c>
-      <c r="G29" s="236">
+      <c r="G29" s="235">
         <f>Statement!Q124</f>
         <v>1.526562875884657</v>
       </c>
-      <c r="I29" s="236">
+      <c r="I29" s="235">
         <f>Statement!AC124</f>
         <v>1.5264074746513994</v>
       </c>
@@ -34469,27 +34596,27 @@
       <c r="B30" s="32" t="s">
         <v>123</v>
       </c>
-      <c r="C30" s="198">
+      <c r="C30" s="197">
         <f>Statement!M125</f>
         <v>-0.27346966596372269</v>
       </c>
-      <c r="D30" s="198">
+      <c r="D30" s="197">
         <f>Statement!N125</f>
         <v>-0.17100259457815453</v>
       </c>
-      <c r="E30" s="198">
+      <c r="E30" s="197">
         <f>Statement!O125</f>
         <v>-4.4582300405631825E-2</v>
       </c>
-      <c r="F30" s="198">
+      <c r="F30" s="197">
         <f>Statement!P125</f>
         <v>-3.9926057639067224E-2</v>
       </c>
-      <c r="G30" s="198">
+      <c r="G30" s="197">
         <f>Statement!Q125</f>
         <v>0.13556696550972422</v>
       </c>
-      <c r="I30" s="198">
+      <c r="I30" s="197">
         <f>Statement!AC125</f>
         <v>0.17205256008386913</v>
       </c>
@@ -34509,27 +34636,27 @@
       <c r="B33" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="C33" s="197">
+      <c r="C33" s="196">
         <f>C28</f>
         <v>-0.20431339773367801</v>
       </c>
-      <c r="D33" s="197">
+      <c r="D33" s="196">
         <f t="shared" ref="D33:G33" si="1">D28</f>
         <v>-0.12004653397221271</v>
       </c>
-      <c r="E33" s="197">
+      <c r="E33" s="196">
         <f t="shared" si="1"/>
         <v>-3.0419750111515053E-2</v>
       </c>
-      <c r="F33" s="197">
+      <c r="F33" s="196">
         <f t="shared" si="1"/>
         <v>-2.5719740199003933E-2</v>
       </c>
-      <c r="G33" s="197">
+      <c r="G33" s="196">
         <f t="shared" si="1"/>
         <v>8.8805359838953199E-2</v>
       </c>
-      <c r="I33" s="197">
+      <c r="I33" s="196">
         <f>I28</f>
         <v>0.1127173202051847</v>
       </c>
@@ -34538,27 +34665,27 @@
       <c r="B34" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="C34" s="197">
+      <c r="C34" s="196">
         <f>C30</f>
         <v>-0.27346966596372269</v>
       </c>
-      <c r="D34" s="197">
+      <c r="D34" s="196">
         <f t="shared" ref="D34:G34" si="2">D30</f>
         <v>-0.17100259457815453</v>
       </c>
-      <c r="E34" s="197">
+      <c r="E34" s="196">
         <f t="shared" si="2"/>
         <v>-4.4582300405631825E-2</v>
       </c>
-      <c r="F34" s="197">
+      <c r="F34" s="196">
         <f t="shared" si="2"/>
         <v>-3.9926057639067224E-2</v>
       </c>
-      <c r="G34" s="197">
+      <c r="G34" s="196">
         <f t="shared" si="2"/>
         <v>0.13556696550972422</v>
       </c>
-      <c r="I34" s="197">
+      <c r="I34" s="196">
         <f>I30</f>
         <v>0.17205256008386913</v>
       </c>
@@ -34567,27 +34694,27 @@
       <c r="B35" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="C35" s="197">
+      <c r="C35" s="196">
         <f>Statement!M140</f>
         <v>-13.446770816556612</v>
       </c>
-      <c r="D35" s="197">
+      <c r="D35" s="196">
         <f>Statement!N140</f>
         <v>-2.1723832513114152</v>
       </c>
-      <c r="E35" s="197">
+      <c r="E35" s="196">
         <f>Statement!O140</f>
         <v>-1.2085904425090432</v>
       </c>
-      <c r="F35" s="197">
+      <c r="F35" s="196">
         <f>Statement!P140</f>
         <v>-1.3311034872391121</v>
       </c>
-      <c r="G35" s="197">
+      <c r="G35" s="196">
         <f>Statement!Q140</f>
         <v>0.14438669993971168</v>
       </c>
-      <c r="I35" s="197">
+      <c r="I35" s="196">
         <f>Statement!AC140</f>
         <v>0.2076253183886507</v>
       </c>
@@ -34607,27 +34734,27 @@
       <c r="B38" s="20" t="s">
         <v>180</v>
       </c>
-      <c r="C38" s="196">
+      <c r="C38" s="195">
         <f>Statement!M141</f>
         <v>133.69421979440784</v>
       </c>
-      <c r="D38" s="196">
+      <c r="D38" s="195">
         <f>Statement!N141</f>
         <v>152.91140215061483</v>
       </c>
-      <c r="E38" s="196">
+      <c r="E38" s="195">
         <f>Statement!O141</f>
         <v>145.23661159324561</v>
       </c>
-      <c r="F38" s="196">
+      <c r="F38" s="195">
         <f>Statement!P141</f>
         <v>137.8303503480538</v>
       </c>
-      <c r="G38" s="196">
+      <c r="G38" s="195">
         <f>Statement!Q141</f>
         <v>131.6037563052133</v>
       </c>
-      <c r="I38" s="196">
+      <c r="I38" s="195">
         <f>Statement!AC141</f>
         <v>65.477289171395597</v>
       </c>
@@ -34636,27 +34763,27 @@
       <c r="B39" s="20" t="s">
         <v>181</v>
       </c>
-      <c r="C39" s="196">
+      <c r="C39" s="195">
         <f>Statement!M142</f>
         <v>0</v>
       </c>
-      <c r="D39" s="196">
+      <c r="D39" s="195">
         <f>Statement!N142</f>
         <v>0</v>
       </c>
-      <c r="E39" s="196">
+      <c r="E39" s="195">
         <f>Statement!O142</f>
         <v>0</v>
       </c>
-      <c r="F39" s="196">
+      <c r="F39" s="195">
         <f>Statement!P142</f>
         <v>0</v>
       </c>
-      <c r="G39" s="196">
+      <c r="G39" s="195">
         <f>Statement!Q142</f>
         <v>0</v>
       </c>
-      <c r="I39" s="196">
+      <c r="I39" s="195">
         <f>Statement!AC142</f>
         <v>0</v>
       </c>
@@ -34665,27 +34792,27 @@
       <c r="B40" s="20" t="s">
         <v>182</v>
       </c>
-      <c r="C40" s="196">
+      <c r="C40" s="195">
         <f>Statement!M143</f>
         <v>24.889114574697395</v>
       </c>
-      <c r="D40" s="196">
+      <c r="D40" s="195">
         <f>Statement!N143</f>
         <v>18.023865460341792</v>
       </c>
-      <c r="E40" s="196">
+      <c r="E40" s="195">
         <f>Statement!O143</f>
         <v>6.4216481901145333</v>
       </c>
-      <c r="F40" s="196">
+      <c r="F40" s="195">
         <f>Statement!P143</f>
         <v>49.039734026613537</v>
       </c>
-      <c r="G40" s="196">
+      <c r="G40" s="195">
         <f>Statement!Q143</f>
         <v>13.686287751306349</v>
       </c>
-      <c r="I40" s="196">
+      <c r="I40" s="195">
         <f>Statement!AC143</f>
         <v>25.312474696801676</v>
       </c>
@@ -34694,27 +34821,27 @@
       <c r="B41" s="20" t="s">
         <v>183</v>
       </c>
-      <c r="C41" s="196">
+      <c r="C41" s="195">
         <f>Statement!M144</f>
         <v>108.80510521971044</v>
       </c>
-      <c r="D41" s="196">
+      <c r="D41" s="195">
         <f>Statement!N144</f>
         <v>134.88753669027304</v>
       </c>
-      <c r="E41" s="196">
+      <c r="E41" s="195">
         <f>Statement!O144</f>
         <v>138.81496340313109</v>
       </c>
-      <c r="F41" s="196">
+      <c r="F41" s="195">
         <f>Statement!P144</f>
         <v>88.790616321440268</v>
       </c>
-      <c r="G41" s="196">
+      <c r="G41" s="195">
         <f>Statement!Q144</f>
         <v>117.91746855390694</v>
       </c>
-      <c r="I41" s="196">
+      <c r="I41" s="195">
         <f>Statement!AC144</f>
         <v>40.164814474593925</v>
       </c>
@@ -34734,27 +34861,27 @@
       <c r="B44" s="20" t="s">
         <v>306</v>
       </c>
-      <c r="C44" s="202">
+      <c r="C44" s="201">
         <f>Statement!M145</f>
         <v>0</v>
       </c>
-      <c r="D44" s="202">
+      <c r="D44" s="201">
         <f>Statement!N145</f>
         <v>0</v>
       </c>
-      <c r="E44" s="202">
+      <c r="E44" s="201">
         <f>Statement!O145</f>
         <v>0</v>
       </c>
-      <c r="F44" s="202">
+      <c r="F44" s="201">
         <f>Statement!P145</f>
         <v>0</v>
       </c>
-      <c r="G44" s="202">
+      <c r="G44" s="201">
         <f>Statement!Q145</f>
         <v>0</v>
       </c>
-      <c r="I44" s="202">
+      <c r="I44" s="201">
         <f>Statement!AC145</f>
         <v>0</v>
       </c>
@@ -34763,27 +34890,27 @@
       <c r="B45" s="20" t="s">
         <v>307</v>
       </c>
-      <c r="C45" s="202">
+      <c r="C45" s="201">
         <f>Statement!M146</f>
         <v>-0.98061622848437269</v>
       </c>
-      <c r="D45" s="202">
+      <c r="D45" s="201">
         <f>Statement!N146</f>
         <v>-0.91650530841732814</v>
       </c>
-      <c r="E45" s="202">
+      <c r="E45" s="201">
         <f>Statement!O146</f>
         <v>-0.93239915996813671</v>
       </c>
-      <c r="F45" s="202">
+      <c r="F45" s="201">
         <f>Statement!P146</f>
         <v>-0.93383166410403939</v>
       </c>
-      <c r="G45" s="202">
+      <c r="G45" s="201">
         <f>Statement!Q146</f>
         <v>-0.81123909829457308</v>
       </c>
-      <c r="I45" s="202">
+      <c r="I45" s="201">
         <f>Statement!AC146</f>
         <v>-0.74396849127545694</v>
       </c>
@@ -34792,27 +34919,27 @@
       <c r="B46" s="20" t="s">
         <v>301</v>
       </c>
-      <c r="C46" s="202">
+      <c r="C46" s="201">
         <f>Statement!M147</f>
         <v>4.192374990758311</v>
       </c>
-      <c r="D46" s="202">
+      <c r="D46" s="201">
         <f>Statement!N147</f>
         <v>3.5171282077477604</v>
       </c>
-      <c r="E46" s="202">
+      <c r="E46" s="201">
         <f>Statement!O147</f>
         <v>3.3726940484002186</v>
       </c>
-      <c r="F46" s="202">
+      <c r="F46" s="201">
         <f>Statement!P147</f>
         <v>2.833196064687328</v>
       </c>
-      <c r="G46" s="202">
+      <c r="G46" s="201">
         <f>Statement!Q147</f>
         <v>2.5073153653043936</v>
       </c>
-      <c r="I46" s="202">
+      <c r="I46" s="201">
         <f>Statement!AC147</f>
         <v>2.063021693804965</v>
       </c>
@@ -34821,27 +34948,27 @@
       <c r="B47" s="20" t="s">
         <v>302</v>
       </c>
-      <c r="C47" s="202">
+      <c r="C47" s="201">
         <f>Statement!M148</f>
         <v>4.3171501096680389</v>
       </c>
-      <c r="D47" s="202">
+      <c r="D47" s="201">
         <f>Statement!N148</f>
         <v>3.7423569563190795</v>
       </c>
-      <c r="E47" s="202">
+      <c r="E47" s="201">
         <f>Statement!O148</f>
         <v>3.6257476910625539</v>
       </c>
-      <c r="F47" s="202">
+      <c r="F47" s="201">
         <f>Statement!P148</f>
         <v>2.9271504030441093</v>
       </c>
-      <c r="G47" s="202">
+      <c r="G47" s="201">
         <f>Statement!Q148</f>
         <v>2.4783388537733191</v>
       </c>
-      <c r="I47" s="202">
+      <c r="I47" s="201">
         <f>Statement!AC148</f>
         <v>2.3066495444084523</v>
       </c>
@@ -34850,27 +34977,27 @@
       <c r="B48" s="20" t="s">
         <v>308</v>
       </c>
-      <c r="C48" s="204" t="str">
+      <c r="C48" s="203" t="str">
         <f>Statement!M149</f>
         <v>N/A</v>
       </c>
-      <c r="D48" s="204" t="str">
+      <c r="D48" s="203" t="str">
         <f>Statement!N149</f>
         <v>N/A</v>
       </c>
-      <c r="E48" s="204" t="str">
+      <c r="E48" s="203" t="str">
         <f>Statement!O149</f>
         <v>N/A</v>
       </c>
-      <c r="F48" s="204" t="str">
+      <c r="F48" s="203" t="str">
         <f>Statement!P149</f>
         <v>N/A</v>
       </c>
-      <c r="G48" s="204" t="str">
+      <c r="G48" s="203" t="str">
         <f>Statement!Q149</f>
         <v>N/A</v>
       </c>
-      <c r="I48" s="204" t="str">
+      <c r="I48" s="203" t="str">
         <f>Statement!AC149</f>
         <v>N/A</v>
       </c>
@@ -34890,85 +35017,85 @@
       <c r="B51" s="20" t="s">
         <v>315</v>
       </c>
-      <c r="C51" s="197">
+      <c r="C51" s="196">
         <f>Statement!M162</f>
         <v>-3.4699371821717021E-2</v>
       </c>
-      <c r="D51" s="197">
+      <c r="D51" s="196">
         <f>Statement!N162</f>
         <v>-4.1180507892930679E-2</v>
       </c>
-      <c r="E51" s="197">
+      <c r="E51" s="196">
         <f>Statement!O162</f>
         <v>-6.7085953878406705E-3</v>
       </c>
-      <c r="F51" s="197">
+      <c r="F51" s="196">
         <f>Statement!P162</f>
         <v>-8.9163237311385458E-3</v>
       </c>
-      <c r="G51" s="197">
+      <c r="G51" s="196">
         <f>Statement!Q162</f>
         <v>4.1302621127879274E-2</v>
       </c>
-      <c r="I51" s="197">
+      <c r="I51" s="196">
         <f ca="1">Statement!AC162</f>
-        <v>5.6751004965712941E-2</v>
+        <v>5.8479532163742701E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
         <v>318</v>
       </c>
-      <c r="C52" s="197">
+      <c r="C52" s="196">
         <f>Statement!M161</f>
         <v>-3.2136350340421331E-2</v>
       </c>
-      <c r="D52" s="197">
+      <c r="D52" s="196">
         <f>Statement!N161</f>
         <v>-4.9698749076467263E-2</v>
       </c>
-      <c r="E52" s="197">
+      <c r="E52" s="196">
         <f>Statement!O161</f>
         <v>-5.9107830031523813E-3</v>
       </c>
-      <c r="F52" s="197">
+      <c r="F52" s="196">
         <f>Statement!P161</f>
         <v>-6.5303464037043202E-3</v>
       </c>
-      <c r="G52" s="197">
+      <c r="G52" s="196">
         <f>Statement!Q161</f>
         <v>9.2028530287292954E-3</v>
       </c>
-      <c r="I52" s="197">
+      <c r="I52" s="196">
         <f ca="1">Statement!AC161</f>
-        <v>1.9485212462008288E-2</v>
+        <v>2.0078694810388171E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B53" s="20" t="s">
         <v>316</v>
       </c>
-      <c r="C53" s="197">
+      <c r="C53" s="196">
         <f>Statement!M163</f>
         <v>0</v>
       </c>
-      <c r="D53" s="197">
+      <c r="D53" s="196">
         <f>Statement!N163</f>
         <v>0</v>
       </c>
-      <c r="E53" s="197">
+      <c r="E53" s="196">
         <f>Statement!O163</f>
         <v>0</v>
       </c>
-      <c r="F53" s="197">
+      <c r="F53" s="196">
         <f>Statement!P163</f>
         <v>0</v>
       </c>
-      <c r="G53" s="197">
+      <c r="G53" s="196">
         <f>Statement!Q163</f>
         <v>0</v>
       </c>
-      <c r="I53" s="197">
+      <c r="I53" s="196">
         <f ca="1">Statement!AC163</f>
         <v>0</v>
       </c>
@@ -34977,58 +35104,58 @@
       <c r="B54" s="20" t="s">
         <v>341</v>
       </c>
-      <c r="C54" s="197">
+      <c r="C54" s="196">
         <f>Statement!M164</f>
         <v>0</v>
       </c>
-      <c r="D54" s="197">
+      <c r="D54" s="196">
         <f>Statement!N164</f>
         <v>0</v>
       </c>
-      <c r="E54" s="197">
+      <c r="E54" s="196">
         <f>Statement!O164</f>
         <v>7.5613663014209515E-3</v>
       </c>
-      <c r="F54" s="197">
+      <c r="F54" s="196">
         <f>Statement!P164</f>
         <v>4.8596228981581578E-2</v>
       </c>
-      <c r="G54" s="197">
+      <c r="G54" s="196">
         <f>Statement!Q164</f>
         <v>4.9259451802222368E-2</v>
       </c>
-      <c r="I54" s="197">
+      <c r="I54" s="196">
         <f ca="1">Statement!AC164</f>
-        <v>6.2537954989161926E-2</v>
+        <v>6.4442741629913702E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B55" s="20" t="s">
         <v>343</v>
       </c>
-      <c r="C55" s="197">
+      <c r="C55" s="196">
         <f>Statement!M165</f>
         <v>0</v>
       </c>
-      <c r="D55" s="197">
+      <c r="D55" s="196">
         <f>Statement!N165</f>
         <v>0</v>
       </c>
-      <c r="E55" s="197">
+      <c r="E55" s="196">
         <f>Statement!O165</f>
         <v>7.5613663014209515E-3</v>
       </c>
-      <c r="F55" s="197">
+      <c r="F55" s="196">
         <f>Statement!P165</f>
         <v>4.8596228981581578E-2</v>
       </c>
-      <c r="G55" s="197">
+      <c r="G55" s="196">
         <f>Statement!Q165</f>
         <v>4.9259451802222368E-2</v>
       </c>
-      <c r="I55" s="197">
+      <c r="I55" s="196">
         <f ca="1">Statement!AC165</f>
-        <v>6.2537954989161926E-2</v>
+        <v>6.4442741629913702E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35046,27 +35173,27 @@
       <c r="B58" s="20" t="s">
         <v>319</v>
       </c>
-      <c r="C58" s="197">
+      <c r="C58" s="196">
         <f>Statement!M168</f>
         <v>0</v>
       </c>
-      <c r="D58" s="197">
+      <c r="D58" s="196">
         <f>Statement!N168</f>
         <v>0</v>
       </c>
-      <c r="E58" s="197">
+      <c r="E58" s="196">
         <f>Statement!O168</f>
         <v>0</v>
       </c>
-      <c r="F58" s="197">
+      <c r="F58" s="196">
         <f>Statement!P168</f>
         <v>0</v>
       </c>
-      <c r="G58" s="197">
+      <c r="G58" s="196">
         <f>Statement!Q168</f>
         <v>0</v>
       </c>
-      <c r="I58" s="197">
+      <c r="I58" s="196">
         <f>Statement!AC168</f>
         <v>0</v>
       </c>
@@ -35075,27 +35202,27 @@
       <c r="B59" s="20" t="s">
         <v>321</v>
       </c>
-      <c r="C59" s="197">
+      <c r="C59" s="196">
         <f>Statement!M169</f>
         <v>0</v>
       </c>
-      <c r="D59" s="197">
+      <c r="D59" s="196">
         <f>Statement!N169</f>
         <v>0</v>
       </c>
-      <c r="E59" s="197">
+      <c r="E59" s="196">
         <f>Statement!O169</f>
         <v>-1.2792495169232687</v>
       </c>
-      <c r="F59" s="197">
+      <c r="F59" s="196">
         <f>Statement!P169</f>
         <v>-7.44160048753547</v>
       </c>
-      <c r="G59" s="197">
+      <c r="G59" s="196">
         <f>Statement!Q169</f>
         <v>5.3526283260685705</v>
       </c>
-      <c r="I59" s="197">
+      <c r="I59" s="196">
         <f>Statement!AC169</f>
         <v>3.2095084983598028</v>
       </c>
@@ -35104,27 +35231,27 @@
       <c r="B60" s="20" t="s">
         <v>322</v>
       </c>
-      <c r="C60" s="197">
+      <c r="C60" s="196">
         <f>Statement!M170</f>
         <v>0</v>
       </c>
-      <c r="D60" s="197">
+      <c r="D60" s="196">
         <f>Statement!N170</f>
         <v>0</v>
       </c>
-      <c r="E60" s="197">
+      <c r="E60" s="196">
         <f>Statement!O170</f>
         <v>-1.2792495169232687</v>
       </c>
-      <c r="F60" s="197">
+      <c r="F60" s="196">
         <f>Statement!P170</f>
         <v>-7.44160048753547</v>
       </c>
-      <c r="G60" s="197">
+      <c r="G60" s="196">
         <f>Statement!Q170</f>
         <v>5.3526283260685705</v>
       </c>
-      <c r="I60" s="197">
+      <c r="I60" s="196">
         <f>Statement!AC170</f>
         <v>3.2095084983598028</v>
       </c>
@@ -35144,27 +35271,27 @@
       <c r="B63" s="20" t="s">
         <v>326</v>
       </c>
-      <c r="C63" s="197">
+      <c r="C63" s="196">
         <f>Statement!M171</f>
         <v>0.32041292188722126</v>
       </c>
-      <c r="D63" s="197">
+      <c r="D63" s="196">
         <f>Statement!N171</f>
         <v>0.31207180184527727</v>
       </c>
-      <c r="E63" s="197">
+      <c r="E63" s="196">
         <f>Statement!O171</f>
         <v>0.22510733498180183</v>
       </c>
-      <c r="F63" s="197">
+      <c r="F63" s="196">
         <f>Statement!P171</f>
         <v>0.22494029842627195</v>
       </c>
-      <c r="G63" s="197">
+      <c r="G63" s="196">
         <f>Statement!Q171</f>
         <v>0.22012147206199109</v>
       </c>
-      <c r="I63" s="197">
+      <c r="I63" s="196">
         <f>Statement!AC171</f>
         <v>0.2236199519483876</v>
       </c>
@@ -35184,27 +35311,27 @@
       <c r="B66" s="20" t="s">
         <v>327</v>
       </c>
-      <c r="C66" s="196">
+      <c r="C66" s="195">
         <f>Statement!M172</f>
         <v>3.4766735290211184</v>
       </c>
-      <c r="D66" s="196">
+      <c r="D66" s="195">
         <f>Statement!N172</f>
         <v>3.157090755135687</v>
       </c>
-      <c r="E66" s="196">
+      <c r="E66" s="195">
         <f>Statement!O172</f>
         <v>3.3036556282545391</v>
       </c>
-      <c r="F66" s="196">
+      <c r="F66" s="195">
         <f>Statement!P172</f>
         <v>3.125390530795495</v>
       </c>
-      <c r="G66" s="196">
+      <c r="G66" s="195">
         <f>Statement!Q172</f>
         <v>3.224670847950649</v>
       </c>
-      <c r="I66" s="196">
+      <c r="I66" s="195">
         <f>Statement!AC172</f>
         <v>2.732462108272006</v>
       </c>
@@ -35213,27 +35340,27 @@
       <c r="B67" s="20" t="s">
         <v>335</v>
       </c>
-      <c r="C67" s="196">
+      <c r="C67" s="195">
         <f>Statement!M175</f>
         <v>3.4766735290211184</v>
       </c>
-      <c r="D67" s="196">
+      <c r="D67" s="195">
         <f>Statement!N175</f>
         <v>3.157090755135687</v>
       </c>
-      <c r="E67" s="196">
+      <c r="E67" s="195">
         <f>Statement!O175</f>
         <v>3.3036556282545391</v>
       </c>
-      <c r="F67" s="196">
+      <c r="F67" s="195">
         <f>Statement!P175</f>
         <v>3.125390530795495</v>
       </c>
-      <c r="G67" s="196">
+      <c r="G67" s="195">
         <f>Statement!Q175</f>
         <v>3.224670847950649</v>
       </c>
-      <c r="I67" s="196">
+      <c r="I67" s="195">
         <f>Statement!AC175</f>
         <v>2.732462108272006</v>
       </c>
@@ -35242,29 +35369,29 @@
       <c r="B68" s="20" t="s">
         <v>340</v>
       </c>
-      <c r="C68" s="218">
+      <c r="C68" s="217">
         <f>Statement!M176</f>
         <v>0.10399860990191799</v>
       </c>
-      <c r="D68" s="218">
+      <c r="D68" s="217">
         <f>Statement!N176</f>
         <v>0.21668433460093939</v>
       </c>
-      <c r="E68" s="218">
+      <c r="E68" s="217">
         <f>Statement!O176</f>
         <v>0.1385180556920142</v>
       </c>
-      <c r="F68" s="218">
+      <c r="F68" s="217">
         <f>Statement!P176</f>
         <v>0.21436149045236591</v>
       </c>
-      <c r="G68" s="218">
+      <c r="G68" s="217">
         <f>Statement!Q176</f>
         <v>0.25287878673419845</v>
       </c>
-      <c r="I68" s="218">
+      <c r="I68" s="217">
         <f ca="1">Statement!AC176</f>
-        <v>0.2563550595418449</v>
+        <v>0.26416314493237375</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35282,27 +35409,27 @@
       <c r="B71" s="20" t="s">
         <v>329</v>
       </c>
-      <c r="C71" s="197">
+      <c r="C71" s="196">
         <f>Statement!M173</f>
         <v>-9.3805469133780903</v>
       </c>
-      <c r="D71" s="197">
+      <c r="D71" s="196">
         <f>Statement!N173</f>
         <v>-37.054403366396151</v>
       </c>
-      <c r="E71" s="197">
+      <c r="E71" s="196">
         <f>Statement!O173</f>
         <v>1.243655586093446</v>
       </c>
-      <c r="F71" s="197">
+      <c r="F71" s="196">
         <f>Statement!P173</f>
         <v>1.1172492318250589</v>
       </c>
-      <c r="G71" s="197">
+      <c r="G71" s="196">
         <f>Statement!Q173</f>
         <v>0.78305424452059225</v>
       </c>
-      <c r="I71" s="197">
+      <c r="I71" s="196">
         <f>Statement!AC173</f>
         <v>0.69669698594761198</v>
       </c>
@@ -35311,27 +35438,27 @@
       <c r="B72" s="20" t="s">
         <v>330</v>
       </c>
-      <c r="C72" s="197">
+      <c r="C72" s="196">
         <f>Statement!M174</f>
         <v>0.57784459995606618</v>
       </c>
-      <c r="D72" s="197">
+      <c r="D72" s="196">
         <f>Statement!N174</f>
         <v>0.3493733592422309</v>
       </c>
-      <c r="E72" s="197">
+      <c r="E72" s="196">
         <f>Statement!O174</f>
         <v>0.28435361356255617</v>
       </c>
-      <c r="F72" s="197">
+      <c r="F72" s="196">
         <f>Statement!P174</f>
         <v>0.25051410681111086</v>
       </c>
-      <c r="G72" s="197">
+      <c r="G72" s="196">
         <f>Statement!Q174</f>
         <v>0.18047997854178516</v>
       </c>
-      <c r="I72" s="197">
+      <c r="I72" s="196">
         <f>Statement!AC174</f>
         <v>0.16003121393504871</v>
       </c>
@@ -35351,27 +35478,27 @@
       <c r="B75" s="20" t="s">
         <v>353</v>
       </c>
-      <c r="C75" s="197">
+      <c r="C75" s="196">
         <f>Statement!M177</f>
         <v>1.325746537973577E-2</v>
       </c>
-      <c r="D75" s="197">
+      <c r="D75" s="196">
         <f>Statement!N177</f>
         <v>2.2497097529617479E-2</v>
       </c>
-      <c r="E75" s="197">
+      <c r="E75" s="196">
         <f>Statement!O177</f>
         <v>5.6128408833764501E-3</v>
       </c>
-      <c r="F75" s="197">
+      <c r="F75" s="196">
         <f>Statement!P177</f>
         <v>1.0438116928173332E-2</v>
       </c>
-      <c r="G75" s="197">
+      <c r="G75" s="196">
         <f>Statement!Q177</f>
         <v>1.1826854061786744E-2</v>
       </c>
-      <c r="I75" s="197">
+      <c r="I75" s="196">
         <f>Statement!AC177</f>
         <v>5.3219161289936798E-3</v>
       </c>
@@ -35380,27 +35507,27 @@
       <c r="B76" s="20" t="s">
         <v>350</v>
       </c>
-      <c r="C76" s="197">
+      <c r="C76" s="196">
         <f>Statement!M178</f>
         <v>-0.21521750996124667</v>
       </c>
-      <c r="D76" s="197">
+      <c r="D76" s="196">
         <f>Statement!N178</f>
         <v>-2.3860334635808034</v>
       </c>
-      <c r="E76" s="197">
+      <c r="E76" s="196">
         <f>Statement!O178</f>
         <v>2.4548451595214689E-2</v>
       </c>
-      <c r="F76" s="197">
+      <c r="F76" s="196">
         <f>Statement!P178</f>
         <v>4.6552181304883568E-2</v>
       </c>
-      <c r="G76" s="197">
+      <c r="G76" s="196">
         <f>Statement!Q178</f>
         <v>5.1313549276955236E-2</v>
       </c>
-      <c r="I76" s="197">
+      <c r="I76" s="196">
         <f>Statement!AC178</f>
         <v>2.3168998318295178E-2</v>
       </c>
@@ -35409,27 +35536,27 @@
       <c r="B77" s="20" t="s">
         <v>351</v>
       </c>
-      <c r="C77" s="197">
+      <c r="C77" s="196">
         <f>Statement!M179</f>
         <v>0.80442026521591292</v>
       </c>
-      <c r="D77" s="197">
+      <c r="D77" s="196">
         <f>Statement!N179</f>
         <v>1.2719649628798804</v>
       </c>
-      <c r="E77" s="197">
+      <c r="E77" s="196">
         <f>Statement!O179</f>
         <v>0.32491038633446917</v>
       </c>
-      <c r="F77" s="197">
+      <c r="F77" s="196">
         <f>Statement!P179</f>
         <v>0.86600510677808729</v>
       </c>
-      <c r="G77" s="197">
+      <c r="G77" s="196">
         <f>Statement!Q179</f>
         <v>1.1225175319700631</v>
       </c>
-      <c r="I77" s="197">
+      <c r="I77" s="196">
         <f>Statement!AC179</f>
         <v>0.41931684334511188</v>
       </c>
@@ -35449,157 +35576,157 @@
       <c r="B80" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="C80" s="197">
+      <c r="C80" s="196">
         <f>Statement!M89</f>
         <v>1</v>
       </c>
-      <c r="D80" s="197">
+      <c r="D80" s="196">
         <f>Statement!N89</f>
         <v>0.18641482451146088</v>
       </c>
-      <c r="E80" s="197">
+      <c r="E80" s="196">
         <f>Statement!O89</f>
         <v>0.23568437370404344</v>
       </c>
-      <c r="F80" s="197">
+      <c r="F80" s="196">
         <f>Statement!P89</f>
         <v>9.2955127852289474E-2</v>
       </c>
-      <c r="G80" s="197">
+      <c r="G80" s="196">
         <f>Statement!Q89</f>
         <v>0.12653882310808692</v>
       </c>
-      <c r="I80" s="219"/>
+      <c r="I80" s="218"/>
     </row>
     <row r="81" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B81" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="C81" s="197">
+      <c r="C81" s="196">
         <f>Statement!M90</f>
         <v>1</v>
       </c>
-      <c r="D81" s="197">
+      <c r="D81" s="196">
         <f>Statement!N90</f>
         <v>6.6223322358291689E-2</v>
       </c>
-      <c r="E81" s="197">
+      <c r="E81" s="196">
         <f>Statement!O90</f>
         <v>8.8158355132712404E-2</v>
       </c>
-      <c r="F81" s="197">
+      <c r="F81" s="196">
         <f>Statement!P90</f>
         <v>0.26039688858945303</v>
       </c>
-      <c r="G81" s="197">
+      <c r="G81" s="196">
         <f>Statement!Q90</f>
         <v>9.7358893991301598E-2</v>
       </c>
-      <c r="I81" s="219"/>
+      <c r="I81" s="218"/>
     </row>
     <row r="82" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B82" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="C82" s="197">
+      <c r="C82" s="196">
         <f>Statement!M91</f>
         <v>1</v>
       </c>
-      <c r="D82" s="197">
+      <c r="D82" s="196">
         <f>Statement!N91</f>
         <v>0.21447253464273469</v>
       </c>
-      <c r="E82" s="197">
+      <c r="E82" s="196">
         <f>Statement!O91</f>
         <v>0.26591920594629664</v>
       </c>
-      <c r="F82" s="197">
+      <c r="F82" s="196">
         <f>Statement!P91</f>
         <v>6.3457381571517466E-2</v>
       </c>
-      <c r="G82" s="197">
+      <c r="G82" s="196">
         <f>Statement!Q91</f>
         <v>0.13263133686529885</v>
       </c>
-      <c r="I82" s="219"/>
+      <c r="I82" s="218"/>
     </row>
     <row r="83" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B83" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="C83" s="197">
+      <c r="C83" s="196">
         <f>Statement!M95</f>
         <v>1</v>
       </c>
-      <c r="D83" s="197">
+      <c r="D83" s="196">
         <f>Statement!N95</f>
         <v>2.0280479935964979E-3</v>
       </c>
-      <c r="E83" s="197">
+      <c r="E83" s="196">
         <f>Statement!O95</f>
         <v>4.080083924770931E-2</v>
       </c>
-      <c r="F83" s="197">
+      <c r="F83" s="196">
         <f>Statement!P95</f>
         <v>5.3586588433573397E-2</v>
       </c>
-      <c r="G83" s="197">
+      <c r="G83" s="196">
         <f>Statement!Q95</f>
         <v>-4.6430846560335276E-2</v>
       </c>
-      <c r="I83" s="219"/>
+      <c r="I83" s="218"/>
     </row>
     <row r="84" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B84" s="20" t="s">
         <v>357</v>
       </c>
-      <c r="C84" s="197">
+      <c r="C84" s="196">
         <f>Statement!M96</f>
         <v>-1</v>
       </c>
-      <c r="D84" s="197">
+      <c r="D84" s="196">
         <f>Statement!N96</f>
         <v>0.3047494141085067</v>
       </c>
-      <c r="E84" s="197">
+      <c r="E84" s="196">
         <f>Statement!O96</f>
         <v>0.52705127726590162</v>
       </c>
-      <c r="F84" s="197">
+      <c r="F84" s="196">
         <f>Statement!P96</f>
         <v>1.3058523555123847E-2</v>
       </c>
-      <c r="G84" s="197">
+      <c r="G84" s="196">
         <f>Statement!Q96</f>
         <v>1.3491440557547871</v>
       </c>
-      <c r="I84" s="219"/>
+      <c r="I84" s="218"/>
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B85" s="20" t="s">
         <v>358</v>
       </c>
-      <c r="C85" s="197">
+      <c r="C85" s="196">
         <f>Statement!M98</f>
         <v>-1</v>
       </c>
-      <c r="D85" s="197">
+      <c r="D85" s="196">
         <f>Statement!N98</f>
         <v>0.37526494236908897</v>
       </c>
-      <c r="E85" s="197">
+      <c r="E85" s="196">
         <f>Statement!O98</f>
         <v>0.72626023292076791</v>
       </c>
-      <c r="F85" s="197">
+      <c r="F85" s="196">
         <f>Statement!P98</f>
         <v>0.18011192327803924</v>
       </c>
-      <c r="G85" s="197">
+      <c r="G85" s="196">
         <f>Statement!Q98</f>
         <v>4.8311124379189625</v>
       </c>
-      <c r="I85" s="219"/>
+      <c r="I85" s="218"/>
     </row>
     <row r="88" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B88" s="14" t="s">
@@ -35616,79 +35743,79 @@
       <c r="B89" s="20" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="197">
-        <f>Statement!M194</f>
+      <c r="C89" s="196">
+        <f>Statement!M197</f>
         <v>1</v>
       </c>
-      <c r="D89" s="197">
-        <f>Statement!N194</f>
+      <c r="D89" s="196">
+        <f>Statement!N197</f>
         <v>3.4084087514825716E-2</v>
       </c>
-      <c r="E89" s="197">
-        <f>Statement!O194</f>
+      <c r="E89" s="196">
+        <f>Statement!O197</f>
         <v>0.24818614965570993</v>
       </c>
-      <c r="F89" s="197">
-        <f>Statement!P194</f>
+      <c r="F89" s="196">
+        <f>Statement!P197</f>
         <v>-5.5102093364575021E-2</v>
       </c>
-      <c r="G89" s="197">
-        <f>Statement!Q194</f>
+      <c r="G89" s="196">
+        <f>Statement!Q197</f>
         <v>3.2771752459329104E-2</v>
       </c>
-      <c r="I89" s="219"/>
+      <c r="I89" s="218"/>
     </row>
     <row r="90" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B90" s="20" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="197">
-        <f>Statement!M195</f>
+      <c r="C90" s="196">
+        <f>Statement!M198</f>
         <v>1</v>
       </c>
-      <c r="D90" s="197">
-        <f>Statement!N195</f>
+      <c r="D90" s="196">
+        <f>Statement!N198</f>
         <v>0.37569180272908909</v>
       </c>
-      <c r="E90" s="197">
-        <f>Statement!O195</f>
+      <c r="E90" s="196">
+        <f>Statement!O198</f>
         <v>0.27729682030883041</v>
       </c>
-      <c r="F90" s="197">
-        <f>Statement!P195</f>
+      <c r="F90" s="196">
+        <f>Statement!P198</f>
         <v>0.23392027917368038</v>
       </c>
-      <c r="G90" s="197">
-        <f>Statement!Q195</f>
+      <c r="G90" s="196">
+        <f>Statement!Q198</f>
         <v>0.19019336689332336</v>
       </c>
-      <c r="I90" s="219"/>
+      <c r="I90" s="218"/>
     </row>
     <row r="91" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B91" s="20" t="s">
         <v>362</v>
       </c>
-      <c r="C91" s="197">
-        <f>Statement!M196</f>
+      <c r="C91" s="196">
+        <f>Statement!M199</f>
         <v>1</v>
       </c>
-      <c r="D91" s="197">
-        <f>Statement!N196</f>
+      <c r="D91" s="196">
+        <f>Statement!N199</f>
         <v>0.26768885199472631</v>
       </c>
-      <c r="E91" s="197">
-        <f>Statement!O196</f>
+      <c r="E91" s="196">
+        <f>Statement!O199</f>
         <v>-0.29197642617772812</v>
       </c>
-      <c r="F91" s="197">
-        <f>Statement!P196</f>
+      <c r="F91" s="196">
+        <f>Statement!P199</f>
         <v>0.10317719384146673</v>
       </c>
-      <c r="G91" s="197">
-        <f>Statement!Q196</f>
+      <c r="G91" s="196">
+        <f>Statement!Q199</f>
         <v>0.22564418690666996</v>
       </c>
-      <c r="I91" s="219"/>
+      <c r="I91" s="218"/>
     </row>
     <row r="93" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B93" s="14" t="s">
@@ -35705,27 +35832,27 @@
       <c r="B94" s="20" t="s">
         <v>333</v>
       </c>
-      <c r="C94" s="197">
-        <f>Statement!M200</f>
-        <v>0</v>
-      </c>
-      <c r="D94" s="197">
-        <f>Statement!N200</f>
-        <v>0</v>
-      </c>
-      <c r="E94" s="197">
-        <f>Statement!O200</f>
-        <v>0</v>
-      </c>
-      <c r="F94" s="197">
-        <f>Statement!P200</f>
-        <v>0</v>
-      </c>
-      <c r="G94" s="197">
-        <f>Statement!Q200</f>
-        <v>0</v>
-      </c>
-      <c r="I94" s="219"/>
+      <c r="C94" s="196">
+        <f>Statement!M203</f>
+        <v>0</v>
+      </c>
+      <c r="D94" s="196">
+        <f>Statement!N203</f>
+        <v>0</v>
+      </c>
+      <c r="E94" s="196">
+        <f>Statement!O203</f>
+        <v>0</v>
+      </c>
+      <c r="F94" s="196">
+        <f>Statement!P203</f>
+        <v>0</v>
+      </c>
+      <c r="G94" s="196">
+        <f>Statement!Q203</f>
+        <v>0</v>
+      </c>
+      <c r="I94" s="218"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -35765,15 +35892,15 @@
         <f>Statement!Z2</f>
         <v>31.01.2026</v>
       </c>
-      <c r="D4" s="225" t="str">
+      <c r="D4" s="224" t="str">
         <f>Statement!AA2</f>
         <v>30.04.2026</v>
       </c>
-      <c r="F4" s="226" t="str">
+      <c r="F4" s="225" t="str">
         <f>Statement!W2</f>
         <v>30.04.2025</v>
       </c>
-      <c r="G4" s="225" t="str">
+      <c r="G4" s="224" t="str">
         <f>Statement!AA2</f>
         <v>30.04.2026</v>
       </c>
@@ -35786,42 +35913,42 @@
         <f>Statement!Z3</f>
         <v>Q4 2026</v>
       </c>
-      <c r="D5" s="225" t="str">
+      <c r="D5" s="224" t="str">
         <f>Statement!AA3</f>
         <v>Q1 2027</v>
       </c>
-      <c r="F5" s="226" t="str">
+      <c r="F5" s="225" t="str">
         <f>Statement!W3</f>
         <v>Q1 2026</v>
       </c>
-      <c r="G5" s="225" t="str">
+      <c r="G5" s="224" t="str">
         <f>Statement!AA3</f>
         <v>Q1 2027</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B6" s="227" t="s">
+      <c r="B6" s="226" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="221">
+      <c r="C6" s="220">
         <f>Statement!Z5</f>
         <v>481107</v>
       </c>
-      <c r="D6" s="220">
+      <c r="D6" s="219">
         <f>Statement!AA5</f>
         <v>418382</v>
       </c>
-      <c r="F6" s="221">
+      <c r="F6" s="220">
         <f>Statement!W5</f>
         <v>356624</v>
       </c>
-      <c r="G6" s="220">
+      <c r="G6" s="219">
         <f>Statement!AA5</f>
         <v>418382</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B7" s="228" t="s">
+      <c r="B7" s="227" t="s">
         <v>367</v>
       </c>
       <c r="C7" s="255">
@@ -35839,28 +35966,28 @@
       <c r="G7" s="256"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B8" s="229" t="s">
+      <c r="B8" s="228" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="222">
+      <c r="C8" s="221">
         <f>Statement!Z6</f>
         <v>73935</v>
       </c>
-      <c r="D8" s="220">
+      <c r="D8" s="219">
         <f>Statement!AA6</f>
         <v>76928</v>
       </c>
-      <c r="F8" s="222">
+      <c r="F8" s="221">
         <f>Statement!W6</f>
         <v>63857</v>
       </c>
-      <c r="G8" s="220">
+      <c r="G8" s="219">
         <f>Statement!AA6</f>
         <v>76928</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B9" s="228" t="s">
+      <c r="B9" s="227" t="s">
         <v>367</v>
       </c>
       <c r="C9" s="255">
@@ -35878,28 +36005,28 @@
       <c r="G9" s="256"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B10" s="229" t="s">
+      <c r="B10" s="228" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="222">
+      <c r="C10" s="221">
         <f>Statement!Z7</f>
         <v>407172</v>
       </c>
-      <c r="D10" s="220">
+      <c r="D10" s="219">
         <f>Statement!AA7</f>
         <v>341454</v>
       </c>
-      <c r="F10" s="222">
+      <c r="F10" s="221">
         <f>Statement!W7</f>
         <v>292767</v>
       </c>
-      <c r="G10" s="220">
+      <c r="G10" s="219">
         <f>Statement!AA7</f>
         <v>341454</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B11" s="228" t="s">
+      <c r="B11" s="227" t="s">
         <v>367</v>
       </c>
       <c r="C11" s="255">
@@ -35917,28 +36044,28 @@
       <c r="G11" s="256"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B12" s="229" t="s">
+      <c r="B12" s="228" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="222">
+      <c r="C12" s="221">
         <f>Statement!Z11</f>
         <v>326886</v>
       </c>
-      <c r="D12" s="220">
+      <c r="D12" s="219">
         <f>Statement!AA11</f>
         <v>313467</v>
       </c>
-      <c r="F12" s="222">
+      <c r="F12" s="221">
         <f>Statement!W11</f>
         <v>309179</v>
       </c>
-      <c r="G12" s="220">
+      <c r="G12" s="219">
         <f>Statement!AA11</f>
         <v>313467</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B13" s="228" t="s">
+      <c r="B13" s="227" t="s">
         <v>367</v>
       </c>
       <c r="C13" s="255">
@@ -35956,28 +36083,28 @@
       <c r="G13" s="256"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B14" s="229" t="s">
+      <c r="B14" s="228" t="s">
         <v>368</v>
       </c>
-      <c r="C14" s="222">
+      <c r="C14" s="221">
         <f>Statement!Z12</f>
         <v>80286</v>
       </c>
-      <c r="D14" s="220">
+      <c r="D14" s="219">
         <f>Statement!AA12</f>
         <v>27987</v>
       </c>
-      <c r="F14" s="222">
+      <c r="F14" s="221">
         <f>Statement!W12</f>
         <v>-16412</v>
       </c>
-      <c r="G14" s="220">
+      <c r="G14" s="219">
         <f>Statement!AA12</f>
         <v>27987</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="228" t="s">
+      <c r="B15" s="227" t="s">
         <v>367</v>
       </c>
       <c r="C15" s="255">
@@ -35995,28 +36122,28 @@
       <c r="G15" s="256"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B16" s="229" t="s">
+      <c r="B16" s="228" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="222">
+      <c r="C16" s="221">
         <f>Statement!Z18</f>
         <v>104462</v>
       </c>
-      <c r="D16" s="220">
+      <c r="D16" s="219">
         <f>Statement!AA18</f>
         <v>22525</v>
       </c>
-      <c r="F16" s="222">
+      <c r="F16" s="221">
         <f>Statement!W18</f>
         <v>-22555</v>
       </c>
-      <c r="G16" s="220">
+      <c r="G16" s="219">
         <f>Statement!AA18</f>
         <v>22525</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B17" s="228" t="s">
+      <c r="B17" s="227" t="s">
         <v>367</v>
       </c>
       <c r="C17" s="255">
@@ -36034,28 +36161,28 @@
       <c r="G17" s="256"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B18" s="229" t="s">
+      <c r="B18" s="228" t="s">
         <v>369</v>
       </c>
-      <c r="C18" s="222">
+      <c r="C18" s="221">
         <f>Statement!Z22</f>
         <v>545284</v>
       </c>
-      <c r="D18" s="220">
+      <c r="D18" s="219">
         <f>Statement!AA22</f>
         <v>527818</v>
       </c>
-      <c r="F18" s="222">
+      <c r="F18" s="221">
         <f>Statement!W22</f>
         <v>548451</v>
       </c>
-      <c r="G18" s="220">
+      <c r="G18" s="219">
         <f>Statement!AA22</f>
         <v>527818</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B19" s="228" t="s">
+      <c r="B19" s="227" t="s">
         <v>367</v>
       </c>
       <c r="C19" s="255">
@@ -36076,28 +36203,28 @@
       <c r="G19" s="256"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B20" s="229" t="s">
+      <c r="B20" s="228" t="s">
         <v>39</v>
       </c>
-      <c r="C20" s="223">
+      <c r="C20" s="222">
         <f>Statement!Z26</f>
         <v>0.19</v>
       </c>
-      <c r="D20" s="224">
+      <c r="D20" s="223">
         <f>Statement!AA26</f>
         <v>0.04</v>
       </c>
-      <c r="F20" s="223">
+      <c r="F20" s="222">
         <f>Statement!W26</f>
         <v>-0.04</v>
       </c>
-      <c r="G20" s="224">
+      <c r="G20" s="223">
         <f>Statement!AA26</f>
         <v>0.04</v>
       </c>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B21" s="228" t="s">
+      <c r="B21" s="227" t="s">
         <v>367</v>
       </c>
       <c r="C21" s="255">
@@ -36125,15 +36252,15 @@
         <f>C5</f>
         <v>Q4 2026</v>
       </c>
-      <c r="D23" s="225" t="str">
+      <c r="D23" s="224" t="str">
         <f>D5</f>
         <v>Q1 2027</v>
       </c>
-      <c r="F23" s="226" t="str">
+      <c r="F23" s="225" t="str">
         <f>F5</f>
         <v>Q1 2026</v>
       </c>
-      <c r="G23" s="225" t="str">
+      <c r="G23" s="224" t="str">
         <f>G5</f>
         <v>Q1 2027</v>
       </c>
@@ -36142,25 +36269,25 @@
       <c r="B24" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="C24" s="222">
-        <f>Statement!Z184</f>
+      <c r="C24" s="221">
+        <f>Statement!Z187</f>
         <v>215904</v>
       </c>
-      <c r="D24" s="220">
-        <f>Statement!AA184</f>
+      <c r="D24" s="219">
+        <f>Statement!AA187</f>
         <v>149309</v>
       </c>
-      <c r="F24" s="222">
-        <f>Statement!W184</f>
+      <c r="F24" s="221">
+        <f>Statement!W187</f>
         <v>128286</v>
       </c>
-      <c r="G24" s="220">
-        <f>Statement!AA184</f>
+      <c r="G24" s="219">
+        <f>Statement!AA187</f>
         <v>149309</v>
       </c>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B25" s="228" t="s">
+      <c r="B25" s="227" t="s">
         <v>367</v>
       </c>
       <c r="C25" s="255">
@@ -36184,25 +36311,25 @@
       <c r="B26" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="C26" s="222">
-        <f>Statement!Z185</f>
+      <c r="C26" s="221">
+        <f>Statement!Z188</f>
         <v>251233</v>
       </c>
-      <c r="D26" s="220">
-        <f>Statement!AA185</f>
+      <c r="D26" s="219">
+        <f>Statement!AA188</f>
         <v>252903</v>
       </c>
-      <c r="F26" s="222">
-        <f>Statement!W185</f>
+      <c r="F26" s="221">
+        <f>Statement!W188</f>
         <v>217303</v>
       </c>
-      <c r="G26" s="220">
-        <f>Statement!AA185</f>
+      <c r="G26" s="219">
+        <f>Statement!AA188</f>
         <v>252903</v>
       </c>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B27" s="228" t="s">
+      <c r="B27" s="227" t="s">
         <v>367</v>
       </c>
       <c r="C27" s="255">
@@ -36226,25 +36353,25 @@
       <c r="B28" s="20" t="s">
         <v>115</v>
       </c>
-      <c r="C28" s="222">
-        <f>Statement!Z186</f>
+      <c r="C28" s="221">
+        <f>Statement!Z189</f>
         <v>13970</v>
       </c>
-      <c r="D28" s="220">
-        <f>Statement!AA186</f>
+      <c r="D28" s="219">
+        <f>Statement!AA189</f>
         <v>16170</v>
       </c>
-      <c r="F28" s="222">
-        <f>Statement!W186</f>
+      <c r="F28" s="221">
+        <f>Statement!W189</f>
         <v>11035</v>
       </c>
-      <c r="G28" s="220">
-        <f>Statement!AA186</f>
+      <c r="G28" s="219">
+        <f>Statement!AA189</f>
         <v>16170</v>
       </c>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B29" s="228" t="s">
+      <c r="B29" s="227" t="s">
         <v>367</v>
       </c>
       <c r="C29" s="255">
@@ -36289,25 +36416,25 @@
       <c r="B32" s="20" t="s">
         <v>130</v>
       </c>
-      <c r="C32" s="222">
-        <f>Statement!Z210</f>
+      <c r="C32" s="221">
+        <f>Statement!Z213</f>
         <v>1852567</v>
       </c>
-      <c r="D32" s="222">
-        <f>Statement!AA210</f>
+      <c r="D32" s="221">
+        <f>Statement!AA213</f>
         <v>1901211</v>
       </c>
-      <c r="F32" s="222">
-        <f>Statement!W210</f>
+      <c r="F32" s="221">
+        <f>Statement!W213</f>
         <v>1692683</v>
       </c>
-      <c r="G32" s="220">
-        <f>Statement!AA210</f>
+      <c r="G32" s="219">
+        <f>Statement!AA213</f>
         <v>1901211</v>
       </c>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B33" s="228" t="s">
+      <c r="B33" s="227" t="s">
         <v>367</v>
       </c>
       <c r="C33" s="255">
@@ -36331,25 +36458,25 @@
       <c r="B34" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="C34" s="222">
-        <f>Statement!Z214</f>
+      <c r="C34" s="221">
+        <f>Statement!Z217</f>
         <v>2565</v>
       </c>
-      <c r="D34" s="222">
-        <f>Statement!AA214</f>
+      <c r="D34" s="221">
+        <f>Statement!AA217</f>
         <v>2624</v>
       </c>
-      <c r="F34" s="222">
-        <f>Statement!W214</f>
+      <c r="F34" s="221">
+        <f>Statement!W217</f>
         <v>2365</v>
       </c>
-      <c r="G34" s="220">
-        <f>Statement!AA214</f>
+      <c r="G34" s="219">
+        <f>Statement!AA217</f>
         <v>2624</v>
       </c>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B35" s="228" t="s">
+      <c r="B35" s="227" t="s">
         <v>367</v>
       </c>
       <c r="C35" s="255">
@@ -36868,43 +36995,43 @@
         <v>398</v>
       </c>
       <c r="C65" s="64">
-        <f>Statement!H184</f>
+        <f>Statement!H187</f>
         <v>0</v>
       </c>
       <c r="D65" s="64">
-        <f>Statement!I184</f>
+        <f>Statement!I187</f>
         <v>0</v>
       </c>
       <c r="E65" s="64">
-        <f>Statement!J184</f>
+        <f>Statement!J187</f>
         <v>0</v>
       </c>
       <c r="F65" s="64">
-        <f>Statement!K184</f>
+        <f>Statement!K187</f>
         <v>0</v>
       </c>
       <c r="G65" s="64">
-        <f>Statement!L184</f>
+        <f>Statement!L187</f>
         <v>0</v>
       </c>
       <c r="H65" s="64">
-        <f>Statement!M184</f>
+        <f>Statement!M187</f>
         <v>481427</v>
       </c>
       <c r="I65" s="64">
-        <f>Statement!N184</f>
+        <f>Statement!N187</f>
         <v>497836</v>
       </c>
       <c r="J65" s="64">
-        <f>Statement!O184</f>
+        <f>Statement!O187</f>
         <v>621392</v>
       </c>
       <c r="K65" s="64">
-        <f>Statement!P184</f>
+        <f>Statement!P187</f>
         <v>587152</v>
       </c>
       <c r="L65" s="64">
-        <f>Statement!Q184</f>
+        <f>Statement!Q187</f>
         <v>606394</v>
       </c>
     </row>
@@ -36913,43 +37040,43 @@
         <v>399</v>
       </c>
       <c r="C66" s="64">
-        <f>Statement!H185</f>
+        <f>Statement!H188</f>
         <v>0</v>
       </c>
       <c r="D66" s="64">
-        <f>Statement!I185</f>
+        <f>Statement!I188</f>
         <v>0</v>
       </c>
       <c r="E66" s="64">
-        <f>Statement!J185</f>
+        <f>Statement!J188</f>
         <v>0</v>
       </c>
       <c r="F66" s="64">
-        <f>Statement!K185</f>
+        <f>Statement!K188</f>
         <v>0</v>
       </c>
       <c r="G66" s="64">
-        <f>Statement!L185</f>
+        <f>Statement!L188</f>
         <v>0</v>
       </c>
       <c r="H66" s="64">
-        <f>Statement!M185</f>
+        <f>Statement!M188</f>
         <v>369867</v>
       </c>
       <c r="I66" s="64">
-        <f>Statement!N185</f>
+        <f>Statement!N188</f>
         <v>508823</v>
       </c>
       <c r="J66" s="64">
-        <f>Statement!O185</f>
+        <f>Statement!O188</f>
         <v>649918</v>
       </c>
       <c r="K66" s="64">
-        <f>Statement!P185</f>
+        <f>Statement!P188</f>
         <v>801947</v>
       </c>
       <c r="L66" s="64">
-        <f>Statement!Q185</f>
+        <f>Statement!Q188</f>
         <v>954472</v>
       </c>
     </row>
@@ -36958,43 +37085,43 @@
         <v>400</v>
       </c>
       <c r="C67" s="64">
-        <f>Statement!H186</f>
+        <f>Statement!H189</f>
         <v>0</v>
       </c>
       <c r="D67" s="64">
-        <f>Statement!I186</f>
+        <f>Statement!I189</f>
         <v>0</v>
       </c>
       <c r="E67" s="64">
-        <f>Statement!J186</f>
+        <f>Statement!J189</f>
         <v>0</v>
       </c>
       <c r="F67" s="64">
-        <f>Statement!K186</f>
+        <f>Statement!K189</f>
         <v>0</v>
       </c>
       <c r="G67" s="64">
-        <f>Statement!L186</f>
+        <f>Statement!L189</f>
         <v>0</v>
       </c>
       <c r="H67" s="64">
-        <f>Statement!M186</f>
+        <f>Statement!M189</f>
         <v>40958</v>
       </c>
       <c r="I67" s="64">
-        <f>Statement!N186</f>
+        <f>Statement!N189</f>
         <v>51922</v>
       </c>
       <c r="J67" s="64">
-        <f>Statement!O186</f>
+        <f>Statement!O189</f>
         <v>36762</v>
       </c>
       <c r="K67" s="64">
-        <f>Statement!P186</f>
+        <f>Statement!P189</f>
         <v>40555</v>
       </c>
       <c r="L67" s="64">
-        <f>Statement!Q186</f>
+        <f>Statement!Q189</f>
         <v>49706</v>
       </c>
     </row>
@@ -37002,43 +37129,43 @@
       <c r="B68" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="C68" s="241">
+      <c r="C68" s="239">
         <f>Statement!H123</f>
         <v>0</v>
       </c>
-      <c r="D68" s="241">
+      <c r="D68" s="239">
         <f>Statement!I123</f>
         <v>0</v>
       </c>
-      <c r="E68" s="241">
+      <c r="E68" s="239">
         <f>Statement!J123</f>
         <v>0</v>
       </c>
-      <c r="F68" s="241">
+      <c r="F68" s="239">
         <f>Statement!K123</f>
         <v>0</v>
       </c>
-      <c r="G68" s="241">
+      <c r="G68" s="239">
         <f>Statement!L123</f>
         <v>0</v>
       </c>
-      <c r="H68" s="241">
+      <c r="H68" s="239">
         <f>Statement!M123</f>
         <v>-0.20431339773367801</v>
       </c>
-      <c r="I68" s="241">
+      <c r="I68" s="239">
         <f>Statement!N123</f>
         <v>-0.12004653397221271</v>
       </c>
-      <c r="J68" s="241">
+      <c r="J68" s="239">
         <f>Statement!O123</f>
         <v>-3.0419750111515053E-2</v>
       </c>
-      <c r="K68" s="241">
+      <c r="K68" s="239">
         <f>Statement!P123</f>
         <v>-2.5719740199003933E-2</v>
       </c>
-      <c r="L68" s="241">
+      <c r="L68" s="239">
         <f>Statement!Q123</f>
         <v>8.8805359838953199E-2</v>
       </c>
@@ -37047,43 +37174,43 @@
       <c r="B69" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="C69" s="241">
+      <c r="C69" s="239">
         <f>Statement!H125</f>
         <v>0</v>
       </c>
-      <c r="D69" s="241">
+      <c r="D69" s="239">
         <f>Statement!I125</f>
         <v>0</v>
       </c>
-      <c r="E69" s="241">
+      <c r="E69" s="239">
         <f>Statement!J125</f>
         <v>0</v>
       </c>
-      <c r="F69" s="241">
+      <c r="F69" s="239">
         <f>Statement!K125</f>
         <v>0</v>
       </c>
-      <c r="G69" s="241">
+      <c r="G69" s="239">
         <f>Statement!L125</f>
         <v>0</v>
       </c>
-      <c r="H69" s="241">
+      <c r="H69" s="239">
         <f>Statement!M125</f>
         <v>-0.27346966596372269</v>
       </c>
-      <c r="I69" s="241">
+      <c r="I69" s="239">
         <f>Statement!N125</f>
         <v>-0.17100259457815453</v>
       </c>
-      <c r="J69" s="241">
+      <c r="J69" s="239">
         <f>Statement!O125</f>
         <v>-4.4582300405631825E-2</v>
       </c>
-      <c r="K69" s="241">
+      <c r="K69" s="239">
         <f>Statement!P125</f>
         <v>-3.9926057639067224E-2</v>
       </c>
-      <c r="L69" s="241">
+      <c r="L69" s="239">
         <f>Statement!Q125</f>
         <v>0.13556696550972422</v>
       </c>
@@ -37092,43 +37219,43 @@
       <c r="B70" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="C70" s="241">
+      <c r="C70" s="239">
         <f>Statement!H140</f>
         <v>0</v>
       </c>
-      <c r="D70" s="241">
+      <c r="D70" s="239">
         <f>Statement!I140</f>
         <v>0</v>
       </c>
-      <c r="E70" s="241">
+      <c r="E70" s="239">
         <f>Statement!J140</f>
         <v>0</v>
       </c>
-      <c r="F70" s="241">
+      <c r="F70" s="239">
         <f>Statement!K140</f>
         <v>0</v>
       </c>
-      <c r="G70" s="241">
+      <c r="G70" s="239">
         <f>Statement!L140</f>
         <v>0</v>
       </c>
-      <c r="H70" s="241">
+      <c r="H70" s="239">
         <f>Statement!M140</f>
         <v>-13.446770816556612</v>
       </c>
-      <c r="I70" s="241">
+      <c r="I70" s="239">
         <f>Statement!N140</f>
         <v>-2.1723832513114152</v>
       </c>
-      <c r="J70" s="241">
+      <c r="J70" s="239">
         <f>Statement!O140</f>
         <v>-1.2085904425090432</v>
       </c>
-      <c r="K70" s="241">
+      <c r="K70" s="239">
         <f>Statement!P140</f>
         <v>-1.3311034872391121</v>
       </c>
-      <c r="L70" s="241">
+      <c r="L70" s="239">
         <f>Statement!Q140</f>
         <v>0.14438669993971168</v>
       </c>
@@ -37446,35 +37573,35 @@
         <v>398</v>
       </c>
       <c r="C63" s="64">
-        <f>Statement!T184</f>
+        <f>Statement!T187</f>
         <v>112251</v>
       </c>
       <c r="D63" s="64">
-        <f>Statement!U184</f>
+        <f>Statement!U187</f>
         <v>137174</v>
       </c>
       <c r="E63" s="64">
-        <f>Statement!V184</f>
+        <f>Statement!V187</f>
         <v>197609</v>
       </c>
       <c r="F63" s="64">
-        <f>Statement!W184</f>
+        <f>Statement!W187</f>
         <v>128286</v>
       </c>
       <c r="G63" s="64">
-        <f>Statement!X184</f>
+        <f>Statement!X187</f>
         <v>112161</v>
       </c>
       <c r="H63" s="64">
-        <f>Statement!Y184</f>
+        <f>Statement!Y187</f>
         <v>150043</v>
       </c>
       <c r="I63" s="64">
-        <f>Statement!Z184</f>
+        <f>Statement!Z187</f>
         <v>215904</v>
       </c>
       <c r="J63" s="64">
-        <f>Statement!AA184</f>
+        <f>Statement!AA187</f>
         <v>149309</v>
       </c>
     </row>
@@ -37483,35 +37610,35 @@
         <v>399</v>
       </c>
       <c r="C64" s="64">
-        <f>Statement!T185</f>
+        <f>Statement!T188</f>
         <v>194673</v>
       </c>
       <c r="D64" s="64">
-        <f>Statement!U185</f>
+        <f>Statement!U188</f>
         <v>206922</v>
       </c>
       <c r="E64" s="64">
-        <f>Statement!V185</f>
+        <f>Statement!V188</f>
         <v>215221</v>
       </c>
       <c r="F64" s="64">
-        <f>Statement!W185</f>
+        <f>Statement!W188</f>
         <v>217303</v>
       </c>
       <c r="G64" s="64">
-        <f>Statement!X185</f>
+        <f>Statement!X188</f>
         <v>238363</v>
       </c>
       <c r="H64" s="64">
-        <f>Statement!Y185</f>
+        <f>Statement!Y188</f>
         <v>247573</v>
       </c>
       <c r="I64" s="64">
-        <f>Statement!Z185</f>
+        <f>Statement!Z188</f>
         <v>251233</v>
       </c>
       <c r="J64" s="64">
-        <f>Statement!AA185</f>
+        <f>Statement!AA188</f>
         <v>252903</v>
       </c>
     </row>
@@ -37520,35 +37647,35 @@
         <v>400</v>
       </c>
       <c r="C65" s="64">
-        <f>Statement!T186</f>
+        <f>Statement!T189</f>
         <v>9329</v>
       </c>
       <c r="D65" s="64">
-        <f>Statement!U186</f>
+        <f>Statement!U189</f>
         <v>10557</v>
       </c>
       <c r="E65" s="64">
-        <f>Statement!V186</f>
+        <f>Statement!V189</f>
         <v>10816</v>
       </c>
       <c r="F65" s="64">
-        <f>Statement!W186</f>
+        <f>Statement!W189</f>
         <v>11035</v>
       </c>
       <c r="G65" s="64">
-        <f>Statement!X186</f>
+        <f>Statement!X189</f>
         <v>11204</v>
       </c>
       <c r="H65" s="64">
-        <f>Statement!Y186</f>
+        <f>Statement!Y189</f>
         <v>13497</v>
       </c>
       <c r="I65" s="64">
-        <f>Statement!Z186</f>
+        <f>Statement!Z189</f>
         <v>13970</v>
       </c>
       <c r="J65" s="64">
-        <f>Statement!AA186</f>
+        <f>Statement!AA189</f>
         <v>16170</v>
       </c>
     </row>

--- a/PATH.xlsx
+++ b/PATH.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{429B8039-99B6-8842-810E-0C385785D173}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F22103E5-2DEB-5A49-B213-CFD9B7F02E77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -168,7 +168,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="769" uniqueCount="419">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="419">
   <si>
     <t>Ticker</t>
   </si>
@@ -2050,7 +2050,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="266">
+  <cellXfs count="267">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -2375,9 +2375,7 @@
     <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2385,6 +2383,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2396,10 +2403,10 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2409,12 +2416,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2908,6 +2909,301 @@
         </a:p>
       </c:txPr>
     </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:gradFill flip="none" rotWithShape="1">
+      <a:gsLst>
+        <a:gs pos="0">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:gs>
+        <a:gs pos="100000">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="85000"/>
+            <a:lumOff val="15000"/>
+          </a:schemeClr>
+        </a:gs>
+      </a:gsLst>
+      <a:path path="circle">
+        <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+      </a:path>
+      <a:tileRect/>
+    </a:gradFill>
+    <a:ln>
+      <a:noFill/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="95000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:effectLst>
+                  <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+                    <a:prstClr val="black">
+                      <a:alpha val="40000"/>
+                    </a:prstClr>
+                  </a:outerShdw>
+                </a:effectLst>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>FCFE</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:effectLst>
+                <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="40000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="34925" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'Graphs Quarter'!$C$66:$J$66</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0_);\(#,##0\)</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>-49347</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-64293</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>29809</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-36419</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-46368</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>114462</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>75934</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-2537-A641-96D5-AEFA40A2B2D6}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1163393471"/>
+        <c:axId val="1163381375"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1163393471"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1163381375"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1163381375"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="95000"/>
+                  <a:alpha val="10000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="#,##0_);\(#,##0\)" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1163393471"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
@@ -4710,6 +5006,368 @@
     <c:autoTitleDeleted val="1"/>
     <c:plotArea>
       <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Price 5y</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="34925" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'Graphs Year'!$H$71:$L$71</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>43.583607538139404</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>71.343104995513016</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>43.613520789709838</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>37.660783727191152</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-E1C7-E644-B67E-BC4064FDD059}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Revenue 5y</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="34925" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'Graphs Year'!$H$72:$L$72</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>118.64148245114609</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>146.60342593796372</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>160.23096613961079</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>180.50640402038886</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-E1C7-E644-B67E-BC4064FDD059}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>EPS 5y</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="34925" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'Graphs Year'!$H$73:$L$73</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>148.27586206896552</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>186.20689655172413</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>188.79310344827584</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>244.82758620689654</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-E1C7-E644-B67E-BC4064FDD059}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1656736831"/>
+        <c:axId val="1848533759"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1656736831"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1848533759"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1848533759"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="95000"/>
+                  <a:alpha val="10000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1656736831"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:gradFill flip="none" rotWithShape="1">
+      <a:gsLst>
+        <a:gs pos="0">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:gs>
+        <a:gs pos="100000">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="85000"/>
+            <a:lumOff val="15000"/>
+          </a:schemeClr>
+        </a:gs>
+      </a:gsLst>
+      <a:path path="circle">
+        <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+      </a:path>
+      <a:tileRect/>
+    </a:gradFill>
+    <a:ln>
+      <a:noFill/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
@@ -5144,7 +5802,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -5595,7 +6253,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -6145,302 +6803,47 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="lt1">
-                    <a:lumMod val="95000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:effectLst>
-                  <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
-                    <a:prstClr val="black">
-                      <a:alpha val="40000"/>
-                    </a:prstClr>
-                  </a:outerShdw>
-                </a:effectLst>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US"/>
-              <a:t>FCFE</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="lt1">
-                  <a:lumMod val="95000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:effectLst>
-                <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
-                  <a:prstClr val="black">
-                    <a:alpha val="40000"/>
-                  </a:prstClr>
-                </a:outerShdw>
-              </a:effectLst>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:spPr>
-            <a:ln w="34925" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst>
-              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-                <a:srgbClr val="000000">
-                  <a:alpha val="63000"/>
-                </a:srgbClr>
-              </a:outerShdw>
-            </a:effectLst>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:val>
-            <c:numRef>
-              <c:f>'Graphs Quarter'!$C$66:$J$66</c:f>
-              <c:numCache>
-                <c:formatCode>#,##0_);\(#,##0\)</c:formatCode>
-                <c:ptCount val="8"/>
-                <c:pt idx="0">
-                  <c:v>-49347</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>-64293</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>29809</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>-36419</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>-46368</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>114462</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>75934</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-2537-A641-96D5-AEFA40A2B2D6}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:smooth val="0"/>
-        <c:axId val="1163393471"/>
-        <c:axId val="1163381375"/>
-      </c:lineChart>
-      <c:catAx>
-        <c:axId val="1163393471"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="1"/>
-        <c:axPos val="b"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="1163381375"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="1163381375"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="lt1">
-                  <a:lumMod val="95000"/>
-                  <a:alpha val="10000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="#,##0_);\(#,##0\)" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="lt1">
-                    <a:lumMod val="85000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1163393471"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:gradFill flip="none" rotWithShape="1">
-      <a:gsLst>
-        <a:gs pos="0">
-          <a:schemeClr val="dk1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:gs>
-        <a:gs pos="100000">
-          <a:schemeClr val="dk1">
-            <a:lumMod val="85000"/>
-            <a:lumOff val="15000"/>
-          </a:schemeClr>
-        </a:gs>
-      </a:gsLst>
-      <a:path path="circle">
-        <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-      </a:path>
-      <a:tileRect/>
-    </a:gradFill>
-    <a:ln>
-      <a:noFill/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
 </file>
 
-<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/colors10.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -7291,6 +7694,502 @@
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style10.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="233">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200" cap="all"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="10000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill flip="none" rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="65000"/>
+              <a:lumOff val="35000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="85000"/>
+              <a:lumOff val="15000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+        </a:path>
+        <a:tileRect/>
+      </a:gradFill>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="34925" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="10000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="5000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="95000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200" spc="100" baseline="0">
+      <a:effectLst>
+        <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="40000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:defRPr>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
   </cs:wall>
 </cs:chartStyle>
@@ -9281,7 +10180,7 @@
 </file>
 
 <file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="209">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="233">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -9303,11 +10202,11 @@
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="lt1">
             <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
+            <a:alpha val="10000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -9384,7 +10283,7 @@
     </cs:fillRef>
     <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
   </cs:dataPoint>
   <cs:dataPoint3D>
@@ -9394,7 +10293,7 @@
     </cs:fillRef>
     <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
   </cs:dataPoint3D>
   <cs:dataPointLine>
@@ -9404,7 +10303,7 @@
     <cs:fillRef idx="3"/>
     <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="34925" cap="rnd">
@@ -9424,7 +10323,7 @@
     </cs:fillRef>
     <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525">
@@ -9443,7 +10342,7 @@
     <cs:fillRef idx="3"/>
     <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="rnd">
@@ -9480,7 +10379,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
@@ -9504,7 +10403,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525">
@@ -9523,7 +10422,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
@@ -9541,7 +10440,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
   </cs:floor>
   <cs:gridlineMajor>
@@ -9549,7 +10448,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
@@ -9568,7 +10467,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln>
@@ -9586,7 +10485,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525">
@@ -9605,7 +10504,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525">
@@ -9634,7 +10533,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
   </cs:plotArea>
   <cs:plotArea3D>
@@ -9642,7 +10541,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
   </cs:plotArea3D>
   <cs:seriesAxis>
@@ -9712,7 +10611,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="19050" cap="rnd">
@@ -9738,7 +10637,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
@@ -9770,7 +10669,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
   </cs:wall>
 </cs:chartStyle>
@@ -10769,7 +11668,7 @@
 </file>
 
 <file path=xl/charts/style9.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="233">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="209">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -10791,11 +11690,11 @@
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="lt1">
             <a:lumMod val="95000"/>
-            <a:alpha val="10000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -10872,7 +11771,7 @@
     </cs:fillRef>
     <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
   </cs:dataPoint>
   <cs:dataPoint3D>
@@ -10882,7 +11781,7 @@
     </cs:fillRef>
     <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
   </cs:dataPoint3D>
   <cs:dataPointLine>
@@ -10892,7 +11791,7 @@
     <cs:fillRef idx="3"/>
     <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="34925" cap="rnd">
@@ -10912,7 +11811,7 @@
     </cs:fillRef>
     <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525">
@@ -10931,7 +11830,7 @@
     <cs:fillRef idx="3"/>
     <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="rnd">
@@ -10968,7 +11867,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
@@ -10992,7 +11891,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525">
@@ -11011,7 +11910,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
@@ -11029,7 +11928,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
   </cs:floor>
   <cs:gridlineMajor>
@@ -11037,7 +11936,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
@@ -11056,7 +11955,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln>
@@ -11074,7 +11973,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525">
@@ -11093,7 +11992,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525">
@@ -11122,7 +12021,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
   </cs:plotArea>
   <cs:plotArea3D>
@@ -11130,7 +12029,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
   </cs:plotArea3D>
   <cs:seriesAxis>
@@ -11200,7 +12099,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="19050" cap="rnd">
@@ -11226,7 +12125,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
@@ -11258,7 +12157,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
   </cs:wall>
 </cs:chartStyle>
@@ -11441,6 +12340,42 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>709282</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>54154</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>345056</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>1757</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="Chart 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F0680505-B7C9-318D-14CF-8CEACBFA963A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -11814,11 +12749,11 @@
     <v>Powered by Refinitiv</v>
     <v>19.84</v>
     <v>9.2002000000000006</v>
-    <v>0.97860000000000003</v>
-    <v>-0.26</v>
-    <v>-2.4714999999999997E-2</v>
-    <v>0.08</v>
-    <v>7.8200000000000006E-3</v>
+    <v>0.98270000000000002</v>
+    <v>0.04</v>
+    <v>3.9100000000000003E-3</v>
+    <v>-2.98E-2</v>
+    <v>-2.9020000000000001E-3</v>
     <v>USD</v>
     <v>UiPath, Inc. is focused on agentic automation and orchestration, empowering enterprises to harness the full potential of AI agents to autonomously execute and optimize complex business processes. It is focused on building and managing automations, starting with computer vision technology and user interface automation in its initial robotic process automation offering. Its AI-powered UiPath Platform offers a robust set of capabilities that allows its customers to discover opportunities for automation, automate using a digital workforce that seamlessly collaborates with humans, and operate a mission-critical automation program at scale. It enables employees to quickly build automations for both existing and new processes and to automate a range of actions including logging into applications, moving folders, filling in forms, reading emails and others. Its platform allows users to design and combine UI automations, API integrations and AI-based document understanding in a single workflow.</v>
     <v>3981</v>
@@ -11826,25 +12761,25 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>One Vanderbilt Avenue, 60th Floor, NEW YORK, NY, 10017 US</v>
-    <v>10.8</v>
+    <v>10.36</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46190.872235647657</v>
+    <v>46191.999378865628</v>
     <v>0</v>
-    <v>10.23</v>
-    <v>5315914278</v>
+    <v>9.8800000000000008</v>
+    <v>5321095481</v>
     <v>UIPATH, INC.</v>
     <v>UIPATH, INC.</v>
-    <v>10.44</v>
-    <v>17.054500000000001</v>
-    <v>10.52</v>
-    <v>10.26</v>
-    <v>10.31</v>
+    <v>10.199999999999999</v>
+    <v>17.005500000000001</v>
+    <v>10.23</v>
+    <v>10.27</v>
+    <v>10.2402</v>
     <v>518120300</v>
     <v>PATH</v>
     <v>UIPATH, INC. (XNYS:PATH)</v>
-    <v>40413749</v>
-    <v>45663865</v>
+    <v>45204618</v>
+    <v>46059779</v>
     <v>2015</v>
   </rv>
   <rv s="2">
@@ -11868,17 +12803,17 @@
     <v>Powered by Refinitiv</v>
     <v>46.87</v>
     <v>39.47</v>
-    <v>-0.41</v>
-    <v>-9.1739999999999999E-3</v>
+    <v>-0.12</v>
+    <v>-2.6889999999999996E-3</v>
     <v>US</v>
-    <v>44.59</v>
+    <v>44.53</v>
     <v>Index</v>
     <v>3</v>
     <v>44.2</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>44.43</v>
-    <v>44.69</v>
-    <v>44.28</v>
+    <v>44.53</v>
+    <v>44.63</v>
+    <v>44.51</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -12100,9 +13035,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq Last Sale</v>
+      <v>Source: Nasdaq</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>Delayed 15 minutes</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -12705,7 +13640,7 @@
       </c>
       <c r="F3" s="208">
         <f ca="1">Statement!AC153</f>
-        <v>5359362.3</v>
+        <v>5364585.8499999996</v>
       </c>
       <c r="H3" s="206" t="str">
         <f>'AVG target price'!B5</f>
@@ -12729,7 +13664,7 @@
       </c>
       <c r="F4" s="209">
         <f ca="1">Statement!AC154</f>
-        <v>3943616.3</v>
+        <v>3948839.8499999996</v>
       </c>
       <c r="H4" s="206" t="str">
         <f>'AVG target price'!B6</f>
@@ -12746,7 +13681,7 @@
       </c>
       <c r="C5" s="229" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>10.26</v>
+        <v>10.27</v>
       </c>
       <c r="E5" s="206" t="s">
         <v>292</v>
@@ -12770,14 +13705,14 @@
       </c>
       <c r="C6" s="229" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>10.31</v>
+        <v>10.2402</v>
       </c>
       <c r="E6" s="206" t="s">
         <v>286</v>
       </c>
       <c r="F6" s="211">
         <f ca="1">Statement!AC150</f>
-        <v>17.099999999999998</v>
+        <v>17.116666666666664</v>
       </c>
       <c r="H6" s="206" t="str">
         <f>'AVG target price'!B8</f>
@@ -12794,14 +13729,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-0.26</v>
+        <v>0.04</v>
       </c>
       <c r="E7" s="207" t="s">
         <v>242</v>
       </c>
       <c r="F7" s="212">
         <f ca="1">Statement!AC151</f>
-        <v>3.305290537752716</v>
+        <v>3.3085120684912663</v>
       </c>
       <c r="H7" s="205" t="str">
         <f>'AVG target price'!B9</f>
@@ -12818,14 +13753,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>0.08</v>
+        <v>-2.98E-2</v>
       </c>
       <c r="E8" s="206" t="s">
         <v>314</v>
       </c>
       <c r="F8" s="213">
         <f ca="1">Statement!AC161</f>
-        <v>2.0078694810388171E-2</v>
+        <v>2.0059143987787988E-2</v>
       </c>
       <c r="H8" s="205" t="str">
         <f>'AVG target price'!B11</f>
@@ -12833,7 +13768,7 @@
       </c>
       <c r="I8" s="234">
         <f ca="1">'AVG target price'!C11</f>
-        <v>0.12121740537257168</v>
+        <v>0.12012566495838224</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -12842,14 +13777,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-2.4714999999999997E-2</v>
+        <v>3.9100000000000003E-3</v>
       </c>
       <c r="E9" s="206" t="s">
         <v>337</v>
       </c>
       <c r="F9" s="213">
         <f ca="1">Statement!AC162</f>
-        <v>5.8479532163742701E-2</v>
+        <v>5.8422590068159697E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -12858,14 +13793,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>7.8200000000000006E-3</v>
+        <v>-2.9020000000000001E-3</v>
       </c>
       <c r="E10" s="206" t="s">
         <v>342</v>
       </c>
       <c r="F10" s="213">
         <f ca="1">Statement!AC164</f>
-        <v>6.4442741629913702E-2</v>
+        <v>6.4379993098628491E-2</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -12906,7 +13841,7 @@
       </c>
       <c r="C13" s="230" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>0.97860000000000003</v>
+        <v>0.98270000000000002</v>
       </c>
       <c r="E13" s="206" t="s">
         <v>123</v>
@@ -12922,7 +13857,7 @@
       </c>
       <c r="C14" s="231" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>45663865</v>
+        <v>46059779</v>
       </c>
       <c r="E14" s="207" t="s">
         <v>124</v>
@@ -12938,7 +13873,7 @@
       </c>
       <c r="F15" s="213">
         <f ca="1">Statement!AC176</f>
-        <v>0.26416314493237375</v>
+        <v>0.26390592668024876</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -13048,7 +13983,7 @@
       </c>
       <c r="F26" s="240" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>44.28</v>
+        <v>44.51</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -13063,7 +13998,7 @@
       </c>
       <c r="F27" s="241">
         <f ca="1">F26/1000</f>
-        <v>4.428E-2</v>
+        <v>4.4510000000000001E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -13083,15 +14018,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="248" t="s">
+      <c r="B33" s="252" t="s">
         <v>391</v>
       </c>
-      <c r="C33" s="248"/>
-      <c r="D33" s="248"/>
-      <c r="E33" s="248"/>
-      <c r="F33" s="248"/>
-      <c r="G33" s="248"/>
-      <c r="H33" s="248"/>
+      <c r="C33" s="252"/>
+      <c r="D33" s="252"/>
+      <c r="E33" s="252"/>
+      <c r="F33" s="252"/>
+      <c r="G33" s="252"/>
+      <c r="H33" s="252"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -13110,24 +14045,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="248"/>
-      <c r="C39" s="248"/>
-      <c r="D39" s="248"/>
-      <c r="E39" s="248"/>
-      <c r="F39" s="248"/>
-      <c r="G39" s="248"/>
-      <c r="H39" s="248"/>
+      <c r="B39" s="252"/>
+      <c r="C39" s="252"/>
+      <c r="D39" s="252"/>
+      <c r="E39" s="252"/>
+      <c r="F39" s="252"/>
+      <c r="G39" s="252"/>
+      <c r="H39" s="252"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="248" t="s">
+      <c r="B42" s="252" t="s">
         <v>394</v>
       </c>
-      <c r="C42" s="248"/>
-      <c r="D42" s="248"/>
-      <c r="E42" s="248"/>
-      <c r="F42" s="248"/>
-      <c r="G42" s="248"/>
-      <c r="H42" s="248"/>
+      <c r="C42" s="252"/>
+      <c r="D42" s="252"/>
+      <c r="E42" s="252"/>
+      <c r="F42" s="252"/>
+      <c r="G42" s="252"/>
+      <c r="H42" s="252"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -13142,24 +14077,24 @@
       </c>
     </row>
     <row r="49" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="248"/>
-      <c r="C49" s="248"/>
-      <c r="D49" s="248"/>
-      <c r="E49" s="248"/>
-      <c r="F49" s="248"/>
-      <c r="G49" s="248"/>
-      <c r="H49" s="248"/>
+      <c r="B49" s="252"/>
+      <c r="C49" s="252"/>
+      <c r="D49" s="252"/>
+      <c r="E49" s="252"/>
+      <c r="F49" s="252"/>
+      <c r="G49" s="252"/>
+      <c r="H49" s="252"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B52" s="248" t="s">
+      <c r="B52" s="252" t="s">
         <v>128</v>
       </c>
-      <c r="C52" s="248"/>
-      <c r="D52" s="248"/>
-      <c r="E52" s="248"/>
-      <c r="F52" s="248"/>
-      <c r="G52" s="248"/>
-      <c r="H52" s="248"/>
+      <c r="C52" s="252"/>
+      <c r="D52" s="252"/>
+      <c r="E52" s="252"/>
+      <c r="F52" s="252"/>
+      <c r="G52" s="252"/>
+      <c r="H52" s="252"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B54" s="41" t="s">
@@ -13174,28 +14109,28 @@
       </c>
     </row>
     <row r="59" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="248"/>
-      <c r="C59" s="248"/>
-      <c r="D59" s="248"/>
-      <c r="E59" s="248"/>
-      <c r="F59" s="248"/>
-      <c r="G59" s="248"/>
-      <c r="H59" s="248"/>
+      <c r="B59" s="252"/>
+      <c r="C59" s="252"/>
+      <c r="D59" s="252"/>
+      <c r="E59" s="252"/>
+      <c r="F59" s="252"/>
+      <c r="G59" s="252"/>
+      <c r="H59" s="252"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B52:H52"/>
+    <mergeCell ref="B59:H59"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="B49:H49"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="E25:F25"/>
-    <mergeCell ref="B52:H52"/>
-    <mergeCell ref="B59:H59"/>
-    <mergeCell ref="B33:H33"/>
-    <mergeCell ref="B39:H39"/>
-    <mergeCell ref="B42:H42"/>
-    <mergeCell ref="B49:H49"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -13265,36 +14200,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="248" t="s">
+      <c r="C2" s="252" t="s">
         <v>137</v>
       </c>
-      <c r="D2" s="248"/>
-      <c r="E2" s="248"/>
-      <c r="F2" s="248"/>
-      <c r="G2" s="260"/>
-      <c r="H2" s="261" t="s">
+      <c r="D2" s="252"/>
+      <c r="E2" s="252"/>
+      <c r="F2" s="252"/>
+      <c r="G2" s="258"/>
+      <c r="H2" s="259" t="s">
         <v>138</v>
       </c>
-      <c r="I2" s="248"/>
-      <c r="J2" s="248"/>
-      <c r="K2" s="248"/>
-      <c r="L2" s="248"/>
+      <c r="I2" s="252"/>
+      <c r="J2" s="252"/>
+      <c r="K2" s="252"/>
+      <c r="L2" s="252"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="248" t="s">
+      <c r="S2" s="252" t="s">
         <v>137</v>
       </c>
-      <c r="T2" s="248"/>
-      <c r="U2" s="248"/>
-      <c r="V2" s="248"/>
-      <c r="W2" s="248"/>
-      <c r="X2" s="248"/>
-      <c r="Y2" s="248"/>
-      <c r="Z2" s="248"/>
-      <c r="AA2" s="248" t="s">
+      <c r="T2" s="252"/>
+      <c r="U2" s="252"/>
+      <c r="V2" s="252"/>
+      <c r="W2" s="252"/>
+      <c r="X2" s="252"/>
+      <c r="Y2" s="252"/>
+      <c r="Z2" s="252"/>
+      <c r="AA2" s="252" t="s">
         <v>138</v>
       </c>
-      <c r="AB2" s="248"/>
-      <c r="AC2" s="248"/>
+      <c r="AB2" s="252"/>
+      <c r="AC2" s="252"/>
       <c r="AE2" s="87" t="s">
         <v>139</v>
       </c>
@@ -13305,32 +14240,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="257" t="s">
+      <c r="C4" s="260" t="s">
         <v>140</v>
       </c>
-      <c r="D4" s="257"/>
-      <c r="E4" s="257"/>
-      <c r="F4" s="257"/>
-      <c r="G4" s="257"/>
-      <c r="H4" s="257"/>
-      <c r="I4" s="257"/>
-      <c r="J4" s="257"/>
-      <c r="K4" s="257"/>
-      <c r="L4" s="257"/>
+      <c r="D4" s="260"/>
+      <c r="E4" s="260"/>
+      <c r="F4" s="260"/>
+      <c r="G4" s="260"/>
+      <c r="H4" s="260"/>
+      <c r="I4" s="260"/>
+      <c r="J4" s="260"/>
+      <c r="K4" s="260"/>
+      <c r="L4" s="260"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="258" t="s">
+      <c r="S4" s="261" t="s">
         <v>140</v>
       </c>
-      <c r="T4" s="259"/>
-      <c r="U4" s="259"/>
-      <c r="V4" s="259"/>
-      <c r="W4" s="259"/>
-      <c r="X4" s="259"/>
-      <c r="Y4" s="259"/>
-      <c r="Z4" s="259"/>
-      <c r="AA4" s="259"/>
-      <c r="AB4" s="259"/>
-      <c r="AC4" s="259"/>
+      <c r="T4" s="262"/>
+      <c r="U4" s="262"/>
+      <c r="V4" s="262"/>
+      <c r="W4" s="262"/>
+      <c r="X4" s="262"/>
+      <c r="Y4" s="262"/>
+      <c r="Z4" s="262"/>
+      <c r="AA4" s="262"/>
+      <c r="AB4" s="262"/>
+      <c r="AC4" s="262"/>
       <c r="AE4" s="89"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -13826,33 +14761,33 @@
       <c r="Q10" s="93"/>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C11" s="257" t="s">
+      <c r="C11" s="260" t="s">
         <v>146</v>
       </c>
-      <c r="D11" s="257"/>
-      <c r="E11" s="257"/>
-      <c r="F11" s="257"/>
-      <c r="G11" s="257"/>
-      <c r="H11" s="257"/>
-      <c r="I11" s="257"/>
-      <c r="J11" s="257"/>
-      <c r="K11" s="257"/>
-      <c r="L11" s="257"/>
+      <c r="D11" s="260"/>
+      <c r="E11" s="260"/>
+      <c r="F11" s="260"/>
+      <c r="G11" s="260"/>
+      <c r="H11" s="260"/>
+      <c r="I11" s="260"/>
+      <c r="J11" s="260"/>
+      <c r="K11" s="260"/>
+      <c r="L11" s="260"/>
       <c r="O11" s="5"/>
       <c r="Q11" s="93"/>
-      <c r="S11" s="258" t="s">
+      <c r="S11" s="261" t="s">
         <v>146</v>
       </c>
-      <c r="T11" s="259"/>
-      <c r="U11" s="259"/>
-      <c r="V11" s="259"/>
-      <c r="W11" s="259"/>
-      <c r="X11" s="259"/>
-      <c r="Y11" s="259"/>
-      <c r="Z11" s="259"/>
-      <c r="AA11" s="259"/>
-      <c r="AB11" s="259"/>
-      <c r="AC11" s="259"/>
+      <c r="T11" s="262"/>
+      <c r="U11" s="262"/>
+      <c r="V11" s="262"/>
+      <c r="W11" s="262"/>
+      <c r="X11" s="262"/>
+      <c r="Y11" s="262"/>
+      <c r="Z11" s="262"/>
+      <c r="AA11" s="262"/>
+      <c r="AB11" s="262"/>
+      <c r="AC11" s="262"/>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B12" s="16" t="s">
@@ -14293,33 +15228,33 @@
       <c r="Q18" s="93"/>
     </row>
     <row r="19" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C19" s="257" t="s">
+      <c r="C19" s="260" t="s">
         <v>148</v>
       </c>
-      <c r="D19" s="257"/>
-      <c r="E19" s="257"/>
-      <c r="F19" s="257"/>
-      <c r="G19" s="257"/>
-      <c r="H19" s="257"/>
-      <c r="I19" s="257"/>
-      <c r="J19" s="257"/>
-      <c r="K19" s="257"/>
-      <c r="L19" s="257"/>
+      <c r="D19" s="260"/>
+      <c r="E19" s="260"/>
+      <c r="F19" s="260"/>
+      <c r="G19" s="260"/>
+      <c r="H19" s="260"/>
+      <c r="I19" s="260"/>
+      <c r="J19" s="260"/>
+      <c r="K19" s="260"/>
+      <c r="L19" s="260"/>
       <c r="O19" s="5"/>
       <c r="Q19" s="93"/>
-      <c r="S19" s="258" t="s">
+      <c r="S19" s="261" t="s">
         <v>148</v>
       </c>
-      <c r="T19" s="259"/>
-      <c r="U19" s="259"/>
-      <c r="V19" s="259"/>
-      <c r="W19" s="259"/>
-      <c r="X19" s="259"/>
-      <c r="Y19" s="259"/>
-      <c r="Z19" s="259"/>
-      <c r="AA19" s="259"/>
-      <c r="AB19" s="259"/>
-      <c r="AC19" s="259"/>
+      <c r="T19" s="262"/>
+      <c r="U19" s="262"/>
+      <c r="V19" s="262"/>
+      <c r="W19" s="262"/>
+      <c r="X19" s="262"/>
+      <c r="Y19" s="262"/>
+      <c r="Z19" s="262"/>
+      <c r="AA19" s="262"/>
+      <c r="AB19" s="262"/>
+      <c r="AC19" s="262"/>
       <c r="AE19" s="89">
         <f>AE4</f>
         <v>0</v>
@@ -15137,32 +16072,32 @@
       <c r="O31" s="5"/>
     </row>
     <row r="32" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C32" s="257" t="s">
+      <c r="C32" s="260" t="s">
         <v>150</v>
       </c>
-      <c r="D32" s="257"/>
-      <c r="E32" s="257"/>
-      <c r="F32" s="257"/>
-      <c r="G32" s="257"/>
-      <c r="H32" s="257"/>
-      <c r="I32" s="257"/>
-      <c r="J32" s="257"/>
-      <c r="K32" s="257"/>
-      <c r="L32" s="257"/>
+      <c r="D32" s="260"/>
+      <c r="E32" s="260"/>
+      <c r="F32" s="260"/>
+      <c r="G32" s="260"/>
+      <c r="H32" s="260"/>
+      <c r="I32" s="260"/>
+      <c r="J32" s="260"/>
+      <c r="K32" s="260"/>
+      <c r="L32" s="260"/>
       <c r="O32" s="5"/>
-      <c r="S32" s="258" t="s">
+      <c r="S32" s="261" t="s">
         <v>150</v>
       </c>
-      <c r="T32" s="259"/>
-      <c r="U32" s="259"/>
-      <c r="V32" s="259"/>
-      <c r="W32" s="259"/>
-      <c r="X32" s="259"/>
-      <c r="Y32" s="259"/>
-      <c r="Z32" s="259"/>
-      <c r="AA32" s="259"/>
-      <c r="AB32" s="259"/>
-      <c r="AC32" s="259"/>
+      <c r="T32" s="262"/>
+      <c r="U32" s="262"/>
+      <c r="V32" s="262"/>
+      <c r="W32" s="262"/>
+      <c r="X32" s="262"/>
+      <c r="Y32" s="262"/>
+      <c r="Z32" s="262"/>
+      <c r="AA32" s="262"/>
+      <c r="AB32" s="262"/>
+      <c r="AC32" s="262"/>
     </row>
     <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B33" s="16" t="s">
@@ -15419,18 +16354,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="C11:L11"/>
+    <mergeCell ref="S11:AC11"/>
+    <mergeCell ref="C19:L19"/>
+    <mergeCell ref="S19:AC19"/>
+    <mergeCell ref="C32:L32"/>
+    <mergeCell ref="S32:AC32"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C11:L11"/>
-    <mergeCell ref="S11:AC11"/>
-    <mergeCell ref="C19:L19"/>
-    <mergeCell ref="S19:AC19"/>
-    <mergeCell ref="C32:L32"/>
-    <mergeCell ref="S32:AC32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -15467,35 +16402,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="248" t="s">
+      <c r="C2" s="252" t="s">
         <v>137</v>
       </c>
-      <c r="D2" s="248"/>
-      <c r="E2" s="248"/>
-      <c r="F2" s="248"/>
-      <c r="G2" s="260"/>
-      <c r="H2" s="261" t="s">
+      <c r="D2" s="252"/>
+      <c r="E2" s="252"/>
+      <c r="F2" s="252"/>
+      <c r="G2" s="258"/>
+      <c r="H2" s="259" t="s">
         <v>138</v>
       </c>
-      <c r="I2" s="248"/>
-      <c r="J2" s="248"/>
-      <c r="K2" s="248"/>
-      <c r="L2" s="248"/>
-      <c r="P2" s="248" t="s">
+      <c r="I2" s="252"/>
+      <c r="J2" s="252"/>
+      <c r="K2" s="252"/>
+      <c r="L2" s="252"/>
+      <c r="P2" s="252" t="s">
         <v>137</v>
       </c>
-      <c r="Q2" s="248"/>
-      <c r="R2" s="248"/>
-      <c r="S2" s="248"/>
-      <c r="T2" s="248"/>
-      <c r="U2" s="248"/>
-      <c r="V2" s="248"/>
-      <c r="W2" s="248"/>
-      <c r="X2" s="248" t="s">
+      <c r="Q2" s="252"/>
+      <c r="R2" s="252"/>
+      <c r="S2" s="252"/>
+      <c r="T2" s="252"/>
+      <c r="U2" s="252"/>
+      <c r="V2" s="252"/>
+      <c r="W2" s="252"/>
+      <c r="X2" s="252" t="s">
         <v>138</v>
       </c>
-      <c r="Y2" s="248"/>
-      <c r="Z2" s="248"/>
+      <c r="Y2" s="252"/>
+      <c r="Z2" s="252"/>
       <c r="AB2" s="87" t="s">
         <v>139</v>
       </c>
@@ -15504,31 +16439,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="257" t="s">
+      <c r="C4" s="260" t="s">
         <v>140</v>
       </c>
-      <c r="D4" s="257"/>
-      <c r="E4" s="257"/>
-      <c r="F4" s="257"/>
-      <c r="G4" s="257"/>
-      <c r="H4" s="257"/>
-      <c r="I4" s="257"/>
-      <c r="J4" s="257"/>
-      <c r="K4" s="257"/>
-      <c r="L4" s="257"/>
-      <c r="P4" s="259" t="s">
+      <c r="D4" s="260"/>
+      <c r="E4" s="260"/>
+      <c r="F4" s="260"/>
+      <c r="G4" s="260"/>
+      <c r="H4" s="260"/>
+      <c r="I4" s="260"/>
+      <c r="J4" s="260"/>
+      <c r="K4" s="260"/>
+      <c r="L4" s="260"/>
+      <c r="P4" s="262" t="s">
         <v>140</v>
       </c>
-      <c r="Q4" s="259"/>
-      <c r="R4" s="259"/>
-      <c r="S4" s="259"/>
-      <c r="T4" s="259"/>
-      <c r="U4" s="259"/>
-      <c r="V4" s="259"/>
-      <c r="W4" s="259"/>
-      <c r="X4" s="259"/>
-      <c r="Y4" s="259"/>
-      <c r="Z4" s="259"/>
+      <c r="Q4" s="262"/>
+      <c r="R4" s="262"/>
+      <c r="S4" s="262"/>
+      <c r="T4" s="262"/>
+      <c r="U4" s="262"/>
+      <c r="V4" s="262"/>
+      <c r="W4" s="262"/>
+      <c r="X4" s="262"/>
+      <c r="Y4" s="262"/>
+      <c r="Z4" s="262"/>
       <c r="AB4" s="89"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -15723,32 +16658,32 @@
       <c r="N8" s="93"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="257" t="s">
+      <c r="C9" s="260" t="s">
         <v>166</v>
       </c>
-      <c r="D9" s="257"/>
-      <c r="E9" s="257"/>
-      <c r="F9" s="257"/>
-      <c r="G9" s="257"/>
-      <c r="H9" s="257"/>
-      <c r="I9" s="257"/>
-      <c r="J9" s="257"/>
-      <c r="K9" s="257"/>
-      <c r="L9" s="257"/>
+      <c r="D9" s="260"/>
+      <c r="E9" s="260"/>
+      <c r="F9" s="260"/>
+      <c r="G9" s="260"/>
+      <c r="H9" s="260"/>
+      <c r="I9" s="260"/>
+      <c r="J9" s="260"/>
+      <c r="K9" s="260"/>
+      <c r="L9" s="260"/>
       <c r="N9" s="93"/>
-      <c r="P9" s="259" t="s">
+      <c r="P9" s="262" t="s">
         <v>167</v>
       </c>
-      <c r="Q9" s="259"/>
-      <c r="R9" s="259"/>
-      <c r="S9" s="259"/>
-      <c r="T9" s="259"/>
-      <c r="U9" s="259"/>
-      <c r="V9" s="259"/>
-      <c r="W9" s="259"/>
-      <c r="X9" s="259"/>
-      <c r="Y9" s="259"/>
-      <c r="Z9" s="259"/>
+      <c r="Q9" s="262"/>
+      <c r="R9" s="262"/>
+      <c r="S9" s="262"/>
+      <c r="T9" s="262"/>
+      <c r="U9" s="262"/>
+      <c r="V9" s="262"/>
+      <c r="W9" s="262"/>
+      <c r="X9" s="262"/>
+      <c r="Y9" s="262"/>
+      <c r="Z9" s="262"/>
       <c r="AB9" s="89">
         <f>AB4</f>
         <v>0</v>
@@ -16597,31 +17532,31 @@
       </c>
     </row>
     <row r="21" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="C21" s="257" t="s">
+      <c r="C21" s="260" t="s">
         <v>169</v>
       </c>
-      <c r="D21" s="257"/>
-      <c r="E21" s="257"/>
-      <c r="F21" s="257"/>
-      <c r="G21" s="257"/>
-      <c r="H21" s="257"/>
-      <c r="I21" s="257"/>
-      <c r="J21" s="257"/>
-      <c r="K21" s="257"/>
-      <c r="L21" s="257"/>
-      <c r="P21" s="259" t="s">
+      <c r="D21" s="260"/>
+      <c r="E21" s="260"/>
+      <c r="F21" s="260"/>
+      <c r="G21" s="260"/>
+      <c r="H21" s="260"/>
+      <c r="I21" s="260"/>
+      <c r="J21" s="260"/>
+      <c r="K21" s="260"/>
+      <c r="L21" s="260"/>
+      <c r="P21" s="262" t="s">
         <v>169</v>
       </c>
-      <c r="Q21" s="259"/>
-      <c r="R21" s="259"/>
-      <c r="S21" s="259"/>
-      <c r="T21" s="259"/>
-      <c r="U21" s="259"/>
-      <c r="V21" s="259"/>
-      <c r="W21" s="259"/>
-      <c r="X21" s="259"/>
-      <c r="Y21" s="259"/>
-      <c r="Z21" s="259"/>
+      <c r="Q21" s="262"/>
+      <c r="R21" s="262"/>
+      <c r="S21" s="262"/>
+      <c r="T21" s="262"/>
+      <c r="U21" s="262"/>
+      <c r="V21" s="262"/>
+      <c r="W21" s="262"/>
+      <c r="X21" s="262"/>
+      <c r="Y21" s="262"/>
+      <c r="Z21" s="262"/>
     </row>
     <row r="22" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B22" s="16" t="s">
@@ -17436,60 +18371,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="248" t="s">
+      <c r="C3" s="252" t="s">
         <v>137</v>
       </c>
-      <c r="D3" s="248"/>
-      <c r="E3" s="248"/>
-      <c r="F3" s="248"/>
-      <c r="G3" s="260"/>
-      <c r="H3" s="261" t="s">
+      <c r="D3" s="252"/>
+      <c r="E3" s="252"/>
+      <c r="F3" s="252"/>
+      <c r="G3" s="258"/>
+      <c r="H3" s="259" t="s">
         <v>138</v>
       </c>
-      <c r="I3" s="248"/>
-      <c r="J3" s="248"/>
-      <c r="K3" s="248"/>
-      <c r="L3" s="248"/>
-      <c r="P3" s="262"/>
-      <c r="Q3" s="262"/>
-      <c r="R3" s="262"/>
-      <c r="S3" s="262"/>
-      <c r="T3" s="262"/>
-      <c r="U3" s="262"/>
-      <c r="V3" s="262"/>
-      <c r="W3" s="262"/>
-      <c r="X3" s="262"/>
-      <c r="Y3" s="262"/>
-      <c r="Z3" s="262"/>
+      <c r="I3" s="252"/>
+      <c r="J3" s="252"/>
+      <c r="K3" s="252"/>
+      <c r="L3" s="252"/>
+      <c r="P3" s="263"/>
+      <c r="Q3" s="263"/>
+      <c r="R3" s="263"/>
+      <c r="S3" s="263"/>
+      <c r="T3" s="263"/>
+      <c r="U3" s="263"/>
+      <c r="V3" s="263"/>
+      <c r="W3" s="263"/>
+      <c r="X3" s="263"/>
+      <c r="Y3" s="263"/>
+      <c r="Z3" s="263"/>
       <c r="AB3" s="130"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="88"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="257" t="s">
+      <c r="C5" s="260" t="s">
         <v>140</v>
       </c>
-      <c r="D5" s="257"/>
-      <c r="E5" s="257"/>
-      <c r="F5" s="257"/>
-      <c r="G5" s="257"/>
-      <c r="H5" s="257"/>
-      <c r="I5" s="257"/>
-      <c r="J5" s="257"/>
-      <c r="K5" s="257"/>
-      <c r="L5" s="257"/>
-      <c r="P5" s="262"/>
-      <c r="Q5" s="262"/>
-      <c r="R5" s="262"/>
-      <c r="S5" s="262"/>
-      <c r="T5" s="262"/>
-      <c r="U5" s="262"/>
-      <c r="V5" s="262"/>
-      <c r="W5" s="262"/>
-      <c r="X5" s="262"/>
-      <c r="Y5" s="262"/>
-      <c r="Z5" s="262"/>
+      <c r="D5" s="260"/>
+      <c r="E5" s="260"/>
+      <c r="F5" s="260"/>
+      <c r="G5" s="260"/>
+      <c r="H5" s="260"/>
+      <c r="I5" s="260"/>
+      <c r="J5" s="260"/>
+      <c r="K5" s="260"/>
+      <c r="L5" s="260"/>
+      <c r="P5" s="263"/>
+      <c r="Q5" s="263"/>
+      <c r="R5" s="263"/>
+      <c r="S5" s="263"/>
+      <c r="T5" s="263"/>
+      <c r="U5" s="263"/>
+      <c r="V5" s="263"/>
+      <c r="W5" s="263"/>
+      <c r="X5" s="263"/>
+      <c r="Y5" s="263"/>
+      <c r="Z5" s="263"/>
       <c r="AB5" s="131"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -17675,30 +18610,30 @@
       <c r="N10" s="93"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="257" t="s">
+      <c r="C11" s="260" t="s">
         <v>173</v>
       </c>
-      <c r="D11" s="257"/>
-      <c r="E11" s="257"/>
-      <c r="F11" s="257"/>
-      <c r="G11" s="257"/>
-      <c r="H11" s="257"/>
-      <c r="I11" s="257"/>
-      <c r="J11" s="257"/>
-      <c r="K11" s="257"/>
-      <c r="L11" s="257"/>
+      <c r="D11" s="260"/>
+      <c r="E11" s="260"/>
+      <c r="F11" s="260"/>
+      <c r="G11" s="260"/>
+      <c r="H11" s="260"/>
+      <c r="I11" s="260"/>
+      <c r="J11" s="260"/>
+      <c r="K11" s="260"/>
+      <c r="L11" s="260"/>
       <c r="N11" s="93"/>
-      <c r="P11" s="262"/>
-      <c r="Q11" s="262"/>
-      <c r="R11" s="262"/>
-      <c r="S11" s="262"/>
-      <c r="T11" s="262"/>
-      <c r="U11" s="262"/>
-      <c r="V11" s="262"/>
-      <c r="W11" s="262"/>
-      <c r="X11" s="262"/>
-      <c r="Y11" s="262"/>
-      <c r="Z11" s="262"/>
+      <c r="P11" s="263"/>
+      <c r="Q11" s="263"/>
+      <c r="R11" s="263"/>
+      <c r="S11" s="263"/>
+      <c r="T11" s="263"/>
+      <c r="U11" s="263"/>
+      <c r="V11" s="263"/>
+      <c r="W11" s="263"/>
+      <c r="X11" s="263"/>
+      <c r="Y11" s="263"/>
+      <c r="Z11" s="263"/>
       <c r="AB11" s="131"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -17940,18 +18875,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="257" t="s">
+      <c r="C18" s="260" t="s">
         <v>178</v>
       </c>
-      <c r="D18" s="257"/>
-      <c r="E18" s="257"/>
-      <c r="F18" s="257"/>
-      <c r="G18" s="257"/>
-      <c r="H18" s="257"/>
-      <c r="I18" s="257"/>
-      <c r="J18" s="257"/>
-      <c r="K18" s="257"/>
-      <c r="L18" s="257"/>
+      <c r="D18" s="260"/>
+      <c r="E18" s="260"/>
+      <c r="F18" s="260"/>
+      <c r="G18" s="260"/>
+      <c r="H18" s="260"/>
+      <c r="I18" s="260"/>
+      <c r="J18" s="260"/>
+      <c r="K18" s="260"/>
+      <c r="L18" s="260"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -18164,23 +19099,23 @@
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="262"/>
-      <c r="C25" s="262"/>
+      <c r="B25" s="263"/>
+      <c r="C25" s="263"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="130"/>
-      <c r="C26" s="257" t="s">
+      <c r="C26" s="260" t="s">
         <v>184</v>
       </c>
-      <c r="D26" s="257"/>
-      <c r="E26" s="257"/>
-      <c r="F26" s="257"/>
-      <c r="G26" s="257"/>
-      <c r="H26" s="257"/>
-      <c r="I26" s="257"/>
-      <c r="J26" s="257"/>
-      <c r="K26" s="257"/>
-      <c r="L26" s="257"/>
+      <c r="D26" s="260"/>
+      <c r="E26" s="260"/>
+      <c r="F26" s="260"/>
+      <c r="G26" s="260"/>
+      <c r="H26" s="260"/>
+      <c r="I26" s="260"/>
+      <c r="J26" s="260"/>
+      <c r="K26" s="260"/>
+      <c r="L26" s="260"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -18372,18 +19307,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="130"/>
-      <c r="C33" s="257" t="s">
+      <c r="C33" s="260" t="s">
         <v>188</v>
       </c>
-      <c r="D33" s="257"/>
-      <c r="E33" s="257"/>
-      <c r="F33" s="257"/>
-      <c r="G33" s="257"/>
-      <c r="H33" s="257"/>
-      <c r="I33" s="257"/>
-      <c r="J33" s="257"/>
-      <c r="K33" s="257"/>
-      <c r="L33" s="257"/>
+      <c r="D33" s="260"/>
+      <c r="E33" s="260"/>
+      <c r="F33" s="260"/>
+      <c r="G33" s="260"/>
+      <c r="H33" s="260"/>
+      <c r="I33" s="260"/>
+      <c r="J33" s="260"/>
+      <c r="K33" s="260"/>
+      <c r="L33" s="260"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -18567,18 +19502,18 @@
       <c r="C39" s="146"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="257" t="s">
+      <c r="C40" s="260" t="s">
         <v>191</v>
       </c>
-      <c r="D40" s="257"/>
-      <c r="E40" s="257"/>
-      <c r="F40" s="257"/>
-      <c r="G40" s="257"/>
-      <c r="H40" s="257"/>
-      <c r="I40" s="257"/>
-      <c r="J40" s="257"/>
-      <c r="K40" s="257"/>
-      <c r="L40" s="257"/>
+      <c r="D40" s="260"/>
+      <c r="E40" s="260"/>
+      <c r="F40" s="260"/>
+      <c r="G40" s="260"/>
+      <c r="H40" s="260"/>
+      <c r="I40" s="260"/>
+      <c r="J40" s="260"/>
+      <c r="K40" s="260"/>
+      <c r="L40" s="260"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -18842,6 +19777,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18849,12 +19790,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -18892,60 +19827,60 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="248" t="s">
+      <c r="C2" s="252" t="s">
         <v>137</v>
       </c>
-      <c r="D2" s="248"/>
-      <c r="E2" s="248"/>
-      <c r="F2" s="248"/>
-      <c r="G2" s="260"/>
-      <c r="H2" s="261" t="s">
+      <c r="D2" s="252"/>
+      <c r="E2" s="252"/>
+      <c r="F2" s="252"/>
+      <c r="G2" s="258"/>
+      <c r="H2" s="259" t="s">
         <v>138</v>
       </c>
-      <c r="I2" s="248"/>
-      <c r="J2" s="248"/>
-      <c r="K2" s="248"/>
-      <c r="L2" s="248"/>
-      <c r="S2" s="262"/>
-      <c r="T2" s="262"/>
-      <c r="U2" s="262"/>
-      <c r="V2" s="262"/>
-      <c r="W2" s="262"/>
-      <c r="X2" s="262"/>
-      <c r="Y2" s="262"/>
-      <c r="Z2" s="262"/>
-      <c r="AA2" s="262"/>
-      <c r="AB2" s="262"/>
-      <c r="AC2" s="262"/>
+      <c r="I2" s="252"/>
+      <c r="J2" s="252"/>
+      <c r="K2" s="252"/>
+      <c r="L2" s="252"/>
+      <c r="S2" s="263"/>
+      <c r="T2" s="263"/>
+      <c r="U2" s="263"/>
+      <c r="V2" s="263"/>
+      <c r="W2" s="263"/>
+      <c r="X2" s="263"/>
+      <c r="Y2" s="263"/>
+      <c r="Z2" s="263"/>
+      <c r="AA2" s="263"/>
+      <c r="AB2" s="263"/>
+      <c r="AC2" s="263"/>
       <c r="AE2" s="130"/>
     </row>
     <row r="3" spans="1:31" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="257" t="s">
+      <c r="C4" s="260" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="257"/>
-      <c r="E4" s="257"/>
-      <c r="F4" s="257"/>
-      <c r="G4" s="257"/>
-      <c r="H4" s="257"/>
-      <c r="I4" s="257"/>
-      <c r="J4" s="257"/>
-      <c r="K4" s="257"/>
-      <c r="L4" s="257"/>
-      <c r="S4" s="262"/>
-      <c r="T4" s="262"/>
-      <c r="U4" s="262"/>
-      <c r="V4" s="262"/>
-      <c r="W4" s="262"/>
-      <c r="X4" s="262"/>
-      <c r="Y4" s="262"/>
-      <c r="Z4" s="262"/>
-      <c r="AA4" s="262"/>
-      <c r="AB4" s="262"/>
-      <c r="AC4" s="262"/>
+      <c r="D4" s="260"/>
+      <c r="E4" s="260"/>
+      <c r="F4" s="260"/>
+      <c r="G4" s="260"/>
+      <c r="H4" s="260"/>
+      <c r="I4" s="260"/>
+      <c r="J4" s="260"/>
+      <c r="K4" s="260"/>
+      <c r="L4" s="260"/>
+      <c r="S4" s="263"/>
+      <c r="T4" s="263"/>
+      <c r="U4" s="263"/>
+      <c r="V4" s="263"/>
+      <c r="W4" s="263"/>
+      <c r="X4" s="263"/>
+      <c r="Y4" s="263"/>
+      <c r="Z4" s="263"/>
+      <c r="AA4" s="263"/>
+      <c r="AB4" s="263"/>
+      <c r="AC4" s="263"/>
       <c r="AE4" s="131"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -19308,18 +20243,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="257" t="s">
+      <c r="C13" s="260" t="s">
         <v>199</v>
       </c>
-      <c r="D13" s="257"/>
-      <c r="E13" s="257"/>
-      <c r="F13" s="257"/>
-      <c r="G13" s="257"/>
-      <c r="H13" s="257"/>
-      <c r="I13" s="257"/>
-      <c r="J13" s="257"/>
-      <c r="K13" s="257"/>
-      <c r="L13" s="257"/>
+      <c r="D13" s="260"/>
+      <c r="E13" s="260"/>
+      <c r="F13" s="260"/>
+      <c r="G13" s="260"/>
+      <c r="H13" s="260"/>
+      <c r="I13" s="260"/>
+      <c r="J13" s="260"/>
+      <c r="K13" s="260"/>
+      <c r="L13" s="260"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -19412,18 +20347,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="257" t="s">
+      <c r="C18" s="260" t="s">
         <v>200</v>
       </c>
-      <c r="D18" s="257"/>
-      <c r="E18" s="257"/>
-      <c r="F18" s="257"/>
-      <c r="G18" s="257"/>
-      <c r="H18" s="257"/>
-      <c r="I18" s="257"/>
-      <c r="J18" s="257"/>
-      <c r="K18" s="257"/>
-      <c r="L18" s="257"/>
+      <c r="D18" s="260"/>
+      <c r="E18" s="260"/>
+      <c r="F18" s="260"/>
+      <c r="G18" s="260"/>
+      <c r="H18" s="260"/>
+      <c r="I18" s="260"/>
+      <c r="J18" s="260"/>
+      <c r="K18" s="260"/>
+      <c r="L18" s="260"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19615,18 +20550,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="257" t="s">
+      <c r="C25" s="260" t="s">
         <v>311</v>
       </c>
-      <c r="D25" s="257"/>
-      <c r="E25" s="257"/>
-      <c r="F25" s="257"/>
-      <c r="G25" s="257"/>
-      <c r="H25" s="257"/>
-      <c r="I25" s="257"/>
-      <c r="J25" s="257"/>
-      <c r="K25" s="257"/>
-      <c r="L25" s="257"/>
+      <c r="D25" s="260"/>
+      <c r="E25" s="260"/>
+      <c r="F25" s="260"/>
+      <c r="G25" s="260"/>
+      <c r="H25" s="260"/>
+      <c r="I25" s="260"/>
+      <c r="J25" s="260"/>
+      <c r="K25" s="260"/>
+      <c r="L25" s="260"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -19764,18 +20699,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="257" t="s">
+      <c r="C31" s="260" t="s">
         <v>78</v>
       </c>
-      <c r="D31" s="257"/>
-      <c r="E31" s="257"/>
-      <c r="F31" s="257"/>
-      <c r="G31" s="257"/>
-      <c r="H31" s="257"/>
-      <c r="I31" s="257"/>
-      <c r="J31" s="257"/>
-      <c r="K31" s="257"/>
-      <c r="L31" s="257"/>
+      <c r="D31" s="260"/>
+      <c r="E31" s="260"/>
+      <c r="F31" s="260"/>
+      <c r="G31" s="260"/>
+      <c r="H31" s="260"/>
+      <c r="I31" s="260"/>
+      <c r="J31" s="260"/>
+      <c r="K31" s="260"/>
+      <c r="L31" s="260"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -19914,16 +20849,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19986,10 +20921,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="248" t="s">
+      <c r="B4" s="252" t="s">
         <v>207</v>
       </c>
-      <c r="C4" s="248"/>
+      <c r="C4" s="252"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -20006,7 +20941,7 @@
       </c>
       <c r="C6" s="154">
         <f ca="1">Overview!C5</f>
-        <v>10.26</v>
+        <v>10.27</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20015,7 +20950,7 @@
       </c>
       <c r="C7" s="155">
         <f ca="1">C5*C6</f>
-        <v>5359362.3</v>
+        <v>5364585.8499999996</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20033,7 +20968,7 @@
       </c>
       <c r="C9" s="156">
         <f ca="1">Overview!F27</f>
-        <v>4.428E-2</v>
+        <v>4.4510000000000001E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20042,7 +20977,7 @@
       </c>
       <c r="C10" s="154">
         <f ca="1">Overview!C13</f>
-        <v>0.97860000000000003</v>
+        <v>0.98270000000000002</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20074,10 +21009,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="248" t="s">
+      <c r="B15" s="252" t="s">
         <v>214</v>
       </c>
-      <c r="C15" s="248"/>
+      <c r="C15" s="252"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -20112,7 +21047,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>8.8317000000000007E-2</v>
+        <v>8.8731499999999991E-2</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20121,7 +21056,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>8.8317000000000007E-2</v>
+        <v>8.8731499999999991E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20166,60 +21101,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="248" t="s">
+      <c r="C3" s="252" t="s">
         <v>137</v>
       </c>
-      <c r="D3" s="248"/>
-      <c r="E3" s="248"/>
-      <c r="F3" s="248"/>
-      <c r="G3" s="260"/>
-      <c r="H3" s="261" t="s">
+      <c r="D3" s="252"/>
+      <c r="E3" s="252"/>
+      <c r="F3" s="252"/>
+      <c r="G3" s="258"/>
+      <c r="H3" s="259" t="s">
         <v>138</v>
       </c>
-      <c r="I3" s="248"/>
-      <c r="J3" s="248"/>
-      <c r="K3" s="248"/>
-      <c r="L3" s="248"/>
-      <c r="P3" s="262"/>
-      <c r="Q3" s="262"/>
-      <c r="R3" s="262"/>
-      <c r="S3" s="262"/>
-      <c r="T3" s="262"/>
-      <c r="U3" s="262"/>
-      <c r="V3" s="262"/>
-      <c r="W3" s="262"/>
-      <c r="X3" s="262"/>
-      <c r="Y3" s="262"/>
-      <c r="Z3" s="262"/>
+      <c r="I3" s="252"/>
+      <c r="J3" s="252"/>
+      <c r="K3" s="252"/>
+      <c r="L3" s="252"/>
+      <c r="P3" s="263"/>
+      <c r="Q3" s="263"/>
+      <c r="R3" s="263"/>
+      <c r="S3" s="263"/>
+      <c r="T3" s="263"/>
+      <c r="U3" s="263"/>
+      <c r="V3" s="263"/>
+      <c r="W3" s="263"/>
+      <c r="X3" s="263"/>
+      <c r="Y3" s="263"/>
+      <c r="Z3" s="263"/>
       <c r="AB3" s="130"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="88"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="257" t="s">
+      <c r="C5" s="260" t="s">
         <v>221</v>
       </c>
-      <c r="D5" s="257"/>
-      <c r="E5" s="257"/>
-      <c r="F5" s="257"/>
-      <c r="G5" s="257"/>
-      <c r="H5" s="257"/>
-      <c r="I5" s="257"/>
-      <c r="J5" s="257"/>
-      <c r="K5" s="257"/>
-      <c r="L5" s="257"/>
-      <c r="P5" s="262"/>
-      <c r="Q5" s="262"/>
-      <c r="R5" s="262"/>
-      <c r="S5" s="262"/>
-      <c r="T5" s="262"/>
-      <c r="U5" s="262"/>
-      <c r="V5" s="262"/>
-      <c r="W5" s="262"/>
-      <c r="X5" s="262"/>
-      <c r="Y5" s="262"/>
-      <c r="Z5" s="262"/>
+      <c r="D5" s="260"/>
+      <c r="E5" s="260"/>
+      <c r="F5" s="260"/>
+      <c r="G5" s="260"/>
+      <c r="H5" s="260"/>
+      <c r="I5" s="260"/>
+      <c r="J5" s="260"/>
+      <c r="K5" s="260"/>
+      <c r="L5" s="260"/>
+      <c r="P5" s="263"/>
+      <c r="Q5" s="263"/>
+      <c r="R5" s="263"/>
+      <c r="S5" s="263"/>
+      <c r="T5" s="263"/>
+      <c r="U5" s="263"/>
+      <c r="V5" s="263"/>
+      <c r="W5" s="263"/>
+      <c r="X5" s="263"/>
+      <c r="Y5" s="263"/>
+      <c r="Z5" s="263"/>
       <c r="AB5" s="131"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -20227,43 +21162,43 @@
         <v>174</v>
       </c>
       <c r="C6" s="12">
-        <f>Revenue!C20</f>
+        <f>Revenue!C5</f>
         <v>2022</v>
       </c>
       <c r="D6" s="12">
-        <f>Revenue!D20</f>
+        <f>Revenue!D5</f>
         <v>2023</v>
       </c>
       <c r="E6" s="12">
-        <f>Revenue!E20</f>
+        <f>Revenue!E5</f>
         <v>2024</v>
       </c>
       <c r="F6" s="12">
-        <f>Revenue!F20</f>
+        <f>Revenue!F5</f>
         <v>2025</v>
       </c>
       <c r="G6" s="12">
-        <f>Revenue!G20</f>
+        <f>Revenue!G5</f>
         <v>2026</v>
       </c>
       <c r="H6" s="12">
-        <f>Revenue!H20</f>
+        <f>Revenue!H5</f>
         <v>2027</v>
       </c>
       <c r="I6" s="12">
-        <f>Revenue!I20</f>
+        <f>Revenue!I5</f>
         <v>2028</v>
       </c>
       <c r="J6" s="12">
-        <f>Revenue!J20</f>
+        <f>Revenue!J5</f>
         <v>2029</v>
       </c>
       <c r="K6" s="12">
-        <f>Revenue!K20</f>
+        <f>Revenue!K5</f>
         <v>2030</v>
       </c>
       <c r="L6" s="12">
-        <f>Revenue!L20</f>
+        <f>Revenue!L5</f>
         <v>2031</v>
       </c>
       <c r="O6" s="16"/>
@@ -20465,10 +21400,10 @@
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="248" t="s">
+      <c r="B13" s="252" t="s">
         <v>225</v>
       </c>
-      <c r="C13" s="248"/>
+      <c r="C13" s="252"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -20488,10 +21423,10 @@
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="248" t="s">
+      <c r="B18" s="252" t="s">
         <v>227</v>
       </c>
-      <c r="C18" s="248"/>
+      <c r="C18" s="252"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -20605,80 +21540,80 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="248" t="s">
+      <c r="C2" s="252" t="s">
         <v>137</v>
       </c>
-      <c r="D2" s="248"/>
-      <c r="E2" s="248"/>
-      <c r="F2" s="248"/>
-      <c r="G2" s="260"/>
-      <c r="H2" s="261" t="s">
+      <c r="D2" s="252"/>
+      <c r="E2" s="252"/>
+      <c r="F2" s="252"/>
+      <c r="G2" s="258"/>
+      <c r="H2" s="259" t="s">
         <v>138</v>
       </c>
-      <c r="I2" s="248"/>
-      <c r="J2" s="248"/>
-      <c r="K2" s="248"/>
-      <c r="L2" s="248"/>
+      <c r="I2" s="252"/>
+      <c r="J2" s="252"/>
+      <c r="K2" s="252"/>
+      <c r="L2" s="252"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="257" t="s">
+      <c r="C4" s="260" t="s">
         <v>235</v>
       </c>
-      <c r="D4" s="257"/>
-      <c r="E4" s="257"/>
-      <c r="F4" s="257"/>
-      <c r="G4" s="257"/>
-      <c r="H4" s="257"/>
-      <c r="I4" s="257"/>
-      <c r="J4" s="257"/>
-      <c r="K4" s="257"/>
-      <c r="L4" s="257"/>
+      <c r="D4" s="260"/>
+      <c r="E4" s="260"/>
+      <c r="F4" s="260"/>
+      <c r="G4" s="260"/>
+      <c r="H4" s="260"/>
+      <c r="I4" s="260"/>
+      <c r="J4" s="260"/>
+      <c r="K4" s="260"/>
+      <c r="L4" s="260"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
         <v>141</v>
       </c>
       <c r="C5" s="12">
-        <f>Revenue!C20</f>
+        <f>Revenue!C5</f>
         <v>2022</v>
       </c>
       <c r="D5" s="12">
-        <f>Revenue!D20</f>
+        <f>Revenue!D5</f>
         <v>2023</v>
       </c>
       <c r="E5" s="12">
-        <f>Revenue!E20</f>
+        <f>Revenue!E5</f>
         <v>2024</v>
       </c>
       <c r="F5" s="12">
-        <f>Revenue!F20</f>
+        <f>Revenue!F5</f>
         <v>2025</v>
       </c>
       <c r="G5" s="12">
-        <f>Revenue!G20</f>
+        <f>Revenue!G5</f>
         <v>2026</v>
       </c>
       <c r="H5" s="12">
-        <f>Revenue!H20</f>
+        <f>Revenue!H5</f>
         <v>2027</v>
       </c>
       <c r="I5" s="12">
-        <f>Revenue!I20</f>
+        <f>Revenue!I5</f>
         <v>2028</v>
       </c>
       <c r="J5" s="12">
-        <f>Revenue!J20</f>
+        <f>Revenue!J5</f>
         <v>2029</v>
       </c>
       <c r="K5" s="12">
-        <f>Revenue!K20</f>
+        <f>Revenue!K5</f>
         <v>2030</v>
       </c>
       <c r="L5" s="12">
-        <f>Revenue!L20</f>
+        <f>Revenue!L5</f>
         <v>2031</v>
       </c>
     </row>
@@ -20824,18 +21759,18 @@
       <c r="N9" s="93"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C10" s="257" t="s">
+      <c r="C10" s="260" t="s">
         <v>146</v>
       </c>
-      <c r="D10" s="257"/>
-      <c r="E10" s="257"/>
-      <c r="F10" s="257"/>
-      <c r="G10" s="257"/>
-      <c r="H10" s="257"/>
-      <c r="I10" s="257"/>
-      <c r="J10" s="257"/>
-      <c r="K10" s="257"/>
-      <c r="L10" s="257"/>
+      <c r="D10" s="260"/>
+      <c r="E10" s="260"/>
+      <c r="F10" s="260"/>
+      <c r="G10" s="260"/>
+      <c r="H10" s="260"/>
+      <c r="I10" s="260"/>
+      <c r="J10" s="260"/>
+      <c r="K10" s="260"/>
+      <c r="L10" s="260"/>
       <c r="N10" s="93"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21029,18 +21964,18 @@
       <c r="N15" s="93"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C16" s="257" t="s">
+      <c r="C16" s="260" t="s">
         <v>237</v>
       </c>
-      <c r="D16" s="257"/>
-      <c r="E16" s="257"/>
-      <c r="F16" s="257"/>
-      <c r="G16" s="257"/>
-      <c r="H16" s="257"/>
-      <c r="I16" s="257"/>
-      <c r="J16" s="257"/>
-      <c r="K16" s="257"/>
-      <c r="L16" s="257"/>
+      <c r="D16" s="260"/>
+      <c r="E16" s="260"/>
+      <c r="F16" s="260"/>
+      <c r="G16" s="260"/>
+      <c r="H16" s="260"/>
+      <c r="I16" s="260"/>
+      <c r="J16" s="260"/>
+      <c r="K16" s="260"/>
+      <c r="L16" s="260"/>
       <c r="N16" s="93"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
@@ -21174,18 +22109,18 @@
       <c r="N20" s="93"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C21" s="257" t="s">
+      <c r="C21" s="260" t="s">
         <v>240</v>
       </c>
-      <c r="D21" s="257"/>
-      <c r="E21" s="257"/>
-      <c r="F21" s="257"/>
-      <c r="G21" s="257"/>
-      <c r="H21" s="257"/>
-      <c r="I21" s="257"/>
-      <c r="J21" s="257"/>
-      <c r="K21" s="257"/>
-      <c r="L21" s="257"/>
+      <c r="D21" s="260"/>
+      <c r="E21" s="260"/>
+      <c r="F21" s="260"/>
+      <c r="G21" s="260"/>
+      <c r="H21" s="260"/>
+      <c r="I21" s="260"/>
+      <c r="J21" s="260"/>
+      <c r="K21" s="260"/>
+      <c r="L21" s="260"/>
       <c r="N21" s="93"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
@@ -21269,18 +22204,18 @@
       <c r="N25" s="93"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C26" s="257" t="s">
+      <c r="C26" s="260" t="s">
         <v>241</v>
       </c>
-      <c r="D26" s="257"/>
-      <c r="E26" s="257"/>
-      <c r="F26" s="257"/>
-      <c r="G26" s="257"/>
-      <c r="H26" s="257"/>
-      <c r="I26" s="257"/>
-      <c r="J26" s="257"/>
-      <c r="K26" s="257"/>
-      <c r="L26" s="257"/>
+      <c r="D26" s="260"/>
+      <c r="E26" s="260"/>
+      <c r="F26" s="260"/>
+      <c r="G26" s="260"/>
+      <c r="H26" s="260"/>
+      <c r="I26" s="260"/>
+      <c r="J26" s="260"/>
+      <c r="K26" s="260"/>
+      <c r="L26" s="260"/>
       <c r="N26" s="93"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
@@ -21550,10 +22485,10 @@
       <c r="N36" s="93"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="248" t="s">
+      <c r="B37" s="252" t="s">
         <v>246</v>
       </c>
-      <c r="C37" s="248"/>
+      <c r="C37" s="252"/>
       <c r="N37" s="93"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -21628,10 +22563,10 @@
       </c>
     </row>
     <row r="47" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B47" s="248" t="s">
+      <c r="B47" s="252" t="s">
         <v>251</v>
       </c>
-      <c r="C47" s="248"/>
+      <c r="C47" s="252"/>
     </row>
     <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B48" s="1" t="s">
@@ -21687,10 +22622,10 @@
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B55" s="248" t="s">
+      <c r="B55" s="252" t="s">
         <v>375</v>
       </c>
-      <c r="C55" s="248"/>
+      <c r="C55" s="252"/>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B56" s="1" t="s">
@@ -21803,10 +22738,10 @@
       <c r="N3" s="93"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="248" t="s">
+      <c r="B4" s="252" t="s">
         <v>256</v>
       </c>
-      <c r="C4" s="248"/>
+      <c r="C4" s="252"/>
       <c r="N4" s="93"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -21860,7 +22795,7 @@
       </c>
       <c r="C10" s="154">
         <f ca="1">Overview!C5</f>
-        <v>10.26</v>
+        <v>10.27</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21869,7 +22804,7 @@
       </c>
       <c r="C11" s="175">
         <f ca="1">(C9-C10)/C10</f>
-        <v>0.12121740537257168</v>
+        <v>0.12012566495838224</v>
       </c>
     </row>
   </sheetData>
@@ -21934,60 +22869,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="248" t="s">
+      <c r="C3" s="252" t="s">
         <v>137</v>
       </c>
-      <c r="D3" s="248"/>
-      <c r="E3" s="248"/>
-      <c r="F3" s="248"/>
-      <c r="G3" s="260"/>
-      <c r="H3" s="261" t="s">
+      <c r="D3" s="252"/>
+      <c r="E3" s="252"/>
+      <c r="F3" s="252"/>
+      <c r="G3" s="258"/>
+      <c r="H3" s="259" t="s">
         <v>138</v>
       </c>
-      <c r="I3" s="248"/>
-      <c r="J3" s="248"/>
-      <c r="K3" s="248"/>
-      <c r="L3" s="248"/>
-      <c r="P3" s="262"/>
-      <c r="Q3" s="262"/>
-      <c r="R3" s="262"/>
-      <c r="S3" s="262"/>
-      <c r="T3" s="262"/>
-      <c r="U3" s="262"/>
-      <c r="V3" s="262"/>
-      <c r="W3" s="262"/>
-      <c r="X3" s="262"/>
-      <c r="Y3" s="262"/>
-      <c r="Z3" s="262"/>
+      <c r="I3" s="252"/>
+      <c r="J3" s="252"/>
+      <c r="K3" s="252"/>
+      <c r="L3" s="252"/>
+      <c r="P3" s="263"/>
+      <c r="Q3" s="263"/>
+      <c r="R3" s="263"/>
+      <c r="S3" s="263"/>
+      <c r="T3" s="263"/>
+      <c r="U3" s="263"/>
+      <c r="V3" s="263"/>
+      <c r="W3" s="263"/>
+      <c r="X3" s="263"/>
+      <c r="Y3" s="263"/>
+      <c r="Z3" s="263"/>
       <c r="AB3" s="130"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="88"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="257" t="s">
+      <c r="C5" s="260" t="s">
         <v>221</v>
       </c>
-      <c r="D5" s="257"/>
-      <c r="E5" s="257"/>
-      <c r="F5" s="257"/>
-      <c r="G5" s="257"/>
-      <c r="H5" s="257"/>
-      <c r="I5" s="257"/>
-      <c r="J5" s="257"/>
-      <c r="K5" s="257"/>
-      <c r="L5" s="257"/>
-      <c r="P5" s="262"/>
-      <c r="Q5" s="262"/>
-      <c r="R5" s="262"/>
-      <c r="S5" s="262"/>
-      <c r="T5" s="262"/>
-      <c r="U5" s="262"/>
-      <c r="V5" s="262"/>
-      <c r="W5" s="262"/>
-      <c r="X5" s="262"/>
-      <c r="Y5" s="262"/>
-      <c r="Z5" s="262"/>
+      <c r="D5" s="260"/>
+      <c r="E5" s="260"/>
+      <c r="F5" s="260"/>
+      <c r="G5" s="260"/>
+      <c r="H5" s="260"/>
+      <c r="I5" s="260"/>
+      <c r="J5" s="260"/>
+      <c r="K5" s="260"/>
+      <c r="L5" s="260"/>
+      <c r="P5" s="263"/>
+      <c r="Q5" s="263"/>
+      <c r="R5" s="263"/>
+      <c r="S5" s="263"/>
+      <c r="T5" s="263"/>
+      <c r="U5" s="263"/>
+      <c r="V5" s="263"/>
+      <c r="W5" s="263"/>
+      <c r="X5" s="263"/>
+      <c r="Y5" s="263"/>
+      <c r="Z5" s="263"/>
       <c r="AB5" s="131"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -22215,10 +23150,10 @@
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="263" t="s">
+      <c r="B14" s="264" t="s">
         <v>264</v>
       </c>
-      <c r="C14" s="264"/>
+      <c r="C14" s="265"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="176" t="s">
@@ -22226,7 +23161,7 @@
       </c>
       <c r="C15" s="177">
         <f ca="1">Overview!C5</f>
-        <v>10.26</v>
+        <v>10.27</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22245,20 +23180,20 @@
       <c r="C17" s="179">
         <v>1.2</v>
       </c>
-      <c r="E17" s="265" t="s">
+      <c r="E17" s="266" t="s">
         <v>267</v>
       </c>
-      <c r="F17" s="265"/>
-      <c r="G17" s="265"/>
-      <c r="H17" s="265"/>
-      <c r="I17" s="265"/>
+      <c r="F17" s="266"/>
+      <c r="G17" s="266"/>
+      <c r="H17" s="266"/>
+      <c r="I17" s="266"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="263" t="s">
+      <c r="B19" s="264" t="s">
         <v>225</v>
       </c>
-      <c r="C19" s="264"/>
+      <c r="C19" s="265"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="180" t="s">
@@ -22292,7 +23227,7 @@
       </c>
       <c r="C23" s="182">
         <f ca="1">C15*C22</f>
-        <v>5315921.46</v>
+        <v>5321102.67</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22319,15 +23254,15 @@
       </c>
       <c r="C26" s="183">
         <f ca="1">C23+C25-C24</f>
-        <v>3900175.46</v>
+        <v>3905356.67</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="263" t="s">
+      <c r="B28" s="264" t="s">
         <v>227</v>
       </c>
-      <c r="C28" s="264"/>
+      <c r="C28" s="265"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="180" t="s">
@@ -22402,18 +23337,18 @@
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C39" s="257" t="s">
+      <c r="C39" s="260" t="s">
         <v>270</v>
       </c>
-      <c r="D39" s="257"/>
-      <c r="E39" s="257"/>
-      <c r="F39" s="257"/>
-      <c r="G39" s="257"/>
-      <c r="H39" s="257"/>
-      <c r="I39" s="257"/>
-      <c r="J39" s="257"/>
-      <c r="K39" s="257"/>
-      <c r="L39" s="257"/>
+      <c r="D39" s="260"/>
+      <c r="E39" s="260"/>
+      <c r="F39" s="260"/>
+      <c r="G39" s="260"/>
+      <c r="H39" s="260"/>
+      <c r="I39" s="260"/>
+      <c r="J39" s="260"/>
+      <c r="K39" s="260"/>
+      <c r="L39" s="260"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="12">
@@ -22845,17 +23780,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -24479,6 +25414,8 @@
         <f>Q25/Q$85</f>
         <v>0.52</v>
       </c>
+      <c r="R26" s="1"/>
+      <c r="S26" s="1"/>
       <c r="T26" s="66">
         <f t="shared" ref="T26:AA26" si="17">T25/T$85</f>
         <v>-0.15</v>
@@ -29466,7 +30403,7 @@
       <c r="AA116" s="68"/>
       <c r="AC116" s="63">
         <f ca="1">Overview!C5</f>
-        <v>10.26</v>
+        <v>10.27</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -29513,7 +30450,7 @@
       <c r="AA117" s="68"/>
       <c r="AC117" s="65">
         <f ca="1">AC116/AC85</f>
-        <v>10.26</v>
+        <v>10.27</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -30819,7 +31756,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>17.099999999999998</v>
+        <v>17.116666666666664</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -30856,7 +31793,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>3.305290537752716</v>
+        <v>3.3085120684912663</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -30893,7 +31830,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="72">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>2.7934940789767544</v>
+        <v>2.7962167827574334</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -30930,7 +31867,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="164">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>5359362.3</v>
+        <v>5364585.8499999996</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -30967,7 +31904,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="164">
         <f ca="1">AC153+AC108-AC107+AC48+AC45</f>
-        <v>3943616.3</v>
+        <v>3948839.8499999996</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -31004,7 +31941,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="204">
         <f ca="1">AC154/AC5</f>
-        <v>2.3581567633182443</v>
+        <v>2.3612802796098853</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -31041,7 +31978,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="204">
         <f ca="1">AC154/AC12</f>
-        <v>38.98433456242153</v>
+        <v>39.035971589280237</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -31176,7 +32113,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="72">
         <f t="shared" ref="AC159:AC160" ca="1" si="101">AC153/AC157</f>
-        <v>49.804034049196623</v>
+        <v>49.852575992714364</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -31213,7 +32150,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
         <f t="shared" ca="1" si="101"/>
-        <v>-72.713493131741487</v>
+        <v>-72.809806398082415</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -31250,7 +32187,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="74">
         <f t="shared" ref="AC161" ca="1" si="104">AC157/AC153</f>
-        <v>2.0078694810388171E-2</v>
+        <v>2.0059143987787988E-2</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -31287,7 +32224,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f ca="1">AC26/AC117</f>
-        <v>5.8479532163742701E-2</v>
+        <v>5.8422590068159697E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31361,7 +32298,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="175">
         <f ca="1">-AC63/AC153</f>
-        <v>6.4442741629913702E-2</v>
+        <v>6.4379993098628491E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -31398,7 +32335,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="175">
         <f ca="1">-(AC63+AC64)/AC153</f>
-        <v>6.4442741629913702E-2</v>
+        <v>6.4379993098628491E-2</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -31901,7 +32838,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="175">
         <f ca="1">(AC107-AC108)/AC153</f>
-        <v>0.26416314493237375</v>
+        <v>0.26390592668024876</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -33406,15 +34343,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="248" t="s">
+      <c r="B4" s="252" t="s">
         <v>282</v>
       </c>
-      <c r="C4" s="248"/>
-      <c r="E4" s="248" t="s">
+      <c r="C4" s="252"/>
+      <c r="E4" s="252" t="s">
         <v>289</v>
       </c>
-      <c r="F4" s="248"/>
-      <c r="G4" s="248"/>
+      <c r="F4" s="252"/>
+      <c r="G4" s="252"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -33422,7 +34359,7 @@
       </c>
       <c r="C5" s="193">
         <f ca="1">Overview!C5</f>
-        <v>10.26</v>
+        <v>10.27</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="153" t="s">
@@ -33438,7 +34375,7 @@
       </c>
       <c r="C6" s="194">
         <f ca="1">Statement!AC153</f>
-        <v>5359362.3</v>
+        <v>5364585.8499999996</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>20</v>
@@ -33458,7 +34395,7 @@
       </c>
       <c r="C7" s="194">
         <f ca="1">Statement!AC154</f>
-        <v>3943616.3</v>
+        <v>3948839.8499999996</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>32</v>
@@ -33478,7 +34415,7 @@
       </c>
       <c r="C8" s="195">
         <f ca="1">Statement!AC150</f>
-        <v>17.099999999999998</v>
+        <v>17.116666666666664</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>292</v>
@@ -33498,7 +34435,7 @@
       </c>
       <c r="C9" s="195">
         <f ca="1">Statement!AC151</f>
-        <v>3.305290537752716</v>
+        <v>3.3085120684912663</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>293</v>
@@ -33518,7 +34455,7 @@
       </c>
       <c r="C10" s="195">
         <f ca="1">Statement!AC152</f>
-        <v>2.7934940789767544</v>
+        <v>2.7962167827574334</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -33538,7 +34475,7 @@
       </c>
       <c r="C11" s="195">
         <f ca="1">Statement!AC155</f>
-        <v>2.3581567633182443</v>
+        <v>2.3612802796098853</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33547,18 +34484,18 @@
       </c>
       <c r="C12" s="195">
         <f ca="1">Statement!AC156</f>
-        <v>38.98433456242153</v>
+        <v>39.035971589280237</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="248" t="s">
+      <c r="B15" s="252" t="s">
         <v>78</v>
       </c>
-      <c r="C15" s="248"/>
-      <c r="E15" s="248" t="s">
+      <c r="C15" s="252"/>
+      <c r="E15" s="252" t="s">
         <v>295</v>
       </c>
-      <c r="F15" s="248"/>
+      <c r="F15" s="252"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -33609,14 +34546,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="248" t="s">
+      <c r="B21" s="252" t="s">
         <v>294</v>
       </c>
-      <c r="C21" s="248"/>
-      <c r="E21" s="248" t="s">
+      <c r="C21" s="252"/>
+      <c r="E21" s="252" t="s">
         <v>298</v>
       </c>
-      <c r="F21" s="248"/>
+      <c r="F21" s="252"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -33685,14 +34622,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="248" t="s">
+      <c r="B29" s="252" t="s">
         <v>299</v>
       </c>
-      <c r="C29" s="248"/>
-      <c r="E29" s="248" t="s">
+      <c r="C29" s="252"/>
+      <c r="E29" s="252" t="s">
         <v>305</v>
       </c>
-      <c r="F29" s="248"/>
+      <c r="F29" s="252"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -33768,14 +34705,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="248" t="s">
+      <c r="B37" s="252" t="s">
         <v>317</v>
       </c>
-      <c r="C37" s="248"/>
-      <c r="E37" s="248" t="s">
+      <c r="C37" s="252"/>
+      <c r="E37" s="252" t="s">
         <v>320</v>
       </c>
-      <c r="F37" s="248"/>
+      <c r="F37" s="252"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -33783,7 +34720,7 @@
       </c>
       <c r="C38" s="196">
         <f ca="1">Statement!AC162</f>
-        <v>5.8479532163742701E-2</v>
+        <v>5.8422590068159697E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>319</v>
@@ -33799,7 +34736,7 @@
       </c>
       <c r="C39" s="236">
         <f ca="1">Statement!AC161</f>
-        <v>2.0078694810388171E-2</v>
+        <v>2.0059143987787988E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>321</v>
@@ -33831,7 +34768,7 @@
       </c>
       <c r="C41" s="196">
         <f ca="1">Statement!AC164</f>
-        <v>6.4442741629913702E-2</v>
+        <v>6.4379993098628491E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -33840,18 +34777,18 @@
       </c>
       <c r="C42" s="196">
         <f ca="1">Statement!AC165</f>
-        <v>6.4442741629913702E-2</v>
+        <v>6.4379993098628491E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="248" t="s">
+      <c r="B45" s="252" t="s">
         <v>328</v>
       </c>
-      <c r="C45" s="248"/>
-      <c r="E45" s="248" t="s">
+      <c r="C45" s="252"/>
+      <c r="E45" s="252" t="s">
         <v>334</v>
       </c>
-      <c r="F45" s="248"/>
+      <c r="F45" s="252"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -33884,18 +34821,18 @@
       </c>
       <c r="F48" s="196">
         <f ca="1">Statement!AC176</f>
-        <v>0.26416314493237375</v>
+        <v>0.26390592668024876</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="248" t="s">
+      <c r="B51" s="252" t="s">
         <v>331</v>
       </c>
-      <c r="C51" s="248"/>
-      <c r="E51" s="248" t="s">
+      <c r="C51" s="252"/>
+      <c r="E51" s="252" t="s">
         <v>352</v>
       </c>
-      <c r="F51" s="248"/>
+      <c r="F51" s="252"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -34063,7 +35000,7 @@
       </c>
       <c r="I6" s="193">
         <f ca="1">Statement!AC116</f>
-        <v>10.26</v>
+        <v>10.27</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -34092,7 +35029,7 @@
       </c>
       <c r="I7" s="194">
         <f ca="1">Statement!AC153</f>
-        <v>5359362.3</v>
+        <v>5364585.8499999996</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -34121,7 +35058,7 @@
       </c>
       <c r="I8" s="194">
         <f ca="1">Statement!AC154</f>
-        <v>3943616.3</v>
+        <v>3948839.8499999996</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -34150,7 +35087,7 @@
       </c>
       <c r="I9" s="195">
         <f ca="1">Statement!AC150</f>
-        <v>17.099999999999998</v>
+        <v>17.116666666666664</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -34179,7 +35116,7 @@
       </c>
       <c r="I10" s="195">
         <f ca="1">Statement!AC151</f>
-        <v>3.305290537752716</v>
+        <v>3.3085120684912663</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -34208,7 +35145,7 @@
       </c>
       <c r="I11" s="195">
         <f ca="1">Statement!AC152</f>
-        <v>2.7934940789767544</v>
+        <v>2.7962167827574334</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -34237,7 +35174,7 @@
       </c>
       <c r="I12" s="195">
         <f ca="1">Statement!AC155</f>
-        <v>2.3581567633182443</v>
+        <v>2.3612802796098853</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -34266,7 +35203,7 @@
       </c>
       <c r="I13" s="195">
         <f ca="1">Statement!AC156</f>
-        <v>38.98433456242153</v>
+        <v>39.035971589280237</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35039,7 +35976,7 @@
       </c>
       <c r="I51" s="196">
         <f ca="1">Statement!AC162</f>
-        <v>5.8479532163742701E-2</v>
+        <v>5.8422590068159697E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -35068,7 +36005,7 @@
       </c>
       <c r="I52" s="196">
         <f ca="1">Statement!AC161</f>
-        <v>2.0078694810388171E-2</v>
+        <v>2.0059143987787988E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -35126,7 +36063,7 @@
       </c>
       <c r="I54" s="196">
         <f ca="1">Statement!AC164</f>
-        <v>6.4442741629913702E-2</v>
+        <v>6.4379993098628491E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -35155,7 +36092,7 @@
       </c>
       <c r="I55" s="196">
         <f ca="1">Statement!AC165</f>
-        <v>6.4442741629913702E-2</v>
+        <v>6.4379993098628491E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35391,7 +36328,7 @@
       </c>
       <c r="I68" s="217">
         <f ca="1">Statement!AC176</f>
-        <v>0.26416314493237375</v>
+        <v>0.26390592668024876</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35877,14 +36814,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="252" t="s">
+      <c r="C3" s="255" t="s">
         <v>365</v>
       </c>
-      <c r="D3" s="253"/>
-      <c r="F3" s="254" t="s">
+      <c r="D3" s="256"/>
+      <c r="F3" s="257" t="s">
         <v>366</v>
       </c>
-      <c r="G3" s="253"/>
+      <c r="G3" s="256"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -35951,19 +36888,19 @@
       <c r="B7" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C7" s="255">
+      <c r="C7" s="253">
         <f>Statement!AA89</f>
         <v>-0.13037640275448081</v>
       </c>
-      <c r="D7" s="256"/>
-      <c r="F7" s="255">
+      <c r="D7" s="254"/>
+      <c r="F7" s="253">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.17317398716855847</v>
       </c>
-      <c r="G7" s="256"/>
+      <c r="G7" s="254"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="228" t="s">
@@ -35990,19 +36927,19 @@
       <c r="B9" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C9" s="255">
+      <c r="C9" s="253">
         <f>Statement!AA90</f>
         <v>4.0481504023804696E-2</v>
       </c>
-      <c r="D9" s="256"/>
-      <c r="F9" s="255">
+      <c r="D9" s="254"/>
+      <c r="F9" s="253">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.20469173309112548</v>
       </c>
-      <c r="G9" s="256"/>
+      <c r="G9" s="254"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="228" t="s">
@@ -36029,19 +36966,19 @@
       <c r="B11" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C11" s="255">
+      <c r="C11" s="253">
         <f>Statement!AA91</f>
         <v>-0.1614010786596328</v>
       </c>
-      <c r="D11" s="256"/>
-      <c r="F11" s="255">
+      <c r="D11" s="254"/>
+      <c r="F11" s="253">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.16629948047423376</v>
       </c>
-      <c r="G11" s="256"/>
+      <c r="G11" s="254"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="228" t="s">
@@ -36068,19 +37005,19 @@
       <c r="B13" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C13" s="255">
+      <c r="C13" s="253">
         <f>Statement!AA95</f>
         <v>-4.1051008608505718E-2</v>
       </c>
-      <c r="D13" s="256"/>
-      <c r="F13" s="255">
+      <c r="D13" s="254"/>
+      <c r="F13" s="253">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>1.3868988514743887E-2</v>
       </c>
-      <c r="G13" s="256"/>
+      <c r="G13" s="254"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="228" t="s">
@@ -36107,19 +37044,19 @@
       <c r="B15" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C15" s="255">
+      <c r="C15" s="253">
         <f>Statement!AA96</f>
         <v>-0.65140871384799337</v>
       </c>
-      <c r="D15" s="256"/>
-      <c r="F15" s="255">
+      <c r="D15" s="254"/>
+      <c r="F15" s="253">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>2.7052766268583963</v>
       </c>
-      <c r="G15" s="256"/>
+      <c r="G15" s="254"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="228" t="s">
@@ -36146,19 +37083,19 @@
       <c r="B17" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C17" s="255">
+      <c r="C17" s="253">
         <f>Statement!AA98</f>
         <v>-0.78437135034749483</v>
       </c>
-      <c r="D17" s="256"/>
-      <c r="F17" s="255">
+      <c r="D17" s="254"/>
+      <c r="F17" s="253">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>1.9986699179782754</v>
       </c>
-      <c r="G17" s="256"/>
+      <c r="G17" s="254"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="228" t="s">
@@ -36185,22 +37122,22 @@
       <c r="B19" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C19" s="255">
+      <c r="C19" s="253">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-3.2031015030699599E-2</v>
       </c>
-      <c r="D19" s="256"/>
-      <c r="F19" s="255">
+      <c r="D19" s="254"/>
+      <c r="F19" s="253">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-3.7620498458385526E-2</v>
       </c>
-      <c r="G19" s="256"/>
+      <c r="G19" s="254"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="228" t="s">
@@ -36227,22 +37164,22 @@
       <c r="B21" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C21" s="255">
+      <c r="C21" s="253">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>-0.78947368421052633</v>
       </c>
-      <c r="D21" s="256"/>
-      <c r="F21" s="255">
+      <c r="D21" s="254"/>
+      <c r="F21" s="253">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>2</v>
       </c>
-      <c r="G21" s="256"/>
+      <c r="G21" s="254"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -36290,22 +37227,22 @@
       <c r="B25" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C25" s="255">
+      <c r="C25" s="253">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>-0.30844727286201273</v>
       </c>
-      <c r="D25" s="256"/>
-      <c r="F25" s="255">
+      <c r="D25" s="254"/>
+      <c r="F25" s="253">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.16387602700216702</v>
       </c>
-      <c r="G25" s="256"/>
+      <c r="G25" s="254"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="s">
@@ -36332,22 +37269,22 @@
       <c r="B27" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C27" s="255">
+      <c r="C27" s="253">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>6.6472159310281692E-3</v>
       </c>
-      <c r="D27" s="256"/>
-      <c r="F27" s="255">
+      <c r="D27" s="254"/>
+      <c r="F27" s="253">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.16382654634312457</v>
       </c>
-      <c r="G27" s="256"/>
+      <c r="G27" s="254"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
@@ -36374,22 +37311,22 @@
       <c r="B29" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C29" s="255">
+      <c r="C29" s="253">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.15748031496062992</v>
       </c>
-      <c r="D29" s="256"/>
-      <c r="F29" s="255">
+      <c r="D29" s="254"/>
+      <c r="F29" s="253">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>0.46533756230176709</v>
       </c>
-      <c r="G29" s="256"/>
+      <c r="G29" s="254"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B31" s="8" t="s">
@@ -36437,22 +37374,22 @@
       <c r="B33" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C33" s="255">
+      <c r="C33" s="253">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>2.6257619832373135E-2</v>
       </c>
-      <c r="D33" s="256"/>
-      <c r="F33" s="255">
+      <c r="D33" s="254"/>
+      <c r="F33" s="253">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>0.12319376989075922</v>
       </c>
-      <c r="G33" s="256"/>
+      <c r="G33" s="254"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B34" s="20" t="s">
@@ -36479,25 +37416,43 @@
       <c r="B35" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C35" s="255">
+      <c r="C35" s="253">
         <f>IF(C34=0,
 IF(D34=0,0,IF(D34&gt;0,1,-1)),
 (D34-C34)/ABS(C34)
 )</f>
         <v>2.3001949317738791E-2</v>
       </c>
-      <c r="D35" s="256"/>
-      <c r="F35" s="255">
+      <c r="D35" s="254"/>
+      <c r="F35" s="253">
         <f>IF(F34=0,
 IF(G34=0,0,IF(G34&gt;0,1,-1)),
 (G34-F34)/ABS(F34)
 )</f>
         <v>0.10951374207188161</v>
       </c>
-      <c r="G35" s="256"/>
+      <c r="G35" s="254"/>
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="F33:G33"/>
     <mergeCell ref="C35:D35"/>
@@ -36508,24 +37463,6 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -36536,7 +37473,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E59D4CD5-3D15-DF4B-A135-ED758F2E1A8D}">
-  <dimension ref="B55:L70"/>
+  <dimension ref="B55:L73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
@@ -37258,6 +38195,141 @@
       <c r="L70" s="239">
         <f>Statement!Q140</f>
         <v>0.14438669993971168</v>
+      </c>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B71" s="20" t="s">
+        <v>411</v>
+      </c>
+      <c r="C71" s="248">
+        <f>Statement!H207</f>
+        <v>0</v>
+      </c>
+      <c r="D71" s="248">
+        <f>Statement!I207</f>
+        <v>0</v>
+      </c>
+      <c r="E71" s="248">
+        <f>Statement!J207</f>
+        <v>0</v>
+      </c>
+      <c r="F71" s="248">
+        <f>Statement!K207</f>
+        <v>0</v>
+      </c>
+      <c r="G71" s="248">
+        <f>Statement!L207</f>
+        <v>0</v>
+      </c>
+      <c r="H71" s="248">
+        <f>Statement!M207</f>
+        <v>100</v>
+      </c>
+      <c r="I71" s="248">
+        <f>Statement!N207</f>
+        <v>43.583607538139404</v>
+      </c>
+      <c r="J71" s="248">
+        <f>Statement!O207</f>
+        <v>71.343104995513016</v>
+      </c>
+      <c r="K71" s="248">
+        <f>Statement!P207</f>
+        <v>43.613520789709838</v>
+      </c>
+      <c r="L71" s="248">
+        <f>Statement!Q207</f>
+        <v>37.660783727191152</v>
+      </c>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B72" s="20" t="s">
+        <v>412</v>
+      </c>
+      <c r="C72" s="248">
+        <f>Statement!H208</f>
+        <v>0</v>
+      </c>
+      <c r="D72" s="248">
+        <f>Statement!I208</f>
+        <v>0</v>
+      </c>
+      <c r="E72" s="248">
+        <f>Statement!J208</f>
+        <v>0</v>
+      </c>
+      <c r="F72" s="248">
+        <f>Statement!K208</f>
+        <v>0</v>
+      </c>
+      <c r="G72" s="248">
+        <f>Statement!L208</f>
+        <v>0</v>
+      </c>
+      <c r="H72" s="248">
+        <f>Statement!M208</f>
+        <v>100</v>
+      </c>
+      <c r="I72" s="248">
+        <f>Statement!N208</f>
+        <v>118.64148245114609</v>
+      </c>
+      <c r="J72" s="248">
+        <f>Statement!O208</f>
+        <v>146.60342593796372</v>
+      </c>
+      <c r="K72" s="248">
+        <f>Statement!P208</f>
+        <v>160.23096613961079</v>
+      </c>
+      <c r="L72" s="248">
+        <f>Statement!Q208</f>
+        <v>180.50640402038886</v>
+      </c>
+    </row>
+    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B73" s="20" t="s">
+        <v>413</v>
+      </c>
+      <c r="C73" s="248">
+        <f>Statement!H209</f>
+        <v>0</v>
+      </c>
+      <c r="D73" s="248">
+        <f>Statement!I209</f>
+        <v>0</v>
+      </c>
+      <c r="E73" s="248">
+        <f>Statement!J209</f>
+        <v>0</v>
+      </c>
+      <c r="F73" s="248">
+        <f>Statement!K209</f>
+        <v>0</v>
+      </c>
+      <c r="G73" s="248">
+        <f>Statement!L209</f>
+        <v>0</v>
+      </c>
+      <c r="H73" s="248">
+        <f>Statement!M209</f>
+        <v>100</v>
+      </c>
+      <c r="I73" s="248">
+        <f>Statement!N209</f>
+        <v>148.27586206896552</v>
+      </c>
+      <c r="J73" s="248">
+        <f>Statement!O209</f>
+        <v>186.20689655172413</v>
+      </c>
+      <c r="K73" s="248">
+        <f>Statement!P209</f>
+        <v>188.79310344827584</v>
+      </c>
+      <c r="L73" s="248">
+        <f>Statement!Q209</f>
+        <v>244.82758620689654</v>
       </c>
     </row>
   </sheetData>

--- a/PATH.xlsx
+++ b/PATH.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F22103E5-2DEB-5A49-B213-CFD9B7F02E77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CA6BD3E-A04D-C748-89CE-9456D34D0E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="2" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -2376,6 +2376,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2383,15 +2386,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2403,10 +2397,10 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2416,6 +2410,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -12750,10 +12750,10 @@
     <v>19.84</v>
     <v>9.2002000000000006</v>
     <v>0.98270000000000002</v>
-    <v>0.04</v>
-    <v>3.9100000000000003E-3</v>
-    <v>-2.98E-2</v>
-    <v>-2.9020000000000001E-3</v>
+    <v>-0.12</v>
+    <v>-1.1685000000000001E-2</v>
+    <v>0.02</v>
+    <v>1.9689999999999998E-3</v>
     <v>USD</v>
     <v>UiPath, Inc. is focused on agentic automation and orchestration, empowering enterprises to harness the full potential of AI agents to autonomously execute and optimize complex business processes. It is focused on building and managing automations, starting with computer vision technology and user interface automation in its initial robotic process automation offering. Its AI-powered UiPath Platform offers a robust set of capabilities that allows its customers to discover opportunities for automation, automate using a digital workforce that seamlessly collaborates with humans, and operate a mission-critical automation program at scale. It enables employees to quickly build automations for both existing and new processes and to automate a range of actions including logging into applications, moving folders, filling in forms, reading emails and others. Its platform allows users to design and combine UI automations, API integrations and AI-based document understanding in a single workflow.</v>
     <v>3981</v>
@@ -12761,25 +12761,25 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>One Vanderbilt Avenue, 60th Floor, NEW YORK, NY, 10017 US</v>
-    <v>10.36</v>
+    <v>10.52</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46191.999378865628</v>
+    <v>46195.970821087503</v>
     <v>0</v>
-    <v>9.8800000000000008</v>
-    <v>5321095481</v>
+    <v>10</v>
+    <v>5258921045</v>
     <v>UIPATH, INC.</v>
     <v>UIPATH, INC.</v>
-    <v>10.199999999999999</v>
-    <v>17.005500000000001</v>
-    <v>10.23</v>
+    <v>10.175000000000001</v>
+    <v>16.871700000000001</v>
     <v>10.27</v>
-    <v>10.2402</v>
+    <v>10.15</v>
+    <v>10.18</v>
     <v>518120300</v>
     <v>PATH</v>
     <v>UIPATH, INC. (XNYS:PATH)</v>
-    <v>45204618</v>
-    <v>46059779</v>
+    <v>51864958</v>
+    <v>46136980</v>
     <v>2015</v>
   </rv>
   <rv s="2">
@@ -12803,17 +12803,17 @@
     <v>Powered by Refinitiv</v>
     <v>46.87</v>
     <v>39.47</v>
-    <v>-0.12</v>
-    <v>-2.6889999999999996E-3</v>
+    <v>0.57999999999999996</v>
+    <v>1.3030999999999999E-2</v>
     <v>US</v>
-    <v>44.53</v>
+    <v>45.15</v>
     <v>Index</v>
     <v>3</v>
-    <v>44.2</v>
+    <v>44.81</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>44.53</v>
-    <v>44.63</v>
+    <v>44.95</v>
     <v>44.51</v>
+    <v>45.09</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -13035,9 +13035,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq</v>
+      <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Delayed 15 minutes</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -13614,18 +13614,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="249" t="s">
+      <c r="B2" s="250" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="250"/>
-      <c r="E2" s="249" t="s">
+      <c r="C2" s="251"/>
+      <c r="E2" s="250" t="s">
         <v>336</v>
       </c>
-      <c r="F2" s="250"/>
-      <c r="H2" s="249" t="s">
+      <c r="F2" s="251"/>
+      <c r="H2" s="250" t="s">
         <v>381</v>
       </c>
-      <c r="I2" s="250"/>
+      <c r="I2" s="251"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="206" t="s">
@@ -13640,7 +13640,7 @@
       </c>
       <c r="F3" s="208">
         <f ca="1">Statement!AC153</f>
-        <v>5364585.8499999996</v>
+        <v>5301903.25</v>
       </c>
       <c r="H3" s="206" t="str">
         <f>'AVG target price'!B5</f>
@@ -13664,7 +13664,7 @@
       </c>
       <c r="F4" s="209">
         <f ca="1">Statement!AC154</f>
-        <v>3948839.8499999996</v>
+        <v>3886157.25</v>
       </c>
       <c r="H4" s="206" t="str">
         <f>'AVG target price'!B6</f>
@@ -13681,12 +13681,12 @@
       </c>
       <c r="C5" s="229" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>10.27</v>
+        <v>10.15</v>
       </c>
       <c r="E5" s="206" t="s">
         <v>292</v>
       </c>
-      <c r="F5" s="210">
+      <c r="F5" s="211">
         <f>Statement!AC26</f>
         <v>0.60000000000000009</v>
       </c>
@@ -13705,14 +13705,14 @@
       </c>
       <c r="C6" s="229" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>10.2402</v>
+        <v>10.18</v>
       </c>
       <c r="E6" s="206" t="s">
         <v>286</v>
       </c>
       <c r="F6" s="211">
         <f ca="1">Statement!AC150</f>
-        <v>17.116666666666664</v>
+        <v>16.916666666666664</v>
       </c>
       <c r="H6" s="206" t="str">
         <f>'AVG target price'!B8</f>
@@ -13729,14 +13729,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>0.04</v>
+        <v>-0.12</v>
       </c>
       <c r="E7" s="207" t="s">
         <v>242</v>
       </c>
       <c r="F7" s="212">
         <f ca="1">Statement!AC151</f>
-        <v>3.3085120684912663</v>
+        <v>3.269853699628662</v>
       </c>
       <c r="H7" s="205" t="str">
         <f>'AVG target price'!B9</f>
@@ -13753,14 +13753,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-2.98E-2</v>
+        <v>0.02</v>
       </c>
       <c r="E8" s="206" t="s">
         <v>314</v>
       </c>
       <c r="F8" s="213">
         <f ca="1">Statement!AC161</f>
-        <v>2.0059143987787988E-2</v>
+        <v>2.0296296429022916E-2</v>
       </c>
       <c r="H8" s="205" t="str">
         <f>'AVG target price'!B11</f>
@@ -13768,7 +13768,7 @@
       </c>
       <c r="I8" s="234">
         <f ca="1">'AVG target price'!C11</f>
-        <v>0.12012566495838224</v>
+        <v>0.13336852996281623</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13777,14 +13777,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>3.9100000000000003E-3</v>
+        <v>-1.1685000000000001E-2</v>
       </c>
       <c r="E9" s="206" t="s">
         <v>337</v>
       </c>
       <c r="F9" s="213">
         <f ca="1">Statement!AC162</f>
-        <v>5.8422590068159697E-2</v>
+        <v>5.9113300492610842E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -13793,14 +13793,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-2.9020000000000001E-3</v>
+        <v>1.9689999999999998E-3</v>
       </c>
       <c r="E10" s="206" t="s">
         <v>342</v>
       </c>
       <c r="F10" s="213">
         <f ca="1">Statement!AC164</f>
-        <v>6.4379993098628491E-2</v>
+        <v>6.5141135874178774E-2</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -13857,7 +13857,7 @@
       </c>
       <c r="C14" s="231" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>46059779</v>
+        <v>46136980</v>
       </c>
       <c r="E14" s="207" t="s">
         <v>124</v>
@@ -13873,7 +13873,7 @@
       </c>
       <c r="F15" s="213">
         <f ca="1">Statement!AC176</f>
-        <v>0.26390592668024876</v>
+        <v>0.26702599674937488</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -13886,10 +13886,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="251" t="s">
+      <c r="B17" s="252" t="s">
         <v>103</v>
       </c>
-      <c r="C17" s="251"/>
+      <c r="C17" s="252"/>
       <c r="E17" s="205" t="s">
         <v>345</v>
       </c>
@@ -13962,14 +13962,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="251" t="s">
+      <c r="B25" s="252" t="s">
         <v>126</v>
       </c>
-      <c r="C25" s="251"/>
-      <c r="E25" s="249" t="s">
+      <c r="C25" s="252"/>
+      <c r="E25" s="250" t="s">
         <v>401</v>
       </c>
-      <c r="F25" s="250"/>
+      <c r="F25" s="251"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="205" t="s">
@@ -13983,7 +13983,7 @@
       </c>
       <c r="F26" s="240" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>44.51</v>
+        <v>45.09</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -13998,7 +13998,7 @@
       </c>
       <c r="F27" s="241">
         <f ca="1">F26/1000</f>
-        <v>4.4510000000000001E-2</v>
+        <v>4.5090000000000005E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14018,15 +14018,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="252" t="s">
+      <c r="B33" s="249" t="s">
         <v>391</v>
       </c>
-      <c r="C33" s="252"/>
-      <c r="D33" s="252"/>
-      <c r="E33" s="252"/>
-      <c r="F33" s="252"/>
-      <c r="G33" s="252"/>
-      <c r="H33" s="252"/>
+      <c r="C33" s="249"/>
+      <c r="D33" s="249"/>
+      <c r="E33" s="249"/>
+      <c r="F33" s="249"/>
+      <c r="G33" s="249"/>
+      <c r="H33" s="249"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -14045,24 +14045,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="252"/>
-      <c r="C39" s="252"/>
-      <c r="D39" s="252"/>
-      <c r="E39" s="252"/>
-      <c r="F39" s="252"/>
-      <c r="G39" s="252"/>
-      <c r="H39" s="252"/>
+      <c r="B39" s="249"/>
+      <c r="C39" s="249"/>
+      <c r="D39" s="249"/>
+      <c r="E39" s="249"/>
+      <c r="F39" s="249"/>
+      <c r="G39" s="249"/>
+      <c r="H39" s="249"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="252" t="s">
+      <c r="B42" s="249" t="s">
         <v>394</v>
       </c>
-      <c r="C42" s="252"/>
-      <c r="D42" s="252"/>
-      <c r="E42" s="252"/>
-      <c r="F42" s="252"/>
-      <c r="G42" s="252"/>
-      <c r="H42" s="252"/>
+      <c r="C42" s="249"/>
+      <c r="D42" s="249"/>
+      <c r="E42" s="249"/>
+      <c r="F42" s="249"/>
+      <c r="G42" s="249"/>
+      <c r="H42" s="249"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -14077,24 +14077,24 @@
       </c>
     </row>
     <row r="49" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="252"/>
-      <c r="C49" s="252"/>
-      <c r="D49" s="252"/>
-      <c r="E49" s="252"/>
-      <c r="F49" s="252"/>
-      <c r="G49" s="252"/>
-      <c r="H49" s="252"/>
+      <c r="B49" s="249"/>
+      <c r="C49" s="249"/>
+      <c r="D49" s="249"/>
+      <c r="E49" s="249"/>
+      <c r="F49" s="249"/>
+      <c r="G49" s="249"/>
+      <c r="H49" s="249"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B52" s="252" t="s">
+      <c r="B52" s="249" t="s">
         <v>128</v>
       </c>
-      <c r="C52" s="252"/>
-      <c r="D52" s="252"/>
-      <c r="E52" s="252"/>
-      <c r="F52" s="252"/>
-      <c r="G52" s="252"/>
-      <c r="H52" s="252"/>
+      <c r="C52" s="249"/>
+      <c r="D52" s="249"/>
+      <c r="E52" s="249"/>
+      <c r="F52" s="249"/>
+      <c r="G52" s="249"/>
+      <c r="H52" s="249"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B54" s="41" t="s">
@@ -14109,28 +14109,28 @@
       </c>
     </row>
     <row r="59" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="252"/>
-      <c r="C59" s="252"/>
-      <c r="D59" s="252"/>
-      <c r="E59" s="252"/>
-      <c r="F59" s="252"/>
-      <c r="G59" s="252"/>
-      <c r="H59" s="252"/>
+      <c r="B59" s="249"/>
+      <c r="C59" s="249"/>
+      <c r="D59" s="249"/>
+      <c r="E59" s="249"/>
+      <c r="F59" s="249"/>
+      <c r="G59" s="249"/>
+      <c r="H59" s="249"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="E25:F25"/>
     <mergeCell ref="B52:H52"/>
     <mergeCell ref="B59:H59"/>
     <mergeCell ref="B33:H33"/>
     <mergeCell ref="B39:H39"/>
     <mergeCell ref="B42:H42"/>
     <mergeCell ref="B49:H49"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="E25:F25"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -14200,36 +14200,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="252" t="s">
+      <c r="C2" s="249" t="s">
         <v>137</v>
       </c>
-      <c r="D2" s="252"/>
-      <c r="E2" s="252"/>
-      <c r="F2" s="252"/>
-      <c r="G2" s="258"/>
-      <c r="H2" s="259" t="s">
+      <c r="D2" s="249"/>
+      <c r="E2" s="249"/>
+      <c r="F2" s="249"/>
+      <c r="G2" s="261"/>
+      <c r="H2" s="262" t="s">
         <v>138</v>
       </c>
-      <c r="I2" s="252"/>
-      <c r="J2" s="252"/>
-      <c r="K2" s="252"/>
-      <c r="L2" s="252"/>
+      <c r="I2" s="249"/>
+      <c r="J2" s="249"/>
+      <c r="K2" s="249"/>
+      <c r="L2" s="249"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="252" t="s">
+      <c r="S2" s="249" t="s">
         <v>137</v>
       </c>
-      <c r="T2" s="252"/>
-      <c r="U2" s="252"/>
-      <c r="V2" s="252"/>
-      <c r="W2" s="252"/>
-      <c r="X2" s="252"/>
-      <c r="Y2" s="252"/>
-      <c r="Z2" s="252"/>
-      <c r="AA2" s="252" t="s">
+      <c r="T2" s="249"/>
+      <c r="U2" s="249"/>
+      <c r="V2" s="249"/>
+      <c r="W2" s="249"/>
+      <c r="X2" s="249"/>
+      <c r="Y2" s="249"/>
+      <c r="Z2" s="249"/>
+      <c r="AA2" s="249" t="s">
         <v>138</v>
       </c>
-      <c r="AB2" s="252"/>
-      <c r="AC2" s="252"/>
+      <c r="AB2" s="249"/>
+      <c r="AC2" s="249"/>
       <c r="AE2" s="87" t="s">
         <v>139</v>
       </c>
@@ -14240,32 +14240,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="260" t="s">
+      <c r="C4" s="258" t="s">
         <v>140</v>
       </c>
-      <c r="D4" s="260"/>
-      <c r="E4" s="260"/>
-      <c r="F4" s="260"/>
-      <c r="G4" s="260"/>
-      <c r="H4" s="260"/>
-      <c r="I4" s="260"/>
-      <c r="J4" s="260"/>
-      <c r="K4" s="260"/>
-      <c r="L4" s="260"/>
+      <c r="D4" s="258"/>
+      <c r="E4" s="258"/>
+      <c r="F4" s="258"/>
+      <c r="G4" s="258"/>
+      <c r="H4" s="258"/>
+      <c r="I4" s="258"/>
+      <c r="J4" s="258"/>
+      <c r="K4" s="258"/>
+      <c r="L4" s="258"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="261" t="s">
+      <c r="S4" s="259" t="s">
         <v>140</v>
       </c>
-      <c r="T4" s="262"/>
-      <c r="U4" s="262"/>
-      <c r="V4" s="262"/>
-      <c r="W4" s="262"/>
-      <c r="X4" s="262"/>
-      <c r="Y4" s="262"/>
-      <c r="Z4" s="262"/>
-      <c r="AA4" s="262"/>
-      <c r="AB4" s="262"/>
-      <c r="AC4" s="262"/>
+      <c r="T4" s="260"/>
+      <c r="U4" s="260"/>
+      <c r="V4" s="260"/>
+      <c r="W4" s="260"/>
+      <c r="X4" s="260"/>
+      <c r="Y4" s="260"/>
+      <c r="Z4" s="260"/>
+      <c r="AA4" s="260"/>
+      <c r="AB4" s="260"/>
+      <c r="AC4" s="260"/>
       <c r="AE4" s="89"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -14761,33 +14761,33 @@
       <c r="Q10" s="93"/>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C11" s="260" t="s">
+      <c r="C11" s="258" t="s">
         <v>146</v>
       </c>
-      <c r="D11" s="260"/>
-      <c r="E11" s="260"/>
-      <c r="F11" s="260"/>
-      <c r="G11" s="260"/>
-      <c r="H11" s="260"/>
-      <c r="I11" s="260"/>
-      <c r="J11" s="260"/>
-      <c r="K11" s="260"/>
-      <c r="L11" s="260"/>
+      <c r="D11" s="258"/>
+      <c r="E11" s="258"/>
+      <c r="F11" s="258"/>
+      <c r="G11" s="258"/>
+      <c r="H11" s="258"/>
+      <c r="I11" s="258"/>
+      <c r="J11" s="258"/>
+      <c r="K11" s="258"/>
+      <c r="L11" s="258"/>
       <c r="O11" s="5"/>
       <c r="Q11" s="93"/>
-      <c r="S11" s="261" t="s">
+      <c r="S11" s="259" t="s">
         <v>146</v>
       </c>
-      <c r="T11" s="262"/>
-      <c r="U11" s="262"/>
-      <c r="V11" s="262"/>
-      <c r="W11" s="262"/>
-      <c r="X11" s="262"/>
-      <c r="Y11" s="262"/>
-      <c r="Z11" s="262"/>
-      <c r="AA11" s="262"/>
-      <c r="AB11" s="262"/>
-      <c r="AC11" s="262"/>
+      <c r="T11" s="260"/>
+      <c r="U11" s="260"/>
+      <c r="V11" s="260"/>
+      <c r="W11" s="260"/>
+      <c r="X11" s="260"/>
+      <c r="Y11" s="260"/>
+      <c r="Z11" s="260"/>
+      <c r="AA11" s="260"/>
+      <c r="AB11" s="260"/>
+      <c r="AC11" s="260"/>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B12" s="16" t="s">
@@ -15228,33 +15228,33 @@
       <c r="Q18" s="93"/>
     </row>
     <row r="19" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C19" s="260" t="s">
+      <c r="C19" s="258" t="s">
         <v>148</v>
       </c>
-      <c r="D19" s="260"/>
-      <c r="E19" s="260"/>
-      <c r="F19" s="260"/>
-      <c r="G19" s="260"/>
-      <c r="H19" s="260"/>
-      <c r="I19" s="260"/>
-      <c r="J19" s="260"/>
-      <c r="K19" s="260"/>
-      <c r="L19" s="260"/>
+      <c r="D19" s="258"/>
+      <c r="E19" s="258"/>
+      <c r="F19" s="258"/>
+      <c r="G19" s="258"/>
+      <c r="H19" s="258"/>
+      <c r="I19" s="258"/>
+      <c r="J19" s="258"/>
+      <c r="K19" s="258"/>
+      <c r="L19" s="258"/>
       <c r="O19" s="5"/>
       <c r="Q19" s="93"/>
-      <c r="S19" s="261" t="s">
+      <c r="S19" s="259" t="s">
         <v>148</v>
       </c>
-      <c r="T19" s="262"/>
-      <c r="U19" s="262"/>
-      <c r="V19" s="262"/>
-      <c r="W19" s="262"/>
-      <c r="X19" s="262"/>
-      <c r="Y19" s="262"/>
-      <c r="Z19" s="262"/>
-      <c r="AA19" s="262"/>
-      <c r="AB19" s="262"/>
-      <c r="AC19" s="262"/>
+      <c r="T19" s="260"/>
+      <c r="U19" s="260"/>
+      <c r="V19" s="260"/>
+      <c r="W19" s="260"/>
+      <c r="X19" s="260"/>
+      <c r="Y19" s="260"/>
+      <c r="Z19" s="260"/>
+      <c r="AA19" s="260"/>
+      <c r="AB19" s="260"/>
+      <c r="AC19" s="260"/>
       <c r="AE19" s="89">
         <f>AE4</f>
         <v>0</v>
@@ -16072,32 +16072,32 @@
       <c r="O31" s="5"/>
     </row>
     <row r="32" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C32" s="260" t="s">
+      <c r="C32" s="258" t="s">
         <v>150</v>
       </c>
-      <c r="D32" s="260"/>
-      <c r="E32" s="260"/>
-      <c r="F32" s="260"/>
-      <c r="G32" s="260"/>
-      <c r="H32" s="260"/>
-      <c r="I32" s="260"/>
-      <c r="J32" s="260"/>
-      <c r="K32" s="260"/>
-      <c r="L32" s="260"/>
+      <c r="D32" s="258"/>
+      <c r="E32" s="258"/>
+      <c r="F32" s="258"/>
+      <c r="G32" s="258"/>
+      <c r="H32" s="258"/>
+      <c r="I32" s="258"/>
+      <c r="J32" s="258"/>
+      <c r="K32" s="258"/>
+      <c r="L32" s="258"/>
       <c r="O32" s="5"/>
-      <c r="S32" s="261" t="s">
+      <c r="S32" s="259" t="s">
         <v>150</v>
       </c>
-      <c r="T32" s="262"/>
-      <c r="U32" s="262"/>
-      <c r="V32" s="262"/>
-      <c r="W32" s="262"/>
-      <c r="X32" s="262"/>
-      <c r="Y32" s="262"/>
-      <c r="Z32" s="262"/>
-      <c r="AA32" s="262"/>
-      <c r="AB32" s="262"/>
-      <c r="AC32" s="262"/>
+      <c r="T32" s="260"/>
+      <c r="U32" s="260"/>
+      <c r="V32" s="260"/>
+      <c r="W32" s="260"/>
+      <c r="X32" s="260"/>
+      <c r="Y32" s="260"/>
+      <c r="Z32" s="260"/>
+      <c r="AA32" s="260"/>
+      <c r="AB32" s="260"/>
+      <c r="AC32" s="260"/>
     </row>
     <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B33" s="16" t="s">
@@ -16354,18 +16354,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="S11:AC11"/>
     <mergeCell ref="C19:L19"/>
     <mergeCell ref="S19:AC19"/>
     <mergeCell ref="C32:L32"/>
     <mergeCell ref="S32:AC32"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -16402,35 +16402,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="252" t="s">
+      <c r="C2" s="249" t="s">
         <v>137</v>
       </c>
-      <c r="D2" s="252"/>
-      <c r="E2" s="252"/>
-      <c r="F2" s="252"/>
-      <c r="G2" s="258"/>
-      <c r="H2" s="259" t="s">
+      <c r="D2" s="249"/>
+      <c r="E2" s="249"/>
+      <c r="F2" s="249"/>
+      <c r="G2" s="261"/>
+      <c r="H2" s="262" t="s">
         <v>138</v>
       </c>
-      <c r="I2" s="252"/>
-      <c r="J2" s="252"/>
-      <c r="K2" s="252"/>
-      <c r="L2" s="252"/>
-      <c r="P2" s="252" t="s">
+      <c r="I2" s="249"/>
+      <c r="J2" s="249"/>
+      <c r="K2" s="249"/>
+      <c r="L2" s="249"/>
+      <c r="P2" s="249" t="s">
         <v>137</v>
       </c>
-      <c r="Q2" s="252"/>
-      <c r="R2" s="252"/>
-      <c r="S2" s="252"/>
-      <c r="T2" s="252"/>
-      <c r="U2" s="252"/>
-      <c r="V2" s="252"/>
-      <c r="W2" s="252"/>
-      <c r="X2" s="252" t="s">
+      <c r="Q2" s="249"/>
+      <c r="R2" s="249"/>
+      <c r="S2" s="249"/>
+      <c r="T2" s="249"/>
+      <c r="U2" s="249"/>
+      <c r="V2" s="249"/>
+      <c r="W2" s="249"/>
+      <c r="X2" s="249" t="s">
         <v>138</v>
       </c>
-      <c r="Y2" s="252"/>
-      <c r="Z2" s="252"/>
+      <c r="Y2" s="249"/>
+      <c r="Z2" s="249"/>
       <c r="AB2" s="87" t="s">
         <v>139</v>
       </c>
@@ -16439,31 +16439,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="260" t="s">
+      <c r="C4" s="258" t="s">
         <v>140</v>
       </c>
-      <c r="D4" s="260"/>
-      <c r="E4" s="260"/>
-      <c r="F4" s="260"/>
-      <c r="G4" s="260"/>
-      <c r="H4" s="260"/>
-      <c r="I4" s="260"/>
-      <c r="J4" s="260"/>
-      <c r="K4" s="260"/>
-      <c r="L4" s="260"/>
-      <c r="P4" s="262" t="s">
+      <c r="D4" s="258"/>
+      <c r="E4" s="258"/>
+      <c r="F4" s="258"/>
+      <c r="G4" s="258"/>
+      <c r="H4" s="258"/>
+      <c r="I4" s="258"/>
+      <c r="J4" s="258"/>
+      <c r="K4" s="258"/>
+      <c r="L4" s="258"/>
+      <c r="P4" s="260" t="s">
         <v>140</v>
       </c>
-      <c r="Q4" s="262"/>
-      <c r="R4" s="262"/>
-      <c r="S4" s="262"/>
-      <c r="T4" s="262"/>
-      <c r="U4" s="262"/>
-      <c r="V4" s="262"/>
-      <c r="W4" s="262"/>
-      <c r="X4" s="262"/>
-      <c r="Y4" s="262"/>
-      <c r="Z4" s="262"/>
+      <c r="Q4" s="260"/>
+      <c r="R4" s="260"/>
+      <c r="S4" s="260"/>
+      <c r="T4" s="260"/>
+      <c r="U4" s="260"/>
+      <c r="V4" s="260"/>
+      <c r="W4" s="260"/>
+      <c r="X4" s="260"/>
+      <c r="Y4" s="260"/>
+      <c r="Z4" s="260"/>
       <c r="AB4" s="89"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -16658,32 +16658,32 @@
       <c r="N8" s="93"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="260" t="s">
+      <c r="C9" s="258" t="s">
         <v>166</v>
       </c>
-      <c r="D9" s="260"/>
-      <c r="E9" s="260"/>
-      <c r="F9" s="260"/>
-      <c r="G9" s="260"/>
-      <c r="H9" s="260"/>
-      <c r="I9" s="260"/>
-      <c r="J9" s="260"/>
-      <c r="K9" s="260"/>
-      <c r="L9" s="260"/>
+      <c r="D9" s="258"/>
+      <c r="E9" s="258"/>
+      <c r="F9" s="258"/>
+      <c r="G9" s="258"/>
+      <c r="H9" s="258"/>
+      <c r="I9" s="258"/>
+      <c r="J9" s="258"/>
+      <c r="K9" s="258"/>
+      <c r="L9" s="258"/>
       <c r="N9" s="93"/>
-      <c r="P9" s="262" t="s">
+      <c r="P9" s="260" t="s">
         <v>167</v>
       </c>
-      <c r="Q9" s="262"/>
-      <c r="R9" s="262"/>
-      <c r="S9" s="262"/>
-      <c r="T9" s="262"/>
-      <c r="U9" s="262"/>
-      <c r="V9" s="262"/>
-      <c r="W9" s="262"/>
-      <c r="X9" s="262"/>
-      <c r="Y9" s="262"/>
-      <c r="Z9" s="262"/>
+      <c r="Q9" s="260"/>
+      <c r="R9" s="260"/>
+      <c r="S9" s="260"/>
+      <c r="T9" s="260"/>
+      <c r="U9" s="260"/>
+      <c r="V9" s="260"/>
+      <c r="W9" s="260"/>
+      <c r="X9" s="260"/>
+      <c r="Y9" s="260"/>
+      <c r="Z9" s="260"/>
       <c r="AB9" s="89">
         <f>AB4</f>
         <v>0</v>
@@ -17532,31 +17532,31 @@
       </c>
     </row>
     <row r="21" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="C21" s="260" t="s">
+      <c r="C21" s="258" t="s">
         <v>169</v>
       </c>
-      <c r="D21" s="260"/>
-      <c r="E21" s="260"/>
-      <c r="F21" s="260"/>
-      <c r="G21" s="260"/>
-      <c r="H21" s="260"/>
-      <c r="I21" s="260"/>
-      <c r="J21" s="260"/>
-      <c r="K21" s="260"/>
-      <c r="L21" s="260"/>
-      <c r="P21" s="262" t="s">
+      <c r="D21" s="258"/>
+      <c r="E21" s="258"/>
+      <c r="F21" s="258"/>
+      <c r="G21" s="258"/>
+      <c r="H21" s="258"/>
+      <c r="I21" s="258"/>
+      <c r="J21" s="258"/>
+      <c r="K21" s="258"/>
+      <c r="L21" s="258"/>
+      <c r="P21" s="260" t="s">
         <v>169</v>
       </c>
-      <c r="Q21" s="262"/>
-      <c r="R21" s="262"/>
-      <c r="S21" s="262"/>
-      <c r="T21" s="262"/>
-      <c r="U21" s="262"/>
-      <c r="V21" s="262"/>
-      <c r="W21" s="262"/>
-      <c r="X21" s="262"/>
-      <c r="Y21" s="262"/>
-      <c r="Z21" s="262"/>
+      <c r="Q21" s="260"/>
+      <c r="R21" s="260"/>
+      <c r="S21" s="260"/>
+      <c r="T21" s="260"/>
+      <c r="U21" s="260"/>
+      <c r="V21" s="260"/>
+      <c r="W21" s="260"/>
+      <c r="X21" s="260"/>
+      <c r="Y21" s="260"/>
+      <c r="Z21" s="260"/>
     </row>
     <row r="22" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B22" s="16" t="s">
@@ -18371,20 +18371,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="252" t="s">
+      <c r="C3" s="249" t="s">
         <v>137</v>
       </c>
-      <c r="D3" s="252"/>
-      <c r="E3" s="252"/>
-      <c r="F3" s="252"/>
-      <c r="G3" s="258"/>
-      <c r="H3" s="259" t="s">
+      <c r="D3" s="249"/>
+      <c r="E3" s="249"/>
+      <c r="F3" s="249"/>
+      <c r="G3" s="261"/>
+      <c r="H3" s="262" t="s">
         <v>138</v>
       </c>
-      <c r="I3" s="252"/>
-      <c r="J3" s="252"/>
-      <c r="K3" s="252"/>
-      <c r="L3" s="252"/>
+      <c r="I3" s="249"/>
+      <c r="J3" s="249"/>
+      <c r="K3" s="249"/>
+      <c r="L3" s="249"/>
       <c r="P3" s="263"/>
       <c r="Q3" s="263"/>
       <c r="R3" s="263"/>
@@ -18402,18 +18402,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="88"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="260" t="s">
+      <c r="C5" s="258" t="s">
         <v>140</v>
       </c>
-      <c r="D5" s="260"/>
-      <c r="E5" s="260"/>
-      <c r="F5" s="260"/>
-      <c r="G5" s="260"/>
-      <c r="H5" s="260"/>
-      <c r="I5" s="260"/>
-      <c r="J5" s="260"/>
-      <c r="K5" s="260"/>
-      <c r="L5" s="260"/>
+      <c r="D5" s="258"/>
+      <c r="E5" s="258"/>
+      <c r="F5" s="258"/>
+      <c r="G5" s="258"/>
+      <c r="H5" s="258"/>
+      <c r="I5" s="258"/>
+      <c r="J5" s="258"/>
+      <c r="K5" s="258"/>
+      <c r="L5" s="258"/>
       <c r="P5" s="263"/>
       <c r="Q5" s="263"/>
       <c r="R5" s="263"/>
@@ -18610,18 +18610,18 @@
       <c r="N10" s="93"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="260" t="s">
+      <c r="C11" s="258" t="s">
         <v>173</v>
       </c>
-      <c r="D11" s="260"/>
-      <c r="E11" s="260"/>
-      <c r="F11" s="260"/>
-      <c r="G11" s="260"/>
-      <c r="H11" s="260"/>
-      <c r="I11" s="260"/>
-      <c r="J11" s="260"/>
-      <c r="K11" s="260"/>
-      <c r="L11" s="260"/>
+      <c r="D11" s="258"/>
+      <c r="E11" s="258"/>
+      <c r="F11" s="258"/>
+      <c r="G11" s="258"/>
+      <c r="H11" s="258"/>
+      <c r="I11" s="258"/>
+      <c r="J11" s="258"/>
+      <c r="K11" s="258"/>
+      <c r="L11" s="258"/>
       <c r="N11" s="93"/>
       <c r="P11" s="263"/>
       <c r="Q11" s="263"/>
@@ -18875,18 +18875,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="260" t="s">
+      <c r="C18" s="258" t="s">
         <v>178</v>
       </c>
-      <c r="D18" s="260"/>
-      <c r="E18" s="260"/>
-      <c r="F18" s="260"/>
-      <c r="G18" s="260"/>
-      <c r="H18" s="260"/>
-      <c r="I18" s="260"/>
-      <c r="J18" s="260"/>
-      <c r="K18" s="260"/>
-      <c r="L18" s="260"/>
+      <c r="D18" s="258"/>
+      <c r="E18" s="258"/>
+      <c r="F18" s="258"/>
+      <c r="G18" s="258"/>
+      <c r="H18" s="258"/>
+      <c r="I18" s="258"/>
+      <c r="J18" s="258"/>
+      <c r="K18" s="258"/>
+      <c r="L18" s="258"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19104,18 +19104,18 @@
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="130"/>
-      <c r="C26" s="260" t="s">
+      <c r="C26" s="258" t="s">
         <v>184</v>
       </c>
-      <c r="D26" s="260"/>
-      <c r="E26" s="260"/>
-      <c r="F26" s="260"/>
-      <c r="G26" s="260"/>
-      <c r="H26" s="260"/>
-      <c r="I26" s="260"/>
-      <c r="J26" s="260"/>
-      <c r="K26" s="260"/>
-      <c r="L26" s="260"/>
+      <c r="D26" s="258"/>
+      <c r="E26" s="258"/>
+      <c r="F26" s="258"/>
+      <c r="G26" s="258"/>
+      <c r="H26" s="258"/>
+      <c r="I26" s="258"/>
+      <c r="J26" s="258"/>
+      <c r="K26" s="258"/>
+      <c r="L26" s="258"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -19307,18 +19307,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="130"/>
-      <c r="C33" s="260" t="s">
+      <c r="C33" s="258" t="s">
         <v>188</v>
       </c>
-      <c r="D33" s="260"/>
-      <c r="E33" s="260"/>
-      <c r="F33" s="260"/>
-      <c r="G33" s="260"/>
-      <c r="H33" s="260"/>
-      <c r="I33" s="260"/>
-      <c r="J33" s="260"/>
-      <c r="K33" s="260"/>
-      <c r="L33" s="260"/>
+      <c r="D33" s="258"/>
+      <c r="E33" s="258"/>
+      <c r="F33" s="258"/>
+      <c r="G33" s="258"/>
+      <c r="H33" s="258"/>
+      <c r="I33" s="258"/>
+      <c r="J33" s="258"/>
+      <c r="K33" s="258"/>
+      <c r="L33" s="258"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -19502,18 +19502,18 @@
       <c r="C39" s="146"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="260" t="s">
+      <c r="C40" s="258" t="s">
         <v>191</v>
       </c>
-      <c r="D40" s="260"/>
-      <c r="E40" s="260"/>
-      <c r="F40" s="260"/>
-      <c r="G40" s="260"/>
-      <c r="H40" s="260"/>
-      <c r="I40" s="260"/>
-      <c r="J40" s="260"/>
-      <c r="K40" s="260"/>
-      <c r="L40" s="260"/>
+      <c r="D40" s="258"/>
+      <c r="E40" s="258"/>
+      <c r="F40" s="258"/>
+      <c r="G40" s="258"/>
+      <c r="H40" s="258"/>
+      <c r="I40" s="258"/>
+      <c r="J40" s="258"/>
+      <c r="K40" s="258"/>
+      <c r="L40" s="258"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -19777,12 +19777,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -19790,6 +19784,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -19827,20 +19827,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="252" t="s">
+      <c r="C2" s="249" t="s">
         <v>137</v>
       </c>
-      <c r="D2" s="252"/>
-      <c r="E2" s="252"/>
-      <c r="F2" s="252"/>
-      <c r="G2" s="258"/>
-      <c r="H2" s="259" t="s">
+      <c r="D2" s="249"/>
+      <c r="E2" s="249"/>
+      <c r="F2" s="249"/>
+      <c r="G2" s="261"/>
+      <c r="H2" s="262" t="s">
         <v>138</v>
       </c>
-      <c r="I2" s="252"/>
-      <c r="J2" s="252"/>
-      <c r="K2" s="252"/>
-      <c r="L2" s="252"/>
+      <c r="I2" s="249"/>
+      <c r="J2" s="249"/>
+      <c r="K2" s="249"/>
+      <c r="L2" s="249"/>
       <c r="S2" s="263"/>
       <c r="T2" s="263"/>
       <c r="U2" s="263"/>
@@ -19858,18 +19858,18 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="260" t="s">
+      <c r="C4" s="258" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="260"/>
-      <c r="E4" s="260"/>
-      <c r="F4" s="260"/>
-      <c r="G4" s="260"/>
-      <c r="H4" s="260"/>
-      <c r="I4" s="260"/>
-      <c r="J4" s="260"/>
-      <c r="K4" s="260"/>
-      <c r="L4" s="260"/>
+      <c r="D4" s="258"/>
+      <c r="E4" s="258"/>
+      <c r="F4" s="258"/>
+      <c r="G4" s="258"/>
+      <c r="H4" s="258"/>
+      <c r="I4" s="258"/>
+      <c r="J4" s="258"/>
+      <c r="K4" s="258"/>
+      <c r="L4" s="258"/>
       <c r="S4" s="263"/>
       <c r="T4" s="263"/>
       <c r="U4" s="263"/>
@@ -20243,18 +20243,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="260" t="s">
+      <c r="C13" s="258" t="s">
         <v>199</v>
       </c>
-      <c r="D13" s="260"/>
-      <c r="E13" s="260"/>
-      <c r="F13" s="260"/>
-      <c r="G13" s="260"/>
-      <c r="H13" s="260"/>
-      <c r="I13" s="260"/>
-      <c r="J13" s="260"/>
-      <c r="K13" s="260"/>
-      <c r="L13" s="260"/>
+      <c r="D13" s="258"/>
+      <c r="E13" s="258"/>
+      <c r="F13" s="258"/>
+      <c r="G13" s="258"/>
+      <c r="H13" s="258"/>
+      <c r="I13" s="258"/>
+      <c r="J13" s="258"/>
+      <c r="K13" s="258"/>
+      <c r="L13" s="258"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -20347,18 +20347,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="260" t="s">
+      <c r="C18" s="258" t="s">
         <v>200</v>
       </c>
-      <c r="D18" s="260"/>
-      <c r="E18" s="260"/>
-      <c r="F18" s="260"/>
-      <c r="G18" s="260"/>
-      <c r="H18" s="260"/>
-      <c r="I18" s="260"/>
-      <c r="J18" s="260"/>
-      <c r="K18" s="260"/>
-      <c r="L18" s="260"/>
+      <c r="D18" s="258"/>
+      <c r="E18" s="258"/>
+      <c r="F18" s="258"/>
+      <c r="G18" s="258"/>
+      <c r="H18" s="258"/>
+      <c r="I18" s="258"/>
+      <c r="J18" s="258"/>
+      <c r="K18" s="258"/>
+      <c r="L18" s="258"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -20550,18 +20550,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="260" t="s">
+      <c r="C25" s="258" t="s">
         <v>311</v>
       </c>
-      <c r="D25" s="260"/>
-      <c r="E25" s="260"/>
-      <c r="F25" s="260"/>
-      <c r="G25" s="260"/>
-      <c r="H25" s="260"/>
-      <c r="I25" s="260"/>
-      <c r="J25" s="260"/>
-      <c r="K25" s="260"/>
-      <c r="L25" s="260"/>
+      <c r="D25" s="258"/>
+      <c r="E25" s="258"/>
+      <c r="F25" s="258"/>
+      <c r="G25" s="258"/>
+      <c r="H25" s="258"/>
+      <c r="I25" s="258"/>
+      <c r="J25" s="258"/>
+      <c r="K25" s="258"/>
+      <c r="L25" s="258"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -20699,18 +20699,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="260" t="s">
+      <c r="C31" s="258" t="s">
         <v>78</v>
       </c>
-      <c r="D31" s="260"/>
-      <c r="E31" s="260"/>
-      <c r="F31" s="260"/>
-      <c r="G31" s="260"/>
-      <c r="H31" s="260"/>
-      <c r="I31" s="260"/>
-      <c r="J31" s="260"/>
-      <c r="K31" s="260"/>
-      <c r="L31" s="260"/>
+      <c r="D31" s="258"/>
+      <c r="E31" s="258"/>
+      <c r="F31" s="258"/>
+      <c r="G31" s="258"/>
+      <c r="H31" s="258"/>
+      <c r="I31" s="258"/>
+      <c r="J31" s="258"/>
+      <c r="K31" s="258"/>
+      <c r="L31" s="258"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -20849,16 +20849,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -20921,10 +20921,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="252" t="s">
+      <c r="B4" s="249" t="s">
         <v>207</v>
       </c>
-      <c r="C4" s="252"/>
+      <c r="C4" s="249"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -20941,7 +20941,7 @@
       </c>
       <c r="C6" s="154">
         <f ca="1">Overview!C5</f>
-        <v>10.27</v>
+        <v>10.15</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20950,7 +20950,7 @@
       </c>
       <c r="C7" s="155">
         <f ca="1">C5*C6</f>
-        <v>5364585.8499999996</v>
+        <v>5301903.25</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20968,7 +20968,7 @@
       </c>
       <c r="C9" s="156">
         <f ca="1">Overview!F27</f>
-        <v>4.4510000000000001E-2</v>
+        <v>4.5090000000000005E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21009,10 +21009,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="252" t="s">
+      <c r="B15" s="249" t="s">
         <v>214</v>
       </c>
-      <c r="C15" s="252"/>
+      <c r="C15" s="249"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -21047,7 +21047,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>8.8731499999999991E-2</v>
+        <v>8.9311500000000002E-2</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21056,7 +21056,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>8.8731499999999991E-2</v>
+        <v>8.9311500000000002E-2</v>
       </c>
     </row>
   </sheetData>
@@ -21101,20 +21101,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="252" t="s">
+      <c r="C3" s="249" t="s">
         <v>137</v>
       </c>
-      <c r="D3" s="252"/>
-      <c r="E3" s="252"/>
-      <c r="F3" s="252"/>
-      <c r="G3" s="258"/>
-      <c r="H3" s="259" t="s">
+      <c r="D3" s="249"/>
+      <c r="E3" s="249"/>
+      <c r="F3" s="249"/>
+      <c r="G3" s="261"/>
+      <c r="H3" s="262" t="s">
         <v>138</v>
       </c>
-      <c r="I3" s="252"/>
-      <c r="J3" s="252"/>
-      <c r="K3" s="252"/>
-      <c r="L3" s="252"/>
+      <c r="I3" s="249"/>
+      <c r="J3" s="249"/>
+      <c r="K3" s="249"/>
+      <c r="L3" s="249"/>
       <c r="P3" s="263"/>
       <c r="Q3" s="263"/>
       <c r="R3" s="263"/>
@@ -21132,18 +21132,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="88"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="260" t="s">
+      <c r="C5" s="258" t="s">
         <v>221</v>
       </c>
-      <c r="D5" s="260"/>
-      <c r="E5" s="260"/>
-      <c r="F5" s="260"/>
-      <c r="G5" s="260"/>
-      <c r="H5" s="260"/>
-      <c r="I5" s="260"/>
-      <c r="J5" s="260"/>
-      <c r="K5" s="260"/>
-      <c r="L5" s="260"/>
+      <c r="D5" s="258"/>
+      <c r="E5" s="258"/>
+      <c r="F5" s="258"/>
+      <c r="G5" s="258"/>
+      <c r="H5" s="258"/>
+      <c r="I5" s="258"/>
+      <c r="J5" s="258"/>
+      <c r="K5" s="258"/>
+      <c r="L5" s="258"/>
       <c r="P5" s="263"/>
       <c r="Q5" s="263"/>
       <c r="R5" s="263"/>
@@ -21400,10 +21400,10 @@
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="252" t="s">
+      <c r="B13" s="249" t="s">
         <v>225</v>
       </c>
-      <c r="C13" s="252"/>
+      <c r="C13" s="249"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -21423,10 +21423,10 @@
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="252" t="s">
+      <c r="B18" s="249" t="s">
         <v>227</v>
       </c>
-      <c r="C18" s="252"/>
+      <c r="C18" s="249"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -21540,37 +21540,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="252" t="s">
+      <c r="C2" s="249" t="s">
         <v>137</v>
       </c>
-      <c r="D2" s="252"/>
-      <c r="E2" s="252"/>
-      <c r="F2" s="252"/>
-      <c r="G2" s="258"/>
-      <c r="H2" s="259" t="s">
+      <c r="D2" s="249"/>
+      <c r="E2" s="249"/>
+      <c r="F2" s="249"/>
+      <c r="G2" s="261"/>
+      <c r="H2" s="262" t="s">
         <v>138</v>
       </c>
-      <c r="I2" s="252"/>
-      <c r="J2" s="252"/>
-      <c r="K2" s="252"/>
-      <c r="L2" s="252"/>
+      <c r="I2" s="249"/>
+      <c r="J2" s="249"/>
+      <c r="K2" s="249"/>
+      <c r="L2" s="249"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="260" t="s">
+      <c r="C4" s="258" t="s">
         <v>235</v>
       </c>
-      <c r="D4" s="260"/>
-      <c r="E4" s="260"/>
-      <c r="F4" s="260"/>
-      <c r="G4" s="260"/>
-      <c r="H4" s="260"/>
-      <c r="I4" s="260"/>
-      <c r="J4" s="260"/>
-      <c r="K4" s="260"/>
-      <c r="L4" s="260"/>
+      <c r="D4" s="258"/>
+      <c r="E4" s="258"/>
+      <c r="F4" s="258"/>
+      <c r="G4" s="258"/>
+      <c r="H4" s="258"/>
+      <c r="I4" s="258"/>
+      <c r="J4" s="258"/>
+      <c r="K4" s="258"/>
+      <c r="L4" s="258"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -21759,18 +21759,18 @@
       <c r="N9" s="93"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C10" s="260" t="s">
+      <c r="C10" s="258" t="s">
         <v>146</v>
       </c>
-      <c r="D10" s="260"/>
-      <c r="E10" s="260"/>
-      <c r="F10" s="260"/>
-      <c r="G10" s="260"/>
-      <c r="H10" s="260"/>
-      <c r="I10" s="260"/>
-      <c r="J10" s="260"/>
-      <c r="K10" s="260"/>
-      <c r="L10" s="260"/>
+      <c r="D10" s="258"/>
+      <c r="E10" s="258"/>
+      <c r="F10" s="258"/>
+      <c r="G10" s="258"/>
+      <c r="H10" s="258"/>
+      <c r="I10" s="258"/>
+      <c r="J10" s="258"/>
+      <c r="K10" s="258"/>
+      <c r="L10" s="258"/>
       <c r="N10" s="93"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21964,18 +21964,18 @@
       <c r="N15" s="93"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C16" s="260" t="s">
+      <c r="C16" s="258" t="s">
         <v>237</v>
       </c>
-      <c r="D16" s="260"/>
-      <c r="E16" s="260"/>
-      <c r="F16" s="260"/>
-      <c r="G16" s="260"/>
-      <c r="H16" s="260"/>
-      <c r="I16" s="260"/>
-      <c r="J16" s="260"/>
-      <c r="K16" s="260"/>
-      <c r="L16" s="260"/>
+      <c r="D16" s="258"/>
+      <c r="E16" s="258"/>
+      <c r="F16" s="258"/>
+      <c r="G16" s="258"/>
+      <c r="H16" s="258"/>
+      <c r="I16" s="258"/>
+      <c r="J16" s="258"/>
+      <c r="K16" s="258"/>
+      <c r="L16" s="258"/>
       <c r="N16" s="93"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
@@ -22109,18 +22109,18 @@
       <c r="N20" s="93"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C21" s="260" t="s">
+      <c r="C21" s="258" t="s">
         <v>240</v>
       </c>
-      <c r="D21" s="260"/>
-      <c r="E21" s="260"/>
-      <c r="F21" s="260"/>
-      <c r="G21" s="260"/>
-      <c r="H21" s="260"/>
-      <c r="I21" s="260"/>
-      <c r="J21" s="260"/>
-      <c r="K21" s="260"/>
-      <c r="L21" s="260"/>
+      <c r="D21" s="258"/>
+      <c r="E21" s="258"/>
+      <c r="F21" s="258"/>
+      <c r="G21" s="258"/>
+      <c r="H21" s="258"/>
+      <c r="I21" s="258"/>
+      <c r="J21" s="258"/>
+      <c r="K21" s="258"/>
+      <c r="L21" s="258"/>
       <c r="N21" s="93"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
@@ -22204,18 +22204,18 @@
       <c r="N25" s="93"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C26" s="260" t="s">
+      <c r="C26" s="258" t="s">
         <v>241</v>
       </c>
-      <c r="D26" s="260"/>
-      <c r="E26" s="260"/>
-      <c r="F26" s="260"/>
-      <c r="G26" s="260"/>
-      <c r="H26" s="260"/>
-      <c r="I26" s="260"/>
-      <c r="J26" s="260"/>
-      <c r="K26" s="260"/>
-      <c r="L26" s="260"/>
+      <c r="D26" s="258"/>
+      <c r="E26" s="258"/>
+      <c r="F26" s="258"/>
+      <c r="G26" s="258"/>
+      <c r="H26" s="258"/>
+      <c r="I26" s="258"/>
+      <c r="J26" s="258"/>
+      <c r="K26" s="258"/>
+      <c r="L26" s="258"/>
       <c r="N26" s="93"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
@@ -22485,10 +22485,10 @@
       <c r="N36" s="93"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="252" t="s">
+      <c r="B37" s="249" t="s">
         <v>246</v>
       </c>
-      <c r="C37" s="252"/>
+      <c r="C37" s="249"/>
       <c r="N37" s="93"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -22563,10 +22563,10 @@
       </c>
     </row>
     <row r="47" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B47" s="252" t="s">
+      <c r="B47" s="249" t="s">
         <v>251</v>
       </c>
-      <c r="C47" s="252"/>
+      <c r="C47" s="249"/>
     </row>
     <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B48" s="1" t="s">
@@ -22622,10 +22622,10 @@
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B55" s="252" t="s">
+      <c r="B55" s="249" t="s">
         <v>375</v>
       </c>
-      <c r="C55" s="252"/>
+      <c r="C55" s="249"/>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B56" s="1" t="s">
@@ -22738,10 +22738,10 @@
       <c r="N3" s="93"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="252" t="s">
+      <c r="B4" s="249" t="s">
         <v>256</v>
       </c>
-      <c r="C4" s="252"/>
+      <c r="C4" s="249"/>
       <c r="N4" s="93"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -22795,7 +22795,7 @@
       </c>
       <c r="C10" s="154">
         <f ca="1">Overview!C5</f>
-        <v>10.27</v>
+        <v>10.15</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -22804,7 +22804,7 @@
       </c>
       <c r="C11" s="175">
         <f ca="1">(C9-C10)/C10</f>
-        <v>0.12012566495838224</v>
+        <v>0.13336852996281623</v>
       </c>
     </row>
   </sheetData>
@@ -22869,20 +22869,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="252" t="s">
+      <c r="C3" s="249" t="s">
         <v>137</v>
       </c>
-      <c r="D3" s="252"/>
-      <c r="E3" s="252"/>
-      <c r="F3" s="252"/>
-      <c r="G3" s="258"/>
-      <c r="H3" s="259" t="s">
+      <c r="D3" s="249"/>
+      <c r="E3" s="249"/>
+      <c r="F3" s="249"/>
+      <c r="G3" s="261"/>
+      <c r="H3" s="262" t="s">
         <v>138</v>
       </c>
-      <c r="I3" s="252"/>
-      <c r="J3" s="252"/>
-      <c r="K3" s="252"/>
-      <c r="L3" s="252"/>
+      <c r="I3" s="249"/>
+      <c r="J3" s="249"/>
+      <c r="K3" s="249"/>
+      <c r="L3" s="249"/>
       <c r="P3" s="263"/>
       <c r="Q3" s="263"/>
       <c r="R3" s="263"/>
@@ -22900,18 +22900,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="88"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="260" t="s">
+      <c r="C5" s="258" t="s">
         <v>221</v>
       </c>
-      <c r="D5" s="260"/>
-      <c r="E5" s="260"/>
-      <c r="F5" s="260"/>
-      <c r="G5" s="260"/>
-      <c r="H5" s="260"/>
-      <c r="I5" s="260"/>
-      <c r="J5" s="260"/>
-      <c r="K5" s="260"/>
-      <c r="L5" s="260"/>
+      <c r="D5" s="258"/>
+      <c r="E5" s="258"/>
+      <c r="F5" s="258"/>
+      <c r="G5" s="258"/>
+      <c r="H5" s="258"/>
+      <c r="I5" s="258"/>
+      <c r="J5" s="258"/>
+      <c r="K5" s="258"/>
+      <c r="L5" s="258"/>
       <c r="P5" s="263"/>
       <c r="Q5" s="263"/>
       <c r="R5" s="263"/>
@@ -23161,7 +23161,7 @@
       </c>
       <c r="C15" s="177">
         <f ca="1">Overview!C5</f>
-        <v>10.27</v>
+        <v>10.15</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -23227,7 +23227,7 @@
       </c>
       <c r="C23" s="182">
         <f ca="1">C15*C22</f>
-        <v>5321102.67</v>
+        <v>5258928.1500000004</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -23254,7 +23254,7 @@
       </c>
       <c r="C26" s="183">
         <f ca="1">C23+C25-C24</f>
-        <v>3905356.67</v>
+        <v>3843182.1500000004</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -23337,18 +23337,18 @@
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C39" s="260" t="s">
+      <c r="C39" s="258" t="s">
         <v>270</v>
       </c>
-      <c r="D39" s="260"/>
-      <c r="E39" s="260"/>
-      <c r="F39" s="260"/>
-      <c r="G39" s="260"/>
-      <c r="H39" s="260"/>
-      <c r="I39" s="260"/>
-      <c r="J39" s="260"/>
-      <c r="K39" s="260"/>
-      <c r="L39" s="260"/>
+      <c r="D39" s="258"/>
+      <c r="E39" s="258"/>
+      <c r="F39" s="258"/>
+      <c r="G39" s="258"/>
+      <c r="H39" s="258"/>
+      <c r="I39" s="258"/>
+      <c r="J39" s="258"/>
+      <c r="K39" s="258"/>
+      <c r="L39" s="258"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="12">
@@ -23780,17 +23780,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -30403,7 +30403,7 @@
       <c r="AA116" s="68"/>
       <c r="AC116" s="63">
         <f ca="1">Overview!C5</f>
-        <v>10.27</v>
+        <v>10.15</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -30450,7 +30450,7 @@
       <c r="AA117" s="68"/>
       <c r="AC117" s="65">
         <f ca="1">AC116/AC85</f>
-        <v>10.27</v>
+        <v>10.15</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -31756,7 +31756,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>17.116666666666664</v>
+        <v>16.916666666666664</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -31793,7 +31793,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>3.3085120684912663</v>
+        <v>3.269853699628662</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -31830,7 +31830,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="72">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>2.7962167827574334</v>
+        <v>2.7635443373892845</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -31867,7 +31867,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="164">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>5364585.8499999996</v>
+        <v>5301903.25</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -31904,7 +31904,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="164">
         <f ca="1">AC153+AC108-AC107+AC48+AC45</f>
-        <v>3948839.8499999996</v>
+        <v>3886157.25</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -31941,7 +31941,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="204">
         <f ca="1">AC154/AC5</f>
-        <v>2.3612802796098853</v>
+        <v>2.3237980841101935</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -31978,7 +31978,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="204">
         <f ca="1">AC154/AC12</f>
-        <v>39.035971589280237</v>
+        <v>38.416327266975749</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -32113,7 +32113,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="72">
         <f t="shared" ref="AC159:AC160" ca="1" si="101">AC153/AC157</f>
-        <v>49.852575992714364</v>
+        <v>49.270072670501541</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -32150,7 +32150,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
         <f t="shared" ca="1" si="101"/>
-        <v>-72.809806398082415</v>
+        <v>-71.654047201991332</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -32187,7 +32187,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="74">
         <f t="shared" ref="AC161" ca="1" si="104">AC157/AC153</f>
-        <v>2.0059143987787988E-2</v>
+        <v>2.0296296429022916E-2</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -32224,7 +32224,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f ca="1">AC26/AC117</f>
-        <v>5.8422590068159697E-2</v>
+        <v>5.9113300492610842E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -32298,7 +32298,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="175">
         <f ca="1">-AC63/AC153</f>
-        <v>6.4379993098628491E-2</v>
+        <v>6.5141135874178774E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -32335,7 +32335,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="175">
         <f ca="1">-(AC63+AC64)/AC153</f>
-        <v>6.4379993098628491E-2</v>
+        <v>6.5141135874178774E-2</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -32838,7 +32838,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="175">
         <f ca="1">(AC107-AC108)/AC153</f>
-        <v>0.26390592668024876</v>
+        <v>0.26702599674937488</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -34343,15 +34343,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="252" t="s">
+      <c r="B4" s="249" t="s">
         <v>282</v>
       </c>
-      <c r="C4" s="252"/>
-      <c r="E4" s="252" t="s">
+      <c r="C4" s="249"/>
+      <c r="E4" s="249" t="s">
         <v>289</v>
       </c>
-      <c r="F4" s="252"/>
-      <c r="G4" s="252"/>
+      <c r="F4" s="249"/>
+      <c r="G4" s="249"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -34359,7 +34359,7 @@
       </c>
       <c r="C5" s="193">
         <f ca="1">Overview!C5</f>
-        <v>10.27</v>
+        <v>10.15</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="153" t="s">
@@ -34375,7 +34375,7 @@
       </c>
       <c r="C6" s="194">
         <f ca="1">Statement!AC153</f>
-        <v>5364585.8499999996</v>
+        <v>5301903.25</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>20</v>
@@ -34395,7 +34395,7 @@
       </c>
       <c r="C7" s="194">
         <f ca="1">Statement!AC154</f>
-        <v>3948839.8499999996</v>
+        <v>3886157.25</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>32</v>
@@ -34415,7 +34415,7 @@
       </c>
       <c r="C8" s="195">
         <f ca="1">Statement!AC150</f>
-        <v>17.116666666666664</v>
+        <v>16.916666666666664</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>292</v>
@@ -34435,7 +34435,7 @@
       </c>
       <c r="C9" s="195">
         <f ca="1">Statement!AC151</f>
-        <v>3.3085120684912663</v>
+        <v>3.269853699628662</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>293</v>
@@ -34455,7 +34455,7 @@
       </c>
       <c r="C10" s="195">
         <f ca="1">Statement!AC152</f>
-        <v>2.7962167827574334</v>
+        <v>2.7635443373892845</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -34475,7 +34475,7 @@
       </c>
       <c r="C11" s="195">
         <f ca="1">Statement!AC155</f>
-        <v>2.3612802796098853</v>
+        <v>2.3237980841101935</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -34484,18 +34484,18 @@
       </c>
       <c r="C12" s="195">
         <f ca="1">Statement!AC156</f>
-        <v>39.035971589280237</v>
+        <v>38.416327266975749</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="252" t="s">
+      <c r="B15" s="249" t="s">
         <v>78</v>
       </c>
-      <c r="C15" s="252"/>
-      <c r="E15" s="252" t="s">
+      <c r="C15" s="249"/>
+      <c r="E15" s="249" t="s">
         <v>295</v>
       </c>
-      <c r="F15" s="252"/>
+      <c r="F15" s="249"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -34546,14 +34546,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="252" t="s">
+      <c r="B21" s="249" t="s">
         <v>294</v>
       </c>
-      <c r="C21" s="252"/>
-      <c r="E21" s="252" t="s">
+      <c r="C21" s="249"/>
+      <c r="E21" s="249" t="s">
         <v>298</v>
       </c>
-      <c r="F21" s="252"/>
+      <c r="F21" s="249"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -34622,14 +34622,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="252" t="s">
+      <c r="B29" s="249" t="s">
         <v>299</v>
       </c>
-      <c r="C29" s="252"/>
-      <c r="E29" s="252" t="s">
+      <c r="C29" s="249"/>
+      <c r="E29" s="249" t="s">
         <v>305</v>
       </c>
-      <c r="F29" s="252"/>
+      <c r="F29" s="249"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -34705,14 +34705,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="252" t="s">
+      <c r="B37" s="249" t="s">
         <v>317</v>
       </c>
-      <c r="C37" s="252"/>
-      <c r="E37" s="252" t="s">
+      <c r="C37" s="249"/>
+      <c r="E37" s="249" t="s">
         <v>320</v>
       </c>
-      <c r="F37" s="252"/>
+      <c r="F37" s="249"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -34720,7 +34720,7 @@
       </c>
       <c r="C38" s="196">
         <f ca="1">Statement!AC162</f>
-        <v>5.8422590068159697E-2</v>
+        <v>5.9113300492610842E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>319</v>
@@ -34736,7 +34736,7 @@
       </c>
       <c r="C39" s="236">
         <f ca="1">Statement!AC161</f>
-        <v>2.0059143987787988E-2</v>
+        <v>2.0296296429022916E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>321</v>
@@ -34768,7 +34768,7 @@
       </c>
       <c r="C41" s="196">
         <f ca="1">Statement!AC164</f>
-        <v>6.4379993098628491E-2</v>
+        <v>6.5141135874178774E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -34777,18 +34777,18 @@
       </c>
       <c r="C42" s="196">
         <f ca="1">Statement!AC165</f>
-        <v>6.4379993098628491E-2</v>
+        <v>6.5141135874178774E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="252" t="s">
+      <c r="B45" s="249" t="s">
         <v>328</v>
       </c>
-      <c r="C45" s="252"/>
-      <c r="E45" s="252" t="s">
+      <c r="C45" s="249"/>
+      <c r="E45" s="249" t="s">
         <v>334</v>
       </c>
-      <c r="F45" s="252"/>
+      <c r="F45" s="249"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -34821,18 +34821,18 @@
       </c>
       <c r="F48" s="196">
         <f ca="1">Statement!AC176</f>
-        <v>0.26390592668024876</v>
+        <v>0.26702599674937488</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="252" t="s">
+      <c r="B51" s="249" t="s">
         <v>331</v>
       </c>
-      <c r="C51" s="252"/>
-      <c r="E51" s="252" t="s">
+      <c r="C51" s="249"/>
+      <c r="E51" s="249" t="s">
         <v>352</v>
       </c>
-      <c r="F51" s="252"/>
+      <c r="F51" s="249"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -35000,7 +35000,7 @@
       </c>
       <c r="I6" s="193">
         <f ca="1">Statement!AC116</f>
-        <v>10.27</v>
+        <v>10.15</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -35029,7 +35029,7 @@
       </c>
       <c r="I7" s="194">
         <f ca="1">Statement!AC153</f>
-        <v>5364585.8499999996</v>
+        <v>5301903.25</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -35058,7 +35058,7 @@
       </c>
       <c r="I8" s="194">
         <f ca="1">Statement!AC154</f>
-        <v>3948839.8499999996</v>
+        <v>3886157.25</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -35087,7 +35087,7 @@
       </c>
       <c r="I9" s="195">
         <f ca="1">Statement!AC150</f>
-        <v>17.116666666666664</v>
+        <v>16.916666666666664</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -35116,7 +35116,7 @@
       </c>
       <c r="I10" s="195">
         <f ca="1">Statement!AC151</f>
-        <v>3.3085120684912663</v>
+        <v>3.269853699628662</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -35145,7 +35145,7 @@
       </c>
       <c r="I11" s="195">
         <f ca="1">Statement!AC152</f>
-        <v>2.7962167827574334</v>
+        <v>2.7635443373892845</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -35174,7 +35174,7 @@
       </c>
       <c r="I12" s="195">
         <f ca="1">Statement!AC155</f>
-        <v>2.3612802796098853</v>
+        <v>2.3237980841101935</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -35203,7 +35203,7 @@
       </c>
       <c r="I13" s="195">
         <f ca="1">Statement!AC156</f>
-        <v>39.035971589280237</v>
+        <v>38.416327266975749</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35976,7 +35976,7 @@
       </c>
       <c r="I51" s="196">
         <f ca="1">Statement!AC162</f>
-        <v>5.8422590068159697E-2</v>
+        <v>5.9113300492610842E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -36005,7 +36005,7 @@
       </c>
       <c r="I52" s="196">
         <f ca="1">Statement!AC161</f>
-        <v>2.0059143987787988E-2</v>
+        <v>2.0296296429022916E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -36063,7 +36063,7 @@
       </c>
       <c r="I54" s="196">
         <f ca="1">Statement!AC164</f>
-        <v>6.4379993098628491E-2</v>
+        <v>6.5141135874178774E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -36092,7 +36092,7 @@
       </c>
       <c r="I55" s="196">
         <f ca="1">Statement!AC165</f>
-        <v>6.4379993098628491E-2</v>
+        <v>6.5141135874178774E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36328,7 +36328,7 @@
       </c>
       <c r="I68" s="217">
         <f ca="1">Statement!AC176</f>
-        <v>0.26390592668024876</v>
+        <v>0.26702599674937488</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36814,14 +36814,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="255" t="s">
+      <c r="C3" s="253" t="s">
         <v>365</v>
       </c>
-      <c r="D3" s="256"/>
-      <c r="F3" s="257" t="s">
+      <c r="D3" s="254"/>
+      <c r="F3" s="255" t="s">
         <v>366</v>
       </c>
-      <c r="G3" s="256"/>
+      <c r="G3" s="254"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -36888,19 +36888,19 @@
       <c r="B7" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C7" s="253">
+      <c r="C7" s="256">
         <f>Statement!AA89</f>
         <v>-0.13037640275448081</v>
       </c>
-      <c r="D7" s="254"/>
-      <c r="F7" s="253">
+      <c r="D7" s="257"/>
+      <c r="F7" s="256">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.17317398716855847</v>
       </c>
-      <c r="G7" s="254"/>
+      <c r="G7" s="257"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="228" t="s">
@@ -36927,19 +36927,19 @@
       <c r="B9" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C9" s="253">
+      <c r="C9" s="256">
         <f>Statement!AA90</f>
         <v>4.0481504023804696E-2</v>
       </c>
-      <c r="D9" s="254"/>
-      <c r="F9" s="253">
+      <c r="D9" s="257"/>
+      <c r="F9" s="256">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.20469173309112548</v>
       </c>
-      <c r="G9" s="254"/>
+      <c r="G9" s="257"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="228" t="s">
@@ -36966,19 +36966,19 @@
       <c r="B11" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C11" s="253">
+      <c r="C11" s="256">
         <f>Statement!AA91</f>
         <v>-0.1614010786596328</v>
       </c>
-      <c r="D11" s="254"/>
-      <c r="F11" s="253">
+      <c r="D11" s="257"/>
+      <c r="F11" s="256">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.16629948047423376</v>
       </c>
-      <c r="G11" s="254"/>
+      <c r="G11" s="257"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="228" t="s">
@@ -37005,19 +37005,19 @@
       <c r="B13" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C13" s="253">
+      <c r="C13" s="256">
         <f>Statement!AA95</f>
         <v>-4.1051008608505718E-2</v>
       </c>
-      <c r="D13" s="254"/>
-      <c r="F13" s="253">
+      <c r="D13" s="257"/>
+      <c r="F13" s="256">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>1.3868988514743887E-2</v>
       </c>
-      <c r="G13" s="254"/>
+      <c r="G13" s="257"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="228" t="s">
@@ -37044,19 +37044,19 @@
       <c r="B15" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C15" s="253">
+      <c r="C15" s="256">
         <f>Statement!AA96</f>
         <v>-0.65140871384799337</v>
       </c>
-      <c r="D15" s="254"/>
-      <c r="F15" s="253">
+      <c r="D15" s="257"/>
+      <c r="F15" s="256">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>2.7052766268583963</v>
       </c>
-      <c r="G15" s="254"/>
+      <c r="G15" s="257"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="228" t="s">
@@ -37083,19 +37083,19 @@
       <c r="B17" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C17" s="253">
+      <c r="C17" s="256">
         <f>Statement!AA98</f>
         <v>-0.78437135034749483</v>
       </c>
-      <c r="D17" s="254"/>
-      <c r="F17" s="253">
+      <c r="D17" s="257"/>
+      <c r="F17" s="256">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>1.9986699179782754</v>
       </c>
-      <c r="G17" s="254"/>
+      <c r="G17" s="257"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="228" t="s">
@@ -37122,22 +37122,22 @@
       <c r="B19" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C19" s="253">
+      <c r="C19" s="256">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-3.2031015030699599E-2</v>
       </c>
-      <c r="D19" s="254"/>
-      <c r="F19" s="253">
+      <c r="D19" s="257"/>
+      <c r="F19" s="256">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-3.7620498458385526E-2</v>
       </c>
-      <c r="G19" s="254"/>
+      <c r="G19" s="257"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="228" t="s">
@@ -37164,22 +37164,22 @@
       <c r="B21" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C21" s="253">
+      <c r="C21" s="256">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>-0.78947368421052633</v>
       </c>
-      <c r="D21" s="254"/>
-      <c r="F21" s="253">
+      <c r="D21" s="257"/>
+      <c r="F21" s="256">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>2</v>
       </c>
-      <c r="G21" s="254"/>
+      <c r="G21" s="257"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -37227,22 +37227,22 @@
       <c r="B25" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C25" s="253">
+      <c r="C25" s="256">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>-0.30844727286201273</v>
       </c>
-      <c r="D25" s="254"/>
-      <c r="F25" s="253">
+      <c r="D25" s="257"/>
+      <c r="F25" s="256">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.16387602700216702</v>
       </c>
-      <c r="G25" s="254"/>
+      <c r="G25" s="257"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="s">
@@ -37269,22 +37269,22 @@
       <c r="B27" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C27" s="253">
+      <c r="C27" s="256">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>6.6472159310281692E-3</v>
       </c>
-      <c r="D27" s="254"/>
-      <c r="F27" s="253">
+      <c r="D27" s="257"/>
+      <c r="F27" s="256">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.16382654634312457</v>
       </c>
-      <c r="G27" s="254"/>
+      <c r="G27" s="257"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
@@ -37311,22 +37311,22 @@
       <c r="B29" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C29" s="253">
+      <c r="C29" s="256">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.15748031496062992</v>
       </c>
-      <c r="D29" s="254"/>
-      <c r="F29" s="253">
+      <c r="D29" s="257"/>
+      <c r="F29" s="256">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>0.46533756230176709</v>
       </c>
-      <c r="G29" s="254"/>
+      <c r="G29" s="257"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B31" s="8" t="s">
@@ -37374,22 +37374,22 @@
       <c r="B33" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C33" s="253">
+      <c r="C33" s="256">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>2.6257619832373135E-2</v>
       </c>
-      <c r="D33" s="254"/>
-      <c r="F33" s="253">
+      <c r="D33" s="257"/>
+      <c r="F33" s="256">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>0.12319376989075922</v>
       </c>
-      <c r="G33" s="254"/>
+      <c r="G33" s="257"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B34" s="20" t="s">
@@ -37416,43 +37416,25 @@
       <c r="B35" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C35" s="253">
+      <c r="C35" s="256">
         <f>IF(C34=0,
 IF(D34=0,0,IF(D34&gt;0,1,-1)),
 (D34-C34)/ABS(C34)
 )</f>
         <v>2.3001949317738791E-2</v>
       </c>
-      <c r="D35" s="254"/>
-      <c r="F35" s="253">
+      <c r="D35" s="257"/>
+      <c r="F35" s="256">
         <f>IF(F34=0,
 IF(G34=0,0,IF(G34&gt;0,1,-1)),
 (G34-F34)/ABS(F34)
 )</f>
         <v>0.10951374207188161</v>
       </c>
-      <c r="G35" s="254"/>
+      <c r="G35" s="257"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="F33:G33"/>
     <mergeCell ref="C35:D35"/>
@@ -37463,6 +37445,24 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/PATH.xlsx
+++ b/PATH.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CA6BD3E-A04D-C748-89CE-9456D34D0E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74269887-1599-534E-8EB3-6DC412C34B42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="2" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -2376,9 +2376,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2386,6 +2383,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2397,10 +2403,10 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2410,12 +2416,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -12749,11 +12749,11 @@
     <v>Powered by Refinitiv</v>
     <v>19.84</v>
     <v>9.2002000000000006</v>
-    <v>0.98270000000000002</v>
-    <v>-0.12</v>
-    <v>-1.1685000000000001E-2</v>
-    <v>0.02</v>
-    <v>1.9689999999999998E-3</v>
+    <v>0.98829999999999996</v>
+    <v>-0.375</v>
+    <v>-3.6372000000000002E-2</v>
+    <v>0.04</v>
+    <v>4.0280000000000003E-3</v>
     <v>USD</v>
     <v>UiPath, Inc. is focused on agentic automation and orchestration, empowering enterprises to harness the full potential of AI agents to autonomously execute and optimize complex business processes. It is focused on building and managing automations, starting with computer vision technology and user interface automation in its initial robotic process automation offering. Its AI-powered UiPath Platform offers a robust set of capabilities that allows its customers to discover opportunities for automation, automate using a digital workforce that seamlessly collaborates with humans, and operate a mission-critical automation program at scale. It enables employees to quickly build automations for both existing and new processes and to automate a range of actions including logging into applications, moving folders, filling in forms, reading emails and others. Its platform allows users to design and combine UI automations, API integrations and AI-based document understanding in a single workflow.</v>
     <v>3981</v>
@@ -12761,25 +12761,25 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>One Vanderbilt Avenue, 60th Floor, NEW YORK, NY, 10017 US</v>
-    <v>10.52</v>
+    <v>10.315</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46195.970821087503</v>
+    <v>46198.912302546094</v>
     <v>0</v>
-    <v>10</v>
-    <v>5258921045</v>
+    <v>9.91</v>
+    <v>5147525180</v>
     <v>UIPATH, INC.</v>
     <v>UIPATH, INC.</v>
-    <v>10.175000000000001</v>
-    <v>16.871700000000001</v>
-    <v>10.27</v>
-    <v>10.15</v>
-    <v>10.18</v>
+    <v>10.11</v>
+    <v>16.514299999999999</v>
+    <v>10.31</v>
+    <v>9.9350000000000005</v>
+    <v>9.9700000000000006</v>
     <v>518120300</v>
     <v>PATH</v>
     <v>UIPATH, INC. (XNYS:PATH)</v>
-    <v>51864958</v>
-    <v>46136980</v>
+    <v>50714464</v>
+    <v>49244198</v>
     <v>2015</v>
   </rv>
   <rv s="2">
@@ -12803,17 +12803,17 @@
     <v>Powered by Refinitiv</v>
     <v>46.87</v>
     <v>39.47</v>
-    <v>0.57999999999999996</v>
-    <v>1.3030999999999999E-2</v>
+    <v>-0.1</v>
+    <v>-2.2720000000000001E-3</v>
     <v>US</v>
-    <v>45.15</v>
+    <v>44.14</v>
     <v>Index</v>
     <v>3</v>
-    <v>44.81</v>
+    <v>43.63</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>44.95</v>
-    <v>44.51</v>
-    <v>45.09</v>
+    <v>44.12</v>
+    <v>44.02</v>
+    <v>43.92</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -13614,18 +13614,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="250" t="s">
+      <c r="B2" s="249" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="251"/>
-      <c r="E2" s="250" t="s">
+      <c r="C2" s="250"/>
+      <c r="E2" s="249" t="s">
         <v>336</v>
       </c>
-      <c r="F2" s="251"/>
-      <c r="H2" s="250" t="s">
+      <c r="F2" s="250"/>
+      <c r="H2" s="249" t="s">
         <v>381</v>
       </c>
-      <c r="I2" s="251"/>
+      <c r="I2" s="250"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="206" t="s">
@@ -13640,7 +13640,7 @@
       </c>
       <c r="F3" s="208">
         <f ca="1">Statement!AC153</f>
-        <v>5301903.25</v>
+        <v>5189596.9249999998</v>
       </c>
       <c r="H3" s="206" t="str">
         <f>'AVG target price'!B5</f>
@@ -13664,7 +13664,7 @@
       </c>
       <c r="F4" s="209">
         <f ca="1">Statement!AC154</f>
-        <v>3886157.25</v>
+        <v>3773850.9249999998</v>
       </c>
       <c r="H4" s="206" t="str">
         <f>'AVG target price'!B6</f>
@@ -13681,7 +13681,7 @@
       </c>
       <c r="C5" s="229" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>10.15</v>
+        <v>9.9350000000000005</v>
       </c>
       <c r="E5" s="206" t="s">
         <v>292</v>
@@ -13705,14 +13705,14 @@
       </c>
       <c r="C6" s="229" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>10.18</v>
+        <v>9.9700000000000006</v>
       </c>
       <c r="E6" s="206" t="s">
         <v>286</v>
       </c>
       <c r="F6" s="211">
         <f ca="1">Statement!AC150</f>
-        <v>16.916666666666664</v>
+        <v>16.55833333333333</v>
       </c>
       <c r="H6" s="206" t="str">
         <f>'AVG target price'!B8</f>
@@ -13729,14 +13729,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-0.12</v>
+        <v>-0.375</v>
       </c>
       <c r="E7" s="207" t="s">
         <v>242</v>
       </c>
       <c r="F7" s="212">
         <f ca="1">Statement!AC151</f>
-        <v>3.269853699628662</v>
+        <v>3.2005907887498282</v>
       </c>
       <c r="H7" s="205" t="str">
         <f>'AVG target price'!B9</f>
@@ -13753,14 +13753,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="E8" s="206" t="s">
         <v>314</v>
       </c>
       <c r="F8" s="213">
         <f ca="1">Statement!AC161</f>
-        <v>2.0296296429022916E-2</v>
+        <v>2.0735521766943394E-2</v>
       </c>
       <c r="H8" s="205" t="str">
         <f>'AVG target price'!B11</f>
@@ -13768,7 +13768,7 @@
       </c>
       <c r="I8" s="234">
         <f ca="1">'AVG target price'!C11</f>
-        <v>0.13336852996281623</v>
+        <v>0.15789537786840308</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13777,14 +13777,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-1.1685000000000001E-2</v>
+        <v>-3.6372000000000002E-2</v>
       </c>
       <c r="E9" s="206" t="s">
         <v>337</v>
       </c>
       <c r="F9" s="213">
         <f ca="1">Statement!AC162</f>
-        <v>5.9113300492610842E-2</v>
+        <v>6.0392551585304488E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -13793,14 +13793,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>1.9689999999999998E-3</v>
+        <v>4.0280000000000003E-3</v>
       </c>
       <c r="E10" s="206" t="s">
         <v>342</v>
       </c>
       <c r="F10" s="213">
         <f ca="1">Statement!AC164</f>
-        <v>6.5141135874178774E-2</v>
+        <v>6.6550833328929498E-2</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -13841,7 +13841,7 @@
       </c>
       <c r="C13" s="230" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>0.98270000000000002</v>
+        <v>0.98829999999999996</v>
       </c>
       <c r="E13" s="206" t="s">
         <v>123</v>
@@ -13857,7 +13857,7 @@
       </c>
       <c r="C14" s="231" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>46136980</v>
+        <v>49244198</v>
       </c>
       <c r="E14" s="207" t="s">
         <v>124</v>
@@ -13873,7 +13873,7 @@
       </c>
       <c r="F15" s="213">
         <f ca="1">Statement!AC176</f>
-        <v>0.26702599674937488</v>
+        <v>0.27280461670922546</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -13886,10 +13886,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="252" t="s">
+      <c r="B17" s="251" t="s">
         <v>103</v>
       </c>
-      <c r="C17" s="252"/>
+      <c r="C17" s="251"/>
       <c r="E17" s="205" t="s">
         <v>345</v>
       </c>
@@ -13962,14 +13962,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="252" t="s">
+      <c r="B25" s="251" t="s">
         <v>126</v>
       </c>
-      <c r="C25" s="252"/>
-      <c r="E25" s="250" t="s">
+      <c r="C25" s="251"/>
+      <c r="E25" s="249" t="s">
         <v>401</v>
       </c>
-      <c r="F25" s="251"/>
+      <c r="F25" s="250"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="205" t="s">
@@ -13983,7 +13983,7 @@
       </c>
       <c r="F26" s="240" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>45.09</v>
+        <v>43.92</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -13998,7 +13998,7 @@
       </c>
       <c r="F27" s="241">
         <f ca="1">F26/1000</f>
-        <v>4.5090000000000005E-2</v>
+        <v>4.3920000000000001E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14018,15 +14018,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="249" t="s">
+      <c r="B33" s="252" t="s">
         <v>391</v>
       </c>
-      <c r="C33" s="249"/>
-      <c r="D33" s="249"/>
-      <c r="E33" s="249"/>
-      <c r="F33" s="249"/>
-      <c r="G33" s="249"/>
-      <c r="H33" s="249"/>
+      <c r="C33" s="252"/>
+      <c r="D33" s="252"/>
+      <c r="E33" s="252"/>
+      <c r="F33" s="252"/>
+      <c r="G33" s="252"/>
+      <c r="H33" s="252"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -14045,24 +14045,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="249"/>
-      <c r="C39" s="249"/>
-      <c r="D39" s="249"/>
-      <c r="E39" s="249"/>
-      <c r="F39" s="249"/>
-      <c r="G39" s="249"/>
-      <c r="H39" s="249"/>
+      <c r="B39" s="252"/>
+      <c r="C39" s="252"/>
+      <c r="D39" s="252"/>
+      <c r="E39" s="252"/>
+      <c r="F39" s="252"/>
+      <c r="G39" s="252"/>
+      <c r="H39" s="252"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="249" t="s">
+      <c r="B42" s="252" t="s">
         <v>394</v>
       </c>
-      <c r="C42" s="249"/>
-      <c r="D42" s="249"/>
-      <c r="E42" s="249"/>
-      <c r="F42" s="249"/>
-      <c r="G42" s="249"/>
-      <c r="H42" s="249"/>
+      <c r="C42" s="252"/>
+      <c r="D42" s="252"/>
+      <c r="E42" s="252"/>
+      <c r="F42" s="252"/>
+      <c r="G42" s="252"/>
+      <c r="H42" s="252"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -14077,24 +14077,24 @@
       </c>
     </row>
     <row r="49" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="249"/>
-      <c r="C49" s="249"/>
-      <c r="D49" s="249"/>
-      <c r="E49" s="249"/>
-      <c r="F49" s="249"/>
-      <c r="G49" s="249"/>
-      <c r="H49" s="249"/>
+      <c r="B49" s="252"/>
+      <c r="C49" s="252"/>
+      <c r="D49" s="252"/>
+      <c r="E49" s="252"/>
+      <c r="F49" s="252"/>
+      <c r="G49" s="252"/>
+      <c r="H49" s="252"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B52" s="249" t="s">
+      <c r="B52" s="252" t="s">
         <v>128</v>
       </c>
-      <c r="C52" s="249"/>
-      <c r="D52" s="249"/>
-      <c r="E52" s="249"/>
-      <c r="F52" s="249"/>
-      <c r="G52" s="249"/>
-      <c r="H52" s="249"/>
+      <c r="C52" s="252"/>
+      <c r="D52" s="252"/>
+      <c r="E52" s="252"/>
+      <c r="F52" s="252"/>
+      <c r="G52" s="252"/>
+      <c r="H52" s="252"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B54" s="41" t="s">
@@ -14109,28 +14109,28 @@
       </c>
     </row>
     <row r="59" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="249"/>
-      <c r="C59" s="249"/>
-      <c r="D59" s="249"/>
-      <c r="E59" s="249"/>
-      <c r="F59" s="249"/>
-      <c r="G59" s="249"/>
-      <c r="H59" s="249"/>
+      <c r="B59" s="252"/>
+      <c r="C59" s="252"/>
+      <c r="D59" s="252"/>
+      <c r="E59" s="252"/>
+      <c r="F59" s="252"/>
+      <c r="G59" s="252"/>
+      <c r="H59" s="252"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B52:H52"/>
+    <mergeCell ref="B59:H59"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="B49:H49"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="E25:F25"/>
-    <mergeCell ref="B52:H52"/>
-    <mergeCell ref="B59:H59"/>
-    <mergeCell ref="B33:H33"/>
-    <mergeCell ref="B39:H39"/>
-    <mergeCell ref="B42:H42"/>
-    <mergeCell ref="B49:H49"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -14200,36 +14200,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="249" t="s">
+      <c r="C2" s="252" t="s">
         <v>137</v>
       </c>
-      <c r="D2" s="249"/>
-      <c r="E2" s="249"/>
-      <c r="F2" s="249"/>
-      <c r="G2" s="261"/>
-      <c r="H2" s="262" t="s">
+      <c r="D2" s="252"/>
+      <c r="E2" s="252"/>
+      <c r="F2" s="252"/>
+      <c r="G2" s="258"/>
+      <c r="H2" s="259" t="s">
         <v>138</v>
       </c>
-      <c r="I2" s="249"/>
-      <c r="J2" s="249"/>
-      <c r="K2" s="249"/>
-      <c r="L2" s="249"/>
+      <c r="I2" s="252"/>
+      <c r="J2" s="252"/>
+      <c r="K2" s="252"/>
+      <c r="L2" s="252"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="249" t="s">
+      <c r="S2" s="252" t="s">
         <v>137</v>
       </c>
-      <c r="T2" s="249"/>
-      <c r="U2" s="249"/>
-      <c r="V2" s="249"/>
-      <c r="W2" s="249"/>
-      <c r="X2" s="249"/>
-      <c r="Y2" s="249"/>
-      <c r="Z2" s="249"/>
-      <c r="AA2" s="249" t="s">
+      <c r="T2" s="252"/>
+      <c r="U2" s="252"/>
+      <c r="V2" s="252"/>
+      <c r="W2" s="252"/>
+      <c r="X2" s="252"/>
+      <c r="Y2" s="252"/>
+      <c r="Z2" s="252"/>
+      <c r="AA2" s="252" t="s">
         <v>138</v>
       </c>
-      <c r="AB2" s="249"/>
-      <c r="AC2" s="249"/>
+      <c r="AB2" s="252"/>
+      <c r="AC2" s="252"/>
       <c r="AE2" s="87" t="s">
         <v>139</v>
       </c>
@@ -14240,32 +14240,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="258" t="s">
+      <c r="C4" s="260" t="s">
         <v>140</v>
       </c>
-      <c r="D4" s="258"/>
-      <c r="E4" s="258"/>
-      <c r="F4" s="258"/>
-      <c r="G4" s="258"/>
-      <c r="H4" s="258"/>
-      <c r="I4" s="258"/>
-      <c r="J4" s="258"/>
-      <c r="K4" s="258"/>
-      <c r="L4" s="258"/>
+      <c r="D4" s="260"/>
+      <c r="E4" s="260"/>
+      <c r="F4" s="260"/>
+      <c r="G4" s="260"/>
+      <c r="H4" s="260"/>
+      <c r="I4" s="260"/>
+      <c r="J4" s="260"/>
+      <c r="K4" s="260"/>
+      <c r="L4" s="260"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="259" t="s">
+      <c r="S4" s="261" t="s">
         <v>140</v>
       </c>
-      <c r="T4" s="260"/>
-      <c r="U4" s="260"/>
-      <c r="V4" s="260"/>
-      <c r="W4" s="260"/>
-      <c r="X4" s="260"/>
-      <c r="Y4" s="260"/>
-      <c r="Z4" s="260"/>
-      <c r="AA4" s="260"/>
-      <c r="AB4" s="260"/>
-      <c r="AC4" s="260"/>
+      <c r="T4" s="262"/>
+      <c r="U4" s="262"/>
+      <c r="V4" s="262"/>
+      <c r="W4" s="262"/>
+      <c r="X4" s="262"/>
+      <c r="Y4" s="262"/>
+      <c r="Z4" s="262"/>
+      <c r="AA4" s="262"/>
+      <c r="AB4" s="262"/>
+      <c r="AC4" s="262"/>
       <c r="AE4" s="89"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -14761,33 +14761,33 @@
       <c r="Q10" s="93"/>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C11" s="258" t="s">
+      <c r="C11" s="260" t="s">
         <v>146</v>
       </c>
-      <c r="D11" s="258"/>
-      <c r="E11" s="258"/>
-      <c r="F11" s="258"/>
-      <c r="G11" s="258"/>
-      <c r="H11" s="258"/>
-      <c r="I11" s="258"/>
-      <c r="J11" s="258"/>
-      <c r="K11" s="258"/>
-      <c r="L11" s="258"/>
+      <c r="D11" s="260"/>
+      <c r="E11" s="260"/>
+      <c r="F11" s="260"/>
+      <c r="G11" s="260"/>
+      <c r="H11" s="260"/>
+      <c r="I11" s="260"/>
+      <c r="J11" s="260"/>
+      <c r="K11" s="260"/>
+      <c r="L11" s="260"/>
       <c r="O11" s="5"/>
       <c r="Q11" s="93"/>
-      <c r="S11" s="259" t="s">
+      <c r="S11" s="261" t="s">
         <v>146</v>
       </c>
-      <c r="T11" s="260"/>
-      <c r="U11" s="260"/>
-      <c r="V11" s="260"/>
-      <c r="W11" s="260"/>
-      <c r="X11" s="260"/>
-      <c r="Y11" s="260"/>
-      <c r="Z11" s="260"/>
-      <c r="AA11" s="260"/>
-      <c r="AB11" s="260"/>
-      <c r="AC11" s="260"/>
+      <c r="T11" s="262"/>
+      <c r="U11" s="262"/>
+      <c r="V11" s="262"/>
+      <c r="W11" s="262"/>
+      <c r="X11" s="262"/>
+      <c r="Y11" s="262"/>
+      <c r="Z11" s="262"/>
+      <c r="AA11" s="262"/>
+      <c r="AB11" s="262"/>
+      <c r="AC11" s="262"/>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B12" s="16" t="s">
@@ -15228,33 +15228,33 @@
       <c r="Q18" s="93"/>
     </row>
     <row r="19" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C19" s="258" t="s">
+      <c r="C19" s="260" t="s">
         <v>148</v>
       </c>
-      <c r="D19" s="258"/>
-      <c r="E19" s="258"/>
-      <c r="F19" s="258"/>
-      <c r="G19" s="258"/>
-      <c r="H19" s="258"/>
-      <c r="I19" s="258"/>
-      <c r="J19" s="258"/>
-      <c r="K19" s="258"/>
-      <c r="L19" s="258"/>
+      <c r="D19" s="260"/>
+      <c r="E19" s="260"/>
+      <c r="F19" s="260"/>
+      <c r="G19" s="260"/>
+      <c r="H19" s="260"/>
+      <c r="I19" s="260"/>
+      <c r="J19" s="260"/>
+      <c r="K19" s="260"/>
+      <c r="L19" s="260"/>
       <c r="O19" s="5"/>
       <c r="Q19" s="93"/>
-      <c r="S19" s="259" t="s">
+      <c r="S19" s="261" t="s">
         <v>148</v>
       </c>
-      <c r="T19" s="260"/>
-      <c r="U19" s="260"/>
-      <c r="V19" s="260"/>
-      <c r="W19" s="260"/>
-      <c r="X19" s="260"/>
-      <c r="Y19" s="260"/>
-      <c r="Z19" s="260"/>
-      <c r="AA19" s="260"/>
-      <c r="AB19" s="260"/>
-      <c r="AC19" s="260"/>
+      <c r="T19" s="262"/>
+      <c r="U19" s="262"/>
+      <c r="V19" s="262"/>
+      <c r="W19" s="262"/>
+      <c r="X19" s="262"/>
+      <c r="Y19" s="262"/>
+      <c r="Z19" s="262"/>
+      <c r="AA19" s="262"/>
+      <c r="AB19" s="262"/>
+      <c r="AC19" s="262"/>
       <c r="AE19" s="89">
         <f>AE4</f>
         <v>0</v>
@@ -16072,32 +16072,32 @@
       <c r="O31" s="5"/>
     </row>
     <row r="32" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C32" s="258" t="s">
+      <c r="C32" s="260" t="s">
         <v>150</v>
       </c>
-      <c r="D32" s="258"/>
-      <c r="E32" s="258"/>
-      <c r="F32" s="258"/>
-      <c r="G32" s="258"/>
-      <c r="H32" s="258"/>
-      <c r="I32" s="258"/>
-      <c r="J32" s="258"/>
-      <c r="K32" s="258"/>
-      <c r="L32" s="258"/>
+      <c r="D32" s="260"/>
+      <c r="E32" s="260"/>
+      <c r="F32" s="260"/>
+      <c r="G32" s="260"/>
+      <c r="H32" s="260"/>
+      <c r="I32" s="260"/>
+      <c r="J32" s="260"/>
+      <c r="K32" s="260"/>
+      <c r="L32" s="260"/>
       <c r="O32" s="5"/>
-      <c r="S32" s="259" t="s">
+      <c r="S32" s="261" t="s">
         <v>150</v>
       </c>
-      <c r="T32" s="260"/>
-      <c r="U32" s="260"/>
-      <c r="V32" s="260"/>
-      <c r="W32" s="260"/>
-      <c r="X32" s="260"/>
-      <c r="Y32" s="260"/>
-      <c r="Z32" s="260"/>
-      <c r="AA32" s="260"/>
-      <c r="AB32" s="260"/>
-      <c r="AC32" s="260"/>
+      <c r="T32" s="262"/>
+      <c r="U32" s="262"/>
+      <c r="V32" s="262"/>
+      <c r="W32" s="262"/>
+      <c r="X32" s="262"/>
+      <c r="Y32" s="262"/>
+      <c r="Z32" s="262"/>
+      <c r="AA32" s="262"/>
+      <c r="AB32" s="262"/>
+      <c r="AC32" s="262"/>
     </row>
     <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B33" s="16" t="s">
@@ -16354,18 +16354,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="C11:L11"/>
+    <mergeCell ref="S11:AC11"/>
+    <mergeCell ref="C19:L19"/>
+    <mergeCell ref="S19:AC19"/>
+    <mergeCell ref="C32:L32"/>
+    <mergeCell ref="S32:AC32"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C11:L11"/>
-    <mergeCell ref="S11:AC11"/>
-    <mergeCell ref="C19:L19"/>
-    <mergeCell ref="S19:AC19"/>
-    <mergeCell ref="C32:L32"/>
-    <mergeCell ref="S32:AC32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -16402,35 +16402,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="249" t="s">
+      <c r="C2" s="252" t="s">
         <v>137</v>
       </c>
-      <c r="D2" s="249"/>
-      <c r="E2" s="249"/>
-      <c r="F2" s="249"/>
-      <c r="G2" s="261"/>
-      <c r="H2" s="262" t="s">
+      <c r="D2" s="252"/>
+      <c r="E2" s="252"/>
+      <c r="F2" s="252"/>
+      <c r="G2" s="258"/>
+      <c r="H2" s="259" t="s">
         <v>138</v>
       </c>
-      <c r="I2" s="249"/>
-      <c r="J2" s="249"/>
-      <c r="K2" s="249"/>
-      <c r="L2" s="249"/>
-      <c r="P2" s="249" t="s">
+      <c r="I2" s="252"/>
+      <c r="J2" s="252"/>
+      <c r="K2" s="252"/>
+      <c r="L2" s="252"/>
+      <c r="P2" s="252" t="s">
         <v>137</v>
       </c>
-      <c r="Q2" s="249"/>
-      <c r="R2" s="249"/>
-      <c r="S2" s="249"/>
-      <c r="T2" s="249"/>
-      <c r="U2" s="249"/>
-      <c r="V2" s="249"/>
-      <c r="W2" s="249"/>
-      <c r="X2" s="249" t="s">
+      <c r="Q2" s="252"/>
+      <c r="R2" s="252"/>
+      <c r="S2" s="252"/>
+      <c r="T2" s="252"/>
+      <c r="U2" s="252"/>
+      <c r="V2" s="252"/>
+      <c r="W2" s="252"/>
+      <c r="X2" s="252" t="s">
         <v>138</v>
       </c>
-      <c r="Y2" s="249"/>
-      <c r="Z2" s="249"/>
+      <c r="Y2" s="252"/>
+      <c r="Z2" s="252"/>
       <c r="AB2" s="87" t="s">
         <v>139</v>
       </c>
@@ -16439,31 +16439,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="258" t="s">
+      <c r="C4" s="260" t="s">
         <v>140</v>
       </c>
-      <c r="D4" s="258"/>
-      <c r="E4" s="258"/>
-      <c r="F4" s="258"/>
-      <c r="G4" s="258"/>
-      <c r="H4" s="258"/>
-      <c r="I4" s="258"/>
-      <c r="J4" s="258"/>
-      <c r="K4" s="258"/>
-      <c r="L4" s="258"/>
-      <c r="P4" s="260" t="s">
+      <c r="D4" s="260"/>
+      <c r="E4" s="260"/>
+      <c r="F4" s="260"/>
+      <c r="G4" s="260"/>
+      <c r="H4" s="260"/>
+      <c r="I4" s="260"/>
+      <c r="J4" s="260"/>
+      <c r="K4" s="260"/>
+      <c r="L4" s="260"/>
+      <c r="P4" s="262" t="s">
         <v>140</v>
       </c>
-      <c r="Q4" s="260"/>
-      <c r="R4" s="260"/>
-      <c r="S4" s="260"/>
-      <c r="T4" s="260"/>
-      <c r="U4" s="260"/>
-      <c r="V4" s="260"/>
-      <c r="W4" s="260"/>
-      <c r="X4" s="260"/>
-      <c r="Y4" s="260"/>
-      <c r="Z4" s="260"/>
+      <c r="Q4" s="262"/>
+      <c r="R4" s="262"/>
+      <c r="S4" s="262"/>
+      <c r="T4" s="262"/>
+      <c r="U4" s="262"/>
+      <c r="V4" s="262"/>
+      <c r="W4" s="262"/>
+      <c r="X4" s="262"/>
+      <c r="Y4" s="262"/>
+      <c r="Z4" s="262"/>
       <c r="AB4" s="89"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -16658,32 +16658,32 @@
       <c r="N8" s="93"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="258" t="s">
+      <c r="C9" s="260" t="s">
         <v>166</v>
       </c>
-      <c r="D9" s="258"/>
-      <c r="E9" s="258"/>
-      <c r="F9" s="258"/>
-      <c r="G9" s="258"/>
-      <c r="H9" s="258"/>
-      <c r="I9" s="258"/>
-      <c r="J9" s="258"/>
-      <c r="K9" s="258"/>
-      <c r="L9" s="258"/>
+      <c r="D9" s="260"/>
+      <c r="E9" s="260"/>
+      <c r="F9" s="260"/>
+      <c r="G9" s="260"/>
+      <c r="H9" s="260"/>
+      <c r="I9" s="260"/>
+      <c r="J9" s="260"/>
+      <c r="K9" s="260"/>
+      <c r="L9" s="260"/>
       <c r="N9" s="93"/>
-      <c r="P9" s="260" t="s">
+      <c r="P9" s="262" t="s">
         <v>167</v>
       </c>
-      <c r="Q9" s="260"/>
-      <c r="R9" s="260"/>
-      <c r="S9" s="260"/>
-      <c r="T9" s="260"/>
-      <c r="U9" s="260"/>
-      <c r="V9" s="260"/>
-      <c r="W9" s="260"/>
-      <c r="X9" s="260"/>
-      <c r="Y9" s="260"/>
-      <c r="Z9" s="260"/>
+      <c r="Q9" s="262"/>
+      <c r="R9" s="262"/>
+      <c r="S9" s="262"/>
+      <c r="T9" s="262"/>
+      <c r="U9" s="262"/>
+      <c r="V9" s="262"/>
+      <c r="W9" s="262"/>
+      <c r="X9" s="262"/>
+      <c r="Y9" s="262"/>
+      <c r="Z9" s="262"/>
       <c r="AB9" s="89">
         <f>AB4</f>
         <v>0</v>
@@ -17532,31 +17532,31 @@
       </c>
     </row>
     <row r="21" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="C21" s="258" t="s">
+      <c r="C21" s="260" t="s">
         <v>169</v>
       </c>
-      <c r="D21" s="258"/>
-      <c r="E21" s="258"/>
-      <c r="F21" s="258"/>
-      <c r="G21" s="258"/>
-      <c r="H21" s="258"/>
-      <c r="I21" s="258"/>
-      <c r="J21" s="258"/>
-      <c r="K21" s="258"/>
-      <c r="L21" s="258"/>
-      <c r="P21" s="260" t="s">
+      <c r="D21" s="260"/>
+      <c r="E21" s="260"/>
+      <c r="F21" s="260"/>
+      <c r="G21" s="260"/>
+      <c r="H21" s="260"/>
+      <c r="I21" s="260"/>
+      <c r="J21" s="260"/>
+      <c r="K21" s="260"/>
+      <c r="L21" s="260"/>
+      <c r="P21" s="262" t="s">
         <v>169</v>
       </c>
-      <c r="Q21" s="260"/>
-      <c r="R21" s="260"/>
-      <c r="S21" s="260"/>
-      <c r="T21" s="260"/>
-      <c r="U21" s="260"/>
-      <c r="V21" s="260"/>
-      <c r="W21" s="260"/>
-      <c r="X21" s="260"/>
-      <c r="Y21" s="260"/>
-      <c r="Z21" s="260"/>
+      <c r="Q21" s="262"/>
+      <c r="R21" s="262"/>
+      <c r="S21" s="262"/>
+      <c r="T21" s="262"/>
+      <c r="U21" s="262"/>
+      <c r="V21" s="262"/>
+      <c r="W21" s="262"/>
+      <c r="X21" s="262"/>
+      <c r="Y21" s="262"/>
+      <c r="Z21" s="262"/>
     </row>
     <row r="22" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B22" s="16" t="s">
@@ -18371,20 +18371,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="249" t="s">
+      <c r="C3" s="252" t="s">
         <v>137</v>
       </c>
-      <c r="D3" s="249"/>
-      <c r="E3" s="249"/>
-      <c r="F3" s="249"/>
-      <c r="G3" s="261"/>
-      <c r="H3" s="262" t="s">
+      <c r="D3" s="252"/>
+      <c r="E3" s="252"/>
+      <c r="F3" s="252"/>
+      <c r="G3" s="258"/>
+      <c r="H3" s="259" t="s">
         <v>138</v>
       </c>
-      <c r="I3" s="249"/>
-      <c r="J3" s="249"/>
-      <c r="K3" s="249"/>
-      <c r="L3" s="249"/>
+      <c r="I3" s="252"/>
+      <c r="J3" s="252"/>
+      <c r="K3" s="252"/>
+      <c r="L3" s="252"/>
       <c r="P3" s="263"/>
       <c r="Q3" s="263"/>
       <c r="R3" s="263"/>
@@ -18402,18 +18402,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="88"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="258" t="s">
+      <c r="C5" s="260" t="s">
         <v>140</v>
       </c>
-      <c r="D5" s="258"/>
-      <c r="E5" s="258"/>
-      <c r="F5" s="258"/>
-      <c r="G5" s="258"/>
-      <c r="H5" s="258"/>
-      <c r="I5" s="258"/>
-      <c r="J5" s="258"/>
-      <c r="K5" s="258"/>
-      <c r="L5" s="258"/>
+      <c r="D5" s="260"/>
+      <c r="E5" s="260"/>
+      <c r="F5" s="260"/>
+      <c r="G5" s="260"/>
+      <c r="H5" s="260"/>
+      <c r="I5" s="260"/>
+      <c r="J5" s="260"/>
+      <c r="K5" s="260"/>
+      <c r="L5" s="260"/>
       <c r="P5" s="263"/>
       <c r="Q5" s="263"/>
       <c r="R5" s="263"/>
@@ -18610,18 +18610,18 @@
       <c r="N10" s="93"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="258" t="s">
+      <c r="C11" s="260" t="s">
         <v>173</v>
       </c>
-      <c r="D11" s="258"/>
-      <c r="E11" s="258"/>
-      <c r="F11" s="258"/>
-      <c r="G11" s="258"/>
-      <c r="H11" s="258"/>
-      <c r="I11" s="258"/>
-      <c r="J11" s="258"/>
-      <c r="K11" s="258"/>
-      <c r="L11" s="258"/>
+      <c r="D11" s="260"/>
+      <c r="E11" s="260"/>
+      <c r="F11" s="260"/>
+      <c r="G11" s="260"/>
+      <c r="H11" s="260"/>
+      <c r="I11" s="260"/>
+      <c r="J11" s="260"/>
+      <c r="K11" s="260"/>
+      <c r="L11" s="260"/>
       <c r="N11" s="93"/>
       <c r="P11" s="263"/>
       <c r="Q11" s="263"/>
@@ -18875,18 +18875,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="258" t="s">
+      <c r="C18" s="260" t="s">
         <v>178</v>
       </c>
-      <c r="D18" s="258"/>
-      <c r="E18" s="258"/>
-      <c r="F18" s="258"/>
-      <c r="G18" s="258"/>
-      <c r="H18" s="258"/>
-      <c r="I18" s="258"/>
-      <c r="J18" s="258"/>
-      <c r="K18" s="258"/>
-      <c r="L18" s="258"/>
+      <c r="D18" s="260"/>
+      <c r="E18" s="260"/>
+      <c r="F18" s="260"/>
+      <c r="G18" s="260"/>
+      <c r="H18" s="260"/>
+      <c r="I18" s="260"/>
+      <c r="J18" s="260"/>
+      <c r="K18" s="260"/>
+      <c r="L18" s="260"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19104,18 +19104,18 @@
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="130"/>
-      <c r="C26" s="258" t="s">
+      <c r="C26" s="260" t="s">
         <v>184</v>
       </c>
-      <c r="D26" s="258"/>
-      <c r="E26" s="258"/>
-      <c r="F26" s="258"/>
-      <c r="G26" s="258"/>
-      <c r="H26" s="258"/>
-      <c r="I26" s="258"/>
-      <c r="J26" s="258"/>
-      <c r="K26" s="258"/>
-      <c r="L26" s="258"/>
+      <c r="D26" s="260"/>
+      <c r="E26" s="260"/>
+      <c r="F26" s="260"/>
+      <c r="G26" s="260"/>
+      <c r="H26" s="260"/>
+      <c r="I26" s="260"/>
+      <c r="J26" s="260"/>
+      <c r="K26" s="260"/>
+      <c r="L26" s="260"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -19307,18 +19307,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="130"/>
-      <c r="C33" s="258" t="s">
+      <c r="C33" s="260" t="s">
         <v>188</v>
       </c>
-      <c r="D33" s="258"/>
-      <c r="E33" s="258"/>
-      <c r="F33" s="258"/>
-      <c r="G33" s="258"/>
-      <c r="H33" s="258"/>
-      <c r="I33" s="258"/>
-      <c r="J33" s="258"/>
-      <c r="K33" s="258"/>
-      <c r="L33" s="258"/>
+      <c r="D33" s="260"/>
+      <c r="E33" s="260"/>
+      <c r="F33" s="260"/>
+      <c r="G33" s="260"/>
+      <c r="H33" s="260"/>
+      <c r="I33" s="260"/>
+      <c r="J33" s="260"/>
+      <c r="K33" s="260"/>
+      <c r="L33" s="260"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -19502,18 +19502,18 @@
       <c r="C39" s="146"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="258" t="s">
+      <c r="C40" s="260" t="s">
         <v>191</v>
       </c>
-      <c r="D40" s="258"/>
-      <c r="E40" s="258"/>
-      <c r="F40" s="258"/>
-      <c r="G40" s="258"/>
-      <c r="H40" s="258"/>
-      <c r="I40" s="258"/>
-      <c r="J40" s="258"/>
-      <c r="K40" s="258"/>
-      <c r="L40" s="258"/>
+      <c r="D40" s="260"/>
+      <c r="E40" s="260"/>
+      <c r="F40" s="260"/>
+      <c r="G40" s="260"/>
+      <c r="H40" s="260"/>
+      <c r="I40" s="260"/>
+      <c r="J40" s="260"/>
+      <c r="K40" s="260"/>
+      <c r="L40" s="260"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -19777,6 +19777,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -19784,12 +19790,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -19827,20 +19827,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="249" t="s">
+      <c r="C2" s="252" t="s">
         <v>137</v>
       </c>
-      <c r="D2" s="249"/>
-      <c r="E2" s="249"/>
-      <c r="F2" s="249"/>
-      <c r="G2" s="261"/>
-      <c r="H2" s="262" t="s">
+      <c r="D2" s="252"/>
+      <c r="E2" s="252"/>
+      <c r="F2" s="252"/>
+      <c r="G2" s="258"/>
+      <c r="H2" s="259" t="s">
         <v>138</v>
       </c>
-      <c r="I2" s="249"/>
-      <c r="J2" s="249"/>
-      <c r="K2" s="249"/>
-      <c r="L2" s="249"/>
+      <c r="I2" s="252"/>
+      <c r="J2" s="252"/>
+      <c r="K2" s="252"/>
+      <c r="L2" s="252"/>
       <c r="S2" s="263"/>
       <c r="T2" s="263"/>
       <c r="U2" s="263"/>
@@ -19858,18 +19858,18 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="258" t="s">
+      <c r="C4" s="260" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="258"/>
-      <c r="E4" s="258"/>
-      <c r="F4" s="258"/>
-      <c r="G4" s="258"/>
-      <c r="H4" s="258"/>
-      <c r="I4" s="258"/>
-      <c r="J4" s="258"/>
-      <c r="K4" s="258"/>
-      <c r="L4" s="258"/>
+      <c r="D4" s="260"/>
+      <c r="E4" s="260"/>
+      <c r="F4" s="260"/>
+      <c r="G4" s="260"/>
+      <c r="H4" s="260"/>
+      <c r="I4" s="260"/>
+      <c r="J4" s="260"/>
+      <c r="K4" s="260"/>
+      <c r="L4" s="260"/>
       <c r="S4" s="263"/>
       <c r="T4" s="263"/>
       <c r="U4" s="263"/>
@@ -20243,18 +20243,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="258" t="s">
+      <c r="C13" s="260" t="s">
         <v>199</v>
       </c>
-      <c r="D13" s="258"/>
-      <c r="E13" s="258"/>
-      <c r="F13" s="258"/>
-      <c r="G13" s="258"/>
-      <c r="H13" s="258"/>
-      <c r="I13" s="258"/>
-      <c r="J13" s="258"/>
-      <c r="K13" s="258"/>
-      <c r="L13" s="258"/>
+      <c r="D13" s="260"/>
+      <c r="E13" s="260"/>
+      <c r="F13" s="260"/>
+      <c r="G13" s="260"/>
+      <c r="H13" s="260"/>
+      <c r="I13" s="260"/>
+      <c r="J13" s="260"/>
+      <c r="K13" s="260"/>
+      <c r="L13" s="260"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -20347,18 +20347,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="258" t="s">
+      <c r="C18" s="260" t="s">
         <v>200</v>
       </c>
-      <c r="D18" s="258"/>
-      <c r="E18" s="258"/>
-      <c r="F18" s="258"/>
-      <c r="G18" s="258"/>
-      <c r="H18" s="258"/>
-      <c r="I18" s="258"/>
-      <c r="J18" s="258"/>
-      <c r="K18" s="258"/>
-      <c r="L18" s="258"/>
+      <c r="D18" s="260"/>
+      <c r="E18" s="260"/>
+      <c r="F18" s="260"/>
+      <c r="G18" s="260"/>
+      <c r="H18" s="260"/>
+      <c r="I18" s="260"/>
+      <c r="J18" s="260"/>
+      <c r="K18" s="260"/>
+      <c r="L18" s="260"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -20550,18 +20550,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="258" t="s">
+      <c r="C25" s="260" t="s">
         <v>311</v>
       </c>
-      <c r="D25" s="258"/>
-      <c r="E25" s="258"/>
-      <c r="F25" s="258"/>
-      <c r="G25" s="258"/>
-      <c r="H25" s="258"/>
-      <c r="I25" s="258"/>
-      <c r="J25" s="258"/>
-      <c r="K25" s="258"/>
-      <c r="L25" s="258"/>
+      <c r="D25" s="260"/>
+      <c r="E25" s="260"/>
+      <c r="F25" s="260"/>
+      <c r="G25" s="260"/>
+      <c r="H25" s="260"/>
+      <c r="I25" s="260"/>
+      <c r="J25" s="260"/>
+      <c r="K25" s="260"/>
+      <c r="L25" s="260"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -20699,18 +20699,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="258" t="s">
+      <c r="C31" s="260" t="s">
         <v>78</v>
       </c>
-      <c r="D31" s="258"/>
-      <c r="E31" s="258"/>
-      <c r="F31" s="258"/>
-      <c r="G31" s="258"/>
-      <c r="H31" s="258"/>
-      <c r="I31" s="258"/>
-      <c r="J31" s="258"/>
-      <c r="K31" s="258"/>
-      <c r="L31" s="258"/>
+      <c r="D31" s="260"/>
+      <c r="E31" s="260"/>
+      <c r="F31" s="260"/>
+      <c r="G31" s="260"/>
+      <c r="H31" s="260"/>
+      <c r="I31" s="260"/>
+      <c r="J31" s="260"/>
+      <c r="K31" s="260"/>
+      <c r="L31" s="260"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -20849,16 +20849,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -20921,10 +20921,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="249" t="s">
+      <c r="B4" s="252" t="s">
         <v>207</v>
       </c>
-      <c r="C4" s="249"/>
+      <c r="C4" s="252"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -20941,7 +20941,7 @@
       </c>
       <c r="C6" s="154">
         <f ca="1">Overview!C5</f>
-        <v>10.15</v>
+        <v>9.9350000000000005</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20950,7 +20950,7 @@
       </c>
       <c r="C7" s="155">
         <f ca="1">C5*C6</f>
-        <v>5301903.25</v>
+        <v>5189596.9249999998</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20968,7 +20968,7 @@
       </c>
       <c r="C9" s="156">
         <f ca="1">Overview!F27</f>
-        <v>4.5090000000000005E-2</v>
+        <v>4.3920000000000001E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20977,7 +20977,7 @@
       </c>
       <c r="C10" s="154">
         <f ca="1">Overview!C13</f>
-        <v>0.98270000000000002</v>
+        <v>0.98829999999999996</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21009,10 +21009,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="249" t="s">
+      <c r="B15" s="252" t="s">
         <v>214</v>
       </c>
-      <c r="C15" s="249"/>
+      <c r="C15" s="252"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -21047,7 +21047,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>8.9311500000000002E-2</v>
+        <v>8.83935E-2</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21056,7 +21056,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>8.9311500000000002E-2</v>
+        <v>8.83935E-2</v>
       </c>
     </row>
   </sheetData>
@@ -21101,20 +21101,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="249" t="s">
+      <c r="C3" s="252" t="s">
         <v>137</v>
       </c>
-      <c r="D3" s="249"/>
-      <c r="E3" s="249"/>
-      <c r="F3" s="249"/>
-      <c r="G3" s="261"/>
-      <c r="H3" s="262" t="s">
+      <c r="D3" s="252"/>
+      <c r="E3" s="252"/>
+      <c r="F3" s="252"/>
+      <c r="G3" s="258"/>
+      <c r="H3" s="259" t="s">
         <v>138</v>
       </c>
-      <c r="I3" s="249"/>
-      <c r="J3" s="249"/>
-      <c r="K3" s="249"/>
-      <c r="L3" s="249"/>
+      <c r="I3" s="252"/>
+      <c r="J3" s="252"/>
+      <c r="K3" s="252"/>
+      <c r="L3" s="252"/>
       <c r="P3" s="263"/>
       <c r="Q3" s="263"/>
       <c r="R3" s="263"/>
@@ -21132,18 +21132,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="88"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="258" t="s">
+      <c r="C5" s="260" t="s">
         <v>221</v>
       </c>
-      <c r="D5" s="258"/>
-      <c r="E5" s="258"/>
-      <c r="F5" s="258"/>
-      <c r="G5" s="258"/>
-      <c r="H5" s="258"/>
-      <c r="I5" s="258"/>
-      <c r="J5" s="258"/>
-      <c r="K5" s="258"/>
-      <c r="L5" s="258"/>
+      <c r="D5" s="260"/>
+      <c r="E5" s="260"/>
+      <c r="F5" s="260"/>
+      <c r="G5" s="260"/>
+      <c r="H5" s="260"/>
+      <c r="I5" s="260"/>
+      <c r="J5" s="260"/>
+      <c r="K5" s="260"/>
+      <c r="L5" s="260"/>
       <c r="P5" s="263"/>
       <c r="Q5" s="263"/>
       <c r="R5" s="263"/>
@@ -21400,10 +21400,10 @@
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="249" t="s">
+      <c r="B13" s="252" t="s">
         <v>225</v>
       </c>
-      <c r="C13" s="249"/>
+      <c r="C13" s="252"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -21423,10 +21423,10 @@
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="249" t="s">
+      <c r="B18" s="252" t="s">
         <v>227</v>
       </c>
-      <c r="C18" s="249"/>
+      <c r="C18" s="252"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -21540,37 +21540,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="249" t="s">
+      <c r="C2" s="252" t="s">
         <v>137</v>
       </c>
-      <c r="D2" s="249"/>
-      <c r="E2" s="249"/>
-      <c r="F2" s="249"/>
-      <c r="G2" s="261"/>
-      <c r="H2" s="262" t="s">
+      <c r="D2" s="252"/>
+      <c r="E2" s="252"/>
+      <c r="F2" s="252"/>
+      <c r="G2" s="258"/>
+      <c r="H2" s="259" t="s">
         <v>138</v>
       </c>
-      <c r="I2" s="249"/>
-      <c r="J2" s="249"/>
-      <c r="K2" s="249"/>
-      <c r="L2" s="249"/>
+      <c r="I2" s="252"/>
+      <c r="J2" s="252"/>
+      <c r="K2" s="252"/>
+      <c r="L2" s="252"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="258" t="s">
+      <c r="C4" s="260" t="s">
         <v>235</v>
       </c>
-      <c r="D4" s="258"/>
-      <c r="E4" s="258"/>
-      <c r="F4" s="258"/>
-      <c r="G4" s="258"/>
-      <c r="H4" s="258"/>
-      <c r="I4" s="258"/>
-      <c r="J4" s="258"/>
-      <c r="K4" s="258"/>
-      <c r="L4" s="258"/>
+      <c r="D4" s="260"/>
+      <c r="E4" s="260"/>
+      <c r="F4" s="260"/>
+      <c r="G4" s="260"/>
+      <c r="H4" s="260"/>
+      <c r="I4" s="260"/>
+      <c r="J4" s="260"/>
+      <c r="K4" s="260"/>
+      <c r="L4" s="260"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -21759,18 +21759,18 @@
       <c r="N9" s="93"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C10" s="258" t="s">
+      <c r="C10" s="260" t="s">
         <v>146</v>
       </c>
-      <c r="D10" s="258"/>
-      <c r="E10" s="258"/>
-      <c r="F10" s="258"/>
-      <c r="G10" s="258"/>
-      <c r="H10" s="258"/>
-      <c r="I10" s="258"/>
-      <c r="J10" s="258"/>
-      <c r="K10" s="258"/>
-      <c r="L10" s="258"/>
+      <c r="D10" s="260"/>
+      <c r="E10" s="260"/>
+      <c r="F10" s="260"/>
+      <c r="G10" s="260"/>
+      <c r="H10" s="260"/>
+      <c r="I10" s="260"/>
+      <c r="J10" s="260"/>
+      <c r="K10" s="260"/>
+      <c r="L10" s="260"/>
       <c r="N10" s="93"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21964,18 +21964,18 @@
       <c r="N15" s="93"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C16" s="258" t="s">
+      <c r="C16" s="260" t="s">
         <v>237</v>
       </c>
-      <c r="D16" s="258"/>
-      <c r="E16" s="258"/>
-      <c r="F16" s="258"/>
-      <c r="G16" s="258"/>
-      <c r="H16" s="258"/>
-      <c r="I16" s="258"/>
-      <c r="J16" s="258"/>
-      <c r="K16" s="258"/>
-      <c r="L16" s="258"/>
+      <c r="D16" s="260"/>
+      <c r="E16" s="260"/>
+      <c r="F16" s="260"/>
+      <c r="G16" s="260"/>
+      <c r="H16" s="260"/>
+      <c r="I16" s="260"/>
+      <c r="J16" s="260"/>
+      <c r="K16" s="260"/>
+      <c r="L16" s="260"/>
       <c r="N16" s="93"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
@@ -22109,18 +22109,18 @@
       <c r="N20" s="93"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C21" s="258" t="s">
+      <c r="C21" s="260" t="s">
         <v>240</v>
       </c>
-      <c r="D21" s="258"/>
-      <c r="E21" s="258"/>
-      <c r="F21" s="258"/>
-      <c r="G21" s="258"/>
-      <c r="H21" s="258"/>
-      <c r="I21" s="258"/>
-      <c r="J21" s="258"/>
-      <c r="K21" s="258"/>
-      <c r="L21" s="258"/>
+      <c r="D21" s="260"/>
+      <c r="E21" s="260"/>
+      <c r="F21" s="260"/>
+      <c r="G21" s="260"/>
+      <c r="H21" s="260"/>
+      <c r="I21" s="260"/>
+      <c r="J21" s="260"/>
+      <c r="K21" s="260"/>
+      <c r="L21" s="260"/>
       <c r="N21" s="93"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
@@ -22204,18 +22204,18 @@
       <c r="N25" s="93"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C26" s="258" t="s">
+      <c r="C26" s="260" t="s">
         <v>241</v>
       </c>
-      <c r="D26" s="258"/>
-      <c r="E26" s="258"/>
-      <c r="F26" s="258"/>
-      <c r="G26" s="258"/>
-      <c r="H26" s="258"/>
-      <c r="I26" s="258"/>
-      <c r="J26" s="258"/>
-      <c r="K26" s="258"/>
-      <c r="L26" s="258"/>
+      <c r="D26" s="260"/>
+      <c r="E26" s="260"/>
+      <c r="F26" s="260"/>
+      <c r="G26" s="260"/>
+      <c r="H26" s="260"/>
+      <c r="I26" s="260"/>
+      <c r="J26" s="260"/>
+      <c r="K26" s="260"/>
+      <c r="L26" s="260"/>
       <c r="N26" s="93"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
@@ -22485,10 +22485,10 @@
       <c r="N36" s="93"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="249" t="s">
+      <c r="B37" s="252" t="s">
         <v>246</v>
       </c>
-      <c r="C37" s="249"/>
+      <c r="C37" s="252"/>
       <c r="N37" s="93"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -22563,10 +22563,10 @@
       </c>
     </row>
     <row r="47" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B47" s="249" t="s">
+      <c r="B47" s="252" t="s">
         <v>251</v>
       </c>
-      <c r="C47" s="249"/>
+      <c r="C47" s="252"/>
     </row>
     <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B48" s="1" t="s">
@@ -22622,10 +22622,10 @@
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B55" s="249" t="s">
+      <c r="B55" s="252" t="s">
         <v>375</v>
       </c>
-      <c r="C55" s="249"/>
+      <c r="C55" s="252"/>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B56" s="1" t="s">
@@ -22738,10 +22738,10 @@
       <c r="N3" s="93"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="249" t="s">
+      <c r="B4" s="252" t="s">
         <v>256</v>
       </c>
-      <c r="C4" s="249"/>
+      <c r="C4" s="252"/>
       <c r="N4" s="93"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -22795,7 +22795,7 @@
       </c>
       <c r="C10" s="154">
         <f ca="1">Overview!C5</f>
-        <v>10.15</v>
+        <v>9.9350000000000005</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -22804,7 +22804,7 @@
       </c>
       <c r="C11" s="175">
         <f ca="1">(C9-C10)/C10</f>
-        <v>0.13336852996281623</v>
+        <v>0.15789537786840308</v>
       </c>
     </row>
   </sheetData>
@@ -22869,20 +22869,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="249" t="s">
+      <c r="C3" s="252" t="s">
         <v>137</v>
       </c>
-      <c r="D3" s="249"/>
-      <c r="E3" s="249"/>
-      <c r="F3" s="249"/>
-      <c r="G3" s="261"/>
-      <c r="H3" s="262" t="s">
+      <c r="D3" s="252"/>
+      <c r="E3" s="252"/>
+      <c r="F3" s="252"/>
+      <c r="G3" s="258"/>
+      <c r="H3" s="259" t="s">
         <v>138</v>
       </c>
-      <c r="I3" s="249"/>
-      <c r="J3" s="249"/>
-      <c r="K3" s="249"/>
-      <c r="L3" s="249"/>
+      <c r="I3" s="252"/>
+      <c r="J3" s="252"/>
+      <c r="K3" s="252"/>
+      <c r="L3" s="252"/>
       <c r="P3" s="263"/>
       <c r="Q3" s="263"/>
       <c r="R3" s="263"/>
@@ -22900,18 +22900,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="88"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="258" t="s">
+      <c r="C5" s="260" t="s">
         <v>221</v>
       </c>
-      <c r="D5" s="258"/>
-      <c r="E5" s="258"/>
-      <c r="F5" s="258"/>
-      <c r="G5" s="258"/>
-      <c r="H5" s="258"/>
-      <c r="I5" s="258"/>
-      <c r="J5" s="258"/>
-      <c r="K5" s="258"/>
-      <c r="L5" s="258"/>
+      <c r="D5" s="260"/>
+      <c r="E5" s="260"/>
+      <c r="F5" s="260"/>
+      <c r="G5" s="260"/>
+      <c r="H5" s="260"/>
+      <c r="I5" s="260"/>
+      <c r="J5" s="260"/>
+      <c r="K5" s="260"/>
+      <c r="L5" s="260"/>
       <c r="P5" s="263"/>
       <c r="Q5" s="263"/>
       <c r="R5" s="263"/>
@@ -23161,7 +23161,7 @@
       </c>
       <c r="C15" s="177">
         <f ca="1">Overview!C5</f>
-        <v>10.15</v>
+        <v>9.9350000000000005</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -23227,7 +23227,7 @@
       </c>
       <c r="C23" s="182">
         <f ca="1">C15*C22</f>
-        <v>5258928.1500000004</v>
+        <v>5147532.1350000007</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -23254,7 +23254,7 @@
       </c>
       <c r="C26" s="183">
         <f ca="1">C23+C25-C24</f>
-        <v>3843182.1500000004</v>
+        <v>3731786.1350000007</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -23337,18 +23337,18 @@
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C39" s="258" t="s">
+      <c r="C39" s="260" t="s">
         <v>270</v>
       </c>
-      <c r="D39" s="258"/>
-      <c r="E39" s="258"/>
-      <c r="F39" s="258"/>
-      <c r="G39" s="258"/>
-      <c r="H39" s="258"/>
-      <c r="I39" s="258"/>
-      <c r="J39" s="258"/>
-      <c r="K39" s="258"/>
-      <c r="L39" s="258"/>
+      <c r="D39" s="260"/>
+      <c r="E39" s="260"/>
+      <c r="F39" s="260"/>
+      <c r="G39" s="260"/>
+      <c r="H39" s="260"/>
+      <c r="I39" s="260"/>
+      <c r="J39" s="260"/>
+      <c r="K39" s="260"/>
+      <c r="L39" s="260"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="12">
@@ -23780,17 +23780,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -30403,7 +30403,7 @@
       <c r="AA116" s="68"/>
       <c r="AC116" s="63">
         <f ca="1">Overview!C5</f>
-        <v>10.15</v>
+        <v>9.9350000000000005</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -30450,7 +30450,7 @@
       <c r="AA117" s="68"/>
       <c r="AC117" s="65">
         <f ca="1">AC116/AC85</f>
-        <v>10.15</v>
+        <v>9.9350000000000005</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -31756,7 +31756,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>16.916666666666664</v>
+        <v>16.55833333333333</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -31793,7 +31793,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>3.269853699628662</v>
+        <v>3.2005907887498282</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -31830,7 +31830,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="72">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>2.7635443373892845</v>
+        <v>2.705006206104684</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -31867,7 +31867,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="164">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>5301903.25</v>
+        <v>5189596.9249999998</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -31904,7 +31904,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="164">
         <f ca="1">AC153+AC108-AC107+AC48+AC45</f>
-        <v>3886157.25</v>
+        <v>3773850.9249999998</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -31941,7 +31941,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="204">
         <f ca="1">AC154/AC5</f>
-        <v>2.3237980841101935</v>
+        <v>2.256642483839912</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -31978,7 +31978,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="204">
         <f ca="1">AC154/AC12</f>
-        <v>38.416327266975749</v>
+        <v>37.306131189513536</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -32113,7 +32113,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="72">
         <f t="shared" ref="AC159:AC160" ca="1" si="101">AC153/AC157</f>
-        <v>49.270072670501541</v>
+        <v>48.226420884870222</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -32150,7 +32150,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
         <f t="shared" ca="1" si="101"/>
-        <v>-71.654047201991332</v>
+        <v>-69.583311975661474</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -32187,7 +32187,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="74">
         <f t="shared" ref="AC161" ca="1" si="104">AC157/AC153</f>
-        <v>2.0296296429022916E-2</v>
+        <v>2.0735521766943394E-2</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -32224,7 +32224,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f ca="1">AC26/AC117</f>
-        <v>5.9113300492610842E-2</v>
+        <v>6.0392551585304488E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -32298,7 +32298,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="175">
         <f ca="1">-AC63/AC153</f>
-        <v>6.5141135874178774E-2</v>
+        <v>6.6550833328929498E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -32335,7 +32335,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="175">
         <f ca="1">-(AC63+AC64)/AC153</f>
-        <v>6.5141135874178774E-2</v>
+        <v>6.6550833328929498E-2</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -32838,7 +32838,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="175">
         <f ca="1">(AC107-AC108)/AC153</f>
-        <v>0.26702599674937488</v>
+        <v>0.27280461670922546</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -34343,15 +34343,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="249" t="s">
+      <c r="B4" s="252" t="s">
         <v>282</v>
       </c>
-      <c r="C4" s="249"/>
-      <c r="E4" s="249" t="s">
+      <c r="C4" s="252"/>
+      <c r="E4" s="252" t="s">
         <v>289</v>
       </c>
-      <c r="F4" s="249"/>
-      <c r="G4" s="249"/>
+      <c r="F4" s="252"/>
+      <c r="G4" s="252"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -34359,7 +34359,7 @@
       </c>
       <c r="C5" s="193">
         <f ca="1">Overview!C5</f>
-        <v>10.15</v>
+        <v>9.9350000000000005</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="153" t="s">
@@ -34375,7 +34375,7 @@
       </c>
       <c r="C6" s="194">
         <f ca="1">Statement!AC153</f>
-        <v>5301903.25</v>
+        <v>5189596.9249999998</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>20</v>
@@ -34395,7 +34395,7 @@
       </c>
       <c r="C7" s="194">
         <f ca="1">Statement!AC154</f>
-        <v>3886157.25</v>
+        <v>3773850.9249999998</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>32</v>
@@ -34415,7 +34415,7 @@
       </c>
       <c r="C8" s="195">
         <f ca="1">Statement!AC150</f>
-        <v>16.916666666666664</v>
+        <v>16.55833333333333</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>292</v>
@@ -34435,7 +34435,7 @@
       </c>
       <c r="C9" s="195">
         <f ca="1">Statement!AC151</f>
-        <v>3.269853699628662</v>
+        <v>3.2005907887498282</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>293</v>
@@ -34455,7 +34455,7 @@
       </c>
       <c r="C10" s="195">
         <f ca="1">Statement!AC152</f>
-        <v>2.7635443373892845</v>
+        <v>2.705006206104684</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -34475,7 +34475,7 @@
       </c>
       <c r="C11" s="195">
         <f ca="1">Statement!AC155</f>
-        <v>2.3237980841101935</v>
+        <v>2.256642483839912</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -34484,18 +34484,18 @@
       </c>
       <c r="C12" s="195">
         <f ca="1">Statement!AC156</f>
-        <v>38.416327266975749</v>
+        <v>37.306131189513536</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="249" t="s">
+      <c r="B15" s="252" t="s">
         <v>78</v>
       </c>
-      <c r="C15" s="249"/>
-      <c r="E15" s="249" t="s">
+      <c r="C15" s="252"/>
+      <c r="E15" s="252" t="s">
         <v>295</v>
       </c>
-      <c r="F15" s="249"/>
+      <c r="F15" s="252"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -34546,14 +34546,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="249" t="s">
+      <c r="B21" s="252" t="s">
         <v>294</v>
       </c>
-      <c r="C21" s="249"/>
-      <c r="E21" s="249" t="s">
+      <c r="C21" s="252"/>
+      <c r="E21" s="252" t="s">
         <v>298</v>
       </c>
-      <c r="F21" s="249"/>
+      <c r="F21" s="252"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -34622,14 +34622,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="249" t="s">
+      <c r="B29" s="252" t="s">
         <v>299</v>
       </c>
-      <c r="C29" s="249"/>
-      <c r="E29" s="249" t="s">
+      <c r="C29" s="252"/>
+      <c r="E29" s="252" t="s">
         <v>305</v>
       </c>
-      <c r="F29" s="249"/>
+      <c r="F29" s="252"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -34705,14 +34705,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="249" t="s">
+      <c r="B37" s="252" t="s">
         <v>317</v>
       </c>
-      <c r="C37" s="249"/>
-      <c r="E37" s="249" t="s">
+      <c r="C37" s="252"/>
+      <c r="E37" s="252" t="s">
         <v>320</v>
       </c>
-      <c r="F37" s="249"/>
+      <c r="F37" s="252"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -34720,7 +34720,7 @@
       </c>
       <c r="C38" s="196">
         <f ca="1">Statement!AC162</f>
-        <v>5.9113300492610842E-2</v>
+        <v>6.0392551585304488E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>319</v>
@@ -34736,7 +34736,7 @@
       </c>
       <c r="C39" s="236">
         <f ca="1">Statement!AC161</f>
-        <v>2.0296296429022916E-2</v>
+        <v>2.0735521766943394E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>321</v>
@@ -34768,7 +34768,7 @@
       </c>
       <c r="C41" s="196">
         <f ca="1">Statement!AC164</f>
-        <v>6.5141135874178774E-2</v>
+        <v>6.6550833328929498E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -34777,18 +34777,18 @@
       </c>
       <c r="C42" s="196">
         <f ca="1">Statement!AC165</f>
-        <v>6.5141135874178774E-2</v>
+        <v>6.6550833328929498E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="249" t="s">
+      <c r="B45" s="252" t="s">
         <v>328</v>
       </c>
-      <c r="C45" s="249"/>
-      <c r="E45" s="249" t="s">
+      <c r="C45" s="252"/>
+      <c r="E45" s="252" t="s">
         <v>334</v>
       </c>
-      <c r="F45" s="249"/>
+      <c r="F45" s="252"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -34821,18 +34821,18 @@
       </c>
       <c r="F48" s="196">
         <f ca="1">Statement!AC176</f>
-        <v>0.26702599674937488</v>
+        <v>0.27280461670922546</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="249" t="s">
+      <c r="B51" s="252" t="s">
         <v>331</v>
       </c>
-      <c r="C51" s="249"/>
-      <c r="E51" s="249" t="s">
+      <c r="C51" s="252"/>
+      <c r="E51" s="252" t="s">
         <v>352</v>
       </c>
-      <c r="F51" s="249"/>
+      <c r="F51" s="252"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -35000,7 +35000,7 @@
       </c>
       <c r="I6" s="193">
         <f ca="1">Statement!AC116</f>
-        <v>10.15</v>
+        <v>9.9350000000000005</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -35029,7 +35029,7 @@
       </c>
       <c r="I7" s="194">
         <f ca="1">Statement!AC153</f>
-        <v>5301903.25</v>
+        <v>5189596.9249999998</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -35058,7 +35058,7 @@
       </c>
       <c r="I8" s="194">
         <f ca="1">Statement!AC154</f>
-        <v>3886157.25</v>
+        <v>3773850.9249999998</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -35087,7 +35087,7 @@
       </c>
       <c r="I9" s="195">
         <f ca="1">Statement!AC150</f>
-        <v>16.916666666666664</v>
+        <v>16.55833333333333</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -35116,7 +35116,7 @@
       </c>
       <c r="I10" s="195">
         <f ca="1">Statement!AC151</f>
-        <v>3.269853699628662</v>
+        <v>3.2005907887498282</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -35145,7 +35145,7 @@
       </c>
       <c r="I11" s="195">
         <f ca="1">Statement!AC152</f>
-        <v>2.7635443373892845</v>
+        <v>2.705006206104684</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -35174,7 +35174,7 @@
       </c>
       <c r="I12" s="195">
         <f ca="1">Statement!AC155</f>
-        <v>2.3237980841101935</v>
+        <v>2.256642483839912</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -35203,7 +35203,7 @@
       </c>
       <c r="I13" s="195">
         <f ca="1">Statement!AC156</f>
-        <v>38.416327266975749</v>
+        <v>37.306131189513536</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35976,7 +35976,7 @@
       </c>
       <c r="I51" s="196">
         <f ca="1">Statement!AC162</f>
-        <v>5.9113300492610842E-2</v>
+        <v>6.0392551585304488E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -36005,7 +36005,7 @@
       </c>
       <c r="I52" s="196">
         <f ca="1">Statement!AC161</f>
-        <v>2.0296296429022916E-2</v>
+        <v>2.0735521766943394E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -36063,7 +36063,7 @@
       </c>
       <c r="I54" s="196">
         <f ca="1">Statement!AC164</f>
-        <v>6.5141135874178774E-2</v>
+        <v>6.6550833328929498E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -36092,7 +36092,7 @@
       </c>
       <c r="I55" s="196">
         <f ca="1">Statement!AC165</f>
-        <v>6.5141135874178774E-2</v>
+        <v>6.6550833328929498E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36328,7 +36328,7 @@
       </c>
       <c r="I68" s="217">
         <f ca="1">Statement!AC176</f>
-        <v>0.26702599674937488</v>
+        <v>0.27280461670922546</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36814,14 +36814,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="253" t="s">
+      <c r="C3" s="255" t="s">
         <v>365</v>
       </c>
-      <c r="D3" s="254"/>
-      <c r="F3" s="255" t="s">
+      <c r="D3" s="256"/>
+      <c r="F3" s="257" t="s">
         <v>366</v>
       </c>
-      <c r="G3" s="254"/>
+      <c r="G3" s="256"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -36888,19 +36888,19 @@
       <c r="B7" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C7" s="256">
+      <c r="C7" s="253">
         <f>Statement!AA89</f>
         <v>-0.13037640275448081</v>
       </c>
-      <c r="D7" s="257"/>
-      <c r="F7" s="256">
+      <c r="D7" s="254"/>
+      <c r="F7" s="253">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.17317398716855847</v>
       </c>
-      <c r="G7" s="257"/>
+      <c r="G7" s="254"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="228" t="s">
@@ -36927,19 +36927,19 @@
       <c r="B9" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C9" s="256">
+      <c r="C9" s="253">
         <f>Statement!AA90</f>
         <v>4.0481504023804696E-2</v>
       </c>
-      <c r="D9" s="257"/>
-      <c r="F9" s="256">
+      <c r="D9" s="254"/>
+      <c r="F9" s="253">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.20469173309112548</v>
       </c>
-      <c r="G9" s="257"/>
+      <c r="G9" s="254"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="228" t="s">
@@ -36966,19 +36966,19 @@
       <c r="B11" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C11" s="256">
+      <c r="C11" s="253">
         <f>Statement!AA91</f>
         <v>-0.1614010786596328</v>
       </c>
-      <c r="D11" s="257"/>
-      <c r="F11" s="256">
+      <c r="D11" s="254"/>
+      <c r="F11" s="253">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.16629948047423376</v>
       </c>
-      <c r="G11" s="257"/>
+      <c r="G11" s="254"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="228" t="s">
@@ -37005,19 +37005,19 @@
       <c r="B13" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C13" s="256">
+      <c r="C13" s="253">
         <f>Statement!AA95</f>
         <v>-4.1051008608505718E-2</v>
       </c>
-      <c r="D13" s="257"/>
-      <c r="F13" s="256">
+      <c r="D13" s="254"/>
+      <c r="F13" s="253">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>1.3868988514743887E-2</v>
       </c>
-      <c r="G13" s="257"/>
+      <c r="G13" s="254"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="228" t="s">
@@ -37044,19 +37044,19 @@
       <c r="B15" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C15" s="256">
+      <c r="C15" s="253">
         <f>Statement!AA96</f>
         <v>-0.65140871384799337</v>
       </c>
-      <c r="D15" s="257"/>
-      <c r="F15" s="256">
+      <c r="D15" s="254"/>
+      <c r="F15" s="253">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>2.7052766268583963</v>
       </c>
-      <c r="G15" s="257"/>
+      <c r="G15" s="254"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="228" t="s">
@@ -37083,19 +37083,19 @@
       <c r="B17" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C17" s="256">
+      <c r="C17" s="253">
         <f>Statement!AA98</f>
         <v>-0.78437135034749483</v>
       </c>
-      <c r="D17" s="257"/>
-      <c r="F17" s="256">
+      <c r="D17" s="254"/>
+      <c r="F17" s="253">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>1.9986699179782754</v>
       </c>
-      <c r="G17" s="257"/>
+      <c r="G17" s="254"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="228" t="s">
@@ -37122,22 +37122,22 @@
       <c r="B19" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C19" s="256">
+      <c r="C19" s="253">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-3.2031015030699599E-2</v>
       </c>
-      <c r="D19" s="257"/>
-      <c r="F19" s="256">
+      <c r="D19" s="254"/>
+      <c r="F19" s="253">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-3.7620498458385526E-2</v>
       </c>
-      <c r="G19" s="257"/>
+      <c r="G19" s="254"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="228" t="s">
@@ -37164,22 +37164,22 @@
       <c r="B21" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C21" s="256">
+      <c r="C21" s="253">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>-0.78947368421052633</v>
       </c>
-      <c r="D21" s="257"/>
-      <c r="F21" s="256">
+      <c r="D21" s="254"/>
+      <c r="F21" s="253">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>2</v>
       </c>
-      <c r="G21" s="257"/>
+      <c r="G21" s="254"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -37227,22 +37227,22 @@
       <c r="B25" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C25" s="256">
+      <c r="C25" s="253">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>-0.30844727286201273</v>
       </c>
-      <c r="D25" s="257"/>
-      <c r="F25" s="256">
+      <c r="D25" s="254"/>
+      <c r="F25" s="253">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.16387602700216702</v>
       </c>
-      <c r="G25" s="257"/>
+      <c r="G25" s="254"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="s">
@@ -37269,22 +37269,22 @@
       <c r="B27" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C27" s="256">
+      <c r="C27" s="253">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>6.6472159310281692E-3</v>
       </c>
-      <c r="D27" s="257"/>
-      <c r="F27" s="256">
+      <c r="D27" s="254"/>
+      <c r="F27" s="253">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.16382654634312457</v>
       </c>
-      <c r="G27" s="257"/>
+      <c r="G27" s="254"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
@@ -37311,22 +37311,22 @@
       <c r="B29" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C29" s="256">
+      <c r="C29" s="253">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.15748031496062992</v>
       </c>
-      <c r="D29" s="257"/>
-      <c r="F29" s="256">
+      <c r="D29" s="254"/>
+      <c r="F29" s="253">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>0.46533756230176709</v>
       </c>
-      <c r="G29" s="257"/>
+      <c r="G29" s="254"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B31" s="8" t="s">
@@ -37374,22 +37374,22 @@
       <c r="B33" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C33" s="256">
+      <c r="C33" s="253">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>2.6257619832373135E-2</v>
       </c>
-      <c r="D33" s="257"/>
-      <c r="F33" s="256">
+      <c r="D33" s="254"/>
+      <c r="F33" s="253">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>0.12319376989075922</v>
       </c>
-      <c r="G33" s="257"/>
+      <c r="G33" s="254"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B34" s="20" t="s">
@@ -37416,25 +37416,43 @@
       <c r="B35" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C35" s="256">
+      <c r="C35" s="253">
         <f>IF(C34=0,
 IF(D34=0,0,IF(D34&gt;0,1,-1)),
 (D34-C34)/ABS(C34)
 )</f>
         <v>2.3001949317738791E-2</v>
       </c>
-      <c r="D35" s="257"/>
-      <c r="F35" s="256">
+      <c r="D35" s="254"/>
+      <c r="F35" s="253">
         <f>IF(F34=0,
 IF(G34=0,0,IF(G34&gt;0,1,-1)),
 (G34-F34)/ABS(F34)
 )</f>
         <v>0.10951374207188161</v>
       </c>
-      <c r="G35" s="257"/>
+      <c r="G35" s="254"/>
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="F33:G33"/>
     <mergeCell ref="C35:D35"/>
@@ -37445,24 +37463,6 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/PATH.xlsx
+++ b/PATH.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74269887-1599-534E-8EB3-6DC412C34B42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B58222A8-DD7B-6246-96E4-F65E2ED1FC17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -2376,6 +2376,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2383,15 +2386,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2403,10 +2397,10 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2416,6 +2410,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -12749,11 +12749,11 @@
     <v>Powered by Refinitiv</v>
     <v>19.84</v>
     <v>9.2002000000000006</v>
-    <v>0.98829999999999996</v>
-    <v>-0.375</v>
-    <v>-3.6372000000000002E-2</v>
-    <v>0.04</v>
-    <v>4.0280000000000003E-3</v>
+    <v>0.97809999999999997</v>
+    <v>0.19</v>
+    <v>1.779E-2</v>
+    <v>-0.01</v>
+    <v>-9.2000000000000003E-4</v>
     <v>USD</v>
     <v>UiPath, Inc. is focused on agentic automation and orchestration, empowering enterprises to harness the full potential of AI agents to autonomously execute and optimize complex business processes. It is focused on building and managing automations, starting with computer vision technology and user interface automation in its initial robotic process automation offering. Its AI-powered UiPath Platform offers a robust set of capabilities that allows its customers to discover opportunities for automation, automate using a digital workforce that seamlessly collaborates with humans, and operate a mission-critical automation program at scale. It enables employees to quickly build automations for both existing and new processes and to automate a range of actions including logging into applications, moving folders, filling in forms, reading emails and others. Its platform allows users to design and combine UI automations, API integrations and AI-based document understanding in a single workflow.</v>
     <v>3981</v>
@@ -12761,25 +12761,25 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>One Vanderbilt Avenue, 60th Floor, NEW YORK, NY, 10017 US</v>
-    <v>10.315</v>
+    <v>11.04</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46198.912302546094</v>
+    <v>46203.950890126565</v>
     <v>0</v>
-    <v>9.91</v>
-    <v>5147525180</v>
+    <v>10.48</v>
+    <v>5631967661</v>
     <v>UIPATH, INC.</v>
     <v>UIPATH, INC.</v>
-    <v>10.11</v>
-    <v>16.514299999999999</v>
-    <v>10.31</v>
-    <v>9.9350000000000005</v>
-    <v>9.9700000000000006</v>
+    <v>10.52</v>
+    <v>18.0685</v>
+    <v>10.68</v>
+    <v>10.87</v>
+    <v>10.86</v>
     <v>518120300</v>
     <v>PATH</v>
     <v>UIPATH, INC. (XNYS:PATH)</v>
-    <v>50714464</v>
-    <v>49244198</v>
+    <v>64731597</v>
+    <v>51447922</v>
     <v>2015</v>
   </rv>
   <rv s="2">
@@ -12803,17 +12803,17 @@
     <v>Powered by Refinitiv</v>
     <v>46.87</v>
     <v>39.47</v>
-    <v>-0.1</v>
-    <v>-2.2720000000000001E-3</v>
+    <v>0.02</v>
+    <v>4.5750000000000001E-4</v>
     <v>US</v>
-    <v>44.14</v>
+    <v>43.9</v>
     <v>Index</v>
     <v>3</v>
-    <v>43.63</v>
+    <v>43.67</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>44.12</v>
-    <v>44.02</v>
-    <v>43.92</v>
+    <v>43.78</v>
+    <v>43.72</v>
+    <v>43.74</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -13614,18 +13614,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="249" t="s">
+      <c r="B2" s="250" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="250"/>
-      <c r="E2" s="249" t="s">
+      <c r="C2" s="251"/>
+      <c r="E2" s="250" t="s">
         <v>336</v>
       </c>
-      <c r="F2" s="250"/>
-      <c r="H2" s="249" t="s">
+      <c r="F2" s="251"/>
+      <c r="H2" s="250" t="s">
         <v>381</v>
       </c>
-      <c r="I2" s="250"/>
+      <c r="I2" s="251"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="206" t="s">
@@ -13640,7 +13640,7 @@
       </c>
       <c r="F3" s="208">
         <f ca="1">Statement!AC153</f>
-        <v>5189596.9249999998</v>
+        <v>5677998.8499999996</v>
       </c>
       <c r="H3" s="206" t="str">
         <f>'AVG target price'!B5</f>
@@ -13664,7 +13664,7 @@
       </c>
       <c r="F4" s="209">
         <f ca="1">Statement!AC154</f>
-        <v>3773850.9249999998</v>
+        <v>4262252.8499999996</v>
       </c>
       <c r="H4" s="206" t="str">
         <f>'AVG target price'!B6</f>
@@ -13681,7 +13681,7 @@
       </c>
       <c r="C5" s="229" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>9.9350000000000005</v>
+        <v>10.87</v>
       </c>
       <c r="E5" s="206" t="s">
         <v>292</v>
@@ -13705,14 +13705,14 @@
       </c>
       <c r="C6" s="229" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>9.9700000000000006</v>
+        <v>10.86</v>
       </c>
       <c r="E6" s="206" t="s">
         <v>286</v>
       </c>
       <c r="F6" s="211">
         <f ca="1">Statement!AC150</f>
-        <v>16.55833333333333</v>
+        <v>18.116666666666664</v>
       </c>
       <c r="H6" s="206" t="str">
         <f>'AVG target price'!B8</f>
@@ -13729,14 +13729,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-0.375</v>
+        <v>0.19</v>
       </c>
       <c r="E7" s="207" t="s">
         <v>242</v>
       </c>
       <c r="F7" s="212">
         <f ca="1">Statement!AC151</f>
-        <v>3.2005907887498282</v>
+        <v>3.5018039128042906</v>
       </c>
       <c r="H7" s="205" t="str">
         <f>'AVG target price'!B9</f>
@@ -13753,14 +13753,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="E8" s="206" t="s">
         <v>314</v>
       </c>
       <c r="F8" s="213">
         <f ca="1">Statement!AC161</f>
-        <v>2.0735521766943394E-2</v>
+        <v>1.8951923528480463E-2</v>
       </c>
       <c r="H8" s="205" t="str">
         <f>'AVG target price'!B11</f>
@@ -13768,7 +13768,7 @@
       </c>
       <c r="I8" s="234">
         <f ca="1">'AVG target price'!C11</f>
-        <v>0.15789537786840308</v>
+        <v>5.8297201391222263E-2</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13777,14 +13777,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-3.6372000000000002E-2</v>
+        <v>1.779E-2</v>
       </c>
       <c r="E9" s="206" t="s">
         <v>337</v>
       </c>
       <c r="F9" s="213">
         <f ca="1">Statement!AC162</f>
-        <v>6.0392551585304488E-2</v>
+        <v>5.5197792088316482E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -13793,14 +13793,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>4.0280000000000003E-3</v>
+        <v>-9.2000000000000003E-4</v>
       </c>
       <c r="E10" s="206" t="s">
         <v>342</v>
       </c>
       <c r="F10" s="213">
         <f ca="1">Statement!AC164</f>
-        <v>6.6550833328929498E-2</v>
+        <v>6.0826359624923138E-2</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -13841,7 +13841,7 @@
       </c>
       <c r="C13" s="230" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>0.98829999999999996</v>
+        <v>0.97809999999999997</v>
       </c>
       <c r="E13" s="206" t="s">
         <v>123</v>
@@ -13857,7 +13857,7 @@
       </c>
       <c r="C14" s="231" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>49244198</v>
+        <v>51447922</v>
       </c>
       <c r="E14" s="207" t="s">
         <v>124</v>
@@ -13873,7 +13873,7 @@
       </c>
       <c r="F15" s="213">
         <f ca="1">Statement!AC176</f>
-        <v>0.27280461670922546</v>
+        <v>0.24933890220847793</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -13886,10 +13886,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="251" t="s">
+      <c r="B17" s="252" t="s">
         <v>103</v>
       </c>
-      <c r="C17" s="251"/>
+      <c r="C17" s="252"/>
       <c r="E17" s="205" t="s">
         <v>345</v>
       </c>
@@ -13962,14 +13962,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="251" t="s">
+      <c r="B25" s="252" t="s">
         <v>126</v>
       </c>
-      <c r="C25" s="251"/>
-      <c r="E25" s="249" t="s">
+      <c r="C25" s="252"/>
+      <c r="E25" s="250" t="s">
         <v>401</v>
       </c>
-      <c r="F25" s="250"/>
+      <c r="F25" s="251"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="205" t="s">
@@ -13983,7 +13983,7 @@
       </c>
       <c r="F26" s="240" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>43.92</v>
+        <v>43.74</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -13998,7 +13998,7 @@
       </c>
       <c r="F27" s="241">
         <f ca="1">F26/1000</f>
-        <v>4.3920000000000001E-2</v>
+        <v>4.3740000000000001E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14018,15 +14018,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="252" t="s">
+      <c r="B33" s="249" t="s">
         <v>391</v>
       </c>
-      <c r="C33" s="252"/>
-      <c r="D33" s="252"/>
-      <c r="E33" s="252"/>
-      <c r="F33" s="252"/>
-      <c r="G33" s="252"/>
-      <c r="H33" s="252"/>
+      <c r="C33" s="249"/>
+      <c r="D33" s="249"/>
+      <c r="E33" s="249"/>
+      <c r="F33" s="249"/>
+      <c r="G33" s="249"/>
+      <c r="H33" s="249"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -14045,24 +14045,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="252"/>
-      <c r="C39" s="252"/>
-      <c r="D39" s="252"/>
-      <c r="E39" s="252"/>
-      <c r="F39" s="252"/>
-      <c r="G39" s="252"/>
-      <c r="H39" s="252"/>
+      <c r="B39" s="249"/>
+      <c r="C39" s="249"/>
+      <c r="D39" s="249"/>
+      <c r="E39" s="249"/>
+      <c r="F39" s="249"/>
+      <c r="G39" s="249"/>
+      <c r="H39" s="249"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="252" t="s">
+      <c r="B42" s="249" t="s">
         <v>394</v>
       </c>
-      <c r="C42" s="252"/>
-      <c r="D42" s="252"/>
-      <c r="E42" s="252"/>
-      <c r="F42" s="252"/>
-      <c r="G42" s="252"/>
-      <c r="H42" s="252"/>
+      <c r="C42" s="249"/>
+      <c r="D42" s="249"/>
+      <c r="E42" s="249"/>
+      <c r="F42" s="249"/>
+      <c r="G42" s="249"/>
+      <c r="H42" s="249"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -14077,24 +14077,24 @@
       </c>
     </row>
     <row r="49" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="252"/>
-      <c r="C49" s="252"/>
-      <c r="D49" s="252"/>
-      <c r="E49" s="252"/>
-      <c r="F49" s="252"/>
-      <c r="G49" s="252"/>
-      <c r="H49" s="252"/>
+      <c r="B49" s="249"/>
+      <c r="C49" s="249"/>
+      <c r="D49" s="249"/>
+      <c r="E49" s="249"/>
+      <c r="F49" s="249"/>
+      <c r="G49" s="249"/>
+      <c r="H49" s="249"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B52" s="252" t="s">
+      <c r="B52" s="249" t="s">
         <v>128</v>
       </c>
-      <c r="C52" s="252"/>
-      <c r="D52" s="252"/>
-      <c r="E52" s="252"/>
-      <c r="F52" s="252"/>
-      <c r="G52" s="252"/>
-      <c r="H52" s="252"/>
+      <c r="C52" s="249"/>
+      <c r="D52" s="249"/>
+      <c r="E52" s="249"/>
+      <c r="F52" s="249"/>
+      <c r="G52" s="249"/>
+      <c r="H52" s="249"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B54" s="41" t="s">
@@ -14109,28 +14109,28 @@
       </c>
     </row>
     <row r="59" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="252"/>
-      <c r="C59" s="252"/>
-      <c r="D59" s="252"/>
-      <c r="E59" s="252"/>
-      <c r="F59" s="252"/>
-      <c r="G59" s="252"/>
-      <c r="H59" s="252"/>
+      <c r="B59" s="249"/>
+      <c r="C59" s="249"/>
+      <c r="D59" s="249"/>
+      <c r="E59" s="249"/>
+      <c r="F59" s="249"/>
+      <c r="G59" s="249"/>
+      <c r="H59" s="249"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="E25:F25"/>
     <mergeCell ref="B52:H52"/>
     <mergeCell ref="B59:H59"/>
     <mergeCell ref="B33:H33"/>
     <mergeCell ref="B39:H39"/>
     <mergeCell ref="B42:H42"/>
     <mergeCell ref="B49:H49"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="E25:F25"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -14200,36 +14200,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="252" t="s">
+      <c r="C2" s="249" t="s">
         <v>137</v>
       </c>
-      <c r="D2" s="252"/>
-      <c r="E2" s="252"/>
-      <c r="F2" s="252"/>
-      <c r="G2" s="258"/>
-      <c r="H2" s="259" t="s">
+      <c r="D2" s="249"/>
+      <c r="E2" s="249"/>
+      <c r="F2" s="249"/>
+      <c r="G2" s="261"/>
+      <c r="H2" s="262" t="s">
         <v>138</v>
       </c>
-      <c r="I2" s="252"/>
-      <c r="J2" s="252"/>
-      <c r="K2" s="252"/>
-      <c r="L2" s="252"/>
+      <c r="I2" s="249"/>
+      <c r="J2" s="249"/>
+      <c r="K2" s="249"/>
+      <c r="L2" s="249"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="252" t="s">
+      <c r="S2" s="249" t="s">
         <v>137</v>
       </c>
-      <c r="T2" s="252"/>
-      <c r="U2" s="252"/>
-      <c r="V2" s="252"/>
-      <c r="W2" s="252"/>
-      <c r="X2" s="252"/>
-      <c r="Y2" s="252"/>
-      <c r="Z2" s="252"/>
-      <c r="AA2" s="252" t="s">
+      <c r="T2" s="249"/>
+      <c r="U2" s="249"/>
+      <c r="V2" s="249"/>
+      <c r="W2" s="249"/>
+      <c r="X2" s="249"/>
+      <c r="Y2" s="249"/>
+      <c r="Z2" s="249"/>
+      <c r="AA2" s="249" t="s">
         <v>138</v>
       </c>
-      <c r="AB2" s="252"/>
-      <c r="AC2" s="252"/>
+      <c r="AB2" s="249"/>
+      <c r="AC2" s="249"/>
       <c r="AE2" s="87" t="s">
         <v>139</v>
       </c>
@@ -14240,32 +14240,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="260" t="s">
+      <c r="C4" s="258" t="s">
         <v>140</v>
       </c>
-      <c r="D4" s="260"/>
-      <c r="E4" s="260"/>
-      <c r="F4" s="260"/>
-      <c r="G4" s="260"/>
-      <c r="H4" s="260"/>
-      <c r="I4" s="260"/>
-      <c r="J4" s="260"/>
-      <c r="K4" s="260"/>
-      <c r="L4" s="260"/>
+      <c r="D4" s="258"/>
+      <c r="E4" s="258"/>
+      <c r="F4" s="258"/>
+      <c r="G4" s="258"/>
+      <c r="H4" s="258"/>
+      <c r="I4" s="258"/>
+      <c r="J4" s="258"/>
+      <c r="K4" s="258"/>
+      <c r="L4" s="258"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="261" t="s">
+      <c r="S4" s="259" t="s">
         <v>140</v>
       </c>
-      <c r="T4" s="262"/>
-      <c r="U4" s="262"/>
-      <c r="V4" s="262"/>
-      <c r="W4" s="262"/>
-      <c r="X4" s="262"/>
-      <c r="Y4" s="262"/>
-      <c r="Z4" s="262"/>
-      <c r="AA4" s="262"/>
-      <c r="AB4" s="262"/>
-      <c r="AC4" s="262"/>
+      <c r="T4" s="260"/>
+      <c r="U4" s="260"/>
+      <c r="V4" s="260"/>
+      <c r="W4" s="260"/>
+      <c r="X4" s="260"/>
+      <c r="Y4" s="260"/>
+      <c r="Z4" s="260"/>
+      <c r="AA4" s="260"/>
+      <c r="AB4" s="260"/>
+      <c r="AC4" s="260"/>
       <c r="AE4" s="89"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -14761,33 +14761,33 @@
       <c r="Q10" s="93"/>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C11" s="260" t="s">
+      <c r="C11" s="258" t="s">
         <v>146</v>
       </c>
-      <c r="D11" s="260"/>
-      <c r="E11" s="260"/>
-      <c r="F11" s="260"/>
-      <c r="G11" s="260"/>
-      <c r="H11" s="260"/>
-      <c r="I11" s="260"/>
-      <c r="J11" s="260"/>
-      <c r="K11" s="260"/>
-      <c r="L11" s="260"/>
+      <c r="D11" s="258"/>
+      <c r="E11" s="258"/>
+      <c r="F11" s="258"/>
+      <c r="G11" s="258"/>
+      <c r="H11" s="258"/>
+      <c r="I11" s="258"/>
+      <c r="J11" s="258"/>
+      <c r="K11" s="258"/>
+      <c r="L11" s="258"/>
       <c r="O11" s="5"/>
       <c r="Q11" s="93"/>
-      <c r="S11" s="261" t="s">
+      <c r="S11" s="259" t="s">
         <v>146</v>
       </c>
-      <c r="T11" s="262"/>
-      <c r="U11" s="262"/>
-      <c r="V11" s="262"/>
-      <c r="W11" s="262"/>
-      <c r="X11" s="262"/>
-      <c r="Y11" s="262"/>
-      <c r="Z11" s="262"/>
-      <c r="AA11" s="262"/>
-      <c r="AB11" s="262"/>
-      <c r="AC11" s="262"/>
+      <c r="T11" s="260"/>
+      <c r="U11" s="260"/>
+      <c r="V11" s="260"/>
+      <c r="W11" s="260"/>
+      <c r="X11" s="260"/>
+      <c r="Y11" s="260"/>
+      <c r="Z11" s="260"/>
+      <c r="AA11" s="260"/>
+      <c r="AB11" s="260"/>
+      <c r="AC11" s="260"/>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B12" s="16" t="s">
@@ -15228,33 +15228,33 @@
       <c r="Q18" s="93"/>
     </row>
     <row r="19" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C19" s="260" t="s">
+      <c r="C19" s="258" t="s">
         <v>148</v>
       </c>
-      <c r="D19" s="260"/>
-      <c r="E19" s="260"/>
-      <c r="F19" s="260"/>
-      <c r="G19" s="260"/>
-      <c r="H19" s="260"/>
-      <c r="I19" s="260"/>
-      <c r="J19" s="260"/>
-      <c r="K19" s="260"/>
-      <c r="L19" s="260"/>
+      <c r="D19" s="258"/>
+      <c r="E19" s="258"/>
+      <c r="F19" s="258"/>
+      <c r="G19" s="258"/>
+      <c r="H19" s="258"/>
+      <c r="I19" s="258"/>
+      <c r="J19" s="258"/>
+      <c r="K19" s="258"/>
+      <c r="L19" s="258"/>
       <c r="O19" s="5"/>
       <c r="Q19" s="93"/>
-      <c r="S19" s="261" t="s">
+      <c r="S19" s="259" t="s">
         <v>148</v>
       </c>
-      <c r="T19" s="262"/>
-      <c r="U19" s="262"/>
-      <c r="V19" s="262"/>
-      <c r="W19" s="262"/>
-      <c r="X19" s="262"/>
-      <c r="Y19" s="262"/>
-      <c r="Z19" s="262"/>
-      <c r="AA19" s="262"/>
-      <c r="AB19" s="262"/>
-      <c r="AC19" s="262"/>
+      <c r="T19" s="260"/>
+      <c r="U19" s="260"/>
+      <c r="V19" s="260"/>
+      <c r="W19" s="260"/>
+      <c r="X19" s="260"/>
+      <c r="Y19" s="260"/>
+      <c r="Z19" s="260"/>
+      <c r="AA19" s="260"/>
+      <c r="AB19" s="260"/>
+      <c r="AC19" s="260"/>
       <c r="AE19" s="89">
         <f>AE4</f>
         <v>0</v>
@@ -16072,32 +16072,32 @@
       <c r="O31" s="5"/>
     </row>
     <row r="32" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C32" s="260" t="s">
+      <c r="C32" s="258" t="s">
         <v>150</v>
       </c>
-      <c r="D32" s="260"/>
-      <c r="E32" s="260"/>
-      <c r="F32" s="260"/>
-      <c r="G32" s="260"/>
-      <c r="H32" s="260"/>
-      <c r="I32" s="260"/>
-      <c r="J32" s="260"/>
-      <c r="K32" s="260"/>
-      <c r="L32" s="260"/>
+      <c r="D32" s="258"/>
+      <c r="E32" s="258"/>
+      <c r="F32" s="258"/>
+      <c r="G32" s="258"/>
+      <c r="H32" s="258"/>
+      <c r="I32" s="258"/>
+      <c r="J32" s="258"/>
+      <c r="K32" s="258"/>
+      <c r="L32" s="258"/>
       <c r="O32" s="5"/>
-      <c r="S32" s="261" t="s">
+      <c r="S32" s="259" t="s">
         <v>150</v>
       </c>
-      <c r="T32" s="262"/>
-      <c r="U32" s="262"/>
-      <c r="V32" s="262"/>
-      <c r="W32" s="262"/>
-      <c r="X32" s="262"/>
-      <c r="Y32" s="262"/>
-      <c r="Z32" s="262"/>
-      <c r="AA32" s="262"/>
-      <c r="AB32" s="262"/>
-      <c r="AC32" s="262"/>
+      <c r="T32" s="260"/>
+      <c r="U32" s="260"/>
+      <c r="V32" s="260"/>
+      <c r="W32" s="260"/>
+      <c r="X32" s="260"/>
+      <c r="Y32" s="260"/>
+      <c r="Z32" s="260"/>
+      <c r="AA32" s="260"/>
+      <c r="AB32" s="260"/>
+      <c r="AC32" s="260"/>
     </row>
     <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B33" s="16" t="s">
@@ -16354,18 +16354,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="S11:AC11"/>
     <mergeCell ref="C19:L19"/>
     <mergeCell ref="S19:AC19"/>
     <mergeCell ref="C32:L32"/>
     <mergeCell ref="S32:AC32"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -16402,35 +16402,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="252" t="s">
+      <c r="C2" s="249" t="s">
         <v>137</v>
       </c>
-      <c r="D2" s="252"/>
-      <c r="E2" s="252"/>
-      <c r="F2" s="252"/>
-      <c r="G2" s="258"/>
-      <c r="H2" s="259" t="s">
+      <c r="D2" s="249"/>
+      <c r="E2" s="249"/>
+      <c r="F2" s="249"/>
+      <c r="G2" s="261"/>
+      <c r="H2" s="262" t="s">
         <v>138</v>
       </c>
-      <c r="I2" s="252"/>
-      <c r="J2" s="252"/>
-      <c r="K2" s="252"/>
-      <c r="L2" s="252"/>
-      <c r="P2" s="252" t="s">
+      <c r="I2" s="249"/>
+      <c r="J2" s="249"/>
+      <c r="K2" s="249"/>
+      <c r="L2" s="249"/>
+      <c r="P2" s="249" t="s">
         <v>137</v>
       </c>
-      <c r="Q2" s="252"/>
-      <c r="R2" s="252"/>
-      <c r="S2" s="252"/>
-      <c r="T2" s="252"/>
-      <c r="U2" s="252"/>
-      <c r="V2" s="252"/>
-      <c r="W2" s="252"/>
-      <c r="X2" s="252" t="s">
+      <c r="Q2" s="249"/>
+      <c r="R2" s="249"/>
+      <c r="S2" s="249"/>
+      <c r="T2" s="249"/>
+      <c r="U2" s="249"/>
+      <c r="V2" s="249"/>
+      <c r="W2" s="249"/>
+      <c r="X2" s="249" t="s">
         <v>138</v>
       </c>
-      <c r="Y2" s="252"/>
-      <c r="Z2" s="252"/>
+      <c r="Y2" s="249"/>
+      <c r="Z2" s="249"/>
       <c r="AB2" s="87" t="s">
         <v>139</v>
       </c>
@@ -16439,31 +16439,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="260" t="s">
+      <c r="C4" s="258" t="s">
         <v>140</v>
       </c>
-      <c r="D4" s="260"/>
-      <c r="E4" s="260"/>
-      <c r="F4" s="260"/>
-      <c r="G4" s="260"/>
-      <c r="H4" s="260"/>
-      <c r="I4" s="260"/>
-      <c r="J4" s="260"/>
-      <c r="K4" s="260"/>
-      <c r="L4" s="260"/>
-      <c r="P4" s="262" t="s">
+      <c r="D4" s="258"/>
+      <c r="E4" s="258"/>
+      <c r="F4" s="258"/>
+      <c r="G4" s="258"/>
+      <c r="H4" s="258"/>
+      <c r="I4" s="258"/>
+      <c r="J4" s="258"/>
+      <c r="K4" s="258"/>
+      <c r="L4" s="258"/>
+      <c r="P4" s="260" t="s">
         <v>140</v>
       </c>
-      <c r="Q4" s="262"/>
-      <c r="R4" s="262"/>
-      <c r="S4" s="262"/>
-      <c r="T4" s="262"/>
-      <c r="U4" s="262"/>
-      <c r="V4" s="262"/>
-      <c r="W4" s="262"/>
-      <c r="X4" s="262"/>
-      <c r="Y4" s="262"/>
-      <c r="Z4" s="262"/>
+      <c r="Q4" s="260"/>
+      <c r="R4" s="260"/>
+      <c r="S4" s="260"/>
+      <c r="T4" s="260"/>
+      <c r="U4" s="260"/>
+      <c r="V4" s="260"/>
+      <c r="W4" s="260"/>
+      <c r="X4" s="260"/>
+      <c r="Y4" s="260"/>
+      <c r="Z4" s="260"/>
       <c r="AB4" s="89"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -16658,32 +16658,32 @@
       <c r="N8" s="93"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="260" t="s">
+      <c r="C9" s="258" t="s">
         <v>166</v>
       </c>
-      <c r="D9" s="260"/>
-      <c r="E9" s="260"/>
-      <c r="F9" s="260"/>
-      <c r="G9" s="260"/>
-      <c r="H9" s="260"/>
-      <c r="I9" s="260"/>
-      <c r="J9" s="260"/>
-      <c r="K9" s="260"/>
-      <c r="L9" s="260"/>
+      <c r="D9" s="258"/>
+      <c r="E9" s="258"/>
+      <c r="F9" s="258"/>
+      <c r="G9" s="258"/>
+      <c r="H9" s="258"/>
+      <c r="I9" s="258"/>
+      <c r="J9" s="258"/>
+      <c r="K9" s="258"/>
+      <c r="L9" s="258"/>
       <c r="N9" s="93"/>
-      <c r="P9" s="262" t="s">
+      <c r="P9" s="260" t="s">
         <v>167</v>
       </c>
-      <c r="Q9" s="262"/>
-      <c r="R9" s="262"/>
-      <c r="S9" s="262"/>
-      <c r="T9" s="262"/>
-      <c r="U9" s="262"/>
-      <c r="V9" s="262"/>
-      <c r="W9" s="262"/>
-      <c r="X9" s="262"/>
-      <c r="Y9" s="262"/>
-      <c r="Z9" s="262"/>
+      <c r="Q9" s="260"/>
+      <c r="R9" s="260"/>
+      <c r="S9" s="260"/>
+      <c r="T9" s="260"/>
+      <c r="U9" s="260"/>
+      <c r="V9" s="260"/>
+      <c r="W9" s="260"/>
+      <c r="X9" s="260"/>
+      <c r="Y9" s="260"/>
+      <c r="Z9" s="260"/>
       <c r="AB9" s="89">
         <f>AB4</f>
         <v>0</v>
@@ -17532,31 +17532,31 @@
       </c>
     </row>
     <row r="21" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="C21" s="260" t="s">
+      <c r="C21" s="258" t="s">
         <v>169</v>
       </c>
-      <c r="D21" s="260"/>
-      <c r="E21" s="260"/>
-      <c r="F21" s="260"/>
-      <c r="G21" s="260"/>
-      <c r="H21" s="260"/>
-      <c r="I21" s="260"/>
-      <c r="J21" s="260"/>
-      <c r="K21" s="260"/>
-      <c r="L21" s="260"/>
-      <c r="P21" s="262" t="s">
+      <c r="D21" s="258"/>
+      <c r="E21" s="258"/>
+      <c r="F21" s="258"/>
+      <c r="G21" s="258"/>
+      <c r="H21" s="258"/>
+      <c r="I21" s="258"/>
+      <c r="J21" s="258"/>
+      <c r="K21" s="258"/>
+      <c r="L21" s="258"/>
+      <c r="P21" s="260" t="s">
         <v>169</v>
       </c>
-      <c r="Q21" s="262"/>
-      <c r="R21" s="262"/>
-      <c r="S21" s="262"/>
-      <c r="T21" s="262"/>
-      <c r="U21" s="262"/>
-      <c r="V21" s="262"/>
-      <c r="W21" s="262"/>
-      <c r="X21" s="262"/>
-      <c r="Y21" s="262"/>
-      <c r="Z21" s="262"/>
+      <c r="Q21" s="260"/>
+      <c r="R21" s="260"/>
+      <c r="S21" s="260"/>
+      <c r="T21" s="260"/>
+      <c r="U21" s="260"/>
+      <c r="V21" s="260"/>
+      <c r="W21" s="260"/>
+      <c r="X21" s="260"/>
+      <c r="Y21" s="260"/>
+      <c r="Z21" s="260"/>
     </row>
     <row r="22" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B22" s="16" t="s">
@@ -18371,20 +18371,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="252" t="s">
+      <c r="C3" s="249" t="s">
         <v>137</v>
       </c>
-      <c r="D3" s="252"/>
-      <c r="E3" s="252"/>
-      <c r="F3" s="252"/>
-      <c r="G3" s="258"/>
-      <c r="H3" s="259" t="s">
+      <c r="D3" s="249"/>
+      <c r="E3" s="249"/>
+      <c r="F3" s="249"/>
+      <c r="G3" s="261"/>
+      <c r="H3" s="262" t="s">
         <v>138</v>
       </c>
-      <c r="I3" s="252"/>
-      <c r="J3" s="252"/>
-      <c r="K3" s="252"/>
-      <c r="L3" s="252"/>
+      <c r="I3" s="249"/>
+      <c r="J3" s="249"/>
+      <c r="K3" s="249"/>
+      <c r="L3" s="249"/>
       <c r="P3" s="263"/>
       <c r="Q3" s="263"/>
       <c r="R3" s="263"/>
@@ -18402,18 +18402,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="88"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="260" t="s">
+      <c r="C5" s="258" t="s">
         <v>140</v>
       </c>
-      <c r="D5" s="260"/>
-      <c r="E5" s="260"/>
-      <c r="F5" s="260"/>
-      <c r="G5" s="260"/>
-      <c r="H5" s="260"/>
-      <c r="I5" s="260"/>
-      <c r="J5" s="260"/>
-      <c r="K5" s="260"/>
-      <c r="L5" s="260"/>
+      <c r="D5" s="258"/>
+      <c r="E5" s="258"/>
+      <c r="F5" s="258"/>
+      <c r="G5" s="258"/>
+      <c r="H5" s="258"/>
+      <c r="I5" s="258"/>
+      <c r="J5" s="258"/>
+      <c r="K5" s="258"/>
+      <c r="L5" s="258"/>
       <c r="P5" s="263"/>
       <c r="Q5" s="263"/>
       <c r="R5" s="263"/>
@@ -18610,18 +18610,18 @@
       <c r="N10" s="93"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="260" t="s">
+      <c r="C11" s="258" t="s">
         <v>173</v>
       </c>
-      <c r="D11" s="260"/>
-      <c r="E11" s="260"/>
-      <c r="F11" s="260"/>
-      <c r="G11" s="260"/>
-      <c r="H11" s="260"/>
-      <c r="I11" s="260"/>
-      <c r="J11" s="260"/>
-      <c r="K11" s="260"/>
-      <c r="L11" s="260"/>
+      <c r="D11" s="258"/>
+      <c r="E11" s="258"/>
+      <c r="F11" s="258"/>
+      <c r="G11" s="258"/>
+      <c r="H11" s="258"/>
+      <c r="I11" s="258"/>
+      <c r="J11" s="258"/>
+      <c r="K11" s="258"/>
+      <c r="L11" s="258"/>
       <c r="N11" s="93"/>
       <c r="P11" s="263"/>
       <c r="Q11" s="263"/>
@@ -18875,18 +18875,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="260" t="s">
+      <c r="C18" s="258" t="s">
         <v>178</v>
       </c>
-      <c r="D18" s="260"/>
-      <c r="E18" s="260"/>
-      <c r="F18" s="260"/>
-      <c r="G18" s="260"/>
-      <c r="H18" s="260"/>
-      <c r="I18" s="260"/>
-      <c r="J18" s="260"/>
-      <c r="K18" s="260"/>
-      <c r="L18" s="260"/>
+      <c r="D18" s="258"/>
+      <c r="E18" s="258"/>
+      <c r="F18" s="258"/>
+      <c r="G18" s="258"/>
+      <c r="H18" s="258"/>
+      <c r="I18" s="258"/>
+      <c r="J18" s="258"/>
+      <c r="K18" s="258"/>
+      <c r="L18" s="258"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19104,18 +19104,18 @@
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="130"/>
-      <c r="C26" s="260" t="s">
+      <c r="C26" s="258" t="s">
         <v>184</v>
       </c>
-      <c r="D26" s="260"/>
-      <c r="E26" s="260"/>
-      <c r="F26" s="260"/>
-      <c r="G26" s="260"/>
-      <c r="H26" s="260"/>
-      <c r="I26" s="260"/>
-      <c r="J26" s="260"/>
-      <c r="K26" s="260"/>
-      <c r="L26" s="260"/>
+      <c r="D26" s="258"/>
+      <c r="E26" s="258"/>
+      <c r="F26" s="258"/>
+      <c r="G26" s="258"/>
+      <c r="H26" s="258"/>
+      <c r="I26" s="258"/>
+      <c r="J26" s="258"/>
+      <c r="K26" s="258"/>
+      <c r="L26" s="258"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -19307,18 +19307,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="130"/>
-      <c r="C33" s="260" t="s">
+      <c r="C33" s="258" t="s">
         <v>188</v>
       </c>
-      <c r="D33" s="260"/>
-      <c r="E33" s="260"/>
-      <c r="F33" s="260"/>
-      <c r="G33" s="260"/>
-      <c r="H33" s="260"/>
-      <c r="I33" s="260"/>
-      <c r="J33" s="260"/>
-      <c r="K33" s="260"/>
-      <c r="L33" s="260"/>
+      <c r="D33" s="258"/>
+      <c r="E33" s="258"/>
+      <c r="F33" s="258"/>
+      <c r="G33" s="258"/>
+      <c r="H33" s="258"/>
+      <c r="I33" s="258"/>
+      <c r="J33" s="258"/>
+      <c r="K33" s="258"/>
+      <c r="L33" s="258"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -19502,18 +19502,18 @@
       <c r="C39" s="146"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="260" t="s">
+      <c r="C40" s="258" t="s">
         <v>191</v>
       </c>
-      <c r="D40" s="260"/>
-      <c r="E40" s="260"/>
-      <c r="F40" s="260"/>
-      <c r="G40" s="260"/>
-      <c r="H40" s="260"/>
-      <c r="I40" s="260"/>
-      <c r="J40" s="260"/>
-      <c r="K40" s="260"/>
-      <c r="L40" s="260"/>
+      <c r="D40" s="258"/>
+      <c r="E40" s="258"/>
+      <c r="F40" s="258"/>
+      <c r="G40" s="258"/>
+      <c r="H40" s="258"/>
+      <c r="I40" s="258"/>
+      <c r="J40" s="258"/>
+      <c r="K40" s="258"/>
+      <c r="L40" s="258"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -19777,12 +19777,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -19790,6 +19784,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -19827,20 +19827,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="252" t="s">
+      <c r="C2" s="249" t="s">
         <v>137</v>
       </c>
-      <c r="D2" s="252"/>
-      <c r="E2" s="252"/>
-      <c r="F2" s="252"/>
-      <c r="G2" s="258"/>
-      <c r="H2" s="259" t="s">
+      <c r="D2" s="249"/>
+      <c r="E2" s="249"/>
+      <c r="F2" s="249"/>
+      <c r="G2" s="261"/>
+      <c r="H2" s="262" t="s">
         <v>138</v>
       </c>
-      <c r="I2" s="252"/>
-      <c r="J2" s="252"/>
-      <c r="K2" s="252"/>
-      <c r="L2" s="252"/>
+      <c r="I2" s="249"/>
+      <c r="J2" s="249"/>
+      <c r="K2" s="249"/>
+      <c r="L2" s="249"/>
       <c r="S2" s="263"/>
       <c r="T2" s="263"/>
       <c r="U2" s="263"/>
@@ -19858,18 +19858,18 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="260" t="s">
+      <c r="C4" s="258" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="260"/>
-      <c r="E4" s="260"/>
-      <c r="F4" s="260"/>
-      <c r="G4" s="260"/>
-      <c r="H4" s="260"/>
-      <c r="I4" s="260"/>
-      <c r="J4" s="260"/>
-      <c r="K4" s="260"/>
-      <c r="L4" s="260"/>
+      <c r="D4" s="258"/>
+      <c r="E4" s="258"/>
+      <c r="F4" s="258"/>
+      <c r="G4" s="258"/>
+      <c r="H4" s="258"/>
+      <c r="I4" s="258"/>
+      <c r="J4" s="258"/>
+      <c r="K4" s="258"/>
+      <c r="L4" s="258"/>
       <c r="S4" s="263"/>
       <c r="T4" s="263"/>
       <c r="U4" s="263"/>
@@ -20243,18 +20243,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="260" t="s">
+      <c r="C13" s="258" t="s">
         <v>199</v>
       </c>
-      <c r="D13" s="260"/>
-      <c r="E13" s="260"/>
-      <c r="F13" s="260"/>
-      <c r="G13" s="260"/>
-      <c r="H13" s="260"/>
-      <c r="I13" s="260"/>
-      <c r="J13" s="260"/>
-      <c r="K13" s="260"/>
-      <c r="L13" s="260"/>
+      <c r="D13" s="258"/>
+      <c r="E13" s="258"/>
+      <c r="F13" s="258"/>
+      <c r="G13" s="258"/>
+      <c r="H13" s="258"/>
+      <c r="I13" s="258"/>
+      <c r="J13" s="258"/>
+      <c r="K13" s="258"/>
+      <c r="L13" s="258"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -20347,18 +20347,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="260" t="s">
+      <c r="C18" s="258" t="s">
         <v>200</v>
       </c>
-      <c r="D18" s="260"/>
-      <c r="E18" s="260"/>
-      <c r="F18" s="260"/>
-      <c r="G18" s="260"/>
-      <c r="H18" s="260"/>
-      <c r="I18" s="260"/>
-      <c r="J18" s="260"/>
-      <c r="K18" s="260"/>
-      <c r="L18" s="260"/>
+      <c r="D18" s="258"/>
+      <c r="E18" s="258"/>
+      <c r="F18" s="258"/>
+      <c r="G18" s="258"/>
+      <c r="H18" s="258"/>
+      <c r="I18" s="258"/>
+      <c r="J18" s="258"/>
+      <c r="K18" s="258"/>
+      <c r="L18" s="258"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -20550,18 +20550,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="260" t="s">
+      <c r="C25" s="258" t="s">
         <v>311</v>
       </c>
-      <c r="D25" s="260"/>
-      <c r="E25" s="260"/>
-      <c r="F25" s="260"/>
-      <c r="G25" s="260"/>
-      <c r="H25" s="260"/>
-      <c r="I25" s="260"/>
-      <c r="J25" s="260"/>
-      <c r="K25" s="260"/>
-      <c r="L25" s="260"/>
+      <c r="D25" s="258"/>
+      <c r="E25" s="258"/>
+      <c r="F25" s="258"/>
+      <c r="G25" s="258"/>
+      <c r="H25" s="258"/>
+      <c r="I25" s="258"/>
+      <c r="J25" s="258"/>
+      <c r="K25" s="258"/>
+      <c r="L25" s="258"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -20699,18 +20699,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="260" t="s">
+      <c r="C31" s="258" t="s">
         <v>78</v>
       </c>
-      <c r="D31" s="260"/>
-      <c r="E31" s="260"/>
-      <c r="F31" s="260"/>
-      <c r="G31" s="260"/>
-      <c r="H31" s="260"/>
-      <c r="I31" s="260"/>
-      <c r="J31" s="260"/>
-      <c r="K31" s="260"/>
-      <c r="L31" s="260"/>
+      <c r="D31" s="258"/>
+      <c r="E31" s="258"/>
+      <c r="F31" s="258"/>
+      <c r="G31" s="258"/>
+      <c r="H31" s="258"/>
+      <c r="I31" s="258"/>
+      <c r="J31" s="258"/>
+      <c r="K31" s="258"/>
+      <c r="L31" s="258"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -20849,16 +20849,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -20921,10 +20921,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="252" t="s">
+      <c r="B4" s="249" t="s">
         <v>207</v>
       </c>
-      <c r="C4" s="252"/>
+      <c r="C4" s="249"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -20941,7 +20941,7 @@
       </c>
       <c r="C6" s="154">
         <f ca="1">Overview!C5</f>
-        <v>9.9350000000000005</v>
+        <v>10.87</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20950,7 +20950,7 @@
       </c>
       <c r="C7" s="155">
         <f ca="1">C5*C6</f>
-        <v>5189596.9249999998</v>
+        <v>5677998.8499999996</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20968,7 +20968,7 @@
       </c>
       <c r="C9" s="156">
         <f ca="1">Overview!F27</f>
-        <v>4.3920000000000001E-2</v>
+        <v>4.3740000000000001E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20977,7 +20977,7 @@
       </c>
       <c r="C10" s="154">
         <f ca="1">Overview!C13</f>
-        <v>0.98829999999999996</v>
+        <v>0.97809999999999997</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21009,10 +21009,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="252" t="s">
+      <c r="B15" s="249" t="s">
         <v>214</v>
       </c>
-      <c r="C15" s="252"/>
+      <c r="C15" s="249"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -21047,7 +21047,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>8.83935E-2</v>
+        <v>8.7754499999999999E-2</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21056,7 +21056,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>8.83935E-2</v>
+        <v>8.7754499999999999E-2</v>
       </c>
     </row>
   </sheetData>
@@ -21101,20 +21101,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="252" t="s">
+      <c r="C3" s="249" t="s">
         <v>137</v>
       </c>
-      <c r="D3" s="252"/>
-      <c r="E3" s="252"/>
-      <c r="F3" s="252"/>
-      <c r="G3" s="258"/>
-      <c r="H3" s="259" t="s">
+      <c r="D3" s="249"/>
+      <c r="E3" s="249"/>
+      <c r="F3" s="249"/>
+      <c r="G3" s="261"/>
+      <c r="H3" s="262" t="s">
         <v>138</v>
       </c>
-      <c r="I3" s="252"/>
-      <c r="J3" s="252"/>
-      <c r="K3" s="252"/>
-      <c r="L3" s="252"/>
+      <c r="I3" s="249"/>
+      <c r="J3" s="249"/>
+      <c r="K3" s="249"/>
+      <c r="L3" s="249"/>
       <c r="P3" s="263"/>
       <c r="Q3" s="263"/>
       <c r="R3" s="263"/>
@@ -21132,18 +21132,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="88"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="260" t="s">
+      <c r="C5" s="258" t="s">
         <v>221</v>
       </c>
-      <c r="D5" s="260"/>
-      <c r="E5" s="260"/>
-      <c r="F5" s="260"/>
-      <c r="G5" s="260"/>
-      <c r="H5" s="260"/>
-      <c r="I5" s="260"/>
-      <c r="J5" s="260"/>
-      <c r="K5" s="260"/>
-      <c r="L5" s="260"/>
+      <c r="D5" s="258"/>
+      <c r="E5" s="258"/>
+      <c r="F5" s="258"/>
+      <c r="G5" s="258"/>
+      <c r="H5" s="258"/>
+      <c r="I5" s="258"/>
+      <c r="J5" s="258"/>
+      <c r="K5" s="258"/>
+      <c r="L5" s="258"/>
       <c r="P5" s="263"/>
       <c r="Q5" s="263"/>
       <c r="R5" s="263"/>
@@ -21400,10 +21400,10 @@
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="252" t="s">
+      <c r="B13" s="249" t="s">
         <v>225</v>
       </c>
-      <c r="C13" s="252"/>
+      <c r="C13" s="249"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -21423,10 +21423,10 @@
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="252" t="s">
+      <c r="B18" s="249" t="s">
         <v>227</v>
       </c>
-      <c r="C18" s="252"/>
+      <c r="C18" s="249"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -21540,37 +21540,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="252" t="s">
+      <c r="C2" s="249" t="s">
         <v>137</v>
       </c>
-      <c r="D2" s="252"/>
-      <c r="E2" s="252"/>
-      <c r="F2" s="252"/>
-      <c r="G2" s="258"/>
-      <c r="H2" s="259" t="s">
+      <c r="D2" s="249"/>
+      <c r="E2" s="249"/>
+      <c r="F2" s="249"/>
+      <c r="G2" s="261"/>
+      <c r="H2" s="262" t="s">
         <v>138</v>
       </c>
-      <c r="I2" s="252"/>
-      <c r="J2" s="252"/>
-      <c r="K2" s="252"/>
-      <c r="L2" s="252"/>
+      <c r="I2" s="249"/>
+      <c r="J2" s="249"/>
+      <c r="K2" s="249"/>
+      <c r="L2" s="249"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="260" t="s">
+      <c r="C4" s="258" t="s">
         <v>235</v>
       </c>
-      <c r="D4" s="260"/>
-      <c r="E4" s="260"/>
-      <c r="F4" s="260"/>
-      <c r="G4" s="260"/>
-      <c r="H4" s="260"/>
-      <c r="I4" s="260"/>
-      <c r="J4" s="260"/>
-      <c r="K4" s="260"/>
-      <c r="L4" s="260"/>
+      <c r="D4" s="258"/>
+      <c r="E4" s="258"/>
+      <c r="F4" s="258"/>
+      <c r="G4" s="258"/>
+      <c r="H4" s="258"/>
+      <c r="I4" s="258"/>
+      <c r="J4" s="258"/>
+      <c r="K4" s="258"/>
+      <c r="L4" s="258"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -21759,18 +21759,18 @@
       <c r="N9" s="93"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C10" s="260" t="s">
+      <c r="C10" s="258" t="s">
         <v>146</v>
       </c>
-      <c r="D10" s="260"/>
-      <c r="E10" s="260"/>
-      <c r="F10" s="260"/>
-      <c r="G10" s="260"/>
-      <c r="H10" s="260"/>
-      <c r="I10" s="260"/>
-      <c r="J10" s="260"/>
-      <c r="K10" s="260"/>
-      <c r="L10" s="260"/>
+      <c r="D10" s="258"/>
+      <c r="E10" s="258"/>
+      <c r="F10" s="258"/>
+      <c r="G10" s="258"/>
+      <c r="H10" s="258"/>
+      <c r="I10" s="258"/>
+      <c r="J10" s="258"/>
+      <c r="K10" s="258"/>
+      <c r="L10" s="258"/>
       <c r="N10" s="93"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21964,18 +21964,18 @@
       <c r="N15" s="93"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C16" s="260" t="s">
+      <c r="C16" s="258" t="s">
         <v>237</v>
       </c>
-      <c r="D16" s="260"/>
-      <c r="E16" s="260"/>
-      <c r="F16" s="260"/>
-      <c r="G16" s="260"/>
-      <c r="H16" s="260"/>
-      <c r="I16" s="260"/>
-      <c r="J16" s="260"/>
-      <c r="K16" s="260"/>
-      <c r="L16" s="260"/>
+      <c r="D16" s="258"/>
+      <c r="E16" s="258"/>
+      <c r="F16" s="258"/>
+      <c r="G16" s="258"/>
+      <c r="H16" s="258"/>
+      <c r="I16" s="258"/>
+      <c r="J16" s="258"/>
+      <c r="K16" s="258"/>
+      <c r="L16" s="258"/>
       <c r="N16" s="93"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
@@ -22109,18 +22109,18 @@
       <c r="N20" s="93"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C21" s="260" t="s">
+      <c r="C21" s="258" t="s">
         <v>240</v>
       </c>
-      <c r="D21" s="260"/>
-      <c r="E21" s="260"/>
-      <c r="F21" s="260"/>
-      <c r="G21" s="260"/>
-      <c r="H21" s="260"/>
-      <c r="I21" s="260"/>
-      <c r="J21" s="260"/>
-      <c r="K21" s="260"/>
-      <c r="L21" s="260"/>
+      <c r="D21" s="258"/>
+      <c r="E21" s="258"/>
+      <c r="F21" s="258"/>
+      <c r="G21" s="258"/>
+      <c r="H21" s="258"/>
+      <c r="I21" s="258"/>
+      <c r="J21" s="258"/>
+      <c r="K21" s="258"/>
+      <c r="L21" s="258"/>
       <c r="N21" s="93"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
@@ -22204,18 +22204,18 @@
       <c r="N25" s="93"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C26" s="260" t="s">
+      <c r="C26" s="258" t="s">
         <v>241</v>
       </c>
-      <c r="D26" s="260"/>
-      <c r="E26" s="260"/>
-      <c r="F26" s="260"/>
-      <c r="G26" s="260"/>
-      <c r="H26" s="260"/>
-      <c r="I26" s="260"/>
-      <c r="J26" s="260"/>
-      <c r="K26" s="260"/>
-      <c r="L26" s="260"/>
+      <c r="D26" s="258"/>
+      <c r="E26" s="258"/>
+      <c r="F26" s="258"/>
+      <c r="G26" s="258"/>
+      <c r="H26" s="258"/>
+      <c r="I26" s="258"/>
+      <c r="J26" s="258"/>
+      <c r="K26" s="258"/>
+      <c r="L26" s="258"/>
       <c r="N26" s="93"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
@@ -22485,10 +22485,10 @@
       <c r="N36" s="93"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="252" t="s">
+      <c r="B37" s="249" t="s">
         <v>246</v>
       </c>
-      <c r="C37" s="252"/>
+      <c r="C37" s="249"/>
       <c r="N37" s="93"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -22563,10 +22563,10 @@
       </c>
     </row>
     <row r="47" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B47" s="252" t="s">
+      <c r="B47" s="249" t="s">
         <v>251</v>
       </c>
-      <c r="C47" s="252"/>
+      <c r="C47" s="249"/>
     </row>
     <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B48" s="1" t="s">
@@ -22622,10 +22622,10 @@
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B55" s="252" t="s">
+      <c r="B55" s="249" t="s">
         <v>375</v>
       </c>
-      <c r="C55" s="252"/>
+      <c r="C55" s="249"/>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B56" s="1" t="s">
@@ -22738,10 +22738,10 @@
       <c r="N3" s="93"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="252" t="s">
+      <c r="B4" s="249" t="s">
         <v>256</v>
       </c>
-      <c r="C4" s="252"/>
+      <c r="C4" s="249"/>
       <c r="N4" s="93"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -22795,7 +22795,7 @@
       </c>
       <c r="C10" s="154">
         <f ca="1">Overview!C5</f>
-        <v>9.9350000000000005</v>
+        <v>10.87</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -22804,7 +22804,7 @@
       </c>
       <c r="C11" s="175">
         <f ca="1">(C9-C10)/C10</f>
-        <v>0.15789537786840308</v>
+        <v>5.8297201391222263E-2</v>
       </c>
     </row>
   </sheetData>
@@ -22869,20 +22869,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="252" t="s">
+      <c r="C3" s="249" t="s">
         <v>137</v>
       </c>
-      <c r="D3" s="252"/>
-      <c r="E3" s="252"/>
-      <c r="F3" s="252"/>
-      <c r="G3" s="258"/>
-      <c r="H3" s="259" t="s">
+      <c r="D3" s="249"/>
+      <c r="E3" s="249"/>
+      <c r="F3" s="249"/>
+      <c r="G3" s="261"/>
+      <c r="H3" s="262" t="s">
         <v>138</v>
       </c>
-      <c r="I3" s="252"/>
-      <c r="J3" s="252"/>
-      <c r="K3" s="252"/>
-      <c r="L3" s="252"/>
+      <c r="I3" s="249"/>
+      <c r="J3" s="249"/>
+      <c r="K3" s="249"/>
+      <c r="L3" s="249"/>
       <c r="P3" s="263"/>
       <c r="Q3" s="263"/>
       <c r="R3" s="263"/>
@@ -22900,18 +22900,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="88"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="260" t="s">
+      <c r="C5" s="258" t="s">
         <v>221</v>
       </c>
-      <c r="D5" s="260"/>
-      <c r="E5" s="260"/>
-      <c r="F5" s="260"/>
-      <c r="G5" s="260"/>
-      <c r="H5" s="260"/>
-      <c r="I5" s="260"/>
-      <c r="J5" s="260"/>
-      <c r="K5" s="260"/>
-      <c r="L5" s="260"/>
+      <c r="D5" s="258"/>
+      <c r="E5" s="258"/>
+      <c r="F5" s="258"/>
+      <c r="G5" s="258"/>
+      <c r="H5" s="258"/>
+      <c r="I5" s="258"/>
+      <c r="J5" s="258"/>
+      <c r="K5" s="258"/>
+      <c r="L5" s="258"/>
       <c r="P5" s="263"/>
       <c r="Q5" s="263"/>
       <c r="R5" s="263"/>
@@ -23161,7 +23161,7 @@
       </c>
       <c r="C15" s="177">
         <f ca="1">Overview!C5</f>
-        <v>9.9350000000000005</v>
+        <v>10.87</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -23227,7 +23227,7 @@
       </c>
       <c r="C23" s="182">
         <f ca="1">C15*C22</f>
-        <v>5147532.1350000007</v>
+        <v>5631975.2699999996</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -23254,7 +23254,7 @@
       </c>
       <c r="C26" s="183">
         <f ca="1">C23+C25-C24</f>
-        <v>3731786.1350000007</v>
+        <v>4216229.2699999996</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -23337,18 +23337,18 @@
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C39" s="260" t="s">
+      <c r="C39" s="258" t="s">
         <v>270</v>
       </c>
-      <c r="D39" s="260"/>
-      <c r="E39" s="260"/>
-      <c r="F39" s="260"/>
-      <c r="G39" s="260"/>
-      <c r="H39" s="260"/>
-      <c r="I39" s="260"/>
-      <c r="J39" s="260"/>
-      <c r="K39" s="260"/>
-      <c r="L39" s="260"/>
+      <c r="D39" s="258"/>
+      <c r="E39" s="258"/>
+      <c r="F39" s="258"/>
+      <c r="G39" s="258"/>
+      <c r="H39" s="258"/>
+      <c r="I39" s="258"/>
+      <c r="J39" s="258"/>
+      <c r="K39" s="258"/>
+      <c r="L39" s="258"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="12">
@@ -23780,17 +23780,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -30403,7 +30403,7 @@
       <c r="AA116" s="68"/>
       <c r="AC116" s="63">
         <f ca="1">Overview!C5</f>
-        <v>9.9350000000000005</v>
+        <v>10.87</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -30450,7 +30450,7 @@
       <c r="AA117" s="68"/>
       <c r="AC117" s="65">
         <f ca="1">AC116/AC85</f>
-        <v>9.9350000000000005</v>
+        <v>10.87</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -31756,7 +31756,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>16.55833333333333</v>
+        <v>18.116666666666664</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -31793,7 +31793,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>3.2005907887498282</v>
+        <v>3.5018039128042906</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -31830,7 +31830,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="72">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>2.705006206104684</v>
+        <v>2.9595790095981793</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -31867,7 +31867,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="164">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>5189596.9249999998</v>
+        <v>5677998.8499999996</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -31904,7 +31904,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="164">
         <f ca="1">AC153+AC108-AC107+AC48+AC45</f>
-        <v>3773850.9249999998</v>
+        <v>4262252.8499999996</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -31941,7 +31941,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="204">
         <f ca="1">AC154/AC5</f>
-        <v>2.256642483839912</v>
+        <v>2.5486912571083455</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -31978,7 +31978,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="204">
         <f ca="1">AC154/AC12</f>
-        <v>37.306131189513536</v>
+        <v>42.134193200802692</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -32113,7 +32113,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="72">
         <f t="shared" ref="AC159:AC160" ca="1" si="101">AC153/AC157</f>
-        <v>48.226420884870222</v>
+        <v>52.765092603778491</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -32150,7 +32150,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
         <f t="shared" ca="1" si="101"/>
-        <v>-69.583311975661474</v>
+        <v>-78.588602378537843</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -32187,7 +32187,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="74">
         <f t="shared" ref="AC161" ca="1" si="104">AC157/AC153</f>
-        <v>2.0735521766943394E-2</v>
+        <v>1.8951923528480463E-2</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -32224,7 +32224,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f ca="1">AC26/AC117</f>
-        <v>6.0392551585304488E-2</v>
+        <v>5.5197792088316482E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -32298,7 +32298,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="175">
         <f ca="1">-AC63/AC153</f>
-        <v>6.6550833328929498E-2</v>
+        <v>6.0826359624923138E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -32335,7 +32335,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="175">
         <f ca="1">-(AC63+AC64)/AC153</f>
-        <v>6.6550833328929498E-2</v>
+        <v>6.0826359624923138E-2</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -32838,7 +32838,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="175">
         <f ca="1">(AC107-AC108)/AC153</f>
-        <v>0.27280461670922546</v>
+        <v>0.24933890220847793</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -34343,15 +34343,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="252" t="s">
+      <c r="B4" s="249" t="s">
         <v>282</v>
       </c>
-      <c r="C4" s="252"/>
-      <c r="E4" s="252" t="s">
+      <c r="C4" s="249"/>
+      <c r="E4" s="249" t="s">
         <v>289</v>
       </c>
-      <c r="F4" s="252"/>
-      <c r="G4" s="252"/>
+      <c r="F4" s="249"/>
+      <c r="G4" s="249"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -34359,7 +34359,7 @@
       </c>
       <c r="C5" s="193">
         <f ca="1">Overview!C5</f>
-        <v>9.9350000000000005</v>
+        <v>10.87</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="153" t="s">
@@ -34375,7 +34375,7 @@
       </c>
       <c r="C6" s="194">
         <f ca="1">Statement!AC153</f>
-        <v>5189596.9249999998</v>
+        <v>5677998.8499999996</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>20</v>
@@ -34395,7 +34395,7 @@
       </c>
       <c r="C7" s="194">
         <f ca="1">Statement!AC154</f>
-        <v>3773850.9249999998</v>
+        <v>4262252.8499999996</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>32</v>
@@ -34415,7 +34415,7 @@
       </c>
       <c r="C8" s="195">
         <f ca="1">Statement!AC150</f>
-        <v>16.55833333333333</v>
+        <v>18.116666666666664</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>292</v>
@@ -34435,7 +34435,7 @@
       </c>
       <c r="C9" s="195">
         <f ca="1">Statement!AC151</f>
-        <v>3.2005907887498282</v>
+        <v>3.5018039128042906</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>293</v>
@@ -34455,7 +34455,7 @@
       </c>
       <c r="C10" s="195">
         <f ca="1">Statement!AC152</f>
-        <v>2.705006206104684</v>
+        <v>2.9595790095981793</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -34475,7 +34475,7 @@
       </c>
       <c r="C11" s="195">
         <f ca="1">Statement!AC155</f>
-        <v>2.256642483839912</v>
+        <v>2.5486912571083455</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -34484,18 +34484,18 @@
       </c>
       <c r="C12" s="195">
         <f ca="1">Statement!AC156</f>
-        <v>37.306131189513536</v>
+        <v>42.134193200802692</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="252" t="s">
+      <c r="B15" s="249" t="s">
         <v>78</v>
       </c>
-      <c r="C15" s="252"/>
-      <c r="E15" s="252" t="s">
+      <c r="C15" s="249"/>
+      <c r="E15" s="249" t="s">
         <v>295</v>
       </c>
-      <c r="F15" s="252"/>
+      <c r="F15" s="249"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -34546,14 +34546,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="252" t="s">
+      <c r="B21" s="249" t="s">
         <v>294</v>
       </c>
-      <c r="C21" s="252"/>
-      <c r="E21" s="252" t="s">
+      <c r="C21" s="249"/>
+      <c r="E21" s="249" t="s">
         <v>298</v>
       </c>
-      <c r="F21" s="252"/>
+      <c r="F21" s="249"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -34622,14 +34622,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="252" t="s">
+      <c r="B29" s="249" t="s">
         <v>299</v>
       </c>
-      <c r="C29" s="252"/>
-      <c r="E29" s="252" t="s">
+      <c r="C29" s="249"/>
+      <c r="E29" s="249" t="s">
         <v>305</v>
       </c>
-      <c r="F29" s="252"/>
+      <c r="F29" s="249"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -34705,14 +34705,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="252" t="s">
+      <c r="B37" s="249" t="s">
         <v>317</v>
       </c>
-      <c r="C37" s="252"/>
-      <c r="E37" s="252" t="s">
+      <c r="C37" s="249"/>
+      <c r="E37" s="249" t="s">
         <v>320</v>
       </c>
-      <c r="F37" s="252"/>
+      <c r="F37" s="249"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -34720,7 +34720,7 @@
       </c>
       <c r="C38" s="196">
         <f ca="1">Statement!AC162</f>
-        <v>6.0392551585304488E-2</v>
+        <v>5.5197792088316482E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>319</v>
@@ -34736,7 +34736,7 @@
       </c>
       <c r="C39" s="236">
         <f ca="1">Statement!AC161</f>
-        <v>2.0735521766943394E-2</v>
+        <v>1.8951923528480463E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>321</v>
@@ -34768,7 +34768,7 @@
       </c>
       <c r="C41" s="196">
         <f ca="1">Statement!AC164</f>
-        <v>6.6550833328929498E-2</v>
+        <v>6.0826359624923138E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -34777,18 +34777,18 @@
       </c>
       <c r="C42" s="196">
         <f ca="1">Statement!AC165</f>
-        <v>6.6550833328929498E-2</v>
+        <v>6.0826359624923138E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="252" t="s">
+      <c r="B45" s="249" t="s">
         <v>328</v>
       </c>
-      <c r="C45" s="252"/>
-      <c r="E45" s="252" t="s">
+      <c r="C45" s="249"/>
+      <c r="E45" s="249" t="s">
         <v>334</v>
       </c>
-      <c r="F45" s="252"/>
+      <c r="F45" s="249"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -34821,18 +34821,18 @@
       </c>
       <c r="F48" s="196">
         <f ca="1">Statement!AC176</f>
-        <v>0.27280461670922546</v>
+        <v>0.24933890220847793</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="252" t="s">
+      <c r="B51" s="249" t="s">
         <v>331</v>
       </c>
-      <c r="C51" s="252"/>
-      <c r="E51" s="252" t="s">
+      <c r="C51" s="249"/>
+      <c r="E51" s="249" t="s">
         <v>352</v>
       </c>
-      <c r="F51" s="252"/>
+      <c r="F51" s="249"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -35000,7 +35000,7 @@
       </c>
       <c r="I6" s="193">
         <f ca="1">Statement!AC116</f>
-        <v>9.9350000000000005</v>
+        <v>10.87</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -35029,7 +35029,7 @@
       </c>
       <c r="I7" s="194">
         <f ca="1">Statement!AC153</f>
-        <v>5189596.9249999998</v>
+        <v>5677998.8499999996</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -35058,7 +35058,7 @@
       </c>
       <c r="I8" s="194">
         <f ca="1">Statement!AC154</f>
-        <v>3773850.9249999998</v>
+        <v>4262252.8499999996</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -35087,7 +35087,7 @@
       </c>
       <c r="I9" s="195">
         <f ca="1">Statement!AC150</f>
-        <v>16.55833333333333</v>
+        <v>18.116666666666664</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -35116,7 +35116,7 @@
       </c>
       <c r="I10" s="195">
         <f ca="1">Statement!AC151</f>
-        <v>3.2005907887498282</v>
+        <v>3.5018039128042906</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -35145,7 +35145,7 @@
       </c>
       <c r="I11" s="195">
         <f ca="1">Statement!AC152</f>
-        <v>2.705006206104684</v>
+        <v>2.9595790095981793</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -35174,7 +35174,7 @@
       </c>
       <c r="I12" s="195">
         <f ca="1">Statement!AC155</f>
-        <v>2.256642483839912</v>
+        <v>2.5486912571083455</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -35203,7 +35203,7 @@
       </c>
       <c r="I13" s="195">
         <f ca="1">Statement!AC156</f>
-        <v>37.306131189513536</v>
+        <v>42.134193200802692</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35976,7 +35976,7 @@
       </c>
       <c r="I51" s="196">
         <f ca="1">Statement!AC162</f>
-        <v>6.0392551585304488E-2</v>
+        <v>5.5197792088316482E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -36005,7 +36005,7 @@
       </c>
       <c r="I52" s="196">
         <f ca="1">Statement!AC161</f>
-        <v>2.0735521766943394E-2</v>
+        <v>1.8951923528480463E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -36063,7 +36063,7 @@
       </c>
       <c r="I54" s="196">
         <f ca="1">Statement!AC164</f>
-        <v>6.6550833328929498E-2</v>
+        <v>6.0826359624923138E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -36092,7 +36092,7 @@
       </c>
       <c r="I55" s="196">
         <f ca="1">Statement!AC165</f>
-        <v>6.6550833328929498E-2</v>
+        <v>6.0826359624923138E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36328,7 +36328,7 @@
       </c>
       <c r="I68" s="217">
         <f ca="1">Statement!AC176</f>
-        <v>0.27280461670922546</v>
+        <v>0.24933890220847793</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36814,14 +36814,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="255" t="s">
+      <c r="C3" s="253" t="s">
         <v>365</v>
       </c>
-      <c r="D3" s="256"/>
-      <c r="F3" s="257" t="s">
+      <c r="D3" s="254"/>
+      <c r="F3" s="255" t="s">
         <v>366</v>
       </c>
-      <c r="G3" s="256"/>
+      <c r="G3" s="254"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -36888,19 +36888,19 @@
       <c r="B7" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C7" s="253">
+      <c r="C7" s="256">
         <f>Statement!AA89</f>
         <v>-0.13037640275448081</v>
       </c>
-      <c r="D7" s="254"/>
-      <c r="F7" s="253">
+      <c r="D7" s="257"/>
+      <c r="F7" s="256">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.17317398716855847</v>
       </c>
-      <c r="G7" s="254"/>
+      <c r="G7" s="257"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="228" t="s">
@@ -36927,19 +36927,19 @@
       <c r="B9" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C9" s="253">
+      <c r="C9" s="256">
         <f>Statement!AA90</f>
         <v>4.0481504023804696E-2</v>
       </c>
-      <c r="D9" s="254"/>
-      <c r="F9" s="253">
+      <c r="D9" s="257"/>
+      <c r="F9" s="256">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.20469173309112548</v>
       </c>
-      <c r="G9" s="254"/>
+      <c r="G9" s="257"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="228" t="s">
@@ -36966,19 +36966,19 @@
       <c r="B11" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C11" s="253">
+      <c r="C11" s="256">
         <f>Statement!AA91</f>
         <v>-0.1614010786596328</v>
       </c>
-      <c r="D11" s="254"/>
-      <c r="F11" s="253">
+      <c r="D11" s="257"/>
+      <c r="F11" s="256">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.16629948047423376</v>
       </c>
-      <c r="G11" s="254"/>
+      <c r="G11" s="257"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="228" t="s">
@@ -37005,19 +37005,19 @@
       <c r="B13" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C13" s="253">
+      <c r="C13" s="256">
         <f>Statement!AA95</f>
         <v>-4.1051008608505718E-2</v>
       </c>
-      <c r="D13" s="254"/>
-      <c r="F13" s="253">
+      <c r="D13" s="257"/>
+      <c r="F13" s="256">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>1.3868988514743887E-2</v>
       </c>
-      <c r="G13" s="254"/>
+      <c r="G13" s="257"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="228" t="s">
@@ -37044,19 +37044,19 @@
       <c r="B15" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C15" s="253">
+      <c r="C15" s="256">
         <f>Statement!AA96</f>
         <v>-0.65140871384799337</v>
       </c>
-      <c r="D15" s="254"/>
-      <c r="F15" s="253">
+      <c r="D15" s="257"/>
+      <c r="F15" s="256">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>2.7052766268583963</v>
       </c>
-      <c r="G15" s="254"/>
+      <c r="G15" s="257"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="228" t="s">
@@ -37083,19 +37083,19 @@
       <c r="B17" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C17" s="253">
+      <c r="C17" s="256">
         <f>Statement!AA98</f>
         <v>-0.78437135034749483</v>
       </c>
-      <c r="D17" s="254"/>
-      <c r="F17" s="253">
+      <c r="D17" s="257"/>
+      <c r="F17" s="256">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>1.9986699179782754</v>
       </c>
-      <c r="G17" s="254"/>
+      <c r="G17" s="257"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="228" t="s">
@@ -37122,22 +37122,22 @@
       <c r="B19" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C19" s="253">
+      <c r="C19" s="256">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-3.2031015030699599E-2</v>
       </c>
-      <c r="D19" s="254"/>
-      <c r="F19" s="253">
+      <c r="D19" s="257"/>
+      <c r="F19" s="256">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-3.7620498458385526E-2</v>
       </c>
-      <c r="G19" s="254"/>
+      <c r="G19" s="257"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="228" t="s">
@@ -37164,22 +37164,22 @@
       <c r="B21" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C21" s="253">
+      <c r="C21" s="256">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>-0.78947368421052633</v>
       </c>
-      <c r="D21" s="254"/>
-      <c r="F21" s="253">
+      <c r="D21" s="257"/>
+      <c r="F21" s="256">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>2</v>
       </c>
-      <c r="G21" s="254"/>
+      <c r="G21" s="257"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -37227,22 +37227,22 @@
       <c r="B25" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C25" s="253">
+      <c r="C25" s="256">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>-0.30844727286201273</v>
       </c>
-      <c r="D25" s="254"/>
-      <c r="F25" s="253">
+      <c r="D25" s="257"/>
+      <c r="F25" s="256">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.16387602700216702</v>
       </c>
-      <c r="G25" s="254"/>
+      <c r="G25" s="257"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="s">
@@ -37269,22 +37269,22 @@
       <c r="B27" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C27" s="253">
+      <c r="C27" s="256">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>6.6472159310281692E-3</v>
       </c>
-      <c r="D27" s="254"/>
-      <c r="F27" s="253">
+      <c r="D27" s="257"/>
+      <c r="F27" s="256">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.16382654634312457</v>
       </c>
-      <c r="G27" s="254"/>
+      <c r="G27" s="257"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
@@ -37311,22 +37311,22 @@
       <c r="B29" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C29" s="253">
+      <c r="C29" s="256">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.15748031496062992</v>
       </c>
-      <c r="D29" s="254"/>
-      <c r="F29" s="253">
+      <c r="D29" s="257"/>
+      <c r="F29" s="256">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>0.46533756230176709</v>
       </c>
-      <c r="G29" s="254"/>
+      <c r="G29" s="257"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B31" s="8" t="s">
@@ -37374,22 +37374,22 @@
       <c r="B33" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C33" s="253">
+      <c r="C33" s="256">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>2.6257619832373135E-2</v>
       </c>
-      <c r="D33" s="254"/>
-      <c r="F33" s="253">
+      <c r="D33" s="257"/>
+      <c r="F33" s="256">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>0.12319376989075922</v>
       </c>
-      <c r="G33" s="254"/>
+      <c r="G33" s="257"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B34" s="20" t="s">
@@ -37416,43 +37416,25 @@
       <c r="B35" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C35" s="253">
+      <c r="C35" s="256">
         <f>IF(C34=0,
 IF(D34=0,0,IF(D34&gt;0,1,-1)),
 (D34-C34)/ABS(C34)
 )</f>
         <v>2.3001949317738791E-2</v>
       </c>
-      <c r="D35" s="254"/>
-      <c r="F35" s="253">
+      <c r="D35" s="257"/>
+      <c r="F35" s="256">
         <f>IF(F34=0,
 IF(G34=0,0,IF(G34&gt;0,1,-1)),
 (G34-F34)/ABS(F34)
 )</f>
         <v>0.10951374207188161</v>
       </c>
-      <c r="G35" s="254"/>
+      <c r="G35" s="257"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="F33:G33"/>
     <mergeCell ref="C35:D35"/>
@@ -37463,6 +37445,24 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/PATH.xlsx
+++ b/PATH.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B58222A8-DD7B-6246-96E4-F65E2ED1FC17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55CB232D-E1B2-724F-B762-734A63D19DD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="3" activeTab="12" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -2376,9 +2376,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2386,6 +2383,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2397,10 +2403,10 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2410,12 +2416,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -12749,11 +12749,11 @@
     <v>Powered by Refinitiv</v>
     <v>19.84</v>
     <v>9.2002000000000006</v>
-    <v>0.97809999999999997</v>
-    <v>0.19</v>
-    <v>1.779E-2</v>
+    <v>0.9708</v>
+    <v>0.16</v>
+    <v>1.3852999999999999E-2</v>
     <v>-0.01</v>
-    <v>-9.2000000000000003E-4</v>
+    <v>-8.5400000000000005E-4</v>
     <v>USD</v>
     <v>UiPath, Inc. is focused on agentic automation and orchestration, empowering enterprises to harness the full potential of AI agents to autonomously execute and optimize complex business processes. It is focused on building and managing automations, starting with computer vision technology and user interface automation in its initial robotic process automation offering. Its AI-powered UiPath Platform offers a robust set of capabilities that allows its customers to discover opportunities for automation, automate using a digital workforce that seamlessly collaborates with humans, and operate a mission-critical automation program at scale. It enables employees to quickly build automations for both existing and new processes and to automate a range of actions including logging into applications, moving folders, filling in forms, reading emails and others. Its platform allows users to design and combine UI automations, API integrations and AI-based document understanding in a single workflow.</v>
     <v>3981</v>
@@ -12761,25 +12761,25 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>One Vanderbilt Avenue, 60th Floor, NEW YORK, NY, 10017 US</v>
-    <v>11.04</v>
+    <v>11.775</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46203.950890126565</v>
+    <v>46205.999765902343</v>
     <v>0</v>
-    <v>10.48</v>
-    <v>5631967661</v>
+    <v>11.3</v>
+    <v>6067188713</v>
     <v>UIPATH, INC.</v>
     <v>UIPATH, INC.</v>
-    <v>10.52</v>
-    <v>18.0685</v>
-    <v>10.68</v>
-    <v>10.87</v>
-    <v>10.86</v>
+    <v>11.36</v>
+    <v>19.1998</v>
+    <v>11.55</v>
+    <v>11.71</v>
+    <v>11.7</v>
     <v>518120300</v>
     <v>PATH</v>
     <v>UIPATH, INC. (XNYS:PATH)</v>
-    <v>64731597</v>
-    <v>51447922</v>
+    <v>58403970</v>
+    <v>53048341</v>
     <v>2015</v>
   </rv>
   <rv s="2">
@@ -12803,17 +12803,17 @@
     <v>Powered by Refinitiv</v>
     <v>46.87</v>
     <v>39.47</v>
-    <v>0.02</v>
-    <v>4.5750000000000001E-4</v>
+    <v>0.1</v>
+    <v>2.235E-3</v>
     <v>US</v>
-    <v>43.9</v>
+    <v>45.05</v>
     <v>Index</v>
     <v>3</v>
-    <v>43.67</v>
+    <v>44.53</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>43.78</v>
-    <v>43.72</v>
-    <v>43.74</v>
+    <v>45.03</v>
+    <v>44.75</v>
+    <v>44.85</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -13035,9 +13035,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq Last Sale</v>
+      <v>Source: Nasdaq</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>Delayed 15 minutes</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -13614,18 +13614,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="250" t="s">
+      <c r="B2" s="249" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="251"/>
-      <c r="E2" s="250" t="s">
+      <c r="C2" s="250"/>
+      <c r="E2" s="249" t="s">
         <v>336</v>
       </c>
-      <c r="F2" s="251"/>
-      <c r="H2" s="250" t="s">
+      <c r="F2" s="250"/>
+      <c r="H2" s="249" t="s">
         <v>381</v>
       </c>
-      <c r="I2" s="251"/>
+      <c r="I2" s="250"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="206" t="s">
@@ -13640,7 +13640,7 @@
       </c>
       <c r="F3" s="208">
         <f ca="1">Statement!AC153</f>
-        <v>5677998.8499999996</v>
+        <v>6116777.0500000007</v>
       </c>
       <c r="H3" s="206" t="str">
         <f>'AVG target price'!B5</f>
@@ -13664,7 +13664,7 @@
       </c>
       <c r="F4" s="209">
         <f ca="1">Statement!AC154</f>
-        <v>4262252.8499999996</v>
+        <v>4701031.0500000007</v>
       </c>
       <c r="H4" s="206" t="str">
         <f>'AVG target price'!B6</f>
@@ -13681,7 +13681,7 @@
       </c>
       <c r="C5" s="229" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>10.87</v>
+        <v>11.71</v>
       </c>
       <c r="E5" s="206" t="s">
         <v>292</v>
@@ -13705,14 +13705,14 @@
       </c>
       <c r="C6" s="229" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>10.86</v>
+        <v>11.7</v>
       </c>
       <c r="E6" s="206" t="s">
         <v>286</v>
       </c>
       <c r="F6" s="211">
         <f ca="1">Statement!AC150</f>
-        <v>18.116666666666664</v>
+        <v>19.516666666666666</v>
       </c>
       <c r="H6" s="206" t="str">
         <f>'AVG target price'!B8</f>
@@ -13729,14 +13729,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>0.19</v>
+        <v>0.16</v>
       </c>
       <c r="E7" s="207" t="s">
         <v>242</v>
       </c>
       <c r="F7" s="212">
         <f ca="1">Statement!AC151</f>
-        <v>3.5018039128042906</v>
+        <v>3.7724124948425253</v>
       </c>
       <c r="H7" s="205" t="str">
         <f>'AVG target price'!B9</f>
@@ -13760,7 +13760,7 @@
       </c>
       <c r="F8" s="213">
         <f ca="1">Statement!AC161</f>
-        <v>1.8951923528480463E-2</v>
+        <v>1.7592434564866147E-2</v>
       </c>
       <c r="H8" s="205" t="str">
         <f>'AVG target price'!B11</f>
@@ -13768,7 +13768,7 @@
       </c>
       <c r="I8" s="234">
         <f ca="1">'AVG target price'!C11</f>
-        <v>5.8297201391222263E-2</v>
+        <v>-1.7618225523263507E-2</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13777,14 +13777,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>1.779E-2</v>
+        <v>1.3852999999999999E-2</v>
       </c>
       <c r="E9" s="206" t="s">
         <v>337</v>
       </c>
       <c r="F9" s="213">
         <f ca="1">Statement!AC162</f>
-        <v>5.5197792088316482E-2</v>
+        <v>5.1238257899231428E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -13793,14 +13793,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-9.2000000000000003E-4</v>
+        <v>-8.5400000000000005E-4</v>
       </c>
       <c r="E10" s="206" t="s">
         <v>342</v>
       </c>
       <c r="F10" s="213">
         <f ca="1">Statement!AC164</f>
-        <v>6.0826359624923138E-2</v>
+        <v>5.6463068242776637E-2</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -13841,7 +13841,7 @@
       </c>
       <c r="C13" s="230" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>0.97809999999999997</v>
+        <v>0.9708</v>
       </c>
       <c r="E13" s="206" t="s">
         <v>123</v>
@@ -13857,7 +13857,7 @@
       </c>
       <c r="C14" s="231" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>51447922</v>
+        <v>53048341</v>
       </c>
       <c r="E14" s="207" t="s">
         <v>124</v>
@@ -13873,7 +13873,7 @@
       </c>
       <c r="F15" s="213">
         <f ca="1">Statement!AC176</f>
-        <v>0.24933890220847793</v>
+        <v>0.23145293484254095</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -13886,10 +13886,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="252" t="s">
+      <c r="B17" s="251" t="s">
         <v>103</v>
       </c>
-      <c r="C17" s="252"/>
+      <c r="C17" s="251"/>
       <c r="E17" s="205" t="s">
         <v>345</v>
       </c>
@@ -13962,14 +13962,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="252" t="s">
+      <c r="B25" s="251" t="s">
         <v>126</v>
       </c>
-      <c r="C25" s="252"/>
-      <c r="E25" s="250" t="s">
+      <c r="C25" s="251"/>
+      <c r="E25" s="249" t="s">
         <v>401</v>
       </c>
-      <c r="F25" s="251"/>
+      <c r="F25" s="250"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="205" t="s">
@@ -13983,7 +13983,7 @@
       </c>
       <c r="F26" s="240" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>43.74</v>
+        <v>44.85</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -13998,7 +13998,7 @@
       </c>
       <c r="F27" s="241">
         <f ca="1">F26/1000</f>
-        <v>4.3740000000000001E-2</v>
+        <v>4.4850000000000001E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14018,15 +14018,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="249" t="s">
+      <c r="B33" s="252" t="s">
         <v>391</v>
       </c>
-      <c r="C33" s="249"/>
-      <c r="D33" s="249"/>
-      <c r="E33" s="249"/>
-      <c r="F33" s="249"/>
-      <c r="G33" s="249"/>
-      <c r="H33" s="249"/>
+      <c r="C33" s="252"/>
+      <c r="D33" s="252"/>
+      <c r="E33" s="252"/>
+      <c r="F33" s="252"/>
+      <c r="G33" s="252"/>
+      <c r="H33" s="252"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -14045,24 +14045,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="249"/>
-      <c r="C39" s="249"/>
-      <c r="D39" s="249"/>
-      <c r="E39" s="249"/>
-      <c r="F39" s="249"/>
-      <c r="G39" s="249"/>
-      <c r="H39" s="249"/>
+      <c r="B39" s="252"/>
+      <c r="C39" s="252"/>
+      <c r="D39" s="252"/>
+      <c r="E39" s="252"/>
+      <c r="F39" s="252"/>
+      <c r="G39" s="252"/>
+      <c r="H39" s="252"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="249" t="s">
+      <c r="B42" s="252" t="s">
         <v>394</v>
       </c>
-      <c r="C42" s="249"/>
-      <c r="D42" s="249"/>
-      <c r="E42" s="249"/>
-      <c r="F42" s="249"/>
-      <c r="G42" s="249"/>
-      <c r="H42" s="249"/>
+      <c r="C42" s="252"/>
+      <c r="D42" s="252"/>
+      <c r="E42" s="252"/>
+      <c r="F42" s="252"/>
+      <c r="G42" s="252"/>
+      <c r="H42" s="252"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -14077,24 +14077,24 @@
       </c>
     </row>
     <row r="49" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="249"/>
-      <c r="C49" s="249"/>
-      <c r="D49" s="249"/>
-      <c r="E49" s="249"/>
-      <c r="F49" s="249"/>
-      <c r="G49" s="249"/>
-      <c r="H49" s="249"/>
+      <c r="B49" s="252"/>
+      <c r="C49" s="252"/>
+      <c r="D49" s="252"/>
+      <c r="E49" s="252"/>
+      <c r="F49" s="252"/>
+      <c r="G49" s="252"/>
+      <c r="H49" s="252"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B52" s="249" t="s">
+      <c r="B52" s="252" t="s">
         <v>128</v>
       </c>
-      <c r="C52" s="249"/>
-      <c r="D52" s="249"/>
-      <c r="E52" s="249"/>
-      <c r="F52" s="249"/>
-      <c r="G52" s="249"/>
-      <c r="H52" s="249"/>
+      <c r="C52" s="252"/>
+      <c r="D52" s="252"/>
+      <c r="E52" s="252"/>
+      <c r="F52" s="252"/>
+      <c r="G52" s="252"/>
+      <c r="H52" s="252"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B54" s="41" t="s">
@@ -14109,28 +14109,28 @@
       </c>
     </row>
     <row r="59" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="249"/>
-      <c r="C59" s="249"/>
-      <c r="D59" s="249"/>
-      <c r="E59" s="249"/>
-      <c r="F59" s="249"/>
-      <c r="G59" s="249"/>
-      <c r="H59" s="249"/>
+      <c r="B59" s="252"/>
+      <c r="C59" s="252"/>
+      <c r="D59" s="252"/>
+      <c r="E59" s="252"/>
+      <c r="F59" s="252"/>
+      <c r="G59" s="252"/>
+      <c r="H59" s="252"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B52:H52"/>
+    <mergeCell ref="B59:H59"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="B49:H49"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="E25:F25"/>
-    <mergeCell ref="B52:H52"/>
-    <mergeCell ref="B59:H59"/>
-    <mergeCell ref="B33:H33"/>
-    <mergeCell ref="B39:H39"/>
-    <mergeCell ref="B42:H42"/>
-    <mergeCell ref="B49:H49"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -14200,36 +14200,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="249" t="s">
+      <c r="C2" s="252" t="s">
         <v>137</v>
       </c>
-      <c r="D2" s="249"/>
-      <c r="E2" s="249"/>
-      <c r="F2" s="249"/>
-      <c r="G2" s="261"/>
-      <c r="H2" s="262" t="s">
+      <c r="D2" s="252"/>
+      <c r="E2" s="252"/>
+      <c r="F2" s="252"/>
+      <c r="G2" s="258"/>
+      <c r="H2" s="259" t="s">
         <v>138</v>
       </c>
-      <c r="I2" s="249"/>
-      <c r="J2" s="249"/>
-      <c r="K2" s="249"/>
-      <c r="L2" s="249"/>
+      <c r="I2" s="252"/>
+      <c r="J2" s="252"/>
+      <c r="K2" s="252"/>
+      <c r="L2" s="252"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="249" t="s">
+      <c r="S2" s="252" t="s">
         <v>137</v>
       </c>
-      <c r="T2" s="249"/>
-      <c r="U2" s="249"/>
-      <c r="V2" s="249"/>
-      <c r="W2" s="249"/>
-      <c r="X2" s="249"/>
-      <c r="Y2" s="249"/>
-      <c r="Z2" s="249"/>
-      <c r="AA2" s="249" t="s">
+      <c r="T2" s="252"/>
+      <c r="U2" s="252"/>
+      <c r="V2" s="252"/>
+      <c r="W2" s="252"/>
+      <c r="X2" s="252"/>
+      <c r="Y2" s="252"/>
+      <c r="Z2" s="252"/>
+      <c r="AA2" s="252" t="s">
         <v>138</v>
       </c>
-      <c r="AB2" s="249"/>
-      <c r="AC2" s="249"/>
+      <c r="AB2" s="252"/>
+      <c r="AC2" s="252"/>
       <c r="AE2" s="87" t="s">
         <v>139</v>
       </c>
@@ -14240,32 +14240,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="258" t="s">
+      <c r="C4" s="260" t="s">
         <v>140</v>
       </c>
-      <c r="D4" s="258"/>
-      <c r="E4" s="258"/>
-      <c r="F4" s="258"/>
-      <c r="G4" s="258"/>
-      <c r="H4" s="258"/>
-      <c r="I4" s="258"/>
-      <c r="J4" s="258"/>
-      <c r="K4" s="258"/>
-      <c r="L4" s="258"/>
+      <c r="D4" s="260"/>
+      <c r="E4" s="260"/>
+      <c r="F4" s="260"/>
+      <c r="G4" s="260"/>
+      <c r="H4" s="260"/>
+      <c r="I4" s="260"/>
+      <c r="J4" s="260"/>
+      <c r="K4" s="260"/>
+      <c r="L4" s="260"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="259" t="s">
+      <c r="S4" s="261" t="s">
         <v>140</v>
       </c>
-      <c r="T4" s="260"/>
-      <c r="U4" s="260"/>
-      <c r="V4" s="260"/>
-      <c r="W4" s="260"/>
-      <c r="X4" s="260"/>
-      <c r="Y4" s="260"/>
-      <c r="Z4" s="260"/>
-      <c r="AA4" s="260"/>
-      <c r="AB4" s="260"/>
-      <c r="AC4" s="260"/>
+      <c r="T4" s="262"/>
+      <c r="U4" s="262"/>
+      <c r="V4" s="262"/>
+      <c r="W4" s="262"/>
+      <c r="X4" s="262"/>
+      <c r="Y4" s="262"/>
+      <c r="Z4" s="262"/>
+      <c r="AA4" s="262"/>
+      <c r="AB4" s="262"/>
+      <c r="AC4" s="262"/>
       <c r="AE4" s="89"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -14761,33 +14761,33 @@
       <c r="Q10" s="93"/>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C11" s="258" t="s">
+      <c r="C11" s="260" t="s">
         <v>146</v>
       </c>
-      <c r="D11" s="258"/>
-      <c r="E11" s="258"/>
-      <c r="F11" s="258"/>
-      <c r="G11" s="258"/>
-      <c r="H11" s="258"/>
-      <c r="I11" s="258"/>
-      <c r="J11" s="258"/>
-      <c r="K11" s="258"/>
-      <c r="L11" s="258"/>
+      <c r="D11" s="260"/>
+      <c r="E11" s="260"/>
+      <c r="F11" s="260"/>
+      <c r="G11" s="260"/>
+      <c r="H11" s="260"/>
+      <c r="I11" s="260"/>
+      <c r="J11" s="260"/>
+      <c r="K11" s="260"/>
+      <c r="L11" s="260"/>
       <c r="O11" s="5"/>
       <c r="Q11" s="93"/>
-      <c r="S11" s="259" t="s">
+      <c r="S11" s="261" t="s">
         <v>146</v>
       </c>
-      <c r="T11" s="260"/>
-      <c r="U11" s="260"/>
-      <c r="V11" s="260"/>
-      <c r="W11" s="260"/>
-      <c r="X11" s="260"/>
-      <c r="Y11" s="260"/>
-      <c r="Z11" s="260"/>
-      <c r="AA11" s="260"/>
-      <c r="AB11" s="260"/>
-      <c r="AC11" s="260"/>
+      <c r="T11" s="262"/>
+      <c r="U11" s="262"/>
+      <c r="V11" s="262"/>
+      <c r="W11" s="262"/>
+      <c r="X11" s="262"/>
+      <c r="Y11" s="262"/>
+      <c r="Z11" s="262"/>
+      <c r="AA11" s="262"/>
+      <c r="AB11" s="262"/>
+      <c r="AC11" s="262"/>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B12" s="16" t="s">
@@ -15228,33 +15228,33 @@
       <c r="Q18" s="93"/>
     </row>
     <row r="19" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C19" s="258" t="s">
+      <c r="C19" s="260" t="s">
         <v>148</v>
       </c>
-      <c r="D19" s="258"/>
-      <c r="E19" s="258"/>
-      <c r="F19" s="258"/>
-      <c r="G19" s="258"/>
-      <c r="H19" s="258"/>
-      <c r="I19" s="258"/>
-      <c r="J19" s="258"/>
-      <c r="K19" s="258"/>
-      <c r="L19" s="258"/>
+      <c r="D19" s="260"/>
+      <c r="E19" s="260"/>
+      <c r="F19" s="260"/>
+      <c r="G19" s="260"/>
+      <c r="H19" s="260"/>
+      <c r="I19" s="260"/>
+      <c r="J19" s="260"/>
+      <c r="K19" s="260"/>
+      <c r="L19" s="260"/>
       <c r="O19" s="5"/>
       <c r="Q19" s="93"/>
-      <c r="S19" s="259" t="s">
+      <c r="S19" s="261" t="s">
         <v>148</v>
       </c>
-      <c r="T19" s="260"/>
-      <c r="U19" s="260"/>
-      <c r="V19" s="260"/>
-      <c r="W19" s="260"/>
-      <c r="X19" s="260"/>
-      <c r="Y19" s="260"/>
-      <c r="Z19" s="260"/>
-      <c r="AA19" s="260"/>
-      <c r="AB19" s="260"/>
-      <c r="AC19" s="260"/>
+      <c r="T19" s="262"/>
+      <c r="U19" s="262"/>
+      <c r="V19" s="262"/>
+      <c r="W19" s="262"/>
+      <c r="X19" s="262"/>
+      <c r="Y19" s="262"/>
+      <c r="Z19" s="262"/>
+      <c r="AA19" s="262"/>
+      <c r="AB19" s="262"/>
+      <c r="AC19" s="262"/>
       <c r="AE19" s="89">
         <f>AE4</f>
         <v>0</v>
@@ -16072,32 +16072,32 @@
       <c r="O31" s="5"/>
     </row>
     <row r="32" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C32" s="258" t="s">
+      <c r="C32" s="260" t="s">
         <v>150</v>
       </c>
-      <c r="D32" s="258"/>
-      <c r="E32" s="258"/>
-      <c r="F32" s="258"/>
-      <c r="G32" s="258"/>
-      <c r="H32" s="258"/>
-      <c r="I32" s="258"/>
-      <c r="J32" s="258"/>
-      <c r="K32" s="258"/>
-      <c r="L32" s="258"/>
+      <c r="D32" s="260"/>
+      <c r="E32" s="260"/>
+      <c r="F32" s="260"/>
+      <c r="G32" s="260"/>
+      <c r="H32" s="260"/>
+      <c r="I32" s="260"/>
+      <c r="J32" s="260"/>
+      <c r="K32" s="260"/>
+      <c r="L32" s="260"/>
       <c r="O32" s="5"/>
-      <c r="S32" s="259" t="s">
+      <c r="S32" s="261" t="s">
         <v>150</v>
       </c>
-      <c r="T32" s="260"/>
-      <c r="U32" s="260"/>
-      <c r="V32" s="260"/>
-      <c r="W32" s="260"/>
-      <c r="X32" s="260"/>
-      <c r="Y32" s="260"/>
-      <c r="Z32" s="260"/>
-      <c r="AA32" s="260"/>
-      <c r="AB32" s="260"/>
-      <c r="AC32" s="260"/>
+      <c r="T32" s="262"/>
+      <c r="U32" s="262"/>
+      <c r="V32" s="262"/>
+      <c r="W32" s="262"/>
+      <c r="X32" s="262"/>
+      <c r="Y32" s="262"/>
+      <c r="Z32" s="262"/>
+      <c r="AA32" s="262"/>
+      <c r="AB32" s="262"/>
+      <c r="AC32" s="262"/>
     </row>
     <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B33" s="16" t="s">
@@ -16354,18 +16354,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="C11:L11"/>
+    <mergeCell ref="S11:AC11"/>
+    <mergeCell ref="C19:L19"/>
+    <mergeCell ref="S19:AC19"/>
+    <mergeCell ref="C32:L32"/>
+    <mergeCell ref="S32:AC32"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C11:L11"/>
-    <mergeCell ref="S11:AC11"/>
-    <mergeCell ref="C19:L19"/>
-    <mergeCell ref="S19:AC19"/>
-    <mergeCell ref="C32:L32"/>
-    <mergeCell ref="S32:AC32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -16402,35 +16402,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="249" t="s">
+      <c r="C2" s="252" t="s">
         <v>137</v>
       </c>
-      <c r="D2" s="249"/>
-      <c r="E2" s="249"/>
-      <c r="F2" s="249"/>
-      <c r="G2" s="261"/>
-      <c r="H2" s="262" t="s">
+      <c r="D2" s="252"/>
+      <c r="E2" s="252"/>
+      <c r="F2" s="252"/>
+      <c r="G2" s="258"/>
+      <c r="H2" s="259" t="s">
         <v>138</v>
       </c>
-      <c r="I2" s="249"/>
-      <c r="J2" s="249"/>
-      <c r="K2" s="249"/>
-      <c r="L2" s="249"/>
-      <c r="P2" s="249" t="s">
+      <c r="I2" s="252"/>
+      <c r="J2" s="252"/>
+      <c r="K2" s="252"/>
+      <c r="L2" s="252"/>
+      <c r="P2" s="252" t="s">
         <v>137</v>
       </c>
-      <c r="Q2" s="249"/>
-      <c r="R2" s="249"/>
-      <c r="S2" s="249"/>
-      <c r="T2" s="249"/>
-      <c r="U2" s="249"/>
-      <c r="V2" s="249"/>
-      <c r="W2" s="249"/>
-      <c r="X2" s="249" t="s">
+      <c r="Q2" s="252"/>
+      <c r="R2" s="252"/>
+      <c r="S2" s="252"/>
+      <c r="T2" s="252"/>
+      <c r="U2" s="252"/>
+      <c r="V2" s="252"/>
+      <c r="W2" s="252"/>
+      <c r="X2" s="252" t="s">
         <v>138</v>
       </c>
-      <c r="Y2" s="249"/>
-      <c r="Z2" s="249"/>
+      <c r="Y2" s="252"/>
+      <c r="Z2" s="252"/>
       <c r="AB2" s="87" t="s">
         <v>139</v>
       </c>
@@ -16439,31 +16439,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="258" t="s">
+      <c r="C4" s="260" t="s">
         <v>140</v>
       </c>
-      <c r="D4" s="258"/>
-      <c r="E4" s="258"/>
-      <c r="F4" s="258"/>
-      <c r="G4" s="258"/>
-      <c r="H4" s="258"/>
-      <c r="I4" s="258"/>
-      <c r="J4" s="258"/>
-      <c r="K4" s="258"/>
-      <c r="L4" s="258"/>
-      <c r="P4" s="260" t="s">
+      <c r="D4" s="260"/>
+      <c r="E4" s="260"/>
+      <c r="F4" s="260"/>
+      <c r="G4" s="260"/>
+      <c r="H4" s="260"/>
+      <c r="I4" s="260"/>
+      <c r="J4" s="260"/>
+      <c r="K4" s="260"/>
+      <c r="L4" s="260"/>
+      <c r="P4" s="262" t="s">
         <v>140</v>
       </c>
-      <c r="Q4" s="260"/>
-      <c r="R4" s="260"/>
-      <c r="S4" s="260"/>
-      <c r="T4" s="260"/>
-      <c r="U4" s="260"/>
-      <c r="V4" s="260"/>
-      <c r="W4" s="260"/>
-      <c r="X4" s="260"/>
-      <c r="Y4" s="260"/>
-      <c r="Z4" s="260"/>
+      <c r="Q4" s="262"/>
+      <c r="R4" s="262"/>
+      <c r="S4" s="262"/>
+      <c r="T4" s="262"/>
+      <c r="U4" s="262"/>
+      <c r="V4" s="262"/>
+      <c r="W4" s="262"/>
+      <c r="X4" s="262"/>
+      <c r="Y4" s="262"/>
+      <c r="Z4" s="262"/>
       <c r="AB4" s="89"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -16658,32 +16658,32 @@
       <c r="N8" s="93"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="258" t="s">
+      <c r="C9" s="260" t="s">
         <v>166</v>
       </c>
-      <c r="D9" s="258"/>
-      <c r="E9" s="258"/>
-      <c r="F9" s="258"/>
-      <c r="G9" s="258"/>
-      <c r="H9" s="258"/>
-      <c r="I9" s="258"/>
-      <c r="J9" s="258"/>
-      <c r="K9" s="258"/>
-      <c r="L9" s="258"/>
+      <c r="D9" s="260"/>
+      <c r="E9" s="260"/>
+      <c r="F9" s="260"/>
+      <c r="G9" s="260"/>
+      <c r="H9" s="260"/>
+      <c r="I9" s="260"/>
+      <c r="J9" s="260"/>
+      <c r="K9" s="260"/>
+      <c r="L9" s="260"/>
       <c r="N9" s="93"/>
-      <c r="P9" s="260" t="s">
+      <c r="P9" s="262" t="s">
         <v>167</v>
       </c>
-      <c r="Q9" s="260"/>
-      <c r="R9" s="260"/>
-      <c r="S9" s="260"/>
-      <c r="T9" s="260"/>
-      <c r="U9" s="260"/>
-      <c r="V9" s="260"/>
-      <c r="W9" s="260"/>
-      <c r="X9" s="260"/>
-      <c r="Y9" s="260"/>
-      <c r="Z9" s="260"/>
+      <c r="Q9" s="262"/>
+      <c r="R9" s="262"/>
+      <c r="S9" s="262"/>
+      <c r="T9" s="262"/>
+      <c r="U9" s="262"/>
+      <c r="V9" s="262"/>
+      <c r="W9" s="262"/>
+      <c r="X9" s="262"/>
+      <c r="Y9" s="262"/>
+      <c r="Z9" s="262"/>
       <c r="AB9" s="89">
         <f>AB4</f>
         <v>0</v>
@@ -17532,31 +17532,31 @@
       </c>
     </row>
     <row r="21" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="C21" s="258" t="s">
+      <c r="C21" s="260" t="s">
         <v>169</v>
       </c>
-      <c r="D21" s="258"/>
-      <c r="E21" s="258"/>
-      <c r="F21" s="258"/>
-      <c r="G21" s="258"/>
-      <c r="H21" s="258"/>
-      <c r="I21" s="258"/>
-      <c r="J21" s="258"/>
-      <c r="K21" s="258"/>
-      <c r="L21" s="258"/>
-      <c r="P21" s="260" t="s">
+      <c r="D21" s="260"/>
+      <c r="E21" s="260"/>
+      <c r="F21" s="260"/>
+      <c r="G21" s="260"/>
+      <c r="H21" s="260"/>
+      <c r="I21" s="260"/>
+      <c r="J21" s="260"/>
+      <c r="K21" s="260"/>
+      <c r="L21" s="260"/>
+      <c r="P21" s="262" t="s">
         <v>169</v>
       </c>
-      <c r="Q21" s="260"/>
-      <c r="R21" s="260"/>
-      <c r="S21" s="260"/>
-      <c r="T21" s="260"/>
-      <c r="U21" s="260"/>
-      <c r="V21" s="260"/>
-      <c r="W21" s="260"/>
-      <c r="X21" s="260"/>
-      <c r="Y21" s="260"/>
-      <c r="Z21" s="260"/>
+      <c r="Q21" s="262"/>
+      <c r="R21" s="262"/>
+      <c r="S21" s="262"/>
+      <c r="T21" s="262"/>
+      <c r="U21" s="262"/>
+      <c r="V21" s="262"/>
+      <c r="W21" s="262"/>
+      <c r="X21" s="262"/>
+      <c r="Y21" s="262"/>
+      <c r="Z21" s="262"/>
     </row>
     <row r="22" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B22" s="16" t="s">
@@ -18371,20 +18371,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="249" t="s">
+      <c r="C3" s="252" t="s">
         <v>137</v>
       </c>
-      <c r="D3" s="249"/>
-      <c r="E3" s="249"/>
-      <c r="F3" s="249"/>
-      <c r="G3" s="261"/>
-      <c r="H3" s="262" t="s">
+      <c r="D3" s="252"/>
+      <c r="E3" s="252"/>
+      <c r="F3" s="252"/>
+      <c r="G3" s="258"/>
+      <c r="H3" s="259" t="s">
         <v>138</v>
       </c>
-      <c r="I3" s="249"/>
-      <c r="J3" s="249"/>
-      <c r="K3" s="249"/>
-      <c r="L3" s="249"/>
+      <c r="I3" s="252"/>
+      <c r="J3" s="252"/>
+      <c r="K3" s="252"/>
+      <c r="L3" s="252"/>
       <c r="P3" s="263"/>
       <c r="Q3" s="263"/>
       <c r="R3" s="263"/>
@@ -18402,18 +18402,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="88"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="258" t="s">
+      <c r="C5" s="260" t="s">
         <v>140</v>
       </c>
-      <c r="D5" s="258"/>
-      <c r="E5" s="258"/>
-      <c r="F5" s="258"/>
-      <c r="G5" s="258"/>
-      <c r="H5" s="258"/>
-      <c r="I5" s="258"/>
-      <c r="J5" s="258"/>
-      <c r="K5" s="258"/>
-      <c r="L5" s="258"/>
+      <c r="D5" s="260"/>
+      <c r="E5" s="260"/>
+      <c r="F5" s="260"/>
+      <c r="G5" s="260"/>
+      <c r="H5" s="260"/>
+      <c r="I5" s="260"/>
+      <c r="J5" s="260"/>
+      <c r="K5" s="260"/>
+      <c r="L5" s="260"/>
       <c r="P5" s="263"/>
       <c r="Q5" s="263"/>
       <c r="R5" s="263"/>
@@ -18610,18 +18610,18 @@
       <c r="N10" s="93"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="258" t="s">
+      <c r="C11" s="260" t="s">
         <v>173</v>
       </c>
-      <c r="D11" s="258"/>
-      <c r="E11" s="258"/>
-      <c r="F11" s="258"/>
-      <c r="G11" s="258"/>
-      <c r="H11" s="258"/>
-      <c r="I11" s="258"/>
-      <c r="J11" s="258"/>
-      <c r="K11" s="258"/>
-      <c r="L11" s="258"/>
+      <c r="D11" s="260"/>
+      <c r="E11" s="260"/>
+      <c r="F11" s="260"/>
+      <c r="G11" s="260"/>
+      <c r="H11" s="260"/>
+      <c r="I11" s="260"/>
+      <c r="J11" s="260"/>
+      <c r="K11" s="260"/>
+      <c r="L11" s="260"/>
       <c r="N11" s="93"/>
       <c r="P11" s="263"/>
       <c r="Q11" s="263"/>
@@ -18875,18 +18875,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="258" t="s">
+      <c r="C18" s="260" t="s">
         <v>178</v>
       </c>
-      <c r="D18" s="258"/>
-      <c r="E18" s="258"/>
-      <c r="F18" s="258"/>
-      <c r="G18" s="258"/>
-      <c r="H18" s="258"/>
-      <c r="I18" s="258"/>
-      <c r="J18" s="258"/>
-      <c r="K18" s="258"/>
-      <c r="L18" s="258"/>
+      <c r="D18" s="260"/>
+      <c r="E18" s="260"/>
+      <c r="F18" s="260"/>
+      <c r="G18" s="260"/>
+      <c r="H18" s="260"/>
+      <c r="I18" s="260"/>
+      <c r="J18" s="260"/>
+      <c r="K18" s="260"/>
+      <c r="L18" s="260"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19104,18 +19104,18 @@
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="130"/>
-      <c r="C26" s="258" t="s">
+      <c r="C26" s="260" t="s">
         <v>184</v>
       </c>
-      <c r="D26" s="258"/>
-      <c r="E26" s="258"/>
-      <c r="F26" s="258"/>
-      <c r="G26" s="258"/>
-      <c r="H26" s="258"/>
-      <c r="I26" s="258"/>
-      <c r="J26" s="258"/>
-      <c r="K26" s="258"/>
-      <c r="L26" s="258"/>
+      <c r="D26" s="260"/>
+      <c r="E26" s="260"/>
+      <c r="F26" s="260"/>
+      <c r="G26" s="260"/>
+      <c r="H26" s="260"/>
+      <c r="I26" s="260"/>
+      <c r="J26" s="260"/>
+      <c r="K26" s="260"/>
+      <c r="L26" s="260"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -19307,18 +19307,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="130"/>
-      <c r="C33" s="258" t="s">
+      <c r="C33" s="260" t="s">
         <v>188</v>
       </c>
-      <c r="D33" s="258"/>
-      <c r="E33" s="258"/>
-      <c r="F33" s="258"/>
-      <c r="G33" s="258"/>
-      <c r="H33" s="258"/>
-      <c r="I33" s="258"/>
-      <c r="J33" s="258"/>
-      <c r="K33" s="258"/>
-      <c r="L33" s="258"/>
+      <c r="D33" s="260"/>
+      <c r="E33" s="260"/>
+      <c r="F33" s="260"/>
+      <c r="G33" s="260"/>
+      <c r="H33" s="260"/>
+      <c r="I33" s="260"/>
+      <c r="J33" s="260"/>
+      <c r="K33" s="260"/>
+      <c r="L33" s="260"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -19502,18 +19502,18 @@
       <c r="C39" s="146"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="258" t="s">
+      <c r="C40" s="260" t="s">
         <v>191</v>
       </c>
-      <c r="D40" s="258"/>
-      <c r="E40" s="258"/>
-      <c r="F40" s="258"/>
-      <c r="G40" s="258"/>
-      <c r="H40" s="258"/>
-      <c r="I40" s="258"/>
-      <c r="J40" s="258"/>
-      <c r="K40" s="258"/>
-      <c r="L40" s="258"/>
+      <c r="D40" s="260"/>
+      <c r="E40" s="260"/>
+      <c r="F40" s="260"/>
+      <c r="G40" s="260"/>
+      <c r="H40" s="260"/>
+      <c r="I40" s="260"/>
+      <c r="J40" s="260"/>
+      <c r="K40" s="260"/>
+      <c r="L40" s="260"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -19651,7 +19651,7 @@
       </c>
       <c r="C44" s="144">
         <f>C42/C45</f>
-        <v>1.6561549724068025</v>
+        <v>1.2431312875137375</v>
       </c>
       <c r="D44" s="144">
         <f t="shared" ref="D44:L44" si="13">D42/D45</f>
@@ -19695,23 +19695,23 @@
         <v>61</v>
       </c>
       <c r="C45" s="135">
-        <f>-Statement!M60</f>
-        <v>8879</v>
+        <f>-Statement!M110</f>
+        <v>11829</v>
       </c>
       <c r="D45" s="135">
-        <f>-Statement!N60</f>
+        <f>-Statement!N110</f>
         <v>23815</v>
       </c>
       <c r="E45" s="135">
-        <f>-Statement!O60</f>
+        <f>-Statement!O110</f>
         <v>7342</v>
       </c>
       <c r="F45" s="135">
-        <f>-Statement!P60</f>
+        <f>-Statement!P110</f>
         <v>14923</v>
       </c>
       <c r="G45" s="136">
-        <f>-Statement!Q60</f>
+        <f>-Statement!Q110</f>
         <v>19048</v>
       </c>
       <c r="H45" s="25">
@@ -19741,7 +19741,7 @@
       </c>
       <c r="C46" s="144">
         <f>C45/C7</f>
-        <v>9.951224541945549E-3</v>
+        <v>1.325746537973577E-2</v>
       </c>
       <c r="D46" s="144">
         <f>D45/D7</f>
@@ -19777,6 +19777,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -19784,12 +19790,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -19827,20 +19827,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="249" t="s">
+      <c r="C2" s="252" t="s">
         <v>137</v>
       </c>
-      <c r="D2" s="249"/>
-      <c r="E2" s="249"/>
-      <c r="F2" s="249"/>
-      <c r="G2" s="261"/>
-      <c r="H2" s="262" t="s">
+      <c r="D2" s="252"/>
+      <c r="E2" s="252"/>
+      <c r="F2" s="252"/>
+      <c r="G2" s="258"/>
+      <c r="H2" s="259" t="s">
         <v>138</v>
       </c>
-      <c r="I2" s="249"/>
-      <c r="J2" s="249"/>
-      <c r="K2" s="249"/>
-      <c r="L2" s="249"/>
+      <c r="I2" s="252"/>
+      <c r="J2" s="252"/>
+      <c r="K2" s="252"/>
+      <c r="L2" s="252"/>
       <c r="S2" s="263"/>
       <c r="T2" s="263"/>
       <c r="U2" s="263"/>
@@ -19858,18 +19858,18 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="258" t="s">
+      <c r="C4" s="260" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="258"/>
-      <c r="E4" s="258"/>
-      <c r="F4" s="258"/>
-      <c r="G4" s="258"/>
-      <c r="H4" s="258"/>
-      <c r="I4" s="258"/>
-      <c r="J4" s="258"/>
-      <c r="K4" s="258"/>
-      <c r="L4" s="258"/>
+      <c r="D4" s="260"/>
+      <c r="E4" s="260"/>
+      <c r="F4" s="260"/>
+      <c r="G4" s="260"/>
+      <c r="H4" s="260"/>
+      <c r="I4" s="260"/>
+      <c r="J4" s="260"/>
+      <c r="K4" s="260"/>
+      <c r="L4" s="260"/>
       <c r="S4" s="263"/>
       <c r="T4" s="263"/>
       <c r="U4" s="263"/>
@@ -20243,18 +20243,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="258" t="s">
+      <c r="C13" s="260" t="s">
         <v>199</v>
       </c>
-      <c r="D13" s="258"/>
-      <c r="E13" s="258"/>
-      <c r="F13" s="258"/>
-      <c r="G13" s="258"/>
-      <c r="H13" s="258"/>
-      <c r="I13" s="258"/>
-      <c r="J13" s="258"/>
-      <c r="K13" s="258"/>
-      <c r="L13" s="258"/>
+      <c r="D13" s="260"/>
+      <c r="E13" s="260"/>
+      <c r="F13" s="260"/>
+      <c r="G13" s="260"/>
+      <c r="H13" s="260"/>
+      <c r="I13" s="260"/>
+      <c r="J13" s="260"/>
+      <c r="K13" s="260"/>
+      <c r="L13" s="260"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -20347,18 +20347,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="258" t="s">
+      <c r="C18" s="260" t="s">
         <v>200</v>
       </c>
-      <c r="D18" s="258"/>
-      <c r="E18" s="258"/>
-      <c r="F18" s="258"/>
-      <c r="G18" s="258"/>
-      <c r="H18" s="258"/>
-      <c r="I18" s="258"/>
-      <c r="J18" s="258"/>
-      <c r="K18" s="258"/>
-      <c r="L18" s="258"/>
+      <c r="D18" s="260"/>
+      <c r="E18" s="260"/>
+      <c r="F18" s="260"/>
+      <c r="G18" s="260"/>
+      <c r="H18" s="260"/>
+      <c r="I18" s="260"/>
+      <c r="J18" s="260"/>
+      <c r="K18" s="260"/>
+      <c r="L18" s="260"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -20459,7 +20459,7 @@
       </c>
       <c r="C21" s="90">
         <f>'WC &amp; Investments'!C45</f>
-        <v>8879</v>
+        <v>11829</v>
       </c>
       <c r="D21" s="90">
         <f>'WC &amp; Investments'!D45</f>
@@ -20550,18 +20550,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="258" t="s">
+      <c r="C25" s="260" t="s">
         <v>311</v>
       </c>
-      <c r="D25" s="258"/>
-      <c r="E25" s="258"/>
-      <c r="F25" s="258"/>
-      <c r="G25" s="258"/>
-      <c r="H25" s="258"/>
-      <c r="I25" s="258"/>
-      <c r="J25" s="258"/>
-      <c r="K25" s="258"/>
-      <c r="L25" s="258"/>
+      <c r="D25" s="260"/>
+      <c r="E25" s="260"/>
+      <c r="F25" s="260"/>
+      <c r="G25" s="260"/>
+      <c r="H25" s="260"/>
+      <c r="I25" s="260"/>
+      <c r="J25" s="260"/>
+      <c r="K25" s="260"/>
+      <c r="L25" s="260"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -20659,7 +20659,7 @@
       </c>
       <c r="C28" s="96">
         <f>C27+C20-C21+C22</f>
-        <v>-601022</v>
+        <v>-603972</v>
       </c>
       <c r="D28" s="96">
         <f t="shared" ref="D28:L28" si="7">D27+D20-D21+D22</f>
@@ -20699,18 +20699,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="258" t="s">
+      <c r="C31" s="260" t="s">
         <v>78</v>
       </c>
-      <c r="D31" s="258"/>
-      <c r="E31" s="258"/>
-      <c r="F31" s="258"/>
-      <c r="G31" s="258"/>
-      <c r="H31" s="258"/>
-      <c r="I31" s="258"/>
-      <c r="J31" s="258"/>
-      <c r="K31" s="258"/>
-      <c r="L31" s="258"/>
+      <c r="D31" s="260"/>
+      <c r="E31" s="260"/>
+      <c r="F31" s="260"/>
+      <c r="G31" s="260"/>
+      <c r="H31" s="260"/>
+      <c r="I31" s="260"/>
+      <c r="J31" s="260"/>
+      <c r="K31" s="260"/>
+      <c r="L31" s="260"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -20849,16 +20849,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -20921,10 +20921,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="249" t="s">
+      <c r="B4" s="252" t="s">
         <v>207</v>
       </c>
-      <c r="C4" s="249"/>
+      <c r="C4" s="252"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -20941,7 +20941,7 @@
       </c>
       <c r="C6" s="154">
         <f ca="1">Overview!C5</f>
-        <v>10.87</v>
+        <v>11.71</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20950,7 +20950,7 @@
       </c>
       <c r="C7" s="155">
         <f ca="1">C5*C6</f>
-        <v>5677998.8499999996</v>
+        <v>6116777.0500000007</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20968,7 +20968,7 @@
       </c>
       <c r="C9" s="156">
         <f ca="1">Overview!F27</f>
-        <v>4.3740000000000001E-2</v>
+        <v>4.4850000000000001E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20977,7 +20977,7 @@
       </c>
       <c r="C10" s="154">
         <f ca="1">Overview!C13</f>
-        <v>0.97809999999999997</v>
+        <v>0.9708</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21009,10 +21009,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="249" t="s">
+      <c r="B15" s="252" t="s">
         <v>214</v>
       </c>
-      <c r="C15" s="249"/>
+      <c r="C15" s="252"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -21047,7 +21047,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>8.7754499999999999E-2</v>
+        <v>8.8536000000000004E-2</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21056,7 +21056,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>8.7754499999999999E-2</v>
+        <v>8.8536000000000004E-2</v>
       </c>
     </row>
   </sheetData>
@@ -21101,20 +21101,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="249" t="s">
+      <c r="C3" s="252" t="s">
         <v>137</v>
       </c>
-      <c r="D3" s="249"/>
-      <c r="E3" s="249"/>
-      <c r="F3" s="249"/>
-      <c r="G3" s="261"/>
-      <c r="H3" s="262" t="s">
+      <c r="D3" s="252"/>
+      <c r="E3" s="252"/>
+      <c r="F3" s="252"/>
+      <c r="G3" s="258"/>
+      <c r="H3" s="259" t="s">
         <v>138</v>
       </c>
-      <c r="I3" s="249"/>
-      <c r="J3" s="249"/>
-      <c r="K3" s="249"/>
-      <c r="L3" s="249"/>
+      <c r="I3" s="252"/>
+      <c r="J3" s="252"/>
+      <c r="K3" s="252"/>
+      <c r="L3" s="252"/>
       <c r="P3" s="263"/>
       <c r="Q3" s="263"/>
       <c r="R3" s="263"/>
@@ -21132,18 +21132,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="88"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="258" t="s">
+      <c r="C5" s="260" t="s">
         <v>221</v>
       </c>
-      <c r="D5" s="258"/>
-      <c r="E5" s="258"/>
-      <c r="F5" s="258"/>
-      <c r="G5" s="258"/>
-      <c r="H5" s="258"/>
-      <c r="I5" s="258"/>
-      <c r="J5" s="258"/>
-      <c r="K5" s="258"/>
-      <c r="L5" s="258"/>
+      <c r="D5" s="260"/>
+      <c r="E5" s="260"/>
+      <c r="F5" s="260"/>
+      <c r="G5" s="260"/>
+      <c r="H5" s="260"/>
+      <c r="I5" s="260"/>
+      <c r="J5" s="260"/>
+      <c r="K5" s="260"/>
+      <c r="L5" s="260"/>
       <c r="P5" s="263"/>
       <c r="Q5" s="263"/>
       <c r="R5" s="263"/>
@@ -21221,7 +21221,7 @@
       </c>
       <c r="C7" s="133">
         <f>'FCF &amp; Other'!C28</f>
-        <v>-601022</v>
+        <v>-603972</v>
       </c>
       <c r="D7" s="133">
         <f>'FCF &amp; Other'!D28</f>
@@ -21400,10 +21400,10 @@
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="249" t="s">
+      <c r="B13" s="252" t="s">
         <v>225</v>
       </c>
-      <c r="C13" s="249"/>
+      <c r="C13" s="252"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -21423,10 +21423,10 @@
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="249" t="s">
+      <c r="B18" s="252" t="s">
         <v>227</v>
       </c>
-      <c r="C18" s="249"/>
+      <c r="C18" s="252"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -21540,37 +21540,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="249" t="s">
+      <c r="C2" s="252" t="s">
         <v>137</v>
       </c>
-      <c r="D2" s="249"/>
-      <c r="E2" s="249"/>
-      <c r="F2" s="249"/>
-      <c r="G2" s="261"/>
-      <c r="H2" s="262" t="s">
+      <c r="D2" s="252"/>
+      <c r="E2" s="252"/>
+      <c r="F2" s="252"/>
+      <c r="G2" s="258"/>
+      <c r="H2" s="259" t="s">
         <v>138</v>
       </c>
-      <c r="I2" s="249"/>
-      <c r="J2" s="249"/>
-      <c r="K2" s="249"/>
-      <c r="L2" s="249"/>
+      <c r="I2" s="252"/>
+      <c r="J2" s="252"/>
+      <c r="K2" s="252"/>
+      <c r="L2" s="252"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="258" t="s">
+      <c r="C4" s="260" t="s">
         <v>235</v>
       </c>
-      <c r="D4" s="258"/>
-      <c r="E4" s="258"/>
-      <c r="F4" s="258"/>
-      <c r="G4" s="258"/>
-      <c r="H4" s="258"/>
-      <c r="I4" s="258"/>
-      <c r="J4" s="258"/>
-      <c r="K4" s="258"/>
-      <c r="L4" s="258"/>
+      <c r="D4" s="260"/>
+      <c r="E4" s="260"/>
+      <c r="F4" s="260"/>
+      <c r="G4" s="260"/>
+      <c r="H4" s="260"/>
+      <c r="I4" s="260"/>
+      <c r="J4" s="260"/>
+      <c r="K4" s="260"/>
+      <c r="L4" s="260"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -21715,7 +21715,7 @@
       </c>
       <c r="C8" s="94">
         <f>'FCF &amp; Other'!C28</f>
-        <v>-601022</v>
+        <v>-603972</v>
       </c>
       <c r="D8" s="94">
         <f>'FCF &amp; Other'!D28</f>
@@ -21759,18 +21759,18 @@
       <c r="N9" s="93"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C10" s="258" t="s">
+      <c r="C10" s="260" t="s">
         <v>146</v>
       </c>
-      <c r="D10" s="258"/>
-      <c r="E10" s="258"/>
-      <c r="F10" s="258"/>
-      <c r="G10" s="258"/>
-      <c r="H10" s="258"/>
-      <c r="I10" s="258"/>
-      <c r="J10" s="258"/>
-      <c r="K10" s="258"/>
-      <c r="L10" s="258"/>
+      <c r="D10" s="260"/>
+      <c r="E10" s="260"/>
+      <c r="F10" s="260"/>
+      <c r="G10" s="260"/>
+      <c r="H10" s="260"/>
+      <c r="I10" s="260"/>
+      <c r="J10" s="260"/>
+      <c r="K10" s="260"/>
+      <c r="L10" s="260"/>
       <c r="N10" s="93"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21921,7 +21921,7 @@
 IF(D8=0,0,IF(D8&gt;0,1,-1)),
 (D8-C8)/ABS(C8)
 )</f>
-        <v>0.16798053981385042</v>
+        <v>0.17204439940924413</v>
       </c>
       <c r="E14" s="97">
         <f t="shared" ref="E14:L14" si="3">IF(D8=0,
@@ -21964,18 +21964,18 @@
       <c r="N15" s="93"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C16" s="258" t="s">
+      <c r="C16" s="260" t="s">
         <v>237</v>
       </c>
-      <c r="D16" s="258"/>
-      <c r="E16" s="258"/>
-      <c r="F16" s="258"/>
-      <c r="G16" s="258"/>
-      <c r="H16" s="258"/>
-      <c r="I16" s="258"/>
-      <c r="J16" s="258"/>
-      <c r="K16" s="258"/>
-      <c r="L16" s="258"/>
+      <c r="D16" s="260"/>
+      <c r="E16" s="260"/>
+      <c r="F16" s="260"/>
+      <c r="G16" s="260"/>
+      <c r="H16" s="260"/>
+      <c r="I16" s="260"/>
+      <c r="J16" s="260"/>
+      <c r="K16" s="260"/>
+      <c r="L16" s="260"/>
       <c r="N16" s="93"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
@@ -22109,18 +22109,18 @@
       <c r="N20" s="93"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C21" s="258" t="s">
+      <c r="C21" s="260" t="s">
         <v>240</v>
       </c>
-      <c r="D21" s="258"/>
-      <c r="E21" s="258"/>
-      <c r="F21" s="258"/>
-      <c r="G21" s="258"/>
-      <c r="H21" s="258"/>
-      <c r="I21" s="258"/>
-      <c r="J21" s="258"/>
-      <c r="K21" s="258"/>
-      <c r="L21" s="258"/>
+      <c r="D21" s="260"/>
+      <c r="E21" s="260"/>
+      <c r="F21" s="260"/>
+      <c r="G21" s="260"/>
+      <c r="H21" s="260"/>
+      <c r="I21" s="260"/>
+      <c r="J21" s="260"/>
+      <c r="K21" s="260"/>
+      <c r="L21" s="260"/>
       <c r="N21" s="93"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
@@ -22204,18 +22204,18 @@
       <c r="N25" s="93"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C26" s="258" t="s">
+      <c r="C26" s="260" t="s">
         <v>241</v>
       </c>
-      <c r="D26" s="258"/>
-      <c r="E26" s="258"/>
-      <c r="F26" s="258"/>
-      <c r="G26" s="258"/>
-      <c r="H26" s="258"/>
-      <c r="I26" s="258"/>
-      <c r="J26" s="258"/>
-      <c r="K26" s="258"/>
-      <c r="L26" s="258"/>
+      <c r="D26" s="260"/>
+      <c r="E26" s="260"/>
+      <c r="F26" s="260"/>
+      <c r="G26" s="260"/>
+      <c r="H26" s="260"/>
+      <c r="I26" s="260"/>
+      <c r="J26" s="260"/>
+      <c r="K26" s="260"/>
+      <c r="L26" s="260"/>
       <c r="N26" s="93"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
@@ -22453,7 +22453,7 @@
       </c>
       <c r="C34" s="170">
         <f>C32/C8</f>
-        <v>-22.151353444632644</v>
+        <v>-22.043158871603321</v>
       </c>
       <c r="D34" s="170">
         <f t="shared" ref="D34:G34" si="13">D32/D8</f>
@@ -22485,10 +22485,10 @@
       <c r="N36" s="93"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="249" t="s">
+      <c r="B37" s="252" t="s">
         <v>246</v>
       </c>
-      <c r="C37" s="249"/>
+      <c r="C37" s="252"/>
       <c r="N37" s="93"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -22563,10 +22563,10 @@
       </c>
     </row>
     <row r="47" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B47" s="249" t="s">
+      <c r="B47" s="252" t="s">
         <v>251</v>
       </c>
-      <c r="C47" s="249"/>
+      <c r="C47" s="252"/>
     </row>
     <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B48" s="1" t="s">
@@ -22622,10 +22622,10 @@
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B55" s="249" t="s">
+      <c r="B55" s="252" t="s">
         <v>375</v>
       </c>
-      <c r="C55" s="249"/>
+      <c r="C55" s="252"/>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B56" s="1" t="s">
@@ -22738,10 +22738,10 @@
       <c r="N3" s="93"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="249" t="s">
+      <c r="B4" s="252" t="s">
         <v>256</v>
       </c>
-      <c r="C4" s="249"/>
+      <c r="C4" s="252"/>
       <c r="N4" s="93"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -22795,7 +22795,7 @@
       </c>
       <c r="C10" s="154">
         <f ca="1">Overview!C5</f>
-        <v>10.87</v>
+        <v>11.71</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -22804,7 +22804,7 @@
       </c>
       <c r="C11" s="175">
         <f ca="1">(C9-C10)/C10</f>
-        <v>5.8297201391222263E-2</v>
+        <v>-1.7618225523263507E-2</v>
       </c>
     </row>
   </sheetData>
@@ -22869,20 +22869,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="249" t="s">
+      <c r="C3" s="252" t="s">
         <v>137</v>
       </c>
-      <c r="D3" s="249"/>
-      <c r="E3" s="249"/>
-      <c r="F3" s="249"/>
-      <c r="G3" s="261"/>
-      <c r="H3" s="262" t="s">
+      <c r="D3" s="252"/>
+      <c r="E3" s="252"/>
+      <c r="F3" s="252"/>
+      <c r="G3" s="258"/>
+      <c r="H3" s="259" t="s">
         <v>138</v>
       </c>
-      <c r="I3" s="249"/>
-      <c r="J3" s="249"/>
-      <c r="K3" s="249"/>
-      <c r="L3" s="249"/>
+      <c r="I3" s="252"/>
+      <c r="J3" s="252"/>
+      <c r="K3" s="252"/>
+      <c r="L3" s="252"/>
       <c r="P3" s="263"/>
       <c r="Q3" s="263"/>
       <c r="R3" s="263"/>
@@ -22900,18 +22900,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="88"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="258" t="s">
+      <c r="C5" s="260" t="s">
         <v>221</v>
       </c>
-      <c r="D5" s="258"/>
-      <c r="E5" s="258"/>
-      <c r="F5" s="258"/>
-      <c r="G5" s="258"/>
-      <c r="H5" s="258"/>
-      <c r="I5" s="258"/>
-      <c r="J5" s="258"/>
-      <c r="K5" s="258"/>
-      <c r="L5" s="258"/>
+      <c r="D5" s="260"/>
+      <c r="E5" s="260"/>
+      <c r="F5" s="260"/>
+      <c r="G5" s="260"/>
+      <c r="H5" s="260"/>
+      <c r="I5" s="260"/>
+      <c r="J5" s="260"/>
+      <c r="K5" s="260"/>
+      <c r="L5" s="260"/>
       <c r="P5" s="263"/>
       <c r="Q5" s="263"/>
       <c r="R5" s="263"/>
@@ -22989,7 +22989,7 @@
       </c>
       <c r="C7" s="133">
         <f>'FCF &amp; Other'!C28</f>
-        <v>-601022</v>
+        <v>-603972</v>
       </c>
       <c r="D7" s="133">
         <f>'FCF &amp; Other'!D28</f>
@@ -23161,7 +23161,7 @@
       </c>
       <c r="C15" s="177">
         <f ca="1">Overview!C5</f>
-        <v>10.87</v>
+        <v>11.71</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -23227,7 +23227,7 @@
       </c>
       <c r="C23" s="182">
         <f ca="1">C15*C22</f>
-        <v>5631975.2699999996</v>
+        <v>6067196.9100000001</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -23254,7 +23254,7 @@
       </c>
       <c r="C26" s="183">
         <f ca="1">C23+C25-C24</f>
-        <v>4216229.2699999996</v>
+        <v>4651450.91</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -23337,18 +23337,18 @@
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C39" s="258" t="s">
+      <c r="C39" s="260" t="s">
         <v>270</v>
       </c>
-      <c r="D39" s="258"/>
-      <c r="E39" s="258"/>
-      <c r="F39" s="258"/>
-      <c r="G39" s="258"/>
-      <c r="H39" s="258"/>
-      <c r="I39" s="258"/>
-      <c r="J39" s="258"/>
-      <c r="K39" s="258"/>
-      <c r="L39" s="258"/>
+      <c r="D39" s="260"/>
+      <c r="E39" s="260"/>
+      <c r="F39" s="260"/>
+      <c r="G39" s="260"/>
+      <c r="H39" s="260"/>
+      <c r="I39" s="260"/>
+      <c r="J39" s="260"/>
+      <c r="K39" s="260"/>
+      <c r="L39" s="260"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="12">
@@ -23398,7 +23398,7 @@
       </c>
       <c r="C41" s="133">
         <f>C7</f>
-        <v>-601022</v>
+        <v>-603972</v>
       </c>
       <c r="D41" s="133">
         <f t="shared" si="2"/>
@@ -23488,7 +23488,7 @@
       </c>
       <c r="C43" s="97">
         <f>C41/C42</f>
-        <v>1.1997740275398945</v>
+        <v>1.2056628858200285</v>
       </c>
       <c r="D43" s="97">
         <f t="shared" ref="D43:G43" si="4">D41/D42</f>
@@ -23573,7 +23573,7 @@
       </c>
       <c r="C45" s="97">
         <f>C41/C44</f>
-        <v>-0.67360117993571322</v>
+        <v>-0.67690742077350341</v>
       </c>
       <c r="D45" s="97">
         <f t="shared" ref="D45:G45" si="6">D41/D44</f>
@@ -23614,7 +23614,7 @@
       <c r="C46" s="158"/>
       <c r="D46" s="97">
         <f>D41/C41-1</f>
-        <v>-0.16798053981385042</v>
+        <v>-0.1720443994092441</v>
       </c>
       <c r="E46" s="97">
         <f t="shared" ref="E46:L47" si="7">E41/D41-1</f>
@@ -23780,17 +23780,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -30403,7 +30403,7 @@
       <c r="AA116" s="68"/>
       <c r="AC116" s="63">
         <f ca="1">Overview!C5</f>
-        <v>10.87</v>
+        <v>11.71</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -30450,7 +30450,7 @@
       <c r="AA117" s="68"/>
       <c r="AC117" s="65">
         <f ca="1">AC116/AC85</f>
-        <v>10.87</v>
+        <v>11.71</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -31756,7 +31756,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>18.116666666666664</v>
+        <v>19.516666666666666</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -31793,7 +31793,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>3.5018039128042906</v>
+        <v>3.7724124948425253</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -31830,7 +31830,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="72">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>2.9595790095981793</v>
+        <v>3.1882861271752239</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -31867,7 +31867,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="164">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>5677998.8499999996</v>
+        <v>6116777.0500000007</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -31904,7 +31904,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="164">
         <f ca="1">AC153+AC108-AC107+AC48+AC45</f>
-        <v>4262252.8499999996</v>
+        <v>4701031.0500000007</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -31941,7 +31941,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="204">
         <f ca="1">AC154/AC5</f>
-        <v>2.5486912571083455</v>
+        <v>2.8110666256061907</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -31978,7 +31978,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="204">
         <f ca="1">AC154/AC12</f>
-        <v>42.134193200802692</v>
+        <v>46.471703456934144</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -32113,7 +32113,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="72">
         <f t="shared" ref="AC159:AC160" ca="1" si="101">AC153/AC157</f>
-        <v>52.765092603778491</v>
+        <v>56.842615859268285</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -32150,7 +32150,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
         <f t="shared" ca="1" si="101"/>
-        <v>-78.588602378537843</v>
+        <v>-86.67891675117545</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -32187,7 +32187,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="74">
         <f t="shared" ref="AC161" ca="1" si="104">AC157/AC153</f>
-        <v>1.8951923528480463E-2</v>
+        <v>1.7592434564866147E-2</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -32224,7 +32224,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f ca="1">AC26/AC117</f>
-        <v>5.5197792088316482E-2</v>
+        <v>5.1238257899231428E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -32298,7 +32298,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="175">
         <f ca="1">-AC63/AC153</f>
-        <v>6.0826359624923138E-2</v>
+        <v>5.6463068242776637E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -32335,7 +32335,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="175">
         <f ca="1">-(AC63+AC64)/AC153</f>
-        <v>6.0826359624923138E-2</v>
+        <v>5.6463068242776637E-2</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -32838,7 +32838,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="175">
         <f ca="1">(AC107-AC108)/AC153</f>
-        <v>0.24933890220847793</v>
+        <v>0.23145293484254095</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -34343,15 +34343,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="249" t="s">
+      <c r="B4" s="252" t="s">
         <v>282</v>
       </c>
-      <c r="C4" s="249"/>
-      <c r="E4" s="249" t="s">
+      <c r="C4" s="252"/>
+      <c r="E4" s="252" t="s">
         <v>289</v>
       </c>
-      <c r="F4" s="249"/>
-      <c r="G4" s="249"/>
+      <c r="F4" s="252"/>
+      <c r="G4" s="252"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -34359,7 +34359,7 @@
       </c>
       <c r="C5" s="193">
         <f ca="1">Overview!C5</f>
-        <v>10.87</v>
+        <v>11.71</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="153" t="s">
@@ -34375,7 +34375,7 @@
       </c>
       <c r="C6" s="194">
         <f ca="1">Statement!AC153</f>
-        <v>5677998.8499999996</v>
+        <v>6116777.0500000007</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>20</v>
@@ -34395,7 +34395,7 @@
       </c>
       <c r="C7" s="194">
         <f ca="1">Statement!AC154</f>
-        <v>4262252.8499999996</v>
+        <v>4701031.0500000007</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>32</v>
@@ -34415,7 +34415,7 @@
       </c>
       <c r="C8" s="195">
         <f ca="1">Statement!AC150</f>
-        <v>18.116666666666664</v>
+        <v>19.516666666666666</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>292</v>
@@ -34435,7 +34435,7 @@
       </c>
       <c r="C9" s="195">
         <f ca="1">Statement!AC151</f>
-        <v>3.5018039128042906</v>
+        <v>3.7724124948425253</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>293</v>
@@ -34455,7 +34455,7 @@
       </c>
       <c r="C10" s="195">
         <f ca="1">Statement!AC152</f>
-        <v>2.9595790095981793</v>
+        <v>3.1882861271752239</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -34475,7 +34475,7 @@
       </c>
       <c r="C11" s="195">
         <f ca="1">Statement!AC155</f>
-        <v>2.5486912571083455</v>
+        <v>2.8110666256061907</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -34484,18 +34484,18 @@
       </c>
       <c r="C12" s="195">
         <f ca="1">Statement!AC156</f>
-        <v>42.134193200802692</v>
+        <v>46.471703456934144</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="249" t="s">
+      <c r="B15" s="252" t="s">
         <v>78</v>
       </c>
-      <c r="C15" s="249"/>
-      <c r="E15" s="249" t="s">
+      <c r="C15" s="252"/>
+      <c r="E15" s="252" t="s">
         <v>295</v>
       </c>
-      <c r="F15" s="249"/>
+      <c r="F15" s="252"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -34546,14 +34546,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="249" t="s">
+      <c r="B21" s="252" t="s">
         <v>294</v>
       </c>
-      <c r="C21" s="249"/>
-      <c r="E21" s="249" t="s">
+      <c r="C21" s="252"/>
+      <c r="E21" s="252" t="s">
         <v>298</v>
       </c>
-      <c r="F21" s="249"/>
+      <c r="F21" s="252"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -34622,14 +34622,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="249" t="s">
+      <c r="B29" s="252" t="s">
         <v>299</v>
       </c>
-      <c r="C29" s="249"/>
-      <c r="E29" s="249" t="s">
+      <c r="C29" s="252"/>
+      <c r="E29" s="252" t="s">
         <v>305</v>
       </c>
-      <c r="F29" s="249"/>
+      <c r="F29" s="252"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -34705,14 +34705,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="249" t="s">
+      <c r="B37" s="252" t="s">
         <v>317</v>
       </c>
-      <c r="C37" s="249"/>
-      <c r="E37" s="249" t="s">
+      <c r="C37" s="252"/>
+      <c r="E37" s="252" t="s">
         <v>320</v>
       </c>
-      <c r="F37" s="249"/>
+      <c r="F37" s="252"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -34720,7 +34720,7 @@
       </c>
       <c r="C38" s="196">
         <f ca="1">Statement!AC162</f>
-        <v>5.5197792088316482E-2</v>
+        <v>5.1238257899231428E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>319</v>
@@ -34736,7 +34736,7 @@
       </c>
       <c r="C39" s="236">
         <f ca="1">Statement!AC161</f>
-        <v>1.8951923528480463E-2</v>
+        <v>1.7592434564866147E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>321</v>
@@ -34768,7 +34768,7 @@
       </c>
       <c r="C41" s="196">
         <f ca="1">Statement!AC164</f>
-        <v>6.0826359624923138E-2</v>
+        <v>5.6463068242776637E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -34777,18 +34777,18 @@
       </c>
       <c r="C42" s="196">
         <f ca="1">Statement!AC165</f>
-        <v>6.0826359624923138E-2</v>
+        <v>5.6463068242776637E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="249" t="s">
+      <c r="B45" s="252" t="s">
         <v>328</v>
       </c>
-      <c r="C45" s="249"/>
-      <c r="E45" s="249" t="s">
+      <c r="C45" s="252"/>
+      <c r="E45" s="252" t="s">
         <v>334</v>
       </c>
-      <c r="F45" s="249"/>
+      <c r="F45" s="252"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -34821,18 +34821,18 @@
       </c>
       <c r="F48" s="196">
         <f ca="1">Statement!AC176</f>
-        <v>0.24933890220847793</v>
+        <v>0.23145293484254095</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="249" t="s">
+      <c r="B51" s="252" t="s">
         <v>331</v>
       </c>
-      <c r="C51" s="249"/>
-      <c r="E51" s="249" t="s">
+      <c r="C51" s="252"/>
+      <c r="E51" s="252" t="s">
         <v>352</v>
       </c>
-      <c r="F51" s="249"/>
+      <c r="F51" s="252"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -35000,7 +35000,7 @@
       </c>
       <c r="I6" s="193">
         <f ca="1">Statement!AC116</f>
-        <v>10.87</v>
+        <v>11.71</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -35029,7 +35029,7 @@
       </c>
       <c r="I7" s="194">
         <f ca="1">Statement!AC153</f>
-        <v>5677998.8499999996</v>
+        <v>6116777.0500000007</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -35058,7 +35058,7 @@
       </c>
       <c r="I8" s="194">
         <f ca="1">Statement!AC154</f>
-        <v>4262252.8499999996</v>
+        <v>4701031.0500000007</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -35087,7 +35087,7 @@
       </c>
       <c r="I9" s="195">
         <f ca="1">Statement!AC150</f>
-        <v>18.116666666666664</v>
+        <v>19.516666666666666</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -35116,7 +35116,7 @@
       </c>
       <c r="I10" s="195">
         <f ca="1">Statement!AC151</f>
-        <v>3.5018039128042906</v>
+        <v>3.7724124948425253</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -35145,7 +35145,7 @@
       </c>
       <c r="I11" s="195">
         <f ca="1">Statement!AC152</f>
-        <v>2.9595790095981793</v>
+        <v>3.1882861271752239</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -35174,7 +35174,7 @@
       </c>
       <c r="I12" s="195">
         <f ca="1">Statement!AC155</f>
-        <v>2.5486912571083455</v>
+        <v>2.8110666256061907</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -35203,7 +35203,7 @@
       </c>
       <c r="I13" s="195">
         <f ca="1">Statement!AC156</f>
-        <v>42.134193200802692</v>
+        <v>46.471703456934144</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35976,7 +35976,7 @@
       </c>
       <c r="I51" s="196">
         <f ca="1">Statement!AC162</f>
-        <v>5.5197792088316482E-2</v>
+        <v>5.1238257899231428E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -36005,7 +36005,7 @@
       </c>
       <c r="I52" s="196">
         <f ca="1">Statement!AC161</f>
-        <v>1.8951923528480463E-2</v>
+        <v>1.7592434564866147E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -36063,7 +36063,7 @@
       </c>
       <c r="I54" s="196">
         <f ca="1">Statement!AC164</f>
-        <v>6.0826359624923138E-2</v>
+        <v>5.6463068242776637E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -36092,7 +36092,7 @@
       </c>
       <c r="I55" s="196">
         <f ca="1">Statement!AC165</f>
-        <v>6.0826359624923138E-2</v>
+        <v>5.6463068242776637E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36328,7 +36328,7 @@
       </c>
       <c r="I68" s="217">
         <f ca="1">Statement!AC176</f>
-        <v>0.24933890220847793</v>
+        <v>0.23145293484254095</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36814,14 +36814,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="253" t="s">
+      <c r="C3" s="255" t="s">
         <v>365</v>
       </c>
-      <c r="D3" s="254"/>
-      <c r="F3" s="255" t="s">
+      <c r="D3" s="256"/>
+      <c r="F3" s="257" t="s">
         <v>366</v>
       </c>
-      <c r="G3" s="254"/>
+      <c r="G3" s="256"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -36888,19 +36888,19 @@
       <c r="B7" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C7" s="256">
+      <c r="C7" s="253">
         <f>Statement!AA89</f>
         <v>-0.13037640275448081</v>
       </c>
-      <c r="D7" s="257"/>
-      <c r="F7" s="256">
+      <c r="D7" s="254"/>
+      <c r="F7" s="253">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.17317398716855847</v>
       </c>
-      <c r="G7" s="257"/>
+      <c r="G7" s="254"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="228" t="s">
@@ -36927,19 +36927,19 @@
       <c r="B9" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C9" s="256">
+      <c r="C9" s="253">
         <f>Statement!AA90</f>
         <v>4.0481504023804696E-2</v>
       </c>
-      <c r="D9" s="257"/>
-      <c r="F9" s="256">
+      <c r="D9" s="254"/>
+      <c r="F9" s="253">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.20469173309112548</v>
       </c>
-      <c r="G9" s="257"/>
+      <c r="G9" s="254"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="228" t="s">
@@ -36966,19 +36966,19 @@
       <c r="B11" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C11" s="256">
+      <c r="C11" s="253">
         <f>Statement!AA91</f>
         <v>-0.1614010786596328</v>
       </c>
-      <c r="D11" s="257"/>
-      <c r="F11" s="256">
+      <c r="D11" s="254"/>
+      <c r="F11" s="253">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.16629948047423376</v>
       </c>
-      <c r="G11" s="257"/>
+      <c r="G11" s="254"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="228" t="s">
@@ -37005,19 +37005,19 @@
       <c r="B13" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C13" s="256">
+      <c r="C13" s="253">
         <f>Statement!AA95</f>
         <v>-4.1051008608505718E-2</v>
       </c>
-      <c r="D13" s="257"/>
-      <c r="F13" s="256">
+      <c r="D13" s="254"/>
+      <c r="F13" s="253">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>1.3868988514743887E-2</v>
       </c>
-      <c r="G13" s="257"/>
+      <c r="G13" s="254"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="228" t="s">
@@ -37044,19 +37044,19 @@
       <c r="B15" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C15" s="256">
+      <c r="C15" s="253">
         <f>Statement!AA96</f>
         <v>-0.65140871384799337</v>
       </c>
-      <c r="D15" s="257"/>
-      <c r="F15" s="256">
+      <c r="D15" s="254"/>
+      <c r="F15" s="253">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>2.7052766268583963</v>
       </c>
-      <c r="G15" s="257"/>
+      <c r="G15" s="254"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="228" t="s">
@@ -37083,19 +37083,19 @@
       <c r="B17" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C17" s="256">
+      <c r="C17" s="253">
         <f>Statement!AA98</f>
         <v>-0.78437135034749483</v>
       </c>
-      <c r="D17" s="257"/>
-      <c r="F17" s="256">
+      <c r="D17" s="254"/>
+      <c r="F17" s="253">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>1.9986699179782754</v>
       </c>
-      <c r="G17" s="257"/>
+      <c r="G17" s="254"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="228" t="s">
@@ -37122,22 +37122,22 @@
       <c r="B19" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C19" s="256">
+      <c r="C19" s="253">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-3.2031015030699599E-2</v>
       </c>
-      <c r="D19" s="257"/>
-      <c r="F19" s="256">
+      <c r="D19" s="254"/>
+      <c r="F19" s="253">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-3.7620498458385526E-2</v>
       </c>
-      <c r="G19" s="257"/>
+      <c r="G19" s="254"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="228" t="s">
@@ -37164,22 +37164,22 @@
       <c r="B21" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C21" s="256">
+      <c r="C21" s="253">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>-0.78947368421052633</v>
       </c>
-      <c r="D21" s="257"/>
-      <c r="F21" s="256">
+      <c r="D21" s="254"/>
+      <c r="F21" s="253">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>2</v>
       </c>
-      <c r="G21" s="257"/>
+      <c r="G21" s="254"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -37227,22 +37227,22 @@
       <c r="B25" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C25" s="256">
+      <c r="C25" s="253">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>-0.30844727286201273</v>
       </c>
-      <c r="D25" s="257"/>
-      <c r="F25" s="256">
+      <c r="D25" s="254"/>
+      <c r="F25" s="253">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.16387602700216702</v>
       </c>
-      <c r="G25" s="257"/>
+      <c r="G25" s="254"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="s">
@@ -37269,22 +37269,22 @@
       <c r="B27" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C27" s="256">
+      <c r="C27" s="253">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>6.6472159310281692E-3</v>
       </c>
-      <c r="D27" s="257"/>
-      <c r="F27" s="256">
+      <c r="D27" s="254"/>
+      <c r="F27" s="253">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.16382654634312457</v>
       </c>
-      <c r="G27" s="257"/>
+      <c r="G27" s="254"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
@@ -37311,22 +37311,22 @@
       <c r="B29" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C29" s="256">
+      <c r="C29" s="253">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.15748031496062992</v>
       </c>
-      <c r="D29" s="257"/>
-      <c r="F29" s="256">
+      <c r="D29" s="254"/>
+      <c r="F29" s="253">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>0.46533756230176709</v>
       </c>
-      <c r="G29" s="257"/>
+      <c r="G29" s="254"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B31" s="8" t="s">
@@ -37374,22 +37374,22 @@
       <c r="B33" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C33" s="256">
+      <c r="C33" s="253">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>2.6257619832373135E-2</v>
       </c>
-      <c r="D33" s="257"/>
-      <c r="F33" s="256">
+      <c r="D33" s="254"/>
+      <c r="F33" s="253">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>0.12319376989075922</v>
       </c>
-      <c r="G33" s="257"/>
+      <c r="G33" s="254"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B34" s="20" t="s">
@@ -37416,25 +37416,43 @@
       <c r="B35" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C35" s="256">
+      <c r="C35" s="253">
         <f>IF(C34=0,
 IF(D34=0,0,IF(D34&gt;0,1,-1)),
 (D34-C34)/ABS(C34)
 )</f>
         <v>2.3001949317738791E-2</v>
       </c>
-      <c r="D35" s="257"/>
-      <c r="F35" s="256">
+      <c r="D35" s="254"/>
+      <c r="F35" s="253">
         <f>IF(F34=0,
 IF(G34=0,0,IF(G34&gt;0,1,-1)),
 (G34-F34)/ABS(F34)
 )</f>
         <v>0.10951374207188161</v>
       </c>
-      <c r="G35" s="257"/>
+      <c r="G35" s="254"/>
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="F33:G33"/>
     <mergeCell ref="C35:D35"/>
@@ -37445,24 +37463,6 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/PATH.xlsx
+++ b/PATH.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55CB232D-E1B2-724F-B762-734A63D19DD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3102B096-1CA3-B64F-9219-F9B8E6513959}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="3" activeTab="12" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="8" activeTab="18" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -135,7 +135,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="2">
+  <futureMetadata name="XLRICHVALUE" count="5">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -146,7 +146,28 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="3"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="4"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="5"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="8"/>
         </ext>
       </extLst>
     </bk>
@@ -156,19 +177,28 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="2">
+  <valueMetadata count="5">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
     </bk>
+    <bk>
+      <rc t="2" v="2"/>
+    </bk>
+    <bk>
+      <rc t="2" v="3"/>
+    </bk>
+    <bk>
+      <rc t="2" v="4"/>
+    </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="419">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="419">
   <si>
     <t>Ticker</t>
   </si>
@@ -2376,6 +2406,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2383,9 +2416,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -12730,7 +12760,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=c1dbvh&amp;q=XNYS%3aPATH&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
@@ -12749,11 +12779,9 @@
     <v>Powered by Refinitiv</v>
     <v>19.84</v>
     <v>9.2002000000000006</v>
-    <v>0.9708</v>
-    <v>0.16</v>
-    <v>1.3852999999999999E-2</v>
-    <v>-0.01</v>
-    <v>-8.5400000000000005E-4</v>
+    <v>0.97689999999999999</v>
+    <v>0.08</v>
+    <v>6.7620000000000006E-3</v>
     <v>USD</v>
     <v>UiPath, Inc. is focused on agentic automation and orchestration, empowering enterprises to harness the full potential of AI agents to autonomously execute and optimize complex business processes. It is focused on building and managing automations, starting with computer vision technology and user interface automation in its initial robotic process automation offering. Its AI-powered UiPath Platform offers a robust set of capabilities that allows its customers to discover opportunities for automation, automate using a digital workforce that seamlessly collaborates with humans, and operate a mission-critical automation program at scale. It enables employees to quickly build automations for both existing and new processes and to automate a range of actions including logging into applications, moving folders, filling in forms, reading emails and others. Its platform allows users to design and combine UI automations, API integrations and AI-based document understanding in a single workflow.</v>
     <v>3981</v>
@@ -12761,35 +12789,49 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>One Vanderbilt Avenue, 60th Floor, NEW YORK, NY, 10017 US</v>
-    <v>11.775</v>
+    <v>12.315</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46205.999765902343</v>
+    <v>46210.766399571097</v>
     <v>0</v>
-    <v>11.3</v>
-    <v>6067188713</v>
+    <v>11.56</v>
+    <v>6170812773</v>
     <v>UIPATH, INC.</v>
     <v>UIPATH, INC.</v>
-    <v>11.36</v>
-    <v>19.1998</v>
-    <v>11.55</v>
-    <v>11.71</v>
-    <v>11.7</v>
+    <v>12.17</v>
+    <v>19.7972</v>
+    <v>11.83</v>
+    <v>11.91</v>
     <v>518120300</v>
     <v>PATH</v>
     <v>UIPATH, INC. (XNYS:PATH)</v>
-    <v>58403970</v>
-    <v>53048341</v>
+    <v>51665960</v>
+    <v>53115954</v>
     <v>2015</v>
   </rv>
   <rv s="2">
     <v>1</v>
   </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Price (Extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Change (extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Change % (extended hours)</v>
+    <v>0</v>
+  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="3">
+  <rv s="4">
     <v>5</v>
     <v>10 Y TSY YLD NDX</v>
     <v>6</v>
@@ -12803,28 +12845,28 @@
     <v>Powered by Refinitiv</v>
     <v>46.87</v>
     <v>39.47</v>
-    <v>0.1</v>
-    <v>2.235E-3</v>
+    <v>-0.06</v>
+    <v>-1.338E-3</v>
     <v>US</v>
-    <v>45.05</v>
+    <v>44.91</v>
     <v>Index</v>
-    <v>3</v>
-    <v>44.53</v>
+    <v>6</v>
+    <v>44.57</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>45.03</v>
-    <v>44.75</v>
+    <v>44.57</v>
     <v>44.85</v>
+    <v>44.79</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="2">
-    <v>4</v>
+    <v>7</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -12846,8 +12888,6 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
-    <k n="Change (Extended hours)"/>
-    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -12868,7 +12908,6 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
-    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -12878,6 +12917,11 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
+  </s>
+  <s t="_error">
+    <k n="errorType" t="i"/>
+    <k n="field" t="s"/>
+    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -12913,7 +12957,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="45">
+    <a count="42">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -12924,16 +12968,13 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
-      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
-      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
-      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -13027,19 +13068,13 @@
       <v>8</v>
       <v>9</v>
       <v>4</v>
-      <v>1</v>
-      <v>1</v>
-      <v>5</v>
     </spb>
     <spb s="4">
-      <v>at close</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq</v>
+      <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Delayed 15 minutes</v>
-      <v>from close</v>
-      <v>from close</v>
     </spb>
     <spb s="0">
       <v>1</v>
@@ -13111,9 +13146,6 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
-    <k n="Price (Extended hours)" t="i"/>
-    <k n="Change (Extended hours)" t="i"/>
-    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -13121,9 +13153,6 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
-    <k n="Price (Extended hours)" t="s"/>
-    <k n="Change (Extended hours)" t="s"/>
-    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="UniqueName" t="spb"/>
@@ -13614,18 +13643,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="249" t="s">
+      <c r="B2" s="250" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="250"/>
-      <c r="E2" s="249" t="s">
+      <c r="C2" s="251"/>
+      <c r="E2" s="250" t="s">
         <v>336</v>
       </c>
-      <c r="F2" s="250"/>
-      <c r="H2" s="249" t="s">
+      <c r="F2" s="251"/>
+      <c r="H2" s="250" t="s">
         <v>381</v>
       </c>
-      <c r="I2" s="250"/>
+      <c r="I2" s="251"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="206" t="s">
@@ -13640,7 +13669,7 @@
       </c>
       <c r="F3" s="208">
         <f ca="1">Statement!AC153</f>
-        <v>6116777.0500000007</v>
+        <v>6221248.0499999998</v>
       </c>
       <c r="H3" s="206" t="str">
         <f>'AVG target price'!B5</f>
@@ -13664,7 +13693,7 @@
       </c>
       <c r="F4" s="209">
         <f ca="1">Statement!AC154</f>
-        <v>4701031.0500000007</v>
+        <v>4805502.05</v>
       </c>
       <c r="H4" s="206" t="str">
         <f>'AVG target price'!B6</f>
@@ -13672,7 +13701,7 @@
       </c>
       <c r="I4" s="232">
         <f>'AVG target price'!C6</f>
-        <v>15.469508957927841</v>
+        <v>18.179822824933996</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -13681,7 +13710,7 @@
       </c>
       <c r="C5" s="229" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>11.71</v>
+        <v>11.91</v>
       </c>
       <c r="E5" s="206" t="s">
         <v>292</v>
@@ -13703,16 +13732,16 @@
       <c r="B6" s="206" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="229" cm="1">
-        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>11.7</v>
+      <c r="C6" s="229" t="e" cm="1" vm="2">
+        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E6" s="206" t="s">
         <v>286</v>
       </c>
       <c r="F6" s="211">
         <f ca="1">Statement!AC150</f>
-        <v>19.516666666666666</v>
+        <v>19.849999999999998</v>
       </c>
       <c r="H6" s="206" t="str">
         <f>'AVG target price'!B8</f>
@@ -13720,7 +13749,7 @@
       </c>
       <c r="I6" s="232">
         <f>'AVG target price'!C8</f>
-        <v>10.334200177437685</v>
+        <v>13.04451404444384</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -13729,14 +13758,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>0.16</v>
+        <v>0.08</v>
       </c>
       <c r="E7" s="207" t="s">
         <v>242</v>
       </c>
       <c r="F7" s="212">
         <f ca="1">Statement!AC151</f>
-        <v>3.7724124948425253</v>
+        <v>3.8368431096135334</v>
       </c>
       <c r="H7" s="205" t="str">
         <f>'AVG target price'!B9</f>
@@ -13744,23 +13773,23 @@
       </c>
       <c r="I7" s="233">
         <f>'AVG target price'!C9</f>
-        <v>11.503690579122585</v>
+        <v>12.858847512625662</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B8" s="206" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" cm="1">
-        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-0.01</v>
+      <c r="C8" s="6" t="e" cm="1" vm="3">
+        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E8" s="206" t="s">
         <v>314</v>
       </c>
       <c r="F8" s="213">
         <f ca="1">Statement!AC161</f>
-        <v>1.7592434564866147E-2</v>
+        <v>1.7297011650258827E-2</v>
       </c>
       <c r="H8" s="205" t="str">
         <f>'AVG target price'!B11</f>
@@ -13768,7 +13797,7 @@
       </c>
       <c r="I8" s="234">
         <f ca="1">'AVG target price'!C11</f>
-        <v>-1.7618225523263507E-2</v>
+        <v>7.9668137080240273E-2</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13777,30 +13806,30 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>1.3852999999999999E-2</v>
+        <v>6.7620000000000006E-3</v>
       </c>
       <c r="E9" s="206" t="s">
         <v>337</v>
       </c>
       <c r="F9" s="213">
         <f ca="1">Statement!AC162</f>
-        <v>5.1238257899231428E-2</v>
+        <v>5.0377833753148624E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B10" s="206" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" cm="1">
-        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-8.5400000000000005E-4</v>
+      <c r="C10" s="73" t="e" cm="1" vm="4">
+        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E10" s="206" t="s">
         <v>342</v>
       </c>
       <c r="F10" s="213">
         <f ca="1">Statement!AC164</f>
-        <v>5.6463068242776637E-2</v>
+        <v>5.5514905887734216E-2</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -13841,7 +13870,7 @@
       </c>
       <c r="C13" s="230" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>0.9708</v>
+        <v>0.97689999999999999</v>
       </c>
       <c r="E13" s="206" t="s">
         <v>123</v>
@@ -13857,7 +13886,7 @@
       </c>
       <c r="C14" s="231" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>53048341</v>
+        <v>53115954</v>
       </c>
       <c r="E14" s="207" t="s">
         <v>124</v>
@@ -13873,7 +13902,7 @@
       </c>
       <c r="F15" s="213">
         <f ca="1">Statement!AC176</f>
-        <v>0.23145293484254095</v>
+        <v>0.22756623568481568</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -13886,10 +13915,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="251" t="s">
+      <c r="B17" s="252" t="s">
         <v>103</v>
       </c>
-      <c r="C17" s="251"/>
+      <c r="C17" s="252"/>
       <c r="E17" s="205" t="s">
         <v>345</v>
       </c>
@@ -13962,14 +13991,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="251" t="s">
+      <c r="B25" s="252" t="s">
         <v>126</v>
       </c>
-      <c r="C25" s="251"/>
-      <c r="E25" s="249" t="s">
+      <c r="C25" s="252"/>
+      <c r="E25" s="250" t="s">
         <v>401</v>
       </c>
-      <c r="F25" s="250"/>
+      <c r="F25" s="251"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="205" t="s">
@@ -13978,12 +14007,12 @@
       <c r="C26" s="191">
         <v>0.21</v>
       </c>
-      <c r="E26" s="206" t="e" vm="2">
+      <c r="E26" s="206" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="240" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>44.85</v>
+        <v>44.79</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -13998,7 +14027,7 @@
       </c>
       <c r="F27" s="241">
         <f ca="1">F26/1000</f>
-        <v>4.4850000000000001E-2</v>
+        <v>4.4789999999999996E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14018,15 +14047,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="252" t="s">
+      <c r="B33" s="249" t="s">
         <v>391</v>
       </c>
-      <c r="C33" s="252"/>
-      <c r="D33" s="252"/>
-      <c r="E33" s="252"/>
-      <c r="F33" s="252"/>
-      <c r="G33" s="252"/>
-      <c r="H33" s="252"/>
+      <c r="C33" s="249"/>
+      <c r="D33" s="249"/>
+      <c r="E33" s="249"/>
+      <c r="F33" s="249"/>
+      <c r="G33" s="249"/>
+      <c r="H33" s="249"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -14045,24 +14074,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="252"/>
-      <c r="C39" s="252"/>
-      <c r="D39" s="252"/>
-      <c r="E39" s="252"/>
-      <c r="F39" s="252"/>
-      <c r="G39" s="252"/>
-      <c r="H39" s="252"/>
+      <c r="B39" s="249"/>
+      <c r="C39" s="249"/>
+      <c r="D39" s="249"/>
+      <c r="E39" s="249"/>
+      <c r="F39" s="249"/>
+      <c r="G39" s="249"/>
+      <c r="H39" s="249"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="252" t="s">
+      <c r="B42" s="249" t="s">
         <v>394</v>
       </c>
-      <c r="C42" s="252"/>
-      <c r="D42" s="252"/>
-      <c r="E42" s="252"/>
-      <c r="F42" s="252"/>
-      <c r="G42" s="252"/>
-      <c r="H42" s="252"/>
+      <c r="C42" s="249"/>
+      <c r="D42" s="249"/>
+      <c r="E42" s="249"/>
+      <c r="F42" s="249"/>
+      <c r="G42" s="249"/>
+      <c r="H42" s="249"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -14077,24 +14106,24 @@
       </c>
     </row>
     <row r="49" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="252"/>
-      <c r="C49" s="252"/>
-      <c r="D49" s="252"/>
-      <c r="E49" s="252"/>
-      <c r="F49" s="252"/>
-      <c r="G49" s="252"/>
-      <c r="H49" s="252"/>
+      <c r="B49" s="249"/>
+      <c r="C49" s="249"/>
+      <c r="D49" s="249"/>
+      <c r="E49" s="249"/>
+      <c r="F49" s="249"/>
+      <c r="G49" s="249"/>
+      <c r="H49" s="249"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B52" s="252" t="s">
+      <c r="B52" s="249" t="s">
         <v>128</v>
       </c>
-      <c r="C52" s="252"/>
-      <c r="D52" s="252"/>
-      <c r="E52" s="252"/>
-      <c r="F52" s="252"/>
-      <c r="G52" s="252"/>
-      <c r="H52" s="252"/>
+      <c r="C52" s="249"/>
+      <c r="D52" s="249"/>
+      <c r="E52" s="249"/>
+      <c r="F52" s="249"/>
+      <c r="G52" s="249"/>
+      <c r="H52" s="249"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B54" s="41" t="s">
@@ -14109,13 +14138,13 @@
       </c>
     </row>
     <row r="59" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="252"/>
-      <c r="C59" s="252"/>
-      <c r="D59" s="252"/>
-      <c r="E59" s="252"/>
-      <c r="F59" s="252"/>
-      <c r="G59" s="252"/>
-      <c r="H59" s="252"/>
+      <c r="B59" s="249"/>
+      <c r="C59" s="249"/>
+      <c r="D59" s="249"/>
+      <c r="E59" s="249"/>
+      <c r="F59" s="249"/>
+      <c r="G59" s="249"/>
+      <c r="H59" s="249"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -14200,36 +14229,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="252" t="s">
+      <c r="C2" s="249" t="s">
         <v>137</v>
       </c>
-      <c r="D2" s="252"/>
-      <c r="E2" s="252"/>
-      <c r="F2" s="252"/>
+      <c r="D2" s="249"/>
+      <c r="E2" s="249"/>
+      <c r="F2" s="249"/>
       <c r="G2" s="258"/>
       <c r="H2" s="259" t="s">
         <v>138</v>
       </c>
-      <c r="I2" s="252"/>
-      <c r="J2" s="252"/>
-      <c r="K2" s="252"/>
-      <c r="L2" s="252"/>
+      <c r="I2" s="249"/>
+      <c r="J2" s="249"/>
+      <c r="K2" s="249"/>
+      <c r="L2" s="249"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="252" t="s">
+      <c r="S2" s="249" t="s">
         <v>137</v>
       </c>
-      <c r="T2" s="252"/>
-      <c r="U2" s="252"/>
-      <c r="V2" s="252"/>
-      <c r="W2" s="252"/>
-      <c r="X2" s="252"/>
-      <c r="Y2" s="252"/>
-      <c r="Z2" s="252"/>
-      <c r="AA2" s="252" t="s">
+      <c r="T2" s="249"/>
+      <c r="U2" s="249"/>
+      <c r="V2" s="249"/>
+      <c r="W2" s="249"/>
+      <c r="X2" s="249"/>
+      <c r="Y2" s="249"/>
+      <c r="Z2" s="249"/>
+      <c r="AA2" s="249" t="s">
         <v>138</v>
       </c>
-      <c r="AB2" s="252"/>
-      <c r="AC2" s="252"/>
+      <c r="AB2" s="249"/>
+      <c r="AC2" s="249"/>
       <c r="AE2" s="87" t="s">
         <v>139</v>
       </c>
@@ -16402,35 +16431,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="252" t="s">
+      <c r="C2" s="249" t="s">
         <v>137</v>
       </c>
-      <c r="D2" s="252"/>
-      <c r="E2" s="252"/>
-      <c r="F2" s="252"/>
+      <c r="D2" s="249"/>
+      <c r="E2" s="249"/>
+      <c r="F2" s="249"/>
       <c r="G2" s="258"/>
       <c r="H2" s="259" t="s">
         <v>138</v>
       </c>
-      <c r="I2" s="252"/>
-      <c r="J2" s="252"/>
-      <c r="K2" s="252"/>
-      <c r="L2" s="252"/>
-      <c r="P2" s="252" t="s">
+      <c r="I2" s="249"/>
+      <c r="J2" s="249"/>
+      <c r="K2" s="249"/>
+      <c r="L2" s="249"/>
+      <c r="P2" s="249" t="s">
         <v>137</v>
       </c>
-      <c r="Q2" s="252"/>
-      <c r="R2" s="252"/>
-      <c r="S2" s="252"/>
-      <c r="T2" s="252"/>
-      <c r="U2" s="252"/>
-      <c r="V2" s="252"/>
-      <c r="W2" s="252"/>
-      <c r="X2" s="252" t="s">
+      <c r="Q2" s="249"/>
+      <c r="R2" s="249"/>
+      <c r="S2" s="249"/>
+      <c r="T2" s="249"/>
+      <c r="U2" s="249"/>
+      <c r="V2" s="249"/>
+      <c r="W2" s="249"/>
+      <c r="X2" s="249" t="s">
         <v>138</v>
       </c>
-      <c r="Y2" s="252"/>
-      <c r="Z2" s="252"/>
+      <c r="Y2" s="249"/>
+      <c r="Z2" s="249"/>
       <c r="AB2" s="87" t="s">
         <v>139</v>
       </c>
@@ -18371,20 +18400,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="252" t="s">
+      <c r="C3" s="249" t="s">
         <v>137</v>
       </c>
-      <c r="D3" s="252"/>
-      <c r="E3" s="252"/>
-      <c r="F3" s="252"/>
+      <c r="D3" s="249"/>
+      <c r="E3" s="249"/>
+      <c r="F3" s="249"/>
       <c r="G3" s="258"/>
       <c r="H3" s="259" t="s">
         <v>138</v>
       </c>
-      <c r="I3" s="252"/>
-      <c r="J3" s="252"/>
-      <c r="K3" s="252"/>
-      <c r="L3" s="252"/>
+      <c r="I3" s="249"/>
+      <c r="J3" s="249"/>
+      <c r="K3" s="249"/>
+      <c r="L3" s="249"/>
       <c r="P3" s="263"/>
       <c r="Q3" s="263"/>
       <c r="R3" s="263"/>
@@ -19827,20 +19856,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="252" t="s">
+      <c r="C2" s="249" t="s">
         <v>137</v>
       </c>
-      <c r="D2" s="252"/>
-      <c r="E2" s="252"/>
-      <c r="F2" s="252"/>
+      <c r="D2" s="249"/>
+      <c r="E2" s="249"/>
+      <c r="F2" s="249"/>
       <c r="G2" s="258"/>
       <c r="H2" s="259" t="s">
         <v>138</v>
       </c>
-      <c r="I2" s="252"/>
-      <c r="J2" s="252"/>
-      <c r="K2" s="252"/>
-      <c r="L2" s="252"/>
+      <c r="I2" s="249"/>
+      <c r="J2" s="249"/>
+      <c r="K2" s="249"/>
+      <c r="L2" s="249"/>
       <c r="S2" s="263"/>
       <c r="T2" s="263"/>
       <c r="U2" s="263"/>
@@ -20921,10 +20950,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="252" t="s">
+      <c r="B4" s="249" t="s">
         <v>207</v>
       </c>
-      <c r="C4" s="252"/>
+      <c r="C4" s="249"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -20941,7 +20970,7 @@
       </c>
       <c r="C6" s="154">
         <f ca="1">Overview!C5</f>
-        <v>11.71</v>
+        <v>11.91</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20950,7 +20979,7 @@
       </c>
       <c r="C7" s="155">
         <f ca="1">C5*C6</f>
-        <v>6116777.0500000007</v>
+        <v>6221248.0499999998</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20968,7 +20997,7 @@
       </c>
       <c r="C9" s="156">
         <f ca="1">Overview!F27</f>
-        <v>4.4850000000000001E-2</v>
+        <v>4.4789999999999996E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20977,7 +21006,7 @@
       </c>
       <c r="C10" s="154">
         <f ca="1">Overview!C13</f>
-        <v>0.9708</v>
+        <v>0.97689999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21009,10 +21038,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="252" t="s">
+      <c r="B15" s="249" t="s">
         <v>214</v>
       </c>
-      <c r="C15" s="252"/>
+      <c r="C15" s="249"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -21047,7 +21076,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>8.8536000000000004E-2</v>
+        <v>8.8750499999999996E-2</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21056,7 +21085,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>8.8536000000000004E-2</v>
+        <v>8.8750499999999996E-2</v>
       </c>
     </row>
   </sheetData>
@@ -21101,20 +21130,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="252" t="s">
+      <c r="C3" s="249" t="s">
         <v>137</v>
       </c>
-      <c r="D3" s="252"/>
-      <c r="E3" s="252"/>
-      <c r="F3" s="252"/>
+      <c r="D3" s="249"/>
+      <c r="E3" s="249"/>
+      <c r="F3" s="249"/>
       <c r="G3" s="258"/>
       <c r="H3" s="259" t="s">
         <v>138</v>
       </c>
-      <c r="I3" s="252"/>
-      <c r="J3" s="252"/>
-      <c r="K3" s="252"/>
-      <c r="L3" s="252"/>
+      <c r="I3" s="249"/>
+      <c r="J3" s="249"/>
+      <c r="K3" s="249"/>
+      <c r="L3" s="249"/>
       <c r="P3" s="263"/>
       <c r="Q3" s="263"/>
       <c r="R3" s="263"/>
@@ -21400,10 +21429,10 @@
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="252" t="s">
+      <c r="B13" s="249" t="s">
         <v>225</v>
       </c>
-      <c r="C13" s="252"/>
+      <c r="C13" s="249"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -21423,10 +21452,10 @@
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="252" t="s">
+      <c r="B18" s="249" t="s">
         <v>227</v>
       </c>
-      <c r="C18" s="252"/>
+      <c r="C18" s="249"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -21518,7 +21547,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2D33819-10E3-B843-9B8A-30FFCAB234A7}">
-  <dimension ref="A1:N62"/>
+  <dimension ref="A1:N67"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="85" customWidth="1"/>
@@ -21540,20 +21569,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="252" t="s">
+      <c r="C2" s="249" t="s">
         <v>137</v>
       </c>
-      <c r="D2" s="252"/>
-      <c r="E2" s="252"/>
-      <c r="F2" s="252"/>
+      <c r="D2" s="249"/>
+      <c r="E2" s="249"/>
+      <c r="F2" s="249"/>
       <c r="G2" s="258"/>
       <c r="H2" s="259" t="s">
         <v>138</v>
       </c>
-      <c r="I2" s="252"/>
-      <c r="J2" s="252"/>
-      <c r="K2" s="252"/>
-      <c r="L2" s="252"/>
+      <c r="I2" s="249"/>
+      <c r="J2" s="249"/>
+      <c r="K2" s="249"/>
+      <c r="L2" s="249"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -22485,10 +22514,10 @@
       <c r="N36" s="93"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="252" t="s">
+      <c r="B37" s="249" t="s">
         <v>246</v>
       </c>
-      <c r="C37" s="252"/>
+      <c r="C37" s="249"/>
       <c r="N37" s="93"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -22519,182 +22548,227 @@
     </row>
     <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B41" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="C41" s="24">
+        <f>(C38*C40)</f>
+        <v>10292929.416936001</v>
+      </c>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B42" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="C42" s="24">
+        <f>C41/(1+C39)^5-G30+G31</f>
+        <v>8080575.3517183978</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B43" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C43" s="90">
+        <f>Statement!AC107</f>
+        <v>1415746</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B44" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="C44" s="90">
+        <f>Statement!AC108</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B45" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="C45" s="24">
+        <f>C42+C43-C44</f>
+        <v>9496321.3517183978</v>
+      </c>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B46" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C46" s="90">
+        <f>Statement!AC78</f>
+        <v>522355</v>
+      </c>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B47" s="162" t="s">
+        <v>250</v>
+      </c>
+      <c r="C47" s="163">
+        <f>C45/C46</f>
+        <v>18.179822824933996</v>
+      </c>
+    </row>
+    <row r="49" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B49" s="249" t="s">
+        <v>251</v>
+      </c>
+      <c r="C49" s="249"/>
+    </row>
+    <row r="50" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B50" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="C50" s="64">
+        <f>L6</f>
+        <v>2379868.0732800001</v>
+      </c>
+    </row>
+    <row r="51" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B51" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="C51" s="156">
+        <f>Overview!C29</f>
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="52" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B52" s="39" t="s">
+        <v>253</v>
+      </c>
+      <c r="C52" s="114">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B53" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="C41" s="24">
+      <c r="C53" s="24">
         <f>L18</f>
         <v>482510.33681860787</v>
       </c>
     </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B42" s="1" t="s">
+    <row r="54" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B54" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="C54" s="24">
+        <f>(C50*C52)/C53</f>
+        <v>24.661316988268727</v>
+      </c>
+    </row>
+    <row r="55" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B55" s="162" t="s">
+        <v>250</v>
+      </c>
+      <c r="C55" s="163">
+        <f>C54/(1+C51)^5</f>
+        <v>13.993493556532998</v>
+      </c>
+    </row>
+    <row r="57" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B57" s="249" t="s">
+        <v>375</v>
+      </c>
+      <c r="C57" s="249"/>
+    </row>
+    <row r="58" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B58" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C58" s="64">
+        <f>L8</f>
+        <v>199093.66914172584</v>
+      </c>
+    </row>
+    <row r="59" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B59" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="C59" s="156">
+        <f>IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="60" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B60" s="39" t="s">
+        <v>409</v>
+      </c>
+      <c r="C60" s="114">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="61" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B61" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="C42" s="24">
-        <f>(C38*C40)</f>
-        <v>10292929.416936001</v>
-      </c>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B43" s="1" t="s">
+      <c r="C61" s="24">
+        <f>(C58*C60)</f>
+        <v>5972810.0742517756</v>
+      </c>
+    </row>
+    <row r="62" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B62" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="C43" s="24">
-        <f>C42/(1+C39)^5-G30+G31</f>
-        <v>8080575.3517183978</v>
-      </c>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B44" s="1" t="s">
+      <c r="C62" s="24">
+        <f>C61/(1+C59)^5-G30+G31</f>
+        <v>5398121.1336854622</v>
+      </c>
+    </row>
+    <row r="63" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B63" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C63" s="90">
+        <f>Statement!AC107</f>
+        <v>1415746</v>
+      </c>
+    </row>
+    <row r="64" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B64" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="C64" s="90">
+        <f>Statement!AC108</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B65" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="C65" s="24">
+        <f>C62+C63-C64</f>
+        <v>6813867.1336854622</v>
+      </c>
+    </row>
+    <row r="66" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B66" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C44" s="90">
+      <c r="C66" s="90">
         <f>Statement!AC78</f>
         <v>522355</v>
       </c>
     </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B45" s="162" t="s">
+    <row r="67" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B67" s="162" t="s">
         <v>250</v>
       </c>
-      <c r="C45" s="163">
-        <f>C43/C44</f>
-        <v>15.469508957927841</v>
-      </c>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B47" s="252" t="s">
-        <v>251</v>
-      </c>
-      <c r="C47" s="252"/>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B48" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="C48" s="64">
-        <f>L6</f>
-        <v>2379868.0732800001</v>
-      </c>
-    </row>
-    <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="C49" s="156">
-        <f>Overview!C29</f>
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="50" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B50" s="39" t="s">
-        <v>253</v>
-      </c>
-      <c r="C50" s="114">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="51" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B51" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="C51" s="24">
-        <f>L18</f>
-        <v>482510.33681860787</v>
-      </c>
-    </row>
-    <row r="52" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B52" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="C52" s="24">
-        <f>(C48*C50)/C51</f>
-        <v>24.661316988268727</v>
-      </c>
-    </row>
-    <row r="53" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B53" s="162" t="s">
-        <v>250</v>
-      </c>
-      <c r="C53" s="163">
-        <f>C52/(1+C49)^5</f>
-        <v>13.993493556532998</v>
-      </c>
-    </row>
-    <row r="55" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B55" s="252" t="s">
-        <v>375</v>
-      </c>
-      <c r="C55" s="252"/>
-    </row>
-    <row r="56" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B56" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="C56" s="64">
-        <f>L8</f>
-        <v>199093.66914172584</v>
-      </c>
-    </row>
-    <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="C57" s="156">
-        <f>IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="58" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B58" s="39" t="s">
-        <v>409</v>
-      </c>
-      <c r="C58" s="114">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="59" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B59" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="C59" s="24">
-        <f>(C56*C58)</f>
-        <v>5972810.0742517756</v>
-      </c>
-    </row>
-    <row r="60" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B60" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="C60" s="24">
-        <f>C59/(1+C57)^5-G30+G31</f>
-        <v>5398121.1336854622</v>
-      </c>
-    </row>
-    <row r="61" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B61" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C61" s="90">
-        <f>Statement!AC78</f>
-        <v>522355</v>
-      </c>
-    </row>
-    <row r="62" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B62" s="162" t="s">
-        <v>250</v>
-      </c>
-      <c r="C62" s="163">
-        <f>C60/C61</f>
-        <v>10.334200177437685</v>
+      <c r="C67" s="163">
+        <f>C65/C66</f>
+        <v>13.04451404444384</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B57:C57"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
@@ -22738,10 +22812,10 @@
       <c r="N3" s="93"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="252" t="s">
+      <c r="B4" s="249" t="s">
         <v>256</v>
       </c>
-      <c r="C4" s="252"/>
+      <c r="C4" s="249"/>
       <c r="N4" s="93"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -22758,8 +22832,8 @@
         <v>258</v>
       </c>
       <c r="C6" s="154">
-        <f>Multiples!C45</f>
-        <v>15.469508957927841</v>
+        <f>Multiples!C47</f>
+        <v>18.179822824933996</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -22767,7 +22841,7 @@
         <v>259</v>
       </c>
       <c r="C7" s="154">
-        <f>Multiples!C53</f>
+        <f>Multiples!C55</f>
         <v>13.993493556532998</v>
       </c>
     </row>
@@ -22776,8 +22850,8 @@
         <v>376</v>
       </c>
       <c r="C8" s="154">
-        <f>Multiples!C62</f>
-        <v>10.334200177437685</v>
+        <f>Multiples!C67</f>
+        <v>13.04451404444384</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -22786,7 +22860,7 @@
       </c>
       <c r="C9" s="163">
         <f>AVERAGE(C5:C8)</f>
-        <v>11.503690579122585</v>
+        <v>12.858847512625662</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -22795,7 +22869,7 @@
       </c>
       <c r="C10" s="154">
         <f ca="1">Overview!C5</f>
-        <v>11.71</v>
+        <v>11.91</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -22804,7 +22878,7 @@
       </c>
       <c r="C11" s="175">
         <f ca="1">(C9-C10)/C10</f>
-        <v>-1.7618225523263507E-2</v>
+        <v>7.9668137080240273E-2</v>
       </c>
     </row>
   </sheetData>
@@ -22869,20 +22943,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="252" t="s">
+      <c r="C3" s="249" t="s">
         <v>137</v>
       </c>
-      <c r="D3" s="252"/>
-      <c r="E3" s="252"/>
-      <c r="F3" s="252"/>
+      <c r="D3" s="249"/>
+      <c r="E3" s="249"/>
+      <c r="F3" s="249"/>
       <c r="G3" s="258"/>
       <c r="H3" s="259" t="s">
         <v>138</v>
       </c>
-      <c r="I3" s="252"/>
-      <c r="J3" s="252"/>
-      <c r="K3" s="252"/>
-      <c r="L3" s="252"/>
+      <c r="I3" s="249"/>
+      <c r="J3" s="249"/>
+      <c r="K3" s="249"/>
+      <c r="L3" s="249"/>
       <c r="P3" s="263"/>
       <c r="Q3" s="263"/>
       <c r="R3" s="263"/>
@@ -23161,7 +23235,7 @@
       </c>
       <c r="C15" s="177">
         <f ca="1">Overview!C5</f>
-        <v>11.71</v>
+        <v>11.91</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -23227,7 +23301,7 @@
       </c>
       <c r="C23" s="182">
         <f ca="1">C15*C22</f>
-        <v>6067196.9100000001</v>
+        <v>6170821.1100000003</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -23254,7 +23328,7 @@
       </c>
       <c r="C26" s="183">
         <f ca="1">C23+C25-C24</f>
-        <v>4651450.91</v>
+        <v>4755075.1100000003</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -30403,7 +30477,7 @@
       <c r="AA116" s="68"/>
       <c r="AC116" s="63">
         <f ca="1">Overview!C5</f>
-        <v>11.71</v>
+        <v>11.91</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -30450,7 +30524,7 @@
       <c r="AA117" s="68"/>
       <c r="AC117" s="65">
         <f ca="1">AC116/AC85</f>
-        <v>11.71</v>
+        <v>11.91</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -31756,7 +31830,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>19.516666666666666</v>
+        <v>19.849999999999998</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -31793,7 +31867,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>3.7724124948425253</v>
+        <v>3.8368431096135334</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -31830,7 +31904,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="72">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>3.1882861271752239</v>
+        <v>3.2427402027888057</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -31867,7 +31941,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="164">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>6116777.0500000007</v>
+        <v>6221248.0499999998</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -31904,7 +31978,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="164">
         <f ca="1">AC153+AC108-AC107+AC48+AC45</f>
-        <v>4701031.0500000007</v>
+        <v>4805502.05</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -31941,7 +32015,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="204">
         <f ca="1">AC154/AC5</f>
-        <v>2.8110666256061907</v>
+        <v>2.8735369514390103</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -31978,7 +32052,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="204">
         <f ca="1">AC154/AC12</f>
-        <v>46.471703456934144</v>
+        <v>47.504443994108286</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -32113,7 +32187,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="72">
         <f t="shared" ref="AC159:AC160" ca="1" si="101">AC153/AC157</f>
-        <v>56.842615859268285</v>
+        <v>57.813454729622983</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -32150,7 +32224,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
         <f t="shared" ca="1" si="101"/>
-        <v>-86.67891675117545</v>
+        <v>-88.605182077993916</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -32187,7 +32261,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="74">
         <f t="shared" ref="AC161" ca="1" si="104">AC157/AC153</f>
-        <v>1.7592434564866147E-2</v>
+        <v>1.7297011650258827E-2</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -32224,7 +32298,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f ca="1">AC26/AC117</f>
-        <v>5.1238257899231428E-2</v>
+        <v>5.0377833753148624E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -32298,7 +32372,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="175">
         <f ca="1">-AC63/AC153</f>
-        <v>5.6463068242776637E-2</v>
+        <v>5.5514905887734216E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -32335,7 +32409,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="175">
         <f ca="1">-(AC63+AC64)/AC153</f>
-        <v>5.6463068242776637E-2</v>
+        <v>5.5514905887734216E-2</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -32838,7 +32912,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="175">
         <f ca="1">(AC107-AC108)/AC153</f>
-        <v>0.23145293484254095</v>
+        <v>0.22756623568481568</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -34343,15 +34417,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="252" t="s">
+      <c r="B4" s="249" t="s">
         <v>282</v>
       </c>
-      <c r="C4" s="252"/>
-      <c r="E4" s="252" t="s">
+      <c r="C4" s="249"/>
+      <c r="E4" s="249" t="s">
         <v>289</v>
       </c>
-      <c r="F4" s="252"/>
-      <c r="G4" s="252"/>
+      <c r="F4" s="249"/>
+      <c r="G4" s="249"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -34359,7 +34433,7 @@
       </c>
       <c r="C5" s="193">
         <f ca="1">Overview!C5</f>
-        <v>11.71</v>
+        <v>11.91</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="153" t="s">
@@ -34375,7 +34449,7 @@
       </c>
       <c r="C6" s="194">
         <f ca="1">Statement!AC153</f>
-        <v>6116777.0500000007</v>
+        <v>6221248.0499999998</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>20</v>
@@ -34395,7 +34469,7 @@
       </c>
       <c r="C7" s="194">
         <f ca="1">Statement!AC154</f>
-        <v>4701031.0500000007</v>
+        <v>4805502.05</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>32</v>
@@ -34415,7 +34489,7 @@
       </c>
       <c r="C8" s="195">
         <f ca="1">Statement!AC150</f>
-        <v>19.516666666666666</v>
+        <v>19.849999999999998</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>292</v>
@@ -34435,7 +34509,7 @@
       </c>
       <c r="C9" s="195">
         <f ca="1">Statement!AC151</f>
-        <v>3.7724124948425253</v>
+        <v>3.8368431096135334</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>293</v>
@@ -34455,7 +34529,7 @@
       </c>
       <c r="C10" s="195">
         <f ca="1">Statement!AC152</f>
-        <v>3.1882861271752239</v>
+        <v>3.2427402027888057</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -34475,7 +34549,7 @@
       </c>
       <c r="C11" s="195">
         <f ca="1">Statement!AC155</f>
-        <v>2.8110666256061907</v>
+        <v>2.8735369514390103</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -34484,18 +34558,18 @@
       </c>
       <c r="C12" s="195">
         <f ca="1">Statement!AC156</f>
-        <v>46.471703456934144</v>
+        <v>47.504443994108286</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="252" t="s">
+      <c r="B15" s="249" t="s">
         <v>78</v>
       </c>
-      <c r="C15" s="252"/>
-      <c r="E15" s="252" t="s">
+      <c r="C15" s="249"/>
+      <c r="E15" s="249" t="s">
         <v>295</v>
       </c>
-      <c r="F15" s="252"/>
+      <c r="F15" s="249"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -34546,14 +34620,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="252" t="s">
+      <c r="B21" s="249" t="s">
         <v>294</v>
       </c>
-      <c r="C21" s="252"/>
-      <c r="E21" s="252" t="s">
+      <c r="C21" s="249"/>
+      <c r="E21" s="249" t="s">
         <v>298</v>
       </c>
-      <c r="F21" s="252"/>
+      <c r="F21" s="249"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -34622,14 +34696,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="252" t="s">
+      <c r="B29" s="249" t="s">
         <v>299</v>
       </c>
-      <c r="C29" s="252"/>
-      <c r="E29" s="252" t="s">
+      <c r="C29" s="249"/>
+      <c r="E29" s="249" t="s">
         <v>305</v>
       </c>
-      <c r="F29" s="252"/>
+      <c r="F29" s="249"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -34705,14 +34779,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="252" t="s">
+      <c r="B37" s="249" t="s">
         <v>317</v>
       </c>
-      <c r="C37" s="252"/>
-      <c r="E37" s="252" t="s">
+      <c r="C37" s="249"/>
+      <c r="E37" s="249" t="s">
         <v>320</v>
       </c>
-      <c r="F37" s="252"/>
+      <c r="F37" s="249"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -34720,7 +34794,7 @@
       </c>
       <c r="C38" s="196">
         <f ca="1">Statement!AC162</f>
-        <v>5.1238257899231428E-2</v>
+        <v>5.0377833753148624E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>319</v>
@@ -34736,7 +34810,7 @@
       </c>
       <c r="C39" s="236">
         <f ca="1">Statement!AC161</f>
-        <v>1.7592434564866147E-2</v>
+        <v>1.7297011650258827E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>321</v>
@@ -34768,7 +34842,7 @@
       </c>
       <c r="C41" s="196">
         <f ca="1">Statement!AC164</f>
-        <v>5.6463068242776637E-2</v>
+        <v>5.5514905887734216E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -34777,18 +34851,18 @@
       </c>
       <c r="C42" s="196">
         <f ca="1">Statement!AC165</f>
-        <v>5.6463068242776637E-2</v>
+        <v>5.5514905887734216E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="252" t="s">
+      <c r="B45" s="249" t="s">
         <v>328</v>
       </c>
-      <c r="C45" s="252"/>
-      <c r="E45" s="252" t="s">
+      <c r="C45" s="249"/>
+      <c r="E45" s="249" t="s">
         <v>334</v>
       </c>
-      <c r="F45" s="252"/>
+      <c r="F45" s="249"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -34821,18 +34895,18 @@
       </c>
       <c r="F48" s="196">
         <f ca="1">Statement!AC176</f>
-        <v>0.23145293484254095</v>
+        <v>0.22756623568481568</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="252" t="s">
+      <c r="B51" s="249" t="s">
         <v>331</v>
       </c>
-      <c r="C51" s="252"/>
-      <c r="E51" s="252" t="s">
+      <c r="C51" s="249"/>
+      <c r="E51" s="249" t="s">
         <v>352</v>
       </c>
-      <c r="F51" s="252"/>
+      <c r="F51" s="249"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -35000,7 +35074,7 @@
       </c>
       <c r="I6" s="193">
         <f ca="1">Statement!AC116</f>
-        <v>11.71</v>
+        <v>11.91</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -35029,7 +35103,7 @@
       </c>
       <c r="I7" s="194">
         <f ca="1">Statement!AC153</f>
-        <v>6116777.0500000007</v>
+        <v>6221248.0499999998</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -35058,7 +35132,7 @@
       </c>
       <c r="I8" s="194">
         <f ca="1">Statement!AC154</f>
-        <v>4701031.0500000007</v>
+        <v>4805502.05</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -35087,7 +35161,7 @@
       </c>
       <c r="I9" s="195">
         <f ca="1">Statement!AC150</f>
-        <v>19.516666666666666</v>
+        <v>19.849999999999998</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -35116,7 +35190,7 @@
       </c>
       <c r="I10" s="195">
         <f ca="1">Statement!AC151</f>
-        <v>3.7724124948425253</v>
+        <v>3.8368431096135334</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -35145,7 +35219,7 @@
       </c>
       <c r="I11" s="195">
         <f ca="1">Statement!AC152</f>
-        <v>3.1882861271752239</v>
+        <v>3.2427402027888057</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -35174,7 +35248,7 @@
       </c>
       <c r="I12" s="195">
         <f ca="1">Statement!AC155</f>
-        <v>2.8110666256061907</v>
+        <v>2.8735369514390103</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -35203,7 +35277,7 @@
       </c>
       <c r="I13" s="195">
         <f ca="1">Statement!AC156</f>
-        <v>46.471703456934144</v>
+        <v>47.504443994108286</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35976,7 +36050,7 @@
       </c>
       <c r="I51" s="196">
         <f ca="1">Statement!AC162</f>
-        <v>5.1238257899231428E-2</v>
+        <v>5.0377833753148624E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -36005,7 +36079,7 @@
       </c>
       <c r="I52" s="196">
         <f ca="1">Statement!AC161</f>
-        <v>1.7592434564866147E-2</v>
+        <v>1.7297011650258827E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -36063,7 +36137,7 @@
       </c>
       <c r="I54" s="196">
         <f ca="1">Statement!AC164</f>
-        <v>5.6463068242776637E-2</v>
+        <v>5.5514905887734216E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -36092,7 +36166,7 @@
       </c>
       <c r="I55" s="196">
         <f ca="1">Statement!AC165</f>
-        <v>5.6463068242776637E-2</v>
+        <v>5.5514905887734216E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36328,7 +36402,7 @@
       </c>
       <c r="I68" s="217">
         <f ca="1">Statement!AC176</f>
-        <v>0.23145293484254095</v>
+        <v>0.22756623568481568</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">

--- a/PATH.xlsx
+++ b/PATH.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3102B096-1CA3-B64F-9219-F9B8E6513959}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBF55030-C3B4-944B-B417-CCCE8CE0970E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="8" activeTab="18" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -135,7 +135,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="5">
+  <futureMetadata name="XLRICHVALUE" count="2">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -146,28 +146,7 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="3"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="4"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="5"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="8"/>
         </ext>
       </extLst>
     </bk>
@@ -177,21 +156,12 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="5">
+  <valueMetadata count="2">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
-    </bk>
-    <bk>
-      <rc t="2" v="2"/>
-    </bk>
-    <bk>
-      <rc t="2" v="3"/>
-    </bk>
-    <bk>
-      <rc t="2" v="4"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -2406,9 +2376,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2416,6 +2383,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -12760,7 +12730,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=c1dbvh&amp;q=XNYS%3aPATH&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
@@ -12779,9 +12749,11 @@
     <v>Powered by Refinitiv</v>
     <v>19.84</v>
     <v>9.2002000000000006</v>
-    <v>0.97689999999999999</v>
-    <v>0.08</v>
-    <v>6.7620000000000006E-3</v>
+    <v>0.97770000000000001</v>
+    <v>-0.12</v>
+    <v>-1.0168999999999999E-2</v>
+    <v>-0.01</v>
+    <v>-8.5619999999999999E-4</v>
     <v>USD</v>
     <v>UiPath, Inc. is focused on agentic automation and orchestration, empowering enterprises to harness the full potential of AI agents to autonomously execute and optimize complex business processes. It is focused on building and managing automations, starting with computer vision technology and user interface automation in its initial robotic process automation offering. Its AI-powered UiPath Platform offers a robust set of capabilities that allows its customers to discover opportunities for automation, automate using a digital workforce that seamlessly collaborates with humans, and operate a mission-critical automation program at scale. It enables employees to quickly build automations for both existing and new processes and to automate a range of actions including logging into applications, moving folders, filling in forms, reading emails and others. Its platform allows users to design and combine UI automations, API integrations and AI-based document understanding in a single workflow.</v>
     <v>3981</v>
@@ -12789,49 +12761,35 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>One Vanderbilt Avenue, 60th Floor, NEW YORK, NY, 10017 US</v>
-    <v>12.315</v>
+    <v>12.23</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46210.766399571097</v>
+    <v>46213.886025265623</v>
     <v>0</v>
-    <v>11.56</v>
-    <v>6170812773</v>
+    <v>11.51</v>
+    <v>6051645104</v>
     <v>UIPATH, INC.</v>
     <v>UIPATH, INC.</v>
-    <v>12.17</v>
-    <v>19.7972</v>
-    <v>11.83</v>
-    <v>11.91</v>
+    <v>12.12</v>
+    <v>19.414899999999999</v>
+    <v>11.8</v>
+    <v>11.68</v>
+    <v>11.67</v>
     <v>518120300</v>
     <v>PATH</v>
     <v>UIPATH, INC. (XNYS:PATH)</v>
-    <v>51665960</v>
-    <v>53115954</v>
+    <v>78662541</v>
+    <v>54552944</v>
     <v>2015</v>
   </rv>
   <rv s="2">
     <v>1</v>
   </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Price (Extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Change (extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Change % (extended hours)</v>
-    <v>0</v>
-  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="4">
+  <rv s="3">
     <v>5</v>
     <v>10 Y TSY YLD NDX</v>
     <v>6</v>
@@ -12845,28 +12803,28 @@
     <v>Powered by Refinitiv</v>
     <v>46.87</v>
     <v>39.47</v>
-    <v>-0.06</v>
-    <v>-1.338E-3</v>
+    <v>-0.3</v>
+    <v>-6.5659999999999998E-3</v>
     <v>US</v>
-    <v>44.91</v>
+    <v>45.81</v>
     <v>Index</v>
-    <v>6</v>
-    <v>44.57</v>
+    <v>3</v>
+    <v>45.29</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>44.57</v>
-    <v>44.85</v>
-    <v>44.79</v>
+    <v>45.77</v>
+    <v>45.69</v>
+    <v>45.39</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="2">
-    <v>7</v>
+    <v>4</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -12888,6 +12846,8 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
+    <k n="Change (Extended hours)"/>
+    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -12908,6 +12868,7 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
+    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -12917,11 +12878,6 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
-  </s>
-  <s t="_error">
-    <k n="errorType" t="i"/>
-    <k n="field" t="s"/>
-    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -12957,7 +12913,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="42">
+    <a count="45">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -12968,13 +12924,16 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
+      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
+      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
+      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -13068,13 +13027,19 @@
       <v>8</v>
       <v>9</v>
       <v>4</v>
+      <v>1</v>
+      <v>1</v>
+      <v>5</v>
     </spb>
     <spb s="4">
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
       <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
+      <v>Real-Time Nasdaq Last Sale</v>
+      <v>from close</v>
+      <v>from close</v>
     </spb>
     <spb s="0">
       <v>1</v>
@@ -13146,6 +13111,9 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
+    <k n="Price (Extended hours)" t="i"/>
+    <k n="Change (Extended hours)" t="i"/>
+    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -13153,6 +13121,9 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
+    <k n="Price (Extended hours)" t="s"/>
+    <k n="Change (Extended hours)" t="s"/>
+    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="UniqueName" t="spb"/>
@@ -13643,18 +13614,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="250" t="s">
+      <c r="B2" s="249" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="251"/>
-      <c r="E2" s="250" t="s">
+      <c r="C2" s="250"/>
+      <c r="E2" s="249" t="s">
         <v>336</v>
       </c>
-      <c r="F2" s="251"/>
-      <c r="H2" s="250" t="s">
+      <c r="F2" s="250"/>
+      <c r="H2" s="249" t="s">
         <v>381</v>
       </c>
-      <c r="I2" s="251"/>
+      <c r="I2" s="250"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="206" t="s">
@@ -13669,7 +13640,7 @@
       </c>
       <c r="F3" s="208">
         <f ca="1">Statement!AC153</f>
-        <v>6221248.0499999998</v>
+        <v>6101106.3999999994</v>
       </c>
       <c r="H3" s="206" t="str">
         <f>'AVG target price'!B5</f>
@@ -13693,7 +13664,7 @@
       </c>
       <c r="F4" s="209">
         <f ca="1">Statement!AC154</f>
-        <v>4805502.05</v>
+        <v>4685360.3999999994</v>
       </c>
       <c r="H4" s="206" t="str">
         <f>'AVG target price'!B6</f>
@@ -13710,7 +13681,7 @@
       </c>
       <c r="C5" s="229" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>11.91</v>
+        <v>11.68</v>
       </c>
       <c r="E5" s="206" t="s">
         <v>292</v>
@@ -13732,16 +13703,16 @@
       <c r="B6" s="206" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="229" t="e" cm="1" vm="2">
-        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C6" s="229" cm="1">
+        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>11.67</v>
       </c>
       <c r="E6" s="206" t="s">
         <v>286</v>
       </c>
       <c r="F6" s="211">
         <f ca="1">Statement!AC150</f>
-        <v>19.849999999999998</v>
+        <v>19.466666666666665</v>
       </c>
       <c r="H6" s="206" t="str">
         <f>'AVG target price'!B8</f>
@@ -13758,14 +13729,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>0.08</v>
+        <v>-0.12</v>
       </c>
       <c r="E7" s="207" t="s">
         <v>242</v>
       </c>
       <c r="F7" s="212">
         <f ca="1">Statement!AC151</f>
-        <v>3.8368431096135334</v>
+        <v>3.7627479026268738</v>
       </c>
       <c r="H7" s="205" t="str">
         <f>'AVG target price'!B9</f>
@@ -13780,16 +13751,16 @@
       <c r="B8" s="206" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" t="e" cm="1" vm="3">
-        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C8" s="6" cm="1">
+        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>-0.01</v>
       </c>
       <c r="E8" s="206" t="s">
         <v>314</v>
       </c>
       <c r="F8" s="213">
         <f ca="1">Statement!AC161</f>
-        <v>1.7297011650258827E-2</v>
+        <v>1.7637620612549882E-2</v>
       </c>
       <c r="H8" s="205" t="str">
         <f>'AVG target price'!B11</f>
@@ -13797,7 +13768,7 @@
       </c>
       <c r="I8" s="234">
         <f ca="1">'AVG target price'!C11</f>
-        <v>7.9668137080240273E-2</v>
+        <v>0.10092872539603272</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13806,30 +13777,30 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>6.7620000000000006E-3</v>
+        <v>-1.0168999999999999E-2</v>
       </c>
       <c r="E9" s="206" t="s">
         <v>337</v>
       </c>
       <c r="F9" s="213">
         <f ca="1">Statement!AC162</f>
-        <v>5.0377833753148624E-2</v>
+        <v>5.1369863013698641E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B10" s="206" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" t="e" cm="1" vm="4">
-        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C10" s="73" cm="1">
+        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>-8.5619999999999999E-4</v>
       </c>
       <c r="E10" s="206" t="s">
         <v>342</v>
       </c>
       <c r="F10" s="213">
         <f ca="1">Statement!AC164</f>
-        <v>5.5514905887734216E-2</v>
+        <v>5.6608093246824878E-2</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -13870,7 +13841,7 @@
       </c>
       <c r="C13" s="230" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>0.97689999999999999</v>
+        <v>0.97770000000000001</v>
       </c>
       <c r="E13" s="206" t="s">
         <v>123</v>
@@ -13886,7 +13857,7 @@
       </c>
       <c r="C14" s="231" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>53115954</v>
+        <v>54552944</v>
       </c>
       <c r="E14" s="207" t="s">
         <v>124</v>
@@ -13902,7 +13873,7 @@
       </c>
       <c r="F15" s="213">
         <f ca="1">Statement!AC176</f>
-        <v>0.22756623568481568</v>
+        <v>0.23204742012038998</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -13915,10 +13886,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="252" t="s">
+      <c r="B17" s="251" t="s">
         <v>103</v>
       </c>
-      <c r="C17" s="252"/>
+      <c r="C17" s="251"/>
       <c r="E17" s="205" t="s">
         <v>345</v>
       </c>
@@ -13991,14 +13962,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="252" t="s">
+      <c r="B25" s="251" t="s">
         <v>126</v>
       </c>
-      <c r="C25" s="252"/>
-      <c r="E25" s="250" t="s">
+      <c r="C25" s="251"/>
+      <c r="E25" s="249" t="s">
         <v>401</v>
       </c>
-      <c r="F25" s="251"/>
+      <c r="F25" s="250"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="205" t="s">
@@ -14007,12 +13978,12 @@
       <c r="C26" s="191">
         <v>0.21</v>
       </c>
-      <c r="E26" s="206" t="e" vm="5">
+      <c r="E26" s="206" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="240" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>44.79</v>
+        <v>45.39</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14027,7 +13998,7 @@
       </c>
       <c r="F27" s="241">
         <f ca="1">F26/1000</f>
-        <v>4.4789999999999996E-2</v>
+        <v>4.539E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14047,15 +14018,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="249" t="s">
+      <c r="B33" s="252" t="s">
         <v>391</v>
       </c>
-      <c r="C33" s="249"/>
-      <c r="D33" s="249"/>
-      <c r="E33" s="249"/>
-      <c r="F33" s="249"/>
-      <c r="G33" s="249"/>
-      <c r="H33" s="249"/>
+      <c r="C33" s="252"/>
+      <c r="D33" s="252"/>
+      <c r="E33" s="252"/>
+      <c r="F33" s="252"/>
+      <c r="G33" s="252"/>
+      <c r="H33" s="252"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -14074,24 +14045,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="249"/>
-      <c r="C39" s="249"/>
-      <c r="D39" s="249"/>
-      <c r="E39" s="249"/>
-      <c r="F39" s="249"/>
-      <c r="G39" s="249"/>
-      <c r="H39" s="249"/>
+      <c r="B39" s="252"/>
+      <c r="C39" s="252"/>
+      <c r="D39" s="252"/>
+      <c r="E39" s="252"/>
+      <c r="F39" s="252"/>
+      <c r="G39" s="252"/>
+      <c r="H39" s="252"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="249" t="s">
+      <c r="B42" s="252" t="s">
         <v>394</v>
       </c>
-      <c r="C42" s="249"/>
-      <c r="D42" s="249"/>
-      <c r="E42" s="249"/>
-      <c r="F42" s="249"/>
-      <c r="G42" s="249"/>
-      <c r="H42" s="249"/>
+      <c r="C42" s="252"/>
+      <c r="D42" s="252"/>
+      <c r="E42" s="252"/>
+      <c r="F42" s="252"/>
+      <c r="G42" s="252"/>
+      <c r="H42" s="252"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -14106,24 +14077,24 @@
       </c>
     </row>
     <row r="49" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="249"/>
-      <c r="C49" s="249"/>
-      <c r="D49" s="249"/>
-      <c r="E49" s="249"/>
-      <c r="F49" s="249"/>
-      <c r="G49" s="249"/>
-      <c r="H49" s="249"/>
+      <c r="B49" s="252"/>
+      <c r="C49" s="252"/>
+      <c r="D49" s="252"/>
+      <c r="E49" s="252"/>
+      <c r="F49" s="252"/>
+      <c r="G49" s="252"/>
+      <c r="H49" s="252"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B52" s="249" t="s">
+      <c r="B52" s="252" t="s">
         <v>128</v>
       </c>
-      <c r="C52" s="249"/>
-      <c r="D52" s="249"/>
-      <c r="E52" s="249"/>
-      <c r="F52" s="249"/>
-      <c r="G52" s="249"/>
-      <c r="H52" s="249"/>
+      <c r="C52" s="252"/>
+      <c r="D52" s="252"/>
+      <c r="E52" s="252"/>
+      <c r="F52" s="252"/>
+      <c r="G52" s="252"/>
+      <c r="H52" s="252"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B54" s="41" t="s">
@@ -14138,13 +14109,13 @@
       </c>
     </row>
     <row r="59" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="249"/>
-      <c r="C59" s="249"/>
-      <c r="D59" s="249"/>
-      <c r="E59" s="249"/>
-      <c r="F59" s="249"/>
-      <c r="G59" s="249"/>
-      <c r="H59" s="249"/>
+      <c r="B59" s="252"/>
+      <c r="C59" s="252"/>
+      <c r="D59" s="252"/>
+      <c r="E59" s="252"/>
+      <c r="F59" s="252"/>
+      <c r="G59" s="252"/>
+      <c r="H59" s="252"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -14229,36 +14200,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="249" t="s">
+      <c r="C2" s="252" t="s">
         <v>137</v>
       </c>
-      <c r="D2" s="249"/>
-      <c r="E2" s="249"/>
-      <c r="F2" s="249"/>
+      <c r="D2" s="252"/>
+      <c r="E2" s="252"/>
+      <c r="F2" s="252"/>
       <c r="G2" s="258"/>
       <c r="H2" s="259" t="s">
         <v>138</v>
       </c>
-      <c r="I2" s="249"/>
-      <c r="J2" s="249"/>
-      <c r="K2" s="249"/>
-      <c r="L2" s="249"/>
+      <c r="I2" s="252"/>
+      <c r="J2" s="252"/>
+      <c r="K2" s="252"/>
+      <c r="L2" s="252"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="249" t="s">
+      <c r="S2" s="252" t="s">
         <v>137</v>
       </c>
-      <c r="T2" s="249"/>
-      <c r="U2" s="249"/>
-      <c r="V2" s="249"/>
-      <c r="W2" s="249"/>
-      <c r="X2" s="249"/>
-      <c r="Y2" s="249"/>
-      <c r="Z2" s="249"/>
-      <c r="AA2" s="249" t="s">
+      <c r="T2" s="252"/>
+      <c r="U2" s="252"/>
+      <c r="V2" s="252"/>
+      <c r="W2" s="252"/>
+      <c r="X2" s="252"/>
+      <c r="Y2" s="252"/>
+      <c r="Z2" s="252"/>
+      <c r="AA2" s="252" t="s">
         <v>138</v>
       </c>
-      <c r="AB2" s="249"/>
-      <c r="AC2" s="249"/>
+      <c r="AB2" s="252"/>
+      <c r="AC2" s="252"/>
       <c r="AE2" s="87" t="s">
         <v>139</v>
       </c>
@@ -16431,35 +16402,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="249" t="s">
+      <c r="C2" s="252" t="s">
         <v>137</v>
       </c>
-      <c r="D2" s="249"/>
-      <c r="E2" s="249"/>
-      <c r="F2" s="249"/>
+      <c r="D2" s="252"/>
+      <c r="E2" s="252"/>
+      <c r="F2" s="252"/>
       <c r="G2" s="258"/>
       <c r="H2" s="259" t="s">
         <v>138</v>
       </c>
-      <c r="I2" s="249"/>
-      <c r="J2" s="249"/>
-      <c r="K2" s="249"/>
-      <c r="L2" s="249"/>
-      <c r="P2" s="249" t="s">
+      <c r="I2" s="252"/>
+      <c r="J2" s="252"/>
+      <c r="K2" s="252"/>
+      <c r="L2" s="252"/>
+      <c r="P2" s="252" t="s">
         <v>137</v>
       </c>
-      <c r="Q2" s="249"/>
-      <c r="R2" s="249"/>
-      <c r="S2" s="249"/>
-      <c r="T2" s="249"/>
-      <c r="U2" s="249"/>
-      <c r="V2" s="249"/>
-      <c r="W2" s="249"/>
-      <c r="X2" s="249" t="s">
+      <c r="Q2" s="252"/>
+      <c r="R2" s="252"/>
+      <c r="S2" s="252"/>
+      <c r="T2" s="252"/>
+      <c r="U2" s="252"/>
+      <c r="V2" s="252"/>
+      <c r="W2" s="252"/>
+      <c r="X2" s="252" t="s">
         <v>138</v>
       </c>
-      <c r="Y2" s="249"/>
-      <c r="Z2" s="249"/>
+      <c r="Y2" s="252"/>
+      <c r="Z2" s="252"/>
       <c r="AB2" s="87" t="s">
         <v>139</v>
       </c>
@@ -18400,20 +18371,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="249" t="s">
+      <c r="C3" s="252" t="s">
         <v>137</v>
       </c>
-      <c r="D3" s="249"/>
-      <c r="E3" s="249"/>
-      <c r="F3" s="249"/>
+      <c r="D3" s="252"/>
+      <c r="E3" s="252"/>
+      <c r="F3" s="252"/>
       <c r="G3" s="258"/>
       <c r="H3" s="259" t="s">
         <v>138</v>
       </c>
-      <c r="I3" s="249"/>
-      <c r="J3" s="249"/>
-      <c r="K3" s="249"/>
-      <c r="L3" s="249"/>
+      <c r="I3" s="252"/>
+      <c r="J3" s="252"/>
+      <c r="K3" s="252"/>
+      <c r="L3" s="252"/>
       <c r="P3" s="263"/>
       <c r="Q3" s="263"/>
       <c r="R3" s="263"/>
@@ -19856,20 +19827,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="249" t="s">
+      <c r="C2" s="252" t="s">
         <v>137</v>
       </c>
-      <c r="D2" s="249"/>
-      <c r="E2" s="249"/>
-      <c r="F2" s="249"/>
+      <c r="D2" s="252"/>
+      <c r="E2" s="252"/>
+      <c r="F2" s="252"/>
       <c r="G2" s="258"/>
       <c r="H2" s="259" t="s">
         <v>138</v>
       </c>
-      <c r="I2" s="249"/>
-      <c r="J2" s="249"/>
-      <c r="K2" s="249"/>
-      <c r="L2" s="249"/>
+      <c r="I2" s="252"/>
+      <c r="J2" s="252"/>
+      <c r="K2" s="252"/>
+      <c r="L2" s="252"/>
       <c r="S2" s="263"/>
       <c r="T2" s="263"/>
       <c r="U2" s="263"/>
@@ -20950,10 +20921,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="249" t="s">
+      <c r="B4" s="252" t="s">
         <v>207</v>
       </c>
-      <c r="C4" s="249"/>
+      <c r="C4" s="252"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -20970,7 +20941,7 @@
       </c>
       <c r="C6" s="154">
         <f ca="1">Overview!C5</f>
-        <v>11.91</v>
+        <v>11.68</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20979,7 +20950,7 @@
       </c>
       <c r="C7" s="155">
         <f ca="1">C5*C6</f>
-        <v>6221248.0499999998</v>
+        <v>6101106.3999999994</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20997,7 +20968,7 @@
       </c>
       <c r="C9" s="156">
         <f ca="1">Overview!F27</f>
-        <v>4.4789999999999996E-2</v>
+        <v>4.539E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21006,7 +20977,7 @@
       </c>
       <c r="C10" s="154">
         <f ca="1">Overview!C13</f>
-        <v>0.97689999999999999</v>
+        <v>0.97770000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21038,10 +21009,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="249" t="s">
+      <c r="B15" s="252" t="s">
         <v>214</v>
       </c>
-      <c r="C15" s="249"/>
+      <c r="C15" s="252"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -21076,7 +21047,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>8.8750499999999996E-2</v>
+        <v>8.9386500000000008E-2</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21085,7 +21056,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>8.8750499999999996E-2</v>
+        <v>8.9386500000000008E-2</v>
       </c>
     </row>
   </sheetData>
@@ -21130,20 +21101,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="249" t="s">
+      <c r="C3" s="252" t="s">
         <v>137</v>
       </c>
-      <c r="D3" s="249"/>
-      <c r="E3" s="249"/>
-      <c r="F3" s="249"/>
+      <c r="D3" s="252"/>
+      <c r="E3" s="252"/>
+      <c r="F3" s="252"/>
       <c r="G3" s="258"/>
       <c r="H3" s="259" t="s">
         <v>138</v>
       </c>
-      <c r="I3" s="249"/>
-      <c r="J3" s="249"/>
-      <c r="K3" s="249"/>
-      <c r="L3" s="249"/>
+      <c r="I3" s="252"/>
+      <c r="J3" s="252"/>
+      <c r="K3" s="252"/>
+      <c r="L3" s="252"/>
       <c r="P3" s="263"/>
       <c r="Q3" s="263"/>
       <c r="R3" s="263"/>
@@ -21429,10 +21400,10 @@
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="249" t="s">
+      <c r="B13" s="252" t="s">
         <v>225</v>
       </c>
-      <c r="C13" s="249"/>
+      <c r="C13" s="252"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -21452,10 +21423,10 @@
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="249" t="s">
+      <c r="B18" s="252" t="s">
         <v>227</v>
       </c>
-      <c r="C18" s="249"/>
+      <c r="C18" s="252"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -21569,20 +21540,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="249" t="s">
+      <c r="C2" s="252" t="s">
         <v>137</v>
       </c>
-      <c r="D2" s="249"/>
-      <c r="E2" s="249"/>
-      <c r="F2" s="249"/>
+      <c r="D2" s="252"/>
+      <c r="E2" s="252"/>
+      <c r="F2" s="252"/>
       <c r="G2" s="258"/>
       <c r="H2" s="259" t="s">
         <v>138</v>
       </c>
-      <c r="I2" s="249"/>
-      <c r="J2" s="249"/>
-      <c r="K2" s="249"/>
-      <c r="L2" s="249"/>
+      <c r="I2" s="252"/>
+      <c r="J2" s="252"/>
+      <c r="K2" s="252"/>
+      <c r="L2" s="252"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -22514,10 +22485,10 @@
       <c r="N36" s="93"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="249" t="s">
+      <c r="B37" s="252" t="s">
         <v>246</v>
       </c>
-      <c r="C37" s="249"/>
+      <c r="C37" s="252"/>
       <c r="N37" s="93"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -22610,10 +22581,10 @@
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="249" t="s">
+      <c r="B49" s="252" t="s">
         <v>251</v>
       </c>
-      <c r="C49" s="249"/>
+      <c r="C49" s="252"/>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
@@ -22669,10 +22640,10 @@
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="249" t="s">
+      <c r="B57" s="252" t="s">
         <v>375</v>
       </c>
-      <c r="C57" s="249"/>
+      <c r="C57" s="252"/>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
@@ -22812,10 +22783,10 @@
       <c r="N3" s="93"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="249" t="s">
+      <c r="B4" s="252" t="s">
         <v>256</v>
       </c>
-      <c r="C4" s="249"/>
+      <c r="C4" s="252"/>
       <c r="N4" s="93"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -22869,7 +22840,7 @@
       </c>
       <c r="C10" s="154">
         <f ca="1">Overview!C5</f>
-        <v>11.91</v>
+        <v>11.68</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -22878,7 +22849,7 @@
       </c>
       <c r="C11" s="175">
         <f ca="1">(C9-C10)/C10</f>
-        <v>7.9668137080240273E-2</v>
+        <v>0.10092872539603272</v>
       </c>
     </row>
   </sheetData>
@@ -22943,20 +22914,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="249" t="s">
+      <c r="C3" s="252" t="s">
         <v>137</v>
       </c>
-      <c r="D3" s="249"/>
-      <c r="E3" s="249"/>
-      <c r="F3" s="249"/>
+      <c r="D3" s="252"/>
+      <c r="E3" s="252"/>
+      <c r="F3" s="252"/>
       <c r="G3" s="258"/>
       <c r="H3" s="259" t="s">
         <v>138</v>
       </c>
-      <c r="I3" s="249"/>
-      <c r="J3" s="249"/>
-      <c r="K3" s="249"/>
-      <c r="L3" s="249"/>
+      <c r="I3" s="252"/>
+      <c r="J3" s="252"/>
+      <c r="K3" s="252"/>
+      <c r="L3" s="252"/>
       <c r="P3" s="263"/>
       <c r="Q3" s="263"/>
       <c r="R3" s="263"/>
@@ -23235,7 +23206,7 @@
       </c>
       <c r="C15" s="177">
         <f ca="1">Overview!C5</f>
-        <v>11.91</v>
+        <v>11.68</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -23301,7 +23272,7 @@
       </c>
       <c r="C23" s="182">
         <f ca="1">C15*C22</f>
-        <v>6170821.1100000003</v>
+        <v>6051653.2800000003</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -23328,7 +23299,7 @@
       </c>
       <c r="C26" s="183">
         <f ca="1">C23+C25-C24</f>
-        <v>4755075.1100000003</v>
+        <v>4635907.28</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -30477,7 +30448,7 @@
       <c r="AA116" s="68"/>
       <c r="AC116" s="63">
         <f ca="1">Overview!C5</f>
-        <v>11.91</v>
+        <v>11.68</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -30524,7 +30495,7 @@
       <c r="AA117" s="68"/>
       <c r="AC117" s="65">
         <f ca="1">AC116/AC85</f>
-        <v>11.91</v>
+        <v>11.68</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -31830,7 +31801,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>19.849999999999998</v>
+        <v>19.466666666666665</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -31867,7 +31838,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>3.8368431096135334</v>
+        <v>3.7627479026268738</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -31904,7 +31875,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="72">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>3.2427402027888057</v>
+        <v>3.1801180158331865</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -31941,7 +31912,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="164">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>6221248.0499999998</v>
+        <v>6101106.3999999994</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -31978,7 +31949,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="164">
         <f ca="1">AC153+AC108-AC107+AC48+AC45</f>
-        <v>4805502.05</v>
+        <v>4685360.3999999994</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -32015,7 +31986,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="204">
         <f ca="1">AC154/AC5</f>
-        <v>2.8735369514390103</v>
+        <v>2.8016960767312669</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -32052,7 +32023,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="204">
         <f ca="1">AC154/AC12</f>
-        <v>47.504443994108286</v>
+        <v>46.316792376358002</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -32187,7 +32158,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="72">
         <f t="shared" ref="AC159:AC160" ca="1" si="101">AC153/AC157</f>
-        <v>57.813454729622983</v>
+        <v>56.696990028715064</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -32224,7 +32195,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
         <f t="shared" ca="1" si="101"/>
-        <v>-88.605182077993916</v>
+        <v>-86.389976952152665</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -32261,7 +32232,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="74">
         <f t="shared" ref="AC161" ca="1" si="104">AC157/AC153</f>
-        <v>1.7297011650258827E-2</v>
+        <v>1.7637620612549882E-2</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -32298,7 +32269,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f ca="1">AC26/AC117</f>
-        <v>5.0377833753148624E-2</v>
+        <v>5.1369863013698641E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -32372,7 +32343,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="175">
         <f ca="1">-AC63/AC153</f>
-        <v>5.5514905887734216E-2</v>
+        <v>5.6608093246824878E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -32409,7 +32380,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="175">
         <f ca="1">-(AC63+AC64)/AC153</f>
-        <v>5.5514905887734216E-2</v>
+        <v>5.6608093246824878E-2</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -32912,7 +32883,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="175">
         <f ca="1">(AC107-AC108)/AC153</f>
-        <v>0.22756623568481568</v>
+        <v>0.23204742012038998</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -34417,15 +34388,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="249" t="s">
+      <c r="B4" s="252" t="s">
         <v>282</v>
       </c>
-      <c r="C4" s="249"/>
-      <c r="E4" s="249" t="s">
+      <c r="C4" s="252"/>
+      <c r="E4" s="252" t="s">
         <v>289</v>
       </c>
-      <c r="F4" s="249"/>
-      <c r="G4" s="249"/>
+      <c r="F4" s="252"/>
+      <c r="G4" s="252"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -34433,7 +34404,7 @@
       </c>
       <c r="C5" s="193">
         <f ca="1">Overview!C5</f>
-        <v>11.91</v>
+        <v>11.68</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="153" t="s">
@@ -34449,7 +34420,7 @@
       </c>
       <c r="C6" s="194">
         <f ca="1">Statement!AC153</f>
-        <v>6221248.0499999998</v>
+        <v>6101106.3999999994</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>20</v>
@@ -34469,7 +34440,7 @@
       </c>
       <c r="C7" s="194">
         <f ca="1">Statement!AC154</f>
-        <v>4805502.05</v>
+        <v>4685360.3999999994</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>32</v>
@@ -34489,7 +34460,7 @@
       </c>
       <c r="C8" s="195">
         <f ca="1">Statement!AC150</f>
-        <v>19.849999999999998</v>
+        <v>19.466666666666665</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>292</v>
@@ -34509,7 +34480,7 @@
       </c>
       <c r="C9" s="195">
         <f ca="1">Statement!AC151</f>
-        <v>3.8368431096135334</v>
+        <v>3.7627479026268738</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>293</v>
@@ -34529,7 +34500,7 @@
       </c>
       <c r="C10" s="195">
         <f ca="1">Statement!AC152</f>
-        <v>3.2427402027888057</v>
+        <v>3.1801180158331865</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -34549,7 +34520,7 @@
       </c>
       <c r="C11" s="195">
         <f ca="1">Statement!AC155</f>
-        <v>2.8735369514390103</v>
+        <v>2.8016960767312669</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -34558,18 +34529,18 @@
       </c>
       <c r="C12" s="195">
         <f ca="1">Statement!AC156</f>
-        <v>47.504443994108286</v>
+        <v>46.316792376358002</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="249" t="s">
+      <c r="B15" s="252" t="s">
         <v>78</v>
       </c>
-      <c r="C15" s="249"/>
-      <c r="E15" s="249" t="s">
+      <c r="C15" s="252"/>
+      <c r="E15" s="252" t="s">
         <v>295</v>
       </c>
-      <c r="F15" s="249"/>
+      <c r="F15" s="252"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -34620,14 +34591,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="249" t="s">
+      <c r="B21" s="252" t="s">
         <v>294</v>
       </c>
-      <c r="C21" s="249"/>
-      <c r="E21" s="249" t="s">
+      <c r="C21" s="252"/>
+      <c r="E21" s="252" t="s">
         <v>298</v>
       </c>
-      <c r="F21" s="249"/>
+      <c r="F21" s="252"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -34696,14 +34667,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="249" t="s">
+      <c r="B29" s="252" t="s">
         <v>299</v>
       </c>
-      <c r="C29" s="249"/>
-      <c r="E29" s="249" t="s">
+      <c r="C29" s="252"/>
+      <c r="E29" s="252" t="s">
         <v>305</v>
       </c>
-      <c r="F29" s="249"/>
+      <c r="F29" s="252"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -34779,14 +34750,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="249" t="s">
+      <c r="B37" s="252" t="s">
         <v>317</v>
       </c>
-      <c r="C37" s="249"/>
-      <c r="E37" s="249" t="s">
+      <c r="C37" s="252"/>
+      <c r="E37" s="252" t="s">
         <v>320</v>
       </c>
-      <c r="F37" s="249"/>
+      <c r="F37" s="252"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -34794,7 +34765,7 @@
       </c>
       <c r="C38" s="196">
         <f ca="1">Statement!AC162</f>
-        <v>5.0377833753148624E-2</v>
+        <v>5.1369863013698641E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>319</v>
@@ -34810,7 +34781,7 @@
       </c>
       <c r="C39" s="236">
         <f ca="1">Statement!AC161</f>
-        <v>1.7297011650258827E-2</v>
+        <v>1.7637620612549882E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>321</v>
@@ -34842,7 +34813,7 @@
       </c>
       <c r="C41" s="196">
         <f ca="1">Statement!AC164</f>
-        <v>5.5514905887734216E-2</v>
+        <v>5.6608093246824878E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -34851,18 +34822,18 @@
       </c>
       <c r="C42" s="196">
         <f ca="1">Statement!AC165</f>
-        <v>5.5514905887734216E-2</v>
+        <v>5.6608093246824878E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="249" t="s">
+      <c r="B45" s="252" t="s">
         <v>328</v>
       </c>
-      <c r="C45" s="249"/>
-      <c r="E45" s="249" t="s">
+      <c r="C45" s="252"/>
+      <c r="E45" s="252" t="s">
         <v>334</v>
       </c>
-      <c r="F45" s="249"/>
+      <c r="F45" s="252"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -34895,18 +34866,18 @@
       </c>
       <c r="F48" s="196">
         <f ca="1">Statement!AC176</f>
-        <v>0.22756623568481568</v>
+        <v>0.23204742012038998</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="249" t="s">
+      <c r="B51" s="252" t="s">
         <v>331</v>
       </c>
-      <c r="C51" s="249"/>
-      <c r="E51" s="249" t="s">
+      <c r="C51" s="252"/>
+      <c r="E51" s="252" t="s">
         <v>352</v>
       </c>
-      <c r="F51" s="249"/>
+      <c r="F51" s="252"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -35074,7 +35045,7 @@
       </c>
       <c r="I6" s="193">
         <f ca="1">Statement!AC116</f>
-        <v>11.91</v>
+        <v>11.68</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -35103,7 +35074,7 @@
       </c>
       <c r="I7" s="194">
         <f ca="1">Statement!AC153</f>
-        <v>6221248.0499999998</v>
+        <v>6101106.3999999994</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -35132,7 +35103,7 @@
       </c>
       <c r="I8" s="194">
         <f ca="1">Statement!AC154</f>
-        <v>4805502.05</v>
+        <v>4685360.3999999994</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -35161,7 +35132,7 @@
       </c>
       <c r="I9" s="195">
         <f ca="1">Statement!AC150</f>
-        <v>19.849999999999998</v>
+        <v>19.466666666666665</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -35190,7 +35161,7 @@
       </c>
       <c r="I10" s="195">
         <f ca="1">Statement!AC151</f>
-        <v>3.8368431096135334</v>
+        <v>3.7627479026268738</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -35219,7 +35190,7 @@
       </c>
       <c r="I11" s="195">
         <f ca="1">Statement!AC152</f>
-        <v>3.2427402027888057</v>
+        <v>3.1801180158331865</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -35248,7 +35219,7 @@
       </c>
       <c r="I12" s="195">
         <f ca="1">Statement!AC155</f>
-        <v>2.8735369514390103</v>
+        <v>2.8016960767312669</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -35277,7 +35248,7 @@
       </c>
       <c r="I13" s="195">
         <f ca="1">Statement!AC156</f>
-        <v>47.504443994108286</v>
+        <v>46.316792376358002</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36050,7 +36021,7 @@
       </c>
       <c r="I51" s="196">
         <f ca="1">Statement!AC162</f>
-        <v>5.0377833753148624E-2</v>
+        <v>5.1369863013698641E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -36079,7 +36050,7 @@
       </c>
       <c r="I52" s="196">
         <f ca="1">Statement!AC161</f>
-        <v>1.7297011650258827E-2</v>
+        <v>1.7637620612549882E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -36137,7 +36108,7 @@
       </c>
       <c r="I54" s="196">
         <f ca="1">Statement!AC164</f>
-        <v>5.5514905887734216E-2</v>
+        <v>5.6608093246824878E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -36166,7 +36137,7 @@
       </c>
       <c r="I55" s="196">
         <f ca="1">Statement!AC165</f>
-        <v>5.5514905887734216E-2</v>
+        <v>5.6608093246824878E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36402,7 +36373,7 @@
       </c>
       <c r="I68" s="217">
         <f ca="1">Statement!AC176</f>
-        <v>0.22756623568481568</v>
+        <v>0.23204742012038998</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">

--- a/PATH.xlsx
+++ b/PATH.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBF55030-C3B4-944B-B417-CCCE8CE0970E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE951E3E-08E0-0D46-B191-3DA6C2773C52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -32,10 +32,12 @@
     <sheet name="DCF" sheetId="11" r:id="rId17"/>
     <sheet name="Multiples" sheetId="12" r:id="rId18"/>
     <sheet name="AVG target price" sheetId="13" r:id="rId19"/>
-    <sheet name="Reverse DCF" sheetId="14" r:id="rId20"/>
+    <sheet name="DDM" sheetId="21" r:id="rId20"/>
+    <sheet name="Reverse DCF" sheetId="14" r:id="rId21"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId21"/>
+    <externalReference r:id="rId22"/>
+    <externalReference r:id="rId23"/>
   </externalReferences>
   <calcPr calcId="191029" iterate="1"/>
   <extLst>
@@ -168,7 +170,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="419">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="430">
   <si>
     <t>Ticker</t>
   </si>
@@ -1425,6 +1427,39 @@
   </si>
   <si>
     <t>Sales/Assets</t>
+  </si>
+  <si>
+    <t>Manual Cost of Equity</t>
+  </si>
+  <si>
+    <t>Dividend discount model</t>
+  </si>
+  <si>
+    <t>Dividend per share</t>
+  </si>
+  <si>
+    <t>Ratios</t>
+  </si>
+  <si>
+    <t>Payout</t>
+  </si>
+  <si>
+    <t>DDM valuation</t>
+  </si>
+  <si>
+    <t>Latest dividend</t>
+  </si>
+  <si>
+    <t>Year 1 growth rate</t>
+  </si>
+  <si>
+    <t>Year 1 dividend</t>
+  </si>
+  <si>
+    <t>Perpetual dividend growth</t>
+  </si>
+  <si>
+    <t>DDM price</t>
   </si>
 </sst>
 </file>
@@ -2050,7 +2085,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="267">
+  <cellXfs count="271">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -2376,6 +2411,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2383,15 +2421,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2403,10 +2432,10 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2416,6 +2445,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2430,6 +2465,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="39" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="39" fontId="17" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="39" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -12620,6 +12659,95 @@
 </externalLink>
 </file>
 
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Overview"/>
+      <sheetName val="Financials -&gt;"/>
+      <sheetName val="Statement"/>
+      <sheetName val="Analysis -&gt;"/>
+      <sheetName val="Basic"/>
+      <sheetName val="Yearly Analysis"/>
+      <sheetName val="Quarter analysis"/>
+      <sheetName val="Graphs Year"/>
+      <sheetName val="Graphs Quarter"/>
+      <sheetName val="Forecast -&gt;"/>
+      <sheetName val="Revenue"/>
+      <sheetName val="COGS &amp; OpEx"/>
+      <sheetName val="WC &amp; Investments"/>
+      <sheetName val="FCF &amp; Other"/>
+      <sheetName val="Valuation -&gt;"/>
+      <sheetName val="WACC"/>
+      <sheetName val="DCF"/>
+      <sheetName val="Multiples"/>
+      <sheetName val="AVG target price"/>
+      <sheetName val="DDM"/>
+      <sheetName val="Reverse DCF"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10">
+        <row r="5">
+          <cell r="C5">
+            <v>2021</v>
+          </cell>
+          <cell r="D5">
+            <v>2022</v>
+          </cell>
+          <cell r="E5">
+            <v>2023</v>
+          </cell>
+          <cell r="F5">
+            <v>2024</v>
+          </cell>
+          <cell r="G5">
+            <v>2025</v>
+          </cell>
+          <cell r="H5">
+            <v>2026</v>
+          </cell>
+          <cell r="I5">
+            <v>2027</v>
+          </cell>
+          <cell r="J5">
+            <v>2028</v>
+          </cell>
+          <cell r="K5">
+            <v>2029</v>
+          </cell>
+          <cell r="L5">
+            <v>2030</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18"/>
+      <sheetData sheetId="19"/>
+      <sheetData sheetId="20"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <person displayName="adi dumitras" id="{A0F62302-F8D3-B346-B5DF-839B413AE710}" userId="b24535bb88af1c42" providerId="Windows Live"/>
@@ -12749,11 +12877,11 @@
     <v>Powered by Refinitiv</v>
     <v>19.84</v>
     <v>9.2002000000000006</v>
-    <v>0.97770000000000001</v>
+    <v>0.98140000000000005</v>
     <v>-0.12</v>
     <v>-1.0168999999999999E-2</v>
-    <v>-0.01</v>
-    <v>-8.5619999999999999E-4</v>
+    <v>1.72E-2</v>
+    <v>1.4729999999999999E-3</v>
     <v>USD</v>
     <v>UiPath, Inc. is focused on agentic automation and orchestration, empowering enterprises to harness the full potential of AI agents to autonomously execute and optimize complex business processes. It is focused on building and managing automations, starting with computer vision technology and user interface automation in its initial robotic process automation offering. Its AI-powered UiPath Platform offers a robust set of capabilities that allows its customers to discover opportunities for automation, automate using a digital workforce that seamlessly collaborates with humans, and operate a mission-critical automation program at scale. It enables employees to quickly build automations for both existing and new processes and to automate a range of actions including logging into applications, moving folders, filling in forms, reading emails and others. Its platform allows users to design and combine UI automations, API integrations and AI-based document understanding in a single workflow.</v>
     <v>3981</v>
@@ -12764,21 +12892,21 @@
     <v>12.23</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46213.886025265623</v>
+    <v>46213.999831562498</v>
     <v>0</v>
     <v>11.51</v>
     <v>6051645104</v>
     <v>UIPATH, INC.</v>
     <v>UIPATH, INC.</v>
     <v>12.12</v>
-    <v>19.414899999999999</v>
+    <v>19.615300000000001</v>
     <v>11.8</v>
     <v>11.68</v>
-    <v>11.67</v>
+    <v>11.6972</v>
     <v>518120300</v>
     <v>PATH</v>
     <v>UIPATH, INC. (XNYS:PATH)</v>
-    <v>78662541</v>
+    <v>78695436</v>
     <v>54552944</v>
     <v>2015</v>
   </rv>
@@ -12803,17 +12931,17 @@
     <v>Powered by Refinitiv</v>
     <v>46.87</v>
     <v>39.47</v>
-    <v>-0.3</v>
-    <v>-6.5659999999999998E-3</v>
+    <v>0.3</v>
+    <v>6.6090000000000003E-3</v>
     <v>US</v>
-    <v>45.81</v>
+    <v>45.71</v>
     <v>Index</v>
     <v>3</v>
-    <v>45.29</v>
+    <v>45.39</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>45.77</v>
+    <v>45.41</v>
+    <v>45.39</v>
     <v>45.69</v>
-    <v>45.39</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -13035,9 +13163,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq Last Sale</v>
+      <v>Source: Nasdaq</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>Delayed 15 minutes</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -13614,18 +13742,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="249" t="s">
+      <c r="B2" s="250" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="250"/>
-      <c r="E2" s="249" t="s">
+      <c r="C2" s="251"/>
+      <c r="E2" s="250" t="s">
         <v>336</v>
       </c>
-      <c r="F2" s="250"/>
-      <c r="H2" s="249" t="s">
+      <c r="F2" s="251"/>
+      <c r="H2" s="250" t="s">
         <v>381</v>
       </c>
-      <c r="I2" s="250"/>
+      <c r="I2" s="251"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="206" t="s">
@@ -13705,7 +13833,7 @@
       </c>
       <c r="C6" s="229" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>11.67</v>
+        <v>11.6972</v>
       </c>
       <c r="E6" s="206" t="s">
         <v>286</v>
@@ -13753,7 +13881,7 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-0.01</v>
+        <v>1.72E-2</v>
       </c>
       <c r="E8" s="206" t="s">
         <v>314</v>
@@ -13793,7 +13921,7 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-8.5619999999999999E-4</v>
+        <v>1.4729999999999999E-3</v>
       </c>
       <c r="E10" s="206" t="s">
         <v>342</v>
@@ -13802,6 +13930,13 @@
         <f ca="1">Statement!AC164</f>
         <v>5.6608093246824878E-2</v>
       </c>
+      <c r="H10" s="205" t="s">
+        <v>429</v>
+      </c>
+      <c r="I10" s="233">
+        <f>DDM!C26</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B11" s="206" t="s">
@@ -13841,7 +13976,7 @@
       </c>
       <c r="C13" s="230" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>0.97770000000000001</v>
+        <v>0.98140000000000005</v>
       </c>
       <c r="E13" s="206" t="s">
         <v>123</v>
@@ -13886,10 +14021,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="251" t="s">
+      <c r="B17" s="252" t="s">
         <v>103</v>
       </c>
-      <c r="C17" s="251"/>
+      <c r="C17" s="252"/>
       <c r="E17" s="205" t="s">
         <v>345</v>
       </c>
@@ -13962,14 +14097,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="251" t="s">
+      <c r="B25" s="252" t="s">
         <v>126</v>
       </c>
-      <c r="C25" s="251"/>
-      <c r="E25" s="249" t="s">
+      <c r="C25" s="252"/>
+      <c r="E25" s="250" t="s">
         <v>401</v>
       </c>
-      <c r="F25" s="250"/>
+      <c r="F25" s="251"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="205" t="s">
@@ -13983,7 +14118,7 @@
       </c>
       <c r="F26" s="240" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>45.39</v>
+        <v>45.69</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -13998,7 +14133,7 @@
       </c>
       <c r="F27" s="241">
         <f ca="1">F26/1000</f>
-        <v>4.539E-2</v>
+        <v>4.5689999999999995E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14011,22 +14146,22 @@
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="205" t="s">
-        <v>407</v>
+        <v>419</v>
       </c>
       <c r="C29" s="242">
         <v>0.12</v>
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="252" t="s">
+      <c r="B33" s="249" t="s">
         <v>391</v>
       </c>
-      <c r="C33" s="252"/>
-      <c r="D33" s="252"/>
-      <c r="E33" s="252"/>
-      <c r="F33" s="252"/>
-      <c r="G33" s="252"/>
-      <c r="H33" s="252"/>
+      <c r="C33" s="249"/>
+      <c r="D33" s="249"/>
+      <c r="E33" s="249"/>
+      <c r="F33" s="249"/>
+      <c r="G33" s="249"/>
+      <c r="H33" s="249"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -14045,24 +14180,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="252"/>
-      <c r="C39" s="252"/>
-      <c r="D39" s="252"/>
-      <c r="E39" s="252"/>
-      <c r="F39" s="252"/>
-      <c r="G39" s="252"/>
-      <c r="H39" s="252"/>
+      <c r="B39" s="249"/>
+      <c r="C39" s="249"/>
+      <c r="D39" s="249"/>
+      <c r="E39" s="249"/>
+      <c r="F39" s="249"/>
+      <c r="G39" s="249"/>
+      <c r="H39" s="249"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="252" t="s">
+      <c r="B42" s="249" t="s">
         <v>394</v>
       </c>
-      <c r="C42" s="252"/>
-      <c r="D42" s="252"/>
-      <c r="E42" s="252"/>
-      <c r="F42" s="252"/>
-      <c r="G42" s="252"/>
-      <c r="H42" s="252"/>
+      <c r="C42" s="249"/>
+      <c r="D42" s="249"/>
+      <c r="E42" s="249"/>
+      <c r="F42" s="249"/>
+      <c r="G42" s="249"/>
+      <c r="H42" s="249"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -14077,24 +14212,24 @@
       </c>
     </row>
     <row r="49" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="252"/>
-      <c r="C49" s="252"/>
-      <c r="D49" s="252"/>
-      <c r="E49" s="252"/>
-      <c r="F49" s="252"/>
-      <c r="G49" s="252"/>
-      <c r="H49" s="252"/>
+      <c r="B49" s="249"/>
+      <c r="C49" s="249"/>
+      <c r="D49" s="249"/>
+      <c r="E49" s="249"/>
+      <c r="F49" s="249"/>
+      <c r="G49" s="249"/>
+      <c r="H49" s="249"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B52" s="252" t="s">
+      <c r="B52" s="249" t="s">
         <v>128</v>
       </c>
-      <c r="C52" s="252"/>
-      <c r="D52" s="252"/>
-      <c r="E52" s="252"/>
-      <c r="F52" s="252"/>
-      <c r="G52" s="252"/>
-      <c r="H52" s="252"/>
+      <c r="C52" s="249"/>
+      <c r="D52" s="249"/>
+      <c r="E52" s="249"/>
+      <c r="F52" s="249"/>
+      <c r="G52" s="249"/>
+      <c r="H52" s="249"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B54" s="41" t="s">
@@ -14109,28 +14244,28 @@
       </c>
     </row>
     <row r="59" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="252"/>
-      <c r="C59" s="252"/>
-      <c r="D59" s="252"/>
-      <c r="E59" s="252"/>
-      <c r="F59" s="252"/>
-      <c r="G59" s="252"/>
-      <c r="H59" s="252"/>
+      <c r="B59" s="249"/>
+      <c r="C59" s="249"/>
+      <c r="D59" s="249"/>
+      <c r="E59" s="249"/>
+      <c r="F59" s="249"/>
+      <c r="G59" s="249"/>
+      <c r="H59" s="249"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="E25:F25"/>
     <mergeCell ref="B52:H52"/>
     <mergeCell ref="B59:H59"/>
     <mergeCell ref="B33:H33"/>
     <mergeCell ref="B39:H39"/>
     <mergeCell ref="B42:H42"/>
     <mergeCell ref="B49:H49"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="E25:F25"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -14200,36 +14335,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="252" t="s">
+      <c r="C2" s="249" t="s">
         <v>137</v>
       </c>
-      <c r="D2" s="252"/>
-      <c r="E2" s="252"/>
-      <c r="F2" s="252"/>
-      <c r="G2" s="258"/>
-      <c r="H2" s="259" t="s">
+      <c r="D2" s="249"/>
+      <c r="E2" s="249"/>
+      <c r="F2" s="249"/>
+      <c r="G2" s="261"/>
+      <c r="H2" s="262" t="s">
         <v>138</v>
       </c>
-      <c r="I2" s="252"/>
-      <c r="J2" s="252"/>
-      <c r="K2" s="252"/>
-      <c r="L2" s="252"/>
+      <c r="I2" s="249"/>
+      <c r="J2" s="249"/>
+      <c r="K2" s="249"/>
+      <c r="L2" s="249"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="252" t="s">
+      <c r="S2" s="249" t="s">
         <v>137</v>
       </c>
-      <c r="T2" s="252"/>
-      <c r="U2" s="252"/>
-      <c r="V2" s="252"/>
-      <c r="W2" s="252"/>
-      <c r="X2" s="252"/>
-      <c r="Y2" s="252"/>
-      <c r="Z2" s="252"/>
-      <c r="AA2" s="252" t="s">
+      <c r="T2" s="249"/>
+      <c r="U2" s="249"/>
+      <c r="V2" s="249"/>
+      <c r="W2" s="249"/>
+      <c r="X2" s="249"/>
+      <c r="Y2" s="249"/>
+      <c r="Z2" s="249"/>
+      <c r="AA2" s="249" t="s">
         <v>138</v>
       </c>
-      <c r="AB2" s="252"/>
-      <c r="AC2" s="252"/>
+      <c r="AB2" s="249"/>
+      <c r="AC2" s="249"/>
       <c r="AE2" s="87" t="s">
         <v>139</v>
       </c>
@@ -14240,32 +14375,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="260" t="s">
+      <c r="C4" s="258" t="s">
         <v>140</v>
       </c>
-      <c r="D4" s="260"/>
-      <c r="E4" s="260"/>
-      <c r="F4" s="260"/>
-      <c r="G4" s="260"/>
-      <c r="H4" s="260"/>
-      <c r="I4" s="260"/>
-      <c r="J4" s="260"/>
-      <c r="K4" s="260"/>
-      <c r="L4" s="260"/>
+      <c r="D4" s="258"/>
+      <c r="E4" s="258"/>
+      <c r="F4" s="258"/>
+      <c r="G4" s="258"/>
+      <c r="H4" s="258"/>
+      <c r="I4" s="258"/>
+      <c r="J4" s="258"/>
+      <c r="K4" s="258"/>
+      <c r="L4" s="258"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="261" t="s">
+      <c r="S4" s="259" t="s">
         <v>140</v>
       </c>
-      <c r="T4" s="262"/>
-      <c r="U4" s="262"/>
-      <c r="V4" s="262"/>
-      <c r="W4" s="262"/>
-      <c r="X4" s="262"/>
-      <c r="Y4" s="262"/>
-      <c r="Z4" s="262"/>
-      <c r="AA4" s="262"/>
-      <c r="AB4" s="262"/>
-      <c r="AC4" s="262"/>
+      <c r="T4" s="260"/>
+      <c r="U4" s="260"/>
+      <c r="V4" s="260"/>
+      <c r="W4" s="260"/>
+      <c r="X4" s="260"/>
+      <c r="Y4" s="260"/>
+      <c r="Z4" s="260"/>
+      <c r="AA4" s="260"/>
+      <c r="AB4" s="260"/>
+      <c r="AC4" s="260"/>
       <c r="AE4" s="89"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -14761,33 +14896,33 @@
       <c r="Q10" s="93"/>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C11" s="260" t="s">
+      <c r="C11" s="258" t="s">
         <v>146</v>
       </c>
-      <c r="D11" s="260"/>
-      <c r="E11" s="260"/>
-      <c r="F11" s="260"/>
-      <c r="G11" s="260"/>
-      <c r="H11" s="260"/>
-      <c r="I11" s="260"/>
-      <c r="J11" s="260"/>
-      <c r="K11" s="260"/>
-      <c r="L11" s="260"/>
+      <c r="D11" s="258"/>
+      <c r="E11" s="258"/>
+      <c r="F11" s="258"/>
+      <c r="G11" s="258"/>
+      <c r="H11" s="258"/>
+      <c r="I11" s="258"/>
+      <c r="J11" s="258"/>
+      <c r="K11" s="258"/>
+      <c r="L11" s="258"/>
       <c r="O11" s="5"/>
       <c r="Q11" s="93"/>
-      <c r="S11" s="261" t="s">
+      <c r="S11" s="259" t="s">
         <v>146</v>
       </c>
-      <c r="T11" s="262"/>
-      <c r="U11" s="262"/>
-      <c r="V11" s="262"/>
-      <c r="W11" s="262"/>
-      <c r="X11" s="262"/>
-      <c r="Y11" s="262"/>
-      <c r="Z11" s="262"/>
-      <c r="AA11" s="262"/>
-      <c r="AB11" s="262"/>
-      <c r="AC11" s="262"/>
+      <c r="T11" s="260"/>
+      <c r="U11" s="260"/>
+      <c r="V11" s="260"/>
+      <c r="W11" s="260"/>
+      <c r="X11" s="260"/>
+      <c r="Y11" s="260"/>
+      <c r="Z11" s="260"/>
+      <c r="AA11" s="260"/>
+      <c r="AB11" s="260"/>
+      <c r="AC11" s="260"/>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B12" s="16" t="s">
@@ -15228,33 +15363,33 @@
       <c r="Q18" s="93"/>
     </row>
     <row r="19" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C19" s="260" t="s">
+      <c r="C19" s="258" t="s">
         <v>148</v>
       </c>
-      <c r="D19" s="260"/>
-      <c r="E19" s="260"/>
-      <c r="F19" s="260"/>
-      <c r="G19" s="260"/>
-      <c r="H19" s="260"/>
-      <c r="I19" s="260"/>
-      <c r="J19" s="260"/>
-      <c r="K19" s="260"/>
-      <c r="L19" s="260"/>
+      <c r="D19" s="258"/>
+      <c r="E19" s="258"/>
+      <c r="F19" s="258"/>
+      <c r="G19" s="258"/>
+      <c r="H19" s="258"/>
+      <c r="I19" s="258"/>
+      <c r="J19" s="258"/>
+      <c r="K19" s="258"/>
+      <c r="L19" s="258"/>
       <c r="O19" s="5"/>
       <c r="Q19" s="93"/>
-      <c r="S19" s="261" t="s">
+      <c r="S19" s="259" t="s">
         <v>148</v>
       </c>
-      <c r="T19" s="262"/>
-      <c r="U19" s="262"/>
-      <c r="V19" s="262"/>
-      <c r="W19" s="262"/>
-      <c r="X19" s="262"/>
-      <c r="Y19" s="262"/>
-      <c r="Z19" s="262"/>
-      <c r="AA19" s="262"/>
-      <c r="AB19" s="262"/>
-      <c r="AC19" s="262"/>
+      <c r="T19" s="260"/>
+      <c r="U19" s="260"/>
+      <c r="V19" s="260"/>
+      <c r="W19" s="260"/>
+      <c r="X19" s="260"/>
+      <c r="Y19" s="260"/>
+      <c r="Z19" s="260"/>
+      <c r="AA19" s="260"/>
+      <c r="AB19" s="260"/>
+      <c r="AC19" s="260"/>
       <c r="AE19" s="89">
         <f>AE4</f>
         <v>0</v>
@@ -16072,32 +16207,32 @@
       <c r="O31" s="5"/>
     </row>
     <row r="32" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C32" s="260" t="s">
+      <c r="C32" s="258" t="s">
         <v>150</v>
       </c>
-      <c r="D32" s="260"/>
-      <c r="E32" s="260"/>
-      <c r="F32" s="260"/>
-      <c r="G32" s="260"/>
-      <c r="H32" s="260"/>
-      <c r="I32" s="260"/>
-      <c r="J32" s="260"/>
-      <c r="K32" s="260"/>
-      <c r="L32" s="260"/>
+      <c r="D32" s="258"/>
+      <c r="E32" s="258"/>
+      <c r="F32" s="258"/>
+      <c r="G32" s="258"/>
+      <c r="H32" s="258"/>
+      <c r="I32" s="258"/>
+      <c r="J32" s="258"/>
+      <c r="K32" s="258"/>
+      <c r="L32" s="258"/>
       <c r="O32" s="5"/>
-      <c r="S32" s="261" t="s">
+      <c r="S32" s="259" t="s">
         <v>150</v>
       </c>
-      <c r="T32" s="262"/>
-      <c r="U32" s="262"/>
-      <c r="V32" s="262"/>
-      <c r="W32" s="262"/>
-      <c r="X32" s="262"/>
-      <c r="Y32" s="262"/>
-      <c r="Z32" s="262"/>
-      <c r="AA32" s="262"/>
-      <c r="AB32" s="262"/>
-      <c r="AC32" s="262"/>
+      <c r="T32" s="260"/>
+      <c r="U32" s="260"/>
+      <c r="V32" s="260"/>
+      <c r="W32" s="260"/>
+      <c r="X32" s="260"/>
+      <c r="Y32" s="260"/>
+      <c r="Z32" s="260"/>
+      <c r="AA32" s="260"/>
+      <c r="AB32" s="260"/>
+      <c r="AC32" s="260"/>
     </row>
     <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B33" s="16" t="s">
@@ -16354,18 +16489,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="S11:AC11"/>
     <mergeCell ref="C19:L19"/>
     <mergeCell ref="S19:AC19"/>
     <mergeCell ref="C32:L32"/>
     <mergeCell ref="S32:AC32"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -16402,35 +16537,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="252" t="s">
+      <c r="C2" s="249" t="s">
         <v>137</v>
       </c>
-      <c r="D2" s="252"/>
-      <c r="E2" s="252"/>
-      <c r="F2" s="252"/>
-      <c r="G2" s="258"/>
-      <c r="H2" s="259" t="s">
+      <c r="D2" s="249"/>
+      <c r="E2" s="249"/>
+      <c r="F2" s="249"/>
+      <c r="G2" s="261"/>
+      <c r="H2" s="262" t="s">
         <v>138</v>
       </c>
-      <c r="I2" s="252"/>
-      <c r="J2" s="252"/>
-      <c r="K2" s="252"/>
-      <c r="L2" s="252"/>
-      <c r="P2" s="252" t="s">
+      <c r="I2" s="249"/>
+      <c r="J2" s="249"/>
+      <c r="K2" s="249"/>
+      <c r="L2" s="249"/>
+      <c r="P2" s="249" t="s">
         <v>137</v>
       </c>
-      <c r="Q2" s="252"/>
-      <c r="R2" s="252"/>
-      <c r="S2" s="252"/>
-      <c r="T2" s="252"/>
-      <c r="U2" s="252"/>
-      <c r="V2" s="252"/>
-      <c r="W2" s="252"/>
-      <c r="X2" s="252" t="s">
+      <c r="Q2" s="249"/>
+      <c r="R2" s="249"/>
+      <c r="S2" s="249"/>
+      <c r="T2" s="249"/>
+      <c r="U2" s="249"/>
+      <c r="V2" s="249"/>
+      <c r="W2" s="249"/>
+      <c r="X2" s="249" t="s">
         <v>138</v>
       </c>
-      <c r="Y2" s="252"/>
-      <c r="Z2" s="252"/>
+      <c r="Y2" s="249"/>
+      <c r="Z2" s="249"/>
       <c r="AB2" s="87" t="s">
         <v>139</v>
       </c>
@@ -16439,31 +16574,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="260" t="s">
+      <c r="C4" s="258" t="s">
         <v>140</v>
       </c>
-      <c r="D4" s="260"/>
-      <c r="E4" s="260"/>
-      <c r="F4" s="260"/>
-      <c r="G4" s="260"/>
-      <c r="H4" s="260"/>
-      <c r="I4" s="260"/>
-      <c r="J4" s="260"/>
-      <c r="K4" s="260"/>
-      <c r="L4" s="260"/>
-      <c r="P4" s="262" t="s">
+      <c r="D4" s="258"/>
+      <c r="E4" s="258"/>
+      <c r="F4" s="258"/>
+      <c r="G4" s="258"/>
+      <c r="H4" s="258"/>
+      <c r="I4" s="258"/>
+      <c r="J4" s="258"/>
+      <c r="K4" s="258"/>
+      <c r="L4" s="258"/>
+      <c r="P4" s="260" t="s">
         <v>140</v>
       </c>
-      <c r="Q4" s="262"/>
-      <c r="R4" s="262"/>
-      <c r="S4" s="262"/>
-      <c r="T4" s="262"/>
-      <c r="U4" s="262"/>
-      <c r="V4" s="262"/>
-      <c r="W4" s="262"/>
-      <c r="X4" s="262"/>
-      <c r="Y4" s="262"/>
-      <c r="Z4" s="262"/>
+      <c r="Q4" s="260"/>
+      <c r="R4" s="260"/>
+      <c r="S4" s="260"/>
+      <c r="T4" s="260"/>
+      <c r="U4" s="260"/>
+      <c r="V4" s="260"/>
+      <c r="W4" s="260"/>
+      <c r="X4" s="260"/>
+      <c r="Y4" s="260"/>
+      <c r="Z4" s="260"/>
       <c r="AB4" s="89"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -16658,32 +16793,32 @@
       <c r="N8" s="93"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="260" t="s">
+      <c r="C9" s="258" t="s">
         <v>166</v>
       </c>
-      <c r="D9" s="260"/>
-      <c r="E9" s="260"/>
-      <c r="F9" s="260"/>
-      <c r="G9" s="260"/>
-      <c r="H9" s="260"/>
-      <c r="I9" s="260"/>
-      <c r="J9" s="260"/>
-      <c r="K9" s="260"/>
-      <c r="L9" s="260"/>
+      <c r="D9" s="258"/>
+      <c r="E9" s="258"/>
+      <c r="F9" s="258"/>
+      <c r="G9" s="258"/>
+      <c r="H9" s="258"/>
+      <c r="I9" s="258"/>
+      <c r="J9" s="258"/>
+      <c r="K9" s="258"/>
+      <c r="L9" s="258"/>
       <c r="N9" s="93"/>
-      <c r="P9" s="262" t="s">
+      <c r="P9" s="260" t="s">
         <v>167</v>
       </c>
-      <c r="Q9" s="262"/>
-      <c r="R9" s="262"/>
-      <c r="S9" s="262"/>
-      <c r="T9" s="262"/>
-      <c r="U9" s="262"/>
-      <c r="V9" s="262"/>
-      <c r="W9" s="262"/>
-      <c r="X9" s="262"/>
-      <c r="Y9" s="262"/>
-      <c r="Z9" s="262"/>
+      <c r="Q9" s="260"/>
+      <c r="R9" s="260"/>
+      <c r="S9" s="260"/>
+      <c r="T9" s="260"/>
+      <c r="U9" s="260"/>
+      <c r="V9" s="260"/>
+      <c r="W9" s="260"/>
+      <c r="X9" s="260"/>
+      <c r="Y9" s="260"/>
+      <c r="Z9" s="260"/>
       <c r="AB9" s="89">
         <f>AB4</f>
         <v>0</v>
@@ -17532,31 +17667,31 @@
       </c>
     </row>
     <row r="21" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="C21" s="260" t="s">
+      <c r="C21" s="258" t="s">
         <v>169</v>
       </c>
-      <c r="D21" s="260"/>
-      <c r="E21" s="260"/>
-      <c r="F21" s="260"/>
-      <c r="G21" s="260"/>
-      <c r="H21" s="260"/>
-      <c r="I21" s="260"/>
-      <c r="J21" s="260"/>
-      <c r="K21" s="260"/>
-      <c r="L21" s="260"/>
-      <c r="P21" s="262" t="s">
+      <c r="D21" s="258"/>
+      <c r="E21" s="258"/>
+      <c r="F21" s="258"/>
+      <c r="G21" s="258"/>
+      <c r="H21" s="258"/>
+      <c r="I21" s="258"/>
+      <c r="J21" s="258"/>
+      <c r="K21" s="258"/>
+      <c r="L21" s="258"/>
+      <c r="P21" s="260" t="s">
         <v>169</v>
       </c>
-      <c r="Q21" s="262"/>
-      <c r="R21" s="262"/>
-      <c r="S21" s="262"/>
-      <c r="T21" s="262"/>
-      <c r="U21" s="262"/>
-      <c r="V21" s="262"/>
-      <c r="W21" s="262"/>
-      <c r="X21" s="262"/>
-      <c r="Y21" s="262"/>
-      <c r="Z21" s="262"/>
+      <c r="Q21" s="260"/>
+      <c r="R21" s="260"/>
+      <c r="S21" s="260"/>
+      <c r="T21" s="260"/>
+      <c r="U21" s="260"/>
+      <c r="V21" s="260"/>
+      <c r="W21" s="260"/>
+      <c r="X21" s="260"/>
+      <c r="Y21" s="260"/>
+      <c r="Z21" s="260"/>
     </row>
     <row r="22" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B22" s="16" t="s">
@@ -18371,20 +18506,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="252" t="s">
+      <c r="C3" s="249" t="s">
         <v>137</v>
       </c>
-      <c r="D3" s="252"/>
-      <c r="E3" s="252"/>
-      <c r="F3" s="252"/>
-      <c r="G3" s="258"/>
-      <c r="H3" s="259" t="s">
+      <c r="D3" s="249"/>
+      <c r="E3" s="249"/>
+      <c r="F3" s="249"/>
+      <c r="G3" s="261"/>
+      <c r="H3" s="262" t="s">
         <v>138</v>
       </c>
-      <c r="I3" s="252"/>
-      <c r="J3" s="252"/>
-      <c r="K3" s="252"/>
-      <c r="L3" s="252"/>
+      <c r="I3" s="249"/>
+      <c r="J3" s="249"/>
+      <c r="K3" s="249"/>
+      <c r="L3" s="249"/>
       <c r="P3" s="263"/>
       <c r="Q3" s="263"/>
       <c r="R3" s="263"/>
@@ -18402,18 +18537,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="88"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="260" t="s">
+      <c r="C5" s="258" t="s">
         <v>140</v>
       </c>
-      <c r="D5" s="260"/>
-      <c r="E5" s="260"/>
-      <c r="F5" s="260"/>
-      <c r="G5" s="260"/>
-      <c r="H5" s="260"/>
-      <c r="I5" s="260"/>
-      <c r="J5" s="260"/>
-      <c r="K5" s="260"/>
-      <c r="L5" s="260"/>
+      <c r="D5" s="258"/>
+      <c r="E5" s="258"/>
+      <c r="F5" s="258"/>
+      <c r="G5" s="258"/>
+      <c r="H5" s="258"/>
+      <c r="I5" s="258"/>
+      <c r="J5" s="258"/>
+      <c r="K5" s="258"/>
+      <c r="L5" s="258"/>
       <c r="P5" s="263"/>
       <c r="Q5" s="263"/>
       <c r="R5" s="263"/>
@@ -18610,18 +18745,18 @@
       <c r="N10" s="93"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="260" t="s">
+      <c r="C11" s="258" t="s">
         <v>173</v>
       </c>
-      <c r="D11" s="260"/>
-      <c r="E11" s="260"/>
-      <c r="F11" s="260"/>
-      <c r="G11" s="260"/>
-      <c r="H11" s="260"/>
-      <c r="I11" s="260"/>
-      <c r="J11" s="260"/>
-      <c r="K11" s="260"/>
-      <c r="L11" s="260"/>
+      <c r="D11" s="258"/>
+      <c r="E11" s="258"/>
+      <c r="F11" s="258"/>
+      <c r="G11" s="258"/>
+      <c r="H11" s="258"/>
+      <c r="I11" s="258"/>
+      <c r="J11" s="258"/>
+      <c r="K11" s="258"/>
+      <c r="L11" s="258"/>
       <c r="N11" s="93"/>
       <c r="P11" s="263"/>
       <c r="Q11" s="263"/>
@@ -18875,18 +19010,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="260" t="s">
+      <c r="C18" s="258" t="s">
         <v>178</v>
       </c>
-      <c r="D18" s="260"/>
-      <c r="E18" s="260"/>
-      <c r="F18" s="260"/>
-      <c r="G18" s="260"/>
-      <c r="H18" s="260"/>
-      <c r="I18" s="260"/>
-      <c r="J18" s="260"/>
-      <c r="K18" s="260"/>
-      <c r="L18" s="260"/>
+      <c r="D18" s="258"/>
+      <c r="E18" s="258"/>
+      <c r="F18" s="258"/>
+      <c r="G18" s="258"/>
+      <c r="H18" s="258"/>
+      <c r="I18" s="258"/>
+      <c r="J18" s="258"/>
+      <c r="K18" s="258"/>
+      <c r="L18" s="258"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19104,18 +19239,18 @@
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="130"/>
-      <c r="C26" s="260" t="s">
+      <c r="C26" s="258" t="s">
         <v>184</v>
       </c>
-      <c r="D26" s="260"/>
-      <c r="E26" s="260"/>
-      <c r="F26" s="260"/>
-      <c r="G26" s="260"/>
-      <c r="H26" s="260"/>
-      <c r="I26" s="260"/>
-      <c r="J26" s="260"/>
-      <c r="K26" s="260"/>
-      <c r="L26" s="260"/>
+      <c r="D26" s="258"/>
+      <c r="E26" s="258"/>
+      <c r="F26" s="258"/>
+      <c r="G26" s="258"/>
+      <c r="H26" s="258"/>
+      <c r="I26" s="258"/>
+      <c r="J26" s="258"/>
+      <c r="K26" s="258"/>
+      <c r="L26" s="258"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -19307,18 +19442,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="130"/>
-      <c r="C33" s="260" t="s">
+      <c r="C33" s="258" t="s">
         <v>188</v>
       </c>
-      <c r="D33" s="260"/>
-      <c r="E33" s="260"/>
-      <c r="F33" s="260"/>
-      <c r="G33" s="260"/>
-      <c r="H33" s="260"/>
-      <c r="I33" s="260"/>
-      <c r="J33" s="260"/>
-      <c r="K33" s="260"/>
-      <c r="L33" s="260"/>
+      <c r="D33" s="258"/>
+      <c r="E33" s="258"/>
+      <c r="F33" s="258"/>
+      <c r="G33" s="258"/>
+      <c r="H33" s="258"/>
+      <c r="I33" s="258"/>
+      <c r="J33" s="258"/>
+      <c r="K33" s="258"/>
+      <c r="L33" s="258"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -19502,18 +19637,18 @@
       <c r="C39" s="146"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="260" t="s">
+      <c r="C40" s="258" t="s">
         <v>191</v>
       </c>
-      <c r="D40" s="260"/>
-      <c r="E40" s="260"/>
-      <c r="F40" s="260"/>
-      <c r="G40" s="260"/>
-      <c r="H40" s="260"/>
-      <c r="I40" s="260"/>
-      <c r="J40" s="260"/>
-      <c r="K40" s="260"/>
-      <c r="L40" s="260"/>
+      <c r="D40" s="258"/>
+      <c r="E40" s="258"/>
+      <c r="F40" s="258"/>
+      <c r="G40" s="258"/>
+      <c r="H40" s="258"/>
+      <c r="I40" s="258"/>
+      <c r="J40" s="258"/>
+      <c r="K40" s="258"/>
+      <c r="L40" s="258"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -19777,12 +19912,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -19790,6 +19919,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -19827,20 +19962,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="252" t="s">
+      <c r="C2" s="249" t="s">
         <v>137</v>
       </c>
-      <c r="D2" s="252"/>
-      <c r="E2" s="252"/>
-      <c r="F2" s="252"/>
-      <c r="G2" s="258"/>
-      <c r="H2" s="259" t="s">
+      <c r="D2" s="249"/>
+      <c r="E2" s="249"/>
+      <c r="F2" s="249"/>
+      <c r="G2" s="261"/>
+      <c r="H2" s="262" t="s">
         <v>138</v>
       </c>
-      <c r="I2" s="252"/>
-      <c r="J2" s="252"/>
-      <c r="K2" s="252"/>
-      <c r="L2" s="252"/>
+      <c r="I2" s="249"/>
+      <c r="J2" s="249"/>
+      <c r="K2" s="249"/>
+      <c r="L2" s="249"/>
       <c r="S2" s="263"/>
       <c r="T2" s="263"/>
       <c r="U2" s="263"/>
@@ -19858,18 +19993,18 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="260" t="s">
+      <c r="C4" s="258" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="260"/>
-      <c r="E4" s="260"/>
-      <c r="F4" s="260"/>
-      <c r="G4" s="260"/>
-      <c r="H4" s="260"/>
-      <c r="I4" s="260"/>
-      <c r="J4" s="260"/>
-      <c r="K4" s="260"/>
-      <c r="L4" s="260"/>
+      <c r="D4" s="258"/>
+      <c r="E4" s="258"/>
+      <c r="F4" s="258"/>
+      <c r="G4" s="258"/>
+      <c r="H4" s="258"/>
+      <c r="I4" s="258"/>
+      <c r="J4" s="258"/>
+      <c r="K4" s="258"/>
+      <c r="L4" s="258"/>
       <c r="S4" s="263"/>
       <c r="T4" s="263"/>
       <c r="U4" s="263"/>
@@ -20243,18 +20378,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="260" t="s">
+      <c r="C13" s="258" t="s">
         <v>199</v>
       </c>
-      <c r="D13" s="260"/>
-      <c r="E13" s="260"/>
-      <c r="F13" s="260"/>
-      <c r="G13" s="260"/>
-      <c r="H13" s="260"/>
-      <c r="I13" s="260"/>
-      <c r="J13" s="260"/>
-      <c r="K13" s="260"/>
-      <c r="L13" s="260"/>
+      <c r="D13" s="258"/>
+      <c r="E13" s="258"/>
+      <c r="F13" s="258"/>
+      <c r="G13" s="258"/>
+      <c r="H13" s="258"/>
+      <c r="I13" s="258"/>
+      <c r="J13" s="258"/>
+      <c r="K13" s="258"/>
+      <c r="L13" s="258"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -20347,18 +20482,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="260" t="s">
+      <c r="C18" s="258" t="s">
         <v>200</v>
       </c>
-      <c r="D18" s="260"/>
-      <c r="E18" s="260"/>
-      <c r="F18" s="260"/>
-      <c r="G18" s="260"/>
-      <c r="H18" s="260"/>
-      <c r="I18" s="260"/>
-      <c r="J18" s="260"/>
-      <c r="K18" s="260"/>
-      <c r="L18" s="260"/>
+      <c r="D18" s="258"/>
+      <c r="E18" s="258"/>
+      <c r="F18" s="258"/>
+      <c r="G18" s="258"/>
+      <c r="H18" s="258"/>
+      <c r="I18" s="258"/>
+      <c r="J18" s="258"/>
+      <c r="K18" s="258"/>
+      <c r="L18" s="258"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -20550,18 +20685,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="260" t="s">
+      <c r="C25" s="258" t="s">
         <v>311</v>
       </c>
-      <c r="D25" s="260"/>
-      <c r="E25" s="260"/>
-      <c r="F25" s="260"/>
-      <c r="G25" s="260"/>
-      <c r="H25" s="260"/>
-      <c r="I25" s="260"/>
-      <c r="J25" s="260"/>
-      <c r="K25" s="260"/>
-      <c r="L25" s="260"/>
+      <c r="D25" s="258"/>
+      <c r="E25" s="258"/>
+      <c r="F25" s="258"/>
+      <c r="G25" s="258"/>
+      <c r="H25" s="258"/>
+      <c r="I25" s="258"/>
+      <c r="J25" s="258"/>
+      <c r="K25" s="258"/>
+      <c r="L25" s="258"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -20699,18 +20834,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="260" t="s">
+      <c r="C31" s="258" t="s">
         <v>78</v>
       </c>
-      <c r="D31" s="260"/>
-      <c r="E31" s="260"/>
-      <c r="F31" s="260"/>
-      <c r="G31" s="260"/>
-      <c r="H31" s="260"/>
-      <c r="I31" s="260"/>
-      <c r="J31" s="260"/>
-      <c r="K31" s="260"/>
-      <c r="L31" s="260"/>
+      <c r="D31" s="258"/>
+      <c r="E31" s="258"/>
+      <c r="F31" s="258"/>
+      <c r="G31" s="258"/>
+      <c r="H31" s="258"/>
+      <c r="I31" s="258"/>
+      <c r="J31" s="258"/>
+      <c r="K31" s="258"/>
+      <c r="L31" s="258"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -20849,16 +20984,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -20921,10 +21056,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="252" t="s">
+      <c r="B4" s="249" t="s">
         <v>207</v>
       </c>
-      <c r="C4" s="252"/>
+      <c r="C4" s="249"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -20968,7 +21103,7 @@
       </c>
       <c r="C9" s="156">
         <f ca="1">Overview!F27</f>
-        <v>4.539E-2</v>
+        <v>4.5689999999999995E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20977,7 +21112,7 @@
       </c>
       <c r="C10" s="154">
         <f ca="1">Overview!C13</f>
-        <v>0.97770000000000001</v>
+        <v>0.98140000000000005</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21009,10 +21144,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="252" t="s">
+      <c r="B15" s="249" t="s">
         <v>214</v>
       </c>
-      <c r="C15" s="252"/>
+      <c r="C15" s="249"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -21047,7 +21182,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>8.9386500000000008E-2</v>
+        <v>8.9852999999999988E-2</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21056,7 +21191,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>8.9386500000000008E-2</v>
+        <v>8.9852999999999988E-2</v>
       </c>
     </row>
   </sheetData>
@@ -21101,20 +21236,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="252" t="s">
+      <c r="C3" s="249" t="s">
         <v>137</v>
       </c>
-      <c r="D3" s="252"/>
-      <c r="E3" s="252"/>
-      <c r="F3" s="252"/>
-      <c r="G3" s="258"/>
-      <c r="H3" s="259" t="s">
+      <c r="D3" s="249"/>
+      <c r="E3" s="249"/>
+      <c r="F3" s="249"/>
+      <c r="G3" s="261"/>
+      <c r="H3" s="262" t="s">
         <v>138</v>
       </c>
-      <c r="I3" s="252"/>
-      <c r="J3" s="252"/>
-      <c r="K3" s="252"/>
-      <c r="L3" s="252"/>
+      <c r="I3" s="249"/>
+      <c r="J3" s="249"/>
+      <c r="K3" s="249"/>
+      <c r="L3" s="249"/>
       <c r="P3" s="263"/>
       <c r="Q3" s="263"/>
       <c r="R3" s="263"/>
@@ -21132,18 +21267,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="88"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="260" t="s">
+      <c r="C5" s="258" t="s">
         <v>221</v>
       </c>
-      <c r="D5" s="260"/>
-      <c r="E5" s="260"/>
-      <c r="F5" s="260"/>
-      <c r="G5" s="260"/>
-      <c r="H5" s="260"/>
-      <c r="I5" s="260"/>
-      <c r="J5" s="260"/>
-      <c r="K5" s="260"/>
-      <c r="L5" s="260"/>
+      <c r="D5" s="258"/>
+      <c r="E5" s="258"/>
+      <c r="F5" s="258"/>
+      <c r="G5" s="258"/>
+      <c r="H5" s="258"/>
+      <c r="I5" s="258"/>
+      <c r="J5" s="258"/>
+      <c r="K5" s="258"/>
+      <c r="L5" s="258"/>
       <c r="P5" s="263"/>
       <c r="Q5" s="263"/>
       <c r="R5" s="263"/>
@@ -21400,10 +21535,10 @@
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="252" t="s">
+      <c r="B13" s="249" t="s">
         <v>225</v>
       </c>
-      <c r="C13" s="252"/>
+      <c r="C13" s="249"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -21423,10 +21558,10 @@
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="252" t="s">
+      <c r="B18" s="249" t="s">
         <v>227</v>
       </c>
-      <c r="C18" s="252"/>
+      <c r="C18" s="249"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -21540,37 +21675,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="252" t="s">
+      <c r="C2" s="249" t="s">
         <v>137</v>
       </c>
-      <c r="D2" s="252"/>
-      <c r="E2" s="252"/>
-      <c r="F2" s="252"/>
-      <c r="G2" s="258"/>
-      <c r="H2" s="259" t="s">
+      <c r="D2" s="249"/>
+      <c r="E2" s="249"/>
+      <c r="F2" s="249"/>
+      <c r="G2" s="261"/>
+      <c r="H2" s="262" t="s">
         <v>138</v>
       </c>
-      <c r="I2" s="252"/>
-      <c r="J2" s="252"/>
-      <c r="K2" s="252"/>
-      <c r="L2" s="252"/>
+      <c r="I2" s="249"/>
+      <c r="J2" s="249"/>
+      <c r="K2" s="249"/>
+      <c r="L2" s="249"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="260" t="s">
+      <c r="C4" s="258" t="s">
         <v>235</v>
       </c>
-      <c r="D4" s="260"/>
-      <c r="E4" s="260"/>
-      <c r="F4" s="260"/>
-      <c r="G4" s="260"/>
-      <c r="H4" s="260"/>
-      <c r="I4" s="260"/>
-      <c r="J4" s="260"/>
-      <c r="K4" s="260"/>
-      <c r="L4" s="260"/>
+      <c r="D4" s="258"/>
+      <c r="E4" s="258"/>
+      <c r="F4" s="258"/>
+      <c r="G4" s="258"/>
+      <c r="H4" s="258"/>
+      <c r="I4" s="258"/>
+      <c r="J4" s="258"/>
+      <c r="K4" s="258"/>
+      <c r="L4" s="258"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -21759,18 +21894,18 @@
       <c r="N9" s="93"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C10" s="260" t="s">
+      <c r="C10" s="258" t="s">
         <v>146</v>
       </c>
-      <c r="D10" s="260"/>
-      <c r="E10" s="260"/>
-      <c r="F10" s="260"/>
-      <c r="G10" s="260"/>
-      <c r="H10" s="260"/>
-      <c r="I10" s="260"/>
-      <c r="J10" s="260"/>
-      <c r="K10" s="260"/>
-      <c r="L10" s="260"/>
+      <c r="D10" s="258"/>
+      <c r="E10" s="258"/>
+      <c r="F10" s="258"/>
+      <c r="G10" s="258"/>
+      <c r="H10" s="258"/>
+      <c r="I10" s="258"/>
+      <c r="J10" s="258"/>
+      <c r="K10" s="258"/>
+      <c r="L10" s="258"/>
       <c r="N10" s="93"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21964,18 +22099,18 @@
       <c r="N15" s="93"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C16" s="260" t="s">
+      <c r="C16" s="258" t="s">
         <v>237</v>
       </c>
-      <c r="D16" s="260"/>
-      <c r="E16" s="260"/>
-      <c r="F16" s="260"/>
-      <c r="G16" s="260"/>
-      <c r="H16" s="260"/>
-      <c r="I16" s="260"/>
-      <c r="J16" s="260"/>
-      <c r="K16" s="260"/>
-      <c r="L16" s="260"/>
+      <c r="D16" s="258"/>
+      <c r="E16" s="258"/>
+      <c r="F16" s="258"/>
+      <c r="G16" s="258"/>
+      <c r="H16" s="258"/>
+      <c r="I16" s="258"/>
+      <c r="J16" s="258"/>
+      <c r="K16" s="258"/>
+      <c r="L16" s="258"/>
       <c r="N16" s="93"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
@@ -22109,18 +22244,18 @@
       <c r="N20" s="93"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C21" s="260" t="s">
+      <c r="C21" s="258" t="s">
         <v>240</v>
       </c>
-      <c r="D21" s="260"/>
-      <c r="E21" s="260"/>
-      <c r="F21" s="260"/>
-      <c r="G21" s="260"/>
-      <c r="H21" s="260"/>
-      <c r="I21" s="260"/>
-      <c r="J21" s="260"/>
-      <c r="K21" s="260"/>
-      <c r="L21" s="260"/>
+      <c r="D21" s="258"/>
+      <c r="E21" s="258"/>
+      <c r="F21" s="258"/>
+      <c r="G21" s="258"/>
+      <c r="H21" s="258"/>
+      <c r="I21" s="258"/>
+      <c r="J21" s="258"/>
+      <c r="K21" s="258"/>
+      <c r="L21" s="258"/>
       <c r="N21" s="93"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
@@ -22204,18 +22339,18 @@
       <c r="N25" s="93"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C26" s="260" t="s">
+      <c r="C26" s="258" t="s">
         <v>241</v>
       </c>
-      <c r="D26" s="260"/>
-      <c r="E26" s="260"/>
-      <c r="F26" s="260"/>
-      <c r="G26" s="260"/>
-      <c r="H26" s="260"/>
-      <c r="I26" s="260"/>
-      <c r="J26" s="260"/>
-      <c r="K26" s="260"/>
-      <c r="L26" s="260"/>
+      <c r="D26" s="258"/>
+      <c r="E26" s="258"/>
+      <c r="F26" s="258"/>
+      <c r="G26" s="258"/>
+      <c r="H26" s="258"/>
+      <c r="I26" s="258"/>
+      <c r="J26" s="258"/>
+      <c r="K26" s="258"/>
+      <c r="L26" s="258"/>
       <c r="N26" s="93"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
@@ -22485,10 +22620,10 @@
       <c r="N36" s="93"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="252" t="s">
+      <c r="B37" s="249" t="s">
         <v>246</v>
       </c>
-      <c r="C37" s="252"/>
+      <c r="C37" s="249"/>
       <c r="N37" s="93"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -22581,10 +22716,10 @@
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="252" t="s">
+      <c r="B49" s="249" t="s">
         <v>251</v>
       </c>
-      <c r="C49" s="252"/>
+      <c r="C49" s="249"/>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
@@ -22600,7 +22735,7 @@
         <v>407</v>
       </c>
       <c r="C51" s="156">
-        <f>Overview!C29</f>
+        <f>IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
         <v>0.12</v>
       </c>
     </row>
@@ -22640,10 +22775,10 @@
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="252" t="s">
+      <c r="B57" s="249" t="s">
         <v>375</v>
       </c>
-      <c r="C57" s="252"/>
+      <c r="C57" s="249"/>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
@@ -22783,10 +22918,10 @@
       <c r="N3" s="93"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="252" t="s">
+      <c r="B4" s="249" t="s">
         <v>256</v>
       </c>
-      <c r="C4" s="252"/>
+      <c r="C4" s="249"/>
       <c r="N4" s="93"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -22882,6 +23017,477 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2A29FA4-3F46-6F4E-9026-BAD13DCD8999}">
+  <dimension ref="A1:N26"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="2" style="85" customWidth="1"/>
+    <col min="2" max="2" width="25.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" style="1"/>
+    <col min="4" max="4" width="10.83203125" style="1" customWidth="1"/>
+    <col min="5" max="7" width="10.83203125" style="1"/>
+    <col min="8" max="8" width="10.83203125" style="1" customWidth="1"/>
+    <col min="9" max="12" width="10.83203125" style="1"/>
+    <col min="13" max="14" width="9.5" style="1" customWidth="1"/>
+    <col min="15" max="16384" width="10.83203125" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" s="85" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="4"/>
+      <c r="B1" s="84" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A2" s="4"/>
+      <c r="C2" s="249" t="s">
+        <v>137</v>
+      </c>
+      <c r="D2" s="249"/>
+      <c r="E2" s="249"/>
+      <c r="F2" s="249"/>
+      <c r="G2" s="261"/>
+      <c r="H2" s="262" t="s">
+        <v>138</v>
+      </c>
+      <c r="I2" s="249"/>
+      <c r="J2" s="249"/>
+      <c r="K2" s="249"/>
+      <c r="L2" s="249"/>
+    </row>
+    <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="88"/>
+      <c r="B4" s="60"/>
+      <c r="C4" s="258" t="s">
+        <v>235</v>
+      </c>
+      <c r="D4" s="258"/>
+      <c r="E4" s="258"/>
+      <c r="F4" s="258"/>
+      <c r="G4" s="258"/>
+      <c r="H4" s="258"/>
+      <c r="I4" s="258"/>
+      <c r="J4" s="258"/>
+      <c r="K4" s="258"/>
+      <c r="L4" s="258"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B5" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="C5" s="12">
+        <f>[2]Revenue!C5</f>
+        <v>2021</v>
+      </c>
+      <c r="D5" s="12">
+        <f>[2]Revenue!D5</f>
+        <v>2022</v>
+      </c>
+      <c r="E5" s="12">
+        <f>[2]Revenue!E5</f>
+        <v>2023</v>
+      </c>
+      <c r="F5" s="12">
+        <f>[2]Revenue!F5</f>
+        <v>2024</v>
+      </c>
+      <c r="G5" s="12">
+        <f>[2]Revenue!G5</f>
+        <v>2025</v>
+      </c>
+      <c r="H5" s="12">
+        <f>[2]Revenue!H5</f>
+        <v>2026</v>
+      </c>
+      <c r="I5" s="12">
+        <f>[2]Revenue!I5</f>
+        <v>2027</v>
+      </c>
+      <c r="J5" s="12">
+        <f>[2]Revenue!J5</f>
+        <v>2028</v>
+      </c>
+      <c r="K5" s="12">
+        <f>[2]Revenue!K5</f>
+        <v>2029</v>
+      </c>
+      <c r="L5" s="12">
+        <f>[2]Revenue!L5</f>
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B6" s="16" t="s">
+        <v>292</v>
+      </c>
+      <c r="C6" s="267">
+        <f>Statement!M26</f>
+        <v>-1.1599999999999999</v>
+      </c>
+      <c r="D6" s="267">
+        <f>Statement!N26</f>
+        <v>-0.6</v>
+      </c>
+      <c r="E6" s="267">
+        <f>Statement!O26</f>
+        <v>-0.16</v>
+      </c>
+      <c r="F6" s="267">
+        <f>Statement!P26</f>
+        <v>-0.13</v>
+      </c>
+      <c r="G6" s="268">
+        <f>Statement!Q26</f>
+        <v>0.52</v>
+      </c>
+      <c r="H6" s="158"/>
+      <c r="I6" s="158"/>
+      <c r="J6" s="158"/>
+      <c r="K6" s="158"/>
+      <c r="L6" s="158"/>
+      <c r="N6" s="93"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B7" s="16" t="s">
+        <v>421</v>
+      </c>
+      <c r="C7" s="267">
+        <f>Statement!M82</f>
+        <v>0</v>
+      </c>
+      <c r="D7" s="267">
+        <f>Statement!N82</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="267">
+        <f>Statement!O82</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="267">
+        <f>Statement!P82</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="268">
+        <f>Statement!Q82</f>
+        <v>0</v>
+      </c>
+      <c r="H7" s="158"/>
+      <c r="I7" s="158"/>
+      <c r="J7" s="158"/>
+      <c r="K7" s="158"/>
+      <c r="L7" s="158"/>
+      <c r="N7" s="93"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N8" s="93"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="C9" s="258" t="s">
+        <v>146</v>
+      </c>
+      <c r="D9" s="258"/>
+      <c r="E9" s="258"/>
+      <c r="F9" s="258"/>
+      <c r="G9" s="258"/>
+      <c r="H9" s="258"/>
+      <c r="I9" s="258"/>
+      <c r="J9" s="258"/>
+      <c r="K9" s="258"/>
+      <c r="L9" s="258"/>
+      <c r="N9" s="93"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B10" s="16" t="s">
+        <v>236</v>
+      </c>
+      <c r="C10" s="12">
+        <f t="shared" ref="C10:L10" si="0">C5</f>
+        <v>2021</v>
+      </c>
+      <c r="D10" s="12">
+        <f t="shared" si="0"/>
+        <v>2022</v>
+      </c>
+      <c r="E10" s="12">
+        <f t="shared" si="0"/>
+        <v>2023</v>
+      </c>
+      <c r="F10" s="12">
+        <f t="shared" si="0"/>
+        <v>2024</v>
+      </c>
+      <c r="G10" s="12">
+        <f t="shared" si="0"/>
+        <v>2025</v>
+      </c>
+      <c r="H10" s="12">
+        <f t="shared" si="0"/>
+        <v>2026</v>
+      </c>
+      <c r="I10" s="12">
+        <f t="shared" si="0"/>
+        <v>2027</v>
+      </c>
+      <c r="J10" s="12">
+        <f t="shared" si="0"/>
+        <v>2028</v>
+      </c>
+      <c r="K10" s="12">
+        <f t="shared" si="0"/>
+        <v>2029</v>
+      </c>
+      <c r="L10" s="12">
+        <f t="shared" si="0"/>
+        <v>2030</v>
+      </c>
+      <c r="N10" s="93"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B11" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="C11" s="158"/>
+      <c r="D11" s="97">
+        <f>(D6-C6)/C6</f>
+        <v>-0.48275862068965514</v>
+      </c>
+      <c r="E11" s="97">
+        <f>(E6-D6)/D6</f>
+        <v>-0.73333333333333328</v>
+      </c>
+      <c r="F11" s="97">
+        <f>(F6-E6)/E6</f>
+        <v>-0.1875</v>
+      </c>
+      <c r="G11" s="98">
+        <f>(G6-F6)/F6</f>
+        <v>-5</v>
+      </c>
+      <c r="H11" s="158"/>
+      <c r="I11" s="158"/>
+      <c r="J11" s="158"/>
+      <c r="K11" s="158"/>
+      <c r="L11" s="158"/>
+      <c r="N11" s="93"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B12" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="C12" s="158"/>
+      <c r="D12" s="97">
+        <f>IF(C7=0,
+IF(D7=0,0,IF(D7&gt;0,1,-1)),
+(D7-C7)/ABS(C7)
+)</f>
+        <v>0</v>
+      </c>
+      <c r="E12" s="97">
+        <f>IF(D7=0,
+IF(E7=0,0,IF(E7&gt;0,1,-1)),
+(E7-D7)/ABS(D7)
+)</f>
+        <v>0</v>
+      </c>
+      <c r="F12" s="97">
+        <f>IF(E7=0,
+IF(F7=0,0,IF(F7&gt;0,1,-1)),
+(F7-E7)/ABS(E7)
+)</f>
+        <v>0</v>
+      </c>
+      <c r="G12" s="98">
+        <f>IF(F7=0,
+IF(G7=0,0,IF(G7&gt;0,1,-1)),
+(G7-F7)/ABS(F7)
+)</f>
+        <v>0</v>
+      </c>
+      <c r="H12" s="158"/>
+      <c r="I12" s="158"/>
+      <c r="J12" s="158"/>
+      <c r="K12" s="158"/>
+      <c r="L12" s="158"/>
+      <c r="N12" s="93"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N13" s="93"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="C14" s="258" t="s">
+        <v>422</v>
+      </c>
+      <c r="D14" s="258"/>
+      <c r="E14" s="258"/>
+      <c r="F14" s="258"/>
+      <c r="G14" s="258"/>
+      <c r="H14" s="258"/>
+      <c r="I14" s="258"/>
+      <c r="J14" s="258"/>
+      <c r="K14" s="258"/>
+      <c r="L14" s="258"/>
+      <c r="N14" s="93"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B15" s="16" t="s">
+        <v>390</v>
+      </c>
+      <c r="C15" s="12">
+        <f>C5</f>
+        <v>2021</v>
+      </c>
+      <c r="D15" s="12">
+        <f t="shared" ref="D15:L15" si="1">D5</f>
+        <v>2022</v>
+      </c>
+      <c r="E15" s="12">
+        <f t="shared" si="1"/>
+        <v>2023</v>
+      </c>
+      <c r="F15" s="12">
+        <f t="shared" si="1"/>
+        <v>2024</v>
+      </c>
+      <c r="G15" s="12">
+        <f t="shared" si="1"/>
+        <v>2025</v>
+      </c>
+      <c r="H15" s="12">
+        <f t="shared" si="1"/>
+        <v>2026</v>
+      </c>
+      <c r="I15" s="12">
+        <f t="shared" si="1"/>
+        <v>2027</v>
+      </c>
+      <c r="J15" s="12">
+        <f t="shared" si="1"/>
+        <v>2028</v>
+      </c>
+      <c r="K15" s="12">
+        <f t="shared" si="1"/>
+        <v>2029</v>
+      </c>
+      <c r="L15" s="12">
+        <f t="shared" si="1"/>
+        <v>2030</v>
+      </c>
+      <c r="N15" s="93"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B16" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="C16" s="97">
+        <f>C7/C6</f>
+        <v>0</v>
+      </c>
+      <c r="D16" s="97">
+        <f t="shared" ref="D16:G16" si="2">D7/D6</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="97">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F16" s="97">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="98">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H16" s="158"/>
+      <c r="I16" s="158"/>
+      <c r="J16" s="158"/>
+      <c r="K16" s="158"/>
+      <c r="L16" s="158"/>
+      <c r="N16" s="93"/>
+    </row>
+    <row r="17" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N17" s="93"/>
+    </row>
+    <row r="18" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N18" s="93"/>
+    </row>
+    <row r="19" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N19" s="93"/>
+    </row>
+    <row r="20" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B20" s="249" t="s">
+        <v>424</v>
+      </c>
+      <c r="C20" s="249"/>
+      <c r="N20" s="93"/>
+    </row>
+    <row r="21" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B21" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="C21" s="122">
+        <f>G7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B22" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="C22" s="269">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B23" s="39" t="s">
+        <v>427</v>
+      </c>
+      <c r="C23" s="270">
+        <f>C21*(1+C22)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B24" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="C24" s="156">
+        <f>IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="25" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B25" s="39" t="s">
+        <v>428</v>
+      </c>
+      <c r="C25" s="269">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B26" s="162" t="s">
+        <v>250</v>
+      </c>
+      <c r="C26" s="163">
+        <f>C23/(C24-C25)</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="C9:L9"/>
+    <mergeCell ref="C14:L14"/>
+    <mergeCell ref="B20:C20"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0116CE1A-CCEC-514B-9208-A0DCC7740441}">
   <dimension ref="A1:AB49"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -22914,20 +23520,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="252" t="s">
+      <c r="C3" s="249" t="s">
         <v>137</v>
       </c>
-      <c r="D3" s="252"/>
-      <c r="E3" s="252"/>
-      <c r="F3" s="252"/>
-      <c r="G3" s="258"/>
-      <c r="H3" s="259" t="s">
+      <c r="D3" s="249"/>
+      <c r="E3" s="249"/>
+      <c r="F3" s="249"/>
+      <c r="G3" s="261"/>
+      <c r="H3" s="262" t="s">
         <v>138</v>
       </c>
-      <c r="I3" s="252"/>
-      <c r="J3" s="252"/>
-      <c r="K3" s="252"/>
-      <c r="L3" s="252"/>
+      <c r="I3" s="249"/>
+      <c r="J3" s="249"/>
+      <c r="K3" s="249"/>
+      <c r="L3" s="249"/>
       <c r="P3" s="263"/>
       <c r="Q3" s="263"/>
       <c r="R3" s="263"/>
@@ -22945,18 +23551,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="88"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="260" t="s">
+      <c r="C5" s="258" t="s">
         <v>221</v>
       </c>
-      <c r="D5" s="260"/>
-      <c r="E5" s="260"/>
-      <c r="F5" s="260"/>
-      <c r="G5" s="260"/>
-      <c r="H5" s="260"/>
-      <c r="I5" s="260"/>
-      <c r="J5" s="260"/>
-      <c r="K5" s="260"/>
-      <c r="L5" s="260"/>
+      <c r="D5" s="258"/>
+      <c r="E5" s="258"/>
+      <c r="F5" s="258"/>
+      <c r="G5" s="258"/>
+      <c r="H5" s="258"/>
+      <c r="I5" s="258"/>
+      <c r="J5" s="258"/>
+      <c r="K5" s="258"/>
+      <c r="L5" s="258"/>
       <c r="P5" s="263"/>
       <c r="Q5" s="263"/>
       <c r="R5" s="263"/>
@@ -23382,18 +23988,18 @@
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C39" s="260" t="s">
+      <c r="C39" s="258" t="s">
         <v>270</v>
       </c>
-      <c r="D39" s="260"/>
-      <c r="E39" s="260"/>
-      <c r="F39" s="260"/>
-      <c r="G39" s="260"/>
-      <c r="H39" s="260"/>
-      <c r="I39" s="260"/>
-      <c r="J39" s="260"/>
-      <c r="K39" s="260"/>
-      <c r="L39" s="260"/>
+      <c r="D39" s="258"/>
+      <c r="E39" s="258"/>
+      <c r="F39" s="258"/>
+      <c r="G39" s="258"/>
+      <c r="H39" s="258"/>
+      <c r="I39" s="258"/>
+      <c r="J39" s="258"/>
+      <c r="K39" s="258"/>
+      <c r="L39" s="258"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="12">
@@ -23825,17 +24431,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -34388,15 +34994,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="252" t="s">
+      <c r="B4" s="249" t="s">
         <v>282</v>
       </c>
-      <c r="C4" s="252"/>
-      <c r="E4" s="252" t="s">
+      <c r="C4" s="249"/>
+      <c r="E4" s="249" t="s">
         <v>289</v>
       </c>
-      <c r="F4" s="252"/>
-      <c r="G4" s="252"/>
+      <c r="F4" s="249"/>
+      <c r="G4" s="249"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -34533,14 +35139,14 @@
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="252" t="s">
+      <c r="B15" s="249" t="s">
         <v>78</v>
       </c>
-      <c r="C15" s="252"/>
-      <c r="E15" s="252" t="s">
+      <c r="C15" s="249"/>
+      <c r="E15" s="249" t="s">
         <v>295</v>
       </c>
-      <c r="F15" s="252"/>
+      <c r="F15" s="249"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -34591,14 +35197,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="252" t="s">
+      <c r="B21" s="249" t="s">
         <v>294</v>
       </c>
-      <c r="C21" s="252"/>
-      <c r="E21" s="252" t="s">
+      <c r="C21" s="249"/>
+      <c r="E21" s="249" t="s">
         <v>298</v>
       </c>
-      <c r="F21" s="252"/>
+      <c r="F21" s="249"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -34667,14 +35273,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="252" t="s">
+      <c r="B29" s="249" t="s">
         <v>299</v>
       </c>
-      <c r="C29" s="252"/>
-      <c r="E29" s="252" t="s">
+      <c r="C29" s="249"/>
+      <c r="E29" s="249" t="s">
         <v>305</v>
       </c>
-      <c r="F29" s="252"/>
+      <c r="F29" s="249"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -34750,14 +35356,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="252" t="s">
+      <c r="B37" s="249" t="s">
         <v>317</v>
       </c>
-      <c r="C37" s="252"/>
-      <c r="E37" s="252" t="s">
+      <c r="C37" s="249"/>
+      <c r="E37" s="249" t="s">
         <v>320</v>
       </c>
-      <c r="F37" s="252"/>
+      <c r="F37" s="249"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -34826,14 +35432,14 @@
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="252" t="s">
+      <c r="B45" s="249" t="s">
         <v>328</v>
       </c>
-      <c r="C45" s="252"/>
-      <c r="E45" s="252" t="s">
+      <c r="C45" s="249"/>
+      <c r="E45" s="249" t="s">
         <v>334</v>
       </c>
-      <c r="F45" s="252"/>
+      <c r="F45" s="249"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -34870,14 +35476,14 @@
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="252" t="s">
+      <c r="B51" s="249" t="s">
         <v>331</v>
       </c>
-      <c r="C51" s="252"/>
-      <c r="E51" s="252" t="s">
+      <c r="C51" s="249"/>
+      <c r="E51" s="249" t="s">
         <v>352</v>
       </c>
-      <c r="F51" s="252"/>
+      <c r="F51" s="249"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -36859,14 +37465,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="255" t="s">
+      <c r="C3" s="253" t="s">
         <v>365</v>
       </c>
-      <c r="D3" s="256"/>
-      <c r="F3" s="257" t="s">
+      <c r="D3" s="254"/>
+      <c r="F3" s="255" t="s">
         <v>366</v>
       </c>
-      <c r="G3" s="256"/>
+      <c r="G3" s="254"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -36933,19 +37539,19 @@
       <c r="B7" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C7" s="253">
+      <c r="C7" s="256">
         <f>Statement!AA89</f>
         <v>-0.13037640275448081</v>
       </c>
-      <c r="D7" s="254"/>
-      <c r="F7" s="253">
+      <c r="D7" s="257"/>
+      <c r="F7" s="256">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.17317398716855847</v>
       </c>
-      <c r="G7" s="254"/>
+      <c r="G7" s="257"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="228" t="s">
@@ -36972,19 +37578,19 @@
       <c r="B9" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C9" s="253">
+      <c r="C9" s="256">
         <f>Statement!AA90</f>
         <v>4.0481504023804696E-2</v>
       </c>
-      <c r="D9" s="254"/>
-      <c r="F9" s="253">
+      <c r="D9" s="257"/>
+      <c r="F9" s="256">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.20469173309112548</v>
       </c>
-      <c r="G9" s="254"/>
+      <c r="G9" s="257"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="228" t="s">
@@ -37011,19 +37617,19 @@
       <c r="B11" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C11" s="253">
+      <c r="C11" s="256">
         <f>Statement!AA91</f>
         <v>-0.1614010786596328</v>
       </c>
-      <c r="D11" s="254"/>
-      <c r="F11" s="253">
+      <c r="D11" s="257"/>
+      <c r="F11" s="256">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.16629948047423376</v>
       </c>
-      <c r="G11" s="254"/>
+      <c r="G11" s="257"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="228" t="s">
@@ -37050,19 +37656,19 @@
       <c r="B13" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C13" s="253">
+      <c r="C13" s="256">
         <f>Statement!AA95</f>
         <v>-4.1051008608505718E-2</v>
       </c>
-      <c r="D13" s="254"/>
-      <c r="F13" s="253">
+      <c r="D13" s="257"/>
+      <c r="F13" s="256">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>1.3868988514743887E-2</v>
       </c>
-      <c r="G13" s="254"/>
+      <c r="G13" s="257"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="228" t="s">
@@ -37089,19 +37695,19 @@
       <c r="B15" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C15" s="253">
+      <c r="C15" s="256">
         <f>Statement!AA96</f>
         <v>-0.65140871384799337</v>
       </c>
-      <c r="D15" s="254"/>
-      <c r="F15" s="253">
+      <c r="D15" s="257"/>
+      <c r="F15" s="256">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>2.7052766268583963</v>
       </c>
-      <c r="G15" s="254"/>
+      <c r="G15" s="257"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="228" t="s">
@@ -37128,19 +37734,19 @@
       <c r="B17" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C17" s="253">
+      <c r="C17" s="256">
         <f>Statement!AA98</f>
         <v>-0.78437135034749483</v>
       </c>
-      <c r="D17" s="254"/>
-      <c r="F17" s="253">
+      <c r="D17" s="257"/>
+      <c r="F17" s="256">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>1.9986699179782754</v>
       </c>
-      <c r="G17" s="254"/>
+      <c r="G17" s="257"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="228" t="s">
@@ -37167,22 +37773,22 @@
       <c r="B19" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C19" s="253">
+      <c r="C19" s="256">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-3.2031015030699599E-2</v>
       </c>
-      <c r="D19" s="254"/>
-      <c r="F19" s="253">
+      <c r="D19" s="257"/>
+      <c r="F19" s="256">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-3.7620498458385526E-2</v>
       </c>
-      <c r="G19" s="254"/>
+      <c r="G19" s="257"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="228" t="s">
@@ -37209,22 +37815,22 @@
       <c r="B21" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C21" s="253">
+      <c r="C21" s="256">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>-0.78947368421052633</v>
       </c>
-      <c r="D21" s="254"/>
-      <c r="F21" s="253">
+      <c r="D21" s="257"/>
+      <c r="F21" s="256">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>2</v>
       </c>
-      <c r="G21" s="254"/>
+      <c r="G21" s="257"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -37272,22 +37878,22 @@
       <c r="B25" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C25" s="253">
+      <c r="C25" s="256">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>-0.30844727286201273</v>
       </c>
-      <c r="D25" s="254"/>
-      <c r="F25" s="253">
+      <c r="D25" s="257"/>
+      <c r="F25" s="256">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.16387602700216702</v>
       </c>
-      <c r="G25" s="254"/>
+      <c r="G25" s="257"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="s">
@@ -37314,22 +37920,22 @@
       <c r="B27" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C27" s="253">
+      <c r="C27" s="256">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>6.6472159310281692E-3</v>
       </c>
-      <c r="D27" s="254"/>
-      <c r="F27" s="253">
+      <c r="D27" s="257"/>
+      <c r="F27" s="256">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.16382654634312457</v>
       </c>
-      <c r="G27" s="254"/>
+      <c r="G27" s="257"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
@@ -37356,22 +37962,22 @@
       <c r="B29" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C29" s="253">
+      <c r="C29" s="256">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.15748031496062992</v>
       </c>
-      <c r="D29" s="254"/>
-      <c r="F29" s="253">
+      <c r="D29" s="257"/>
+      <c r="F29" s="256">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>0.46533756230176709</v>
       </c>
-      <c r="G29" s="254"/>
+      <c r="G29" s="257"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B31" s="8" t="s">
@@ -37419,22 +38025,22 @@
       <c r="B33" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C33" s="253">
+      <c r="C33" s="256">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>2.6257619832373135E-2</v>
       </c>
-      <c r="D33" s="254"/>
-      <c r="F33" s="253">
+      <c r="D33" s="257"/>
+      <c r="F33" s="256">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>0.12319376989075922</v>
       </c>
-      <c r="G33" s="254"/>
+      <c r="G33" s="257"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B34" s="20" t="s">
@@ -37461,43 +38067,25 @@
       <c r="B35" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C35" s="253">
+      <c r="C35" s="256">
         <f>IF(C34=0,
 IF(D34=0,0,IF(D34&gt;0,1,-1)),
 (D34-C34)/ABS(C34)
 )</f>
         <v>2.3001949317738791E-2</v>
       </c>
-      <c r="D35" s="254"/>
-      <c r="F35" s="253">
+      <c r="D35" s="257"/>
+      <c r="F35" s="256">
         <f>IF(F34=0,
 IF(G34=0,0,IF(G34&gt;0,1,-1)),
 (G34-F34)/ABS(F34)
 )</f>
         <v>0.10951374207188161</v>
       </c>
-      <c r="G35" s="254"/>
+      <c r="G35" s="257"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="F33:G33"/>
     <mergeCell ref="C35:D35"/>
@@ -37508,6 +38096,24 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/PATH.xlsx
+++ b/PATH.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE951E3E-08E0-0D46-B191-3DA6C2773C52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E58B7392-23F5-954E-9949-7A33721D2B1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="2" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -137,7 +137,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="2">
+  <futureMetadata name="XLRICHVALUE" count="5">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -148,7 +148,28 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="3"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="4"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="5"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="8"/>
         </ext>
       </extLst>
     </bk>
@@ -158,12 +179,21 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="2">
+  <valueMetadata count="5">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
+    </bk>
+    <bk>
+      <rc t="2" v="2"/>
+    </bk>
+    <bk>
+      <rc t="2" v="3"/>
+    </bk>
+    <bk>
+      <rc t="2" v="4"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -2411,6 +2441,10 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="39" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="39" fontId="17" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="39" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2465,10 +2499,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="39" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="39" fontId="17" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="39" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -12858,7 +12888,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=c1dbvh&amp;q=XNYS%3aPATH&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
@@ -12877,11 +12907,9 @@
     <v>Powered by Refinitiv</v>
     <v>19.84</v>
     <v>9.2002000000000006</v>
-    <v>0.98140000000000005</v>
-    <v>-0.12</v>
-    <v>-1.0168999999999999E-2</v>
-    <v>1.72E-2</v>
-    <v>1.4729999999999999E-3</v>
+    <v>0.92379999999999995</v>
+    <v>0.27010000000000001</v>
+    <v>2.1835E-2</v>
     <v>USD</v>
     <v>UiPath, Inc. is focused on agentic automation and orchestration, empowering enterprises to harness the full potential of AI agents to autonomously execute and optimize complex business processes. It is focused on building and managing automations, starting with computer vision technology and user interface automation in its initial robotic process automation offering. Its AI-powered UiPath Platform offers a robust set of capabilities that allows its customers to discover opportunities for automation, automate using a digital workforce that seamlessly collaborates with humans, and operate a mission-critical automation program at scale. It enables employees to quickly build automations for both existing and new processes and to automate a range of actions including logging into applications, moving folders, filling in forms, reading emails and others. Its platform allows users to design and combine UI automations, API integrations and AI-based document understanding in a single workflow.</v>
     <v>3981</v>
@@ -12889,35 +12917,49 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>One Vanderbilt Avenue, 60th Floor, NEW YORK, NY, 10017 US</v>
-    <v>12.23</v>
+    <v>12.72</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46213.999831562498</v>
+    <v>46234.71753704844</v>
     <v>0</v>
-    <v>11.51</v>
-    <v>6051645104</v>
+    <v>12.160500000000001</v>
+    <v>6549092404</v>
     <v>UIPATH, INC.</v>
     <v>UIPATH, INC.</v>
-    <v>12.12</v>
-    <v>19.615300000000001</v>
-    <v>11.8</v>
-    <v>11.68</v>
-    <v>11.6972</v>
+    <v>12.29</v>
+    <v>21.0108</v>
+    <v>12.37</v>
+    <v>12.6401</v>
     <v>518120300</v>
     <v>PATH</v>
     <v>UIPATH, INC. (XNYS:PATH)</v>
-    <v>78695436</v>
-    <v>54552944</v>
+    <v>21004447</v>
+    <v>80967510</v>
     <v>2015</v>
   </rv>
   <rv s="2">
     <v>1</v>
   </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Price (Extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Change (extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Change % (extended hours)</v>
+    <v>0</v>
+  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="3">
+  <rv s="4">
     <v>5</v>
     <v>10 Y TSY YLD NDX</v>
     <v>6</v>
@@ -12929,30 +12971,30 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>46.87</v>
+    <v>47.14</v>
     <v>39.47</v>
-    <v>0.3</v>
-    <v>6.6090000000000003E-3</v>
+    <v>0.41</v>
+    <v>8.8710000000000004E-3</v>
     <v>US</v>
-    <v>45.71</v>
+    <v>46.86</v>
     <v>Index</v>
-    <v>3</v>
-    <v>45.39</v>
+    <v>6</v>
+    <v>46.51</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>45.41</v>
-    <v>45.39</v>
-    <v>45.69</v>
+    <v>46.69</v>
+    <v>46.22</v>
+    <v>46.63</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="2">
-    <v>4</v>
+    <v>7</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -12974,8 +13016,6 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
-    <k n="Change (Extended hours)"/>
-    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -12996,7 +13036,6 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
-    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -13006,6 +13045,11 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
+  </s>
+  <s t="_error">
+    <k n="errorType" t="i"/>
+    <k n="field" t="s"/>
+    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -13041,7 +13085,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="45">
+    <a count="42">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -13052,16 +13096,13 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
-      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
-      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
-      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -13155,19 +13196,13 @@
       <v>8</v>
       <v>9</v>
       <v>4</v>
-      <v>1</v>
-      <v>1</v>
-      <v>5</v>
     </spb>
     <spb s="4">
-      <v>at close</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq</v>
+      <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Delayed 15 minutes</v>
-      <v>from close</v>
-      <v>from close</v>
     </spb>
     <spb s="0">
       <v>1</v>
@@ -13239,9 +13274,6 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
-    <k n="Price (Extended hours)" t="i"/>
-    <k n="Change (Extended hours)" t="i"/>
-    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -13249,9 +13281,6 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
-    <k n="Price (Extended hours)" t="s"/>
-    <k n="Change (Extended hours)" t="s"/>
-    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="UniqueName" t="spb"/>
@@ -13742,18 +13771,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="250" t="s">
+      <c r="B2" s="254" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="251"/>
-      <c r="E2" s="250" t="s">
+      <c r="C2" s="255"/>
+      <c r="E2" s="254" t="s">
         <v>336</v>
       </c>
-      <c r="F2" s="251"/>
-      <c r="H2" s="250" t="s">
+      <c r="F2" s="255"/>
+      <c r="H2" s="254" t="s">
         <v>381</v>
       </c>
-      <c r="I2" s="251"/>
+      <c r="I2" s="255"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="206" t="s">
@@ -13768,7 +13797,7 @@
       </c>
       <c r="F3" s="208">
         <f ca="1">Statement!AC153</f>
-        <v>6101106.3999999994</v>
+        <v>6602619.4355000006</v>
       </c>
       <c r="H3" s="206" t="str">
         <f>'AVG target price'!B5</f>
@@ -13792,7 +13821,7 @@
       </c>
       <c r="F4" s="209">
         <f ca="1">Statement!AC154</f>
-        <v>4685360.3999999994</v>
+        <v>5186873.4355000006</v>
       </c>
       <c r="H4" s="206" t="str">
         <f>'AVG target price'!B6</f>
@@ -13809,7 +13838,7 @@
       </c>
       <c r="C5" s="229" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>11.68</v>
+        <v>12.6401</v>
       </c>
       <c r="E5" s="206" t="s">
         <v>292</v>
@@ -13831,16 +13860,16 @@
       <c r="B6" s="206" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="229" cm="1">
-        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>11.6972</v>
+      <c r="C6" s="229" t="e" cm="1" vm="2">
+        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E6" s="206" t="s">
         <v>286</v>
       </c>
       <c r="F6" s="211">
         <f ca="1">Statement!AC150</f>
-        <v>19.466666666666665</v>
+        <v>21.066833333333332</v>
       </c>
       <c r="H6" s="206" t="str">
         <f>'AVG target price'!B8</f>
@@ -13857,14 +13886,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-0.12</v>
+        <v>0.27010000000000001</v>
       </c>
       <c r="E7" s="207" t="s">
         <v>242</v>
       </c>
       <c r="F7" s="212">
         <f ca="1">Statement!AC151</f>
-        <v>3.7627479026268738</v>
+        <v>4.072047068835098</v>
       </c>
       <c r="H7" s="205" t="str">
         <f>'AVG target price'!B9</f>
@@ -13879,16 +13908,16 @@
       <c r="B8" s="206" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" cm="1">
-        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>1.72E-2</v>
+      <c r="C8" s="6" t="e" cm="1" vm="3">
+        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E8" s="206" t="s">
         <v>314</v>
       </c>
       <c r="F8" s="213">
         <f ca="1">Statement!AC161</f>
-        <v>1.7637620612549882E-2</v>
+        <v>1.6297925550793315E-2</v>
       </c>
       <c r="H8" s="205" t="str">
         <f>'AVG target price'!B11</f>
@@ -13896,7 +13925,7 @@
       </c>
       <c r="I8" s="234">
         <f ca="1">'AVG target price'!C11</f>
-        <v>0.10092872539603272</v>
+        <v>1.7305837186862565E-2</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13905,30 +13934,30 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-1.0168999999999999E-2</v>
+        <v>2.1835E-2</v>
       </c>
       <c r="E9" s="206" t="s">
         <v>337</v>
       </c>
       <c r="F9" s="213">
         <f ca="1">Statement!AC162</f>
-        <v>5.1369863013698641E-2</v>
+        <v>4.7467978892572059E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B10" s="206" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" cm="1">
-        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>1.4729999999999999E-3</v>
+      <c r="C10" s="73" t="e" cm="1" vm="4">
+        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E10" s="206" t="s">
         <v>342</v>
       </c>
       <c r="F10" s="213">
         <f ca="1">Statement!AC164</f>
-        <v>5.6608093246824878E-2</v>
+        <v>5.2308330560906516E-2</v>
       </c>
       <c r="H10" s="205" t="s">
         <v>429</v>
@@ -13976,7 +14005,7 @@
       </c>
       <c r="C13" s="230" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>0.98140000000000005</v>
+        <v>0.92379999999999995</v>
       </c>
       <c r="E13" s="206" t="s">
         <v>123</v>
@@ -13992,7 +14021,7 @@
       </c>
       <c r="C14" s="231" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>54552944</v>
+        <v>80967510</v>
       </c>
       <c r="E14" s="207" t="s">
         <v>124</v>
@@ -14008,7 +14037,7 @@
       </c>
       <c r="F15" s="213">
         <f ca="1">Statement!AC176</f>
-        <v>0.23204742012038998</v>
+        <v>0.21442186905215579</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -14021,10 +14050,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="252" t="s">
+      <c r="B17" s="256" t="s">
         <v>103</v>
       </c>
-      <c r="C17" s="252"/>
+      <c r="C17" s="256"/>
       <c r="E17" s="205" t="s">
         <v>345</v>
       </c>
@@ -14097,14 +14126,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="252" t="s">
+      <c r="B25" s="256" t="s">
         <v>126</v>
       </c>
-      <c r="C25" s="252"/>
-      <c r="E25" s="250" t="s">
+      <c r="C25" s="256"/>
+      <c r="E25" s="254" t="s">
         <v>401</v>
       </c>
-      <c r="F25" s="251"/>
+      <c r="F25" s="255"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="205" t="s">
@@ -14113,12 +14142,12 @@
       <c r="C26" s="191">
         <v>0.21</v>
       </c>
-      <c r="E26" s="206" t="e" vm="2">
+      <c r="E26" s="206" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="240" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>45.69</v>
+        <v>46.63</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14133,7 +14162,7 @@
       </c>
       <c r="F27" s="241">
         <f ca="1">F26/1000</f>
-        <v>4.5689999999999995E-2</v>
+        <v>4.6630000000000005E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14153,15 +14182,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="249" t="s">
+      <c r="B33" s="253" t="s">
         <v>391</v>
       </c>
-      <c r="C33" s="249"/>
-      <c r="D33" s="249"/>
-      <c r="E33" s="249"/>
-      <c r="F33" s="249"/>
-      <c r="G33" s="249"/>
-      <c r="H33" s="249"/>
+      <c r="C33" s="253"/>
+      <c r="D33" s="253"/>
+      <c r="E33" s="253"/>
+      <c r="F33" s="253"/>
+      <c r="G33" s="253"/>
+      <c r="H33" s="253"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -14180,24 +14209,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="249"/>
-      <c r="C39" s="249"/>
-      <c r="D39" s="249"/>
-      <c r="E39" s="249"/>
-      <c r="F39" s="249"/>
-      <c r="G39" s="249"/>
-      <c r="H39" s="249"/>
+      <c r="B39" s="253"/>
+      <c r="C39" s="253"/>
+      <c r="D39" s="253"/>
+      <c r="E39" s="253"/>
+      <c r="F39" s="253"/>
+      <c r="G39" s="253"/>
+      <c r="H39" s="253"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="249" t="s">
+      <c r="B42" s="253" t="s">
         <v>394</v>
       </c>
-      <c r="C42" s="249"/>
-      <c r="D42" s="249"/>
-      <c r="E42" s="249"/>
-      <c r="F42" s="249"/>
-      <c r="G42" s="249"/>
-      <c r="H42" s="249"/>
+      <c r="C42" s="253"/>
+      <c r="D42" s="253"/>
+      <c r="E42" s="253"/>
+      <c r="F42" s="253"/>
+      <c r="G42" s="253"/>
+      <c r="H42" s="253"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -14212,24 +14241,24 @@
       </c>
     </row>
     <row r="49" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="249"/>
-      <c r="C49" s="249"/>
-      <c r="D49" s="249"/>
-      <c r="E49" s="249"/>
-      <c r="F49" s="249"/>
-      <c r="G49" s="249"/>
-      <c r="H49" s="249"/>
+      <c r="B49" s="253"/>
+      <c r="C49" s="253"/>
+      <c r="D49" s="253"/>
+      <c r="E49" s="253"/>
+      <c r="F49" s="253"/>
+      <c r="G49" s="253"/>
+      <c r="H49" s="253"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B52" s="249" t="s">
+      <c r="B52" s="253" t="s">
         <v>128</v>
       </c>
-      <c r="C52" s="249"/>
-      <c r="D52" s="249"/>
-      <c r="E52" s="249"/>
-      <c r="F52" s="249"/>
-      <c r="G52" s="249"/>
-      <c r="H52" s="249"/>
+      <c r="C52" s="253"/>
+      <c r="D52" s="253"/>
+      <c r="E52" s="253"/>
+      <c r="F52" s="253"/>
+      <c r="G52" s="253"/>
+      <c r="H52" s="253"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B54" s="41" t="s">
@@ -14244,13 +14273,13 @@
       </c>
     </row>
     <row r="59" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="249"/>
-      <c r="C59" s="249"/>
-      <c r="D59" s="249"/>
-      <c r="E59" s="249"/>
-      <c r="F59" s="249"/>
-      <c r="G59" s="249"/>
-      <c r="H59" s="249"/>
+      <c r="B59" s="253"/>
+      <c r="C59" s="253"/>
+      <c r="D59" s="253"/>
+      <c r="E59" s="253"/>
+      <c r="F59" s="253"/>
+      <c r="G59" s="253"/>
+      <c r="H59" s="253"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -14335,36 +14364,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="249" t="s">
+      <c r="C2" s="253" t="s">
         <v>137</v>
       </c>
-      <c r="D2" s="249"/>
-      <c r="E2" s="249"/>
-      <c r="F2" s="249"/>
-      <c r="G2" s="261"/>
-      <c r="H2" s="262" t="s">
+      <c r="D2" s="253"/>
+      <c r="E2" s="253"/>
+      <c r="F2" s="253"/>
+      <c r="G2" s="265"/>
+      <c r="H2" s="266" t="s">
         <v>138</v>
       </c>
-      <c r="I2" s="249"/>
-      <c r="J2" s="249"/>
-      <c r="K2" s="249"/>
-      <c r="L2" s="249"/>
+      <c r="I2" s="253"/>
+      <c r="J2" s="253"/>
+      <c r="K2" s="253"/>
+      <c r="L2" s="253"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="249" t="s">
+      <c r="S2" s="253" t="s">
         <v>137</v>
       </c>
-      <c r="T2" s="249"/>
-      <c r="U2" s="249"/>
-      <c r="V2" s="249"/>
-      <c r="W2" s="249"/>
-      <c r="X2" s="249"/>
-      <c r="Y2" s="249"/>
-      <c r="Z2" s="249"/>
-      <c r="AA2" s="249" t="s">
+      <c r="T2" s="253"/>
+      <c r="U2" s="253"/>
+      <c r="V2" s="253"/>
+      <c r="W2" s="253"/>
+      <c r="X2" s="253"/>
+      <c r="Y2" s="253"/>
+      <c r="Z2" s="253"/>
+      <c r="AA2" s="253" t="s">
         <v>138</v>
       </c>
-      <c r="AB2" s="249"/>
-      <c r="AC2" s="249"/>
+      <c r="AB2" s="253"/>
+      <c r="AC2" s="253"/>
       <c r="AE2" s="87" t="s">
         <v>139</v>
       </c>
@@ -14375,32 +14404,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="258" t="s">
+      <c r="C4" s="262" t="s">
         <v>140</v>
       </c>
-      <c r="D4" s="258"/>
-      <c r="E4" s="258"/>
-      <c r="F4" s="258"/>
-      <c r="G4" s="258"/>
-      <c r="H4" s="258"/>
-      <c r="I4" s="258"/>
-      <c r="J4" s="258"/>
-      <c r="K4" s="258"/>
-      <c r="L4" s="258"/>
+      <c r="D4" s="262"/>
+      <c r="E4" s="262"/>
+      <c r="F4" s="262"/>
+      <c r="G4" s="262"/>
+      <c r="H4" s="262"/>
+      <c r="I4" s="262"/>
+      <c r="J4" s="262"/>
+      <c r="K4" s="262"/>
+      <c r="L4" s="262"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="259" t="s">
+      <c r="S4" s="263" t="s">
         <v>140</v>
       </c>
-      <c r="T4" s="260"/>
-      <c r="U4" s="260"/>
-      <c r="V4" s="260"/>
-      <c r="W4" s="260"/>
-      <c r="X4" s="260"/>
-      <c r="Y4" s="260"/>
-      <c r="Z4" s="260"/>
-      <c r="AA4" s="260"/>
-      <c r="AB4" s="260"/>
-      <c r="AC4" s="260"/>
+      <c r="T4" s="264"/>
+      <c r="U4" s="264"/>
+      <c r="V4" s="264"/>
+      <c r="W4" s="264"/>
+      <c r="X4" s="264"/>
+      <c r="Y4" s="264"/>
+      <c r="Z4" s="264"/>
+      <c r="AA4" s="264"/>
+      <c r="AB4" s="264"/>
+      <c r="AC4" s="264"/>
       <c r="AE4" s="89"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -14896,33 +14925,33 @@
       <c r="Q10" s="93"/>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C11" s="258" t="s">
+      <c r="C11" s="262" t="s">
         <v>146</v>
       </c>
-      <c r="D11" s="258"/>
-      <c r="E11" s="258"/>
-      <c r="F11" s="258"/>
-      <c r="G11" s="258"/>
-      <c r="H11" s="258"/>
-      <c r="I11" s="258"/>
-      <c r="J11" s="258"/>
-      <c r="K11" s="258"/>
-      <c r="L11" s="258"/>
+      <c r="D11" s="262"/>
+      <c r="E11" s="262"/>
+      <c r="F11" s="262"/>
+      <c r="G11" s="262"/>
+      <c r="H11" s="262"/>
+      <c r="I11" s="262"/>
+      <c r="J11" s="262"/>
+      <c r="K11" s="262"/>
+      <c r="L11" s="262"/>
       <c r="O11" s="5"/>
       <c r="Q11" s="93"/>
-      <c r="S11" s="259" t="s">
+      <c r="S11" s="263" t="s">
         <v>146</v>
       </c>
-      <c r="T11" s="260"/>
-      <c r="U11" s="260"/>
-      <c r="V11" s="260"/>
-      <c r="W11" s="260"/>
-      <c r="X11" s="260"/>
-      <c r="Y11" s="260"/>
-      <c r="Z11" s="260"/>
-      <c r="AA11" s="260"/>
-      <c r="AB11" s="260"/>
-      <c r="AC11" s="260"/>
+      <c r="T11" s="264"/>
+      <c r="U11" s="264"/>
+      <c r="V11" s="264"/>
+      <c r="W11" s="264"/>
+      <c r="X11" s="264"/>
+      <c r="Y11" s="264"/>
+      <c r="Z11" s="264"/>
+      <c r="AA11" s="264"/>
+      <c r="AB11" s="264"/>
+      <c r="AC11" s="264"/>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B12" s="16" t="s">
@@ -15363,33 +15392,33 @@
       <c r="Q18" s="93"/>
     </row>
     <row r="19" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C19" s="258" t="s">
+      <c r="C19" s="262" t="s">
         <v>148</v>
       </c>
-      <c r="D19" s="258"/>
-      <c r="E19" s="258"/>
-      <c r="F19" s="258"/>
-      <c r="G19" s="258"/>
-      <c r="H19" s="258"/>
-      <c r="I19" s="258"/>
-      <c r="J19" s="258"/>
-      <c r="K19" s="258"/>
-      <c r="L19" s="258"/>
+      <c r="D19" s="262"/>
+      <c r="E19" s="262"/>
+      <c r="F19" s="262"/>
+      <c r="G19" s="262"/>
+      <c r="H19" s="262"/>
+      <c r="I19" s="262"/>
+      <c r="J19" s="262"/>
+      <c r="K19" s="262"/>
+      <c r="L19" s="262"/>
       <c r="O19" s="5"/>
       <c r="Q19" s="93"/>
-      <c r="S19" s="259" t="s">
+      <c r="S19" s="263" t="s">
         <v>148</v>
       </c>
-      <c r="T19" s="260"/>
-      <c r="U19" s="260"/>
-      <c r="V19" s="260"/>
-      <c r="W19" s="260"/>
-      <c r="X19" s="260"/>
-      <c r="Y19" s="260"/>
-      <c r="Z19" s="260"/>
-      <c r="AA19" s="260"/>
-      <c r="AB19" s="260"/>
-      <c r="AC19" s="260"/>
+      <c r="T19" s="264"/>
+      <c r="U19" s="264"/>
+      <c r="V19" s="264"/>
+      <c r="W19" s="264"/>
+      <c r="X19" s="264"/>
+      <c r="Y19" s="264"/>
+      <c r="Z19" s="264"/>
+      <c r="AA19" s="264"/>
+      <c r="AB19" s="264"/>
+      <c r="AC19" s="264"/>
       <c r="AE19" s="89">
         <f>AE4</f>
         <v>0</v>
@@ -16207,32 +16236,32 @@
       <c r="O31" s="5"/>
     </row>
     <row r="32" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C32" s="258" t="s">
+      <c r="C32" s="262" t="s">
         <v>150</v>
       </c>
-      <c r="D32" s="258"/>
-      <c r="E32" s="258"/>
-      <c r="F32" s="258"/>
-      <c r="G32" s="258"/>
-      <c r="H32" s="258"/>
-      <c r="I32" s="258"/>
-      <c r="J32" s="258"/>
-      <c r="K32" s="258"/>
-      <c r="L32" s="258"/>
+      <c r="D32" s="262"/>
+      <c r="E32" s="262"/>
+      <c r="F32" s="262"/>
+      <c r="G32" s="262"/>
+      <c r="H32" s="262"/>
+      <c r="I32" s="262"/>
+      <c r="J32" s="262"/>
+      <c r="K32" s="262"/>
+      <c r="L32" s="262"/>
       <c r="O32" s="5"/>
-      <c r="S32" s="259" t="s">
+      <c r="S32" s="263" t="s">
         <v>150</v>
       </c>
-      <c r="T32" s="260"/>
-      <c r="U32" s="260"/>
-      <c r="V32" s="260"/>
-      <c r="W32" s="260"/>
-      <c r="X32" s="260"/>
-      <c r="Y32" s="260"/>
-      <c r="Z32" s="260"/>
-      <c r="AA32" s="260"/>
-      <c r="AB32" s="260"/>
-      <c r="AC32" s="260"/>
+      <c r="T32" s="264"/>
+      <c r="U32" s="264"/>
+      <c r="V32" s="264"/>
+      <c r="W32" s="264"/>
+      <c r="X32" s="264"/>
+      <c r="Y32" s="264"/>
+      <c r="Z32" s="264"/>
+      <c r="AA32" s="264"/>
+      <c r="AB32" s="264"/>
+      <c r="AC32" s="264"/>
     </row>
     <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B33" s="16" t="s">
@@ -16537,35 +16566,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="249" t="s">
+      <c r="C2" s="253" t="s">
         <v>137</v>
       </c>
-      <c r="D2" s="249"/>
-      <c r="E2" s="249"/>
-      <c r="F2" s="249"/>
-      <c r="G2" s="261"/>
-      <c r="H2" s="262" t="s">
+      <c r="D2" s="253"/>
+      <c r="E2" s="253"/>
+      <c r="F2" s="253"/>
+      <c r="G2" s="265"/>
+      <c r="H2" s="266" t="s">
         <v>138</v>
       </c>
-      <c r="I2" s="249"/>
-      <c r="J2" s="249"/>
-      <c r="K2" s="249"/>
-      <c r="L2" s="249"/>
-      <c r="P2" s="249" t="s">
+      <c r="I2" s="253"/>
+      <c r="J2" s="253"/>
+      <c r="K2" s="253"/>
+      <c r="L2" s="253"/>
+      <c r="P2" s="253" t="s">
         <v>137</v>
       </c>
-      <c r="Q2" s="249"/>
-      <c r="R2" s="249"/>
-      <c r="S2" s="249"/>
-      <c r="T2" s="249"/>
-      <c r="U2" s="249"/>
-      <c r="V2" s="249"/>
-      <c r="W2" s="249"/>
-      <c r="X2" s="249" t="s">
+      <c r="Q2" s="253"/>
+      <c r="R2" s="253"/>
+      <c r="S2" s="253"/>
+      <c r="T2" s="253"/>
+      <c r="U2" s="253"/>
+      <c r="V2" s="253"/>
+      <c r="W2" s="253"/>
+      <c r="X2" s="253" t="s">
         <v>138</v>
       </c>
-      <c r="Y2" s="249"/>
-      <c r="Z2" s="249"/>
+      <c r="Y2" s="253"/>
+      <c r="Z2" s="253"/>
       <c r="AB2" s="87" t="s">
         <v>139</v>
       </c>
@@ -16574,31 +16603,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="258" t="s">
+      <c r="C4" s="262" t="s">
         <v>140</v>
       </c>
-      <c r="D4" s="258"/>
-      <c r="E4" s="258"/>
-      <c r="F4" s="258"/>
-      <c r="G4" s="258"/>
-      <c r="H4" s="258"/>
-      <c r="I4" s="258"/>
-      <c r="J4" s="258"/>
-      <c r="K4" s="258"/>
-      <c r="L4" s="258"/>
-      <c r="P4" s="260" t="s">
+      <c r="D4" s="262"/>
+      <c r="E4" s="262"/>
+      <c r="F4" s="262"/>
+      <c r="G4" s="262"/>
+      <c r="H4" s="262"/>
+      <c r="I4" s="262"/>
+      <c r="J4" s="262"/>
+      <c r="K4" s="262"/>
+      <c r="L4" s="262"/>
+      <c r="P4" s="264" t="s">
         <v>140</v>
       </c>
-      <c r="Q4" s="260"/>
-      <c r="R4" s="260"/>
-      <c r="S4" s="260"/>
-      <c r="T4" s="260"/>
-      <c r="U4" s="260"/>
-      <c r="V4" s="260"/>
-      <c r="W4" s="260"/>
-      <c r="X4" s="260"/>
-      <c r="Y4" s="260"/>
-      <c r="Z4" s="260"/>
+      <c r="Q4" s="264"/>
+      <c r="R4" s="264"/>
+      <c r="S4" s="264"/>
+      <c r="T4" s="264"/>
+      <c r="U4" s="264"/>
+      <c r="V4" s="264"/>
+      <c r="W4" s="264"/>
+      <c r="X4" s="264"/>
+      <c r="Y4" s="264"/>
+      <c r="Z4" s="264"/>
       <c r="AB4" s="89"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -16793,32 +16822,32 @@
       <c r="N8" s="93"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="258" t="s">
+      <c r="C9" s="262" t="s">
         <v>166</v>
       </c>
-      <c r="D9" s="258"/>
-      <c r="E9" s="258"/>
-      <c r="F9" s="258"/>
-      <c r="G9" s="258"/>
-      <c r="H9" s="258"/>
-      <c r="I9" s="258"/>
-      <c r="J9" s="258"/>
-      <c r="K9" s="258"/>
-      <c r="L9" s="258"/>
+      <c r="D9" s="262"/>
+      <c r="E9" s="262"/>
+      <c r="F9" s="262"/>
+      <c r="G9" s="262"/>
+      <c r="H9" s="262"/>
+      <c r="I9" s="262"/>
+      <c r="J9" s="262"/>
+      <c r="K9" s="262"/>
+      <c r="L9" s="262"/>
       <c r="N9" s="93"/>
-      <c r="P9" s="260" t="s">
+      <c r="P9" s="264" t="s">
         <v>167</v>
       </c>
-      <c r="Q9" s="260"/>
-      <c r="R9" s="260"/>
-      <c r="S9" s="260"/>
-      <c r="T9" s="260"/>
-      <c r="U9" s="260"/>
-      <c r="V9" s="260"/>
-      <c r="W9" s="260"/>
-      <c r="X9" s="260"/>
-      <c r="Y9" s="260"/>
-      <c r="Z9" s="260"/>
+      <c r="Q9" s="264"/>
+      <c r="R9" s="264"/>
+      <c r="S9" s="264"/>
+      <c r="T9" s="264"/>
+      <c r="U9" s="264"/>
+      <c r="V9" s="264"/>
+      <c r="W9" s="264"/>
+      <c r="X9" s="264"/>
+      <c r="Y9" s="264"/>
+      <c r="Z9" s="264"/>
       <c r="AB9" s="89">
         <f>AB4</f>
         <v>0</v>
@@ -17667,31 +17696,31 @@
       </c>
     </row>
     <row r="21" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="C21" s="258" t="s">
+      <c r="C21" s="262" t="s">
         <v>169</v>
       </c>
-      <c r="D21" s="258"/>
-      <c r="E21" s="258"/>
-      <c r="F21" s="258"/>
-      <c r="G21" s="258"/>
-      <c r="H21" s="258"/>
-      <c r="I21" s="258"/>
-      <c r="J21" s="258"/>
-      <c r="K21" s="258"/>
-      <c r="L21" s="258"/>
-      <c r="P21" s="260" t="s">
+      <c r="D21" s="262"/>
+      <c r="E21" s="262"/>
+      <c r="F21" s="262"/>
+      <c r="G21" s="262"/>
+      <c r="H21" s="262"/>
+      <c r="I21" s="262"/>
+      <c r="J21" s="262"/>
+      <c r="K21" s="262"/>
+      <c r="L21" s="262"/>
+      <c r="P21" s="264" t="s">
         <v>169</v>
       </c>
-      <c r="Q21" s="260"/>
-      <c r="R21" s="260"/>
-      <c r="S21" s="260"/>
-      <c r="T21" s="260"/>
-      <c r="U21" s="260"/>
-      <c r="V21" s="260"/>
-      <c r="W21" s="260"/>
-      <c r="X21" s="260"/>
-      <c r="Y21" s="260"/>
-      <c r="Z21" s="260"/>
+      <c r="Q21" s="264"/>
+      <c r="R21" s="264"/>
+      <c r="S21" s="264"/>
+      <c r="T21" s="264"/>
+      <c r="U21" s="264"/>
+      <c r="V21" s="264"/>
+      <c r="W21" s="264"/>
+      <c r="X21" s="264"/>
+      <c r="Y21" s="264"/>
+      <c r="Z21" s="264"/>
     </row>
     <row r="22" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B22" s="16" t="s">
@@ -18506,60 +18535,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="249" t="s">
+      <c r="C3" s="253" t="s">
         <v>137</v>
       </c>
-      <c r="D3" s="249"/>
-      <c r="E3" s="249"/>
-      <c r="F3" s="249"/>
-      <c r="G3" s="261"/>
-      <c r="H3" s="262" t="s">
+      <c r="D3" s="253"/>
+      <c r="E3" s="253"/>
+      <c r="F3" s="253"/>
+      <c r="G3" s="265"/>
+      <c r="H3" s="266" t="s">
         <v>138</v>
       </c>
-      <c r="I3" s="249"/>
-      <c r="J3" s="249"/>
-      <c r="K3" s="249"/>
-      <c r="L3" s="249"/>
-      <c r="P3" s="263"/>
-      <c r="Q3" s="263"/>
-      <c r="R3" s="263"/>
-      <c r="S3" s="263"/>
-      <c r="T3" s="263"/>
-      <c r="U3" s="263"/>
-      <c r="V3" s="263"/>
-      <c r="W3" s="263"/>
-      <c r="X3" s="263"/>
-      <c r="Y3" s="263"/>
-      <c r="Z3" s="263"/>
+      <c r="I3" s="253"/>
+      <c r="J3" s="253"/>
+      <c r="K3" s="253"/>
+      <c r="L3" s="253"/>
+      <c r="P3" s="267"/>
+      <c r="Q3" s="267"/>
+      <c r="R3" s="267"/>
+      <c r="S3" s="267"/>
+      <c r="T3" s="267"/>
+      <c r="U3" s="267"/>
+      <c r="V3" s="267"/>
+      <c r="W3" s="267"/>
+      <c r="X3" s="267"/>
+      <c r="Y3" s="267"/>
+      <c r="Z3" s="267"/>
       <c r="AB3" s="130"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="88"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="258" t="s">
+      <c r="C5" s="262" t="s">
         <v>140</v>
       </c>
-      <c r="D5" s="258"/>
-      <c r="E5" s="258"/>
-      <c r="F5" s="258"/>
-      <c r="G5" s="258"/>
-      <c r="H5" s="258"/>
-      <c r="I5" s="258"/>
-      <c r="J5" s="258"/>
-      <c r="K5" s="258"/>
-      <c r="L5" s="258"/>
-      <c r="P5" s="263"/>
-      <c r="Q5" s="263"/>
-      <c r="R5" s="263"/>
-      <c r="S5" s="263"/>
-      <c r="T5" s="263"/>
-      <c r="U5" s="263"/>
-      <c r="V5" s="263"/>
-      <c r="W5" s="263"/>
-      <c r="X5" s="263"/>
-      <c r="Y5" s="263"/>
-      <c r="Z5" s="263"/>
+      <c r="D5" s="262"/>
+      <c r="E5" s="262"/>
+      <c r="F5" s="262"/>
+      <c r="G5" s="262"/>
+      <c r="H5" s="262"/>
+      <c r="I5" s="262"/>
+      <c r="J5" s="262"/>
+      <c r="K5" s="262"/>
+      <c r="L5" s="262"/>
+      <c r="P5" s="267"/>
+      <c r="Q5" s="267"/>
+      <c r="R5" s="267"/>
+      <c r="S5" s="267"/>
+      <c r="T5" s="267"/>
+      <c r="U5" s="267"/>
+      <c r="V5" s="267"/>
+      <c r="W5" s="267"/>
+      <c r="X5" s="267"/>
+      <c r="Y5" s="267"/>
+      <c r="Z5" s="267"/>
       <c r="AB5" s="131"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -18745,30 +18774,30 @@
       <c r="N10" s="93"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="258" t="s">
+      <c r="C11" s="262" t="s">
         <v>173</v>
       </c>
-      <c r="D11" s="258"/>
-      <c r="E11" s="258"/>
-      <c r="F11" s="258"/>
-      <c r="G11" s="258"/>
-      <c r="H11" s="258"/>
-      <c r="I11" s="258"/>
-      <c r="J11" s="258"/>
-      <c r="K11" s="258"/>
-      <c r="L11" s="258"/>
+      <c r="D11" s="262"/>
+      <c r="E11" s="262"/>
+      <c r="F11" s="262"/>
+      <c r="G11" s="262"/>
+      <c r="H11" s="262"/>
+      <c r="I11" s="262"/>
+      <c r="J11" s="262"/>
+      <c r="K11" s="262"/>
+      <c r="L11" s="262"/>
       <c r="N11" s="93"/>
-      <c r="P11" s="263"/>
-      <c r="Q11" s="263"/>
-      <c r="R11" s="263"/>
-      <c r="S11" s="263"/>
-      <c r="T11" s="263"/>
-      <c r="U11" s="263"/>
-      <c r="V11" s="263"/>
-      <c r="W11" s="263"/>
-      <c r="X11" s="263"/>
-      <c r="Y11" s="263"/>
-      <c r="Z11" s="263"/>
+      <c r="P11" s="267"/>
+      <c r="Q11" s="267"/>
+      <c r="R11" s="267"/>
+      <c r="S11" s="267"/>
+      <c r="T11" s="267"/>
+      <c r="U11" s="267"/>
+      <c r="V11" s="267"/>
+      <c r="W11" s="267"/>
+      <c r="X11" s="267"/>
+      <c r="Y11" s="267"/>
+      <c r="Z11" s="267"/>
       <c r="AB11" s="131"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -19010,18 +19039,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="258" t="s">
+      <c r="C18" s="262" t="s">
         <v>178</v>
       </c>
-      <c r="D18" s="258"/>
-      <c r="E18" s="258"/>
-      <c r="F18" s="258"/>
-      <c r="G18" s="258"/>
-      <c r="H18" s="258"/>
-      <c r="I18" s="258"/>
-      <c r="J18" s="258"/>
-      <c r="K18" s="258"/>
-      <c r="L18" s="258"/>
+      <c r="D18" s="262"/>
+      <c r="E18" s="262"/>
+      <c r="F18" s="262"/>
+      <c r="G18" s="262"/>
+      <c r="H18" s="262"/>
+      <c r="I18" s="262"/>
+      <c r="J18" s="262"/>
+      <c r="K18" s="262"/>
+      <c r="L18" s="262"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19234,23 +19263,23 @@
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="263"/>
-      <c r="C25" s="263"/>
+      <c r="B25" s="267"/>
+      <c r="C25" s="267"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="130"/>
-      <c r="C26" s="258" t="s">
+      <c r="C26" s="262" t="s">
         <v>184</v>
       </c>
-      <c r="D26" s="258"/>
-      <c r="E26" s="258"/>
-      <c r="F26" s="258"/>
-      <c r="G26" s="258"/>
-      <c r="H26" s="258"/>
-      <c r="I26" s="258"/>
-      <c r="J26" s="258"/>
-      <c r="K26" s="258"/>
-      <c r="L26" s="258"/>
+      <c r="D26" s="262"/>
+      <c r="E26" s="262"/>
+      <c r="F26" s="262"/>
+      <c r="G26" s="262"/>
+      <c r="H26" s="262"/>
+      <c r="I26" s="262"/>
+      <c r="J26" s="262"/>
+      <c r="K26" s="262"/>
+      <c r="L26" s="262"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -19442,18 +19471,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="130"/>
-      <c r="C33" s="258" t="s">
+      <c r="C33" s="262" t="s">
         <v>188</v>
       </c>
-      <c r="D33" s="258"/>
-      <c r="E33" s="258"/>
-      <c r="F33" s="258"/>
-      <c r="G33" s="258"/>
-      <c r="H33" s="258"/>
-      <c r="I33" s="258"/>
-      <c r="J33" s="258"/>
-      <c r="K33" s="258"/>
-      <c r="L33" s="258"/>
+      <c r="D33" s="262"/>
+      <c r="E33" s="262"/>
+      <c r="F33" s="262"/>
+      <c r="G33" s="262"/>
+      <c r="H33" s="262"/>
+      <c r="I33" s="262"/>
+      <c r="J33" s="262"/>
+      <c r="K33" s="262"/>
+      <c r="L33" s="262"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -19637,18 +19666,18 @@
       <c r="C39" s="146"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="258" t="s">
+      <c r="C40" s="262" t="s">
         <v>191</v>
       </c>
-      <c r="D40" s="258"/>
-      <c r="E40" s="258"/>
-      <c r="F40" s="258"/>
-      <c r="G40" s="258"/>
-      <c r="H40" s="258"/>
-      <c r="I40" s="258"/>
-      <c r="J40" s="258"/>
-      <c r="K40" s="258"/>
-      <c r="L40" s="258"/>
+      <c r="D40" s="262"/>
+      <c r="E40" s="262"/>
+      <c r="F40" s="262"/>
+      <c r="G40" s="262"/>
+      <c r="H40" s="262"/>
+      <c r="I40" s="262"/>
+      <c r="J40" s="262"/>
+      <c r="K40" s="262"/>
+      <c r="L40" s="262"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -19962,60 +19991,60 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="249" t="s">
+      <c r="C2" s="253" t="s">
         <v>137</v>
       </c>
-      <c r="D2" s="249"/>
-      <c r="E2" s="249"/>
-      <c r="F2" s="249"/>
-      <c r="G2" s="261"/>
-      <c r="H2" s="262" t="s">
+      <c r="D2" s="253"/>
+      <c r="E2" s="253"/>
+      <c r="F2" s="253"/>
+      <c r="G2" s="265"/>
+      <c r="H2" s="266" t="s">
         <v>138</v>
       </c>
-      <c r="I2" s="249"/>
-      <c r="J2" s="249"/>
-      <c r="K2" s="249"/>
-      <c r="L2" s="249"/>
-      <c r="S2" s="263"/>
-      <c r="T2" s="263"/>
-      <c r="U2" s="263"/>
-      <c r="V2" s="263"/>
-      <c r="W2" s="263"/>
-      <c r="X2" s="263"/>
-      <c r="Y2" s="263"/>
-      <c r="Z2" s="263"/>
-      <c r="AA2" s="263"/>
-      <c r="AB2" s="263"/>
-      <c r="AC2" s="263"/>
+      <c r="I2" s="253"/>
+      <c r="J2" s="253"/>
+      <c r="K2" s="253"/>
+      <c r="L2" s="253"/>
+      <c r="S2" s="267"/>
+      <c r="T2" s="267"/>
+      <c r="U2" s="267"/>
+      <c r="V2" s="267"/>
+      <c r="W2" s="267"/>
+      <c r="X2" s="267"/>
+      <c r="Y2" s="267"/>
+      <c r="Z2" s="267"/>
+      <c r="AA2" s="267"/>
+      <c r="AB2" s="267"/>
+      <c r="AC2" s="267"/>
       <c r="AE2" s="130"/>
     </row>
     <row r="3" spans="1:31" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="258" t="s">
+      <c r="C4" s="262" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="258"/>
-      <c r="E4" s="258"/>
-      <c r="F4" s="258"/>
-      <c r="G4" s="258"/>
-      <c r="H4" s="258"/>
-      <c r="I4" s="258"/>
-      <c r="J4" s="258"/>
-      <c r="K4" s="258"/>
-      <c r="L4" s="258"/>
-      <c r="S4" s="263"/>
-      <c r="T4" s="263"/>
-      <c r="U4" s="263"/>
-      <c r="V4" s="263"/>
-      <c r="W4" s="263"/>
-      <c r="X4" s="263"/>
-      <c r="Y4" s="263"/>
-      <c r="Z4" s="263"/>
-      <c r="AA4" s="263"/>
-      <c r="AB4" s="263"/>
-      <c r="AC4" s="263"/>
+      <c r="D4" s="262"/>
+      <c r="E4" s="262"/>
+      <c r="F4" s="262"/>
+      <c r="G4" s="262"/>
+      <c r="H4" s="262"/>
+      <c r="I4" s="262"/>
+      <c r="J4" s="262"/>
+      <c r="K4" s="262"/>
+      <c r="L4" s="262"/>
+      <c r="S4" s="267"/>
+      <c r="T4" s="267"/>
+      <c r="U4" s="267"/>
+      <c r="V4" s="267"/>
+      <c r="W4" s="267"/>
+      <c r="X4" s="267"/>
+      <c r="Y4" s="267"/>
+      <c r="Z4" s="267"/>
+      <c r="AA4" s="267"/>
+      <c r="AB4" s="267"/>
+      <c r="AC4" s="267"/>
       <c r="AE4" s="131"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -20378,18 +20407,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="258" t="s">
+      <c r="C13" s="262" t="s">
         <v>199</v>
       </c>
-      <c r="D13" s="258"/>
-      <c r="E13" s="258"/>
-      <c r="F13" s="258"/>
-      <c r="G13" s="258"/>
-      <c r="H13" s="258"/>
-      <c r="I13" s="258"/>
-      <c r="J13" s="258"/>
-      <c r="K13" s="258"/>
-      <c r="L13" s="258"/>
+      <c r="D13" s="262"/>
+      <c r="E13" s="262"/>
+      <c r="F13" s="262"/>
+      <c r="G13" s="262"/>
+      <c r="H13" s="262"/>
+      <c r="I13" s="262"/>
+      <c r="J13" s="262"/>
+      <c r="K13" s="262"/>
+      <c r="L13" s="262"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -20482,18 +20511,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="258" t="s">
+      <c r="C18" s="262" t="s">
         <v>200</v>
       </c>
-      <c r="D18" s="258"/>
-      <c r="E18" s="258"/>
-      <c r="F18" s="258"/>
-      <c r="G18" s="258"/>
-      <c r="H18" s="258"/>
-      <c r="I18" s="258"/>
-      <c r="J18" s="258"/>
-      <c r="K18" s="258"/>
-      <c r="L18" s="258"/>
+      <c r="D18" s="262"/>
+      <c r="E18" s="262"/>
+      <c r="F18" s="262"/>
+      <c r="G18" s="262"/>
+      <c r="H18" s="262"/>
+      <c r="I18" s="262"/>
+      <c r="J18" s="262"/>
+      <c r="K18" s="262"/>
+      <c r="L18" s="262"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -20685,18 +20714,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="258" t="s">
+      <c r="C25" s="262" t="s">
         <v>311</v>
       </c>
-      <c r="D25" s="258"/>
-      <c r="E25" s="258"/>
-      <c r="F25" s="258"/>
-      <c r="G25" s="258"/>
-      <c r="H25" s="258"/>
-      <c r="I25" s="258"/>
-      <c r="J25" s="258"/>
-      <c r="K25" s="258"/>
-      <c r="L25" s="258"/>
+      <c r="D25" s="262"/>
+      <c r="E25" s="262"/>
+      <c r="F25" s="262"/>
+      <c r="G25" s="262"/>
+      <c r="H25" s="262"/>
+      <c r="I25" s="262"/>
+      <c r="J25" s="262"/>
+      <c r="K25" s="262"/>
+      <c r="L25" s="262"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -20834,18 +20863,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="258" t="s">
+      <c r="C31" s="262" t="s">
         <v>78</v>
       </c>
-      <c r="D31" s="258"/>
-      <c r="E31" s="258"/>
-      <c r="F31" s="258"/>
-      <c r="G31" s="258"/>
-      <c r="H31" s="258"/>
-      <c r="I31" s="258"/>
-      <c r="J31" s="258"/>
-      <c r="K31" s="258"/>
-      <c r="L31" s="258"/>
+      <c r="D31" s="262"/>
+      <c r="E31" s="262"/>
+      <c r="F31" s="262"/>
+      <c r="G31" s="262"/>
+      <c r="H31" s="262"/>
+      <c r="I31" s="262"/>
+      <c r="J31" s="262"/>
+      <c r="K31" s="262"/>
+      <c r="L31" s="262"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -21056,10 +21085,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="249" t="s">
+      <c r="B4" s="253" t="s">
         <v>207</v>
       </c>
-      <c r="C4" s="249"/>
+      <c r="C4" s="253"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -21076,7 +21105,7 @@
       </c>
       <c r="C6" s="154">
         <f ca="1">Overview!C5</f>
-        <v>11.68</v>
+        <v>12.6401</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21085,7 +21114,7 @@
       </c>
       <c r="C7" s="155">
         <f ca="1">C5*C6</f>
-        <v>6101106.3999999994</v>
+        <v>6602619.4355000006</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21103,7 +21132,7 @@
       </c>
       <c r="C9" s="156">
         <f ca="1">Overview!F27</f>
-        <v>4.5689999999999995E-2</v>
+        <v>4.6630000000000005E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21112,7 +21141,7 @@
       </c>
       <c r="C10" s="154">
         <f ca="1">Overview!C13</f>
-        <v>0.98140000000000005</v>
+        <v>0.92379999999999995</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21144,10 +21173,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="249" t="s">
+      <c r="B15" s="253" t="s">
         <v>214</v>
       </c>
-      <c r="C15" s="249"/>
+      <c r="C15" s="253"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -21182,7 +21211,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>8.9852999999999988E-2</v>
+        <v>8.8201000000000002E-2</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21191,7 +21220,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>8.9852999999999988E-2</v>
+        <v>8.8201000000000002E-2</v>
       </c>
     </row>
   </sheetData>
@@ -21236,60 +21265,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="249" t="s">
+      <c r="C3" s="253" t="s">
         <v>137</v>
       </c>
-      <c r="D3" s="249"/>
-      <c r="E3" s="249"/>
-      <c r="F3" s="249"/>
-      <c r="G3" s="261"/>
-      <c r="H3" s="262" t="s">
+      <c r="D3" s="253"/>
+      <c r="E3" s="253"/>
+      <c r="F3" s="253"/>
+      <c r="G3" s="265"/>
+      <c r="H3" s="266" t="s">
         <v>138</v>
       </c>
-      <c r="I3" s="249"/>
-      <c r="J3" s="249"/>
-      <c r="K3" s="249"/>
-      <c r="L3" s="249"/>
-      <c r="P3" s="263"/>
-      <c r="Q3" s="263"/>
-      <c r="R3" s="263"/>
-      <c r="S3" s="263"/>
-      <c r="T3" s="263"/>
-      <c r="U3" s="263"/>
-      <c r="V3" s="263"/>
-      <c r="W3" s="263"/>
-      <c r="X3" s="263"/>
-      <c r="Y3" s="263"/>
-      <c r="Z3" s="263"/>
+      <c r="I3" s="253"/>
+      <c r="J3" s="253"/>
+      <c r="K3" s="253"/>
+      <c r="L3" s="253"/>
+      <c r="P3" s="267"/>
+      <c r="Q3" s="267"/>
+      <c r="R3" s="267"/>
+      <c r="S3" s="267"/>
+      <c r="T3" s="267"/>
+      <c r="U3" s="267"/>
+      <c r="V3" s="267"/>
+      <c r="W3" s="267"/>
+      <c r="X3" s="267"/>
+      <c r="Y3" s="267"/>
+      <c r="Z3" s="267"/>
       <c r="AB3" s="130"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="88"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="258" t="s">
+      <c r="C5" s="262" t="s">
         <v>221</v>
       </c>
-      <c r="D5" s="258"/>
-      <c r="E5" s="258"/>
-      <c r="F5" s="258"/>
-      <c r="G5" s="258"/>
-      <c r="H5" s="258"/>
-      <c r="I5" s="258"/>
-      <c r="J5" s="258"/>
-      <c r="K5" s="258"/>
-      <c r="L5" s="258"/>
-      <c r="P5" s="263"/>
-      <c r="Q5" s="263"/>
-      <c r="R5" s="263"/>
-      <c r="S5" s="263"/>
-      <c r="T5" s="263"/>
-      <c r="U5" s="263"/>
-      <c r="V5" s="263"/>
-      <c r="W5" s="263"/>
-      <c r="X5" s="263"/>
-      <c r="Y5" s="263"/>
-      <c r="Z5" s="263"/>
+      <c r="D5" s="262"/>
+      <c r="E5" s="262"/>
+      <c r="F5" s="262"/>
+      <c r="G5" s="262"/>
+      <c r="H5" s="262"/>
+      <c r="I5" s="262"/>
+      <c r="J5" s="262"/>
+      <c r="K5" s="262"/>
+      <c r="L5" s="262"/>
+      <c r="P5" s="267"/>
+      <c r="Q5" s="267"/>
+      <c r="R5" s="267"/>
+      <c r="S5" s="267"/>
+      <c r="T5" s="267"/>
+      <c r="U5" s="267"/>
+      <c r="V5" s="267"/>
+      <c r="W5" s="267"/>
+      <c r="X5" s="267"/>
+      <c r="Y5" s="267"/>
+      <c r="Z5" s="267"/>
       <c r="AB5" s="131"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -21535,10 +21564,10 @@
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="249" t="s">
+      <c r="B13" s="253" t="s">
         <v>225</v>
       </c>
-      <c r="C13" s="249"/>
+      <c r="C13" s="253"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -21558,10 +21587,10 @@
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="249" t="s">
+      <c r="B18" s="253" t="s">
         <v>227</v>
       </c>
-      <c r="C18" s="249"/>
+      <c r="C18" s="253"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -21675,37 +21704,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="249" t="s">
+      <c r="C2" s="253" t="s">
         <v>137</v>
       </c>
-      <c r="D2" s="249"/>
-      <c r="E2" s="249"/>
-      <c r="F2" s="249"/>
-      <c r="G2" s="261"/>
-      <c r="H2" s="262" t="s">
+      <c r="D2" s="253"/>
+      <c r="E2" s="253"/>
+      <c r="F2" s="253"/>
+      <c r="G2" s="265"/>
+      <c r="H2" s="266" t="s">
         <v>138</v>
       </c>
-      <c r="I2" s="249"/>
-      <c r="J2" s="249"/>
-      <c r="K2" s="249"/>
-      <c r="L2" s="249"/>
+      <c r="I2" s="253"/>
+      <c r="J2" s="253"/>
+      <c r="K2" s="253"/>
+      <c r="L2" s="253"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="258" t="s">
+      <c r="C4" s="262" t="s">
         <v>235</v>
       </c>
-      <c r="D4" s="258"/>
-      <c r="E4" s="258"/>
-      <c r="F4" s="258"/>
-      <c r="G4" s="258"/>
-      <c r="H4" s="258"/>
-      <c r="I4" s="258"/>
-      <c r="J4" s="258"/>
-      <c r="K4" s="258"/>
-      <c r="L4" s="258"/>
+      <c r="D4" s="262"/>
+      <c r="E4" s="262"/>
+      <c r="F4" s="262"/>
+      <c r="G4" s="262"/>
+      <c r="H4" s="262"/>
+      <c r="I4" s="262"/>
+      <c r="J4" s="262"/>
+      <c r="K4" s="262"/>
+      <c r="L4" s="262"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -21894,18 +21923,18 @@
       <c r="N9" s="93"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C10" s="258" t="s">
+      <c r="C10" s="262" t="s">
         <v>146</v>
       </c>
-      <c r="D10" s="258"/>
-      <c r="E10" s="258"/>
-      <c r="F10" s="258"/>
-      <c r="G10" s="258"/>
-      <c r="H10" s="258"/>
-      <c r="I10" s="258"/>
-      <c r="J10" s="258"/>
-      <c r="K10" s="258"/>
-      <c r="L10" s="258"/>
+      <c r="D10" s="262"/>
+      <c r="E10" s="262"/>
+      <c r="F10" s="262"/>
+      <c r="G10" s="262"/>
+      <c r="H10" s="262"/>
+      <c r="I10" s="262"/>
+      <c r="J10" s="262"/>
+      <c r="K10" s="262"/>
+      <c r="L10" s="262"/>
       <c r="N10" s="93"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -22099,18 +22128,18 @@
       <c r="N15" s="93"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C16" s="258" t="s">
+      <c r="C16" s="262" t="s">
         <v>237</v>
       </c>
-      <c r="D16" s="258"/>
-      <c r="E16" s="258"/>
-      <c r="F16" s="258"/>
-      <c r="G16" s="258"/>
-      <c r="H16" s="258"/>
-      <c r="I16" s="258"/>
-      <c r="J16" s="258"/>
-      <c r="K16" s="258"/>
-      <c r="L16" s="258"/>
+      <c r="D16" s="262"/>
+      <c r="E16" s="262"/>
+      <c r="F16" s="262"/>
+      <c r="G16" s="262"/>
+      <c r="H16" s="262"/>
+      <c r="I16" s="262"/>
+      <c r="J16" s="262"/>
+      <c r="K16" s="262"/>
+      <c r="L16" s="262"/>
       <c r="N16" s="93"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
@@ -22244,18 +22273,18 @@
       <c r="N20" s="93"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C21" s="258" t="s">
+      <c r="C21" s="262" t="s">
         <v>240</v>
       </c>
-      <c r="D21" s="258"/>
-      <c r="E21" s="258"/>
-      <c r="F21" s="258"/>
-      <c r="G21" s="258"/>
-      <c r="H21" s="258"/>
-      <c r="I21" s="258"/>
-      <c r="J21" s="258"/>
-      <c r="K21" s="258"/>
-      <c r="L21" s="258"/>
+      <c r="D21" s="262"/>
+      <c r="E21" s="262"/>
+      <c r="F21" s="262"/>
+      <c r="G21" s="262"/>
+      <c r="H21" s="262"/>
+      <c r="I21" s="262"/>
+      <c r="J21" s="262"/>
+      <c r="K21" s="262"/>
+      <c r="L21" s="262"/>
       <c r="N21" s="93"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
@@ -22339,18 +22368,18 @@
       <c r="N25" s="93"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C26" s="258" t="s">
+      <c r="C26" s="262" t="s">
         <v>241</v>
       </c>
-      <c r="D26" s="258"/>
-      <c r="E26" s="258"/>
-      <c r="F26" s="258"/>
-      <c r="G26" s="258"/>
-      <c r="H26" s="258"/>
-      <c r="I26" s="258"/>
-      <c r="J26" s="258"/>
-      <c r="K26" s="258"/>
-      <c r="L26" s="258"/>
+      <c r="D26" s="262"/>
+      <c r="E26" s="262"/>
+      <c r="F26" s="262"/>
+      <c r="G26" s="262"/>
+      <c r="H26" s="262"/>
+      <c r="I26" s="262"/>
+      <c r="J26" s="262"/>
+      <c r="K26" s="262"/>
+      <c r="L26" s="262"/>
       <c r="N26" s="93"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
@@ -22620,10 +22649,10 @@
       <c r="N36" s="93"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="249" t="s">
+      <c r="B37" s="253" t="s">
         <v>246</v>
       </c>
-      <c r="C37" s="249"/>
+      <c r="C37" s="253"/>
       <c r="N37" s="93"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -22716,10 +22745,10 @@
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="249" t="s">
+      <c r="B49" s="253" t="s">
         <v>251</v>
       </c>
-      <c r="C49" s="249"/>
+      <c r="C49" s="253"/>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
@@ -22775,10 +22804,10 @@
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="249" t="s">
+      <c r="B57" s="253" t="s">
         <v>375</v>
       </c>
-      <c r="C57" s="249"/>
+      <c r="C57" s="253"/>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
@@ -22918,10 +22947,10 @@
       <c r="N3" s="93"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="249" t="s">
+      <c r="B4" s="253" t="s">
         <v>256</v>
       </c>
-      <c r="C4" s="249"/>
+      <c r="C4" s="253"/>
       <c r="N4" s="93"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -22975,7 +23004,7 @@
       </c>
       <c r="C10" s="154">
         <f ca="1">Overview!C5</f>
-        <v>11.68</v>
+        <v>12.6401</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -22984,7 +23013,7 @@
       </c>
       <c r="C11" s="175">
         <f ca="1">(C9-C10)/C10</f>
-        <v>0.10092872539603272</v>
+        <v>1.7305837186862565E-2</v>
       </c>
     </row>
   </sheetData>
@@ -23040,37 +23069,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="249" t="s">
+      <c r="C2" s="253" t="s">
         <v>137</v>
       </c>
-      <c r="D2" s="249"/>
-      <c r="E2" s="249"/>
-      <c r="F2" s="249"/>
-      <c r="G2" s="261"/>
-      <c r="H2" s="262" t="s">
+      <c r="D2" s="253"/>
+      <c r="E2" s="253"/>
+      <c r="F2" s="253"/>
+      <c r="G2" s="265"/>
+      <c r="H2" s="266" t="s">
         <v>138</v>
       </c>
-      <c r="I2" s="249"/>
-      <c r="J2" s="249"/>
-      <c r="K2" s="249"/>
-      <c r="L2" s="249"/>
+      <c r="I2" s="253"/>
+      <c r="J2" s="253"/>
+      <c r="K2" s="253"/>
+      <c r="L2" s="253"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="88"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="258" t="s">
+      <c r="C4" s="262" t="s">
         <v>235</v>
       </c>
-      <c r="D4" s="258"/>
-      <c r="E4" s="258"/>
-      <c r="F4" s="258"/>
-      <c r="G4" s="258"/>
-      <c r="H4" s="258"/>
-      <c r="I4" s="258"/>
-      <c r="J4" s="258"/>
-      <c r="K4" s="258"/>
-      <c r="L4" s="258"/>
+      <c r="D4" s="262"/>
+      <c r="E4" s="262"/>
+      <c r="F4" s="262"/>
+      <c r="G4" s="262"/>
+      <c r="H4" s="262"/>
+      <c r="I4" s="262"/>
+      <c r="J4" s="262"/>
+      <c r="K4" s="262"/>
+      <c r="L4" s="262"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -23121,23 +23150,23 @@
       <c r="B6" s="16" t="s">
         <v>292</v>
       </c>
-      <c r="C6" s="267">
+      <c r="C6" s="249">
         <f>Statement!M26</f>
         <v>-1.1599999999999999</v>
       </c>
-      <c r="D6" s="267">
+      <c r="D6" s="249">
         <f>Statement!N26</f>
         <v>-0.6</v>
       </c>
-      <c r="E6" s="267">
+      <c r="E6" s="249">
         <f>Statement!O26</f>
         <v>-0.16</v>
       </c>
-      <c r="F6" s="267">
+      <c r="F6" s="249">
         <f>Statement!P26</f>
         <v>-0.13</v>
       </c>
-      <c r="G6" s="268">
+      <c r="G6" s="250">
         <f>Statement!Q26</f>
         <v>0.52</v>
       </c>
@@ -23152,23 +23181,23 @@
       <c r="B7" s="16" t="s">
         <v>421</v>
       </c>
-      <c r="C7" s="267">
+      <c r="C7" s="249">
         <f>Statement!M82</f>
         <v>0</v>
       </c>
-      <c r="D7" s="267">
+      <c r="D7" s="249">
         <f>Statement!N82</f>
         <v>0</v>
       </c>
-      <c r="E7" s="267">
+      <c r="E7" s="249">
         <f>Statement!O82</f>
         <v>0</v>
       </c>
-      <c r="F7" s="267">
+      <c r="F7" s="249">
         <f>Statement!P82</f>
         <v>0</v>
       </c>
-      <c r="G7" s="268">
+      <c r="G7" s="250">
         <f>Statement!Q82</f>
         <v>0</v>
       </c>
@@ -23183,18 +23212,18 @@
       <c r="N8" s="93"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="258" t="s">
+      <c r="C9" s="262" t="s">
         <v>146</v>
       </c>
-      <c r="D9" s="258"/>
-      <c r="E9" s="258"/>
-      <c r="F9" s="258"/>
-      <c r="G9" s="258"/>
-      <c r="H9" s="258"/>
-      <c r="I9" s="258"/>
-      <c r="J9" s="258"/>
-      <c r="K9" s="258"/>
-      <c r="L9" s="258"/>
+      <c r="D9" s="262"/>
+      <c r="E9" s="262"/>
+      <c r="F9" s="262"/>
+      <c r="G9" s="262"/>
+      <c r="H9" s="262"/>
+      <c r="I9" s="262"/>
+      <c r="J9" s="262"/>
+      <c r="K9" s="262"/>
+      <c r="L9" s="262"/>
       <c r="N9" s="93"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -23315,18 +23344,18 @@
       <c r="N13" s="93"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="258" t="s">
+      <c r="C14" s="262" t="s">
         <v>422</v>
       </c>
-      <c r="D14" s="258"/>
-      <c r="E14" s="258"/>
-      <c r="F14" s="258"/>
-      <c r="G14" s="258"/>
-      <c r="H14" s="258"/>
-      <c r="I14" s="258"/>
-      <c r="J14" s="258"/>
-      <c r="K14" s="258"/>
-      <c r="L14" s="258"/>
+      <c r="D14" s="262"/>
+      <c r="E14" s="262"/>
+      <c r="F14" s="262"/>
+      <c r="G14" s="262"/>
+      <c r="H14" s="262"/>
+      <c r="I14" s="262"/>
+      <c r="J14" s="262"/>
+      <c r="K14" s="262"/>
+      <c r="L14" s="262"/>
       <c r="N14" s="93"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -23416,10 +23445,10 @@
       <c r="N19" s="93"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="249" t="s">
+      <c r="B20" s="253" t="s">
         <v>424</v>
       </c>
-      <c r="C20" s="249"/>
+      <c r="C20" s="253"/>
       <c r="N20" s="93"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -23435,7 +23464,7 @@
       <c r="B22" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="C22" s="269">
+      <c r="C22" s="251">
         <v>0</v>
       </c>
     </row>
@@ -23443,7 +23472,7 @@
       <c r="B23" s="39" t="s">
         <v>427</v>
       </c>
-      <c r="C23" s="270">
+      <c r="C23" s="252">
         <f>C21*(1+C22)</f>
         <v>0</v>
       </c>
@@ -23461,7 +23490,7 @@
       <c r="B25" s="39" t="s">
         <v>428</v>
       </c>
-      <c r="C25" s="269">
+      <c r="C25" s="251">
         <v>0</v>
       </c>
     </row>
@@ -23476,12 +23505,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="B20:C20"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C9:L9"/>
     <mergeCell ref="C14:L14"/>
-    <mergeCell ref="B20:C20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -23520,60 +23549,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="249" t="s">
+      <c r="C3" s="253" t="s">
         <v>137</v>
       </c>
-      <c r="D3" s="249"/>
-      <c r="E3" s="249"/>
-      <c r="F3" s="249"/>
-      <c r="G3" s="261"/>
-      <c r="H3" s="262" t="s">
+      <c r="D3" s="253"/>
+      <c r="E3" s="253"/>
+      <c r="F3" s="253"/>
+      <c r="G3" s="265"/>
+      <c r="H3" s="266" t="s">
         <v>138</v>
       </c>
-      <c r="I3" s="249"/>
-      <c r="J3" s="249"/>
-      <c r="K3" s="249"/>
-      <c r="L3" s="249"/>
-      <c r="P3" s="263"/>
-      <c r="Q3" s="263"/>
-      <c r="R3" s="263"/>
-      <c r="S3" s="263"/>
-      <c r="T3" s="263"/>
-      <c r="U3" s="263"/>
-      <c r="V3" s="263"/>
-      <c r="W3" s="263"/>
-      <c r="X3" s="263"/>
-      <c r="Y3" s="263"/>
-      <c r="Z3" s="263"/>
+      <c r="I3" s="253"/>
+      <c r="J3" s="253"/>
+      <c r="K3" s="253"/>
+      <c r="L3" s="253"/>
+      <c r="P3" s="267"/>
+      <c r="Q3" s="267"/>
+      <c r="R3" s="267"/>
+      <c r="S3" s="267"/>
+      <c r="T3" s="267"/>
+      <c r="U3" s="267"/>
+      <c r="V3" s="267"/>
+      <c r="W3" s="267"/>
+      <c r="X3" s="267"/>
+      <c r="Y3" s="267"/>
+      <c r="Z3" s="267"/>
       <c r="AB3" s="130"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="88"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="258" t="s">
+      <c r="C5" s="262" t="s">
         <v>221</v>
       </c>
-      <c r="D5" s="258"/>
-      <c r="E5" s="258"/>
-      <c r="F5" s="258"/>
-      <c r="G5" s="258"/>
-      <c r="H5" s="258"/>
-      <c r="I5" s="258"/>
-      <c r="J5" s="258"/>
-      <c r="K5" s="258"/>
-      <c r="L5" s="258"/>
-      <c r="P5" s="263"/>
-      <c r="Q5" s="263"/>
-      <c r="R5" s="263"/>
-      <c r="S5" s="263"/>
-      <c r="T5" s="263"/>
-      <c r="U5" s="263"/>
-      <c r="V5" s="263"/>
-      <c r="W5" s="263"/>
-      <c r="X5" s="263"/>
-      <c r="Y5" s="263"/>
-      <c r="Z5" s="263"/>
+      <c r="D5" s="262"/>
+      <c r="E5" s="262"/>
+      <c r="F5" s="262"/>
+      <c r="G5" s="262"/>
+      <c r="H5" s="262"/>
+      <c r="I5" s="262"/>
+      <c r="J5" s="262"/>
+      <c r="K5" s="262"/>
+      <c r="L5" s="262"/>
+      <c r="P5" s="267"/>
+      <c r="Q5" s="267"/>
+      <c r="R5" s="267"/>
+      <c r="S5" s="267"/>
+      <c r="T5" s="267"/>
+      <c r="U5" s="267"/>
+      <c r="V5" s="267"/>
+      <c r="W5" s="267"/>
+      <c r="X5" s="267"/>
+      <c r="Y5" s="267"/>
+      <c r="Z5" s="267"/>
       <c r="AB5" s="131"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -23801,10 +23830,10 @@
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="264" t="s">
+      <c r="B14" s="268" t="s">
         <v>264</v>
       </c>
-      <c r="C14" s="265"/>
+      <c r="C14" s="269"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="176" t="s">
@@ -23812,7 +23841,7 @@
       </c>
       <c r="C15" s="177">
         <f ca="1">Overview!C5</f>
-        <v>11.68</v>
+        <v>12.6401</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -23831,20 +23860,20 @@
       <c r="C17" s="179">
         <v>1.2</v>
       </c>
-      <c r="E17" s="266" t="s">
+      <c r="E17" s="270" t="s">
         <v>267</v>
       </c>
-      <c r="F17" s="266"/>
-      <c r="G17" s="266"/>
-      <c r="H17" s="266"/>
-      <c r="I17" s="266"/>
+      <c r="F17" s="270"/>
+      <c r="G17" s="270"/>
+      <c r="H17" s="270"/>
+      <c r="I17" s="270"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="264" t="s">
+      <c r="B19" s="268" t="s">
         <v>225</v>
       </c>
-      <c r="C19" s="265"/>
+      <c r="C19" s="269"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="180" t="s">
@@ -23878,7 +23907,7 @@
       </c>
       <c r="C23" s="182">
         <f ca="1">C15*C22</f>
-        <v>6051653.2800000003</v>
+        <v>6549101.2521000002</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -23905,15 +23934,15 @@
       </c>
       <c r="C26" s="183">
         <f ca="1">C23+C25-C24</f>
-        <v>4635907.28</v>
+        <v>5133355.2521000002</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="264" t="s">
+      <c r="B28" s="268" t="s">
         <v>227</v>
       </c>
-      <c r="C28" s="265"/>
+      <c r="C28" s="269"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="180" t="s">
@@ -23988,18 +24017,18 @@
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C39" s="258" t="s">
+      <c r="C39" s="262" t="s">
         <v>270</v>
       </c>
-      <c r="D39" s="258"/>
-      <c r="E39" s="258"/>
-      <c r="F39" s="258"/>
-      <c r="G39" s="258"/>
-      <c r="H39" s="258"/>
-      <c r="I39" s="258"/>
-      <c r="J39" s="258"/>
-      <c r="K39" s="258"/>
-      <c r="L39" s="258"/>
+      <c r="D39" s="262"/>
+      <c r="E39" s="262"/>
+      <c r="F39" s="262"/>
+      <c r="G39" s="262"/>
+      <c r="H39" s="262"/>
+      <c r="I39" s="262"/>
+      <c r="J39" s="262"/>
+      <c r="K39" s="262"/>
+      <c r="L39" s="262"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="12">
@@ -31044,17 +31073,33 @@
       <c r="Q116" s="63">
         <v>12.59</v>
       </c>
-      <c r="T116" s="68"/>
-      <c r="U116" s="68"/>
-      <c r="V116" s="68"/>
-      <c r="W116" s="68"/>
-      <c r="X116" s="68"/>
-      <c r="Y116" s="68"/>
-      <c r="Z116" s="68"/>
-      <c r="AA116" s="68"/>
+      <c r="T116" s="63">
+        <v>12.17</v>
+      </c>
+      <c r="U116" s="63">
+        <v>12.35</v>
+      </c>
+      <c r="V116" s="63">
+        <v>14.58</v>
+      </c>
+      <c r="W116" s="63">
+        <v>11.94</v>
+      </c>
+      <c r="X116" s="63">
+        <v>11.75</v>
+      </c>
+      <c r="Y116" s="63">
+        <v>15.86</v>
+      </c>
+      <c r="Z116" s="63">
+        <v>12.59</v>
+      </c>
+      <c r="AA116" s="63">
+        <v>10.3</v>
+      </c>
       <c r="AC116" s="63">
         <f ca="1">Overview!C5</f>
-        <v>11.68</v>
+        <v>12.6401</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -31091,17 +31136,41 @@
         <f>Q116/Q85</f>
         <v>12.59</v>
       </c>
-      <c r="T117" s="68"/>
-      <c r="U117" s="68"/>
-      <c r="V117" s="68"/>
-      <c r="W117" s="68"/>
-      <c r="X117" s="68"/>
-      <c r="Y117" s="68"/>
-      <c r="Z117" s="68"/>
-      <c r="AA117" s="68"/>
+      <c r="T117" s="65">
+        <f t="shared" ref="T117:AA117" si="75">T116/T85</f>
+        <v>12.17</v>
+      </c>
+      <c r="U117" s="65">
+        <f t="shared" si="75"/>
+        <v>12.35</v>
+      </c>
+      <c r="V117" s="65">
+        <f t="shared" si="75"/>
+        <v>14.58</v>
+      </c>
+      <c r="W117" s="65">
+        <f t="shared" si="75"/>
+        <v>11.94</v>
+      </c>
+      <c r="X117" s="65">
+        <f t="shared" si="75"/>
+        <v>11.75</v>
+      </c>
+      <c r="Y117" s="65">
+        <f t="shared" si="75"/>
+        <v>15.86</v>
+      </c>
+      <c r="Z117" s="65">
+        <f t="shared" si="75"/>
+        <v>12.59</v>
+      </c>
+      <c r="AA117" s="65">
+        <f t="shared" si="75"/>
+        <v>10.3</v>
+      </c>
       <c r="AC117" s="65">
         <f ca="1">AC116/AC85</f>
-        <v>11.68</v>
+        <v>12.6401</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -31215,19 +31284,19 @@
         <v>121</v>
       </c>
       <c r="M123" s="76">
-        <f t="shared" ref="M123:P123" si="75">M121*M122</f>
+        <f t="shared" ref="M123:P123" si="76">M121*M122</f>
         <v>-0.20431339773367801</v>
       </c>
       <c r="N123" s="76">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>-0.12004653397221271</v>
       </c>
       <c r="O123" s="76">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>-3.0419750111515053E-2</v>
       </c>
       <c r="P123" s="76">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>-2.5719740199003933E-2</v>
       </c>
       <c r="Q123" s="76">
@@ -31289,19 +31358,19 @@
         <v>123</v>
       </c>
       <c r="M125" s="76">
-        <f t="shared" ref="M125:P125" si="76">M123*M124</f>
+        <f t="shared" ref="M125:P125" si="77">M123*M124</f>
         <v>-0.27346966596372269</v>
       </c>
       <c r="N125" s="76">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>-0.17100259457815453</v>
       </c>
       <c r="O125" s="76">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>-4.4582300405631825E-2</v>
       </c>
       <c r="P125" s="76">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>-3.9926057639067224E-2</v>
       </c>
       <c r="Q125" s="76">
@@ -31463,35 +31532,35 @@
       <c r="P131" s="49"/>
       <c r="Q131" s="49"/>
       <c r="T131" s="25">
-        <f t="shared" ref="T131:AA131" si="77">U5</f>
+        <f t="shared" ref="T131:AA131" si="78">U5</f>
         <v>354653</v>
       </c>
       <c r="U131" s="25">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>423646</v>
       </c>
       <c r="V131" s="25">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>356624</v>
       </c>
       <c r="W131" s="25">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>361728</v>
       </c>
       <c r="X131" s="25">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>411113</v>
       </c>
       <c r="Y131" s="25">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>481107</v>
       </c>
       <c r="Z131" s="25">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>418382</v>
       </c>
       <c r="AA131" s="25">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="AC131" s="49"/>
@@ -31516,31 +31585,31 @@
       <c r="P132" s="49"/>
       <c r="Q132" s="49"/>
       <c r="T132" s="246" t="str">
-        <f t="shared" ref="T132:Z132" si="78">IF(T131&gt;T130, "BEAT", IF(T131&lt;T129, "MISSED", "MET"))</f>
+        <f t="shared" ref="T132:Z132" si="79">IF(T131&gt;T130, "BEAT", IF(T131&lt;T129, "MISSED", "MET"))</f>
         <v>BEAT</v>
       </c>
       <c r="U132" s="246" t="str">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>MET</v>
       </c>
       <c r="V132" s="246" t="str">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>BEAT</v>
       </c>
       <c r="W132" s="246" t="str">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>BEAT</v>
       </c>
       <c r="X132" s="246" t="str">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>BEAT</v>
       </c>
       <c r="Y132" s="246" t="str">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>BEAT</v>
       </c>
       <c r="Z132" s="246" t="str">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>BEAT</v>
       </c>
       <c r="AA132" s="246" t="str">
@@ -31659,35 +31728,35 @@
       <c r="P135" s="49"/>
       <c r="Q135" s="49"/>
       <c r="T135" s="25">
-        <f t="shared" ref="T135:AA135" si="79">U213</f>
+        <f t="shared" ref="T135:AA135" si="80">U213</f>
         <v>1606561</v>
       </c>
       <c r="U135" s="25">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>1666136</v>
       </c>
       <c r="V135" s="25">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>1692683</v>
       </c>
       <c r="W135" s="25">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>1723401</v>
       </c>
       <c r="X135" s="25">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>1782384</v>
       </c>
       <c r="Y135" s="25">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>1852567</v>
       </c>
       <c r="Z135" s="25">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>1901211</v>
       </c>
       <c r="AA135" s="25">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="AC135" s="49"/>
@@ -31712,31 +31781,31 @@
       <c r="P136" s="49"/>
       <c r="Q136" s="49"/>
       <c r="T136" s="246" t="str">
-        <f t="shared" ref="T136:Z136" si="80">IF(T135&gt;T134, "BEAT", IF(T135&lt;T133, "MISSED", "MET"))</f>
+        <f t="shared" ref="T136:Z136" si="81">IF(T135&gt;T134, "BEAT", IF(T135&lt;T133, "MISSED", "MET"))</f>
         <v>BEAT</v>
       </c>
       <c r="U136" s="246" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>MISSED</v>
       </c>
       <c r="V136" s="246" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>BEAT</v>
       </c>
       <c r="W136" s="246" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>BEAT</v>
       </c>
       <c r="X136" s="246" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>BEAT</v>
       </c>
       <c r="Y136" s="246" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>BEAT</v>
       </c>
       <c r="Z136" s="246" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>BEAT</v>
       </c>
       <c r="AA136" s="246" t="str">
@@ -31829,55 +31898,55 @@
         <v>180</v>
       </c>
       <c r="M141" s="139">
-        <f t="shared" ref="M141:Q142" si="81">M30/M5*365</f>
+        <f t="shared" ref="M141:Q142" si="82">M30/M5*365</f>
         <v>133.69421979440784</v>
       </c>
       <c r="N141" s="139">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>152.91140215061483</v>
       </c>
       <c r="O141" s="139">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>145.23661159324561</v>
       </c>
       <c r="P141" s="139">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>137.8303503480538</v>
       </c>
       <c r="Q141" s="139">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>131.6037563052133</v>
       </c>
       <c r="T141" s="139">
-        <f t="shared" ref="T141:AA141" si="82">T30/T5*90</f>
+        <f t="shared" ref="T141:AA141" si="83">T30/T5*90</f>
         <v>104.95764467056439</v>
       </c>
       <c r="U141" s="139">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>113.19501033404484</v>
       </c>
       <c r="V141" s="139">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>114.68995340449337</v>
       </c>
       <c r="W141" s="139">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>93.317359459823237</v>
       </c>
       <c r="X141" s="139">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>96.344546178343947</v>
       </c>
       <c r="Y141" s="139">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>108.60342533561332</v>
       </c>
       <c r="Z141" s="139">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>108.63165574394054</v>
       </c>
       <c r="AA141" s="139">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>64.534109976050601</v>
       </c>
       <c r="AC141" s="139">
@@ -31890,55 +31959,55 @@
         <v>181</v>
       </c>
       <c r="M142" s="139">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="N142" s="139">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="O142" s="139">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="P142" s="139">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="Q142" s="139">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="T142" s="139">
-        <f t="shared" ref="T142:AA142" si="83">T31/T6*365</f>
+        <f t="shared" ref="T142:AA142" si="84">T31/T6*365</f>
         <v>0</v>
       </c>
       <c r="U142" s="139">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="V142" s="139">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="W142" s="139">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="X142" s="139">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="Y142" s="139">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="Z142" s="139">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="AA142" s="139">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="AC142" s="139">
@@ -31971,35 +32040,35 @@
         <v>13.686287751306349</v>
       </c>
       <c r="T143" s="139">
-        <f t="shared" ref="T143:AA143" si="84">T38/T6*90</f>
+        <f t="shared" ref="T143:AA143" si="85">T38/T6*90</f>
         <v>14.085596967782692</v>
       </c>
       <c r="U143" s="139">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>26.007872904348915</v>
       </c>
       <c r="V143" s="139">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>46.270493073418663</v>
       </c>
       <c r="W143" s="139">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>23.797704245423365</v>
       </c>
       <c r="X143" s="139">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>27.599720410065238</v>
       </c>
       <c r="Y143" s="139">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>18.67697494623031</v>
       </c>
       <c r="Z143" s="139">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>12.368837492391966</v>
       </c>
       <c r="AA143" s="139">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>23.046355033277873</v>
       </c>
       <c r="AC143" s="139">
@@ -32016,55 +32085,55 @@
         <v>108.80510521971044</v>
       </c>
       <c r="N144" s="139">
-        <f t="shared" ref="N144:Q144" si="85">N141+N142-N143</f>
+        <f t="shared" ref="N144:Q144" si="86">N141+N142-N143</f>
         <v>134.88753669027304</v>
       </c>
       <c r="O144" s="139">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>138.81496340313109</v>
       </c>
       <c r="P144" s="139">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>88.790616321440268</v>
       </c>
       <c r="Q144" s="139">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>117.91746855390694</v>
       </c>
       <c r="T144" s="139">
-        <f t="shared" ref="T144" si="86">T141+T142-T143</f>
+        <f t="shared" ref="T144" si="87">T141+T142-T143</f>
         <v>90.8720477027817</v>
       </c>
       <c r="U144" s="139">
-        <f t="shared" ref="U144" si="87">U141+U142-U143</f>
+        <f t="shared" ref="U144" si="88">U141+U142-U143</f>
         <v>87.187137429695923</v>
       </c>
       <c r="V144" s="139">
-        <f t="shared" ref="V144" si="88">V141+V142-V143</f>
+        <f t="shared" ref="V144" si="89">V141+V142-V143</f>
         <v>68.419460331074703</v>
       </c>
       <c r="W144" s="139">
-        <f t="shared" ref="W144" si="89">W141+W142-W143</f>
+        <f t="shared" ref="W144" si="90">W141+W142-W143</f>
         <v>69.519655214399876</v>
       </c>
       <c r="X144" s="139">
-        <f t="shared" ref="X144" si="90">X141+X142-X143</f>
+        <f t="shared" ref="X144" si="91">X141+X142-X143</f>
         <v>68.744825768278702</v>
       </c>
       <c r="Y144" s="139">
-        <f t="shared" ref="Y144" si="91">Y141+Y142-Y143</f>
+        <f t="shared" ref="Y144" si="92">Y141+Y142-Y143</f>
         <v>89.926450389383007</v>
       </c>
       <c r="Z144" s="139">
-        <f t="shared" ref="Z144:AA144" si="92">Z141+Z142-Z143</f>
+        <f t="shared" ref="Z144:AA144" si="93">Z141+Z142-Z143</f>
         <v>96.26281825154858</v>
       </c>
       <c r="AA144" s="139">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>41.487754942772725</v>
       </c>
       <c r="AC144" s="139">
-        <f t="shared" ref="AC144" si="93">AC141+AC142-AC143</f>
+        <f t="shared" ref="AC144" si="94">AC141+AC142-AC143</f>
         <v>40.164814474593925</v>
       </c>
     </row>
@@ -32093,35 +32162,35 @@
         <v>0</v>
       </c>
       <c r="T145" s="139">
-        <f t="shared" ref="T145:AA145" si="94">T108/T49</f>
+        <f t="shared" ref="T145:AA145" si="95">T108/T49</f>
         <v>0</v>
       </c>
       <c r="U145" s="139">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="V145" s="139">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="W145" s="139">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="X145" s="139">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="Y145" s="139">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="Z145" s="139">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="AA145" s="139">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="AC145" s="139">
@@ -32154,35 +32223,35 @@
         <v>-0.81123909829457308</v>
       </c>
       <c r="T146" s="200">
-        <f t="shared" ref="T146:AA146" si="95">(T108-T107)/T49</f>
+        <f t="shared" ref="T146:AA146" si="96">(T108-T107)/T49</f>
         <v>-0.95080282790888426</v>
       </c>
       <c r="U146" s="200">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>-0.92585537389316019</v>
       </c>
       <c r="V146" s="200">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>-0.93383166410403939</v>
       </c>
       <c r="W146" s="200">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>-0.93702475358574611</v>
       </c>
       <c r="X146" s="200">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>-0.91411133917631171</v>
       </c>
       <c r="Y146" s="200">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>-0.78966100787845062</v>
       </c>
       <c r="Z146" s="200">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>-0.81123909829457308</v>
       </c>
       <c r="AA146" s="200">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>-0.74396849127545694</v>
       </c>
       <c r="AC146" s="200">
@@ -32215,35 +32284,35 @@
         <v>2.5073153653043936</v>
       </c>
       <c r="T147" s="139">
-        <f t="shared" ref="T147:AA147" si="96">(T107+T30)/T40</f>
+        <f t="shared" ref="T147:AA147" si="97">(T107+T30)/T40</f>
         <v>3.3394102478565317</v>
       </c>
       <c r="U147" s="139">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>2.9469051997705158</v>
       </c>
       <c r="V147" s="139">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>2.833196064687328</v>
       </c>
       <c r="W147" s="139">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>2.7397114268432543</v>
       </c>
       <c r="X147" s="139">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>2.5864328692324254</v>
       </c>
       <c r="Y147" s="139">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>2.5559617091416253</v>
       </c>
       <c r="Z147" s="139">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>2.5073153653043936</v>
       </c>
       <c r="AA147" s="139">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>2.063021693804965</v>
       </c>
       <c r="AC147" s="139">
@@ -32276,35 +32345,35 @@
         <v>2.4783388537733191</v>
       </c>
       <c r="T148" s="139">
-        <f t="shared" ref="T148:AA148" si="97">T32/T40</f>
+        <f t="shared" ref="T148:AA148" si="98">T32/T40</f>
         <v>3.5957679252114221</v>
       </c>
       <c r="U148" s="139">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>3.129493165083332</v>
       </c>
       <c r="V148" s="139">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>2.9271504030441093</v>
       </c>
       <c r="W148" s="139">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>2.9470125037192663</v>
       </c>
       <c r="X148" s="139">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>2.7501208666647705</v>
       </c>
       <c r="Y148" s="139">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>2.6541688855077976</v>
       </c>
       <c r="Z148" s="139">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>2.4783388537733191</v>
       </c>
       <c r="AA148" s="139">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>2.3066495444084523</v>
       </c>
       <c r="AC148" s="139">
@@ -32337,35 +32406,35 @@
         <v>N/A</v>
       </c>
       <c r="T149" s="202" t="str">
-        <f t="shared" ref="T149:AA149" si="98">IF(T13&gt;=0,"N/A",IF(T12&lt;=0,"N/A",T12/-T13))</f>
+        <f t="shared" ref="T149:AA149" si="99">IF(T13&gt;=0,"N/A",IF(T12&lt;=0,"N/A",T12/-T13))</f>
         <v>N/A</v>
       </c>
       <c r="U149" s="202" t="str">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>N/A</v>
       </c>
       <c r="V149" s="202" t="str">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>N/A</v>
       </c>
       <c r="W149" s="202" t="str">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>N/A</v>
       </c>
       <c r="X149" s="202" t="str">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>N/A</v>
       </c>
       <c r="Y149" s="202" t="str">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>N/A</v>
       </c>
       <c r="Z149" s="202" t="str">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>N/A</v>
       </c>
       <c r="AA149" s="202" t="str">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>N/A</v>
       </c>
       <c r="AC149" s="202" t="str">
@@ -32407,7 +32476,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>19.466666666666665</v>
+        <v>21.066833333333332</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -32444,7 +32513,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>3.7627479026268738</v>
+        <v>4.072047068835098</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -32471,17 +32540,41 @@
         <f>Q117/(Statement!Q49/Statement!Q75)</f>
         <v>3.1673000839820857</v>
       </c>
-      <c r="T152" s="49"/>
-      <c r="U152" s="49"/>
-      <c r="V152" s="49"/>
-      <c r="W152" s="49"/>
-      <c r="X152" s="49"/>
-      <c r="Y152" s="49"/>
-      <c r="Z152" s="49"/>
-      <c r="AA152" s="49"/>
+      <c r="T152" s="72">
+        <f>T117/(Statement!T49/Statement!T75)</f>
+        <v>3.6502280837334156</v>
+      </c>
+      <c r="U152" s="72">
+        <f>U117/(Statement!U49/Statement!U75)</f>
+        <v>3.9192581610940933</v>
+      </c>
+      <c r="V152" s="72">
+        <f>V117/(Statement!V49/Statement!V75)</f>
+        <v>4.3563406007925183</v>
+      </c>
+      <c r="W152" s="72">
+        <f>W117/(Statement!W49/Statement!W75)</f>
+        <v>3.7612672060176831</v>
+      </c>
+      <c r="X152" s="72">
+        <f>X117/(Statement!X49/Statement!X75)</f>
+        <v>3.74587096259057</v>
+      </c>
+      <c r="Y152" s="72">
+        <f>Y117/(Statement!Y49/Statement!Y75)</f>
+        <v>4.4066611694690421</v>
+      </c>
+      <c r="Z152" s="72">
+        <f>Z117/(Statement!Z49/Statement!Z75)</f>
+        <v>3.1673000839820857</v>
+      </c>
+      <c r="AA152" s="72">
+        <f>AA117/(Statement!AA49/Statement!AA75)</f>
+        <v>2.8043848940994711</v>
+      </c>
       <c r="AC152" s="72">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>3.1801180158331865</v>
+        <v>3.4415248058161869</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -32508,17 +32601,41 @@
         <f>Statement!Q117*Statement!Q78</f>
         <v>6680971.6299999999</v>
       </c>
-      <c r="T153" s="49"/>
-      <c r="U153" s="49"/>
-      <c r="V153" s="49"/>
-      <c r="W153" s="49"/>
-      <c r="X153" s="49"/>
-      <c r="Y153" s="49"/>
-      <c r="Z153" s="49"/>
-      <c r="AA153" s="49"/>
+      <c r="T153" s="164">
+        <f>Statement!T117*Statement!T78</f>
+        <v>6692988.8600000003</v>
+      </c>
+      <c r="U153" s="164">
+        <f>Statement!U117*Statement!U78</f>
+        <v>6787547.6499999994</v>
+      </c>
+      <c r="V153" s="164">
+        <f>Statement!V117*Statement!V78</f>
+        <v>8040767.9400000004</v>
+      </c>
+      <c r="W153" s="164">
+        <f>Statement!W117*Statement!W78</f>
+        <v>6388365.6600000001</v>
+      </c>
+      <c r="X153" s="164">
+        <f>Statement!X117*Statement!X78</f>
+        <v>6318186.5</v>
+      </c>
+      <c r="Y153" s="164">
+        <f>Statement!Y117*Statement!Y78</f>
+        <v>8588396.1799999997</v>
+      </c>
+      <c r="Z153" s="164">
+        <f>Statement!Z117*Statement!Z78</f>
+        <v>6680971.6299999999</v>
+      </c>
+      <c r="AA153" s="164">
+        <f>Statement!AA117*Statement!AA78</f>
+        <v>5380256.5</v>
+      </c>
       <c r="AC153" s="164">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>6101106.3999999994</v>
+        <v>6602619.4355000006</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -32545,17 +32662,41 @@
         <f>Q153+Q108-Q107+Q48+Q45</f>
         <v>4991495.63</v>
       </c>
-      <c r="T154" s="49"/>
-      <c r="U154" s="49"/>
-      <c r="V154" s="49"/>
-      <c r="W154" s="49"/>
-      <c r="X154" s="49"/>
-      <c r="Y154" s="49"/>
-      <c r="Z154" s="49"/>
-      <c r="AA154" s="49"/>
+      <c r="T154" s="164">
+        <f t="shared" ref="T154:AA154" si="100">T153+T108-T107+T48+T45</f>
+        <v>4949614.8600000003</v>
+      </c>
+      <c r="U154" s="164">
+        <f t="shared" si="100"/>
+        <v>5184109.6499999994</v>
+      </c>
+      <c r="V154" s="164">
+        <f t="shared" si="100"/>
+        <v>6317136.9400000004</v>
+      </c>
+      <c r="W154" s="164">
+        <f t="shared" si="100"/>
+        <v>4796865.66</v>
+      </c>
+      <c r="X154" s="164">
+        <f t="shared" si="100"/>
+        <v>4795548.5</v>
+      </c>
+      <c r="Y154" s="164">
+        <f t="shared" si="100"/>
+        <v>7068601.1799999997</v>
+      </c>
+      <c r="Z154" s="164">
+        <f t="shared" si="100"/>
+        <v>4991495.63</v>
+      </c>
+      <c r="AA154" s="164">
+        <f t="shared" si="100"/>
+        <v>3964510.5</v>
+      </c>
       <c r="AC154" s="164">
         <f ca="1">AC153+AC108-AC107+AC48+AC45</f>
-        <v>4685360.3999999994</v>
+        <v>5186873.4355000006</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -32592,7 +32733,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="204">
         <f ca="1">AC154/AC5</f>
-        <v>2.8016960767312669</v>
+        <v>3.1015848758917204</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -32629,7 +32770,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="204">
         <f ca="1">AC154/AC12</f>
-        <v>46.316792376358002</v>
+        <v>51.274463325062534</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -32657,35 +32798,35 @@
         <v>61484</v>
       </c>
       <c r="T157" s="64">
-        <f t="shared" ref="T157:AA157" si="99">T59-T54+T110+T65</f>
+        <f t="shared" ref="T157:AA157" si="101">T59-T54+T110+T65</f>
         <v>-49347</v>
       </c>
       <c r="U157" s="64">
-        <f t="shared" si="99"/>
+        <f t="shared" si="101"/>
         <v>-64293</v>
       </c>
       <c r="V157" s="64">
-        <f t="shared" si="99"/>
+        <f t="shared" si="101"/>
         <v>0</v>
       </c>
       <c r="W157" s="64">
-        <f t="shared" si="99"/>
+        <f t="shared" si="101"/>
         <v>29809</v>
       </c>
       <c r="X157" s="64">
-        <f t="shared" si="99"/>
+        <f t="shared" si="101"/>
         <v>-36419</v>
       </c>
       <c r="Y157" s="64">
-        <f t="shared" si="99"/>
+        <f t="shared" si="101"/>
         <v>-46368</v>
       </c>
       <c r="Z157" s="64">
-        <f t="shared" si="99"/>
+        <f t="shared" si="101"/>
         <v>114462</v>
       </c>
       <c r="AA157" s="64">
-        <f t="shared" si="99"/>
+        <f t="shared" si="101"/>
         <v>75934</v>
       </c>
       <c r="AC157" s="64">
@@ -32739,19 +32880,19 @@
         <v>-31.117410328396652</v>
       </c>
       <c r="N159" s="72">
-        <f t="shared" ref="N159:Q159" si="100">N153/N157</f>
+        <f t="shared" ref="N159:Q159" si="102">N153/N157</f>
         <v>-20.121230787144853</v>
       </c>
       <c r="O159" s="72">
-        <f t="shared" si="100"/>
+        <f t="shared" si="102"/>
         <v>-169.18232313158387</v>
       </c>
       <c r="P159" s="72">
-        <f t="shared" si="100"/>
+        <f t="shared" si="102"/>
         <v>-153.13123350282808</v>
       </c>
       <c r="Q159" s="72">
-        <f t="shared" si="100"/>
+        <f t="shared" si="102"/>
         <v>108.6619548175135</v>
       </c>
       <c r="T159" s="49"/>
@@ -32763,8 +32904,8 @@
       <c r="Z159" s="49"/>
       <c r="AA159" s="49"/>
       <c r="AC159" s="72">
-        <f t="shared" ref="AC159:AC160" ca="1" si="101">AC153/AC157</f>
-        <v>56.696990028715064</v>
+        <f t="shared" ref="AC159:AC160" ca="1" si="103">AC153/AC157</f>
+        <v>61.35750202585286</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -32776,19 +32917,19 @@
         <v>-26.884257614591405</v>
       </c>
       <c r="N160" s="72">
-        <f t="shared" ref="N160:Q160" si="102">N154/N158</f>
+        <f t="shared" ref="N160:Q160" si="104">N154/N158</f>
         <v>-12.722058684723095</v>
       </c>
       <c r="O160" s="72">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>-54.027334756669582</v>
       </c>
       <c r="P160" s="72">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>-31.268001801694783</v>
       </c>
       <c r="Q160" s="72">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>-52.805531070816492</v>
       </c>
       <c r="T160" s="49"/>
@@ -32800,8 +32941,8 @@
       <c r="Z160" s="49"/>
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
-        <f t="shared" ca="1" si="101"/>
-        <v>-86.389976952152665</v>
+        <f t="shared" ca="1" si="103"/>
+        <v>-95.63701365354477</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -32813,19 +32954,19 @@
         <v>-3.2136350340421331E-2</v>
       </c>
       <c r="N161" s="74">
-        <f t="shared" ref="N161:Q161" si="103">N157/N153</f>
+        <f t="shared" ref="N161:Q161" si="105">N157/N153</f>
         <v>-4.9698749076467263E-2</v>
       </c>
       <c r="O161" s="74">
-        <f t="shared" si="103"/>
+        <f t="shared" si="105"/>
         <v>-5.9107830031523813E-3</v>
       </c>
       <c r="P161" s="74">
-        <f t="shared" si="103"/>
+        <f t="shared" si="105"/>
         <v>-6.5303464037043202E-3</v>
       </c>
       <c r="Q161" s="74">
-        <f t="shared" si="103"/>
+        <f t="shared" si="105"/>
         <v>9.2028530287292954E-3</v>
       </c>
       <c r="T161" s="49"/>
@@ -32837,8 +32978,8 @@
       <c r="Z161" s="49"/>
       <c r="AA161" s="49"/>
       <c r="AC161" s="74">
-        <f t="shared" ref="AC161" ca="1" si="104">AC157/AC153</f>
-        <v>1.7637620612549882E-2</v>
+        <f t="shared" ref="AC161" ca="1" si="106">AC157/AC153</f>
+        <v>1.6297925550793315E-2</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -32875,7 +33016,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f ca="1">AC26/AC117</f>
-        <v>5.1369863013698641E-2</v>
+        <v>4.7467978892572059E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -32949,7 +33090,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="175">
         <f ca="1">-AC63/AC153</f>
-        <v>5.6608093246824878E-2</v>
+        <v>5.2308330560906516E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -32986,7 +33127,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="175">
         <f ca="1">-(AC63+AC64)/AC153</f>
-        <v>5.6608093246824878E-2</v>
+        <v>5.2308330560906516E-2</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -33236,35 +33377,35 @@
         <v>3.224670847950649</v>
       </c>
       <c r="T172" s="72">
-        <f t="shared" ref="T172:AA172" si="105">T107/T75</f>
+        <f t="shared" ref="T172:AA172" si="107">T107/T75</f>
         <v>3.1700129828095962</v>
       </c>
       <c r="U172" s="72">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>2.9174689182476676</v>
       </c>
       <c r="V172" s="72">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>3.125390530795495</v>
       </c>
       <c r="W172" s="72">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>2.9745495188201234</v>
       </c>
       <c r="X172" s="72">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>2.8673727265537021</v>
       </c>
       <c r="Y172" s="72">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>2.8420663861617577</v>
       </c>
       <c r="Z172" s="72">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>3.224670847950649</v>
       </c>
       <c r="AA172" s="72">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>2.732462108272006</v>
       </c>
       <c r="AC172" s="72">
@@ -33297,35 +33438,35 @@
         <v>0.78305424452059225</v>
       </c>
       <c r="T173" s="175">
-        <f t="shared" ref="T173:AA173" si="106">T54/T59</f>
+        <f t="shared" ref="T173:AA173" si="108">T54/T59</f>
         <v>2.0334871485250994</v>
       </c>
       <c r="U173" s="175">
-        <f t="shared" si="106"/>
+        <f t="shared" si="108"/>
         <v>3.1167794798717492</v>
       </c>
       <c r="V173" s="175" t="e">
-        <f t="shared" si="106"/>
+        <f t="shared" si="108"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W173" s="175">
-        <f t="shared" si="106"/>
+        <f t="shared" si="108"/>
         <v>0.6416782911211576</v>
       </c>
       <c r="X173" s="175">
-        <f t="shared" si="106"/>
+        <f t="shared" si="108"/>
         <v>1.8757303965181427</v>
       </c>
       <c r="Y173" s="175">
-        <f t="shared" si="106"/>
+        <f t="shared" si="108"/>
         <v>2.5282091188850764</v>
       </c>
       <c r="Z173" s="175">
-        <f t="shared" si="106"/>
+        <f t="shared" si="108"/>
         <v>0.35555092460569898</v>
       </c>
       <c r="AA173" s="175">
-        <f t="shared" si="106"/>
+        <f t="shared" si="108"/>
         <v>0.40408404584318719</v>
       </c>
       <c r="AC173" s="175">
@@ -33358,35 +33499,35 @@
         <v>0.18047997854178516</v>
       </c>
       <c r="T174" s="175">
-        <f t="shared" ref="T174:AA174" si="107">T54/T5</f>
+        <f t="shared" ref="T174:AA174" si="109">T54/T5</f>
         <v>0.29819479973312507</v>
       </c>
       <c r="U174" s="175">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>0.24668619749445234</v>
       </c>
       <c r="V174" s="175">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="W174" s="175">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>0.21412187626183318</v>
       </c>
       <c r="X174" s="175">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>0.21564822186836519</v>
       </c>
       <c r="Y174" s="175">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>0.17385730930425455</v>
       </c>
       <c r="Z174" s="175">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>0.13476004298420102</v>
       </c>
       <c r="AA174" s="175">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>0.1274194396508454</v>
       </c>
       <c r="AC174" s="175">
@@ -33419,35 +33560,35 @@
         <v>3.224670847950649</v>
       </c>
       <c r="T175" s="72">
-        <f t="shared" ref="T175:AA175" si="108">(T107-T108)/T75</f>
+        <f t="shared" ref="T175:AA175" si="110">(T107-T108)/T75</f>
         <v>3.1700129828095962</v>
       </c>
       <c r="U175" s="72">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>2.9174689182476676</v>
       </c>
       <c r="V175" s="72">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>3.125390530795495</v>
       </c>
       <c r="W175" s="72">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>2.9745495188201234</v>
       </c>
       <c r="X175" s="72">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>2.8673727265537021</v>
       </c>
       <c r="Y175" s="72">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>2.8420663861617577</v>
       </c>
       <c r="Z175" s="72">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>3.224670847950649</v>
       </c>
       <c r="AA175" s="72">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>2.732462108272006</v>
       </c>
       <c r="AC175" s="72">
@@ -33489,7 +33630,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="175">
         <f ca="1">(AC107-AC108)/AC153</f>
-        <v>0.23204742012038998</v>
+        <v>0.21442186905215579</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -33517,35 +33658,35 @@
         <v>1.1826854061786744E-2</v>
       </c>
       <c r="T177" s="175">
-        <f t="shared" ref="T177:AA177" si="109">-T110/T5</f>
+        <f t="shared" ref="T177:AA177" si="111">-T110/T5</f>
         <v>4.4837519327879894E-3</v>
       </c>
       <c r="U177" s="175">
-        <f t="shared" si="109"/>
+        <f t="shared" si="111"/>
         <v>1.3745830431435797E-2</v>
       </c>
       <c r="V177" s="175">
-        <f t="shared" si="109"/>
+        <f t="shared" si="111"/>
         <v>0</v>
       </c>
       <c r="W177" s="175">
-        <f t="shared" si="109"/>
+        <f t="shared" si="111"/>
         <v>3.5981874467225984E-2</v>
       </c>
       <c r="X177" s="175">
-        <f t="shared" si="109"/>
+        <f t="shared" si="111"/>
         <v>0</v>
       </c>
       <c r="Y177" s="175">
-        <f t="shared" si="109"/>
+        <f t="shared" si="111"/>
         <v>7.6961808553852587E-3</v>
       </c>
       <c r="Z177" s="175">
-        <f t="shared" si="109"/>
+        <f t="shared" si="111"/>
         <v>6.3437031679023587E-3</v>
       </c>
       <c r="AA177" s="175">
-        <f t="shared" si="109"/>
+        <f t="shared" si="111"/>
         <v>6.415189946030183E-3</v>
       </c>
       <c r="AC177" s="175">
@@ -33578,35 +33719,35 @@
         <v>5.1313549276955236E-2</v>
       </c>
       <c r="T178" s="175">
-        <f t="shared" ref="T178:AA178" si="110">-(T110/T59)</f>
+        <f t="shared" ref="T178:AA178" si="112">-(T110/T59)</f>
         <v>3.0576160082801448E-2</v>
       </c>
       <c r="U178" s="175">
-        <f t="shared" si="110"/>
+        <f t="shared" si="112"/>
         <v>0.17367296045600286</v>
       </c>
       <c r="V178" s="175" t="e">
-        <f t="shared" si="110"/>
+        <f t="shared" si="112"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W178" s="175">
-        <f t="shared" si="110"/>
+        <f t="shared" si="112"/>
         <v>0.10783012050217644</v>
       </c>
       <c r="X178" s="175">
-        <f t="shared" si="110"/>
+        <f t="shared" si="112"/>
         <v>0</v>
       </c>
       <c r="Y178" s="175">
-        <f t="shared" si="110"/>
+        <f t="shared" si="112"/>
         <v>0.11191680520674896</v>
       </c>
       <c r="Z178" s="175">
-        <f t="shared" si="110"/>
+        <f t="shared" si="112"/>
         <v>1.6737227718428501E-2</v>
       </c>
       <c r="AA178" s="175">
-        <f t="shared" si="110"/>
+        <f t="shared" si="112"/>
         <v>2.0344430295312594E-2</v>
       </c>
       <c r="AC178" s="175">
@@ -33639,35 +33780,35 @@
         <v>1.1225175319700631</v>
       </c>
       <c r="T179" s="175">
-        <f t="shared" ref="T179:AA179" si="111">-T110/T53</f>
+        <f t="shared" ref="T179:AA179" si="113">-T110/T53</f>
         <v>0.30953940187731938</v>
       </c>
       <c r="U179" s="175">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>1.0752095280105867</v>
       </c>
       <c r="V179" s="175" t="e">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W179" s="175">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>3.9446664617276359</v>
       </c>
       <c r="X179" s="175">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>0</v>
       </c>
       <c r="Y179" s="175">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>0.7010857522712165</v>
       </c>
       <c r="Z179" s="175">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>0.61371405590187011</v>
       </c>
       <c r="AA179" s="175">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>0.35743774137701423</v>
       </c>
       <c r="AC179" s="175">
@@ -33684,19 +33825,19 @@
         <v>0.346849112713561</v>
       </c>
       <c r="N180" s="245">
-        <f t="shared" ref="N180:Q180" si="112">N5/N37</f>
+        <f t="shared" ref="N180:Q180" si="114">N5/N37</f>
         <v>0.38702057541552631</v>
       </c>
       <c r="O180" s="245">
-        <f t="shared" si="112"/>
+        <f t="shared" si="114"/>
         <v>0.44270021436611728</v>
       </c>
       <c r="P180" s="245">
-        <f t="shared" si="112"/>
+        <f t="shared" si="114"/>
         <v>0.49896309946357587</v>
       </c>
       <c r="Q180" s="245">
-        <f t="shared" si="112"/>
+        <f t="shared" si="114"/>
         <v>0.50659662808253647</v>
       </c>
       <c r="T180" s="49"/>
@@ -33708,7 +33849,7 @@
       <c r="Z180" s="49"/>
       <c r="AA180" s="49"/>
       <c r="AC180" s="245">
-        <f t="shared" ref="AC180" si="113">AC5/AC37</f>
+        <f t="shared" ref="AC180" si="115">AC5/AC37</f>
         <v>0.57573243364202842</v>
       </c>
     </row>
@@ -33721,19 +33862,19 @@
         <v>N/A</v>
       </c>
       <c r="N181" s="247" t="str">
-        <f t="shared" ref="N181:Q181" si="114">IF(AND(N12&gt;0,N108&gt;0),N108/N12,"N/A")</f>
+        <f t="shared" ref="N181:Q181" si="116">IF(AND(N12&gt;0,N108&gt;0),N108/N12,"N/A")</f>
         <v>N/A</v>
       </c>
       <c r="O181" s="247" t="str">
-        <f t="shared" si="114"/>
+        <f t="shared" si="116"/>
         <v>N/A</v>
       </c>
       <c r="P181" s="247" t="str">
-        <f t="shared" si="114"/>
+        <f t="shared" si="116"/>
         <v>N/A</v>
       </c>
       <c r="Q181" s="247" t="str">
-        <f t="shared" si="114"/>
+        <f t="shared" si="116"/>
         <v>N/A</v>
       </c>
       <c r="T181" s="49"/>
@@ -33745,7 +33886,7 @@
       <c r="Z181" s="49"/>
       <c r="AA181" s="49"/>
       <c r="AC181" s="247" t="str">
-        <f t="shared" ref="AC181" si="115">IF(AND(AC12&gt;0,AC108&gt;0),AC108/AC12,"N/A")</f>
+        <f t="shared" ref="AC181" si="117">IF(AND(AC12&gt;0,AC108&gt;0),AC108/AC12,"N/A")</f>
         <v>N/A</v>
       </c>
     </row>
@@ -33758,19 +33899,19 @@
         <v>N/A</v>
       </c>
       <c r="N182" s="247" t="str">
-        <f t="shared" ref="N182:Q182" si="116">IF(AND(N12&gt;0,N108&gt;0),(N108-N107)/N12,"N/A")</f>
+        <f t="shared" ref="N182:Q182" si="118">IF(AND(N12&gt;0,N108&gt;0),(N108-N107)/N12,"N/A")</f>
         <v>N/A</v>
       </c>
       <c r="O182" s="247" t="str">
-        <f t="shared" si="116"/>
+        <f t="shared" si="118"/>
         <v>N/A</v>
       </c>
       <c r="P182" s="247" t="str">
-        <f t="shared" si="116"/>
+        <f t="shared" si="118"/>
         <v>N/A</v>
       </c>
       <c r="Q182" s="247" t="str">
-        <f t="shared" si="116"/>
+        <f t="shared" si="118"/>
         <v>N/A</v>
       </c>
       <c r="T182" s="49"/>
@@ -33782,7 +33923,7 @@
       <c r="Z182" s="49"/>
       <c r="AA182" s="49"/>
       <c r="AC182" s="247" t="str">
-        <f t="shared" ref="AC182" si="117">IF(AND(AC12&gt;0,AC108&gt;0),(AC108-AC107)/AC12,"N/A")</f>
+        <f t="shared" ref="AC182" si="119">IF(AND(AC12&gt;0,AC108&gt;0),(AC108-AC107)/AC12,"N/A")</f>
         <v>N/A</v>
       </c>
     </row>
@@ -33795,19 +33936,19 @@
         <v>23.950501959521127</v>
       </c>
       <c r="N183" s="247">
-        <f t="shared" ref="N183:Q183" si="118">N5/(N108+N112-N107)</f>
+        <f t="shared" ref="N183:Q183" si="120">N5/(N108+N112-N107)</f>
         <v>6.6028018437778737</v>
       </c>
       <c r="O183" s="247">
-        <f t="shared" si="118"/>
+        <f t="shared" si="120"/>
         <v>9.5976403430894184</v>
       </c>
       <c r="P183" s="247">
-        <f t="shared" si="118"/>
+        <f t="shared" si="120"/>
         <v>11.705987832736978</v>
       </c>
       <c r="Q183" s="247">
-        <f t="shared" si="118"/>
+        <f t="shared" si="120"/>
         <v>4.0969904174647871</v>
       </c>
       <c r="T183" s="49"/>
@@ -33819,7 +33960,7 @@
       <c r="Z183" s="49"/>
       <c r="AA183" s="49"/>
       <c r="AC183" s="247">
-        <f t="shared" ref="AC183" si="119">AC5/(AC108+AC112-AC107)</f>
+        <f t="shared" ref="AC183" si="121">AC5/(AC108+AC112-AC107)</f>
         <v>3.4323989827982899</v>
       </c>
     </row>
@@ -33949,7 +34090,7 @@
         <v>252903</v>
       </c>
       <c r="AC188" s="62">
-        <f t="shared" ref="AC188:AC193" si="120">SUM(X188:AA188)</f>
+        <f t="shared" ref="AC188:AC193" si="122">SUM(X188:AA188)</f>
         <v>990072</v>
       </c>
     </row>
@@ -34007,7 +34148,7 @@
         <v>16170</v>
       </c>
       <c r="AC189" s="62">
-        <f t="shared" si="120"/>
+        <f t="shared" si="122"/>
         <v>54841</v>
       </c>
     </row>
@@ -34079,7 +34220,7 @@
         <v>1664</v>
       </c>
       <c r="AC191" s="62">
-        <f t="shared" si="120"/>
+        <f t="shared" si="122"/>
         <v>5730</v>
       </c>
     </row>
@@ -34137,7 +34278,7 @@
         <v>43988</v>
       </c>
       <c r="AC192" s="62">
-        <f t="shared" si="120"/>
+        <f t="shared" si="122"/>
         <v>163108</v>
       </c>
     </row>
@@ -34195,7 +34336,7 @@
         <v>31276</v>
       </c>
       <c r="AC193" s="62">
-        <f t="shared" si="120"/>
+        <f t="shared" si="122"/>
         <v>115217</v>
       </c>
     </row>
@@ -34259,61 +34400,61 @@
       <c r="K197" s="81"/>
       <c r="L197" s="81"/>
       <c r="M197" s="81">
-        <f t="shared" ref="M197:Q199" si="121">IF(L187=0,
+        <f t="shared" ref="M197:Q199" si="123">IF(L187=0,
 IF(M187=0,0,IF(M187&gt;0,1,-1)),
 (M187-L187)/ABS(L187)
 )</f>
         <v>1</v>
       </c>
       <c r="N197" s="81">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>3.4084087514825716E-2</v>
       </c>
       <c r="O197" s="81">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>0.24818614965570993</v>
       </c>
       <c r="P197" s="81">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>-5.5102093364575021E-2</v>
       </c>
       <c r="Q197" s="81">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>3.2771752459329104E-2</v>
       </c>
       <c r="T197" s="81">
-        <f t="shared" ref="T197:AA199" si="122">IF(S187=0,
+        <f t="shared" ref="T197:AA199" si="124">IF(S187=0,
 IF(T187=0,0,IF(T187&gt;0,1,-1)),
 (T187-S187)/ABS(S187)
 )</f>
         <v>1</v>
       </c>
       <c r="U197" s="81">
-        <f t="shared" si="122"/>
+        <f t="shared" si="124"/>
         <v>0.22202920241245067</v>
       </c>
       <c r="V197" s="81">
-        <f t="shared" si="122"/>
+        <f t="shared" si="124"/>
         <v>0.44057182848061588</v>
       </c>
       <c r="W197" s="81">
-        <f t="shared" si="122"/>
+        <f t="shared" si="124"/>
         <v>-0.35080892064632685</v>
       </c>
       <c r="X197" s="81">
-        <f t="shared" si="122"/>
+        <f t="shared" si="124"/>
         <v>-0.12569571114540948</v>
       </c>
       <c r="Y197" s="81">
-        <f t="shared" si="122"/>
+        <f t="shared" si="124"/>
         <v>0.33774663207353717</v>
       </c>
       <c r="Z197" s="81">
-        <f t="shared" si="122"/>
+        <f t="shared" si="124"/>
         <v>0.43894750171617469</v>
       </c>
       <c r="AA197" s="81">
-        <f t="shared" si="122"/>
+        <f t="shared" si="124"/>
         <v>-0.30844727286201273</v>
       </c>
       <c r="AC197" s="49"/>
@@ -34323,55 +34464,55 @@
         <v>114</v>
       </c>
       <c r="M198" s="81">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>1</v>
       </c>
       <c r="N198" s="81">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>0.37569180272908909</v>
       </c>
       <c r="O198" s="81">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>0.27729682030883041</v>
       </c>
       <c r="P198" s="81">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>0.23392027917368038</v>
       </c>
       <c r="Q198" s="81">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>0.19019336689332336</v>
       </c>
       <c r="T198" s="81">
-        <f t="shared" si="122"/>
+        <f t="shared" si="124"/>
         <v>1</v>
       </c>
       <c r="U198" s="81">
-        <f t="shared" si="122"/>
+        <f t="shared" si="124"/>
         <v>6.292089812146523E-2</v>
       </c>
       <c r="V198" s="81">
-        <f t="shared" si="122"/>
+        <f t="shared" si="124"/>
         <v>4.0106900184610626E-2</v>
       </c>
       <c r="W198" s="81">
-        <f t="shared" si="122"/>
+        <f t="shared" si="124"/>
         <v>9.673777187170397E-3</v>
       </c>
       <c r="X198" s="81">
-        <f t="shared" si="122"/>
+        <f t="shared" si="124"/>
         <v>9.6915367022084364E-2</v>
       </c>
       <c r="Y198" s="81">
-        <f t="shared" si="122"/>
+        <f t="shared" si="124"/>
         <v>3.8638547089942653E-2</v>
       </c>
       <c r="Z198" s="81">
-        <f t="shared" si="122"/>
+        <f t="shared" si="124"/>
         <v>1.4783518396594137E-2</v>
       </c>
       <c r="AA198" s="81">
-        <f t="shared" si="122"/>
+        <f t="shared" si="124"/>
         <v>6.6472159310281692E-3</v>
       </c>
       <c r="AC198" s="49"/>
@@ -34381,55 +34522,55 @@
         <v>115</v>
       </c>
       <c r="M199" s="81">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>1</v>
       </c>
       <c r="N199" s="81">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>0.26768885199472631</v>
       </c>
       <c r="O199" s="81">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>-0.29197642617772812</v>
       </c>
       <c r="P199" s="81">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>0.10317719384146673</v>
       </c>
       <c r="Q199" s="81">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>0.22564418690666996</v>
       </c>
       <c r="T199" s="81">
-        <f t="shared" si="122"/>
+        <f t="shared" si="124"/>
         <v>1</v>
       </c>
       <c r="U199" s="81">
-        <f t="shared" si="122"/>
+        <f t="shared" si="124"/>
         <v>0.13163254368099475</v>
       </c>
       <c r="V199" s="81">
-        <f t="shared" si="122"/>
+        <f t="shared" si="124"/>
         <v>2.4533484891541158E-2</v>
       </c>
       <c r="W199" s="81">
-        <f t="shared" si="122"/>
+        <f t="shared" si="124"/>
         <v>2.0247781065088757E-2</v>
       </c>
       <c r="X199" s="81">
-        <f t="shared" si="122"/>
+        <f t="shared" si="124"/>
         <v>1.5314907113729044E-2</v>
       </c>
       <c r="Y199" s="81">
-        <f t="shared" si="122"/>
+        <f t="shared" si="124"/>
         <v>0.20465905033916459</v>
       </c>
       <c r="Z199" s="81">
-        <f t="shared" si="122"/>
+        <f t="shared" si="124"/>
         <v>3.5044824775876122E-2</v>
       </c>
       <c r="AA199" s="81">
-        <f t="shared" si="122"/>
+        <f t="shared" si="124"/>
         <v>0.15748031496062992</v>
       </c>
       <c r="AC199" s="49"/>
@@ -34569,15 +34710,15 @@
         <v>43.583607538139404</v>
       </c>
       <c r="O207" s="164">
-        <f t="shared" ref="O207:Q207" si="123">100*(1+((O117-$M117)/ABS($M117)))</f>
+        <f t="shared" ref="O207:Q207" si="125">100*(1+((O117-$M117)/ABS($M117)))</f>
         <v>71.343104995513016</v>
       </c>
       <c r="P207" s="164">
-        <f t="shared" si="123"/>
+        <f t="shared" si="125"/>
         <v>43.613520789709838</v>
       </c>
       <c r="Q207" s="164">
-        <f t="shared" si="123"/>
+        <f t="shared" si="125"/>
         <v>37.660783727191152</v>
       </c>
       <c r="T207" s="49"/>
@@ -34602,15 +34743,15 @@
         <v>118.64148245114609</v>
       </c>
       <c r="O208" s="164">
-        <f t="shared" ref="O208:Q208" si="124">100*(1+((O5-$M5)/ABS($M5)))</f>
+        <f t="shared" ref="O208:Q208" si="126">100*(1+((O5-$M5)/ABS($M5)))</f>
         <v>146.60342593796372</v>
       </c>
       <c r="P208" s="164">
-        <f t="shared" si="124"/>
+        <f t="shared" si="126"/>
         <v>160.23096613961079</v>
       </c>
       <c r="Q208" s="164">
-        <f t="shared" si="124"/>
+        <f t="shared" si="126"/>
         <v>180.50640402038886</v>
       </c>
       <c r="T208" s="49"/>
@@ -34635,15 +34776,15 @@
         <v>148.27586206896552</v>
       </c>
       <c r="O209" s="164">
-        <f t="shared" ref="O209:Q209" si="125">100*(1+((O26-$M26)/ABS($M26)))</f>
+        <f t="shared" ref="O209:Q209" si="127">100*(1+((O26-$M26)/ABS($M26)))</f>
         <v>186.20689655172413</v>
       </c>
       <c r="P209" s="164">
-        <f t="shared" si="125"/>
+        <f t="shared" si="127"/>
         <v>188.79310344827584</v>
       </c>
       <c r="Q209" s="164">
-        <f t="shared" si="125"/>
+        <f t="shared" si="127"/>
         <v>244.82758620689654</v>
       </c>
       <c r="T209" s="49"/>
@@ -34994,15 +35135,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="249" t="s">
+      <c r="B4" s="253" t="s">
         <v>282</v>
       </c>
-      <c r="C4" s="249"/>
-      <c r="E4" s="249" t="s">
+      <c r="C4" s="253"/>
+      <c r="E4" s="253" t="s">
         <v>289</v>
       </c>
-      <c r="F4" s="249"/>
-      <c r="G4" s="249"/>
+      <c r="F4" s="253"/>
+      <c r="G4" s="253"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -35010,7 +35151,7 @@
       </c>
       <c r="C5" s="193">
         <f ca="1">Overview!C5</f>
-        <v>11.68</v>
+        <v>12.6401</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="153" t="s">
@@ -35026,7 +35167,7 @@
       </c>
       <c r="C6" s="194">
         <f ca="1">Statement!AC153</f>
-        <v>6101106.3999999994</v>
+        <v>6602619.4355000006</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>20</v>
@@ -35046,7 +35187,7 @@
       </c>
       <c r="C7" s="194">
         <f ca="1">Statement!AC154</f>
-        <v>4685360.3999999994</v>
+        <v>5186873.4355000006</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>32</v>
@@ -35066,7 +35207,7 @@
       </c>
       <c r="C8" s="195">
         <f ca="1">Statement!AC150</f>
-        <v>19.466666666666665</v>
+        <v>21.066833333333332</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>292</v>
@@ -35086,7 +35227,7 @@
       </c>
       <c r="C9" s="195">
         <f ca="1">Statement!AC151</f>
-        <v>3.7627479026268738</v>
+        <v>4.072047068835098</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>293</v>
@@ -35106,7 +35247,7 @@
       </c>
       <c r="C10" s="195">
         <f ca="1">Statement!AC152</f>
-        <v>3.1801180158331865</v>
+        <v>3.4415248058161869</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -35126,7 +35267,7 @@
       </c>
       <c r="C11" s="195">
         <f ca="1">Statement!AC155</f>
-        <v>2.8016960767312669</v>
+        <v>3.1015848758917204</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -35135,18 +35276,18 @@
       </c>
       <c r="C12" s="195">
         <f ca="1">Statement!AC156</f>
-        <v>46.316792376358002</v>
+        <v>51.274463325062534</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="249" t="s">
+      <c r="B15" s="253" t="s">
         <v>78</v>
       </c>
-      <c r="C15" s="249"/>
-      <c r="E15" s="249" t="s">
+      <c r="C15" s="253"/>
+      <c r="E15" s="253" t="s">
         <v>295</v>
       </c>
-      <c r="F15" s="249"/>
+      <c r="F15" s="253"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -35197,14 +35338,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="249" t="s">
+      <c r="B21" s="253" t="s">
         <v>294</v>
       </c>
-      <c r="C21" s="249"/>
-      <c r="E21" s="249" t="s">
+      <c r="C21" s="253"/>
+      <c r="E21" s="253" t="s">
         <v>298</v>
       </c>
-      <c r="F21" s="249"/>
+      <c r="F21" s="253"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -35273,14 +35414,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="249" t="s">
+      <c r="B29" s="253" t="s">
         <v>299</v>
       </c>
-      <c r="C29" s="249"/>
-      <c r="E29" s="249" t="s">
+      <c r="C29" s="253"/>
+      <c r="E29" s="253" t="s">
         <v>305</v>
       </c>
-      <c r="F29" s="249"/>
+      <c r="F29" s="253"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -35356,14 +35497,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="249" t="s">
+      <c r="B37" s="253" t="s">
         <v>317</v>
       </c>
-      <c r="C37" s="249"/>
-      <c r="E37" s="249" t="s">
+      <c r="C37" s="253"/>
+      <c r="E37" s="253" t="s">
         <v>320</v>
       </c>
-      <c r="F37" s="249"/>
+      <c r="F37" s="253"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -35371,7 +35512,7 @@
       </c>
       <c r="C38" s="196">
         <f ca="1">Statement!AC162</f>
-        <v>5.1369863013698641E-2</v>
+        <v>4.7467978892572059E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>319</v>
@@ -35387,7 +35528,7 @@
       </c>
       <c r="C39" s="236">
         <f ca="1">Statement!AC161</f>
-        <v>1.7637620612549882E-2</v>
+        <v>1.6297925550793315E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>321</v>
@@ -35419,7 +35560,7 @@
       </c>
       <c r="C41" s="196">
         <f ca="1">Statement!AC164</f>
-        <v>5.6608093246824878E-2</v>
+        <v>5.2308330560906516E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -35428,18 +35569,18 @@
       </c>
       <c r="C42" s="196">
         <f ca="1">Statement!AC165</f>
-        <v>5.6608093246824878E-2</v>
+        <v>5.2308330560906516E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="249" t="s">
+      <c r="B45" s="253" t="s">
         <v>328</v>
       </c>
-      <c r="C45" s="249"/>
-      <c r="E45" s="249" t="s">
+      <c r="C45" s="253"/>
+      <c r="E45" s="253" t="s">
         <v>334</v>
       </c>
-      <c r="F45" s="249"/>
+      <c r="F45" s="253"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -35472,18 +35613,18 @@
       </c>
       <c r="F48" s="196">
         <f ca="1">Statement!AC176</f>
-        <v>0.23204742012038998</v>
+        <v>0.21442186905215579</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="249" t="s">
+      <c r="B51" s="253" t="s">
         <v>331</v>
       </c>
-      <c r="C51" s="249"/>
-      <c r="E51" s="249" t="s">
+      <c r="C51" s="253"/>
+      <c r="E51" s="253" t="s">
         <v>352</v>
       </c>
-      <c r="F51" s="249"/>
+      <c r="F51" s="253"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -35651,7 +35792,7 @@
       </c>
       <c r="I6" s="193">
         <f ca="1">Statement!AC116</f>
-        <v>11.68</v>
+        <v>12.6401</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -35680,7 +35821,7 @@
       </c>
       <c r="I7" s="194">
         <f ca="1">Statement!AC153</f>
-        <v>6101106.3999999994</v>
+        <v>6602619.4355000006</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -35709,7 +35850,7 @@
       </c>
       <c r="I8" s="194">
         <f ca="1">Statement!AC154</f>
-        <v>4685360.3999999994</v>
+        <v>5186873.4355000006</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -35738,7 +35879,7 @@
       </c>
       <c r="I9" s="195">
         <f ca="1">Statement!AC150</f>
-        <v>19.466666666666665</v>
+        <v>21.066833333333332</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -35767,7 +35908,7 @@
       </c>
       <c r="I10" s="195">
         <f ca="1">Statement!AC151</f>
-        <v>3.7627479026268738</v>
+        <v>4.072047068835098</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -35796,7 +35937,7 @@
       </c>
       <c r="I11" s="195">
         <f ca="1">Statement!AC152</f>
-        <v>3.1801180158331865</v>
+        <v>3.4415248058161869</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -35825,7 +35966,7 @@
       </c>
       <c r="I12" s="195">
         <f ca="1">Statement!AC155</f>
-        <v>2.8016960767312669</v>
+        <v>3.1015848758917204</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -35854,7 +35995,7 @@
       </c>
       <c r="I13" s="195">
         <f ca="1">Statement!AC156</f>
-        <v>46.316792376358002</v>
+        <v>51.274463325062534</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36627,7 +36768,7 @@
       </c>
       <c r="I51" s="196">
         <f ca="1">Statement!AC162</f>
-        <v>5.1369863013698641E-2</v>
+        <v>4.7467978892572059E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -36656,7 +36797,7 @@
       </c>
       <c r="I52" s="196">
         <f ca="1">Statement!AC161</f>
-        <v>1.7637620612549882E-2</v>
+        <v>1.6297925550793315E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -36714,7 +36855,7 @@
       </c>
       <c r="I54" s="196">
         <f ca="1">Statement!AC164</f>
-        <v>5.6608093246824878E-2</v>
+        <v>5.2308330560906516E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -36743,7 +36884,7 @@
       </c>
       <c r="I55" s="196">
         <f ca="1">Statement!AC165</f>
-        <v>5.6608093246824878E-2</v>
+        <v>5.2308330560906516E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36979,7 +37120,7 @@
       </c>
       <c r="I68" s="217">
         <f ca="1">Statement!AC176</f>
-        <v>0.23204742012038998</v>
+        <v>0.21442186905215579</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -37465,14 +37606,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="253" t="s">
+      <c r="C3" s="257" t="s">
         <v>365</v>
       </c>
-      <c r="D3" s="254"/>
-      <c r="F3" s="255" t="s">
+      <c r="D3" s="258"/>
+      <c r="F3" s="259" t="s">
         <v>366</v>
       </c>
-      <c r="G3" s="254"/>
+      <c r="G3" s="258"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -37539,19 +37680,19 @@
       <c r="B7" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C7" s="256">
+      <c r="C7" s="260">
         <f>Statement!AA89</f>
         <v>-0.13037640275448081</v>
       </c>
-      <c r="D7" s="257"/>
-      <c r="F7" s="256">
+      <c r="D7" s="261"/>
+      <c r="F7" s="260">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.17317398716855847</v>
       </c>
-      <c r="G7" s="257"/>
+      <c r="G7" s="261"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="228" t="s">
@@ -37578,19 +37719,19 @@
       <c r="B9" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C9" s="256">
+      <c r="C9" s="260">
         <f>Statement!AA90</f>
         <v>4.0481504023804696E-2</v>
       </c>
-      <c r="D9" s="257"/>
-      <c r="F9" s="256">
+      <c r="D9" s="261"/>
+      <c r="F9" s="260">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.20469173309112548</v>
       </c>
-      <c r="G9" s="257"/>
+      <c r="G9" s="261"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="228" t="s">
@@ -37617,19 +37758,19 @@
       <c r="B11" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C11" s="256">
+      <c r="C11" s="260">
         <f>Statement!AA91</f>
         <v>-0.1614010786596328</v>
       </c>
-      <c r="D11" s="257"/>
-      <c r="F11" s="256">
+      <c r="D11" s="261"/>
+      <c r="F11" s="260">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.16629948047423376</v>
       </c>
-      <c r="G11" s="257"/>
+      <c r="G11" s="261"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="228" t="s">
@@ -37656,19 +37797,19 @@
       <c r="B13" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C13" s="256">
+      <c r="C13" s="260">
         <f>Statement!AA95</f>
         <v>-4.1051008608505718E-2</v>
       </c>
-      <c r="D13" s="257"/>
-      <c r="F13" s="256">
+      <c r="D13" s="261"/>
+      <c r="F13" s="260">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>1.3868988514743887E-2</v>
       </c>
-      <c r="G13" s="257"/>
+      <c r="G13" s="261"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="228" t="s">
@@ -37695,19 +37836,19 @@
       <c r="B15" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C15" s="256">
+      <c r="C15" s="260">
         <f>Statement!AA96</f>
         <v>-0.65140871384799337</v>
       </c>
-      <c r="D15" s="257"/>
-      <c r="F15" s="256">
+      <c r="D15" s="261"/>
+      <c r="F15" s="260">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>2.7052766268583963</v>
       </c>
-      <c r="G15" s="257"/>
+      <c r="G15" s="261"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="228" t="s">
@@ -37734,19 +37875,19 @@
       <c r="B17" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C17" s="256">
+      <c r="C17" s="260">
         <f>Statement!AA98</f>
         <v>-0.78437135034749483</v>
       </c>
-      <c r="D17" s="257"/>
-      <c r="F17" s="256">
+      <c r="D17" s="261"/>
+      <c r="F17" s="260">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>1.9986699179782754</v>
       </c>
-      <c r="G17" s="257"/>
+      <c r="G17" s="261"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="228" t="s">
@@ -37773,22 +37914,22 @@
       <c r="B19" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C19" s="256">
+      <c r="C19" s="260">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-3.2031015030699599E-2</v>
       </c>
-      <c r="D19" s="257"/>
-      <c r="F19" s="256">
+      <c r="D19" s="261"/>
+      <c r="F19" s="260">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-3.7620498458385526E-2</v>
       </c>
-      <c r="G19" s="257"/>
+      <c r="G19" s="261"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="228" t="s">
@@ -37815,22 +37956,22 @@
       <c r="B21" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C21" s="256">
+      <c r="C21" s="260">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>-0.78947368421052633</v>
       </c>
-      <c r="D21" s="257"/>
-      <c r="F21" s="256">
+      <c r="D21" s="261"/>
+      <c r="F21" s="260">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>2</v>
       </c>
-      <c r="G21" s="257"/>
+      <c r="G21" s="261"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -37878,22 +38019,22 @@
       <c r="B25" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C25" s="256">
+      <c r="C25" s="260">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>-0.30844727286201273</v>
       </c>
-      <c r="D25" s="257"/>
-      <c r="F25" s="256">
+      <c r="D25" s="261"/>
+      <c r="F25" s="260">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.16387602700216702</v>
       </c>
-      <c r="G25" s="257"/>
+      <c r="G25" s="261"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="s">
@@ -37920,22 +38061,22 @@
       <c r="B27" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C27" s="256">
+      <c r="C27" s="260">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>6.6472159310281692E-3</v>
       </c>
-      <c r="D27" s="257"/>
-      <c r="F27" s="256">
+      <c r="D27" s="261"/>
+      <c r="F27" s="260">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.16382654634312457</v>
       </c>
-      <c r="G27" s="257"/>
+      <c r="G27" s="261"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
@@ -37962,22 +38103,22 @@
       <c r="B29" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C29" s="256">
+      <c r="C29" s="260">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.15748031496062992</v>
       </c>
-      <c r="D29" s="257"/>
-      <c r="F29" s="256">
+      <c r="D29" s="261"/>
+      <c r="F29" s="260">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>0.46533756230176709</v>
       </c>
-      <c r="G29" s="257"/>
+      <c r="G29" s="261"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B31" s="8" t="s">
@@ -38025,22 +38166,22 @@
       <c r="B33" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C33" s="256">
+      <c r="C33" s="260">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>2.6257619832373135E-2</v>
       </c>
-      <c r="D33" s="257"/>
-      <c r="F33" s="256">
+      <c r="D33" s="261"/>
+      <c r="F33" s="260">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>0.12319376989075922</v>
       </c>
-      <c r="G33" s="257"/>
+      <c r="G33" s="261"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B34" s="20" t="s">
@@ -38067,22 +38208,22 @@
       <c r="B35" s="227" t="s">
         <v>367</v>
       </c>
-      <c r="C35" s="256">
+      <c r="C35" s="260">
         <f>IF(C34=0,
 IF(D34=0,0,IF(D34&gt;0,1,-1)),
 (D34-C34)/ABS(C34)
 )</f>
         <v>2.3001949317738791E-2</v>
       </c>
-      <c r="D35" s="257"/>
-      <c r="F35" s="256">
+      <c r="D35" s="261"/>
+      <c r="F35" s="260">
         <f>IF(F34=0,
 IF(G34=0,0,IF(G34&gt;0,1,-1)),
 (G34-F34)/ABS(F34)
 )</f>
         <v>0.10951374207188161</v>
       </c>
-      <c r="G35" s="257"/>
+      <c r="G35" s="261"/>
     </row>
   </sheetData>
   <mergeCells count="28">
